--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FE91FB-8A30-40FF-AE5B-D9E0779D0B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381529B7-7DD5-4C42-AA18-290F70592C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Rechazos Calle" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$551</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$632</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4707" uniqueCount="1608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5403" uniqueCount="1818">
   <si>
     <t>Fecha</t>
   </si>
@@ -4871,6 +4871,636 @@
   </si>
   <si>
     <t>MPMSMHSSKO3D</t>
+  </si>
+  <si>
+    <t>MPMTUIB9GBCV</t>
+  </si>
+  <si>
+    <t>01:06 p. m.</t>
+  </si>
+  <si>
+    <t>Faltan los Doritos de 20grs</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779811583/xnsibpofbxhfofiucne5.jpg</t>
+  </si>
+  <si>
+    <t>MPMU30EM2CKA</t>
+  </si>
+  <si>
+    <t>Precio</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779811971/rk7c9c1hsqgor2o3q1bi.jpg</t>
+  </si>
+  <si>
+    <t>MPMU4HD2XX3N</t>
+  </si>
+  <si>
+    <t>Falto lays 40g y dorito dinamita 45g</t>
+  </si>
+  <si>
+    <t>MPMU72CXARJV</t>
+  </si>
+  <si>
+    <t>01:16 p. m.</t>
+  </si>
+  <si>
+    <t>MPMU89KRY9LF</t>
+  </si>
+  <si>
+    <t>01:17 p. m.</t>
+  </si>
+  <si>
+    <t>Rechazo los twistos porque fueron mal</t>
+  </si>
+  <si>
+    <t>MPMUM1TL65JX</t>
+  </si>
+  <si>
+    <t>01:27 p. m.</t>
+  </si>
+  <si>
+    <t>MPMUR0M53P4O</t>
+  </si>
+  <si>
+    <t>01:31 p. m.</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — Mal armado</t>
+  </si>
+  <si>
+    <t>MPMUVODFBK2Y</t>
+  </si>
+  <si>
+    <t>01:35 p. m.</t>
+  </si>
+  <si>
+    <t>MPMV68JTCWIV</t>
+  </si>
+  <si>
+    <t>MPMVDH8ZP2KE</t>
+  </si>
+  <si>
+    <t>01:49 p. m.</t>
+  </si>
+  <si>
+    <t>Sin dinero</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779814148/tcqtfrtnud6uwluph53l.jpg</t>
+  </si>
+  <si>
+    <t>MPMVFUTLKM5K</t>
+  </si>
+  <si>
+    <t>Fuera de ruta</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779814257/zniepbgrh7egm93am4hc.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Pedido fuera de ruta, facturado fuera de tiempo.</t>
+  </si>
+  <si>
+    <t>MPMWD12BZ1WL</t>
+  </si>
+  <si>
+    <t>1 twisto 40g</t>
+  </si>
+  <si>
+    <t>MPMWGL2N0AFZ</t>
+  </si>
+  <si>
+    <t>1yerba rota</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779815972/wjcnv7euhnso9tolomec.jpg</t>
+  </si>
+  <si>
+    <t>MPNYS78S4BBE</t>
+  </si>
+  <si>
+    <t>08:12 a. m.</t>
+  </si>
+  <si>
+    <t>Faltan 2 Doritos x 129 recibe lo otro</t>
+  </si>
+  <si>
+    <t>MPNZKW74GGLY</t>
+  </si>
+  <si>
+    <t>MPNZNJ2X85NH</t>
+  </si>
+  <si>
+    <t>08:36 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779881793/frwynejlrcxuwsrngzya.jpg</t>
+  </si>
+  <si>
+    <t>MPNZPLRE8561</t>
+  </si>
+  <si>
+    <t>Big naranja y durazno y todo alfajor</t>
+  </si>
+  <si>
+    <t>MPO0MR49BD7G</t>
+  </si>
+  <si>
+    <t>MPO18O65WG5B</t>
+  </si>
+  <si>
+    <t>No trabaja ese gramaje</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779884461/rnv6iddsc7z1qerlcnfp.jpg</t>
+  </si>
+  <si>
+    <t>MPO1U2YNRYI7</t>
+  </si>
+  <si>
+    <t>MPO2GLO954Q5</t>
+  </si>
+  <si>
+    <t>09:55 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779886509/zx9z0lmm90wdxejeivlh.jpg</t>
+  </si>
+  <si>
+    <t>MPO2L5ZR69DW</t>
+  </si>
+  <si>
+    <t>No trabaja esos gramaje</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779886722/svfppcy831xb4u3bi3wi.jpg</t>
+  </si>
+  <si>
+    <t>MPO2WVDHATK8</t>
+  </si>
+  <si>
+    <t>Está abierto pero la puerta cerrada hace 15 min estoy esperando</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779887269/ukxpfcsvtqa1oe7wluu1.jpg</t>
+  </si>
+  <si>
+    <t>MPO359O3F9DN</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779887658/e2v5l49c6mmsxlveagzj.jpg</t>
+  </si>
+  <si>
+    <t>MPO453CVNH8Z</t>
+  </si>
+  <si>
+    <t>Faltó 1 lays clásica 85gr y 2 lays queso y cebolla 77gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779889334/edczstnkkqndrsap0wbl.jpg</t>
+  </si>
+  <si>
+    <t>MPO48FSD8LY9</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779889490/yqp4czbhd6haodfexuyr.jpg</t>
+  </si>
+  <si>
+    <t>MPO4L6ZBWEWI</t>
+  </si>
+  <si>
+    <t>MPO4POXI23GF</t>
+  </si>
+  <si>
+    <t>10:58 a. m.</t>
+  </si>
+  <si>
+    <t>3 sales rotas</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779890288/cdrvbduk0b5i3duzgdb0.jpg</t>
+  </si>
+  <si>
+    <t>MPO536EO8JOD</t>
+  </si>
+  <si>
+    <t>MPO5GLC9ILC5</t>
+  </si>
+  <si>
+    <t>Faltó 4 lays clásicas 20gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779891570/nojeqoubq7d7i8velrtd.jpg</t>
+  </si>
+  <si>
+    <t>MPO5JF7IS472</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779891677/tzooe41f0bl6f7obwuxz.jpg</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — Cerrado?? Abre muy temprano porque vende desayuno. Raro que este cerrado.</t>
+  </si>
+  <si>
+    <t>MPO5MICF7ERE</t>
+  </si>
+  <si>
+    <t>Rechaza 6 biscochuelo exicsita de coco lo otro recibe</t>
+  </si>
+  <si>
+    <t>MPO5UPTLDHE8</t>
+  </si>
+  <si>
+    <t>11:30 a. m.</t>
+  </si>
+  <si>
+    <t>1sal rota</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779892210/gzslm76yhgu6ckjfuybw.jpg</t>
+  </si>
+  <si>
+    <t>MPO5WWKK7EN4</t>
+  </si>
+  <si>
+    <t>Oh higienol código 1553 se descuenta sin stock</t>
+  </si>
+  <si>
+    <t>MPO62UU8TCY2</t>
+  </si>
+  <si>
+    <t>MPO6H3LHYB9O</t>
+  </si>
+  <si>
+    <t>11:47 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779893253/fi1j3xk4dy30wwhiiall.jpg</t>
+  </si>
+  <si>
+    <t>El cliente va a recibir — seguí viaje — Abre como a la 12 y 30</t>
+  </si>
+  <si>
+    <t>MPO6XOCH509O</t>
+  </si>
+  <si>
+    <t>4 rebozador</t>
+  </si>
+  <si>
+    <t>MPO75NJZ2T7G</t>
+  </si>
+  <si>
+    <t>12:06 p. m.</t>
+  </si>
+  <si>
+    <t>No está la persona encargada</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779894395/vwibjkrfudwqnvvystki.jpg</t>
+  </si>
+  <si>
+    <t>MPO7KD6EABL1</t>
+  </si>
+  <si>
+    <t>12:18 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779895092/fj8jvrrgh2sfxknjxs6g.jpg</t>
+  </si>
+  <si>
+    <t>MPO7S0M2B6Q3</t>
+  </si>
+  <si>
+    <t>Soaguetti sin stock</t>
+  </si>
+  <si>
+    <t>MPO7UK1IG1BI</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779895557/nf9u0pvlgctovyhfenev.jpg</t>
+  </si>
+  <si>
+    <t>MPO7YM1MXICG</t>
+  </si>
+  <si>
+    <t>MPO896M0MB45</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779896246/ddpdctxv5mymwkq12txo.jpg</t>
+  </si>
+  <si>
+    <t>MPO8G9H6GA4Z</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779896569/on4oqojrxtq85nxd064x.jpg</t>
+  </si>
+  <si>
+    <t>MPO8G9VNV90V</t>
+  </si>
+  <si>
+    <t>Falto 2 chetos de 85g</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779896572/ulamn4d1migwkyjri2hc.jpg</t>
+  </si>
+  <si>
+    <t>MPO8HG9TQHZH</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779896639/vy0dtbfwcpuhzeezf073.jpg</t>
+  </si>
+  <si>
+    <t>MPO8M8B4RX66</t>
+  </si>
+  <si>
+    <t>12:47 p. m.</t>
+  </si>
+  <si>
+    <t>Faltó 1 bizcocho salado</t>
+  </si>
+  <si>
+    <t>MPO8MK155GOT</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779896865/cqazv1ydp8ymxqsu1ibj.jpg</t>
+  </si>
+  <si>
+    <t>MPO8SAMWFO7X</t>
+  </si>
+  <si>
+    <t>S stock mousse triple</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779897143/wwtysmp862oruxtdpawv.jpg</t>
+  </si>
+  <si>
+    <t>MPO8XRT0UZOH</t>
+  </si>
+  <si>
+    <t>MPO99FFB252E</t>
+  </si>
+  <si>
+    <t>01:05 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779897937/toodvp60icmemmfwtvxy.jpg</t>
+  </si>
+  <si>
+    <t>MPO9ZE1ECJA7</t>
+  </si>
+  <si>
+    <t>01:25 p. m.</t>
+  </si>
+  <si>
+    <t>Faltó lo marcado</t>
+  </si>
+  <si>
+    <t>MPOA7WNRRG01</t>
+  </si>
+  <si>
+    <t>01:32 p. m.</t>
+  </si>
+  <si>
+    <t>Faltan Cheetos x 85 grs</t>
+  </si>
+  <si>
+    <t>MPOALGKXGCCQ</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779900175/bade25pgxixmo9gluho2.jpg</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — Adrian le erre de cliente, ese cliente no es mío,, nunca le vendí,, ya me fijo de quien es ese pedido</t>
+  </si>
+  <si>
+    <t>MPOAQBU4XVZU</t>
+  </si>
+  <si>
+    <t>Mal fact chocolatada, se vende por 18unid no por 12</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779900399/bxmpyr46oigtfs1vlutr.jpg</t>
+  </si>
+  <si>
+    <t>MPOB8V5GLYX6</t>
+  </si>
+  <si>
+    <t>Cargaron de 40g</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779901336/kbsnrixbhoqt4ebraqvj.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Pedido mal armado.</t>
+  </si>
+  <si>
+    <t>MPOBK8H2QQP9</t>
+  </si>
+  <si>
+    <t>Rechazo los 3d de 45 grs cambiados</t>
+  </si>
+  <si>
+    <t>MPOBOO83TY1C</t>
+  </si>
+  <si>
+    <t>02:14 p. m.</t>
+  </si>
+  <si>
+    <t>Rechazo porque en la boleta dice contra entrega revisar eso por favor</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779902021/moyqvy3cpxs2ikyeph7x.jpg</t>
+  </si>
+  <si>
+    <t>MPOC3EQ29GXJ</t>
+  </si>
+  <si>
+    <t>MPOCCEZ4VH4I</t>
+  </si>
+  <si>
+    <t>Faltan Doritos de 77</t>
+  </si>
+  <si>
+    <t>MPOCDHMM0Z35</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779903154/edyj11guj1hhjoegzmhs.jpg</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — No tiene dinero</t>
+  </si>
+  <si>
+    <t>MPOCCIQDJVTQ</t>
+  </si>
+  <si>
+    <t>MPOCUG3F5MOR</t>
+  </si>
+  <si>
+    <t>02:46 p. m.</t>
+  </si>
+  <si>
+    <t>No avisaron el cambio de dirección</t>
+  </si>
+  <si>
+    <t>MPOCVMI09R6X</t>
+  </si>
+  <si>
+    <t>MPOD2IM3J9NO</t>
+  </si>
+  <si>
+    <t>02:52 p. m.</t>
+  </si>
+  <si>
+    <t>Falto 1 avena tradicional</t>
+  </si>
+  <si>
+    <t>MPOD3LDMHD8C</t>
+  </si>
+  <si>
+    <t>02:53 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779904363/rfnnhob5ziadblf6wphc.jpg</t>
+  </si>
+  <si>
+    <t>MPOD4B98CPCJ</t>
+  </si>
+  <si>
+    <t>Faltaron las avenas instantaneas de 500 mandaron traficional 280</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779904400/lfnds7fxvj0xwdlurw1e.jpg</t>
+  </si>
+  <si>
+    <t>MPOD5XEVR2XO</t>
+  </si>
+  <si>
+    <t>02:54 p. m.</t>
+  </si>
+  <si>
+    <t>MPODE1QJ1IIV</t>
+  </si>
+  <si>
+    <t>Mono don Vicente roto</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779904866/adngx1a8nysifdjdwhqo.jpg</t>
+  </si>
+  <si>
+    <t>MPODVU1G7EXS</t>
+  </si>
+  <si>
+    <t>03:16 p. m.</t>
+  </si>
+  <si>
+    <t>Nido fetuccini roto</t>
+  </si>
+  <si>
+    <t>MPOEMVD4T895</t>
+  </si>
+  <si>
+    <t>03:36 p. m.</t>
+  </si>
+  <si>
+    <t>Hizo este pedido por la aplicación y le marca que iba a llegar el 02/06</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779906954/nl0ibunzgjc6r1e4mfud.jpg</t>
+  </si>
+  <si>
+    <t>MPOFCPFNFTSB</t>
+  </si>
+  <si>
+    <t>03:56 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779908170/fihoepdct9svrqt3jr4r.jpg</t>
+  </si>
+  <si>
+    <t>MPOFW9CNJ5OD</t>
+  </si>
+  <si>
+    <t>04:11 p. m.</t>
+  </si>
+  <si>
+    <t>MPOIYJIO1IRU</t>
+  </si>
+  <si>
+    <t>05:37 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779914242/bamaavoj2r737jdvb8ff.jpg</t>
+  </si>
+  <si>
+    <t>MPOJ7O4X7AO7</t>
+  </si>
+  <si>
+    <t>05:44 p. m.</t>
+  </si>
+  <si>
+    <t>De lo marcado</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779914657/jqbdyjtaszg79c2ctfuw.jpg</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — A ese cliente se le hizo pedido el martes para el miércoles.</t>
+  </si>
+  <si>
+    <t>MPOJBKJU9XPB</t>
+  </si>
+  <si>
+    <t>05:49 p. m.</t>
+  </si>
+  <si>
+    <t>Faltaban 3d de 85</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779914861/cxdrwf4fa8b1vo11mins.jpg</t>
+  </si>
+  <si>
+    <t>MPPEQVPXR3OI</t>
+  </si>
+  <si>
+    <t>08:27 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779967608/z2aokqvaamzvcazqit5i.jpg</t>
+  </si>
+  <si>
+    <t>MPPF0H2LJYTQ</t>
+  </si>
+  <si>
+    <t>Se descuentan 20 don Vicente caserito sin stock</t>
+  </si>
+  <si>
+    <t>MPPF8AY6MXMV</t>
+  </si>
+  <si>
+    <t>Faltaron 4 tostitos de 260g</t>
+  </si>
+  <si>
+    <t>MPPFCSXC4HE0</t>
+  </si>
+  <si>
+    <t>08:44 a. m.</t>
+  </si>
+  <si>
+    <t>Pan rallado</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779968641/rebs2ttdvtgk5smgofmw.jpg</t>
+  </si>
+  <si>
+    <t>MPPFXPXKXHQ3</t>
+  </si>
+  <si>
+    <t>Repetido el pedido</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1779969610/rpr58ezp6jyv1iwkobzv.jpg</t>
   </si>
 </sst>
 </file>
@@ -5042,11 +5672,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:M551">
-  <autoFilter ref="A1:M551" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M1">
-    <sortCondition ref="B1"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:M632">
+  <autoFilter ref="A1:M632" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fecha"/>
@@ -5267,10 +5894,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M551"/>
+  <dimension ref="A1:M632"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" customWidth="1"/>
     <col min="5" max="5" width="31.140625" customWidth="1"/>
@@ -25764,12 +26391,3009 @@
         <v>1098</v>
       </c>
     </row>
+    <row r="552" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A552" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B552" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C552" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D552" t="s">
+        <v>97</v>
+      </c>
+      <c r="E552" t="s">
+        <v>10</v>
+      </c>
+      <c r="F552">
+        <v>6987</v>
+      </c>
+      <c r="G552" t="s">
+        <v>133</v>
+      </c>
+      <c r="H552" t="s">
+        <v>119</v>
+      </c>
+      <c r="I552" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J552" t="s">
+        <v>1611</v>
+      </c>
+      <c r="K552" t="s">
+        <v>110</v>
+      </c>
+      <c r="L552" s="3">
+        <v>46168</v>
+      </c>
+      <c r="M552" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="553" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A553" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B553" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C553" s="4">
+        <v>0.55069444444444449</v>
+      </c>
+      <c r="D553" t="s">
+        <v>97</v>
+      </c>
+      <c r="E553" t="s">
+        <v>11</v>
+      </c>
+      <c r="F553">
+        <v>10980</v>
+      </c>
+      <c r="G553" t="s">
+        <v>132</v>
+      </c>
+      <c r="H553" t="s">
+        <v>100</v>
+      </c>
+      <c r="I553" t="s">
+        <v>1613</v>
+      </c>
+      <c r="J553" t="s">
+        <v>1614</v>
+      </c>
+      <c r="K553" t="s">
+        <v>122</v>
+      </c>
+      <c r="L553" s="3">
+        <v>46168</v>
+      </c>
+      <c r="M553" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="554" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A554" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B554" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C554" s="4">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="D554" t="s">
+        <v>97</v>
+      </c>
+      <c r="E554" t="s">
+        <v>11</v>
+      </c>
+      <c r="F554">
+        <v>5560</v>
+      </c>
+      <c r="G554" t="s">
+        <v>132</v>
+      </c>
+      <c r="H554" t="s">
+        <v>119</v>
+      </c>
+      <c r="I554" t="s">
+        <v>1616</v>
+      </c>
+      <c r="K554" t="s">
+        <v>127</v>
+      </c>
+      <c r="L554" s="3">
+        <v>46168</v>
+      </c>
+      <c r="M554" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="555" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A555" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B555" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C555" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D555" t="s">
+        <v>97</v>
+      </c>
+      <c r="E555" t="s">
+        <v>17</v>
+      </c>
+      <c r="F555">
+        <v>10898</v>
+      </c>
+      <c r="G555" t="s">
+        <v>129</v>
+      </c>
+      <c r="H555" t="s">
+        <v>105</v>
+      </c>
+      <c r="K555" t="s">
+        <v>122</v>
+      </c>
+      <c r="L555" s="3">
+        <v>46168</v>
+      </c>
+      <c r="M555" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="556" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A556" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B556" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C556" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D556" t="s">
+        <v>97</v>
+      </c>
+      <c r="E556" t="s">
+        <v>17</v>
+      </c>
+      <c r="F556">
+        <v>3202</v>
+      </c>
+      <c r="G556" t="s">
+        <v>129</v>
+      </c>
+      <c r="H556" t="s">
+        <v>119</v>
+      </c>
+      <c r="I556" t="s">
+        <v>1621</v>
+      </c>
+      <c r="K556" t="s">
+        <v>122</v>
+      </c>
+      <c r="L556" s="3">
+        <v>46168</v>
+      </c>
+      <c r="M556" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="557" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A557" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B557" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C557" t="s">
+        <v>1623</v>
+      </c>
+      <c r="D557" t="s">
+        <v>97</v>
+      </c>
+      <c r="E557" t="s">
+        <v>17</v>
+      </c>
+      <c r="F557">
+        <v>3238</v>
+      </c>
+      <c r="G557" t="s">
+        <v>129</v>
+      </c>
+      <c r="H557" t="s">
+        <v>98</v>
+      </c>
+      <c r="K557" t="s">
+        <v>122</v>
+      </c>
+      <c r="L557" s="3">
+        <v>46168</v>
+      </c>
+      <c r="M557" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="558" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A558" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B558" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C558" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D558" t="s">
+        <v>97</v>
+      </c>
+      <c r="E558" t="s">
+        <v>24</v>
+      </c>
+      <c r="F558">
+        <v>6449</v>
+      </c>
+      <c r="G558" t="s">
+        <v>114</v>
+      </c>
+      <c r="H558" t="s">
+        <v>119</v>
+      </c>
+      <c r="K558" t="s">
+        <v>1626</v>
+      </c>
+      <c r="L558" s="3">
+        <v>46168</v>
+      </c>
+      <c r="M558" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="559" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A559" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B559" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C559" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D559" t="s">
+        <v>97</v>
+      </c>
+      <c r="E559" t="s">
+        <v>14</v>
+      </c>
+      <c r="F559">
+        <v>5866</v>
+      </c>
+      <c r="G559" t="s">
+        <v>103</v>
+      </c>
+      <c r="H559" t="s">
+        <v>98</v>
+      </c>
+      <c r="K559" t="s">
+        <v>1307</v>
+      </c>
+      <c r="L559" s="3">
+        <v>46168</v>
+      </c>
+      <c r="M559" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="560" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A560" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B560" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C560" t="s">
+        <v>667</v>
+      </c>
+      <c r="D560" t="s">
+        <v>97</v>
+      </c>
+      <c r="E560" t="s">
+        <v>19</v>
+      </c>
+      <c r="F560">
+        <v>8343</v>
+      </c>
+      <c r="G560" t="s">
+        <v>128</v>
+      </c>
+      <c r="H560" t="s">
+        <v>98</v>
+      </c>
+      <c r="K560" t="s">
+        <v>122</v>
+      </c>
+      <c r="L560" s="3">
+        <v>46168</v>
+      </c>
+      <c r="M560" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="561" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A561" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B561" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C561" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D561" t="s">
+        <v>97</v>
+      </c>
+      <c r="E561" t="s">
+        <v>10</v>
+      </c>
+      <c r="F561">
+        <v>6998</v>
+      </c>
+      <c r="G561" t="s">
+        <v>133</v>
+      </c>
+      <c r="H561" t="s">
+        <v>98</v>
+      </c>
+      <c r="I561" t="s">
+        <v>1632</v>
+      </c>
+      <c r="J561" t="s">
+        <v>1633</v>
+      </c>
+      <c r="K561" t="s">
+        <v>122</v>
+      </c>
+      <c r="L561" s="3">
+        <v>46168</v>
+      </c>
+      <c r="M561" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="562" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A562" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B562" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C562" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D562" t="s">
+        <v>97</v>
+      </c>
+      <c r="E562" t="s">
+        <v>10</v>
+      </c>
+      <c r="F562">
+        <v>6979</v>
+      </c>
+      <c r="G562" t="s">
+        <v>121</v>
+      </c>
+      <c r="H562" t="s">
+        <v>130</v>
+      </c>
+      <c r="I562" t="s">
+        <v>1635</v>
+      </c>
+      <c r="J562" t="s">
+        <v>1636</v>
+      </c>
+      <c r="K562" t="s">
+        <v>1637</v>
+      </c>
+      <c r="L562" s="3">
+        <v>46168</v>
+      </c>
+      <c r="M562" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="563" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A563" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B563" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C563" s="4">
+        <v>0.59513888888888888</v>
+      </c>
+      <c r="D563" t="s">
+        <v>97</v>
+      </c>
+      <c r="E563" t="s">
+        <v>11</v>
+      </c>
+      <c r="F563">
+        <v>4929</v>
+      </c>
+      <c r="G563" t="s">
+        <v>113</v>
+      </c>
+      <c r="H563" t="s">
+        <v>119</v>
+      </c>
+      <c r="I563" t="s">
+        <v>1639</v>
+      </c>
+      <c r="M563" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="564" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A564" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B564" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C564" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D564" t="s">
+        <v>97</v>
+      </c>
+      <c r="E564" t="s">
+        <v>15</v>
+      </c>
+      <c r="F564">
+        <v>3975</v>
+      </c>
+      <c r="G564" t="s">
+        <v>99</v>
+      </c>
+      <c r="H564" t="s">
+        <v>12</v>
+      </c>
+      <c r="I564" t="s">
+        <v>1641</v>
+      </c>
+      <c r="J564" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K564" t="s">
+        <v>127</v>
+      </c>
+      <c r="L564" s="3">
+        <v>46168</v>
+      </c>
+      <c r="M564" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="565" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A565" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B565" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C565" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D565" t="s">
+        <v>97</v>
+      </c>
+      <c r="E565" t="s">
+        <v>22</v>
+      </c>
+      <c r="F565">
+        <v>10701</v>
+      </c>
+      <c r="G565" t="s">
+        <v>125</v>
+      </c>
+      <c r="H565" t="s">
+        <v>119</v>
+      </c>
+      <c r="I565" t="s">
+        <v>1645</v>
+      </c>
+      <c r="K565" t="s">
+        <v>126</v>
+      </c>
+      <c r="L565" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M565" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="566" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A566" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B566" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C566" s="4">
+        <v>0.35694444444444445</v>
+      </c>
+      <c r="D566" t="s">
+        <v>97</v>
+      </c>
+      <c r="E566" t="s">
+        <v>23</v>
+      </c>
+      <c r="F566">
+        <v>6218</v>
+      </c>
+      <c r="G566" t="s">
+        <v>114</v>
+      </c>
+      <c r="H566" t="s">
+        <v>101</v>
+      </c>
+      <c r="M566" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="567" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A567" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B567" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C567" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D567" t="s">
+        <v>97</v>
+      </c>
+      <c r="E567" t="s">
+        <v>15</v>
+      </c>
+      <c r="F567">
+        <v>6258</v>
+      </c>
+      <c r="G567" t="s">
+        <v>114</v>
+      </c>
+      <c r="H567" t="s">
+        <v>12</v>
+      </c>
+      <c r="J567" t="s">
+        <v>1649</v>
+      </c>
+      <c r="K567" t="s">
+        <v>126</v>
+      </c>
+      <c r="L567" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M567" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="568" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A568" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B568" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C568" s="4">
+        <v>0.36041666666666666</v>
+      </c>
+      <c r="D568" t="s">
+        <v>97</v>
+      </c>
+      <c r="E568" t="s">
+        <v>23</v>
+      </c>
+      <c r="F568">
+        <v>5929</v>
+      </c>
+      <c r="G568" t="s">
+        <v>114</v>
+      </c>
+      <c r="H568" t="s">
+        <v>12</v>
+      </c>
+      <c r="I568" t="s">
+        <v>1651</v>
+      </c>
+      <c r="M568" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="569" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A569" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B569" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C569" s="4">
+        <v>0.37777777777777777</v>
+      </c>
+      <c r="D569" t="s">
+        <v>97</v>
+      </c>
+      <c r="E569" t="s">
+        <v>23</v>
+      </c>
+      <c r="F569">
+        <v>6498</v>
+      </c>
+      <c r="G569" t="s">
+        <v>109</v>
+      </c>
+      <c r="H569" t="s">
+        <v>101</v>
+      </c>
+      <c r="M569" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="570" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A570" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B570" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C570" t="s">
+        <v>76</v>
+      </c>
+      <c r="D570" t="s">
+        <v>97</v>
+      </c>
+      <c r="E570" t="s">
+        <v>15</v>
+      </c>
+      <c r="F570">
+        <v>6299</v>
+      </c>
+      <c r="G570" t="s">
+        <v>114</v>
+      </c>
+      <c r="H570" t="s">
+        <v>101</v>
+      </c>
+      <c r="I570" t="s">
+        <v>1654</v>
+      </c>
+      <c r="J570" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K570" t="s">
+        <v>126</v>
+      </c>
+      <c r="L570" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M570" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="571" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A571" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B571" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C571" s="4">
+        <v>0.40069444444444446</v>
+      </c>
+      <c r="D571" t="s">
+        <v>97</v>
+      </c>
+      <c r="E571" t="s">
+        <v>23</v>
+      </c>
+      <c r="F571">
+        <v>3573</v>
+      </c>
+      <c r="G571" t="s">
+        <v>109</v>
+      </c>
+      <c r="H571" t="s">
+        <v>12</v>
+      </c>
+      <c r="K571" t="s">
+        <v>127</v>
+      </c>
+      <c r="L571" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M571" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="572" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A572" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B572" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C572" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D572" t="s">
+        <v>97</v>
+      </c>
+      <c r="E572" t="s">
+        <v>20</v>
+      </c>
+      <c r="F572">
+        <v>4159</v>
+      </c>
+      <c r="G572" t="s">
+        <v>123</v>
+      </c>
+      <c r="H572" t="s">
+        <v>12</v>
+      </c>
+      <c r="I572" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J572" t="s">
+        <v>1659</v>
+      </c>
+      <c r="K572" t="s">
+        <v>126</v>
+      </c>
+      <c r="L572" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M572" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="573" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A573" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B573" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C573" t="s">
+        <v>29</v>
+      </c>
+      <c r="D573" t="s">
+        <v>97</v>
+      </c>
+      <c r="E573" t="s">
+        <v>15</v>
+      </c>
+      <c r="F573">
+        <v>6298</v>
+      </c>
+      <c r="G573" t="s">
+        <v>114</v>
+      </c>
+      <c r="H573" t="s">
+        <v>101</v>
+      </c>
+      <c r="I573" t="s">
+        <v>1661</v>
+      </c>
+      <c r="J573" t="s">
+        <v>1662</v>
+      </c>
+      <c r="K573" t="s">
+        <v>126</v>
+      </c>
+      <c r="L573" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M573" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="574" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A574" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B574" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C574" s="4">
+        <v>0.42222222222222222</v>
+      </c>
+      <c r="D574" t="s">
+        <v>97</v>
+      </c>
+      <c r="E574" t="s">
+        <v>9</v>
+      </c>
+      <c r="F574">
+        <v>5901</v>
+      </c>
+      <c r="G574" t="s">
+        <v>111</v>
+      </c>
+      <c r="H574" t="s">
+        <v>105</v>
+      </c>
+      <c r="I574" t="s">
+        <v>1664</v>
+      </c>
+      <c r="J574" t="s">
+        <v>1665</v>
+      </c>
+      <c r="K574" t="s">
+        <v>110</v>
+      </c>
+      <c r="L574" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M574" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="575" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A575" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B575" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C575" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D575" t="s">
+        <v>97</v>
+      </c>
+      <c r="E575" t="s">
+        <v>15</v>
+      </c>
+      <c r="F575">
+        <v>6310</v>
+      </c>
+      <c r="G575" t="s">
+        <v>128</v>
+      </c>
+      <c r="H575" t="s">
+        <v>119</v>
+      </c>
+      <c r="I575" t="s">
+        <v>234</v>
+      </c>
+      <c r="J575" t="s">
+        <v>1667</v>
+      </c>
+      <c r="M575" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="576" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A576" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B576" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C576" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D576" t="s">
+        <v>97</v>
+      </c>
+      <c r="E576" t="s">
+        <v>527</v>
+      </c>
+      <c r="F576">
+        <v>2231</v>
+      </c>
+      <c r="G576" t="s">
+        <v>318</v>
+      </c>
+      <c r="H576" t="s">
+        <v>119</v>
+      </c>
+      <c r="I576" t="s">
+        <v>1669</v>
+      </c>
+      <c r="J576" t="s">
+        <v>1670</v>
+      </c>
+      <c r="K576" t="s">
+        <v>127</v>
+      </c>
+      <c r="L576" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M576" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="577" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A577" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B577" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C577" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D577" t="s">
+        <v>97</v>
+      </c>
+      <c r="E577" t="s">
+        <v>19</v>
+      </c>
+      <c r="F577">
+        <v>3023</v>
+      </c>
+      <c r="G577" t="s">
+        <v>129</v>
+      </c>
+      <c r="H577" t="s">
+        <v>105</v>
+      </c>
+      <c r="J577" t="s">
+        <v>1672</v>
+      </c>
+      <c r="K577" t="s">
+        <v>126</v>
+      </c>
+      <c r="L577" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M577" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="578" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A578" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B578" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C578" s="4">
+        <v>0.45416666666666666</v>
+      </c>
+      <c r="D578" t="s">
+        <v>97</v>
+      </c>
+      <c r="E578" t="s">
+        <v>23</v>
+      </c>
+      <c r="F578">
+        <v>3569</v>
+      </c>
+      <c r="G578" t="s">
+        <v>114</v>
+      </c>
+      <c r="H578" t="s">
+        <v>101</v>
+      </c>
+      <c r="M578" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="579" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A579" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B579" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C579" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D579" t="s">
+        <v>97</v>
+      </c>
+      <c r="E579" t="s">
+        <v>20</v>
+      </c>
+      <c r="F579">
+        <v>4512</v>
+      </c>
+      <c r="G579" t="s">
+        <v>116</v>
+      </c>
+      <c r="H579" t="s">
+        <v>119</v>
+      </c>
+      <c r="I579" t="s">
+        <v>1676</v>
+      </c>
+      <c r="J579" t="s">
+        <v>1677</v>
+      </c>
+      <c r="K579" t="s">
+        <v>122</v>
+      </c>
+      <c r="L579" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M579" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="580" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A580" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B580" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C580" s="4">
+        <v>0.46458333333333335</v>
+      </c>
+      <c r="D580" t="s">
+        <v>97</v>
+      </c>
+      <c r="E580" t="s">
+        <v>23</v>
+      </c>
+      <c r="F580">
+        <v>3574</v>
+      </c>
+      <c r="G580" t="s">
+        <v>132</v>
+      </c>
+      <c r="H580" t="s">
+        <v>119</v>
+      </c>
+      <c r="K580" t="s">
+        <v>127</v>
+      </c>
+      <c r="L580" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M580" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="581" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A581" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B581" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C581" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D581" t="s">
+        <v>97</v>
+      </c>
+      <c r="E581" t="s">
+        <v>527</v>
+      </c>
+      <c r="F581">
+        <v>2067</v>
+      </c>
+      <c r="G581" t="s">
+        <v>318</v>
+      </c>
+      <c r="H581" t="s">
+        <v>119</v>
+      </c>
+      <c r="I581" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J581" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K581" t="s">
+        <v>127</v>
+      </c>
+      <c r="L581" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M581" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="582" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A582" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B582" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C582" t="s">
+        <v>79</v>
+      </c>
+      <c r="D582" t="s">
+        <v>97</v>
+      </c>
+      <c r="E582" t="s">
+        <v>17</v>
+      </c>
+      <c r="F582">
+        <v>7051</v>
+      </c>
+      <c r="G582" t="s">
+        <v>118</v>
+      </c>
+      <c r="H582" t="s">
+        <v>105</v>
+      </c>
+      <c r="J582" t="s">
+        <v>1683</v>
+      </c>
+      <c r="K582" t="s">
+        <v>1684</v>
+      </c>
+      <c r="L582" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M582" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="583" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A583" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B583" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C583" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D583" t="s">
+        <v>97</v>
+      </c>
+      <c r="E583" t="s">
+        <v>22</v>
+      </c>
+      <c r="F583">
+        <v>5385</v>
+      </c>
+      <c r="G583" t="s">
+        <v>128</v>
+      </c>
+      <c r="H583" t="s">
+        <v>119</v>
+      </c>
+      <c r="I583" t="s">
+        <v>1686</v>
+      </c>
+      <c r="K583" t="s">
+        <v>122</v>
+      </c>
+      <c r="L583" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M583" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="584" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A584" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B584" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C584" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D584" t="s">
+        <v>97</v>
+      </c>
+      <c r="E584" t="s">
+        <v>20</v>
+      </c>
+      <c r="F584">
+        <v>4503</v>
+      </c>
+      <c r="G584" t="s">
+        <v>116</v>
+      </c>
+      <c r="H584" t="s">
+        <v>119</v>
+      </c>
+      <c r="I584" t="s">
+        <v>1689</v>
+      </c>
+      <c r="J584" t="s">
+        <v>1690</v>
+      </c>
+      <c r="K584" t="s">
+        <v>122</v>
+      </c>
+      <c r="L584" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M584" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="585" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A585" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B585" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C585" s="4">
+        <v>0.47986111111111113</v>
+      </c>
+      <c r="D585" t="s">
+        <v>97</v>
+      </c>
+      <c r="E585" t="s">
+        <v>9</v>
+      </c>
+      <c r="F585">
+        <v>10852</v>
+      </c>
+      <c r="G585" t="s">
+        <v>108</v>
+      </c>
+      <c r="H585" t="s">
+        <v>12</v>
+      </c>
+      <c r="I585" t="s">
+        <v>1692</v>
+      </c>
+      <c r="K585" t="s">
+        <v>127</v>
+      </c>
+      <c r="L585" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M585" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="586" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A586" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B586" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C586" t="s">
+        <v>813</v>
+      </c>
+      <c r="D586" t="s">
+        <v>97</v>
+      </c>
+      <c r="E586" t="s">
+        <v>723</v>
+      </c>
+      <c r="F586">
+        <v>816</v>
+      </c>
+      <c r="G586" t="s">
+        <v>724</v>
+      </c>
+      <c r="H586" t="s">
+        <v>100</v>
+      </c>
+      <c r="K586" t="s">
+        <v>122</v>
+      </c>
+      <c r="L586" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M586" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="587" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A587" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B587" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C587" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D587" t="s">
+        <v>97</v>
+      </c>
+      <c r="E587" t="s">
+        <v>15</v>
+      </c>
+      <c r="F587">
+        <v>2720</v>
+      </c>
+      <c r="G587" t="s">
+        <v>111</v>
+      </c>
+      <c r="H587" t="s">
+        <v>105</v>
+      </c>
+      <c r="J587" t="s">
+        <v>1696</v>
+      </c>
+      <c r="K587" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L587" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M587" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="588" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A588" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B588" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C588" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D588" t="s">
+        <v>97</v>
+      </c>
+      <c r="E588" t="s">
+        <v>9</v>
+      </c>
+      <c r="F588">
+        <v>6520</v>
+      </c>
+      <c r="G588" t="s">
+        <v>109</v>
+      </c>
+      <c r="H588" t="s">
+        <v>12</v>
+      </c>
+      <c r="I588" t="s">
+        <v>1699</v>
+      </c>
+      <c r="K588" t="s">
+        <v>127</v>
+      </c>
+      <c r="L588" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M588" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="589" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A589" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B589" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C589" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D589" t="s">
+        <v>97</v>
+      </c>
+      <c r="E589" t="s">
+        <v>19</v>
+      </c>
+      <c r="F589">
+        <v>6560</v>
+      </c>
+      <c r="G589" t="s">
+        <v>117</v>
+      </c>
+      <c r="H589" t="s">
+        <v>105</v>
+      </c>
+      <c r="I589" t="s">
+        <v>1702</v>
+      </c>
+      <c r="J589" t="s">
+        <v>1703</v>
+      </c>
+      <c r="K589" t="s">
+        <v>127</v>
+      </c>
+      <c r="L589" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M589" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="590" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A590" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B590" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C590" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D590" t="s">
+        <v>97</v>
+      </c>
+      <c r="E590" t="s">
+        <v>20</v>
+      </c>
+      <c r="F590">
+        <v>4485</v>
+      </c>
+      <c r="G590" t="s">
+        <v>99</v>
+      </c>
+      <c r="H590" t="s">
+        <v>12</v>
+      </c>
+      <c r="J590" t="s">
+        <v>1706</v>
+      </c>
+      <c r="K590" t="s">
+        <v>127</v>
+      </c>
+      <c r="L590" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M590" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="591" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A591" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B591" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C591" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D591" t="s">
+        <v>97</v>
+      </c>
+      <c r="E591" t="s">
+        <v>19</v>
+      </c>
+      <c r="F591">
+        <v>11063</v>
+      </c>
+      <c r="G591" t="s">
+        <v>108</v>
+      </c>
+      <c r="H591" t="s">
+        <v>12</v>
+      </c>
+      <c r="I591" t="s">
+        <v>1708</v>
+      </c>
+      <c r="K591" t="s">
+        <v>127</v>
+      </c>
+      <c r="L591" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M591" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="592" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A592" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B592" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C592" t="s">
+        <v>403</v>
+      </c>
+      <c r="D592" t="s">
+        <v>97</v>
+      </c>
+      <c r="E592" t="s">
+        <v>15</v>
+      </c>
+      <c r="F592">
+        <v>6255</v>
+      </c>
+      <c r="G592" t="s">
+        <v>114</v>
+      </c>
+      <c r="H592" t="s">
+        <v>12</v>
+      </c>
+      <c r="J592" t="s">
+        <v>1710</v>
+      </c>
+      <c r="K592" t="s">
+        <v>1170</v>
+      </c>
+      <c r="L592" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M592" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="593" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A593" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B593" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C593" s="4">
+        <v>0.52013888888888893</v>
+      </c>
+      <c r="D593" t="s">
+        <v>97</v>
+      </c>
+      <c r="E593" t="s">
+        <v>23</v>
+      </c>
+      <c r="F593">
+        <v>3566</v>
+      </c>
+      <c r="G593" t="s">
+        <v>132</v>
+      </c>
+      <c r="H593" t="s">
+        <v>100</v>
+      </c>
+      <c r="M593" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="594" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A594" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B594" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C594" s="4">
+        <v>0.52569444444444446</v>
+      </c>
+      <c r="D594" t="s">
+        <v>97</v>
+      </c>
+      <c r="E594" t="s">
+        <v>11</v>
+      </c>
+      <c r="F594">
+        <v>6273</v>
+      </c>
+      <c r="G594" t="s">
+        <v>114</v>
+      </c>
+      <c r="H594" t="s">
+        <v>119</v>
+      </c>
+      <c r="J594" t="s">
+        <v>1713</v>
+      </c>
+      <c r="K594" t="s">
+        <v>302</v>
+      </c>
+      <c r="L594" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M594" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="595" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A595" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B595" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C595" s="4">
+        <v>0.52916666666666667</v>
+      </c>
+      <c r="D595" t="s">
+        <v>97</v>
+      </c>
+      <c r="E595" t="s">
+        <v>11</v>
+      </c>
+      <c r="F595">
+        <v>5648</v>
+      </c>
+      <c r="G595" t="s">
+        <v>103</v>
+      </c>
+      <c r="H595" t="s">
+        <v>105</v>
+      </c>
+      <c r="J595" t="s">
+        <v>1715</v>
+      </c>
+      <c r="K595" t="s">
+        <v>1307</v>
+      </c>
+      <c r="L595" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M595" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="596" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A596" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B596" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C596" s="4">
+        <v>0.52986111111111112</v>
+      </c>
+      <c r="D596" t="s">
+        <v>97</v>
+      </c>
+      <c r="E596" t="s">
+        <v>9</v>
+      </c>
+      <c r="F596">
+        <v>7355</v>
+      </c>
+      <c r="G596" t="s">
+        <v>106</v>
+      </c>
+      <c r="H596" t="s">
+        <v>119</v>
+      </c>
+      <c r="I596" t="s">
+        <v>1717</v>
+      </c>
+      <c r="J596" t="s">
+        <v>1718</v>
+      </c>
+      <c r="K596" t="s">
+        <v>127</v>
+      </c>
+      <c r="L596" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M596" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="597" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A597" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B597" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C597" s="4">
+        <v>0.53055555555555556</v>
+      </c>
+      <c r="D597" t="s">
+        <v>97</v>
+      </c>
+      <c r="E597" t="s">
+        <v>11</v>
+      </c>
+      <c r="F597">
+        <v>6274</v>
+      </c>
+      <c r="G597" t="s">
+        <v>114</v>
+      </c>
+      <c r="H597" t="s">
+        <v>98</v>
+      </c>
+      <c r="J597" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K597" t="s">
+        <v>363</v>
+      </c>
+      <c r="L597" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M597" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="598" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A598" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B598" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C598" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D598" t="s">
+        <v>97</v>
+      </c>
+      <c r="E598" t="s">
+        <v>20</v>
+      </c>
+      <c r="F598">
+        <v>5028</v>
+      </c>
+      <c r="G598" t="s">
+        <v>124</v>
+      </c>
+      <c r="H598" t="s">
+        <v>119</v>
+      </c>
+      <c r="I598" t="s">
+        <v>1723</v>
+      </c>
+      <c r="K598" t="s">
+        <v>122</v>
+      </c>
+      <c r="L598" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M598" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="599" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A599" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B599" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C599" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D599" t="s">
+        <v>97</v>
+      </c>
+      <c r="E599" t="s">
+        <v>16</v>
+      </c>
+      <c r="F599">
+        <v>5369</v>
+      </c>
+      <c r="G599" t="s">
+        <v>132</v>
+      </c>
+      <c r="H599" t="s">
+        <v>98</v>
+      </c>
+      <c r="J599" t="s">
+        <v>1725</v>
+      </c>
+      <c r="K599" t="s">
+        <v>110</v>
+      </c>
+      <c r="L599" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M599" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="600" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A600" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B600" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C600" t="s">
+        <v>508</v>
+      </c>
+      <c r="D600" t="s">
+        <v>97</v>
+      </c>
+      <c r="E600" t="s">
+        <v>20</v>
+      </c>
+      <c r="F600">
+        <v>5051</v>
+      </c>
+      <c r="G600" t="s">
+        <v>124</v>
+      </c>
+      <c r="H600" t="s">
+        <v>12</v>
+      </c>
+      <c r="I600" t="s">
+        <v>1727</v>
+      </c>
+      <c r="J600" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K600" t="s">
+        <v>122</v>
+      </c>
+      <c r="L600" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M600" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="601" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A601" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B601" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C601" s="4">
+        <v>0.53888888888888886</v>
+      </c>
+      <c r="D601" t="s">
+        <v>97</v>
+      </c>
+      <c r="E601" t="s">
+        <v>23</v>
+      </c>
+      <c r="F601">
+        <v>5003</v>
+      </c>
+      <c r="G601" t="s">
+        <v>109</v>
+      </c>
+      <c r="H601" t="s">
+        <v>119</v>
+      </c>
+      <c r="K601" t="s">
+        <v>127</v>
+      </c>
+      <c r="L601" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M601" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="602" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A602" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B602" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C602" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D602" t="s">
+        <v>97</v>
+      </c>
+      <c r="E602" t="s">
+        <v>17</v>
+      </c>
+      <c r="F602">
+        <v>3127</v>
+      </c>
+      <c r="G602" t="s">
+        <v>129</v>
+      </c>
+      <c r="H602" t="s">
+        <v>101</v>
+      </c>
+      <c r="J602" t="s">
+        <v>1732</v>
+      </c>
+      <c r="K602" t="s">
+        <v>110</v>
+      </c>
+      <c r="L602" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M602" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="603" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A603" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B603" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C603" t="s">
+        <v>1734</v>
+      </c>
+      <c r="D603" t="s">
+        <v>97</v>
+      </c>
+      <c r="E603" t="s">
+        <v>20</v>
+      </c>
+      <c r="F603">
+        <v>4496</v>
+      </c>
+      <c r="G603" t="s">
+        <v>116</v>
+      </c>
+      <c r="H603" t="s">
+        <v>119</v>
+      </c>
+      <c r="I603" t="s">
+        <v>1735</v>
+      </c>
+      <c r="K603" t="s">
+        <v>122</v>
+      </c>
+      <c r="L603" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M603" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="604" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A604" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B604" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C604" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D604" t="s">
+        <v>97</v>
+      </c>
+      <c r="E604" t="s">
+        <v>17</v>
+      </c>
+      <c r="F604">
+        <v>4416</v>
+      </c>
+      <c r="G604" t="s">
+        <v>113</v>
+      </c>
+      <c r="H604" t="s">
+        <v>119</v>
+      </c>
+      <c r="I604" t="s">
+        <v>1738</v>
+      </c>
+      <c r="K604" t="s">
+        <v>127</v>
+      </c>
+      <c r="L604" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M604" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="605" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A605" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B605" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C605" s="4">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="D605" t="s">
+        <v>97</v>
+      </c>
+      <c r="E605" t="s">
+        <v>11</v>
+      </c>
+      <c r="F605">
+        <v>10289</v>
+      </c>
+      <c r="G605" t="s">
+        <v>99</v>
+      </c>
+      <c r="H605" t="s">
+        <v>130</v>
+      </c>
+      <c r="J605" t="s">
+        <v>1740</v>
+      </c>
+      <c r="K605" t="s">
+        <v>1741</v>
+      </c>
+      <c r="L605" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M605" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="606" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A606" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B606" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C606" t="s">
+        <v>39</v>
+      </c>
+      <c r="D606" t="s">
+        <v>97</v>
+      </c>
+      <c r="E606" t="s">
+        <v>20</v>
+      </c>
+      <c r="F606">
+        <v>2259</v>
+      </c>
+      <c r="G606" t="s">
+        <v>123</v>
+      </c>
+      <c r="H606" t="s">
+        <v>119</v>
+      </c>
+      <c r="I606" t="s">
+        <v>1743</v>
+      </c>
+      <c r="J606" t="s">
+        <v>1744</v>
+      </c>
+      <c r="K606" t="s">
+        <v>126</v>
+      </c>
+      <c r="L606" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M606" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="607" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A607" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B607" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C607" s="4">
+        <v>0.58472222222222225</v>
+      </c>
+      <c r="D607" t="s">
+        <v>97</v>
+      </c>
+      <c r="E607" t="s">
+        <v>11</v>
+      </c>
+      <c r="F607">
+        <v>5943</v>
+      </c>
+      <c r="G607" t="s">
+        <v>121</v>
+      </c>
+      <c r="H607" t="s">
+        <v>119</v>
+      </c>
+      <c r="I607" t="s">
+        <v>1746</v>
+      </c>
+      <c r="J607" t="s">
+        <v>1747</v>
+      </c>
+      <c r="K607" t="s">
+        <v>1748</v>
+      </c>
+      <c r="L607" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M607" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="608" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A608" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B608" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C608" t="s">
+        <v>83</v>
+      </c>
+      <c r="D608" t="s">
+        <v>97</v>
+      </c>
+      <c r="E608" t="s">
+        <v>17</v>
+      </c>
+      <c r="F608">
+        <v>4731</v>
+      </c>
+      <c r="G608" t="s">
+        <v>113</v>
+      </c>
+      <c r="H608" t="s">
+        <v>119</v>
+      </c>
+      <c r="I608" t="s">
+        <v>1750</v>
+      </c>
+      <c r="M608" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="609" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A609" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B609" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C609" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D609" t="s">
+        <v>97</v>
+      </c>
+      <c r="E609" t="s">
+        <v>17</v>
+      </c>
+      <c r="F609">
+        <v>4723</v>
+      </c>
+      <c r="G609" t="s">
+        <v>113</v>
+      </c>
+      <c r="H609" t="s">
+        <v>100</v>
+      </c>
+      <c r="I609" t="s">
+        <v>1753</v>
+      </c>
+      <c r="J609" t="s">
+        <v>1754</v>
+      </c>
+      <c r="M609" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="610" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A610" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B610" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C610" s="4">
+        <v>0.60069444444444442</v>
+      </c>
+      <c r="D610" t="s">
+        <v>97</v>
+      </c>
+      <c r="E610" t="s">
+        <v>23</v>
+      </c>
+      <c r="F610">
+        <v>5298</v>
+      </c>
+      <c r="G610" t="s">
+        <v>132</v>
+      </c>
+      <c r="H610" t="s">
+        <v>119</v>
+      </c>
+      <c r="K610" t="s">
+        <v>127</v>
+      </c>
+      <c r="L610" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M610" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="611" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A611" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B611" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C611" t="s">
+        <v>946</v>
+      </c>
+      <c r="D611" t="s">
+        <v>97</v>
+      </c>
+      <c r="E611" t="s">
+        <v>19</v>
+      </c>
+      <c r="F611">
+        <v>6573</v>
+      </c>
+      <c r="G611" t="s">
+        <v>106</v>
+      </c>
+      <c r="H611" t="s">
+        <v>119</v>
+      </c>
+      <c r="I611" t="s">
+        <v>1757</v>
+      </c>
+      <c r="K611" t="s">
+        <v>127</v>
+      </c>
+      <c r="L611" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M611" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="612" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A612" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B612" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C612" t="s">
+        <v>946</v>
+      </c>
+      <c r="D612" t="s">
+        <v>97</v>
+      </c>
+      <c r="E612" t="s">
+        <v>16</v>
+      </c>
+      <c r="F612">
+        <v>3894</v>
+      </c>
+      <c r="G612" t="s">
+        <v>134</v>
+      </c>
+      <c r="H612" t="s">
+        <v>98</v>
+      </c>
+      <c r="J612" t="s">
+        <v>1759</v>
+      </c>
+      <c r="K612" t="s">
+        <v>1760</v>
+      </c>
+      <c r="L612" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M612" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="613" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A613" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B613" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C613" s="4">
+        <v>0.60624999999999996</v>
+      </c>
+      <c r="D613" t="s">
+        <v>97</v>
+      </c>
+      <c r="E613" t="s">
+        <v>11</v>
+      </c>
+      <c r="F613">
+        <v>6256</v>
+      </c>
+      <c r="G613" t="s">
+        <v>114</v>
+      </c>
+      <c r="H613" t="s">
+        <v>119</v>
+      </c>
+      <c r="K613" t="s">
+        <v>302</v>
+      </c>
+      <c r="L613" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M613" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="614" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A614" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B614" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C614" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D614" t="s">
+        <v>97</v>
+      </c>
+      <c r="E614" t="s">
+        <v>17</v>
+      </c>
+      <c r="F614">
+        <v>4724</v>
+      </c>
+      <c r="G614" t="s">
+        <v>113</v>
+      </c>
+      <c r="H614" t="s">
+        <v>130</v>
+      </c>
+      <c r="I614" t="s">
+        <v>1764</v>
+      </c>
+      <c r="M614" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="615" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A615" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B615" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C615" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D615" t="s">
+        <v>97</v>
+      </c>
+      <c r="E615" t="s">
+        <v>22</v>
+      </c>
+      <c r="F615">
+        <v>3324</v>
+      </c>
+      <c r="G615" t="s">
+        <v>125</v>
+      </c>
+      <c r="H615" t="s">
+        <v>98</v>
+      </c>
+      <c r="K615" t="s">
+        <v>122</v>
+      </c>
+      <c r="L615" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M615" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="616" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A616" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B616" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C616" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D616" t="s">
+        <v>97</v>
+      </c>
+      <c r="E616" t="s">
+        <v>14</v>
+      </c>
+      <c r="F616">
+        <v>5076</v>
+      </c>
+      <c r="G616" t="s">
+        <v>124</v>
+      </c>
+      <c r="H616" t="s">
+        <v>119</v>
+      </c>
+      <c r="I616" t="s">
+        <v>1768</v>
+      </c>
+      <c r="M616" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="617" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A617" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B617" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C617" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D617" t="s">
+        <v>97</v>
+      </c>
+      <c r="E617" t="s">
+        <v>14</v>
+      </c>
+      <c r="F617">
+        <v>3920</v>
+      </c>
+      <c r="G617" t="s">
+        <v>134</v>
+      </c>
+      <c r="H617" t="s">
+        <v>130</v>
+      </c>
+      <c r="J617" t="s">
+        <v>1771</v>
+      </c>
+      <c r="M617" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="618" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A618" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B618" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C618" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D618" t="s">
+        <v>97</v>
+      </c>
+      <c r="E618" t="s">
+        <v>14</v>
+      </c>
+      <c r="F618">
+        <v>4800</v>
+      </c>
+      <c r="G618" t="s">
+        <v>113</v>
+      </c>
+      <c r="H618" t="s">
+        <v>119</v>
+      </c>
+      <c r="I618" t="s">
+        <v>1773</v>
+      </c>
+      <c r="J618" t="s">
+        <v>1774</v>
+      </c>
+      <c r="M618" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="619" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A619" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B619" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C619" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D619" t="s">
+        <v>97</v>
+      </c>
+      <c r="E619" t="s">
+        <v>14</v>
+      </c>
+      <c r="F619">
+        <v>5055</v>
+      </c>
+      <c r="G619" t="s">
+        <v>124</v>
+      </c>
+      <c r="H619" t="s">
+        <v>100</v>
+      </c>
+      <c r="M619" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="620" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A620" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B620" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C620" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D620" t="s">
+        <v>97</v>
+      </c>
+      <c r="E620" t="s">
+        <v>19</v>
+      </c>
+      <c r="F620">
+        <v>6564</v>
+      </c>
+      <c r="G620" t="s">
+        <v>108</v>
+      </c>
+      <c r="H620" t="s">
+        <v>12</v>
+      </c>
+      <c r="I620" t="s">
+        <v>1778</v>
+      </c>
+      <c r="J620" t="s">
+        <v>1779</v>
+      </c>
+      <c r="K620" t="s">
+        <v>110</v>
+      </c>
+      <c r="L620" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M620" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="621" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A621" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B621" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C621" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D621" t="s">
+        <v>97</v>
+      </c>
+      <c r="E621" t="s">
+        <v>19</v>
+      </c>
+      <c r="F621">
+        <v>6548</v>
+      </c>
+      <c r="G621" t="s">
+        <v>108</v>
+      </c>
+      <c r="H621" t="s">
+        <v>12</v>
+      </c>
+      <c r="I621" t="s">
+        <v>1782</v>
+      </c>
+      <c r="K621" t="s">
+        <v>127</v>
+      </c>
+      <c r="L621" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M621" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="622" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A622" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B622" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C622" t="s">
+        <v>1784</v>
+      </c>
+      <c r="D622" t="s">
+        <v>97</v>
+      </c>
+      <c r="E622" t="s">
+        <v>17</v>
+      </c>
+      <c r="F622">
+        <v>6792</v>
+      </c>
+      <c r="G622" t="s">
+        <v>133</v>
+      </c>
+      <c r="H622" t="s">
+        <v>100</v>
+      </c>
+      <c r="I622" t="s">
+        <v>1785</v>
+      </c>
+      <c r="J622" t="s">
+        <v>1786</v>
+      </c>
+      <c r="K622" t="s">
+        <v>122</v>
+      </c>
+      <c r="L622" s="3">
+        <v>46170</v>
+      </c>
+      <c r="M622" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="623" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A623" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B623" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C623" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D623" t="s">
+        <v>97</v>
+      </c>
+      <c r="E623" t="s">
+        <v>24</v>
+      </c>
+      <c r="F623">
+        <v>3841</v>
+      </c>
+      <c r="G623" t="s">
+        <v>116</v>
+      </c>
+      <c r="H623" t="s">
+        <v>98</v>
+      </c>
+      <c r="J623" t="s">
+        <v>1789</v>
+      </c>
+      <c r="K623" t="s">
+        <v>122</v>
+      </c>
+      <c r="L623" s="3">
+        <v>46169</v>
+      </c>
+      <c r="M623" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="624" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A624" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B624" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C624" t="s">
+        <v>1791</v>
+      </c>
+      <c r="D624" t="s">
+        <v>97</v>
+      </c>
+      <c r="E624" t="s">
+        <v>17</v>
+      </c>
+      <c r="F624">
+        <v>6784</v>
+      </c>
+      <c r="G624" t="s">
+        <v>133</v>
+      </c>
+      <c r="H624" t="s">
+        <v>104</v>
+      </c>
+      <c r="K624" t="s">
+        <v>122</v>
+      </c>
+      <c r="L624" s="3">
+        <v>46170</v>
+      </c>
+      <c r="M624" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="625" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A625" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B625" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C625" t="s">
+        <v>1793</v>
+      </c>
+      <c r="D625" t="s">
+        <v>97</v>
+      </c>
+      <c r="E625" t="s">
+        <v>10</v>
+      </c>
+      <c r="F625">
+        <v>6825</v>
+      </c>
+      <c r="G625" t="s">
+        <v>133</v>
+      </c>
+      <c r="H625" t="s">
+        <v>105</v>
+      </c>
+      <c r="J625" t="s">
+        <v>1794</v>
+      </c>
+      <c r="M625" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="626" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A626" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B626" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C626" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D626" t="s">
+        <v>97</v>
+      </c>
+      <c r="E626" t="s">
+        <v>10</v>
+      </c>
+      <c r="F626">
+        <v>7117</v>
+      </c>
+      <c r="G626" t="s">
+        <v>118</v>
+      </c>
+      <c r="H626" t="s">
+        <v>101</v>
+      </c>
+      <c r="I626" t="s">
+        <v>1797</v>
+      </c>
+      <c r="J626" t="s">
+        <v>1798</v>
+      </c>
+      <c r="K626" t="s">
+        <v>1799</v>
+      </c>
+      <c r="L626" s="3">
+        <v>46170</v>
+      </c>
+      <c r="M626" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="627" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A627" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B627" s="3">
+        <v>46169</v>
+      </c>
+      <c r="C627" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D627" t="s">
+        <v>97</v>
+      </c>
+      <c r="E627" t="s">
+        <v>10</v>
+      </c>
+      <c r="F627">
+        <v>6843</v>
+      </c>
+      <c r="G627" t="s">
+        <v>133</v>
+      </c>
+      <c r="H627" t="s">
+        <v>119</v>
+      </c>
+      <c r="I627" t="s">
+        <v>1802</v>
+      </c>
+      <c r="J627" t="s">
+        <v>1803</v>
+      </c>
+      <c r="K627" t="s">
+        <v>127</v>
+      </c>
+      <c r="L627" s="3">
+        <v>46170</v>
+      </c>
+      <c r="M627" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="628" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A628" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B628" s="3">
+        <v>46170</v>
+      </c>
+      <c r="C628" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D628" t="s">
+        <v>97</v>
+      </c>
+      <c r="E628" t="s">
+        <v>19</v>
+      </c>
+      <c r="F628">
+        <v>4808</v>
+      </c>
+      <c r="G628" t="s">
+        <v>113</v>
+      </c>
+      <c r="H628" t="s">
+        <v>101</v>
+      </c>
+      <c r="J628" t="s">
+        <v>1806</v>
+      </c>
+      <c r="M628" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="629" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A629" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B629" s="3">
+        <v>46170</v>
+      </c>
+      <c r="C629" s="4">
+        <v>0.35694444444444445</v>
+      </c>
+      <c r="D629" t="s">
+        <v>97</v>
+      </c>
+      <c r="E629" t="s">
+        <v>9</v>
+      </c>
+      <c r="F629">
+        <v>3886</v>
+      </c>
+      <c r="G629" t="s">
+        <v>102</v>
+      </c>
+      <c r="H629" t="s">
+        <v>12</v>
+      </c>
+      <c r="I629" t="s">
+        <v>1808</v>
+      </c>
+      <c r="K629" t="s">
+        <v>126</v>
+      </c>
+      <c r="L629" s="3">
+        <v>46170</v>
+      </c>
+      <c r="M629" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="630" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A630" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B630" s="3">
+        <v>46170</v>
+      </c>
+      <c r="C630" s="4">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="D630" t="s">
+        <v>97</v>
+      </c>
+      <c r="E630" t="s">
+        <v>23</v>
+      </c>
+      <c r="F630">
+        <v>5443</v>
+      </c>
+      <c r="G630" t="s">
+        <v>132</v>
+      </c>
+      <c r="H630" t="s">
+        <v>119</v>
+      </c>
+      <c r="I630" t="s">
+        <v>1810</v>
+      </c>
+      <c r="K630" t="s">
+        <v>127</v>
+      </c>
+      <c r="L630" s="3">
+        <v>46170</v>
+      </c>
+      <c r="M630" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="631" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A631" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B631" s="3">
+        <v>46170</v>
+      </c>
+      <c r="C631" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D631" t="s">
+        <v>97</v>
+      </c>
+      <c r="E631" t="s">
+        <v>10</v>
+      </c>
+      <c r="F631">
+        <v>7603</v>
+      </c>
+      <c r="G631" t="s">
+        <v>109</v>
+      </c>
+      <c r="H631" t="s">
+        <v>12</v>
+      </c>
+      <c r="I631" t="s">
+        <v>1813</v>
+      </c>
+      <c r="J631" t="s">
+        <v>1814</v>
+      </c>
+      <c r="M631" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="632" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A632" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B632" s="3">
+        <v>46170</v>
+      </c>
+      <c r="C632" t="s">
+        <v>47</v>
+      </c>
+      <c r="D632" t="s">
+        <v>97</v>
+      </c>
+      <c r="E632" t="s">
+        <v>10</v>
+      </c>
+      <c r="F632">
+        <v>5764</v>
+      </c>
+      <c r="G632" t="s">
+        <v>103</v>
+      </c>
+      <c r="H632" t="s">
+        <v>100</v>
+      </c>
+      <c r="I632" t="s">
+        <v>1816</v>
+      </c>
+      <c r="J632" t="s">
+        <v>1817</v>
+      </c>
+      <c r="M632" t="s">
+        <v>1097</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="B2:B551" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="B2:B632" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>OR(NOT(ISERROR(DATEVALUE(B2))), AND(ISNUMBER(B2), LEFT(CELL("format", B2))="D"))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="H2:H551" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="H2:H632" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Sin Dinero,Mal Facturado,No hizo pedido,No está el dueño,Cerrado,Sin Stock,Mal armado"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFA1B39-16E3-4345-9367-16EB2C49AECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADEAA76-812B-42DD-BA77-C9B5EDDBBBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Rechazos Calle" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$306</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2666" uniqueCount="913">
   <si>
     <t>Fecha</t>
   </si>
@@ -1956,9 +1956,6 @@
     <t>24 tody galletas</t>
   </si>
   <si>
-    <t>Retirá la mercadería — no se puede entregar — No lo quieren</t>
-  </si>
-  <si>
     <t>MPZQ4NL127PP</t>
   </si>
   <si>
@@ -2122,6 +2119,667 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780600661/gwzglrgcisfrfujilu5i.jpg</t>
+  </si>
+  <si>
+    <t>MQ0TS2WWOUIX</t>
+  </si>
+  <si>
+    <t>08:13 a. m.</t>
+  </si>
+  <si>
+    <t>No pidió 3 d de 43 grs</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780657997/fyu3twb6vgh08k8lnepx.jpg</t>
+  </si>
+  <si>
+    <t>MQ0US6V0KZIP</t>
+  </si>
+  <si>
+    <t>08:41 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780659699/xpkpq8vi6po37m4lezck.jpg</t>
+  </si>
+  <si>
+    <t>MQ0UZ9YTY4CR</t>
+  </si>
+  <si>
+    <t>08:47 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780660003/xmcbsp5gragmx4pfv8ro.jpg</t>
+  </si>
+  <si>
+    <t>MQ0VJWYWDBVR</t>
+  </si>
+  <si>
+    <t>09:03 a. m.</t>
+  </si>
+  <si>
+    <t>Faltó 1 Dorito queso 77gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780660969/wuexcwpwpmgccaxl6xjy.jpg</t>
+  </si>
+  <si>
+    <t>MQ0VZNV0VQB9</t>
+  </si>
+  <si>
+    <t>MQ0WC8F7WZ87</t>
+  </si>
+  <si>
+    <t>09:25 a. m.</t>
+  </si>
+  <si>
+    <t>Gallo queso sin stock</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780662286/dzv2bfici6nqlnwgp6ad.jpg</t>
+  </si>
+  <si>
+    <t>MQ0WT486DKGB</t>
+  </si>
+  <si>
+    <t>Pan rallado 5 
+2 arroz de verdeo</t>
+  </si>
+  <si>
+    <t>MQ0X1CJCS5A7</t>
+  </si>
+  <si>
+    <t>09:44 a. m.</t>
+  </si>
+  <si>
+    <t>Faltaron 12 3d 43grs</t>
+  </si>
+  <si>
+    <t>MQ0YJSUVVGNO</t>
+  </si>
+  <si>
+    <t>10:26 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780665998/couszbljaucid7mom87f.jpg</t>
+  </si>
+  <si>
+    <t>MQ0Z5U2726Z2</t>
+  </si>
+  <si>
+    <t>Rechaza chocoarroz vto corto</t>
+  </si>
+  <si>
+    <t>MQ0ZLNSHHH2P</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780667768/edifce3zasmg2budnjgs.jpg</t>
+  </si>
+  <si>
+    <t>MQ0ZNL7OLVU3</t>
+  </si>
+  <si>
+    <t>Pidió Duracell aa</t>
+  </si>
+  <si>
+    <t>El cliente va a recibir — seguí viaje — Está bien el rechazo de las pilas.</t>
+  </si>
+  <si>
+    <t>MQ0ZNR8MK1HW</t>
+  </si>
+  <si>
+    <t>10:58 a. m.</t>
+  </si>
+  <si>
+    <t>3 exquisita chocolate</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Mal stock en sistema</t>
+  </si>
+  <si>
+    <t>MQ0ZOM4TTBT0</t>
+  </si>
+  <si>
+    <t>MQ0ZWKQFZZOH</t>
+  </si>
+  <si>
+    <t>11:04 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780668280/rjlz46gtw0cj6izmhtfc.jpg</t>
+  </si>
+  <si>
+    <t>MQ103OASHEB1</t>
+  </si>
+  <si>
+    <t>MQ1033HLZTB5</t>
+  </si>
+  <si>
+    <t>Se equivocó quería x 140g descuento lo marcado</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780668640/lbriyepgrzgzw2xzzcff.jpg</t>
+  </si>
+  <si>
+    <t>MQ10KN5FMRQY</t>
+  </si>
+  <si>
+    <t>11:25 a. m.</t>
+  </si>
+  <si>
+    <t>No quiso cheto ondulados de ketchup , no salen en su negocio dice</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780669400/iddomih6pg0flqlrms6a.jpg</t>
+  </si>
+  <si>
+    <t>MQ10MKLM22VV</t>
+  </si>
+  <si>
+    <t>11:26 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780669592/fqilchjh6bupbob7icke.jpg</t>
+  </si>
+  <si>
+    <t>MQ113RZ68FD7</t>
+  </si>
+  <si>
+    <t>Avena x280 tradicional</t>
+  </si>
+  <si>
+    <t>MQ11CBRV8UGC</t>
+  </si>
+  <si>
+    <t>11:45 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780670692/bpnkqehhyubzut9ufbof.jpg</t>
+  </si>
+  <si>
+    <t>MQ11O55Y9MTL</t>
+  </si>
+  <si>
+    <t>11:54 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780671263/mozphpfoettscjqj86s0.jpg</t>
+  </si>
+  <si>
+    <t>MQ11PZ87U4VQ</t>
+  </si>
+  <si>
+    <t>Rechaza tallarin</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780671328/wahd8l16xkq4agskngg6.jpg</t>
+  </si>
+  <si>
+    <t>MQ11XNWTLIME</t>
+  </si>
+  <si>
+    <t>12:01 p. m.</t>
+  </si>
+  <si>
+    <t>Alfajores mousse toddy</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780671687/umbwkakubo2gts4n9snn.jpg</t>
+  </si>
+  <si>
+    <t>MQ128IQYOFTP</t>
+  </si>
+  <si>
+    <t>MQ12B7VAYTEF</t>
+  </si>
+  <si>
+    <t>MQ12ZFL3L4DQ</t>
+  </si>
+  <si>
+    <t>No tiene nota de crédito rechaza el pedido</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780673450/rqctzkz66geoq0lbg0b5.jpg</t>
+  </si>
+  <si>
+    <t>MQ13A010HPJW</t>
+  </si>
+  <si>
+    <t>12:39 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780673939/yr74dsq8lldqoaas3fp7.jpg</t>
+  </si>
+  <si>
+    <t>MQ13F7SZIE4I</t>
+  </si>
+  <si>
+    <t>12:43 p. m.</t>
+  </si>
+  <si>
+    <t>Mantecol y chonuss</t>
+  </si>
+  <si>
+    <t>MQ145XIZ189I</t>
+  </si>
+  <si>
+    <t>01:03 p. m.</t>
+  </si>
+  <si>
+    <t>Playadito</t>
+  </si>
+  <si>
+    <t>MQ14THUO2Q0O</t>
+  </si>
+  <si>
+    <t>Rechaza cacao toddy</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780676530/oug9dozpbuveepvpy8ex.jpg</t>
+  </si>
+  <si>
+    <t>MQ153H5IRMPD</t>
+  </si>
+  <si>
+    <t>Yerba playadito</t>
+  </si>
+  <si>
+    <t>MQ15RUV4MJ4B</t>
+  </si>
+  <si>
+    <t>01:49 p. m.</t>
+  </si>
+  <si>
+    <t>Pidió x 20g rechaza pepsico</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780678134/fagjhtjqyqkiwdswoohv.jpg</t>
+  </si>
+  <si>
+    <t>MQ15T0WH2PB1</t>
+  </si>
+  <si>
+    <t>MQ161IIKT7TX</t>
+  </si>
+  <si>
+    <t>01:56 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780678583/qiogsvzplboiok0w2mxu.jpg</t>
+  </si>
+  <si>
+    <t>MQ16B1X397HI</t>
+  </si>
+  <si>
+    <t>02:03 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780679032/bkhw4zinzuvclq0vmi60.jpg</t>
+  </si>
+  <si>
+    <t>MQ16OU4BYE5X</t>
+  </si>
+  <si>
+    <t>02:14 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780679672/i0sfzab6wg3gjpblvq0g.jpg</t>
+  </si>
+  <si>
+    <t>MQ170RUPU1YP</t>
+  </si>
+  <si>
+    <t>MQ2A7OY0JE36</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780746055/flp0trlckrnmvtjlt9ht.jpg</t>
+  </si>
+  <si>
+    <t>MQ2BK8ZU4D8N</t>
+  </si>
+  <si>
+    <t>No venden x 43g
+Sin nota de crédito no puede dejar el pedido</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780748323/eipd2jg3vna4oqg00gum.jpg</t>
+  </si>
+  <si>
+    <t>MQ2BQP92I293</t>
+  </si>
+  <si>
+    <t>3 sweet chili 74grs</t>
+  </si>
+  <si>
+    <t>MQ2C3NXCF1L3</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780749228/nkl69j0mkm8shv3s138x.jpg</t>
+  </si>
+  <si>
+    <t>MQ2COHTZQQIO</t>
+  </si>
+  <si>
+    <t>MQ2CW0I8SIV5</t>
+  </si>
+  <si>
+    <t>Lo quiere el lunes</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780750563/e4mk0qfosvquojhbvk5e.jpg</t>
+  </si>
+  <si>
+    <t>MQ2D3SCJISZR</t>
+  </si>
+  <si>
+    <t>10:02 a. m.</t>
+  </si>
+  <si>
+    <t>MQ2DBHTX4NUG</t>
+  </si>
+  <si>
+    <t>Faltaron tw queso 95 gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780751284/j1o7e9qptfpzojwfyuxr.jpg</t>
+  </si>
+  <si>
+    <t>MQ2DO3QZ02OE</t>
+  </si>
+  <si>
+    <t>10:18 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780751873/xatvspn3iwkgu1km2hqe.jpg</t>
+  </si>
+  <si>
+    <t>MQ2DVGN49KO5</t>
+  </si>
+  <si>
+    <t>10:23 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780752205/raamumeldlgouson8exk.jpg</t>
+  </si>
+  <si>
+    <t>MQ2DZBFZA0MO</t>
+  </si>
+  <si>
+    <t>Descuento dos tw de 95 de queso pidió solo dos y hay facturado 4</t>
+  </si>
+  <si>
+    <t>MQ2EBL0K2QB9</t>
+  </si>
+  <si>
+    <t>MQ2ED4GK7H10</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780753030/py1scnplsxmd3dghmdg4.jpg</t>
+  </si>
+  <si>
+    <t>MQ2EKPIPOC1Q</t>
+  </si>
+  <si>
+    <t>Se armó mal el pedido y es combo</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780753405/h6t764pgltttscfdzivn.jpg</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — Error en el armado del deposito</t>
+  </si>
+  <si>
+    <t>MQ2ELQE4V2CF</t>
+  </si>
+  <si>
+    <t>Facturaste 20 display en vez de uno rechazo los otros 19</t>
+  </si>
+  <si>
+    <t>MQ2EN4U9N2AH</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780753502/ppok2r6mbzafbcvsf3dv.jpg</t>
+  </si>
+  <si>
+    <t>MQ2F454IG1GP</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780754300/wt8aqfgws99sgltfz2wl.jpg</t>
+  </si>
+  <si>
+    <t>MQ2FE8BDCJAR</t>
+  </si>
+  <si>
+    <t>11:06 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780754763/rqegni5y5ubvdwvxiyye.jpg</t>
+  </si>
+  <si>
+    <t>MQ2FEYO2319Q</t>
+  </si>
+  <si>
+    <t>MQ2FO0JBWGES</t>
+  </si>
+  <si>
+    <t>Lo esperaba el lunes</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780755216/cm3cz1crokbbryn8qouq.jpg</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — 😭😭😭😭</t>
+  </si>
+  <si>
+    <t>MQ2FWG8ZWYKM</t>
+  </si>
+  <si>
+    <t>11:20 a. m.</t>
+  </si>
+  <si>
+    <t>Falto toddy Peppa</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780755608/calchmzkon4ztehkz7b5.jpg</t>
+  </si>
+  <si>
+    <t>MQ2FXI5J6CXG</t>
+  </si>
+  <si>
+    <t>11:21 a. m.</t>
+  </si>
+  <si>
+    <t>No pidió ese gramaje</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780755656/dglwjrlkxgehf3bkn8to.jpg</t>
+  </si>
+  <si>
+    <t>MQ2GSJ9LR6TJ</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780757107/i4ihfnzjji9eh48cazd4.jpg</t>
+  </si>
+  <si>
+    <t>MQ2GZ0A0Q2PD</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780757408/frqcetsrhkx2fu07266o.jpg</t>
+  </si>
+  <si>
+    <t>MQ2HYRVL04T7</t>
+  </si>
+  <si>
+    <t>12:25 p. m.</t>
+  </si>
+  <si>
+    <t>4 ondas vencidas</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780759486/fceyvmbiqqwxkhmdjmh6.jpg</t>
+  </si>
+  <si>
+    <t>MQ2K0DJIAIKN</t>
+  </si>
+  <si>
+    <t>01:15 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780762535/bkb0eykidh2n5p6vlj0v.jpg</t>
+  </si>
+  <si>
+    <t>MQ2K229W0Q2S</t>
+  </si>
+  <si>
+    <t>01:16 p. m.</t>
+  </si>
+  <si>
+    <t>MQ2K2P7WYCOU</t>
+  </si>
+  <si>
+    <t>MQ2K39T0FFQV</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780762633/ij6yjgtoxyuraydsahft.jpg</t>
+  </si>
+  <si>
+    <t>MQ54263QXFCU</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780917122/mikusgj6ll9ezowr9mpx.jpg</t>
+  </si>
+  <si>
+    <t>MQ550LH2GOBU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prueba
+</t>
+  </si>
+  <si>
+    <t>MQ553THKFFQZ</t>
+  </si>
+  <si>
+    <t>MQ55HESO2L10</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780919512/p2q4ffbwjb6rkxljbo20.jpg</t>
+  </si>
+  <si>
+    <t>MQ55MWPSGFRH</t>
+  </si>
+  <si>
+    <t>MQ5680IKS0YF</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780920762/g5uzvn1q498fndnk5ja9.jpg</t>
+  </si>
+  <si>
+    <t>MQ568MUE4JWI</t>
+  </si>
+  <si>
+    <t>09:13 a. m.</t>
+  </si>
+  <si>
+    <t>Pan rallado favorito 4 lo otro recibe</t>
+  </si>
+  <si>
+    <t>MQ56REKCTP0T</t>
+  </si>
+  <si>
+    <t>1 paq roto</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780921663/f95dk23qx3mnqcy4m52g.jpg</t>
+  </si>
+  <si>
+    <t>MQ5727WQR6HD</t>
+  </si>
+  <si>
+    <t>MQ574UZYPX62</t>
+  </si>
+  <si>
+    <t>Se desc alf toddy mousse</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780922285/g2cppzna1yjedxzfdzzl.jpg</t>
+  </si>
+  <si>
+    <t>MQ57CT24GPQ2</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780922654/zarf7kn8oniscwcsc3ok.jpg</t>
+  </si>
+  <si>
+    <t>MQ57H0RMT7SO</t>
+  </si>
+  <si>
+    <t>09:47 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780922857/enhgxgcael6hyeo5i9nu.jpg</t>
+  </si>
+  <si>
+    <t>MQ57ZJ336L0I</t>
+  </si>
+  <si>
+    <t>La cl pidió gramaje chico y está facturado de mediano</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780923722/zzuiwa0ci0oflajvy6i9.jpg</t>
+  </si>
+  <si>
+    <t>MQ57Z82TJ5XM</t>
+  </si>
+  <si>
+    <t>6 galletas sandwich individual y 4 galletas salvado individual</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780923714/e0aia84y7bmabsy6gw7z.jpg</t>
+  </si>
+  <si>
+    <t>MQ584BETYKZB</t>
+  </si>
+  <si>
+    <t>Caserito</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780923937/povrxgnx1hxfky35fmit.jpg</t>
+  </si>
+  <si>
+    <t>MQ582XO99BLS</t>
+  </si>
+  <si>
+    <t>Favorita spaghetti 7
+Favorita tallarín 7</t>
+  </si>
+  <si>
+    <t>MQ585NI5J485</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780924000/fvfjwtdyase0f4n0vmib.jpg</t>
+  </si>
+  <si>
+    <t>MQ58DUSUFYYA</t>
+  </si>
+  <si>
+    <t>MQ58I957WFH3</t>
+  </si>
+  <si>
+    <t>10:16 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780924594/jy0h1g3uusbfltytpxnk.jpg</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — Mal cargado</t>
+  </si>
+  <si>
+    <t>MQ58LHTGHXUG</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1780924755/wbjthsmgv8i82v7tbzuh.jpg</t>
+  </si>
+  <si>
+    <t>Columna1</t>
   </si>
 </sst>
 </file>
@@ -2285,7 +2943,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2355,6 +3013,14 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2473,9 +3139,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:M219">
-  <autoFilter ref="A1:M219" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N306">
+  <autoFilter ref="A1:N306" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fecha"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Hora"/>
@@ -2489,6 +3155,7 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Respuesta Vendedor"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Fecha Respuesta"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Estado"/>
+    <tableColumn id="14" xr3:uid="{CC0C5ACA-E559-4A65-BA2E-D983199EE535}" name="Columna1"/>
   </tableColumns>
   <tableStyleInfo name="Rechazos Calle-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2695,7 +3362,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M219"/>
+  <dimension ref="A1:N306"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -2710,7 +3377,7 @@
     <col min="12" max="13" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -2750,8 +3417,11 @@
       <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N1" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>76</v>
       </c>
@@ -2789,8 +3459,11 @@
       <c r="M2" s="19" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>79</v>
       </c>
@@ -2824,8 +3497,11 @@
       <c r="M3" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>82</v>
       </c>
@@ -2861,8 +3537,11 @@
       <c r="M4" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>84</v>
       </c>
@@ -2898,8 +3577,11 @@
       <c r="M5" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>87</v>
       </c>
@@ -2935,8 +3617,11 @@
       <c r="M6" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>88</v>
       </c>
@@ -2976,8 +3661,11 @@
       <c r="M7" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>91</v>
       </c>
@@ -3017,8 +3705,11 @@
       <c r="M8" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>95</v>
       </c>
@@ -3054,8 +3745,11 @@
       <c r="M9" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>96</v>
       </c>
@@ -3095,8 +3789,11 @@
       <c r="M10" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>99</v>
       </c>
@@ -3132,8 +3829,11 @@
       <c r="M11" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>101</v>
       </c>
@@ -3169,8 +3869,11 @@
       <c r="M12" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>103</v>
       </c>
@@ -3210,8 +3913,11 @@
       <c r="M13" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>107</v>
       </c>
@@ -3251,8 +3957,11 @@
       <c r="M14" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>110</v>
       </c>
@@ -3288,8 +3997,11 @@
       <c r="M15" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>111</v>
       </c>
@@ -3325,8 +4037,11 @@
       <c r="M16" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>112</v>
       </c>
@@ -3362,8 +4077,11 @@
       <c r="M17" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>115</v>
       </c>
@@ -3399,8 +4117,11 @@
       <c r="M18" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>116</v>
       </c>
@@ -3438,8 +4159,11 @@
       <c r="M19" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>118</v>
       </c>
@@ -3475,8 +4199,11 @@
       <c r="M20" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>121</v>
       </c>
@@ -3516,8 +4243,11 @@
       <c r="M21" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>125</v>
       </c>
@@ -3555,8 +4285,11 @@
       <c r="M22" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>128</v>
       </c>
@@ -3592,8 +4325,11 @@
       <c r="M23" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>129</v>
       </c>
@@ -3633,8 +4369,11 @@
       <c r="M24" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>133</v>
       </c>
@@ -3668,8 +4407,11 @@
       <c r="M25" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>135</v>
       </c>
@@ -3703,8 +4445,11 @@
       <c r="M26" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>138</v>
       </c>
@@ -3744,8 +4489,11 @@
       <c r="M27" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>142</v>
       </c>
@@ -3783,8 +4531,11 @@
       <c r="M28" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>145</v>
       </c>
@@ -3822,8 +4573,11 @@
       <c r="M29" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>147</v>
       </c>
@@ -3861,8 +4615,11 @@
       <c r="M30" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>150</v>
       </c>
@@ -3898,8 +4655,11 @@
       <c r="M31" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>153</v>
       </c>
@@ -3937,8 +4697,11 @@
       <c r="M32" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>155</v>
       </c>
@@ -3976,8 +4739,11 @@
       <c r="M33" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>158</v>
       </c>
@@ -4013,8 +4779,11 @@
       <c r="M34" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>161</v>
       </c>
@@ -4052,8 +4821,11 @@
       <c r="M35" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>163</v>
       </c>
@@ -4089,8 +4861,11 @@
       <c r="M36" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>165</v>
       </c>
@@ -4128,8 +4903,11 @@
       <c r="M37" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>167</v>
       </c>
@@ -4165,8 +4943,11 @@
       <c r="M38" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>170</v>
       </c>
@@ -4202,8 +4983,11 @@
       <c r="M39" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>172</v>
       </c>
@@ -4239,8 +5023,11 @@
       <c r="M40" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>174</v>
       </c>
@@ -4276,8 +5063,11 @@
       <c r="M41" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N41">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>177</v>
       </c>
@@ -4315,8 +5105,11 @@
       <c r="M42" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N42">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>180</v>
       </c>
@@ -4354,8 +5147,11 @@
       <c r="M43" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>182</v>
       </c>
@@ -4393,8 +5189,11 @@
       <c r="M44" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>185</v>
       </c>
@@ -4432,8 +5231,11 @@
       <c r="M45" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>187</v>
       </c>
@@ -4473,8 +5275,11 @@
       <c r="M46" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N46">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>191</v>
       </c>
@@ -4508,8 +5313,11 @@
       <c r="M47" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>193</v>
       </c>
@@ -4549,8 +5357,11 @@
       <c r="M48" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>197</v>
       </c>
@@ -4588,8 +5399,11 @@
       <c r="M49" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>201</v>
       </c>
@@ -4627,8 +5441,11 @@
       <c r="M50" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>204</v>
       </c>
@@ -4664,8 +5481,11 @@
       <c r="M51" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N51">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>206</v>
       </c>
@@ -4703,8 +5523,11 @@
       <c r="M52" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>209</v>
       </c>
@@ -4742,8 +5565,11 @@
       <c r="M53" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>212</v>
       </c>
@@ -4783,8 +5609,11 @@
       <c r="M54" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>216</v>
       </c>
@@ -4816,8 +5645,11 @@
       <c r="M55" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N55">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>218</v>
       </c>
@@ -4851,8 +5683,11 @@
       <c r="M56" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>221</v>
       </c>
@@ -4890,8 +5725,11 @@
       <c r="M57" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>223</v>
       </c>
@@ -4923,8 +5761,11 @@
       <c r="M58" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N58">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>224</v>
       </c>
@@ -4964,8 +5805,11 @@
       <c r="M59" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>228</v>
       </c>
@@ -5001,8 +5845,11 @@
       <c r="M60" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N60">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>229</v>
       </c>
@@ -5040,8 +5887,11 @@
       <c r="M61" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N61">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>232</v>
       </c>
@@ -5079,8 +5929,11 @@
       <c r="M62" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N62">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>234</v>
       </c>
@@ -5120,8 +5973,11 @@
       <c r="M63" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>238</v>
       </c>
@@ -5161,8 +6017,11 @@
       <c r="M64" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N64">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>242</v>
       </c>
@@ -5200,8 +6059,11 @@
       <c r="M65" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="66" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N65">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>246</v>
       </c>
@@ -5237,8 +6099,11 @@
       <c r="M66" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N66">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>247</v>
       </c>
@@ -5276,8 +6141,11 @@
       <c r="M67" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N67">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>250</v>
       </c>
@@ -5313,8 +6181,11 @@
       <c r="M68" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N68">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>252</v>
       </c>
@@ -5352,8 +6223,11 @@
       <c r="M69" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N69">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>256</v>
       </c>
@@ -5389,8 +6263,11 @@
       <c r="M70" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N70">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>258</v>
       </c>
@@ -5426,8 +6303,11 @@
       <c r="M71" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N71">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>261</v>
       </c>
@@ -5467,8 +6347,11 @@
       <c r="M72" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N72">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>264</v>
       </c>
@@ -5506,8 +6389,11 @@
       <c r="M73" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N73">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>267</v>
       </c>
@@ -5547,8 +6433,11 @@
       <c r="M74" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>271</v>
       </c>
@@ -5584,8 +6473,11 @@
       <c r="M75" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N75">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>275</v>
       </c>
@@ -5619,8 +6511,11 @@
       <c r="M76" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N76">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>277</v>
       </c>
@@ -5658,8 +6553,11 @@
       <c r="M77" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>280</v>
       </c>
@@ -5699,8 +6597,11 @@
       <c r="M78" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="79" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N78">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>284</v>
       </c>
@@ -5738,8 +6639,11 @@
       <c r="M79" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N79">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>286</v>
       </c>
@@ -5779,8 +6683,11 @@
       <c r="M80" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N80">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>290</v>
       </c>
@@ -5812,8 +6719,11 @@
       <c r="M81" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N81">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>292</v>
       </c>
@@ -5851,8 +6761,11 @@
       <c r="M82" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N82">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>295</v>
       </c>
@@ -5888,8 +6801,11 @@
       <c r="M83" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N83">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>297</v>
       </c>
@@ -5925,8 +6841,11 @@
       <c r="M84" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N84">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>298</v>
       </c>
@@ -5958,8 +6877,11 @@
       <c r="M85" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N85">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>299</v>
       </c>
@@ -5993,8 +6915,11 @@
       <c r="M86" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N86">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>301</v>
       </c>
@@ -6026,8 +6951,11 @@
       <c r="M87" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N87">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>302</v>
       </c>
@@ -6067,8 +6995,11 @@
       <c r="M88" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N88">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>306</v>
       </c>
@@ -6108,8 +7039,11 @@
       <c r="M89" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="90" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N89">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>309</v>
       </c>
@@ -6149,8 +7083,11 @@
       <c r="M90" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N90">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>312</v>
       </c>
@@ -6186,8 +7123,11 @@
       <c r="M91" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N91">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>317</v>
       </c>
@@ -6225,8 +7165,11 @@
       <c r="M92" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="93" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N92">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>320</v>
       </c>
@@ -6262,8 +7205,11 @@
       <c r="M93" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="94" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N93">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>321</v>
       </c>
@@ -6297,8 +7243,11 @@
       <c r="M94" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="95" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N94">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>326</v>
       </c>
@@ -6338,8 +7287,11 @@
       <c r="M95" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="96" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>330</v>
       </c>
@@ -6373,8 +7325,11 @@
       <c r="M96" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="97" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N96">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>333</v>
       </c>
@@ -6412,8 +7367,11 @@
       <c r="M97" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="98" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N97">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>336</v>
       </c>
@@ -6447,8 +7405,11 @@
       <c r="M98" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N98">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>339</v>
       </c>
@@ -6486,8 +7447,11 @@
       <c r="M99" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="100" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N99">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>343</v>
       </c>
@@ -6525,8 +7489,11 @@
       <c r="M100" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="101" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N100">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>347</v>
       </c>
@@ -6564,8 +7531,11 @@
       <c r="M101" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="102" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N101">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>350</v>
       </c>
@@ -6599,8 +7569,11 @@
       <c r="M102" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="103" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N102">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>352</v>
       </c>
@@ -6640,8 +7613,11 @@
       <c r="M103" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="104" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N103">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>356</v>
       </c>
@@ -6681,8 +7657,11 @@
       <c r="M104" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="105" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N104">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>360</v>
       </c>
@@ -6718,8 +7697,11 @@
       <c r="M105" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="106" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N105">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>364</v>
       </c>
@@ -6757,8 +7739,11 @@
       <c r="M106" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="107" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N106">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>368</v>
       </c>
@@ -6792,8 +7777,11 @@
       <c r="M107" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="108" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N107">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>370</v>
       </c>
@@ -6831,8 +7819,11 @@
       <c r="M108" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="109" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N108">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>372</v>
       </c>
@@ -6872,8 +7863,11 @@
       <c r="M109" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="110" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N109">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>376</v>
       </c>
@@ -6911,8 +7905,11 @@
       <c r="M110" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="111" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N110">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>380</v>
       </c>
@@ -6950,8 +7947,11 @@
       <c r="M111" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="112" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N111">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>383</v>
       </c>
@@ -6991,8 +7991,11 @@
       <c r="M112" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="113" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N112">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>386</v>
       </c>
@@ -7030,8 +8033,11 @@
       <c r="M113" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="114" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N113">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>389</v>
       </c>
@@ -7071,8 +8077,11 @@
       <c r="M114" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="115" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N114">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>393</v>
       </c>
@@ -7110,8 +8119,11 @@
       <c r="M115" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="116" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N115">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>396</v>
       </c>
@@ -7151,8 +8163,11 @@
       <c r="M116" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="117" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N116">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>400</v>
       </c>
@@ -7190,8 +8205,11 @@
       <c r="M117" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="118" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N117">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>403</v>
       </c>
@@ -7231,8 +8249,11 @@
       <c r="M118" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="119" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N118">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>408</v>
       </c>
@@ -7270,8 +8291,11 @@
       <c r="M119" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="120" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N119">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>411</v>
       </c>
@@ -7309,8 +8333,11 @@
       <c r="M120" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="121" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N120">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>415</v>
       </c>
@@ -7344,8 +8371,11 @@
       <c r="M121" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="122" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N121">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>417</v>
       </c>
@@ -7379,8 +8409,11 @@
       <c r="M122" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="123" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N122">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>419</v>
       </c>
@@ -7418,8 +8451,11 @@
       <c r="M123" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="124" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N123">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>422</v>
       </c>
@@ -7457,8 +8493,11 @@
       <c r="M124" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="125" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N124">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>424</v>
       </c>
@@ -7494,8 +8533,11 @@
       <c r="M125" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="126" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N125">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>425</v>
       </c>
@@ -7533,8 +8575,11 @@
       <c r="M126" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="127" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N126">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>427</v>
       </c>
@@ -7568,8 +8613,11 @@
       <c r="M127" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="128" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N127">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>429</v>
       </c>
@@ -7607,8 +8655,11 @@
       <c r="M128" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="129" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N128">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>431</v>
       </c>
@@ -7642,8 +8693,11 @@
       <c r="M129" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="130" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N129">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>433</v>
       </c>
@@ -7681,8 +8735,11 @@
       <c r="M130" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="131" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N130">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>435</v>
       </c>
@@ -7720,8 +8777,11 @@
       <c r="M131" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="132" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N131">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>438</v>
       </c>
@@ -7757,8 +8817,11 @@
       <c r="M132" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="133" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N132">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>442</v>
       </c>
@@ -7796,8 +8859,11 @@
       <c r="M133" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="134" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N133">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>445</v>
       </c>
@@ -7837,8 +8903,11 @@
       <c r="M134" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="135" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N134">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>448</v>
       </c>
@@ -7874,8 +8943,11 @@
       <c r="M135" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="136" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N135">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>452</v>
       </c>
@@ -7915,8 +8987,11 @@
       <c r="M136" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="137" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N136">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>456</v>
       </c>
@@ -7954,8 +9029,11 @@
       <c r="M137" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="138" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N137">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>459</v>
       </c>
@@ -7987,8 +9065,11 @@
       <c r="M138" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="139" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N138">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>461</v>
       </c>
@@ -8026,8 +9107,11 @@
       <c r="M139" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="140" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N139">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>463</v>
       </c>
@@ -8065,8 +9149,11 @@
       <c r="M140" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="141" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N140">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>466</v>
       </c>
@@ -8100,8 +9187,11 @@
       <c r="M141" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="142" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N141">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>468</v>
       </c>
@@ -8141,8 +9231,11 @@
       <c r="M142" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="143" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N142">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>472</v>
       </c>
@@ -8176,8 +9269,11 @@
       <c r="M143" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="144" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N143">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>475</v>
       </c>
@@ -8213,8 +9309,11 @@
       <c r="M144" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="145" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N144">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>479</v>
       </c>
@@ -8254,8 +9353,11 @@
       <c r="M145" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="146" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N145">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>483</v>
       </c>
@@ -8293,8 +9395,11 @@
       <c r="M146" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="147" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N146">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>486</v>
       </c>
@@ -8334,8 +9439,11 @@
       <c r="M147" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="148" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N147">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>491</v>
       </c>
@@ -8373,8 +9481,11 @@
       <c r="M148" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="149" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N148">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>493</v>
       </c>
@@ -8412,8 +9523,11 @@
       <c r="M149" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="150" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N149">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>496</v>
       </c>
@@ -8451,8 +9565,11 @@
       <c r="M150" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="151" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N150">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>499</v>
       </c>
@@ -8492,8 +9609,11 @@
       <c r="M151" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="152" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N151">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>504</v>
       </c>
@@ -8533,8 +9653,11 @@
       <c r="M152" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="153" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N152">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>508</v>
       </c>
@@ -8574,8 +9697,11 @@
       <c r="M153" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="154" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N153">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>512</v>
       </c>
@@ -8613,8 +9739,11 @@
       <c r="M154" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="155" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N154">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>515</v>
       </c>
@@ -8652,8 +9781,11 @@
       <c r="M155" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="156" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N155">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>518</v>
       </c>
@@ -8693,8 +9825,11 @@
       <c r="M156" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="157" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N156">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>522</v>
       </c>
@@ -8732,8 +9867,11 @@
       <c r="M157" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="158" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N157">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>525</v>
       </c>
@@ -8771,8 +9909,11 @@
       <c r="M158" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="159" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N158">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
         <v>527</v>
       </c>
@@ -8810,8 +9951,11 @@
       <c r="M159" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="160" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N159">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>529</v>
       </c>
@@ -8851,8 +9995,11 @@
       <c r="M160" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="161" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N160">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>533</v>
       </c>
@@ -8892,8 +10039,11 @@
       <c r="M161" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="162" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N161">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>537</v>
       </c>
@@ -8927,8 +10077,11 @@
       <c r="M162" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="163" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N162">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>540</v>
       </c>
@@ -8966,8 +10119,11 @@
       <c r="M163" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="164" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N163">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>543</v>
       </c>
@@ -9007,8 +10163,11 @@
       <c r="M164" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="165" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N164">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>545</v>
       </c>
@@ -9048,8 +10207,11 @@
       <c r="M165" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="166" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N165">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>548</v>
       </c>
@@ -9083,8 +10245,11 @@
       <c r="M166" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="167" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N166">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>550</v>
       </c>
@@ -9122,8 +10287,11 @@
       <c r="M167" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="168" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N167">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>552</v>
       </c>
@@ -9157,8 +10325,11 @@
       <c r="M168" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="169" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N168">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>555</v>
       </c>
@@ -9192,8 +10363,11 @@
       <c r="M169" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="170" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N169">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>558</v>
       </c>
@@ -9231,8 +10405,11 @@
       <c r="M170" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="171" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N170">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>560</v>
       </c>
@@ -9266,8 +10443,11 @@
       <c r="M171" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="172" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N171">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>563</v>
       </c>
@@ -9307,8 +10487,11 @@
       <c r="M172" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="173" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N172">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>567</v>
       </c>
@@ -9348,8 +10531,11 @@
       <c r="M173" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="174" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N173">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>571</v>
       </c>
@@ -9385,8 +10571,11 @@
       <c r="M174" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="175" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N174">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
         <v>572</v>
       </c>
@@ -9424,8 +10613,11 @@
       <c r="M175" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="176" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N175">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>574</v>
       </c>
@@ -9459,8 +10651,11 @@
       <c r="M176" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="177" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N176">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>576</v>
       </c>
@@ -9498,8 +10693,11 @@
       <c r="M177" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="178" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N177">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>578</v>
       </c>
@@ -9533,8 +10731,11 @@
       <c r="M178" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="179" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N178">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>581</v>
       </c>
@@ -9572,8 +10773,11 @@
       <c r="M179" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="180" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N179">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>584</v>
       </c>
@@ -9611,8 +10815,11 @@
       <c r="M180" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="181" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N180">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>587</v>
       </c>
@@ -9652,8 +10859,11 @@
       <c r="M181" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="182" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N181">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>590</v>
       </c>
@@ -9693,8 +10903,11 @@
       <c r="M182" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="183" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N182">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>594</v>
       </c>
@@ -9728,8 +10941,11 @@
       <c r="M183" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="184" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N183">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>596</v>
       </c>
@@ -9769,8 +10985,11 @@
       <c r="M184" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="185" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N184">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>599</v>
       </c>
@@ -9808,8 +11027,11 @@
       <c r="M185" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="186" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N185">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>600</v>
       </c>
@@ -9849,8 +11071,11 @@
       <c r="M186" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="187" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N186">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>604</v>
       </c>
@@ -9886,8 +11111,11 @@
       <c r="M187" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="188" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N187">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>605</v>
       </c>
@@ -9925,8 +11153,11 @@
       <c r="M188" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="189" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N188">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
         <v>609</v>
       </c>
@@ -9962,8 +11193,11 @@
       <c r="M189" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="190" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N189">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>611</v>
       </c>
@@ -10003,8 +11237,11 @@
       <c r="M190" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="191" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N190">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>614</v>
       </c>
@@ -10042,8 +11279,11 @@
       <c r="M191" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="192" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N191">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>617</v>
       </c>
@@ -10081,8 +11321,11 @@
       <c r="M192" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="193" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N192">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
         <v>620</v>
       </c>
@@ -10118,8 +11361,11 @@
       <c r="M193" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="194" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N193">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>623</v>
       </c>
@@ -10153,8 +11399,11 @@
       <c r="M194" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="195" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N194">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
         <v>626</v>
       </c>
@@ -10188,8 +11437,11 @@
       <c r="M195" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="196" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N195">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>628</v>
       </c>
@@ -10227,8 +11479,11 @@
       <c r="M196" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="197" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N196">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
         <v>630</v>
       </c>
@@ -10260,8 +11515,11 @@
       <c r="M197" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="198" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N197">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
         <v>631</v>
       </c>
@@ -10293,8 +11551,11 @@
       <c r="M198" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="199" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N198">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
         <v>632</v>
       </c>
@@ -10334,8 +11595,11 @@
       <c r="M199" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="200" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N199">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>636</v>
       </c>
@@ -10365,24 +11629,27 @@
       </c>
       <c r="J200" s="8"/>
       <c r="K200" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L200" s="4">
+        <v>46178</v>
+      </c>
+      <c r="M200" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N200">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="s">
         <v>639</v>
-      </c>
-      <c r="L200" s="4">
-        <v>46177</v>
-      </c>
-      <c r="M200" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="201" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="3" t="s">
-        <v>640</v>
       </c>
       <c r="B201" s="4">
         <v>46177</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D201" s="5" t="s">
         <v>34</v>
@@ -10401,7 +11668,7 @@
       </c>
       <c r="I201" s="8"/>
       <c r="J201" s="11" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="K201" s="5" t="s">
         <v>45</v>
@@ -10412,16 +11679,19 @@
       <c r="M201" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="202" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N201">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B202" s="4">
         <v>46177</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D202" s="5" t="s">
         <v>34</v>
@@ -10440,7 +11710,7 @@
       </c>
       <c r="I202" s="8"/>
       <c r="J202" s="11" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="K202" s="5" t="s">
         <v>55</v>
@@ -10451,16 +11721,19 @@
       <c r="M202" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="203" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N202">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B203" s="4">
         <v>46177</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>34</v>
@@ -10479,7 +11752,7 @@
       </c>
       <c r="I203" s="8"/>
       <c r="J203" s="11" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="K203" s="5" t="s">
         <v>56</v>
@@ -10490,16 +11763,19 @@
       <c r="M203" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="204" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N203">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B204" s="4">
         <v>46177</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D204" s="5" t="s">
         <v>34</v>
@@ -10517,7 +11793,7 @@
         <v>52</v>
       </c>
       <c r="I204" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="J204" s="8"/>
       <c r="K204" s="5" t="s">
@@ -10529,16 +11805,19 @@
       <c r="M204" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="205" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N204">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B205" s="4">
         <v>46177</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D205" s="5" t="s">
         <v>34</v>
@@ -10557,7 +11836,7 @@
       </c>
       <c r="I205" s="8"/>
       <c r="J205" s="11" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K205" s="5" t="s">
         <v>54</v>
@@ -10568,10 +11847,13 @@
       <c r="M205" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="206" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N205">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B206" s="4">
         <v>46177</v>
@@ -10605,16 +11887,19 @@
       <c r="M206" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="207" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N206">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B207" s="4">
         <v>46177</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D207" s="5" t="s">
         <v>34</v>
@@ -10633,7 +11918,7 @@
       </c>
       <c r="I207" s="8"/>
       <c r="J207" s="11" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K207" s="5" t="s">
         <v>54</v>
@@ -10644,16 +11929,19 @@
       <c r="M207" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="208" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N207">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B208" s="4">
         <v>46177</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>34</v>
@@ -10681,16 +11969,19 @@
       <c r="M208" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="209" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N208">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B209" s="4">
         <v>46177</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D209" s="5" t="s">
         <v>34</v>
@@ -10709,7 +12000,7 @@
       </c>
       <c r="I209" s="8"/>
       <c r="J209" s="11" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="K209" s="5" t="s">
         <v>54</v>
@@ -10720,16 +12011,19 @@
       <c r="M209" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="210" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N209">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B210" s="4">
         <v>46177</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D210" s="5" t="s">
         <v>34</v>
@@ -10748,7 +12042,7 @@
       </c>
       <c r="I210" s="8"/>
       <c r="J210" s="11" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="K210" s="5" t="s">
         <v>56</v>
@@ -10759,16 +12053,19 @@
       <c r="M210" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="211" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N210">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B211" s="4">
         <v>46177</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>34</v>
@@ -10787,7 +12084,7 @@
       </c>
       <c r="I211" s="8"/>
       <c r="J211" s="11" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K211" s="5" t="s">
         <v>54</v>
@@ -10798,16 +12095,19 @@
       <c r="M211" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="212" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N211">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B212" s="4">
         <v>46177</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D212" s="5" t="s">
         <v>34</v>
@@ -10825,10 +12125,10 @@
         <v>11</v>
       </c>
       <c r="I212" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="J212" s="11" t="s">
         <v>672</v>
-      </c>
-      <c r="J212" s="11" t="s">
-        <v>673</v>
       </c>
       <c r="K212" s="5" t="s">
         <v>56</v>
@@ -10839,16 +12139,19 @@
       <c r="M212" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="213" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N212">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B213" s="4">
         <v>46177</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D213" s="5" t="s">
         <v>34</v>
@@ -10867,7 +12170,7 @@
       </c>
       <c r="I213" s="8"/>
       <c r="J213" s="11" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="K213" s="5" t="s">
         <v>54</v>
@@ -10878,10 +12181,13 @@
       <c r="M213" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="214" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N213">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B214" s="4">
         <v>46177</v>
@@ -10905,13 +12211,13 @@
         <v>38</v>
       </c>
       <c r="I214" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="J214" s="11" t="s">
         <v>678</v>
       </c>
-      <c r="J214" s="11" t="s">
+      <c r="K214" s="5" t="s">
         <v>679</v>
-      </c>
-      <c r="K214" s="5" t="s">
-        <v>680</v>
       </c>
       <c r="L214" s="4">
         <v>46177</v>
@@ -10919,16 +12225,19 @@
       <c r="M214" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="215" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N214">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B215" s="4">
         <v>46177</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D215" s="5" t="s">
         <v>34</v>
@@ -10946,10 +12255,10 @@
         <v>35</v>
       </c>
       <c r="I215" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="J215" s="11" t="s">
         <v>683</v>
-      </c>
-      <c r="J215" s="11" t="s">
-        <v>684</v>
       </c>
       <c r="K215" s="5" t="s">
         <v>54</v>
@@ -10960,10 +12269,13 @@
       <c r="M215" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="216" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N215">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B216" s="4">
         <v>46177</v>
@@ -10997,16 +12309,19 @@
       <c r="M216" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="217" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N216">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B217" s="4">
         <v>46177</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D217" s="5" t="s">
         <v>34</v>
@@ -11025,7 +12340,7 @@
       </c>
       <c r="I217" s="8"/>
       <c r="J217" s="11" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="K217" s="5" t="s">
         <v>55</v>
@@ -11036,16 +12351,19 @@
       <c r="M217" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="218" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N217">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B218" s="4">
         <v>46177</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D218" s="5" t="s">
         <v>34</v>
@@ -11073,16 +12391,19 @@
       <c r="M218" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="219" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N218">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B219" s="4">
         <v>46177</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D219" s="5" t="s">
         <v>34</v>
@@ -11100,156 +12421,3479 @@
         <v>52</v>
       </c>
       <c r="I219" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="J219" s="11" t="s">
         <v>693</v>
       </c>
-      <c r="J219" s="11" t="s">
+      <c r="K219" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L219" s="24">
+        <v>46177</v>
+      </c>
+      <c r="M219" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N219">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
         <v>694</v>
       </c>
-      <c r="K219" s="8"/>
-      <c r="L219" s="8"/>
-      <c r="M219" s="5" t="s">
+      <c r="B220" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C220" t="s">
+        <v>695</v>
+      </c>
+      <c r="D220" t="s">
+        <v>34</v>
+      </c>
+      <c r="E220" t="s">
+        <v>9</v>
+      </c>
+      <c r="F220">
+        <v>4891</v>
+      </c>
+      <c r="G220" t="s">
+        <v>48</v>
+      </c>
+      <c r="H220" t="s">
+        <v>37</v>
+      </c>
+      <c r="I220" t="s">
+        <v>696</v>
+      </c>
+      <c r="J220" t="s">
+        <v>697</v>
+      </c>
+      <c r="K220" t="s">
+        <v>54</v>
+      </c>
+      <c r="L220" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M220" t="s">
+        <v>67</v>
+      </c>
+      <c r="N220">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>698</v>
+      </c>
+      <c r="B221" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C221" t="s">
+        <v>699</v>
+      </c>
+      <c r="D221" t="s">
+        <v>34</v>
+      </c>
+      <c r="E221" t="s">
+        <v>13</v>
+      </c>
+      <c r="F221">
+        <v>11245</v>
+      </c>
+      <c r="G221" t="s">
+        <v>378</v>
+      </c>
+      <c r="H221" t="s">
+        <v>11</v>
+      </c>
+      <c r="J221" t="s">
+        <v>700</v>
+      </c>
+      <c r="K221" t="s">
+        <v>54</v>
+      </c>
+      <c r="L221" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M221" t="s">
+        <v>67</v>
+      </c>
+      <c r="N221">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>701</v>
+      </c>
+      <c r="B222" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C222" t="s">
+        <v>702</v>
+      </c>
+      <c r="D222" t="s">
+        <v>34</v>
+      </c>
+      <c r="E222" t="s">
+        <v>21</v>
+      </c>
+      <c r="F222">
+        <v>2867</v>
+      </c>
+      <c r="G222" t="s">
+        <v>46</v>
+      </c>
+      <c r="H222" t="s">
+        <v>38</v>
+      </c>
+      <c r="J222" t="s">
+        <v>703</v>
+      </c>
+      <c r="K222" t="s">
+        <v>54</v>
+      </c>
+      <c r="L222" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M222" t="s">
+        <v>67</v>
+      </c>
+      <c r="N222">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>704</v>
+      </c>
+      <c r="B223" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C223" t="s">
+        <v>705</v>
+      </c>
+      <c r="D223" t="s">
+        <v>34</v>
+      </c>
+      <c r="E223" t="s">
+        <v>64</v>
+      </c>
+      <c r="F223">
+        <v>1830</v>
+      </c>
+      <c r="G223" t="s">
+        <v>63</v>
+      </c>
+      <c r="H223" t="s">
+        <v>52</v>
+      </c>
+      <c r="I223" t="s">
+        <v>706</v>
+      </c>
+      <c r="J223" t="s">
+        <v>707</v>
+      </c>
+      <c r="K223" t="s">
+        <v>56</v>
+      </c>
+      <c r="L223" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M223" t="s">
+        <v>67</v>
+      </c>
+      <c r="N223">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>708</v>
+      </c>
+      <c r="B224" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C224" s="26">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="D224" t="s">
+        <v>34</v>
+      </c>
+      <c r="E224" t="s">
+        <v>20</v>
+      </c>
+      <c r="F224">
+        <v>3458</v>
+      </c>
+      <c r="G224" t="s">
+        <v>51</v>
+      </c>
+      <c r="H224" t="s">
+        <v>11</v>
+      </c>
+      <c r="K224" t="s">
+        <v>616</v>
+      </c>
+      <c r="L224" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M224" t="s">
+        <v>67</v>
+      </c>
+      <c r="N224">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>709</v>
+      </c>
+      <c r="B225" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C225" t="s">
+        <v>710</v>
+      </c>
+      <c r="D225" t="s">
+        <v>34</v>
+      </c>
+      <c r="E225" t="s">
+        <v>16</v>
+      </c>
+      <c r="F225">
+        <v>6114</v>
+      </c>
+      <c r="G225" t="s">
+        <v>44</v>
+      </c>
+      <c r="H225" t="s">
+        <v>11</v>
+      </c>
+      <c r="I225" t="s">
+        <v>711</v>
+      </c>
+      <c r="J225" t="s">
+        <v>712</v>
+      </c>
+      <c r="K225" t="s">
+        <v>56</v>
+      </c>
+      <c r="L225" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M225" t="s">
+        <v>67</v>
+      </c>
+      <c r="N225">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>713</v>
+      </c>
+      <c r="B226" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C226" t="s">
+        <v>394</v>
+      </c>
+      <c r="D226" t="s">
+        <v>34</v>
+      </c>
+      <c r="E226" t="s">
+        <v>19</v>
+      </c>
+      <c r="F226">
+        <v>6091</v>
+      </c>
+      <c r="G226" t="s">
+        <v>43</v>
+      </c>
+      <c r="H226" t="s">
+        <v>11</v>
+      </c>
+      <c r="I226" s="27" t="s">
+        <v>714</v>
+      </c>
+      <c r="K226" t="s">
+        <v>54</v>
+      </c>
+      <c r="L226" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M226" t="s">
+        <v>67</v>
+      </c>
+      <c r="N226">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>715</v>
+      </c>
+      <c r="B227" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C227" t="s">
+        <v>716</v>
+      </c>
+      <c r="D227" t="s">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>23</v>
+      </c>
+      <c r="F227">
+        <v>2100</v>
+      </c>
+      <c r="G227" t="s">
+        <v>65</v>
+      </c>
+      <c r="H227" t="s">
+        <v>52</v>
+      </c>
+      <c r="I227" t="s">
+        <v>717</v>
+      </c>
+      <c r="K227" t="s">
+        <v>62</v>
+      </c>
+      <c r="L227" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M227" t="s">
+        <v>67</v>
+      </c>
+      <c r="N227">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>718</v>
+      </c>
+      <c r="B228" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C228" t="s">
+        <v>719</v>
+      </c>
+      <c r="D228" t="s">
+        <v>34</v>
+      </c>
+      <c r="E228" t="s">
+        <v>12</v>
+      </c>
+      <c r="F228">
+        <v>4017</v>
+      </c>
+      <c r="G228" t="s">
+        <v>199</v>
+      </c>
+      <c r="H228" t="s">
+        <v>35</v>
+      </c>
+      <c r="J228" t="s">
+        <v>720</v>
+      </c>
+      <c r="M228" t="s">
         <v>66</v>
       </c>
+      <c r="N228">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>721</v>
+      </c>
+      <c r="B229" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C229" s="26">
+        <v>0.44722222222222224</v>
+      </c>
+      <c r="D229" t="s">
+        <v>34</v>
+      </c>
+      <c r="E229" t="s">
+        <v>10</v>
+      </c>
+      <c r="F229">
+        <v>3267</v>
+      </c>
+      <c r="G229" t="s">
+        <v>44</v>
+      </c>
+      <c r="H229" t="s">
+        <v>37</v>
+      </c>
+      <c r="I229" t="s">
+        <v>722</v>
+      </c>
+      <c r="K229" t="s">
+        <v>56</v>
+      </c>
+      <c r="L229" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M229" t="s">
+        <v>67</v>
+      </c>
+      <c r="N229">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>723</v>
+      </c>
+      <c r="B230" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C230" t="s">
+        <v>253</v>
+      </c>
+      <c r="D230" t="s">
+        <v>34</v>
+      </c>
+      <c r="E230" t="s">
+        <v>13</v>
+      </c>
+      <c r="F230">
+        <v>4622</v>
+      </c>
+      <c r="G230" t="s">
+        <v>43</v>
+      </c>
+      <c r="H230" t="s">
+        <v>11</v>
+      </c>
+      <c r="J230" t="s">
+        <v>724</v>
+      </c>
+      <c r="K230" t="s">
+        <v>56</v>
+      </c>
+      <c r="L230" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M230" t="s">
+        <v>67</v>
+      </c>
+      <c r="N230">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>725</v>
+      </c>
+      <c r="B231" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C231" s="26">
+        <v>0.45694444444444443</v>
+      </c>
+      <c r="D231" t="s">
+        <v>34</v>
+      </c>
+      <c r="E231" t="s">
+        <v>20</v>
+      </c>
+      <c r="F231">
+        <v>3459</v>
+      </c>
+      <c r="G231" t="s">
+        <v>51</v>
+      </c>
+      <c r="H231" t="s">
+        <v>38</v>
+      </c>
+      <c r="I231" t="s">
+        <v>726</v>
+      </c>
+      <c r="K231" t="s">
+        <v>727</v>
+      </c>
+      <c r="L231" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M231" t="s">
+        <v>67</v>
+      </c>
+      <c r="N231">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>728</v>
+      </c>
+      <c r="B232" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C232" t="s">
+        <v>729</v>
+      </c>
+      <c r="D232" t="s">
+        <v>34</v>
+      </c>
+      <c r="E232" t="s">
+        <v>23</v>
+      </c>
+      <c r="F232">
+        <v>2111</v>
+      </c>
+      <c r="G232" t="s">
+        <v>65</v>
+      </c>
+      <c r="H232" t="s">
+        <v>11</v>
+      </c>
+      <c r="I232" t="s">
+        <v>730</v>
+      </c>
+      <c r="K232" t="s">
+        <v>731</v>
+      </c>
+      <c r="L232" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M232" t="s">
+        <v>67</v>
+      </c>
+      <c r="N232">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>732</v>
+      </c>
+      <c r="B233" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C233" t="s">
+        <v>729</v>
+      </c>
+      <c r="D233" t="s">
+        <v>34</v>
+      </c>
+      <c r="E233" t="s">
+        <v>19</v>
+      </c>
+      <c r="F233">
+        <v>5491</v>
+      </c>
+      <c r="G233" t="s">
+        <v>53</v>
+      </c>
+      <c r="H233" t="s">
+        <v>35</v>
+      </c>
+      <c r="K233" t="s">
+        <v>54</v>
+      </c>
+      <c r="L233" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M233" t="s">
+        <v>67</v>
+      </c>
+      <c r="N233">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>733</v>
+      </c>
+      <c r="B234" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C234" t="s">
+        <v>734</v>
+      </c>
+      <c r="D234" t="s">
+        <v>34</v>
+      </c>
+      <c r="E234" t="s">
+        <v>21</v>
+      </c>
+      <c r="F234">
+        <v>2883</v>
+      </c>
+      <c r="G234" t="s">
+        <v>46</v>
+      </c>
+      <c r="H234" t="s">
+        <v>52</v>
+      </c>
+      <c r="J234" t="s">
+        <v>735</v>
+      </c>
+      <c r="K234" t="s">
+        <v>56</v>
+      </c>
+      <c r="L234" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M234" t="s">
+        <v>67</v>
+      </c>
+      <c r="N234">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>736</v>
+      </c>
+      <c r="B235" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C235" t="s">
+        <v>130</v>
+      </c>
+      <c r="D235" t="s">
+        <v>34</v>
+      </c>
+      <c r="E235" t="s">
+        <v>314</v>
+      </c>
+      <c r="F235">
+        <v>2335</v>
+      </c>
+      <c r="G235" t="s">
+        <v>315</v>
+      </c>
+      <c r="H235" t="s">
+        <v>11</v>
+      </c>
+      <c r="M235" t="s">
+        <v>66</v>
+      </c>
+      <c r="N235">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>737</v>
+      </c>
+      <c r="B236" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C236" t="s">
+        <v>130</v>
+      </c>
+      <c r="D236" t="s">
+        <v>34</v>
+      </c>
+      <c r="E236" t="s">
+        <v>13</v>
+      </c>
+      <c r="F236">
+        <v>4622</v>
+      </c>
+      <c r="G236" t="s">
+        <v>378</v>
+      </c>
+      <c r="H236" t="s">
+        <v>35</v>
+      </c>
+      <c r="I236" t="s">
+        <v>738</v>
+      </c>
+      <c r="J236" t="s">
+        <v>739</v>
+      </c>
+      <c r="K236" t="s">
+        <v>54</v>
+      </c>
+      <c r="L236" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M236" t="s">
+        <v>67</v>
+      </c>
+      <c r="N236">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>740</v>
+      </c>
+      <c r="B237" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C237" t="s">
+        <v>741</v>
+      </c>
+      <c r="D237" t="s">
+        <v>34</v>
+      </c>
+      <c r="E237" t="s">
+        <v>9</v>
+      </c>
+      <c r="F237">
+        <v>5529</v>
+      </c>
+      <c r="G237" t="s">
+        <v>59</v>
+      </c>
+      <c r="H237" t="s">
+        <v>38</v>
+      </c>
+      <c r="I237" t="s">
+        <v>742</v>
+      </c>
+      <c r="J237" t="s">
+        <v>743</v>
+      </c>
+      <c r="K237" t="s">
+        <v>56</v>
+      </c>
+      <c r="L237" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M237" t="s">
+        <v>67</v>
+      </c>
+      <c r="N237">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>744</v>
+      </c>
+      <c r="B238" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C238" t="s">
+        <v>745</v>
+      </c>
+      <c r="D238" t="s">
+        <v>34</v>
+      </c>
+      <c r="E238" t="s">
+        <v>21</v>
+      </c>
+      <c r="F238">
+        <v>2886</v>
+      </c>
+      <c r="G238" t="s">
+        <v>46</v>
+      </c>
+      <c r="H238" t="s">
+        <v>52</v>
+      </c>
+      <c r="J238" t="s">
+        <v>746</v>
+      </c>
+      <c r="K238" t="s">
+        <v>56</v>
+      </c>
+      <c r="L238" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M238" t="s">
+        <v>67</v>
+      </c>
+      <c r="N238">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>747</v>
+      </c>
+      <c r="B239" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C239" t="s">
+        <v>436</v>
+      </c>
+      <c r="D239" t="s">
+        <v>34</v>
+      </c>
+      <c r="E239" t="s">
+        <v>19</v>
+      </c>
+      <c r="F239">
+        <v>6411</v>
+      </c>
+      <c r="G239" t="s">
+        <v>50</v>
+      </c>
+      <c r="H239" t="s">
+        <v>11</v>
+      </c>
+      <c r="I239" t="s">
+        <v>748</v>
+      </c>
+      <c r="K239" t="s">
+        <v>56</v>
+      </c>
+      <c r="L239" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M239" t="s">
+        <v>67</v>
+      </c>
+      <c r="N239">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>749</v>
+      </c>
+      <c r="B240" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C240" t="s">
+        <v>750</v>
+      </c>
+      <c r="D240" t="s">
+        <v>34</v>
+      </c>
+      <c r="E240" t="s">
+        <v>17</v>
+      </c>
+      <c r="F240">
+        <v>7235</v>
+      </c>
+      <c r="G240" t="s">
+        <v>51</v>
+      </c>
+      <c r="H240" t="s">
+        <v>38</v>
+      </c>
+      <c r="J240" t="s">
+        <v>751</v>
+      </c>
+      <c r="M240" t="s">
+        <v>66</v>
+      </c>
+      <c r="N240">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>752</v>
+      </c>
+      <c r="B241" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C241" t="s">
+        <v>753</v>
+      </c>
+      <c r="D241" t="s">
+        <v>34</v>
+      </c>
+      <c r="E241" t="s">
+        <v>17</v>
+      </c>
+      <c r="F241">
+        <v>7237</v>
+      </c>
+      <c r="G241" t="s">
+        <v>51</v>
+      </c>
+      <c r="H241" t="s">
+        <v>38</v>
+      </c>
+      <c r="J241" t="s">
+        <v>754</v>
+      </c>
+      <c r="K241" t="s">
+        <v>45</v>
+      </c>
+      <c r="L241" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M241" t="s">
+        <v>67</v>
+      </c>
+      <c r="N241">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>755</v>
+      </c>
+      <c r="B242" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C242" t="s">
+        <v>443</v>
+      </c>
+      <c r="D242" t="s">
+        <v>34</v>
+      </c>
+      <c r="E242" t="s">
+        <v>13</v>
+      </c>
+      <c r="F242">
+        <v>4307</v>
+      </c>
+      <c r="G242" t="s">
+        <v>57</v>
+      </c>
+      <c r="H242" t="s">
+        <v>11</v>
+      </c>
+      <c r="I242" t="s">
+        <v>756</v>
+      </c>
+      <c r="J242" t="s">
+        <v>757</v>
+      </c>
+      <c r="K242" t="s">
+        <v>54</v>
+      </c>
+      <c r="L242" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M242" t="s">
+        <v>67</v>
+      </c>
+      <c r="N242">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>758</v>
+      </c>
+      <c r="B243" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C243" t="s">
+        <v>759</v>
+      </c>
+      <c r="D243" t="s">
+        <v>34</v>
+      </c>
+      <c r="E243" t="s">
+        <v>9</v>
+      </c>
+      <c r="F243">
+        <v>8544</v>
+      </c>
+      <c r="G243" t="s">
+        <v>48</v>
+      </c>
+      <c r="H243" t="s">
+        <v>11</v>
+      </c>
+      <c r="I243" t="s">
+        <v>760</v>
+      </c>
+      <c r="J243" t="s">
+        <v>761</v>
+      </c>
+      <c r="M243" t="s">
+        <v>66</v>
+      </c>
+      <c r="N243">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>762</v>
+      </c>
+      <c r="B244" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C244" s="26">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="D244" t="s">
+        <v>34</v>
+      </c>
+      <c r="E244" t="s">
+        <v>20</v>
+      </c>
+      <c r="F244">
+        <v>3455</v>
+      </c>
+      <c r="G244" t="s">
+        <v>199</v>
+      </c>
+      <c r="H244" t="s">
+        <v>38</v>
+      </c>
+      <c r="K244" t="s">
+        <v>55</v>
+      </c>
+      <c r="L244" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M244" t="s">
+        <v>67</v>
+      </c>
+      <c r="N244">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>763</v>
+      </c>
+      <c r="B245" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C245" s="26">
+        <v>0.50763888888888886</v>
+      </c>
+      <c r="D245" t="s">
+        <v>34</v>
+      </c>
+      <c r="E245" t="s">
+        <v>20</v>
+      </c>
+      <c r="F245">
+        <v>7261</v>
+      </c>
+      <c r="G245" t="s">
+        <v>51</v>
+      </c>
+      <c r="H245" t="s">
+        <v>11</v>
+      </c>
+      <c r="K245" t="s">
+        <v>616</v>
+      </c>
+      <c r="L245" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M245" t="s">
+        <v>67</v>
+      </c>
+      <c r="N245">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>764</v>
+      </c>
+      <c r="B246" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C246" t="s">
+        <v>618</v>
+      </c>
+      <c r="D246" t="s">
+        <v>34</v>
+      </c>
+      <c r="E246" t="s">
+        <v>13</v>
+      </c>
+      <c r="F246">
+        <v>4325</v>
+      </c>
+      <c r="G246" t="s">
+        <v>48</v>
+      </c>
+      <c r="H246" t="s">
+        <v>52</v>
+      </c>
+      <c r="I246" t="s">
+        <v>765</v>
+      </c>
+      <c r="J246" t="s">
+        <v>766</v>
+      </c>
+      <c r="K246" t="s">
+        <v>54</v>
+      </c>
+      <c r="L246" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M246" t="s">
+        <v>67</v>
+      </c>
+      <c r="N246">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>767</v>
+      </c>
+      <c r="B247" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C247" t="s">
+        <v>768</v>
+      </c>
+      <c r="D247" t="s">
+        <v>34</v>
+      </c>
+      <c r="E247" t="s">
+        <v>12</v>
+      </c>
+      <c r="F247">
+        <v>4011</v>
+      </c>
+      <c r="G247" t="s">
+        <v>199</v>
+      </c>
+      <c r="H247" t="s">
+        <v>35</v>
+      </c>
+      <c r="J247" t="s">
+        <v>769</v>
+      </c>
+      <c r="K247" t="s">
+        <v>55</v>
+      </c>
+      <c r="L247" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M247" t="s">
+        <v>67</v>
+      </c>
+      <c r="N247">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>770</v>
+      </c>
+      <c r="B248" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C248" t="s">
+        <v>771</v>
+      </c>
+      <c r="D248" t="s">
+        <v>34</v>
+      </c>
+      <c r="E248" t="s">
+        <v>19</v>
+      </c>
+      <c r="F248">
+        <v>11159</v>
+      </c>
+      <c r="G248" t="s">
+        <v>50</v>
+      </c>
+      <c r="H248" t="s">
+        <v>11</v>
+      </c>
+      <c r="I248" t="s">
+        <v>772</v>
+      </c>
+      <c r="K248" t="s">
+        <v>56</v>
+      </c>
+      <c r="L248" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M248" t="s">
+        <v>67</v>
+      </c>
+      <c r="N248">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>773</v>
+      </c>
+      <c r="B249" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C249" t="s">
+        <v>774</v>
+      </c>
+      <c r="D249" t="s">
+        <v>34</v>
+      </c>
+      <c r="E249" t="s">
+        <v>19</v>
+      </c>
+      <c r="F249">
+        <v>6386</v>
+      </c>
+      <c r="G249" t="s">
+        <v>44</v>
+      </c>
+      <c r="H249" t="s">
+        <v>11</v>
+      </c>
+      <c r="I249" t="s">
+        <v>775</v>
+      </c>
+      <c r="K249" t="s">
+        <v>56</v>
+      </c>
+      <c r="L249" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M249" t="s">
+        <v>67</v>
+      </c>
+      <c r="N249">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>776</v>
+      </c>
+      <c r="B250" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C250" s="26">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="D250" t="s">
+        <v>34</v>
+      </c>
+      <c r="E250" t="s">
+        <v>10</v>
+      </c>
+      <c r="F250">
+        <v>5194</v>
+      </c>
+      <c r="G250" t="s">
+        <v>251</v>
+      </c>
+      <c r="H250" t="s">
+        <v>38</v>
+      </c>
+      <c r="I250" t="s">
+        <v>777</v>
+      </c>
+      <c r="J250" t="s">
+        <v>778</v>
+      </c>
+      <c r="K250" t="s">
+        <v>55</v>
+      </c>
+      <c r="L250" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M250" t="s">
+        <v>67</v>
+      </c>
+      <c r="N250">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>779</v>
+      </c>
+      <c r="B251" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C251" t="s">
+        <v>637</v>
+      </c>
+      <c r="D251" t="s">
+        <v>34</v>
+      </c>
+      <c r="E251" t="s">
+        <v>19</v>
+      </c>
+      <c r="F251">
+        <v>11259</v>
+      </c>
+      <c r="G251" t="s">
+        <v>50</v>
+      </c>
+      <c r="H251" t="s">
+        <v>11</v>
+      </c>
+      <c r="I251" t="s">
+        <v>780</v>
+      </c>
+      <c r="M251" t="s">
+        <v>66</v>
+      </c>
+      <c r="N251">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>781</v>
+      </c>
+      <c r="B252" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C252" t="s">
+        <v>782</v>
+      </c>
+      <c r="D252" t="s">
+        <v>34</v>
+      </c>
+      <c r="E252" t="s">
+        <v>13</v>
+      </c>
+      <c r="F252">
+        <v>4914</v>
+      </c>
+      <c r="G252" t="s">
+        <v>48</v>
+      </c>
+      <c r="H252" t="s">
+        <v>38</v>
+      </c>
+      <c r="I252" t="s">
+        <v>783</v>
+      </c>
+      <c r="J252" t="s">
+        <v>784</v>
+      </c>
+      <c r="M252" t="s">
+        <v>66</v>
+      </c>
+      <c r="N252">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>785</v>
+      </c>
+      <c r="B253" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C253" t="s">
+        <v>782</v>
+      </c>
+      <c r="D253" t="s">
+        <v>34</v>
+      </c>
+      <c r="E253" t="s">
+        <v>19</v>
+      </c>
+      <c r="F253">
+        <v>6386</v>
+      </c>
+      <c r="G253" t="s">
+        <v>44</v>
+      </c>
+      <c r="H253" t="s">
+        <v>38</v>
+      </c>
+      <c r="M253" t="s">
+        <v>66</v>
+      </c>
+      <c r="N253">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>786</v>
+      </c>
+      <c r="B254" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C254" t="s">
+        <v>787</v>
+      </c>
+      <c r="D254" t="s">
+        <v>34</v>
+      </c>
+      <c r="E254" t="s">
+        <v>21</v>
+      </c>
+      <c r="F254">
+        <v>2830</v>
+      </c>
+      <c r="G254" t="s">
+        <v>46</v>
+      </c>
+      <c r="H254" t="s">
+        <v>52</v>
+      </c>
+      <c r="J254" t="s">
+        <v>788</v>
+      </c>
+      <c r="K254" t="s">
+        <v>56</v>
+      </c>
+      <c r="L254" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M254" t="s">
+        <v>67</v>
+      </c>
+      <c r="N254">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" t="s">
+        <v>789</v>
+      </c>
+      <c r="B255" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C255" t="s">
+        <v>790</v>
+      </c>
+      <c r="D255" t="s">
+        <v>34</v>
+      </c>
+      <c r="E255" t="s">
+        <v>13</v>
+      </c>
+      <c r="F255">
+        <v>4880</v>
+      </c>
+      <c r="G255" t="s">
+        <v>43</v>
+      </c>
+      <c r="H255" t="s">
+        <v>11</v>
+      </c>
+      <c r="J255" t="s">
+        <v>791</v>
+      </c>
+      <c r="K255" t="s">
+        <v>54</v>
+      </c>
+      <c r="L255" s="25">
+        <v>46178</v>
+      </c>
+      <c r="M255" t="s">
+        <v>67</v>
+      </c>
+      <c r="N255">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A256" t="s">
+        <v>792</v>
+      </c>
+      <c r="B256" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C256" t="s">
+        <v>793</v>
+      </c>
+      <c r="D256" t="s">
+        <v>34</v>
+      </c>
+      <c r="E256" t="s">
+        <v>16</v>
+      </c>
+      <c r="F256">
+        <v>3818</v>
+      </c>
+      <c r="G256" t="s">
+        <v>254</v>
+      </c>
+      <c r="H256" t="s">
+        <v>41</v>
+      </c>
+      <c r="J256" t="s">
+        <v>794</v>
+      </c>
+      <c r="M256" t="s">
+        <v>66</v>
+      </c>
+      <c r="N256">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>795</v>
+      </c>
+      <c r="B257" s="25">
+        <v>46178</v>
+      </c>
+      <c r="C257" t="s">
+        <v>327</v>
+      </c>
+      <c r="D257" t="s">
+        <v>34</v>
+      </c>
+      <c r="E257" t="s">
+        <v>12</v>
+      </c>
+      <c r="F257">
+        <v>3444</v>
+      </c>
+      <c r="G257" t="s">
+        <v>43</v>
+      </c>
+      <c r="H257" t="s">
+        <v>11</v>
+      </c>
+      <c r="M257" t="s">
+        <v>66</v>
+      </c>
+      <c r="N257">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>796</v>
+      </c>
+      <c r="B258" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C258" t="s">
+        <v>699</v>
+      </c>
+      <c r="D258" t="s">
+        <v>34</v>
+      </c>
+      <c r="E258" t="s">
+        <v>13</v>
+      </c>
+      <c r="F258">
+        <v>4346</v>
+      </c>
+      <c r="G258" t="s">
+        <v>254</v>
+      </c>
+      <c r="H258" t="s">
+        <v>37</v>
+      </c>
+      <c r="J258" t="s">
+        <v>797</v>
+      </c>
+      <c r="M258" t="s">
+        <v>66</v>
+      </c>
+      <c r="N258">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>798</v>
+      </c>
+      <c r="B259" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C259" t="s">
+        <v>377</v>
+      </c>
+      <c r="D259" t="s">
+        <v>34</v>
+      </c>
+      <c r="E259" t="s">
+        <v>13</v>
+      </c>
+      <c r="F259">
+        <v>5258</v>
+      </c>
+      <c r="G259" t="s">
+        <v>251</v>
+      </c>
+      <c r="H259" t="s">
+        <v>37</v>
+      </c>
+      <c r="I259" s="27" t="s">
+        <v>799</v>
+      </c>
+      <c r="J259" t="s">
+        <v>800</v>
+      </c>
+      <c r="K259" t="s">
+        <v>54</v>
+      </c>
+      <c r="L259" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M259" t="s">
+        <v>67</v>
+      </c>
+      <c r="N259">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>801</v>
+      </c>
+      <c r="B260" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C260" t="s">
+        <v>534</v>
+      </c>
+      <c r="D260" t="s">
+        <v>34</v>
+      </c>
+      <c r="E260" t="s">
+        <v>23</v>
+      </c>
+      <c r="F260">
+        <v>2605</v>
+      </c>
+      <c r="G260" t="s">
+        <v>63</v>
+      </c>
+      <c r="H260" t="s">
+        <v>52</v>
+      </c>
+      <c r="I260" t="s">
+        <v>802</v>
+      </c>
+      <c r="K260" t="s">
+        <v>56</v>
+      </c>
+      <c r="L260" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M260" t="s">
+        <v>67</v>
+      </c>
+      <c r="N260">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>803</v>
+      </c>
+      <c r="B261" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C261" t="s">
+        <v>205</v>
+      </c>
+      <c r="D261" t="s">
+        <v>34</v>
+      </c>
+      <c r="E261" t="s">
+        <v>13</v>
+      </c>
+      <c r="F261">
+        <v>4356</v>
+      </c>
+      <c r="G261" t="s">
+        <v>251</v>
+      </c>
+      <c r="H261" t="s">
+        <v>11</v>
+      </c>
+      <c r="J261" t="s">
+        <v>804</v>
+      </c>
+      <c r="K261" t="s">
+        <v>54</v>
+      </c>
+      <c r="L261" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M261" t="s">
+        <v>67</v>
+      </c>
+      <c r="N261">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="262" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>805</v>
+      </c>
+      <c r="B262" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C262" s="26">
+        <v>0.40902777777777777</v>
+      </c>
+      <c r="D262" t="s">
+        <v>34</v>
+      </c>
+      <c r="E262" t="s">
+        <v>20</v>
+      </c>
+      <c r="F262">
+        <v>5583</v>
+      </c>
+      <c r="G262" t="s">
+        <v>40</v>
+      </c>
+      <c r="H262" t="s">
+        <v>11</v>
+      </c>
+      <c r="M262" t="s">
+        <v>66</v>
+      </c>
+      <c r="N262">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>806</v>
+      </c>
+      <c r="B263" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C263" t="s">
+        <v>92</v>
+      </c>
+      <c r="D263" t="s">
+        <v>34</v>
+      </c>
+      <c r="E263" t="s">
+        <v>9</v>
+      </c>
+      <c r="F263">
+        <v>7140</v>
+      </c>
+      <c r="G263" t="s">
+        <v>46</v>
+      </c>
+      <c r="H263" t="s">
+        <v>35</v>
+      </c>
+      <c r="I263" t="s">
+        <v>807</v>
+      </c>
+      <c r="J263" t="s">
+        <v>808</v>
+      </c>
+      <c r="K263" t="s">
+        <v>54</v>
+      </c>
+      <c r="L263" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M263" t="s">
+        <v>67</v>
+      </c>
+      <c r="N263">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>809</v>
+      </c>
+      <c r="B264" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C264" t="s">
+        <v>810</v>
+      </c>
+      <c r="D264" t="s">
+        <v>34</v>
+      </c>
+      <c r="E264" t="s">
+        <v>23</v>
+      </c>
+      <c r="F264">
+        <v>1955</v>
+      </c>
+      <c r="G264" t="s">
+        <v>63</v>
+      </c>
+      <c r="H264" t="s">
+        <v>37</v>
+      </c>
+      <c r="M264" t="s">
+        <v>66</v>
+      </c>
+      <c r="N264">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>811</v>
+      </c>
+      <c r="B265" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C265" t="s">
+        <v>556</v>
+      </c>
+      <c r="D265" t="s">
+        <v>34</v>
+      </c>
+      <c r="E265" t="s">
+        <v>17</v>
+      </c>
+      <c r="F265">
+        <v>4949</v>
+      </c>
+      <c r="G265" t="s">
+        <v>251</v>
+      </c>
+      <c r="H265" t="s">
+        <v>52</v>
+      </c>
+      <c r="I265" t="s">
+        <v>812</v>
+      </c>
+      <c r="J265" t="s">
+        <v>813</v>
+      </c>
+      <c r="K265" t="s">
+        <v>54</v>
+      </c>
+      <c r="L265" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M265" t="s">
+        <v>67</v>
+      </c>
+      <c r="N265">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>814</v>
+      </c>
+      <c r="B266" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C266" t="s">
+        <v>815</v>
+      </c>
+      <c r="D266" t="s">
+        <v>34</v>
+      </c>
+      <c r="E266" t="s">
+        <v>17</v>
+      </c>
+      <c r="F266">
+        <v>3215</v>
+      </c>
+      <c r="G266" t="s">
+        <v>44</v>
+      </c>
+      <c r="H266" t="s">
+        <v>11</v>
+      </c>
+      <c r="J266" t="s">
+        <v>816</v>
+      </c>
+      <c r="K266" t="s">
+        <v>56</v>
+      </c>
+      <c r="L266" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M266" t="s">
+        <v>67</v>
+      </c>
+      <c r="N266">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>817</v>
+      </c>
+      <c r="B267" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C267" t="s">
+        <v>818</v>
+      </c>
+      <c r="D267" t="s">
+        <v>34</v>
+      </c>
+      <c r="E267" t="s">
+        <v>9</v>
+      </c>
+      <c r="F267">
+        <v>7128</v>
+      </c>
+      <c r="G267" t="s">
+        <v>46</v>
+      </c>
+      <c r="H267" t="s">
+        <v>35</v>
+      </c>
+      <c r="J267" t="s">
+        <v>819</v>
+      </c>
+      <c r="K267" t="s">
+        <v>54</v>
+      </c>
+      <c r="L267" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M267" t="s">
+        <v>67</v>
+      </c>
+      <c r="N267">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>820</v>
+      </c>
+      <c r="B268" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C268" s="26">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="D268" t="s">
+        <v>34</v>
+      </c>
+      <c r="E268" t="s">
+        <v>210</v>
+      </c>
+      <c r="F268">
+        <v>4680</v>
+      </c>
+      <c r="G268" t="s">
+        <v>254</v>
+      </c>
+      <c r="H268" t="s">
+        <v>37</v>
+      </c>
+      <c r="I268" t="s">
+        <v>821</v>
+      </c>
+      <c r="M268" t="s">
+        <v>66</v>
+      </c>
+      <c r="N268">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>822</v>
+      </c>
+      <c r="B269" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C269" s="26">
+        <v>0.44166666666666665</v>
+      </c>
+      <c r="D269" t="s">
+        <v>34</v>
+      </c>
+      <c r="E269" t="s">
+        <v>20</v>
+      </c>
+      <c r="F269">
+        <v>11027</v>
+      </c>
+      <c r="G269" t="s">
+        <v>58</v>
+      </c>
+      <c r="H269" t="s">
+        <v>11</v>
+      </c>
+      <c r="K269" t="s">
+        <v>54</v>
+      </c>
+      <c r="L269" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M269" t="s">
+        <v>67</v>
+      </c>
+      <c r="N269">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>823</v>
+      </c>
+      <c r="B270" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C270" t="s">
+        <v>420</v>
+      </c>
+      <c r="D270" t="s">
+        <v>34</v>
+      </c>
+      <c r="E270" t="s">
+        <v>12</v>
+      </c>
+      <c r="F270">
+        <v>6229</v>
+      </c>
+      <c r="G270" t="s">
+        <v>44</v>
+      </c>
+      <c r="H270" t="s">
+        <v>41</v>
+      </c>
+      <c r="J270" t="s">
+        <v>824</v>
+      </c>
+      <c r="K270" t="s">
+        <v>55</v>
+      </c>
+      <c r="L270" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M270" t="s">
+        <v>67</v>
+      </c>
+      <c r="N270">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>825</v>
+      </c>
+      <c r="B271" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C271" t="s">
+        <v>248</v>
+      </c>
+      <c r="D271" t="s">
+        <v>34</v>
+      </c>
+      <c r="E271" t="s">
+        <v>14</v>
+      </c>
+      <c r="F271">
+        <v>4634</v>
+      </c>
+      <c r="G271" t="s">
+        <v>378</v>
+      </c>
+      <c r="H271" t="s">
+        <v>52</v>
+      </c>
+      <c r="I271" t="s">
+        <v>826</v>
+      </c>
+      <c r="J271" t="s">
+        <v>827</v>
+      </c>
+      <c r="K271" t="s">
+        <v>828</v>
+      </c>
+      <c r="L271" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M271" t="s">
+        <v>67</v>
+      </c>
+      <c r="N271">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>829</v>
+      </c>
+      <c r="B272" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C272" t="s">
+        <v>68</v>
+      </c>
+      <c r="D272" t="s">
+        <v>34</v>
+      </c>
+      <c r="E272" t="s">
+        <v>244</v>
+      </c>
+      <c r="F272">
+        <v>3470</v>
+      </c>
+      <c r="G272" t="s">
+        <v>199</v>
+      </c>
+      <c r="H272" t="s">
+        <v>37</v>
+      </c>
+      <c r="I272" t="s">
+        <v>830</v>
+      </c>
+      <c r="K272" t="s">
+        <v>55</v>
+      </c>
+      <c r="L272" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M272" t="s">
+        <v>67</v>
+      </c>
+      <c r="N272">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>831</v>
+      </c>
+      <c r="B273" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C273" t="s">
+        <v>24</v>
+      </c>
+      <c r="D273" t="s">
+        <v>34</v>
+      </c>
+      <c r="E273" t="s">
+        <v>12</v>
+      </c>
+      <c r="F273">
+        <v>7067</v>
+      </c>
+      <c r="G273" t="s">
+        <v>51</v>
+      </c>
+      <c r="H273" t="s">
+        <v>35</v>
+      </c>
+      <c r="J273" t="s">
+        <v>832</v>
+      </c>
+      <c r="M273" t="s">
+        <v>66</v>
+      </c>
+      <c r="N273">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>833</v>
+      </c>
+      <c r="B274" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C274" t="s">
+        <v>729</v>
+      </c>
+      <c r="D274" t="s">
+        <v>34</v>
+      </c>
+      <c r="E274" t="s">
+        <v>21</v>
+      </c>
+      <c r="F274">
+        <v>4056</v>
+      </c>
+      <c r="G274" t="s">
+        <v>40</v>
+      </c>
+      <c r="H274" t="s">
+        <v>607</v>
+      </c>
+      <c r="J274" t="s">
+        <v>834</v>
+      </c>
+      <c r="K274" t="s">
+        <v>54</v>
+      </c>
+      <c r="L274" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M274" t="s">
+        <v>67</v>
+      </c>
+      <c r="N274">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>835</v>
+      </c>
+      <c r="B275" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C275" t="s">
+        <v>836</v>
+      </c>
+      <c r="D275" t="s">
+        <v>34</v>
+      </c>
+      <c r="E275" t="s">
+        <v>14</v>
+      </c>
+      <c r="F275">
+        <v>4669</v>
+      </c>
+      <c r="G275" t="s">
+        <v>378</v>
+      </c>
+      <c r="H275" t="s">
+        <v>35</v>
+      </c>
+      <c r="J275" t="s">
+        <v>837</v>
+      </c>
+      <c r="K275" t="s">
+        <v>54</v>
+      </c>
+      <c r="L275" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M275" t="s">
+        <v>67</v>
+      </c>
+      <c r="N275">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>838</v>
+      </c>
+      <c r="B276" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C276" s="26">
+        <v>0.46250000000000002</v>
+      </c>
+      <c r="D276" t="s">
+        <v>34</v>
+      </c>
+      <c r="E276" t="s">
+        <v>20</v>
+      </c>
+      <c r="F276">
+        <v>3506</v>
+      </c>
+      <c r="G276" t="s">
+        <v>199</v>
+      </c>
+      <c r="H276" t="s">
+        <v>38</v>
+      </c>
+      <c r="K276" t="s">
+        <v>55</v>
+      </c>
+      <c r="L276" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M276" t="s">
+        <v>67</v>
+      </c>
+      <c r="N276">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>839</v>
+      </c>
+      <c r="B277" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C277" t="s">
+        <v>582</v>
+      </c>
+      <c r="D277" t="s">
+        <v>34</v>
+      </c>
+      <c r="E277" t="s">
+        <v>9</v>
+      </c>
+      <c r="F277">
+        <v>7403</v>
+      </c>
+      <c r="G277" t="s">
+        <v>46</v>
+      </c>
+      <c r="H277" t="s">
+        <v>35</v>
+      </c>
+      <c r="I277" t="s">
+        <v>840</v>
+      </c>
+      <c r="J277" t="s">
+        <v>841</v>
+      </c>
+      <c r="K277" t="s">
+        <v>842</v>
+      </c>
+      <c r="L277" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M277" t="s">
+        <v>67</v>
+      </c>
+      <c r="N277">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>843</v>
+      </c>
+      <c r="B278" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C278" t="s">
+        <v>844</v>
+      </c>
+      <c r="D278" t="s">
+        <v>34</v>
+      </c>
+      <c r="E278" t="s">
+        <v>16</v>
+      </c>
+      <c r="F278">
+        <v>5222</v>
+      </c>
+      <c r="G278" t="s">
+        <v>251</v>
+      </c>
+      <c r="H278" t="s">
+        <v>11</v>
+      </c>
+      <c r="I278" t="s">
+        <v>845</v>
+      </c>
+      <c r="J278" t="s">
+        <v>846</v>
+      </c>
+      <c r="K278" t="s">
+        <v>54</v>
+      </c>
+      <c r="L278" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M278" t="s">
+        <v>67</v>
+      </c>
+      <c r="N278">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>847</v>
+      </c>
+      <c r="B279" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C279" t="s">
+        <v>848</v>
+      </c>
+      <c r="D279" t="s">
+        <v>34</v>
+      </c>
+      <c r="E279" t="s">
+        <v>16</v>
+      </c>
+      <c r="F279">
+        <v>5247</v>
+      </c>
+      <c r="G279" t="s">
+        <v>251</v>
+      </c>
+      <c r="H279" t="s">
+        <v>37</v>
+      </c>
+      <c r="I279" t="s">
+        <v>849</v>
+      </c>
+      <c r="J279" t="s">
+        <v>850</v>
+      </c>
+      <c r="K279" t="s">
+        <v>54</v>
+      </c>
+      <c r="L279" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M279" t="s">
+        <v>67</v>
+      </c>
+      <c r="N279">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>851</v>
+      </c>
+      <c r="B280" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C280" t="s">
+        <v>750</v>
+      </c>
+      <c r="D280" t="s">
+        <v>34</v>
+      </c>
+      <c r="E280" t="s">
+        <v>17</v>
+      </c>
+      <c r="F280">
+        <v>5632</v>
+      </c>
+      <c r="G280" t="s">
+        <v>40</v>
+      </c>
+      <c r="H280" t="s">
+        <v>35</v>
+      </c>
+      <c r="J280" t="s">
+        <v>852</v>
+      </c>
+      <c r="K280" t="s">
+        <v>54</v>
+      </c>
+      <c r="L280" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M280" t="s">
+        <v>67</v>
+      </c>
+      <c r="N280">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>853</v>
+      </c>
+      <c r="B281" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C281" t="s">
+        <v>139</v>
+      </c>
+      <c r="D281" t="s">
+        <v>34</v>
+      </c>
+      <c r="E281" t="s">
+        <v>14</v>
+      </c>
+      <c r="F281">
+        <v>4654</v>
+      </c>
+      <c r="G281" t="s">
+        <v>378</v>
+      </c>
+      <c r="H281" t="s">
+        <v>35</v>
+      </c>
+      <c r="J281" t="s">
+        <v>854</v>
+      </c>
+      <c r="K281" t="s">
+        <v>54</v>
+      </c>
+      <c r="L281" s="25">
+        <v>46179</v>
+      </c>
+      <c r="M281" t="s">
+        <v>67</v>
+      </c>
+      <c r="N281">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>855</v>
+      </c>
+      <c r="B282" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C282" t="s">
+        <v>856</v>
+      </c>
+      <c r="D282" t="s">
+        <v>34</v>
+      </c>
+      <c r="E282" t="s">
+        <v>21</v>
+      </c>
+      <c r="F282">
+        <v>4062</v>
+      </c>
+      <c r="G282" t="s">
+        <v>61</v>
+      </c>
+      <c r="H282" t="s">
+        <v>52</v>
+      </c>
+      <c r="I282" t="s">
+        <v>857</v>
+      </c>
+      <c r="J282" t="s">
+        <v>858</v>
+      </c>
+      <c r="M282" t="s">
+        <v>66</v>
+      </c>
+      <c r="N282">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>859</v>
+      </c>
+      <c r="B283" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C283" t="s">
+        <v>860</v>
+      </c>
+      <c r="D283" t="s">
+        <v>34</v>
+      </c>
+      <c r="E283" t="s">
+        <v>12</v>
+      </c>
+      <c r="F283">
+        <v>5635</v>
+      </c>
+      <c r="G283" t="s">
+        <v>40</v>
+      </c>
+      <c r="H283" t="s">
+        <v>11</v>
+      </c>
+      <c r="J283" t="s">
+        <v>861</v>
+      </c>
+      <c r="M283" t="s">
+        <v>66</v>
+      </c>
+      <c r="N283">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>862</v>
+      </c>
+      <c r="B284" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C284" t="s">
+        <v>863</v>
+      </c>
+      <c r="D284" t="s">
+        <v>34</v>
+      </c>
+      <c r="E284" t="s">
+        <v>12</v>
+      </c>
+      <c r="F284">
+        <v>5604</v>
+      </c>
+      <c r="G284" t="s">
+        <v>44</v>
+      </c>
+      <c r="H284" t="s">
+        <v>35</v>
+      </c>
+      <c r="M284" t="s">
+        <v>66</v>
+      </c>
+      <c r="N284">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>864</v>
+      </c>
+      <c r="B285" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C285" t="s">
+        <v>473</v>
+      </c>
+      <c r="D285" t="s">
+        <v>34</v>
+      </c>
+      <c r="E285" t="s">
+        <v>12</v>
+      </c>
+      <c r="F285">
+        <v>5624</v>
+      </c>
+      <c r="G285" t="s">
+        <v>49</v>
+      </c>
+      <c r="H285" t="s">
+        <v>35</v>
+      </c>
+      <c r="M285" t="s">
+        <v>66</v>
+      </c>
+      <c r="N285">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>865</v>
+      </c>
+      <c r="B286" s="25">
+        <v>46179</v>
+      </c>
+      <c r="C286" t="s">
+        <v>473</v>
+      </c>
+      <c r="D286" t="s">
+        <v>34</v>
+      </c>
+      <c r="E286" t="s">
+        <v>12</v>
+      </c>
+      <c r="F286">
+        <v>7067</v>
+      </c>
+      <c r="G286" t="s">
+        <v>51</v>
+      </c>
+      <c r="H286" t="s">
+        <v>35</v>
+      </c>
+      <c r="J286" t="s">
+        <v>866</v>
+      </c>
+      <c r="M286" t="s">
+        <v>66</v>
+      </c>
+      <c r="N286">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>867</v>
+      </c>
+      <c r="B287" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C287" s="26">
+        <v>0.34166666666666667</v>
+      </c>
+      <c r="D287" t="s">
+        <v>34</v>
+      </c>
+      <c r="E287" t="s">
+        <v>10</v>
+      </c>
+      <c r="F287">
+        <v>4920</v>
+      </c>
+      <c r="G287" t="s">
+        <v>44</v>
+      </c>
+      <c r="H287" t="s">
+        <v>11</v>
+      </c>
+      <c r="I287" t="s">
+        <v>775</v>
+      </c>
+      <c r="J287" t="s">
+        <v>868</v>
+      </c>
+      <c r="K287" t="s">
+        <v>56</v>
+      </c>
+      <c r="L287" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M287" t="s">
+        <v>67</v>
+      </c>
+      <c r="N287">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>869</v>
+      </c>
+      <c r="B288" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C288" t="s">
+        <v>505</v>
+      </c>
+      <c r="D288" t="s">
+        <v>34</v>
+      </c>
+      <c r="E288" t="s">
+        <v>23</v>
+      </c>
+      <c r="F288">
+        <v>222</v>
+      </c>
+      <c r="G288" t="s">
+        <v>63</v>
+      </c>
+      <c r="H288" t="s">
+        <v>41</v>
+      </c>
+      <c r="I288" s="27" t="s">
+        <v>870</v>
+      </c>
+      <c r="K288" t="s">
+        <v>55</v>
+      </c>
+      <c r="L288" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M288" t="s">
+        <v>67</v>
+      </c>
+      <c r="N288">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>871</v>
+      </c>
+      <c r="B289" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C289" t="s">
+        <v>699</v>
+      </c>
+      <c r="D289" t="s">
+        <v>34</v>
+      </c>
+      <c r="E289" t="s">
+        <v>23</v>
+      </c>
+      <c r="F289">
+        <v>222</v>
+      </c>
+      <c r="G289" t="s">
+        <v>63</v>
+      </c>
+      <c r="H289" t="s">
+        <v>41</v>
+      </c>
+      <c r="I289" t="s">
+        <v>341</v>
+      </c>
+      <c r="K289" t="s">
+        <v>55</v>
+      </c>
+      <c r="L289" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M289" t="s">
+        <v>67</v>
+      </c>
+      <c r="N289">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>872</v>
+      </c>
+      <c r="B290" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C290" t="s">
+        <v>516</v>
+      </c>
+      <c r="D290" t="s">
+        <v>34</v>
+      </c>
+      <c r="E290" t="s">
+        <v>16</v>
+      </c>
+      <c r="F290">
+        <v>4165</v>
+      </c>
+      <c r="G290" t="s">
+        <v>36</v>
+      </c>
+      <c r="H290" t="s">
+        <v>11</v>
+      </c>
+      <c r="J290" t="s">
+        <v>873</v>
+      </c>
+      <c r="K290" t="s">
+        <v>45</v>
+      </c>
+      <c r="L290" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M290" t="s">
+        <v>67</v>
+      </c>
+      <c r="N290">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>874</v>
+      </c>
+      <c r="B291" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C291" s="26">
+        <v>0.37222222222222223</v>
+      </c>
+      <c r="D291" t="s">
+        <v>34</v>
+      </c>
+      <c r="E291" t="s">
+        <v>20</v>
+      </c>
+      <c r="F291">
+        <v>7317</v>
+      </c>
+      <c r="G291" t="s">
+        <v>44</v>
+      </c>
+      <c r="H291" t="s">
+        <v>11</v>
+      </c>
+      <c r="K291" t="s">
+        <v>56</v>
+      </c>
+      <c r="L291" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M291" t="s">
+        <v>67</v>
+      </c>
+      <c r="N291">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>875</v>
+      </c>
+      <c r="B292" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C292" t="s">
+        <v>373</v>
+      </c>
+      <c r="D292" t="s">
+        <v>34</v>
+      </c>
+      <c r="E292" t="s">
+        <v>12</v>
+      </c>
+      <c r="F292">
+        <v>3870</v>
+      </c>
+      <c r="G292" t="s">
+        <v>36</v>
+      </c>
+      <c r="H292" t="s">
+        <v>11</v>
+      </c>
+      <c r="J292" t="s">
+        <v>876</v>
+      </c>
+      <c r="M292" t="s">
+        <v>66</v>
+      </c>
+      <c r="N292">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>877</v>
+      </c>
+      <c r="B293" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C293" t="s">
+        <v>878</v>
+      </c>
+      <c r="D293" t="s">
+        <v>34</v>
+      </c>
+      <c r="E293" t="s">
+        <v>19</v>
+      </c>
+      <c r="F293">
+        <v>3654</v>
+      </c>
+      <c r="G293" t="s">
+        <v>39</v>
+      </c>
+      <c r="H293" t="s">
+        <v>11</v>
+      </c>
+      <c r="I293" t="s">
+        <v>879</v>
+      </c>
+      <c r="K293" t="s">
+        <v>55</v>
+      </c>
+      <c r="L293" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M293" t="s">
+        <v>67</v>
+      </c>
+      <c r="N293">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>880</v>
+      </c>
+      <c r="B294" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C294" t="s">
+        <v>538</v>
+      </c>
+      <c r="D294" t="s">
+        <v>34</v>
+      </c>
+      <c r="E294" t="s">
+        <v>13</v>
+      </c>
+      <c r="F294">
+        <v>2462</v>
+      </c>
+      <c r="G294" t="s">
+        <v>57</v>
+      </c>
+      <c r="H294" t="s">
+        <v>52</v>
+      </c>
+      <c r="I294" t="s">
+        <v>881</v>
+      </c>
+      <c r="J294" t="s">
+        <v>882</v>
+      </c>
+      <c r="M294" t="s">
+        <v>66</v>
+      </c>
+      <c r="N294">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>883</v>
+      </c>
+      <c r="B295" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C295" s="26">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="D295" t="s">
+        <v>34</v>
+      </c>
+      <c r="E295" t="s">
+        <v>20</v>
+      </c>
+      <c r="F295">
+        <v>7546</v>
+      </c>
+      <c r="G295" t="s">
+        <v>50</v>
+      </c>
+      <c r="H295" t="s">
+        <v>52</v>
+      </c>
+      <c r="K295" t="s">
+        <v>56</v>
+      </c>
+      <c r="L295" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M295" t="s">
+        <v>67</v>
+      </c>
+      <c r="N295">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>884</v>
+      </c>
+      <c r="B296" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C296" t="s">
+        <v>394</v>
+      </c>
+      <c r="D296" t="s">
+        <v>34</v>
+      </c>
+      <c r="E296" t="s">
+        <v>17</v>
+      </c>
+      <c r="F296">
+        <v>4956</v>
+      </c>
+      <c r="G296" t="s">
+        <v>58</v>
+      </c>
+      <c r="H296" t="s">
+        <v>11</v>
+      </c>
+      <c r="I296" t="s">
+        <v>885</v>
+      </c>
+      <c r="J296" t="s">
+        <v>886</v>
+      </c>
+      <c r="K296" t="s">
+        <v>54</v>
+      </c>
+      <c r="L296" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M296" t="s">
+        <v>67</v>
+      </c>
+      <c r="N296">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>887</v>
+      </c>
+      <c r="B297" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C297" t="s">
+        <v>716</v>
+      </c>
+      <c r="D297" t="s">
+        <v>34</v>
+      </c>
+      <c r="E297" t="s">
+        <v>13</v>
+      </c>
+      <c r="F297">
+        <v>2797</v>
+      </c>
+      <c r="G297" t="s">
+        <v>36</v>
+      </c>
+      <c r="H297" t="s">
+        <v>11</v>
+      </c>
+      <c r="J297" t="s">
+        <v>888</v>
+      </c>
+      <c r="K297" t="s">
+        <v>45</v>
+      </c>
+      <c r="L297" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M297" t="s">
+        <v>67</v>
+      </c>
+      <c r="N297">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>889</v>
+      </c>
+      <c r="B298" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C298" t="s">
+        <v>890</v>
+      </c>
+      <c r="D298" t="s">
+        <v>34</v>
+      </c>
+      <c r="E298" t="s">
+        <v>13</v>
+      </c>
+      <c r="F298">
+        <v>2797</v>
+      </c>
+      <c r="G298" t="s">
+        <v>36</v>
+      </c>
+      <c r="H298" t="s">
+        <v>52</v>
+      </c>
+      <c r="I298" t="s">
+        <v>881</v>
+      </c>
+      <c r="J298" t="s">
+        <v>891</v>
+      </c>
+      <c r="M298" t="s">
+        <v>66</v>
+      </c>
+      <c r="N298">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A299" t="s">
+        <v>892</v>
+      </c>
+      <c r="B299" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C299" s="26">
+        <v>0.41805555555555557</v>
+      </c>
+      <c r="D299" t="s">
+        <v>34</v>
+      </c>
+      <c r="E299" t="s">
+        <v>210</v>
+      </c>
+      <c r="F299">
+        <v>11302</v>
+      </c>
+      <c r="G299" t="s">
+        <v>50</v>
+      </c>
+      <c r="H299" t="s">
+        <v>37</v>
+      </c>
+      <c r="I299" t="s">
+        <v>893</v>
+      </c>
+      <c r="J299" t="s">
+        <v>894</v>
+      </c>
+      <c r="K299" t="s">
+        <v>54</v>
+      </c>
+      <c r="L299" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M299" t="s">
+        <v>67</v>
+      </c>
+      <c r="N299">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A300" t="s">
+        <v>895</v>
+      </c>
+      <c r="B300" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C300" t="s">
+        <v>810</v>
+      </c>
+      <c r="D300" t="s">
+        <v>34</v>
+      </c>
+      <c r="E300" t="s">
+        <v>64</v>
+      </c>
+      <c r="F300">
+        <v>1391</v>
+      </c>
+      <c r="G300" t="s">
+        <v>63</v>
+      </c>
+      <c r="H300" t="s">
+        <v>11</v>
+      </c>
+      <c r="I300" t="s">
+        <v>896</v>
+      </c>
+      <c r="J300" t="s">
+        <v>897</v>
+      </c>
+      <c r="K300" t="s">
+        <v>56</v>
+      </c>
+      <c r="L300" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M300" t="s">
+        <v>67</v>
+      </c>
+      <c r="N300">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" t="s">
+        <v>898</v>
+      </c>
+      <c r="B301" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C301" t="s">
+        <v>102</v>
+      </c>
+      <c r="D301" t="s">
+        <v>34</v>
+      </c>
+      <c r="E301" t="s">
+        <v>16</v>
+      </c>
+      <c r="F301">
+        <v>3921</v>
+      </c>
+      <c r="G301" t="s">
+        <v>36</v>
+      </c>
+      <c r="H301" t="s">
+        <v>11</v>
+      </c>
+      <c r="I301" t="s">
+        <v>899</v>
+      </c>
+      <c r="J301" t="s">
+        <v>900</v>
+      </c>
+      <c r="K301" t="s">
+        <v>56</v>
+      </c>
+      <c r="L301" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M301" t="s">
+        <v>67</v>
+      </c>
+      <c r="N301">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302" t="s">
+        <v>901</v>
+      </c>
+      <c r="B302" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C302" t="s">
+        <v>553</v>
+      </c>
+      <c r="D302" t="s">
+        <v>34</v>
+      </c>
+      <c r="E302" t="s">
+        <v>19</v>
+      </c>
+      <c r="F302">
+        <v>3656</v>
+      </c>
+      <c r="G302" t="s">
+        <v>43</v>
+      </c>
+      <c r="H302" t="s">
+        <v>11</v>
+      </c>
+      <c r="I302" s="27" t="s">
+        <v>902</v>
+      </c>
+      <c r="K302" t="s">
+        <v>54</v>
+      </c>
+      <c r="L302" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M302" t="s">
+        <v>67</v>
+      </c>
+      <c r="N302">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
+        <v>903</v>
+      </c>
+      <c r="B303" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C303" t="s">
+        <v>225</v>
+      </c>
+      <c r="D303" t="s">
+        <v>34</v>
+      </c>
+      <c r="E303" t="s">
+        <v>12</v>
+      </c>
+      <c r="F303">
+        <v>3919</v>
+      </c>
+      <c r="G303" t="s">
+        <v>36</v>
+      </c>
+      <c r="H303" t="s">
+        <v>11</v>
+      </c>
+      <c r="J303" t="s">
+        <v>904</v>
+      </c>
+      <c r="M303" t="s">
+        <v>66</v>
+      </c>
+      <c r="N303">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
+        <v>905</v>
+      </c>
+      <c r="B304" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C304" s="26">
+        <v>0.42569444444444443</v>
+      </c>
+      <c r="D304" t="s">
+        <v>34</v>
+      </c>
+      <c r="E304" t="s">
+        <v>20</v>
+      </c>
+      <c r="F304">
+        <v>7316</v>
+      </c>
+      <c r="G304" t="s">
+        <v>51</v>
+      </c>
+      <c r="H304" t="s">
+        <v>38</v>
+      </c>
+      <c r="M304" t="s">
+        <v>66</v>
+      </c>
+      <c r="N304">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
+        <v>906</v>
+      </c>
+      <c r="B305" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C305" t="s">
+        <v>907</v>
+      </c>
+      <c r="D305" t="s">
+        <v>34</v>
+      </c>
+      <c r="E305" t="s">
+        <v>21</v>
+      </c>
+      <c r="F305">
+        <v>6490</v>
+      </c>
+      <c r="G305" t="s">
+        <v>49</v>
+      </c>
+      <c r="H305" t="s">
+        <v>37</v>
+      </c>
+      <c r="J305" t="s">
+        <v>908</v>
+      </c>
+      <c r="K305" t="s">
+        <v>909</v>
+      </c>
+      <c r="L305" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M305" t="s">
+        <v>67</v>
+      </c>
+      <c r="N305">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
+        <v>910</v>
+      </c>
+      <c r="B306" s="25">
+        <v>46181</v>
+      </c>
+      <c r="C306" t="s">
+        <v>230</v>
+      </c>
+      <c r="D306" t="s">
+        <v>34</v>
+      </c>
+      <c r="E306" t="s">
+        <v>12</v>
+      </c>
+      <c r="F306">
+        <v>4894</v>
+      </c>
+      <c r="G306" t="s">
+        <v>57</v>
+      </c>
+      <c r="H306" t="s">
+        <v>41</v>
+      </c>
+      <c r="J306" t="s">
+        <v>911</v>
+      </c>
+      <c r="K306" t="s">
+        <v>45</v>
+      </c>
+      <c r="L306" s="25">
+        <v>46181</v>
+      </c>
+      <c r="M306" t="s">
+        <v>67</v>
+      </c>
+      <c r="N306">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="J5" r:id="rId1" xr:uid="{627C6E89-9DBD-4C2E-A5A2-3D5DB0916D84}"/>
-    <hyperlink ref="J7" r:id="rId2" xr:uid="{239098B3-0078-454E-8BEA-CBA7AD9759C9}"/>
-    <hyperlink ref="J8" r:id="rId3" xr:uid="{0FD9EA25-65A2-44D4-A14A-74B2982DB8F4}"/>
-    <hyperlink ref="J10" r:id="rId4" xr:uid="{5089EE65-C897-4D1A-87B4-66FB58666BE3}"/>
-    <hyperlink ref="J13" r:id="rId5" xr:uid="{FA7DF0D5-F93B-4147-B96A-B7177C7D3AA4}"/>
-    <hyperlink ref="J14" r:id="rId6" xr:uid="{9B9E4944-0798-4B19-937B-D45974A44696}"/>
-    <hyperlink ref="J17" r:id="rId7" xr:uid="{142D0237-1B90-4B09-9C6D-290ABADCE11A}"/>
-    <hyperlink ref="J19" r:id="rId8" xr:uid="{850325CF-B171-4EA6-8216-D4E86C337B4E}"/>
-    <hyperlink ref="J20" r:id="rId9" xr:uid="{8BA5E10F-C875-4B3A-AF62-0769386804FD}"/>
-    <hyperlink ref="J21" r:id="rId10" xr:uid="{CA8EC862-61AE-4517-B072-3666EACD197F}"/>
-    <hyperlink ref="J24" r:id="rId11" xr:uid="{128F481E-434D-464F-BD56-CD1D09A751BD}"/>
-    <hyperlink ref="J25" r:id="rId12" xr:uid="{B5CC020B-8A0D-45A5-9026-E7EDE4D14407}"/>
-    <hyperlink ref="J26" r:id="rId13" xr:uid="{22B019E9-2FBC-423E-87BB-17C68DD7721F}"/>
-    <hyperlink ref="J27" r:id="rId14" xr:uid="{A46E892A-BE33-423B-A850-4CD1E107D67C}"/>
-    <hyperlink ref="J29" r:id="rId15" xr:uid="{1B9B0DCF-B8D0-44EC-B2EF-CBA2527D7DD0}"/>
-    <hyperlink ref="J30" r:id="rId16" xr:uid="{14D86E66-35FE-452C-B1E1-EC12C5A48DBA}"/>
-    <hyperlink ref="J31" r:id="rId17" xr:uid="{69DD3FDD-6D95-46D9-9566-4A6C63CA993A}"/>
-    <hyperlink ref="J34" r:id="rId18" xr:uid="{9E8DC370-65F3-4973-A50D-116C078769B6}"/>
-    <hyperlink ref="J35" r:id="rId19" xr:uid="{E5500600-3E67-4175-94F4-9E8A587FD06A}"/>
-    <hyperlink ref="J36" r:id="rId20" xr:uid="{971016C4-CC8E-4F57-9ECC-E270F5A04F5C}"/>
-    <hyperlink ref="J37" r:id="rId21" xr:uid="{45D7297D-2F97-4857-B759-33A6FC910B2B}"/>
-    <hyperlink ref="J38" r:id="rId22" xr:uid="{7336FAB3-8312-40AA-8CD9-AF8B4F480AC7}"/>
-    <hyperlink ref="J46" r:id="rId23" xr:uid="{3E34D50F-69EC-433E-877D-F7EEFC30A451}"/>
-    <hyperlink ref="J47" r:id="rId24" xr:uid="{A95D3111-6CF8-4E22-A879-9897BB8FE68A}"/>
-    <hyperlink ref="J48" r:id="rId25" xr:uid="{5E6C2B39-84A4-4D0C-9C6C-B21670C9B6B5}"/>
-    <hyperlink ref="J49" r:id="rId26" xr:uid="{5E68AD96-6AE4-4FA5-BBDD-B308F587485E}"/>
-    <hyperlink ref="J50" r:id="rId27" xr:uid="{E254320F-E81A-4AC6-AA58-76E1BF425F0F}"/>
-    <hyperlink ref="J52" r:id="rId28" xr:uid="{189F9142-041A-458D-8742-CDBB71EC056B}"/>
-    <hyperlink ref="J53" r:id="rId29" xr:uid="{8EB81BD7-020B-47E9-96EA-1E3ACEF59154}"/>
-    <hyperlink ref="J54" r:id="rId30" xr:uid="{5377AF18-F33E-45A5-A97F-AFFD905EA1E7}"/>
-    <hyperlink ref="J56" r:id="rId31" xr:uid="{4E9C266D-0AB9-4D0C-BC18-58D97AD0152F}"/>
-    <hyperlink ref="J59" r:id="rId32" xr:uid="{DC506E5A-616A-4E89-B529-F292384B1F6D}"/>
-    <hyperlink ref="J61" r:id="rId33" xr:uid="{E7943732-2E44-4BB4-9AC3-55079FA04025}"/>
-    <hyperlink ref="J62" r:id="rId34" xr:uid="{8A5C4EBE-9BD8-4D1D-9141-A98339914D0A}"/>
-    <hyperlink ref="J63" r:id="rId35" xr:uid="{9AD534CD-4C3E-40F0-B250-C01CCE70FD43}"/>
-    <hyperlink ref="J64" r:id="rId36" xr:uid="{3A9E604E-D756-4979-B1A7-AECFA0A2A480}"/>
-    <hyperlink ref="J69" r:id="rId37" xr:uid="{75039D72-F3C8-4972-8CF6-4F697B16F7A9}"/>
-    <hyperlink ref="J71" r:id="rId38" xr:uid="{D0152508-D35D-4373-B190-CADA895718E3}"/>
-    <hyperlink ref="J72" r:id="rId39" xr:uid="{B611FC16-4FE6-4A8F-B524-42BED7322E3F}"/>
-    <hyperlink ref="J73" r:id="rId40" xr:uid="{24017F17-0261-4C21-984E-1357462BD008}"/>
-    <hyperlink ref="J74" r:id="rId41" xr:uid="{5A128042-20B1-46DF-95D2-AD98601058A9}"/>
-    <hyperlink ref="J75" r:id="rId42" xr:uid="{92BAB7D6-CE6A-4CB9-AFA2-15BFEB9FCD72}"/>
-    <hyperlink ref="J76" r:id="rId43" xr:uid="{DC37B963-AEFB-4F06-B969-91BC897B4547}"/>
-    <hyperlink ref="J78" r:id="rId44" xr:uid="{91A071D4-A8CA-4D3B-97D5-C67FB2EDFAE0}"/>
-    <hyperlink ref="J80" r:id="rId45" xr:uid="{0D09AD65-12E5-49CD-A6FD-F48351F72920}"/>
-    <hyperlink ref="J86" r:id="rId46" xr:uid="{0F0F4D67-3133-42C8-AE72-58977E575D62}"/>
-    <hyperlink ref="J88" r:id="rId47" xr:uid="{C6D7A1B6-9062-4BCF-933B-98EBC7411F7F}"/>
-    <hyperlink ref="J89" r:id="rId48" xr:uid="{E3069E2F-8D64-4EDE-969E-B6C7A8919821}"/>
-    <hyperlink ref="J90" r:id="rId49" xr:uid="{CAD78EF1-63F4-4AA2-B05A-E0F179A8FB4A}"/>
-    <hyperlink ref="J92" r:id="rId50" xr:uid="{A7220E7F-BDAD-4231-A121-B1B1F8EFE1B2}"/>
-    <hyperlink ref="J94" r:id="rId51" xr:uid="{F662B31D-0316-48DA-A0D7-6FF37534FC02}"/>
-    <hyperlink ref="J95" r:id="rId52" xr:uid="{7C405F57-364B-47E8-A426-882639A67BFF}"/>
-    <hyperlink ref="J96" r:id="rId53" xr:uid="{61808BAA-CE96-44C9-822F-6C65D174F3B6}"/>
-    <hyperlink ref="J101" r:id="rId54" xr:uid="{DBEFDA6B-300A-4E2A-8236-4A7C0A68A0AC}"/>
-    <hyperlink ref="J103" r:id="rId55" xr:uid="{27796B2B-91BD-4336-A5E8-FBBBB2579CA7}"/>
-    <hyperlink ref="J104" r:id="rId56" xr:uid="{8D97AE5F-1A92-49EC-9F6F-8ECAEA443A7A}"/>
-    <hyperlink ref="J105" r:id="rId57" xr:uid="{B23E0C3D-74C6-4A4F-B999-6B394ED30460}"/>
-    <hyperlink ref="J106" r:id="rId58" xr:uid="{7C35CEE5-922C-4AF2-A0C4-8674D5508BD8}"/>
-    <hyperlink ref="J107" r:id="rId59" xr:uid="{6AC47189-DF9A-4EEA-9653-5DC479BE4012}"/>
-    <hyperlink ref="J109" r:id="rId60" xr:uid="{6115F409-D8FF-4A13-B800-775594951C41}"/>
-    <hyperlink ref="J110" r:id="rId61" xr:uid="{A64AA35B-78AB-4F07-9C2B-AFE33DF3D2A3}"/>
-    <hyperlink ref="J111" r:id="rId62" xr:uid="{E1C0080D-10C0-425D-81DC-D9D7EDF7DA44}"/>
-    <hyperlink ref="J112" r:id="rId63" xr:uid="{43BA66B3-C8FC-4ACD-BA77-40C09B96618D}"/>
-    <hyperlink ref="J113" r:id="rId64" xr:uid="{F713FFA4-DF9B-4267-A36C-F2327F33441E}"/>
-    <hyperlink ref="J114" r:id="rId65" xr:uid="{F0995A35-01B3-4C1C-A847-9E7CCFF2B032}"/>
-    <hyperlink ref="J116" r:id="rId66" xr:uid="{8CFF019A-B7B2-4BA5-8FEC-174891A40B6E}"/>
-    <hyperlink ref="J117" r:id="rId67" xr:uid="{BF64304A-8056-46E5-9F69-DEDA7AF1AB17}"/>
-    <hyperlink ref="J118" r:id="rId68" xr:uid="{3E1F451B-1AB7-4199-BD68-B87E73D32013}"/>
-    <hyperlink ref="J119" r:id="rId69" xr:uid="{2E7A7316-B3D2-4735-A961-24F1E16CF097}"/>
-    <hyperlink ref="J120" r:id="rId70" xr:uid="{97578CAF-9D41-4DB8-8816-4171C74FCEDF}"/>
-    <hyperlink ref="J121" r:id="rId71" xr:uid="{2AE20807-8841-4E6F-8B82-E25A8169BB09}"/>
-    <hyperlink ref="J124" r:id="rId72" xr:uid="{87925EA9-1A3A-455A-BCB4-4FE65C8E187F}"/>
-    <hyperlink ref="J128" r:id="rId73" xr:uid="{94D8E496-8C3F-401C-8CF5-DD8C43C2AA4D}"/>
-    <hyperlink ref="J129" r:id="rId74" xr:uid="{127CFDC8-6B51-4636-AE9C-1348216B7D64}"/>
-    <hyperlink ref="J132" r:id="rId75" xr:uid="{96668B7E-279D-481B-BE7E-11D02F299779}"/>
-    <hyperlink ref="J134" r:id="rId76" xr:uid="{18C567DB-7B9B-4FEB-91C0-05CA8EC82A5F}"/>
-    <hyperlink ref="J135" r:id="rId77" xr:uid="{9C0BBD4B-9C01-4583-9DB4-7F0EF59562E6}"/>
-    <hyperlink ref="J136" r:id="rId78" xr:uid="{8971B9F3-24B5-4CDA-ABD7-B1B0DF7DB1C8}"/>
-    <hyperlink ref="J140" r:id="rId79" xr:uid="{EA797C36-C9AF-4C45-97D1-DC7CE62FA9B0}"/>
-    <hyperlink ref="J142" r:id="rId80" xr:uid="{E4208D86-2EFC-4758-BC7F-96F8C93629F8}"/>
-    <hyperlink ref="J143" r:id="rId81" xr:uid="{22F2A6A8-ADBC-4108-BE58-1E383BEA301C}"/>
-    <hyperlink ref="J144" r:id="rId82" xr:uid="{90400B51-0C29-48EA-908F-2008B9B85049}"/>
-    <hyperlink ref="J145" r:id="rId83" xr:uid="{2D0DD44F-7665-4100-95AC-F91BEB6EE8B1}"/>
-    <hyperlink ref="J147" r:id="rId84" xr:uid="{4E5AF93F-72DE-4862-BA41-1397DF12BCDE}"/>
-    <hyperlink ref="J149" r:id="rId85" xr:uid="{9502F4D1-71AD-452F-917B-1BB2C7AD1F76}"/>
-    <hyperlink ref="J150" r:id="rId86" xr:uid="{B7CCBC89-8134-414C-B32D-FC0DF0419C41}"/>
-    <hyperlink ref="J151" r:id="rId87" xr:uid="{61056907-F8F7-4120-957F-41C89AE38151}"/>
-    <hyperlink ref="J152" r:id="rId88" xr:uid="{1B56FC60-1F66-49ED-842D-BB7FBD6EB630}"/>
-    <hyperlink ref="J153" r:id="rId89" xr:uid="{C01A5452-E0F6-45FB-BFD4-88CAD94ADEBF}"/>
-    <hyperlink ref="J154" r:id="rId90" xr:uid="{94AFBF48-7091-4D16-B7FC-C6D1366ABD0F}"/>
-    <hyperlink ref="J155" r:id="rId91" xr:uid="{AB9D5684-8B27-4EF9-8928-F267DEE0EC72}"/>
-    <hyperlink ref="J156" r:id="rId92" xr:uid="{3E8E4F10-523E-4B29-B1E3-AFB05BC487E9}"/>
-    <hyperlink ref="J159" r:id="rId93" xr:uid="{F0806740-91DC-4B99-8395-1B756C021293}"/>
-    <hyperlink ref="J160" r:id="rId94" xr:uid="{9B0D4483-4E49-400E-8B75-D35FEA1EA07F}"/>
-    <hyperlink ref="J161" r:id="rId95" xr:uid="{8F4F7859-E8EB-4F14-8F2F-26B4F795C579}"/>
-    <hyperlink ref="J162" r:id="rId96" xr:uid="{53FC1D03-F57F-40BF-B35C-14805D85CB8D}"/>
-    <hyperlink ref="J164" r:id="rId97" xr:uid="{8CB1482A-6509-462A-B40C-1D1C14A23C7D}"/>
-    <hyperlink ref="J165" r:id="rId98" xr:uid="{E9D3EDF4-2DBD-47D6-BE74-99F525B67253}"/>
-    <hyperlink ref="J167" r:id="rId99" xr:uid="{03EE1C88-D369-4497-8162-65EC59A892B0}"/>
-    <hyperlink ref="J168" r:id="rId100" xr:uid="{BB7CCA26-1406-46EB-89B8-58C79A09F539}"/>
-    <hyperlink ref="J169" r:id="rId101" xr:uid="{CF28DF22-03B6-4816-82F6-A606515D59F2}"/>
-    <hyperlink ref="J171" r:id="rId102" xr:uid="{F83437CF-925A-4E17-A3AC-AB31014F28EC}"/>
-    <hyperlink ref="J172" r:id="rId103" xr:uid="{98ECD5FA-3880-42B5-AB53-B5108F02D3F6}"/>
-    <hyperlink ref="J173" r:id="rId104" xr:uid="{B4F9F3EA-A086-4229-8157-B0DC6B5AAEB3}"/>
-    <hyperlink ref="J177" r:id="rId105" xr:uid="{976A502D-1F94-4F8A-A8BA-3F84E338735B}"/>
-    <hyperlink ref="J178" r:id="rId106" xr:uid="{A52770BD-3775-4B3A-9EAD-05BAE4C3D6A0}"/>
-    <hyperlink ref="J181" r:id="rId107" xr:uid="{4D9598C1-9F15-49FD-8B5D-5BD9D2FCFFAD}"/>
-    <hyperlink ref="J182" r:id="rId108" xr:uid="{BCD11B64-A793-4984-95CA-705165DD200F}"/>
-    <hyperlink ref="J184" r:id="rId109" xr:uid="{125F82DE-9D14-43BB-B3C7-8CD30377BE61}"/>
-    <hyperlink ref="J186" r:id="rId110" xr:uid="{23A32092-0538-43CB-9D14-FA2E2F917FFA}"/>
-    <hyperlink ref="J190" r:id="rId111" xr:uid="{AE54CFCA-D130-4A19-9465-94743BC52385}"/>
-    <hyperlink ref="J191" r:id="rId112" xr:uid="{C78A73A3-795C-4EE7-85A6-82040242AA6B}"/>
-    <hyperlink ref="J192" r:id="rId113" xr:uid="{58772FFA-0BA7-40BD-845B-FC7479791AAF}"/>
-    <hyperlink ref="J193" r:id="rId114" xr:uid="{2DAC8ED3-8F2E-40A5-9925-CC162D52470F}"/>
-    <hyperlink ref="J194" r:id="rId115" xr:uid="{DF9A186E-AEA0-481C-94DF-D42815AFC22C}"/>
-    <hyperlink ref="J195" r:id="rId116" xr:uid="{7F4DDFA6-C1A6-4A4F-835B-038F962EAA8D}"/>
-    <hyperlink ref="J196" r:id="rId117" xr:uid="{265F618B-8B46-4147-ABF8-3C7182C15BFE}"/>
-    <hyperlink ref="J199" r:id="rId118" xr:uid="{CD62F323-889E-47B7-B94A-6B94E60E6899}"/>
-    <hyperlink ref="J201" r:id="rId119" xr:uid="{1FD85E70-2F1E-4A14-B8E5-9E866A26DD49}"/>
-    <hyperlink ref="J202" r:id="rId120" xr:uid="{35F25FD2-86D5-4E6B-836F-75DA7345DB7B}"/>
-    <hyperlink ref="J203" r:id="rId121" xr:uid="{2F03F93F-DDB8-46BA-A592-420FDFB70FC4}"/>
-    <hyperlink ref="J205" r:id="rId122" xr:uid="{E5DE7C7B-CCA5-4409-8F85-52C1E584860C}"/>
-    <hyperlink ref="J207" r:id="rId123" xr:uid="{C89270FB-AEC9-4CCC-98DF-60D167FCC579}"/>
-    <hyperlink ref="J209" r:id="rId124" xr:uid="{25C9A4BE-FC3D-42EB-B119-B2762237468E}"/>
-    <hyperlink ref="J210" r:id="rId125" xr:uid="{E4DFCFFB-2D86-4764-BFC6-97A5DA5EBBB4}"/>
-    <hyperlink ref="J211" r:id="rId126" xr:uid="{F241BF81-D9DE-4404-BBDC-7E7A009B7B05}"/>
-    <hyperlink ref="J212" r:id="rId127" xr:uid="{3DEC314B-041F-4C6C-B2CC-73A96121FA43}"/>
-    <hyperlink ref="J213" r:id="rId128" xr:uid="{2E73525B-09FE-4FED-B2BE-249987621D8B}"/>
-    <hyperlink ref="J214" r:id="rId129" xr:uid="{EDA2D09A-DBCC-4575-A62F-5EC407B383B5}"/>
-    <hyperlink ref="J215" r:id="rId130" xr:uid="{2CFCDAA5-C9D3-438E-AEA5-3D60F9DA18CA}"/>
-    <hyperlink ref="J217" r:id="rId131" xr:uid="{3383843A-F701-4ABC-BB4E-27155F49F483}"/>
-    <hyperlink ref="J219" r:id="rId132" xr:uid="{34FF5606-E7BD-485D-8BB0-284F20EFAFB7}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId133"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId134"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos junio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B452E95-07E9-48F5-8CD5-6CF5532818ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A469AD91-D69F-44A0-A1A9-917CEBECEE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Rechazos Calle" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$445</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$511</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3896" uniqueCount="1300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4473" uniqueCount="1481">
   <si>
     <t>Fecha</t>
   </si>
@@ -3945,6 +3945,552 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781179936/e6gajipbn76euvptwbvx.jpg</t>
+  </si>
+  <si>
+    <t>MQ9MBSIICZ5E</t>
+  </si>
+  <si>
+    <t>Rechaza lo marcado</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781189660/lpn3b9kewbmeofqhpvpi.jpg</t>
+  </si>
+  <si>
+    <t>MQ9NC3Z09XCE</t>
+  </si>
+  <si>
+    <t>2 acanalada</t>
+  </si>
+  <si>
+    <t>MQ9NHZEC49LC</t>
+  </si>
+  <si>
+    <t>12:27 p. m.</t>
+  </si>
+  <si>
+    <t>Rechaza porque ko le hicieron los cambios</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781191638/uqjkweebgrvzlko2oc4t.jpg</t>
+  </si>
+  <si>
+    <t>MQ9NXQIC9IP8</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781192376/dsnfoana121rlq1ssrfy.jpg</t>
+  </si>
+  <si>
+    <t>MQ9O0XQMZP72</t>
+  </si>
+  <si>
+    <t>12:42 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781192515/jrgohnmqgd2vkmhvcjio.jpg</t>
+  </si>
+  <si>
+    <t>MQ9O2XLCASX4</t>
+  </si>
+  <si>
+    <t>Faltan 3 barbacoa</t>
+  </si>
+  <si>
+    <t>MQ9OYHN7NVXO</t>
+  </si>
+  <si>
+    <t>Falta satur salada</t>
+  </si>
+  <si>
+    <t>MQ9PK79OHQFO</t>
+  </si>
+  <si>
+    <t>01:25 p. m.</t>
+  </si>
+  <si>
+    <t>Faltan 5 twuistos de jamón 95</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781195103/dopvbkyjmeddyxmgzwmj.jpg</t>
+  </si>
+  <si>
+    <t>MQ9QALR94ZTG</t>
+  </si>
+  <si>
+    <t>01:45 p. m.</t>
+  </si>
+  <si>
+    <t>Hace 1 mes que facturan el mismo s/stock</t>
+  </si>
+  <si>
+    <t>MQ9QGWDEQMO8</t>
+  </si>
+  <si>
+    <t>MQ9QSTNKPFUK</t>
+  </si>
+  <si>
+    <t>MQ9QRXE04ADM</t>
+  </si>
+  <si>
+    <t>Falta 1 twisto x 95g 
+Desarmo el cl 4236</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781197144/e3uohsfajo8teht1h1jm.jpg</t>
+  </si>
+  <si>
+    <t>MQ9R14UE98OJ</t>
+  </si>
+  <si>
+    <t>Sal rota 1</t>
+  </si>
+  <si>
+    <t>MQ9RFQBK9MIE</t>
+  </si>
+  <si>
+    <t>02:18 p. m.</t>
+  </si>
+  <si>
+    <t>MQ9RP4WRGIUE</t>
+  </si>
+  <si>
+    <t>Faltaron 4 lays de provo</t>
+  </si>
+  <si>
+    <t>MQ9RWDSQC70G</t>
+  </si>
+  <si>
+    <t>Ítems marcados sin stock</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781199025/mm36fsxsqfzrpgcdevqq.jpg</t>
+  </si>
+  <si>
+    <t>MQ9RXMQZJ55J</t>
+  </si>
+  <si>
+    <t>02:31 p. m.</t>
+  </si>
+  <si>
+    <t>Full mani 17 unidades</t>
+  </si>
+  <si>
+    <t>MQ9SBH9ICW5I</t>
+  </si>
+  <si>
+    <t>MQ9SJPCMLJ9F</t>
+  </si>
+  <si>
+    <t>02:48 p. m.</t>
+  </si>
+  <si>
+    <t>Sal fina todas humedas</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781200114/s4dcsjfw7cc9h363bid4.jpg</t>
+  </si>
+  <si>
+    <t>MQ9W8KLSO7BT</t>
+  </si>
+  <si>
+    <t>04:31 p. m.</t>
+  </si>
+  <si>
+    <t>MQ9WAH7J2C24</t>
+  </si>
+  <si>
+    <t>04:33 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781206408/z5j1nm5h4ge0d0cam6eu.jpg</t>
+  </si>
+  <si>
+    <t>MQA5J1Z2J42X</t>
+  </si>
+  <si>
+    <t>08:53 p. m.</t>
+  </si>
+  <si>
+    <t>ROMANO RODRIGO ERNESTO</t>
+  </si>
+  <si>
+    <t>BAZAN LUCIANO MANUEL</t>
+  </si>
+  <si>
+    <t>Falto 2 doritos 129</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781221924/tqhlyueudh4ulyoyi41t.jpg</t>
+  </si>
+  <si>
+    <t>MQA5LVAM8YS6</t>
+  </si>
+  <si>
+    <t>08:55 p. m.</t>
+  </si>
+  <si>
+    <t>Era 24 negro y24 blanco</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781222063/nlme0ogymbu0r3otkkbf.jpg</t>
+  </si>
+  <si>
+    <t>MQA5NUKT3FGL</t>
+  </si>
+  <si>
+    <t>08:57 p. m.</t>
+  </si>
+  <si>
+    <t>Eran cheetos de 85</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781222162/haxfc6jwpould2sccmvw.jpg</t>
+  </si>
+  <si>
+    <t>MQA5RL4EY07E</t>
+  </si>
+  <si>
+    <t>08:59 p. m.</t>
+  </si>
+  <si>
+    <t>Eran twistos de 95 de jamon</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781222322/mqosqiszbdwu1ychovpd.jpg</t>
+  </si>
+  <si>
+    <t>MQAUB0BS4P7G</t>
+  </si>
+  <si>
+    <t>08:26 a. m.</t>
+  </si>
+  <si>
+    <t>10535105 6</t>
+  </si>
+  <si>
+    <t>MQAV04ACSM5J</t>
+  </si>
+  <si>
+    <t>Devuelve ruedita pidió otro gramaje</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781264698/zvyssjomjhs6g2rd0gga.jpg</t>
+  </si>
+  <si>
+    <t>MQAV34K1A2FI</t>
+  </si>
+  <si>
+    <t>6 tokke choco con leche</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781264859/lafv0lmxmtewbncwrgeo.jpg</t>
+  </si>
+  <si>
+    <t>MQAVEB0AWF7N</t>
+  </si>
+  <si>
+    <t>MQAVSVIMACSV</t>
+  </si>
+  <si>
+    <t>MQAW42K2ZZZ7</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781266570/puidxdhihfcuq6ednogo.jpg</t>
+  </si>
+  <si>
+    <t>MQAWBNGLGC8I</t>
+  </si>
+  <si>
+    <t>Palitos de la selva no hay</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781266932/botfhh1r8w7ozimlpnhz.jpg</t>
+  </si>
+  <si>
+    <t>Dejá el pedido, lo resuelvo después — Si pidió</t>
+  </si>
+  <si>
+    <t>MQAWF3NLB2DY</t>
+  </si>
+  <si>
+    <t>No pidió arroz luchetti pidió arroz gallo</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781267081/nykykdcf7uoh0fao6pqm.jpg</t>
+  </si>
+  <si>
+    <t>MQAWGUSBG0SG</t>
+  </si>
+  <si>
+    <t>09:26 a. m.</t>
+  </si>
+  <si>
+    <t>Pidió mani original salado</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781267162/d6x7kwtpobsckc6llhw9.jpg</t>
+  </si>
+  <si>
+    <t>El cliente va a recibir — seguí viaje — No. Pidió Maniax. El esposo de la señora lo pidió.</t>
+  </si>
+  <si>
+    <t>MQAX4429I8S9</t>
+  </si>
+  <si>
+    <t>Alfajores tody 5</t>
+  </si>
+  <si>
+    <t>MQAXGLN28USV</t>
+  </si>
+  <si>
+    <t>Falto un twisto</t>
+  </si>
+  <si>
+    <t>MQAXQEX5BO1R</t>
+  </si>
+  <si>
+    <t>10:01 a. m.</t>
+  </si>
+  <si>
+    <t>No es lo q pidio</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781269293/rmvq8vwbnmaxzigctl2i.jpg</t>
+  </si>
+  <si>
+    <t>MQAY6PFEX98X</t>
+  </si>
+  <si>
+    <t>10:14 a. m.</t>
+  </si>
+  <si>
+    <t>Municiones Terrabusi 5</t>
+  </si>
+  <si>
+    <t>MQAYKJV1E6WR</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781270717/zslildtdtx92skziyg6s.jpg</t>
+  </si>
+  <si>
+    <t>MQAYODBWIMCN</t>
+  </si>
+  <si>
+    <t>Rechaza alfajores</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781270873/jkkcddobhsdazqj94suj.jpg</t>
+  </si>
+  <si>
+    <t>MQAZ1LXIPM52</t>
+  </si>
+  <si>
+    <t>10:39 a. m.</t>
+  </si>
+  <si>
+    <t>Se pasó 3 veces sigue cerrado</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781271547/pfdsmj9c7xiacrdft6av.jpg</t>
+  </si>
+  <si>
+    <t>MQAZDQH0HM93</t>
+  </si>
+  <si>
+    <t>10:48 a. m.</t>
+  </si>
+  <si>
+    <t>Tiene mucha mercadería</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781272061/whphih5fsnkco4rd7sgc.jpg</t>
+  </si>
+  <si>
+    <t>MQAZMNEUP1IT</t>
+  </si>
+  <si>
+    <t>10:55 a. m.</t>
+  </si>
+  <si>
+    <t>Solo recibe pepsico 
+Rechaza esta 2 boletas</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781272507/cdhhzepqxg6zz6fgnqs4.jpg</t>
+  </si>
+  <si>
+    <t>MQAZP76D3L9I</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781272600/q68iid0n4qx7nuwh6hdm.jpg</t>
+  </si>
+  <si>
+    <t>MQAZQBR1F3VM</t>
+  </si>
+  <si>
+    <t>10:57 a. m.</t>
+  </si>
+  <si>
+    <t>11 papa lisa x 450</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Sin stock se descuenta la mercadería</t>
+  </si>
+  <si>
+    <t>MQAZWNLZ5Z3U</t>
+  </si>
+  <si>
+    <t>11:02 a. m.</t>
+  </si>
+  <si>
+    <t>Se desc lo marcado en lapicera s stock</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781272950/lldhv9bax9llvact4qof.jpg</t>
+  </si>
+  <si>
+    <t>MQAZZH20ZFVT</t>
+  </si>
+  <si>
+    <t>Rechaza porque no le facturaron los cambios</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781273074/nllndyirwlrtweooexwg.jpg</t>
+  </si>
+  <si>
+    <t>MQB0PQ6IIQAZ</t>
+  </si>
+  <si>
+    <t>MQB0QSIUYA5T</t>
+  </si>
+  <si>
+    <t>Smirnoff ice red berrie</t>
+  </si>
+  <si>
+    <t>MQB0WOCOVX9J</t>
+  </si>
+  <si>
+    <t>MQB0YI9FG2TP</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781274728/upgtf8t6zizmijk4yxbn.jpg</t>
+  </si>
+  <si>
+    <t>MQB0ZDPW16WC</t>
+  </si>
+  <si>
+    <t>Se descuentan 3 favorita tallarín sin stock</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781274749/dbukrummr1ygjego5b8m.jpg</t>
+  </si>
+  <si>
+    <t>MQB180G9VWE8</t>
+  </si>
+  <si>
+    <t>11:39 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781275155/vkpy9ijieloncrbzik4y.jpg</t>
+  </si>
+  <si>
+    <t>El cliente va a recibir — seguí viaje — Recibe lo que está bien en el pedido</t>
+  </si>
+  <si>
+    <t>MQ9HBS01DA4X</t>
+  </si>
+  <si>
+    <t>MQ9HQMXDJ5YI</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781181961/cnv9sc8sbhh8cn3sp9ej.jpg</t>
+  </si>
+  <si>
+    <t>MQ9ICZIWFUVL</t>
+  </si>
+  <si>
+    <t>6smirnof green</t>
+  </si>
+  <si>
+    <t>MQ9II3HIW27H</t>
+  </si>
+  <si>
+    <t>S stock gelatina durazno light y mal armado gelatina light cereza mandaron las comunes</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781183241/qcp3r6doem7iaaicp6zp.jpg</t>
+  </si>
+  <si>
+    <t>MQ9IKL3LQ49Y</t>
+  </si>
+  <si>
+    <t>10:09 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781183358/ezlsu3mmbqvgs2fby8ir.jpg</t>
+  </si>
+  <si>
+    <t>MQ9IZPQOC5YT</t>
+  </si>
+  <si>
+    <t>Mousse</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781184066/k6sqyipvoilndazfsw6j.jpg</t>
+  </si>
+  <si>
+    <t>MQ9JND0N5NG1</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781185185/li0rmeop6k3gdq0jkut7.jpg</t>
+  </si>
+  <si>
+    <t>MQ9JSIR5T21C</t>
+  </si>
+  <si>
+    <t>Toddy enviaron x 800g
+Faltaron 2avenas</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781185436/uvebnqiwa0uildj3ncjx.jpg</t>
+  </si>
+  <si>
+    <t>MQ9KP1761DCV</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781186926/mmughypeizjonac1hj6f.jpg</t>
+  </si>
+  <si>
+    <t>MQ9KX0CIDWNT</t>
+  </si>
+  <si>
+    <t>Merm frut prolight violeta oriet</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781187310/x30tjfftcoktbbbvbshv.jpg</t>
+  </si>
+  <si>
+    <t>MQ9L8W8Q8EHI</t>
+  </si>
+  <si>
+    <t>Faltó 1 Cheetos ondulado ketchup 80gr</t>
+  </si>
+  <si>
+    <t>MQ9LHVRBKPXN</t>
+  </si>
+  <si>
+    <t>Faltan Lay de 40</t>
+  </si>
+  <si>
+    <t>MQB1CBGGRQ94</t>
+  </si>
+  <si>
+    <t>11:42 a. m.</t>
+  </si>
+  <si>
+    <t>Se desc luch codito</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781275358/pkwfq4ktzvhz4knb4x3a.jpg</t>
   </si>
 </sst>
 </file>
@@ -4138,7 +4684,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4200,9 +4746,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4214,6 +4757,20 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4332,8 +4889,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N445">
-  <autoFilter ref="A1:N445" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N511">
+  <autoFilter ref="A1:N511" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fecha"/>
@@ -4555,7 +5112,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N445"/>
+  <dimension ref="A1:N511"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -4636,13 +5193,13 @@
       <c r="G2" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="J2" s="22"/>
+      <c r="J2" s="27"/>
       <c r="K2" s="19" t="s">
         <v>78</v>
       </c>
@@ -4652,7 +5209,7 @@
       <c r="M2" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="N2" s="24">
+      <c r="N2" s="23">
         <v>6</v>
       </c>
     </row>
@@ -4678,19 +5235,19 @@
       <c r="G3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="12" t="s">
         <v>11</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="4"/>
       <c r="M3" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="24">
         <v>6</v>
       </c>
     </row>
@@ -4716,10 +5273,10 @@
       <c r="G4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="8"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="8"/>
       <c r="K4" s="5" t="s">
         <v>54</v>
@@ -4730,7 +5287,7 @@
       <c r="M4" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N4" s="25">
+      <c r="N4" s="24">
         <v>6</v>
       </c>
     </row>
@@ -4756,7 +5313,7 @@
       <c r="G5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I5" s="5" t="s">
@@ -4770,7 +5327,7 @@
       <c r="M5" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N5" s="25">
+      <c r="N5" s="24">
         <v>6</v>
       </c>
     </row>
@@ -4796,11 +5353,11 @@
       <c r="G6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
+      <c r="J6" s="11"/>
       <c r="K6" s="5" t="s">
         <v>55</v>
       </c>
@@ -4810,7 +5367,7 @@
       <c r="M6" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N6" s="25">
+      <c r="N6" s="24">
         <v>6</v>
       </c>
     </row>
@@ -4839,22 +5396,22 @@
       <c r="H7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="8" t="s">
         <v>89</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="30">
         <v>46174</v>
       </c>
       <c r="M7" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N7" s="25">
+      <c r="N7" s="24">
         <v>6</v>
       </c>
     </row>
@@ -4880,13 +5437,13 @@
       <c r="G8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="10" t="s">
         <v>37</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="8" t="s">
         <v>94</v>
       </c>
       <c r="K8" s="5" t="s">
@@ -4898,7 +5455,7 @@
       <c r="M8" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="24">
         <v>6</v>
       </c>
     </row>
@@ -4924,21 +5481,21 @@
       <c r="G9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="8"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="8"/>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="30">
         <v>46174</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="24">
         <v>6</v>
       </c>
     </row>
@@ -4964,7 +5521,7 @@
       <c r="G10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="10" t="s">
         <v>11</v>
       </c>
       <c r="I10" s="5" t="s">
@@ -4982,7 +5539,7 @@
       <c r="M10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N10" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5011,7 +5568,7 @@
       <c r="H11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="8"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="8"/>
       <c r="K11" s="5" t="s">
         <v>55</v>
@@ -5022,7 +5579,7 @@
       <c r="M11" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N11" s="25">
+      <c r="N11" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5033,7 +5590,7 @@
       <c r="B12" s="4">
         <v>46174</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="13" t="s">
         <v>102</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -5062,7 +5619,7 @@
       <c r="M12" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N12" s="25">
+      <c r="N12" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5073,7 +5630,7 @@
       <c r="B13" s="4">
         <v>46174</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="13" t="s">
         <v>104</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -5088,13 +5645,13 @@
       <c r="G13" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="8" t="s">
         <v>106</v>
       </c>
       <c r="K13" s="5" t="s">
@@ -5106,7 +5663,7 @@
       <c r="M13" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N13" s="25">
+      <c r="N13" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5141,16 +5698,16 @@
       <c r="J14" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14" s="30">
         <v>46174</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5176,10 +5733,10 @@
       <c r="G15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I15" s="8"/>
+      <c r="I15" s="5"/>
       <c r="J15" s="8"/>
       <c r="K15" s="5" t="s">
         <v>54</v>
@@ -5190,7 +5747,7 @@
       <c r="M15" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N15" s="25">
+      <c r="N15" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5216,21 +5773,21 @@
       <c r="G16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="12" t="s">
         <v>11</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L16" s="30">
         <v>46174</v>
       </c>
       <c r="M16" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N16" s="25">
+      <c r="N16" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5241,7 +5798,7 @@
       <c r="B17" s="4">
         <v>46174</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="13" t="s">
         <v>68</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -5262,15 +5819,15 @@
       <c r="I17" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="4"/>
       <c r="M17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5299,8 +5856,8 @@
       <c r="H18" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="11"/>
       <c r="K18" s="5" t="s">
         <v>54</v>
       </c>
@@ -5310,7 +5867,7 @@
       <c r="M18" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N18" s="25">
+      <c r="N18" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5339,8 +5896,8 @@
       <c r="H19" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="11" t="s">
+      <c r="I19" s="5"/>
+      <c r="J19" s="8" t="s">
         <v>117</v>
       </c>
       <c r="K19" s="5" t="s">
@@ -5352,7 +5909,7 @@
       <c r="M19" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N19" s="25">
+      <c r="N19" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5363,7 +5920,7 @@
       <c r="B20" s="4">
         <v>46174</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="13" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="5" t="s">
@@ -5378,13 +5935,13 @@
       <c r="G20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="J20" s="8" t="s">
         <v>120</v>
       </c>
       <c r="K20" s="8"/>
@@ -5392,7 +5949,7 @@
       <c r="M20" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N20" s="25">
+      <c r="N20" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5427,16 +5984,16 @@
       <c r="J21" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="L21" s="4">
+      <c r="L21" s="30">
         <v>46174</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N21" s="25">
+      <c r="N21" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5462,23 +6019,23 @@
       <c r="G22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="8" t="s">
         <v>127</v>
       </c>
       <c r="J22" s="8"/>
-      <c r="K22" s="5" t="s">
+      <c r="K22" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="L22" s="4">
+      <c r="L22" s="30">
         <v>46174</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N22" s="25">
+      <c r="N22" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5504,21 +6061,21 @@
       <c r="G23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="15" t="s">
         <v>35</v>
       </c>
       <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="5" t="s">
+      <c r="J23" s="11"/>
+      <c r="K23" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="L23" s="4">
+      <c r="L23" s="30">
         <v>46174</v>
       </c>
       <c r="M23" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N23" s="25">
+      <c r="N23" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5544,7 +6101,7 @@
       <c r="G24" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="10" t="s">
         <v>11</v>
       </c>
       <c r="I24" s="5" t="s">
@@ -5562,7 +6119,7 @@
       <c r="M24" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N24" s="25">
+      <c r="N24" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5588,19 +6145,19 @@
       <c r="G25" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H25" s="14" t="s">
+      <c r="H25" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I25" s="8"/>
+      <c r="I25" s="5"/>
       <c r="J25" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="4"/>
       <c r="M25" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N25" s="25">
+      <c r="N25" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5626,19 +6183,19 @@
       <c r="G26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="H26" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I26" s="8"/>
+      <c r="I26" s="5"/>
       <c r="J26" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="4"/>
       <c r="M26" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N26" s="25">
+      <c r="N26" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5664,7 +6221,7 @@
       <c r="G27" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I27" s="5" t="s">
@@ -5682,7 +6239,7 @@
       <c r="M27" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N27" s="25">
+      <c r="N27" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5715,16 +6272,16 @@
         <v>144</v>
       </c>
       <c r="J28" s="8"/>
-      <c r="K28" s="5" t="s">
+      <c r="K28" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="L28" s="4">
+      <c r="L28" s="30">
         <v>46174</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N28" s="25">
+      <c r="N28" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5753,7 +6310,7 @@
       <c r="H29" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="I29" s="8"/>
+      <c r="I29" s="5"/>
       <c r="J29" s="11" t="s">
         <v>146</v>
       </c>
@@ -5766,7 +6323,7 @@
       <c r="M29" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N29" s="25">
+      <c r="N29" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5795,7 +6352,7 @@
       <c r="H30" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I30" s="8"/>
+      <c r="I30" s="5"/>
       <c r="J30" s="11" t="s">
         <v>149</v>
       </c>
@@ -5808,7 +6365,7 @@
       <c r="M30" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N30" s="25">
+      <c r="N30" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5819,7 +6376,7 @@
       <c r="B31" s="4">
         <v>46174</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="13" t="s">
         <v>72</v>
       </c>
       <c r="D31" s="5" t="s">
@@ -5834,13 +6391,13 @@
       <c r="G31" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I31" s="5" t="s">
+      <c r="I31" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="J31" s="8" t="s">
         <v>152</v>
       </c>
       <c r="K31" s="8"/>
@@ -5848,7 +6405,7 @@
       <c r="M31" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N31" s="25">
+      <c r="N31" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5859,7 +6416,7 @@
       <c r="B32" s="4">
         <v>46174</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="13" t="s">
         <v>69</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -5874,10 +6431,10 @@
       <c r="G32" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I32" s="5" t="s">
+      <c r="I32" s="8" t="s">
         <v>154</v>
       </c>
       <c r="J32" s="8"/>
@@ -5890,7 +6447,7 @@
       <c r="M32" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N32" s="25">
+      <c r="N32" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5916,23 +6473,23 @@
       <c r="G33" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H33" s="12" t="s">
+      <c r="H33" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="I33" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="J33" s="8"/>
-      <c r="K33" s="5" t="s">
+      <c r="J33" s="11"/>
+      <c r="K33" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="L33" s="4">
+      <c r="L33" s="30">
         <v>46174</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N33" s="25">
+      <c r="N33" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5958,7 +6515,7 @@
       <c r="G34" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="7" t="s">
         <v>52</v>
       </c>
       <c r="I34" s="5" t="s">
@@ -5967,12 +6524,12 @@
       <c r="J34" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="4"/>
       <c r="M34" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N34" s="25">
+      <c r="N34" s="24">
         <v>6</v>
       </c>
     </row>
@@ -5998,10 +6555,10 @@
       <c r="G35" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I35" s="8"/>
+      <c r="I35" s="5"/>
       <c r="J35" s="11" t="s">
         <v>162</v>
       </c>
@@ -6014,7 +6571,7 @@
       <c r="M35" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N35" s="25">
+      <c r="N35" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6040,7 +6597,7 @@
       <c r="G36" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="14" t="s">
         <v>37</v>
       </c>
       <c r="I36" s="5" t="s">
@@ -6049,12 +6606,12 @@
       <c r="J36" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="4"/>
       <c r="M36" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N36" s="25">
+      <c r="N36" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6080,11 +6637,11 @@
       <c r="G37" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H37" s="9" t="s">
+      <c r="H37" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I37" s="8"/>
-      <c r="J37" s="11" t="s">
+      <c r="I37" s="5"/>
+      <c r="J37" s="8" t="s">
         <v>166</v>
       </c>
       <c r="K37" s="5" t="s">
@@ -6096,7 +6653,7 @@
       <c r="M37" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N37" s="25">
+      <c r="N37" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6122,21 +6679,21 @@
       <c r="G38" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H38" s="14" t="s">
+      <c r="H38" s="10" t="s">
         <v>38</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="J38" s="11" t="s">
+      <c r="J38" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="4"/>
       <c r="M38" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N38" s="25">
+      <c r="N38" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6162,11 +6719,11 @@
       <c r="G39" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="11"/>
       <c r="K39" s="5" t="s">
         <v>62</v>
       </c>
@@ -6176,7 +6733,7 @@
       <c r="M39" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N39" s="25">
+      <c r="N39" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6205,7 +6762,7 @@
       <c r="H40" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I40" s="8"/>
+      <c r="I40" s="5"/>
       <c r="J40" s="8"/>
       <c r="K40" s="5" t="s">
         <v>173</v>
@@ -6216,7 +6773,7 @@
       <c r="M40" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N40" s="25">
+      <c r="N40" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6242,21 +6799,21 @@
       <c r="G41" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H41" s="7" t="s">
+      <c r="H41" s="10" t="s">
         <v>11</v>
       </c>
       <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="5" t="s">
+      <c r="J41" s="11"/>
+      <c r="K41" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="L41" s="4">
+      <c r="L41" s="30">
         <v>46175</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N41" s="25">
+      <c r="N41" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6282,23 +6839,23 @@
       <c r="G42" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H42" s="15" t="s">
+      <c r="H42" s="9" t="s">
         <v>41</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="J42" s="8"/>
-      <c r="K42" s="5" t="s">
+      <c r="J42" s="11"/>
+      <c r="K42" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L42" s="4">
+      <c r="L42" s="30">
         <v>46174</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N42" s="25">
+      <c r="N42" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6324,23 +6881,23 @@
       <c r="G43" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="15" t="s">
         <v>52</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="J43" s="8"/>
-      <c r="K43" s="5" t="s">
+      <c r="J43" s="11"/>
+      <c r="K43" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="L43" s="4">
+      <c r="L43" s="30">
         <v>46175</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N43" s="25">
+      <c r="N43" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6366,13 +6923,13 @@
       <c r="G44" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H44" s="9" t="s">
         <v>11</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="J44" s="8"/>
+      <c r="J44" s="11"/>
       <c r="K44" s="5" t="s">
         <v>184</v>
       </c>
@@ -6382,7 +6939,7 @@
       <c r="M44" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N44" s="25">
+      <c r="N44" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6408,13 +6965,13 @@
       <c r="G45" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H45" s="7" t="s">
+      <c r="H45" s="14" t="s">
         <v>11</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="J45" s="8"/>
+      <c r="J45" s="11"/>
       <c r="K45" s="5" t="s">
         <v>56</v>
       </c>
@@ -6424,7 +6981,7 @@
       <c r="M45" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N45" s="25">
+      <c r="N45" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6450,7 +7007,7 @@
       <c r="G46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H46" s="7" t="s">
+      <c r="H46" s="12" t="s">
         <v>11</v>
       </c>
       <c r="I46" s="5" t="s">
@@ -6468,7 +7025,7 @@
       <c r="M46" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N46" s="25">
+      <c r="N46" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6497,16 +7054,16 @@
       <c r="H47" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I47" s="8"/>
-      <c r="J47" s="11" t="s">
+      <c r="I47" s="5"/>
+      <c r="J47" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="4"/>
       <c r="M47" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N47" s="25">
+      <c r="N47" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6532,7 +7089,7 @@
       <c r="G48" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H48" s="12" t="s">
+      <c r="H48" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I48" s="5" t="s">
@@ -6550,7 +7107,7 @@
       <c r="M48" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N48" s="25">
+      <c r="N48" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6576,23 +7133,23 @@
       <c r="G49" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="H49" s="9" t="s">
+      <c r="H49" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="I49" s="8"/>
+      <c r="I49" s="5"/>
       <c r="J49" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="K49" s="5" t="s">
+      <c r="K49" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L49" s="4">
+      <c r="L49" s="30">
         <v>46175</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N49" s="25">
+      <c r="N49" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6603,7 +7160,7 @@
       <c r="B50" s="4">
         <v>46175</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="13" t="s">
         <v>202</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -6618,11 +7175,11 @@
       <c r="G50" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="H50" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I50" s="8"/>
-      <c r="J50" s="11" t="s">
+      <c r="J50" s="8" t="s">
         <v>203</v>
       </c>
       <c r="K50" s="5" t="s">
@@ -6634,7 +7191,7 @@
       <c r="M50" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N50" s="25">
+      <c r="N50" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6645,7 +7202,7 @@
       <c r="B51" s="4">
         <v>46175</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="13" t="s">
         <v>205</v>
       </c>
       <c r="D51" s="5" t="s">
@@ -6663,7 +7220,7 @@
       <c r="H51" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I51" s="8"/>
+      <c r="I51" s="5"/>
       <c r="J51" s="8"/>
       <c r="K51" s="5" t="s">
         <v>56</v>
@@ -6674,7 +7231,7 @@
       <c r="M51" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N51" s="25">
+      <c r="N51" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6685,7 +7242,7 @@
       <c r="B52" s="4">
         <v>46175</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="13" t="s">
         <v>207</v>
       </c>
       <c r="D52" s="5" t="s">
@@ -6700,23 +7257,23 @@
       <c r="G52" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H52" s="7" t="s">
+      <c r="H52" s="14" t="s">
         <v>11</v>
       </c>
       <c r="I52" s="8"/>
-      <c r="J52" s="11" t="s">
+      <c r="J52" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="K52" s="5" t="s">
+      <c r="K52" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L52" s="4">
+      <c r="L52" s="30">
         <v>46175</v>
       </c>
       <c r="M52" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N52" s="25">
+      <c r="N52" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6742,23 +7299,23 @@
       <c r="G53" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H53" s="7" t="s">
+      <c r="H53" s="10" t="s">
         <v>11</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="K53" s="5" t="s">
+      <c r="K53" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="L53" s="4">
+      <c r="L53" s="30">
         <v>46175</v>
       </c>
       <c r="M53" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N53" s="25">
+      <c r="N53" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6769,7 +7326,7 @@
       <c r="B54" s="4">
         <v>46175</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="13" t="s">
         <v>213</v>
       </c>
       <c r="D54" s="5" t="s">
@@ -6793,16 +7350,16 @@
       <c r="J54" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="K54" s="5" t="s">
+      <c r="K54" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="L54" s="4">
+      <c r="L54" s="30">
         <v>46175</v>
       </c>
       <c r="M54" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N54" s="25">
+      <c r="N54" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6828,17 +7385,17 @@
       <c r="G55" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
+      <c r="J55" s="11"/>
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
       <c r="M55" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N55" s="25">
+      <c r="N55" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6876,7 +7433,7 @@
       <c r="M56" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N56" s="25">
+      <c r="N56" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6918,7 +7475,7 @@
       <c r="M57" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N57" s="25">
+      <c r="N57" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6954,7 +7511,7 @@
       <c r="M58" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N58" s="25">
+      <c r="N58" s="24">
         <v>6</v>
       </c>
     </row>
@@ -6998,7 +7555,7 @@
       <c r="M59" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N59" s="25">
+      <c r="N59" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7038,7 +7595,7 @@
       <c r="M60" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N60" s="25">
+      <c r="N60" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7080,7 +7637,7 @@
       <c r="M61" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N61" s="25">
+      <c r="N61" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7122,7 +7679,7 @@
       <c r="M62" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N62" s="25">
+      <c r="N62" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7166,7 +7723,7 @@
       <c r="M63" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N63" s="25">
+      <c r="N63" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7210,7 +7767,7 @@
       <c r="M64" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N64" s="25">
+      <c r="N64" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7252,7 +7809,7 @@
       <c r="M65" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N65" s="25">
+      <c r="N65" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7292,7 +7849,7 @@
       <c r="M66" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N66" s="25">
+      <c r="N66" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7334,7 +7891,7 @@
       <c r="M67" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N67" s="25">
+      <c r="N67" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7374,7 +7931,7 @@
       <c r="M68" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N68" s="25">
+      <c r="N68" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7416,7 +7973,7 @@
       <c r="M69" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N69" s="25">
+      <c r="N69" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7456,7 +8013,7 @@
       <c r="M70" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N70" s="25">
+      <c r="N70" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7496,7 +8053,7 @@
       <c r="M71" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N71" s="25">
+      <c r="N71" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7540,7 +8097,7 @@
       <c r="M72" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N72" s="25">
+      <c r="N72" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7582,7 +8139,7 @@
       <c r="M73" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N73" s="25">
+      <c r="N73" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7626,7 +8183,7 @@
       <c r="M74" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N74" s="25">
+      <c r="N74" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7666,7 +8223,7 @@
       <c r="M75" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N75" s="25">
+      <c r="N75" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7704,7 +8261,7 @@
       <c r="M76" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N76" s="25">
+      <c r="N76" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7746,7 +8303,7 @@
       <c r="M77" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N77" s="25">
+      <c r="N77" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7790,7 +8347,7 @@
       <c r="M78" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N78" s="25">
+      <c r="N78" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7832,7 +8389,7 @@
       <c r="M79" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N79" s="25">
+      <c r="N79" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7876,7 +8433,7 @@
       <c r="M80" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N80" s="25">
+      <c r="N80" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7912,7 +8469,7 @@
       <c r="M81" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N81" s="25">
+      <c r="N81" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7954,7 +8511,7 @@
       <c r="M82" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N82" s="25">
+      <c r="N82" s="24">
         <v>6</v>
       </c>
     </row>
@@ -7994,7 +8551,7 @@
       <c r="M83" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N83" s="25">
+      <c r="N83" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8034,7 +8591,7 @@
       <c r="M84" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N84" s="25">
+      <c r="N84" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8070,7 +8627,7 @@
       <c r="M85" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N85" s="25">
+      <c r="N85" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8108,7 +8665,7 @@
       <c r="M86" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N86" s="25">
+      <c r="N86" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8144,7 +8701,7 @@
       <c r="M87" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N87" s="25">
+      <c r="N87" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8188,7 +8745,7 @@
       <c r="M88" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N88" s="25">
+      <c r="N88" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8232,7 +8789,7 @@
       <c r="M89" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N89" s="25">
+      <c r="N89" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8276,7 +8833,7 @@
       <c r="M90" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N90" s="25">
+      <c r="N90" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8316,7 +8873,7 @@
       <c r="M91" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N91" s="25">
+      <c r="N91" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8358,7 +8915,7 @@
       <c r="M92" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N92" s="25">
+      <c r="N92" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8398,7 +8955,7 @@
       <c r="M93" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N93" s="25">
+      <c r="N93" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8436,7 +8993,7 @@
       <c r="M94" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N94" s="25">
+      <c r="N94" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8480,7 +9037,7 @@
       <c r="M95" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N95" s="25">
+      <c r="N95" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8518,7 +9075,7 @@
       <c r="M96" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N96" s="25">
+      <c r="N96" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8560,7 +9117,7 @@
       <c r="M97" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N97" s="25">
+      <c r="N97" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8598,7 +9155,7 @@
       <c r="M98" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N98" s="25">
+      <c r="N98" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8640,7 +9197,7 @@
       <c r="M99" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N99" s="25">
+      <c r="N99" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8682,7 +9239,7 @@
       <c r="M100" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N100" s="25">
+      <c r="N100" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8724,7 +9281,7 @@
       <c r="M101" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N101" s="25">
+      <c r="N101" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8762,7 +9319,7 @@
       <c r="M102" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N102" s="25">
+      <c r="N102" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8806,7 +9363,7 @@
       <c r="M103" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N103" s="25">
+      <c r="N103" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8850,7 +9407,7 @@
       <c r="M104" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N104" s="25">
+      <c r="N104" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8890,7 +9447,7 @@
       <c r="M105" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N105" s="25">
+      <c r="N105" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8932,7 +9489,7 @@
       <c r="M106" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N106" s="25">
+      <c r="N106" s="24">
         <v>6</v>
       </c>
     </row>
@@ -8970,7 +9527,7 @@
       <c r="M107" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N107" s="25">
+      <c r="N107" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9012,7 +9569,7 @@
       <c r="M108" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N108" s="25">
+      <c r="N108" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9056,7 +9613,7 @@
       <c r="M109" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N109" s="25">
+      <c r="N109" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9098,7 +9655,7 @@
       <c r="M110" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N110" s="25">
+      <c r="N110" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9140,7 +9697,7 @@
       <c r="M111" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N111" s="25">
+      <c r="N111" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9184,7 +9741,7 @@
       <c r="M112" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N112" s="25">
+      <c r="N112" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9226,7 +9783,7 @@
       <c r="M113" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N113" s="25">
+      <c r="N113" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9270,7 +9827,7 @@
       <c r="M114" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N114" s="25">
+      <c r="N114" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9312,7 +9869,7 @@
       <c r="M115" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N115" s="25">
+      <c r="N115" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9356,7 +9913,7 @@
       <c r="M116" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N116" s="25">
+      <c r="N116" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9398,7 +9955,7 @@
       <c r="M117" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N117" s="25">
+      <c r="N117" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9442,7 +9999,7 @@
       <c r="M118" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N118" s="25">
+      <c r="N118" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9484,7 +10041,7 @@
       <c r="M119" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N119" s="25">
+      <c r="N119" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9526,7 +10083,7 @@
       <c r="M120" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N120" s="25">
+      <c r="N120" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9564,7 +10121,7 @@
       <c r="M121" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N121" s="25">
+      <c r="N121" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9602,7 +10159,7 @@
       <c r="M122" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N122" s="25">
+      <c r="N122" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9644,7 +10201,7 @@
       <c r="M123" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N123" s="25">
+      <c r="N123" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9686,7 +10243,7 @@
       <c r="M124" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N124" s="25">
+      <c r="N124" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9726,7 +10283,7 @@
       <c r="M125" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N125" s="25">
+      <c r="N125" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9768,7 +10325,7 @@
       <c r="M126" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N126" s="25">
+      <c r="N126" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9806,7 +10363,7 @@
       <c r="M127" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N127" s="25">
+      <c r="N127" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9848,7 +10405,7 @@
       <c r="M128" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N128" s="25">
+      <c r="N128" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9886,7 +10443,7 @@
       <c r="M129" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N129" s="25">
+      <c r="N129" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9928,7 +10485,7 @@
       <c r="M130" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N130" s="25">
+      <c r="N130" s="24">
         <v>6</v>
       </c>
     </row>
@@ -9970,7 +10527,7 @@
       <c r="M131" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N131" s="25">
+      <c r="N131" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10010,7 +10567,7 @@
       <c r="M132" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N132" s="25">
+      <c r="N132" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10052,7 +10609,7 @@
       <c r="M133" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N133" s="25">
+      <c r="N133" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10096,7 +10653,7 @@
       <c r="M134" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N134" s="25">
+      <c r="N134" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10136,7 +10693,7 @@
       <c r="M135" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N135" s="25">
+      <c r="N135" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10180,7 +10737,7 @@
       <c r="M136" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N136" s="25">
+      <c r="N136" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10222,7 +10779,7 @@
       <c r="M137" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N137" s="25">
+      <c r="N137" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10258,7 +10815,7 @@
       <c r="M138" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N138" s="25">
+      <c r="N138" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10300,7 +10857,7 @@
       <c r="M139" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N139" s="25">
+      <c r="N139" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10342,7 +10899,7 @@
       <c r="M140" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N140" s="25">
+      <c r="N140" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10380,7 +10937,7 @@
       <c r="M141" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N141" s="25">
+      <c r="N141" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10424,7 +10981,7 @@
       <c r="M142" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N142" s="25">
+      <c r="N142" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10462,7 +11019,7 @@
       <c r="M143" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N143" s="25">
+      <c r="N143" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10502,7 +11059,7 @@
       <c r="M144" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N144" s="25">
+      <c r="N144" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10546,7 +11103,7 @@
       <c r="M145" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N145" s="25">
+      <c r="N145" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10588,7 +11145,7 @@
       <c r="M146" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N146" s="25">
+      <c r="N146" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10632,7 +11189,7 @@
       <c r="M147" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N147" s="25">
+      <c r="N147" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10674,7 +11231,7 @@
       <c r="M148" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N148" s="25">
+      <c r="N148" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10716,7 +11273,7 @@
       <c r="M149" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N149" s="25">
+      <c r="N149" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10758,7 +11315,7 @@
       <c r="M150" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N150" s="25">
+      <c r="N150" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10802,7 +11359,7 @@
       <c r="M151" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N151" s="25">
+      <c r="N151" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10846,7 +11403,7 @@
       <c r="M152" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N152" s="25">
+      <c r="N152" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10890,7 +11447,7 @@
       <c r="M153" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N153" s="25">
+      <c r="N153" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10932,7 +11489,7 @@
       <c r="M154" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N154" s="25">
+      <c r="N154" s="24">
         <v>6</v>
       </c>
     </row>
@@ -10974,7 +11531,7 @@
       <c r="M155" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N155" s="25">
+      <c r="N155" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11018,7 +11575,7 @@
       <c r="M156" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N156" s="25">
+      <c r="N156" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11060,7 +11617,7 @@
       <c r="M157" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N157" s="25">
+      <c r="N157" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11102,7 +11659,7 @@
       <c r="M158" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N158" s="25">
+      <c r="N158" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11144,7 +11701,7 @@
       <c r="M159" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N159" s="25">
+      <c r="N159" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11188,7 +11745,7 @@
       <c r="M160" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N160" s="25">
+      <c r="N160" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11232,7 +11789,7 @@
       <c r="M161" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N161" s="25">
+      <c r="N161" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11270,7 +11827,7 @@
       <c r="M162" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N162" s="25">
+      <c r="N162" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11312,7 +11869,7 @@
       <c r="M163" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N163" s="25">
+      <c r="N163" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11356,7 +11913,7 @@
       <c r="M164" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N164" s="25">
+      <c r="N164" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11400,7 +11957,7 @@
       <c r="M165" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N165" s="25">
+      <c r="N165" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11438,7 +11995,7 @@
       <c r="M166" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N166" s="25">
+      <c r="N166" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11480,7 +12037,7 @@
       <c r="M167" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N167" s="25">
+      <c r="N167" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11518,7 +12075,7 @@
       <c r="M168" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N168" s="25">
+      <c r="N168" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11556,7 +12113,7 @@
       <c r="M169" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N169" s="25">
+      <c r="N169" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11598,7 +12155,7 @@
       <c r="M170" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N170" s="25">
+      <c r="N170" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11636,7 +12193,7 @@
       <c r="M171" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N171" s="25">
+      <c r="N171" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11680,7 +12237,7 @@
       <c r="M172" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N172" s="25">
+      <c r="N172" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11724,7 +12281,7 @@
       <c r="M173" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N173" s="25">
+      <c r="N173" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11764,7 +12321,7 @@
       <c r="M174" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N174" s="25">
+      <c r="N174" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11806,7 +12363,7 @@
       <c r="M175" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N175" s="25">
+      <c r="N175" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11844,7 +12401,7 @@
       <c r="M176" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N176" s="25">
+      <c r="N176" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11886,7 +12443,7 @@
       <c r="M177" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N177" s="25">
+      <c r="N177" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11924,7 +12481,7 @@
       <c r="M178" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N178" s="25">
+      <c r="N178" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11966,7 +12523,7 @@
       <c r="M179" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N179" s="25">
+      <c r="N179" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12008,7 +12565,7 @@
       <c r="M180" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N180" s="25">
+      <c r="N180" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12052,7 +12609,7 @@
       <c r="M181" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N181" s="25">
+      <c r="N181" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12096,7 +12653,7 @@
       <c r="M182" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N182" s="25">
+      <c r="N182" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12134,7 +12691,7 @@
       <c r="M183" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N183" s="25">
+      <c r="N183" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12178,7 +12735,7 @@
       <c r="M184" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N184" s="25">
+      <c r="N184" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12220,7 +12777,7 @@
       <c r="M185" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N185" s="25">
+      <c r="N185" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12264,7 +12821,7 @@
       <c r="M186" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N186" s="25">
+      <c r="N186" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12304,7 +12861,7 @@
       <c r="M187" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N187" s="25">
+      <c r="N187" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12330,7 +12887,7 @@
       <c r="G188" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H188" s="23" t="s">
+      <c r="H188" s="22" t="s">
         <v>607</v>
       </c>
       <c r="I188" s="5" t="s">
@@ -12346,7 +12903,7 @@
       <c r="M188" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N188" s="25">
+      <c r="N188" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12386,7 +12943,7 @@
       <c r="M189" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N189" s="25">
+      <c r="N189" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12430,7 +12987,7 @@
       <c r="M190" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N190" s="25">
+      <c r="N190" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12472,7 +13029,7 @@
       <c r="M191" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N191" s="25">
+      <c r="N191" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12514,7 +13071,7 @@
       <c r="M192" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N192" s="25">
+      <c r="N192" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12554,7 +13111,7 @@
       <c r="M193" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N193" s="25">
+      <c r="N193" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12592,7 +13149,7 @@
       <c r="M194" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N194" s="25">
+      <c r="N194" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12630,7 +13187,7 @@
       <c r="M195" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N195" s="25">
+      <c r="N195" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12672,7 +13229,7 @@
       <c r="M196" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N196" s="25">
+      <c r="N196" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12708,7 +13265,7 @@
       <c r="M197" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N197" s="25">
+      <c r="N197" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12744,7 +13301,7 @@
       <c r="M198" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N198" s="25">
+      <c r="N198" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12788,7 +13345,7 @@
       <c r="M199" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N199" s="25">
+      <c r="N199" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12830,7 +13387,7 @@
       <c r="M200" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N200" s="25">
+      <c r="N200" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12872,7 +13429,7 @@
       <c r="M201" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N201" s="25">
+      <c r="N201" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12914,7 +13471,7 @@
       <c r="M202" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N202" s="25">
+      <c r="N202" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12956,7 +13513,7 @@
       <c r="M203" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N203" s="25">
+      <c r="N203" s="24">
         <v>6</v>
       </c>
     </row>
@@ -12998,7 +13555,7 @@
       <c r="M204" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N204" s="25">
+      <c r="N204" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13040,7 +13597,7 @@
       <c r="M205" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N205" s="25">
+      <c r="N205" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13080,7 +13637,7 @@
       <c r="M206" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N206" s="25">
+      <c r="N206" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13122,7 +13679,7 @@
       <c r="M207" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N207" s="25">
+      <c r="N207" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13162,7 +13719,7 @@
       <c r="M208" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N208" s="25">
+      <c r="N208" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13204,7 +13761,7 @@
       <c r="M209" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N209" s="25">
+      <c r="N209" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13246,7 +13803,7 @@
       <c r="M210" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N210" s="25">
+      <c r="N210" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13288,7 +13845,7 @@
       <c r="M211" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N211" s="25">
+      <c r="N211" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13332,7 +13889,7 @@
       <c r="M212" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N212" s="25">
+      <c r="N212" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13374,7 +13931,7 @@
       <c r="M213" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N213" s="25">
+      <c r="N213" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13418,7 +13975,7 @@
       <c r="M214" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N214" s="25">
+      <c r="N214" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13462,7 +14019,7 @@
       <c r="M215" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N215" s="25">
+      <c r="N215" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13502,7 +14059,7 @@
       <c r="M216" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N216" s="25">
+      <c r="N216" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13544,7 +14101,7 @@
       <c r="M217" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N217" s="25">
+      <c r="N217" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13584,7 +14141,7 @@
       <c r="M218" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N218" s="25">
+      <c r="N218" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13628,7 +14185,7 @@
       <c r="M219" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N219" s="25">
+      <c r="N219" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13672,7 +14229,7 @@
       <c r="M220" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N220" s="25">
+      <c r="N220" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13714,7 +14271,7 @@
       <c r="M221" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N221" s="25">
+      <c r="N221" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13756,7 +14313,7 @@
       <c r="M222" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N222" s="25">
+      <c r="N222" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13800,7 +14357,7 @@
       <c r="M223" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N223" s="25">
+      <c r="N223" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13840,7 +14397,7 @@
       <c r="M224" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N224" s="25">
+      <c r="N224" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13884,7 +14441,7 @@
       <c r="M225" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N225" s="25">
+      <c r="N225" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13926,7 +14483,7 @@
       <c r="M226" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N226" s="25">
+      <c r="N226" s="24">
         <v>6</v>
       </c>
     </row>
@@ -13968,7 +14525,7 @@
       <c r="M227" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N227" s="25">
+      <c r="N227" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14006,7 +14563,7 @@
       <c r="M228" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N228" s="25">
+      <c r="N228" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14048,7 +14605,7 @@
       <c r="M229" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N229" s="25">
+      <c r="N229" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14090,7 +14647,7 @@
       <c r="M230" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N230" s="25">
+      <c r="N230" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14132,7 +14689,7 @@
       <c r="M231" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N231" s="25">
+      <c r="N231" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14174,7 +14731,7 @@
       <c r="M232" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N232" s="25">
+      <c r="N232" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14214,7 +14771,7 @@
       <c r="M233" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N233" s="25">
+      <c r="N233" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14256,7 +14813,7 @@
       <c r="M234" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N234" s="25">
+      <c r="N234" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14292,7 +14849,7 @@
       <c r="M235" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N235" s="25">
+      <c r="N235" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14336,7 +14893,7 @@
       <c r="M236" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N236" s="25">
+      <c r="N236" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14380,7 +14937,7 @@
       <c r="M237" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N237" s="25">
+      <c r="N237" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14422,7 +14979,7 @@
       <c r="M238" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N238" s="25">
+      <c r="N238" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14464,7 +15021,7 @@
       <c r="M239" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N239" s="25">
+      <c r="N239" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14502,7 +15059,7 @@
       <c r="M240" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N240" s="25">
+      <c r="N240" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14544,7 +15101,7 @@
       <c r="M241" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N241" s="25">
+      <c r="N241" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14588,7 +15145,7 @@
       <c r="M242" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N242" s="25">
+      <c r="N242" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14628,7 +15185,7 @@
       <c r="M243" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N243" s="25">
+      <c r="N243" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14668,7 +15225,7 @@
       <c r="M244" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N244" s="25">
+      <c r="N244" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14708,7 +15265,7 @@
       <c r="M245" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N245" s="25">
+      <c r="N245" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14752,7 +15309,7 @@
       <c r="M246" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N246" s="25">
+      <c r="N246" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14794,7 +15351,7 @@
       <c r="M247" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N247" s="25">
+      <c r="N247" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14836,7 +15393,7 @@
       <c r="M248" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N248" s="25">
+      <c r="N248" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14878,7 +15435,7 @@
       <c r="M249" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N249" s="25">
+      <c r="N249" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14922,7 +15479,7 @@
       <c r="M250" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N250" s="25">
+      <c r="N250" s="24">
         <v>6</v>
       </c>
     </row>
@@ -14960,7 +15517,7 @@
       <c r="M251" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N251" s="25">
+      <c r="N251" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15000,7 +15557,7 @@
       <c r="M252" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N252" s="25">
+      <c r="N252" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15036,7 +15593,7 @@
       <c r="M253" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N253" s="25">
+      <c r="N253" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15078,7 +15635,7 @@
       <c r="M254" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N254" s="25">
+      <c r="N254" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15120,7 +15677,7 @@
       <c r="M255" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N255" s="25">
+      <c r="N255" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15158,7 +15715,7 @@
       <c r="M256" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N256" s="25">
+      <c r="N256" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15194,7 +15751,7 @@
       <c r="M257" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N257" s="25">
+      <c r="N257" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15232,7 +15789,7 @@
       <c r="M258" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N258" s="25">
+      <c r="N258" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15276,7 +15833,7 @@
       <c r="M259" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N259" s="25">
+      <c r="N259" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15318,7 +15875,7 @@
       <c r="M260" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N260" s="25">
+      <c r="N260" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15360,7 +15917,7 @@
       <c r="M261" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N261" s="25">
+      <c r="N261" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15396,7 +15953,7 @@
       <c r="M262" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N262" s="25">
+      <c r="N262" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15440,7 +15997,7 @@
       <c r="M263" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N263" s="25">
+      <c r="N263" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15476,7 +16033,7 @@
       <c r="M264" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N264" s="25">
+      <c r="N264" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15520,7 +16077,7 @@
       <c r="M265" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N265" s="25">
+      <c r="N265" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15562,7 +16119,7 @@
       <c r="M266" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N266" s="25">
+      <c r="N266" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15604,7 +16161,7 @@
       <c r="M267" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N267" s="25">
+      <c r="N267" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15642,7 +16199,7 @@
       <c r="M268" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N268" s="25">
+      <c r="N268" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15682,7 +16239,7 @@
       <c r="M269" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N269" s="25">
+      <c r="N269" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15724,7 +16281,7 @@
       <c r="M270" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N270" s="25">
+      <c r="N270" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15768,7 +16325,7 @@
       <c r="M271" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N271" s="25">
+      <c r="N271" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15810,7 +16367,7 @@
       <c r="M272" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N272" s="25">
+      <c r="N272" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15848,7 +16405,7 @@
       <c r="M273" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N273" s="25">
+      <c r="N273" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15874,7 +16431,7 @@
       <c r="G274" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H274" s="23" t="s">
+      <c r="H274" s="22" t="s">
         <v>607</v>
       </c>
       <c r="I274" s="8"/>
@@ -15890,7 +16447,7 @@
       <c r="M274" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N274" s="25">
+      <c r="N274" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15932,7 +16489,7 @@
       <c r="M275" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N275" s="25">
+      <c r="N275" s="24">
         <v>6</v>
       </c>
     </row>
@@ -15972,7 +16529,7 @@
       <c r="M276" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N276" s="25">
+      <c r="N276" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16016,7 +16573,7 @@
       <c r="M277" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N277" s="25">
+      <c r="N277" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16060,7 +16617,7 @@
       <c r="M278" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N278" s="25">
+      <c r="N278" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16104,7 +16661,7 @@
       <c r="M279" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N279" s="25">
+      <c r="N279" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16146,7 +16703,7 @@
       <c r="M280" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N280" s="25">
+      <c r="N280" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16188,7 +16745,7 @@
       <c r="M281" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N281" s="25">
+      <c r="N281" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16228,7 +16785,7 @@
       <c r="M282" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N282" s="25">
+      <c r="N282" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16266,7 +16823,7 @@
       <c r="M283" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N283" s="25">
+      <c r="N283" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16302,7 +16859,7 @@
       <c r="M284" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N284" s="25">
+      <c r="N284" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16338,7 +16895,7 @@
       <c r="M285" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N285" s="25">
+      <c r="N285" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16376,7 +16933,7 @@
       <c r="M286" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N286" s="25">
+      <c r="N286" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16420,7 +16977,7 @@
       <c r="M287" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N287" s="25">
+      <c r="N287" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16462,7 +17019,7 @@
       <c r="M288" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N288" s="25">
+      <c r="N288" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16504,7 +17061,7 @@
       <c r="M289" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N289" s="25">
+      <c r="N289" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16546,7 +17103,7 @@
       <c r="M290" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N290" s="25">
+      <c r="N290" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16586,7 +17143,7 @@
       <c r="M291" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N291" s="25">
+      <c r="N291" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16624,7 +17181,7 @@
       <c r="M292" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N292" s="25">
+      <c r="N292" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16666,7 +17223,7 @@
       <c r="M293" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N293" s="25">
+      <c r="N293" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16706,7 +17263,7 @@
       <c r="M294" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N294" s="25">
+      <c r="N294" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16746,7 +17303,7 @@
       <c r="M295" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N295" s="25">
+      <c r="N295" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16790,7 +17347,7 @@
       <c r="M296" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N296" s="25">
+      <c r="N296" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16832,7 +17389,7 @@
       <c r="M297" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N297" s="25">
+      <c r="N297" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16872,7 +17429,7 @@
       <c r="M298" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N298" s="25">
+      <c r="N298" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16916,7 +17473,7 @@
       <c r="M299" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N299" s="25">
+      <c r="N299" s="24">
         <v>6</v>
       </c>
     </row>
@@ -16960,7 +17517,7 @@
       <c r="M300" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N300" s="25">
+      <c r="N300" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17004,7 +17561,7 @@
       <c r="M301" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N301" s="25">
+      <c r="N301" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17046,7 +17603,7 @@
       <c r="M302" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N302" s="25">
+      <c r="N302" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17084,7 +17641,7 @@
       <c r="M303" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N303" s="25">
+      <c r="N303" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17124,7 +17681,7 @@
       <c r="M304" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N304" s="25">
+      <c r="N304" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17166,7 +17723,7 @@
       <c r="M305" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N305" s="25">
+      <c r="N305" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17208,7 +17765,7 @@
       <c r="M306" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N306" s="25">
+      <c r="N306" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17250,7 +17807,7 @@
       <c r="M307" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N307" s="25">
+      <c r="N307" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17292,7 +17849,7 @@
       <c r="M308" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N308" s="25">
+      <c r="N308" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17334,7 +17891,7 @@
       <c r="M309" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N309" s="25">
+      <c r="N309" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17376,7 +17933,7 @@
       <c r="M310" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N310" s="25">
+      <c r="N310" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17418,7 +17975,7 @@
       <c r="M311" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N311" s="25">
+      <c r="N311" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17460,7 +18017,7 @@
       <c r="M312" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N312" s="25">
+      <c r="N312" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17498,7 +18055,7 @@
       <c r="M313" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N313" s="25">
+      <c r="N313" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17540,7 +18097,7 @@
       <c r="M314" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N314" s="25">
+      <c r="N314" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17582,7 +18139,7 @@
       <c r="M315" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N315" s="25">
+      <c r="N315" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17624,7 +18181,7 @@
       <c r="M316" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N316" s="25">
+      <c r="N316" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17662,7 +18219,7 @@
       <c r="M317" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N317" s="25">
+      <c r="N317" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17702,7 +18259,7 @@
       <c r="M318" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N318" s="25">
+      <c r="N318" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17744,7 +18301,7 @@
       <c r="M319" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N319" s="25">
+      <c r="N319" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17786,7 +18343,7 @@
       <c r="M320" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N320" s="25">
+      <c r="N320" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17828,7 +18385,7 @@
       <c r="M321" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N321" s="25">
+      <c r="N321" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17870,7 +18427,7 @@
       <c r="M322" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N322" s="25">
+      <c r="N322" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17906,7 +18463,7 @@
       <c r="M323" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N323" s="25">
+      <c r="N323" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17946,7 +18503,7 @@
       <c r="M324" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N324" s="25">
+      <c r="N324" s="24">
         <v>6</v>
       </c>
     </row>
@@ -17990,7 +18547,7 @@
       <c r="M325" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N325" s="25">
+      <c r="N325" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18034,7 +18591,7 @@
       <c r="M326" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N326" s="25">
+      <c r="N326" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18076,7 +18633,7 @@
       <c r="M327" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N327" s="25">
+      <c r="N327" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18116,7 +18673,7 @@
       <c r="M328" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N328" s="25">
+      <c r="N328" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18160,7 +18717,7 @@
       <c r="M329" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N329" s="25">
+      <c r="N329" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18204,7 +18761,7 @@
       <c r="M330" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N330" s="25">
+      <c r="N330" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18242,7 +18799,7 @@
       <c r="M331" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N331" s="25">
+      <c r="N331" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18282,7 +18839,7 @@
       <c r="M332" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N332" s="25">
+      <c r="N332" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18322,7 +18879,7 @@
       <c r="M333" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N333" s="25">
+      <c r="N333" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18366,7 +18923,7 @@
       <c r="M334" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N334" s="25">
+      <c r="N334" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18404,7 +18961,7 @@
       <c r="M335" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N335" s="25">
+      <c r="N335" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18446,7 +19003,7 @@
       <c r="M336" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N336" s="25">
+      <c r="N336" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18488,7 +19045,7 @@
       <c r="M337" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N337" s="25">
+      <c r="N337" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18532,7 +19089,7 @@
       <c r="M338" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N338" s="25">
+      <c r="N338" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18574,7 +19131,7 @@
       <c r="M339" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N339" s="25">
+      <c r="N339" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18618,7 +19175,7 @@
       <c r="M340" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N340" s="25">
+      <c r="N340" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18658,7 +19215,7 @@
       <c r="M341" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N341" s="25">
+      <c r="N341" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18702,7 +19259,7 @@
       <c r="M342" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N342" s="25">
+      <c r="N342" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18746,7 +19303,7 @@
       <c r="M343" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N343" s="25">
+      <c r="N343" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18786,7 +19343,7 @@
       <c r="M344" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N344" s="25">
+      <c r="N344" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18828,7 +19385,7 @@
       <c r="M345" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N345" s="25">
+      <c r="N345" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18872,7 +19429,7 @@
       <c r="M346" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N346" s="25">
+      <c r="N346" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18910,7 +19467,7 @@
       <c r="M347" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N347" s="25">
+      <c r="N347" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18952,7 +19509,7 @@
       <c r="M348" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N348" s="25">
+      <c r="N348" s="24">
         <v>6</v>
       </c>
     </row>
@@ -18996,7 +19553,7 @@
       <c r="M349" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N349" s="25">
+      <c r="N349" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19040,7 +19597,7 @@
       <c r="M350" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N350" s="25">
+      <c r="N350" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19078,7 +19635,7 @@
       <c r="M351" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N351" s="25">
+      <c r="N351" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19122,7 +19679,7 @@
       <c r="M352" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N352" s="25">
+      <c r="N352" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19158,7 +19715,7 @@
       <c r="M353" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N353" s="25">
+      <c r="N353" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19202,7 +19759,7 @@
       <c r="M354" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N354" s="25">
+      <c r="N354" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19244,7 +19801,7 @@
       <c r="M355" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N355" s="25">
+      <c r="N355" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19288,7 +19845,7 @@
       <c r="M356" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N356" s="25">
+      <c r="N356" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19332,7 +19889,7 @@
       <c r="M357" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N357" s="25">
+      <c r="N357" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19376,7 +19933,7 @@
       <c r="M358" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N358" s="25">
+      <c r="N358" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19416,7 +19973,7 @@
       <c r="M359" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N359" s="25">
+      <c r="N359" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19456,7 +20013,7 @@
       <c r="M360" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N360" s="25">
+      <c r="N360" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19498,7 +20055,7 @@
       <c r="M361" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N361" s="25">
+      <c r="N361" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19538,7 +20095,7 @@
       <c r="M362" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N362" s="25">
+      <c r="N362" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19580,7 +20137,7 @@
       <c r="M363" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N363" s="25">
+      <c r="N363" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19624,7 +20181,7 @@
       <c r="M364" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N364" s="25">
+      <c r="N364" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19666,7 +20223,7 @@
       <c r="M365" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N365" s="25">
+      <c r="N365" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19710,7 +20267,7 @@
       <c r="M366" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N366" s="25">
+      <c r="N366" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19746,7 +20303,7 @@
       <c r="M367" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N367" s="25">
+      <c r="N367" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19788,7 +20345,7 @@
       <c r="M368" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N368" s="25">
+      <c r="N368" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19830,7 +20387,7 @@
       <c r="M369" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N369" s="25">
+      <c r="N369" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19872,7 +20429,7 @@
       <c r="M370" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N370" s="25">
+      <c r="N370" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19914,7 +20471,7 @@
       <c r="M371" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N371" s="25">
+      <c r="N371" s="24">
         <v>6</v>
       </c>
     </row>
@@ -19958,7 +20515,7 @@
       <c r="M372" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N372" s="25">
+      <c r="N372" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20002,7 +20559,7 @@
       <c r="M373" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N373" s="25">
+      <c r="N373" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20044,7 +20601,7 @@
       <c r="M374" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N374" s="25">
+      <c r="N374" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20086,7 +20643,7 @@
       <c r="M375" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N375" s="25">
+      <c r="N375" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20128,7 +20685,7 @@
       <c r="M376" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N376" s="25">
+      <c r="N376" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20170,7 +20727,7 @@
       <c r="M377" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N377" s="25">
+      <c r="N377" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20214,7 +20771,7 @@
       <c r="M378" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N378" s="25">
+      <c r="N378" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20258,7 +20815,7 @@
       <c r="M379" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N379" s="25">
+      <c r="N379" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20294,7 +20851,7 @@
       <c r="M380" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N380" s="25">
+      <c r="N380" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20336,7 +20893,7 @@
       <c r="M381" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N381" s="25">
+      <c r="N381" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20378,7 +20935,7 @@
       <c r="M382" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N382" s="25">
+      <c r="N382" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20418,7 +20975,7 @@
       <c r="M383" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N383" s="25">
+      <c r="N383" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20458,7 +21015,7 @@
       <c r="M384" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N384" s="25">
+      <c r="N384" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20500,7 +21057,7 @@
       <c r="M385" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N385" s="25">
+      <c r="N385" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20542,7 +21099,7 @@
       <c r="M386" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N386" s="25">
+      <c r="N386" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20582,7 +21139,7 @@
       <c r="M387" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N387" s="25">
+      <c r="N387" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20626,7 +21183,7 @@
       <c r="M388" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N388" s="25">
+      <c r="N388" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20668,7 +21225,7 @@
       <c r="M389" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N389" s="25">
+      <c r="N389" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20712,7 +21269,7 @@
       <c r="M390" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N390" s="25">
+      <c r="N390" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20750,7 +21307,7 @@
       <c r="M391" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N391" s="25">
+      <c r="N391" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20792,7 +21349,7 @@
       <c r="M392" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N392" s="25">
+      <c r="N392" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20834,7 +21391,7 @@
       <c r="M393" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N393" s="25">
+      <c r="N393" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20874,7 +21431,7 @@
       <c r="M394" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N394" s="25">
+      <c r="N394" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20918,7 +21475,7 @@
       <c r="M395" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N395" s="25">
+      <c r="N395" s="24">
         <v>6</v>
       </c>
     </row>
@@ -20960,7 +21517,7 @@
       <c r="M396" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N396" s="25">
+      <c r="N396" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21000,7 +21557,7 @@
       <c r="M397" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N397" s="25">
+      <c r="N397" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21044,7 +21601,7 @@
       <c r="M398" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N398" s="25">
+      <c r="N398" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21088,7 +21645,7 @@
       <c r="M399" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N399" s="25">
+      <c r="N399" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21126,7 +21683,7 @@
       <c r="M400" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N400" s="25">
+      <c r="N400" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21168,7 +21725,7 @@
       <c r="M401" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N401" s="25">
+      <c r="N401" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21208,7 +21765,7 @@
       <c r="M402" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N402" s="25">
+      <c r="N402" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21246,7 +21803,7 @@
       <c r="M403" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N403" s="25">
+      <c r="N403" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21284,7 +21841,7 @@
       <c r="M404" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N404" s="25">
+      <c r="N404" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21324,7 +21881,7 @@
       <c r="M405" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N405" s="25">
+      <c r="N405" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21364,7 +21921,7 @@
       <c r="M406" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N406" s="25">
+      <c r="N406" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21402,7 +21959,7 @@
       <c r="M407" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N407" s="25">
+      <c r="N407" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21442,7 +21999,7 @@
       <c r="M408" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N408" s="25">
+      <c r="N408" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21482,7 +22039,7 @@
       <c r="M409" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N409" s="25">
+      <c r="N409" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21524,7 +22081,7 @@
       <c r="M410" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N410" s="25">
+      <c r="N410" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21564,7 +22121,7 @@
       <c r="M411" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N411" s="25">
+      <c r="N411" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21606,7 +22163,7 @@
       <c r="M412" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N412" s="25">
+      <c r="N412" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21650,7 +22207,7 @@
       <c r="M413" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N413" s="25">
+      <c r="N413" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21692,7 +22249,7 @@
       <c r="M414" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N414" s="25">
+      <c r="N414" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21732,7 +22289,7 @@
       <c r="M415" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N415" s="25">
+      <c r="N415" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21774,7 +22331,7 @@
       <c r="M416" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N416" s="25">
+      <c r="N416" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21810,7 +22367,7 @@
       <c r="M417" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N417" s="25">
+      <c r="N417" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21854,7 +22411,7 @@
       <c r="M418" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N418" s="25">
+      <c r="N418" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21896,7 +22453,7 @@
       <c r="M419" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N419" s="25">
+      <c r="N419" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21938,7 +22495,7 @@
       <c r="M420" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N420" s="25">
+      <c r="N420" s="24">
         <v>6</v>
       </c>
     </row>
@@ -21976,7 +22533,7 @@
       <c r="M421" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N421" s="25">
+      <c r="N421" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22020,7 +22577,7 @@
       <c r="M422" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N422" s="25">
+      <c r="N422" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22062,7 +22619,7 @@
       <c r="M423" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N423" s="25">
+      <c r="N423" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22104,7 +22661,7 @@
       <c r="M424" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N424" s="25">
+      <c r="N424" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22146,7 +22703,7 @@
       <c r="M425" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N425" s="25">
+      <c r="N425" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22184,7 +22741,7 @@
       <c r="M426" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N426" s="25">
+      <c r="N426" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22222,7 +22779,7 @@
       <c r="M427" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N427" s="25">
+      <c r="N427" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22260,7 +22817,7 @@
       <c r="M428" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N428" s="25">
+      <c r="N428" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22298,7 +22855,7 @@
       <c r="M429" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N429" s="25">
+      <c r="N429" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22342,7 +22899,7 @@
       <c r="M430" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N430" s="25">
+      <c r="N430" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22386,7 +22943,7 @@
       <c r="M431" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N431" s="25">
+      <c r="N431" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22430,7 +22987,7 @@
       <c r="M432" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N432" s="25">
+      <c r="N432" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22472,7 +23029,7 @@
       <c r="M433" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N433" s="25">
+      <c r="N433" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22512,7 +23069,7 @@
       <c r="M434" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N434" s="25">
+      <c r="N434" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22556,7 +23113,7 @@
       <c r="M435" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N435" s="25">
+      <c r="N435" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22600,7 +23157,7 @@
       <c r="M436" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N436" s="25">
+      <c r="N436" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22644,7 +23201,7 @@
       <c r="M437" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N437" s="25">
+      <c r="N437" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22688,7 +23245,7 @@
       <c r="M438" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N438" s="25">
+      <c r="N438" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22732,7 +23289,7 @@
       <c r="M439" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N439" s="25">
+      <c r="N439" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22770,7 +23327,7 @@
       <c r="M440" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N440" s="25">
+      <c r="N440" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22812,7 +23369,7 @@
       <c r="M441" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N441" s="25">
+      <c r="N441" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22854,7 +23411,7 @@
       <c r="M442" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N442" s="25">
+      <c r="N442" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22896,7 +23453,7 @@
       <c r="M443" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N443" s="25">
+      <c r="N443" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22938,7 +23495,7 @@
       <c r="M444" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N444" s="25">
+      <c r="N444" s="24">
         <v>6</v>
       </c>
     </row>
@@ -22973,295 +23530,2647 @@
       <c r="J445" s="11" t="s">
         <v>1299</v>
       </c>
-      <c r="K445" s="8"/>
+      <c r="K445" s="8" t="s">
+        <v>1448</v>
+      </c>
       <c r="L445" s="8"/>
       <c r="M445" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N445" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="446" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A446" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B446" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C446" t="s">
+        <v>205</v>
+      </c>
+      <c r="D446" t="s">
+        <v>34</v>
+      </c>
+      <c r="E446" t="s">
+        <v>16</v>
+      </c>
+      <c r="F446">
+        <v>5123</v>
+      </c>
+      <c r="G446" t="s">
+        <v>251</v>
+      </c>
+      <c r="H446" t="s">
+        <v>38</v>
+      </c>
+      <c r="K446" t="s">
+        <v>54</v>
+      </c>
+      <c r="L446" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M446" t="s">
+        <v>67</v>
+      </c>
+      <c r="N446">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="447" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A447" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B447" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C447" t="s">
+        <v>401</v>
+      </c>
+      <c r="D447" t="s">
+        <v>34</v>
+      </c>
+      <c r="E447" t="s">
+        <v>13</v>
+      </c>
+      <c r="F447">
+        <v>7186</v>
+      </c>
+      <c r="G447" t="s">
+        <v>50</v>
+      </c>
+      <c r="H447" t="s">
+        <v>11</v>
+      </c>
+      <c r="J447" t="s">
+        <v>1451</v>
+      </c>
+      <c r="K447" t="s">
+        <v>56</v>
+      </c>
+      <c r="L447" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M447" t="s">
+        <v>67</v>
+      </c>
+      <c r="N447">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="448" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A448" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B448" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C448" t="s">
+        <v>100</v>
+      </c>
+      <c r="D448" t="s">
+        <v>34</v>
+      </c>
+      <c r="E448" t="s">
+        <v>23</v>
+      </c>
+      <c r="F448">
+        <v>1709</v>
+      </c>
+      <c r="G448" t="s">
+        <v>65</v>
+      </c>
+      <c r="H448" t="s">
+        <v>11</v>
+      </c>
+      <c r="I448" t="s">
+        <v>1453</v>
+      </c>
+      <c r="K448" t="s">
+        <v>921</v>
+      </c>
+      <c r="L448" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M448" t="s">
+        <v>67</v>
+      </c>
+      <c r="N448">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="449" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A449" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B449" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C449" t="s">
+        <v>556</v>
+      </c>
+      <c r="D449" t="s">
+        <v>34</v>
+      </c>
+      <c r="E449" t="s">
+        <v>17</v>
+      </c>
+      <c r="F449">
+        <v>6333</v>
+      </c>
+      <c r="G449" t="s">
+        <v>43</v>
+      </c>
+      <c r="H449" t="s">
+        <v>11</v>
+      </c>
+      <c r="I449" t="s">
+        <v>1455</v>
+      </c>
+      <c r="J449" t="s">
+        <v>1456</v>
+      </c>
+      <c r="K449" t="s">
+        <v>54</v>
+      </c>
+      <c r="L449" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M449" t="s">
+        <v>67</v>
+      </c>
+      <c r="N449">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="450" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A450" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B450" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C450" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D450" t="s">
+        <v>34</v>
+      </c>
+      <c r="E450" t="s">
+        <v>12</v>
+      </c>
+      <c r="F450">
+        <v>10966</v>
+      </c>
+      <c r="G450" t="s">
+        <v>254</v>
+      </c>
+      <c r="H450" t="s">
+        <v>41</v>
+      </c>
+      <c r="J450" t="s">
+        <v>1459</v>
+      </c>
+      <c r="K450" t="s">
+        <v>55</v>
+      </c>
+      <c r="L450" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M450" t="s">
+        <v>67</v>
+      </c>
+      <c r="N450">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="451" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A451" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B451" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C451" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D451" t="s">
+        <v>34</v>
+      </c>
+      <c r="E451" t="s">
+        <v>16</v>
+      </c>
+      <c r="F451">
+        <v>4783</v>
+      </c>
+      <c r="G451" t="s">
+        <v>199</v>
+      </c>
+      <c r="H451" t="s">
+        <v>11</v>
+      </c>
+      <c r="I451" t="s">
+        <v>1461</v>
+      </c>
+      <c r="J451" t="s">
+        <v>1462</v>
+      </c>
+      <c r="K451" t="s">
+        <v>54</v>
+      </c>
+      <c r="L451" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M451" t="s">
+        <v>67</v>
+      </c>
+      <c r="N451">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="452" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A452" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B452" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C452" s="28">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="D452" t="s">
+        <v>34</v>
+      </c>
+      <c r="E452" t="s">
+        <v>20</v>
+      </c>
+      <c r="F452">
+        <v>11312</v>
+      </c>
+      <c r="G452" t="s">
+        <v>59</v>
+      </c>
+      <c r="H452" t="s">
+        <v>38</v>
+      </c>
+      <c r="J452" t="s">
+        <v>1464</v>
+      </c>
+      <c r="M452" t="s">
         <v>66</v>
       </c>
-      <c r="N445" s="25">
+      <c r="N452">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="453" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A453" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B453" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C453" t="s">
+        <v>68</v>
+      </c>
+      <c r="D453" t="s">
+        <v>34</v>
+      </c>
+      <c r="E453" t="s">
+        <v>13</v>
+      </c>
+      <c r="F453">
+        <v>11158</v>
+      </c>
+      <c r="G453" t="s">
+        <v>51</v>
+      </c>
+      <c r="H453" t="s">
+        <v>52</v>
+      </c>
+      <c r="I453" s="29" t="s">
+        <v>1466</v>
+      </c>
+      <c r="J453" t="s">
+        <v>1467</v>
+      </c>
+      <c r="M453" t="s">
+        <v>66</v>
+      </c>
+      <c r="N453">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="454" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A454" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B454" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C454" t="s">
+        <v>29</v>
+      </c>
+      <c r="D454" t="s">
+        <v>34</v>
+      </c>
+      <c r="E454" t="s">
+        <v>12</v>
+      </c>
+      <c r="F454">
+        <v>7183</v>
+      </c>
+      <c r="G454" t="s">
+        <v>44</v>
+      </c>
+      <c r="H454" t="s">
+        <v>41</v>
+      </c>
+      <c r="J454" t="s">
+        <v>1469</v>
+      </c>
+      <c r="K454" t="s">
+        <v>55</v>
+      </c>
+      <c r="L454" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M454" t="s">
+        <v>67</v>
+      </c>
+      <c r="N454">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="455" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A455" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B455" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C455" s="28">
+        <v>0.46875</v>
+      </c>
+      <c r="D455" t="s">
+        <v>34</v>
+      </c>
+      <c r="E455" t="s">
+        <v>210</v>
+      </c>
+      <c r="F455">
+        <v>3958</v>
+      </c>
+      <c r="G455" t="s">
+        <v>44</v>
+      </c>
+      <c r="H455" t="s">
+        <v>11</v>
+      </c>
+      <c r="I455" t="s">
+        <v>1471</v>
+      </c>
+      <c r="J455" t="s">
+        <v>1472</v>
+      </c>
+      <c r="K455" t="s">
+        <v>56</v>
+      </c>
+      <c r="L455" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M455" t="s">
+        <v>67</v>
+      </c>
+      <c r="N455">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="456" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A456" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B456" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C456" t="s">
+        <v>741</v>
+      </c>
+      <c r="D456" t="s">
+        <v>34</v>
+      </c>
+      <c r="E456" t="s">
+        <v>64</v>
+      </c>
+      <c r="F456">
+        <v>2033</v>
+      </c>
+      <c r="G456" t="s">
+        <v>63</v>
+      </c>
+      <c r="H456" t="s">
+        <v>52</v>
+      </c>
+      <c r="I456" t="s">
+        <v>1474</v>
+      </c>
+      <c r="K456" t="s">
+        <v>56</v>
+      </c>
+      <c r="L456" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M456" t="s">
+        <v>67</v>
+      </c>
+      <c r="N456">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="457" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B457" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C457" t="s">
+        <v>588</v>
+      </c>
+      <c r="D457" t="s">
+        <v>34</v>
+      </c>
+      <c r="E457" t="s">
+        <v>16</v>
+      </c>
+      <c r="F457">
+        <v>5137</v>
+      </c>
+      <c r="G457" t="s">
+        <v>199</v>
+      </c>
+      <c r="H457" t="s">
+        <v>52</v>
+      </c>
+      <c r="I457" t="s">
+        <v>1476</v>
+      </c>
+      <c r="K457" t="s">
+        <v>55</v>
+      </c>
+      <c r="L457" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M457" t="s">
+        <v>67</v>
+      </c>
+      <c r="N457">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="458" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B458" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C458" t="s">
+        <v>753</v>
+      </c>
+      <c r="D458" t="s">
+        <v>34</v>
+      </c>
+      <c r="E458" t="s">
+        <v>13</v>
+      </c>
+      <c r="F458">
+        <v>7169</v>
+      </c>
+      <c r="G458" t="s">
+        <v>49</v>
+      </c>
+      <c r="H458" t="s">
+        <v>37</v>
+      </c>
+      <c r="I458" t="s">
+        <v>1301</v>
+      </c>
+      <c r="J458" t="s">
+        <v>1302</v>
+      </c>
+      <c r="K458" t="s">
+        <v>55</v>
+      </c>
+      <c r="L458" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M458" t="s">
+        <v>67</v>
+      </c>
+      <c r="N458">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="459" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A459" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B459" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C459" t="s">
+        <v>460</v>
+      </c>
+      <c r="D459" t="s">
+        <v>34</v>
+      </c>
+      <c r="E459" t="s">
+        <v>19</v>
+      </c>
+      <c r="F459">
+        <v>6609</v>
+      </c>
+      <c r="G459" t="s">
+        <v>42</v>
+      </c>
+      <c r="H459" t="s">
+        <v>52</v>
+      </c>
+      <c r="I459" t="s">
+        <v>1304</v>
+      </c>
+      <c r="K459" t="s">
+        <v>55</v>
+      </c>
+      <c r="L459" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M459" t="s">
+        <v>67</v>
+      </c>
+      <c r="N459">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="460" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A460" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B460" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C460" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D460" t="s">
+        <v>34</v>
+      </c>
+      <c r="E460" t="s">
+        <v>16</v>
+      </c>
+      <c r="F460">
+        <v>4825</v>
+      </c>
+      <c r="G460" t="s">
+        <v>48</v>
+      </c>
+      <c r="H460" t="s">
+        <v>37</v>
+      </c>
+      <c r="I460" t="s">
+        <v>1307</v>
+      </c>
+      <c r="J460" t="s">
+        <v>1308</v>
+      </c>
+      <c r="M460" t="s">
+        <v>66</v>
+      </c>
+      <c r="N460">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="461" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A461" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B461" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C461" t="s">
+        <v>768</v>
+      </c>
+      <c r="D461" t="s">
+        <v>34</v>
+      </c>
+      <c r="E461" t="s">
+        <v>21</v>
+      </c>
+      <c r="F461">
+        <v>6067</v>
+      </c>
+      <c r="G461" t="s">
+        <v>43</v>
+      </c>
+      <c r="H461" t="s">
+        <v>52</v>
+      </c>
+      <c r="J461" t="s">
+        <v>1310</v>
+      </c>
+      <c r="K461" t="s">
+        <v>54</v>
+      </c>
+      <c r="L461" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M461" t="s">
+        <v>67</v>
+      </c>
+      <c r="N461">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="462" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A462" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B462" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C462" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D462" t="s">
+        <v>34</v>
+      </c>
+      <c r="E462" t="s">
+        <v>13</v>
+      </c>
+      <c r="F462">
+        <v>6868</v>
+      </c>
+      <c r="G462" t="s">
+        <v>57</v>
+      </c>
+      <c r="H462" t="s">
+        <v>11</v>
+      </c>
+      <c r="J462" t="s">
+        <v>1313</v>
+      </c>
+      <c r="M462" t="s">
+        <v>66</v>
+      </c>
+      <c r="N462">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="463" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A463" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B463" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C463" t="s">
+        <v>69</v>
+      </c>
+      <c r="D463" t="s">
+        <v>34</v>
+      </c>
+      <c r="E463" t="s">
+        <v>9</v>
+      </c>
+      <c r="F463">
+        <v>4240</v>
+      </c>
+      <c r="G463" t="s">
+        <v>40</v>
+      </c>
+      <c r="H463" t="s">
+        <v>52</v>
+      </c>
+      <c r="I463" t="s">
+        <v>1315</v>
+      </c>
+      <c r="K463" t="s">
+        <v>55</v>
+      </c>
+      <c r="L463" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M463" t="s">
+        <v>67</v>
+      </c>
+      <c r="N463">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="464" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A464" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B464" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C464" t="s">
+        <v>303</v>
+      </c>
+      <c r="D464" t="s">
+        <v>34</v>
+      </c>
+      <c r="E464" t="s">
+        <v>16</v>
+      </c>
+      <c r="F464">
+        <v>4849</v>
+      </c>
+      <c r="G464" t="s">
+        <v>48</v>
+      </c>
+      <c r="H464" t="s">
+        <v>52</v>
+      </c>
+      <c r="I464" t="s">
+        <v>1317</v>
+      </c>
+      <c r="M464" t="s">
+        <v>66</v>
+      </c>
+      <c r="N464">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="465" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A465" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B465" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C465" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D465" t="s">
+        <v>34</v>
+      </c>
+      <c r="E465" t="s">
+        <v>9</v>
+      </c>
+      <c r="F465">
+        <v>5726</v>
+      </c>
+      <c r="G465" t="s">
+        <v>40</v>
+      </c>
+      <c r="H465" t="s">
+        <v>52</v>
+      </c>
+      <c r="I465" t="s">
+        <v>1320</v>
+      </c>
+      <c r="J465" t="s">
+        <v>1321</v>
+      </c>
+      <c r="K465" t="s">
+        <v>55</v>
+      </c>
+      <c r="L465" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M465" t="s">
+        <v>67</v>
+      </c>
+      <c r="N465">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="466" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A466" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B466" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C466" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D466" t="s">
+        <v>34</v>
+      </c>
+      <c r="E466" t="s">
+        <v>13</v>
+      </c>
+      <c r="F466">
+        <v>6877</v>
+      </c>
+      <c r="G466" t="s">
+        <v>51</v>
+      </c>
+      <c r="H466" t="s">
+        <v>11</v>
+      </c>
+      <c r="I466" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K466" t="s">
+        <v>616</v>
+      </c>
+      <c r="L466" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M466" t="s">
+        <v>67</v>
+      </c>
+      <c r="N466">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="467" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A467" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B467" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C467" s="28">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="D467" t="s">
+        <v>34</v>
+      </c>
+      <c r="E467" t="s">
+        <v>20</v>
+      </c>
+      <c r="F467">
+        <v>9374</v>
+      </c>
+      <c r="G467" t="s">
+        <v>36</v>
+      </c>
+      <c r="H467" t="s">
+        <v>11</v>
+      </c>
+      <c r="K467" t="s">
+        <v>55</v>
+      </c>
+      <c r="L467" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M467" t="s">
+        <v>67</v>
+      </c>
+      <c r="N467">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="468" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A468" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B468" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C468" s="28">
+        <v>0.58263888888888893</v>
+      </c>
+      <c r="D468" t="s">
+        <v>34</v>
+      </c>
+      <c r="E468" t="s">
+        <v>20</v>
+      </c>
+      <c r="F468">
+        <v>5425</v>
+      </c>
+      <c r="G468" t="s">
+        <v>36</v>
+      </c>
+      <c r="H468" t="s">
+        <v>38</v>
+      </c>
+      <c r="K468" t="s">
+        <v>55</v>
+      </c>
+      <c r="L468" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M468" t="s">
+        <v>67</v>
+      </c>
+      <c r="N468">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="469" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A469" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B469" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C469" t="s">
+        <v>476</v>
+      </c>
+      <c r="D469" t="s">
+        <v>34</v>
+      </c>
+      <c r="E469" t="s">
+        <v>13</v>
+      </c>
+      <c r="F469">
+        <v>6348</v>
+      </c>
+      <c r="G469" t="s">
+        <v>49</v>
+      </c>
+      <c r="H469" t="s">
+        <v>52</v>
+      </c>
+      <c r="I469" s="29" t="s">
+        <v>1328</v>
+      </c>
+      <c r="J469" t="s">
+        <v>1329</v>
+      </c>
+      <c r="M469" t="s">
+        <v>66</v>
+      </c>
+      <c r="N469">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="470" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A470" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B470" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C470" s="28">
+        <v>0.58750000000000002</v>
+      </c>
+      <c r="D470" t="s">
+        <v>34</v>
+      </c>
+      <c r="E470" t="s">
+        <v>20</v>
+      </c>
+      <c r="F470">
+        <v>5459</v>
+      </c>
+      <c r="G470" t="s">
+        <v>36</v>
+      </c>
+      <c r="H470" t="s">
+        <v>52</v>
+      </c>
+      <c r="I470" t="s">
+        <v>1331</v>
+      </c>
+      <c r="K470" t="s">
+        <v>56</v>
+      </c>
+      <c r="L470" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M470" t="s">
+        <v>67</v>
+      </c>
+      <c r="N470">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="471" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A471" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B471" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C471" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D471" t="s">
+        <v>34</v>
+      </c>
+      <c r="E471" t="s">
+        <v>12</v>
+      </c>
+      <c r="F471">
+        <v>11183</v>
+      </c>
+      <c r="G471" t="s">
+        <v>254</v>
+      </c>
+      <c r="H471" t="s">
+        <v>37</v>
+      </c>
+      <c r="M471" t="s">
+        <v>66</v>
+      </c>
+      <c r="N471">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="472" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A472" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B472" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C472" s="28">
+        <v>0.6</v>
+      </c>
+      <c r="D472" t="s">
+        <v>34</v>
+      </c>
+      <c r="E472" t="s">
+        <v>210</v>
+      </c>
+      <c r="F472">
+        <v>10721</v>
+      </c>
+      <c r="G472" t="s">
+        <v>378</v>
+      </c>
+      <c r="H472" t="s">
+        <v>52</v>
+      </c>
+      <c r="I472" t="s">
+        <v>1335</v>
+      </c>
+      <c r="K472" t="s">
+        <v>54</v>
+      </c>
+      <c r="L472" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M472" t="s">
+        <v>67</v>
+      </c>
+      <c r="N472">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="473" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A473" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B473" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C473" t="s">
+        <v>331</v>
+      </c>
+      <c r="D473" t="s">
+        <v>34</v>
+      </c>
+      <c r="E473" t="s">
+        <v>16</v>
+      </c>
+      <c r="F473">
+        <v>4814</v>
+      </c>
+      <c r="G473" t="s">
+        <v>36</v>
+      </c>
+      <c r="H473" t="s">
+        <v>11</v>
+      </c>
+      <c r="I473" t="s">
+        <v>1337</v>
+      </c>
+      <c r="J473" t="s">
+        <v>1338</v>
+      </c>
+      <c r="K473" t="s">
+        <v>45</v>
+      </c>
+      <c r="L473" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M473" t="s">
+        <v>67</v>
+      </c>
+      <c r="N473">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="474" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A474" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B474" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C474" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D474" t="s">
+        <v>34</v>
+      </c>
+      <c r="E474" t="s">
+        <v>19</v>
+      </c>
+      <c r="F474">
+        <v>3688</v>
+      </c>
+      <c r="G474" t="s">
+        <v>47</v>
+      </c>
+      <c r="H474" t="s">
+        <v>11</v>
+      </c>
+      <c r="I474" t="s">
+        <v>1341</v>
+      </c>
+      <c r="K474" t="s">
+        <v>55</v>
+      </c>
+      <c r="L474" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M474" t="s">
+        <v>67</v>
+      </c>
+      <c r="N474">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="475" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A475" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B475" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C475" s="28">
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="D475" t="s">
+        <v>34</v>
+      </c>
+      <c r="E475" t="s">
+        <v>20</v>
+      </c>
+      <c r="F475">
+        <v>5429</v>
+      </c>
+      <c r="G475" t="s">
+        <v>50</v>
+      </c>
+      <c r="H475" t="s">
+        <v>41</v>
+      </c>
+      <c r="M475" t="s">
+        <v>66</v>
+      </c>
+      <c r="N475">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="476" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A476" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B476" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C476" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D476" t="s">
+        <v>34</v>
+      </c>
+      <c r="E476" t="s">
+        <v>16</v>
+      </c>
+      <c r="F476">
+        <v>4807</v>
+      </c>
+      <c r="G476" t="s">
+        <v>48</v>
+      </c>
+      <c r="H476" t="s">
+        <v>11</v>
+      </c>
+      <c r="I476" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J476" t="s">
+        <v>1346</v>
+      </c>
+      <c r="M476" t="s">
+        <v>66</v>
+      </c>
+      <c r="N476">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="477" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A477" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B477" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C477" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D477" t="s">
+        <v>34</v>
+      </c>
+      <c r="E477" t="s">
+        <v>16</v>
+      </c>
+      <c r="F477">
+        <v>4869</v>
+      </c>
+      <c r="G477" t="s">
+        <v>48</v>
+      </c>
+      <c r="H477" t="s">
+        <v>35</v>
+      </c>
+      <c r="M477" t="s">
+        <v>66</v>
+      </c>
+      <c r="N477">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="478" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A478" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B478" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C478" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D478" t="s">
+        <v>34</v>
+      </c>
+      <c r="E478" t="s">
+        <v>16</v>
+      </c>
+      <c r="F478">
+        <v>4854</v>
+      </c>
+      <c r="G478" t="s">
+        <v>48</v>
+      </c>
+      <c r="H478" t="s">
+        <v>41</v>
+      </c>
+      <c r="J478" t="s">
+        <v>1351</v>
+      </c>
+      <c r="M478" t="s">
+        <v>66</v>
+      </c>
+      <c r="N478">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="479" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A479" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B479" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C479" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D479" t="s">
+        <v>34</v>
+      </c>
+      <c r="E479" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F479">
+        <v>61</v>
+      </c>
+      <c r="G479" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H479" t="s">
+        <v>52</v>
+      </c>
+      <c r="I479" t="s">
+        <v>1356</v>
+      </c>
+      <c r="J479" t="s">
+        <v>1357</v>
+      </c>
+      <c r="K479" t="s">
+        <v>45</v>
+      </c>
+      <c r="L479" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M479" t="s">
+        <v>67</v>
+      </c>
+      <c r="N479">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="480" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A480" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B480" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C480" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D480" t="s">
+        <v>34</v>
+      </c>
+      <c r="E480" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F480">
+        <v>219</v>
+      </c>
+      <c r="G480" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H480" t="s">
+        <v>37</v>
+      </c>
+      <c r="I480" t="s">
+        <v>1360</v>
+      </c>
+      <c r="J480" t="s">
+        <v>1361</v>
+      </c>
+      <c r="K480" t="s">
+        <v>54</v>
+      </c>
+      <c r="L480" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M480" t="s">
+        <v>67</v>
+      </c>
+      <c r="N480">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="481" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A481" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B481" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C481" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D481" t="s">
+        <v>34</v>
+      </c>
+      <c r="E481" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F481">
+        <v>224</v>
+      </c>
+      <c r="G481" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H481" t="s">
+        <v>37</v>
+      </c>
+      <c r="I481" t="s">
+        <v>1364</v>
+      </c>
+      <c r="J481" t="s">
+        <v>1365</v>
+      </c>
+      <c r="K481" t="s">
+        <v>45</v>
+      </c>
+      <c r="L481" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M481" t="s">
+        <v>67</v>
+      </c>
+      <c r="N481">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="482" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A482" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B482" s="25">
+        <v>46184</v>
+      </c>
+      <c r="C482" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D482" t="s">
+        <v>34</v>
+      </c>
+      <c r="E482" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F482">
+        <v>2225</v>
+      </c>
+      <c r="G482" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H482" t="s">
+        <v>37</v>
+      </c>
+      <c r="I482" t="s">
+        <v>1368</v>
+      </c>
+      <c r="J482" t="s">
+        <v>1369</v>
+      </c>
+      <c r="K482" t="s">
+        <v>55</v>
+      </c>
+      <c r="L482" s="25">
+        <v>46184</v>
+      </c>
+      <c r="M482" t="s">
+        <v>67</v>
+      </c>
+      <c r="N482">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="483" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A483" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B483" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C483" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D483" t="s">
+        <v>34</v>
+      </c>
+      <c r="E483" t="s">
+        <v>323</v>
+      </c>
+      <c r="F483">
+        <v>936</v>
+      </c>
+      <c r="G483" t="s">
+        <v>324</v>
+      </c>
+      <c r="H483" t="s">
+        <v>11</v>
+      </c>
+      <c r="I483" t="s">
+        <v>1372</v>
+      </c>
+      <c r="M483" t="s">
+        <v>66</v>
+      </c>
+      <c r="N483">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="484" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A484" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B484" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C484" t="s">
+        <v>80</v>
+      </c>
+      <c r="D484" t="s">
+        <v>34</v>
+      </c>
+      <c r="E484" t="s">
+        <v>16</v>
+      </c>
+      <c r="F484">
+        <v>5791</v>
+      </c>
+      <c r="G484" t="s">
+        <v>49</v>
+      </c>
+      <c r="H484" t="s">
+        <v>38</v>
+      </c>
+      <c r="I484" t="s">
+        <v>1374</v>
+      </c>
+      <c r="J484" t="s">
+        <v>1375</v>
+      </c>
+      <c r="K484" t="s">
+        <v>55</v>
+      </c>
+      <c r="L484" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M484" t="s">
+        <v>67</v>
+      </c>
+      <c r="N484">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="485" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A485" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B485" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C485" t="s">
+        <v>509</v>
+      </c>
+      <c r="D485" t="s">
+        <v>34</v>
+      </c>
+      <c r="E485" t="s">
+        <v>64</v>
+      </c>
+      <c r="F485">
+        <v>1830</v>
+      </c>
+      <c r="G485" t="s">
+        <v>63</v>
+      </c>
+      <c r="H485" t="s">
+        <v>11</v>
+      </c>
+      <c r="I485" t="s">
+        <v>1377</v>
+      </c>
+      <c r="J485" t="s">
+        <v>1378</v>
+      </c>
+      <c r="K485" t="s">
+        <v>56</v>
+      </c>
+      <c r="L485" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M485" t="s">
+        <v>67</v>
+      </c>
+      <c r="N485">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="486" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A486" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B486" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C486" s="28">
+        <v>0.37222222222222223</v>
+      </c>
+      <c r="D486" t="s">
+        <v>34</v>
+      </c>
+      <c r="E486" t="s">
+        <v>20</v>
+      </c>
+      <c r="F486">
+        <v>2345</v>
+      </c>
+      <c r="G486" t="s">
+        <v>199</v>
+      </c>
+      <c r="H486" t="s">
+        <v>11</v>
+      </c>
+      <c r="M486" t="s">
+        <v>66</v>
+      </c>
+      <c r="N486">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="487" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A487" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B487" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C487" s="28">
+        <v>0.37986111111111109</v>
+      </c>
+      <c r="D487" t="s">
+        <v>34</v>
+      </c>
+      <c r="E487" t="s">
+        <v>20</v>
+      </c>
+      <c r="F487">
+        <v>3460</v>
+      </c>
+      <c r="G487" t="s">
+        <v>43</v>
+      </c>
+      <c r="H487" t="s">
+        <v>38</v>
+      </c>
+      <c r="K487" t="s">
+        <v>54</v>
+      </c>
+      <c r="L487" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M487" t="s">
+        <v>67</v>
+      </c>
+      <c r="N487">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="488" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A488" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B488" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C488" t="s">
+        <v>983</v>
+      </c>
+      <c r="D488" t="s">
+        <v>34</v>
+      </c>
+      <c r="E488" t="s">
+        <v>12</v>
+      </c>
+      <c r="F488">
+        <v>2940</v>
+      </c>
+      <c r="G488" t="s">
+        <v>61</v>
+      </c>
+      <c r="H488" t="s">
+        <v>38</v>
+      </c>
+      <c r="J488" t="s">
+        <v>1382</v>
+      </c>
+      <c r="M488" t="s">
+        <v>66</v>
+      </c>
+      <c r="N488">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="489" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A489" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B489" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C489" t="s">
+        <v>530</v>
+      </c>
+      <c r="D489" t="s">
+        <v>34</v>
+      </c>
+      <c r="E489" t="s">
+        <v>9</v>
+      </c>
+      <c r="F489">
+        <v>5172</v>
+      </c>
+      <c r="G489" t="s">
+        <v>43</v>
+      </c>
+      <c r="H489" t="s">
+        <v>11</v>
+      </c>
+      <c r="I489" t="s">
+        <v>1384</v>
+      </c>
+      <c r="J489" t="s">
+        <v>1385</v>
+      </c>
+      <c r="K489" t="s">
+        <v>1386</v>
+      </c>
+      <c r="L489" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M489" t="s">
+        <v>67</v>
+      </c>
+      <c r="N489">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="490" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A490" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B490" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C490" t="s">
+        <v>534</v>
+      </c>
+      <c r="D490" t="s">
+        <v>34</v>
+      </c>
+      <c r="E490" t="s">
+        <v>17</v>
+      </c>
+      <c r="F490">
+        <v>11243</v>
+      </c>
+      <c r="G490" t="s">
+        <v>39</v>
+      </c>
+      <c r="H490" t="s">
+        <v>38</v>
+      </c>
+      <c r="I490" t="s">
+        <v>1388</v>
+      </c>
+      <c r="J490" t="s">
+        <v>1389</v>
+      </c>
+      <c r="K490" t="s">
+        <v>55</v>
+      </c>
+      <c r="L490" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M490" t="s">
+        <v>67</v>
+      </c>
+      <c r="N490">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="491" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A491" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B491" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C491" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D491" t="s">
+        <v>34</v>
+      </c>
+      <c r="E491" t="s">
+        <v>17</v>
+      </c>
+      <c r="F491">
+        <v>7242</v>
+      </c>
+      <c r="G491" t="s">
+        <v>51</v>
+      </c>
+      <c r="H491" t="s">
+        <v>38</v>
+      </c>
+      <c r="I491" t="s">
+        <v>1392</v>
+      </c>
+      <c r="J491" t="s">
+        <v>1393</v>
+      </c>
+      <c r="K491" t="s">
+        <v>1394</v>
+      </c>
+      <c r="L491" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M491" t="s">
+        <v>67</v>
+      </c>
+      <c r="N491">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="492" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A492" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B492" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C492" t="s">
+        <v>716</v>
+      </c>
+      <c r="D492" t="s">
+        <v>34</v>
+      </c>
+      <c r="E492" t="s">
+        <v>19</v>
+      </c>
+      <c r="F492">
+        <v>5797</v>
+      </c>
+      <c r="G492" t="s">
+        <v>49</v>
+      </c>
+      <c r="H492" t="s">
+        <v>11</v>
+      </c>
+      <c r="I492" t="s">
+        <v>1396</v>
+      </c>
+      <c r="K492" t="s">
+        <v>55</v>
+      </c>
+      <c r="L492" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M492" t="s">
+        <v>67</v>
+      </c>
+      <c r="N492">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="493" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A493" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B493" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C493" s="28">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="D493" t="s">
+        <v>34</v>
+      </c>
+      <c r="E493" t="s">
+        <v>20</v>
+      </c>
+      <c r="F493">
+        <v>3434</v>
+      </c>
+      <c r="G493" t="s">
+        <v>199</v>
+      </c>
+      <c r="H493" t="s">
+        <v>52</v>
+      </c>
+      <c r="I493" t="s">
+        <v>1398</v>
+      </c>
+      <c r="K493" t="s">
+        <v>55</v>
+      </c>
+      <c r="L493" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M493" t="s">
+        <v>67</v>
+      </c>
+      <c r="N493">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="494" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A494" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B494" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C494" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D494" t="s">
+        <v>34</v>
+      </c>
+      <c r="E494" t="s">
+        <v>14</v>
+      </c>
+      <c r="F494">
+        <v>6398</v>
+      </c>
+      <c r="G494" t="s">
+        <v>50</v>
+      </c>
+      <c r="H494" t="s">
+        <v>35</v>
+      </c>
+      <c r="I494" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J494" t="s">
+        <v>1402</v>
+      </c>
+      <c r="K494" t="s">
+        <v>54</v>
+      </c>
+      <c r="L494" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M494" t="s">
+        <v>67</v>
+      </c>
+      <c r="N494">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="495" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A495" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B495" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C495" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D495" t="s">
+        <v>34</v>
+      </c>
+      <c r="E495" t="s">
+        <v>19</v>
+      </c>
+      <c r="F495">
+        <v>11100</v>
+      </c>
+      <c r="G495" t="s">
+        <v>44</v>
+      </c>
+      <c r="H495" t="s">
+        <v>11</v>
+      </c>
+      <c r="I495" t="s">
+        <v>1405</v>
+      </c>
+      <c r="K495" t="s">
+        <v>56</v>
+      </c>
+      <c r="L495" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M495" t="s">
+        <v>67</v>
+      </c>
+      <c r="N495">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="496" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A496" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B496" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C496" t="s">
+        <v>235</v>
+      </c>
+      <c r="D496" t="s">
+        <v>34</v>
+      </c>
+      <c r="E496" t="s">
+        <v>21</v>
+      </c>
+      <c r="F496">
+        <v>2863</v>
+      </c>
+      <c r="G496" t="s">
+        <v>46</v>
+      </c>
+      <c r="H496" t="s">
+        <v>52</v>
+      </c>
+      <c r="J496" t="s">
+        <v>1407</v>
+      </c>
+      <c r="M496" t="s">
+        <v>66</v>
+      </c>
+      <c r="N496">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="497" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A497" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B497" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C497" t="s">
+        <v>568</v>
+      </c>
+      <c r="D497" t="s">
+        <v>34</v>
+      </c>
+      <c r="E497" t="s">
+        <v>13</v>
+      </c>
+      <c r="F497">
+        <v>4900</v>
+      </c>
+      <c r="G497" t="s">
+        <v>48</v>
+      </c>
+      <c r="H497" t="s">
+        <v>35</v>
+      </c>
+      <c r="I497" t="s">
+        <v>1409</v>
+      </c>
+      <c r="J497" t="s">
+        <v>1410</v>
+      </c>
+      <c r="M497" t="s">
+        <v>66</v>
+      </c>
+      <c r="N497">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="498" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A498" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B498" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D498" t="s">
+        <v>34</v>
+      </c>
+      <c r="E498" t="s">
+        <v>17</v>
+      </c>
+      <c r="F498">
+        <v>7240</v>
+      </c>
+      <c r="G498" t="s">
+        <v>51</v>
+      </c>
+      <c r="H498" t="s">
+        <v>41</v>
+      </c>
+      <c r="I498" t="s">
+        <v>1413</v>
+      </c>
+      <c r="J498" t="s">
+        <v>1414</v>
+      </c>
+      <c r="M498" t="s">
+        <v>66</v>
+      </c>
+      <c r="N498">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="499" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A499" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B499" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C499" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D499" t="s">
+        <v>34</v>
+      </c>
+      <c r="E499" t="s">
+        <v>14</v>
+      </c>
+      <c r="F499">
+        <v>7512</v>
+      </c>
+      <c r="G499" t="s">
+        <v>50</v>
+      </c>
+      <c r="H499" t="s">
+        <v>35</v>
+      </c>
+      <c r="I499" t="s">
+        <v>1417</v>
+      </c>
+      <c r="J499" t="s">
+        <v>1418</v>
+      </c>
+      <c r="K499" t="s">
+        <v>54</v>
+      </c>
+      <c r="L499" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M499" t="s">
+        <v>67</v>
+      </c>
+      <c r="N499">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="500" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A500" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B500" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D500" t="s">
+        <v>34</v>
+      </c>
+      <c r="E500" t="s">
+        <v>13</v>
+      </c>
+      <c r="F500">
+        <v>5198</v>
+      </c>
+      <c r="G500" t="s">
+        <v>251</v>
+      </c>
+      <c r="H500" t="s">
+        <v>38</v>
+      </c>
+      <c r="I500" s="29" t="s">
+        <v>1421</v>
+      </c>
+      <c r="J500" t="s">
+        <v>1422</v>
+      </c>
+      <c r="K500" t="s">
+        <v>54</v>
+      </c>
+      <c r="L500" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M500" t="s">
+        <v>67</v>
+      </c>
+      <c r="N500">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="501" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A501" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B501" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C501" t="s">
+        <v>253</v>
+      </c>
+      <c r="D501" t="s">
+        <v>34</v>
+      </c>
+      <c r="E501" t="s">
+        <v>9</v>
+      </c>
+      <c r="F501">
+        <v>4597</v>
+      </c>
+      <c r="G501" t="s">
+        <v>378</v>
+      </c>
+      <c r="H501" t="s">
+        <v>37</v>
+      </c>
+      <c r="I501" t="s">
+        <v>1024</v>
+      </c>
+      <c r="J501" t="s">
+        <v>1424</v>
+      </c>
+      <c r="K501" t="s">
+        <v>54</v>
+      </c>
+      <c r="L501" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M501" t="s">
+        <v>67</v>
+      </c>
+      <c r="N501">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="502" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A502" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B502" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C502" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D502" t="s">
+        <v>34</v>
+      </c>
+      <c r="E502" t="s">
+        <v>19</v>
+      </c>
+      <c r="F502">
+        <v>6116</v>
+      </c>
+      <c r="G502" t="s">
+        <v>53</v>
+      </c>
+      <c r="H502" t="s">
+        <v>11</v>
+      </c>
+      <c r="I502" t="s">
+        <v>1427</v>
+      </c>
+      <c r="K502" t="s">
+        <v>1428</v>
+      </c>
+      <c r="L502" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M502" t="s">
+        <v>67</v>
+      </c>
+      <c r="N502">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="503" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A503" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B503" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C503" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D503" t="s">
+        <v>34</v>
+      </c>
+      <c r="E503" t="s">
+        <v>17</v>
+      </c>
+      <c r="F503">
+        <v>6942</v>
+      </c>
+      <c r="G503" t="s">
+        <v>39</v>
+      </c>
+      <c r="H503" t="s">
+        <v>11</v>
+      </c>
+      <c r="I503" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J503" t="s">
+        <v>1432</v>
+      </c>
+      <c r="K503" t="s">
+        <v>55</v>
+      </c>
+      <c r="L503" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M503" t="s">
+        <v>67</v>
+      </c>
+      <c r="N503">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="504" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A504" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B504" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C504" t="s">
+        <v>734</v>
+      </c>
+      <c r="D504" t="s">
+        <v>34</v>
+      </c>
+      <c r="E504" t="s">
+        <v>12</v>
+      </c>
+      <c r="F504">
+        <v>4026</v>
+      </c>
+      <c r="G504" t="s">
+        <v>199</v>
+      </c>
+      <c r="H504" t="s">
+        <v>37</v>
+      </c>
+      <c r="I504" t="s">
+        <v>1434</v>
+      </c>
+      <c r="J504" t="s">
+        <v>1435</v>
+      </c>
+      <c r="M504" t="s">
+        <v>66</v>
+      </c>
+      <c r="N504">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="505" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A505" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B505" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C505" s="28">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="D505" t="s">
+        <v>34</v>
+      </c>
+      <c r="E505" t="s">
+        <v>210</v>
+      </c>
+      <c r="F505">
+        <v>4301</v>
+      </c>
+      <c r="G505" t="s">
+        <v>57</v>
+      </c>
+      <c r="H505" t="s">
+        <v>38</v>
+      </c>
+      <c r="K505" t="s">
+        <v>54</v>
+      </c>
+      <c r="L505" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M505" t="s">
+        <v>67</v>
+      </c>
+      <c r="N505">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="506" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A506" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B506" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C506" s="28">
+        <v>0.47638888888888886</v>
+      </c>
+      <c r="D506" t="s">
+        <v>34</v>
+      </c>
+      <c r="E506" t="s">
+        <v>210</v>
+      </c>
+      <c r="F506">
+        <v>5490</v>
+      </c>
+      <c r="G506" t="s">
+        <v>57</v>
+      </c>
+      <c r="H506" t="s">
+        <v>11</v>
+      </c>
+      <c r="I506" t="s">
+        <v>1438</v>
+      </c>
+      <c r="K506" t="s">
+        <v>54</v>
+      </c>
+      <c r="L506" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M506" t="s">
+        <v>67</v>
+      </c>
+      <c r="N506">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="507" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A507" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B507" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C507" s="28">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="D507" t="s">
+        <v>34</v>
+      </c>
+      <c r="E507" t="s">
+        <v>20</v>
+      </c>
+      <c r="F507">
+        <v>7266</v>
+      </c>
+      <c r="G507" t="s">
+        <v>51</v>
+      </c>
+      <c r="H507" t="s">
+        <v>38</v>
+      </c>
+      <c r="M507" t="s">
+        <v>66</v>
+      </c>
+      <c r="N507">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="508" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A508" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B508" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C508" t="s">
+        <v>591</v>
+      </c>
+      <c r="D508" t="s">
+        <v>34</v>
+      </c>
+      <c r="E508" t="s">
+        <v>21</v>
+      </c>
+      <c r="F508">
+        <v>2826</v>
+      </c>
+      <c r="G508" t="s">
+        <v>46</v>
+      </c>
+      <c r="H508" t="s">
+        <v>52</v>
+      </c>
+      <c r="J508" t="s">
+        <v>1441</v>
+      </c>
+      <c r="M508" t="s">
+        <v>66</v>
+      </c>
+      <c r="N508">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="509" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A509" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B509" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C509" s="28">
+        <v>0.48055555555555557</v>
+      </c>
+      <c r="D509" t="s">
+        <v>34</v>
+      </c>
+      <c r="E509" t="s">
+        <v>210</v>
+      </c>
+      <c r="F509">
+        <v>4319</v>
+      </c>
+      <c r="G509" t="s">
+        <v>57</v>
+      </c>
+      <c r="H509" t="s">
+        <v>11</v>
+      </c>
+      <c r="I509" t="s">
+        <v>1443</v>
+      </c>
+      <c r="J509" t="s">
+        <v>1444</v>
+      </c>
+      <c r="M509" t="s">
+        <v>66</v>
+      </c>
+      <c r="N509">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="510" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A510" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B510" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D510" t="s">
+        <v>34</v>
+      </c>
+      <c r="E510" t="s">
+        <v>12</v>
+      </c>
+      <c r="F510">
+        <v>4142</v>
+      </c>
+      <c r="G510" t="s">
+        <v>61</v>
+      </c>
+      <c r="H510" t="s">
+        <v>35</v>
+      </c>
+      <c r="J510" t="s">
+        <v>1447</v>
+      </c>
+      <c r="M510" t="s">
+        <v>66</v>
+      </c>
+      <c r="N510">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="511" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A511" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B511" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D511" t="s">
+        <v>34</v>
+      </c>
+      <c r="E511" t="s">
+        <v>17</v>
+      </c>
+      <c r="F511">
+        <v>6950</v>
+      </c>
+      <c r="G511" t="s">
+        <v>39</v>
+      </c>
+      <c r="H511" t="s">
+        <v>11</v>
+      </c>
+      <c r="I511" t="s">
+        <v>1479</v>
+      </c>
+      <c r="J511" t="s">
+        <v>1480</v>
+      </c>
+      <c r="M511" t="s">
+        <v>66</v>
+      </c>
+      <c r="N511">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="J5" r:id="rId1" xr:uid="{9C40FEBF-DA9D-4951-AA5B-85DCAFA2AE7E}"/>
-    <hyperlink ref="J7" r:id="rId2" xr:uid="{017C10E2-74DB-4AC6-AFC4-8FC2BA166696}"/>
-    <hyperlink ref="J8" r:id="rId3" xr:uid="{B7C181BA-39FB-4443-BA4E-C7AFA2D8C86A}"/>
-    <hyperlink ref="J10" r:id="rId4" xr:uid="{75C2E0F4-85EB-452F-96E6-A94C6DF3C03F}"/>
-    <hyperlink ref="J13" r:id="rId5" xr:uid="{E8F1A5FE-AFBB-46AE-A69D-E04A24635813}"/>
-    <hyperlink ref="J14" r:id="rId6" xr:uid="{7BB8C01D-C1E4-4776-A1E6-82601A96FB13}"/>
-    <hyperlink ref="J17" r:id="rId7" xr:uid="{57108051-7FF2-4C5D-8B2C-0324B706028C}"/>
-    <hyperlink ref="J19" r:id="rId8" xr:uid="{2A6D0108-6963-4A51-9C3F-4A33B8DC21ED}"/>
-    <hyperlink ref="J20" r:id="rId9" xr:uid="{200ADF10-5828-49A0-9506-8152780C400C}"/>
-    <hyperlink ref="J21" r:id="rId10" xr:uid="{B54AFED9-7E55-480C-ACD6-73FB44594E80}"/>
-    <hyperlink ref="J24" r:id="rId11" xr:uid="{05DB60B5-9FCA-4998-9471-BA5ADFD00C1E}"/>
-    <hyperlink ref="J25" r:id="rId12" xr:uid="{D766833F-6371-42D5-8ED2-A2343AF68FF2}"/>
-    <hyperlink ref="J26" r:id="rId13" xr:uid="{7B1C36F3-A56D-47B2-98E9-1E363D3AC216}"/>
-    <hyperlink ref="J27" r:id="rId14" xr:uid="{1BDAA2A1-162A-40B1-A446-7A49933EAF7C}"/>
-    <hyperlink ref="J29" r:id="rId15" xr:uid="{D675FE07-6CF3-40D2-9425-1CD8766E509B}"/>
-    <hyperlink ref="J30" r:id="rId16" xr:uid="{98B2FE2B-2DA9-4554-9F03-73352024F2F8}"/>
-    <hyperlink ref="J31" r:id="rId17" xr:uid="{6B2E6D23-AF34-4A77-BC88-EA04CA28B330}"/>
-    <hyperlink ref="J34" r:id="rId18" xr:uid="{0F921069-4B60-43BE-B95C-538C9AAF7711}"/>
-    <hyperlink ref="J35" r:id="rId19" xr:uid="{AD62F3DA-6EC6-4E15-A990-C9CFCF860F2A}"/>
-    <hyperlink ref="J36" r:id="rId20" xr:uid="{BCF20128-2F56-4013-88C7-7CD67D7AEB8E}"/>
-    <hyperlink ref="J37" r:id="rId21" xr:uid="{030B94D9-0B71-4D6F-A702-63DE14D260E8}"/>
-    <hyperlink ref="J38" r:id="rId22" xr:uid="{9AAC1977-9939-4A3B-AEE1-D383BC3AC6EA}"/>
-    <hyperlink ref="J46" r:id="rId23" xr:uid="{7C2A326E-832A-49B7-96C5-74A889B6BD90}"/>
-    <hyperlink ref="J47" r:id="rId24" xr:uid="{39088EFB-C83C-4033-8E28-9B8C2FE567D0}"/>
-    <hyperlink ref="J48" r:id="rId25" xr:uid="{32DB0729-5C6E-4040-B007-585571CED873}"/>
-    <hyperlink ref="J49" r:id="rId26" xr:uid="{BB5CF202-E3ED-4E2A-BBC2-BB05E665E30D}"/>
-    <hyperlink ref="J50" r:id="rId27" xr:uid="{0020DC88-38F5-4A46-97B4-1110E0D63ED3}"/>
-    <hyperlink ref="J52" r:id="rId28" xr:uid="{10AC946C-EA75-4893-B32A-1AA9AE69DCB6}"/>
-    <hyperlink ref="J53" r:id="rId29" xr:uid="{E4DA8639-1646-421A-B5DF-554C102A3618}"/>
-    <hyperlink ref="J54" r:id="rId30" xr:uid="{0D411C57-9400-4FD9-AA52-196D8FE3FE87}"/>
-    <hyperlink ref="J56" r:id="rId31" xr:uid="{70E971F6-C959-499C-91BA-01DD5E750EF9}"/>
-    <hyperlink ref="J59" r:id="rId32" xr:uid="{E0034927-C156-4DB5-A306-452AA33A9FD2}"/>
-    <hyperlink ref="J61" r:id="rId33" xr:uid="{3E3242F7-FD5D-429C-BF2F-FA5B6933C703}"/>
-    <hyperlink ref="J62" r:id="rId34" xr:uid="{99A7C296-07EA-492E-A9F3-F78D27C41027}"/>
-    <hyperlink ref="J63" r:id="rId35" xr:uid="{E3E449FA-186F-4546-87DE-5E4D888E7F72}"/>
-    <hyperlink ref="J64" r:id="rId36" xr:uid="{D5A6666C-F1E0-495A-ABAD-2C9E40A505D7}"/>
-    <hyperlink ref="J69" r:id="rId37" xr:uid="{84EA4B53-B0B9-4022-B85B-2243ED0442DC}"/>
-    <hyperlink ref="J71" r:id="rId38" xr:uid="{09244506-17A0-422C-94BB-48162C8F2FE8}"/>
-    <hyperlink ref="J72" r:id="rId39" xr:uid="{26297479-78C9-4908-BF78-8C5A2640D312}"/>
-    <hyperlink ref="J73" r:id="rId40" xr:uid="{A7C9BAF0-3871-4EA9-B4E1-4931A06980C5}"/>
-    <hyperlink ref="J74" r:id="rId41" xr:uid="{3B2E03FE-8728-439B-9046-3CFAD942150D}"/>
-    <hyperlink ref="J75" r:id="rId42" xr:uid="{5029D51C-44A3-46ED-99EE-ECB10D1079A8}"/>
-    <hyperlink ref="J76" r:id="rId43" xr:uid="{36B421EB-C004-4DCE-AFA5-B8EDFC4E1556}"/>
-    <hyperlink ref="J78" r:id="rId44" xr:uid="{A4988C70-5785-4C15-8BDF-92DC5027B4DC}"/>
-    <hyperlink ref="J80" r:id="rId45" xr:uid="{6ADFBB05-356D-44F9-BFCF-5349F3CCE162}"/>
-    <hyperlink ref="J86" r:id="rId46" xr:uid="{1C50D401-7D60-47CE-A422-D99ACBB49780}"/>
-    <hyperlink ref="J88" r:id="rId47" xr:uid="{D3B69C65-83EB-4898-BC17-0402345AE5FA}"/>
-    <hyperlink ref="J89" r:id="rId48" xr:uid="{181B3C06-B9AA-4731-8AD0-25D339A1FE32}"/>
-    <hyperlink ref="J90" r:id="rId49" xr:uid="{5A599336-549F-4A8E-90EE-6C947E63794E}"/>
-    <hyperlink ref="J92" r:id="rId50" xr:uid="{9A7F5D7D-2BB0-4530-A3F0-68A6EEA37D28}"/>
-    <hyperlink ref="J94" r:id="rId51" xr:uid="{0B089B25-6111-4623-A6DE-325BBB49B317}"/>
-    <hyperlink ref="J95" r:id="rId52" xr:uid="{AC6B2E4F-A921-4C4B-81C8-B2D6ADA212CA}"/>
-    <hyperlink ref="J96" r:id="rId53" xr:uid="{84B22EB7-BEF6-4FDD-AF18-2901C829D164}"/>
-    <hyperlink ref="J101" r:id="rId54" xr:uid="{8BC75A52-1F65-4908-B22D-21540A59C072}"/>
-    <hyperlink ref="J103" r:id="rId55" xr:uid="{85E700BF-0D12-44FA-8D9C-116BE1ABC6BE}"/>
-    <hyperlink ref="J104" r:id="rId56" xr:uid="{53956A9F-B7FB-4C41-8E3E-7337C0781D1D}"/>
-    <hyperlink ref="J105" r:id="rId57" xr:uid="{00A44AD7-C0BC-45E3-88CA-5BBD948CEF2E}"/>
-    <hyperlink ref="J106" r:id="rId58" xr:uid="{26313C32-BB37-4659-B434-BB540C37E513}"/>
-    <hyperlink ref="J107" r:id="rId59" xr:uid="{E91014A5-3464-4E1A-A392-0A0998816472}"/>
-    <hyperlink ref="J109" r:id="rId60" xr:uid="{50EDAB55-F2F1-4AAC-B5C1-6B0E9B9061BD}"/>
-    <hyperlink ref="J110" r:id="rId61" xr:uid="{B6484408-346C-488E-8F33-ECB798A716CB}"/>
-    <hyperlink ref="J111" r:id="rId62" xr:uid="{7AFFA3ED-F728-4C9E-A265-8B1020F108CB}"/>
-    <hyperlink ref="J112" r:id="rId63" xr:uid="{8C5E44E7-FCB0-459F-8322-61E0D30D8A21}"/>
-    <hyperlink ref="J113" r:id="rId64" xr:uid="{BF105181-5DBE-4290-8B8E-46991505DCE7}"/>
-    <hyperlink ref="J114" r:id="rId65" xr:uid="{67452FE9-7E6B-4CD2-87BC-092F813EBE42}"/>
-    <hyperlink ref="J116" r:id="rId66" xr:uid="{D276F784-3421-4C87-AB72-9FD5B0F2C2CF}"/>
-    <hyperlink ref="J117" r:id="rId67" xr:uid="{45A094FA-40FE-4991-AAAE-27BC48CF1108}"/>
-    <hyperlink ref="J118" r:id="rId68" xr:uid="{F6D9BF74-C115-4E6D-BE44-5BB4BC741EAB}"/>
-    <hyperlink ref="J119" r:id="rId69" xr:uid="{60701ED7-43E7-4797-9AEC-753092CA2807}"/>
-    <hyperlink ref="J120" r:id="rId70" xr:uid="{D2411416-293B-4F8F-9226-336FFF56CF76}"/>
-    <hyperlink ref="J121" r:id="rId71" xr:uid="{A5EA029D-E8E1-4373-BB43-E147FC62E39D}"/>
-    <hyperlink ref="J124" r:id="rId72" xr:uid="{35E132DE-C7F2-4581-848F-5E35B3164139}"/>
-    <hyperlink ref="J128" r:id="rId73" xr:uid="{1E08A152-99EF-4FAD-87DA-BC43B7AE0B09}"/>
-    <hyperlink ref="J129" r:id="rId74" xr:uid="{E0F9B51D-E113-45F5-A499-AA6124F106D0}"/>
-    <hyperlink ref="J132" r:id="rId75" xr:uid="{F2C7872F-81A7-40A8-B673-F49DFAF82124}"/>
-    <hyperlink ref="J134" r:id="rId76" xr:uid="{EC272E17-58AB-4B27-BC46-3E056EFAC3A1}"/>
-    <hyperlink ref="J135" r:id="rId77" xr:uid="{56491BBC-06F6-4514-B6EB-9BEA9C6C1EF6}"/>
-    <hyperlink ref="J136" r:id="rId78" xr:uid="{B8F01B52-0427-4E2B-86CC-D87AC8018ADE}"/>
-    <hyperlink ref="J140" r:id="rId79" xr:uid="{331A803C-ED3C-4C24-923D-7FD9823537F2}"/>
-    <hyperlink ref="J142" r:id="rId80" xr:uid="{BF43BBFC-02A5-42FE-B13E-5DCA3BF725CD}"/>
-    <hyperlink ref="J143" r:id="rId81" xr:uid="{DD085BCA-2A6A-464E-B44F-00557A1C0C06}"/>
-    <hyperlink ref="J144" r:id="rId82" xr:uid="{A98F445E-6516-466C-BF23-920BF365534F}"/>
-    <hyperlink ref="J145" r:id="rId83" xr:uid="{112B52CE-09F3-47B1-B8B6-37EFA5EC47A3}"/>
-    <hyperlink ref="J147" r:id="rId84" xr:uid="{62BE884B-49D9-4C86-8B06-E3C205E96DFA}"/>
-    <hyperlink ref="J149" r:id="rId85" xr:uid="{06D3DC92-DF0C-4BDF-911F-546F8F3B1F83}"/>
-    <hyperlink ref="J150" r:id="rId86" xr:uid="{D9771758-4341-4AD2-918F-7B008C69B51C}"/>
-    <hyperlink ref="J151" r:id="rId87" xr:uid="{467D6DB4-031A-443C-A201-7BD41F45C656}"/>
-    <hyperlink ref="J152" r:id="rId88" xr:uid="{C7AAADF5-EB47-4135-AD52-663DF8F61CF5}"/>
-    <hyperlink ref="J153" r:id="rId89" xr:uid="{4A3038CE-E5FB-48B2-86DA-341F4C556234}"/>
-    <hyperlink ref="J154" r:id="rId90" xr:uid="{B7645B6C-B0D7-4573-9479-35A94253C236}"/>
-    <hyperlink ref="J155" r:id="rId91" xr:uid="{51CF13CA-EE14-4DDD-A589-0C514383D465}"/>
-    <hyperlink ref="J156" r:id="rId92" xr:uid="{CC23FBBA-E7CA-4633-9728-16F37EA3AB2B}"/>
-    <hyperlink ref="J159" r:id="rId93" xr:uid="{47A54587-F98A-443F-BECB-122CABBE428D}"/>
-    <hyperlink ref="J160" r:id="rId94" xr:uid="{51583E26-88C1-477C-9757-DDCFA05D2595}"/>
-    <hyperlink ref="J161" r:id="rId95" xr:uid="{27694FB4-4510-4176-BB46-611533A96CB6}"/>
-    <hyperlink ref="J162" r:id="rId96" xr:uid="{61385185-F276-417E-9889-417B2BA6B5D3}"/>
-    <hyperlink ref="J164" r:id="rId97" xr:uid="{39FB0E46-07E5-463F-9AFC-B4BFFD3FC9FF}"/>
-    <hyperlink ref="J165" r:id="rId98" xr:uid="{99E83562-36D2-4534-9EA2-AF6DF0B279FB}"/>
-    <hyperlink ref="J167" r:id="rId99" xr:uid="{644E64A4-2984-4222-8397-4D802EEC956E}"/>
-    <hyperlink ref="J168" r:id="rId100" xr:uid="{24AA0434-48F7-4903-9A70-FCB67411EF67}"/>
-    <hyperlink ref="J169" r:id="rId101" xr:uid="{07622B2C-EE5A-41BA-88DF-52F8DEFC3D50}"/>
-    <hyperlink ref="J171" r:id="rId102" xr:uid="{C957A3A0-8600-4C8E-A678-50A3ECF7BB81}"/>
-    <hyperlink ref="J172" r:id="rId103" xr:uid="{68BA09B9-5065-49E6-8D19-50977D8B2FB9}"/>
-    <hyperlink ref="J173" r:id="rId104" xr:uid="{4A63165C-424D-4B52-82F2-E189711CE307}"/>
-    <hyperlink ref="J177" r:id="rId105" xr:uid="{0CCDFE6C-E4F9-4536-82FE-5A57E5F4C255}"/>
-    <hyperlink ref="J178" r:id="rId106" xr:uid="{ED1931EB-91B8-4854-9198-BF6B8A3455E5}"/>
-    <hyperlink ref="J181" r:id="rId107" xr:uid="{73F16DBD-071F-4FDC-A50C-720C519D5763}"/>
-    <hyperlink ref="J182" r:id="rId108" xr:uid="{4CD2528B-56A7-44CB-A478-E43953992978}"/>
-    <hyperlink ref="J184" r:id="rId109" xr:uid="{226B5176-69F0-4C0F-8100-5DAC675776AF}"/>
-    <hyperlink ref="J186" r:id="rId110" xr:uid="{8F03B81E-1EAA-494A-94A5-72CFED5DDB31}"/>
-    <hyperlink ref="J190" r:id="rId111" xr:uid="{CFEF20B7-877A-40DE-9A7E-D45BC9B68C36}"/>
-    <hyperlink ref="J191" r:id="rId112" xr:uid="{05336998-45E3-4185-8257-DB093A499157}"/>
-    <hyperlink ref="J192" r:id="rId113" xr:uid="{B31F5B5F-ABA3-4294-B3BA-E3B7639794E0}"/>
-    <hyperlink ref="J193" r:id="rId114" xr:uid="{039BEC4F-D46C-41D8-A1C3-64485BE3960A}"/>
-    <hyperlink ref="J194" r:id="rId115" xr:uid="{EF586651-0C32-4C23-AC01-10DBBD3943EB}"/>
-    <hyperlink ref="J195" r:id="rId116" xr:uid="{5E9C90A2-8103-493F-A6F0-2DB5106B6CC6}"/>
-    <hyperlink ref="J196" r:id="rId117" xr:uid="{D1525128-A7D6-4C92-A9DE-471BA09BB295}"/>
-    <hyperlink ref="J199" r:id="rId118" xr:uid="{D4029439-DC86-4627-BB00-6A41937647C6}"/>
-    <hyperlink ref="J201" r:id="rId119" xr:uid="{72793357-AD90-454D-B277-0027469228DA}"/>
-    <hyperlink ref="J202" r:id="rId120" xr:uid="{B9666B0F-FD39-4558-A61E-6881A7B574DC}"/>
-    <hyperlink ref="J203" r:id="rId121" xr:uid="{E7B30E8C-6A3B-47E5-8675-D789ED1A6724}"/>
-    <hyperlink ref="J205" r:id="rId122" xr:uid="{598C9A77-BAA6-40DD-9BEF-144A8B821FAC}"/>
-    <hyperlink ref="J207" r:id="rId123" xr:uid="{7403281D-A817-478C-AC2B-173894C4BF0B}"/>
-    <hyperlink ref="J209" r:id="rId124" xr:uid="{08334C3D-9A5D-4309-910C-D2942A9AB59A}"/>
-    <hyperlink ref="J210" r:id="rId125" xr:uid="{7ADC68F7-EF90-449F-AD63-A6E044ABA246}"/>
-    <hyperlink ref="J211" r:id="rId126" xr:uid="{A90698CB-4A2A-4F61-82C8-B672C7D84DB1}"/>
-    <hyperlink ref="J212" r:id="rId127" xr:uid="{6E3B7E28-19A3-4844-98EB-8B636B75F1C9}"/>
-    <hyperlink ref="J213" r:id="rId128" xr:uid="{BE2A0912-23AB-476C-B759-3B50A9454C57}"/>
-    <hyperlink ref="J214" r:id="rId129" xr:uid="{ECA1817D-C341-45C3-92E8-3F72E18450D2}"/>
-    <hyperlink ref="J215" r:id="rId130" xr:uid="{43EA7047-DE29-46FB-B3CF-5C6DFB1AC9A1}"/>
-    <hyperlink ref="J217" r:id="rId131" xr:uid="{B57C5643-3936-41BA-B806-4177D0BDACF9}"/>
-    <hyperlink ref="J219" r:id="rId132" xr:uid="{40250C50-1937-4786-8859-33DC86F31209}"/>
-    <hyperlink ref="J220" r:id="rId133" xr:uid="{28BFCABC-DB12-4904-8C87-ED560C426946}"/>
-    <hyperlink ref="J221" r:id="rId134" xr:uid="{3B5C4EF6-F8D1-4881-8549-08E052099B77}"/>
-    <hyperlink ref="J222" r:id="rId135" xr:uid="{158F62C9-C060-4994-A02D-FBA2518237B8}"/>
-    <hyperlink ref="J223" r:id="rId136" xr:uid="{15F8812F-6C28-43FC-99DB-1DA023AF1999}"/>
-    <hyperlink ref="J225" r:id="rId137" xr:uid="{55A54452-4C0C-4166-94D4-FFA7F0BD3023}"/>
-    <hyperlink ref="J228" r:id="rId138" xr:uid="{933F4941-281D-45AC-B777-AA400B15A8C1}"/>
-    <hyperlink ref="J230" r:id="rId139" xr:uid="{97590A4A-AD2F-47F6-8FA7-0E7E9B96FC70}"/>
-    <hyperlink ref="J234" r:id="rId140" xr:uid="{1D73882D-0350-41EA-B914-208BCCC774A5}"/>
-    <hyperlink ref="J236" r:id="rId141" xr:uid="{7A2ABA2A-9CA6-4A9D-98A4-34BCEB38B663}"/>
-    <hyperlink ref="J237" r:id="rId142" xr:uid="{B3FB3BE8-9BBA-4077-A874-942240F7131C}"/>
-    <hyperlink ref="J238" r:id="rId143" xr:uid="{DD81CF90-7264-4F59-90F5-CBE4B698398A}"/>
-    <hyperlink ref="J240" r:id="rId144" xr:uid="{3E92E766-8AD4-421D-90F3-8FB4791C3695}"/>
-    <hyperlink ref="J241" r:id="rId145" xr:uid="{517FB316-3A44-45D4-B6EB-723BEF9EE9C2}"/>
-    <hyperlink ref="J242" r:id="rId146" xr:uid="{E527F99C-A174-455F-A306-53737B4D737C}"/>
-    <hyperlink ref="J243" r:id="rId147" xr:uid="{72508B2E-0CEC-4B4E-9B2C-A0151F6E0EE6}"/>
-    <hyperlink ref="J246" r:id="rId148" xr:uid="{9187E7E7-3FA2-418B-A682-D447362C6C26}"/>
-    <hyperlink ref="J247" r:id="rId149" xr:uid="{23C5ED12-8CC5-4FBE-9132-54E897A0DDD9}"/>
-    <hyperlink ref="J250" r:id="rId150" xr:uid="{124E8379-B649-4DCA-9704-BA2A7E0942FF}"/>
-    <hyperlink ref="J252" r:id="rId151" xr:uid="{75ABFFDD-CFD8-40C3-854F-7082498C58C4}"/>
-    <hyperlink ref="J254" r:id="rId152" xr:uid="{E2676325-F22D-49A1-9D1E-4AAA1AF6A4A7}"/>
-    <hyperlink ref="J255" r:id="rId153" xr:uid="{B564EDD2-DC06-4BCA-983C-6B5F8174389C}"/>
-    <hyperlink ref="J256" r:id="rId154" xr:uid="{8ED073ED-C068-4220-AC34-31C24A6611A4}"/>
-    <hyperlink ref="J258" r:id="rId155" xr:uid="{C4979A60-6539-4A38-9B82-94A8FE3BEC86}"/>
-    <hyperlink ref="J259" r:id="rId156" xr:uid="{9051253F-2B2D-495F-B552-ACD70902957D}"/>
-    <hyperlink ref="J261" r:id="rId157" xr:uid="{CEF41DAD-A2E4-4471-9652-0171A8191DA6}"/>
-    <hyperlink ref="J263" r:id="rId158" xr:uid="{2145CAC7-308E-4850-8A81-95DEA0850500}"/>
-    <hyperlink ref="J265" r:id="rId159" xr:uid="{3BBEAF90-CC2C-4F35-80FD-EA4451CE69E9}"/>
-    <hyperlink ref="J266" r:id="rId160" xr:uid="{8AF672F1-70FC-464C-B386-522C4D5FCBF8}"/>
-    <hyperlink ref="J267" r:id="rId161" xr:uid="{80DC810D-AC38-4395-A372-E6D537F72F91}"/>
-    <hyperlink ref="J270" r:id="rId162" xr:uid="{8C1E966D-B683-4155-AB7C-0B0BF5CEC83B}"/>
-    <hyperlink ref="J271" r:id="rId163" xr:uid="{0DE4A369-42FE-4F6A-B610-3461C5BC6DC0}"/>
-    <hyperlink ref="J273" r:id="rId164" xr:uid="{FFCEAAB8-2D11-4478-9A7F-E0A3B896A435}"/>
-    <hyperlink ref="J274" r:id="rId165" xr:uid="{07A44349-70C3-4837-BEA2-A1BC4E1908BD}"/>
-    <hyperlink ref="J275" r:id="rId166" xr:uid="{E2503CFD-580F-4C1E-91A4-6C004BCD2A94}"/>
-    <hyperlink ref="J277" r:id="rId167" xr:uid="{27442CD6-D452-4B3A-82AF-D80F9C089A05}"/>
-    <hyperlink ref="J278" r:id="rId168" xr:uid="{EF7BB4FD-C076-46F6-A43D-6722A07E8B99}"/>
-    <hyperlink ref="J279" r:id="rId169" xr:uid="{C3673EA0-57B6-4ED1-98F4-9E2461CB4AA7}"/>
-    <hyperlink ref="J280" r:id="rId170" xr:uid="{39624741-B15D-47B7-88F8-697F95DB36E5}"/>
-    <hyperlink ref="J281" r:id="rId171" xr:uid="{018AE6DA-9AAE-430D-A136-3048D351C3BC}"/>
-    <hyperlink ref="J282" r:id="rId172" xr:uid="{6A04C1AF-6D43-4269-A555-5AD2E7A2AAA5}"/>
-    <hyperlink ref="J283" r:id="rId173" xr:uid="{5649FD13-A46A-4A62-A2F7-2582FA99534D}"/>
-    <hyperlink ref="J286" r:id="rId174" xr:uid="{67583C0B-7B4A-4981-81FF-CF2DF996F7BE}"/>
-    <hyperlink ref="J287" r:id="rId175" xr:uid="{B204AC8C-6889-409B-BA89-4C8EB938E04F}"/>
-    <hyperlink ref="J290" r:id="rId176" xr:uid="{06CA1FC7-FC8F-4366-A195-1E325B0DCF16}"/>
-    <hyperlink ref="J292" r:id="rId177" xr:uid="{D8F0B78F-D04A-4DB6-A7DB-F84A21276EDB}"/>
-    <hyperlink ref="J294" r:id="rId178" xr:uid="{1A6F2A5C-C62F-4ED4-9782-7ED9DD510F1B}"/>
-    <hyperlink ref="J296" r:id="rId179" xr:uid="{42DFDAD0-6B1E-4583-899C-EF8E6F3203AB}"/>
-    <hyperlink ref="J297" r:id="rId180" xr:uid="{024F2D56-43BF-4419-822D-016E474C737B}"/>
-    <hyperlink ref="J298" r:id="rId181" xr:uid="{68534943-249E-43F3-9239-FAC6997F8123}"/>
-    <hyperlink ref="J299" r:id="rId182" xr:uid="{ECD7F0D8-711A-4D65-8492-74720BF55B1E}"/>
-    <hyperlink ref="J300" r:id="rId183" xr:uid="{02930181-4692-450B-BA33-921CB0FA6710}"/>
-    <hyperlink ref="J301" r:id="rId184" xr:uid="{54F758E1-576C-490A-8B1A-2FEADD4DA530}"/>
-    <hyperlink ref="J303" r:id="rId185" xr:uid="{40974BBC-4E3C-4D31-A4AC-E9783E34AE25}"/>
-    <hyperlink ref="J305" r:id="rId186" xr:uid="{C9ACC088-1F78-43B0-B312-40CB7005BB83}"/>
-    <hyperlink ref="J306" r:id="rId187" xr:uid="{2B3D99AB-1E62-4600-AF3E-BA0D1F52860B}"/>
-    <hyperlink ref="J308" r:id="rId188" xr:uid="{79DC9D28-1C45-4DC8-906A-DD05696D3172}"/>
-    <hyperlink ref="J309" r:id="rId189" xr:uid="{A999F7DF-613D-4EBB-B7A5-CE2D12C99225}"/>
-    <hyperlink ref="J311" r:id="rId190" xr:uid="{7B898260-4CEA-4D92-92B8-42CF793635DB}"/>
-    <hyperlink ref="J312" r:id="rId191" xr:uid="{26D3BBE0-70D1-4BF9-A9EA-06F546D842E0}"/>
-    <hyperlink ref="J314" r:id="rId192" xr:uid="{45A408FF-D980-4CA2-A525-22F84FD85152}"/>
-    <hyperlink ref="J317" r:id="rId193" xr:uid="{E466F613-B71F-4E3C-8A00-8E7D73D44778}"/>
-    <hyperlink ref="J318" r:id="rId194" xr:uid="{84C60746-DAEE-40D4-8015-9E1B8C05DCE3}"/>
-    <hyperlink ref="J321" r:id="rId195" xr:uid="{1501D411-523B-41D7-A898-F40631B62FD6}"/>
-    <hyperlink ref="J322" r:id="rId196" xr:uid="{D832A6C4-A54B-4ED3-A946-ABC36F874546}"/>
-    <hyperlink ref="J325" r:id="rId197" xr:uid="{90650B9C-8250-4E71-BEB0-B5C8B8BA07BD}"/>
-    <hyperlink ref="J326" r:id="rId198" xr:uid="{390ACB7B-BB50-4D31-955A-DEDBED15CEF2}"/>
-    <hyperlink ref="J329" r:id="rId199" xr:uid="{7C5D5870-62E9-44A7-8A95-D93EBB1F369F}"/>
-    <hyperlink ref="J330" r:id="rId200" xr:uid="{F50C4894-37AE-46E5-9E82-3CB4CBFC0AF2}"/>
-    <hyperlink ref="J331" r:id="rId201" xr:uid="{9A85238A-4293-4B5E-A53F-10E7B5A9C4D8}"/>
-    <hyperlink ref="J333" r:id="rId202" xr:uid="{DD0FBD38-FD31-445F-B561-510698928298}"/>
-    <hyperlink ref="J334" r:id="rId203" xr:uid="{74C6028B-3C74-46A1-98DC-588108E8910C}"/>
-    <hyperlink ref="J335" r:id="rId204" xr:uid="{D57ACBD8-2873-4848-9A0F-4777CE24FA2E}"/>
-    <hyperlink ref="J336" r:id="rId205" xr:uid="{E8ED729A-021D-47F0-B192-8117FCF2A7FC}"/>
-    <hyperlink ref="J338" r:id="rId206" xr:uid="{A28FDD4F-1C10-433D-A305-9D0010933285}"/>
-    <hyperlink ref="J340" r:id="rId207" xr:uid="{19A93FE0-243B-41A8-8B66-D1C5EAE55E8C}"/>
-    <hyperlink ref="J342" r:id="rId208" xr:uid="{D854E6D1-C347-4261-8908-2BC96902761C}"/>
-    <hyperlink ref="J343" r:id="rId209" xr:uid="{32679D75-4C44-49BD-BD7A-4CD6ECC75304}"/>
-    <hyperlink ref="J344" r:id="rId210" xr:uid="{36BA2220-21DA-4DC9-A5B4-7B696C42276A}"/>
-    <hyperlink ref="J346" r:id="rId211" xr:uid="{DB27D9A1-2967-4A0C-8F81-7668A842358E}"/>
-    <hyperlink ref="J349" r:id="rId212" xr:uid="{D215BEFB-DC71-44F9-BCED-9FABAA5C508C}"/>
-    <hyperlink ref="J350" r:id="rId213" xr:uid="{9AF4DD61-7932-4BF7-898D-75E4AB61D1C3}"/>
-    <hyperlink ref="J352" r:id="rId214" xr:uid="{C4397C17-CAD5-4A37-A59C-A1A9ABE56015}"/>
-    <hyperlink ref="J354" r:id="rId215" xr:uid="{204D7493-005C-4212-A310-6336A7766051}"/>
-    <hyperlink ref="J355" r:id="rId216" xr:uid="{C3599657-7593-4428-96C3-8D4AE2530540}"/>
-    <hyperlink ref="J356" r:id="rId217" xr:uid="{86BF3974-A04B-4A30-82B8-62A4108F7E24}"/>
-    <hyperlink ref="J357" r:id="rId218" xr:uid="{BA782521-EF11-48CD-8173-A892F42134B5}"/>
-    <hyperlink ref="J358" r:id="rId219" xr:uid="{5806573F-50B8-43CB-9292-9D5C4F4B2F45}"/>
-    <hyperlink ref="J360" r:id="rId220" xr:uid="{4A64BA11-96AD-4491-B521-5882BCD747DA}"/>
-    <hyperlink ref="J363" r:id="rId221" xr:uid="{E5144D30-24A6-49A4-9B81-14859608ACF3}"/>
-    <hyperlink ref="J364" r:id="rId222" xr:uid="{C5102B0C-B92C-4227-8D4A-5D4FAA3CEE3D}"/>
-    <hyperlink ref="J366" r:id="rId223" xr:uid="{9F3CA873-3054-4FAA-B31E-6C55D1537A62}"/>
-    <hyperlink ref="J368" r:id="rId224" xr:uid="{B37E3BB9-246F-48B6-A4CF-F5F961857AEE}"/>
-    <hyperlink ref="J370" r:id="rId225" xr:uid="{A7791AB0-1BBD-484B-AFFB-0785881263D9}"/>
-    <hyperlink ref="J371" r:id="rId226" xr:uid="{4CF44C9C-1BFC-4F31-8EC6-4B1541C969AD}"/>
-    <hyperlink ref="J372" r:id="rId227" xr:uid="{62C655DA-937B-4B3B-8E8C-57A015615F1C}"/>
-    <hyperlink ref="J373" r:id="rId228" xr:uid="{218F7559-E954-413F-A624-A45092B7906D}"/>
-    <hyperlink ref="J374" r:id="rId229" xr:uid="{B3F1833A-B6CB-4912-AA92-889EE7D99031}"/>
-    <hyperlink ref="J375" r:id="rId230" xr:uid="{66618DBF-9334-4282-8633-50CA60506B59}"/>
-    <hyperlink ref="J376" r:id="rId231" xr:uid="{E5E2288C-5A4D-4281-9F91-F1B718A765C4}"/>
-    <hyperlink ref="J377" r:id="rId232" xr:uid="{AD068761-1D92-49D9-928D-EC8F101AAB2A}"/>
-    <hyperlink ref="J378" r:id="rId233" xr:uid="{20CB2903-6E12-4AAD-A345-90D900DCB533}"/>
-    <hyperlink ref="J379" r:id="rId234" xr:uid="{3A79A497-9193-4FE2-8AA1-BCDDE7D669B6}"/>
-    <hyperlink ref="J381" r:id="rId235" xr:uid="{457A1015-E979-4949-8BBB-7736483D6E2C}"/>
-    <hyperlink ref="J383" r:id="rId236" xr:uid="{4134E23A-1293-42AA-8471-E3A87B505D04}"/>
-    <hyperlink ref="J384" r:id="rId237" xr:uid="{CC019B2B-90EF-47F0-A971-2F4C8B86F995}"/>
-    <hyperlink ref="J386" r:id="rId238" xr:uid="{495B4807-21BB-4264-A2AC-EE919CB7A685}"/>
-    <hyperlink ref="J387" r:id="rId239" xr:uid="{181CBADA-FD3F-4A8D-A4D9-3619A18950E1}"/>
-    <hyperlink ref="J388" r:id="rId240" xr:uid="{341718B9-4595-4E68-A1D6-E5EFC4F63A29}"/>
-    <hyperlink ref="J390" r:id="rId241" xr:uid="{C79221E2-F121-49D0-962A-FDA60E401DF4}"/>
-    <hyperlink ref="J391" r:id="rId242" xr:uid="{386D78E4-E971-4D75-B8C8-6E03C29331CC}"/>
-    <hyperlink ref="J394" r:id="rId243" xr:uid="{AF76F592-0689-4A45-854A-CE9D76F683EB}"/>
-    <hyperlink ref="J395" r:id="rId244" xr:uid="{6D62B792-BA8C-40F2-9256-2248DE97363C}"/>
-    <hyperlink ref="J396" r:id="rId245" xr:uid="{74899FF1-34CD-4DFA-8723-C8CD21C7B07C}"/>
-    <hyperlink ref="J397" r:id="rId246" xr:uid="{59B55D68-7A96-42BA-9E2A-6778A7D3AAA6}"/>
-    <hyperlink ref="J398" r:id="rId247" xr:uid="{ACADA4DA-DCA0-4970-9993-2DD636E9261B}"/>
-    <hyperlink ref="J399" r:id="rId248" xr:uid="{6978F4AA-334D-44C6-BC79-BB22F26BB590}"/>
-    <hyperlink ref="J400" r:id="rId249" xr:uid="{976E0B9A-5201-4E9E-B529-72D66C1391C7}"/>
-    <hyperlink ref="J403" r:id="rId250" xr:uid="{92D2D435-ECC7-4D1C-9B2F-EEB9D5FA8A36}"/>
-    <hyperlink ref="J404" r:id="rId251" xr:uid="{3E5FC639-5A16-4D8A-94A9-CCC50848A6EA}"/>
-    <hyperlink ref="J405" r:id="rId252" xr:uid="{DACE3275-EDF5-4B93-80D7-06C99533242D}"/>
-    <hyperlink ref="J406" r:id="rId253" xr:uid="{B4DCB274-5EA2-4CF0-9096-09B608D9697F}"/>
-    <hyperlink ref="J408" r:id="rId254" xr:uid="{1D32EDC3-3CC6-47B0-8DD2-7D2899726FA6}"/>
-    <hyperlink ref="J409" r:id="rId255" xr:uid="{435E06B5-BF02-42EB-9685-51D72B89FA97}"/>
-    <hyperlink ref="J411" r:id="rId256" xr:uid="{9C506B3D-E52F-4911-B9D2-535F3BE0269E}"/>
-    <hyperlink ref="J413" r:id="rId257" xr:uid="{306A7EAB-DE39-469C-8E9C-7F62C57FB7D3}"/>
-    <hyperlink ref="J415" r:id="rId258" xr:uid="{AB27818F-8EC8-4FE0-A69E-3566231A0254}"/>
-    <hyperlink ref="J416" r:id="rId259" xr:uid="{AABDB855-A351-49E7-8F34-8D8C63C41FB3}"/>
-    <hyperlink ref="J418" r:id="rId260" xr:uid="{4B5F7580-411F-43DE-A5A9-954190140462}"/>
-    <hyperlink ref="J421" r:id="rId261" xr:uid="{5B34DC5B-A2E4-48B3-8E3F-E290B6D1CDA4}"/>
-    <hyperlink ref="J422" r:id="rId262" xr:uid="{2C1EB7C1-D02A-4A21-995D-AB2856B96EAE}"/>
-    <hyperlink ref="J430" r:id="rId263" xr:uid="{D0158FAA-E6C0-40C1-AF02-FD59741BA2F0}"/>
-    <hyperlink ref="J431" r:id="rId264" xr:uid="{E621406F-42FD-4956-AF07-566E02E4B9FF}"/>
-    <hyperlink ref="J432" r:id="rId265" xr:uid="{D42C8E46-0A3B-43D2-A45A-D8F070BD962A}"/>
-    <hyperlink ref="J433" r:id="rId266" xr:uid="{06A377FF-13D6-49BD-8DC0-E0398255EEAE}"/>
-    <hyperlink ref="J434" r:id="rId267" xr:uid="{3EEA2687-AA3D-4515-94DC-D8B94D2FCC51}"/>
-    <hyperlink ref="J435" r:id="rId268" xr:uid="{8F9D606E-EA44-4ED7-85F3-FC6D5FB04A7E}"/>
-    <hyperlink ref="J436" r:id="rId269" xr:uid="{97E23DCA-46DC-4D47-B965-F6700131A42E}"/>
-    <hyperlink ref="J437" r:id="rId270" xr:uid="{9620760B-5535-4D9F-A7AA-34EE4B01E17C}"/>
-    <hyperlink ref="J438" r:id="rId271" xr:uid="{734FF4E2-EEBD-4BBB-9EFD-E37661B0E9FB}"/>
-    <hyperlink ref="J439" r:id="rId272" xr:uid="{593C9709-CFBE-497A-B75B-1D8F28AED631}"/>
-    <hyperlink ref="J445" r:id="rId273" xr:uid="{28A97F7E-3A91-48FB-ACFA-45AFFBA68B2C}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId274"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId275"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos junio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A469AD91-D69F-44A0-A1A9-917CEBECEE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F29400-3B86-450E-8A6A-BAE3B61EE70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Rechazos Calle" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$511</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$588</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4473" uniqueCount="1481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5153" uniqueCount="1689">
   <si>
     <t>Fecha</t>
   </si>
@@ -4491,6 +4491,633 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781275358/pkwfq4ktzvhz4knb4x3a.jpg</t>
+  </si>
+  <si>
+    <t>MQB1N6LG1W3G</t>
+  </si>
+  <si>
+    <t>Pep rueditas x40</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Faltó rueditad de 40gr se descuenta al cliente</t>
+  </si>
+  <si>
+    <t>MQB1YEDQI55W</t>
+  </si>
+  <si>
+    <t>Exq bizc chocolate</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781276386/wg1jugkapfg35vdc5i6v.jpg</t>
+  </si>
+  <si>
+    <t>MQB21B8I7HOW</t>
+  </si>
+  <si>
+    <t>MQB2COR4LMX4</t>
+  </si>
+  <si>
+    <t>12:10 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781277050/od6qlpabnvs2brytgj4j.jpg</t>
+  </si>
+  <si>
+    <t>MQB2VT4G9G8B</t>
+  </si>
+  <si>
+    <t>Luch nido fettuccine</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781277939/mw0se7esxmsnw7tm7drp.jpg</t>
+  </si>
+  <si>
+    <t>MQB34QR5GZ7N</t>
+  </si>
+  <si>
+    <t>MQB3LPYW12SN</t>
+  </si>
+  <si>
+    <t>Mazz tachas 4</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Sin stock 4 tachas descontar de la boleta.</t>
+  </si>
+  <si>
+    <t>MQB4IKYKE1VL</t>
+  </si>
+  <si>
+    <t>Rechaza lo marcado pidió luchetti</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781280682/hbueriloitpnd9vtmwv1.jpg</t>
+  </si>
+  <si>
+    <t>MQB5BB46VXBR</t>
+  </si>
+  <si>
+    <t>01:33 p. m.</t>
+  </si>
+  <si>
+    <t>MQB5M4MMFDXG</t>
+  </si>
+  <si>
+    <t>01:42 p. m.</t>
+  </si>
+  <si>
+    <t>MQB72VGZNHF0</t>
+  </si>
+  <si>
+    <t>02:23 p. m.</t>
+  </si>
+  <si>
+    <t>MQB7S99MJKRJ</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781286178/dzqv26bhnlzzkwp679j9.jpg</t>
+  </si>
+  <si>
+    <t>MQB8A2OCXVAA</t>
+  </si>
+  <si>
+    <t>02:57 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781287026/f5qx7awbwtcxd6uarrek.jpg</t>
+  </si>
+  <si>
+    <t>MQB8RSGMJQIB</t>
+  </si>
+  <si>
+    <t>03:11 p. m.</t>
+  </si>
+  <si>
+    <t>JUNCOS LUIS EZEQUIEL</t>
+  </si>
+  <si>
+    <t>BALDO JULIAN MARCELO</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781287852/rbhbw1jxlm0wlm3rrhka.jpg</t>
+  </si>
+  <si>
+    <t>MQB8YGB8MRCA</t>
+  </si>
+  <si>
+    <t>03:15 p. m.</t>
+  </si>
+  <si>
+    <t>MQB94Q5D1TQO</t>
+  </si>
+  <si>
+    <t>03:20 p. m.</t>
+  </si>
+  <si>
+    <t>Fantoche Sdd x 12 un</t>
+  </si>
+  <si>
+    <t>Dejá el pedido, lo resuelvo después — Descontar</t>
+  </si>
+  <si>
+    <t>MQB96P88PRBH</t>
+  </si>
+  <si>
+    <t>03:22 p. m.</t>
+  </si>
+  <si>
+    <t>Faltó 1 dinam x 45</t>
+  </si>
+  <si>
+    <t>MQB97CTDT91N</t>
+  </si>
+  <si>
+    <t>8 Toddy alfajor</t>
+  </si>
+  <si>
+    <t>MQB98PMRVG8R</t>
+  </si>
+  <si>
+    <t>03:24 p. m.</t>
+  </si>
+  <si>
+    <t>4 alfajor triple súper dulce de leche</t>
+  </si>
+  <si>
+    <t>MQB98K01NKNU</t>
+  </si>
+  <si>
+    <t>Falto 5 mani sal pehuam</t>
+  </si>
+  <si>
+    <t>MQB9A6HY2FNI</t>
+  </si>
+  <si>
+    <t>03:25 p. m.</t>
+  </si>
+  <si>
+    <t>10 alfaj toddy mouse</t>
+  </si>
+  <si>
+    <t>MQB9BCQ9JQ1M</t>
+  </si>
+  <si>
+    <t>03:26 p. m.</t>
+  </si>
+  <si>
+    <t>12 alf SDD FANTO</t>
+  </si>
+  <si>
+    <t>MQB9CGJ6ZJ1D</t>
+  </si>
+  <si>
+    <t>Faltó 1 cheetos x 85gr</t>
+  </si>
+  <si>
+    <t>MQBAH5ETIUHA</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781290693/wvicswz2btko4vzervzs.jpg</t>
+  </si>
+  <si>
+    <t>MQBAPE372XPC</t>
+  </si>
+  <si>
+    <t>04:05 p. m.</t>
+  </si>
+  <si>
+    <t>No quiso los encendedores de 25 y una sal estaba rota</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781291105/pb70qwkm4hyyxuo5oubh.jpg</t>
+  </si>
+  <si>
+    <t>MQBAV6M88IVE</t>
+  </si>
+  <si>
+    <t>04:10 p. m.</t>
+  </si>
+  <si>
+    <t>Dejo los alfajores</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781291376/ienna5bglrt0lu2kbaho.jpg</t>
+  </si>
+  <si>
+    <t>MQBCQVGQY3KD</t>
+  </si>
+  <si>
+    <t>05:02 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781294522/dnj4egaxtdwa76kd7qtg.jpg</t>
+  </si>
+  <si>
+    <t>MQCB1SX5FWLC</t>
+  </si>
+  <si>
+    <t>09:02 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781352131/vpliggicvdugva5onyr2.jpg</t>
+  </si>
+  <si>
+    <t>MQCB267LDGVS</t>
+  </si>
+  <si>
+    <t>No quiere está boleta</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781352154/y1xp2bjsaj2wgvxftwu1.jpg</t>
+  </si>
+  <si>
+    <t>MQCBL2803AFF</t>
+  </si>
+  <si>
+    <t>09:17 a. m.</t>
+  </si>
+  <si>
+    <t>Rechazo 2 Tostitos</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781353038/gf8wvkr9s2nhrijvrw30.jpg</t>
+  </si>
+  <si>
+    <t>MQCBW7X98EW5</t>
+  </si>
+  <si>
+    <t>MQCC1EWAOOW8</t>
+  </si>
+  <si>
+    <t>09:30 a. m.</t>
+  </si>
+  <si>
+    <t>Faltaron 2 lays de 40gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781353789/sxqcrzhujclhp48btxs5.jpg</t>
+  </si>
+  <si>
+    <t>MQCC5CHBB8TF</t>
+  </si>
+  <si>
+    <t>Rechazo 3 lays acana asado 77gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781353990/m3uoak9sxrnnlqilj5bb.jpg</t>
+  </si>
+  <si>
+    <t>MQCCB6MV0WGC</t>
+  </si>
+  <si>
+    <t>Avena tradicional 1 sin stock</t>
+  </si>
+  <si>
+    <t>MQCCHY0TR3WC</t>
+  </si>
+  <si>
+    <t>1 papa lisa de 450</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781354560/ifpn6olnvqbydfdkxq54.jpg</t>
+  </si>
+  <si>
+    <t>MQCCL7E33YRM</t>
+  </si>
+  <si>
+    <t>Rechaza twuistos de 155 grs no pidio</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781354723/brqmhaqgazzyl62klztg.jpg</t>
+  </si>
+  <si>
+    <t>MQCCXEORA2AV</t>
+  </si>
+  <si>
+    <t>Dice abierto pero no hay nadie</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781355282/dez6aoncjxhe0otrw0u8.jpg</t>
+  </si>
+  <si>
+    <t>MQCDD3GC903W</t>
+  </si>
+  <si>
+    <t>10:07 a. m.</t>
+  </si>
+  <si>
+    <t>A qué hora abre</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781356031/pixwaqtmwjo3xyiooafv.jpg</t>
+  </si>
+  <si>
+    <t>MQCDJYYGHVWS</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781356331/k25squwadyhibc5gfgpl.jpg</t>
+  </si>
+  <si>
+    <t>MQCE3T33H8RD</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781357259/edevxsnlfo1xhehyhxoe.jpg</t>
+  </si>
+  <si>
+    <t>MQCE7O7QIM6J</t>
+  </si>
+  <si>
+    <t>Falta 2 clasicas x 85g
+Desarmo otro cl</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781357455/ivtn7trny7pnlbgqz5le.jpg</t>
+  </si>
+  <si>
+    <t>MQCE9C20TY1H</t>
+  </si>
+  <si>
+    <t>MQCEMX78S8IO</t>
+  </si>
+  <si>
+    <t>Se pasó 2 veces</t>
+  </si>
+  <si>
+    <t>MQCF30ZVJF1X</t>
+  </si>
+  <si>
+    <t>48 cubanitos snacks</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781358899/xurmrw1uxsfpmfhdz7aq.jpg</t>
+  </si>
+  <si>
+    <t>MQCF8U7KC6AE</t>
+  </si>
+  <si>
+    <t>10:59 a. m.</t>
+  </si>
+  <si>
+    <t>Mat codito roto</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781359178/upzzmvi1qrzsehrlq4zk.jpg</t>
+  </si>
+  <si>
+    <t>MQCFY9EY9QB4</t>
+  </si>
+  <si>
+    <t>MQCGK5K54YRG</t>
+  </si>
+  <si>
+    <t>Se descontó lo marcado 
+Faltantes de otros cl</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781361380/x7js994rjs7mqgsuohat.jpg</t>
+  </si>
+  <si>
+    <t>MQCGN2F8FT6Z</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781361552/evwf9j2cugabaz2hjcnx.jpg</t>
+  </si>
+  <si>
+    <t>MQCI58VCIM2U</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781364042/xhzkxtgdczussv3bgaax.jpg</t>
+  </si>
+  <si>
+    <t>MQCJRW0RLUTL</t>
+  </si>
+  <si>
+    <t>01:06 p. m.</t>
+  </si>
+  <si>
+    <t>1 Doritos 40 grs</t>
+  </si>
+  <si>
+    <t>MQCKOT692658</t>
+  </si>
+  <si>
+    <t>01:32 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781368318/wddw2b40svup2jvxstix.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Cerrado</t>
+  </si>
+  <si>
+    <t>MQCLGUEMBXAT</t>
+  </si>
+  <si>
+    <t>2 3d 23grs</t>
+  </si>
+  <si>
+    <t>MQDWMNWOQGB7</t>
+  </si>
+  <si>
+    <t>MQDZDWXWNZNH</t>
+  </si>
+  <si>
+    <t>Falta 1</t>
+  </si>
+  <si>
+    <t>MQDZFEJYH3OJ</t>
+  </si>
+  <si>
+    <t>01:12 p. m.</t>
+  </si>
+  <si>
+    <t>MQEHHTYSRQ32</t>
+  </si>
+  <si>
+    <t>09:38 p. m.</t>
+  </si>
+  <si>
+    <t>MARTINEZ MAURICIO SEBASTIAN</t>
+  </si>
+  <si>
+    <t>6 galletas tripack</t>
+  </si>
+  <si>
+    <t>MQEHKR7SX8FM</t>
+  </si>
+  <si>
+    <t>09:40 p. m.</t>
+  </si>
+  <si>
+    <t>Flor cereal 1</t>
+  </si>
+  <si>
+    <t>MQF8040TXO4E</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781528410/c0u5uv8rizbd9yttca9m.jpg</t>
+  </si>
+  <si>
+    <t>MQF828NDKLC1</t>
+  </si>
+  <si>
+    <t>5 satur agridulce</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781528510/rznmda5sqic0zoiuhwup.jpg</t>
+  </si>
+  <si>
+    <t>MQF84A7P17J0</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781528605/bljrrvpcualo0sobwf3e.jpg</t>
+  </si>
+  <si>
+    <t>MQF85ATAOLGQ</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781528647/gsbdwj5zx7dzryjwdcpj.jpg</t>
+  </si>
+  <si>
+    <t>MQF866NPVBW1</t>
+  </si>
+  <si>
+    <t>19yerba playadito 500gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781528702/dvkfk9e5om8reyebjwdc.jpg</t>
+  </si>
+  <si>
+    <t>MQGJU1MKGIQK</t>
+  </si>
+  <si>
+    <t>08:19 a. m.</t>
+  </si>
+  <si>
+    <t>Dada sin stock</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781608746/ofzegnpymsbdv6jlo92c.jpg</t>
+  </si>
+  <si>
+    <t>MQGKBXBJWKBR</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781609582/mcvli2wctbvh8meieluk.jpg</t>
+  </si>
+  <si>
+    <t>MQGKNEY7LZGC</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781610127/scdvcxvtyowyfejy1cgp.jpg</t>
+  </si>
+  <si>
+    <t>MQGL315DASHM</t>
+  </si>
+  <si>
+    <t>Falta pehuamar de 450 grs una unidad</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781610848/vxpy5alwh09frankp1he.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Rechazo parcial</t>
+  </si>
+  <si>
+    <t>MQGLG6PAJAKC</t>
+  </si>
+  <si>
+    <t>09:04 a. m.</t>
+  </si>
+  <si>
+    <t>1 foratini roto</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781611470/dyc2diezk9w3iknc1sfl.jpg</t>
+  </si>
+  <si>
+    <t>MQGLSGBS2BG0</t>
+  </si>
+  <si>
+    <t>Yerbas playadito</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781612036/wephgkymq1tmjh1gxim5.jpg</t>
+  </si>
+  <si>
+    <t>MQGLUTSVIZC5</t>
+  </si>
+  <si>
+    <t>Rechaza arándanos por fecha corta</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781612160/v48hidjdhtybbsygwxxs.jpg</t>
+  </si>
+  <si>
+    <t>MQGM4MHJG0PX</t>
+  </si>
+  <si>
+    <t>Faltaron dos paquetes de ph noble 30mx4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781612596/f3hqyeq6eecctl2ibxla.jpg</t>
+  </si>
+  <si>
+    <t>MQGMLVNR1TY7</t>
+  </si>
+  <si>
+    <t>09:36 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781613400/wpsfax9e2chocq0f9yzb.jpg</t>
+  </si>
+  <si>
+    <t>MQGMS277OVDT</t>
+  </si>
+  <si>
+    <t>09:41 a. m.</t>
+  </si>
+  <si>
+    <t>6polvo tody x 180grs</t>
+  </si>
+  <si>
+    <t>MQGMT6AEEZX5</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781613746/ctpzpawrsmiwsffc1scf.jpg</t>
+  </si>
+  <si>
+    <t>MQGMSXWZYPN6</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781613817/mnkiml5shjratfv2efeh.jpg</t>
+  </si>
+  <si>
+    <t>MQGN6VOR97CS</t>
+  </si>
+  <si>
+    <t>09:53 a. m.</t>
+  </si>
+  <si>
+    <t>No recibe porque no le mandaste el exhibidor</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781614383/cq7er00hwl1kijnipabj.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Está facturado el 12+3 que incluye automáticamente el exhibidor. No lo tengo que facturar yo.</t>
+  </si>
+  <si>
+    <t>MQGN69DOC48C</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781614479/ibsluc4dzyj9moxdtona.jpg</t>
+  </si>
+  <si>
+    <t>MQGNJVSYRRD7</t>
+  </si>
+  <si>
+    <t>Rechaza papa lays x134. Avena extra fina x 470 18 
+1 avena tradicional x 280 sin stock</t>
   </si>
 </sst>
 </file>
@@ -4889,8 +5516,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N511">
-  <autoFilter ref="A1:N511" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N588">
+  <autoFilter ref="A1:N588" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fecha"/>
@@ -5112,7 +5739,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N511"/>
+  <dimension ref="A1:N588"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -25571,8 +26198,14 @@
       <c r="J496" t="s">
         <v>1407</v>
       </c>
+      <c r="K496" t="s">
+        <v>56</v>
+      </c>
+      <c r="L496" s="25">
+        <v>46185</v>
+      </c>
       <c r="M496" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N496">
         <v>6</v>
@@ -26048,8 +26681,14 @@
       <c r="J508" t="s">
         <v>1441</v>
       </c>
+      <c r="K508" t="s">
+        <v>56</v>
+      </c>
+      <c r="L508" s="25">
+        <v>46185</v>
+      </c>
       <c r="M508" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N508">
         <v>6</v>
@@ -26163,6 +26802,3082 @@
         <v>66</v>
       </c>
       <c r="N511">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="512" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A512" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B512" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C512" t="s">
+        <v>143</v>
+      </c>
+      <c r="D512" t="s">
+        <v>34</v>
+      </c>
+      <c r="E512" t="s">
+        <v>19</v>
+      </c>
+      <c r="F512">
+        <v>6104</v>
+      </c>
+      <c r="G512" t="s">
+        <v>53</v>
+      </c>
+      <c r="H512" t="s">
+        <v>11</v>
+      </c>
+      <c r="I512" t="s">
+        <v>1482</v>
+      </c>
+      <c r="K512" t="s">
+        <v>1483</v>
+      </c>
+      <c r="L512" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M512" t="s">
+        <v>67</v>
+      </c>
+      <c r="N512">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="513" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A513" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B513" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C513" t="s">
+        <v>453</v>
+      </c>
+      <c r="D513" t="s">
+        <v>34</v>
+      </c>
+      <c r="E513" t="s">
+        <v>17</v>
+      </c>
+      <c r="F513">
+        <v>6960</v>
+      </c>
+      <c r="G513" t="s">
+        <v>39</v>
+      </c>
+      <c r="H513" t="s">
+        <v>11</v>
+      </c>
+      <c r="I513" t="s">
+        <v>1485</v>
+      </c>
+      <c r="J513" t="s">
+        <v>1486</v>
+      </c>
+      <c r="K513" t="s">
+        <v>55</v>
+      </c>
+      <c r="L513" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M513" t="s">
+        <v>67</v>
+      </c>
+      <c r="N513">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="514" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A514" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B514" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C514" s="28">
+        <v>0.50069444444444444</v>
+      </c>
+      <c r="D514" t="s">
+        <v>34</v>
+      </c>
+      <c r="E514" t="s">
+        <v>20</v>
+      </c>
+      <c r="F514">
+        <v>7250</v>
+      </c>
+      <c r="G514" t="s">
+        <v>51</v>
+      </c>
+      <c r="H514" t="s">
+        <v>41</v>
+      </c>
+      <c r="M514" t="s">
+        <v>66</v>
+      </c>
+      <c r="N514">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="515" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A515" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B515" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C515" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D515" t="s">
+        <v>34</v>
+      </c>
+      <c r="E515" t="s">
+        <v>17</v>
+      </c>
+      <c r="F515">
+        <v>6916</v>
+      </c>
+      <c r="G515" t="s">
+        <v>39</v>
+      </c>
+      <c r="H515" t="s">
+        <v>11</v>
+      </c>
+      <c r="I515" t="s">
+        <v>1265</v>
+      </c>
+      <c r="J515" t="s">
+        <v>1490</v>
+      </c>
+      <c r="K515" t="s">
+        <v>55</v>
+      </c>
+      <c r="L515" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M515" t="s">
+        <v>67</v>
+      </c>
+      <c r="N515">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="516" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A516" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B516" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C516" t="s">
+        <v>856</v>
+      </c>
+      <c r="D516" t="s">
+        <v>34</v>
+      </c>
+      <c r="E516" t="s">
+        <v>17</v>
+      </c>
+      <c r="F516">
+        <v>6953</v>
+      </c>
+      <c r="G516" t="s">
+        <v>39</v>
+      </c>
+      <c r="H516" t="s">
+        <v>11</v>
+      </c>
+      <c r="I516" t="s">
+        <v>1492</v>
+      </c>
+      <c r="J516" t="s">
+        <v>1493</v>
+      </c>
+      <c r="K516" t="s">
+        <v>55</v>
+      </c>
+      <c r="L516" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M516" t="s">
+        <v>67</v>
+      </c>
+      <c r="N516">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="517" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A517" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B517" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C517" s="28">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="D517" t="s">
+        <v>34</v>
+      </c>
+      <c r="E517" t="s">
+        <v>20</v>
+      </c>
+      <c r="F517">
+        <v>7265</v>
+      </c>
+      <c r="G517" t="s">
+        <v>43</v>
+      </c>
+      <c r="H517" t="s">
+        <v>11</v>
+      </c>
+      <c r="K517" t="s">
+        <v>54</v>
+      </c>
+      <c r="L517" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M517" t="s">
+        <v>67</v>
+      </c>
+      <c r="N517">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="518" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A518" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B518" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C518" t="s">
+        <v>156</v>
+      </c>
+      <c r="D518" t="s">
+        <v>34</v>
+      </c>
+      <c r="E518" t="s">
+        <v>19</v>
+      </c>
+      <c r="F518">
+        <v>6096</v>
+      </c>
+      <c r="G518" t="s">
+        <v>53</v>
+      </c>
+      <c r="H518" t="s">
+        <v>11</v>
+      </c>
+      <c r="I518" t="s">
+        <v>1496</v>
+      </c>
+      <c r="K518" t="s">
+        <v>1497</v>
+      </c>
+      <c r="L518" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M518" t="s">
+        <v>67</v>
+      </c>
+      <c r="N518">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="519" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A519" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B519" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C519" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D519" t="s">
+        <v>34</v>
+      </c>
+      <c r="E519" t="s">
+        <v>17</v>
+      </c>
+      <c r="F519">
+        <v>6953</v>
+      </c>
+      <c r="G519" t="s">
+        <v>39</v>
+      </c>
+      <c r="H519" t="s">
+        <v>37</v>
+      </c>
+      <c r="I519" t="s">
+        <v>1499</v>
+      </c>
+      <c r="J519" t="s">
+        <v>1500</v>
+      </c>
+      <c r="K519" t="s">
+        <v>55</v>
+      </c>
+      <c r="L519" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M519" t="s">
+        <v>67</v>
+      </c>
+      <c r="N519">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="520" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A520" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B520" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C520" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D520" t="s">
+        <v>34</v>
+      </c>
+      <c r="E520" t="s">
+        <v>21</v>
+      </c>
+      <c r="F520">
+        <v>2872</v>
+      </c>
+      <c r="G520" t="s">
+        <v>46</v>
+      </c>
+      <c r="H520" t="s">
+        <v>11</v>
+      </c>
+      <c r="M520" t="s">
+        <v>66</v>
+      </c>
+      <c r="N520">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="521" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A521" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B521" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C521" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D521" t="s">
+        <v>34</v>
+      </c>
+      <c r="E521" t="s">
+        <v>13</v>
+      </c>
+      <c r="F521">
+        <v>5213</v>
+      </c>
+      <c r="G521" t="s">
+        <v>251</v>
+      </c>
+      <c r="H521" t="s">
+        <v>35</v>
+      </c>
+      <c r="K521" t="s">
+        <v>54</v>
+      </c>
+      <c r="L521" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M521" t="s">
+        <v>67</v>
+      </c>
+      <c r="N521">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="522" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A522" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B522" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C522" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D522" t="s">
+        <v>34</v>
+      </c>
+      <c r="E522" t="s">
+        <v>12</v>
+      </c>
+      <c r="F522">
+        <v>3462</v>
+      </c>
+      <c r="G522" t="s">
+        <v>199</v>
+      </c>
+      <c r="H522" t="s">
+        <v>52</v>
+      </c>
+      <c r="M522" t="s">
+        <v>66</v>
+      </c>
+      <c r="N522">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="523" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A523" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B523" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C523" s="28">
+        <v>0.61319444444444449</v>
+      </c>
+      <c r="D523" t="s">
+        <v>34</v>
+      </c>
+      <c r="E523" t="s">
+        <v>10</v>
+      </c>
+      <c r="F523">
+        <v>3124</v>
+      </c>
+      <c r="G523" t="s">
+        <v>58</v>
+      </c>
+      <c r="H523" t="s">
+        <v>41</v>
+      </c>
+      <c r="J523" t="s">
+        <v>1508</v>
+      </c>
+      <c r="K523" t="s">
+        <v>54</v>
+      </c>
+      <c r="L523" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M523" t="s">
+        <v>67</v>
+      </c>
+      <c r="N523">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="524" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A524" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B524" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C524" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D524" t="s">
+        <v>34</v>
+      </c>
+      <c r="E524" t="s">
+        <v>21</v>
+      </c>
+      <c r="F524">
+        <v>7394</v>
+      </c>
+      <c r="G524" t="s">
+        <v>46</v>
+      </c>
+      <c r="H524" t="s">
+        <v>607</v>
+      </c>
+      <c r="J524" t="s">
+        <v>1511</v>
+      </c>
+      <c r="M524" t="s">
+        <v>66</v>
+      </c>
+      <c r="N524">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="525" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A525" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B525" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C525" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D525" t="s">
+        <v>34</v>
+      </c>
+      <c r="E525" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F525">
+        <v>35</v>
+      </c>
+      <c r="G525" t="s">
+        <v>1515</v>
+      </c>
+      <c r="H525" t="s">
+        <v>37</v>
+      </c>
+      <c r="I525" t="s">
+        <v>1230</v>
+      </c>
+      <c r="J525" t="s">
+        <v>1516</v>
+      </c>
+      <c r="K525" t="s">
+        <v>56</v>
+      </c>
+      <c r="L525" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M525" t="s">
+        <v>67</v>
+      </c>
+      <c r="N525">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="526" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A526" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B526" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C526" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D526" t="s">
+        <v>34</v>
+      </c>
+      <c r="E526" t="s">
+        <v>16</v>
+      </c>
+      <c r="F526">
+        <v>3795</v>
+      </c>
+      <c r="G526" t="s">
+        <v>49</v>
+      </c>
+      <c r="H526" t="s">
+        <v>41</v>
+      </c>
+      <c r="K526" t="s">
+        <v>55</v>
+      </c>
+      <c r="L526" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M526" t="s">
+        <v>67</v>
+      </c>
+      <c r="N526">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="527" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A527" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B527" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C527" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D527" t="s">
+        <v>34</v>
+      </c>
+      <c r="E527" t="s">
+        <v>957</v>
+      </c>
+      <c r="F527">
+        <v>412</v>
+      </c>
+      <c r="G527" t="s">
+        <v>958</v>
+      </c>
+      <c r="H527" t="s">
+        <v>11</v>
+      </c>
+      <c r="I527" t="s">
+        <v>1521</v>
+      </c>
+      <c r="K527" t="s">
+        <v>1522</v>
+      </c>
+      <c r="L527" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M527" t="s">
+        <v>67</v>
+      </c>
+      <c r="N527">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="528" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A528" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B528" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C528" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D528" t="s">
+        <v>34</v>
+      </c>
+      <c r="E528" t="s">
+        <v>957</v>
+      </c>
+      <c r="F528">
+        <v>1517</v>
+      </c>
+      <c r="G528" t="s">
+        <v>958</v>
+      </c>
+      <c r="H528" t="s">
+        <v>52</v>
+      </c>
+      <c r="I528" t="s">
+        <v>1525</v>
+      </c>
+      <c r="K528" t="s">
+        <v>1522</v>
+      </c>
+      <c r="L528" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M528" t="s">
+        <v>67</v>
+      </c>
+      <c r="N528">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="529" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A529" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B529" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C529" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D529" t="s">
+        <v>34</v>
+      </c>
+      <c r="E529" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F529">
+        <v>43</v>
+      </c>
+      <c r="G529" t="s">
+        <v>1515</v>
+      </c>
+      <c r="H529" t="s">
+        <v>11</v>
+      </c>
+      <c r="I529" t="s">
+        <v>1527</v>
+      </c>
+      <c r="K529" t="s">
+        <v>56</v>
+      </c>
+      <c r="L529" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M529" t="s">
+        <v>67</v>
+      </c>
+      <c r="N529">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="530" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A530" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B530" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C530" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D530" t="s">
+        <v>34</v>
+      </c>
+      <c r="E530" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F530">
+        <v>1211</v>
+      </c>
+      <c r="G530" t="s">
+        <v>1515</v>
+      </c>
+      <c r="H530" t="s">
+        <v>11</v>
+      </c>
+      <c r="I530" t="s">
+        <v>1530</v>
+      </c>
+      <c r="K530" t="s">
+        <v>56</v>
+      </c>
+      <c r="L530" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M530" t="s">
+        <v>67</v>
+      </c>
+      <c r="N530">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="531" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A531" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B531" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C531" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D531" t="s">
+        <v>34</v>
+      </c>
+      <c r="E531" t="s">
+        <v>957</v>
+      </c>
+      <c r="F531">
+        <v>413</v>
+      </c>
+      <c r="G531" t="s">
+        <v>958</v>
+      </c>
+      <c r="H531" t="s">
+        <v>52</v>
+      </c>
+      <c r="I531" t="s">
+        <v>1532</v>
+      </c>
+      <c r="K531" t="s">
+        <v>1522</v>
+      </c>
+      <c r="L531" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M531" t="s">
+        <v>67</v>
+      </c>
+      <c r="N531">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="532" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A532" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B532" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C532" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D532" t="s">
+        <v>34</v>
+      </c>
+      <c r="E532" t="s">
+        <v>957</v>
+      </c>
+      <c r="F532">
+        <v>413</v>
+      </c>
+      <c r="G532" t="s">
+        <v>958</v>
+      </c>
+      <c r="H532" t="s">
+        <v>11</v>
+      </c>
+      <c r="I532" t="s">
+        <v>1535</v>
+      </c>
+      <c r="K532" t="s">
+        <v>1522</v>
+      </c>
+      <c r="L532" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M532" t="s">
+        <v>67</v>
+      </c>
+      <c r="N532">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="533" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A533" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B533" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C533" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D533" t="s">
+        <v>34</v>
+      </c>
+      <c r="E533" t="s">
+        <v>957</v>
+      </c>
+      <c r="F533">
+        <v>995</v>
+      </c>
+      <c r="G533" t="s">
+        <v>958</v>
+      </c>
+      <c r="H533" t="s">
+        <v>11</v>
+      </c>
+      <c r="I533" t="s">
+        <v>1538</v>
+      </c>
+      <c r="K533" t="s">
+        <v>1522</v>
+      </c>
+      <c r="L533" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M533" t="s">
+        <v>67</v>
+      </c>
+      <c r="N533">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="534" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A534" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B534" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C534" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D534" t="s">
+        <v>34</v>
+      </c>
+      <c r="E534" t="s">
+        <v>957</v>
+      </c>
+      <c r="F534">
+        <v>995</v>
+      </c>
+      <c r="G534" t="s">
+        <v>958</v>
+      </c>
+      <c r="H534" t="s">
+        <v>52</v>
+      </c>
+      <c r="I534" t="s">
+        <v>1540</v>
+      </c>
+      <c r="K534" t="s">
+        <v>1522</v>
+      </c>
+      <c r="L534" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M534" t="s">
+        <v>67</v>
+      </c>
+      <c r="N534">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="535" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A535" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B535" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C535" s="28">
+        <v>0.66527777777777775</v>
+      </c>
+      <c r="D535" t="s">
+        <v>34</v>
+      </c>
+      <c r="E535" t="s">
+        <v>10</v>
+      </c>
+      <c r="F535">
+        <v>4420</v>
+      </c>
+      <c r="G535" t="s">
+        <v>43</v>
+      </c>
+      <c r="H535" t="s">
+        <v>11</v>
+      </c>
+      <c r="J535" t="s">
+        <v>1542</v>
+      </c>
+      <c r="K535" t="s">
+        <v>56</v>
+      </c>
+      <c r="L535" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M535" t="s">
+        <v>67</v>
+      </c>
+      <c r="N535">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="536" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A536" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B536" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C536" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D536" t="s">
+        <v>34</v>
+      </c>
+      <c r="E536" t="s">
+        <v>9</v>
+      </c>
+      <c r="F536">
+        <v>4312</v>
+      </c>
+      <c r="G536" t="s">
+        <v>378</v>
+      </c>
+      <c r="H536" t="s">
+        <v>35</v>
+      </c>
+      <c r="I536" t="s">
+        <v>1545</v>
+      </c>
+      <c r="J536" t="s">
+        <v>1546</v>
+      </c>
+      <c r="K536" t="s">
+        <v>54</v>
+      </c>
+      <c r="L536" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M536" t="s">
+        <v>67</v>
+      </c>
+      <c r="N536">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="537" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A537" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B537" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C537" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D537" t="s">
+        <v>34</v>
+      </c>
+      <c r="E537" t="s">
+        <v>9</v>
+      </c>
+      <c r="F537">
+        <v>11133</v>
+      </c>
+      <c r="G537" t="s">
+        <v>43</v>
+      </c>
+      <c r="H537" t="s">
+        <v>35</v>
+      </c>
+      <c r="I537" t="s">
+        <v>1549</v>
+      </c>
+      <c r="J537" t="s">
+        <v>1550</v>
+      </c>
+      <c r="K537" t="s">
+        <v>54</v>
+      </c>
+      <c r="L537" s="25">
+        <v>46185</v>
+      </c>
+      <c r="M537" t="s">
+        <v>67</v>
+      </c>
+      <c r="N537">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="538" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A538" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B538" s="25">
+        <v>46185</v>
+      </c>
+      <c r="C538" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D538" t="s">
+        <v>34</v>
+      </c>
+      <c r="E538" t="s">
+        <v>314</v>
+      </c>
+      <c r="F538">
+        <v>1888</v>
+      </c>
+      <c r="G538" t="s">
+        <v>315</v>
+      </c>
+      <c r="H538" t="s">
+        <v>35</v>
+      </c>
+      <c r="J538" t="s">
+        <v>1553</v>
+      </c>
+      <c r="M538" t="s">
+        <v>66</v>
+      </c>
+      <c r="N538">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="539" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A539" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B539" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C539" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D539" t="s">
+        <v>34</v>
+      </c>
+      <c r="E539" t="s">
+        <v>21</v>
+      </c>
+      <c r="F539">
+        <v>5558</v>
+      </c>
+      <c r="G539" t="s">
+        <v>44</v>
+      </c>
+      <c r="H539" t="s">
+        <v>38</v>
+      </c>
+      <c r="J539" t="s">
+        <v>1556</v>
+      </c>
+      <c r="K539" t="s">
+        <v>54</v>
+      </c>
+      <c r="L539" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M539" t="s">
+        <v>67</v>
+      </c>
+      <c r="N539">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="540" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A540" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B540" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C540" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D540" t="s">
+        <v>34</v>
+      </c>
+      <c r="E540" t="s">
+        <v>9</v>
+      </c>
+      <c r="F540">
+        <v>3548</v>
+      </c>
+      <c r="G540" t="s">
+        <v>59</v>
+      </c>
+      <c r="H540" t="s">
+        <v>35</v>
+      </c>
+      <c r="I540" t="s">
+        <v>1558</v>
+      </c>
+      <c r="J540" t="s">
+        <v>1559</v>
+      </c>
+      <c r="M540" t="s">
+        <v>66</v>
+      </c>
+      <c r="N540">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="541" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A541" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B541" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C541" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D541" t="s">
+        <v>34</v>
+      </c>
+      <c r="E541" t="s">
+        <v>64</v>
+      </c>
+      <c r="F541">
+        <v>2556</v>
+      </c>
+      <c r="G541" t="s">
+        <v>65</v>
+      </c>
+      <c r="H541" t="s">
+        <v>607</v>
+      </c>
+      <c r="I541" t="s">
+        <v>1562</v>
+      </c>
+      <c r="J541" t="s">
+        <v>1563</v>
+      </c>
+      <c r="K541" t="s">
+        <v>54</v>
+      </c>
+      <c r="L541" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M541" t="s">
+        <v>67</v>
+      </c>
+      <c r="N541">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="542" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A542" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B542" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C542" s="28">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="D542" t="s">
+        <v>34</v>
+      </c>
+      <c r="E542" t="s">
+        <v>20</v>
+      </c>
+      <c r="F542">
+        <v>4101</v>
+      </c>
+      <c r="G542" t="s">
+        <v>61</v>
+      </c>
+      <c r="H542" t="s">
+        <v>35</v>
+      </c>
+      <c r="M542" t="s">
+        <v>66</v>
+      </c>
+      <c r="N542">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="543" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A543" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B543" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C543" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D543" t="s">
+        <v>34</v>
+      </c>
+      <c r="E543" t="s">
+        <v>17</v>
+      </c>
+      <c r="F543">
+        <v>4999</v>
+      </c>
+      <c r="G543" t="s">
+        <v>251</v>
+      </c>
+      <c r="H543" t="s">
+        <v>52</v>
+      </c>
+      <c r="I543" t="s">
+        <v>1567</v>
+      </c>
+      <c r="J543" t="s">
+        <v>1568</v>
+      </c>
+      <c r="K543" t="s">
+        <v>54</v>
+      </c>
+      <c r="L543" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M543" t="s">
+        <v>67</v>
+      </c>
+      <c r="N543">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="544" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A544" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B544" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C544" t="s">
+        <v>71</v>
+      </c>
+      <c r="D544" t="s">
+        <v>34</v>
+      </c>
+      <c r="E544" t="s">
+        <v>64</v>
+      </c>
+      <c r="F544">
+        <v>2418</v>
+      </c>
+      <c r="G544" t="s">
+        <v>65</v>
+      </c>
+      <c r="H544" t="s">
+        <v>38</v>
+      </c>
+      <c r="I544" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J544" t="s">
+        <v>1571</v>
+      </c>
+      <c r="K544" t="s">
+        <v>54</v>
+      </c>
+      <c r="L544" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M544" t="s">
+        <v>67</v>
+      </c>
+      <c r="N544">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="545" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A545" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B545" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C545" s="28">
+        <v>0.40069444444444446</v>
+      </c>
+      <c r="D545" t="s">
+        <v>34</v>
+      </c>
+      <c r="E545" t="s">
+        <v>210</v>
+      </c>
+      <c r="F545">
+        <v>7140</v>
+      </c>
+      <c r="G545" t="s">
+        <v>46</v>
+      </c>
+      <c r="H545" t="s">
+        <v>11</v>
+      </c>
+      <c r="I545" t="s">
+        <v>1573</v>
+      </c>
+      <c r="K545" t="s">
+        <v>56</v>
+      </c>
+      <c r="L545" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M545" t="s">
+        <v>67</v>
+      </c>
+      <c r="N545">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="546" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A546" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B546" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C546" s="28">
+        <v>0.40416666666666667</v>
+      </c>
+      <c r="D546" t="s">
+        <v>34</v>
+      </c>
+      <c r="E546" t="s">
+        <v>210</v>
+      </c>
+      <c r="F546">
+        <v>7137</v>
+      </c>
+      <c r="G546" t="s">
+        <v>46</v>
+      </c>
+      <c r="H546" t="s">
+        <v>11</v>
+      </c>
+      <c r="I546" t="s">
+        <v>1575</v>
+      </c>
+      <c r="J546" t="s">
+        <v>1576</v>
+      </c>
+      <c r="K546" t="s">
+        <v>56</v>
+      </c>
+      <c r="L546" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M546" t="s">
+        <v>67</v>
+      </c>
+      <c r="N546">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="547" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A547" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B547" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C547" t="s">
+        <v>992</v>
+      </c>
+      <c r="D547" t="s">
+        <v>34</v>
+      </c>
+      <c r="E547" t="s">
+        <v>9</v>
+      </c>
+      <c r="F547">
+        <v>11267</v>
+      </c>
+      <c r="G547" t="s">
+        <v>48</v>
+      </c>
+      <c r="H547" t="s">
+        <v>35</v>
+      </c>
+      <c r="I547" t="s">
+        <v>1578</v>
+      </c>
+      <c r="J547" t="s">
+        <v>1579</v>
+      </c>
+      <c r="M547" t="s">
+        <v>66</v>
+      </c>
+      <c r="N547">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="548" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A548" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B548" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C548" t="s">
+        <v>73</v>
+      </c>
+      <c r="D548" t="s">
+        <v>34</v>
+      </c>
+      <c r="E548" t="s">
+        <v>12</v>
+      </c>
+      <c r="F548">
+        <v>7067</v>
+      </c>
+      <c r="G548" t="s">
+        <v>51</v>
+      </c>
+      <c r="H548" t="s">
+        <v>607</v>
+      </c>
+      <c r="I548" t="s">
+        <v>1581</v>
+      </c>
+      <c r="J548" t="s">
+        <v>1582</v>
+      </c>
+      <c r="K548" t="s">
+        <v>54</v>
+      </c>
+      <c r="L548" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M548" t="s">
+        <v>67</v>
+      </c>
+      <c r="N548">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="549" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A549" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B549" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C549" t="s">
+        <v>1584</v>
+      </c>
+      <c r="D549" t="s">
+        <v>34</v>
+      </c>
+      <c r="E549" t="s">
+        <v>244</v>
+      </c>
+      <c r="F549">
+        <v>3466</v>
+      </c>
+      <c r="G549" t="s">
+        <v>44</v>
+      </c>
+      <c r="H549" t="s">
+        <v>41</v>
+      </c>
+      <c r="I549" t="s">
+        <v>1585</v>
+      </c>
+      <c r="J549" t="s">
+        <v>1586</v>
+      </c>
+      <c r="K549" t="s">
+        <v>55</v>
+      </c>
+      <c r="L549" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M549" t="s">
+        <v>67</v>
+      </c>
+      <c r="N549">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="550" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A550" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B550" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C550" t="s">
+        <v>104</v>
+      </c>
+      <c r="D550" t="s">
+        <v>34</v>
+      </c>
+      <c r="E550" t="s">
+        <v>12</v>
+      </c>
+      <c r="F550">
+        <v>5604</v>
+      </c>
+      <c r="G550" t="s">
+        <v>44</v>
+      </c>
+      <c r="H550" t="s">
+        <v>35</v>
+      </c>
+      <c r="J550" t="s">
+        <v>1588</v>
+      </c>
+      <c r="K550" t="s">
+        <v>55</v>
+      </c>
+      <c r="L550" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M550" t="s">
+        <v>67</v>
+      </c>
+      <c r="N550">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="551" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A551" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B551" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C551" t="s">
+        <v>564</v>
+      </c>
+      <c r="D551" t="s">
+        <v>34</v>
+      </c>
+      <c r="E551" t="s">
+        <v>12</v>
+      </c>
+      <c r="F551">
+        <v>5628</v>
+      </c>
+      <c r="G551" t="s">
+        <v>40</v>
+      </c>
+      <c r="H551" t="s">
+        <v>41</v>
+      </c>
+      <c r="J551" t="s">
+        <v>1590</v>
+      </c>
+      <c r="K551" t="s">
+        <v>55</v>
+      </c>
+      <c r="L551" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M551" t="s">
+        <v>67</v>
+      </c>
+      <c r="N551">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="552" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A552" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B552" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C552" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D552" t="s">
+        <v>34</v>
+      </c>
+      <c r="E552" t="s">
+        <v>13</v>
+      </c>
+      <c r="F552">
+        <v>4371</v>
+      </c>
+      <c r="G552" t="s">
+        <v>46</v>
+      </c>
+      <c r="H552" t="s">
+        <v>52</v>
+      </c>
+      <c r="I552" s="29" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J552" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M552" t="s">
+        <v>66</v>
+      </c>
+      <c r="N552">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="553" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A553" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B553" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C553" s="28">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="D553" t="s">
+        <v>34</v>
+      </c>
+      <c r="E553" t="s">
+        <v>20</v>
+      </c>
+      <c r="F553">
+        <v>4394</v>
+      </c>
+      <c r="G553" t="s">
+        <v>254</v>
+      </c>
+      <c r="H553" t="s">
+        <v>41</v>
+      </c>
+      <c r="K553" t="s">
+        <v>54</v>
+      </c>
+      <c r="L553" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M553" t="s">
+        <v>67</v>
+      </c>
+      <c r="N553">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="554" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A554" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B554" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C554" s="28">
+        <v>0.44583333333333336</v>
+      </c>
+      <c r="D554" t="s">
+        <v>34</v>
+      </c>
+      <c r="E554" t="s">
+        <v>210</v>
+      </c>
+      <c r="F554">
+        <v>7130</v>
+      </c>
+      <c r="G554" t="s">
+        <v>46</v>
+      </c>
+      <c r="H554" t="s">
+        <v>41</v>
+      </c>
+      <c r="I554" t="s">
+        <v>1596</v>
+      </c>
+      <c r="K554" t="s">
+        <v>54</v>
+      </c>
+      <c r="L554" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M554" t="s">
+        <v>67</v>
+      </c>
+      <c r="N554">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="555" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A555" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B555" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C555" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D555" t="s">
+        <v>34</v>
+      </c>
+      <c r="E555" t="s">
+        <v>64</v>
+      </c>
+      <c r="F555">
+        <v>2450</v>
+      </c>
+      <c r="G555" t="s">
+        <v>65</v>
+      </c>
+      <c r="H555" t="s">
+        <v>11</v>
+      </c>
+      <c r="I555" t="s">
+        <v>1598</v>
+      </c>
+      <c r="J555" t="s">
+        <v>1599</v>
+      </c>
+      <c r="K555" t="s">
+        <v>921</v>
+      </c>
+      <c r="L555" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M555" t="s">
+        <v>67</v>
+      </c>
+      <c r="N555">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="556" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A556" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B556" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C556" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D556" t="s">
+        <v>34</v>
+      </c>
+      <c r="E556" t="s">
+        <v>17</v>
+      </c>
+      <c r="F556">
+        <v>3215</v>
+      </c>
+      <c r="G556" t="s">
+        <v>44</v>
+      </c>
+      <c r="H556" t="s">
+        <v>52</v>
+      </c>
+      <c r="I556" t="s">
+        <v>1602</v>
+      </c>
+      <c r="J556" t="s">
+        <v>1603</v>
+      </c>
+      <c r="K556" t="s">
+        <v>45</v>
+      </c>
+      <c r="L556" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M556" t="s">
+        <v>67</v>
+      </c>
+      <c r="N556">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="557" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A557" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B557" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C557" s="28">
+        <v>0.47152777777777777</v>
+      </c>
+      <c r="D557" t="s">
+        <v>34</v>
+      </c>
+      <c r="E557" t="s">
+        <v>20</v>
+      </c>
+      <c r="F557">
+        <v>4089</v>
+      </c>
+      <c r="G557" t="s">
+        <v>61</v>
+      </c>
+      <c r="H557" t="s">
+        <v>11</v>
+      </c>
+      <c r="M557" t="s">
+        <v>66</v>
+      </c>
+      <c r="N557">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="558" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A558" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B558" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C558" t="s">
+        <v>281</v>
+      </c>
+      <c r="D558" t="s">
+        <v>34</v>
+      </c>
+      <c r="E558" t="s">
+        <v>13</v>
+      </c>
+      <c r="F558">
+        <v>4342</v>
+      </c>
+      <c r="G558" t="s">
+        <v>254</v>
+      </c>
+      <c r="H558" t="s">
+        <v>52</v>
+      </c>
+      <c r="I558" s="29" t="s">
+        <v>1606</v>
+      </c>
+      <c r="J558" t="s">
+        <v>1607</v>
+      </c>
+      <c r="M558" t="s">
+        <v>66</v>
+      </c>
+      <c r="N558">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="559" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A559" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B559" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C559" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D559" t="s">
+        <v>34</v>
+      </c>
+      <c r="E559" t="s">
+        <v>21</v>
+      </c>
+      <c r="F559">
+        <v>3495</v>
+      </c>
+      <c r="G559" t="s">
+        <v>40</v>
+      </c>
+      <c r="H559" t="s">
+        <v>11</v>
+      </c>
+      <c r="J559" t="s">
+        <v>1609</v>
+      </c>
+      <c r="M559" t="s">
+        <v>66</v>
+      </c>
+      <c r="N559">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="560" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A560" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B560" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C560" t="s">
+        <v>296</v>
+      </c>
+      <c r="D560" t="s">
+        <v>34</v>
+      </c>
+      <c r="E560" t="s">
+        <v>13</v>
+      </c>
+      <c r="F560">
+        <v>4681</v>
+      </c>
+      <c r="G560" t="s">
+        <v>254</v>
+      </c>
+      <c r="H560" t="s">
+        <v>52</v>
+      </c>
+      <c r="I560" t="s">
+        <v>881</v>
+      </c>
+      <c r="J560" t="s">
+        <v>1611</v>
+      </c>
+      <c r="M560" t="s">
+        <v>66</v>
+      </c>
+      <c r="N560">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="561" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A561" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B561" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C561" t="s">
+        <v>1613</v>
+      </c>
+      <c r="D561" t="s">
+        <v>34</v>
+      </c>
+      <c r="E561" t="s">
+        <v>23</v>
+      </c>
+      <c r="F561">
+        <v>1716</v>
+      </c>
+      <c r="G561" t="s">
+        <v>63</v>
+      </c>
+      <c r="H561" t="s">
+        <v>52</v>
+      </c>
+      <c r="I561" t="s">
+        <v>1614</v>
+      </c>
+      <c r="K561" t="s">
+        <v>56</v>
+      </c>
+      <c r="L561" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M561" t="s">
+        <v>67</v>
+      </c>
+      <c r="N561">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="562" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A562" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B562" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C562" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D562" t="s">
+        <v>34</v>
+      </c>
+      <c r="E562" t="s">
+        <v>12</v>
+      </c>
+      <c r="F562">
+        <v>5926</v>
+      </c>
+      <c r="G562" t="s">
+        <v>53</v>
+      </c>
+      <c r="H562" t="s">
+        <v>41</v>
+      </c>
+      <c r="J562" t="s">
+        <v>1617</v>
+      </c>
+      <c r="K562" t="s">
+        <v>1618</v>
+      </c>
+      <c r="L562" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M562" t="s">
+        <v>67</v>
+      </c>
+      <c r="N562">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="563" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A563" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B563" s="25">
+        <v>46186</v>
+      </c>
+      <c r="C563" t="s">
+        <v>643</v>
+      </c>
+      <c r="D563" t="s">
+        <v>34</v>
+      </c>
+      <c r="E563" t="s">
+        <v>23</v>
+      </c>
+      <c r="F563">
+        <v>1655</v>
+      </c>
+      <c r="G563" t="s">
+        <v>63</v>
+      </c>
+      <c r="H563" t="s">
+        <v>52</v>
+      </c>
+      <c r="I563" t="s">
+        <v>1620</v>
+      </c>
+      <c r="K563" t="s">
+        <v>56</v>
+      </c>
+      <c r="L563" s="25">
+        <v>46186</v>
+      </c>
+      <c r="M563" t="s">
+        <v>67</v>
+      </c>
+      <c r="N563">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="564" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A564" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B564" s="25">
+        <v>46187</v>
+      </c>
+      <c r="C564" t="s">
+        <v>753</v>
+      </c>
+      <c r="D564" t="s">
+        <v>34</v>
+      </c>
+      <c r="E564" t="s">
+        <v>314</v>
+      </c>
+      <c r="F564">
+        <v>1500</v>
+      </c>
+      <c r="G564" t="s">
+        <v>315</v>
+      </c>
+      <c r="H564" t="s">
+        <v>11</v>
+      </c>
+      <c r="M564" t="s">
+        <v>66</v>
+      </c>
+      <c r="N564">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="565" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A565" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B565" s="25">
+        <v>46187</v>
+      </c>
+      <c r="C565" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D565" t="s">
+        <v>34</v>
+      </c>
+      <c r="E565" t="s">
+        <v>314</v>
+      </c>
+      <c r="F565">
+        <v>1358</v>
+      </c>
+      <c r="G565" t="s">
+        <v>315</v>
+      </c>
+      <c r="H565" t="s">
+        <v>52</v>
+      </c>
+      <c r="I565" t="s">
+        <v>1623</v>
+      </c>
+      <c r="M565" t="s">
+        <v>66</v>
+      </c>
+      <c r="N565">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="566" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A566" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B566" s="25">
+        <v>46187</v>
+      </c>
+      <c r="C566" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D566" t="s">
+        <v>34</v>
+      </c>
+      <c r="E566" t="s">
+        <v>314</v>
+      </c>
+      <c r="F566">
+        <v>1499</v>
+      </c>
+      <c r="G566" t="s">
+        <v>315</v>
+      </c>
+      <c r="H566" t="s">
+        <v>11</v>
+      </c>
+      <c r="M566" t="s">
+        <v>66</v>
+      </c>
+      <c r="N566">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="567" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A567" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B567" s="25">
+        <v>46187</v>
+      </c>
+      <c r="C567" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D567" t="s">
+        <v>34</v>
+      </c>
+      <c r="E567" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F567">
+        <v>668</v>
+      </c>
+      <c r="G567" t="s">
+        <v>1628</v>
+      </c>
+      <c r="H567" t="s">
+        <v>11</v>
+      </c>
+      <c r="I567" t="s">
+        <v>1629</v>
+      </c>
+      <c r="K567" t="s">
+        <v>56</v>
+      </c>
+      <c r="L567" s="25">
+        <v>46187</v>
+      </c>
+      <c r="M567" t="s">
+        <v>67</v>
+      </c>
+      <c r="N567">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="568" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A568" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B568" s="25">
+        <v>46187</v>
+      </c>
+      <c r="C568" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D568" t="s">
+        <v>34</v>
+      </c>
+      <c r="E568" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F568">
+        <v>1121</v>
+      </c>
+      <c r="G568" t="s">
+        <v>1628</v>
+      </c>
+      <c r="H568" t="s">
+        <v>11</v>
+      </c>
+      <c r="I568" t="s">
+        <v>1632</v>
+      </c>
+      <c r="K568" t="s">
+        <v>56</v>
+      </c>
+      <c r="L568" s="25">
+        <v>46187</v>
+      </c>
+      <c r="M568" t="s">
+        <v>67</v>
+      </c>
+      <c r="N568">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="569" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A569" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B569" s="25">
+        <v>46188</v>
+      </c>
+      <c r="C569" t="s">
+        <v>219</v>
+      </c>
+      <c r="D569" t="s">
+        <v>34</v>
+      </c>
+      <c r="E569" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F569">
+        <v>1675</v>
+      </c>
+      <c r="G569" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H569" t="s">
+        <v>35</v>
+      </c>
+      <c r="J569" t="s">
+        <v>1634</v>
+      </c>
+      <c r="M569" t="s">
+        <v>66</v>
+      </c>
+      <c r="N569">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="570" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A570" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B570" s="25">
+        <v>46188</v>
+      </c>
+      <c r="C570" t="s">
+        <v>810</v>
+      </c>
+      <c r="D570" t="s">
+        <v>34</v>
+      </c>
+      <c r="E570" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F570">
+        <v>301</v>
+      </c>
+      <c r="G570" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H570" t="s">
+        <v>37</v>
+      </c>
+      <c r="I570" t="s">
+        <v>1636</v>
+      </c>
+      <c r="J570" t="s">
+        <v>1637</v>
+      </c>
+      <c r="M570" t="s">
+        <v>66</v>
+      </c>
+      <c r="N570">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="571" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A571" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B571" s="25">
+        <v>46188</v>
+      </c>
+      <c r="C571" t="s">
+        <v>100</v>
+      </c>
+      <c r="D571" t="s">
+        <v>34</v>
+      </c>
+      <c r="E571" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F571">
+        <v>611</v>
+      </c>
+      <c r="G571" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H571" t="s">
+        <v>38</v>
+      </c>
+      <c r="J571" t="s">
+        <v>1639</v>
+      </c>
+      <c r="M571" t="s">
+        <v>66</v>
+      </c>
+      <c r="N571">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="572" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A572" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B572" s="25">
+        <v>46188</v>
+      </c>
+      <c r="C572" t="s">
+        <v>553</v>
+      </c>
+      <c r="D572" t="s">
+        <v>34</v>
+      </c>
+      <c r="E572" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F572">
+        <v>1206</v>
+      </c>
+      <c r="G572" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H572" t="s">
+        <v>35</v>
+      </c>
+      <c r="J572" t="s">
+        <v>1641</v>
+      </c>
+      <c r="M572" t="s">
+        <v>66</v>
+      </c>
+      <c r="N572">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="573" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A573" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B573" s="25">
+        <v>46188</v>
+      </c>
+      <c r="C573" t="s">
+        <v>102</v>
+      </c>
+      <c r="D573" t="s">
+        <v>34</v>
+      </c>
+      <c r="E573" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F573">
+        <v>1395</v>
+      </c>
+      <c r="G573" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H573" t="s">
+        <v>11</v>
+      </c>
+      <c r="I573" t="s">
+        <v>1643</v>
+      </c>
+      <c r="J573" t="s">
+        <v>1644</v>
+      </c>
+      <c r="M573" t="s">
+        <v>66</v>
+      </c>
+      <c r="N573">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="574" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A574" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B574" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C574" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D574" t="s">
+        <v>34</v>
+      </c>
+      <c r="E574" t="s">
+        <v>16</v>
+      </c>
+      <c r="F574">
+        <v>4165</v>
+      </c>
+      <c r="G574" t="s">
+        <v>36</v>
+      </c>
+      <c r="H574" t="s">
+        <v>11</v>
+      </c>
+      <c r="I574" t="s">
+        <v>1647</v>
+      </c>
+      <c r="J574" t="s">
+        <v>1648</v>
+      </c>
+      <c r="K574" t="s">
+        <v>56</v>
+      </c>
+      <c r="L574" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M574" t="s">
+        <v>67</v>
+      </c>
+      <c r="N574">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="575" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A575" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B575" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C575" t="s">
+        <v>188</v>
+      </c>
+      <c r="D575" t="s">
+        <v>34</v>
+      </c>
+      <c r="E575" t="s">
+        <v>12</v>
+      </c>
+      <c r="F575">
+        <v>6167</v>
+      </c>
+      <c r="G575" t="s">
+        <v>53</v>
+      </c>
+      <c r="H575" t="s">
+        <v>35</v>
+      </c>
+      <c r="J575" t="s">
+        <v>1650</v>
+      </c>
+      <c r="M575" t="s">
+        <v>66</v>
+      </c>
+      <c r="N575">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="576" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A576" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B576" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C576" t="s">
+        <v>973</v>
+      </c>
+      <c r="D576" t="s">
+        <v>34</v>
+      </c>
+      <c r="E576" t="s">
+        <v>21</v>
+      </c>
+      <c r="F576">
+        <v>6453</v>
+      </c>
+      <c r="G576" t="s">
+        <v>49</v>
+      </c>
+      <c r="H576" t="s">
+        <v>52</v>
+      </c>
+      <c r="J576" t="s">
+        <v>1652</v>
+      </c>
+      <c r="K576" t="s">
+        <v>62</v>
+      </c>
+      <c r="L576" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M576" t="s">
+        <v>67</v>
+      </c>
+      <c r="N576">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="577" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A577" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B577" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C577" t="s">
+        <v>194</v>
+      </c>
+      <c r="D577" t="s">
+        <v>34</v>
+      </c>
+      <c r="E577" t="s">
+        <v>9</v>
+      </c>
+      <c r="F577">
+        <v>6988</v>
+      </c>
+      <c r="G577" t="s">
+        <v>50</v>
+      </c>
+      <c r="H577" t="s">
+        <v>52</v>
+      </c>
+      <c r="I577" t="s">
+        <v>1654</v>
+      </c>
+      <c r="J577" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K577" t="s">
+        <v>1656</v>
+      </c>
+      <c r="L577" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M577" t="s">
+        <v>67</v>
+      </c>
+      <c r="N577">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="578" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A578" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B578" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C578" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D578" t="s">
+        <v>34</v>
+      </c>
+      <c r="E578" t="s">
+        <v>17</v>
+      </c>
+      <c r="F578">
+        <v>4944</v>
+      </c>
+      <c r="G578" t="s">
+        <v>44</v>
+      </c>
+      <c r="H578" t="s">
+        <v>52</v>
+      </c>
+      <c r="I578" t="s">
+        <v>1659</v>
+      </c>
+      <c r="J578" t="s">
+        <v>1660</v>
+      </c>
+      <c r="K578" t="s">
+        <v>56</v>
+      </c>
+      <c r="L578" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M578" t="s">
+        <v>67</v>
+      </c>
+      <c r="N578">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="579" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A579" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B579" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C579" t="s">
+        <v>878</v>
+      </c>
+      <c r="D579" t="s">
+        <v>34</v>
+      </c>
+      <c r="E579" t="s">
+        <v>17</v>
+      </c>
+      <c r="F579">
+        <v>4920</v>
+      </c>
+      <c r="G579" t="s">
+        <v>44</v>
+      </c>
+      <c r="H579" t="s">
+        <v>11</v>
+      </c>
+      <c r="I579" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J579" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K579" t="s">
+        <v>56</v>
+      </c>
+      <c r="L579" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M579" t="s">
+        <v>67</v>
+      </c>
+      <c r="N579">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="580" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A580" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B580" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C580" t="s">
+        <v>983</v>
+      </c>
+      <c r="D580" t="s">
+        <v>34</v>
+      </c>
+      <c r="E580" t="s">
+        <v>12</v>
+      </c>
+      <c r="F580">
+        <v>6170</v>
+      </c>
+      <c r="G580" t="s">
+        <v>53</v>
+      </c>
+      <c r="H580" t="s">
+        <v>52</v>
+      </c>
+      <c r="I580" t="s">
+        <v>1665</v>
+      </c>
+      <c r="J580" t="s">
+        <v>1666</v>
+      </c>
+      <c r="M580" t="s">
+        <v>66</v>
+      </c>
+      <c r="N580">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="581" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A581" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B581" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C581" s="28">
+        <v>0.39097222222222222</v>
+      </c>
+      <c r="D581" t="s">
+        <v>34</v>
+      </c>
+      <c r="E581" t="s">
+        <v>210</v>
+      </c>
+      <c r="F581">
+        <v>4188</v>
+      </c>
+      <c r="G581" t="s">
+        <v>44</v>
+      </c>
+      <c r="H581" t="s">
+        <v>52</v>
+      </c>
+      <c r="I581" t="s">
+        <v>1668</v>
+      </c>
+      <c r="J581" t="s">
+        <v>1669</v>
+      </c>
+      <c r="K581" t="s">
+        <v>56</v>
+      </c>
+      <c r="L581" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M581" t="s">
+        <v>67</v>
+      </c>
+      <c r="N581">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="582" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A582" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B582" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C582" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D582" t="s">
+        <v>34</v>
+      </c>
+      <c r="E582" t="s">
+        <v>17</v>
+      </c>
+      <c r="F582">
+        <v>10978</v>
+      </c>
+      <c r="G582" t="s">
+        <v>199</v>
+      </c>
+      <c r="H582" t="s">
+        <v>35</v>
+      </c>
+      <c r="J582" t="s">
+        <v>1672</v>
+      </c>
+      <c r="K582" t="s">
+        <v>54</v>
+      </c>
+      <c r="L582" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M582" t="s">
+        <v>67</v>
+      </c>
+      <c r="N582">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="583" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A583" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B583" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C583" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D583" t="s">
+        <v>34</v>
+      </c>
+      <c r="E583" t="s">
+        <v>23</v>
+      </c>
+      <c r="F583">
+        <v>4060</v>
+      </c>
+      <c r="G583" t="s">
+        <v>65</v>
+      </c>
+      <c r="H583" t="s">
+        <v>37</v>
+      </c>
+      <c r="I583" t="s">
+        <v>1675</v>
+      </c>
+      <c r="K583" t="s">
+        <v>54</v>
+      </c>
+      <c r="L583" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M583" t="s">
+        <v>67</v>
+      </c>
+      <c r="N583">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="584" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A584" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B584" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C584" t="s">
+        <v>397</v>
+      </c>
+      <c r="D584" t="s">
+        <v>34</v>
+      </c>
+      <c r="E584" t="s">
+        <v>64</v>
+      </c>
+      <c r="F584">
+        <v>1839</v>
+      </c>
+      <c r="G584" t="s">
+        <v>63</v>
+      </c>
+      <c r="H584" t="s">
+        <v>38</v>
+      </c>
+      <c r="I584" t="s">
+        <v>391</v>
+      </c>
+      <c r="J584" t="s">
+        <v>1677</v>
+      </c>
+      <c r="K584" t="s">
+        <v>54</v>
+      </c>
+      <c r="L584" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M584" t="s">
+        <v>67</v>
+      </c>
+      <c r="N584">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="585" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A585" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B585" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C585" t="s">
+        <v>207</v>
+      </c>
+      <c r="D585" t="s">
+        <v>34</v>
+      </c>
+      <c r="E585" t="s">
+        <v>12</v>
+      </c>
+      <c r="F585">
+        <v>6124</v>
+      </c>
+      <c r="G585" t="s">
+        <v>53</v>
+      </c>
+      <c r="H585" t="s">
+        <v>38</v>
+      </c>
+      <c r="J585" t="s">
+        <v>1679</v>
+      </c>
+      <c r="K585" t="s">
+        <v>55</v>
+      </c>
+      <c r="L585" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M585" t="s">
+        <v>67</v>
+      </c>
+      <c r="N585">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="586" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A586" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B586" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C586" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D586" t="s">
+        <v>34</v>
+      </c>
+      <c r="E586" t="s">
+        <v>244</v>
+      </c>
+      <c r="F586">
+        <v>7312</v>
+      </c>
+      <c r="G586" t="s">
+        <v>51</v>
+      </c>
+      <c r="H586" t="s">
+        <v>37</v>
+      </c>
+      <c r="I586" t="s">
+        <v>1682</v>
+      </c>
+      <c r="J586" t="s">
+        <v>1683</v>
+      </c>
+      <c r="K586" t="s">
+        <v>1684</v>
+      </c>
+      <c r="L586" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M586" t="s">
+        <v>67</v>
+      </c>
+      <c r="N586">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="587" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A587" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B587" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C587" t="s">
+        <v>213</v>
+      </c>
+      <c r="D587" t="s">
+        <v>34</v>
+      </c>
+      <c r="E587" t="s">
+        <v>21</v>
+      </c>
+      <c r="F587">
+        <v>6455</v>
+      </c>
+      <c r="G587" t="s">
+        <v>36</v>
+      </c>
+      <c r="H587" t="s">
+        <v>38</v>
+      </c>
+      <c r="J587" t="s">
+        <v>1686</v>
+      </c>
+      <c r="K587" t="s">
+        <v>55</v>
+      </c>
+      <c r="L587" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M587" t="s">
+        <v>67</v>
+      </c>
+      <c r="N587">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="588" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A588" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B588" s="25">
+        <v>46189</v>
+      </c>
+      <c r="C588" t="s">
+        <v>100</v>
+      </c>
+      <c r="D588" t="s">
+        <v>34</v>
+      </c>
+      <c r="E588" t="s">
+        <v>19</v>
+      </c>
+      <c r="F588">
+        <v>7076</v>
+      </c>
+      <c r="G588" t="s">
+        <v>51</v>
+      </c>
+      <c r="H588" t="s">
+        <v>11</v>
+      </c>
+      <c r="I588" s="29" t="s">
+        <v>1688</v>
+      </c>
+      <c r="K588" t="s">
+        <v>45</v>
+      </c>
+      <c r="L588" s="25">
+        <v>46189</v>
+      </c>
+      <c r="M588" t="s">
+        <v>67</v>
+      </c>
+      <c r="N588">
         <v>6</v>
       </c>
     </row>

--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos junio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCEB77EE-7893-4D5A-8426-768C7DEC4DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DBED0C-ABE9-41FA-8362-5FDB246545AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Rechazos Calle" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$705</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$776</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6152" uniqueCount="1973">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6759" uniqueCount="2145">
   <si>
     <t>Fecha</t>
   </si>
@@ -5971,6 +5971,522 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781790248/ba639u3pm5awjiub5oan.jpg</t>
+  </si>
+  <si>
+    <t>MQJJZDEMGHXQ</t>
+  </si>
+  <si>
+    <t>10:46 a. m.</t>
+  </si>
+  <si>
+    <t>Playadito de medio dos</t>
+  </si>
+  <si>
+    <t>MQJKFGV1I0AG</t>
+  </si>
+  <si>
+    <t>MQJKHRFFKU6X</t>
+  </si>
+  <si>
+    <t>11:00 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781791249/vm4wd5lowvobp5osliej.jpg</t>
+  </si>
+  <si>
+    <t>MQJKO1DS7DO9</t>
+  </si>
+  <si>
+    <t>11:05 a. m.</t>
+  </si>
+  <si>
+    <t>4 maicitos</t>
+  </si>
+  <si>
+    <t>MQJKR3N461WV</t>
+  </si>
+  <si>
+    <t>MQJKUXLD85UL</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781791864/bao9dut6rdq2hhaksa4d.jpg</t>
+  </si>
+  <si>
+    <t>MQJL6YNSSZJU</t>
+  </si>
+  <si>
+    <t>Vino sin stock</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781792420/xz676vovl179sho6pa4z.jpg</t>
+  </si>
+  <si>
+    <t>MQJLX590RIS7</t>
+  </si>
+  <si>
+    <t>11:40 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781793647/bf6rdglrdnt5l5ealzok.jpg</t>
+  </si>
+  <si>
+    <t>MQJM5NM76Z7F</t>
+  </si>
+  <si>
+    <t>Faltó 3 pehuamar lisa 135. Y 1 Tostitos 260gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781794046/gru697txlox2ootghf8t.jpg</t>
+  </si>
+  <si>
+    <t>MQJM9XPX1WZ9</t>
+  </si>
+  <si>
+    <t>Rechaza suerox</t>
+  </si>
+  <si>
+    <t>MQJMYEW7WD0V</t>
+  </si>
+  <si>
+    <t>Devolvió tostitos De 100 grs no los pidio</t>
+  </si>
+  <si>
+    <t>MQJN4HMVAFW0</t>
+  </si>
+  <si>
+    <t>Talita sin stock</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781795669/uttxpake3efbhkfcqv8v.jpg</t>
+  </si>
+  <si>
+    <t>MQJNKW5NNQ0B</t>
+  </si>
+  <si>
+    <t>1 bizcochuelo argentina</t>
+  </si>
+  <si>
+    <t>MQJNYPJARQLD</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781797085/z81ehkiynqf0dlc6rjut.jpg</t>
+  </si>
+  <si>
+    <t>MQJOJNUUFWS3</t>
+  </si>
+  <si>
+    <t>12:54 p. m.</t>
+  </si>
+  <si>
+    <t>1paq roto</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781798055/or1z01w09y2sdinwtlhw.jpg</t>
+  </si>
+  <si>
+    <t>El cliente va a recibir — seguí viaje — Retirar mercadería defectuosa.</t>
+  </si>
+  <si>
+    <t>MQJOMLDFIPMD</t>
+  </si>
+  <si>
+    <t>12:56 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781798193/vuhpwrtryovidcoelbnf.jpg</t>
+  </si>
+  <si>
+    <t>MQJOOQBO94XJ</t>
+  </si>
+  <si>
+    <t>MQJOUO1ZNWFT</t>
+  </si>
+  <si>
+    <t>MQJOW9WN22V9</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781798649/cqcnubpndddp4hvnenjz.jpg</t>
+  </si>
+  <si>
+    <t>MQJOVFGQQZ1D</t>
+  </si>
+  <si>
+    <t>Descuenta pañal , pide xxg y mandaron xg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781798613/dhplgq9gtzlpsd1cnrqe.jpg</t>
+  </si>
+  <si>
+    <t>MQJP6XUG93DQ</t>
+  </si>
+  <si>
+    <t>Playadito de medio sin stock 10</t>
+  </si>
+  <si>
+    <t>MQJP9QRQ2R9Z</t>
+  </si>
+  <si>
+    <t>Rechaza Doritos</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781799278/x6mv3bnskcfplto7shcs.jpg</t>
+  </si>
+  <si>
+    <t>MQJP9C7KDK28</t>
+  </si>
+  <si>
+    <t>Lisa 135 tostitos 160</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781799360/vndfocalb0ftgghxvqig.jpg</t>
+  </si>
+  <si>
+    <t>MQJPGTHHUFF6</t>
+  </si>
+  <si>
+    <t>01:21 p. m.</t>
+  </si>
+  <si>
+    <t>5 tokke con leche</t>
+  </si>
+  <si>
+    <t>MQJPR118GEYX</t>
+  </si>
+  <si>
+    <t>01:28 p. m.</t>
+  </si>
+  <si>
+    <t>Fantoche súper dulce de leche 24</t>
+  </si>
+  <si>
+    <t>MQJPU1N0UMR4</t>
+  </si>
+  <si>
+    <t>01:30 p. m.</t>
+  </si>
+  <si>
+    <t>MQJPXRBNNL7H</t>
+  </si>
+  <si>
+    <t>MQJPSF5X3ND1</t>
+  </si>
+  <si>
+    <t>01:35 p. m.</t>
+  </si>
+  <si>
+    <t>1 asado, 2chetos ondulados devolvio</t>
+  </si>
+  <si>
+    <t>MQJQKMLOASVV</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781801475/mhljxhlm4httklfmfzbj.jpg</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — Se pidió que se anulará ese pedido</t>
+  </si>
+  <si>
+    <t>MQJR1LCGN10I</t>
+  </si>
+  <si>
+    <t>MQJRF41NSD3X</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781802879/zars7x12sbmrp7g9rpqo.jpg</t>
+  </si>
+  <si>
+    <t>MQJRH8RF3HCA</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781802990/ccckdlequl5nwft6bkpn.jpg</t>
+  </si>
+  <si>
+    <t>MQJRJ57LVRXZ</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781803093/bhxkfqatnhojiuaibo6j.jpg</t>
+  </si>
+  <si>
+    <t>MQJRL60V3KE1</t>
+  </si>
+  <si>
+    <t>Fantoche súper dulce de leche 6 unid</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781803325/sldpsirawnk0zrflliuv.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Sin stock se descuenta de la boleta.</t>
+  </si>
+  <si>
+    <t>MQJRQE1IB9S0</t>
+  </si>
+  <si>
+    <t>No quizo</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781803428/d74krlngzkjrtkubdvkp.jpg</t>
+  </si>
+  <si>
+    <t>MQJS4DOC5NQ4</t>
+  </si>
+  <si>
+    <t>2 Norton select Malbec</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781804061/vofjowr3on02c4qebncr.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Son stock</t>
+  </si>
+  <si>
+    <t>MQJS5WBBZY5A</t>
+  </si>
+  <si>
+    <t>02:35 p. m.</t>
+  </si>
+  <si>
+    <t>48 cubanitos smacks</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781804128/nec31s06fnuzbyiyczq7.jpg</t>
+  </si>
+  <si>
+    <t>MQJS653WVJB1</t>
+  </si>
+  <si>
+    <t>02:36 p. m.</t>
+  </si>
+  <si>
+    <t>MQJSGXYN0X35</t>
+  </si>
+  <si>
+    <t>02:44 p. m.</t>
+  </si>
+  <si>
+    <t>MQJSNTIEOP7P</t>
+  </si>
+  <si>
+    <t>02:49 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781804976/t1x1lh5udqpar21mytta.jpg</t>
+  </si>
+  <si>
+    <t>MQJU097CUQUG</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781807230/mdq00npqwnza6jxajwon.jpg</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — El cliente cierra a la 13:30</t>
+  </si>
+  <si>
+    <t>MQJUCWT33CA6</t>
+  </si>
+  <si>
+    <t>03:36 p. m.</t>
+  </si>
+  <si>
+    <t>MQJUDHSK4DLP</t>
+  </si>
+  <si>
+    <t>03:37 p. m.</t>
+  </si>
+  <si>
+    <t>MQK2XTHYCEID</t>
+  </si>
+  <si>
+    <t>07:37 p. m.</t>
+  </si>
+  <si>
+    <t>6 Doritos x 40gr</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — Descontar</t>
+  </si>
+  <si>
+    <t>MQK2Z6WOL2CP</t>
+  </si>
+  <si>
+    <t>07:38 p. m.</t>
+  </si>
+  <si>
+    <t>3 galletas leche 260gr</t>
+  </si>
+  <si>
+    <t>MQK30F6LDA9X</t>
+  </si>
+  <si>
+    <t>07:40 p. m.</t>
+  </si>
+  <si>
+    <t>5 tostitos x 160gr, pidió de 100gr</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — No pidieron tostitos de 100grs,pidieron de 129grs y al haber cambio de gramajes,el q sustituye al de 129grs es el de 160</t>
+  </si>
+  <si>
+    <t>MQKPX1GNVJTM</t>
+  </si>
+  <si>
+    <t>06:22 a. m.</t>
+  </si>
+  <si>
+    <t>MQKQ09L8GZWN</t>
+  </si>
+  <si>
+    <t>06:23 a. m.</t>
+  </si>
+  <si>
+    <t>MQKQ1G3371H4</t>
+  </si>
+  <si>
+    <t>06:24 a. m.</t>
+  </si>
+  <si>
+    <t>MQKQ488T8PG3</t>
+  </si>
+  <si>
+    <t>06:26 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781861181/u2ewodopkz10amdkckua.jpg</t>
+  </si>
+  <si>
+    <t>MQKQ6HG6T322</t>
+  </si>
+  <si>
+    <t>06:28 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781861295/o4irbvp2nfbsau6owtlf.jpg</t>
+  </si>
+  <si>
+    <t>MQKU7F4NP4RB</t>
+  </si>
+  <si>
+    <t>Aceite de oliva uno falta</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781868053/cpiwgrdthirartlwrr6r.jpg</t>
+  </si>
+  <si>
+    <t>MQKV51T8JUEW</t>
+  </si>
+  <si>
+    <t>Paq. Rotos</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781869604/vyqo6o34cphtyvw3qabt.jpg</t>
+  </si>
+  <si>
+    <t>MQKVQTB6YHLV</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781870617/xfhbln4vje5srylizsep.jpg</t>
+  </si>
+  <si>
+    <t>MQKVU9TS5WCF</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781870771/wf2urj6xvvn4bevmdouv.jpg</t>
+  </si>
+  <si>
+    <t>MQKW1BXBGXFQ</t>
+  </si>
+  <si>
+    <t>MQKWGXDZYMI2</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781871830/e08o1b6iirygpm73xls3.jpg</t>
+  </si>
+  <si>
+    <t>MQKWJ4TPY2LM</t>
+  </si>
+  <si>
+    <t>Devuelve Doritos de 40 y todo lo dinamita porque no pidió aparte el pep común está sin stock</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781871933/dua762rmea4aqd1avbkr.jpg</t>
+  </si>
+  <si>
+    <t>MQKWM80UMHCJ</t>
+  </si>
+  <si>
+    <t>09:29 a. m.</t>
+  </si>
+  <si>
+    <t>Rechazo alfajor fantoche 6 negro y 6 blanco</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781872085/anqovz1h3juyvs55fpfc.jpg</t>
+  </si>
+  <si>
+    <t>MQKXPBI86NNT</t>
+  </si>
+  <si>
+    <t>Pepa ramitas queso</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781873902/ag969rhji540hxjjwclj.jpg</t>
+  </si>
+  <si>
+    <t>MQKXWUTFPL31</t>
+  </si>
+  <si>
+    <t>Rotura mtzo vegetal tirabuzón 1</t>
+  </si>
+  <si>
+    <t>MQKYGXHMKPYB</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781875190/x53bhbxzoaiifsnhktkj.jpg</t>
+  </si>
+  <si>
+    <t>MQKYW5XJPZY9</t>
+  </si>
+  <si>
+    <t>Pidió 4 unidades de Doritos 40gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781875917/gptjleqsiycplo0uba63.jpg</t>
+  </si>
+  <si>
+    <t>MQKZ3XME851C</t>
+  </si>
+  <si>
+    <t>Don satur talitss y alf mantecol</t>
+  </si>
+  <si>
+    <t>MQKZ6J5WOL7E</t>
+  </si>
+  <si>
+    <t>Faltaron 2 unidades el bulto cerrado tenía 16 trae 18 la caja</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781876384/guihvlzjfhnybg9u73bu.jpg</t>
+  </si>
+  <si>
+    <t>MQKZB89W18K3</t>
+  </si>
+  <si>
+    <t>MQKZFWTOCZH3</t>
+  </si>
+  <si>
+    <t>Gruesa rota</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781876833/rnnirfdmykokelz5j2m6.jpg</t>
+  </si>
+  <si>
+    <t>MQKZS0LO30ZM</t>
+  </si>
+  <si>
+    <t>MQKZXYBLPMGA</t>
+  </si>
+  <si>
+    <t>Dice que lo esperaba hace dos semanas</t>
   </si>
 </sst>
 </file>
@@ -6164,7 +6680,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -6241,8 +6757,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -6360,8 +6874,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N705">
-  <autoFilter ref="A1:N705" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N776">
+  <autoFilter ref="A1:N776" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fecha"/>
@@ -6583,7 +7097,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N705"/>
+  <dimension ref="A1:N776"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -32296,3240 +32810,6744 @@
         <v>6</v>
       </c>
     </row>
-    <row r="623" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A623" t="s">
+    <row r="623" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A623" s="3" t="s">
         <v>1770</v>
       </c>
-      <c r="B623" s="26">
+      <c r="B623" s="4">
         <v>46190</v>
       </c>
-      <c r="C623" t="s">
+      <c r="C623" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="D623" t="s">
-        <v>34</v>
-      </c>
-      <c r="E623" t="s">
+      <c r="D623" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E623" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F623">
+      <c r="F623" s="6">
         <v>11036</v>
       </c>
-      <c r="G623" t="s">
+      <c r="G623" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H623" t="s">
+      <c r="H623" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I623" t="s">
+      <c r="I623" s="5" t="s">
         <v>1753</v>
       </c>
-      <c r="J623" t="s">
+      <c r="J623" s="11" t="s">
         <v>1771</v>
       </c>
-      <c r="K623" t="s">
+      <c r="K623" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="L623" s="26">
+      <c r="L623" s="4">
         <v>46190</v>
       </c>
-      <c r="M623" t="s">
-        <v>67</v>
-      </c>
-      <c r="N623">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="624" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A624" t="s">
+      <c r="M623" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N623" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="624" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A624" s="3" t="s">
         <v>1772</v>
       </c>
-      <c r="B624" s="26">
+      <c r="B624" s="4">
         <v>46190</v>
       </c>
-      <c r="C624" t="s">
+      <c r="C624" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D624" t="s">
-        <v>34</v>
-      </c>
-      <c r="E624" t="s">
+      <c r="D624" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E624" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F624">
+      <c r="F624" s="6">
         <v>2573</v>
       </c>
-      <c r="G624" t="s">
+      <c r="G624" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H624" t="s">
+      <c r="H624" s="22" t="s">
         <v>607</v>
       </c>
-      <c r="J624" t="s">
+      <c r="I624" s="8"/>
+      <c r="J624" s="11" t="s">
         <v>1773</v>
       </c>
-      <c r="K624" t="s">
+      <c r="K624" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L624" s="26">
+      <c r="L624" s="4">
         <v>46190</v>
       </c>
-      <c r="M624" t="s">
-        <v>67</v>
-      </c>
-      <c r="N624">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="625" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A625" t="s">
+      <c r="M624" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N624" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="625" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A625" s="3" t="s">
         <v>1774</v>
       </c>
-      <c r="B625" s="26">
+      <c r="B625" s="4">
         <v>46190</v>
       </c>
-      <c r="C625" t="s">
+      <c r="C625" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D625" t="s">
-        <v>34</v>
-      </c>
-      <c r="E625" t="s">
+      <c r="D625" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E625" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F625">
+      <c r="F625" s="6">
         <v>7429</v>
       </c>
-      <c r="G625" t="s">
+      <c r="G625" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H625" t="s">
+      <c r="H625" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I625" t="s">
+      <c r="I625" s="5" t="s">
         <v>1775</v>
       </c>
-      <c r="K625" t="s">
+      <c r="J625" s="8"/>
+      <c r="K625" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L625" s="26">
+      <c r="L625" s="4">
         <v>46190</v>
       </c>
-      <c r="M625" t="s">
-        <v>67</v>
-      </c>
-      <c r="N625">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="626" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A626" t="s">
+      <c r="M625" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N625" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="626" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A626" s="3" t="s">
         <v>1776</v>
       </c>
-      <c r="B626" s="26">
+      <c r="B626" s="4">
         <v>46190</v>
       </c>
-      <c r="C626" t="s">
+      <c r="C626" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D626" t="s">
-        <v>34</v>
-      </c>
-      <c r="E626" t="s">
+      <c r="D626" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E626" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F626">
+      <c r="F626" s="6">
         <v>3604</v>
       </c>
-      <c r="G626" t="s">
+      <c r="G626" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H626" t="s">
+      <c r="H626" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I626" t="s">
+      <c r="I626" s="5" t="s">
         <v>1777</v>
       </c>
-      <c r="J626" t="s">
+      <c r="J626" s="11" t="s">
         <v>1778</v>
       </c>
-      <c r="K626" t="s">
+      <c r="K626" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L626" s="26">
+      <c r="L626" s="4">
         <v>46190</v>
       </c>
-      <c r="M626" t="s">
-        <v>67</v>
-      </c>
-      <c r="N626">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="627" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A627" t="s">
+      <c r="M626" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N626" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="627" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A627" s="3" t="s">
         <v>1779</v>
       </c>
-      <c r="B627" s="26">
+      <c r="B627" s="4">
         <v>46190</v>
       </c>
-      <c r="C627" t="s">
+      <c r="C627" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D627" t="s">
-        <v>34</v>
-      </c>
-      <c r="E627" t="s">
+      <c r="D627" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E627" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F627">
+      <c r="F627" s="6">
         <v>7429</v>
       </c>
-      <c r="G627" t="s">
+      <c r="G627" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H627" t="s">
+      <c r="H627" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I627" t="s">
+      <c r="I627" s="5" t="s">
         <v>1780</v>
       </c>
-      <c r="K627" t="s">
+      <c r="J627" s="8"/>
+      <c r="K627" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L627" s="26">
+      <c r="L627" s="4">
         <v>46190</v>
       </c>
-      <c r="M627" t="s">
-        <v>67</v>
-      </c>
-      <c r="N627">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="628" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A628" t="s">
+      <c r="M627" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N627" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="628" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A628" s="3" t="s">
         <v>1781</v>
       </c>
-      <c r="B628" s="26">
+      <c r="B628" s="4">
         <v>46190</v>
       </c>
-      <c r="C628" t="s">
+      <c r="C628" s="5" t="s">
         <v>1782</v>
       </c>
-      <c r="D628" t="s">
-        <v>34</v>
-      </c>
-      <c r="E628" t="s">
+      <c r="D628" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E628" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F628">
+      <c r="F628" s="6">
         <v>3638</v>
       </c>
-      <c r="G628" t="s">
+      <c r="G628" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H628" t="s">
+      <c r="H628" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J628" t="s">
+      <c r="I628" s="8"/>
+      <c r="J628" s="11" t="s">
         <v>1783</v>
       </c>
-      <c r="K628" t="s">
+      <c r="K628" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L628" s="26">
+      <c r="L628" s="4">
         <v>46190</v>
       </c>
-      <c r="M628" t="s">
-        <v>67</v>
-      </c>
-      <c r="N628">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="629" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A629" t="s">
+      <c r="M628" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N628" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="629" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A629" s="3" t="s">
         <v>1784</v>
       </c>
-      <c r="B629" s="26">
+      <c r="B629" s="4">
         <v>46190</v>
       </c>
-      <c r="C629" t="s">
+      <c r="C629" s="5" t="s">
         <v>1785</v>
       </c>
-      <c r="D629" t="s">
-        <v>34</v>
-      </c>
-      <c r="E629" t="s">
+      <c r="D629" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E629" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F629">
+      <c r="F629" s="6">
         <v>3600</v>
       </c>
-      <c r="G629" t="s">
+      <c r="G629" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H629" t="s">
+      <c r="H629" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="I629" t="s">
+      <c r="I629" s="5" t="s">
         <v>1786</v>
       </c>
-      <c r="J629" t="s">
+      <c r="J629" s="11" t="s">
         <v>1787</v>
       </c>
-      <c r="K629" t="s">
+      <c r="K629" s="5" t="s">
         <v>1788</v>
       </c>
-      <c r="L629" s="26">
+      <c r="L629" s="4">
         <v>46190</v>
       </c>
-      <c r="M629" t="s">
-        <v>67</v>
-      </c>
-      <c r="N629">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="630" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A630" t="s">
+      <c r="M629" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N629" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="630" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A630" s="3" t="s">
         <v>1789</v>
       </c>
-      <c r="B630" s="26">
+      <c r="B630" s="4">
         <v>46190</v>
       </c>
-      <c r="C630" t="s">
+      <c r="C630" s="5" t="s">
         <v>994</v>
       </c>
-      <c r="D630" t="s">
-        <v>34</v>
-      </c>
-      <c r="E630" t="s">
+      <c r="D630" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E630" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="F630">
+      <c r="F630" s="6">
         <v>6293</v>
       </c>
-      <c r="G630" t="s">
+      <c r="G630" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H630" t="s">
+      <c r="H630" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I630" t="s">
+      <c r="I630" s="5" t="s">
         <v>1790</v>
       </c>
-      <c r="K630" t="s">
+      <c r="J630" s="8"/>
+      <c r="K630" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L630" s="26">
+      <c r="L630" s="4">
         <v>46190</v>
       </c>
-      <c r="M630" t="s">
-        <v>67</v>
-      </c>
-      <c r="N630">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="631" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A631" t="s">
+      <c r="M630" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N630" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="631" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A631" s="3" t="s">
         <v>1791</v>
       </c>
-      <c r="B631" s="26">
+      <c r="B631" s="4">
         <v>46190</v>
       </c>
-      <c r="C631" t="s">
+      <c r="C631" s="5" t="s">
         <v>1583</v>
       </c>
-      <c r="D631" t="s">
-        <v>34</v>
-      </c>
-      <c r="E631" t="s">
+      <c r="D631" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E631" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F631">
+      <c r="F631" s="6">
         <v>3602</v>
       </c>
-      <c r="G631" t="s">
+      <c r="G631" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H631" t="s">
+      <c r="H631" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J631" t="s">
+      <c r="I631" s="8"/>
+      <c r="J631" s="11" t="s">
         <v>1792</v>
       </c>
-      <c r="M631" t="s">
+      <c r="K631" s="8"/>
+      <c r="L631" s="8"/>
+      <c r="M631" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N631">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="632" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A632" t="s">
+      <c r="N631" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="632" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A632" s="3" t="s">
         <v>1793</v>
       </c>
-      <c r="B632" s="26">
+      <c r="B632" s="4">
         <v>46190</v>
       </c>
-      <c r="C632" t="s">
+      <c r="C632" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D632" t="s">
-        <v>34</v>
-      </c>
-      <c r="E632" t="s">
+      <c r="D632" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E632" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F632">
+      <c r="F632" s="6">
         <v>7370</v>
       </c>
-      <c r="G632" t="s">
+      <c r="G632" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H632" t="s">
+      <c r="H632" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I632" t="s">
+      <c r="I632" s="5" t="s">
         <v>1794</v>
       </c>
-      <c r="K632" t="s">
+      <c r="J632" s="8"/>
+      <c r="K632" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L632" s="26">
+      <c r="L632" s="4">
         <v>46190</v>
       </c>
-      <c r="M632" t="s">
-        <v>67</v>
-      </c>
-      <c r="N632">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="633" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A633" t="s">
+      <c r="M632" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N632" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="633" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A633" s="3" t="s">
         <v>1795</v>
       </c>
-      <c r="B633" s="26">
+      <c r="B633" s="4">
         <v>46190</v>
       </c>
-      <c r="C633" t="s">
+      <c r="C633" s="5" t="s">
         <v>907</v>
       </c>
-      <c r="D633" t="s">
-        <v>34</v>
-      </c>
-      <c r="E633" t="s">
+      <c r="D633" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E633" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="F633">
+      <c r="F633" s="6">
         <v>6251</v>
       </c>
-      <c r="G633" t="s">
+      <c r="G633" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H633" t="s">
+      <c r="H633" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I633" t="s">
+      <c r="I633" s="5" t="s">
         <v>1796</v>
       </c>
-      <c r="K633" t="s">
+      <c r="J633" s="8"/>
+      <c r="K633" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L633" s="26">
+      <c r="L633" s="4">
         <v>46190</v>
       </c>
-      <c r="M633" t="s">
-        <v>67</v>
-      </c>
-      <c r="N633">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="634" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A634" t="s">
+      <c r="M633" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N633" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="634" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A634" s="3" t="s">
         <v>1797</v>
       </c>
-      <c r="B634" s="26">
+      <c r="B634" s="4">
         <v>46190</v>
       </c>
-      <c r="C634" t="s">
+      <c r="C634" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="D634" t="s">
-        <v>34</v>
-      </c>
-      <c r="E634" t="s">
+      <c r="D634" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E634" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F634">
+      <c r="F634" s="6">
         <v>5914</v>
       </c>
-      <c r="G634" t="s">
+      <c r="G634" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H634" t="s">
+      <c r="H634" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J634" t="s">
+      <c r="I634" s="8"/>
+      <c r="J634" s="11" t="s">
         <v>1798</v>
       </c>
-      <c r="M634" t="s">
+      <c r="K634" s="8"/>
+      <c r="L634" s="8"/>
+      <c r="M634" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N634">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="635" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A635" t="s">
+      <c r="N634" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="635" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A635" s="3" t="s">
         <v>1799</v>
       </c>
-      <c r="B635" s="26">
+      <c r="B635" s="4">
         <v>46190</v>
       </c>
-      <c r="C635" t="s">
+      <c r="C635" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="D635" t="s">
-        <v>34</v>
-      </c>
-      <c r="E635" t="s">
+      <c r="D635" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E635" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F635">
+      <c r="F635" s="6">
         <v>7141</v>
       </c>
-      <c r="G635" t="s">
+      <c r="G635" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H635" t="s">
+      <c r="H635" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J635" t="s">
+      <c r="I635" s="8"/>
+      <c r="J635" s="11" t="s">
         <v>1800</v>
       </c>
-      <c r="K635" t="s">
+      <c r="K635" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="L635" s="26">
+      <c r="L635" s="4">
         <v>46190</v>
       </c>
-      <c r="M635" t="s">
-        <v>67</v>
-      </c>
-      <c r="N635">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="636" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A636" t="s">
+      <c r="M635" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N635" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="636" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A636" s="3" t="s">
         <v>1801</v>
       </c>
-      <c r="B636" s="26">
+      <c r="B636" s="4">
         <v>46190</v>
       </c>
-      <c r="C636" t="s">
+      <c r="C636" s="5" t="s">
         <v>1802</v>
       </c>
-      <c r="D636" t="s">
-        <v>34</v>
-      </c>
-      <c r="E636" t="s">
+      <c r="D636" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E636" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F636">
+      <c r="F636" s="6">
         <v>10961</v>
       </c>
-      <c r="G636" t="s">
+      <c r="G636" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H636" t="s">
+      <c r="H636" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I636" t="s">
+      <c r="I636" s="5" t="s">
         <v>1803</v>
       </c>
-      <c r="K636" t="s">
+      <c r="J636" s="8"/>
+      <c r="K636" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="L636" s="26">
+      <c r="L636" s="4">
         <v>46190</v>
       </c>
-      <c r="M636" t="s">
-        <v>67</v>
-      </c>
-      <c r="N636">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="637" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A637" t="s">
+      <c r="M636" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N636" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="637" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A637" s="3" t="s">
         <v>1804</v>
       </c>
-      <c r="B637" s="26">
+      <c r="B637" s="4">
         <v>46190</v>
       </c>
-      <c r="C637" s="27">
+      <c r="C637" s="13">
         <v>0.4777777777777778</v>
       </c>
-      <c r="D637" t="s">
-        <v>34</v>
-      </c>
-      <c r="E637" t="s">
+      <c r="D637" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E637" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F637">
+      <c r="F637" s="6">
         <v>6252</v>
       </c>
-      <c r="G637" t="s">
+      <c r="G637" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H637" t="s">
+      <c r="H637" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I637" t="s">
+      <c r="I637" s="5" t="s">
         <v>1805</v>
       </c>
-      <c r="J637" t="s">
+      <c r="J637" s="11" t="s">
         <v>1806</v>
       </c>
-      <c r="K637" t="s">
+      <c r="K637" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L637" s="26">
+      <c r="L637" s="4">
         <v>46190</v>
       </c>
-      <c r="M637" t="s">
-        <v>67</v>
-      </c>
-      <c r="N637">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="638" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A638" t="s">
+      <c r="M637" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N637" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="638" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A638" s="3" t="s">
         <v>1807</v>
       </c>
-      <c r="B638" s="26">
+      <c r="B638" s="4">
         <v>46190</v>
       </c>
-      <c r="C638" t="s">
+      <c r="C638" s="5" t="s">
         <v>1808</v>
       </c>
-      <c r="D638" t="s">
-        <v>34</v>
-      </c>
-      <c r="E638" t="s">
+      <c r="D638" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E638" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F638">
+      <c r="F638" s="6">
         <v>4222</v>
       </c>
-      <c r="G638" t="s">
+      <c r="G638" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H638" t="s">
+      <c r="H638" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I638" t="s">
+      <c r="I638" s="5" t="s">
         <v>1809</v>
       </c>
-      <c r="M638" t="s">
+      <c r="J638" s="8"/>
+      <c r="K638" s="8"/>
+      <c r="L638" s="8"/>
+      <c r="M638" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N638">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="639" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A639" t="s">
+      <c r="N638" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="639" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A639" s="3" t="s">
         <v>1810</v>
       </c>
-      <c r="B639" s="26">
+      <c r="B639" s="4">
         <v>46190</v>
       </c>
-      <c r="C639" t="s">
+      <c r="C639" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="D639" t="s">
-        <v>34</v>
-      </c>
-      <c r="E639" t="s">
+      <c r="D639" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E639" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F639">
+      <c r="F639" s="6">
         <v>6559</v>
       </c>
-      <c r="G639" t="s">
+      <c r="G639" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H639" t="s">
+      <c r="H639" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I639" t="s">
+      <c r="I639" s="5" t="s">
         <v>1811</v>
       </c>
-      <c r="K639" t="s">
+      <c r="J639" s="8"/>
+      <c r="K639" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L639" s="26">
+      <c r="L639" s="4">
         <v>46190</v>
       </c>
-      <c r="M639" t="s">
-        <v>67</v>
-      </c>
-      <c r="N639">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="640" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A640" t="s">
+      <c r="M639" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N639" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="640" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A640" s="3" t="s">
         <v>1812</v>
       </c>
-      <c r="B640" s="26">
+      <c r="B640" s="4">
         <v>46190</v>
       </c>
-      <c r="C640" t="s">
+      <c r="C640" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="D640" t="s">
-        <v>34</v>
-      </c>
-      <c r="E640" t="s">
+      <c r="D640" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E640" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F640">
+      <c r="F640" s="6">
         <v>10862</v>
       </c>
-      <c r="G640" t="s">
+      <c r="G640" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H640" t="s">
+      <c r="H640" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J640" t="s">
+      <c r="I640" s="8"/>
+      <c r="J640" s="11" t="s">
         <v>1813</v>
       </c>
-      <c r="K640" t="s">
+      <c r="K640" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L640" s="26">
+      <c r="L640" s="4">
         <v>46190</v>
       </c>
-      <c r="M640" t="s">
-        <v>67</v>
-      </c>
-      <c r="N640">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="641" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A641" t="s">
+      <c r="M640" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N640" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="641" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A641" s="3" t="s">
         <v>1814</v>
       </c>
-      <c r="B641" s="26">
+      <c r="B641" s="4">
         <v>46190</v>
       </c>
-      <c r="C641" t="s">
+      <c r="C641" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="D641" t="s">
-        <v>34</v>
-      </c>
-      <c r="E641" t="s">
+      <c r="D641" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E641" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F641">
+      <c r="F641" s="6">
         <v>10736</v>
       </c>
-      <c r="G641" t="s">
+      <c r="G641" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H641" t="s">
+      <c r="H641" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I641" t="s">
+      <c r="I641" s="5" t="s">
         <v>1815</v>
       </c>
-      <c r="J641" t="s">
+      <c r="J641" s="11" t="s">
         <v>1816</v>
       </c>
-      <c r="M641" t="s">
+      <c r="K641" s="8"/>
+      <c r="L641" s="8"/>
+      <c r="M641" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N641">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="642" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A642" t="s">
+      <c r="N641" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="642" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A642" s="3" t="s">
         <v>1817</v>
       </c>
-      <c r="B642" s="26">
+      <c r="B642" s="4">
         <v>46190</v>
       </c>
-      <c r="C642" t="s">
+      <c r="C642" s="5" t="s">
         <v>1818</v>
       </c>
-      <c r="D642" t="s">
-        <v>34</v>
-      </c>
-      <c r="E642" t="s">
+      <c r="D642" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E642" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F642">
+      <c r="F642" s="6">
         <v>1927</v>
       </c>
-      <c r="G642" t="s">
+      <c r="G642" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H642" t="s">
+      <c r="H642" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I642" t="s">
+      <c r="I642" s="5" t="s">
         <v>1819</v>
       </c>
-      <c r="J642" t="s">
+      <c r="J642" s="11" t="s">
         <v>1820</v>
       </c>
-      <c r="K642" t="s">
+      <c r="K642" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L642" s="26">
+      <c r="L642" s="4">
         <v>46190</v>
       </c>
-      <c r="M642" t="s">
-        <v>67</v>
-      </c>
-      <c r="N642">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="643" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A643" t="s">
+      <c r="M642" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N642" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="643" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A643" s="3" t="s">
         <v>1821</v>
       </c>
-      <c r="B643" s="26">
+      <c r="B643" s="4">
         <v>46190</v>
       </c>
-      <c r="C643" t="s">
+      <c r="C643" s="5" t="s">
         <v>1822</v>
       </c>
-      <c r="D643" t="s">
-        <v>34</v>
-      </c>
-      <c r="E643" t="s">
+      <c r="D643" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E643" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F643">
+      <c r="F643" s="6">
         <v>1864</v>
       </c>
-      <c r="G643" t="s">
+      <c r="G643" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H643" t="s">
+      <c r="H643" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I643" t="s">
+      <c r="I643" s="5" t="s">
         <v>1823</v>
       </c>
-      <c r="K643" t="s">
+      <c r="J643" s="8"/>
+      <c r="K643" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L643" s="26">
+      <c r="L643" s="4">
         <v>46190</v>
       </c>
-      <c r="M643" t="s">
-        <v>67</v>
-      </c>
-      <c r="N643">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="644" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A644" t="s">
+      <c r="M643" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N643" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="644" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A644" s="3" t="s">
         <v>1824</v>
       </c>
-      <c r="B644" s="26">
+      <c r="B644" s="4">
         <v>46190</v>
       </c>
-      <c r="C644" t="s">
+      <c r="C644" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="D644" t="s">
-        <v>34</v>
-      </c>
-      <c r="E644" t="s">
+      <c r="D644" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E644" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F644">
+      <c r="F644" s="6">
         <v>11161</v>
       </c>
-      <c r="G644" t="s">
+      <c r="G644" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H644" t="s">
+      <c r="H644" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J644" t="s">
+      <c r="I644" s="8"/>
+      <c r="J644" s="11" t="s">
         <v>1825</v>
       </c>
-      <c r="M644" t="s">
+      <c r="K644" s="8"/>
+      <c r="L644" s="8"/>
+      <c r="M644" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N644">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="645" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A645" t="s">
+      <c r="N644" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="645" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A645" s="3" t="s">
         <v>1826</v>
       </c>
-      <c r="B645" s="26">
+      <c r="B645" s="4">
         <v>46190</v>
       </c>
-      <c r="C645" t="s">
+      <c r="C645" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="D645" t="s">
-        <v>34</v>
-      </c>
-      <c r="E645" t="s">
+      <c r="D645" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E645" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F645">
+      <c r="F645" s="6">
         <v>3046</v>
       </c>
-      <c r="G645" t="s">
+      <c r="G645" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H645" t="s">
+      <c r="H645" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I645" t="s">
+      <c r="I645" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="J645" t="s">
+      <c r="J645" s="11" t="s">
         <v>1828</v>
       </c>
-      <c r="K645" t="s">
+      <c r="K645" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L645" s="26">
+      <c r="L645" s="4">
         <v>46190</v>
       </c>
-      <c r="M645" t="s">
-        <v>67</v>
-      </c>
-      <c r="N645">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="646" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A646" t="s">
+      <c r="M645" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N645" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="646" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A646" s="3" t="s">
         <v>1829</v>
       </c>
-      <c r="B646" s="26">
+      <c r="B646" s="4">
         <v>46190</v>
       </c>
-      <c r="C646" t="s">
+      <c r="C646" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="D646" t="s">
-        <v>34</v>
-      </c>
-      <c r="E646" t="s">
+      <c r="D646" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E646" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F646">
+      <c r="F646" s="6">
         <v>3046</v>
       </c>
-      <c r="G646" t="s">
+      <c r="G646" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H646" t="s">
+      <c r="H646" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="I646" t="s">
+      <c r="I646" s="5" t="s">
         <v>1830</v>
       </c>
-      <c r="M646" t="s">
+      <c r="J646" s="8"/>
+      <c r="K646" s="8"/>
+      <c r="L646" s="8"/>
+      <c r="M646" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N646">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="647" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A647" t="s">
+      <c r="N646" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="647" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A647" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="B647" s="26">
+      <c r="B647" s="4">
         <v>46190</v>
       </c>
-      <c r="C647" t="s">
+      <c r="C647" s="5" t="s">
         <v>1311</v>
       </c>
-      <c r="D647" t="s">
-        <v>34</v>
-      </c>
-      <c r="E647" t="s">
+      <c r="D647" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E647" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F647">
+      <c r="F647" s="6">
         <v>1718</v>
       </c>
-      <c r="G647" t="s">
+      <c r="G647" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H647" t="s">
+      <c r="H647" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I647" t="s">
+      <c r="I647" s="5" t="s">
         <v>1832</v>
       </c>
-      <c r="K647" t="s">
+      <c r="J647" s="8"/>
+      <c r="K647" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L647" s="26">
+      <c r="L647" s="4">
         <v>46190</v>
       </c>
-      <c r="M647" t="s">
-        <v>67</v>
-      </c>
-      <c r="N647">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="648" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A648" t="s">
+      <c r="M647" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N647" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="648" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A648" s="3" t="s">
         <v>1833</v>
       </c>
-      <c r="B648" s="26">
+      <c r="B648" s="4">
         <v>46190</v>
       </c>
-      <c r="C648" t="s">
+      <c r="C648" s="5" t="s">
         <v>1834</v>
       </c>
-      <c r="D648" t="s">
-        <v>34</v>
-      </c>
-      <c r="E648" t="s">
+      <c r="D648" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E648" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F648">
+      <c r="F648" s="6">
         <v>6843</v>
       </c>
-      <c r="G648" t="s">
+      <c r="G648" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H648" t="s">
+      <c r="H648" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J648" t="s">
+      <c r="I648" s="8"/>
+      <c r="J648" s="11" t="s">
         <v>1835</v>
       </c>
-      <c r="M648" t="s">
+      <c r="K648" s="8"/>
+      <c r="L648" s="8"/>
+      <c r="M648" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N648">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="649" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A649" t="s">
+      <c r="N648" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="649" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A649" s="3" t="s">
         <v>1836</v>
       </c>
-      <c r="B649" s="26">
+      <c r="B649" s="4">
         <v>46190</v>
       </c>
-      <c r="C649" t="s">
+      <c r="C649" s="5" t="s">
         <v>1837</v>
       </c>
-      <c r="D649" t="s">
-        <v>34</v>
-      </c>
-      <c r="E649" t="s">
+      <c r="D649" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E649" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F649">
+      <c r="F649" s="6">
         <v>3871</v>
       </c>
-      <c r="G649" t="s">
+      <c r="G649" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="H649" t="s">
+      <c r="H649" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J649" t="s">
+      <c r="I649" s="8"/>
+      <c r="J649" s="11" t="s">
         <v>1838</v>
       </c>
-      <c r="K649" t="s">
+      <c r="K649" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L649" s="26">
+      <c r="L649" s="4">
         <v>46190</v>
       </c>
-      <c r="M649" t="s">
-        <v>67</v>
-      </c>
-      <c r="N649">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="650" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A650" t="s">
+      <c r="M649" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N649" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="650" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A650" s="3" t="s">
         <v>1839</v>
       </c>
-      <c r="B650" s="26">
+      <c r="B650" s="4">
         <v>46190</v>
       </c>
-      <c r="C650" t="s">
+      <c r="C650" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="D650" t="s">
-        <v>34</v>
-      </c>
-      <c r="E650" t="s">
+      <c r="D650" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E650" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F650">
+      <c r="F650" s="6">
         <v>6845</v>
       </c>
-      <c r="G650" t="s">
+      <c r="G650" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H650" t="s">
+      <c r="H650" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="M650" t="s">
+      <c r="I650" s="8"/>
+      <c r="J650" s="8"/>
+      <c r="K650" s="8"/>
+      <c r="L650" s="8"/>
+      <c r="M650" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N650">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="651" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A651" t="s">
+      <c r="N650" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="651" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A651" s="3" t="s">
         <v>1840</v>
       </c>
-      <c r="B651" s="26">
+      <c r="B651" s="4">
         <v>46190</v>
       </c>
-      <c r="C651" s="27">
+      <c r="C651" s="13">
         <v>0.56597222222222221</v>
       </c>
-      <c r="D651" t="s">
-        <v>34</v>
-      </c>
-      <c r="E651" t="s">
+      <c r="D651" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E651" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F651">
+      <c r="F651" s="6">
         <v>6516</v>
       </c>
-      <c r="G651" t="s">
+      <c r="G651" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H651" t="s">
+      <c r="H651" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="K651" t="s">
+      <c r="I651" s="8"/>
+      <c r="J651" s="8"/>
+      <c r="K651" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="L651" s="26">
+      <c r="L651" s="4">
         <v>46190</v>
       </c>
-      <c r="M651" t="s">
-        <v>67</v>
-      </c>
-      <c r="N651">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="652" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A652" t="s">
+      <c r="M651" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N651" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="652" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A652" s="3" t="s">
         <v>1841</v>
       </c>
-      <c r="B652" s="26">
+      <c r="B652" s="4">
         <v>46190</v>
       </c>
-      <c r="C652" t="s">
+      <c r="C652" s="5" t="s">
         <v>1842</v>
       </c>
-      <c r="D652" t="s">
-        <v>34</v>
-      </c>
-      <c r="E652" t="s">
+      <c r="D652" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E652" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F652">
+      <c r="F652" s="6">
         <v>5615</v>
       </c>
-      <c r="G652" t="s">
+      <c r="G652" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H652" t="s">
+      <c r="H652" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J652" t="s">
+      <c r="I652" s="8"/>
+      <c r="J652" s="11" t="s">
         <v>1843</v>
       </c>
-      <c r="K652" t="s">
+      <c r="K652" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L652" s="26">
+      <c r="L652" s="4">
         <v>46190</v>
       </c>
-      <c r="M652" t="s">
-        <v>67</v>
-      </c>
-      <c r="N652">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="653" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A653" t="s">
+      <c r="M652" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N652" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="653" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A653" s="3" t="s">
         <v>1844</v>
       </c>
-      <c r="B653" s="26">
+      <c r="B653" s="4">
         <v>46190</v>
       </c>
-      <c r="C653" s="27">
+      <c r="C653" s="13">
         <v>0.57916666666666672</v>
       </c>
-      <c r="D653" t="s">
-        <v>34</v>
-      </c>
-      <c r="E653" t="s">
+      <c r="D653" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E653" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F653">
+      <c r="F653" s="6">
         <v>5905</v>
       </c>
-      <c r="G653" t="s">
+      <c r="G653" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H653" t="s">
+      <c r="H653" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="K653" t="s">
+      <c r="I653" s="8"/>
+      <c r="J653" s="8"/>
+      <c r="K653" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="L653" s="26">
+      <c r="L653" s="4">
         <v>46190</v>
       </c>
-      <c r="M653" t="s">
-        <v>67</v>
-      </c>
-      <c r="N653">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="654" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A654" t="s">
+      <c r="M653" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N653" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="654" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A654" s="3" t="s">
         <v>1845</v>
       </c>
-      <c r="B654" s="26">
+      <c r="B654" s="4">
         <v>46190</v>
       </c>
-      <c r="C654" t="s">
+      <c r="C654" s="5" t="s">
         <v>790</v>
       </c>
-      <c r="D654" t="s">
-        <v>34</v>
-      </c>
-      <c r="E654" t="s">
+      <c r="D654" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E654" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F654">
+      <c r="F654" s="6">
         <v>2648</v>
       </c>
-      <c r="G654" t="s">
+      <c r="G654" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H654" t="s">
+      <c r="H654" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I654" t="s">
+      <c r="I654" s="5" t="s">
         <v>1846</v>
       </c>
-      <c r="J654" t="s">
+      <c r="J654" s="11" t="s">
         <v>1847</v>
       </c>
-      <c r="M654" t="s">
+      <c r="K654" s="8"/>
+      <c r="L654" s="8"/>
+      <c r="M654" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N654">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="655" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A655" t="s">
+      <c r="N654" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="655" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A655" s="3" t="s">
         <v>1848</v>
       </c>
-      <c r="B655" s="26">
+      <c r="B655" s="4">
         <v>46190</v>
       </c>
-      <c r="C655" t="s">
+      <c r="C655" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="D655" t="s">
-        <v>34</v>
-      </c>
-      <c r="E655" t="s">
+      <c r="D655" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E655" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F655">
+      <c r="F655" s="6">
         <v>7368</v>
       </c>
-      <c r="G655" t="s">
+      <c r="G655" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H655" t="s">
+      <c r="H655" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I655" t="s">
+      <c r="I655" s="5" t="s">
         <v>1849</v>
       </c>
-      <c r="K655" t="s">
+      <c r="J655" s="8"/>
+      <c r="K655" s="5" t="s">
         <v>1850</v>
       </c>
-      <c r="L655" s="26">
+      <c r="L655" s="4">
         <v>46190</v>
       </c>
-      <c r="M655" t="s">
-        <v>67</v>
-      </c>
-      <c r="N655">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="656" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A656" t="s">
+      <c r="M655" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N655" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="656" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A656" s="3" t="s">
         <v>1851</v>
       </c>
-      <c r="B656" s="26">
+      <c r="B656" s="4">
         <v>46190</v>
       </c>
-      <c r="C656" t="s">
+      <c r="C656" s="5" t="s">
         <v>659</v>
       </c>
-      <c r="D656" t="s">
-        <v>34</v>
-      </c>
-      <c r="E656" t="s">
+      <c r="D656" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E656" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F656">
+      <c r="F656" s="6">
         <v>6796</v>
       </c>
-      <c r="G656" t="s">
+      <c r="G656" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H656" t="s">
+      <c r="H656" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J656" t="s">
+      <c r="I656" s="8"/>
+      <c r="J656" s="11" t="s">
         <v>1852</v>
       </c>
-      <c r="M656" t="s">
+      <c r="K656" s="8"/>
+      <c r="L656" s="8"/>
+      <c r="M656" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N656">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="657" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A657" t="s">
+      <c r="N656" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="657" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A657" s="3" t="s">
         <v>1853</v>
       </c>
-      <c r="B657" s="26">
+      <c r="B657" s="4">
         <v>46190</v>
       </c>
-      <c r="C657" t="s">
+      <c r="C657" s="5" t="s">
         <v>1854</v>
       </c>
-      <c r="D657" t="s">
-        <v>34</v>
-      </c>
-      <c r="E657" t="s">
+      <c r="D657" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E657" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F657">
+      <c r="F657" s="6">
         <v>3620</v>
       </c>
-      <c r="G657" t="s">
+      <c r="G657" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H657" t="s">
+      <c r="H657" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J657" t="s">
+      <c r="I657" s="8"/>
+      <c r="J657" s="11" t="s">
         <v>1855</v>
       </c>
-      <c r="K657" t="s">
+      <c r="K657" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L657" s="26">
+      <c r="L657" s="4">
         <v>46190</v>
       </c>
-      <c r="M657" t="s">
-        <v>67</v>
-      </c>
-      <c r="N657">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="658" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A658" t="s">
+      <c r="M657" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N657" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="658" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A658" s="3" t="s">
         <v>1856</v>
       </c>
-      <c r="B658" s="26">
+      <c r="B658" s="4">
         <v>46190</v>
       </c>
-      <c r="C658" t="s">
+      <c r="C658" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D658" t="s">
-        <v>34</v>
-      </c>
-      <c r="E658" t="s">
+      <c r="D658" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E658" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F658">
+      <c r="F658" s="6">
         <v>2126</v>
       </c>
-      <c r="G658" t="s">
+      <c r="G658" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H658" t="s">
+      <c r="H658" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I658" t="s">
+      <c r="I658" s="5" t="s">
         <v>1857</v>
       </c>
-      <c r="K658" t="s">
+      <c r="J658" s="8"/>
+      <c r="K658" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L658" s="26">
+      <c r="L658" s="4">
         <v>46190</v>
       </c>
-      <c r="M658" t="s">
-        <v>67</v>
-      </c>
-      <c r="N658">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="659" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A659" t="s">
+      <c r="M658" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N658" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="659" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A659" s="3" t="s">
         <v>1858</v>
       </c>
-      <c r="B659" s="26">
+      <c r="B659" s="4">
         <v>46190</v>
       </c>
-      <c r="C659" s="27">
+      <c r="C659" s="13">
         <v>0.61597222222222225</v>
       </c>
-      <c r="D659" t="s">
-        <v>34</v>
-      </c>
-      <c r="E659" t="s">
+      <c r="D659" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E659" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F659">
+      <c r="F659" s="6">
         <v>6535</v>
       </c>
-      <c r="G659" t="s">
+      <c r="G659" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H659" t="s">
+      <c r="H659" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="M659" t="s">
+      <c r="I659" s="8"/>
+      <c r="J659" s="8"/>
+      <c r="K659" s="8"/>
+      <c r="L659" s="8"/>
+      <c r="M659" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N659">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="660" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A660" t="s">
+      <c r="N659" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="660" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A660" s="3" t="s">
         <v>1859</v>
       </c>
-      <c r="B660" s="26">
+      <c r="B660" s="4">
         <v>46190</v>
       </c>
-      <c r="C660" t="s">
+      <c r="C660" s="5" t="s">
         <v>1860</v>
       </c>
-      <c r="D660" t="s">
-        <v>34</v>
-      </c>
-      <c r="E660" t="s">
+      <c r="D660" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E660" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F660">
+      <c r="F660" s="6">
         <v>11086</v>
       </c>
-      <c r="G660" t="s">
+      <c r="G660" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H660" t="s">
+      <c r="H660" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I660" t="s">
+      <c r="I660" s="5" t="s">
         <v>1861</v>
       </c>
-      <c r="M660" t="s">
+      <c r="J660" s="8"/>
+      <c r="K660" s="8"/>
+      <c r="L660" s="8"/>
+      <c r="M660" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N660">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="661" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A661" t="s">
+      <c r="N660" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="661" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A661" s="3" t="s">
         <v>1862</v>
       </c>
-      <c r="B661" s="26">
+      <c r="B661" s="4">
         <v>46190</v>
       </c>
-      <c r="C661" t="s">
+      <c r="C661" s="5" t="s">
         <v>1863</v>
       </c>
-      <c r="D661" t="s">
-        <v>34</v>
-      </c>
-      <c r="E661" t="s">
+      <c r="D661" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E661" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F661">
+      <c r="F661" s="6">
         <v>3337</v>
       </c>
-      <c r="G661" t="s">
+      <c r="G661" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="H661" t="s">
+      <c r="H661" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="K661" t="s">
+      <c r="I661" s="8"/>
+      <c r="J661" s="8"/>
+      <c r="K661" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L661" s="26">
+      <c r="L661" s="4">
         <v>46190</v>
       </c>
-      <c r="M661" t="s">
-        <v>67</v>
-      </c>
-      <c r="N661">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="662" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A662" t="s">
+      <c r="M661" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N661" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="662" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A662" s="3" t="s">
         <v>1864</v>
       </c>
-      <c r="B662" s="26">
+      <c r="B662" s="4">
         <v>46190</v>
       </c>
-      <c r="C662" t="s">
+      <c r="C662" s="5" t="s">
         <v>1757</v>
       </c>
-      <c r="D662" t="s">
-        <v>34</v>
-      </c>
-      <c r="E662" t="s">
+      <c r="D662" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E662" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F662">
+      <c r="F662" s="6">
         <v>3311</v>
       </c>
-      <c r="G662" t="s">
+      <c r="G662" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="H662" t="s">
+      <c r="H662" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K662" t="s">
+      <c r="I662" s="8"/>
+      <c r="J662" s="8"/>
+      <c r="K662" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L662" s="26">
+      <c r="L662" s="4">
         <v>46190</v>
       </c>
-      <c r="M662" t="s">
-        <v>67</v>
-      </c>
-      <c r="N662">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="663" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A663" t="s">
+      <c r="M662" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N662" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="663" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A663" s="3" t="s">
         <v>1865</v>
       </c>
-      <c r="B663" s="26">
+      <c r="B663" s="4">
         <v>46190</v>
       </c>
-      <c r="C663" t="s">
+      <c r="C663" s="5" t="s">
         <v>1866</v>
       </c>
-      <c r="D663" t="s">
-        <v>34</v>
-      </c>
-      <c r="E663" t="s">
+      <c r="D663" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E663" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F663">
+      <c r="F663" s="6">
         <v>6827</v>
       </c>
-      <c r="G663" t="s">
+      <c r="G663" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H663" t="s">
+      <c r="H663" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I663" t="s">
+      <c r="I663" s="5" t="s">
         <v>881</v>
       </c>
-      <c r="J663" t="s">
+      <c r="J663" s="11" t="s">
         <v>1867</v>
       </c>
-      <c r="M663" t="s">
+      <c r="K663" s="8"/>
+      <c r="L663" s="8"/>
+      <c r="M663" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N663">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="664" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A664" t="s">
+      <c r="N663" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="664" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A664" s="3" t="s">
         <v>1868</v>
       </c>
-      <c r="B664" s="26">
+      <c r="B664" s="4">
         <v>46190</v>
       </c>
-      <c r="C664" t="s">
+      <c r="C664" s="5" t="s">
         <v>1866</v>
       </c>
-      <c r="D664" t="s">
-        <v>34</v>
-      </c>
-      <c r="E664" t="s">
+      <c r="D664" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E664" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F664">
+      <c r="F664" s="6">
         <v>3910</v>
       </c>
-      <c r="G664" t="s">
+      <c r="G664" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H664" t="s">
+      <c r="H664" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J664" t="s">
+      <c r="I664" s="8"/>
+      <c r="J664" s="11" t="s">
         <v>1869</v>
       </c>
-      <c r="M664" t="s">
+      <c r="K664" s="8"/>
+      <c r="L664" s="8"/>
+      <c r="M664" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N664">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="665" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A665" t="s">
+      <c r="N664" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="665" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A665" s="3" t="s">
         <v>1870</v>
       </c>
-      <c r="B665" s="26">
+      <c r="B665" s="4">
         <v>46190</v>
       </c>
-      <c r="C665" t="s">
+      <c r="C665" s="5" t="s">
         <v>1517</v>
       </c>
-      <c r="D665" t="s">
-        <v>34</v>
-      </c>
-      <c r="E665" t="s">
+      <c r="D665" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E665" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F665">
+      <c r="F665" s="6">
         <v>4865</v>
       </c>
-      <c r="G665" t="s">
+      <c r="G665" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="H665" t="s">
+      <c r="H665" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I665" t="s">
+      <c r="I665" s="5" t="s">
         <v>1871</v>
       </c>
-      <c r="J665" t="s">
+      <c r="J665" s="11" t="s">
         <v>1872</v>
       </c>
-      <c r="K665" t="s">
+      <c r="K665" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L665" s="26">
+      <c r="L665" s="4">
         <v>46190</v>
       </c>
-      <c r="M665" t="s">
-        <v>67</v>
-      </c>
-      <c r="N665">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="666" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A666" t="s">
+      <c r="M665" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N665" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="666" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A666" s="3" t="s">
         <v>1873</v>
       </c>
-      <c r="B666" s="26">
+      <c r="B666" s="4">
         <v>46190</v>
       </c>
-      <c r="C666" t="s">
+      <c r="C666" s="5" t="s">
         <v>1874</v>
       </c>
-      <c r="D666" t="s">
-        <v>34</v>
-      </c>
-      <c r="E666" t="s">
+      <c r="D666" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E666" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F666">
+      <c r="F666" s="6">
         <v>11291</v>
       </c>
-      <c r="G666" t="s">
+      <c r="G666" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="H666" t="s">
+      <c r="H666" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J666" t="s">
+      <c r="I666" s="8"/>
+      <c r="J666" s="11" t="s">
         <v>1875</v>
       </c>
-      <c r="K666" t="s">
+      <c r="K666" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L666" s="26">
+      <c r="L666" s="4">
         <v>46190</v>
       </c>
-      <c r="M666" t="s">
-        <v>67</v>
-      </c>
-      <c r="N666">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="667" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A667" t="s">
+      <c r="M666" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N666" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="667" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A667" s="3" t="s">
         <v>1876</v>
       </c>
-      <c r="B667" s="26">
+      <c r="B667" s="4">
         <v>46190</v>
       </c>
-      <c r="C667" t="s">
+      <c r="C667" s="5" t="s">
         <v>1877</v>
       </c>
-      <c r="D667" t="s">
-        <v>34</v>
-      </c>
-      <c r="E667" t="s">
+      <c r="D667" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E667" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F667">
+      <c r="F667" s="6">
         <v>7597</v>
       </c>
-      <c r="G667" t="s">
+      <c r="G667" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H667" t="s">
+      <c r="H667" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I667" t="s">
+      <c r="I667" s="5" t="s">
         <v>1878</v>
       </c>
-      <c r="J667" t="s">
+      <c r="J667" s="11" t="s">
         <v>1879</v>
       </c>
-      <c r="M667" t="s">
+      <c r="K667" s="8"/>
+      <c r="L667" s="8"/>
+      <c r="M667" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N667">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="668" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A668" t="s">
+      <c r="N667" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="668" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A668" s="3" t="s">
         <v>1880</v>
       </c>
-      <c r="B668" s="26">
+      <c r="B668" s="4">
         <v>46190</v>
       </c>
-      <c r="C668" t="s">
+      <c r="C668" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="D668" t="s">
-        <v>34</v>
-      </c>
-      <c r="E668" t="s">
+      <c r="D668" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E668" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F668">
+      <c r="F668" s="6">
         <v>4515</v>
       </c>
-      <c r="G668" t="s">
+      <c r="G668" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H668" t="s">
+      <c r="H668" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I668" t="s">
+      <c r="I668" s="5" t="s">
         <v>1881</v>
       </c>
-      <c r="J668" t="s">
+      <c r="J668" s="11" t="s">
         <v>1882</v>
       </c>
-      <c r="K668" t="s">
+      <c r="K668" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="L668" s="26">
+      <c r="L668" s="4">
         <v>46190</v>
       </c>
-      <c r="M668" t="s">
-        <v>67</v>
-      </c>
-      <c r="N668">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="669" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A669" t="s">
+      <c r="M668" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N668" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="669" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A669" s="3" t="s">
         <v>1883</v>
       </c>
-      <c r="B669" s="26">
+      <c r="B669" s="4">
         <v>46190</v>
       </c>
-      <c r="C669" t="s">
+      <c r="C669" s="5" t="s">
         <v>1519</v>
       </c>
-      <c r="D669" t="s">
-        <v>34</v>
-      </c>
-      <c r="E669" t="s">
+      <c r="D669" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E669" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F669">
+      <c r="F669" s="6">
         <v>4512</v>
       </c>
-      <c r="G669" t="s">
+      <c r="G669" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="H669" t="s">
+      <c r="H669" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I669" t="s">
+      <c r="I669" s="5" t="s">
         <v>1884</v>
       </c>
-      <c r="J669" t="s">
+      <c r="J669" s="11" t="s">
         <v>1885</v>
       </c>
-      <c r="K669" t="s">
+      <c r="K669" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L669" s="26">
+      <c r="L669" s="4">
         <v>46190</v>
       </c>
-      <c r="M669" t="s">
-        <v>67</v>
-      </c>
-      <c r="N669">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="670" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A670" t="s">
+      <c r="M669" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N669" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="670" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A670" s="3" t="s">
         <v>1886</v>
       </c>
-      <c r="B670" s="26">
+      <c r="B670" s="4">
         <v>46190</v>
       </c>
-      <c r="C670" t="s">
+      <c r="C670" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="D670" t="s">
-        <v>34</v>
-      </c>
-      <c r="E670" t="s">
+      <c r="D670" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E670" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F670">
+      <c r="F670" s="6">
         <v>4158</v>
       </c>
-      <c r="G670" t="s">
+      <c r="G670" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="H670" t="s">
+      <c r="H670" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I670" t="s">
+      <c r="I670" s="5" t="s">
         <v>1887</v>
       </c>
-      <c r="J670" t="s">
+      <c r="J670" s="11" t="s">
         <v>1888</v>
       </c>
-      <c r="M670" t="s">
+      <c r="K670" s="8"/>
+      <c r="L670" s="8"/>
+      <c r="M670" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N670">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="671" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A671" t="s">
+      <c r="N670" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="671" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A671" s="3" t="s">
         <v>1889</v>
       </c>
-      <c r="B671" s="26">
+      <c r="B671" s="4">
         <v>46190</v>
       </c>
-      <c r="C671" t="s">
+      <c r="C671" s="5" t="s">
         <v>1523</v>
       </c>
-      <c r="D671" t="s">
-        <v>34</v>
-      </c>
-      <c r="E671" t="s">
+      <c r="D671" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E671" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F671">
+      <c r="F671" s="6">
         <v>5028</v>
       </c>
-      <c r="G671" t="s">
+      <c r="G671" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="H671" t="s">
+      <c r="H671" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I671" t="s">
+      <c r="I671" s="5" t="s">
         <v>1890</v>
       </c>
-      <c r="J671" t="s">
+      <c r="J671" s="11" t="s">
         <v>1891</v>
       </c>
-      <c r="K671" t="s">
+      <c r="K671" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L671" s="26">
+      <c r="L671" s="4">
         <v>46190</v>
       </c>
-      <c r="M671" t="s">
-        <v>67</v>
-      </c>
-      <c r="N671">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="672" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A672" t="s">
+      <c r="M671" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N671" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="672" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A672" s="3" t="s">
         <v>1892</v>
       </c>
-      <c r="B672" s="26">
+      <c r="B672" s="4">
         <v>46190</v>
       </c>
-      <c r="C672" t="s">
+      <c r="C672" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="D672" t="s">
-        <v>34</v>
-      </c>
-      <c r="E672" t="s">
+      <c r="D672" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E672" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F672">
+      <c r="F672" s="6">
         <v>5638</v>
       </c>
-      <c r="G672" t="s">
+      <c r="G672" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H672" t="s">
+      <c r="H672" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J672" t="s">
+      <c r="I672" s="8"/>
+      <c r="J672" s="11" t="s">
         <v>1893</v>
       </c>
-      <c r="M672" t="s">
+      <c r="K672" s="8"/>
+      <c r="L672" s="8"/>
+      <c r="M672" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N672">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="673" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A673" t="s">
+      <c r="N672" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="673" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A673" s="3" t="s">
         <v>1894</v>
       </c>
-      <c r="B673" s="26">
+      <c r="B673" s="4">
         <v>46190</v>
       </c>
-      <c r="C673" t="s">
+      <c r="C673" s="5" t="s">
         <v>1528</v>
       </c>
-      <c r="D673" t="s">
-        <v>34</v>
-      </c>
-      <c r="E673" t="s">
+      <c r="D673" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E673" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F673">
+      <c r="F673" s="6">
         <v>6498</v>
       </c>
-      <c r="G673" t="s">
+      <c r="G673" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H673" t="s">
+      <c r="H673" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J673" t="s">
+      <c r="I673" s="8"/>
+      <c r="J673" s="11" t="s">
         <v>1895</v>
       </c>
-      <c r="M673" t="s">
+      <c r="K673" s="8"/>
+      <c r="L673" s="8"/>
+      <c r="M673" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N673">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="674" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A674" t="s">
+      <c r="N673" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="674" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A674" s="3" t="s">
         <v>1896</v>
       </c>
-      <c r="B674" s="26">
+      <c r="B674" s="4">
         <v>46190</v>
       </c>
-      <c r="C674" t="s">
+      <c r="C674" s="5" t="s">
         <v>1897</v>
       </c>
-      <c r="D674" t="s">
-        <v>34</v>
-      </c>
-      <c r="E674" t="s">
+      <c r="D674" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E674" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F674">
+      <c r="F674" s="6">
         <v>3611</v>
       </c>
-      <c r="G674" t="s">
+      <c r="G674" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H674" t="s">
+      <c r="H674" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J674" t="s">
+      <c r="I674" s="8"/>
+      <c r="J674" s="11" t="s">
         <v>1898</v>
       </c>
-      <c r="K674" t="s">
+      <c r="K674" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L674" s="26">
+      <c r="L674" s="4">
         <v>46190</v>
       </c>
-      <c r="M674" t="s">
-        <v>67</v>
-      </c>
-      <c r="N674">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="675" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A675" t="s">
+      <c r="M674" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N674" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="675" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A675" s="3" t="s">
         <v>1899</v>
       </c>
-      <c r="B675" s="26">
+      <c r="B675" s="4">
         <v>46190</v>
       </c>
-      <c r="C675" t="s">
+      <c r="C675" s="5" t="s">
         <v>686</v>
       </c>
-      <c r="D675" t="s">
-        <v>34</v>
-      </c>
-      <c r="E675" t="s">
+      <c r="D675" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E675" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F675">
+      <c r="F675" s="6">
         <v>4775</v>
       </c>
-      <c r="G675" t="s">
+      <c r="G675" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H675" t="s">
+      <c r="H675" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J675" t="s">
+      <c r="I675" s="8"/>
+      <c r="J675" s="11" t="s">
         <v>1900</v>
       </c>
-      <c r="M675" t="s">
+      <c r="K675" s="8"/>
+      <c r="L675" s="8"/>
+      <c r="M675" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N675">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="676" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A676" t="s">
+      <c r="N675" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="676" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A676" s="3" t="s">
         <v>1901</v>
       </c>
-      <c r="B676" s="26">
+      <c r="B676" s="4">
         <v>46190</v>
       </c>
-      <c r="C676" t="s">
+      <c r="C676" s="5" t="s">
         <v>1902</v>
       </c>
-      <c r="D676" t="s">
-        <v>34</v>
-      </c>
-      <c r="E676" t="s">
+      <c r="D676" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E676" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F676">
+      <c r="F676" s="6">
         <v>4191</v>
       </c>
-      <c r="G676" t="s">
+      <c r="G676" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H676" t="s">
+      <c r="H676" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J676" t="s">
+      <c r="I676" s="8"/>
+      <c r="J676" s="11" t="s">
         <v>1903</v>
       </c>
-      <c r="K676" t="s">
+      <c r="K676" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L676" s="26">
+      <c r="L676" s="4">
         <v>46190</v>
       </c>
-      <c r="M676" t="s">
-        <v>67</v>
-      </c>
-      <c r="N676">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="677" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A677" t="s">
+      <c r="M676" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N676" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="677" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A677" s="3" t="s">
         <v>1904</v>
       </c>
-      <c r="B677" s="26">
+      <c r="B677" s="4">
         <v>46190</v>
       </c>
-      <c r="C677" t="s">
+      <c r="C677" s="5" t="s">
         <v>1905</v>
       </c>
-      <c r="D677" t="s">
-        <v>34</v>
-      </c>
-      <c r="E677" t="s">
+      <c r="D677" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E677" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F677">
+      <c r="F677" s="6">
         <v>4216</v>
       </c>
-      <c r="G677" t="s">
+      <c r="G677" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H677" t="s">
+      <c r="H677" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J677" t="s">
+      <c r="I677" s="8"/>
+      <c r="J677" s="11" t="s">
         <v>1906</v>
       </c>
-      <c r="K677" t="s">
+      <c r="K677" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L677" s="26">
+      <c r="L677" s="4">
         <v>46190</v>
       </c>
-      <c r="M677" t="s">
-        <v>67</v>
-      </c>
-      <c r="N677">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="678" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A678" t="s">
+      <c r="M677" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N677" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="678" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A678" s="3" t="s">
         <v>1907</v>
       </c>
-      <c r="B678" s="26">
+      <c r="B678" s="4">
         <v>46190</v>
       </c>
-      <c r="C678" t="s">
+      <c r="C678" s="5" t="s">
         <v>1908</v>
       </c>
-      <c r="D678" t="s">
-        <v>34</v>
-      </c>
-      <c r="E678" t="s">
+      <c r="D678" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E678" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="F678">
+      <c r="F678" s="6">
         <v>799</v>
       </c>
-      <c r="G678" t="s">
+      <c r="G678" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="H678" t="s">
+      <c r="H678" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M678" t="s">
+      <c r="I678" s="8"/>
+      <c r="J678" s="8"/>
+      <c r="K678" s="8"/>
+      <c r="L678" s="8"/>
+      <c r="M678" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N678">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="679" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A679" t="s">
+      <c r="N678" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="679" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A679" s="3" t="s">
         <v>1909</v>
       </c>
-      <c r="B679" s="26">
+      <c r="B679" s="4">
         <v>46190</v>
       </c>
-      <c r="C679" t="s">
+      <c r="C679" s="5" t="s">
         <v>1908</v>
       </c>
-      <c r="D679" t="s">
-        <v>34</v>
-      </c>
-      <c r="E679" t="s">
+      <c r="D679" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E679" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F679">
+      <c r="F679" s="6">
         <v>5390</v>
       </c>
-      <c r="G679" t="s">
+      <c r="G679" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H679" t="s">
+      <c r="H679" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I679" t="s">
+      <c r="I679" s="5" t="s">
         <v>1910</v>
       </c>
-      <c r="J679" t="s">
+      <c r="J679" s="11" t="s">
         <v>1911</v>
       </c>
-      <c r="M679" t="s">
+      <c r="K679" s="8"/>
+      <c r="L679" s="8"/>
+      <c r="M679" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N679">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="680" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A680" t="s">
+      <c r="N679" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="680" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A680" s="3" t="s">
         <v>1912</v>
       </c>
-      <c r="B680" s="26">
+      <c r="B680" s="4">
         <v>46190</v>
       </c>
-      <c r="C680" t="s">
+      <c r="C680" s="5" t="s">
         <v>1547</v>
       </c>
-      <c r="D680" t="s">
-        <v>34</v>
-      </c>
-      <c r="E680" t="s">
+      <c r="D680" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E680" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="F680">
+      <c r="F680" s="6">
         <v>1496</v>
       </c>
-      <c r="G680" t="s">
+      <c r="G680" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="H680" t="s">
+      <c r="H680" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I680" t="s">
+      <c r="I680" s="5" t="s">
         <v>1913</v>
       </c>
-      <c r="M680" t="s">
+      <c r="J680" s="8"/>
+      <c r="K680" s="8"/>
+      <c r="L680" s="8"/>
+      <c r="M680" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N680">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="681" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A681" t="s">
+      <c r="N680" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="681" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A681" s="3" t="s">
         <v>1914</v>
       </c>
-      <c r="B681" s="26">
+      <c r="B681" s="4">
         <v>46190</v>
       </c>
-      <c r="C681" t="s">
+      <c r="C681" s="5" t="s">
         <v>1915</v>
       </c>
-      <c r="D681" t="s">
-        <v>34</v>
-      </c>
-      <c r="E681" t="s">
+      <c r="D681" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E681" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="F681">
+      <c r="F681" s="6">
         <v>695</v>
       </c>
-      <c r="G681" t="s">
+      <c r="G681" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="H681" t="s">
+      <c r="H681" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I681" t="s">
+      <c r="I681" s="5" t="s">
         <v>1913</v>
       </c>
-      <c r="M681" t="s">
+      <c r="J681" s="8"/>
+      <c r="K681" s="8"/>
+      <c r="L681" s="8"/>
+      <c r="M681" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N681">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="682" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A682" t="s">
+      <c r="N681" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="682" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A682" s="3" t="s">
         <v>1916</v>
       </c>
-      <c r="B682" s="26">
+      <c r="B682" s="4">
         <v>46190</v>
       </c>
-      <c r="C682" t="s">
+      <c r="C682" s="5" t="s">
         <v>1917</v>
       </c>
-      <c r="D682" t="s">
-        <v>34</v>
-      </c>
-      <c r="E682" t="s">
+      <c r="D682" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E682" s="5" t="s">
         <v>1353</v>
       </c>
-      <c r="F682">
+      <c r="F682" s="6">
         <v>1488</v>
       </c>
-      <c r="G682" t="s">
+      <c r="G682" s="5" t="s">
         <v>1354</v>
       </c>
-      <c r="H682" t="s">
+      <c r="H682" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J682" t="s">
+      <c r="I682" s="8"/>
+      <c r="J682" s="11" t="s">
         <v>1918</v>
       </c>
-      <c r="K682" t="s">
+      <c r="K682" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L682" s="26">
+      <c r="L682" s="4">
         <v>46190</v>
       </c>
-      <c r="M682" t="s">
-        <v>67</v>
-      </c>
-      <c r="N682">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="683" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A683" t="s">
+      <c r="M682" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N682" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="683" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A683" s="3" t="s">
         <v>1919</v>
       </c>
-      <c r="B683" s="26">
+      <c r="B683" s="4">
         <v>46190</v>
       </c>
-      <c r="C683" t="s">
+      <c r="C683" s="5" t="s">
         <v>1920</v>
       </c>
-      <c r="D683" t="s">
-        <v>34</v>
-      </c>
-      <c r="E683" t="s">
+      <c r="D683" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E683" s="5" t="s">
         <v>1353</v>
       </c>
-      <c r="F683">
+      <c r="F683" s="6">
         <v>2213</v>
       </c>
-      <c r="G683" t="s">
+      <c r="G683" s="5" t="s">
         <v>1354</v>
       </c>
-      <c r="H683" t="s">
+      <c r="H683" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I683" t="s">
+      <c r="I683" s="5" t="s">
         <v>1921</v>
       </c>
-      <c r="J683" t="s">
+      <c r="J683" s="11" t="s">
         <v>1922</v>
       </c>
-      <c r="K683" t="s">
+      <c r="K683" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="L683" s="26">
+      <c r="L683" s="4">
         <v>46190</v>
       </c>
-      <c r="M683" t="s">
-        <v>67</v>
-      </c>
-      <c r="N683">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="684" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A684" t="s">
+      <c r="M683" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N683" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="684" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A684" s="3" t="s">
         <v>1923</v>
       </c>
-      <c r="B684" s="26">
+      <c r="B684" s="4">
         <v>46190</v>
       </c>
-      <c r="C684" t="s">
+      <c r="C684" s="5" t="s">
         <v>1924</v>
       </c>
-      <c r="D684" t="s">
-        <v>34</v>
-      </c>
-      <c r="E684" t="s">
+      <c r="D684" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E684" s="5" t="s">
         <v>1353</v>
       </c>
-      <c r="F684">
+      <c r="F684" s="6">
         <v>1408</v>
       </c>
-      <c r="G684" t="s">
+      <c r="G684" s="5" t="s">
         <v>1354</v>
       </c>
-      <c r="H684" t="s">
+      <c r="H684" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J684" t="s">
+      <c r="I684" s="8"/>
+      <c r="J684" s="11" t="s">
         <v>1925</v>
       </c>
-      <c r="K684" t="s">
+      <c r="K684" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L684" s="26">
+      <c r="L684" s="4">
         <v>46190</v>
       </c>
-      <c r="M684" t="s">
-        <v>67</v>
-      </c>
-      <c r="N684">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="685" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A685" t="s">
+      <c r="M684" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N684" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="685" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A685" s="3" t="s">
         <v>1926</v>
       </c>
-      <c r="B685" s="26">
+      <c r="B685" s="4">
         <v>46190</v>
       </c>
-      <c r="C685" t="s">
+      <c r="C685" s="5" t="s">
         <v>1927</v>
       </c>
-      <c r="D685" t="s">
-        <v>34</v>
-      </c>
-      <c r="E685" t="s">
+      <c r="D685" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E685" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F685">
+      <c r="F685" s="6">
         <v>6216</v>
       </c>
-      <c r="G685" t="s">
+      <c r="G685" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H685" t="s">
+      <c r="H685" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I685" t="s">
+      <c r="I685" s="5" t="s">
         <v>1928</v>
       </c>
-      <c r="M685" t="s">
+      <c r="J685" s="8"/>
+      <c r="K685" s="8"/>
+      <c r="L685" s="8"/>
+      <c r="M685" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N685">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="686" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A686" t="s">
+      <c r="N685" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="686" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A686" s="3" t="s">
         <v>1929</v>
       </c>
-      <c r="B686" s="26">
+      <c r="B686" s="4">
         <v>46190</v>
       </c>
-      <c r="C686" t="s">
+      <c r="C686" s="5" t="s">
         <v>1930</v>
       </c>
-      <c r="D686" t="s">
-        <v>34</v>
-      </c>
-      <c r="E686" t="s">
+      <c r="D686" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E686" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F686">
+      <c r="F686" s="6">
         <v>4252</v>
       </c>
-      <c r="G686" t="s">
+      <c r="G686" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H686" t="s">
+      <c r="H686" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I686" t="s">
+      <c r="I686" s="5" t="s">
         <v>1931</v>
       </c>
-      <c r="K686" t="s">
+      <c r="J686" s="8"/>
+      <c r="K686" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L686" s="26">
+      <c r="L686" s="4">
         <v>46191</v>
       </c>
-      <c r="M686" t="s">
-        <v>67</v>
-      </c>
-      <c r="N686">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="687" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A687" t="s">
+      <c r="M686" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N686" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="687" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A687" s="3" t="s">
         <v>1932</v>
       </c>
-      <c r="B687" s="26">
+      <c r="B687" s="4">
         <v>46191</v>
       </c>
-      <c r="C687" t="s">
+      <c r="C687" s="5" t="s">
         <v>1933</v>
       </c>
-      <c r="D687" t="s">
-        <v>34</v>
-      </c>
-      <c r="E687" t="s">
+      <c r="D687" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E687" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F687">
+      <c r="F687" s="6">
         <v>3985</v>
       </c>
-      <c r="G687" t="s">
+      <c r="G687" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H687" t="s">
+      <c r="H687" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I687" t="s">
+      <c r="I687" s="5" t="s">
         <v>1934</v>
       </c>
-      <c r="K687" t="s">
+      <c r="J687" s="8"/>
+      <c r="K687" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="L687" s="26">
+      <c r="L687" s="4">
         <v>46191</v>
       </c>
-      <c r="M687" t="s">
-        <v>67</v>
-      </c>
-      <c r="N687">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="688" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A688" t="s">
+      <c r="M687" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N687" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="688" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A688" s="3" t="s">
         <v>1935</v>
       </c>
-      <c r="B688" s="26">
+      <c r="B688" s="4">
         <v>46191</v>
       </c>
-      <c r="C688" t="s">
+      <c r="C688" s="5" t="s">
         <v>972</v>
       </c>
-      <c r="D688" t="s">
-        <v>34</v>
-      </c>
-      <c r="E688" t="s">
+      <c r="D688" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E688" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F688">
+      <c r="F688" s="6">
         <v>4822</v>
       </c>
-      <c r="G688" t="s">
+      <c r="G688" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H688" t="s">
+      <c r="H688" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J688" t="s">
+      <c r="I688" s="8"/>
+      <c r="J688" s="11" t="s">
         <v>1936</v>
       </c>
-      <c r="K688" t="s">
+      <c r="K688" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="L688" s="26">
+      <c r="L688" s="4">
         <v>46191</v>
       </c>
-      <c r="M688" t="s">
-        <v>67</v>
-      </c>
-      <c r="N688">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="689" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A689" t="s">
+      <c r="M688" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N688" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="689" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A689" s="3" t="s">
         <v>1937</v>
       </c>
-      <c r="B689" s="26">
+      <c r="B689" s="4">
         <v>46191</v>
       </c>
-      <c r="C689" s="27">
+      <c r="C689" s="13">
         <v>0.38680555555555557</v>
       </c>
-      <c r="D689" t="s">
-        <v>34</v>
-      </c>
-      <c r="E689" t="s">
+      <c r="D689" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E689" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F689">
+      <c r="F689" s="6">
         <v>5455</v>
       </c>
-      <c r="G689" t="s">
+      <c r="G689" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H689" t="s">
+      <c r="H689" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="K689" t="s">
+      <c r="I689" s="8"/>
+      <c r="J689" s="8"/>
+      <c r="K689" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="L689" s="26">
+      <c r="L689" s="4">
         <v>46191</v>
       </c>
-      <c r="M689" t="s">
-        <v>67</v>
-      </c>
-      <c r="N689">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="690" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A690" t="s">
+      <c r="M689" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N689" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="690" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A690" s="3" t="s">
         <v>1938</v>
       </c>
-      <c r="B690" s="26">
+      <c r="B690" s="4">
         <v>46191</v>
       </c>
-      <c r="C690" s="27">
+      <c r="C690" s="13">
         <v>0.39166666666666666</v>
       </c>
-      <c r="D690" t="s">
-        <v>34</v>
-      </c>
-      <c r="E690" t="s">
+      <c r="D690" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E690" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F690">
+      <c r="F690" s="6">
         <v>5455</v>
       </c>
-      <c r="G690" t="s">
+      <c r="G690" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H690" t="s">
+      <c r="H690" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="M690" t="s">
+      <c r="I690" s="8"/>
+      <c r="J690" s="8"/>
+      <c r="K690" s="8"/>
+      <c r="L690" s="8"/>
+      <c r="M690" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N690">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="691" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A691" t="s">
+      <c r="N690" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="691" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A691" s="3" t="s">
         <v>1939</v>
       </c>
-      <c r="B691" s="26">
+      <c r="B691" s="4">
         <v>46191</v>
       </c>
-      <c r="C691" t="s">
+      <c r="C691" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="D691" t="s">
-        <v>34</v>
-      </c>
-      <c r="E691" t="s">
+      <c r="D691" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E691" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F691">
+      <c r="F691" s="6">
         <v>5132</v>
       </c>
-      <c r="G691" t="s">
+      <c r="G691" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="H691" t="s">
+      <c r="H691" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I691" t="s">
+      <c r="I691" s="5" t="s">
         <v>1940</v>
       </c>
-      <c r="K691" t="s">
+      <c r="J691" s="8"/>
+      <c r="K691" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L691" s="26">
+      <c r="L691" s="4">
         <v>46191</v>
       </c>
-      <c r="M691" t="s">
-        <v>67</v>
-      </c>
-      <c r="N691">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="692" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A692" t="s">
+      <c r="M691" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N691" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="692" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A692" s="3" t="s">
         <v>1941</v>
       </c>
-      <c r="B692" s="26">
+      <c r="B692" s="4">
         <v>46191</v>
       </c>
-      <c r="C692" t="s">
+      <c r="C692" s="5" t="s">
         <v>1673</v>
       </c>
-      <c r="D692" t="s">
-        <v>34</v>
-      </c>
-      <c r="E692" t="s">
+      <c r="D692" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E692" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F692">
+      <c r="F692" s="6">
         <v>4564</v>
       </c>
-      <c r="G692" t="s">
+      <c r="G692" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H692" t="s">
+      <c r="H692" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="I692" t="s">
+      <c r="I692" s="5" t="s">
         <v>1942</v>
       </c>
-      <c r="K692" t="s">
+      <c r="J692" s="8"/>
+      <c r="K692" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="L692" s="26">
+      <c r="L692" s="4">
         <v>46191</v>
       </c>
-      <c r="M692" t="s">
-        <v>67</v>
-      </c>
-      <c r="N692">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="693" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A693" t="s">
+      <c r="M692" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N692" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="693" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A693" s="3" t="s">
         <v>1943</v>
       </c>
-      <c r="B693" s="26">
+      <c r="B693" s="4">
         <v>46191</v>
       </c>
-      <c r="C693" t="s">
+      <c r="C693" s="5" t="s">
         <v>716</v>
       </c>
-      <c r="D693" t="s">
-        <v>34</v>
-      </c>
-      <c r="E693" t="s">
+      <c r="D693" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E693" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F693">
+      <c r="F693" s="6">
         <v>6056</v>
       </c>
-      <c r="G693" t="s">
+      <c r="G693" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H693" t="s">
+      <c r="H693" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J693" t="s">
+      <c r="I693" s="8"/>
+      <c r="J693" s="11" t="s">
         <v>1944</v>
       </c>
-      <c r="M693" t="s">
+      <c r="K693" s="8"/>
+      <c r="L693" s="8"/>
+      <c r="M693" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N693">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="694" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A694" t="s">
+      <c r="N693" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="694" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A694" s="3" t="s">
         <v>1945</v>
       </c>
-      <c r="B694" s="26">
+      <c r="B694" s="4">
         <v>46191</v>
       </c>
-      <c r="C694" t="s">
+      <c r="C694" s="5" t="s">
         <v>991</v>
       </c>
-      <c r="D694" t="s">
-        <v>34</v>
-      </c>
-      <c r="E694" t="s">
+      <c r="D694" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E694" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F694">
+      <c r="F694" s="6">
         <v>6056</v>
       </c>
-      <c r="G694" t="s">
+      <c r="G694" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H694" t="s">
+      <c r="H694" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J694" t="s">
+      <c r="I694" s="8"/>
+      <c r="J694" s="11" t="s">
         <v>1946</v>
       </c>
-      <c r="K694" t="s">
+      <c r="K694" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L694" s="26">
+      <c r="L694" s="4">
         <v>46191</v>
       </c>
-      <c r="M694" t="s">
-        <v>67</v>
-      </c>
-      <c r="N694">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="695" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A695" t="s">
+      <c r="M694" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N694" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="695" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A695" s="3" t="s">
         <v>1947</v>
       </c>
-      <c r="B695" s="26">
+      <c r="B695" s="4">
         <v>46191</v>
       </c>
-      <c r="C695" t="s">
+      <c r="C695" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="D695" t="s">
-        <v>34</v>
-      </c>
-      <c r="E695" t="s">
+      <c r="D695" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E695" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="F695">
+      <c r="F695" s="6">
         <v>2108</v>
       </c>
-      <c r="G695" t="s">
+      <c r="G695" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="H695" t="s">
+      <c r="H695" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J695" t="s">
+      <c r="I695" s="8"/>
+      <c r="J695" s="11" t="s">
         <v>1948</v>
       </c>
-      <c r="M695" t="s">
+      <c r="K695" s="8"/>
+      <c r="L695" s="8"/>
+      <c r="M695" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N695">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="696" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A696" t="s">
+      <c r="N695" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="696" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A696" s="3" t="s">
         <v>1949</v>
       </c>
-      <c r="B696" s="26">
+      <c r="B696" s="4">
         <v>46191</v>
       </c>
-      <c r="C696" t="s">
+      <c r="C696" s="5" t="s">
         <v>1950</v>
       </c>
-      <c r="D696" t="s">
-        <v>34</v>
-      </c>
-      <c r="E696" t="s">
+      <c r="D696" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E696" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F696">
+      <c r="F696" s="6">
         <v>5137</v>
       </c>
-      <c r="G696" t="s">
+      <c r="G696" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="H696" t="s">
+      <c r="H696" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="I696" t="s">
+      <c r="I696" s="5" t="s">
         <v>1951</v>
       </c>
-      <c r="J696" t="s">
+      <c r="J696" s="11" t="s">
         <v>1952</v>
       </c>
-      <c r="K696" t="s">
+      <c r="K696" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L696" s="26">
+      <c r="L696" s="4">
         <v>46191</v>
       </c>
-      <c r="M696" t="s">
-        <v>67</v>
-      </c>
-      <c r="N696">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="697" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A697" t="s">
+      <c r="M696" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N696" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="697" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A697" s="3" t="s">
         <v>1953</v>
       </c>
-      <c r="B697" s="26">
+      <c r="B697" s="4">
         <v>46191</v>
       </c>
-      <c r="C697" t="s">
+      <c r="C697" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D697" t="s">
-        <v>34</v>
-      </c>
-      <c r="E697" t="s">
+      <c r="D697" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E697" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="F697">
+      <c r="F697" s="6">
         <v>1429</v>
       </c>
-      <c r="G697" t="s">
+      <c r="G697" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="H697" t="s">
+      <c r="H697" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J697" t="s">
+      <c r="I697" s="8"/>
+      <c r="J697" s="11" t="s">
         <v>1954</v>
       </c>
-      <c r="M697" t="s">
+      <c r="K697" s="8"/>
+      <c r="L697" s="8"/>
+      <c r="M697" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N697">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="698" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A698" t="s">
+      <c r="N697" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="698" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A698" s="3" t="s">
         <v>1955</v>
       </c>
-      <c r="B698" s="26">
+      <c r="B698" s="4">
         <v>46191</v>
       </c>
-      <c r="C698" t="s">
+      <c r="C698" s="5" t="s">
         <v>1956</v>
       </c>
-      <c r="D698" t="s">
-        <v>34</v>
-      </c>
-      <c r="E698" t="s">
+      <c r="D698" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E698" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F698">
+      <c r="F698" s="6">
         <v>6883</v>
       </c>
-      <c r="G698" t="s">
+      <c r="G698" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H698" t="s">
+      <c r="H698" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J698" t="s">
+      <c r="I698" s="8"/>
+      <c r="J698" s="11" t="s">
         <v>1957</v>
       </c>
-      <c r="K698" t="s">
+      <c r="K698" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="L698" s="26">
+      <c r="L698" s="4">
         <v>46191</v>
       </c>
-      <c r="M698" t="s">
-        <v>67</v>
-      </c>
-      <c r="N698">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="699" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A699" t="s">
+      <c r="M698" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N698" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="699" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A699" s="3" t="s">
         <v>1958</v>
       </c>
-      <c r="B699" s="26">
+      <c r="B699" s="4">
         <v>46191</v>
       </c>
-      <c r="C699" t="s">
+      <c r="C699" s="5" t="s">
         <v>815</v>
       </c>
-      <c r="D699" t="s">
-        <v>34</v>
-      </c>
-      <c r="E699" t="s">
+      <c r="D699" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E699" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F699">
+      <c r="F699" s="6">
         <v>6156</v>
       </c>
-      <c r="G699" t="s">
+      <c r="G699" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H699" t="s">
+      <c r="H699" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="J699" t="s">
+      <c r="I699" s="8"/>
+      <c r="J699" s="11" t="s">
         <v>1959</v>
       </c>
-      <c r="K699" t="s">
+      <c r="K699" s="5" t="s">
         <v>1960</v>
       </c>
-      <c r="L699" s="26">
+      <c r="L699" s="4">
         <v>46191</v>
       </c>
-      <c r="M699" t="s">
-        <v>67</v>
-      </c>
-      <c r="N699">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="700" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A700" t="s">
+      <c r="M699" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N699" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="700" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A700" s="3" t="s">
         <v>1961</v>
       </c>
-      <c r="B700" s="26">
+      <c r="B700" s="4">
         <v>46191</v>
       </c>
-      <c r="C700" t="s">
+      <c r="C700" s="5" t="s">
         <v>1962</v>
       </c>
-      <c r="D700" t="s">
-        <v>34</v>
-      </c>
-      <c r="E700" t="s">
+      <c r="D700" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E700" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F700">
+      <c r="F700" s="6">
         <v>7198</v>
       </c>
-      <c r="G700" t="s">
+      <c r="G700" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H700" t="s">
+      <c r="H700" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="I700" t="s">
+      <c r="I700" s="5" t="s">
         <v>1963</v>
       </c>
-      <c r="J700" t="s">
+      <c r="J700" s="11" t="s">
         <v>1964</v>
       </c>
-      <c r="M700" t="s">
+      <c r="K700" s="8"/>
+      <c r="L700" s="8"/>
+      <c r="M700" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N700">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="701" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A701" t="s">
+      <c r="N700" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="701" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A701" s="3" t="s">
         <v>1965</v>
       </c>
-      <c r="B701" s="26">
+      <c r="B701" s="4">
         <v>46191</v>
       </c>
-      <c r="C701" t="s">
+      <c r="C701" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="D701" t="s">
-        <v>34</v>
-      </c>
-      <c r="E701" t="s">
+      <c r="D701" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E701" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F701">
+      <c r="F701" s="6">
         <v>6583</v>
       </c>
-      <c r="G701" t="s">
+      <c r="G701" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H701" t="s">
+      <c r="H701" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M701" t="s">
+      <c r="I701" s="8"/>
+      <c r="J701" s="8"/>
+      <c r="K701" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L701" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M701" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N701" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="702" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A702" s="3" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B702" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C702" s="5" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D702" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E702" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F702" s="6">
+        <v>1913</v>
+      </c>
+      <c r="G702" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H702" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I702" s="5" t="s">
+        <v>1967</v>
+      </c>
+      <c r="J702" s="8"/>
+      <c r="K702" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L702" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M702" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N702" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="703" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A703" s="3" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B703" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C703" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D703" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E703" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F703" s="6">
+        <v>698</v>
+      </c>
+      <c r="G703" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H703" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I703" s="5" t="s">
+        <v>1969</v>
+      </c>
+      <c r="J703" s="8"/>
+      <c r="K703" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L703" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M703" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N703" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="704" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A704" s="3" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B704" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C704" s="13">
+        <v>0.4465277777777778</v>
+      </c>
+      <c r="D704" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E704" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F704" s="6">
+        <v>5424</v>
+      </c>
+      <c r="G704" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H704" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I704" s="8"/>
+      <c r="J704" s="8"/>
+      <c r="K704" s="8"/>
+      <c r="L704" s="8"/>
+      <c r="M704" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N701">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="702" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A702" t="s">
-        <v>1966</v>
-      </c>
-      <c r="B702" s="26">
+      <c r="N704" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="705" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A705" s="3" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B705" s="4">
         <v>46191</v>
       </c>
-      <c r="C702" t="s">
+      <c r="C705" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D705" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E705" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F705" s="6">
+        <v>11090</v>
+      </c>
+      <c r="G705" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H705" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I705" s="8"/>
+      <c r="J705" s="11" t="s">
+        <v>1972</v>
+      </c>
+      <c r="K705" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L705" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M705" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N705" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="706" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A706" s="3" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B706" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C706" s="5" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D706" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E706" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F706" s="6">
+        <v>4539</v>
+      </c>
+      <c r="G706" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H706" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I706" s="5" t="s">
+        <v>1975</v>
+      </c>
+      <c r="J706" s="8"/>
+      <c r="K706" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L706" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M706" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N706" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="707" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A707" s="3" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B707" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C707" s="5" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D707" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E707" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F707" s="6">
+        <v>7210</v>
+      </c>
+      <c r="G707" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H707" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I707" s="8"/>
+      <c r="J707" s="8"/>
+      <c r="K707" s="8"/>
+      <c r="L707" s="8"/>
+      <c r="M707" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N707" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="708" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A708" s="3" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B708" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C708" s="5" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D708" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E708" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F708" s="6">
+        <v>5729</v>
+      </c>
+      <c r="G708" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H708" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I708" s="8"/>
+      <c r="J708" s="11" t="s">
+        <v>1979</v>
+      </c>
+      <c r="K708" s="8"/>
+      <c r="L708" s="8"/>
+      <c r="M708" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N708" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="709" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A709" s="3" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B709" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C709" s="5" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D709" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E709" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F709" s="6">
+        <v>6615</v>
+      </c>
+      <c r="G709" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H709" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I709" s="5" t="s">
+        <v>1982</v>
+      </c>
+      <c r="J709" s="8"/>
+      <c r="K709" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L709" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M709" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N709" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="710" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A710" s="3" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B710" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C710" s="5" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D710" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E710" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F710" s="6">
+        <v>6615</v>
+      </c>
+      <c r="G710" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H710" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I710" s="5" t="s">
+        <v>1982</v>
+      </c>
+      <c r="J710" s="8"/>
+      <c r="K710" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L710" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M710" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N710" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="711" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A711" s="3" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B711" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C711" s="13">
+        <v>0.46388888888888891</v>
+      </c>
+      <c r="D711" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E711" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F711" s="6">
+        <v>5425</v>
+      </c>
+      <c r="G711" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H711" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I711" s="8"/>
+      <c r="J711" s="8"/>
+      <c r="K711" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L711" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M711" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N711" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="712" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A712" s="3" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B712" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C712" s="13">
+        <v>0.46597222222222223</v>
+      </c>
+      <c r="D712" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E712" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F712" s="6">
+        <v>3381</v>
+      </c>
+      <c r="G712" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H712" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I712" s="8"/>
+      <c r="J712" s="11" t="s">
+        <v>1985</v>
+      </c>
+      <c r="K712" s="8"/>
+      <c r="L712" s="8"/>
+      <c r="M712" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N712" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="713" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A713" s="3" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B713" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C713" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="D713" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E713" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F713" s="6">
+        <v>5120</v>
+      </c>
+      <c r="G713" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H713" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I713" s="5" t="s">
+        <v>1987</v>
+      </c>
+      <c r="J713" s="11" t="s">
+        <v>1988</v>
+      </c>
+      <c r="K713" s="8"/>
+      <c r="L713" s="8"/>
+      <c r="M713" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N713" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="714" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A714" s="3" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B714" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C714" s="5" t="s">
+        <v>1990</v>
+      </c>
+      <c r="D714" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E714" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F714" s="6">
+        <v>7438</v>
+      </c>
+      <c r="G714" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H714" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I714" s="8"/>
+      <c r="J714" s="11" t="s">
+        <v>1991</v>
+      </c>
+      <c r="K714" s="8"/>
+      <c r="L714" s="8"/>
+      <c r="M714" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N714" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="715" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A715" s="3" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B715" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C715" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D715" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E715" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F715" s="6">
+        <v>2336</v>
+      </c>
+      <c r="G715" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H715" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I715" s="5" t="s">
+        <v>1993</v>
+      </c>
+      <c r="J715" s="11" t="s">
+        <v>1994</v>
+      </c>
+      <c r="K715" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="L715" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M715" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N715" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="716" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A716" s="3" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B716" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C716" s="13">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="D716" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E716" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F716" s="6">
+        <v>3365</v>
+      </c>
+      <c r="G716" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H716" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I716" s="5" t="s">
+        <v>1996</v>
+      </c>
+      <c r="J716" s="8"/>
+      <c r="K716" s="8"/>
+      <c r="L716" s="8"/>
+      <c r="M716" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N716" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="717" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A717" s="3" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B717" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C717" s="5" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D717" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E717" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F717" s="6">
+        <v>4</v>
+      </c>
+      <c r="G717" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H717" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I717" s="5" t="s">
+        <v>1998</v>
+      </c>
+      <c r="J717" s="8"/>
+      <c r="K717" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L717" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M717" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N717" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="718" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A718" s="3" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B718" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C718" s="5" t="s">
+        <v>1726</v>
+      </c>
+      <c r="D718" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E718" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F718" s="6">
+        <v>5129</v>
+      </c>
+      <c r="G718" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="H718" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I718" s="5" t="s">
+        <v>2000</v>
+      </c>
+      <c r="J718" s="11" t="s">
+        <v>2001</v>
+      </c>
+      <c r="K718" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L718" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M718" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N718" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="719" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A719" s="3" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B719" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C719" s="5" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D719" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E719" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F719" s="6">
+        <v>6615</v>
+      </c>
+      <c r="G719" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H719" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I719" s="5" t="s">
+        <v>2003</v>
+      </c>
+      <c r="J719" s="8"/>
+      <c r="K719" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L719" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M719" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N719" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="720" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A720" s="3" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B720" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C720" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D720" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E720" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F720" s="6">
+        <v>2383</v>
+      </c>
+      <c r="G720" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H720" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I720" s="8"/>
+      <c r="J720" s="11" t="s">
+        <v>2005</v>
+      </c>
+      <c r="K720" s="8"/>
+      <c r="L720" s="8"/>
+      <c r="M720" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N720" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="721" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A721" s="3" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B721" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C721" s="5" t="s">
+        <v>2007</v>
+      </c>
+      <c r="D721" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E721" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F721" s="6">
+        <v>6885</v>
+      </c>
+      <c r="G721" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H721" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I721" s="5" t="s">
+        <v>2008</v>
+      </c>
+      <c r="J721" s="11" t="s">
+        <v>2009</v>
+      </c>
+      <c r="K721" s="5" t="s">
+        <v>2010</v>
+      </c>
+      <c r="L721" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M721" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N721" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="722" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A722" s="3" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B722" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C722" s="5" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D722" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E722" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F722" s="6">
+        <v>4269</v>
+      </c>
+      <c r="G722" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H722" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I722" s="8"/>
+      <c r="J722" s="11" t="s">
+        <v>2013</v>
+      </c>
+      <c r="K722" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L722" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M722" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N722" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="723" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A723" s="3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B723" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C723" s="13">
+        <v>0.54027777777777775</v>
+      </c>
+      <c r="D723" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E723" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F723" s="6">
+        <v>3094</v>
+      </c>
+      <c r="G723" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H723" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I723" s="8"/>
+      <c r="J723" s="8"/>
+      <c r="K723" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L723" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M723" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N723" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="724" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A724" s="3" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B724" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C724" s="13">
+        <v>0.54374999999999996</v>
+      </c>
+      <c r="D724" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E724" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F724" s="6">
+        <v>3094</v>
+      </c>
+      <c r="G724" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H724" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I724" s="8"/>
+      <c r="J724" s="8"/>
+      <c r="K724" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L724" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M724" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N724" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="725" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A725" s="3" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B725" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C725" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="D725" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E725" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F725" s="6">
+        <v>4825</v>
+      </c>
+      <c r="G725" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H725" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I725" s="8"/>
+      <c r="J725" s="11" t="s">
+        <v>2017</v>
+      </c>
+      <c r="K725" s="8"/>
+      <c r="L725" s="8"/>
+      <c r="M725" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N725" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="726" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A726" s="3" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B726" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C726" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="D726" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E726" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F726" s="6">
+        <v>5720</v>
+      </c>
+      <c r="G726" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H726" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I726" s="5" t="s">
+        <v>2019</v>
+      </c>
+      <c r="J726" s="11" t="s">
+        <v>2020</v>
+      </c>
+      <c r="K726" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L726" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M726" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N726" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="727" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A727" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B727" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C727" s="5" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D727" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E727" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F727" s="6">
+        <v>3969</v>
+      </c>
+      <c r="G727" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H727" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I727" s="5" t="s">
+        <v>2022</v>
+      </c>
+      <c r="J727" s="8"/>
+      <c r="K727" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L727" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M727" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N727" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="728" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A728" s="3" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B728" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C728" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D728" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E728" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F728" s="6">
+        <v>4811</v>
+      </c>
+      <c r="G728" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H728" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I728" s="5" t="s">
+        <v>2024</v>
+      </c>
+      <c r="J728" s="11" t="s">
+        <v>2025</v>
+      </c>
+      <c r="K728" s="8"/>
+      <c r="L728" s="8"/>
+      <c r="M728" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N728" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="729" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A729" s="3" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B729" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C729" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="D729" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E729" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F729" s="6">
+        <v>4277</v>
+      </c>
+      <c r="G729" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H729" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I729" s="5" t="s">
+        <v>2027</v>
+      </c>
+      <c r="J729" s="11" t="s">
+        <v>2028</v>
+      </c>
+      <c r="K729" s="8"/>
+      <c r="L729" s="8"/>
+      <c r="M729" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N729" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="730" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A730" s="3" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B730" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C730" s="5" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D730" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E730" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F730" s="6">
+        <v>2515</v>
+      </c>
+      <c r="G730" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H730" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I730" s="5" t="s">
+        <v>2031</v>
+      </c>
+      <c r="J730" s="8"/>
+      <c r="K730" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="L730" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M730" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N730" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="731" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A731" s="3" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B731" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C731" s="5" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D731" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E731" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F731" s="6">
+        <v>876</v>
+      </c>
+      <c r="G731" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H731" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I731" s="5" t="s">
+        <v>2034</v>
+      </c>
+      <c r="J731" s="8"/>
+      <c r="K731" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L731" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M731" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N731" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="732" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A732" s="3" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B732" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C732" s="5" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D732" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E732" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F732" s="6">
+        <v>6078</v>
+      </c>
+      <c r="G732" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H732" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I732" s="8"/>
+      <c r="J732" s="8"/>
+      <c r="K732" s="8"/>
+      <c r="L732" s="8"/>
+      <c r="M732" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N732" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="733" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A733" s="3" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B733" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C733" s="13">
+        <v>0.56458333333333333</v>
+      </c>
+      <c r="D733" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E733" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F733" s="6">
+        <v>5752</v>
+      </c>
+      <c r="G733" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H733" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I733" s="8"/>
+      <c r="J733" s="8"/>
+      <c r="K733" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L733" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M733" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N733" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="734" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A734" s="3" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B734" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C734" s="5" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D734" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E734" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F734" s="6">
+        <v>1923</v>
+      </c>
+      <c r="G734" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H734" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I734" s="5" t="s">
+        <v>2040</v>
+      </c>
+      <c r="J734" s="8"/>
+      <c r="K734" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L734" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M734" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N734" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="735" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A735" s="3" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B735" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C735" s="5" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D735" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E735" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F735" s="6">
+        <v>10923</v>
+      </c>
+      <c r="G735" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H735" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I735" s="5" t="s">
+        <v>2040</v>
+      </c>
+      <c r="J735" s="8"/>
+      <c r="K735" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L735" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M735" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N735" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="736" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A736" s="3" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B736" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C736" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D736" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E736" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F736" s="6">
+        <v>2449</v>
+      </c>
+      <c r="G736" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H736" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I736" s="8"/>
+      <c r="J736" s="11" t="s">
+        <v>2042</v>
+      </c>
+      <c r="K736" s="5" t="s">
+        <v>2043</v>
+      </c>
+      <c r="L736" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M736" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N736" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="737" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A737" s="3" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B737" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C737" s="13">
+        <v>0.58611111111111114</v>
+      </c>
+      <c r="D737" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E737" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F737" s="6">
+        <v>5411</v>
+      </c>
+      <c r="G737" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H737" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I737" s="8"/>
+      <c r="J737" s="8"/>
+      <c r="K737" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L737" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M737" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N737" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="738" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A738" s="3" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B738" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C738" s="13">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D738" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E738" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F738" s="6">
+        <v>3080</v>
+      </c>
+      <c r="G738" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="H738" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I738" s="8"/>
+      <c r="J738" s="11" t="s">
+        <v>2046</v>
+      </c>
+      <c r="K738" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L738" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M738" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N738" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="739" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A739" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B739" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C739" s="5" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D739" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E739" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F739" s="6">
+        <v>6370</v>
+      </c>
+      <c r="G739" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H739" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I739" s="8"/>
+      <c r="J739" s="11" t="s">
+        <v>2048</v>
+      </c>
+      <c r="K739" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L739" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M739" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N739" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="740" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A740" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B740" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C740" s="5" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D740" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E740" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F740" s="6">
+        <v>6358</v>
+      </c>
+      <c r="G740" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H740" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I740" s="8"/>
+      <c r="J740" s="11" t="s">
+        <v>2050</v>
+      </c>
+      <c r="K740" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L740" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M740" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N740" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="741" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A741" s="3" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B741" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C741" s="5" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D741" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E741" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F741" s="6">
+        <v>6365</v>
+      </c>
+      <c r="G741" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H741" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I741" s="5" t="s">
+        <v>2052</v>
+      </c>
+      <c r="J741" s="11" t="s">
+        <v>2053</v>
+      </c>
+      <c r="K741" s="5" t="s">
+        <v>2054</v>
+      </c>
+      <c r="L741" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M741" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N741" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="742" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A742" s="3" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B742" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C742" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="D742" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E742" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F742" s="6">
+        <v>10931</v>
+      </c>
+      <c r="G742" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H742" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I742" s="5" t="s">
+        <v>2056</v>
+      </c>
+      <c r="J742" s="11" t="s">
+        <v>2057</v>
+      </c>
+      <c r="K742" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L742" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M742" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N742" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="743" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A743" s="3" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B743" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C743" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D743" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E743" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F743" s="6">
+        <v>1329</v>
+      </c>
+      <c r="G743" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H743" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I743" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="J743" s="11" t="s">
+        <v>2060</v>
+      </c>
+      <c r="K743" s="5" t="s">
+        <v>2061</v>
+      </c>
+      <c r="L743" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M743" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N743" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="744" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A744" s="3" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B744" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C744" s="5" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D744" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E744" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F744" s="6">
+        <v>2556</v>
+      </c>
+      <c r="G744" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H744" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I744" s="5" t="s">
+        <v>2064</v>
+      </c>
+      <c r="J744" s="11" t="s">
+        <v>2065</v>
+      </c>
+      <c r="K744" s="8"/>
+      <c r="L744" s="8"/>
+      <c r="M744" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N744" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="745" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A745" s="3" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B745" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C745" s="5" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D745" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E745" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F745" s="6">
+        <v>6321</v>
+      </c>
+      <c r="G745" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H745" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I745" s="8"/>
+      <c r="J745" s="8"/>
+      <c r="K745" s="8"/>
+      <c r="L745" s="8"/>
+      <c r="M745" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N745" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="746" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A746" s="3" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B746" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C746" s="5" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D746" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E746" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F746" s="6">
+        <v>5131</v>
+      </c>
+      <c r="G746" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="H746" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I746" s="8"/>
+      <c r="J746" s="8"/>
+      <c r="K746" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L746" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M746" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N746" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="747" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A747" s="3" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B747" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C747" s="5" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D747" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E747" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F747" s="6">
+        <v>5729</v>
+      </c>
+      <c r="G747" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H747" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I747" s="8"/>
+      <c r="J747" s="11" t="s">
+        <v>2072</v>
+      </c>
+      <c r="K747" s="8"/>
+      <c r="L747" s="8"/>
+      <c r="M747" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N747" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="748" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A748" s="3" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B748" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C748" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D748" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E748" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F748" s="6">
+        <v>3099</v>
+      </c>
+      <c r="G748" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="H748" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I748" s="8"/>
+      <c r="J748" s="11" t="s">
+        <v>2074</v>
+      </c>
+      <c r="K748" s="5" t="s">
+        <v>2075</v>
+      </c>
+      <c r="L748" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M748" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N748" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="749" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A749" s="3" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B749" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C749" s="5" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D749" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E749" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F749" s="6">
+        <v>3105</v>
+      </c>
+      <c r="G749" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H749" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I749" s="8"/>
+      <c r="J749" s="8"/>
+      <c r="K749" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L749" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M749" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N749" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="750" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A750" s="3" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B750" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C750" s="5" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D750" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E750" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F750" s="6">
+        <v>6583</v>
+      </c>
+      <c r="G750" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H750" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I750" s="8"/>
+      <c r="J750" s="8"/>
+      <c r="K750" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L750" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M750" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N750" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="751" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A751" s="3" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B751" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C751" s="5" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D751" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E751" s="5" t="s">
+        <v>956</v>
+      </c>
+      <c r="F751" s="6">
+        <v>2274</v>
+      </c>
+      <c r="G751" s="5" t="s">
+        <v>957</v>
+      </c>
+      <c r="H751" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I751" s="5" t="s">
+        <v>2082</v>
+      </c>
+      <c r="J751" s="8"/>
+      <c r="K751" s="5" t="s">
+        <v>2083</v>
+      </c>
+      <c r="L751" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M751" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N751" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="752" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A752" s="3" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B752" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C752" s="5" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D752" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E752" s="5" t="s">
+        <v>956</v>
+      </c>
+      <c r="F752" s="6">
+        <v>727</v>
+      </c>
+      <c r="G752" s="5" t="s">
+        <v>957</v>
+      </c>
+      <c r="H752" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I752" s="5" t="s">
+        <v>2086</v>
+      </c>
+      <c r="J752" s="8"/>
+      <c r="K752" s="5" t="s">
+        <v>1521</v>
+      </c>
+      <c r="L752" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M752" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N752" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="753" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A753" s="3" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B753" s="4">
+        <v>46191</v>
+      </c>
+      <c r="C753" s="5" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D753" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E753" s="5" t="s">
+        <v>956</v>
+      </c>
+      <c r="F753" s="6">
+        <v>10899</v>
+      </c>
+      <c r="G753" s="5" t="s">
+        <v>957</v>
+      </c>
+      <c r="H753" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I753" s="5" t="s">
+        <v>2089</v>
+      </c>
+      <c r="J753" s="8"/>
+      <c r="K753" s="5" t="s">
+        <v>2090</v>
+      </c>
+      <c r="L753" s="4">
+        <v>46191</v>
+      </c>
+      <c r="M753" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N753" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="754" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A754" s="3" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B754" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C754" s="5" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D754" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E754" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F754" s="6">
+        <v>14</v>
+      </c>
+      <c r="G754" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H754" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I754" s="8"/>
+      <c r="J754" s="8"/>
+      <c r="K754" s="8"/>
+      <c r="L754" s="8"/>
+      <c r="M754" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N754" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="755" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A755" s="3" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B755" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C755" s="5" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D755" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E755" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F755" s="6">
+        <v>17</v>
+      </c>
+      <c r="G755" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H755" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I755" s="8"/>
+      <c r="J755" s="8"/>
+      <c r="K755" s="8"/>
+      <c r="L755" s="8"/>
+      <c r="M755" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N755" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="756" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A756" s="3" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B756" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C756" s="5" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D756" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E756" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F756" s="6">
+        <v>57</v>
+      </c>
+      <c r="G756" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H756" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I756" s="8"/>
+      <c r="J756" s="8"/>
+      <c r="K756" s="8"/>
+      <c r="L756" s="8"/>
+      <c r="M756" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N756" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="757" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A757" s="3" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B757" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C757" s="5" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D757" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E757" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F757" s="6">
+        <v>57</v>
+      </c>
+      <c r="G757" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H757" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I757" s="8"/>
+      <c r="J757" s="11" t="s">
+        <v>2099</v>
+      </c>
+      <c r="K757" s="8"/>
+      <c r="L757" s="8"/>
+      <c r="M757" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N757" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="758" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A758" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B758" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C758" s="5" t="s">
+        <v>2101</v>
+      </c>
+      <c r="D758" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E758" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F758" s="6">
+        <v>1623</v>
+      </c>
+      <c r="G758" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H758" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I758" s="8"/>
+      <c r="J758" s="11" t="s">
+        <v>2102</v>
+      </c>
+      <c r="K758" s="8"/>
+      <c r="L758" s="8"/>
+      <c r="M758" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N758" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="759" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A759" s="3" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B759" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C759" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="D759" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E759" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F759" s="6">
+        <v>3985</v>
+      </c>
+      <c r="G759" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H759" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I759" s="5" t="s">
+        <v>2104</v>
+      </c>
+      <c r="J759" s="11" t="s">
+        <v>2105</v>
+      </c>
+      <c r="K759" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L759" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M759" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N759" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="760" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A760" s="3" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B760" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C760" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="D760" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E760" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F760" s="6">
+        <v>5195</v>
+      </c>
+      <c r="G760" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="H760" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I760" s="5" t="s">
+        <v>2107</v>
+      </c>
+      <c r="J760" s="11" t="s">
+        <v>2108</v>
+      </c>
+      <c r="K760" s="8"/>
+      <c r="L760" s="8"/>
+      <c r="M760" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N760" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="761" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A761" s="3" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B761" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C761" s="5" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D761" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E761" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F761" s="6">
+        <v>2873</v>
+      </c>
+      <c r="G761" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H761" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I761" s="8"/>
+      <c r="J761" s="11" t="s">
+        <v>2110</v>
+      </c>
+      <c r="K761" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L761" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M761" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N761" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="762" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A762" s="3" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B762" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C762" s="5" t="s">
+        <v>979</v>
+      </c>
+      <c r="D762" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E762" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F762" s="6">
+        <v>1339</v>
+      </c>
+      <c r="G762" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H762" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I762" s="8"/>
+      <c r="J762" s="11" t="s">
+        <v>2112</v>
+      </c>
+      <c r="K762" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L762" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M762" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N762" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="763" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A763" s="3" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B763" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C763" s="13">
+        <v>0.38263888888888886</v>
+      </c>
+      <c r="D763" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E763" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F763" s="6">
+        <v>4727</v>
+      </c>
+      <c r="G763" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H763" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I763" s="8"/>
+      <c r="J763" s="8"/>
+      <c r="K763" s="8"/>
+      <c r="L763" s="8"/>
+      <c r="M763" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N763" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="764" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A764" s="3" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B764" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C764" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="D764" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E764" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F764" s="6">
+        <v>5194</v>
+      </c>
+      <c r="G764" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H764" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I764" s="8"/>
+      <c r="J764" s="11" t="s">
+        <v>2115</v>
+      </c>
+      <c r="K764" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L764" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M764" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N764" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="765" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A765" s="3" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B765" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C765" s="5" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D765" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E765" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F765" s="6">
+        <v>5820</v>
+      </c>
+      <c r="G765" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H765" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I765" s="5" t="s">
+        <v>2117</v>
+      </c>
+      <c r="J765" s="11" t="s">
+        <v>2118</v>
+      </c>
+      <c r="K765" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L765" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M765" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N765" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="766" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A766" s="3" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B766" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C766" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D766" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E766" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F766" s="6">
+        <v>1799</v>
+      </c>
+      <c r="G766" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H766" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I766" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="J766" s="11" t="s">
+        <v>2122</v>
+      </c>
+      <c r="K766" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L766" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M766" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N766" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="767" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A767" s="3" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B767" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C767" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D767" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E767" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F767" s="6">
+        <v>11067</v>
+      </c>
+      <c r="G767" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H767" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I767" s="5" t="s">
+        <v>2124</v>
+      </c>
+      <c r="J767" s="11" t="s">
+        <v>2125</v>
+      </c>
+      <c r="K767" s="8"/>
+      <c r="L767" s="8"/>
+      <c r="M767" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N767" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="768" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A768" s="3" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B768" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C768" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="D768" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E768" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F768" s="6">
+        <v>6091</v>
+      </c>
+      <c r="G768" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H768" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I768" s="5" t="s">
+        <v>2127</v>
+      </c>
+      <c r="J768" s="8"/>
+      <c r="K768" s="8"/>
+      <c r="L768" s="8"/>
+      <c r="M768" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N768" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="769" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A769" s="3" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B769" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C769" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D769" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E769" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F769" s="6">
+        <v>5206</v>
+      </c>
+      <c r="G769" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="H769" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I769" s="8"/>
+      <c r="J769" s="11" t="s">
+        <v>2129</v>
+      </c>
+      <c r="K769" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L769" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M769" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N769" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="770" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A770" s="3" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B770" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C770" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D770" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E770" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F770" s="6">
+        <v>2073</v>
+      </c>
+      <c r="G770" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H770" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I770" s="5" t="s">
+        <v>2131</v>
+      </c>
+      <c r="J770" s="11" t="s">
+        <v>2132</v>
+      </c>
+      <c r="K770" s="8"/>
+      <c r="L770" s="8"/>
+      <c r="M770" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N770" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="771" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A771" s="3" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B771" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C771" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D771" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E771" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F771" s="6">
+        <v>3841</v>
+      </c>
+      <c r="G771" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H771" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I771" s="5" t="s">
+        <v>2134</v>
+      </c>
+      <c r="J771" s="8"/>
+      <c r="K771" s="8"/>
+      <c r="L771" s="8"/>
+      <c r="M771" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N771" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="772" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A772" s="3" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B772" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C772" s="5" t="s">
         <v>1802</v>
       </c>
-      <c r="D702" t="s">
-        <v>34</v>
-      </c>
-      <c r="E702" t="s">
-        <v>23</v>
-      </c>
-      <c r="F702">
-        <v>1913</v>
-      </c>
-      <c r="G702" t="s">
-        <v>63</v>
-      </c>
-      <c r="H702" t="s">
+      <c r="D772" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E772" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F772" s="6">
+        <v>5178</v>
+      </c>
+      <c r="G772" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="H772" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I702" t="s">
-        <v>1967</v>
-      </c>
-      <c r="K702" t="s">
-        <v>54</v>
-      </c>
-      <c r="L702" s="26">
-        <v>46191</v>
-      </c>
-      <c r="M702" t="s">
-        <v>67</v>
-      </c>
-      <c r="N702">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="703" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A703" t="s">
-        <v>1968</v>
-      </c>
-      <c r="B703" s="26">
-        <v>46191</v>
-      </c>
-      <c r="C703" t="s">
-        <v>248</v>
-      </c>
-      <c r="D703" t="s">
-        <v>34</v>
-      </c>
-      <c r="E703" t="s">
-        <v>1513</v>
-      </c>
-      <c r="F703">
-        <v>698</v>
-      </c>
-      <c r="G703" t="s">
-        <v>1514</v>
-      </c>
-      <c r="H703" t="s">
+      <c r="I772" s="5" t="s">
+        <v>2136</v>
+      </c>
+      <c r="J772" s="11" t="s">
+        <v>2137</v>
+      </c>
+      <c r="K772" s="8"/>
+      <c r="L772" s="8"/>
+      <c r="M772" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N772" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="773" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A773" s="3" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B773" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C773" s="13">
+        <v>0.4465277777777778</v>
+      </c>
+      <c r="D773" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E773" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F773" s="6">
+        <v>6526</v>
+      </c>
+      <c r="G773" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H773" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I773" s="8"/>
+      <c r="J773" s="8"/>
+      <c r="K773" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L773" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M773" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N773" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="774" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A774" s="3" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B774" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C774" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D774" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E774" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F774" s="6">
+        <v>2858</v>
+      </c>
+      <c r="G774" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H774" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I703" t="s">
-        <v>1969</v>
-      </c>
-      <c r="M703" t="s">
-        <v>66</v>
-      </c>
-      <c r="N703">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="704" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A704" t="s">
-        <v>1970</v>
-      </c>
-      <c r="B704" s="26">
-        <v>46191</v>
-      </c>
-      <c r="C704" s="27">
-        <v>0.4465277777777778</v>
-      </c>
-      <c r="D704" t="s">
-        <v>34</v>
-      </c>
-      <c r="E704" t="s">
+      <c r="I774" s="5" t="s">
+        <v>2140</v>
+      </c>
+      <c r="J774" s="11" t="s">
+        <v>2141</v>
+      </c>
+      <c r="K774" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L774" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M774" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N774" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="775" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A775" s="3" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B775" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C775" s="13">
+        <v>0.45555555555555555</v>
+      </c>
+      <c r="D775" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E775" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F704">
-        <v>5424</v>
-      </c>
-      <c r="G704" t="s">
-        <v>59</v>
-      </c>
-      <c r="H704" t="s">
+      <c r="F775" s="6">
+        <v>3571</v>
+      </c>
+      <c r="G775" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H775" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="M704" t="s">
-        <v>66</v>
-      </c>
-      <c r="N704">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="705" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A705" t="s">
-        <v>1971</v>
-      </c>
-      <c r="B705" s="26">
-        <v>46191</v>
-      </c>
-      <c r="C705" t="s">
-        <v>68</v>
-      </c>
-      <c r="D705" t="s">
-        <v>34</v>
-      </c>
-      <c r="E705" t="s">
-        <v>12</v>
-      </c>
-      <c r="F705">
-        <v>11090</v>
-      </c>
-      <c r="G705" t="s">
-        <v>40</v>
-      </c>
-      <c r="H705" t="s">
-        <v>41</v>
-      </c>
-      <c r="J705" t="s">
-        <v>1972</v>
-      </c>
-      <c r="M705" t="s">
-        <v>66</v>
-      </c>
-      <c r="N705">
+      <c r="I775" s="8"/>
+      <c r="J775" s="8"/>
+      <c r="K775" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L775" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M775" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N775" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="776" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A776" s="3" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B776" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C776" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D776" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E776" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F776" s="6">
+        <v>11111</v>
+      </c>
+      <c r="G776" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H776" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I776" s="5" t="s">
+        <v>2144</v>
+      </c>
+      <c r="J776" s="8"/>
+      <c r="K776" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L776" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M776" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N776" s="24">
         <v>6</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J5" r:id="rId1" xr:uid="{B88996D5-1E93-47D3-9B9D-42040D0097BF}"/>
+    <hyperlink ref="J7" r:id="rId2" xr:uid="{A2C2BD61-46A5-4A18-AE71-0312DA9FA7BA}"/>
+    <hyperlink ref="J8" r:id="rId3" xr:uid="{3AFB78C4-9D4E-4F2A-A6DA-1A50BD9381C5}"/>
+    <hyperlink ref="J10" r:id="rId4" xr:uid="{E42583CD-3494-47A0-A03A-F670E226AA14}"/>
+    <hyperlink ref="J13" r:id="rId5" xr:uid="{A6C68DE7-000A-4B2B-BD99-F6B2C19C194A}"/>
+    <hyperlink ref="J14" r:id="rId6" xr:uid="{72432930-DCEA-4B0F-8503-4BF4FED7A93A}"/>
+    <hyperlink ref="J17" r:id="rId7" xr:uid="{00700B33-6B04-4AD3-8451-D4F79AA7112A}"/>
+    <hyperlink ref="J19" r:id="rId8" xr:uid="{0D23FABC-D87B-4893-98E2-CC265BE75AF4}"/>
+    <hyperlink ref="J20" r:id="rId9" xr:uid="{28D493DD-94DC-4859-9969-65BB25AD51C8}"/>
+    <hyperlink ref="J21" r:id="rId10" xr:uid="{447DC423-AA8B-4247-B2A2-F0CB4C40F294}"/>
+    <hyperlink ref="J24" r:id="rId11" xr:uid="{AFD5E7C3-F1B4-4D58-805B-CF4B8CD0F020}"/>
+    <hyperlink ref="J25" r:id="rId12" xr:uid="{4F4B9C0D-2B68-4FE5-9376-1FF43F140C18}"/>
+    <hyperlink ref="J26" r:id="rId13" xr:uid="{A6D78F7D-2A87-49D0-A276-CC44A3199B9F}"/>
+    <hyperlink ref="J27" r:id="rId14" xr:uid="{4512167F-1AE4-4D5C-9E75-B389C911EA63}"/>
+    <hyperlink ref="J29" r:id="rId15" xr:uid="{FC9AF86A-336B-48C3-9DA3-AC5436C65E98}"/>
+    <hyperlink ref="J30" r:id="rId16" xr:uid="{8D26EC5F-2D3A-4A20-9766-ED681BFF840D}"/>
+    <hyperlink ref="J31" r:id="rId17" xr:uid="{75B3C5FC-935E-4FCC-BA9B-FF37A0C9C3A3}"/>
+    <hyperlink ref="J34" r:id="rId18" xr:uid="{F627A75F-10C5-47EF-9B91-62EA01AD1A97}"/>
+    <hyperlink ref="J35" r:id="rId19" xr:uid="{E4192226-BE39-4863-904B-E1D28756D9DE}"/>
+    <hyperlink ref="J36" r:id="rId20" xr:uid="{A2DBB2A1-8EF7-4C29-B9CB-406175FD4DBE}"/>
+    <hyperlink ref="J37" r:id="rId21" xr:uid="{7F57D855-3760-41EF-97ED-214043EF0B9D}"/>
+    <hyperlink ref="J38" r:id="rId22" xr:uid="{DFB5E4FC-B97A-4992-8486-9DA70E02416C}"/>
+    <hyperlink ref="J46" r:id="rId23" xr:uid="{E93F0C3D-D751-4415-B168-79B60A571F68}"/>
+    <hyperlink ref="J47" r:id="rId24" xr:uid="{2DF34A0A-A4A6-4859-AD6B-0E7A01B59D25}"/>
+    <hyperlink ref="J48" r:id="rId25" xr:uid="{483E8C1E-6AD5-4A35-9BA8-73DAA9D210A8}"/>
+    <hyperlink ref="J49" r:id="rId26" xr:uid="{DEB06DE1-9113-4820-BFED-F3FD4346C7D4}"/>
+    <hyperlink ref="J50" r:id="rId27" xr:uid="{CF892E5A-EED1-463C-B619-81A23289226E}"/>
+    <hyperlink ref="J52" r:id="rId28" xr:uid="{D4ECD12F-9AF0-4326-9349-FAC937EF1635}"/>
+    <hyperlink ref="J53" r:id="rId29" xr:uid="{0DEF4993-7D87-4AD2-9772-DA65FB01B647}"/>
+    <hyperlink ref="J54" r:id="rId30" xr:uid="{3FB151D0-1787-41EE-856E-E4FB3268116C}"/>
+    <hyperlink ref="J56" r:id="rId31" xr:uid="{14534BBF-41B5-45D8-9C39-0E7BF9C00501}"/>
+    <hyperlink ref="J59" r:id="rId32" xr:uid="{DDD1C0DD-645B-402B-ABEB-0428AA35D177}"/>
+    <hyperlink ref="J61" r:id="rId33" xr:uid="{A6FD7A20-E89E-4DB2-86B3-0B440527242C}"/>
+    <hyperlink ref="J62" r:id="rId34" xr:uid="{7C47223A-A2FE-40A2-B63C-499C2930DEF1}"/>
+    <hyperlink ref="J63" r:id="rId35" xr:uid="{96BFB53D-BBB1-4F36-8104-0ACB7CF9F488}"/>
+    <hyperlink ref="J64" r:id="rId36" xr:uid="{35250C88-B635-483F-8071-AC54BC673660}"/>
+    <hyperlink ref="J69" r:id="rId37" xr:uid="{CD28D3FC-B938-493C-9660-F5D03C870D94}"/>
+    <hyperlink ref="J71" r:id="rId38" xr:uid="{2E9542D8-6E35-4B9D-8CE7-1428C759C245}"/>
+    <hyperlink ref="J72" r:id="rId39" xr:uid="{7AE4BFCE-B2C6-4401-8AF1-C861355192C8}"/>
+    <hyperlink ref="J73" r:id="rId40" xr:uid="{4148A84A-4388-4994-9EC0-D8F76320151D}"/>
+    <hyperlink ref="J74" r:id="rId41" xr:uid="{B3C9E6FD-2479-46BE-841D-02629D009755}"/>
+    <hyperlink ref="J75" r:id="rId42" xr:uid="{D0271643-F130-4835-88EB-8411CE97EFF8}"/>
+    <hyperlink ref="J76" r:id="rId43" xr:uid="{30ACD85C-CA03-40B2-893F-9AA2847E322E}"/>
+    <hyperlink ref="J78" r:id="rId44" xr:uid="{E7B6E757-D77B-4DF1-8C70-02F3A3A0BA04}"/>
+    <hyperlink ref="J80" r:id="rId45" xr:uid="{6AACF0F2-C4F7-44AD-9481-69F3ADD398F6}"/>
+    <hyperlink ref="J86" r:id="rId46" xr:uid="{159DE113-54EC-497B-A09A-A63EC6941963}"/>
+    <hyperlink ref="J88" r:id="rId47" xr:uid="{1F13859D-E69D-43C3-B12A-25146A54F769}"/>
+    <hyperlink ref="J89" r:id="rId48" xr:uid="{E35C74E6-710C-4CC5-BFFC-ED87C2B0D3BC}"/>
+    <hyperlink ref="J90" r:id="rId49" xr:uid="{13C3CD02-310B-48C0-9F3D-1BF814CA042E}"/>
+    <hyperlink ref="J92" r:id="rId50" xr:uid="{580C4B01-46ED-4FF3-81CC-E96A2FE99FB9}"/>
+    <hyperlink ref="J94" r:id="rId51" xr:uid="{799618E5-55E8-40C9-930C-422E8623CDFD}"/>
+    <hyperlink ref="J95" r:id="rId52" xr:uid="{E85A4E30-F11F-4A43-A1A8-12A869E267DA}"/>
+    <hyperlink ref="J96" r:id="rId53" xr:uid="{06AB32BA-BC86-4B87-B930-EBD212C200CF}"/>
+    <hyperlink ref="J101" r:id="rId54" xr:uid="{0A4DBD2F-FFFC-4E6D-B0A1-8C91ACF5C9FE}"/>
+    <hyperlink ref="J103" r:id="rId55" xr:uid="{5DCC63BE-4AB0-4B99-9851-A233F04746E9}"/>
+    <hyperlink ref="J104" r:id="rId56" xr:uid="{42644421-339B-407C-BED1-AF0A315C1B31}"/>
+    <hyperlink ref="J105" r:id="rId57" xr:uid="{836D2E43-2990-427C-B914-B9FAC39E0916}"/>
+    <hyperlink ref="J106" r:id="rId58" xr:uid="{45FB1228-B679-47F6-9B02-9D4322C85CFF}"/>
+    <hyperlink ref="J107" r:id="rId59" xr:uid="{1DEAB372-7445-40A4-A735-4959D270133B}"/>
+    <hyperlink ref="J109" r:id="rId60" xr:uid="{772CF91F-1098-44CF-893D-BF21BD3DFD82}"/>
+    <hyperlink ref="J110" r:id="rId61" xr:uid="{7950725E-1BCA-4D36-B6DF-7E26AD7FD801}"/>
+    <hyperlink ref="J111" r:id="rId62" xr:uid="{D95390B9-51D1-4455-84AF-EF5FE71C8592}"/>
+    <hyperlink ref="J112" r:id="rId63" xr:uid="{AAD8376A-F5B2-4D86-8271-9E07A854F5E4}"/>
+    <hyperlink ref="J113" r:id="rId64" xr:uid="{AB2FA5AB-EF4C-4B08-BD3F-BA8BC5CDE703}"/>
+    <hyperlink ref="J114" r:id="rId65" xr:uid="{F8049ED0-F89A-466E-8535-3702B7877D9F}"/>
+    <hyperlink ref="J116" r:id="rId66" xr:uid="{CD057669-F686-439A-955F-43C69707C7AF}"/>
+    <hyperlink ref="J117" r:id="rId67" xr:uid="{57CE08D8-1B23-4CE7-A1B7-A09C90E837D8}"/>
+    <hyperlink ref="J118" r:id="rId68" xr:uid="{D3ABFE1B-1EB2-4A26-AB54-5CF8A9CF9BC1}"/>
+    <hyperlink ref="J119" r:id="rId69" xr:uid="{D06EFE35-D535-464C-B2CE-FDD1BA994D58}"/>
+    <hyperlink ref="J120" r:id="rId70" xr:uid="{C6C4C34A-32A6-4DD4-93F3-2D030C23A6F5}"/>
+    <hyperlink ref="J121" r:id="rId71" xr:uid="{BE924EC4-81FF-4184-9095-733B8B101C70}"/>
+    <hyperlink ref="J124" r:id="rId72" xr:uid="{6D649045-1AB3-49C4-9DE4-FB734A256257}"/>
+    <hyperlink ref="J128" r:id="rId73" xr:uid="{BF2262B4-0D0B-48F1-B4F2-1CF4D225C663}"/>
+    <hyperlink ref="J129" r:id="rId74" xr:uid="{DD6C1AB0-7E7D-4454-AE54-3DC4CDB495F9}"/>
+    <hyperlink ref="J132" r:id="rId75" xr:uid="{45CF6128-20F8-4F77-8EE3-1A43C7196644}"/>
+    <hyperlink ref="J134" r:id="rId76" xr:uid="{C493ED74-D76F-4FDF-89C8-379E0E5A607D}"/>
+    <hyperlink ref="J135" r:id="rId77" xr:uid="{9665401E-5878-4EAD-887D-EF0870DB75EC}"/>
+    <hyperlink ref="J136" r:id="rId78" xr:uid="{FE1C265B-14BD-4DE2-A32A-15C24394162C}"/>
+    <hyperlink ref="J140" r:id="rId79" xr:uid="{75D1069B-51C4-4036-A3B6-D951F19EE717}"/>
+    <hyperlink ref="J142" r:id="rId80" xr:uid="{C3FAF03A-7524-4C4F-B905-C7300D309E2D}"/>
+    <hyperlink ref="J143" r:id="rId81" xr:uid="{7FAB3C0B-D59A-4A71-B3A5-C40781F7FB6B}"/>
+    <hyperlink ref="J144" r:id="rId82" xr:uid="{DDB8CEA7-FC2B-476D-A058-AF12C25EB2A2}"/>
+    <hyperlink ref="J145" r:id="rId83" xr:uid="{868F8CC6-3E76-4ABA-99D6-58E177872278}"/>
+    <hyperlink ref="J147" r:id="rId84" xr:uid="{87688FE5-05B4-4AD0-AEEB-2D58FB5EB301}"/>
+    <hyperlink ref="J149" r:id="rId85" xr:uid="{A6EE35DE-58B2-4091-85C7-864A6077908A}"/>
+    <hyperlink ref="J150" r:id="rId86" xr:uid="{9D2C2140-29B1-49A0-9A38-5727375CF24F}"/>
+    <hyperlink ref="J151" r:id="rId87" xr:uid="{8DF0F3E5-8AE6-4859-8506-A7612503FBF6}"/>
+    <hyperlink ref="J152" r:id="rId88" xr:uid="{C5133B6D-198D-4185-8354-7F64173C3786}"/>
+    <hyperlink ref="J153" r:id="rId89" xr:uid="{BCFF0D76-FB6B-4986-B24B-89627640545B}"/>
+    <hyperlink ref="J154" r:id="rId90" xr:uid="{393AA3F7-F44D-4025-9494-FA1836E64318}"/>
+    <hyperlink ref="J155" r:id="rId91" xr:uid="{A5E38F29-B013-43FF-A907-0E46567A02E5}"/>
+    <hyperlink ref="J156" r:id="rId92" xr:uid="{8D20C537-73B9-405B-9381-8FDC8AFD143D}"/>
+    <hyperlink ref="J159" r:id="rId93" xr:uid="{9433FB2A-DF44-4B4D-9804-04DD21B89AA8}"/>
+    <hyperlink ref="J160" r:id="rId94" xr:uid="{9D01F767-A027-47F9-BFCC-87D57834C72B}"/>
+    <hyperlink ref="J161" r:id="rId95" xr:uid="{3D0EDB9B-9CA3-4C58-9ACC-EE570F0F04B9}"/>
+    <hyperlink ref="J162" r:id="rId96" xr:uid="{F6732FDB-87B9-4AD5-AD31-A6DC149AC7DE}"/>
+    <hyperlink ref="J164" r:id="rId97" xr:uid="{8512379A-E7F9-4D07-8EF7-C62786B1E5CF}"/>
+    <hyperlink ref="J165" r:id="rId98" xr:uid="{9ED05AE4-C442-432C-803A-42D6C3CBB637}"/>
+    <hyperlink ref="J167" r:id="rId99" xr:uid="{5DE6C16D-8D50-40B3-A144-C587CEAC058C}"/>
+    <hyperlink ref="J168" r:id="rId100" xr:uid="{E496BB26-EC71-43D1-B1F0-6887360AE2E0}"/>
+    <hyperlink ref="J169" r:id="rId101" xr:uid="{29E62008-297E-4F1E-8A4F-FE06E5E50AB3}"/>
+    <hyperlink ref="J171" r:id="rId102" xr:uid="{BAB7BEFD-726D-4871-8D36-4EC060405563}"/>
+    <hyperlink ref="J172" r:id="rId103" xr:uid="{CDD7C553-C60F-434A-BEB4-48AE57F17676}"/>
+    <hyperlink ref="J173" r:id="rId104" xr:uid="{64F9B9B7-86EB-437B-A35B-8771BE826530}"/>
+    <hyperlink ref="J177" r:id="rId105" xr:uid="{4A04CDF8-1F66-48A9-922A-036614258228}"/>
+    <hyperlink ref="J178" r:id="rId106" xr:uid="{5BB7D15B-0BC5-40F6-B2E7-B126134DA2CB}"/>
+    <hyperlink ref="J181" r:id="rId107" xr:uid="{2C8F8AF3-44DA-4A55-B614-138F215A7A10}"/>
+    <hyperlink ref="J182" r:id="rId108" xr:uid="{D3327397-CE0F-4CA4-8493-7328C5E77C10}"/>
+    <hyperlink ref="J184" r:id="rId109" xr:uid="{5D9B5AF0-791C-4239-92E3-266E97754AFF}"/>
+    <hyperlink ref="J186" r:id="rId110" xr:uid="{AB0A793A-87E0-4CBA-8EDE-E0307909C8AF}"/>
+    <hyperlink ref="J190" r:id="rId111" xr:uid="{73717102-48AB-46D7-9F29-F50A2D4CE979}"/>
+    <hyperlink ref="J191" r:id="rId112" xr:uid="{0A769538-DEDC-4AA7-9804-892D866ED571}"/>
+    <hyperlink ref="J192" r:id="rId113" xr:uid="{5BB20A68-4E15-43DC-B541-BDA9ACE5D9DD}"/>
+    <hyperlink ref="J193" r:id="rId114" xr:uid="{CDACD140-2997-42F9-8F81-A7505C4F9886}"/>
+    <hyperlink ref="J194" r:id="rId115" xr:uid="{2EB40273-7F71-4946-BDC6-AF2754CC6C05}"/>
+    <hyperlink ref="J195" r:id="rId116" xr:uid="{170BB09B-5E1F-4590-893B-39A786230360}"/>
+    <hyperlink ref="J196" r:id="rId117" xr:uid="{AFAE64F4-2B7C-43A6-8BC7-414AC4F0FB36}"/>
+    <hyperlink ref="J199" r:id="rId118" xr:uid="{661E0EDA-347B-458F-A634-22CAA520D02B}"/>
+    <hyperlink ref="J201" r:id="rId119" xr:uid="{17E12D97-B513-4B14-897C-B463A198619D}"/>
+    <hyperlink ref="J202" r:id="rId120" xr:uid="{D429CBBE-0CDA-4D36-8E53-E4C846E12E70}"/>
+    <hyperlink ref="J203" r:id="rId121" xr:uid="{3A71CBF0-2124-499E-A7DE-826D37981472}"/>
+    <hyperlink ref="J205" r:id="rId122" xr:uid="{B01F768D-2ECE-4593-8373-5483D27D4684}"/>
+    <hyperlink ref="J207" r:id="rId123" xr:uid="{CAB3AA4E-4248-4E49-9EBA-EEC25F79A358}"/>
+    <hyperlink ref="J209" r:id="rId124" xr:uid="{9C3116C1-87E1-47EF-8F10-1084A4AF488E}"/>
+    <hyperlink ref="J210" r:id="rId125" xr:uid="{55181976-3728-4EDF-BAA7-8C4D7CCFEC4F}"/>
+    <hyperlink ref="J211" r:id="rId126" xr:uid="{2CD31C65-42C2-48E1-B226-0ADA1530AC28}"/>
+    <hyperlink ref="J212" r:id="rId127" xr:uid="{D4421AE1-6497-479B-9050-97D3FCCA5400}"/>
+    <hyperlink ref="J213" r:id="rId128" xr:uid="{741E0D66-B211-4C8B-A49E-AECE1B333F62}"/>
+    <hyperlink ref="J214" r:id="rId129" xr:uid="{B616E33E-CDDA-43AC-B413-63B8B7CF513B}"/>
+    <hyperlink ref="J215" r:id="rId130" xr:uid="{0B876CF5-88D8-4C8E-A21D-2372223288C0}"/>
+    <hyperlink ref="J217" r:id="rId131" xr:uid="{48AE988B-AA43-4070-868B-3110793CF54E}"/>
+    <hyperlink ref="J219" r:id="rId132" xr:uid="{302DE7C9-A9F1-4EE1-9F20-E604C061ACA6}"/>
+    <hyperlink ref="J220" r:id="rId133" xr:uid="{5CCFA0BB-572B-430C-B790-A3587A8F42F3}"/>
+    <hyperlink ref="J221" r:id="rId134" xr:uid="{47540183-A567-4552-904F-65B8762832A6}"/>
+    <hyperlink ref="J222" r:id="rId135" xr:uid="{4DF0AA11-2A16-4201-A4AD-BECA47310E61}"/>
+    <hyperlink ref="J223" r:id="rId136" xr:uid="{59B2514A-ECB4-4D6E-BF06-8AB0E1F8400B}"/>
+    <hyperlink ref="J225" r:id="rId137" xr:uid="{48C50357-1115-470B-A3BB-5E42D19AF65F}"/>
+    <hyperlink ref="J228" r:id="rId138" xr:uid="{B6CBAEEB-771C-47FB-88B9-BDC11852323F}"/>
+    <hyperlink ref="J230" r:id="rId139" xr:uid="{636AF7EA-A2F1-44BC-A007-820710BE5B34}"/>
+    <hyperlink ref="J234" r:id="rId140" xr:uid="{970AD978-E6BF-4D91-BB1B-36E11E76151B}"/>
+    <hyperlink ref="J236" r:id="rId141" xr:uid="{AF1982F8-D275-4BFD-AE5D-04B7DF5F6203}"/>
+    <hyperlink ref="J237" r:id="rId142" xr:uid="{310049FF-670E-4433-9A85-E2D1489B5D1D}"/>
+    <hyperlink ref="J238" r:id="rId143" xr:uid="{1FFD6D26-F9BE-4AC6-984A-698F4B8642D3}"/>
+    <hyperlink ref="J240" r:id="rId144" xr:uid="{16169098-5A7B-40C8-B93D-870852C878E4}"/>
+    <hyperlink ref="J241" r:id="rId145" xr:uid="{A87AFDC9-08AE-43EC-A64D-778A8BD47EB7}"/>
+    <hyperlink ref="J242" r:id="rId146" xr:uid="{4111A16F-7165-4AE1-8CA1-181A889C36FE}"/>
+    <hyperlink ref="J243" r:id="rId147" xr:uid="{0E35F663-0408-40CF-91CB-6DBB5CA0103A}"/>
+    <hyperlink ref="J246" r:id="rId148" xr:uid="{F9757982-D13D-4B6B-9A45-BDB4E474C25A}"/>
+    <hyperlink ref="J247" r:id="rId149" xr:uid="{361D136A-BCCF-40F3-8E18-25B1C5718861}"/>
+    <hyperlink ref="J250" r:id="rId150" xr:uid="{D664F274-3C2D-407E-98B4-FD79ECD8DF80}"/>
+    <hyperlink ref="J252" r:id="rId151" xr:uid="{7BC40F0D-C6F2-40E9-B7AC-767DF5CF0B86}"/>
+    <hyperlink ref="J254" r:id="rId152" xr:uid="{3A3C66D7-B240-4A00-8760-CE53EAE5FF13}"/>
+    <hyperlink ref="J255" r:id="rId153" xr:uid="{4DED24B0-7BDF-4F66-85D5-08A82220A3F0}"/>
+    <hyperlink ref="J256" r:id="rId154" xr:uid="{641BA73D-3E8B-42B7-A4A9-BD0EA3BCCD3D}"/>
+    <hyperlink ref="J258" r:id="rId155" xr:uid="{04FBD900-323D-425E-B208-B7206802F0A2}"/>
+    <hyperlink ref="J259" r:id="rId156" xr:uid="{77EB149C-B38C-43D0-9ED3-54C4A078D76B}"/>
+    <hyperlink ref="J261" r:id="rId157" xr:uid="{A19BF520-5EEC-4262-B464-5E3CDEF14833}"/>
+    <hyperlink ref="J263" r:id="rId158" xr:uid="{7246294A-1B7A-4C5D-AC51-1A32EA1A41D8}"/>
+    <hyperlink ref="J265" r:id="rId159" xr:uid="{1E5FCFFC-86D6-4F44-AD25-E584426348AC}"/>
+    <hyperlink ref="J266" r:id="rId160" xr:uid="{B081C88D-DDC0-45D5-8D10-9FC422BE7203}"/>
+    <hyperlink ref="J267" r:id="rId161" xr:uid="{0BB850A1-60D0-46A7-B1A1-7AA6E50851AE}"/>
+    <hyperlink ref="J270" r:id="rId162" xr:uid="{D7F61676-9D9D-46FB-B7B5-918A359014EC}"/>
+    <hyperlink ref="J271" r:id="rId163" xr:uid="{FFD12AC7-08C8-40C7-B36C-922F8300FE4F}"/>
+    <hyperlink ref="J273" r:id="rId164" xr:uid="{83DB86DD-104A-4F54-B937-719862870DC0}"/>
+    <hyperlink ref="J274" r:id="rId165" xr:uid="{1D0ED40C-799F-4353-B863-33137673D10D}"/>
+    <hyperlink ref="J275" r:id="rId166" xr:uid="{49450B40-7042-422A-923A-A077A030743E}"/>
+    <hyperlink ref="J277" r:id="rId167" xr:uid="{1BADF204-10ED-43CE-B58E-09BA383D56EE}"/>
+    <hyperlink ref="J278" r:id="rId168" xr:uid="{A96C232B-CD58-4C60-B660-15D87A4E98EA}"/>
+    <hyperlink ref="J279" r:id="rId169" xr:uid="{317D48CC-A714-4D23-B71F-7DC683324E1E}"/>
+    <hyperlink ref="J280" r:id="rId170" xr:uid="{6BF16EBB-00FD-44E0-9075-5E3DE118D76A}"/>
+    <hyperlink ref="J281" r:id="rId171" xr:uid="{6DCC2F8F-CBB9-4B56-A15E-20446A141B37}"/>
+    <hyperlink ref="J282" r:id="rId172" xr:uid="{A6BC230E-F15B-4B49-A0EE-32D276675675}"/>
+    <hyperlink ref="J283" r:id="rId173" xr:uid="{7106C8A9-FE4F-441C-8632-D77A1F6A820E}"/>
+    <hyperlink ref="J286" r:id="rId174" xr:uid="{8A5F0FE1-162E-4369-B70F-73B9C94D5075}"/>
+    <hyperlink ref="J287" r:id="rId175" xr:uid="{A7A75DAA-AB8D-4C0B-AA60-6779E1182425}"/>
+    <hyperlink ref="J290" r:id="rId176" xr:uid="{35B40E90-430F-4B7C-8AFC-DE8265B6BAE1}"/>
+    <hyperlink ref="J292" r:id="rId177" xr:uid="{BDA0E0E5-C491-4C39-B9E2-B0405B3C5E3C}"/>
+    <hyperlink ref="J294" r:id="rId178" xr:uid="{C5909A1B-4840-4E0C-B7FC-5CA325E76F77}"/>
+    <hyperlink ref="J296" r:id="rId179" xr:uid="{B31D7DE8-F8D4-4F2D-959A-82C3281F99D3}"/>
+    <hyperlink ref="J297" r:id="rId180" xr:uid="{2A73614C-00A9-433B-A3D5-2766BA06EFEF}"/>
+    <hyperlink ref="J298" r:id="rId181" xr:uid="{6755D5AB-7116-44BC-920B-46DE5152B1D0}"/>
+    <hyperlink ref="J299" r:id="rId182" xr:uid="{93C43455-755E-45BF-822F-FFACEEBA47DB}"/>
+    <hyperlink ref="J300" r:id="rId183" xr:uid="{29440318-30CA-45CC-81F0-6A411470A0A7}"/>
+    <hyperlink ref="J301" r:id="rId184" xr:uid="{9C8FE5BF-B79B-41C7-9EDB-9C02D2918ECE}"/>
+    <hyperlink ref="J303" r:id="rId185" xr:uid="{9519C260-4F34-4B3F-B903-9B303D879F00}"/>
+    <hyperlink ref="J305" r:id="rId186" xr:uid="{731EB7A0-0389-440C-A7C8-BE18965141BD}"/>
+    <hyperlink ref="J306" r:id="rId187" xr:uid="{B37B0C8C-8541-4370-954F-818984C628EB}"/>
+    <hyperlink ref="J308" r:id="rId188" xr:uid="{F0CC7679-14DA-4FCE-85B9-B91886799B1A}"/>
+    <hyperlink ref="J309" r:id="rId189" xr:uid="{39CDB470-A841-4D9A-9563-DC5B6996FC0C}"/>
+    <hyperlink ref="J311" r:id="rId190" xr:uid="{27B17F30-E4BF-4E93-8E60-3CD16A859013}"/>
+    <hyperlink ref="J312" r:id="rId191" xr:uid="{AE076C91-E65C-4AD7-A83C-A7F007CA185B}"/>
+    <hyperlink ref="J314" r:id="rId192" xr:uid="{DBB2B8B7-C5C6-4921-9206-7764B70BFB37}"/>
+    <hyperlink ref="J317" r:id="rId193" xr:uid="{87C59B37-0077-4968-B349-86B1B0F99904}"/>
+    <hyperlink ref="J318" r:id="rId194" xr:uid="{3C90603E-A49C-401D-852F-EF3F2F8DF84C}"/>
+    <hyperlink ref="J321" r:id="rId195" xr:uid="{C7466EFF-9908-4825-A4A8-F0C464CD9D97}"/>
+    <hyperlink ref="J322" r:id="rId196" xr:uid="{29842225-97D8-48EE-999C-B73450EFC120}"/>
+    <hyperlink ref="J325" r:id="rId197" xr:uid="{1A9F8F69-31AA-4C5B-9694-E356273CD990}"/>
+    <hyperlink ref="J326" r:id="rId198" xr:uid="{3914A055-3A7E-4978-A3A8-8E23139CDE9D}"/>
+    <hyperlink ref="J329" r:id="rId199" xr:uid="{F37A3C14-0521-4AB3-A300-D28761914BDE}"/>
+    <hyperlink ref="J330" r:id="rId200" xr:uid="{D8BDE4C3-C5E3-4E60-A09D-7278C3DB61DF}"/>
+    <hyperlink ref="J331" r:id="rId201" xr:uid="{8BE702A6-5AB9-494E-B559-FF8E6D6E670D}"/>
+    <hyperlink ref="J333" r:id="rId202" xr:uid="{4B0989C8-CC3C-40BE-BB33-20E39465EB25}"/>
+    <hyperlink ref="J334" r:id="rId203" xr:uid="{A1D08642-1359-4087-9459-8C39C60399B6}"/>
+    <hyperlink ref="J335" r:id="rId204" xr:uid="{87671D62-77A2-4B86-B9A2-76F698CCDB28}"/>
+    <hyperlink ref="J336" r:id="rId205" xr:uid="{763F4C73-F61B-4076-9C5B-451B680CE769}"/>
+    <hyperlink ref="J338" r:id="rId206" xr:uid="{B7F1A47D-A33C-4018-9C67-FEDAE219FC5C}"/>
+    <hyperlink ref="J340" r:id="rId207" xr:uid="{6A535932-0EA1-4D82-8AB1-01DF9B24E800}"/>
+    <hyperlink ref="J342" r:id="rId208" xr:uid="{62AD1E09-4A27-4531-B69B-05FD5214D91E}"/>
+    <hyperlink ref="J343" r:id="rId209" xr:uid="{602063A3-C9EF-43B0-BB68-944F4283201F}"/>
+    <hyperlink ref="J344" r:id="rId210" xr:uid="{30A51D69-8361-4324-9D14-1365CB020816}"/>
+    <hyperlink ref="J346" r:id="rId211" xr:uid="{35F04862-8CB8-45AE-A9A9-6A288064ED9E}"/>
+    <hyperlink ref="J349" r:id="rId212" xr:uid="{16A458FA-4008-4058-8C91-1AD03FA38B8C}"/>
+    <hyperlink ref="J350" r:id="rId213" xr:uid="{065C7560-8957-4931-8A6F-58E9B6199072}"/>
+    <hyperlink ref="J352" r:id="rId214" xr:uid="{1245B78B-0C95-4DE8-AE9D-8173395EB70E}"/>
+    <hyperlink ref="J354" r:id="rId215" xr:uid="{E4563525-D6AF-43C2-828A-A56D8726B1FC}"/>
+    <hyperlink ref="J355" r:id="rId216" xr:uid="{9AC84DE4-C593-4C67-B5BA-469C7EBAAA74}"/>
+    <hyperlink ref="J356" r:id="rId217" xr:uid="{DAC4877F-D366-4B58-9357-87840E602B14}"/>
+    <hyperlink ref="J357" r:id="rId218" xr:uid="{30032090-EE4F-47EC-8247-D16CA1A623F5}"/>
+    <hyperlink ref="J358" r:id="rId219" xr:uid="{9212402A-E85C-4646-A7E2-653E2CCA06F5}"/>
+    <hyperlink ref="J360" r:id="rId220" xr:uid="{22B93211-BE64-4221-855E-4B9AB17FF6A0}"/>
+    <hyperlink ref="J363" r:id="rId221" xr:uid="{734A9250-B35A-4305-BC53-30EF872D1BB9}"/>
+    <hyperlink ref="J364" r:id="rId222" xr:uid="{6FF83BA5-8102-45AB-9D29-C4C70C7060A0}"/>
+    <hyperlink ref="J366" r:id="rId223" xr:uid="{537A655A-DAB8-4B07-976D-D04AE16293C7}"/>
+    <hyperlink ref="J368" r:id="rId224" xr:uid="{DEDDE3AD-9277-4264-AFC4-B6F622137EF7}"/>
+    <hyperlink ref="J370" r:id="rId225" xr:uid="{DFC3736D-569F-420F-BA6E-D633DFC0E70D}"/>
+    <hyperlink ref="J371" r:id="rId226" xr:uid="{BF39F5AC-56E5-4CE5-B30C-6A89280D5289}"/>
+    <hyperlink ref="J372" r:id="rId227" xr:uid="{D0658AF7-B2E3-4CA4-A702-157ECC225F6B}"/>
+    <hyperlink ref="J373" r:id="rId228" xr:uid="{F12DA6B1-EE8C-4CC2-9AD3-36BCFAB21A39}"/>
+    <hyperlink ref="J374" r:id="rId229" xr:uid="{0BBA2A93-65EE-4B88-A948-45351FD9B6B8}"/>
+    <hyperlink ref="J375" r:id="rId230" xr:uid="{0D95A89F-5D1F-42A5-88A8-A3D911A47F7A}"/>
+    <hyperlink ref="J376" r:id="rId231" xr:uid="{11A580EE-4977-4D3F-9DA8-4122CB84282B}"/>
+    <hyperlink ref="J377" r:id="rId232" xr:uid="{30428EC4-EF75-4AC7-B23D-2B2899020983}"/>
+    <hyperlink ref="J378" r:id="rId233" xr:uid="{3F20B6AE-47B7-42EE-A4B6-850FF03242C9}"/>
+    <hyperlink ref="J379" r:id="rId234" xr:uid="{22049983-6ACB-4DE6-9B40-B0F13F15B00B}"/>
+    <hyperlink ref="J381" r:id="rId235" xr:uid="{2152B735-4EB5-4AE2-A519-CEE59C418AD9}"/>
+    <hyperlink ref="J383" r:id="rId236" xr:uid="{8EFB12D4-ED4E-4F9E-8F69-C259DC68E845}"/>
+    <hyperlink ref="J384" r:id="rId237" xr:uid="{C00347B8-E8AB-4A63-A53B-871A10571B3D}"/>
+    <hyperlink ref="J386" r:id="rId238" xr:uid="{32BAB89D-C259-4BE1-B38E-D88B2B14C76F}"/>
+    <hyperlink ref="J387" r:id="rId239" xr:uid="{57C03BA1-05AD-4EE4-88A3-F526E795C860}"/>
+    <hyperlink ref="J388" r:id="rId240" xr:uid="{03448F52-3548-4916-953E-EBC6E5FCBEA6}"/>
+    <hyperlink ref="J390" r:id="rId241" xr:uid="{B9AEEE69-83EB-4027-9DA3-177647D7D45F}"/>
+    <hyperlink ref="J391" r:id="rId242" xr:uid="{7299AB58-6E50-4800-954C-CDD4C5E6D86D}"/>
+    <hyperlink ref="J394" r:id="rId243" xr:uid="{27592250-10ED-4996-BAC1-00ABD14822EC}"/>
+    <hyperlink ref="J395" r:id="rId244" xr:uid="{B15B997C-2F7D-448E-A2D8-928A384421E8}"/>
+    <hyperlink ref="J396" r:id="rId245" xr:uid="{231E6DB8-BA0F-42B1-9416-1107E5FE4F95}"/>
+    <hyperlink ref="J397" r:id="rId246" xr:uid="{0E2BD6AE-69B5-4209-836B-D718BEB5990E}"/>
+    <hyperlink ref="J398" r:id="rId247" xr:uid="{7D2C3ECB-B6B5-4C82-BC5E-E9DF703C6FDA}"/>
+    <hyperlink ref="J399" r:id="rId248" xr:uid="{F7B90D72-2F15-4567-8BA2-BBCFA782D47C}"/>
+    <hyperlink ref="J400" r:id="rId249" xr:uid="{144A44FB-E28B-4E1C-991C-1B83D459A13C}"/>
+    <hyperlink ref="J403" r:id="rId250" xr:uid="{AA6A0DD4-8547-41B1-8B98-BB5BC319C146}"/>
+    <hyperlink ref="J404" r:id="rId251" xr:uid="{9DFB7478-E7CF-4844-96C1-BC75739906DF}"/>
+    <hyperlink ref="J405" r:id="rId252" xr:uid="{111C5E83-C6F6-4879-B8FF-DB39AC4A0B31}"/>
+    <hyperlink ref="J406" r:id="rId253" xr:uid="{55742018-EC53-42F7-AE98-3774A858EDA5}"/>
+    <hyperlink ref="J408" r:id="rId254" xr:uid="{B7B523CF-7FCE-41BA-B879-BE58DE9E4C2F}"/>
+    <hyperlink ref="J409" r:id="rId255" xr:uid="{456AF082-40AD-472E-82CC-D0E9AD53B779}"/>
+    <hyperlink ref="J411" r:id="rId256" xr:uid="{B6D0E4DA-FC78-42A8-A1C3-1DD72CE752CC}"/>
+    <hyperlink ref="J413" r:id="rId257" xr:uid="{2CF54B46-477E-46B7-A38D-37441E63BF3F}"/>
+    <hyperlink ref="J415" r:id="rId258" xr:uid="{7AE15555-9953-4D8D-B9F7-2DC4EE1BC04D}"/>
+    <hyperlink ref="J416" r:id="rId259" xr:uid="{802E4134-EC3B-40DC-BB1D-9532BBF63F4C}"/>
+    <hyperlink ref="J418" r:id="rId260" xr:uid="{24C3C142-B671-4A1B-AAEF-F5621EC761D6}"/>
+    <hyperlink ref="J421" r:id="rId261" xr:uid="{E3BBE5D2-D50D-4E7B-884E-D394441C2E3B}"/>
+    <hyperlink ref="J422" r:id="rId262" xr:uid="{5B0B354A-D599-4535-838B-BD858254344F}"/>
+    <hyperlink ref="J430" r:id="rId263" xr:uid="{DAE45DE8-BA02-4114-AD94-5E4C5660A67C}"/>
+    <hyperlink ref="J431" r:id="rId264" xr:uid="{D675C037-D8CD-4FB1-B7BF-3445FD296B90}"/>
+    <hyperlink ref="J432" r:id="rId265" xr:uid="{33B5FC02-DC00-4573-A48A-227E0090D1DD}"/>
+    <hyperlink ref="J433" r:id="rId266" xr:uid="{190753B8-B793-4290-A7DD-04A9EC54D19D}"/>
+    <hyperlink ref="J434" r:id="rId267" xr:uid="{DCFCE9E8-92BC-4D5F-894A-E63E7333DEF0}"/>
+    <hyperlink ref="J435" r:id="rId268" xr:uid="{2635E524-F9C4-4394-977D-6CB065E611C8}"/>
+    <hyperlink ref="J436" r:id="rId269" xr:uid="{0D4F9019-DF45-4653-8C45-849F711DB6AC}"/>
+    <hyperlink ref="J437" r:id="rId270" xr:uid="{AF4FDA04-EA39-4289-AFC5-87B802E5BE9E}"/>
+    <hyperlink ref="J438" r:id="rId271" xr:uid="{693A1ED5-08CB-4868-A1C7-7C4976F32013}"/>
+    <hyperlink ref="J439" r:id="rId272" xr:uid="{A0728540-E173-4FEB-B0A3-154E0E1FEFAD}"/>
+    <hyperlink ref="J445" r:id="rId273" xr:uid="{547A7B81-0E19-4144-AC6C-B037D3E1D00F}"/>
+    <hyperlink ref="J447" r:id="rId274" xr:uid="{3A577E37-3C9F-4943-B83A-1DD2AC4F81FE}"/>
+    <hyperlink ref="J449" r:id="rId275" xr:uid="{8EA4111A-3A96-43AD-9749-F477CA0BC0FD}"/>
+    <hyperlink ref="J450" r:id="rId276" xr:uid="{26A0FD00-1973-42EC-A1D1-8849038B2652}"/>
+    <hyperlink ref="J451" r:id="rId277" xr:uid="{D8930F0E-2511-44AE-875E-9104E88D21DF}"/>
+    <hyperlink ref="J452" r:id="rId278" xr:uid="{2802D4FA-5839-4592-8296-0466C611148B}"/>
+    <hyperlink ref="J453" r:id="rId279" xr:uid="{E59BB7BB-6FC4-4DBF-9669-003042F73E22}"/>
+    <hyperlink ref="J454" r:id="rId280" xr:uid="{A04B132B-81B3-43C3-99AD-C35D3FC487AB}"/>
+    <hyperlink ref="J455" r:id="rId281" xr:uid="{D73A0AA2-E86A-4EF0-9B1B-A83687D558A8}"/>
+    <hyperlink ref="J458" r:id="rId282" xr:uid="{604EDA95-CC8C-42B9-B3ED-ABE6D164E04A}"/>
+    <hyperlink ref="J460" r:id="rId283" xr:uid="{61D50ACF-11E4-46A2-B477-55813115D358}"/>
+    <hyperlink ref="J461" r:id="rId284" xr:uid="{2F172F7D-2439-469D-B9C2-ECC4B9DC4E88}"/>
+    <hyperlink ref="J462" r:id="rId285" xr:uid="{BEE0C974-6376-443A-912A-F9566B6A7951}"/>
+    <hyperlink ref="J465" r:id="rId286" xr:uid="{957C8DAC-BEED-45F2-B1AE-D1F86A25D690}"/>
+    <hyperlink ref="J469" r:id="rId287" xr:uid="{CBB18CFC-F55E-492C-93F0-243BD0CF1794}"/>
+    <hyperlink ref="J473" r:id="rId288" xr:uid="{54B9105E-B07A-4352-84E5-C1F4CF53C196}"/>
+    <hyperlink ref="J476" r:id="rId289" xr:uid="{05556749-C202-4FF0-8D43-3520298CA29C}"/>
+    <hyperlink ref="J478" r:id="rId290" xr:uid="{CD0F20CC-E3F1-4626-9351-2B28217F21BA}"/>
+    <hyperlink ref="J479" r:id="rId291" xr:uid="{17D1D7F4-80C3-4F71-910A-7333299F1629}"/>
+    <hyperlink ref="J480" r:id="rId292" xr:uid="{8C8AAF60-90C1-4F6F-9360-D5FED4C85D6B}"/>
+    <hyperlink ref="J481" r:id="rId293" xr:uid="{4F623206-2B58-4B50-BC6C-C5582C3C8F58}"/>
+    <hyperlink ref="J482" r:id="rId294" xr:uid="{40886FB2-1B63-4441-8F63-9BA55A4112CB}"/>
+    <hyperlink ref="J484" r:id="rId295" xr:uid="{73FFE5D2-83FB-449C-9B24-D2298A98A685}"/>
+    <hyperlink ref="J485" r:id="rId296" xr:uid="{7F3E85D5-0888-4E1B-AFE1-C508F3BC5744}"/>
+    <hyperlink ref="J488" r:id="rId297" xr:uid="{1992D802-8F96-471E-9DF7-20FDE6E1E6F5}"/>
+    <hyperlink ref="J489" r:id="rId298" xr:uid="{C243C020-3DBC-4CA6-92FA-9563B8E89E2A}"/>
+    <hyperlink ref="J490" r:id="rId299" xr:uid="{8E494181-C1B4-4C3C-AEE3-81428FF3243A}"/>
+    <hyperlink ref="J491" r:id="rId300" xr:uid="{8F68945D-0B73-449E-BDD6-80818EAA984F}"/>
+    <hyperlink ref="J494" r:id="rId301" xr:uid="{49CA0548-C6BC-48AA-B134-89B2625A249B}"/>
+    <hyperlink ref="J496" r:id="rId302" xr:uid="{2BE02F57-4EBF-4A92-97F1-32ACD20E8569}"/>
+    <hyperlink ref="J497" r:id="rId303" xr:uid="{36B77205-C233-4FE9-9382-EF95E891D05A}"/>
+    <hyperlink ref="J498" r:id="rId304" xr:uid="{1137FB75-24E8-4A1B-B6CA-86040FC6897E}"/>
+    <hyperlink ref="J499" r:id="rId305" xr:uid="{CCA45C73-E149-4B75-A166-9F447EA9A7A1}"/>
+    <hyperlink ref="J500" r:id="rId306" xr:uid="{9731E86A-8BF9-421E-97A7-AB2F895173CC}"/>
+    <hyperlink ref="J501" r:id="rId307" xr:uid="{4846EFED-5B32-493D-8924-40CB25401F45}"/>
+    <hyperlink ref="J503" r:id="rId308" xr:uid="{D26972CE-714B-4FFE-A86A-C922183FA5EA}"/>
+    <hyperlink ref="J504" r:id="rId309" xr:uid="{2DCD8805-0F0C-4943-AB07-36988E2983D0}"/>
+    <hyperlink ref="J508" r:id="rId310" xr:uid="{EE9F76C6-AB33-41C1-AAD0-859B11299119}"/>
+    <hyperlink ref="J509" r:id="rId311" xr:uid="{30C74A23-60F4-4BF8-9EE7-9F57860E9AE3}"/>
+    <hyperlink ref="J510" r:id="rId312" xr:uid="{246EE96B-D140-4074-918D-9D7455F242F0}"/>
+    <hyperlink ref="J511" r:id="rId313" xr:uid="{63DD2A69-B5E0-4666-9931-D64AF60AC7E6}"/>
+    <hyperlink ref="J513" r:id="rId314" xr:uid="{6F1927E1-F7D4-4782-9794-FBCC94B43906}"/>
+    <hyperlink ref="J515" r:id="rId315" xr:uid="{7E4DD59C-3FEE-4FA6-B41F-B4D150B49313}"/>
+    <hyperlink ref="J516" r:id="rId316" xr:uid="{BD1A4BE6-6763-488A-B0F6-4A9FA3A85D60}"/>
+    <hyperlink ref="J519" r:id="rId317" xr:uid="{5B3E5B10-BD91-419E-8794-50AFA5C9CB97}"/>
+    <hyperlink ref="J523" r:id="rId318" xr:uid="{0B66F68D-BB4C-449D-A8C5-D69E4B83DE06}"/>
+    <hyperlink ref="J524" r:id="rId319" xr:uid="{DC32AD5C-5728-4101-AEB5-6E59FA56C194}"/>
+    <hyperlink ref="J525" r:id="rId320" xr:uid="{DE958784-3271-455B-B6D5-C7572A48F330}"/>
+    <hyperlink ref="J535" r:id="rId321" xr:uid="{42F03D9F-5ED8-4D23-82AD-BD8A373A1F83}"/>
+    <hyperlink ref="J536" r:id="rId322" xr:uid="{7C4028FC-291F-48E5-BF19-B81093EB2870}"/>
+    <hyperlink ref="J537" r:id="rId323" xr:uid="{C9FE9FF8-7174-4B1F-A866-3E39282EA56F}"/>
+    <hyperlink ref="J538" r:id="rId324" xr:uid="{D25B9AB5-720B-40CA-903A-0A3533879ECD}"/>
+    <hyperlink ref="J539" r:id="rId325" xr:uid="{2894DFBE-F85D-418B-BC20-98089C07526B}"/>
+    <hyperlink ref="J540" r:id="rId326" xr:uid="{5721D230-52A9-4664-854B-C7D620795B70}"/>
+    <hyperlink ref="J541" r:id="rId327" xr:uid="{492DEC2F-B37A-48E2-89E7-36C24884F226}"/>
+    <hyperlink ref="J543" r:id="rId328" xr:uid="{B5D72363-F49A-407A-9C82-7240EBEED83E}"/>
+    <hyperlink ref="J544" r:id="rId329" xr:uid="{0FBCC060-D6F9-46FE-8328-485E3D812170}"/>
+    <hyperlink ref="J546" r:id="rId330" xr:uid="{C2A3031F-861C-4813-8275-C4F4F4458EBD}"/>
+    <hyperlink ref="J547" r:id="rId331" xr:uid="{9231BBD1-83B5-4299-8AFB-63BF1DECE86C}"/>
+    <hyperlink ref="J548" r:id="rId332" xr:uid="{8EBFA4A5-CC79-4DFF-8C30-49B9A4BD02F9}"/>
+    <hyperlink ref="J549" r:id="rId333" xr:uid="{EF13AB94-1B1F-4006-9AC5-34A6BF8466A2}"/>
+    <hyperlink ref="J550" r:id="rId334" xr:uid="{BC234B51-D8BF-418A-B603-E6229A9EBD9A}"/>
+    <hyperlink ref="J551" r:id="rId335" xr:uid="{47B80BCD-1162-4E72-81E6-F2B040C66E90}"/>
+    <hyperlink ref="J552" r:id="rId336" xr:uid="{3280EA33-826E-41E8-AB35-A0FA7EA6AF14}"/>
+    <hyperlink ref="J555" r:id="rId337" xr:uid="{672C70AB-2836-4474-90D9-18F1A0A896C6}"/>
+    <hyperlink ref="J556" r:id="rId338" xr:uid="{E93BCDE7-40BA-4CC8-89DF-80D43484859A}"/>
+    <hyperlink ref="J558" r:id="rId339" xr:uid="{EC016F7A-E8C1-461B-B9FA-9386EC366D42}"/>
+    <hyperlink ref="J559" r:id="rId340" xr:uid="{FEA88681-70CF-4D6B-9050-603EA6312678}"/>
+    <hyperlink ref="J560" r:id="rId341" xr:uid="{3E5960B5-6FE5-445A-A9AD-5306CC1E612C}"/>
+    <hyperlink ref="J562" r:id="rId342" xr:uid="{558BE965-146C-4AA1-AB5B-8FF71A48A7B3}"/>
+    <hyperlink ref="J569" r:id="rId343" xr:uid="{CACDFB75-2AED-44E7-A12A-72428F16218E}"/>
+    <hyperlink ref="J570" r:id="rId344" xr:uid="{71E9B58E-4527-4AB0-BAF2-198245CEA179}"/>
+    <hyperlink ref="J571" r:id="rId345" xr:uid="{5584A699-3660-4E41-A6F3-424C2109A59B}"/>
+    <hyperlink ref="J572" r:id="rId346" xr:uid="{69775804-1D29-4FF0-A4EB-88AC85CCE78E}"/>
+    <hyperlink ref="J573" r:id="rId347" xr:uid="{A3852DFA-1AB6-401D-9B76-C1332ABB5ADE}"/>
+    <hyperlink ref="J574" r:id="rId348" xr:uid="{2B7F5FD7-FE6F-40C1-9DFB-EA7A7A8D8EC8}"/>
+    <hyperlink ref="J575" r:id="rId349" xr:uid="{20DF0733-350E-47FF-ABA6-86C66BD112B2}"/>
+    <hyperlink ref="J576" r:id="rId350" xr:uid="{44DBB282-014D-4991-882C-8795B62D9D5C}"/>
+    <hyperlink ref="J577" r:id="rId351" xr:uid="{189BDD48-050C-4BD8-AE97-FCE43964F67F}"/>
+    <hyperlink ref="J578" r:id="rId352" xr:uid="{917662CD-683A-4592-BE78-298A1A1663A4}"/>
+    <hyperlink ref="J579" r:id="rId353" xr:uid="{0EB435D0-DEFA-4DC5-8AD2-BE2B73FF5A05}"/>
+    <hyperlink ref="J580" r:id="rId354" xr:uid="{88C7A544-DF60-4810-A87F-7E798198180B}"/>
+    <hyperlink ref="J581" r:id="rId355" xr:uid="{DF2710CB-0024-4FE9-9F37-496AB90B82F3}"/>
+    <hyperlink ref="J582" r:id="rId356" xr:uid="{A9FC74DA-E7B2-4D30-97B3-F02FC78509A1}"/>
+    <hyperlink ref="J584" r:id="rId357" xr:uid="{DF72BA24-F778-4995-979A-6CF76C4EC73A}"/>
+    <hyperlink ref="J585" r:id="rId358" xr:uid="{731706D6-2EB1-40F9-A4A0-C907F7666D39}"/>
+    <hyperlink ref="J586" r:id="rId359" xr:uid="{CA2CDDC0-D7E5-40B6-A888-76EEE11CD882}"/>
+    <hyperlink ref="J587" r:id="rId360" xr:uid="{E280284A-235C-45CF-A0A8-86EC2367A63D}"/>
+    <hyperlink ref="J592" r:id="rId361" xr:uid="{6434A4C7-A4E2-481F-BDBD-866DE3838AE0}"/>
+    <hyperlink ref="J593" r:id="rId362" xr:uid="{57B5233E-7B24-473E-95B7-8134056B50D4}"/>
+    <hyperlink ref="J595" r:id="rId363" xr:uid="{1E23C72C-FDFF-48FA-950E-B465AF0A5B3A}"/>
+    <hyperlink ref="J596" r:id="rId364" xr:uid="{49056B52-D64E-4E51-B8E3-BB324A4B9627}"/>
+    <hyperlink ref="J598" r:id="rId365" xr:uid="{B336A840-7AF5-4741-BE76-781592C035A9}"/>
+    <hyperlink ref="J599" r:id="rId366" xr:uid="{3C90513D-BB1B-4E2D-8D65-496B50C3BE15}"/>
+    <hyperlink ref="J602" r:id="rId367" xr:uid="{7577BEF2-75F5-43BE-B71B-74940A449603}"/>
+    <hyperlink ref="J603" r:id="rId368" xr:uid="{841A2CD2-FE30-4542-910F-5F865DCDDD9A}"/>
+    <hyperlink ref="J604" r:id="rId369" xr:uid="{0319EDF4-2A31-438F-AE1D-8475A6ED7139}"/>
+    <hyperlink ref="J605" r:id="rId370" xr:uid="{4BF3B61E-2A27-461C-AF91-DAA726C92136}"/>
+    <hyperlink ref="J606" r:id="rId371" xr:uid="{48EBAB6F-CEE3-4D44-8E18-3D3D71B8680B}"/>
+    <hyperlink ref="J608" r:id="rId372" xr:uid="{F251ED35-8F6E-4F90-A9C9-91D8AAFF21B0}"/>
+    <hyperlink ref="J609" r:id="rId373" xr:uid="{B437A4A8-4B96-4ADF-8BD3-DAA31B1E46A7}"/>
+    <hyperlink ref="J611" r:id="rId374" xr:uid="{13813612-DF1C-4138-8F32-A0BAD20B86B3}"/>
+    <hyperlink ref="J612" r:id="rId375" xr:uid="{DE6F32A9-68E3-476C-A4A7-18A70BDA7C8F}"/>
+    <hyperlink ref="J613" r:id="rId376" xr:uid="{A5C28568-4FAC-4FB1-A9B4-5E2610EA5F2B}"/>
+    <hyperlink ref="J615" r:id="rId377" xr:uid="{6133F0C3-24BB-4E86-AD17-AB676F54D940}"/>
+    <hyperlink ref="J617" r:id="rId378" xr:uid="{1EFC166C-45B4-4E87-9A33-3D6AB88BF853}"/>
+    <hyperlink ref="J618" r:id="rId379" xr:uid="{E686CAE8-9F2E-4159-B8B9-93A5C85B0005}"/>
+    <hyperlink ref="J619" r:id="rId380" xr:uid="{F8BD4B1C-B76D-4E3D-8C98-294E881E3E97}"/>
+    <hyperlink ref="J622" r:id="rId381" xr:uid="{1658E7CF-0D6C-47D5-967C-676844BBDA8F}"/>
+    <hyperlink ref="J623" r:id="rId382" xr:uid="{206D2EFD-1A95-47BB-9E0F-A84CA0D69161}"/>
+    <hyperlink ref="J624" r:id="rId383" xr:uid="{AC5AE00E-352C-4776-9256-EDC394A55775}"/>
+    <hyperlink ref="J626" r:id="rId384" xr:uid="{E5B00B9F-FB3D-41E4-AC3B-80BD1DF17645}"/>
+    <hyperlink ref="J628" r:id="rId385" xr:uid="{2CAA543C-8F62-4736-9842-68D55C5F2DF5}"/>
+    <hyperlink ref="J629" r:id="rId386" xr:uid="{4449395F-A53D-47DF-B535-DB1CCEC3B620}"/>
+    <hyperlink ref="J631" r:id="rId387" xr:uid="{7235EBA1-6E29-420D-8375-3FCE52DA1348}"/>
+    <hyperlink ref="J634" r:id="rId388" xr:uid="{BE2BFFE5-0357-4AE2-89DF-F51ADE2BDFBB}"/>
+    <hyperlink ref="J635" r:id="rId389" xr:uid="{63F7C999-AF9A-4561-BFB5-1C3408142CE9}"/>
+    <hyperlink ref="J637" r:id="rId390" xr:uid="{E0755957-80DD-4C03-AB64-B252021B96FB}"/>
+    <hyperlink ref="J640" r:id="rId391" xr:uid="{DD0AA12D-CBC0-4977-AD25-01E64AEAF930}"/>
+    <hyperlink ref="J641" r:id="rId392" xr:uid="{42FDA13E-D22F-45FC-966D-6F55C7DE9AC4}"/>
+    <hyperlink ref="J642" r:id="rId393" xr:uid="{C30B1471-1256-4B11-AE3C-5A73870B0550}"/>
+    <hyperlink ref="J644" r:id="rId394" xr:uid="{7FCF31B0-D55B-45E4-B24C-2D168B334FF7}"/>
+    <hyperlink ref="J645" r:id="rId395" xr:uid="{268D8E05-77BE-4CF3-8E58-0D997FAD7264}"/>
+    <hyperlink ref="J648" r:id="rId396" xr:uid="{5EA49D87-B3F4-47CA-ADCA-C709D136E3FE}"/>
+    <hyperlink ref="J649" r:id="rId397" xr:uid="{DC268961-BF0F-4D24-B6DA-41E2F5D6C69A}"/>
+    <hyperlink ref="J652" r:id="rId398" xr:uid="{ABC605DA-B6E6-4EFF-83A9-3E58C006FE4E}"/>
+    <hyperlink ref="J654" r:id="rId399" xr:uid="{F949E294-812D-4195-8796-4D638BD000D9}"/>
+    <hyperlink ref="J656" r:id="rId400" xr:uid="{A463E8D1-121A-415C-9EC9-9D69E1FF2BAE}"/>
+    <hyperlink ref="J657" r:id="rId401" xr:uid="{C30AD87E-22CD-461F-92CB-90CA2A6A2886}"/>
+    <hyperlink ref="J663" r:id="rId402" xr:uid="{41B74882-8D85-4131-ACFA-4A51BFB846CD}"/>
+    <hyperlink ref="J664" r:id="rId403" xr:uid="{06E4820C-01DB-46FC-A73C-5E756415CA19}"/>
+    <hyperlink ref="J665" r:id="rId404" xr:uid="{4574F89A-970A-491E-9AF4-C5F17252F1B6}"/>
+    <hyperlink ref="J666" r:id="rId405" xr:uid="{69AB9384-60E8-4F9A-8F01-5C5D86132A82}"/>
+    <hyperlink ref="J667" r:id="rId406" xr:uid="{D32775BA-433C-40CF-82DA-706D1F4FE49D}"/>
+    <hyperlink ref="J668" r:id="rId407" xr:uid="{5B2C401C-EB35-4750-B192-5970C6C21DFB}"/>
+    <hyperlink ref="J669" r:id="rId408" xr:uid="{1658F4EB-1A8A-4096-9108-697E2C146982}"/>
+    <hyperlink ref="J670" r:id="rId409" xr:uid="{95046918-7B19-457B-BDB3-55943EED92E9}"/>
+    <hyperlink ref="J671" r:id="rId410" xr:uid="{0A9CA0E2-4ACF-44AA-ACD5-B6DF5606547D}"/>
+    <hyperlink ref="J672" r:id="rId411" xr:uid="{CD004410-6980-4716-B658-A07F81907772}"/>
+    <hyperlink ref="J673" r:id="rId412" xr:uid="{7C540C45-E4BB-4D92-8668-22F4EDB0F38F}"/>
+    <hyperlink ref="J674" r:id="rId413" xr:uid="{3D7F9E6B-7207-49FE-A4DB-D96CF9F5F414}"/>
+    <hyperlink ref="J675" r:id="rId414" xr:uid="{997B3917-8171-4F89-AD82-D096E83ADCB9}"/>
+    <hyperlink ref="J676" r:id="rId415" xr:uid="{53F87F00-6B0F-4347-BA46-E77C3A808C62}"/>
+    <hyperlink ref="J677" r:id="rId416" xr:uid="{E9F2CBA1-B389-4A12-BD4C-2F19079CDEBD}"/>
+    <hyperlink ref="J679" r:id="rId417" xr:uid="{1459B90F-505E-4903-9E46-9F82175B6C0D}"/>
+    <hyperlink ref="J682" r:id="rId418" xr:uid="{2C36D0BC-C1C6-4C68-8410-B786ADFA663D}"/>
+    <hyperlink ref="J683" r:id="rId419" xr:uid="{00C850C3-7A94-4BE8-82F4-AC648CDCFF78}"/>
+    <hyperlink ref="J684" r:id="rId420" xr:uid="{7F25F684-2B4A-4EBA-8E4D-6D5115504278}"/>
+    <hyperlink ref="J688" r:id="rId421" xr:uid="{C50A884E-2AFF-430C-8BFE-DD1BACC0033C}"/>
+    <hyperlink ref="J693" r:id="rId422" xr:uid="{EFBA682D-6DAE-4B94-B5FC-3CCF2954E3A7}"/>
+    <hyperlink ref="J694" r:id="rId423" xr:uid="{60D16EB6-6E42-4FC1-B576-3C850515CECB}"/>
+    <hyperlink ref="J695" r:id="rId424" xr:uid="{E81C935C-27D7-48E0-8816-8E75A7D38DE5}"/>
+    <hyperlink ref="J696" r:id="rId425" xr:uid="{B9236F26-1F27-49E2-AB9D-70C81707D06F}"/>
+    <hyperlink ref="J697" r:id="rId426" xr:uid="{5B58888B-5607-4821-AD44-CDCEF3EA9373}"/>
+    <hyperlink ref="J698" r:id="rId427" xr:uid="{A4080D31-1B75-4DE2-9D07-FBEC09A7C845}"/>
+    <hyperlink ref="J699" r:id="rId428" xr:uid="{2B6476F0-CB8E-4897-A588-DCFBC4696973}"/>
+    <hyperlink ref="J700" r:id="rId429" xr:uid="{846EF911-7BD7-4C74-9D42-9FE63A27E599}"/>
+    <hyperlink ref="J705" r:id="rId430" xr:uid="{08AE60C6-ED41-4E36-9D0B-5B0B124939D2}"/>
+    <hyperlink ref="J708" r:id="rId431" xr:uid="{86A1F00B-0431-49CB-A382-AD16327D305A}"/>
+    <hyperlink ref="J712" r:id="rId432" xr:uid="{FA0FCD59-A676-49DC-B341-B83EB86D3A62}"/>
+    <hyperlink ref="J713" r:id="rId433" xr:uid="{4B8E0A96-E39F-492F-B4F0-B18B090AB7C7}"/>
+    <hyperlink ref="J714" r:id="rId434" xr:uid="{C7266224-9494-47E2-8DA7-235EB39D00DA}"/>
+    <hyperlink ref="J715" r:id="rId435" xr:uid="{49A3DC4C-2DC3-4383-882D-96F4FC48435E}"/>
+    <hyperlink ref="J718" r:id="rId436" xr:uid="{0CF34283-3A85-4AF9-B374-DD6700031C69}"/>
+    <hyperlink ref="J720" r:id="rId437" xr:uid="{0B5CFC97-7828-4492-8298-2B832580E309}"/>
+    <hyperlink ref="J721" r:id="rId438" xr:uid="{027A1696-CD4F-47B7-AC4B-58B437B317CC}"/>
+    <hyperlink ref="J722" r:id="rId439" xr:uid="{2D779115-B7C3-47C8-A255-17D0C50B840B}"/>
+    <hyperlink ref="J725" r:id="rId440" xr:uid="{C9446CA1-0823-43EC-B945-149F19AEC02D}"/>
+    <hyperlink ref="J726" r:id="rId441" xr:uid="{5CA857F9-67D7-4DC2-BE76-E60CE85D3EFE}"/>
+    <hyperlink ref="J728" r:id="rId442" xr:uid="{47653339-ADF7-43E2-81B0-C50D2826612E}"/>
+    <hyperlink ref="J729" r:id="rId443" xr:uid="{3EE2BB48-547B-4403-A3FF-CACDCB00C276}"/>
+    <hyperlink ref="J736" r:id="rId444" xr:uid="{78372A6A-CE55-4639-BF5E-AA77CA398F46}"/>
+    <hyperlink ref="J738" r:id="rId445" xr:uid="{90D3B4B2-F4EE-4B92-BFF5-FAD5D437A863}"/>
+    <hyperlink ref="J739" r:id="rId446" xr:uid="{BDE26A42-5B63-4843-B945-AB7C9B335800}"/>
+    <hyperlink ref="J740" r:id="rId447" xr:uid="{34213911-A598-4939-8E59-4ABACCB2068C}"/>
+    <hyperlink ref="J741" r:id="rId448" xr:uid="{2C1B0C94-0BC8-4A74-8761-86A8A9CE4FAC}"/>
+    <hyperlink ref="J742" r:id="rId449" xr:uid="{7CC15809-CD84-43A5-8260-06E94653C644}"/>
+    <hyperlink ref="J743" r:id="rId450" xr:uid="{E8359A19-C282-4875-B163-786A1B5440C6}"/>
+    <hyperlink ref="J744" r:id="rId451" xr:uid="{21F17BFD-F853-41CD-ACF9-90E1CB0D99F5}"/>
+    <hyperlink ref="J747" r:id="rId452" xr:uid="{B4B6AE36-4731-4542-BBD9-9A203A52527E}"/>
+    <hyperlink ref="J748" r:id="rId453" xr:uid="{6592A409-007D-4DE3-9935-F13EB7C6CCB5}"/>
+    <hyperlink ref="J757" r:id="rId454" xr:uid="{D97E96E8-5F4B-4F73-8B8F-B4EAACE42DAB}"/>
+    <hyperlink ref="J758" r:id="rId455" xr:uid="{E7EF9DDC-2BC7-4629-BED4-926A077C0A18}"/>
+    <hyperlink ref="J759" r:id="rId456" xr:uid="{C32371DF-B1B2-42C8-A812-6E7A564DDEC1}"/>
+    <hyperlink ref="J760" r:id="rId457" xr:uid="{79F84BE1-0C59-4757-B3D9-BAB125453CA7}"/>
+    <hyperlink ref="J761" r:id="rId458" xr:uid="{8FF51F2D-777A-4AF4-8CE2-2EAB5331BE4A}"/>
+    <hyperlink ref="J762" r:id="rId459" xr:uid="{8D12639E-489C-4250-BB0C-7AF0CBD162EC}"/>
+    <hyperlink ref="J764" r:id="rId460" xr:uid="{704AC996-3B27-4A42-9FEC-12D65CCE0288}"/>
+    <hyperlink ref="J765" r:id="rId461" xr:uid="{97A45E87-4F6E-4CBE-A774-A2E507837E4C}"/>
+    <hyperlink ref="J766" r:id="rId462" xr:uid="{BBF67078-76BF-4F1E-ABCF-DA2223C92313}"/>
+    <hyperlink ref="J767" r:id="rId463" xr:uid="{57101E3C-9C11-4F4E-8F49-E7DF50A4EA11}"/>
+    <hyperlink ref="J769" r:id="rId464" xr:uid="{BF285C3B-5534-4CC3-B7BE-67431C834FE1}"/>
+    <hyperlink ref="J770" r:id="rId465" xr:uid="{9CD2072C-754B-42DB-9040-2F6DA224F7FF}"/>
+    <hyperlink ref="J772" r:id="rId466" xr:uid="{396B1ACB-CFD8-4928-B731-057A1E811F8A}"/>
+    <hyperlink ref="J774" r:id="rId467" xr:uid="{54B1106D-D2C0-466A-BEB5-01DF6541132A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId468"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId469"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos junio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DBED0C-ABE9-41FA-8362-5FDB246545AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A410E716-4BB1-45A7-8F92-C5C43B682992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Rechazos Calle" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$776</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$838</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6759" uniqueCount="2145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7314" uniqueCount="2307">
   <si>
     <t>Fecha</t>
   </si>
@@ -6487,6 +6487,497 @@
   </si>
   <si>
     <t>Dice que lo esperaba hace dos semanas</t>
+  </si>
+  <si>
+    <t>MQL0J89BP0MG</t>
+  </si>
+  <si>
+    <t>10 satur salados</t>
+  </si>
+  <si>
+    <t>MQL0JD953Q0B</t>
+  </si>
+  <si>
+    <t>11:18 a. m.</t>
+  </si>
+  <si>
+    <t>10 galletas salvado individual y 6 galletas salvado tripack</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781878662/rg6m44ktkxvtmuzsotfa.jpg</t>
+  </si>
+  <si>
+    <t>MQL0JMSY96AH</t>
+  </si>
+  <si>
+    <t>MQL0YKMSR0AP</t>
+  </si>
+  <si>
+    <t>Pep común . Lo otro recibe</t>
+  </si>
+  <si>
+    <t>MQL160KJ8XBX</t>
+  </si>
+  <si>
+    <t>11:35 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781879727/d4xpst2wqga9nx4njwyi.jpg</t>
+  </si>
+  <si>
+    <t>MQL1EY8602WT</t>
+  </si>
+  <si>
+    <t>Cerrado se pasó 11:42</t>
+  </si>
+  <si>
+    <t>MQL1R0IZ055G</t>
+  </si>
+  <si>
+    <t>Faltó 3 mani con piel 75gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781880701/r7bnvagnugj3i76kakau.jpg</t>
+  </si>
+  <si>
+    <t>MQL2E1479DKW</t>
+  </si>
+  <si>
+    <t>Falta 5 cheetos 43
+Falta 1 cheetos 85
+Falta 2 3D 85</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781881792/brxiwlpg8wp7ksxdmlbn.jpg</t>
+  </si>
+  <si>
+    <t>MQL2R0DT64EZ</t>
+  </si>
+  <si>
+    <t>3 lays panceta 77gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781882381/jg60trazayipdu3wqixc.jpg</t>
+  </si>
+  <si>
+    <t>MQL36F4VEL7X</t>
+  </si>
+  <si>
+    <t>MQL39L3HRHNS</t>
+  </si>
+  <si>
+    <t>MQL3SMQQGQ6Q</t>
+  </si>
+  <si>
+    <t>Tostito y ondulado de 80</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781884132/f0kbtun1clwotveavwqd.jpg</t>
+  </si>
+  <si>
+    <t>MQL45LVXE1RM</t>
+  </si>
+  <si>
+    <t>El pedido lo esperaba el día lunes rechaza porque está sin dinero para pepsico</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781884734/uqagzl5tmynhmjthnp99.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Sabia que se entregaba el viernes
+Cliente sin dinero</t>
+  </si>
+  <si>
+    <t>MQL45Y692RZ2</t>
+  </si>
+  <si>
+    <t>3 maniax japones jamón 95gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781884759/po5ycbczjy9fbbqtnblm.jpg</t>
+  </si>
+  <si>
+    <t>MQL4C3AVO7GY</t>
+  </si>
+  <si>
+    <t>Rollo susex x 3</t>
+  </si>
+  <si>
+    <t>MQL4FLK2S6XW</t>
+  </si>
+  <si>
+    <t>Alf fantoche super dulce de leche sin stock</t>
+  </si>
+  <si>
+    <t>MQL4SR6OAX11</t>
+  </si>
+  <si>
+    <t>MQL4VPE1VKS9</t>
+  </si>
+  <si>
+    <t>Faltan 3 doritos 40g</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781885965/u2k4pqh8q2zsxdebq8yp.jpg</t>
+  </si>
+  <si>
+    <t>MQL4WDEHZA3R</t>
+  </si>
+  <si>
+    <t>01:20 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781885990/fwodk2nl05w0gcektk6w.jpg</t>
+  </si>
+  <si>
+    <t>MQL5OIXGI0SA</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781887302/syop2irvbmwjm55cuxzl.jpg</t>
+  </si>
+  <si>
+    <t>MQL635T08PEK</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781887982/ng6ikizdkhsj1q2mqbjr.jpg</t>
+  </si>
+  <si>
+    <t>MQL6XNXLLT4N</t>
+  </si>
+  <si>
+    <t>MQL78I78TXKH</t>
+  </si>
+  <si>
+    <t>02:25 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781889914/sjckonxmptlz8aoygdf9.jpg</t>
+  </si>
+  <si>
+    <t>MQL79N8OS1X1</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781889967/lhoscw7mf3fjxqjjuwv3.jpg</t>
+  </si>
+  <si>
+    <t>MQL7AMMOKDXQ</t>
+  </si>
+  <si>
+    <t>02:27 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781890013/ahgpqxadiayla5oyqtne.jpg</t>
+  </si>
+  <si>
+    <t>MQL7BTJO0OIO</t>
+  </si>
+  <si>
+    <t>02:28 p. m.</t>
+  </si>
+  <si>
+    <t>Mani sal con piel</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781890077/sy3bofnstuo09gqz2gip.jpg</t>
+  </si>
+  <si>
+    <t>MQL7D225H0CO</t>
+  </si>
+  <si>
+    <t>02:29 p. m.</t>
+  </si>
+  <si>
+    <t>Fantoche súper dulce de leche</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781890145/tvtkz6pt9mwpwoiuwwfs.jpg</t>
+  </si>
+  <si>
+    <t>MQL7EJ4FWRV5</t>
+  </si>
+  <si>
+    <t>Pidió chocolate full maní no alfajores</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781890198/ul3u4tiqsa0atjvzsryt.jpg</t>
+  </si>
+  <si>
+    <t>MQL7FUWZCB9M</t>
+  </si>
+  <si>
+    <t>Faltó 4 lays panceta</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781890258/ltsqu3iujruynhftpuom.jpg</t>
+  </si>
+  <si>
+    <t>MQL7GX6EE35I</t>
+  </si>
+  <si>
+    <t>Faltó lays panceta</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781890308/kgmudkjeynzny49iirmf.jpg</t>
+  </si>
+  <si>
+    <t>MQL7WB05ZFZC</t>
+  </si>
+  <si>
+    <t>02:43 p. m.</t>
+  </si>
+  <si>
+    <t>Faltó 3 queso cebolla</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Se descuenta lo faltante</t>
+  </si>
+  <si>
+    <t>MQL833VHAYFB</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781891338/rja2joznqg6t3jmmf8ti.jpg</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — El cliente cierra 14 hs</t>
+  </si>
+  <si>
+    <t>MQL83FB5AM71</t>
+  </si>
+  <si>
+    <t>MQL869OIR6A3</t>
+  </si>
+  <si>
+    <t>Se factura 2 veces está boleta</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781891487/gpob6myenmufxakz7jkj.jpg</t>
+  </si>
+  <si>
+    <t>MQL87IN5P0WR</t>
+  </si>
+  <si>
+    <t>02:52 p. m.</t>
+  </si>
+  <si>
+    <t>No hay mas negocio en esa dirección</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781891544/cvtp7frlelraiudcmsmg.jpg</t>
+  </si>
+  <si>
+    <t>MQL872SNTRKC</t>
+  </si>
+  <si>
+    <t>Rechaza esta boleta repetida</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781891520/vbwdvjtsciaydaolwwsk.jpg</t>
+  </si>
+  <si>
+    <t>MQL88LI1850H</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781891595/kyroukrupshdpilyietv.jpg</t>
+  </si>
+  <si>
+    <t>MQL89F1AYU2H</t>
+  </si>
+  <si>
+    <t>02:54 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781891640/gjwqehwn6risbud94mnv.jpg</t>
+  </si>
+  <si>
+    <t>MQL8UFDUKOMF</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781892616/i21vrflbdjhxiewjlpkk.jpg</t>
+  </si>
+  <si>
+    <t>MQL8X2V0X03K</t>
+  </si>
+  <si>
+    <t>03:14 p. m.</t>
+  </si>
+  <si>
+    <t>Rechaza molinos
+No tiene para pagar los 2 pedidos</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781892810/vcysphylkxmk6deryinr.jpg</t>
+  </si>
+  <si>
+    <t>MQL9L5M4QILT</t>
+  </si>
+  <si>
+    <t>03:31 p. m.</t>
+  </si>
+  <si>
+    <t>Satur roto una unidad</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781893880/nrfqkiju3myuzp3ltgna.jpg</t>
+  </si>
+  <si>
+    <t>MQL9S5OSNMM5</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781894187/ykln6igdpeckni54jurx.jpg</t>
+  </si>
+  <si>
+    <t>MQLANT112WFR</t>
+  </si>
+  <si>
+    <t>No quiso este combo</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781895665/itwroszrbjh56a1u1cqq.jpg</t>
+  </si>
+  <si>
+    <t>MQLBTWR2J1US</t>
+  </si>
+  <si>
+    <t>04:34 p. m.</t>
+  </si>
+  <si>
+    <t>4 tf ladysoft rosa 16x20</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781897634/vfcixbkir15bubjvx1sx.jpg</t>
+  </si>
+  <si>
+    <t>MQLDCUARLQ5Y</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781900190/svxrhj5vbjgndwroyvoh.jpg</t>
+  </si>
+  <si>
+    <t>MQLDOCJ0762G</t>
+  </si>
+  <si>
+    <t>05:25 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1781900731/k1ajuzo9o32q24k8kdmk.jpg</t>
+  </si>
+  <si>
+    <t>MQMNX3FSAV0Z</t>
+  </si>
+  <si>
+    <t>03:00 p. m.</t>
+  </si>
+  <si>
+    <t>Cerrado por feriado</t>
+  </si>
+  <si>
+    <t>MQMNY4ZA1B76</t>
+  </si>
+  <si>
+    <t>MQNWFH1B2JPO</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782053184/a15jwr0xvh6fk6vqbxz4.jpg</t>
+  </si>
+  <si>
+    <t>MQNWHJPDHAAE</t>
+  </si>
+  <si>
+    <t>11:49 a. m.</t>
+  </si>
+  <si>
+    <t>No quizo 20 satur salado y 10satur agridulce</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782053269/j1fxhigb0liwb6lzhkvj.jpg</t>
+  </si>
+  <si>
+    <t>MQNWKYWB0WU3</t>
+  </si>
+  <si>
+    <t>Faltaron 5 de asado de 77g</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782053444/msrzcefrmxndjyqtonah.jpg</t>
+  </si>
+  <si>
+    <t>MQP60ZCG2GFU</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782129749/kytapba8shvudavowltb.jpg</t>
+  </si>
+  <si>
+    <t>MQP6AWVM3J7O</t>
+  </si>
+  <si>
+    <t>09:10 a. m.</t>
+  </si>
+  <si>
+    <t>Maxx tachas</t>
+  </si>
+  <si>
+    <t>MQP76E1FXVYK</t>
+  </si>
+  <si>
+    <t>Rechaza . Chipa x12 
+12 café x 50</t>
+  </si>
+  <si>
+    <t>MQP798P0VAFB</t>
+  </si>
+  <si>
+    <t>09:37 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782131862/cr1unl6k3c0ge138ecnc.jpg</t>
+  </si>
+  <si>
+    <t>MQP7GBXDYUH2</t>
+  </si>
+  <si>
+    <t>Rechaza únicamente las yerbas</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782132149/kidvuu3rsgisioutxnmk.jpg</t>
+  </si>
+  <si>
+    <t>MQP7QL63CG7G</t>
+  </si>
+  <si>
+    <t>Suerox frutilla fecha corta</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782132628/udxedh5rvslzfejoeesb.jpg</t>
+  </si>
+  <si>
+    <t>MQP7YHII2NHU</t>
+  </si>
+  <si>
+    <t>Cargaron 3D</t>
+  </si>
+  <si>
+    <t>MQP8BFR4X399</t>
+  </si>
+  <si>
+    <t>12 pilas aa</t>
+  </si>
+  <si>
+    <t>MQP8R8R4G2PX</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782134337/clyywyy1vqghe2wbj0ha.jpg</t>
+  </si>
+  <si>
+    <t>MQP8WFW6O5TU</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782134577/xzn7a6w2ohcdgveg3q3w.jpg</t>
+  </si>
+  <si>
+    <t>MQP8ZH3NM6HE</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782134716/cbkbgaljwwbcpwsmvbep.jpg</t>
   </si>
 </sst>
 </file>
@@ -6874,8 +7365,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N776">
-  <autoFilter ref="A1:N776" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N838">
+  <autoFilter ref="A1:N838" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fecha"/>
@@ -7097,7 +7588,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N776"/>
+  <dimension ref="A1:N838"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -35371,10 +35862,14 @@
         <v>1928</v>
       </c>
       <c r="J685" s="8"/>
-      <c r="K685" s="8"/>
-      <c r="L685" s="8"/>
+      <c r="K685" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L685" s="4">
+        <v>46195</v>
+      </c>
       <c r="M685" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N685" s="24">
         <v>6</v>
@@ -38821,10 +39316,14 @@
       <c r="J770" s="11" t="s">
         <v>2132</v>
       </c>
-      <c r="K770" s="8"/>
-      <c r="L770" s="8"/>
+      <c r="K770" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L770" s="4">
+        <v>46192</v>
+      </c>
       <c r="M770" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N770" s="24">
         <v>6</v>
@@ -38859,10 +39358,14 @@
         <v>2134</v>
       </c>
       <c r="J771" s="8"/>
-      <c r="K771" s="8"/>
-      <c r="L771" s="8"/>
+      <c r="K771" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L771" s="4">
+        <v>46192</v>
+      </c>
       <c r="M771" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N771" s="24">
         <v>6</v>
@@ -39074,480 +39577,3086 @@
         <v>6</v>
       </c>
     </row>
+    <row r="777" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A777" s="3" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B777" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C777" s="5" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D777" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E777" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F777" s="6">
+        <v>2177</v>
+      </c>
+      <c r="G777" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H777" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I777" s="5" t="s">
+        <v>2146</v>
+      </c>
+      <c r="J777" s="8"/>
+      <c r="K777" s="8"/>
+      <c r="L777" s="8"/>
+      <c r="M777" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N777" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="778" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A778" s="3" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B778" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C778" s="5" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D778" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E778" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F778" s="6">
+        <v>1852</v>
+      </c>
+      <c r="G778" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H778" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I778" s="5" t="s">
+        <v>2149</v>
+      </c>
+      <c r="J778" s="11" t="s">
+        <v>2150</v>
+      </c>
+      <c r="K778" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L778" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M778" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N778" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="779" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A779" s="3" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B779" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C779" s="13">
+        <v>0.47152777777777777</v>
+      </c>
+      <c r="D779" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E779" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F779" s="6">
+        <v>6218</v>
+      </c>
+      <c r="G779" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H779" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I779" s="8"/>
+      <c r="J779" s="8"/>
+      <c r="K779" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L779" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M779" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N779" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="780" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A780" s="3" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B780" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C780" s="5" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D780" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E780" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F780" s="6">
+        <v>6110</v>
+      </c>
+      <c r="G780" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H780" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I780" s="5" t="s">
+        <v>2153</v>
+      </c>
+      <c r="J780" s="8"/>
+      <c r="K780" s="5" t="s">
+        <v>1655</v>
+      </c>
+      <c r="L780" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M780" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N780" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="781" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A781" s="3" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B781" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C781" s="5" t="s">
+        <v>2155</v>
+      </c>
+      <c r="D781" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E781" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F781" s="6">
+        <v>2822</v>
+      </c>
+      <c r="G781" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H781" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I781" s="8"/>
+      <c r="J781" s="11" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K781" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L781" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M781" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N781" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="782" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A782" s="3" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B782" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C782" s="5" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D782" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E782" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F782" s="6">
+        <v>3835</v>
+      </c>
+      <c r="G782" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H782" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I782" s="5" t="s">
+        <v>2158</v>
+      </c>
+      <c r="J782" s="8"/>
+      <c r="K782" s="8"/>
+      <c r="L782" s="8"/>
+      <c r="M782" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N782" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="783" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A783" s="3" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B783" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C783" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D783" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E783" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F783" s="6">
+        <v>10741</v>
+      </c>
+      <c r="G783" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H783" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I783" s="5" t="s">
+        <v>2160</v>
+      </c>
+      <c r="J783" s="11" t="s">
+        <v>2161</v>
+      </c>
+      <c r="K783" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L783" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M783" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N783" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="784" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A784" s="3" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B784" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C784" s="13">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="D784" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E784" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F784" s="6">
+        <v>3284</v>
+      </c>
+      <c r="G784" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="H784" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I784" s="5" t="s">
+        <v>2163</v>
+      </c>
+      <c r="J784" s="11" t="s">
+        <v>2164</v>
+      </c>
+      <c r="K784" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L784" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M784" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N784" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="785" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A785" s="3" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B785" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C785" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="D785" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E785" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F785" s="6">
+        <v>2117</v>
+      </c>
+      <c r="G785" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H785" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I785" s="5" t="s">
+        <v>2166</v>
+      </c>
+      <c r="J785" s="11" t="s">
+        <v>2167</v>
+      </c>
+      <c r="K785" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L785" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M785" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N785" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="786" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A786" s="3" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B786" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C786" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="D786" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E786" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F786" s="6">
+        <v>4591</v>
+      </c>
+      <c r="G786" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="H786" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I786" s="8"/>
+      <c r="J786" s="8"/>
+      <c r="K786" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L786" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M786" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N786" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="787" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A787" s="3" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B787" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C787" s="5" t="s">
+        <v>947</v>
+      </c>
+      <c r="D787" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E787" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F787" s="6">
+        <v>3226</v>
+      </c>
+      <c r="G787" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H787" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I787" s="8"/>
+      <c r="J787" s="8"/>
+      <c r="K787" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L787" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M787" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N787" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="788" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A788" s="3" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B788" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C788" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="D788" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E788" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F788" s="6">
+        <v>6715</v>
+      </c>
+      <c r="G788" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H788" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I788" s="5" t="s">
+        <v>2171</v>
+      </c>
+      <c r="J788" s="11" t="s">
+        <v>2172</v>
+      </c>
+      <c r="K788" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L788" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M788" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N788" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="789" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A789" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B789" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C789" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D789" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E789" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F789" s="6">
+        <v>6737</v>
+      </c>
+      <c r="G789" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H789" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I789" s="5" t="s">
+        <v>2174</v>
+      </c>
+      <c r="J789" s="11" t="s">
+        <v>2175</v>
+      </c>
+      <c r="K789" s="5" t="s">
+        <v>2176</v>
+      </c>
+      <c r="L789" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M789" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N789" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="790" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A790" s="3" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B790" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C790" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D790" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E790" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F790" s="6">
+        <v>2773</v>
+      </c>
+      <c r="G790" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H790" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I790" s="5" t="s">
+        <v>2178</v>
+      </c>
+      <c r="J790" s="11" t="s">
+        <v>2179</v>
+      </c>
+      <c r="K790" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L790" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M790" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N790" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="791" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A791" s="3" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B791" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C791" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="D791" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E791" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F791" s="6">
+        <v>4622</v>
+      </c>
+      <c r="G791" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H791" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I791" s="5" t="s">
+        <v>2181</v>
+      </c>
+      <c r="J791" s="8"/>
+      <c r="K791" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L791" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M791" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N791" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="792" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A792" s="3" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B792" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C792" s="5" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D792" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E792" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F792" s="6">
+        <v>7065</v>
+      </c>
+      <c r="G792" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H792" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I792" s="5" t="s">
+        <v>2183</v>
+      </c>
+      <c r="J792" s="8"/>
+      <c r="K792" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="L792" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M792" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N792" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="793" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A793" s="3" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B793" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C793" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="D793" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E793" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F793" s="6">
+        <v>4316</v>
+      </c>
+      <c r="G793" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="H793" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I793" s="8"/>
+      <c r="J793" s="8"/>
+      <c r="K793" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L793" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M793" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N793" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="794" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A794" s="3" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B794" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C794" s="13">
+        <v>0.55486111111111114</v>
+      </c>
+      <c r="D794" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E794" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F794" s="6">
+        <v>3156</v>
+      </c>
+      <c r="G794" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H794" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I794" s="5" t="s">
+        <v>2186</v>
+      </c>
+      <c r="J794" s="11" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K794" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L794" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M794" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N794" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="795" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A795" s="3" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B795" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C795" s="5" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D795" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E795" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F795" s="6">
+        <v>2098</v>
+      </c>
+      <c r="G795" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H795" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I795" s="8"/>
+      <c r="J795" s="11" t="s">
+        <v>2190</v>
+      </c>
+      <c r="K795" s="8"/>
+      <c r="L795" s="8"/>
+      <c r="M795" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N795" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="796" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A796" s="3" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B796" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C796" s="5" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D796" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E796" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F796" s="6">
+        <v>1302</v>
+      </c>
+      <c r="G796" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H796" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I796" s="8"/>
+      <c r="J796" s="11" t="s">
+        <v>2192</v>
+      </c>
+      <c r="K796" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L796" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M796" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N796" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="797" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A797" s="3" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B797" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C797" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="D797" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E797" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F797" s="6">
+        <v>6213</v>
+      </c>
+      <c r="G797" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H797" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I797" s="8"/>
+      <c r="J797" s="11" t="s">
+        <v>2194</v>
+      </c>
+      <c r="K797" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L797" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M797" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N797" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="798" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A798" s="3" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B798" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C798" s="5" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D798" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E798" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F798" s="6">
+        <v>2827</v>
+      </c>
+      <c r="G798" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H798" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I798" s="8"/>
+      <c r="J798" s="8"/>
+      <c r="K798" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L798" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M798" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N798" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="799" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A799" s="3" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B799" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C799" s="5" t="s">
+        <v>2197</v>
+      </c>
+      <c r="D799" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E799" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F799" s="6">
+        <v>6928</v>
+      </c>
+      <c r="G799" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H799" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I799" s="8"/>
+      <c r="J799" s="11" t="s">
+        <v>2198</v>
+      </c>
+      <c r="K799" s="8"/>
+      <c r="L799" s="8"/>
+      <c r="M799" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N799" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="800" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A800" s="3" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B800" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C800" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="D800" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E800" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F800" s="6">
+        <v>6919</v>
+      </c>
+      <c r="G800" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H800" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I800" s="8"/>
+      <c r="J800" s="11" t="s">
+        <v>2200</v>
+      </c>
+      <c r="K800" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L800" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M800" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N800" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="801" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A801" s="3" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B801" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C801" s="5" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D801" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E801" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F801" s="6">
+        <v>7237</v>
+      </c>
+      <c r="G801" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H801" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I801" s="8"/>
+      <c r="J801" s="11" t="s">
+        <v>2203</v>
+      </c>
+      <c r="K801" s="8"/>
+      <c r="L801" s="8"/>
+      <c r="M801" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N801" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="802" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A802" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B802" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C802" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D802" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E802" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F802" s="6">
+        <v>7245</v>
+      </c>
+      <c r="G802" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H802" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I802" s="5" t="s">
+        <v>2206</v>
+      </c>
+      <c r="J802" s="11" t="s">
+        <v>2207</v>
+      </c>
+      <c r="K802" s="8"/>
+      <c r="L802" s="8"/>
+      <c r="M802" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N802" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="803" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A803" s="3" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B803" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C803" s="5" t="s">
+        <v>2209</v>
+      </c>
+      <c r="D803" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E803" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F803" s="6">
+        <v>7237</v>
+      </c>
+      <c r="G803" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H803" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I803" s="5" t="s">
+        <v>2210</v>
+      </c>
+      <c r="J803" s="11" t="s">
+        <v>2211</v>
+      </c>
+      <c r="K803" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="L803" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M803" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N803" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="804" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A804" s="3" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B804" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C804" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="D804" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E804" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F804" s="6">
+        <v>6963</v>
+      </c>
+      <c r="G804" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H804" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I804" s="5" t="s">
+        <v>2213</v>
+      </c>
+      <c r="J804" s="11" t="s">
+        <v>2214</v>
+      </c>
+      <c r="K804" s="8"/>
+      <c r="L804" s="8"/>
+      <c r="M804" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N804" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="805" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A805" s="3" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B805" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C805" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D805" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E805" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F805" s="6">
+        <v>6953</v>
+      </c>
+      <c r="G805" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H805" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I805" s="5" t="s">
+        <v>2216</v>
+      </c>
+      <c r="J805" s="11" t="s">
+        <v>2217</v>
+      </c>
+      <c r="K805" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L805" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M805" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N805" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="806" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A806" s="3" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B806" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C806" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D806" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E806" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F806" s="6">
+        <v>6964</v>
+      </c>
+      <c r="G806" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H806" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I806" s="5" t="s">
+        <v>2219</v>
+      </c>
+      <c r="J806" s="11" t="s">
+        <v>2220</v>
+      </c>
+      <c r="K806" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L806" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M806" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N806" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="807" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A807" s="3" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B807" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C807" s="5" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D807" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E807" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F807" s="6">
+        <v>5817</v>
+      </c>
+      <c r="G807" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H807" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I807" s="5" t="s">
+        <v>2223</v>
+      </c>
+      <c r="J807" s="8"/>
+      <c r="K807" s="5" t="s">
+        <v>2224</v>
+      </c>
+      <c r="L807" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M807" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N807" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="808" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A808" s="3" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B808" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C808" s="5" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D808" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E808" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F808" s="6">
+        <v>6679</v>
+      </c>
+      <c r="G808" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H808" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I808" s="8"/>
+      <c r="J808" s="11" t="s">
+        <v>2226</v>
+      </c>
+      <c r="K808" s="5" t="s">
+        <v>2227</v>
+      </c>
+      <c r="L808" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M808" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N808" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="809" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A809" s="3" t="s">
+        <v>2228</v>
+      </c>
+      <c r="B809" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C809" s="5" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D809" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E809" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F809" s="6">
+        <v>11170</v>
+      </c>
+      <c r="G809" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H809" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I809" s="8"/>
+      <c r="J809" s="8"/>
+      <c r="K809" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L809" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M809" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N809" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="810" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A810" s="3" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B810" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C810" s="5" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D810" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E810" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F810" s="6">
+        <v>10934</v>
+      </c>
+      <c r="G810" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H810" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I810" s="5" t="s">
+        <v>2230</v>
+      </c>
+      <c r="J810" s="11" t="s">
+        <v>2231</v>
+      </c>
+      <c r="K810" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L810" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M810" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N810" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="811" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A811" s="3" t="s">
+        <v>2232</v>
+      </c>
+      <c r="B811" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C811" s="5" t="s">
+        <v>2233</v>
+      </c>
+      <c r="D811" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E811" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F811" s="6">
+        <v>4027</v>
+      </c>
+      <c r="G811" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="H811" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="I811" s="5" t="s">
+        <v>2234</v>
+      </c>
+      <c r="J811" s="11" t="s">
+        <v>2235</v>
+      </c>
+      <c r="K811" s="8"/>
+      <c r="L811" s="8"/>
+      <c r="M811" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N811" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="812" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A812" s="3" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B812" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C812" s="13">
+        <v>0.61944444444444446</v>
+      </c>
+      <c r="D812" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E812" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F812" s="6">
+        <v>3152</v>
+      </c>
+      <c r="G812" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H812" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I812" s="5" t="s">
+        <v>2237</v>
+      </c>
+      <c r="J812" s="11" t="s">
+        <v>2238</v>
+      </c>
+      <c r="K812" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L812" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M812" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N812" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="813" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A813" s="3" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B813" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C813" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="D813" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E813" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F813" s="6">
+        <v>5481</v>
+      </c>
+      <c r="G813" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H813" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="I813" s="5" t="s">
+        <v>1913</v>
+      </c>
+      <c r="J813" s="11" t="s">
+        <v>2240</v>
+      </c>
+      <c r="K813" s="8"/>
+      <c r="L813" s="8"/>
+      <c r="M813" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N813" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="814" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A814" s="3" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B814" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C814" s="5" t="s">
+        <v>2242</v>
+      </c>
+      <c r="D814" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E814" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F814" s="6">
+        <v>3986</v>
+      </c>
+      <c r="G814" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H814" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I814" s="8"/>
+      <c r="J814" s="11" t="s">
+        <v>2243</v>
+      </c>
+      <c r="K814" s="8"/>
+      <c r="L814" s="8"/>
+      <c r="M814" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N814" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="815" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A815" s="3" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B815" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C815" s="13">
+        <v>0.63263888888888886</v>
+      </c>
+      <c r="D815" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E815" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F815" s="6">
+        <v>3720</v>
+      </c>
+      <c r="G815" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H815" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I815" s="5" t="s">
+        <v>1408</v>
+      </c>
+      <c r="J815" s="11" t="s">
+        <v>2245</v>
+      </c>
+      <c r="K815" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L815" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M815" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N815" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="816" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A816" s="3" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B816" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C816" s="5" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D816" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E816" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F816" s="6">
+        <v>3221</v>
+      </c>
+      <c r="G816" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H816" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I816" s="5" t="s">
+        <v>2248</v>
+      </c>
+      <c r="J816" s="11" t="s">
+        <v>2249</v>
+      </c>
+      <c r="K816" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L816" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M816" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N816" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="817" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A817" s="3" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B817" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C817" s="5" t="s">
+        <v>2251</v>
+      </c>
+      <c r="D817" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E817" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F817" s="6">
+        <v>3561</v>
+      </c>
+      <c r="G817" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H817" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I817" s="5" t="s">
+        <v>2252</v>
+      </c>
+      <c r="J817" s="11" t="s">
+        <v>2253</v>
+      </c>
+      <c r="K817" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L817" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M817" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N817" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="818" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A818" s="3" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B818" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C818" s="5" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D818" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E818" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F818" s="6">
+        <v>4908</v>
+      </c>
+      <c r="G818" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H818" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I818" s="8"/>
+      <c r="J818" s="11" t="s">
+        <v>2255</v>
+      </c>
+      <c r="K818" s="8"/>
+      <c r="L818" s="8"/>
+      <c r="M818" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N818" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="819" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A819" s="3" t="s">
+        <v>2256</v>
+      </c>
+      <c r="B819" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C819" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="D819" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E819" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F819" s="6">
+        <v>5506</v>
+      </c>
+      <c r="G819" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H819" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I819" s="5" t="s">
+        <v>2257</v>
+      </c>
+      <c r="J819" s="11" t="s">
+        <v>2258</v>
+      </c>
+      <c r="K819" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L819" s="4">
+        <v>46192</v>
+      </c>
+      <c r="M819" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N819" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="820" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A820" s="3" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B820" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C820" s="5" t="s">
+        <v>2260</v>
+      </c>
+      <c r="D820" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E820" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F820" s="6">
+        <v>2074</v>
+      </c>
+      <c r="G820" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H820" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I820" s="5" t="s">
+        <v>2261</v>
+      </c>
+      <c r="J820" s="11" t="s">
+        <v>2262</v>
+      </c>
+      <c r="K820" s="8"/>
+      <c r="L820" s="8"/>
+      <c r="M820" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N820" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="821" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A821" s="3" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B821" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C821" s="5" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D821" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E821" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F821" s="6">
+        <v>2885</v>
+      </c>
+      <c r="G821" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H821" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I821" s="8"/>
+      <c r="J821" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="K821" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L821" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M821" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N821" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="822" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A822" s="3" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B822" s="4">
+        <v>46192</v>
+      </c>
+      <c r="C822" s="5" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D822" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E822" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F822" s="6">
+        <v>3795</v>
+      </c>
+      <c r="G822" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H822" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I822" s="8"/>
+      <c r="J822" s="11" t="s">
+        <v>2267</v>
+      </c>
+      <c r="K822" s="8"/>
+      <c r="L822" s="8"/>
+      <c r="M822" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N822" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="823" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A823" s="3" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B823" s="4">
+        <v>46193</v>
+      </c>
+      <c r="C823" s="5" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D823" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E823" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F823" s="6">
+        <v>37</v>
+      </c>
+      <c r="G823" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H823" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I823" s="5" t="s">
+        <v>2270</v>
+      </c>
+      <c r="J823" s="8"/>
+      <c r="K823" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L823" s="4">
+        <v>46193</v>
+      </c>
+      <c r="M823" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N823" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="824" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A824" s="3" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B824" s="4">
+        <v>46193</v>
+      </c>
+      <c r="C824" s="5" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D824" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E824" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F824" s="6">
+        <v>19</v>
+      </c>
+      <c r="G824" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H824" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I824" s="5" t="s">
+        <v>2270</v>
+      </c>
+      <c r="J824" s="8"/>
+      <c r="K824" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L824" s="4">
+        <v>46193</v>
+      </c>
+      <c r="M824" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N824" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="825" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A825" s="3" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B825" s="4">
+        <v>46194</v>
+      </c>
+      <c r="C825" s="5" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D825" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E825" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F825" s="6">
+        <v>1675</v>
+      </c>
+      <c r="G825" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H825" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I825" s="8"/>
+      <c r="J825" s="11" t="s">
+        <v>2273</v>
+      </c>
+      <c r="K825" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L825" s="4">
+        <v>46194</v>
+      </c>
+      <c r="M825" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N825" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="826" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A826" s="3" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B826" s="4">
+        <v>46194</v>
+      </c>
+      <c r="C826" s="5" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D826" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E826" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F826" s="6">
+        <v>275</v>
+      </c>
+      <c r="G826" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H826" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I826" s="5" t="s">
+        <v>2276</v>
+      </c>
+      <c r="J826" s="11" t="s">
+        <v>2277</v>
+      </c>
+      <c r="K826" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L826" s="4">
+        <v>46194</v>
+      </c>
+      <c r="M826" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N826" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="827" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A827" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B827" s="4">
+        <v>46194</v>
+      </c>
+      <c r="C827" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D827" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E827" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F827" s="6">
+        <v>519</v>
+      </c>
+      <c r="G827" s="5" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H827" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I827" s="5" t="s">
+        <v>2279</v>
+      </c>
+      <c r="J827" s="11" t="s">
+        <v>2280</v>
+      </c>
+      <c r="K827" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L827" s="4">
+        <v>46194</v>
+      </c>
+      <c r="M827" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N827" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="828" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A828" s="3" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B828" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C828" s="5" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D828" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E828" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F828" s="6">
+        <v>2347</v>
+      </c>
+      <c r="G828" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H828" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I828" s="8"/>
+      <c r="J828" s="11" t="s">
+        <v>2282</v>
+      </c>
+      <c r="K828" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L828" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M828" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N828" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="829" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A829" s="3" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B829" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C829" s="5" t="s">
+        <v>2284</v>
+      </c>
+      <c r="D829" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E829" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F829" s="6">
+        <v>7536</v>
+      </c>
+      <c r="G829" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H829" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I829" s="5" t="s">
+        <v>2285</v>
+      </c>
+      <c r="J829" s="8"/>
+      <c r="K829" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L829" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M829" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N829" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="830" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A830" s="3" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B830" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C830" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D830" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E830" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F830" s="6">
+        <v>3681</v>
+      </c>
+      <c r="G830" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H830" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I830" s="5" t="s">
+        <v>2287</v>
+      </c>
+      <c r="J830" s="8"/>
+      <c r="K830" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L830" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M830" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N830" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="831" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A831" s="3" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B831" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C831" s="5" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D831" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E831" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F831" s="6">
+        <v>1888</v>
+      </c>
+      <c r="G831" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H831" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I831" s="8"/>
+      <c r="J831" s="11" t="s">
+        <v>2290</v>
+      </c>
+      <c r="K831" s="8"/>
+      <c r="L831" s="8"/>
+      <c r="M831" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N831" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="832" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A832" s="3" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B832" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C832" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D832" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E832" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F832" s="6">
+        <v>4966</v>
+      </c>
+      <c r="G832" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H832" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I832" s="5" t="s">
+        <v>2292</v>
+      </c>
+      <c r="J832" s="11" t="s">
+        <v>2293</v>
+      </c>
+      <c r="K832" s="8"/>
+      <c r="L832" s="8"/>
+      <c r="M832" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N832" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="833" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A833" s="3" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B833" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C833" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="D833" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E833" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F833" s="6">
+        <v>4062</v>
+      </c>
+      <c r="G833" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H833" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I833" s="5" t="s">
+        <v>2295</v>
+      </c>
+      <c r="J833" s="11" t="s">
+        <v>2296</v>
+      </c>
+      <c r="K833" s="8"/>
+      <c r="L833" s="8"/>
+      <c r="M833" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N833" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="834" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A834" s="3" t="s">
+        <v>2297</v>
+      </c>
+      <c r="B834" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C834" s="13">
+        <v>0.41458333333333336</v>
+      </c>
+      <c r="D834" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E834" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F834" s="6">
+        <v>5554</v>
+      </c>
+      <c r="G834" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H834" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I834" s="5" t="s">
+        <v>2298</v>
+      </c>
+      <c r="J834" s="8"/>
+      <c r="K834" s="8"/>
+      <c r="L834" s="8"/>
+      <c r="M834" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N834" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="835" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A835" s="3" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B835" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C835" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D835" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E835" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F835" s="6">
+        <v>1683</v>
+      </c>
+      <c r="G835" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H835" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I835" s="5" t="s">
+        <v>2300</v>
+      </c>
+      <c r="J835" s="8"/>
+      <c r="K835" s="8"/>
+      <c r="L835" s="8"/>
+      <c r="M835" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N835" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="836" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A836" s="3" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B836" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C836" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D836" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E836" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F836" s="6">
+        <v>4049</v>
+      </c>
+      <c r="G836" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H836" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I836" s="8"/>
+      <c r="J836" s="11" t="s">
+        <v>2302</v>
+      </c>
+      <c r="K836" s="8"/>
+      <c r="L836" s="8"/>
+      <c r="M836" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N836" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="837" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A837" s="3" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B837" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C837" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="D837" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E837" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F837" s="6">
+        <v>4088</v>
+      </c>
+      <c r="G837" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H837" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I837" s="8"/>
+      <c r="J837" s="11" t="s">
+        <v>2304</v>
+      </c>
+      <c r="K837" s="8"/>
+      <c r="L837" s="8"/>
+      <c r="M837" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N837" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="838" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A838" s="3" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B838" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C838" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D838" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E838" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F838" s="6">
+        <v>3236</v>
+      </c>
+      <c r="G838" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H838" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I838" s="5" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J838" s="11" t="s">
+        <v>2306</v>
+      </c>
+      <c r="K838" s="8"/>
+      <c r="L838" s="8"/>
+      <c r="M838" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N838" s="24">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J5" r:id="rId1" xr:uid="{B88996D5-1E93-47D3-9B9D-42040D0097BF}"/>
-    <hyperlink ref="J7" r:id="rId2" xr:uid="{A2C2BD61-46A5-4A18-AE71-0312DA9FA7BA}"/>
-    <hyperlink ref="J8" r:id="rId3" xr:uid="{3AFB78C4-9D4E-4F2A-A6DA-1A50BD9381C5}"/>
-    <hyperlink ref="J10" r:id="rId4" xr:uid="{E42583CD-3494-47A0-A03A-F670E226AA14}"/>
-    <hyperlink ref="J13" r:id="rId5" xr:uid="{A6C68DE7-000A-4B2B-BD99-F6B2C19C194A}"/>
-    <hyperlink ref="J14" r:id="rId6" xr:uid="{72432930-DCEA-4B0F-8503-4BF4FED7A93A}"/>
-    <hyperlink ref="J17" r:id="rId7" xr:uid="{00700B33-6B04-4AD3-8451-D4F79AA7112A}"/>
-    <hyperlink ref="J19" r:id="rId8" xr:uid="{0D23FABC-D87B-4893-98E2-CC265BE75AF4}"/>
-    <hyperlink ref="J20" r:id="rId9" xr:uid="{28D493DD-94DC-4859-9969-65BB25AD51C8}"/>
-    <hyperlink ref="J21" r:id="rId10" xr:uid="{447DC423-AA8B-4247-B2A2-F0CB4C40F294}"/>
-    <hyperlink ref="J24" r:id="rId11" xr:uid="{AFD5E7C3-F1B4-4D58-805B-CF4B8CD0F020}"/>
-    <hyperlink ref="J25" r:id="rId12" xr:uid="{4F4B9C0D-2B68-4FE5-9376-1FF43F140C18}"/>
-    <hyperlink ref="J26" r:id="rId13" xr:uid="{A6D78F7D-2A87-49D0-A276-CC44A3199B9F}"/>
-    <hyperlink ref="J27" r:id="rId14" xr:uid="{4512167F-1AE4-4D5C-9E75-B389C911EA63}"/>
-    <hyperlink ref="J29" r:id="rId15" xr:uid="{FC9AF86A-336B-48C3-9DA3-AC5436C65E98}"/>
-    <hyperlink ref="J30" r:id="rId16" xr:uid="{8D26EC5F-2D3A-4A20-9766-ED681BFF840D}"/>
-    <hyperlink ref="J31" r:id="rId17" xr:uid="{75B3C5FC-935E-4FCC-BA9B-FF37A0C9C3A3}"/>
-    <hyperlink ref="J34" r:id="rId18" xr:uid="{F627A75F-10C5-47EF-9B91-62EA01AD1A97}"/>
-    <hyperlink ref="J35" r:id="rId19" xr:uid="{E4192226-BE39-4863-904B-E1D28756D9DE}"/>
-    <hyperlink ref="J36" r:id="rId20" xr:uid="{A2DBB2A1-8EF7-4C29-B9CB-406175FD4DBE}"/>
-    <hyperlink ref="J37" r:id="rId21" xr:uid="{7F57D855-3760-41EF-97ED-214043EF0B9D}"/>
-    <hyperlink ref="J38" r:id="rId22" xr:uid="{DFB5E4FC-B97A-4992-8486-9DA70E02416C}"/>
-    <hyperlink ref="J46" r:id="rId23" xr:uid="{E93F0C3D-D751-4415-B168-79B60A571F68}"/>
-    <hyperlink ref="J47" r:id="rId24" xr:uid="{2DF34A0A-A4A6-4859-AD6B-0E7A01B59D25}"/>
-    <hyperlink ref="J48" r:id="rId25" xr:uid="{483E8C1E-6AD5-4A35-9BA8-73DAA9D210A8}"/>
-    <hyperlink ref="J49" r:id="rId26" xr:uid="{DEB06DE1-9113-4820-BFED-F3FD4346C7D4}"/>
-    <hyperlink ref="J50" r:id="rId27" xr:uid="{CF892E5A-EED1-463C-B619-81A23289226E}"/>
-    <hyperlink ref="J52" r:id="rId28" xr:uid="{D4ECD12F-9AF0-4326-9349-FAC937EF1635}"/>
-    <hyperlink ref="J53" r:id="rId29" xr:uid="{0DEF4993-7D87-4AD2-9772-DA65FB01B647}"/>
-    <hyperlink ref="J54" r:id="rId30" xr:uid="{3FB151D0-1787-41EE-856E-E4FB3268116C}"/>
-    <hyperlink ref="J56" r:id="rId31" xr:uid="{14534BBF-41B5-45D8-9C39-0E7BF9C00501}"/>
-    <hyperlink ref="J59" r:id="rId32" xr:uid="{DDD1C0DD-645B-402B-ABEB-0428AA35D177}"/>
-    <hyperlink ref="J61" r:id="rId33" xr:uid="{A6FD7A20-E89E-4DB2-86B3-0B440527242C}"/>
-    <hyperlink ref="J62" r:id="rId34" xr:uid="{7C47223A-A2FE-40A2-B63C-499C2930DEF1}"/>
-    <hyperlink ref="J63" r:id="rId35" xr:uid="{96BFB53D-BBB1-4F36-8104-0ACB7CF9F488}"/>
-    <hyperlink ref="J64" r:id="rId36" xr:uid="{35250C88-B635-483F-8071-AC54BC673660}"/>
-    <hyperlink ref="J69" r:id="rId37" xr:uid="{CD28D3FC-B938-493C-9660-F5D03C870D94}"/>
-    <hyperlink ref="J71" r:id="rId38" xr:uid="{2E9542D8-6E35-4B9D-8CE7-1428C759C245}"/>
-    <hyperlink ref="J72" r:id="rId39" xr:uid="{7AE4BFCE-B2C6-4401-8AF1-C861355192C8}"/>
-    <hyperlink ref="J73" r:id="rId40" xr:uid="{4148A84A-4388-4994-9EC0-D8F76320151D}"/>
-    <hyperlink ref="J74" r:id="rId41" xr:uid="{B3C9E6FD-2479-46BE-841D-02629D009755}"/>
-    <hyperlink ref="J75" r:id="rId42" xr:uid="{D0271643-F130-4835-88EB-8411CE97EFF8}"/>
-    <hyperlink ref="J76" r:id="rId43" xr:uid="{30ACD85C-CA03-40B2-893F-9AA2847E322E}"/>
-    <hyperlink ref="J78" r:id="rId44" xr:uid="{E7B6E757-D77B-4DF1-8C70-02F3A3A0BA04}"/>
-    <hyperlink ref="J80" r:id="rId45" xr:uid="{6AACF0F2-C4F7-44AD-9481-69F3ADD398F6}"/>
-    <hyperlink ref="J86" r:id="rId46" xr:uid="{159DE113-54EC-497B-A09A-A63EC6941963}"/>
-    <hyperlink ref="J88" r:id="rId47" xr:uid="{1F13859D-E69D-43C3-B12A-25146A54F769}"/>
-    <hyperlink ref="J89" r:id="rId48" xr:uid="{E35C74E6-710C-4CC5-BFFC-ED87C2B0D3BC}"/>
-    <hyperlink ref="J90" r:id="rId49" xr:uid="{13C3CD02-310B-48C0-9F3D-1BF814CA042E}"/>
-    <hyperlink ref="J92" r:id="rId50" xr:uid="{580C4B01-46ED-4FF3-81CC-E96A2FE99FB9}"/>
-    <hyperlink ref="J94" r:id="rId51" xr:uid="{799618E5-55E8-40C9-930C-422E8623CDFD}"/>
-    <hyperlink ref="J95" r:id="rId52" xr:uid="{E85A4E30-F11F-4A43-A1A8-12A869E267DA}"/>
-    <hyperlink ref="J96" r:id="rId53" xr:uid="{06AB32BA-BC86-4B87-B930-EBD212C200CF}"/>
-    <hyperlink ref="J101" r:id="rId54" xr:uid="{0A4DBD2F-FFFC-4E6D-B0A1-8C91ACF5C9FE}"/>
-    <hyperlink ref="J103" r:id="rId55" xr:uid="{5DCC63BE-4AB0-4B99-9851-A233F04746E9}"/>
-    <hyperlink ref="J104" r:id="rId56" xr:uid="{42644421-339B-407C-BED1-AF0A315C1B31}"/>
-    <hyperlink ref="J105" r:id="rId57" xr:uid="{836D2E43-2990-427C-B914-B9FAC39E0916}"/>
-    <hyperlink ref="J106" r:id="rId58" xr:uid="{45FB1228-B679-47F6-9B02-9D4322C85CFF}"/>
-    <hyperlink ref="J107" r:id="rId59" xr:uid="{1DEAB372-7445-40A4-A735-4959D270133B}"/>
-    <hyperlink ref="J109" r:id="rId60" xr:uid="{772CF91F-1098-44CF-893D-BF21BD3DFD82}"/>
-    <hyperlink ref="J110" r:id="rId61" xr:uid="{7950725E-1BCA-4D36-B6DF-7E26AD7FD801}"/>
-    <hyperlink ref="J111" r:id="rId62" xr:uid="{D95390B9-51D1-4455-84AF-EF5FE71C8592}"/>
-    <hyperlink ref="J112" r:id="rId63" xr:uid="{AAD8376A-F5B2-4D86-8271-9E07A854F5E4}"/>
-    <hyperlink ref="J113" r:id="rId64" xr:uid="{AB2FA5AB-EF4C-4B08-BD3F-BA8BC5CDE703}"/>
-    <hyperlink ref="J114" r:id="rId65" xr:uid="{F8049ED0-F89A-466E-8535-3702B7877D9F}"/>
-    <hyperlink ref="J116" r:id="rId66" xr:uid="{CD057669-F686-439A-955F-43C69707C7AF}"/>
-    <hyperlink ref="J117" r:id="rId67" xr:uid="{57CE08D8-1B23-4CE7-A1B7-A09C90E837D8}"/>
-    <hyperlink ref="J118" r:id="rId68" xr:uid="{D3ABFE1B-1EB2-4A26-AB54-5CF8A9CF9BC1}"/>
-    <hyperlink ref="J119" r:id="rId69" xr:uid="{D06EFE35-D535-464C-B2CE-FDD1BA994D58}"/>
-    <hyperlink ref="J120" r:id="rId70" xr:uid="{C6C4C34A-32A6-4DD4-93F3-2D030C23A6F5}"/>
-    <hyperlink ref="J121" r:id="rId71" xr:uid="{BE924EC4-81FF-4184-9095-733B8B101C70}"/>
-    <hyperlink ref="J124" r:id="rId72" xr:uid="{6D649045-1AB3-49C4-9DE4-FB734A256257}"/>
-    <hyperlink ref="J128" r:id="rId73" xr:uid="{BF2262B4-0D0B-48F1-B4F2-1CF4D225C663}"/>
-    <hyperlink ref="J129" r:id="rId74" xr:uid="{DD6C1AB0-7E7D-4454-AE54-3DC4CDB495F9}"/>
-    <hyperlink ref="J132" r:id="rId75" xr:uid="{45CF6128-20F8-4F77-8EE3-1A43C7196644}"/>
-    <hyperlink ref="J134" r:id="rId76" xr:uid="{C493ED74-D76F-4FDF-89C8-379E0E5A607D}"/>
-    <hyperlink ref="J135" r:id="rId77" xr:uid="{9665401E-5878-4EAD-887D-EF0870DB75EC}"/>
-    <hyperlink ref="J136" r:id="rId78" xr:uid="{FE1C265B-14BD-4DE2-A32A-15C24394162C}"/>
-    <hyperlink ref="J140" r:id="rId79" xr:uid="{75D1069B-51C4-4036-A3B6-D951F19EE717}"/>
-    <hyperlink ref="J142" r:id="rId80" xr:uid="{C3FAF03A-7524-4C4F-B905-C7300D309E2D}"/>
-    <hyperlink ref="J143" r:id="rId81" xr:uid="{7FAB3C0B-D59A-4A71-B3A5-C40781F7FB6B}"/>
-    <hyperlink ref="J144" r:id="rId82" xr:uid="{DDB8CEA7-FC2B-476D-A058-AF12C25EB2A2}"/>
-    <hyperlink ref="J145" r:id="rId83" xr:uid="{868F8CC6-3E76-4ABA-99D6-58E177872278}"/>
-    <hyperlink ref="J147" r:id="rId84" xr:uid="{87688FE5-05B4-4AD0-AEEB-2D58FB5EB301}"/>
-    <hyperlink ref="J149" r:id="rId85" xr:uid="{A6EE35DE-58B2-4091-85C7-864A6077908A}"/>
-    <hyperlink ref="J150" r:id="rId86" xr:uid="{9D2C2140-29B1-49A0-9A38-5727375CF24F}"/>
-    <hyperlink ref="J151" r:id="rId87" xr:uid="{8DF0F3E5-8AE6-4859-8506-A7612503FBF6}"/>
-    <hyperlink ref="J152" r:id="rId88" xr:uid="{C5133B6D-198D-4185-8354-7F64173C3786}"/>
-    <hyperlink ref="J153" r:id="rId89" xr:uid="{BCFF0D76-FB6B-4986-B24B-89627640545B}"/>
-    <hyperlink ref="J154" r:id="rId90" xr:uid="{393AA3F7-F44D-4025-9494-FA1836E64318}"/>
-    <hyperlink ref="J155" r:id="rId91" xr:uid="{A5E38F29-B013-43FF-A907-0E46567A02E5}"/>
-    <hyperlink ref="J156" r:id="rId92" xr:uid="{8D20C537-73B9-405B-9381-8FDC8AFD143D}"/>
-    <hyperlink ref="J159" r:id="rId93" xr:uid="{9433FB2A-DF44-4B4D-9804-04DD21B89AA8}"/>
-    <hyperlink ref="J160" r:id="rId94" xr:uid="{9D01F767-A027-47F9-BFCC-87D57834C72B}"/>
-    <hyperlink ref="J161" r:id="rId95" xr:uid="{3D0EDB9B-9CA3-4C58-9ACC-EE570F0F04B9}"/>
-    <hyperlink ref="J162" r:id="rId96" xr:uid="{F6732FDB-87B9-4AD5-AD31-A6DC149AC7DE}"/>
-    <hyperlink ref="J164" r:id="rId97" xr:uid="{8512379A-E7F9-4D07-8EF7-C62786B1E5CF}"/>
-    <hyperlink ref="J165" r:id="rId98" xr:uid="{9ED05AE4-C442-432C-803A-42D6C3CBB637}"/>
-    <hyperlink ref="J167" r:id="rId99" xr:uid="{5DE6C16D-8D50-40B3-A144-C587CEAC058C}"/>
-    <hyperlink ref="J168" r:id="rId100" xr:uid="{E496BB26-EC71-43D1-B1F0-6887360AE2E0}"/>
-    <hyperlink ref="J169" r:id="rId101" xr:uid="{29E62008-297E-4F1E-8A4F-FE06E5E50AB3}"/>
-    <hyperlink ref="J171" r:id="rId102" xr:uid="{BAB7BEFD-726D-4871-8D36-4EC060405563}"/>
-    <hyperlink ref="J172" r:id="rId103" xr:uid="{CDD7C553-C60F-434A-BEB4-48AE57F17676}"/>
-    <hyperlink ref="J173" r:id="rId104" xr:uid="{64F9B9B7-86EB-437B-A35B-8771BE826530}"/>
-    <hyperlink ref="J177" r:id="rId105" xr:uid="{4A04CDF8-1F66-48A9-922A-036614258228}"/>
-    <hyperlink ref="J178" r:id="rId106" xr:uid="{5BB7D15B-0BC5-40F6-B2E7-B126134DA2CB}"/>
-    <hyperlink ref="J181" r:id="rId107" xr:uid="{2C8F8AF3-44DA-4A55-B614-138F215A7A10}"/>
-    <hyperlink ref="J182" r:id="rId108" xr:uid="{D3327397-CE0F-4CA4-8493-7328C5E77C10}"/>
-    <hyperlink ref="J184" r:id="rId109" xr:uid="{5D9B5AF0-791C-4239-92E3-266E97754AFF}"/>
-    <hyperlink ref="J186" r:id="rId110" xr:uid="{AB0A793A-87E0-4CBA-8EDE-E0307909C8AF}"/>
-    <hyperlink ref="J190" r:id="rId111" xr:uid="{73717102-48AB-46D7-9F29-F50A2D4CE979}"/>
-    <hyperlink ref="J191" r:id="rId112" xr:uid="{0A769538-DEDC-4AA7-9804-892D866ED571}"/>
-    <hyperlink ref="J192" r:id="rId113" xr:uid="{5BB20A68-4E15-43DC-B541-BDA9ACE5D9DD}"/>
-    <hyperlink ref="J193" r:id="rId114" xr:uid="{CDACD140-2997-42F9-8F81-A7505C4F9886}"/>
-    <hyperlink ref="J194" r:id="rId115" xr:uid="{2EB40273-7F71-4946-BDC6-AF2754CC6C05}"/>
-    <hyperlink ref="J195" r:id="rId116" xr:uid="{170BB09B-5E1F-4590-893B-39A786230360}"/>
-    <hyperlink ref="J196" r:id="rId117" xr:uid="{AFAE64F4-2B7C-43A6-8BC7-414AC4F0FB36}"/>
-    <hyperlink ref="J199" r:id="rId118" xr:uid="{661E0EDA-347B-458F-A634-22CAA520D02B}"/>
-    <hyperlink ref="J201" r:id="rId119" xr:uid="{17E12D97-B513-4B14-897C-B463A198619D}"/>
-    <hyperlink ref="J202" r:id="rId120" xr:uid="{D429CBBE-0CDA-4D36-8E53-E4C846E12E70}"/>
-    <hyperlink ref="J203" r:id="rId121" xr:uid="{3A71CBF0-2124-499E-A7DE-826D37981472}"/>
-    <hyperlink ref="J205" r:id="rId122" xr:uid="{B01F768D-2ECE-4593-8373-5483D27D4684}"/>
-    <hyperlink ref="J207" r:id="rId123" xr:uid="{CAB3AA4E-4248-4E49-9EBA-EEC25F79A358}"/>
-    <hyperlink ref="J209" r:id="rId124" xr:uid="{9C3116C1-87E1-47EF-8F10-1084A4AF488E}"/>
-    <hyperlink ref="J210" r:id="rId125" xr:uid="{55181976-3728-4EDF-BAA7-8C4D7CCFEC4F}"/>
-    <hyperlink ref="J211" r:id="rId126" xr:uid="{2CD31C65-42C2-48E1-B226-0ADA1530AC28}"/>
-    <hyperlink ref="J212" r:id="rId127" xr:uid="{D4421AE1-6497-479B-9050-97D3FCCA5400}"/>
-    <hyperlink ref="J213" r:id="rId128" xr:uid="{741E0D66-B211-4C8B-A49E-AECE1B333F62}"/>
-    <hyperlink ref="J214" r:id="rId129" xr:uid="{B616E33E-CDDA-43AC-B413-63B8B7CF513B}"/>
-    <hyperlink ref="J215" r:id="rId130" xr:uid="{0B876CF5-88D8-4C8E-A21D-2372223288C0}"/>
-    <hyperlink ref="J217" r:id="rId131" xr:uid="{48AE988B-AA43-4070-868B-3110793CF54E}"/>
-    <hyperlink ref="J219" r:id="rId132" xr:uid="{302DE7C9-A9F1-4EE1-9F20-E604C061ACA6}"/>
-    <hyperlink ref="J220" r:id="rId133" xr:uid="{5CCFA0BB-572B-430C-B790-A3587A8F42F3}"/>
-    <hyperlink ref="J221" r:id="rId134" xr:uid="{47540183-A567-4552-904F-65B8762832A6}"/>
-    <hyperlink ref="J222" r:id="rId135" xr:uid="{4DF0AA11-2A16-4201-A4AD-BECA47310E61}"/>
-    <hyperlink ref="J223" r:id="rId136" xr:uid="{59B2514A-ECB4-4D6E-BF06-8AB0E1F8400B}"/>
-    <hyperlink ref="J225" r:id="rId137" xr:uid="{48C50357-1115-470B-A3BB-5E42D19AF65F}"/>
-    <hyperlink ref="J228" r:id="rId138" xr:uid="{B6CBAEEB-771C-47FB-88B9-BDC11852323F}"/>
-    <hyperlink ref="J230" r:id="rId139" xr:uid="{636AF7EA-A2F1-44BC-A007-820710BE5B34}"/>
-    <hyperlink ref="J234" r:id="rId140" xr:uid="{970AD978-E6BF-4D91-BB1B-36E11E76151B}"/>
-    <hyperlink ref="J236" r:id="rId141" xr:uid="{AF1982F8-D275-4BFD-AE5D-04B7DF5F6203}"/>
-    <hyperlink ref="J237" r:id="rId142" xr:uid="{310049FF-670E-4433-9A85-E2D1489B5D1D}"/>
-    <hyperlink ref="J238" r:id="rId143" xr:uid="{1FFD6D26-F9BE-4AC6-984A-698F4B8642D3}"/>
-    <hyperlink ref="J240" r:id="rId144" xr:uid="{16169098-5A7B-40C8-B93D-870852C878E4}"/>
-    <hyperlink ref="J241" r:id="rId145" xr:uid="{A87AFDC9-08AE-43EC-A64D-778A8BD47EB7}"/>
-    <hyperlink ref="J242" r:id="rId146" xr:uid="{4111A16F-7165-4AE1-8CA1-181A889C36FE}"/>
-    <hyperlink ref="J243" r:id="rId147" xr:uid="{0E35F663-0408-40CF-91CB-6DBB5CA0103A}"/>
-    <hyperlink ref="J246" r:id="rId148" xr:uid="{F9757982-D13D-4B6B-9A45-BDB4E474C25A}"/>
-    <hyperlink ref="J247" r:id="rId149" xr:uid="{361D136A-BCCF-40F3-8E18-25B1C5718861}"/>
-    <hyperlink ref="J250" r:id="rId150" xr:uid="{D664F274-3C2D-407E-98B4-FD79ECD8DF80}"/>
-    <hyperlink ref="J252" r:id="rId151" xr:uid="{7BC40F0D-C6F2-40E9-B7AC-767DF5CF0B86}"/>
-    <hyperlink ref="J254" r:id="rId152" xr:uid="{3A3C66D7-B240-4A00-8760-CE53EAE5FF13}"/>
-    <hyperlink ref="J255" r:id="rId153" xr:uid="{4DED24B0-7BDF-4F66-85D5-08A82220A3F0}"/>
-    <hyperlink ref="J256" r:id="rId154" xr:uid="{641BA73D-3E8B-42B7-A4A9-BD0EA3BCCD3D}"/>
-    <hyperlink ref="J258" r:id="rId155" xr:uid="{04FBD900-323D-425E-B208-B7206802F0A2}"/>
-    <hyperlink ref="J259" r:id="rId156" xr:uid="{77EB149C-B38C-43D0-9ED3-54C4A078D76B}"/>
-    <hyperlink ref="J261" r:id="rId157" xr:uid="{A19BF520-5EEC-4262-B464-5E3CDEF14833}"/>
-    <hyperlink ref="J263" r:id="rId158" xr:uid="{7246294A-1B7A-4C5D-AC51-1A32EA1A41D8}"/>
-    <hyperlink ref="J265" r:id="rId159" xr:uid="{1E5FCFFC-86D6-4F44-AD25-E584426348AC}"/>
-    <hyperlink ref="J266" r:id="rId160" xr:uid="{B081C88D-DDC0-45D5-8D10-9FC422BE7203}"/>
-    <hyperlink ref="J267" r:id="rId161" xr:uid="{0BB850A1-60D0-46A7-B1A1-7AA6E50851AE}"/>
-    <hyperlink ref="J270" r:id="rId162" xr:uid="{D7F61676-9D9D-46FB-B7B5-918A359014EC}"/>
-    <hyperlink ref="J271" r:id="rId163" xr:uid="{FFD12AC7-08C8-40C7-B36C-922F8300FE4F}"/>
-    <hyperlink ref="J273" r:id="rId164" xr:uid="{83DB86DD-104A-4F54-B937-719862870DC0}"/>
-    <hyperlink ref="J274" r:id="rId165" xr:uid="{1D0ED40C-799F-4353-B863-33137673D10D}"/>
-    <hyperlink ref="J275" r:id="rId166" xr:uid="{49450B40-7042-422A-923A-A077A030743E}"/>
-    <hyperlink ref="J277" r:id="rId167" xr:uid="{1BADF204-10ED-43CE-B58E-09BA383D56EE}"/>
-    <hyperlink ref="J278" r:id="rId168" xr:uid="{A96C232B-CD58-4C60-B660-15D87A4E98EA}"/>
-    <hyperlink ref="J279" r:id="rId169" xr:uid="{317D48CC-A714-4D23-B71F-7DC683324E1E}"/>
-    <hyperlink ref="J280" r:id="rId170" xr:uid="{6BF16EBB-00FD-44E0-9075-5E3DE118D76A}"/>
-    <hyperlink ref="J281" r:id="rId171" xr:uid="{6DCC2F8F-CBB9-4B56-A15E-20446A141B37}"/>
-    <hyperlink ref="J282" r:id="rId172" xr:uid="{A6BC230E-F15B-4B49-A0EE-32D276675675}"/>
-    <hyperlink ref="J283" r:id="rId173" xr:uid="{7106C8A9-FE4F-441C-8632-D77A1F6A820E}"/>
-    <hyperlink ref="J286" r:id="rId174" xr:uid="{8A5F0FE1-162E-4369-B70F-73B9C94D5075}"/>
-    <hyperlink ref="J287" r:id="rId175" xr:uid="{A7A75DAA-AB8D-4C0B-AA60-6779E1182425}"/>
-    <hyperlink ref="J290" r:id="rId176" xr:uid="{35B40E90-430F-4B7C-8AFC-DE8265B6BAE1}"/>
-    <hyperlink ref="J292" r:id="rId177" xr:uid="{BDA0E0E5-C491-4C39-B9E2-B0405B3C5E3C}"/>
-    <hyperlink ref="J294" r:id="rId178" xr:uid="{C5909A1B-4840-4E0C-B7FC-5CA325E76F77}"/>
-    <hyperlink ref="J296" r:id="rId179" xr:uid="{B31D7DE8-F8D4-4F2D-959A-82C3281F99D3}"/>
-    <hyperlink ref="J297" r:id="rId180" xr:uid="{2A73614C-00A9-433B-A3D5-2766BA06EFEF}"/>
-    <hyperlink ref="J298" r:id="rId181" xr:uid="{6755D5AB-7116-44BC-920B-46DE5152B1D0}"/>
-    <hyperlink ref="J299" r:id="rId182" xr:uid="{93C43455-755E-45BF-822F-FFACEEBA47DB}"/>
-    <hyperlink ref="J300" r:id="rId183" xr:uid="{29440318-30CA-45CC-81F0-6A411470A0A7}"/>
-    <hyperlink ref="J301" r:id="rId184" xr:uid="{9C8FE5BF-B79B-41C7-9EDB-9C02D2918ECE}"/>
-    <hyperlink ref="J303" r:id="rId185" xr:uid="{9519C260-4F34-4B3F-B903-9B303D879F00}"/>
-    <hyperlink ref="J305" r:id="rId186" xr:uid="{731EB7A0-0389-440C-A7C8-BE18965141BD}"/>
-    <hyperlink ref="J306" r:id="rId187" xr:uid="{B37B0C8C-8541-4370-954F-818984C628EB}"/>
-    <hyperlink ref="J308" r:id="rId188" xr:uid="{F0CC7679-14DA-4FCE-85B9-B91886799B1A}"/>
-    <hyperlink ref="J309" r:id="rId189" xr:uid="{39CDB470-A841-4D9A-9563-DC5B6996FC0C}"/>
-    <hyperlink ref="J311" r:id="rId190" xr:uid="{27B17F30-E4BF-4E93-8E60-3CD16A859013}"/>
-    <hyperlink ref="J312" r:id="rId191" xr:uid="{AE076C91-E65C-4AD7-A83C-A7F007CA185B}"/>
-    <hyperlink ref="J314" r:id="rId192" xr:uid="{DBB2B8B7-C5C6-4921-9206-7764B70BFB37}"/>
-    <hyperlink ref="J317" r:id="rId193" xr:uid="{87C59B37-0077-4968-B349-86B1B0F99904}"/>
-    <hyperlink ref="J318" r:id="rId194" xr:uid="{3C90603E-A49C-401D-852F-EF3F2F8DF84C}"/>
-    <hyperlink ref="J321" r:id="rId195" xr:uid="{C7466EFF-9908-4825-A4A8-F0C464CD9D97}"/>
-    <hyperlink ref="J322" r:id="rId196" xr:uid="{29842225-97D8-48EE-999C-B73450EFC120}"/>
-    <hyperlink ref="J325" r:id="rId197" xr:uid="{1A9F8F69-31AA-4C5B-9694-E356273CD990}"/>
-    <hyperlink ref="J326" r:id="rId198" xr:uid="{3914A055-3A7E-4978-A3A8-8E23139CDE9D}"/>
-    <hyperlink ref="J329" r:id="rId199" xr:uid="{F37A3C14-0521-4AB3-A300-D28761914BDE}"/>
-    <hyperlink ref="J330" r:id="rId200" xr:uid="{D8BDE4C3-C5E3-4E60-A09D-7278C3DB61DF}"/>
-    <hyperlink ref="J331" r:id="rId201" xr:uid="{8BE702A6-5AB9-494E-B559-FF8E6D6E670D}"/>
-    <hyperlink ref="J333" r:id="rId202" xr:uid="{4B0989C8-CC3C-40BE-BB33-20E39465EB25}"/>
-    <hyperlink ref="J334" r:id="rId203" xr:uid="{A1D08642-1359-4087-9459-8C39C60399B6}"/>
-    <hyperlink ref="J335" r:id="rId204" xr:uid="{87671D62-77A2-4B86-B9A2-76F698CCDB28}"/>
-    <hyperlink ref="J336" r:id="rId205" xr:uid="{763F4C73-F61B-4076-9C5B-451B680CE769}"/>
-    <hyperlink ref="J338" r:id="rId206" xr:uid="{B7F1A47D-A33C-4018-9C67-FEDAE219FC5C}"/>
-    <hyperlink ref="J340" r:id="rId207" xr:uid="{6A535932-0EA1-4D82-8AB1-01DF9B24E800}"/>
-    <hyperlink ref="J342" r:id="rId208" xr:uid="{62AD1E09-4A27-4531-B69B-05FD5214D91E}"/>
-    <hyperlink ref="J343" r:id="rId209" xr:uid="{602063A3-C9EF-43B0-BB68-944F4283201F}"/>
-    <hyperlink ref="J344" r:id="rId210" xr:uid="{30A51D69-8361-4324-9D14-1365CB020816}"/>
-    <hyperlink ref="J346" r:id="rId211" xr:uid="{35F04862-8CB8-45AE-A9A9-6A288064ED9E}"/>
-    <hyperlink ref="J349" r:id="rId212" xr:uid="{16A458FA-4008-4058-8C91-1AD03FA38B8C}"/>
-    <hyperlink ref="J350" r:id="rId213" xr:uid="{065C7560-8957-4931-8A6F-58E9B6199072}"/>
-    <hyperlink ref="J352" r:id="rId214" xr:uid="{1245B78B-0C95-4DE8-AE9D-8173395EB70E}"/>
-    <hyperlink ref="J354" r:id="rId215" xr:uid="{E4563525-D6AF-43C2-828A-A56D8726B1FC}"/>
-    <hyperlink ref="J355" r:id="rId216" xr:uid="{9AC84DE4-C593-4C67-B5BA-469C7EBAAA74}"/>
-    <hyperlink ref="J356" r:id="rId217" xr:uid="{DAC4877F-D366-4B58-9357-87840E602B14}"/>
-    <hyperlink ref="J357" r:id="rId218" xr:uid="{30032090-EE4F-47EC-8247-D16CA1A623F5}"/>
-    <hyperlink ref="J358" r:id="rId219" xr:uid="{9212402A-E85C-4646-A7E2-653E2CCA06F5}"/>
-    <hyperlink ref="J360" r:id="rId220" xr:uid="{22B93211-BE64-4221-855E-4B9AB17FF6A0}"/>
-    <hyperlink ref="J363" r:id="rId221" xr:uid="{734A9250-B35A-4305-BC53-30EF872D1BB9}"/>
-    <hyperlink ref="J364" r:id="rId222" xr:uid="{6FF83BA5-8102-45AB-9D29-C4C70C7060A0}"/>
-    <hyperlink ref="J366" r:id="rId223" xr:uid="{537A655A-DAB8-4B07-976D-D04AE16293C7}"/>
-    <hyperlink ref="J368" r:id="rId224" xr:uid="{DEDDE3AD-9277-4264-AFC4-B6F622137EF7}"/>
-    <hyperlink ref="J370" r:id="rId225" xr:uid="{DFC3736D-569F-420F-BA6E-D633DFC0E70D}"/>
-    <hyperlink ref="J371" r:id="rId226" xr:uid="{BF39F5AC-56E5-4CE5-B30C-6A89280D5289}"/>
-    <hyperlink ref="J372" r:id="rId227" xr:uid="{D0658AF7-B2E3-4CA4-A702-157ECC225F6B}"/>
-    <hyperlink ref="J373" r:id="rId228" xr:uid="{F12DA6B1-EE8C-4CC2-9AD3-36BCFAB21A39}"/>
-    <hyperlink ref="J374" r:id="rId229" xr:uid="{0BBA2A93-65EE-4B88-A948-45351FD9B6B8}"/>
-    <hyperlink ref="J375" r:id="rId230" xr:uid="{0D95A89F-5D1F-42A5-88A8-A3D911A47F7A}"/>
-    <hyperlink ref="J376" r:id="rId231" xr:uid="{11A580EE-4977-4D3F-9DA8-4122CB84282B}"/>
-    <hyperlink ref="J377" r:id="rId232" xr:uid="{30428EC4-EF75-4AC7-B23D-2B2899020983}"/>
-    <hyperlink ref="J378" r:id="rId233" xr:uid="{3F20B6AE-47B7-42EE-A4B6-850FF03242C9}"/>
-    <hyperlink ref="J379" r:id="rId234" xr:uid="{22049983-6ACB-4DE6-9B40-B0F13F15B00B}"/>
-    <hyperlink ref="J381" r:id="rId235" xr:uid="{2152B735-4EB5-4AE2-A519-CEE59C418AD9}"/>
-    <hyperlink ref="J383" r:id="rId236" xr:uid="{8EFB12D4-ED4E-4F9E-8F69-C259DC68E845}"/>
-    <hyperlink ref="J384" r:id="rId237" xr:uid="{C00347B8-E8AB-4A63-A53B-871A10571B3D}"/>
-    <hyperlink ref="J386" r:id="rId238" xr:uid="{32BAB89D-C259-4BE1-B38E-D88B2B14C76F}"/>
-    <hyperlink ref="J387" r:id="rId239" xr:uid="{57C03BA1-05AD-4EE4-88A3-F526E795C860}"/>
-    <hyperlink ref="J388" r:id="rId240" xr:uid="{03448F52-3548-4916-953E-EBC6E5FCBEA6}"/>
-    <hyperlink ref="J390" r:id="rId241" xr:uid="{B9AEEE69-83EB-4027-9DA3-177647D7D45F}"/>
-    <hyperlink ref="J391" r:id="rId242" xr:uid="{7299AB58-6E50-4800-954C-CDD4C5E6D86D}"/>
-    <hyperlink ref="J394" r:id="rId243" xr:uid="{27592250-10ED-4996-BAC1-00ABD14822EC}"/>
-    <hyperlink ref="J395" r:id="rId244" xr:uid="{B15B997C-2F7D-448E-A2D8-928A384421E8}"/>
-    <hyperlink ref="J396" r:id="rId245" xr:uid="{231E6DB8-BA0F-42B1-9416-1107E5FE4F95}"/>
-    <hyperlink ref="J397" r:id="rId246" xr:uid="{0E2BD6AE-69B5-4209-836B-D718BEB5990E}"/>
-    <hyperlink ref="J398" r:id="rId247" xr:uid="{7D2C3ECB-B6B5-4C82-BC5E-E9DF703C6FDA}"/>
-    <hyperlink ref="J399" r:id="rId248" xr:uid="{F7B90D72-2F15-4567-8BA2-BBCFA782D47C}"/>
-    <hyperlink ref="J400" r:id="rId249" xr:uid="{144A44FB-E28B-4E1C-991C-1B83D459A13C}"/>
-    <hyperlink ref="J403" r:id="rId250" xr:uid="{AA6A0DD4-8547-41B1-8B98-BB5BC319C146}"/>
-    <hyperlink ref="J404" r:id="rId251" xr:uid="{9DFB7478-E7CF-4844-96C1-BC75739906DF}"/>
-    <hyperlink ref="J405" r:id="rId252" xr:uid="{111C5E83-C6F6-4879-B8FF-DB39AC4A0B31}"/>
-    <hyperlink ref="J406" r:id="rId253" xr:uid="{55742018-EC53-42F7-AE98-3774A858EDA5}"/>
-    <hyperlink ref="J408" r:id="rId254" xr:uid="{B7B523CF-7FCE-41BA-B879-BE58DE9E4C2F}"/>
-    <hyperlink ref="J409" r:id="rId255" xr:uid="{456AF082-40AD-472E-82CC-D0E9AD53B779}"/>
-    <hyperlink ref="J411" r:id="rId256" xr:uid="{B6D0E4DA-FC78-42A8-A1C3-1DD72CE752CC}"/>
-    <hyperlink ref="J413" r:id="rId257" xr:uid="{2CF54B46-477E-46B7-A38D-37441E63BF3F}"/>
-    <hyperlink ref="J415" r:id="rId258" xr:uid="{7AE15555-9953-4D8D-B9F7-2DC4EE1BC04D}"/>
-    <hyperlink ref="J416" r:id="rId259" xr:uid="{802E4134-EC3B-40DC-BB1D-9532BBF63F4C}"/>
-    <hyperlink ref="J418" r:id="rId260" xr:uid="{24C3C142-B671-4A1B-AAEF-F5621EC761D6}"/>
-    <hyperlink ref="J421" r:id="rId261" xr:uid="{E3BBE5D2-D50D-4E7B-884E-D394441C2E3B}"/>
-    <hyperlink ref="J422" r:id="rId262" xr:uid="{5B0B354A-D599-4535-838B-BD858254344F}"/>
-    <hyperlink ref="J430" r:id="rId263" xr:uid="{DAE45DE8-BA02-4114-AD94-5E4C5660A67C}"/>
-    <hyperlink ref="J431" r:id="rId264" xr:uid="{D675C037-D8CD-4FB1-B7BF-3445FD296B90}"/>
-    <hyperlink ref="J432" r:id="rId265" xr:uid="{33B5FC02-DC00-4573-A48A-227E0090D1DD}"/>
-    <hyperlink ref="J433" r:id="rId266" xr:uid="{190753B8-B793-4290-A7DD-04A9EC54D19D}"/>
-    <hyperlink ref="J434" r:id="rId267" xr:uid="{DCFCE9E8-92BC-4D5F-894A-E63E7333DEF0}"/>
-    <hyperlink ref="J435" r:id="rId268" xr:uid="{2635E524-F9C4-4394-977D-6CB065E611C8}"/>
-    <hyperlink ref="J436" r:id="rId269" xr:uid="{0D4F9019-DF45-4653-8C45-849F711DB6AC}"/>
-    <hyperlink ref="J437" r:id="rId270" xr:uid="{AF4FDA04-EA39-4289-AFC5-87B802E5BE9E}"/>
-    <hyperlink ref="J438" r:id="rId271" xr:uid="{693A1ED5-08CB-4868-A1C7-7C4976F32013}"/>
-    <hyperlink ref="J439" r:id="rId272" xr:uid="{A0728540-E173-4FEB-B0A3-154E0E1FEFAD}"/>
-    <hyperlink ref="J445" r:id="rId273" xr:uid="{547A7B81-0E19-4144-AC6C-B037D3E1D00F}"/>
-    <hyperlink ref="J447" r:id="rId274" xr:uid="{3A577E37-3C9F-4943-B83A-1DD2AC4F81FE}"/>
-    <hyperlink ref="J449" r:id="rId275" xr:uid="{8EA4111A-3A96-43AD-9749-F477CA0BC0FD}"/>
-    <hyperlink ref="J450" r:id="rId276" xr:uid="{26A0FD00-1973-42EC-A1D1-8849038B2652}"/>
-    <hyperlink ref="J451" r:id="rId277" xr:uid="{D8930F0E-2511-44AE-875E-9104E88D21DF}"/>
-    <hyperlink ref="J452" r:id="rId278" xr:uid="{2802D4FA-5839-4592-8296-0466C611148B}"/>
-    <hyperlink ref="J453" r:id="rId279" xr:uid="{E59BB7BB-6FC4-4DBF-9669-003042F73E22}"/>
-    <hyperlink ref="J454" r:id="rId280" xr:uid="{A04B132B-81B3-43C3-99AD-C35D3FC487AB}"/>
-    <hyperlink ref="J455" r:id="rId281" xr:uid="{D73A0AA2-E86A-4EF0-9B1B-A83687D558A8}"/>
-    <hyperlink ref="J458" r:id="rId282" xr:uid="{604EDA95-CC8C-42B9-B3ED-ABE6D164E04A}"/>
-    <hyperlink ref="J460" r:id="rId283" xr:uid="{61D50ACF-11E4-46A2-B477-55813115D358}"/>
-    <hyperlink ref="J461" r:id="rId284" xr:uid="{2F172F7D-2439-469D-B9C2-ECC4B9DC4E88}"/>
-    <hyperlink ref="J462" r:id="rId285" xr:uid="{BEE0C974-6376-443A-912A-F9566B6A7951}"/>
-    <hyperlink ref="J465" r:id="rId286" xr:uid="{957C8DAC-BEED-45F2-B1AE-D1F86A25D690}"/>
-    <hyperlink ref="J469" r:id="rId287" xr:uid="{CBB18CFC-F55E-492C-93F0-243BD0CF1794}"/>
-    <hyperlink ref="J473" r:id="rId288" xr:uid="{54B9105E-B07A-4352-84E5-C1F4CF53C196}"/>
-    <hyperlink ref="J476" r:id="rId289" xr:uid="{05556749-C202-4FF0-8D43-3520298CA29C}"/>
-    <hyperlink ref="J478" r:id="rId290" xr:uid="{CD0F20CC-E3F1-4626-9351-2B28217F21BA}"/>
-    <hyperlink ref="J479" r:id="rId291" xr:uid="{17D1D7F4-80C3-4F71-910A-7333299F1629}"/>
-    <hyperlink ref="J480" r:id="rId292" xr:uid="{8C8AAF60-90C1-4F6F-9360-D5FED4C85D6B}"/>
-    <hyperlink ref="J481" r:id="rId293" xr:uid="{4F623206-2B58-4B50-BC6C-C5582C3C8F58}"/>
-    <hyperlink ref="J482" r:id="rId294" xr:uid="{40886FB2-1B63-4441-8F63-9BA55A4112CB}"/>
-    <hyperlink ref="J484" r:id="rId295" xr:uid="{73FFE5D2-83FB-449C-9B24-D2298A98A685}"/>
-    <hyperlink ref="J485" r:id="rId296" xr:uid="{7F3E85D5-0888-4E1B-AFE1-C508F3BC5744}"/>
-    <hyperlink ref="J488" r:id="rId297" xr:uid="{1992D802-8F96-471E-9DF7-20FDE6E1E6F5}"/>
-    <hyperlink ref="J489" r:id="rId298" xr:uid="{C243C020-3DBC-4CA6-92FA-9563B8E89E2A}"/>
-    <hyperlink ref="J490" r:id="rId299" xr:uid="{8E494181-C1B4-4C3C-AEE3-81428FF3243A}"/>
-    <hyperlink ref="J491" r:id="rId300" xr:uid="{8F68945D-0B73-449E-BDD6-80818EAA984F}"/>
-    <hyperlink ref="J494" r:id="rId301" xr:uid="{49CA0548-C6BC-48AA-B134-89B2625A249B}"/>
-    <hyperlink ref="J496" r:id="rId302" xr:uid="{2BE02F57-4EBF-4A92-97F1-32ACD20E8569}"/>
-    <hyperlink ref="J497" r:id="rId303" xr:uid="{36B77205-C233-4FE9-9382-EF95E891D05A}"/>
-    <hyperlink ref="J498" r:id="rId304" xr:uid="{1137FB75-24E8-4A1B-B6CA-86040FC6897E}"/>
-    <hyperlink ref="J499" r:id="rId305" xr:uid="{CCA45C73-E149-4B75-A166-9F447EA9A7A1}"/>
-    <hyperlink ref="J500" r:id="rId306" xr:uid="{9731E86A-8BF9-421E-97A7-AB2F895173CC}"/>
-    <hyperlink ref="J501" r:id="rId307" xr:uid="{4846EFED-5B32-493D-8924-40CB25401F45}"/>
-    <hyperlink ref="J503" r:id="rId308" xr:uid="{D26972CE-714B-4FFE-A86A-C922183FA5EA}"/>
-    <hyperlink ref="J504" r:id="rId309" xr:uid="{2DCD8805-0F0C-4943-AB07-36988E2983D0}"/>
-    <hyperlink ref="J508" r:id="rId310" xr:uid="{EE9F76C6-AB33-41C1-AAD0-859B11299119}"/>
-    <hyperlink ref="J509" r:id="rId311" xr:uid="{30C74A23-60F4-4BF8-9EE7-9F57860E9AE3}"/>
-    <hyperlink ref="J510" r:id="rId312" xr:uid="{246EE96B-D140-4074-918D-9D7455F242F0}"/>
-    <hyperlink ref="J511" r:id="rId313" xr:uid="{63DD2A69-B5E0-4666-9931-D64AF60AC7E6}"/>
-    <hyperlink ref="J513" r:id="rId314" xr:uid="{6F1927E1-F7D4-4782-9794-FBCC94B43906}"/>
-    <hyperlink ref="J515" r:id="rId315" xr:uid="{7E4DD59C-3FEE-4FA6-B41F-B4D150B49313}"/>
-    <hyperlink ref="J516" r:id="rId316" xr:uid="{BD1A4BE6-6763-488A-B0F6-4A9FA3A85D60}"/>
-    <hyperlink ref="J519" r:id="rId317" xr:uid="{5B3E5B10-BD91-419E-8794-50AFA5C9CB97}"/>
-    <hyperlink ref="J523" r:id="rId318" xr:uid="{0B66F68D-BB4C-449D-A8C5-D69E4B83DE06}"/>
-    <hyperlink ref="J524" r:id="rId319" xr:uid="{DC32AD5C-5728-4101-AEB5-6E59FA56C194}"/>
-    <hyperlink ref="J525" r:id="rId320" xr:uid="{DE958784-3271-455B-B6D5-C7572A48F330}"/>
-    <hyperlink ref="J535" r:id="rId321" xr:uid="{42F03D9F-5ED8-4D23-82AD-BD8A373A1F83}"/>
-    <hyperlink ref="J536" r:id="rId322" xr:uid="{7C4028FC-291F-48E5-BF19-B81093EB2870}"/>
-    <hyperlink ref="J537" r:id="rId323" xr:uid="{C9FE9FF8-7174-4B1F-A866-3E39282EA56F}"/>
-    <hyperlink ref="J538" r:id="rId324" xr:uid="{D25B9AB5-720B-40CA-903A-0A3533879ECD}"/>
-    <hyperlink ref="J539" r:id="rId325" xr:uid="{2894DFBE-F85D-418B-BC20-98089C07526B}"/>
-    <hyperlink ref="J540" r:id="rId326" xr:uid="{5721D230-52A9-4664-854B-C7D620795B70}"/>
-    <hyperlink ref="J541" r:id="rId327" xr:uid="{492DEC2F-B37A-48E2-89E7-36C24884F226}"/>
-    <hyperlink ref="J543" r:id="rId328" xr:uid="{B5D72363-F49A-407A-9C82-7240EBEED83E}"/>
-    <hyperlink ref="J544" r:id="rId329" xr:uid="{0FBCC060-D6F9-46FE-8328-485E3D812170}"/>
-    <hyperlink ref="J546" r:id="rId330" xr:uid="{C2A3031F-861C-4813-8275-C4F4F4458EBD}"/>
-    <hyperlink ref="J547" r:id="rId331" xr:uid="{9231BBD1-83B5-4299-8AFB-63BF1DECE86C}"/>
-    <hyperlink ref="J548" r:id="rId332" xr:uid="{8EBFA4A5-CC79-4DFF-8C30-49B9A4BD02F9}"/>
-    <hyperlink ref="J549" r:id="rId333" xr:uid="{EF13AB94-1B1F-4006-9AC5-34A6BF8466A2}"/>
-    <hyperlink ref="J550" r:id="rId334" xr:uid="{BC234B51-D8BF-418A-B603-E6229A9EBD9A}"/>
-    <hyperlink ref="J551" r:id="rId335" xr:uid="{47B80BCD-1162-4E72-81E6-F2B040C66E90}"/>
-    <hyperlink ref="J552" r:id="rId336" xr:uid="{3280EA33-826E-41E8-AB35-A0FA7EA6AF14}"/>
-    <hyperlink ref="J555" r:id="rId337" xr:uid="{672C70AB-2836-4474-90D9-18F1A0A896C6}"/>
-    <hyperlink ref="J556" r:id="rId338" xr:uid="{E93BCDE7-40BA-4CC8-89DF-80D43484859A}"/>
-    <hyperlink ref="J558" r:id="rId339" xr:uid="{EC016F7A-E8C1-461B-B9FA-9386EC366D42}"/>
-    <hyperlink ref="J559" r:id="rId340" xr:uid="{FEA88681-70CF-4D6B-9050-603EA6312678}"/>
-    <hyperlink ref="J560" r:id="rId341" xr:uid="{3E5960B5-6FE5-445A-A9AD-5306CC1E612C}"/>
-    <hyperlink ref="J562" r:id="rId342" xr:uid="{558BE965-146C-4AA1-AB5B-8FF71A48A7B3}"/>
-    <hyperlink ref="J569" r:id="rId343" xr:uid="{CACDFB75-2AED-44E7-A12A-72428F16218E}"/>
-    <hyperlink ref="J570" r:id="rId344" xr:uid="{71E9B58E-4527-4AB0-BAF2-198245CEA179}"/>
-    <hyperlink ref="J571" r:id="rId345" xr:uid="{5584A699-3660-4E41-A6F3-424C2109A59B}"/>
-    <hyperlink ref="J572" r:id="rId346" xr:uid="{69775804-1D29-4FF0-A4EB-88AC85CCE78E}"/>
-    <hyperlink ref="J573" r:id="rId347" xr:uid="{A3852DFA-1AB6-401D-9B76-C1332ABB5ADE}"/>
-    <hyperlink ref="J574" r:id="rId348" xr:uid="{2B7F5FD7-FE6F-40C1-9DFB-EA7A7A8D8EC8}"/>
-    <hyperlink ref="J575" r:id="rId349" xr:uid="{20DF0733-350E-47FF-ABA6-86C66BD112B2}"/>
-    <hyperlink ref="J576" r:id="rId350" xr:uid="{44DBB282-014D-4991-882C-8795B62D9D5C}"/>
-    <hyperlink ref="J577" r:id="rId351" xr:uid="{189BDD48-050C-4BD8-AE97-FCE43964F67F}"/>
-    <hyperlink ref="J578" r:id="rId352" xr:uid="{917662CD-683A-4592-BE78-298A1A1663A4}"/>
-    <hyperlink ref="J579" r:id="rId353" xr:uid="{0EB435D0-DEFA-4DC5-8AD2-BE2B73FF5A05}"/>
-    <hyperlink ref="J580" r:id="rId354" xr:uid="{88C7A544-DF60-4810-A87F-7E798198180B}"/>
-    <hyperlink ref="J581" r:id="rId355" xr:uid="{DF2710CB-0024-4FE9-9F37-496AB90B82F3}"/>
-    <hyperlink ref="J582" r:id="rId356" xr:uid="{A9FC74DA-E7B2-4D30-97B3-F02FC78509A1}"/>
-    <hyperlink ref="J584" r:id="rId357" xr:uid="{DF72BA24-F778-4995-979A-6CF76C4EC73A}"/>
-    <hyperlink ref="J585" r:id="rId358" xr:uid="{731706D6-2EB1-40F9-A4A0-C907F7666D39}"/>
-    <hyperlink ref="J586" r:id="rId359" xr:uid="{CA2CDDC0-D7E5-40B6-A888-76EEE11CD882}"/>
-    <hyperlink ref="J587" r:id="rId360" xr:uid="{E280284A-235C-45CF-A0A8-86EC2367A63D}"/>
-    <hyperlink ref="J592" r:id="rId361" xr:uid="{6434A4C7-A4E2-481F-BDBD-866DE3838AE0}"/>
-    <hyperlink ref="J593" r:id="rId362" xr:uid="{57B5233E-7B24-473E-95B7-8134056B50D4}"/>
-    <hyperlink ref="J595" r:id="rId363" xr:uid="{1E23C72C-FDFF-48FA-950E-B465AF0A5B3A}"/>
-    <hyperlink ref="J596" r:id="rId364" xr:uid="{49056B52-D64E-4E51-B8E3-BB324A4B9627}"/>
-    <hyperlink ref="J598" r:id="rId365" xr:uid="{B336A840-7AF5-4741-BE76-781592C035A9}"/>
-    <hyperlink ref="J599" r:id="rId366" xr:uid="{3C90513D-BB1B-4E2D-8D65-496B50C3BE15}"/>
-    <hyperlink ref="J602" r:id="rId367" xr:uid="{7577BEF2-75F5-43BE-B71B-74940A449603}"/>
-    <hyperlink ref="J603" r:id="rId368" xr:uid="{841A2CD2-FE30-4542-910F-5F865DCDDD9A}"/>
-    <hyperlink ref="J604" r:id="rId369" xr:uid="{0319EDF4-2A31-438F-AE1D-8475A6ED7139}"/>
-    <hyperlink ref="J605" r:id="rId370" xr:uid="{4BF3B61E-2A27-461C-AF91-DAA726C92136}"/>
-    <hyperlink ref="J606" r:id="rId371" xr:uid="{48EBAB6F-CEE3-4D44-8E18-3D3D71B8680B}"/>
-    <hyperlink ref="J608" r:id="rId372" xr:uid="{F251ED35-8F6E-4F90-A9C9-91D8AAFF21B0}"/>
-    <hyperlink ref="J609" r:id="rId373" xr:uid="{B437A4A8-4B96-4ADF-8BD3-DAA31B1E46A7}"/>
-    <hyperlink ref="J611" r:id="rId374" xr:uid="{13813612-DF1C-4138-8F32-A0BAD20B86B3}"/>
-    <hyperlink ref="J612" r:id="rId375" xr:uid="{DE6F32A9-68E3-476C-A4A7-18A70BDA7C8F}"/>
-    <hyperlink ref="J613" r:id="rId376" xr:uid="{A5C28568-4FAC-4FB1-A9B4-5E2610EA5F2B}"/>
-    <hyperlink ref="J615" r:id="rId377" xr:uid="{6133F0C3-24BB-4E86-AD17-AB676F54D940}"/>
-    <hyperlink ref="J617" r:id="rId378" xr:uid="{1EFC166C-45B4-4E87-9A33-3D6AB88BF853}"/>
-    <hyperlink ref="J618" r:id="rId379" xr:uid="{E686CAE8-9F2E-4159-B8B9-93A5C85B0005}"/>
-    <hyperlink ref="J619" r:id="rId380" xr:uid="{F8BD4B1C-B76D-4E3D-8C98-294E881E3E97}"/>
-    <hyperlink ref="J622" r:id="rId381" xr:uid="{1658E7CF-0D6C-47D5-967C-676844BBDA8F}"/>
-    <hyperlink ref="J623" r:id="rId382" xr:uid="{206D2EFD-1A95-47BB-9E0F-A84CA0D69161}"/>
-    <hyperlink ref="J624" r:id="rId383" xr:uid="{AC5AE00E-352C-4776-9256-EDC394A55775}"/>
-    <hyperlink ref="J626" r:id="rId384" xr:uid="{E5B00B9F-FB3D-41E4-AC3B-80BD1DF17645}"/>
-    <hyperlink ref="J628" r:id="rId385" xr:uid="{2CAA543C-8F62-4736-9842-68D55C5F2DF5}"/>
-    <hyperlink ref="J629" r:id="rId386" xr:uid="{4449395F-A53D-47DF-B535-DB1CCEC3B620}"/>
-    <hyperlink ref="J631" r:id="rId387" xr:uid="{7235EBA1-6E29-420D-8375-3FCE52DA1348}"/>
-    <hyperlink ref="J634" r:id="rId388" xr:uid="{BE2BFFE5-0357-4AE2-89DF-F51ADE2BDFBB}"/>
-    <hyperlink ref="J635" r:id="rId389" xr:uid="{63F7C999-AF9A-4561-BFB5-1C3408142CE9}"/>
-    <hyperlink ref="J637" r:id="rId390" xr:uid="{E0755957-80DD-4C03-AB64-B252021B96FB}"/>
-    <hyperlink ref="J640" r:id="rId391" xr:uid="{DD0AA12D-CBC0-4977-AD25-01E64AEAF930}"/>
-    <hyperlink ref="J641" r:id="rId392" xr:uid="{42FDA13E-D22F-45FC-966D-6F55C7DE9AC4}"/>
-    <hyperlink ref="J642" r:id="rId393" xr:uid="{C30B1471-1256-4B11-AE3C-5A73870B0550}"/>
-    <hyperlink ref="J644" r:id="rId394" xr:uid="{7FCF31B0-D55B-45E4-B24C-2D168B334FF7}"/>
-    <hyperlink ref="J645" r:id="rId395" xr:uid="{268D8E05-77BE-4CF3-8E58-0D997FAD7264}"/>
-    <hyperlink ref="J648" r:id="rId396" xr:uid="{5EA49D87-B3F4-47CA-ADCA-C709D136E3FE}"/>
-    <hyperlink ref="J649" r:id="rId397" xr:uid="{DC268961-BF0F-4D24-B6DA-41E2F5D6C69A}"/>
-    <hyperlink ref="J652" r:id="rId398" xr:uid="{ABC605DA-B6E6-4EFF-83A9-3E58C006FE4E}"/>
-    <hyperlink ref="J654" r:id="rId399" xr:uid="{F949E294-812D-4195-8796-4D638BD000D9}"/>
-    <hyperlink ref="J656" r:id="rId400" xr:uid="{A463E8D1-121A-415C-9EC9-9D69E1FF2BAE}"/>
-    <hyperlink ref="J657" r:id="rId401" xr:uid="{C30AD87E-22CD-461F-92CB-90CA2A6A2886}"/>
-    <hyperlink ref="J663" r:id="rId402" xr:uid="{41B74882-8D85-4131-ACFA-4A51BFB846CD}"/>
-    <hyperlink ref="J664" r:id="rId403" xr:uid="{06E4820C-01DB-46FC-A73C-5E756415CA19}"/>
-    <hyperlink ref="J665" r:id="rId404" xr:uid="{4574F89A-970A-491E-9AF4-C5F17252F1B6}"/>
-    <hyperlink ref="J666" r:id="rId405" xr:uid="{69AB9384-60E8-4F9A-8F01-5C5D86132A82}"/>
-    <hyperlink ref="J667" r:id="rId406" xr:uid="{D32775BA-433C-40CF-82DA-706D1F4FE49D}"/>
-    <hyperlink ref="J668" r:id="rId407" xr:uid="{5B2C401C-EB35-4750-B192-5970C6C21DFB}"/>
-    <hyperlink ref="J669" r:id="rId408" xr:uid="{1658F4EB-1A8A-4096-9108-697E2C146982}"/>
-    <hyperlink ref="J670" r:id="rId409" xr:uid="{95046918-7B19-457B-BDB3-55943EED92E9}"/>
-    <hyperlink ref="J671" r:id="rId410" xr:uid="{0A9CA0E2-4ACF-44AA-ACD5-B6DF5606547D}"/>
-    <hyperlink ref="J672" r:id="rId411" xr:uid="{CD004410-6980-4716-B658-A07F81907772}"/>
-    <hyperlink ref="J673" r:id="rId412" xr:uid="{7C540C45-E4BB-4D92-8668-22F4EDB0F38F}"/>
-    <hyperlink ref="J674" r:id="rId413" xr:uid="{3D7F9E6B-7207-49FE-A4DB-D96CF9F5F414}"/>
-    <hyperlink ref="J675" r:id="rId414" xr:uid="{997B3917-8171-4F89-AD82-D096E83ADCB9}"/>
-    <hyperlink ref="J676" r:id="rId415" xr:uid="{53F87F00-6B0F-4347-BA46-E77C3A808C62}"/>
-    <hyperlink ref="J677" r:id="rId416" xr:uid="{E9F2CBA1-B389-4A12-BD4C-2F19079CDEBD}"/>
-    <hyperlink ref="J679" r:id="rId417" xr:uid="{1459B90F-505E-4903-9E46-9F82175B6C0D}"/>
-    <hyperlink ref="J682" r:id="rId418" xr:uid="{2C36D0BC-C1C6-4C68-8410-B786ADFA663D}"/>
-    <hyperlink ref="J683" r:id="rId419" xr:uid="{00C850C3-7A94-4BE8-82F4-AC648CDCFF78}"/>
-    <hyperlink ref="J684" r:id="rId420" xr:uid="{7F25F684-2B4A-4EBA-8E4D-6D5115504278}"/>
-    <hyperlink ref="J688" r:id="rId421" xr:uid="{C50A884E-2AFF-430C-8BFE-DD1BACC0033C}"/>
-    <hyperlink ref="J693" r:id="rId422" xr:uid="{EFBA682D-6DAE-4B94-B5FC-3CCF2954E3A7}"/>
-    <hyperlink ref="J694" r:id="rId423" xr:uid="{60D16EB6-6E42-4FC1-B576-3C850515CECB}"/>
-    <hyperlink ref="J695" r:id="rId424" xr:uid="{E81C935C-27D7-48E0-8816-8E75A7D38DE5}"/>
-    <hyperlink ref="J696" r:id="rId425" xr:uid="{B9236F26-1F27-49E2-AB9D-70C81707D06F}"/>
-    <hyperlink ref="J697" r:id="rId426" xr:uid="{5B58888B-5607-4821-AD44-CDCEF3EA9373}"/>
-    <hyperlink ref="J698" r:id="rId427" xr:uid="{A4080D31-1B75-4DE2-9D07-FBEC09A7C845}"/>
-    <hyperlink ref="J699" r:id="rId428" xr:uid="{2B6476F0-CB8E-4897-A588-DCFBC4696973}"/>
-    <hyperlink ref="J700" r:id="rId429" xr:uid="{846EF911-7BD7-4C74-9D42-9FE63A27E599}"/>
-    <hyperlink ref="J705" r:id="rId430" xr:uid="{08AE60C6-ED41-4E36-9D0B-5B0B124939D2}"/>
-    <hyperlink ref="J708" r:id="rId431" xr:uid="{86A1F00B-0431-49CB-A382-AD16327D305A}"/>
-    <hyperlink ref="J712" r:id="rId432" xr:uid="{FA0FCD59-A676-49DC-B341-B83EB86D3A62}"/>
-    <hyperlink ref="J713" r:id="rId433" xr:uid="{4B8E0A96-E39F-492F-B4F0-B18B090AB7C7}"/>
-    <hyperlink ref="J714" r:id="rId434" xr:uid="{C7266224-9494-47E2-8DA7-235EB39D00DA}"/>
-    <hyperlink ref="J715" r:id="rId435" xr:uid="{49A3DC4C-2DC3-4383-882D-96F4FC48435E}"/>
-    <hyperlink ref="J718" r:id="rId436" xr:uid="{0CF34283-3A85-4AF9-B374-DD6700031C69}"/>
-    <hyperlink ref="J720" r:id="rId437" xr:uid="{0B5CFC97-7828-4492-8298-2B832580E309}"/>
-    <hyperlink ref="J721" r:id="rId438" xr:uid="{027A1696-CD4F-47B7-AC4B-58B437B317CC}"/>
-    <hyperlink ref="J722" r:id="rId439" xr:uid="{2D779115-B7C3-47C8-A255-17D0C50B840B}"/>
-    <hyperlink ref="J725" r:id="rId440" xr:uid="{C9446CA1-0823-43EC-B945-149F19AEC02D}"/>
-    <hyperlink ref="J726" r:id="rId441" xr:uid="{5CA857F9-67D7-4DC2-BE76-E60CE85D3EFE}"/>
-    <hyperlink ref="J728" r:id="rId442" xr:uid="{47653339-ADF7-43E2-81B0-C50D2826612E}"/>
-    <hyperlink ref="J729" r:id="rId443" xr:uid="{3EE2BB48-547B-4403-A3FF-CACDCB00C276}"/>
-    <hyperlink ref="J736" r:id="rId444" xr:uid="{78372A6A-CE55-4639-BF5E-AA77CA398F46}"/>
-    <hyperlink ref="J738" r:id="rId445" xr:uid="{90D3B4B2-F4EE-4B92-BFF5-FAD5D437A863}"/>
-    <hyperlink ref="J739" r:id="rId446" xr:uid="{BDE26A42-5B63-4843-B945-AB7C9B335800}"/>
-    <hyperlink ref="J740" r:id="rId447" xr:uid="{34213911-A598-4939-8E59-4ABACCB2068C}"/>
-    <hyperlink ref="J741" r:id="rId448" xr:uid="{2C1B0C94-0BC8-4A74-8761-86A8A9CE4FAC}"/>
-    <hyperlink ref="J742" r:id="rId449" xr:uid="{7CC15809-CD84-43A5-8260-06E94653C644}"/>
-    <hyperlink ref="J743" r:id="rId450" xr:uid="{E8359A19-C282-4875-B163-786A1B5440C6}"/>
-    <hyperlink ref="J744" r:id="rId451" xr:uid="{21F17BFD-F853-41CD-ACF9-90E1CB0D99F5}"/>
-    <hyperlink ref="J747" r:id="rId452" xr:uid="{B4B6AE36-4731-4542-BBD9-9A203A52527E}"/>
-    <hyperlink ref="J748" r:id="rId453" xr:uid="{6592A409-007D-4DE3-9935-F13EB7C6CCB5}"/>
-    <hyperlink ref="J757" r:id="rId454" xr:uid="{D97E96E8-5F4B-4F73-8B8F-B4EAACE42DAB}"/>
-    <hyperlink ref="J758" r:id="rId455" xr:uid="{E7EF9DDC-2BC7-4629-BED4-926A077C0A18}"/>
-    <hyperlink ref="J759" r:id="rId456" xr:uid="{C32371DF-B1B2-42C8-A812-6E7A564DDEC1}"/>
-    <hyperlink ref="J760" r:id="rId457" xr:uid="{79F84BE1-0C59-4757-B3D9-BAB125453CA7}"/>
-    <hyperlink ref="J761" r:id="rId458" xr:uid="{8FF51F2D-777A-4AF4-8CE2-2EAB5331BE4A}"/>
-    <hyperlink ref="J762" r:id="rId459" xr:uid="{8D12639E-489C-4250-BB0C-7AF0CBD162EC}"/>
-    <hyperlink ref="J764" r:id="rId460" xr:uid="{704AC996-3B27-4A42-9FEC-12D65CCE0288}"/>
-    <hyperlink ref="J765" r:id="rId461" xr:uid="{97A45E87-4F6E-4CBE-A774-A2E507837E4C}"/>
-    <hyperlink ref="J766" r:id="rId462" xr:uid="{BBF67078-76BF-4F1E-ABCF-DA2223C92313}"/>
-    <hyperlink ref="J767" r:id="rId463" xr:uid="{57101E3C-9C11-4F4E-8F49-E7DF50A4EA11}"/>
-    <hyperlink ref="J769" r:id="rId464" xr:uid="{BF285C3B-5534-4CC3-B7BE-67431C834FE1}"/>
-    <hyperlink ref="J770" r:id="rId465" xr:uid="{9CD2072C-754B-42DB-9040-2F6DA224F7FF}"/>
-    <hyperlink ref="J772" r:id="rId466" xr:uid="{396B1ACB-CFD8-4928-B731-057A1E811F8A}"/>
-    <hyperlink ref="J774" r:id="rId467" xr:uid="{54B1106D-D2C0-466A-BEB5-01DF6541132A}"/>
+    <hyperlink ref="J5" r:id="rId1" xr:uid="{1656769E-16F9-402C-8E91-D76F55FC947E}"/>
+    <hyperlink ref="J7" r:id="rId2" xr:uid="{2310EAEA-1B3E-44D4-BA3C-531AC0C7419F}"/>
+    <hyperlink ref="J8" r:id="rId3" xr:uid="{F6102953-257C-409B-A6AF-5F6ABECC80B3}"/>
+    <hyperlink ref="J10" r:id="rId4" xr:uid="{E98A8D1B-ACED-4BF5-AF0B-FB4D008DC531}"/>
+    <hyperlink ref="J13" r:id="rId5" xr:uid="{4EBB52CF-185B-468B-B812-5A86412D179D}"/>
+    <hyperlink ref="J14" r:id="rId6" xr:uid="{28FC8FE1-586C-4056-B41F-4BD3ACCF204B}"/>
+    <hyperlink ref="J17" r:id="rId7" xr:uid="{E9607504-EB9F-4DEF-AEEE-A72B4E65B4BC}"/>
+    <hyperlink ref="J19" r:id="rId8" xr:uid="{C7560DCC-A710-4B5E-A1FA-5BDF51958D35}"/>
+    <hyperlink ref="J20" r:id="rId9" xr:uid="{F28DB54D-C562-4C78-8316-F8E06351FFC6}"/>
+    <hyperlink ref="J21" r:id="rId10" xr:uid="{C66FA2A5-6700-4545-A69D-539D2A26A94C}"/>
+    <hyperlink ref="J24" r:id="rId11" xr:uid="{68BBBA05-E9E5-4BC9-91CC-94C624C7E0F9}"/>
+    <hyperlink ref="J25" r:id="rId12" xr:uid="{DE8C363E-AB32-410A-A74F-167630C91FA6}"/>
+    <hyperlink ref="J26" r:id="rId13" xr:uid="{FE0CBC8B-F6F7-4B95-836C-A4E10AD6D013}"/>
+    <hyperlink ref="J27" r:id="rId14" xr:uid="{EC94E8D7-F231-4231-AB6B-A85D653E9D3C}"/>
+    <hyperlink ref="J29" r:id="rId15" xr:uid="{48EB4E6C-6BC9-42B8-8CEC-5E349DA9FEC9}"/>
+    <hyperlink ref="J30" r:id="rId16" xr:uid="{CBB72E40-0F1C-4EB4-8B7C-2E6B3645A358}"/>
+    <hyperlink ref="J31" r:id="rId17" xr:uid="{CE7923CB-7997-4A35-9513-02F8AED83429}"/>
+    <hyperlink ref="J34" r:id="rId18" xr:uid="{9D3B9B1E-B2D4-4B95-BF26-3E9679BDAC3F}"/>
+    <hyperlink ref="J35" r:id="rId19" xr:uid="{56782A9E-072C-43EE-A506-4CDA4EA39239}"/>
+    <hyperlink ref="J36" r:id="rId20" xr:uid="{B8380768-F695-4667-8C60-54DB032BA5EB}"/>
+    <hyperlink ref="J37" r:id="rId21" xr:uid="{0077679A-6421-47C0-B66C-DAF27FFF9782}"/>
+    <hyperlink ref="J38" r:id="rId22" xr:uid="{4931036E-0E0D-4B9F-B549-AD539A53BED5}"/>
+    <hyperlink ref="J46" r:id="rId23" xr:uid="{80AEE082-82C9-435E-AB52-9DDC460F3809}"/>
+    <hyperlink ref="J47" r:id="rId24" xr:uid="{12AF2E7A-EBC5-4A06-96D0-66BA0E4A55DB}"/>
+    <hyperlink ref="J48" r:id="rId25" xr:uid="{2E57B502-94BC-43E0-A597-15F245AFB16B}"/>
+    <hyperlink ref="J49" r:id="rId26" xr:uid="{DEB44B3C-B8D7-495A-AAC7-1262E9619C9A}"/>
+    <hyperlink ref="J50" r:id="rId27" xr:uid="{2D9E5C70-7888-4E67-92FE-2667F9F236FE}"/>
+    <hyperlink ref="J52" r:id="rId28" xr:uid="{11A81ED4-0B09-4222-AAFD-72F45E8DFF4F}"/>
+    <hyperlink ref="J53" r:id="rId29" xr:uid="{84530DB2-363F-4A2E-BA0C-3D925D4DBDDC}"/>
+    <hyperlink ref="J54" r:id="rId30" xr:uid="{6717E373-EE8A-4402-82C4-728D05C53943}"/>
+    <hyperlink ref="J56" r:id="rId31" xr:uid="{BB642912-A582-4C4B-8BCF-DBC4862F05DB}"/>
+    <hyperlink ref="J59" r:id="rId32" xr:uid="{BCB2C4AF-9162-4A5E-915C-815E84F29D41}"/>
+    <hyperlink ref="J61" r:id="rId33" xr:uid="{74D6ACE2-72DA-4DB0-8E56-24549CFBEC00}"/>
+    <hyperlink ref="J62" r:id="rId34" xr:uid="{598D53A9-87B4-4597-A2C7-57F70E6B7852}"/>
+    <hyperlink ref="J63" r:id="rId35" xr:uid="{7D679FB1-A70B-44C8-B60F-1C47F11D6D68}"/>
+    <hyperlink ref="J64" r:id="rId36" xr:uid="{CE7B8CEC-E66C-4056-A4BC-F50FD0BCD765}"/>
+    <hyperlink ref="J69" r:id="rId37" xr:uid="{418FB194-6D81-4848-BEFC-F1D100EADE76}"/>
+    <hyperlink ref="J71" r:id="rId38" xr:uid="{CB89306B-2749-4ECB-B1D5-8EC926319B2A}"/>
+    <hyperlink ref="J72" r:id="rId39" xr:uid="{66013A53-362C-4762-BAB1-7939CF397647}"/>
+    <hyperlink ref="J73" r:id="rId40" xr:uid="{9A130A48-7AD4-402D-B23E-9F8D5B32A59F}"/>
+    <hyperlink ref="J74" r:id="rId41" xr:uid="{3FC14995-C0EC-49B1-B08F-CDF1CE3F5568}"/>
+    <hyperlink ref="J75" r:id="rId42" xr:uid="{9FA080A9-104E-4D27-9B05-BE0AEFB4C8E5}"/>
+    <hyperlink ref="J76" r:id="rId43" xr:uid="{495703A2-618F-4AA1-9B0A-884A4C9E84BB}"/>
+    <hyperlink ref="J78" r:id="rId44" xr:uid="{623984D0-3F3F-4239-BB0E-FE949A5FBE33}"/>
+    <hyperlink ref="J80" r:id="rId45" xr:uid="{6877F3C5-B8CC-4816-AD9B-0F891FD0A155}"/>
+    <hyperlink ref="J86" r:id="rId46" xr:uid="{7B0883B5-60E1-4ADD-9AE4-4639BE3964A3}"/>
+    <hyperlink ref="J88" r:id="rId47" xr:uid="{166A0949-4396-4D4F-91DF-8C261F430FC4}"/>
+    <hyperlink ref="J89" r:id="rId48" xr:uid="{7EFEA78C-0C7E-42A6-8D63-437FE85C41FD}"/>
+    <hyperlink ref="J90" r:id="rId49" xr:uid="{8295EF04-202A-42EC-817F-BFE4712CD614}"/>
+    <hyperlink ref="J92" r:id="rId50" xr:uid="{E27D8E34-B6AF-4109-817F-E5B57CDECD6C}"/>
+    <hyperlink ref="J94" r:id="rId51" xr:uid="{D867BEB1-D601-4596-A9FD-B8128BFFAC6A}"/>
+    <hyperlink ref="J95" r:id="rId52" xr:uid="{F16165BA-4662-4DBA-9AD5-BD945302C1E0}"/>
+    <hyperlink ref="J96" r:id="rId53" xr:uid="{7DE35CA9-76F0-459C-BCD5-3DDF62590DB1}"/>
+    <hyperlink ref="J101" r:id="rId54" xr:uid="{AB81B2B5-660D-4EBD-AC89-07E6CF025758}"/>
+    <hyperlink ref="J103" r:id="rId55" xr:uid="{E512EC40-4BB8-456F-828A-1BDC9C4EE1C4}"/>
+    <hyperlink ref="J104" r:id="rId56" xr:uid="{64FDE682-9A68-478D-9777-B16CA8B1CEC6}"/>
+    <hyperlink ref="J105" r:id="rId57" xr:uid="{15D0EF3F-EA4A-4853-BBEE-33413520C85F}"/>
+    <hyperlink ref="J106" r:id="rId58" xr:uid="{9200E29C-20CE-4778-9CD7-FA465C3B64A1}"/>
+    <hyperlink ref="J107" r:id="rId59" xr:uid="{FCE45A75-496E-4EAF-8E21-45511A4827A0}"/>
+    <hyperlink ref="J109" r:id="rId60" xr:uid="{A16CDCFC-A5AC-4AAF-8660-16CF2E5B17EF}"/>
+    <hyperlink ref="J110" r:id="rId61" xr:uid="{A4DFBEDE-2875-443A-8FE3-E41A86A68C50}"/>
+    <hyperlink ref="J111" r:id="rId62" xr:uid="{046DE095-24D2-4169-9FF9-797F8A2D3284}"/>
+    <hyperlink ref="J112" r:id="rId63" xr:uid="{1FF91637-C08E-4FD7-9CC5-E2F00FB7648E}"/>
+    <hyperlink ref="J113" r:id="rId64" xr:uid="{3A4EA8F2-558C-468C-926D-F23AF3E99BB9}"/>
+    <hyperlink ref="J114" r:id="rId65" xr:uid="{98CE5626-B47D-4157-A3A1-4FEF7679EDD8}"/>
+    <hyperlink ref="J116" r:id="rId66" xr:uid="{465B03D3-AFB1-4AFF-AE60-954E031DFCEA}"/>
+    <hyperlink ref="J117" r:id="rId67" xr:uid="{D4FD91EB-168F-4EC5-A059-9586A9518131}"/>
+    <hyperlink ref="J118" r:id="rId68" xr:uid="{38805BA2-64CF-4B68-9837-8C9915C86A40}"/>
+    <hyperlink ref="J119" r:id="rId69" xr:uid="{4E015EED-B797-42D0-A3A5-9EC87ED158D5}"/>
+    <hyperlink ref="J120" r:id="rId70" xr:uid="{1370FD76-A1C9-4F05-B562-8A080944E3F4}"/>
+    <hyperlink ref="J121" r:id="rId71" xr:uid="{8A0FC5EE-45F6-4731-82ED-1DB06811879E}"/>
+    <hyperlink ref="J124" r:id="rId72" xr:uid="{C0B0C75F-73A6-434D-B310-BBB5EF86936A}"/>
+    <hyperlink ref="J128" r:id="rId73" xr:uid="{327FE683-3936-4638-A6E5-91624F735631}"/>
+    <hyperlink ref="J129" r:id="rId74" xr:uid="{BE068995-9A40-48FF-AFB5-48AB5CA3F6BD}"/>
+    <hyperlink ref="J132" r:id="rId75" xr:uid="{D2BF3AB9-4C11-456C-8756-9D7D43AF9FEB}"/>
+    <hyperlink ref="J134" r:id="rId76" xr:uid="{4195FFC4-9B46-484F-8835-9BB09F4CA9CB}"/>
+    <hyperlink ref="J135" r:id="rId77" xr:uid="{33374009-958A-4AEF-B44B-0424CFBBE604}"/>
+    <hyperlink ref="J136" r:id="rId78" xr:uid="{F75E454A-A937-4D4C-B16D-F7FD87903554}"/>
+    <hyperlink ref="J140" r:id="rId79" xr:uid="{EAA9820C-2071-416A-B37D-723737B8FFE4}"/>
+    <hyperlink ref="J142" r:id="rId80" xr:uid="{82DA56F4-DBAA-4FD2-887D-69E98211D4E8}"/>
+    <hyperlink ref="J143" r:id="rId81" xr:uid="{A6D18EBD-F3CD-496E-9E6A-4F0231A4D9DB}"/>
+    <hyperlink ref="J144" r:id="rId82" xr:uid="{FD88915F-6B12-43EA-AE5E-0C2053D46374}"/>
+    <hyperlink ref="J145" r:id="rId83" xr:uid="{E596BCE4-8646-4F3E-9AC2-387BEC7CCBB7}"/>
+    <hyperlink ref="J147" r:id="rId84" xr:uid="{7CF8F5E2-94A7-4E77-8B69-48B37EFB0C69}"/>
+    <hyperlink ref="J149" r:id="rId85" xr:uid="{EDDB114B-5D17-47D5-A2FA-E9007807198F}"/>
+    <hyperlink ref="J150" r:id="rId86" xr:uid="{6F6BD5FF-FEC6-4836-AD35-9D7F75421AC6}"/>
+    <hyperlink ref="J151" r:id="rId87" xr:uid="{BFB52EDF-1AED-4316-A0AC-FF2781D840FA}"/>
+    <hyperlink ref="J152" r:id="rId88" xr:uid="{08356FB5-C773-41E5-800E-FDEB83A4560C}"/>
+    <hyperlink ref="J153" r:id="rId89" xr:uid="{3883F90E-BDB6-48DE-93E5-060D9A4EE2D9}"/>
+    <hyperlink ref="J154" r:id="rId90" xr:uid="{B721042A-B914-4932-8ED9-AC8153C1074E}"/>
+    <hyperlink ref="J155" r:id="rId91" xr:uid="{254FFF41-00E4-4691-9FF5-B08EFF5735CE}"/>
+    <hyperlink ref="J156" r:id="rId92" xr:uid="{F2E7415D-590F-469A-B409-33B2359C4DE9}"/>
+    <hyperlink ref="J159" r:id="rId93" xr:uid="{A5EE8BCD-77FE-4809-BE58-F1793D8EB066}"/>
+    <hyperlink ref="J160" r:id="rId94" xr:uid="{B50221ED-D3CA-47E5-89F4-7C838A75001B}"/>
+    <hyperlink ref="J161" r:id="rId95" xr:uid="{FC7FDFC3-91B6-4E35-A064-713B21CE8FB9}"/>
+    <hyperlink ref="J162" r:id="rId96" xr:uid="{8E3F82E4-F9DF-412F-9E45-DA19FE5A6A28}"/>
+    <hyperlink ref="J164" r:id="rId97" xr:uid="{062436F9-3ADD-44C1-B165-F6956BF338CA}"/>
+    <hyperlink ref="J165" r:id="rId98" xr:uid="{CBC549AA-782F-4F44-A7AE-B04582018BF5}"/>
+    <hyperlink ref="J167" r:id="rId99" xr:uid="{4F43BCC4-95A4-4041-86BD-CDB177C4AA18}"/>
+    <hyperlink ref="J168" r:id="rId100" xr:uid="{F5F21216-9069-4696-9BA7-50FE1B7CB900}"/>
+    <hyperlink ref="J169" r:id="rId101" xr:uid="{E2E18ED1-8EBA-473A-A249-4C19765D7F3A}"/>
+    <hyperlink ref="J171" r:id="rId102" xr:uid="{0E30D440-BD4D-4889-9147-3A80CB776D52}"/>
+    <hyperlink ref="J172" r:id="rId103" xr:uid="{77F708FD-551E-432E-A993-E4ECC7DE8A63}"/>
+    <hyperlink ref="J173" r:id="rId104" xr:uid="{F23F9734-AC3C-47F6-9E2D-E7C969CCF5C0}"/>
+    <hyperlink ref="J177" r:id="rId105" xr:uid="{08813910-1BAE-46B3-99F4-ADAFDAA0F826}"/>
+    <hyperlink ref="J178" r:id="rId106" xr:uid="{51B3945D-36FD-4BB8-83ED-8403AA1821DD}"/>
+    <hyperlink ref="J181" r:id="rId107" xr:uid="{619E6E19-4FD6-43FA-A8A9-2B43AB102AD4}"/>
+    <hyperlink ref="J182" r:id="rId108" xr:uid="{13C1272B-24FE-4F06-B698-07D8C90EB0C2}"/>
+    <hyperlink ref="J184" r:id="rId109" xr:uid="{6F265D7B-167A-4193-8372-431BD5FF407D}"/>
+    <hyperlink ref="J186" r:id="rId110" xr:uid="{745989D7-FDFE-4FA7-AAAC-8743157636FA}"/>
+    <hyperlink ref="J190" r:id="rId111" xr:uid="{7AA8B3FC-FDDF-482B-BEB6-D294B95B9BFB}"/>
+    <hyperlink ref="J191" r:id="rId112" xr:uid="{AB9ADC7A-3D88-48DD-A541-BA7D49C22D3D}"/>
+    <hyperlink ref="J192" r:id="rId113" xr:uid="{6BC9E39D-D638-47C4-9FEA-6AA75EA2F3B3}"/>
+    <hyperlink ref="J193" r:id="rId114" xr:uid="{1F48591E-22BA-4C04-8DB0-D3486D497B71}"/>
+    <hyperlink ref="J194" r:id="rId115" xr:uid="{6462B1AD-A949-4A0F-8D4D-C5F4113DAF9D}"/>
+    <hyperlink ref="J195" r:id="rId116" xr:uid="{C0B53D5D-C94A-4768-8286-CE5F62F4A1E6}"/>
+    <hyperlink ref="J196" r:id="rId117" xr:uid="{CCEC94C9-3CA7-4976-A2F8-EC919FC7A0E1}"/>
+    <hyperlink ref="J199" r:id="rId118" xr:uid="{7780F1A2-2102-41C6-B2A6-51298C7703B8}"/>
+    <hyperlink ref="J201" r:id="rId119" xr:uid="{81123EE5-C5E7-4207-8737-2D63E377E5E2}"/>
+    <hyperlink ref="J202" r:id="rId120" xr:uid="{8A6B21A6-DB31-4F82-889C-96E818C33ED5}"/>
+    <hyperlink ref="J203" r:id="rId121" xr:uid="{49D5179E-DFD3-4E1B-A62A-C940C195EBDE}"/>
+    <hyperlink ref="J205" r:id="rId122" xr:uid="{1D7637A6-4EEB-49CB-AE57-3AF0679BEC10}"/>
+    <hyperlink ref="J207" r:id="rId123" xr:uid="{21E65C84-F8A2-49AD-86FD-CB32BDDC2763}"/>
+    <hyperlink ref="J209" r:id="rId124" xr:uid="{FDB5C2E0-52E6-4F85-8372-535428A4CD45}"/>
+    <hyperlink ref="J210" r:id="rId125" xr:uid="{995F909F-795A-41AD-9C49-B157C4B4DBD4}"/>
+    <hyperlink ref="J211" r:id="rId126" xr:uid="{8CA5F2E8-E31A-4A57-8BFB-E10B817CFDE9}"/>
+    <hyperlink ref="J212" r:id="rId127" xr:uid="{4781F631-4322-41E1-AEC7-6E9F848D2151}"/>
+    <hyperlink ref="J213" r:id="rId128" xr:uid="{9181065B-CF06-4373-A00D-14940093DEDA}"/>
+    <hyperlink ref="J214" r:id="rId129" xr:uid="{47C938E3-E9D4-4540-A361-827E3E1A1E5C}"/>
+    <hyperlink ref="J215" r:id="rId130" xr:uid="{3BAB20CD-FA5B-4C1E-9D5A-182BE7672F2B}"/>
+    <hyperlink ref="J217" r:id="rId131" xr:uid="{3E1F3B91-86D8-4804-B5F3-4B9B4D3DDE1A}"/>
+    <hyperlink ref="J219" r:id="rId132" xr:uid="{E98F05BF-D502-4EB4-9DDD-161A13A2A5DA}"/>
+    <hyperlink ref="J220" r:id="rId133" xr:uid="{3E849910-45F2-43A3-B41B-002C86CCF4AD}"/>
+    <hyperlink ref="J221" r:id="rId134" xr:uid="{8D8B5C36-9E98-47EA-AB9B-A73973EB563D}"/>
+    <hyperlink ref="J222" r:id="rId135" xr:uid="{E8A6493B-EDE3-420B-8F93-0786F033C88E}"/>
+    <hyperlink ref="J223" r:id="rId136" xr:uid="{99657EAE-74BF-4A96-BB57-5F5C5194D145}"/>
+    <hyperlink ref="J225" r:id="rId137" xr:uid="{F23146C3-364B-42F4-9191-15CF0931B4F0}"/>
+    <hyperlink ref="J228" r:id="rId138" xr:uid="{7583070C-0C69-43C6-B060-3F7F3BAA54E7}"/>
+    <hyperlink ref="J230" r:id="rId139" xr:uid="{FF2B8DFD-B691-40D3-B1AD-7E0F84E3B4D5}"/>
+    <hyperlink ref="J234" r:id="rId140" xr:uid="{497A0718-8396-401C-9A80-A3F824A69DC8}"/>
+    <hyperlink ref="J236" r:id="rId141" xr:uid="{408DDBE0-CB5B-4174-84E8-0B7D13CB2C75}"/>
+    <hyperlink ref="J237" r:id="rId142" xr:uid="{A2F0AA8B-0C47-4B72-AC0F-2A5A1E31CB89}"/>
+    <hyperlink ref="J238" r:id="rId143" xr:uid="{711F85A9-B61D-4B8D-B1E2-8E3588899A14}"/>
+    <hyperlink ref="J240" r:id="rId144" xr:uid="{370F8260-50CE-4B0A-AEBB-8D19DD1AE969}"/>
+    <hyperlink ref="J241" r:id="rId145" xr:uid="{BC05828F-5D0A-490A-8DD6-8B1523A1CE52}"/>
+    <hyperlink ref="J242" r:id="rId146" xr:uid="{EE741DF7-5BD9-4500-BB37-2DCEBA76BE36}"/>
+    <hyperlink ref="J243" r:id="rId147" xr:uid="{C9A4E807-83D4-4BE4-9F75-41E5CC24C512}"/>
+    <hyperlink ref="J246" r:id="rId148" xr:uid="{DD1244DC-C156-4796-863B-FB35B4E5EE53}"/>
+    <hyperlink ref="J247" r:id="rId149" xr:uid="{95384304-D024-4182-A18B-33BE0D32C9A9}"/>
+    <hyperlink ref="J250" r:id="rId150" xr:uid="{8F401B6A-EF83-417C-A767-AE3518DEEC3B}"/>
+    <hyperlink ref="J252" r:id="rId151" xr:uid="{E466C4FA-11DF-4BDA-9459-A2ABA51FC1F7}"/>
+    <hyperlink ref="J254" r:id="rId152" xr:uid="{B508FB4D-06A9-4887-B42E-08B497EFC233}"/>
+    <hyperlink ref="J255" r:id="rId153" xr:uid="{3250E2C8-5CEA-4B16-B5CB-B7D9C8C24446}"/>
+    <hyperlink ref="J256" r:id="rId154" xr:uid="{D775A6D6-65EC-4A38-915E-DB8423AA2EC3}"/>
+    <hyperlink ref="J258" r:id="rId155" xr:uid="{FE504412-5B6B-4096-AD84-1F39FF46558F}"/>
+    <hyperlink ref="J259" r:id="rId156" xr:uid="{634F68EE-6C53-4D09-B956-6067357BA704}"/>
+    <hyperlink ref="J261" r:id="rId157" xr:uid="{048102C0-7A58-47D5-AE81-6AD85B5ECE86}"/>
+    <hyperlink ref="J263" r:id="rId158" xr:uid="{F37A052A-9055-4983-8568-185B971D9528}"/>
+    <hyperlink ref="J265" r:id="rId159" xr:uid="{796091D5-A6BE-4BDC-9AC5-8E4BBC51C783}"/>
+    <hyperlink ref="J266" r:id="rId160" xr:uid="{3F8C040A-AFCF-4512-904F-3501DEB28793}"/>
+    <hyperlink ref="J267" r:id="rId161" xr:uid="{17841B76-DE01-4292-8A7D-E0190B313723}"/>
+    <hyperlink ref="J270" r:id="rId162" xr:uid="{6D8CECAC-80C2-468E-90FF-A8CF21F8D9BE}"/>
+    <hyperlink ref="J271" r:id="rId163" xr:uid="{C2044BA5-7EBB-421E-917B-31698F553CD3}"/>
+    <hyperlink ref="J273" r:id="rId164" xr:uid="{D26AE9A2-6C84-4A67-8AA2-B3DC9CB8D0A6}"/>
+    <hyperlink ref="J274" r:id="rId165" xr:uid="{521DCF9E-8C17-443B-9322-4CD551971F8C}"/>
+    <hyperlink ref="J275" r:id="rId166" xr:uid="{9792BFD4-692F-4E24-AD32-DE396F3E343B}"/>
+    <hyperlink ref="J277" r:id="rId167" xr:uid="{F2013110-735B-4923-BCA8-C5DB37C2B0BD}"/>
+    <hyperlink ref="J278" r:id="rId168" xr:uid="{A29C6A32-FD96-42A3-A820-9A1A780AD7C9}"/>
+    <hyperlink ref="J279" r:id="rId169" xr:uid="{ED76E569-6815-402E-9F60-68E88A6F4E9C}"/>
+    <hyperlink ref="J280" r:id="rId170" xr:uid="{F68EF8FE-D96A-4421-BB53-7D2CC2E7652B}"/>
+    <hyperlink ref="J281" r:id="rId171" xr:uid="{BFE9F28A-5788-411C-B4CF-A7F4C7D81C7B}"/>
+    <hyperlink ref="J282" r:id="rId172" xr:uid="{5C8A4F1D-386D-4A9A-A1ED-4126DE9BD636}"/>
+    <hyperlink ref="J283" r:id="rId173" xr:uid="{B4A50492-B0EE-4B7C-97F6-B42C2AFA7530}"/>
+    <hyperlink ref="J286" r:id="rId174" xr:uid="{F7B94D29-1D7E-49DA-A5F0-F3B80FBB5613}"/>
+    <hyperlink ref="J287" r:id="rId175" xr:uid="{CF0744BA-4770-4619-90CA-2B8DA5069A4A}"/>
+    <hyperlink ref="J290" r:id="rId176" xr:uid="{0600B257-6159-4641-A693-78C9DEAEFC66}"/>
+    <hyperlink ref="J292" r:id="rId177" xr:uid="{036641A2-3F6E-4F7B-B0F6-98F844E1E8D3}"/>
+    <hyperlink ref="J294" r:id="rId178" xr:uid="{D555C104-9CBA-42CE-A2E8-7B5DAC671785}"/>
+    <hyperlink ref="J296" r:id="rId179" xr:uid="{8724B5B0-F39A-43A7-9AFC-E32BDBD4FAD4}"/>
+    <hyperlink ref="J297" r:id="rId180" xr:uid="{946CDEAD-156C-47C7-8BCA-B37733B831DF}"/>
+    <hyperlink ref="J298" r:id="rId181" xr:uid="{D89F4F1E-8B60-45CE-A859-5FC0EAA96891}"/>
+    <hyperlink ref="J299" r:id="rId182" xr:uid="{E1673360-C55B-42CD-ADF4-664BBB72FB50}"/>
+    <hyperlink ref="J300" r:id="rId183" xr:uid="{E52C5117-9D56-4C02-818A-50906AB886FA}"/>
+    <hyperlink ref="J301" r:id="rId184" xr:uid="{2AC2C43D-EF1C-4E6E-8688-0A8D6B061F7A}"/>
+    <hyperlink ref="J303" r:id="rId185" xr:uid="{9CC3D012-2B20-4035-89A5-546C6BD3010D}"/>
+    <hyperlink ref="J305" r:id="rId186" xr:uid="{6146EE2C-8006-47BB-BA3F-81120FF0F8BA}"/>
+    <hyperlink ref="J306" r:id="rId187" xr:uid="{D02B8922-3CAD-4CD5-ABD2-3735F60C9E81}"/>
+    <hyperlink ref="J308" r:id="rId188" xr:uid="{33D1CB9A-F198-4E1E-A1A3-EF68CAFE47D6}"/>
+    <hyperlink ref="J309" r:id="rId189" xr:uid="{A8987BA4-86E7-4459-9795-C15E0B13F347}"/>
+    <hyperlink ref="J311" r:id="rId190" xr:uid="{F5A3DBE4-76A5-4B0E-9E99-20797EAC9720}"/>
+    <hyperlink ref="J312" r:id="rId191" xr:uid="{A85FF729-EE62-40A1-855C-B994AE349068}"/>
+    <hyperlink ref="J314" r:id="rId192" xr:uid="{2CB2CA3D-10A0-490F-949C-6C9C5627A984}"/>
+    <hyperlink ref="J317" r:id="rId193" xr:uid="{6A743EBE-7958-4E85-80B7-B76C5048B7A4}"/>
+    <hyperlink ref="J318" r:id="rId194" xr:uid="{AF0989A4-CDE0-4A2D-B4FD-0AAC33E93B22}"/>
+    <hyperlink ref="J321" r:id="rId195" xr:uid="{CA1B5ED5-5085-4D1E-A365-48BB0DE52F6A}"/>
+    <hyperlink ref="J322" r:id="rId196" xr:uid="{688F51F2-C6EC-4E91-9F52-2AEBA43BE984}"/>
+    <hyperlink ref="J325" r:id="rId197" xr:uid="{FAB343C6-C3E1-4061-B67C-4190754A5A5C}"/>
+    <hyperlink ref="J326" r:id="rId198" xr:uid="{84FCA762-7558-4010-910E-A82E2DE7382A}"/>
+    <hyperlink ref="J329" r:id="rId199" xr:uid="{463244DD-2206-410A-882B-0344DBFB32A2}"/>
+    <hyperlink ref="J330" r:id="rId200" xr:uid="{23B2C2F4-EF69-4033-BAE0-F5A0560156A2}"/>
+    <hyperlink ref="J331" r:id="rId201" xr:uid="{9CF6313D-4800-42E5-8A3D-71A5F21C8373}"/>
+    <hyperlink ref="J333" r:id="rId202" xr:uid="{B613891F-83EF-474E-8DC3-428C85E72B49}"/>
+    <hyperlink ref="J334" r:id="rId203" xr:uid="{269E05D5-0EB8-4E29-B0C9-74E884E59E15}"/>
+    <hyperlink ref="J335" r:id="rId204" xr:uid="{05913387-7D2C-4BE7-A2CA-469820EEE41D}"/>
+    <hyperlink ref="J336" r:id="rId205" xr:uid="{815352EE-8227-4A5C-982A-205BD0E7AE7D}"/>
+    <hyperlink ref="J338" r:id="rId206" xr:uid="{89A76775-B46B-4CFB-B7A0-621DC676DDDA}"/>
+    <hyperlink ref="J340" r:id="rId207" xr:uid="{2843D8AE-3F39-49B2-8F5E-3B067B74FAC8}"/>
+    <hyperlink ref="J342" r:id="rId208" xr:uid="{FDECEBB5-35C9-4791-9EC3-A9AF3CF43E37}"/>
+    <hyperlink ref="J343" r:id="rId209" xr:uid="{8E406645-DA51-41DE-B1FD-A1E2269528E0}"/>
+    <hyperlink ref="J344" r:id="rId210" xr:uid="{66D8C996-B07B-4306-9BB3-193135B934FD}"/>
+    <hyperlink ref="J346" r:id="rId211" xr:uid="{06A82845-E298-4141-96E1-B5B304BC9240}"/>
+    <hyperlink ref="J349" r:id="rId212" xr:uid="{E1515A13-7D35-4FD9-9FBD-5A6639A6FBF1}"/>
+    <hyperlink ref="J350" r:id="rId213" xr:uid="{65A1E4AE-600A-4996-87AE-C706B0F4925E}"/>
+    <hyperlink ref="J352" r:id="rId214" xr:uid="{B949B37B-44F6-4EC7-AA2D-630124DE549F}"/>
+    <hyperlink ref="J354" r:id="rId215" xr:uid="{2C2DAE79-FB69-4241-A037-9EB5C6F36916}"/>
+    <hyperlink ref="J355" r:id="rId216" xr:uid="{C6513B94-A8C5-4B70-923D-269699E68F14}"/>
+    <hyperlink ref="J356" r:id="rId217" xr:uid="{48B69B20-CBF0-4FC7-975F-EC2E08E26C00}"/>
+    <hyperlink ref="J357" r:id="rId218" xr:uid="{E4D2A5C8-19B2-4D7B-89E1-FF6C80F6A9E8}"/>
+    <hyperlink ref="J358" r:id="rId219" xr:uid="{5F2116D5-1205-4257-9CBE-A2105D79DCAE}"/>
+    <hyperlink ref="J360" r:id="rId220" xr:uid="{8DE738A5-15ED-466D-8ED2-CEBCE6094846}"/>
+    <hyperlink ref="J363" r:id="rId221" xr:uid="{FC383E8C-7847-4311-8810-EE580E65FE22}"/>
+    <hyperlink ref="J364" r:id="rId222" xr:uid="{CBBC3B83-6AB7-4F8C-A6C1-06C74C6A378B}"/>
+    <hyperlink ref="J366" r:id="rId223" xr:uid="{DE596A6F-6BD8-4246-AF5C-FB5A28EBC628}"/>
+    <hyperlink ref="J368" r:id="rId224" xr:uid="{AF900B2E-3C14-4B67-B233-9E6E8E3E4CF8}"/>
+    <hyperlink ref="J370" r:id="rId225" xr:uid="{A5B18557-9A62-49BE-8D02-F54BB6B6993F}"/>
+    <hyperlink ref="J371" r:id="rId226" xr:uid="{2A289B0C-96F2-46DB-8E1A-B9BA1831224F}"/>
+    <hyperlink ref="J372" r:id="rId227" xr:uid="{B1E133BA-0502-4FCB-B525-D18C9E505057}"/>
+    <hyperlink ref="J373" r:id="rId228" xr:uid="{F099F0BA-1D92-45EA-9A25-E3281E633FD1}"/>
+    <hyperlink ref="J374" r:id="rId229" xr:uid="{79C7A11B-DC07-4CE9-AD25-9E4C1A1F7595}"/>
+    <hyperlink ref="J375" r:id="rId230" xr:uid="{C72A32A1-A6EC-4744-A3A0-A738924C81A2}"/>
+    <hyperlink ref="J376" r:id="rId231" xr:uid="{8BF5A26B-2C1F-4177-B2B6-AD0558E0A0C2}"/>
+    <hyperlink ref="J377" r:id="rId232" xr:uid="{2008AF1C-426A-4891-A926-52D75B66D5E2}"/>
+    <hyperlink ref="J378" r:id="rId233" xr:uid="{1D7CABF5-7CCD-48D0-AFC0-69FAB69F296A}"/>
+    <hyperlink ref="J379" r:id="rId234" xr:uid="{F82C449B-9926-4359-8093-A665B7673BCF}"/>
+    <hyperlink ref="J381" r:id="rId235" xr:uid="{2D83CCD4-34A0-4587-99E6-088FB2EABF11}"/>
+    <hyperlink ref="J383" r:id="rId236" xr:uid="{461C745C-25BE-4A8F-8AD4-B413301C25D7}"/>
+    <hyperlink ref="J384" r:id="rId237" xr:uid="{7C507930-D188-4C33-8604-8EBB54023A1C}"/>
+    <hyperlink ref="J386" r:id="rId238" xr:uid="{84A491FF-5E4B-4ACB-929C-0473744DC3A1}"/>
+    <hyperlink ref="J387" r:id="rId239" xr:uid="{CB3ED842-07D1-4E1A-8E0E-B71408C0D9FC}"/>
+    <hyperlink ref="J388" r:id="rId240" xr:uid="{D57F9FFF-624C-451A-8BDA-BA90023B722C}"/>
+    <hyperlink ref="J390" r:id="rId241" xr:uid="{556CD98C-7E70-4183-BAE1-BF40BCDFF738}"/>
+    <hyperlink ref="J391" r:id="rId242" xr:uid="{D15590DC-93BC-4C4E-927A-FA555ADEF788}"/>
+    <hyperlink ref="J394" r:id="rId243" xr:uid="{F4BD0455-C91A-4C10-96EF-5E2EF7566080}"/>
+    <hyperlink ref="J395" r:id="rId244" xr:uid="{4E48F696-B98A-41FB-A0F3-FD3673D743EB}"/>
+    <hyperlink ref="J396" r:id="rId245" xr:uid="{95BF9619-2DCB-4E1E-92BB-BC64ED00139C}"/>
+    <hyperlink ref="J397" r:id="rId246" xr:uid="{58B877EA-C1C0-436D-9B0C-DFC9DC6C921A}"/>
+    <hyperlink ref="J398" r:id="rId247" xr:uid="{DB06995A-EF43-4E74-BEFA-01A040AEA747}"/>
+    <hyperlink ref="J399" r:id="rId248" xr:uid="{FA09726A-3095-493C-AF4F-BBC3B3660EBF}"/>
+    <hyperlink ref="J400" r:id="rId249" xr:uid="{6B82A861-5D0B-4FA4-98DE-053E68AC5A5C}"/>
+    <hyperlink ref="J403" r:id="rId250" xr:uid="{56EA08FB-CBC6-4E6B-8EF6-740E41E299D7}"/>
+    <hyperlink ref="J404" r:id="rId251" xr:uid="{6BCD6F5D-D95D-4C71-A674-ECDB0D4999AE}"/>
+    <hyperlink ref="J405" r:id="rId252" xr:uid="{C5C83347-2D0B-40AD-B60B-E7B0FD52A63F}"/>
+    <hyperlink ref="J406" r:id="rId253" xr:uid="{23BDCC3D-499D-48D9-9493-A532108E3707}"/>
+    <hyperlink ref="J408" r:id="rId254" xr:uid="{3EE656D1-01EC-42CF-848E-CE3A255647C3}"/>
+    <hyperlink ref="J409" r:id="rId255" xr:uid="{CF23FFE1-ABAD-4268-9F83-BC75544D36A6}"/>
+    <hyperlink ref="J411" r:id="rId256" xr:uid="{746AAD2E-3A35-46AB-A944-3EC29C469A77}"/>
+    <hyperlink ref="J413" r:id="rId257" xr:uid="{B881AB44-C5F6-4D56-B125-E78DD0C3B7C3}"/>
+    <hyperlink ref="J415" r:id="rId258" xr:uid="{A6AA2EF1-0164-4DF5-9AD0-5267C6E82CFD}"/>
+    <hyperlink ref="J416" r:id="rId259" xr:uid="{24F3076C-1425-48C3-97BD-AF70A901CCEF}"/>
+    <hyperlink ref="J418" r:id="rId260" xr:uid="{C8A8431B-4E86-4539-8D69-ED2CE344E1B9}"/>
+    <hyperlink ref="J421" r:id="rId261" xr:uid="{DC457436-9F6A-4659-ABCB-31159B15912A}"/>
+    <hyperlink ref="J422" r:id="rId262" xr:uid="{55E22071-AE31-48A1-B43E-431B01723B37}"/>
+    <hyperlink ref="J430" r:id="rId263" xr:uid="{F0995B6E-442E-47B2-A678-ADB185E34168}"/>
+    <hyperlink ref="J431" r:id="rId264" xr:uid="{286703F9-2720-4BEA-A44D-B033191EB170}"/>
+    <hyperlink ref="J432" r:id="rId265" xr:uid="{91083325-8408-4BBD-BF51-73532BB1D6B6}"/>
+    <hyperlink ref="J433" r:id="rId266" xr:uid="{35E74D6C-0160-43F6-AB32-AA0A0EDC6753}"/>
+    <hyperlink ref="J434" r:id="rId267" xr:uid="{8BD058F9-AD71-4DE9-A4D8-4C899689D42C}"/>
+    <hyperlink ref="J435" r:id="rId268" xr:uid="{4EAFDDD3-673A-4839-A611-4E2F249932B3}"/>
+    <hyperlink ref="J436" r:id="rId269" xr:uid="{E4077B97-6A99-4343-9914-6900B63DBE81}"/>
+    <hyperlink ref="J437" r:id="rId270" xr:uid="{4C0F8B2D-66C9-4D18-87F0-B305F4A7F652}"/>
+    <hyperlink ref="J438" r:id="rId271" xr:uid="{DBE7337E-B617-4659-ABF1-7576FF9E4E1A}"/>
+    <hyperlink ref="J439" r:id="rId272" xr:uid="{BA6C6C98-13DF-4DAD-8FDB-24222F0C182E}"/>
+    <hyperlink ref="J445" r:id="rId273" xr:uid="{D1842A82-FD34-4478-A030-25D66D07FBEE}"/>
+    <hyperlink ref="J447" r:id="rId274" xr:uid="{FCBB35E4-77AC-4C58-8B73-0B33700B5F0D}"/>
+    <hyperlink ref="J449" r:id="rId275" xr:uid="{3539A0A0-12AD-4E57-AE00-B00EB7258587}"/>
+    <hyperlink ref="J450" r:id="rId276" xr:uid="{4EB76706-5915-4D62-82BE-92D90DB03807}"/>
+    <hyperlink ref="J451" r:id="rId277" xr:uid="{BC5A0A1F-1BBA-42D7-BE05-8702C52EE527}"/>
+    <hyperlink ref="J452" r:id="rId278" xr:uid="{6C0FFE74-8E55-49C8-9896-821BA2C59460}"/>
+    <hyperlink ref="J453" r:id="rId279" xr:uid="{F31A79F9-3B1F-47B7-97BE-F0277D6A5475}"/>
+    <hyperlink ref="J454" r:id="rId280" xr:uid="{063AC402-2069-4E86-8C9A-FEF354BFF105}"/>
+    <hyperlink ref="J455" r:id="rId281" xr:uid="{EF19D966-DEE2-4295-8EEC-EEC20E8AC5FE}"/>
+    <hyperlink ref="J458" r:id="rId282" xr:uid="{9F67E2B1-D9C1-4A32-8C3C-E339E4ECEDA5}"/>
+    <hyperlink ref="J460" r:id="rId283" xr:uid="{D1D55433-8BDE-466E-8414-1B1530BF218D}"/>
+    <hyperlink ref="J461" r:id="rId284" xr:uid="{ED23F819-87D5-41F2-8B7E-76848430916F}"/>
+    <hyperlink ref="J462" r:id="rId285" xr:uid="{531475FD-B490-46D1-9CFC-7F69D51CBFDB}"/>
+    <hyperlink ref="J465" r:id="rId286" xr:uid="{22060D6B-27AC-450D-AA45-CF3D4DE840A6}"/>
+    <hyperlink ref="J469" r:id="rId287" xr:uid="{B8D3722F-E012-46C8-986C-0D1593392EAF}"/>
+    <hyperlink ref="J473" r:id="rId288" xr:uid="{B81BE3E5-47F7-44A1-B420-BD96BF45532D}"/>
+    <hyperlink ref="J476" r:id="rId289" xr:uid="{40E712EA-4EF7-4A23-BEA5-9C2E24624757}"/>
+    <hyperlink ref="J478" r:id="rId290" xr:uid="{727ECBA8-6DB9-4295-9F77-367A830074B2}"/>
+    <hyperlink ref="J479" r:id="rId291" xr:uid="{C021C050-B9F2-4BD2-B346-9AABF7BC2531}"/>
+    <hyperlink ref="J480" r:id="rId292" xr:uid="{6FE5A092-FD4A-4E23-8BF3-D43E5751514A}"/>
+    <hyperlink ref="J481" r:id="rId293" xr:uid="{B8CC86C8-36E5-4D4B-83DD-A1DADEF66968}"/>
+    <hyperlink ref="J482" r:id="rId294" xr:uid="{61AF5E8E-0FA6-41AA-9E47-6A562A9353DF}"/>
+    <hyperlink ref="J484" r:id="rId295" xr:uid="{79297FF2-1ADC-43A8-B6E2-7CEF68B458D4}"/>
+    <hyperlink ref="J485" r:id="rId296" xr:uid="{B48171BF-EB1D-4376-BF7A-FC3202429A82}"/>
+    <hyperlink ref="J488" r:id="rId297" xr:uid="{FA26C5D9-D2C4-4B12-A6B3-AA4EA8A017BF}"/>
+    <hyperlink ref="J489" r:id="rId298" xr:uid="{EFC9E957-2DE2-4ADD-9E2B-86D4B4CD6EB3}"/>
+    <hyperlink ref="J490" r:id="rId299" xr:uid="{BCCC3CA1-6BE4-48CE-B3BD-84D22A358356}"/>
+    <hyperlink ref="J491" r:id="rId300" xr:uid="{25F597B3-F132-4158-A554-F9A5002B657A}"/>
+    <hyperlink ref="J494" r:id="rId301" xr:uid="{5DEF3900-90DE-44D7-B55D-3B0D25F4CE44}"/>
+    <hyperlink ref="J496" r:id="rId302" xr:uid="{211080F3-121D-444B-9737-410961D2E4D6}"/>
+    <hyperlink ref="J497" r:id="rId303" xr:uid="{36042A31-CBA8-42C6-AA03-71F94A7FB8C9}"/>
+    <hyperlink ref="J498" r:id="rId304" xr:uid="{62B8C29A-C0E7-4157-B541-C4EE845C7BA5}"/>
+    <hyperlink ref="J499" r:id="rId305" xr:uid="{509D63D4-2A20-47CF-93DA-0969A80F5FDF}"/>
+    <hyperlink ref="J500" r:id="rId306" xr:uid="{E780FFF0-1415-4D2D-BCA0-A4DB88E6EB2F}"/>
+    <hyperlink ref="J501" r:id="rId307" xr:uid="{E0B35826-AF78-4EC7-9466-841AC5C5B9FF}"/>
+    <hyperlink ref="J503" r:id="rId308" xr:uid="{43E11080-B267-47E7-A9AA-99DC9E7E8FF8}"/>
+    <hyperlink ref="J504" r:id="rId309" xr:uid="{38CAC708-CA51-4FFD-91EF-20D66B887BF5}"/>
+    <hyperlink ref="J508" r:id="rId310" xr:uid="{7ECED189-CEE5-4016-8176-9944212CEAFE}"/>
+    <hyperlink ref="J509" r:id="rId311" xr:uid="{37662333-98AB-42C5-81C1-417C2B982E12}"/>
+    <hyperlink ref="J510" r:id="rId312" xr:uid="{7C040D03-154E-49D4-9A2E-795D6E400C35}"/>
+    <hyperlink ref="J511" r:id="rId313" xr:uid="{51A072A9-B017-4C99-85C2-3EEFFAC54510}"/>
+    <hyperlink ref="J513" r:id="rId314" xr:uid="{1878C060-3E71-4504-8CAB-B0ADF516723D}"/>
+    <hyperlink ref="J515" r:id="rId315" xr:uid="{D8C391EF-2E7A-44F1-88B8-150876255481}"/>
+    <hyperlink ref="J516" r:id="rId316" xr:uid="{603D1AA7-2E54-403E-83EC-CAE294398E80}"/>
+    <hyperlink ref="J519" r:id="rId317" xr:uid="{593122A2-97DE-457F-979A-9B5CFA088EE3}"/>
+    <hyperlink ref="J523" r:id="rId318" xr:uid="{AACF8BBE-5236-456B-ABFE-880B1948D343}"/>
+    <hyperlink ref="J524" r:id="rId319" xr:uid="{D62912DB-DEC4-4621-A791-12BC5334364B}"/>
+    <hyperlink ref="J525" r:id="rId320" xr:uid="{218B09FD-3F30-491C-90E7-C03605A71200}"/>
+    <hyperlink ref="J535" r:id="rId321" xr:uid="{6F0F854D-D5DD-4106-90E5-D7709B35014B}"/>
+    <hyperlink ref="J536" r:id="rId322" xr:uid="{CCC294B7-BEBD-4980-BE1F-BA1D5680767B}"/>
+    <hyperlink ref="J537" r:id="rId323" xr:uid="{C66057D9-90F2-457C-80A0-A010482E374B}"/>
+    <hyperlink ref="J538" r:id="rId324" xr:uid="{882B5F47-8654-4A40-B6A2-857EC489A1F9}"/>
+    <hyperlink ref="J539" r:id="rId325" xr:uid="{BE607D49-82E9-4794-A1E3-05169ED300C8}"/>
+    <hyperlink ref="J540" r:id="rId326" xr:uid="{44F5FC7A-DA91-4125-960E-D9936C63E915}"/>
+    <hyperlink ref="J541" r:id="rId327" xr:uid="{CE8EBE7C-D4A0-444D-9CA1-85A8D1A03BCC}"/>
+    <hyperlink ref="J543" r:id="rId328" xr:uid="{E26560C6-7123-4A1A-A777-ACDC87F9344F}"/>
+    <hyperlink ref="J544" r:id="rId329" xr:uid="{89AF09C5-E02F-46DE-B5E2-B22DE3225025}"/>
+    <hyperlink ref="J546" r:id="rId330" xr:uid="{0761886B-AE02-4E70-A319-E39FB66E4BE1}"/>
+    <hyperlink ref="J547" r:id="rId331" xr:uid="{FD5264B5-CFB1-41A9-8614-3BCBAFAFDB8C}"/>
+    <hyperlink ref="J548" r:id="rId332" xr:uid="{C724748E-250A-421B-ABB3-2719DB169919}"/>
+    <hyperlink ref="J549" r:id="rId333" xr:uid="{ACFD955F-36E4-40B2-B685-949D6D1509EC}"/>
+    <hyperlink ref="J550" r:id="rId334" xr:uid="{B6281555-4047-4BEE-A582-1DFEE3680615}"/>
+    <hyperlink ref="J551" r:id="rId335" xr:uid="{0C6C8AA3-41E8-4B72-81BD-22603D0A3138}"/>
+    <hyperlink ref="J552" r:id="rId336" xr:uid="{D72E5C67-51B7-42E3-A9D5-98B452338A55}"/>
+    <hyperlink ref="J555" r:id="rId337" xr:uid="{292F4244-6063-437B-BE2D-CAA82411F95B}"/>
+    <hyperlink ref="J556" r:id="rId338" xr:uid="{DB582C2A-431D-46E8-9E1E-26CA1527774D}"/>
+    <hyperlink ref="J558" r:id="rId339" xr:uid="{360ACC93-3B98-4068-A090-B3FAF54F2E42}"/>
+    <hyperlink ref="J559" r:id="rId340" xr:uid="{E3D72344-3253-424F-A039-2EFADBBFD98E}"/>
+    <hyperlink ref="J560" r:id="rId341" xr:uid="{4366F85D-7AC3-4469-9AC6-177C5DC6977C}"/>
+    <hyperlink ref="J562" r:id="rId342" xr:uid="{30673CD5-06A0-47DB-A4F2-E4146146AE1D}"/>
+    <hyperlink ref="J569" r:id="rId343" xr:uid="{11B47F36-F3DD-4F46-96DA-96002A2505D7}"/>
+    <hyperlink ref="J570" r:id="rId344" xr:uid="{4C426E84-4B8B-4E87-8D01-B44E58357895}"/>
+    <hyperlink ref="J571" r:id="rId345" xr:uid="{F25AA6BF-8FC6-4055-A0D2-AC8772FDC5BF}"/>
+    <hyperlink ref="J572" r:id="rId346" xr:uid="{DF749404-7D8D-4960-96DA-25736F53C85C}"/>
+    <hyperlink ref="J573" r:id="rId347" xr:uid="{460FE7A7-1CB6-4364-8D48-CE7825919A1E}"/>
+    <hyperlink ref="J574" r:id="rId348" xr:uid="{0E1A3F51-10D1-4AAB-B705-77AB10BF4E71}"/>
+    <hyperlink ref="J575" r:id="rId349" xr:uid="{590560D1-BDFC-44F4-8CB2-02772DC2F6B4}"/>
+    <hyperlink ref="J576" r:id="rId350" xr:uid="{65BC9630-A157-40CD-A598-32CE61ED3210}"/>
+    <hyperlink ref="J577" r:id="rId351" xr:uid="{244D58FC-8AD1-40D0-BDBD-C1F224282407}"/>
+    <hyperlink ref="J578" r:id="rId352" xr:uid="{EF5D6097-D177-4BCE-A237-CBB769C1A1E7}"/>
+    <hyperlink ref="J579" r:id="rId353" xr:uid="{4C243BA1-B4DD-4D5A-B864-E3B53B3EE6E4}"/>
+    <hyperlink ref="J580" r:id="rId354" xr:uid="{5AAD3DA7-B739-4970-90EF-06A2A29F8256}"/>
+    <hyperlink ref="J581" r:id="rId355" xr:uid="{F464C8A4-975E-4858-9A0F-3EE46511EEA4}"/>
+    <hyperlink ref="J582" r:id="rId356" xr:uid="{0E443C3C-8866-4199-BC30-EC07C5B98D21}"/>
+    <hyperlink ref="J584" r:id="rId357" xr:uid="{C0A6FB9F-3B6C-4AA0-8919-773EC0BE825A}"/>
+    <hyperlink ref="J585" r:id="rId358" xr:uid="{B275C95B-19DA-4A11-BCB4-486ADA34C9D6}"/>
+    <hyperlink ref="J586" r:id="rId359" xr:uid="{345DFD8B-5707-4026-A92C-7ABB8110ACFA}"/>
+    <hyperlink ref="J587" r:id="rId360" xr:uid="{4493316E-D8A1-490E-921B-013FD791DB2C}"/>
+    <hyperlink ref="J592" r:id="rId361" xr:uid="{67053CAC-9B94-4C94-841F-C0085F6948E1}"/>
+    <hyperlink ref="J593" r:id="rId362" xr:uid="{6E9576A1-0EF7-4AB8-BAEE-2BF7182C0FE1}"/>
+    <hyperlink ref="J595" r:id="rId363" xr:uid="{0B6FB5A7-F6D6-4238-9F41-D9AFF994D366}"/>
+    <hyperlink ref="J596" r:id="rId364" xr:uid="{13140AD1-8F85-44FB-8C76-09F7C78E5EBF}"/>
+    <hyperlink ref="J598" r:id="rId365" xr:uid="{37F14D7D-8BEE-47F4-94B4-4E7ED8DBDCB4}"/>
+    <hyperlink ref="J599" r:id="rId366" xr:uid="{A7404B31-57EB-4CC4-858A-B9F72AA4ED1E}"/>
+    <hyperlink ref="J602" r:id="rId367" xr:uid="{FC6C6098-E203-4D43-8CC7-C0978F5D6B5F}"/>
+    <hyperlink ref="J603" r:id="rId368" xr:uid="{26B10AC1-1194-445D-8876-A6BA1BD499BC}"/>
+    <hyperlink ref="J604" r:id="rId369" xr:uid="{C83D951D-3BAA-404F-95B0-979CA5A5048D}"/>
+    <hyperlink ref="J605" r:id="rId370" xr:uid="{45CC58A0-9F74-41A4-9DE8-AAB21F9F984D}"/>
+    <hyperlink ref="J606" r:id="rId371" xr:uid="{488DD32C-7612-4E1C-879C-013B899632B0}"/>
+    <hyperlink ref="J608" r:id="rId372" xr:uid="{94B66F62-DAFE-4559-8AB4-448D26D8383F}"/>
+    <hyperlink ref="J609" r:id="rId373" xr:uid="{C36A0ED8-009C-45DF-84FE-19F6FBD0852F}"/>
+    <hyperlink ref="J611" r:id="rId374" xr:uid="{414894F9-7A81-40AC-8208-4D662FABB904}"/>
+    <hyperlink ref="J612" r:id="rId375" xr:uid="{8BCBF94E-4CE5-4189-A4C7-DD2F1B69A5BE}"/>
+    <hyperlink ref="J613" r:id="rId376" xr:uid="{05CFFFAE-07AE-46E1-B06D-6D02C1F2029F}"/>
+    <hyperlink ref="J615" r:id="rId377" xr:uid="{9158D2A8-C229-4D04-BCA1-620075D1D98B}"/>
+    <hyperlink ref="J617" r:id="rId378" xr:uid="{83AFC8F0-6630-4E8D-BEAA-5B2ECE358138}"/>
+    <hyperlink ref="J618" r:id="rId379" xr:uid="{BA7C825E-8842-486C-80FE-3AB537A9A569}"/>
+    <hyperlink ref="J619" r:id="rId380" xr:uid="{452BD0BE-A401-43B6-B540-74DC7BDA8B1C}"/>
+    <hyperlink ref="J622" r:id="rId381" xr:uid="{EE51528D-3278-4DBB-8CFE-AD5F1EFF85C6}"/>
+    <hyperlink ref="J623" r:id="rId382" xr:uid="{F5DCE901-BE19-4868-95C7-41CF7D93FCF9}"/>
+    <hyperlink ref="J624" r:id="rId383" xr:uid="{D1AD9DCB-029F-415B-A75E-C542125AA550}"/>
+    <hyperlink ref="J626" r:id="rId384" xr:uid="{7B0BBA61-4F2D-4EB2-B52C-6F3758CADD68}"/>
+    <hyperlink ref="J628" r:id="rId385" xr:uid="{8EB1D3CB-CB7B-4DCE-9B69-83A63663DE79}"/>
+    <hyperlink ref="J629" r:id="rId386" xr:uid="{D4FF30B7-53E8-434A-9848-D0E5362EA1DE}"/>
+    <hyperlink ref="J631" r:id="rId387" xr:uid="{13FF074E-EEB3-4FE6-86A1-B1FA6CE0CA66}"/>
+    <hyperlink ref="J634" r:id="rId388" xr:uid="{4B1F88D4-BF50-4210-A5A6-CB2835B82950}"/>
+    <hyperlink ref="J635" r:id="rId389" xr:uid="{447AC015-2882-478A-9342-6320A31667C1}"/>
+    <hyperlink ref="J637" r:id="rId390" xr:uid="{AE8C175D-6EED-4A82-8374-AE94788B9EBE}"/>
+    <hyperlink ref="J640" r:id="rId391" xr:uid="{95CB2846-05C4-4A1C-857F-B58C5C641000}"/>
+    <hyperlink ref="J641" r:id="rId392" xr:uid="{B6B38FCF-5BA8-4714-A07B-52DD84796D55}"/>
+    <hyperlink ref="J642" r:id="rId393" xr:uid="{A09C35CB-1061-470B-BD40-A390DA4B7559}"/>
+    <hyperlink ref="J644" r:id="rId394" xr:uid="{96D90A05-892F-45DE-A323-3D21BD14E654}"/>
+    <hyperlink ref="J645" r:id="rId395" xr:uid="{AB6324E8-3699-4128-BA5B-C2D438905480}"/>
+    <hyperlink ref="J648" r:id="rId396" xr:uid="{701ACFE3-541B-442B-B6BE-6E2309FF39B8}"/>
+    <hyperlink ref="J649" r:id="rId397" xr:uid="{9884EDE4-BDE5-4ADC-9F25-4021B976C97B}"/>
+    <hyperlink ref="J652" r:id="rId398" xr:uid="{6A7E7DBC-10AC-4557-B92B-64FFAC79A489}"/>
+    <hyperlink ref="J654" r:id="rId399" xr:uid="{EC656962-E5FC-45A4-AA83-D842C94F55B7}"/>
+    <hyperlink ref="J656" r:id="rId400" xr:uid="{A83A86D5-A671-4C3C-8F11-A4A82C158AE4}"/>
+    <hyperlink ref="J657" r:id="rId401" xr:uid="{9B4FCDF3-7D1A-49BE-BCB9-25DCD77AD87A}"/>
+    <hyperlink ref="J663" r:id="rId402" xr:uid="{FC91B183-2E37-404E-8788-8AFD90FCE74D}"/>
+    <hyperlink ref="J664" r:id="rId403" xr:uid="{47CD8C94-2C9E-4012-8823-6E4862D7A711}"/>
+    <hyperlink ref="J665" r:id="rId404" xr:uid="{70C68714-1A21-4DA8-AC74-42AE58734AB3}"/>
+    <hyperlink ref="J666" r:id="rId405" xr:uid="{2F269C0F-B007-41A7-A6A3-B2837F4BD785}"/>
+    <hyperlink ref="J667" r:id="rId406" xr:uid="{5AE6EA4D-E8EB-472A-8B36-0898C315727C}"/>
+    <hyperlink ref="J668" r:id="rId407" xr:uid="{1120A492-1207-49EA-9777-379C69379E62}"/>
+    <hyperlink ref="J669" r:id="rId408" xr:uid="{109DE9FD-7A8C-4737-9A25-E534D5522F94}"/>
+    <hyperlink ref="J670" r:id="rId409" xr:uid="{6E7198FE-D10F-4B98-B8CF-9E0528A346C7}"/>
+    <hyperlink ref="J671" r:id="rId410" xr:uid="{4A4A1CCD-3F19-46BB-A45C-195F91D2B848}"/>
+    <hyperlink ref="J672" r:id="rId411" xr:uid="{DB87502B-436E-4150-862B-9D2FFCE15A5D}"/>
+    <hyperlink ref="J673" r:id="rId412" xr:uid="{0ABEE9E0-1C5E-459C-AAD0-6DC593FD505E}"/>
+    <hyperlink ref="J674" r:id="rId413" xr:uid="{11BEBBF9-9F96-435E-BD8F-5DC778F43F03}"/>
+    <hyperlink ref="J675" r:id="rId414" xr:uid="{CBF9A151-F8F2-4EE8-B72E-4B0872434923}"/>
+    <hyperlink ref="J676" r:id="rId415" xr:uid="{81509844-656A-43E3-87DD-B7DBD93D0FEE}"/>
+    <hyperlink ref="J677" r:id="rId416" xr:uid="{52028704-7406-4328-870B-EAB0C0A6BC4E}"/>
+    <hyperlink ref="J679" r:id="rId417" xr:uid="{F176F576-F740-4337-AE54-97B2008050A9}"/>
+    <hyperlink ref="J682" r:id="rId418" xr:uid="{2E14C30F-8634-45FD-8E9D-322D67EEFF7F}"/>
+    <hyperlink ref="J683" r:id="rId419" xr:uid="{AD727ED9-DAE5-45BD-A80D-62446876022E}"/>
+    <hyperlink ref="J684" r:id="rId420" xr:uid="{256F1D9A-5AC3-418D-B244-3435688CEE38}"/>
+    <hyperlink ref="J688" r:id="rId421" xr:uid="{FFE86B26-F017-446B-B49C-89F9E5448FDF}"/>
+    <hyperlink ref="J693" r:id="rId422" xr:uid="{9DF9F0BE-2C85-4BE0-9C74-215B732D1719}"/>
+    <hyperlink ref="J694" r:id="rId423" xr:uid="{F90FE874-813D-4E83-A061-DDB1723C931D}"/>
+    <hyperlink ref="J695" r:id="rId424" xr:uid="{8B7DF9F1-0706-4392-8977-175823739B86}"/>
+    <hyperlink ref="J696" r:id="rId425" xr:uid="{4DCFCB53-17B1-48DA-9391-1E4FE31E0ADF}"/>
+    <hyperlink ref="J697" r:id="rId426" xr:uid="{AD0269AA-03CA-44AF-A3F2-481D6B2A792C}"/>
+    <hyperlink ref="J698" r:id="rId427" xr:uid="{13463103-9E21-4E91-BB7B-A610CA68B281}"/>
+    <hyperlink ref="J699" r:id="rId428" xr:uid="{41536A0B-B329-4B80-8E2D-047EEBC5DDA6}"/>
+    <hyperlink ref="J700" r:id="rId429" xr:uid="{0F2849CC-148A-4609-87AA-ECFFC9D7D9EF}"/>
+    <hyperlink ref="J705" r:id="rId430" xr:uid="{1D4E09A6-25D8-433A-9DC2-9264150176DE}"/>
+    <hyperlink ref="J708" r:id="rId431" xr:uid="{4517048C-6F8E-4DF2-ADDD-D190E88C86CD}"/>
+    <hyperlink ref="J712" r:id="rId432" xr:uid="{CBEDCF0D-A1CA-4505-9E48-A10CE41E4BF9}"/>
+    <hyperlink ref="J713" r:id="rId433" xr:uid="{0E46991D-0205-4B7B-A8D4-3DA58BADD129}"/>
+    <hyperlink ref="J714" r:id="rId434" xr:uid="{D68FCDA3-DB67-4967-9050-2A05E3FC993F}"/>
+    <hyperlink ref="J715" r:id="rId435" xr:uid="{870804FA-B02F-47B2-B588-95C198A9EBF7}"/>
+    <hyperlink ref="J718" r:id="rId436" xr:uid="{47AF4FB3-D64E-470B-AED7-3C3F25B23D77}"/>
+    <hyperlink ref="J720" r:id="rId437" xr:uid="{A897EFF5-CF39-4738-8CFB-7EEA16243349}"/>
+    <hyperlink ref="J721" r:id="rId438" xr:uid="{9D8C239D-4EEA-40A7-A2B6-F8D40F9E221F}"/>
+    <hyperlink ref="J722" r:id="rId439" xr:uid="{EB34B59B-97FC-4690-B922-CA75FE703AFB}"/>
+    <hyperlink ref="J725" r:id="rId440" xr:uid="{0D905AD4-CC31-412E-AE4D-127A0A48445B}"/>
+    <hyperlink ref="J726" r:id="rId441" xr:uid="{2BA40DB2-1C66-434B-91C4-ACAB11096C8E}"/>
+    <hyperlink ref="J728" r:id="rId442" xr:uid="{03E9DCD0-A77D-4535-B0BD-1E8E6D5B2420}"/>
+    <hyperlink ref="J729" r:id="rId443" xr:uid="{F931C5FC-5EBA-4852-B68F-0B63C290D2B7}"/>
+    <hyperlink ref="J736" r:id="rId444" xr:uid="{C0EAA12F-96F0-4577-8AC2-3A3E8FDD354A}"/>
+    <hyperlink ref="J738" r:id="rId445" xr:uid="{FF593967-D880-425F-AED6-80CB9391D2C7}"/>
+    <hyperlink ref="J739" r:id="rId446" xr:uid="{D76ED555-F492-4899-8527-F28B1F4F6B79}"/>
+    <hyperlink ref="J740" r:id="rId447" xr:uid="{E00D5FF6-7311-4D9E-A93C-3BE7B9045830}"/>
+    <hyperlink ref="J741" r:id="rId448" xr:uid="{238D3AA8-3CE0-4F33-9DE9-CEA265434528}"/>
+    <hyperlink ref="J742" r:id="rId449" xr:uid="{2ABF1E49-8E3F-4427-9A06-BF5664D5B9C5}"/>
+    <hyperlink ref="J743" r:id="rId450" xr:uid="{2584B41F-D52D-4CFF-925C-AB8DB83EC6CA}"/>
+    <hyperlink ref="J744" r:id="rId451" xr:uid="{A3C886B6-E5BF-4ECB-818B-76EFAFE0744B}"/>
+    <hyperlink ref="J747" r:id="rId452" xr:uid="{7275A71F-5E52-4010-A184-239AA9D1D548}"/>
+    <hyperlink ref="J748" r:id="rId453" xr:uid="{BE0D981E-9C78-4DF9-9ECF-5DADAF8308C9}"/>
+    <hyperlink ref="J757" r:id="rId454" xr:uid="{E76ECC85-B5E4-4EE1-BCCF-81D00B5A486F}"/>
+    <hyperlink ref="J758" r:id="rId455" xr:uid="{EFA9FB04-BBEF-44C8-88B0-C6BDDD633DE9}"/>
+    <hyperlink ref="J759" r:id="rId456" xr:uid="{69BE81CD-19ED-41CA-A0C3-040EABE08C96}"/>
+    <hyperlink ref="J760" r:id="rId457" xr:uid="{1EBE7E41-AF47-402E-A965-DD04BF69C098}"/>
+    <hyperlink ref="J761" r:id="rId458" xr:uid="{5B65B56A-DDC1-4E22-B778-59170A69BAFF}"/>
+    <hyperlink ref="J762" r:id="rId459" xr:uid="{B395B4B3-BC3C-4C2C-8397-1881F783854A}"/>
+    <hyperlink ref="J764" r:id="rId460" xr:uid="{27F5669C-4373-4EE8-A647-5594DC527BE2}"/>
+    <hyperlink ref="J765" r:id="rId461" xr:uid="{41AC0CA5-3EAA-4A46-95C6-DCF9DA4E7912}"/>
+    <hyperlink ref="J766" r:id="rId462" xr:uid="{8F8D8D31-3B65-4CC6-A9D7-79F7D4893369}"/>
+    <hyperlink ref="J767" r:id="rId463" xr:uid="{2725A120-98D0-4EE3-B7DA-FE7CF70428FB}"/>
+    <hyperlink ref="J769" r:id="rId464" xr:uid="{79024639-C18A-45C1-B562-CB4A85C45ED8}"/>
+    <hyperlink ref="J770" r:id="rId465" xr:uid="{19C44815-7F11-49BF-84D8-3E6DF80AF281}"/>
+    <hyperlink ref="J772" r:id="rId466" xr:uid="{2B56B16B-2494-432E-B37A-26FBAA610715}"/>
+    <hyperlink ref="J774" r:id="rId467" xr:uid="{150E6958-D205-41A2-85BF-D2A5B019E705}"/>
+    <hyperlink ref="J778" r:id="rId468" xr:uid="{98C10E0E-FA3D-443A-A7A9-231A33D1B4AE}"/>
+    <hyperlink ref="J781" r:id="rId469" xr:uid="{0069FA23-60A9-41CB-8D63-BED8C6F0E6B3}"/>
+    <hyperlink ref="J783" r:id="rId470" xr:uid="{CDF9950E-30E1-482A-9D05-48B2D48833F9}"/>
+    <hyperlink ref="J784" r:id="rId471" xr:uid="{C8652258-A6E6-4BAB-907B-725E88F93FD9}"/>
+    <hyperlink ref="J785" r:id="rId472" xr:uid="{282D9643-2CB1-4934-A77A-F0D840CB7492}"/>
+    <hyperlink ref="J788" r:id="rId473" xr:uid="{C6FACBE3-EBD5-4F8C-BD97-66CE2BFD3A1F}"/>
+    <hyperlink ref="J789" r:id="rId474" xr:uid="{AA7618B6-E401-4F87-9620-9FBA89BF4B7A}"/>
+    <hyperlink ref="J790" r:id="rId475" xr:uid="{0B88235D-5456-4A3C-A0FD-78DA5826E3B9}"/>
+    <hyperlink ref="J794" r:id="rId476" xr:uid="{4C4DBCAC-9E5E-43BC-8AC6-307FAE2F2BA6}"/>
+    <hyperlink ref="J795" r:id="rId477" xr:uid="{D71EA2C1-14CB-4A13-B660-4B93B312A850}"/>
+    <hyperlink ref="J796" r:id="rId478" xr:uid="{BFA81D40-7AEB-49E0-A994-4FAC6AA896EE}"/>
+    <hyperlink ref="J797" r:id="rId479" xr:uid="{F11E5F55-67C0-42E4-8985-609F03B1153F}"/>
+    <hyperlink ref="J799" r:id="rId480" xr:uid="{27D26171-E560-4D19-867C-771B234415E7}"/>
+    <hyperlink ref="J800" r:id="rId481" xr:uid="{3B9D3327-A0F6-426A-A79A-B4836718FDC0}"/>
+    <hyperlink ref="J801" r:id="rId482" xr:uid="{A915DA2E-C282-4877-A209-BD9A4B5DB2CF}"/>
+    <hyperlink ref="J802" r:id="rId483" xr:uid="{1E5A6584-B6C7-46C6-9ADC-D7B43B1E1F3C}"/>
+    <hyperlink ref="J803" r:id="rId484" xr:uid="{D43CBCDE-5142-4756-9143-F577425B68AE}"/>
+    <hyperlink ref="J804" r:id="rId485" xr:uid="{4DE2729C-8F8C-4D0C-ADF2-D796F9D0B664}"/>
+    <hyperlink ref="J805" r:id="rId486" xr:uid="{EE4F8E23-DD6A-4CB6-8FD4-FD711C9383C3}"/>
+    <hyperlink ref="J806" r:id="rId487" xr:uid="{0ACF8FBD-EA22-47E5-A677-267482DD682F}"/>
+    <hyperlink ref="J808" r:id="rId488" xr:uid="{2363ED59-956D-4F3E-9309-E6348DFCC466}"/>
+    <hyperlink ref="J810" r:id="rId489" xr:uid="{CD79C10A-0175-44EF-A4EC-2E93AE14F056}"/>
+    <hyperlink ref="J811" r:id="rId490" xr:uid="{1010E506-8CDE-4336-9DD0-085B0CF5F34A}"/>
+    <hyperlink ref="J812" r:id="rId491" xr:uid="{B1F8EC00-EBBF-47E7-9472-F94A34AE56A2}"/>
+    <hyperlink ref="J813" r:id="rId492" xr:uid="{464F82E1-26A1-4898-BC31-01741F6745B5}"/>
+    <hyperlink ref="J814" r:id="rId493" xr:uid="{77C2B74E-077D-45B9-AB7E-552C4AD3DA16}"/>
+    <hyperlink ref="J815" r:id="rId494" xr:uid="{19B6C0E1-BC07-4323-AD28-30D94D7165C6}"/>
+    <hyperlink ref="J816" r:id="rId495" xr:uid="{CE0E4578-9C6D-4E6F-BB33-D3237A83CFF6}"/>
+    <hyperlink ref="J817" r:id="rId496" xr:uid="{87D7B5DE-0D89-4414-A3D3-82D59BAC4963}"/>
+    <hyperlink ref="J818" r:id="rId497" xr:uid="{8D98E8D0-1AE0-4F23-B327-E1AE0AD45339}"/>
+    <hyperlink ref="J819" r:id="rId498" xr:uid="{B453850A-162B-44C1-832E-002E64762E87}"/>
+    <hyperlink ref="J820" r:id="rId499" xr:uid="{0E277BC6-F505-4CAA-AB23-DB72367172A5}"/>
+    <hyperlink ref="J821" r:id="rId500" xr:uid="{27611892-7060-4851-A942-B4C0F2012C45}"/>
+    <hyperlink ref="J822" r:id="rId501" xr:uid="{12A96A3B-EAA1-46A0-A627-9C97B5EE20B8}"/>
+    <hyperlink ref="J825" r:id="rId502" xr:uid="{A58D8C0E-D750-4E24-8395-7EA1DF0E9D2C}"/>
+    <hyperlink ref="J826" r:id="rId503" xr:uid="{F31F0B67-CE27-4ED2-8EAE-F0DA1FAED81D}"/>
+    <hyperlink ref="J827" r:id="rId504" xr:uid="{70A2F12E-9EE2-441E-B2E9-DDCB4A2FA095}"/>
+    <hyperlink ref="J828" r:id="rId505" xr:uid="{63064BF9-AA00-455F-9456-1827C0AB57E7}"/>
+    <hyperlink ref="J831" r:id="rId506" xr:uid="{3823E4C8-1CA2-400D-8260-82812B48D1D8}"/>
+    <hyperlink ref="J832" r:id="rId507" xr:uid="{BAE6D454-6FE5-4F16-ADE8-70B1AE9CC396}"/>
+    <hyperlink ref="J833" r:id="rId508" xr:uid="{F0A469CA-FA9E-4AA3-93F9-68616FB24EAD}"/>
+    <hyperlink ref="J836" r:id="rId509" xr:uid="{3E144F19-7124-4A9D-A276-573584360807}"/>
+    <hyperlink ref="J837" r:id="rId510" xr:uid="{B9C00CBF-6E8D-48EC-9C6B-EA78A2203113}"/>
+    <hyperlink ref="J838" r:id="rId511" xr:uid="{DE6B53A0-9E26-41BC-9429-EFCC8204205A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId468"/>
+  <pageSetup orientation="portrait" r:id="rId512"/>
   <tableParts count="1">
-    <tablePart r:id="rId469"/>
+    <tablePart r:id="rId513"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos junio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A410E716-4BB1-45A7-8F92-C5C43B682992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4A46E5-6F21-464E-A3ED-CF0948D3E310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Rechazos Calle" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$838</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$871</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7314" uniqueCount="2307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7600" uniqueCount="2390">
   <si>
     <t>Fecha</t>
   </si>
@@ -6978,6 +6978,259 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782134716/cbkbgaljwwbcpwsmvbep.jpg</t>
+  </si>
+  <si>
+    <t>MQP9AA1YXEJJ</t>
+  </si>
+  <si>
+    <t>10:34 a. m.</t>
+  </si>
+  <si>
+    <t>Está la mitad del alfajor 
+El bulto estába cerrado 
+Se abrió x que el CL pide 12 unidades</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782135234/xegenxztp9c31nxn1czd.jpg</t>
+  </si>
+  <si>
+    <t>MQP9OOGWPLZV</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782135907/crki9sujdctcdiq4cicp.jpg</t>
+  </si>
+  <si>
+    <t>MQP9P1PUX4IL</t>
+  </si>
+  <si>
+    <t>Recibe pepsico 
+Rechaza esta boleta</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782135917/r8moig9hgtbluaqyv8dt.jpg</t>
+  </si>
+  <si>
+    <t>MQP9QE0PE871</t>
+  </si>
+  <si>
+    <t>Rechaza molinos 
+No pidio</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782135979/yilxzspppbm6fuzanzvv.jpg</t>
+  </si>
+  <si>
+    <t>MQP9YE71GQI1</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782136342/stfwjbc7pmgk6gkjnklm.jpg</t>
+  </si>
+  <si>
+    <t>MQPA3KVQ1BQ5</t>
+  </si>
+  <si>
+    <t>Fantoche sdd</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782136617/qd2bkzwksybxxewxkwu2.jpg</t>
+  </si>
+  <si>
+    <t>MQPAYIX92RZM</t>
+  </si>
+  <si>
+    <t>Municiones</t>
+  </si>
+  <si>
+    <t>MQPB1R9DGFB2</t>
+  </si>
+  <si>
+    <t>11:23 a. m.</t>
+  </si>
+  <si>
+    <t>Cl 7017</t>
+  </si>
+  <si>
+    <t>Se retira el pedido completo porque faltaron 9 pep común de 84 g y es combo</t>
+  </si>
+  <si>
+    <t>MQPBTB7MM79J</t>
+  </si>
+  <si>
+    <t>11:44 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782139467/a1mr1kxmyehlkajdy2za.jpg</t>
+  </si>
+  <si>
+    <t>MQPCGBDQB1Y0</t>
+  </si>
+  <si>
+    <t>12:02 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782140545/p0ubwmvc0tpjdltbtnip.jpg</t>
+  </si>
+  <si>
+    <t>MQPD5URMK41C</t>
+  </si>
+  <si>
+    <t>2 exquisita limon</t>
+  </si>
+  <si>
+    <t>MQPD5VKHOBIX</t>
+  </si>
+  <si>
+    <t>No es el precio que le pasaron</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782141757/ufl8kilgxtaijpxoglhr.jpg</t>
+  </si>
+  <si>
+    <t>MQPD93FZZ7DF</t>
+  </si>
+  <si>
+    <t>MQPDHOT9FPL5</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782142284/tnot8dzffluzx4d1bm1p.jpg</t>
+  </si>
+  <si>
+    <t>MQPDQKN2MMJT</t>
+  </si>
+  <si>
+    <t>Faltan los pep común</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782142700/xf64irfpdgp1dwhfymcm.jpg</t>
+  </si>
+  <si>
+    <t>MQPE97HPIGVV</t>
+  </si>
+  <si>
+    <t>MQPED2I7VBYU</t>
+  </si>
+  <si>
+    <t>12:55 p. m.</t>
+  </si>
+  <si>
+    <t>MQPEHQ2BUZ35</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782143970/p7lujdyjy8cm8ji6xtca.jpg</t>
+  </si>
+  <si>
+    <t>MQPF8DRC3QEN</t>
+  </si>
+  <si>
+    <t>Pidió cambio de razón socioal</t>
+  </si>
+  <si>
+    <t>MQPFP7XSPBKS</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782146000/c7f1mjzxzxdbpz2tooe0.jpg</t>
+  </si>
+  <si>
+    <t>MQPG29MJYGS9</t>
+  </si>
+  <si>
+    <t>MQPG3BXY5NK6</t>
+  </si>
+  <si>
+    <t>01:44 p. m.</t>
+  </si>
+  <si>
+    <t>Falto 6 3d de143 grs</t>
+  </si>
+  <si>
+    <t>MQPGJKU8YP4Z</t>
+  </si>
+  <si>
+    <t>01:57 p. m.</t>
+  </si>
+  <si>
+    <t>Habré después de las 17.30</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782147419/oly5tc9fkfpagwsz9ghp.jpg</t>
+  </si>
+  <si>
+    <t>MQPGRIE5DHSP</t>
+  </si>
+  <si>
+    <t>Faltan 3 salados</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782147787/g2kbbdnvq5fek9pr5wcv.jpg</t>
+  </si>
+  <si>
+    <t>MQPINMW4X507</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782150962/zs3qdcdsmb1e3rgqucf8.jpg</t>
+  </si>
+  <si>
+    <t>MQPM3JC2RZ98</t>
+  </si>
+  <si>
+    <t>Rechaza rina matarazzo morron</t>
+  </si>
+  <si>
+    <t>MQPM6Z79L50Y</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782156907/kuprwfhnh0zwvdfph8u0.jpg</t>
+  </si>
+  <si>
+    <t>MQPNLM1KRZ5A</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782159265/e6qpujhsdteco5u8gcbk.jpg</t>
+  </si>
+  <si>
+    <t>MQPNMTIYHNN6</t>
+  </si>
+  <si>
+    <t>Pedido fuera de ruta el cliente cierra alas 14 hs y no se llegan a a destino</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782159319/wrv98zsn3ote1as40v50.jpg</t>
+  </si>
+  <si>
+    <t>MQPNOJXS31HZ</t>
+  </si>
+  <si>
+    <t>Cliente fuera de ruta cierra 14.30 y no se llegaba antes de ese horario</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782159400/pp1y5ajgsnli13vna8ju.jpg</t>
+  </si>
+  <si>
+    <t>MQPOJCIZQLBF</t>
+  </si>
+  <si>
+    <t>05:40 p. m.</t>
+  </si>
+  <si>
+    <t>Rechazo los Cheetos de 43 grs</t>
+  </si>
+  <si>
+    <t>MQQKGZHQRHNA</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782214493/k5n8qmr1bd8rmtfccpxn.jpg</t>
+  </si>
+  <si>
+    <t>MQQKKGGI5NDU</t>
+  </si>
+  <si>
+    <t>08:37 a. m.</t>
+  </si>
+  <si>
+    <t>Pep comun</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782214646/zil6tso4c86dckcjr0re.jpg</t>
   </si>
 </sst>
 </file>
@@ -7365,8 +7618,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N838">
-  <autoFilter ref="A1:N838" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N871">
+  <autoFilter ref="A1:N871" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fecha"/>
@@ -7588,7 +7841,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N838"/>
+  <dimension ref="A1:N871"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -42014,10 +42267,14 @@
         <v>2300</v>
       </c>
       <c r="J835" s="8"/>
-      <c r="K835" s="8"/>
-      <c r="L835" s="8"/>
+      <c r="K835" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L835" s="4">
+        <v>46195</v>
+      </c>
       <c r="M835" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N835" s="24">
         <v>6</v>
@@ -42139,524 +42396,1890 @@
         <v>6</v>
       </c>
     </row>
+    <row r="839" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A839" s="3" t="s">
+        <v>2307</v>
+      </c>
+      <c r="B839" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C839" s="5" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D839" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E839" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F839" s="6">
+        <v>7047</v>
+      </c>
+      <c r="G839" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H839" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I839" s="5" t="s">
+        <v>2309</v>
+      </c>
+      <c r="J839" s="11" t="s">
+        <v>2310</v>
+      </c>
+      <c r="K839" s="8"/>
+      <c r="L839" s="8"/>
+      <c r="M839" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N839" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="840" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A840" s="3" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B840" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C840" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D840" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E840" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F840" s="6">
+        <v>4367</v>
+      </c>
+      <c r="G840" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H840" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I840" s="8"/>
+      <c r="J840" s="11" t="s">
+        <v>2312</v>
+      </c>
+      <c r="K840" s="8"/>
+      <c r="L840" s="8"/>
+      <c r="M840" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N840" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="841" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A841" s="3" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B841" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C841" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D841" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E841" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F841" s="6">
+        <v>7047</v>
+      </c>
+      <c r="G841" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H841" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I841" s="5" t="s">
+        <v>2314</v>
+      </c>
+      <c r="J841" s="11" t="s">
+        <v>2315</v>
+      </c>
+      <c r="K841" s="8"/>
+      <c r="L841" s="8"/>
+      <c r="M841" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N841" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="842" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A842" s="3" t="s">
+        <v>2316</v>
+      </c>
+      <c r="B842" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C842" s="5" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D842" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E842" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F842" s="6">
+        <v>7047</v>
+      </c>
+      <c r="G842" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H842" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I842" s="5" t="s">
+        <v>2317</v>
+      </c>
+      <c r="J842" s="11" t="s">
+        <v>2318</v>
+      </c>
+      <c r="K842" s="8"/>
+      <c r="L842" s="8"/>
+      <c r="M842" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N842" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="843" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A843" s="3" t="s">
+        <v>2319</v>
+      </c>
+      <c r="B843" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C843" s="5" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D843" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E843" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F843" s="6">
+        <v>11329</v>
+      </c>
+      <c r="G843" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H843" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I843" s="8"/>
+      <c r="J843" s="11" t="s">
+        <v>2320</v>
+      </c>
+      <c r="K843" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L843" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M843" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N843" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="844" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A844" s="3" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B844" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C844" s="5" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D844" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E844" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F844" s="6">
+        <v>5238</v>
+      </c>
+      <c r="G844" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H844" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I844" s="5" t="s">
+        <v>2322</v>
+      </c>
+      <c r="J844" s="11" t="s">
+        <v>2323</v>
+      </c>
+      <c r="K844" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L844" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M844" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N844" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="845" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A845" s="3" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B845" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C845" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="D845" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E845" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F845" s="6">
+        <v>5276</v>
+      </c>
+      <c r="G845" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H845" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I845" s="5" t="s">
+        <v>2325</v>
+      </c>
+      <c r="J845" s="8"/>
+      <c r="K845" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L845" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M845" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N845" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="846" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A846" s="3" t="s">
+        <v>2326</v>
+      </c>
+      <c r="B846" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C846" s="5" t="s">
+        <v>2327</v>
+      </c>
+      <c r="D846" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E846" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F846" s="5" t="s">
+        <v>2328</v>
+      </c>
+      <c r="G846" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H846" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I846" s="5" t="s">
+        <v>2329</v>
+      </c>
+      <c r="J846" s="8"/>
+      <c r="K846" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L846" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M846" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N846" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="847" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A847" s="3" t="s">
+        <v>2330</v>
+      </c>
+      <c r="B847" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C847" s="5" t="s">
+        <v>2331</v>
+      </c>
+      <c r="D847" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E847" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F847" s="6">
+        <v>4359</v>
+      </c>
+      <c r="G847" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H847" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I847" s="8"/>
+      <c r="J847" s="11" t="s">
+        <v>2332</v>
+      </c>
+      <c r="K847" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L847" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M847" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N847" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="848" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A848" s="3" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B848" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C848" s="5" t="s">
+        <v>2334</v>
+      </c>
+      <c r="D848" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E848" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F848" s="6">
+        <v>6154</v>
+      </c>
+      <c r="G848" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H848" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I848" s="8"/>
+      <c r="J848" s="11" t="s">
+        <v>2335</v>
+      </c>
+      <c r="K848" s="8"/>
+      <c r="L848" s="8"/>
+      <c r="M848" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N848" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="849" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A849" s="3" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B849" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C849" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="D849" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E849" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F849" s="6">
+        <v>1716</v>
+      </c>
+      <c r="G849" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H849" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I849" s="5" t="s">
+        <v>2337</v>
+      </c>
+      <c r="J849" s="8"/>
+      <c r="K849" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L849" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M849" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N849" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="850" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A850" s="3" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B850" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C850" s="5" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D850" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E850" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F850" s="6">
+        <v>4663</v>
+      </c>
+      <c r="G850" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H850" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I850" s="5" t="s">
+        <v>2339</v>
+      </c>
+      <c r="J850" s="11" t="s">
+        <v>2340</v>
+      </c>
+      <c r="K850" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L850" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M850" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N850" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="851" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A851" s="3" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B851" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C851" s="13">
+        <v>0.51666666666666672</v>
+      </c>
+      <c r="D851" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E851" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F851" s="6">
+        <v>6731</v>
+      </c>
+      <c r="G851" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H851" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I851" s="8"/>
+      <c r="J851" s="8"/>
+      <c r="K851" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L851" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M851" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N851" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="852" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A852" s="3" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B852" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C852" s="13">
+        <v>0.52222222222222225</v>
+      </c>
+      <c r="D852" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E852" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F852" s="6">
+        <v>4044</v>
+      </c>
+      <c r="G852" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H852" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I852" s="8"/>
+      <c r="J852" s="11" t="s">
+        <v>2343</v>
+      </c>
+      <c r="K852" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L852" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M852" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N852" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="853" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A853" s="3" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B853" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C853" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D853" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E853" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F853" s="6">
+        <v>9789</v>
+      </c>
+      <c r="G853" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H853" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I853" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="J853" s="11" t="s">
+        <v>2346</v>
+      </c>
+      <c r="K853" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L853" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M853" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N853" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="854" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A854" s="3" t="s">
+        <v>2347</v>
+      </c>
+      <c r="B854" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C854" s="13">
+        <v>0.53611111111111109</v>
+      </c>
+      <c r="D854" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E854" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F854" s="6">
+        <v>6694</v>
+      </c>
+      <c r="G854" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H854" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I854" s="8"/>
+      <c r="J854" s="8"/>
+      <c r="K854" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L854" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M854" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N854" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="855" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A855" s="3" t="s">
+        <v>2348</v>
+      </c>
+      <c r="B855" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C855" s="5" t="s">
+        <v>2349</v>
+      </c>
+      <c r="D855" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E855" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F855" s="6">
+        <v>5265</v>
+      </c>
+      <c r="G855" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="H855" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I855" s="8"/>
+      <c r="J855" s="8"/>
+      <c r="K855" s="8"/>
+      <c r="L855" s="8"/>
+      <c r="M855" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N855" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="856" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A856" s="3" t="s">
+        <v>2350</v>
+      </c>
+      <c r="B856" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C856" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D856" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E856" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F856" s="6">
+        <v>3528</v>
+      </c>
+      <c r="G856" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H856" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I856" s="8"/>
+      <c r="J856" s="11" t="s">
+        <v>2351</v>
+      </c>
+      <c r="K856" s="8"/>
+      <c r="L856" s="8"/>
+      <c r="M856" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N856" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="857" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A857" s="3" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B857" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C857" s="5" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D857" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E857" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F857" s="6">
+        <v>398</v>
+      </c>
+      <c r="G857" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H857" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I857" s="5" t="s">
+        <v>2353</v>
+      </c>
+      <c r="J857" s="8"/>
+      <c r="K857" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L857" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M857" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N857" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="858" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A858" s="3" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B858" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C858" s="5" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D858" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E858" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F858" s="6">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="G858" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H858" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I858" s="8"/>
+      <c r="J858" s="11" t="s">
+        <v>2355</v>
+      </c>
+      <c r="K858" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L858" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M858" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N858" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="859" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A859" s="3" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B859" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C859" s="13">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="D859" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E859" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F859" s="6">
+        <v>5591</v>
+      </c>
+      <c r="G859" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H859" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I859" s="8"/>
+      <c r="J859" s="8"/>
+      <c r="K859" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L859" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M859" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N859" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="860" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A860" s="3" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B860" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C860" s="5" t="s">
+        <v>2358</v>
+      </c>
+      <c r="D860" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E860" s="5" t="s">
+        <v>1513</v>
+      </c>
+      <c r="F860" s="6">
+        <v>1365</v>
+      </c>
+      <c r="G860" s="5" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H860" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I860" s="5" t="s">
+        <v>2359</v>
+      </c>
+      <c r="J860" s="8"/>
+      <c r="K860" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L860" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M860" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N860" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="861" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A861" s="3" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B861" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C861" s="5" t="s">
+        <v>2361</v>
+      </c>
+      <c r="D861" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E861" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F861" s="6">
+        <v>11193</v>
+      </c>
+      <c r="G861" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H861" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I861" s="5" t="s">
+        <v>2362</v>
+      </c>
+      <c r="J861" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="K861" s="8"/>
+      <c r="L861" s="8"/>
+      <c r="M861" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N861" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="862" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A862" s="3" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B862" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C862" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="D862" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E862" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F862" s="6">
+        <v>5216</v>
+      </c>
+      <c r="G862" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H862" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I862" s="5" t="s">
+        <v>2365</v>
+      </c>
+      <c r="J862" s="11" t="s">
+        <v>2366</v>
+      </c>
+      <c r="K862" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L862" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M862" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N862" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="863" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A863" s="3" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B863" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C863" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="D863" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E863" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F863" s="6">
+        <v>10926</v>
+      </c>
+      <c r="G863" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H863" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I863" s="8"/>
+      <c r="J863" s="11" t="s">
+        <v>2368</v>
+      </c>
+      <c r="K863" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L863" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M863" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N863" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="864" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A864" s="3" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B864" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C864" s="13">
+        <v>0.68958333333333333</v>
+      </c>
+      <c r="D864" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E864" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F864" s="6">
+        <v>5574</v>
+      </c>
+      <c r="G864" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H864" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I864" s="5" t="s">
+        <v>2370</v>
+      </c>
+      <c r="J864" s="8"/>
+      <c r="K864" s="8"/>
+      <c r="L864" s="8"/>
+      <c r="M864" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N864" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="865" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A865" s="3" t="s">
+        <v>2371</v>
+      </c>
+      <c r="B865" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C865" s="13">
+        <v>0.69097222222222221</v>
+      </c>
+      <c r="D865" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E865" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F865" s="6">
+        <v>5541</v>
+      </c>
+      <c r="G865" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H865" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I865" s="8"/>
+      <c r="J865" s="11" t="s">
+        <v>2372</v>
+      </c>
+      <c r="K865" s="8"/>
+      <c r="L865" s="8"/>
+      <c r="M865" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N865" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="866" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A866" s="3" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B866" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C866" s="5" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D866" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E866" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F866" s="6">
+        <v>4956</v>
+      </c>
+      <c r="G866" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H866" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I866" s="8"/>
+      <c r="J866" s="11" t="s">
+        <v>2374</v>
+      </c>
+      <c r="K866" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L866" s="4">
+        <v>46195</v>
+      </c>
+      <c r="M866" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N866" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="867" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A867" s="3" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B867" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C867" s="5" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D867" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E867" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F867" s="6">
+        <v>4853</v>
+      </c>
+      <c r="G867" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H867" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I867" s="5" t="s">
+        <v>2376</v>
+      </c>
+      <c r="J867" s="11" t="s">
+        <v>2377</v>
+      </c>
+      <c r="K867" s="8"/>
+      <c r="L867" s="8"/>
+      <c r="M867" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N867" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="868" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A868" s="3" t="s">
+        <v>2378</v>
+      </c>
+      <c r="B868" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C868" s="5" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D868" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E868" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F868" s="6">
+        <v>3879</v>
+      </c>
+      <c r="G868" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H868" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I868" s="5" t="s">
+        <v>2379</v>
+      </c>
+      <c r="J868" s="11" t="s">
+        <v>2380</v>
+      </c>
+      <c r="K868" s="8"/>
+      <c r="L868" s="8"/>
+      <c r="M868" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N868" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="869" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A869" s="3" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B869" s="4">
+        <v>46195</v>
+      </c>
+      <c r="C869" s="5" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D869" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E869" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F869" s="6">
+        <v>11231</v>
+      </c>
+      <c r="G869" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H869" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I869" s="5" t="s">
+        <v>2383</v>
+      </c>
+      <c r="J869" s="8"/>
+      <c r="K869" s="8"/>
+      <c r="L869" s="8"/>
+      <c r="M869" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N869" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="870" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A870" s="3" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B870" s="4">
+        <v>46196</v>
+      </c>
+      <c r="C870" s="5" t="s">
+        <v>970</v>
+      </c>
+      <c r="D870" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E870" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F870" s="6">
+        <v>4839</v>
+      </c>
+      <c r="G870" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H870" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I870" s="8"/>
+      <c r="J870" s="11" t="s">
+        <v>2385</v>
+      </c>
+      <c r="K870" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L870" s="4">
+        <v>46196</v>
+      </c>
+      <c r="M870" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N870" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="871" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A871" s="3" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B871" s="4">
+        <v>46196</v>
+      </c>
+      <c r="C871" s="5" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D871" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E871" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F871" s="6">
+        <v>6218</v>
+      </c>
+      <c r="G871" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H871" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I871" s="5" t="s">
+        <v>2388</v>
+      </c>
+      <c r="J871" s="11" t="s">
+        <v>2389</v>
+      </c>
+      <c r="K871" s="8"/>
+      <c r="L871" s="8"/>
+      <c r="M871" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N871" s="24">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J5" r:id="rId1" xr:uid="{1656769E-16F9-402C-8E91-D76F55FC947E}"/>
-    <hyperlink ref="J7" r:id="rId2" xr:uid="{2310EAEA-1B3E-44D4-BA3C-531AC0C7419F}"/>
-    <hyperlink ref="J8" r:id="rId3" xr:uid="{F6102953-257C-409B-A6AF-5F6ABECC80B3}"/>
-    <hyperlink ref="J10" r:id="rId4" xr:uid="{E98A8D1B-ACED-4BF5-AF0B-FB4D008DC531}"/>
-    <hyperlink ref="J13" r:id="rId5" xr:uid="{4EBB52CF-185B-468B-B812-5A86412D179D}"/>
-    <hyperlink ref="J14" r:id="rId6" xr:uid="{28FC8FE1-586C-4056-B41F-4BD3ACCF204B}"/>
-    <hyperlink ref="J17" r:id="rId7" xr:uid="{E9607504-EB9F-4DEF-AEEE-A72B4E65B4BC}"/>
-    <hyperlink ref="J19" r:id="rId8" xr:uid="{C7560DCC-A710-4B5E-A1FA-5BDF51958D35}"/>
-    <hyperlink ref="J20" r:id="rId9" xr:uid="{F28DB54D-C562-4C78-8316-F8E06351FFC6}"/>
-    <hyperlink ref="J21" r:id="rId10" xr:uid="{C66FA2A5-6700-4545-A69D-539D2A26A94C}"/>
-    <hyperlink ref="J24" r:id="rId11" xr:uid="{68BBBA05-E9E5-4BC9-91CC-94C624C7E0F9}"/>
-    <hyperlink ref="J25" r:id="rId12" xr:uid="{DE8C363E-AB32-410A-A74F-167630C91FA6}"/>
-    <hyperlink ref="J26" r:id="rId13" xr:uid="{FE0CBC8B-F6F7-4B95-836C-A4E10AD6D013}"/>
-    <hyperlink ref="J27" r:id="rId14" xr:uid="{EC94E8D7-F231-4231-AB6B-A85D653E9D3C}"/>
-    <hyperlink ref="J29" r:id="rId15" xr:uid="{48EB4E6C-6BC9-42B8-8CEC-5E349DA9FEC9}"/>
-    <hyperlink ref="J30" r:id="rId16" xr:uid="{CBB72E40-0F1C-4EB4-8B7C-2E6B3645A358}"/>
-    <hyperlink ref="J31" r:id="rId17" xr:uid="{CE7923CB-7997-4A35-9513-02F8AED83429}"/>
-    <hyperlink ref="J34" r:id="rId18" xr:uid="{9D3B9B1E-B2D4-4B95-BF26-3E9679BDAC3F}"/>
-    <hyperlink ref="J35" r:id="rId19" xr:uid="{56782A9E-072C-43EE-A506-4CDA4EA39239}"/>
-    <hyperlink ref="J36" r:id="rId20" xr:uid="{B8380768-F695-4667-8C60-54DB032BA5EB}"/>
-    <hyperlink ref="J37" r:id="rId21" xr:uid="{0077679A-6421-47C0-B66C-DAF27FFF9782}"/>
-    <hyperlink ref="J38" r:id="rId22" xr:uid="{4931036E-0E0D-4B9F-B549-AD539A53BED5}"/>
-    <hyperlink ref="J46" r:id="rId23" xr:uid="{80AEE082-82C9-435E-AB52-9DDC460F3809}"/>
-    <hyperlink ref="J47" r:id="rId24" xr:uid="{12AF2E7A-EBC5-4A06-96D0-66BA0E4A55DB}"/>
-    <hyperlink ref="J48" r:id="rId25" xr:uid="{2E57B502-94BC-43E0-A597-15F245AFB16B}"/>
-    <hyperlink ref="J49" r:id="rId26" xr:uid="{DEB44B3C-B8D7-495A-AAC7-1262E9619C9A}"/>
-    <hyperlink ref="J50" r:id="rId27" xr:uid="{2D9E5C70-7888-4E67-92FE-2667F9F236FE}"/>
-    <hyperlink ref="J52" r:id="rId28" xr:uid="{11A81ED4-0B09-4222-AAFD-72F45E8DFF4F}"/>
-    <hyperlink ref="J53" r:id="rId29" xr:uid="{84530DB2-363F-4A2E-BA0C-3D925D4DBDDC}"/>
-    <hyperlink ref="J54" r:id="rId30" xr:uid="{6717E373-EE8A-4402-82C4-728D05C53943}"/>
-    <hyperlink ref="J56" r:id="rId31" xr:uid="{BB642912-A582-4C4B-8BCF-DBC4862F05DB}"/>
-    <hyperlink ref="J59" r:id="rId32" xr:uid="{BCB2C4AF-9162-4A5E-915C-815E84F29D41}"/>
-    <hyperlink ref="J61" r:id="rId33" xr:uid="{74D6ACE2-72DA-4DB0-8E56-24549CFBEC00}"/>
-    <hyperlink ref="J62" r:id="rId34" xr:uid="{598D53A9-87B4-4597-A2C7-57F70E6B7852}"/>
-    <hyperlink ref="J63" r:id="rId35" xr:uid="{7D679FB1-A70B-44C8-B60F-1C47F11D6D68}"/>
-    <hyperlink ref="J64" r:id="rId36" xr:uid="{CE7B8CEC-E66C-4056-A4BC-F50FD0BCD765}"/>
-    <hyperlink ref="J69" r:id="rId37" xr:uid="{418FB194-6D81-4848-BEFC-F1D100EADE76}"/>
-    <hyperlink ref="J71" r:id="rId38" xr:uid="{CB89306B-2749-4ECB-B1D5-8EC926319B2A}"/>
-    <hyperlink ref="J72" r:id="rId39" xr:uid="{66013A53-362C-4762-BAB1-7939CF397647}"/>
-    <hyperlink ref="J73" r:id="rId40" xr:uid="{9A130A48-7AD4-402D-B23E-9F8D5B32A59F}"/>
-    <hyperlink ref="J74" r:id="rId41" xr:uid="{3FC14995-C0EC-49B1-B08F-CDF1CE3F5568}"/>
-    <hyperlink ref="J75" r:id="rId42" xr:uid="{9FA080A9-104E-4D27-9B05-BE0AEFB4C8E5}"/>
-    <hyperlink ref="J76" r:id="rId43" xr:uid="{495703A2-618F-4AA1-9B0A-884A4C9E84BB}"/>
-    <hyperlink ref="J78" r:id="rId44" xr:uid="{623984D0-3F3F-4239-BB0E-FE949A5FBE33}"/>
-    <hyperlink ref="J80" r:id="rId45" xr:uid="{6877F3C5-B8CC-4816-AD9B-0F891FD0A155}"/>
-    <hyperlink ref="J86" r:id="rId46" xr:uid="{7B0883B5-60E1-4ADD-9AE4-4639BE3964A3}"/>
-    <hyperlink ref="J88" r:id="rId47" xr:uid="{166A0949-4396-4D4F-91DF-8C261F430FC4}"/>
-    <hyperlink ref="J89" r:id="rId48" xr:uid="{7EFEA78C-0C7E-42A6-8D63-437FE85C41FD}"/>
-    <hyperlink ref="J90" r:id="rId49" xr:uid="{8295EF04-202A-42EC-817F-BFE4712CD614}"/>
-    <hyperlink ref="J92" r:id="rId50" xr:uid="{E27D8E34-B6AF-4109-817F-E5B57CDECD6C}"/>
-    <hyperlink ref="J94" r:id="rId51" xr:uid="{D867BEB1-D601-4596-A9FD-B8128BFFAC6A}"/>
-    <hyperlink ref="J95" r:id="rId52" xr:uid="{F16165BA-4662-4DBA-9AD5-BD945302C1E0}"/>
-    <hyperlink ref="J96" r:id="rId53" xr:uid="{7DE35CA9-76F0-459C-BCD5-3DDF62590DB1}"/>
-    <hyperlink ref="J101" r:id="rId54" xr:uid="{AB81B2B5-660D-4EBD-AC89-07E6CF025758}"/>
-    <hyperlink ref="J103" r:id="rId55" xr:uid="{E512EC40-4BB8-456F-828A-1BDC9C4EE1C4}"/>
-    <hyperlink ref="J104" r:id="rId56" xr:uid="{64FDE682-9A68-478D-9777-B16CA8B1CEC6}"/>
-    <hyperlink ref="J105" r:id="rId57" xr:uid="{15D0EF3F-EA4A-4853-BBEE-33413520C85F}"/>
-    <hyperlink ref="J106" r:id="rId58" xr:uid="{9200E29C-20CE-4778-9CD7-FA465C3B64A1}"/>
-    <hyperlink ref="J107" r:id="rId59" xr:uid="{FCE45A75-496E-4EAF-8E21-45511A4827A0}"/>
-    <hyperlink ref="J109" r:id="rId60" xr:uid="{A16CDCFC-A5AC-4AAF-8660-16CF2E5B17EF}"/>
-    <hyperlink ref="J110" r:id="rId61" xr:uid="{A4DFBEDE-2875-443A-8FE3-E41A86A68C50}"/>
-    <hyperlink ref="J111" r:id="rId62" xr:uid="{046DE095-24D2-4169-9FF9-797F8A2D3284}"/>
-    <hyperlink ref="J112" r:id="rId63" xr:uid="{1FF91637-C08E-4FD7-9CC5-E2F00FB7648E}"/>
-    <hyperlink ref="J113" r:id="rId64" xr:uid="{3A4EA8F2-558C-468C-926D-F23AF3E99BB9}"/>
-    <hyperlink ref="J114" r:id="rId65" xr:uid="{98CE5626-B47D-4157-A3A1-4FEF7679EDD8}"/>
-    <hyperlink ref="J116" r:id="rId66" xr:uid="{465B03D3-AFB1-4AFF-AE60-954E031DFCEA}"/>
-    <hyperlink ref="J117" r:id="rId67" xr:uid="{D4FD91EB-168F-4EC5-A059-9586A9518131}"/>
-    <hyperlink ref="J118" r:id="rId68" xr:uid="{38805BA2-64CF-4B68-9837-8C9915C86A40}"/>
-    <hyperlink ref="J119" r:id="rId69" xr:uid="{4E015EED-B797-42D0-A3A5-9EC87ED158D5}"/>
-    <hyperlink ref="J120" r:id="rId70" xr:uid="{1370FD76-A1C9-4F05-B562-8A080944E3F4}"/>
-    <hyperlink ref="J121" r:id="rId71" xr:uid="{8A0FC5EE-45F6-4731-82ED-1DB06811879E}"/>
-    <hyperlink ref="J124" r:id="rId72" xr:uid="{C0B0C75F-73A6-434D-B310-BBB5EF86936A}"/>
-    <hyperlink ref="J128" r:id="rId73" xr:uid="{327FE683-3936-4638-A6E5-91624F735631}"/>
-    <hyperlink ref="J129" r:id="rId74" xr:uid="{BE068995-9A40-48FF-AFB5-48AB5CA3F6BD}"/>
-    <hyperlink ref="J132" r:id="rId75" xr:uid="{D2BF3AB9-4C11-456C-8756-9D7D43AF9FEB}"/>
-    <hyperlink ref="J134" r:id="rId76" xr:uid="{4195FFC4-9B46-484F-8835-9BB09F4CA9CB}"/>
-    <hyperlink ref="J135" r:id="rId77" xr:uid="{33374009-958A-4AEF-B44B-0424CFBBE604}"/>
-    <hyperlink ref="J136" r:id="rId78" xr:uid="{F75E454A-A937-4D4C-B16D-F7FD87903554}"/>
-    <hyperlink ref="J140" r:id="rId79" xr:uid="{EAA9820C-2071-416A-B37D-723737B8FFE4}"/>
-    <hyperlink ref="J142" r:id="rId80" xr:uid="{82DA56F4-DBAA-4FD2-887D-69E98211D4E8}"/>
-    <hyperlink ref="J143" r:id="rId81" xr:uid="{A6D18EBD-F3CD-496E-9E6A-4F0231A4D9DB}"/>
-    <hyperlink ref="J144" r:id="rId82" xr:uid="{FD88915F-6B12-43EA-AE5E-0C2053D46374}"/>
-    <hyperlink ref="J145" r:id="rId83" xr:uid="{E596BCE4-8646-4F3E-9AC2-387BEC7CCBB7}"/>
-    <hyperlink ref="J147" r:id="rId84" xr:uid="{7CF8F5E2-94A7-4E77-8B69-48B37EFB0C69}"/>
-    <hyperlink ref="J149" r:id="rId85" xr:uid="{EDDB114B-5D17-47D5-A2FA-E9007807198F}"/>
-    <hyperlink ref="J150" r:id="rId86" xr:uid="{6F6BD5FF-FEC6-4836-AD35-9D7F75421AC6}"/>
-    <hyperlink ref="J151" r:id="rId87" xr:uid="{BFB52EDF-1AED-4316-A0AC-FF2781D840FA}"/>
-    <hyperlink ref="J152" r:id="rId88" xr:uid="{08356FB5-C773-41E5-800E-FDEB83A4560C}"/>
-    <hyperlink ref="J153" r:id="rId89" xr:uid="{3883F90E-BDB6-48DE-93E5-060D9A4EE2D9}"/>
-    <hyperlink ref="J154" r:id="rId90" xr:uid="{B721042A-B914-4932-8ED9-AC8153C1074E}"/>
-    <hyperlink ref="J155" r:id="rId91" xr:uid="{254FFF41-00E4-4691-9FF5-B08EFF5735CE}"/>
-    <hyperlink ref="J156" r:id="rId92" xr:uid="{F2E7415D-590F-469A-B409-33B2359C4DE9}"/>
-    <hyperlink ref="J159" r:id="rId93" xr:uid="{A5EE8BCD-77FE-4809-BE58-F1793D8EB066}"/>
-    <hyperlink ref="J160" r:id="rId94" xr:uid="{B50221ED-D3CA-47E5-89F4-7C838A75001B}"/>
-    <hyperlink ref="J161" r:id="rId95" xr:uid="{FC7FDFC3-91B6-4E35-A064-713B21CE8FB9}"/>
-    <hyperlink ref="J162" r:id="rId96" xr:uid="{8E3F82E4-F9DF-412F-9E45-DA19FE5A6A28}"/>
-    <hyperlink ref="J164" r:id="rId97" xr:uid="{062436F9-3ADD-44C1-B165-F6956BF338CA}"/>
-    <hyperlink ref="J165" r:id="rId98" xr:uid="{CBC549AA-782F-4F44-A7AE-B04582018BF5}"/>
-    <hyperlink ref="J167" r:id="rId99" xr:uid="{4F43BCC4-95A4-4041-86BD-CDB177C4AA18}"/>
-    <hyperlink ref="J168" r:id="rId100" xr:uid="{F5F21216-9069-4696-9BA7-50FE1B7CB900}"/>
-    <hyperlink ref="J169" r:id="rId101" xr:uid="{E2E18ED1-8EBA-473A-A249-4C19765D7F3A}"/>
-    <hyperlink ref="J171" r:id="rId102" xr:uid="{0E30D440-BD4D-4889-9147-3A80CB776D52}"/>
-    <hyperlink ref="J172" r:id="rId103" xr:uid="{77F708FD-551E-432E-A993-E4ECC7DE8A63}"/>
-    <hyperlink ref="J173" r:id="rId104" xr:uid="{F23F9734-AC3C-47F6-9E2D-E7C969CCF5C0}"/>
-    <hyperlink ref="J177" r:id="rId105" xr:uid="{08813910-1BAE-46B3-99F4-ADAFDAA0F826}"/>
-    <hyperlink ref="J178" r:id="rId106" xr:uid="{51B3945D-36FD-4BB8-83ED-8403AA1821DD}"/>
-    <hyperlink ref="J181" r:id="rId107" xr:uid="{619E6E19-4FD6-43FA-A8A9-2B43AB102AD4}"/>
-    <hyperlink ref="J182" r:id="rId108" xr:uid="{13C1272B-24FE-4F06-B698-07D8C90EB0C2}"/>
-    <hyperlink ref="J184" r:id="rId109" xr:uid="{6F265D7B-167A-4193-8372-431BD5FF407D}"/>
-    <hyperlink ref="J186" r:id="rId110" xr:uid="{745989D7-FDFE-4FA7-AAAC-8743157636FA}"/>
-    <hyperlink ref="J190" r:id="rId111" xr:uid="{7AA8B3FC-FDDF-482B-BEB6-D294B95B9BFB}"/>
-    <hyperlink ref="J191" r:id="rId112" xr:uid="{AB9ADC7A-3D88-48DD-A541-BA7D49C22D3D}"/>
-    <hyperlink ref="J192" r:id="rId113" xr:uid="{6BC9E39D-D638-47C4-9FEA-6AA75EA2F3B3}"/>
-    <hyperlink ref="J193" r:id="rId114" xr:uid="{1F48591E-22BA-4C04-8DB0-D3486D497B71}"/>
-    <hyperlink ref="J194" r:id="rId115" xr:uid="{6462B1AD-A949-4A0F-8D4D-C5F4113DAF9D}"/>
-    <hyperlink ref="J195" r:id="rId116" xr:uid="{C0B53D5D-C94A-4768-8286-CE5F62F4A1E6}"/>
-    <hyperlink ref="J196" r:id="rId117" xr:uid="{CCEC94C9-3CA7-4976-A2F8-EC919FC7A0E1}"/>
-    <hyperlink ref="J199" r:id="rId118" xr:uid="{7780F1A2-2102-41C6-B2A6-51298C7703B8}"/>
-    <hyperlink ref="J201" r:id="rId119" xr:uid="{81123EE5-C5E7-4207-8737-2D63E377E5E2}"/>
-    <hyperlink ref="J202" r:id="rId120" xr:uid="{8A6B21A6-DB31-4F82-889C-96E818C33ED5}"/>
-    <hyperlink ref="J203" r:id="rId121" xr:uid="{49D5179E-DFD3-4E1B-A62A-C940C195EBDE}"/>
-    <hyperlink ref="J205" r:id="rId122" xr:uid="{1D7637A6-4EEB-49CB-AE57-3AF0679BEC10}"/>
-    <hyperlink ref="J207" r:id="rId123" xr:uid="{21E65C84-F8A2-49AD-86FD-CB32BDDC2763}"/>
-    <hyperlink ref="J209" r:id="rId124" xr:uid="{FDB5C2E0-52E6-4F85-8372-535428A4CD45}"/>
-    <hyperlink ref="J210" r:id="rId125" xr:uid="{995F909F-795A-41AD-9C49-B157C4B4DBD4}"/>
-    <hyperlink ref="J211" r:id="rId126" xr:uid="{8CA5F2E8-E31A-4A57-8BFB-E10B817CFDE9}"/>
-    <hyperlink ref="J212" r:id="rId127" xr:uid="{4781F631-4322-41E1-AEC7-6E9F848D2151}"/>
-    <hyperlink ref="J213" r:id="rId128" xr:uid="{9181065B-CF06-4373-A00D-14940093DEDA}"/>
-    <hyperlink ref="J214" r:id="rId129" xr:uid="{47C938E3-E9D4-4540-A361-827E3E1A1E5C}"/>
-    <hyperlink ref="J215" r:id="rId130" xr:uid="{3BAB20CD-FA5B-4C1E-9D5A-182BE7672F2B}"/>
-    <hyperlink ref="J217" r:id="rId131" xr:uid="{3E1F3B91-86D8-4804-B5F3-4B9B4D3DDE1A}"/>
-    <hyperlink ref="J219" r:id="rId132" xr:uid="{E98F05BF-D502-4EB4-9DDD-161A13A2A5DA}"/>
-    <hyperlink ref="J220" r:id="rId133" xr:uid="{3E849910-45F2-43A3-B41B-002C86CCF4AD}"/>
-    <hyperlink ref="J221" r:id="rId134" xr:uid="{8D8B5C36-9E98-47EA-AB9B-A73973EB563D}"/>
-    <hyperlink ref="J222" r:id="rId135" xr:uid="{E8A6493B-EDE3-420B-8F93-0786F033C88E}"/>
-    <hyperlink ref="J223" r:id="rId136" xr:uid="{99657EAE-74BF-4A96-BB57-5F5C5194D145}"/>
-    <hyperlink ref="J225" r:id="rId137" xr:uid="{F23146C3-364B-42F4-9191-15CF0931B4F0}"/>
-    <hyperlink ref="J228" r:id="rId138" xr:uid="{7583070C-0C69-43C6-B060-3F7F3BAA54E7}"/>
-    <hyperlink ref="J230" r:id="rId139" xr:uid="{FF2B8DFD-B691-40D3-B1AD-7E0F84E3B4D5}"/>
-    <hyperlink ref="J234" r:id="rId140" xr:uid="{497A0718-8396-401C-9A80-A3F824A69DC8}"/>
-    <hyperlink ref="J236" r:id="rId141" xr:uid="{408DDBE0-CB5B-4174-84E8-0B7D13CB2C75}"/>
-    <hyperlink ref="J237" r:id="rId142" xr:uid="{A2F0AA8B-0C47-4B72-AC0F-2A5A1E31CB89}"/>
-    <hyperlink ref="J238" r:id="rId143" xr:uid="{711F85A9-B61D-4B8D-B1E2-8E3588899A14}"/>
-    <hyperlink ref="J240" r:id="rId144" xr:uid="{370F8260-50CE-4B0A-AEBB-8D19DD1AE969}"/>
-    <hyperlink ref="J241" r:id="rId145" xr:uid="{BC05828F-5D0A-490A-8DD6-8B1523A1CE52}"/>
-    <hyperlink ref="J242" r:id="rId146" xr:uid="{EE741DF7-5BD9-4500-BB37-2DCEBA76BE36}"/>
-    <hyperlink ref="J243" r:id="rId147" xr:uid="{C9A4E807-83D4-4BE4-9F75-41E5CC24C512}"/>
-    <hyperlink ref="J246" r:id="rId148" xr:uid="{DD1244DC-C156-4796-863B-FB35B4E5EE53}"/>
-    <hyperlink ref="J247" r:id="rId149" xr:uid="{95384304-D024-4182-A18B-33BE0D32C9A9}"/>
-    <hyperlink ref="J250" r:id="rId150" xr:uid="{8F401B6A-EF83-417C-A767-AE3518DEEC3B}"/>
-    <hyperlink ref="J252" r:id="rId151" xr:uid="{E466C4FA-11DF-4BDA-9459-A2ABA51FC1F7}"/>
-    <hyperlink ref="J254" r:id="rId152" xr:uid="{B508FB4D-06A9-4887-B42E-08B497EFC233}"/>
-    <hyperlink ref="J255" r:id="rId153" xr:uid="{3250E2C8-5CEA-4B16-B5CB-B7D9C8C24446}"/>
-    <hyperlink ref="J256" r:id="rId154" xr:uid="{D775A6D6-65EC-4A38-915E-DB8423AA2EC3}"/>
-    <hyperlink ref="J258" r:id="rId155" xr:uid="{FE504412-5B6B-4096-AD84-1F39FF46558F}"/>
-    <hyperlink ref="J259" r:id="rId156" xr:uid="{634F68EE-6C53-4D09-B956-6067357BA704}"/>
-    <hyperlink ref="J261" r:id="rId157" xr:uid="{048102C0-7A58-47D5-AE81-6AD85B5ECE86}"/>
-    <hyperlink ref="J263" r:id="rId158" xr:uid="{F37A052A-9055-4983-8568-185B971D9528}"/>
-    <hyperlink ref="J265" r:id="rId159" xr:uid="{796091D5-A6BE-4BDC-9AC5-8E4BBC51C783}"/>
-    <hyperlink ref="J266" r:id="rId160" xr:uid="{3F8C040A-AFCF-4512-904F-3501DEB28793}"/>
-    <hyperlink ref="J267" r:id="rId161" xr:uid="{17841B76-DE01-4292-8A7D-E0190B313723}"/>
-    <hyperlink ref="J270" r:id="rId162" xr:uid="{6D8CECAC-80C2-468E-90FF-A8CF21F8D9BE}"/>
-    <hyperlink ref="J271" r:id="rId163" xr:uid="{C2044BA5-7EBB-421E-917B-31698F553CD3}"/>
-    <hyperlink ref="J273" r:id="rId164" xr:uid="{D26AE9A2-6C84-4A67-8AA2-B3DC9CB8D0A6}"/>
-    <hyperlink ref="J274" r:id="rId165" xr:uid="{521DCF9E-8C17-443B-9322-4CD551971F8C}"/>
-    <hyperlink ref="J275" r:id="rId166" xr:uid="{9792BFD4-692F-4E24-AD32-DE396F3E343B}"/>
-    <hyperlink ref="J277" r:id="rId167" xr:uid="{F2013110-735B-4923-BCA8-C5DB37C2B0BD}"/>
-    <hyperlink ref="J278" r:id="rId168" xr:uid="{A29C6A32-FD96-42A3-A820-9A1A780AD7C9}"/>
-    <hyperlink ref="J279" r:id="rId169" xr:uid="{ED76E569-6815-402E-9F60-68E88A6F4E9C}"/>
-    <hyperlink ref="J280" r:id="rId170" xr:uid="{F68EF8FE-D96A-4421-BB53-7D2CC2E7652B}"/>
-    <hyperlink ref="J281" r:id="rId171" xr:uid="{BFE9F28A-5788-411C-B4CF-A7F4C7D81C7B}"/>
-    <hyperlink ref="J282" r:id="rId172" xr:uid="{5C8A4F1D-386D-4A9A-A1ED-4126DE9BD636}"/>
-    <hyperlink ref="J283" r:id="rId173" xr:uid="{B4A50492-B0EE-4B7C-97F6-B42C2AFA7530}"/>
-    <hyperlink ref="J286" r:id="rId174" xr:uid="{F7B94D29-1D7E-49DA-A5F0-F3B80FBB5613}"/>
-    <hyperlink ref="J287" r:id="rId175" xr:uid="{CF0744BA-4770-4619-90CA-2B8DA5069A4A}"/>
-    <hyperlink ref="J290" r:id="rId176" xr:uid="{0600B257-6159-4641-A693-78C9DEAEFC66}"/>
-    <hyperlink ref="J292" r:id="rId177" xr:uid="{036641A2-3F6E-4F7B-B0F6-98F844E1E8D3}"/>
-    <hyperlink ref="J294" r:id="rId178" xr:uid="{D555C104-9CBA-42CE-A2E8-7B5DAC671785}"/>
-    <hyperlink ref="J296" r:id="rId179" xr:uid="{8724B5B0-F39A-43A7-9AFC-E32BDBD4FAD4}"/>
-    <hyperlink ref="J297" r:id="rId180" xr:uid="{946CDEAD-156C-47C7-8BCA-B37733B831DF}"/>
-    <hyperlink ref="J298" r:id="rId181" xr:uid="{D89F4F1E-8B60-45CE-A859-5FC0EAA96891}"/>
-    <hyperlink ref="J299" r:id="rId182" xr:uid="{E1673360-C55B-42CD-ADF4-664BBB72FB50}"/>
-    <hyperlink ref="J300" r:id="rId183" xr:uid="{E52C5117-9D56-4C02-818A-50906AB886FA}"/>
-    <hyperlink ref="J301" r:id="rId184" xr:uid="{2AC2C43D-EF1C-4E6E-8688-0A8D6B061F7A}"/>
-    <hyperlink ref="J303" r:id="rId185" xr:uid="{9CC3D012-2B20-4035-89A5-546C6BD3010D}"/>
-    <hyperlink ref="J305" r:id="rId186" xr:uid="{6146EE2C-8006-47BB-BA3F-81120FF0F8BA}"/>
-    <hyperlink ref="J306" r:id="rId187" xr:uid="{D02B8922-3CAD-4CD5-ABD2-3735F60C9E81}"/>
-    <hyperlink ref="J308" r:id="rId188" xr:uid="{33D1CB9A-F198-4E1E-A1A3-EF68CAFE47D6}"/>
-    <hyperlink ref="J309" r:id="rId189" xr:uid="{A8987BA4-86E7-4459-9795-C15E0B13F347}"/>
-    <hyperlink ref="J311" r:id="rId190" xr:uid="{F5A3DBE4-76A5-4B0E-9E99-20797EAC9720}"/>
-    <hyperlink ref="J312" r:id="rId191" xr:uid="{A85FF729-EE62-40A1-855C-B994AE349068}"/>
-    <hyperlink ref="J314" r:id="rId192" xr:uid="{2CB2CA3D-10A0-490F-949C-6C9C5627A984}"/>
-    <hyperlink ref="J317" r:id="rId193" xr:uid="{6A743EBE-7958-4E85-80B7-B76C5048B7A4}"/>
-    <hyperlink ref="J318" r:id="rId194" xr:uid="{AF0989A4-CDE0-4A2D-B4FD-0AAC33E93B22}"/>
-    <hyperlink ref="J321" r:id="rId195" xr:uid="{CA1B5ED5-5085-4D1E-A365-48BB0DE52F6A}"/>
-    <hyperlink ref="J322" r:id="rId196" xr:uid="{688F51F2-C6EC-4E91-9F52-2AEBA43BE984}"/>
-    <hyperlink ref="J325" r:id="rId197" xr:uid="{FAB343C6-C3E1-4061-B67C-4190754A5A5C}"/>
-    <hyperlink ref="J326" r:id="rId198" xr:uid="{84FCA762-7558-4010-910E-A82E2DE7382A}"/>
-    <hyperlink ref="J329" r:id="rId199" xr:uid="{463244DD-2206-410A-882B-0344DBFB32A2}"/>
-    <hyperlink ref="J330" r:id="rId200" xr:uid="{23B2C2F4-EF69-4033-BAE0-F5A0560156A2}"/>
-    <hyperlink ref="J331" r:id="rId201" xr:uid="{9CF6313D-4800-42E5-8A3D-71A5F21C8373}"/>
-    <hyperlink ref="J333" r:id="rId202" xr:uid="{B613891F-83EF-474E-8DC3-428C85E72B49}"/>
-    <hyperlink ref="J334" r:id="rId203" xr:uid="{269E05D5-0EB8-4E29-B0C9-74E884E59E15}"/>
-    <hyperlink ref="J335" r:id="rId204" xr:uid="{05913387-7D2C-4BE7-A2CA-469820EEE41D}"/>
-    <hyperlink ref="J336" r:id="rId205" xr:uid="{815352EE-8227-4A5C-982A-205BD0E7AE7D}"/>
-    <hyperlink ref="J338" r:id="rId206" xr:uid="{89A76775-B46B-4CFB-B7A0-621DC676DDDA}"/>
-    <hyperlink ref="J340" r:id="rId207" xr:uid="{2843D8AE-3F39-49B2-8F5E-3B067B74FAC8}"/>
-    <hyperlink ref="J342" r:id="rId208" xr:uid="{FDECEBB5-35C9-4791-9EC3-A9AF3CF43E37}"/>
-    <hyperlink ref="J343" r:id="rId209" xr:uid="{8E406645-DA51-41DE-B1FD-A1E2269528E0}"/>
-    <hyperlink ref="J344" r:id="rId210" xr:uid="{66D8C996-B07B-4306-9BB3-193135B934FD}"/>
-    <hyperlink ref="J346" r:id="rId211" xr:uid="{06A82845-E298-4141-96E1-B5B304BC9240}"/>
-    <hyperlink ref="J349" r:id="rId212" xr:uid="{E1515A13-7D35-4FD9-9FBD-5A6639A6FBF1}"/>
-    <hyperlink ref="J350" r:id="rId213" xr:uid="{65A1E4AE-600A-4996-87AE-C706B0F4925E}"/>
-    <hyperlink ref="J352" r:id="rId214" xr:uid="{B949B37B-44F6-4EC7-AA2D-630124DE549F}"/>
-    <hyperlink ref="J354" r:id="rId215" xr:uid="{2C2DAE79-FB69-4241-A037-9EB5C6F36916}"/>
-    <hyperlink ref="J355" r:id="rId216" xr:uid="{C6513B94-A8C5-4B70-923D-269699E68F14}"/>
-    <hyperlink ref="J356" r:id="rId217" xr:uid="{48B69B20-CBF0-4FC7-975F-EC2E08E26C00}"/>
-    <hyperlink ref="J357" r:id="rId218" xr:uid="{E4D2A5C8-19B2-4D7B-89E1-FF6C80F6A9E8}"/>
-    <hyperlink ref="J358" r:id="rId219" xr:uid="{5F2116D5-1205-4257-9CBE-A2105D79DCAE}"/>
-    <hyperlink ref="J360" r:id="rId220" xr:uid="{8DE738A5-15ED-466D-8ED2-CEBCE6094846}"/>
-    <hyperlink ref="J363" r:id="rId221" xr:uid="{FC383E8C-7847-4311-8810-EE580E65FE22}"/>
-    <hyperlink ref="J364" r:id="rId222" xr:uid="{CBBC3B83-6AB7-4F8C-A6C1-06C74C6A378B}"/>
-    <hyperlink ref="J366" r:id="rId223" xr:uid="{DE596A6F-6BD8-4246-AF5C-FB5A28EBC628}"/>
-    <hyperlink ref="J368" r:id="rId224" xr:uid="{AF900B2E-3C14-4B67-B233-9E6E8E3E4CF8}"/>
-    <hyperlink ref="J370" r:id="rId225" xr:uid="{A5B18557-9A62-49BE-8D02-F54BB6B6993F}"/>
-    <hyperlink ref="J371" r:id="rId226" xr:uid="{2A289B0C-96F2-46DB-8E1A-B9BA1831224F}"/>
-    <hyperlink ref="J372" r:id="rId227" xr:uid="{B1E133BA-0502-4FCB-B525-D18C9E505057}"/>
-    <hyperlink ref="J373" r:id="rId228" xr:uid="{F099F0BA-1D92-45EA-9A25-E3281E633FD1}"/>
-    <hyperlink ref="J374" r:id="rId229" xr:uid="{79C7A11B-DC07-4CE9-AD25-9E4C1A1F7595}"/>
-    <hyperlink ref="J375" r:id="rId230" xr:uid="{C72A32A1-A6EC-4744-A3A0-A738924C81A2}"/>
-    <hyperlink ref="J376" r:id="rId231" xr:uid="{8BF5A26B-2C1F-4177-B2B6-AD0558E0A0C2}"/>
-    <hyperlink ref="J377" r:id="rId232" xr:uid="{2008AF1C-426A-4891-A926-52D75B66D5E2}"/>
-    <hyperlink ref="J378" r:id="rId233" xr:uid="{1D7CABF5-7CCD-48D0-AFC0-69FAB69F296A}"/>
-    <hyperlink ref="J379" r:id="rId234" xr:uid="{F82C449B-9926-4359-8093-A665B7673BCF}"/>
-    <hyperlink ref="J381" r:id="rId235" xr:uid="{2D83CCD4-34A0-4587-99E6-088FB2EABF11}"/>
-    <hyperlink ref="J383" r:id="rId236" xr:uid="{461C745C-25BE-4A8F-8AD4-B413301C25D7}"/>
-    <hyperlink ref="J384" r:id="rId237" xr:uid="{7C507930-D188-4C33-8604-8EBB54023A1C}"/>
-    <hyperlink ref="J386" r:id="rId238" xr:uid="{84A491FF-5E4B-4ACB-929C-0473744DC3A1}"/>
-    <hyperlink ref="J387" r:id="rId239" xr:uid="{CB3ED842-07D1-4E1A-8E0E-B71408C0D9FC}"/>
-    <hyperlink ref="J388" r:id="rId240" xr:uid="{D57F9FFF-624C-451A-8BDA-BA90023B722C}"/>
-    <hyperlink ref="J390" r:id="rId241" xr:uid="{556CD98C-7E70-4183-BAE1-BF40BCDFF738}"/>
-    <hyperlink ref="J391" r:id="rId242" xr:uid="{D15590DC-93BC-4C4E-927A-FA555ADEF788}"/>
-    <hyperlink ref="J394" r:id="rId243" xr:uid="{F4BD0455-C91A-4C10-96EF-5E2EF7566080}"/>
-    <hyperlink ref="J395" r:id="rId244" xr:uid="{4E48F696-B98A-41FB-A0F3-FD3673D743EB}"/>
-    <hyperlink ref="J396" r:id="rId245" xr:uid="{95BF9619-2DCB-4E1E-92BB-BC64ED00139C}"/>
-    <hyperlink ref="J397" r:id="rId246" xr:uid="{58B877EA-C1C0-436D-9B0C-DFC9DC6C921A}"/>
-    <hyperlink ref="J398" r:id="rId247" xr:uid="{DB06995A-EF43-4E74-BEFA-01A040AEA747}"/>
-    <hyperlink ref="J399" r:id="rId248" xr:uid="{FA09726A-3095-493C-AF4F-BBC3B3660EBF}"/>
-    <hyperlink ref="J400" r:id="rId249" xr:uid="{6B82A861-5D0B-4FA4-98DE-053E68AC5A5C}"/>
-    <hyperlink ref="J403" r:id="rId250" xr:uid="{56EA08FB-CBC6-4E6B-8EF6-740E41E299D7}"/>
-    <hyperlink ref="J404" r:id="rId251" xr:uid="{6BCD6F5D-D95D-4C71-A674-ECDB0D4999AE}"/>
-    <hyperlink ref="J405" r:id="rId252" xr:uid="{C5C83347-2D0B-40AD-B60B-E7B0FD52A63F}"/>
-    <hyperlink ref="J406" r:id="rId253" xr:uid="{23BDCC3D-499D-48D9-9493-A532108E3707}"/>
-    <hyperlink ref="J408" r:id="rId254" xr:uid="{3EE656D1-01EC-42CF-848E-CE3A255647C3}"/>
-    <hyperlink ref="J409" r:id="rId255" xr:uid="{CF23FFE1-ABAD-4268-9F83-BC75544D36A6}"/>
-    <hyperlink ref="J411" r:id="rId256" xr:uid="{746AAD2E-3A35-46AB-A944-3EC29C469A77}"/>
-    <hyperlink ref="J413" r:id="rId257" xr:uid="{B881AB44-C5F6-4D56-B125-E78DD0C3B7C3}"/>
-    <hyperlink ref="J415" r:id="rId258" xr:uid="{A6AA2EF1-0164-4DF5-9AD0-5267C6E82CFD}"/>
-    <hyperlink ref="J416" r:id="rId259" xr:uid="{24F3076C-1425-48C3-97BD-AF70A901CCEF}"/>
-    <hyperlink ref="J418" r:id="rId260" xr:uid="{C8A8431B-4E86-4539-8D69-ED2CE344E1B9}"/>
-    <hyperlink ref="J421" r:id="rId261" xr:uid="{DC457436-9F6A-4659-ABCB-31159B15912A}"/>
-    <hyperlink ref="J422" r:id="rId262" xr:uid="{55E22071-AE31-48A1-B43E-431B01723B37}"/>
-    <hyperlink ref="J430" r:id="rId263" xr:uid="{F0995B6E-442E-47B2-A678-ADB185E34168}"/>
-    <hyperlink ref="J431" r:id="rId264" xr:uid="{286703F9-2720-4BEA-A44D-B033191EB170}"/>
-    <hyperlink ref="J432" r:id="rId265" xr:uid="{91083325-8408-4BBD-BF51-73532BB1D6B6}"/>
-    <hyperlink ref="J433" r:id="rId266" xr:uid="{35E74D6C-0160-43F6-AB32-AA0A0EDC6753}"/>
-    <hyperlink ref="J434" r:id="rId267" xr:uid="{8BD058F9-AD71-4DE9-A4D8-4C899689D42C}"/>
-    <hyperlink ref="J435" r:id="rId268" xr:uid="{4EAFDDD3-673A-4839-A611-4E2F249932B3}"/>
-    <hyperlink ref="J436" r:id="rId269" xr:uid="{E4077B97-6A99-4343-9914-6900B63DBE81}"/>
-    <hyperlink ref="J437" r:id="rId270" xr:uid="{4C0F8B2D-66C9-4D18-87F0-B305F4A7F652}"/>
-    <hyperlink ref="J438" r:id="rId271" xr:uid="{DBE7337E-B617-4659-ABF1-7576FF9E4E1A}"/>
-    <hyperlink ref="J439" r:id="rId272" xr:uid="{BA6C6C98-13DF-4DAD-8FDB-24222F0C182E}"/>
-    <hyperlink ref="J445" r:id="rId273" xr:uid="{D1842A82-FD34-4478-A030-25D66D07FBEE}"/>
-    <hyperlink ref="J447" r:id="rId274" xr:uid="{FCBB35E4-77AC-4C58-8B73-0B33700B5F0D}"/>
-    <hyperlink ref="J449" r:id="rId275" xr:uid="{3539A0A0-12AD-4E57-AE00-B00EB7258587}"/>
-    <hyperlink ref="J450" r:id="rId276" xr:uid="{4EB76706-5915-4D62-82BE-92D90DB03807}"/>
-    <hyperlink ref="J451" r:id="rId277" xr:uid="{BC5A0A1F-1BBA-42D7-BE05-8702C52EE527}"/>
-    <hyperlink ref="J452" r:id="rId278" xr:uid="{6C0FFE74-8E55-49C8-9896-821BA2C59460}"/>
-    <hyperlink ref="J453" r:id="rId279" xr:uid="{F31A79F9-3B1F-47B7-97BE-F0277D6A5475}"/>
-    <hyperlink ref="J454" r:id="rId280" xr:uid="{063AC402-2069-4E86-8C9A-FEF354BFF105}"/>
-    <hyperlink ref="J455" r:id="rId281" xr:uid="{EF19D966-DEE2-4295-8EEC-EEC20E8AC5FE}"/>
-    <hyperlink ref="J458" r:id="rId282" xr:uid="{9F67E2B1-D9C1-4A32-8C3C-E339E4ECEDA5}"/>
-    <hyperlink ref="J460" r:id="rId283" xr:uid="{D1D55433-8BDE-466E-8414-1B1530BF218D}"/>
-    <hyperlink ref="J461" r:id="rId284" xr:uid="{ED23F819-87D5-41F2-8B7E-76848430916F}"/>
-    <hyperlink ref="J462" r:id="rId285" xr:uid="{531475FD-B490-46D1-9CFC-7F69D51CBFDB}"/>
-    <hyperlink ref="J465" r:id="rId286" xr:uid="{22060D6B-27AC-450D-AA45-CF3D4DE840A6}"/>
-    <hyperlink ref="J469" r:id="rId287" xr:uid="{B8D3722F-E012-46C8-986C-0D1593392EAF}"/>
-    <hyperlink ref="J473" r:id="rId288" xr:uid="{B81BE3E5-47F7-44A1-B420-BD96BF45532D}"/>
-    <hyperlink ref="J476" r:id="rId289" xr:uid="{40E712EA-4EF7-4A23-BEA5-9C2E24624757}"/>
-    <hyperlink ref="J478" r:id="rId290" xr:uid="{727ECBA8-6DB9-4295-9F77-367A830074B2}"/>
-    <hyperlink ref="J479" r:id="rId291" xr:uid="{C021C050-B9F2-4BD2-B346-9AABF7BC2531}"/>
-    <hyperlink ref="J480" r:id="rId292" xr:uid="{6FE5A092-FD4A-4E23-8BF3-D43E5751514A}"/>
-    <hyperlink ref="J481" r:id="rId293" xr:uid="{B8CC86C8-36E5-4D4B-83DD-A1DADEF66968}"/>
-    <hyperlink ref="J482" r:id="rId294" xr:uid="{61AF5E8E-0FA6-41AA-9E47-6A562A9353DF}"/>
-    <hyperlink ref="J484" r:id="rId295" xr:uid="{79297FF2-1ADC-43A8-B6E2-7CEF68B458D4}"/>
-    <hyperlink ref="J485" r:id="rId296" xr:uid="{B48171BF-EB1D-4376-BF7A-FC3202429A82}"/>
-    <hyperlink ref="J488" r:id="rId297" xr:uid="{FA26C5D9-D2C4-4B12-A6B3-AA4EA8A017BF}"/>
-    <hyperlink ref="J489" r:id="rId298" xr:uid="{EFC9E957-2DE2-4ADD-9E2B-86D4B4CD6EB3}"/>
-    <hyperlink ref="J490" r:id="rId299" xr:uid="{BCCC3CA1-6BE4-48CE-B3BD-84D22A358356}"/>
-    <hyperlink ref="J491" r:id="rId300" xr:uid="{25F597B3-F132-4158-A554-F9A5002B657A}"/>
-    <hyperlink ref="J494" r:id="rId301" xr:uid="{5DEF3900-90DE-44D7-B55D-3B0D25F4CE44}"/>
-    <hyperlink ref="J496" r:id="rId302" xr:uid="{211080F3-121D-444B-9737-410961D2E4D6}"/>
-    <hyperlink ref="J497" r:id="rId303" xr:uid="{36042A31-CBA8-42C6-AA03-71F94A7FB8C9}"/>
-    <hyperlink ref="J498" r:id="rId304" xr:uid="{62B8C29A-C0E7-4157-B541-C4EE845C7BA5}"/>
-    <hyperlink ref="J499" r:id="rId305" xr:uid="{509D63D4-2A20-47CF-93DA-0969A80F5FDF}"/>
-    <hyperlink ref="J500" r:id="rId306" xr:uid="{E780FFF0-1415-4D2D-BCA0-A4DB88E6EB2F}"/>
-    <hyperlink ref="J501" r:id="rId307" xr:uid="{E0B35826-AF78-4EC7-9466-841AC5C5B9FF}"/>
-    <hyperlink ref="J503" r:id="rId308" xr:uid="{43E11080-B267-47E7-A9AA-99DC9E7E8FF8}"/>
-    <hyperlink ref="J504" r:id="rId309" xr:uid="{38CAC708-CA51-4FFD-91EF-20D66B887BF5}"/>
-    <hyperlink ref="J508" r:id="rId310" xr:uid="{7ECED189-CEE5-4016-8176-9944212CEAFE}"/>
-    <hyperlink ref="J509" r:id="rId311" xr:uid="{37662333-98AB-42C5-81C1-417C2B982E12}"/>
-    <hyperlink ref="J510" r:id="rId312" xr:uid="{7C040D03-154E-49D4-9A2E-795D6E400C35}"/>
-    <hyperlink ref="J511" r:id="rId313" xr:uid="{51A072A9-B017-4C99-85C2-3EEFFAC54510}"/>
-    <hyperlink ref="J513" r:id="rId314" xr:uid="{1878C060-3E71-4504-8CAB-B0ADF516723D}"/>
-    <hyperlink ref="J515" r:id="rId315" xr:uid="{D8C391EF-2E7A-44F1-88B8-150876255481}"/>
-    <hyperlink ref="J516" r:id="rId316" xr:uid="{603D1AA7-2E54-403E-83EC-CAE294398E80}"/>
-    <hyperlink ref="J519" r:id="rId317" xr:uid="{593122A2-97DE-457F-979A-9B5CFA088EE3}"/>
-    <hyperlink ref="J523" r:id="rId318" xr:uid="{AACF8BBE-5236-456B-ABFE-880B1948D343}"/>
-    <hyperlink ref="J524" r:id="rId319" xr:uid="{D62912DB-DEC4-4621-A791-12BC5334364B}"/>
-    <hyperlink ref="J525" r:id="rId320" xr:uid="{218B09FD-3F30-491C-90E7-C03605A71200}"/>
-    <hyperlink ref="J535" r:id="rId321" xr:uid="{6F0F854D-D5DD-4106-90E5-D7709B35014B}"/>
-    <hyperlink ref="J536" r:id="rId322" xr:uid="{CCC294B7-BEBD-4980-BE1F-BA1D5680767B}"/>
-    <hyperlink ref="J537" r:id="rId323" xr:uid="{C66057D9-90F2-457C-80A0-A010482E374B}"/>
-    <hyperlink ref="J538" r:id="rId324" xr:uid="{882B5F47-8654-4A40-B6A2-857EC489A1F9}"/>
-    <hyperlink ref="J539" r:id="rId325" xr:uid="{BE607D49-82E9-4794-A1E3-05169ED300C8}"/>
-    <hyperlink ref="J540" r:id="rId326" xr:uid="{44F5FC7A-DA91-4125-960E-D9936C63E915}"/>
-    <hyperlink ref="J541" r:id="rId327" xr:uid="{CE8EBE7C-D4A0-444D-9CA1-85A8D1A03BCC}"/>
-    <hyperlink ref="J543" r:id="rId328" xr:uid="{E26560C6-7123-4A1A-A777-ACDC87F9344F}"/>
-    <hyperlink ref="J544" r:id="rId329" xr:uid="{89AF09C5-E02F-46DE-B5E2-B22DE3225025}"/>
-    <hyperlink ref="J546" r:id="rId330" xr:uid="{0761886B-AE02-4E70-A319-E39FB66E4BE1}"/>
-    <hyperlink ref="J547" r:id="rId331" xr:uid="{FD5264B5-CFB1-41A9-8614-3BCBAFAFDB8C}"/>
-    <hyperlink ref="J548" r:id="rId332" xr:uid="{C724748E-250A-421B-ABB3-2719DB169919}"/>
-    <hyperlink ref="J549" r:id="rId333" xr:uid="{ACFD955F-36E4-40B2-B685-949D6D1509EC}"/>
-    <hyperlink ref="J550" r:id="rId334" xr:uid="{B6281555-4047-4BEE-A582-1DFEE3680615}"/>
-    <hyperlink ref="J551" r:id="rId335" xr:uid="{0C6C8AA3-41E8-4B72-81BD-22603D0A3138}"/>
-    <hyperlink ref="J552" r:id="rId336" xr:uid="{D72E5C67-51B7-42E3-A9D5-98B452338A55}"/>
-    <hyperlink ref="J555" r:id="rId337" xr:uid="{292F4244-6063-437B-BE2D-CAA82411F95B}"/>
-    <hyperlink ref="J556" r:id="rId338" xr:uid="{DB582C2A-431D-46E8-9E1E-26CA1527774D}"/>
-    <hyperlink ref="J558" r:id="rId339" xr:uid="{360ACC93-3B98-4068-A090-B3FAF54F2E42}"/>
-    <hyperlink ref="J559" r:id="rId340" xr:uid="{E3D72344-3253-424F-A039-2EFADBBFD98E}"/>
-    <hyperlink ref="J560" r:id="rId341" xr:uid="{4366F85D-7AC3-4469-9AC6-177C5DC6977C}"/>
-    <hyperlink ref="J562" r:id="rId342" xr:uid="{30673CD5-06A0-47DB-A4F2-E4146146AE1D}"/>
-    <hyperlink ref="J569" r:id="rId343" xr:uid="{11B47F36-F3DD-4F46-96DA-96002A2505D7}"/>
-    <hyperlink ref="J570" r:id="rId344" xr:uid="{4C426E84-4B8B-4E87-8D01-B44E58357895}"/>
-    <hyperlink ref="J571" r:id="rId345" xr:uid="{F25AA6BF-8FC6-4055-A0D2-AC8772FDC5BF}"/>
-    <hyperlink ref="J572" r:id="rId346" xr:uid="{DF749404-7D8D-4960-96DA-25736F53C85C}"/>
-    <hyperlink ref="J573" r:id="rId347" xr:uid="{460FE7A7-1CB6-4364-8D48-CE7825919A1E}"/>
-    <hyperlink ref="J574" r:id="rId348" xr:uid="{0E1A3F51-10D1-4AAB-B705-77AB10BF4E71}"/>
-    <hyperlink ref="J575" r:id="rId349" xr:uid="{590560D1-BDFC-44F4-8CB2-02772DC2F6B4}"/>
-    <hyperlink ref="J576" r:id="rId350" xr:uid="{65BC9630-A157-40CD-A598-32CE61ED3210}"/>
-    <hyperlink ref="J577" r:id="rId351" xr:uid="{244D58FC-8AD1-40D0-BDBD-C1F224282407}"/>
-    <hyperlink ref="J578" r:id="rId352" xr:uid="{EF5D6097-D177-4BCE-A237-CBB769C1A1E7}"/>
-    <hyperlink ref="J579" r:id="rId353" xr:uid="{4C243BA1-B4DD-4D5A-B864-E3B53B3EE6E4}"/>
-    <hyperlink ref="J580" r:id="rId354" xr:uid="{5AAD3DA7-B739-4970-90EF-06A2A29F8256}"/>
-    <hyperlink ref="J581" r:id="rId355" xr:uid="{F464C8A4-975E-4858-9A0F-3EE46511EEA4}"/>
-    <hyperlink ref="J582" r:id="rId356" xr:uid="{0E443C3C-8866-4199-BC30-EC07C5B98D21}"/>
-    <hyperlink ref="J584" r:id="rId357" xr:uid="{C0A6FB9F-3B6C-4AA0-8919-773EC0BE825A}"/>
-    <hyperlink ref="J585" r:id="rId358" xr:uid="{B275C95B-19DA-4A11-BCB4-486ADA34C9D6}"/>
-    <hyperlink ref="J586" r:id="rId359" xr:uid="{345DFD8B-5707-4026-A92C-7ABB8110ACFA}"/>
-    <hyperlink ref="J587" r:id="rId360" xr:uid="{4493316E-D8A1-490E-921B-013FD791DB2C}"/>
-    <hyperlink ref="J592" r:id="rId361" xr:uid="{67053CAC-9B94-4C94-841F-C0085F6948E1}"/>
-    <hyperlink ref="J593" r:id="rId362" xr:uid="{6E9576A1-0EF7-4AB8-BAEE-2BF7182C0FE1}"/>
-    <hyperlink ref="J595" r:id="rId363" xr:uid="{0B6FB5A7-F6D6-4238-9F41-D9AFF994D366}"/>
-    <hyperlink ref="J596" r:id="rId364" xr:uid="{13140AD1-8F85-44FB-8C76-09F7C78E5EBF}"/>
-    <hyperlink ref="J598" r:id="rId365" xr:uid="{37F14D7D-8BEE-47F4-94B4-4E7ED8DBDCB4}"/>
-    <hyperlink ref="J599" r:id="rId366" xr:uid="{A7404B31-57EB-4CC4-858A-B9F72AA4ED1E}"/>
-    <hyperlink ref="J602" r:id="rId367" xr:uid="{FC6C6098-E203-4D43-8CC7-C0978F5D6B5F}"/>
-    <hyperlink ref="J603" r:id="rId368" xr:uid="{26B10AC1-1194-445D-8876-A6BA1BD499BC}"/>
-    <hyperlink ref="J604" r:id="rId369" xr:uid="{C83D951D-3BAA-404F-95B0-979CA5A5048D}"/>
-    <hyperlink ref="J605" r:id="rId370" xr:uid="{45CC58A0-9F74-41A4-9DE8-AAB21F9F984D}"/>
-    <hyperlink ref="J606" r:id="rId371" xr:uid="{488DD32C-7612-4E1C-879C-013B899632B0}"/>
-    <hyperlink ref="J608" r:id="rId372" xr:uid="{94B66F62-DAFE-4559-8AB4-448D26D8383F}"/>
-    <hyperlink ref="J609" r:id="rId373" xr:uid="{C36A0ED8-009C-45DF-84FE-19F6FBD0852F}"/>
-    <hyperlink ref="J611" r:id="rId374" xr:uid="{414894F9-7A81-40AC-8208-4D662FABB904}"/>
-    <hyperlink ref="J612" r:id="rId375" xr:uid="{8BCBF94E-4CE5-4189-A4C7-DD2F1B69A5BE}"/>
-    <hyperlink ref="J613" r:id="rId376" xr:uid="{05CFFFAE-07AE-46E1-B06D-6D02C1F2029F}"/>
-    <hyperlink ref="J615" r:id="rId377" xr:uid="{9158D2A8-C229-4D04-BCA1-620075D1D98B}"/>
-    <hyperlink ref="J617" r:id="rId378" xr:uid="{83AFC8F0-6630-4E8D-BEAA-5B2ECE358138}"/>
-    <hyperlink ref="J618" r:id="rId379" xr:uid="{BA7C825E-8842-486C-80FE-3AB537A9A569}"/>
-    <hyperlink ref="J619" r:id="rId380" xr:uid="{452BD0BE-A401-43B6-B540-74DC7BDA8B1C}"/>
-    <hyperlink ref="J622" r:id="rId381" xr:uid="{EE51528D-3278-4DBB-8CFE-AD5F1EFF85C6}"/>
-    <hyperlink ref="J623" r:id="rId382" xr:uid="{F5DCE901-BE19-4868-95C7-41CF7D93FCF9}"/>
-    <hyperlink ref="J624" r:id="rId383" xr:uid="{D1AD9DCB-029F-415B-A75E-C542125AA550}"/>
-    <hyperlink ref="J626" r:id="rId384" xr:uid="{7B0BBA61-4F2D-4EB2-B52C-6F3758CADD68}"/>
-    <hyperlink ref="J628" r:id="rId385" xr:uid="{8EB1D3CB-CB7B-4DCE-9B69-83A63663DE79}"/>
-    <hyperlink ref="J629" r:id="rId386" xr:uid="{D4FF30B7-53E8-434A-9848-D0E5362EA1DE}"/>
-    <hyperlink ref="J631" r:id="rId387" xr:uid="{13FF074E-EEB3-4FE6-86A1-B1FA6CE0CA66}"/>
-    <hyperlink ref="J634" r:id="rId388" xr:uid="{4B1F88D4-BF50-4210-A5A6-CB2835B82950}"/>
-    <hyperlink ref="J635" r:id="rId389" xr:uid="{447AC015-2882-478A-9342-6320A31667C1}"/>
-    <hyperlink ref="J637" r:id="rId390" xr:uid="{AE8C175D-6EED-4A82-8374-AE94788B9EBE}"/>
-    <hyperlink ref="J640" r:id="rId391" xr:uid="{95CB2846-05C4-4A1C-857F-B58C5C641000}"/>
-    <hyperlink ref="J641" r:id="rId392" xr:uid="{B6B38FCF-5BA8-4714-A07B-52DD84796D55}"/>
-    <hyperlink ref="J642" r:id="rId393" xr:uid="{A09C35CB-1061-470B-BD40-A390DA4B7559}"/>
-    <hyperlink ref="J644" r:id="rId394" xr:uid="{96D90A05-892F-45DE-A323-3D21BD14E654}"/>
-    <hyperlink ref="J645" r:id="rId395" xr:uid="{AB6324E8-3699-4128-BA5B-C2D438905480}"/>
-    <hyperlink ref="J648" r:id="rId396" xr:uid="{701ACFE3-541B-442B-B6BE-6E2309FF39B8}"/>
-    <hyperlink ref="J649" r:id="rId397" xr:uid="{9884EDE4-BDE5-4ADC-9F25-4021B976C97B}"/>
-    <hyperlink ref="J652" r:id="rId398" xr:uid="{6A7E7DBC-10AC-4557-B92B-64FFAC79A489}"/>
-    <hyperlink ref="J654" r:id="rId399" xr:uid="{EC656962-E5FC-45A4-AA83-D842C94F55B7}"/>
-    <hyperlink ref="J656" r:id="rId400" xr:uid="{A83A86D5-A671-4C3C-8F11-A4A82C158AE4}"/>
-    <hyperlink ref="J657" r:id="rId401" xr:uid="{9B4FCDF3-7D1A-49BE-BCB9-25DCD77AD87A}"/>
-    <hyperlink ref="J663" r:id="rId402" xr:uid="{FC91B183-2E37-404E-8788-8AFD90FCE74D}"/>
-    <hyperlink ref="J664" r:id="rId403" xr:uid="{47CD8C94-2C9E-4012-8823-6E4862D7A711}"/>
-    <hyperlink ref="J665" r:id="rId404" xr:uid="{70C68714-1A21-4DA8-AC74-42AE58734AB3}"/>
-    <hyperlink ref="J666" r:id="rId405" xr:uid="{2F269C0F-B007-41A7-A6A3-B2837F4BD785}"/>
-    <hyperlink ref="J667" r:id="rId406" xr:uid="{5AE6EA4D-E8EB-472A-8B36-0898C315727C}"/>
-    <hyperlink ref="J668" r:id="rId407" xr:uid="{1120A492-1207-49EA-9777-379C69379E62}"/>
-    <hyperlink ref="J669" r:id="rId408" xr:uid="{109DE9FD-7A8C-4737-9A25-E534D5522F94}"/>
-    <hyperlink ref="J670" r:id="rId409" xr:uid="{6E7198FE-D10F-4B98-B8CF-9E0528A346C7}"/>
-    <hyperlink ref="J671" r:id="rId410" xr:uid="{4A4A1CCD-3F19-46BB-A45C-195F91D2B848}"/>
-    <hyperlink ref="J672" r:id="rId411" xr:uid="{DB87502B-436E-4150-862B-9D2FFCE15A5D}"/>
-    <hyperlink ref="J673" r:id="rId412" xr:uid="{0ABEE9E0-1C5E-459C-AAD0-6DC593FD505E}"/>
-    <hyperlink ref="J674" r:id="rId413" xr:uid="{11BEBBF9-9F96-435E-BD8F-5DC778F43F03}"/>
-    <hyperlink ref="J675" r:id="rId414" xr:uid="{CBF9A151-F8F2-4EE8-B72E-4B0872434923}"/>
-    <hyperlink ref="J676" r:id="rId415" xr:uid="{81509844-656A-43E3-87DD-B7DBD93D0FEE}"/>
-    <hyperlink ref="J677" r:id="rId416" xr:uid="{52028704-7406-4328-870B-EAB0C0A6BC4E}"/>
-    <hyperlink ref="J679" r:id="rId417" xr:uid="{F176F576-F740-4337-AE54-97B2008050A9}"/>
-    <hyperlink ref="J682" r:id="rId418" xr:uid="{2E14C30F-8634-45FD-8E9D-322D67EEFF7F}"/>
-    <hyperlink ref="J683" r:id="rId419" xr:uid="{AD727ED9-DAE5-45BD-A80D-62446876022E}"/>
-    <hyperlink ref="J684" r:id="rId420" xr:uid="{256F1D9A-5AC3-418D-B244-3435688CEE38}"/>
-    <hyperlink ref="J688" r:id="rId421" xr:uid="{FFE86B26-F017-446B-B49C-89F9E5448FDF}"/>
-    <hyperlink ref="J693" r:id="rId422" xr:uid="{9DF9F0BE-2C85-4BE0-9C74-215B732D1719}"/>
-    <hyperlink ref="J694" r:id="rId423" xr:uid="{F90FE874-813D-4E83-A061-DDB1723C931D}"/>
-    <hyperlink ref="J695" r:id="rId424" xr:uid="{8B7DF9F1-0706-4392-8977-175823739B86}"/>
-    <hyperlink ref="J696" r:id="rId425" xr:uid="{4DCFCB53-17B1-48DA-9391-1E4FE31E0ADF}"/>
-    <hyperlink ref="J697" r:id="rId426" xr:uid="{AD0269AA-03CA-44AF-A3F2-481D6B2A792C}"/>
-    <hyperlink ref="J698" r:id="rId427" xr:uid="{13463103-9E21-4E91-BB7B-A610CA68B281}"/>
-    <hyperlink ref="J699" r:id="rId428" xr:uid="{41536A0B-B329-4B80-8E2D-047EEBC5DDA6}"/>
-    <hyperlink ref="J700" r:id="rId429" xr:uid="{0F2849CC-148A-4609-87AA-ECFFC9D7D9EF}"/>
-    <hyperlink ref="J705" r:id="rId430" xr:uid="{1D4E09A6-25D8-433A-9DC2-9264150176DE}"/>
-    <hyperlink ref="J708" r:id="rId431" xr:uid="{4517048C-6F8E-4DF2-ADDD-D190E88C86CD}"/>
-    <hyperlink ref="J712" r:id="rId432" xr:uid="{CBEDCF0D-A1CA-4505-9E48-A10CE41E4BF9}"/>
-    <hyperlink ref="J713" r:id="rId433" xr:uid="{0E46991D-0205-4B7B-A8D4-3DA58BADD129}"/>
-    <hyperlink ref="J714" r:id="rId434" xr:uid="{D68FCDA3-DB67-4967-9050-2A05E3FC993F}"/>
-    <hyperlink ref="J715" r:id="rId435" xr:uid="{870804FA-B02F-47B2-B588-95C198A9EBF7}"/>
-    <hyperlink ref="J718" r:id="rId436" xr:uid="{47AF4FB3-D64E-470B-AED7-3C3F25B23D77}"/>
-    <hyperlink ref="J720" r:id="rId437" xr:uid="{A897EFF5-CF39-4738-8CFB-7EEA16243349}"/>
-    <hyperlink ref="J721" r:id="rId438" xr:uid="{9D8C239D-4EEA-40A7-A2B6-F8D40F9E221F}"/>
-    <hyperlink ref="J722" r:id="rId439" xr:uid="{EB34B59B-97FC-4690-B922-CA75FE703AFB}"/>
-    <hyperlink ref="J725" r:id="rId440" xr:uid="{0D905AD4-CC31-412E-AE4D-127A0A48445B}"/>
-    <hyperlink ref="J726" r:id="rId441" xr:uid="{2BA40DB2-1C66-434B-91C4-ACAB11096C8E}"/>
-    <hyperlink ref="J728" r:id="rId442" xr:uid="{03E9DCD0-A77D-4535-B0BD-1E8E6D5B2420}"/>
-    <hyperlink ref="J729" r:id="rId443" xr:uid="{F931C5FC-5EBA-4852-B68F-0B63C290D2B7}"/>
-    <hyperlink ref="J736" r:id="rId444" xr:uid="{C0EAA12F-96F0-4577-8AC2-3A3E8FDD354A}"/>
-    <hyperlink ref="J738" r:id="rId445" xr:uid="{FF593967-D880-425F-AED6-80CB9391D2C7}"/>
-    <hyperlink ref="J739" r:id="rId446" xr:uid="{D76ED555-F492-4899-8527-F28B1F4F6B79}"/>
-    <hyperlink ref="J740" r:id="rId447" xr:uid="{E00D5FF6-7311-4D9E-A93C-3BE7B9045830}"/>
-    <hyperlink ref="J741" r:id="rId448" xr:uid="{238D3AA8-3CE0-4F33-9DE9-CEA265434528}"/>
-    <hyperlink ref="J742" r:id="rId449" xr:uid="{2ABF1E49-8E3F-4427-9A06-BF5664D5B9C5}"/>
-    <hyperlink ref="J743" r:id="rId450" xr:uid="{2584B41F-D52D-4CFF-925C-AB8DB83EC6CA}"/>
-    <hyperlink ref="J744" r:id="rId451" xr:uid="{A3C886B6-E5BF-4ECB-818B-76EFAFE0744B}"/>
-    <hyperlink ref="J747" r:id="rId452" xr:uid="{7275A71F-5E52-4010-A184-239AA9D1D548}"/>
-    <hyperlink ref="J748" r:id="rId453" xr:uid="{BE0D981E-9C78-4DF9-9ECF-5DADAF8308C9}"/>
-    <hyperlink ref="J757" r:id="rId454" xr:uid="{E76ECC85-B5E4-4EE1-BCCF-81D00B5A486F}"/>
-    <hyperlink ref="J758" r:id="rId455" xr:uid="{EFA9FB04-BBEF-44C8-88B0-C6BDDD633DE9}"/>
-    <hyperlink ref="J759" r:id="rId456" xr:uid="{69BE81CD-19ED-41CA-A0C3-040EABE08C96}"/>
-    <hyperlink ref="J760" r:id="rId457" xr:uid="{1EBE7E41-AF47-402E-A965-DD04BF69C098}"/>
-    <hyperlink ref="J761" r:id="rId458" xr:uid="{5B65B56A-DDC1-4E22-B778-59170A69BAFF}"/>
-    <hyperlink ref="J762" r:id="rId459" xr:uid="{B395B4B3-BC3C-4C2C-8397-1881F783854A}"/>
-    <hyperlink ref="J764" r:id="rId460" xr:uid="{27F5669C-4373-4EE8-A647-5594DC527BE2}"/>
-    <hyperlink ref="J765" r:id="rId461" xr:uid="{41AC0CA5-3EAA-4A46-95C6-DCF9DA4E7912}"/>
-    <hyperlink ref="J766" r:id="rId462" xr:uid="{8F8D8D31-3B65-4CC6-A9D7-79F7D4893369}"/>
-    <hyperlink ref="J767" r:id="rId463" xr:uid="{2725A120-98D0-4EE3-B7DA-FE7CF70428FB}"/>
-    <hyperlink ref="J769" r:id="rId464" xr:uid="{79024639-C18A-45C1-B562-CB4A85C45ED8}"/>
-    <hyperlink ref="J770" r:id="rId465" xr:uid="{19C44815-7F11-49BF-84D8-3E6DF80AF281}"/>
-    <hyperlink ref="J772" r:id="rId466" xr:uid="{2B56B16B-2494-432E-B37A-26FBAA610715}"/>
-    <hyperlink ref="J774" r:id="rId467" xr:uid="{150E6958-D205-41A2-85BF-D2A5B019E705}"/>
-    <hyperlink ref="J778" r:id="rId468" xr:uid="{98C10E0E-FA3D-443A-A7A9-231A33D1B4AE}"/>
-    <hyperlink ref="J781" r:id="rId469" xr:uid="{0069FA23-60A9-41CB-8D63-BED8C6F0E6B3}"/>
-    <hyperlink ref="J783" r:id="rId470" xr:uid="{CDF9950E-30E1-482A-9D05-48B2D48833F9}"/>
-    <hyperlink ref="J784" r:id="rId471" xr:uid="{C8652258-A6E6-4BAB-907B-725E88F93FD9}"/>
-    <hyperlink ref="J785" r:id="rId472" xr:uid="{282D9643-2CB1-4934-A77A-F0D840CB7492}"/>
-    <hyperlink ref="J788" r:id="rId473" xr:uid="{C6FACBE3-EBD5-4F8C-BD97-66CE2BFD3A1F}"/>
-    <hyperlink ref="J789" r:id="rId474" xr:uid="{AA7618B6-E401-4F87-9620-9FBA89BF4B7A}"/>
-    <hyperlink ref="J790" r:id="rId475" xr:uid="{0B88235D-5456-4A3C-A0FD-78DA5826E3B9}"/>
-    <hyperlink ref="J794" r:id="rId476" xr:uid="{4C4DBCAC-9E5E-43BC-8AC6-307FAE2F2BA6}"/>
-    <hyperlink ref="J795" r:id="rId477" xr:uid="{D71EA2C1-14CB-4A13-B660-4B93B312A850}"/>
-    <hyperlink ref="J796" r:id="rId478" xr:uid="{BFA81D40-7AEB-49E0-A994-4FAC6AA896EE}"/>
-    <hyperlink ref="J797" r:id="rId479" xr:uid="{F11E5F55-67C0-42E4-8985-609F03B1153F}"/>
-    <hyperlink ref="J799" r:id="rId480" xr:uid="{27D26171-E560-4D19-867C-771B234415E7}"/>
-    <hyperlink ref="J800" r:id="rId481" xr:uid="{3B9D3327-A0F6-426A-A79A-B4836718FDC0}"/>
-    <hyperlink ref="J801" r:id="rId482" xr:uid="{A915DA2E-C282-4877-A209-BD9A4B5DB2CF}"/>
-    <hyperlink ref="J802" r:id="rId483" xr:uid="{1E5A6584-B6C7-46C6-9ADC-D7B43B1E1F3C}"/>
-    <hyperlink ref="J803" r:id="rId484" xr:uid="{D43CBCDE-5142-4756-9143-F577425B68AE}"/>
-    <hyperlink ref="J804" r:id="rId485" xr:uid="{4DE2729C-8F8C-4D0C-ADF2-D796F9D0B664}"/>
-    <hyperlink ref="J805" r:id="rId486" xr:uid="{EE4F8E23-DD6A-4CB6-8FD4-FD711C9383C3}"/>
-    <hyperlink ref="J806" r:id="rId487" xr:uid="{0ACF8FBD-EA22-47E5-A677-267482DD682F}"/>
-    <hyperlink ref="J808" r:id="rId488" xr:uid="{2363ED59-956D-4F3E-9309-E6348DFCC466}"/>
-    <hyperlink ref="J810" r:id="rId489" xr:uid="{CD79C10A-0175-44EF-A4EC-2E93AE14F056}"/>
-    <hyperlink ref="J811" r:id="rId490" xr:uid="{1010E506-8CDE-4336-9DD0-085B0CF5F34A}"/>
-    <hyperlink ref="J812" r:id="rId491" xr:uid="{B1F8EC00-EBBF-47E7-9472-F94A34AE56A2}"/>
-    <hyperlink ref="J813" r:id="rId492" xr:uid="{464F82E1-26A1-4898-BC31-01741F6745B5}"/>
-    <hyperlink ref="J814" r:id="rId493" xr:uid="{77C2B74E-077D-45B9-AB7E-552C4AD3DA16}"/>
-    <hyperlink ref="J815" r:id="rId494" xr:uid="{19B6C0E1-BC07-4323-AD28-30D94D7165C6}"/>
-    <hyperlink ref="J816" r:id="rId495" xr:uid="{CE0E4578-9C6D-4E6F-BB33-D3237A83CFF6}"/>
-    <hyperlink ref="J817" r:id="rId496" xr:uid="{87D7B5DE-0D89-4414-A3D3-82D59BAC4963}"/>
-    <hyperlink ref="J818" r:id="rId497" xr:uid="{8D98E8D0-1AE0-4F23-B327-E1AE0AD45339}"/>
-    <hyperlink ref="J819" r:id="rId498" xr:uid="{B453850A-162B-44C1-832E-002E64762E87}"/>
-    <hyperlink ref="J820" r:id="rId499" xr:uid="{0E277BC6-F505-4CAA-AB23-DB72367172A5}"/>
-    <hyperlink ref="J821" r:id="rId500" xr:uid="{27611892-7060-4851-A942-B4C0F2012C45}"/>
-    <hyperlink ref="J822" r:id="rId501" xr:uid="{12A96A3B-EAA1-46A0-A627-9C97B5EE20B8}"/>
-    <hyperlink ref="J825" r:id="rId502" xr:uid="{A58D8C0E-D750-4E24-8395-7EA1DF0E9D2C}"/>
-    <hyperlink ref="J826" r:id="rId503" xr:uid="{F31F0B67-CE27-4ED2-8EAE-F0DA1FAED81D}"/>
-    <hyperlink ref="J827" r:id="rId504" xr:uid="{70A2F12E-9EE2-441E-B2E9-DDCB4A2FA095}"/>
-    <hyperlink ref="J828" r:id="rId505" xr:uid="{63064BF9-AA00-455F-9456-1827C0AB57E7}"/>
-    <hyperlink ref="J831" r:id="rId506" xr:uid="{3823E4C8-1CA2-400D-8260-82812B48D1D8}"/>
-    <hyperlink ref="J832" r:id="rId507" xr:uid="{BAE6D454-6FE5-4F16-ADE8-70B1AE9CC396}"/>
-    <hyperlink ref="J833" r:id="rId508" xr:uid="{F0A469CA-FA9E-4AA3-93F9-68616FB24EAD}"/>
-    <hyperlink ref="J836" r:id="rId509" xr:uid="{3E144F19-7124-4A9D-A276-573584360807}"/>
-    <hyperlink ref="J837" r:id="rId510" xr:uid="{B9C00CBF-6E8D-48EC-9C6B-EA78A2203113}"/>
-    <hyperlink ref="J838" r:id="rId511" xr:uid="{DE6B53A0-9E26-41BC-9429-EFCC8204205A}"/>
+    <hyperlink ref="J5" r:id="rId1" xr:uid="{347EEE58-E3DD-4F58-9B05-5D784C33B809}"/>
+    <hyperlink ref="J7" r:id="rId2" xr:uid="{3CB2AABA-1735-4209-A65C-DAD1D34FCDAA}"/>
+    <hyperlink ref="J8" r:id="rId3" xr:uid="{C9E6D028-1099-469F-AD45-D2A1FE803F93}"/>
+    <hyperlink ref="J10" r:id="rId4" xr:uid="{53A519F6-5A4A-4510-AA6A-7D0CA4575A40}"/>
+    <hyperlink ref="J13" r:id="rId5" xr:uid="{8D189C7F-EDFF-4483-93CE-6B2E11BB1C91}"/>
+    <hyperlink ref="J14" r:id="rId6" xr:uid="{90D81A7A-AC74-412B-B744-DC3AB9A8944A}"/>
+    <hyperlink ref="J17" r:id="rId7" xr:uid="{792CB45F-2429-46B4-B427-3366BFDE7A32}"/>
+    <hyperlink ref="J19" r:id="rId8" xr:uid="{884B5C9B-0657-4DAE-87AC-903E8460DC2E}"/>
+    <hyperlink ref="J20" r:id="rId9" xr:uid="{494C43C1-C921-4782-BC39-F1C2CEA1CFB3}"/>
+    <hyperlink ref="J21" r:id="rId10" xr:uid="{F67B4B3F-F8A5-4A2E-AF7E-0B2E89F6DBF5}"/>
+    <hyperlink ref="J24" r:id="rId11" xr:uid="{39145CA9-E7BA-4136-911E-3AF3B9A59A92}"/>
+    <hyperlink ref="J25" r:id="rId12" xr:uid="{8B233F34-6541-4B0C-8AE0-6E251E3E7DD9}"/>
+    <hyperlink ref="J26" r:id="rId13" xr:uid="{1EC910A4-7A86-431F-B0B3-8F4EF577B0B4}"/>
+    <hyperlink ref="J27" r:id="rId14" xr:uid="{9E2EBA7B-4ABF-46C7-9EDA-B56C29417ACE}"/>
+    <hyperlink ref="J29" r:id="rId15" xr:uid="{547D2471-7794-48E0-B288-D02D9086E44F}"/>
+    <hyperlink ref="J30" r:id="rId16" xr:uid="{50C75725-1674-4661-9B58-77ED0EFBF682}"/>
+    <hyperlink ref="J31" r:id="rId17" xr:uid="{7C9A2171-C857-463D-95A1-5D92E0FFDD60}"/>
+    <hyperlink ref="J34" r:id="rId18" xr:uid="{A7C9CC02-F3C0-42F4-BA39-212A2A3EB097}"/>
+    <hyperlink ref="J35" r:id="rId19" xr:uid="{8F4282E3-4BB9-4086-B9E6-88405DE792E0}"/>
+    <hyperlink ref="J36" r:id="rId20" xr:uid="{BAD9E013-5553-42CE-8D83-156A870DBE06}"/>
+    <hyperlink ref="J37" r:id="rId21" xr:uid="{461371D0-9E82-4999-91F2-CC6729B03312}"/>
+    <hyperlink ref="J38" r:id="rId22" xr:uid="{784B55EE-6B4D-4176-83B0-DA870C85C1A6}"/>
+    <hyperlink ref="J46" r:id="rId23" xr:uid="{6480FB94-D6D5-423D-A5F5-C0CCD44D852D}"/>
+    <hyperlink ref="J47" r:id="rId24" xr:uid="{79024234-D181-4B85-BAE3-6FCE8C20FBF0}"/>
+    <hyperlink ref="J48" r:id="rId25" xr:uid="{5C69C50E-8736-4B80-9B22-A0BF2ADB708F}"/>
+    <hyperlink ref="J49" r:id="rId26" xr:uid="{B26219FA-D0CF-43B8-AC6F-BC74E7E49FF0}"/>
+    <hyperlink ref="J50" r:id="rId27" xr:uid="{890B450E-5693-4F94-AC53-250C3FDDDF50}"/>
+    <hyperlink ref="J52" r:id="rId28" xr:uid="{070FD6C5-085C-4FE2-8F75-910416464143}"/>
+    <hyperlink ref="J53" r:id="rId29" xr:uid="{9BAE4006-3C81-49A6-A368-146AE1F3464B}"/>
+    <hyperlink ref="J54" r:id="rId30" xr:uid="{6B3231D9-324D-4143-8A32-54F4DD4D35E2}"/>
+    <hyperlink ref="J56" r:id="rId31" xr:uid="{54C87045-FADF-4558-8F90-A0128B229DA6}"/>
+    <hyperlink ref="J59" r:id="rId32" xr:uid="{600CA509-97A7-48C4-9E7E-A3B3180CF792}"/>
+    <hyperlink ref="J61" r:id="rId33" xr:uid="{5F6F2E97-C12E-4A93-ACF7-ACB0A29F1982}"/>
+    <hyperlink ref="J62" r:id="rId34" xr:uid="{FD04D79F-7936-4A8D-A0D7-CD5F0166A2B4}"/>
+    <hyperlink ref="J63" r:id="rId35" xr:uid="{1B22ED25-8858-45B9-9681-6735BAF09B00}"/>
+    <hyperlink ref="J64" r:id="rId36" xr:uid="{030C4DB6-E847-4C4E-8460-BCB4531AC422}"/>
+    <hyperlink ref="J69" r:id="rId37" xr:uid="{36388BE9-A10F-4CDD-A77C-3C1E7F599DEF}"/>
+    <hyperlink ref="J71" r:id="rId38" xr:uid="{FBCC2F6B-531A-41AE-BDA1-948779F8903E}"/>
+    <hyperlink ref="J72" r:id="rId39" xr:uid="{51B88202-D54D-4AD9-BBEB-D61251B82154}"/>
+    <hyperlink ref="J73" r:id="rId40" xr:uid="{A7B65147-E56E-43F3-8476-1B3218ADD808}"/>
+    <hyperlink ref="J74" r:id="rId41" xr:uid="{2BBD0681-C438-4020-8AB9-52E7D00FD4F5}"/>
+    <hyperlink ref="J75" r:id="rId42" xr:uid="{88739BB9-1BF0-4AF0-B0DE-4F49B85CAD7E}"/>
+    <hyperlink ref="J76" r:id="rId43" xr:uid="{BD9B01AF-D5F8-457F-BC52-41C59DD93D7D}"/>
+    <hyperlink ref="J78" r:id="rId44" xr:uid="{18D20E17-B9B8-4F21-B849-7B022E70EB3F}"/>
+    <hyperlink ref="J80" r:id="rId45" xr:uid="{4D3E8CA4-FB12-4C4A-8254-F3463F2B1D72}"/>
+    <hyperlink ref="J86" r:id="rId46" xr:uid="{D117F880-B11F-4DD8-9F7C-CD3ED4C56E82}"/>
+    <hyperlink ref="J88" r:id="rId47" xr:uid="{7193CD4F-2FB7-4E23-855B-AF53A83D1845}"/>
+    <hyperlink ref="J89" r:id="rId48" xr:uid="{50FDAC4C-0769-4721-9785-21F50408EA91}"/>
+    <hyperlink ref="J90" r:id="rId49" xr:uid="{FA7E2118-ACA7-4C47-8799-896948927415}"/>
+    <hyperlink ref="J92" r:id="rId50" xr:uid="{CA4708B7-B4F0-4792-82CC-EFAA3A732AEA}"/>
+    <hyperlink ref="J94" r:id="rId51" xr:uid="{A71A28BA-3894-491C-8046-46C9AE628950}"/>
+    <hyperlink ref="J95" r:id="rId52" xr:uid="{57DD5CB7-1EE5-4272-A415-ABA21060A790}"/>
+    <hyperlink ref="J96" r:id="rId53" xr:uid="{D2ABE5FD-16F0-4C14-8286-A6AF7C9A924A}"/>
+    <hyperlink ref="J101" r:id="rId54" xr:uid="{E3AA0310-B1D5-43BE-8C51-260827B6360C}"/>
+    <hyperlink ref="J103" r:id="rId55" xr:uid="{EABD3DD9-CE3C-4594-9941-DEA1B00EDA84}"/>
+    <hyperlink ref="J104" r:id="rId56" xr:uid="{DB78157D-56BA-4BE3-9A72-E68A479906EF}"/>
+    <hyperlink ref="J105" r:id="rId57" xr:uid="{68CB30DD-9566-41DD-811D-4FAA8FE0ADEC}"/>
+    <hyperlink ref="J106" r:id="rId58" xr:uid="{3604D3D3-1154-4F95-A9D1-B7506120E26B}"/>
+    <hyperlink ref="J107" r:id="rId59" xr:uid="{61686618-7FC1-4A77-8D57-919381673E25}"/>
+    <hyperlink ref="J109" r:id="rId60" xr:uid="{F468D453-AD25-48CE-BD8B-522FA2A4988C}"/>
+    <hyperlink ref="J110" r:id="rId61" xr:uid="{64C0336A-0737-470B-B36D-5559104AE71A}"/>
+    <hyperlink ref="J111" r:id="rId62" xr:uid="{56C5B5D4-BF1E-418F-A29A-9594B88462BC}"/>
+    <hyperlink ref="J112" r:id="rId63" xr:uid="{C7A2F3DD-9A9B-416B-8517-587A00ABFFB1}"/>
+    <hyperlink ref="J113" r:id="rId64" xr:uid="{0C1082D6-0428-4197-81EE-C12D7693F359}"/>
+    <hyperlink ref="J114" r:id="rId65" xr:uid="{AEDAE6D5-6120-4470-8EAC-E9452E5C5852}"/>
+    <hyperlink ref="J116" r:id="rId66" xr:uid="{E8612177-CA9D-4CFA-A458-93A049270F21}"/>
+    <hyperlink ref="J117" r:id="rId67" xr:uid="{0479FC67-695E-43D2-A244-53CCF781AE2F}"/>
+    <hyperlink ref="J118" r:id="rId68" xr:uid="{6BE9D51F-6CEA-4C8F-9DAD-1D9E366CC286}"/>
+    <hyperlink ref="J119" r:id="rId69" xr:uid="{3D7FE342-F44A-48FF-8F7E-FCB6C491EB3A}"/>
+    <hyperlink ref="J120" r:id="rId70" xr:uid="{DD31AADC-E525-4246-BCA5-276BB7570196}"/>
+    <hyperlink ref="J121" r:id="rId71" xr:uid="{E4260B70-2481-4E1D-A1BA-6A666DC4373E}"/>
+    <hyperlink ref="J124" r:id="rId72" xr:uid="{929AB755-B4D2-48F9-961C-2FD0F9996F5A}"/>
+    <hyperlink ref="J128" r:id="rId73" xr:uid="{24188C6D-D6D0-422E-A5AA-CF70F98C2944}"/>
+    <hyperlink ref="J129" r:id="rId74" xr:uid="{8445679E-F15B-40FA-B120-96E1373868BA}"/>
+    <hyperlink ref="J132" r:id="rId75" xr:uid="{B063C2A9-15B6-4784-927E-B70119A93AFC}"/>
+    <hyperlink ref="J134" r:id="rId76" xr:uid="{6C88C26E-FC18-4863-B0E1-032F220BDABB}"/>
+    <hyperlink ref="J135" r:id="rId77" xr:uid="{BCB373D3-8822-4184-BC74-1F4C82012105}"/>
+    <hyperlink ref="J136" r:id="rId78" xr:uid="{EE0CA0D2-E190-4CC6-968E-E86F6997BA15}"/>
+    <hyperlink ref="J140" r:id="rId79" xr:uid="{3590C6D3-87F6-4E6D-B2B1-9243AECEDECD}"/>
+    <hyperlink ref="J142" r:id="rId80" xr:uid="{CB8732B6-7759-4F06-99DF-91D13E023A5A}"/>
+    <hyperlink ref="J143" r:id="rId81" xr:uid="{060CB918-DE41-4587-9888-0809277FDDBD}"/>
+    <hyperlink ref="J144" r:id="rId82" xr:uid="{7FB1BDB2-28C2-48C9-9D25-1FFDC331ABB8}"/>
+    <hyperlink ref="J145" r:id="rId83" xr:uid="{16D801A1-991B-42FC-8650-6BB64038B41E}"/>
+    <hyperlink ref="J147" r:id="rId84" xr:uid="{A419B631-B594-483F-83AE-89D98B5DB185}"/>
+    <hyperlink ref="J149" r:id="rId85" xr:uid="{C44D669C-A32D-4C04-81C5-99BC2C20D373}"/>
+    <hyperlink ref="J150" r:id="rId86" xr:uid="{D9CF90A5-0DB0-4E86-B505-427367397BD1}"/>
+    <hyperlink ref="J151" r:id="rId87" xr:uid="{42E24C9F-0988-4835-B510-B70E43DAB384}"/>
+    <hyperlink ref="J152" r:id="rId88" xr:uid="{E4811F11-509A-4622-BB5B-209A109A8C5B}"/>
+    <hyperlink ref="J153" r:id="rId89" xr:uid="{8B6F2B5F-AC50-4B34-A225-E09A9902F591}"/>
+    <hyperlink ref="J154" r:id="rId90" xr:uid="{0F6B3772-0C4E-4F95-9766-CDCED6EB914A}"/>
+    <hyperlink ref="J155" r:id="rId91" xr:uid="{EAF43B61-175E-4AA5-BB51-4DF1B97A7635}"/>
+    <hyperlink ref="J156" r:id="rId92" xr:uid="{5B30775D-485E-48BB-B4CF-AF281E2DE364}"/>
+    <hyperlink ref="J159" r:id="rId93" xr:uid="{BD3AB75F-1E84-406E-B719-DEF5CD532BA1}"/>
+    <hyperlink ref="J160" r:id="rId94" xr:uid="{C607A994-601A-4793-A09F-D934C4A8B9C9}"/>
+    <hyperlink ref="J161" r:id="rId95" xr:uid="{A54C9A99-B124-4D24-A483-E093FA0D66D4}"/>
+    <hyperlink ref="J162" r:id="rId96" xr:uid="{8595A34A-DCAA-445F-B01A-44DCB3E251E4}"/>
+    <hyperlink ref="J164" r:id="rId97" xr:uid="{F9360426-C4B1-4F99-84BE-60C346DE6C7A}"/>
+    <hyperlink ref="J165" r:id="rId98" xr:uid="{C6451242-FFCC-48FD-BBE2-ED9733126662}"/>
+    <hyperlink ref="J167" r:id="rId99" xr:uid="{66AFD6D5-C269-466F-A6C3-AD4487EE5A03}"/>
+    <hyperlink ref="J168" r:id="rId100" xr:uid="{B21EFD2D-458A-4E2B-90D9-723CBBAF3C7F}"/>
+    <hyperlink ref="J169" r:id="rId101" xr:uid="{FE5488DE-6075-489C-A697-B2CCFB4DBBDB}"/>
+    <hyperlink ref="J171" r:id="rId102" xr:uid="{41659C50-22A5-4AAD-90D0-36A847859523}"/>
+    <hyperlink ref="J172" r:id="rId103" xr:uid="{7D7862D8-57FD-4694-9CC5-1E9487183AE9}"/>
+    <hyperlink ref="J173" r:id="rId104" xr:uid="{D270D2A8-BA30-4D93-9905-CBACA49F8344}"/>
+    <hyperlink ref="J177" r:id="rId105" xr:uid="{C044B4B7-C453-4B17-A412-7B16B18D02FD}"/>
+    <hyperlink ref="J178" r:id="rId106" xr:uid="{8A78415D-AD4F-440F-BA0F-B48B28DAB8D0}"/>
+    <hyperlink ref="J181" r:id="rId107" xr:uid="{8D65DA1E-94CC-4B93-8C10-2115D3CE7276}"/>
+    <hyperlink ref="J182" r:id="rId108" xr:uid="{6F932761-5BBF-4748-856B-F31751136BC1}"/>
+    <hyperlink ref="J184" r:id="rId109" xr:uid="{799D7FCB-78F8-4BD0-8B60-A40C8CA9FA52}"/>
+    <hyperlink ref="J186" r:id="rId110" xr:uid="{D2369F5D-386D-453A-B0B8-238C121028B1}"/>
+    <hyperlink ref="J190" r:id="rId111" xr:uid="{91F5C2A2-C582-4D64-AA8F-9B831D7DF06B}"/>
+    <hyperlink ref="J191" r:id="rId112" xr:uid="{2935F1E2-3E6E-4DC7-A8D3-ADF82B24166C}"/>
+    <hyperlink ref="J192" r:id="rId113" xr:uid="{72799BCD-A19D-407E-B2E1-B15DE2B8F468}"/>
+    <hyperlink ref="J193" r:id="rId114" xr:uid="{2FDD4B6F-F448-48CD-84C7-8B26AA5A662F}"/>
+    <hyperlink ref="J194" r:id="rId115" xr:uid="{0DABADAA-EC41-4C4F-AA2D-F809EA83D09D}"/>
+    <hyperlink ref="J195" r:id="rId116" xr:uid="{17A63467-5A20-4FEB-A6C0-861F45EC2746}"/>
+    <hyperlink ref="J196" r:id="rId117" xr:uid="{BA720475-1F1F-4BC7-BD64-BDDAE2E829D6}"/>
+    <hyperlink ref="J199" r:id="rId118" xr:uid="{2BD5C6A3-CD97-44A5-8EFB-56218F21A7CE}"/>
+    <hyperlink ref="J201" r:id="rId119" xr:uid="{78F7E594-0ED3-4204-BE8B-8D448554B435}"/>
+    <hyperlink ref="J202" r:id="rId120" xr:uid="{7DEDBDBC-29B5-4DE6-ABAD-217F2DE5CA7C}"/>
+    <hyperlink ref="J203" r:id="rId121" xr:uid="{1B085470-BA2A-4DF3-BF28-8FBF9297C86C}"/>
+    <hyperlink ref="J205" r:id="rId122" xr:uid="{991B4ECF-EECF-486E-9EB0-D528D4844BC7}"/>
+    <hyperlink ref="J207" r:id="rId123" xr:uid="{DE4355F6-46E8-4832-B9C7-9CCF9BFE4AE9}"/>
+    <hyperlink ref="J209" r:id="rId124" xr:uid="{D09DD3F5-6957-4771-8755-38B7606D8B70}"/>
+    <hyperlink ref="J210" r:id="rId125" xr:uid="{6BB42872-CC1D-4306-90A0-6FBE7CCED7E9}"/>
+    <hyperlink ref="J211" r:id="rId126" xr:uid="{BD5278C7-4697-42AF-9E66-2DA4F50BD285}"/>
+    <hyperlink ref="J212" r:id="rId127" xr:uid="{36114D99-6ACF-4EB2-9666-09B1287A8BD3}"/>
+    <hyperlink ref="J213" r:id="rId128" xr:uid="{FFD13021-E00B-444B-B23B-2A3CF772E7DE}"/>
+    <hyperlink ref="J214" r:id="rId129" xr:uid="{01F2AB0F-6F7A-4377-9D5C-B6562A5DBDE5}"/>
+    <hyperlink ref="J215" r:id="rId130" xr:uid="{C32C4390-7C32-42F8-89AD-090B8473DFBE}"/>
+    <hyperlink ref="J217" r:id="rId131" xr:uid="{3852B469-D0DB-4052-A92B-7952E15AA925}"/>
+    <hyperlink ref="J219" r:id="rId132" xr:uid="{F0B78EB4-6F7D-43C8-B193-04867C42D6BA}"/>
+    <hyperlink ref="J220" r:id="rId133" xr:uid="{090897C0-6136-4A4C-824E-C92C1EAC1C7D}"/>
+    <hyperlink ref="J221" r:id="rId134" xr:uid="{2A19309A-C192-4E1A-A403-CB03E26150A2}"/>
+    <hyperlink ref="J222" r:id="rId135" xr:uid="{0AAEB04F-D3BC-4A54-AE41-4808D8AE00EB}"/>
+    <hyperlink ref="J223" r:id="rId136" xr:uid="{EAA1E64B-9912-4AA4-8EE1-27AC3B81E8EB}"/>
+    <hyperlink ref="J225" r:id="rId137" xr:uid="{2D2DEFF8-080C-46FC-85C6-95DA589E5C4A}"/>
+    <hyperlink ref="J228" r:id="rId138" xr:uid="{B6A672C9-21E1-45DA-BA6B-03D70ACA30AA}"/>
+    <hyperlink ref="J230" r:id="rId139" xr:uid="{FFE879EB-D996-4788-8081-5A133ABC2AA4}"/>
+    <hyperlink ref="J234" r:id="rId140" xr:uid="{B372644F-C043-4E80-A1DE-CA1A1A75A024}"/>
+    <hyperlink ref="J236" r:id="rId141" xr:uid="{6BEE5531-594B-4666-B14F-95DF8D7073FD}"/>
+    <hyperlink ref="J237" r:id="rId142" xr:uid="{DD9BB9B1-D56F-4DE5-B891-CD41105B61D7}"/>
+    <hyperlink ref="J238" r:id="rId143" xr:uid="{F2193BE2-8A1D-4A30-849D-BF6B9688E509}"/>
+    <hyperlink ref="J240" r:id="rId144" xr:uid="{7511A71F-4ED9-4542-A224-619B1E29B5F2}"/>
+    <hyperlink ref="J241" r:id="rId145" xr:uid="{5CEB2158-7CB3-4E78-BCE3-D05D353781A7}"/>
+    <hyperlink ref="J242" r:id="rId146" xr:uid="{ECA55E3E-B12D-44C8-AE9D-859F47726953}"/>
+    <hyperlink ref="J243" r:id="rId147" xr:uid="{CB0043FA-686B-4293-81B4-FD9AB274105A}"/>
+    <hyperlink ref="J246" r:id="rId148" xr:uid="{024874DA-198C-4424-A93E-873AF1C54C9B}"/>
+    <hyperlink ref="J247" r:id="rId149" xr:uid="{C6603A81-6409-442A-B090-B941654CDDC2}"/>
+    <hyperlink ref="J250" r:id="rId150" xr:uid="{4C4F1963-94C7-49ED-8273-D329D4375FE9}"/>
+    <hyperlink ref="J252" r:id="rId151" xr:uid="{C4D7EBA4-6DBD-4349-BAC7-AC4F26493B2E}"/>
+    <hyperlink ref="J254" r:id="rId152" xr:uid="{7E7968FF-2576-4C55-B57D-D88594CAE02C}"/>
+    <hyperlink ref="J255" r:id="rId153" xr:uid="{E3BEBDDE-1FC5-4D18-AEB9-739095B93407}"/>
+    <hyperlink ref="J256" r:id="rId154" xr:uid="{4B961348-C36D-4DEF-BD7F-73CFCC3B7658}"/>
+    <hyperlink ref="J258" r:id="rId155" xr:uid="{B24F76E4-8991-41A7-A6AB-6C21C597638A}"/>
+    <hyperlink ref="J259" r:id="rId156" xr:uid="{46FC5580-F9E7-4DD1-AE7B-207A8BC96FB9}"/>
+    <hyperlink ref="J261" r:id="rId157" xr:uid="{B1C60F34-36E0-4341-B8EC-6B06953ABD6C}"/>
+    <hyperlink ref="J263" r:id="rId158" xr:uid="{D1A16041-44A1-4713-81DA-B0195CA18478}"/>
+    <hyperlink ref="J265" r:id="rId159" xr:uid="{46AD5679-5737-43FC-A8EA-450B1F241BF7}"/>
+    <hyperlink ref="J266" r:id="rId160" xr:uid="{9FB58615-04ED-4E40-A533-9F13DA62A489}"/>
+    <hyperlink ref="J267" r:id="rId161" xr:uid="{706669CD-C5AA-4CBA-BA8A-7880223E2207}"/>
+    <hyperlink ref="J270" r:id="rId162" xr:uid="{B4D9C6C8-733B-4283-A7F9-E27603D48FFB}"/>
+    <hyperlink ref="J271" r:id="rId163" xr:uid="{79919F7D-9A6B-4528-829F-A079ADC8CA14}"/>
+    <hyperlink ref="J273" r:id="rId164" xr:uid="{84FA890A-D84A-4F3C-BE42-CC8AEE1427AD}"/>
+    <hyperlink ref="J274" r:id="rId165" xr:uid="{1B2A206B-E1EB-45E6-9649-BD879E64899E}"/>
+    <hyperlink ref="J275" r:id="rId166" xr:uid="{C165166C-B6CF-4E35-B212-772A5D462FEA}"/>
+    <hyperlink ref="J277" r:id="rId167" xr:uid="{C1D14DB9-7C93-45B3-B9A3-1D316D81BA7F}"/>
+    <hyperlink ref="J278" r:id="rId168" xr:uid="{4D95043C-1B47-48FA-8066-4E64563B52D7}"/>
+    <hyperlink ref="J279" r:id="rId169" xr:uid="{7E6D103F-DE2A-4BE0-BDD2-159F071DFD7C}"/>
+    <hyperlink ref="J280" r:id="rId170" xr:uid="{C4B5498F-D580-4A30-A8C5-FA89EF0E99AE}"/>
+    <hyperlink ref="J281" r:id="rId171" xr:uid="{52E60B8F-5259-4228-87F4-B853A8275BA5}"/>
+    <hyperlink ref="J282" r:id="rId172" xr:uid="{87C8D86B-04B4-453D-A5C3-753BA8459C6D}"/>
+    <hyperlink ref="J283" r:id="rId173" xr:uid="{E5F7FB43-8258-4E8B-BD72-04310BEBD47F}"/>
+    <hyperlink ref="J286" r:id="rId174" xr:uid="{4BE9C831-6D3B-4EC9-A6F8-9AC6F9B34713}"/>
+    <hyperlink ref="J287" r:id="rId175" xr:uid="{6192BA4F-7AF9-4EC4-A42E-8913FC24E989}"/>
+    <hyperlink ref="J290" r:id="rId176" xr:uid="{B6A17185-0955-486B-9A61-586C1076387F}"/>
+    <hyperlink ref="J292" r:id="rId177" xr:uid="{257A88BF-0C0F-4B15-842B-02C0BA674923}"/>
+    <hyperlink ref="J294" r:id="rId178" xr:uid="{6EA3046B-7441-4B3D-BA77-CEEF8DBECF07}"/>
+    <hyperlink ref="J296" r:id="rId179" xr:uid="{80C8831A-4A19-48C0-A1C0-FDD6D6078A6D}"/>
+    <hyperlink ref="J297" r:id="rId180" xr:uid="{75886204-6584-4293-8B49-6A392C47B29A}"/>
+    <hyperlink ref="J298" r:id="rId181" xr:uid="{58A15B10-C0AE-45A1-81FE-DA8A5E9E409D}"/>
+    <hyperlink ref="J299" r:id="rId182" xr:uid="{BCAD2587-D1AB-40E4-B686-4D38EE99264C}"/>
+    <hyperlink ref="J300" r:id="rId183" xr:uid="{B3FDAE16-70F7-46EE-A611-A56399012F82}"/>
+    <hyperlink ref="J301" r:id="rId184" xr:uid="{CD4BBD1E-FB27-4B57-AF5A-0DB76A77CAF3}"/>
+    <hyperlink ref="J303" r:id="rId185" xr:uid="{187240AE-FFE5-4B2F-A9F1-2177B97830B9}"/>
+    <hyperlink ref="J305" r:id="rId186" xr:uid="{3FF4E42C-9EC9-472D-A3AD-FF085B844285}"/>
+    <hyperlink ref="J306" r:id="rId187" xr:uid="{6C2C4327-0144-4FF6-B08F-303E15A7681D}"/>
+    <hyperlink ref="J308" r:id="rId188" xr:uid="{54E7D503-6E90-4F32-8194-1550E460C4CB}"/>
+    <hyperlink ref="J309" r:id="rId189" xr:uid="{CD089430-207F-4C0C-849B-CD6650809A31}"/>
+    <hyperlink ref="J311" r:id="rId190" xr:uid="{6BBE8C51-34F1-47C4-89B1-F6EAF894E2A3}"/>
+    <hyperlink ref="J312" r:id="rId191" xr:uid="{158D2880-6FF0-45A2-AF3B-F1870202A18B}"/>
+    <hyperlink ref="J314" r:id="rId192" xr:uid="{B2728111-B4CB-4178-8175-47535439B702}"/>
+    <hyperlink ref="J317" r:id="rId193" xr:uid="{4C6AF07C-8771-4858-8C47-78D373B3BF01}"/>
+    <hyperlink ref="J318" r:id="rId194" xr:uid="{C8179FC7-B97A-4A29-B096-18719326C53E}"/>
+    <hyperlink ref="J321" r:id="rId195" xr:uid="{25193CF5-E875-404C-AAAA-1B58B6159079}"/>
+    <hyperlink ref="J322" r:id="rId196" xr:uid="{80936FD6-D876-445C-9FF6-B406C1568E50}"/>
+    <hyperlink ref="J325" r:id="rId197" xr:uid="{6B6C2F34-1123-43F7-9F64-A2CA7B82907E}"/>
+    <hyperlink ref="J326" r:id="rId198" xr:uid="{CB4A163F-7AD5-466D-8AAD-DD9E4B229AB1}"/>
+    <hyperlink ref="J329" r:id="rId199" xr:uid="{4B5CA76F-E3EA-4563-9B03-2E96D7A855C3}"/>
+    <hyperlink ref="J330" r:id="rId200" xr:uid="{C7DC04BD-7B15-469D-813B-E7350D2D02CA}"/>
+    <hyperlink ref="J331" r:id="rId201" xr:uid="{32E97C79-64F2-4FED-A180-66595C886981}"/>
+    <hyperlink ref="J333" r:id="rId202" xr:uid="{57635E6E-5DF8-48DB-9FA5-72BEE38E7BCC}"/>
+    <hyperlink ref="J334" r:id="rId203" xr:uid="{54489741-D8A0-4155-B6E2-3583020003C6}"/>
+    <hyperlink ref="J335" r:id="rId204" xr:uid="{556EAB6B-C7EA-4BFB-BD01-52DE6BC2D851}"/>
+    <hyperlink ref="J336" r:id="rId205" xr:uid="{F59986CD-0676-4561-B6A9-A68C5B3CABFB}"/>
+    <hyperlink ref="J338" r:id="rId206" xr:uid="{4166A8A9-69CA-4785-8B4E-9E17BCB1306C}"/>
+    <hyperlink ref="J340" r:id="rId207" xr:uid="{EC3EECE1-AA16-431D-B9F8-8D7C2DD01327}"/>
+    <hyperlink ref="J342" r:id="rId208" xr:uid="{8494A5FF-5191-48C2-838F-D6E446FEA440}"/>
+    <hyperlink ref="J343" r:id="rId209" xr:uid="{66D2C537-1E1A-40B5-952B-A9E391AC80D6}"/>
+    <hyperlink ref="J344" r:id="rId210" xr:uid="{DB40B62D-81BF-4130-9231-C1A97B301378}"/>
+    <hyperlink ref="J346" r:id="rId211" xr:uid="{68FA639F-8C1B-4E50-B200-4A87E34140C6}"/>
+    <hyperlink ref="J349" r:id="rId212" xr:uid="{0499977F-F3C2-4628-A509-AF2DBE35CD55}"/>
+    <hyperlink ref="J350" r:id="rId213" xr:uid="{5D692D03-7480-4852-B376-803001B2A52B}"/>
+    <hyperlink ref="J352" r:id="rId214" xr:uid="{B010F9FB-F8FD-47B2-9902-79EBDBB4883A}"/>
+    <hyperlink ref="J354" r:id="rId215" xr:uid="{CCB5AF74-EB14-490A-849D-F74BC7A85B2F}"/>
+    <hyperlink ref="J355" r:id="rId216" xr:uid="{3610A5E3-D4B3-4D24-9BEB-5058F70789F3}"/>
+    <hyperlink ref="J356" r:id="rId217" xr:uid="{6046CF7F-2565-4CEC-8B80-E2C0BAEC7D42}"/>
+    <hyperlink ref="J357" r:id="rId218" xr:uid="{EA106168-18E8-4A40-A325-900EA6F66C38}"/>
+    <hyperlink ref="J358" r:id="rId219" xr:uid="{A577A99D-88F2-4497-93A3-3B5545663D99}"/>
+    <hyperlink ref="J360" r:id="rId220" xr:uid="{9F7C570E-D340-4DD6-B820-AFE490F5FBEA}"/>
+    <hyperlink ref="J363" r:id="rId221" xr:uid="{61B0DBE2-933A-4A68-BC7E-AFE62A573278}"/>
+    <hyperlink ref="J364" r:id="rId222" xr:uid="{6E455620-D20A-4CB3-B0B0-401F2AE1114C}"/>
+    <hyperlink ref="J366" r:id="rId223" xr:uid="{138ED6A6-546B-4F43-AF64-6B76E4643B98}"/>
+    <hyperlink ref="J368" r:id="rId224" xr:uid="{E4511C12-2CAC-4DFA-ACB3-2B463FF3BE27}"/>
+    <hyperlink ref="J370" r:id="rId225" xr:uid="{F172C7BE-D691-4311-B648-F62CB7953C1A}"/>
+    <hyperlink ref="J371" r:id="rId226" xr:uid="{33C15F62-BC64-42BC-9D28-11904555777B}"/>
+    <hyperlink ref="J372" r:id="rId227" xr:uid="{75491697-4C29-427C-8893-E89AA35F916C}"/>
+    <hyperlink ref="J373" r:id="rId228" xr:uid="{5AB6B958-3623-4972-B65B-4CF25DEB8D1E}"/>
+    <hyperlink ref="J374" r:id="rId229" xr:uid="{77D5BA4A-E74C-46F8-8B40-A7FC2DA23DDB}"/>
+    <hyperlink ref="J375" r:id="rId230" xr:uid="{7F13817B-453A-43B8-AFC9-D34D26307004}"/>
+    <hyperlink ref="J376" r:id="rId231" xr:uid="{437C9D07-092D-4B55-97DE-0AA7D0EC1E1A}"/>
+    <hyperlink ref="J377" r:id="rId232" xr:uid="{AD20C639-8D2F-47C5-AF6F-07039DA7EDE9}"/>
+    <hyperlink ref="J378" r:id="rId233" xr:uid="{FA006A49-2B08-4764-8D95-0AC53F9D4FA3}"/>
+    <hyperlink ref="J379" r:id="rId234" xr:uid="{AB2D6353-3C9C-4546-852B-D2E727028DD9}"/>
+    <hyperlink ref="J381" r:id="rId235" xr:uid="{6D6480B9-1390-46A2-8D7C-E2A446FABABD}"/>
+    <hyperlink ref="J383" r:id="rId236" xr:uid="{AE81F38E-C4F8-4BBE-B638-BC86A8150DC4}"/>
+    <hyperlink ref="J384" r:id="rId237" xr:uid="{AE33A833-3E2F-4BB0-9A8A-F84BC530CC86}"/>
+    <hyperlink ref="J386" r:id="rId238" xr:uid="{B277B269-4E86-442A-A3C3-759C12F0D8DB}"/>
+    <hyperlink ref="J387" r:id="rId239" xr:uid="{D6FFC37E-45BB-4949-A99A-38681F34676B}"/>
+    <hyperlink ref="J388" r:id="rId240" xr:uid="{6AED2FD6-4E1D-408C-8362-EA158BD80774}"/>
+    <hyperlink ref="J390" r:id="rId241" xr:uid="{BF3D4CC1-6051-4661-A0EC-168683FC6586}"/>
+    <hyperlink ref="J391" r:id="rId242" xr:uid="{B99F3C64-73CC-4E45-8CB6-775E21F771F3}"/>
+    <hyperlink ref="J394" r:id="rId243" xr:uid="{F375CAB5-F40B-48F7-ADBD-097463011C99}"/>
+    <hyperlink ref="J395" r:id="rId244" xr:uid="{4600324A-F041-4735-B7B5-248404FC58F1}"/>
+    <hyperlink ref="J396" r:id="rId245" xr:uid="{3D304724-AFA4-4606-B615-46BE313BAEA1}"/>
+    <hyperlink ref="J397" r:id="rId246" xr:uid="{689740D8-BA20-41D3-9B31-ED0EB83FAA26}"/>
+    <hyperlink ref="J398" r:id="rId247" xr:uid="{015BF356-D90D-4F61-9D5F-ACF1E9A1CE8D}"/>
+    <hyperlink ref="J399" r:id="rId248" xr:uid="{D979BE71-79C6-4DE3-AC78-040F6A5363DC}"/>
+    <hyperlink ref="J400" r:id="rId249" xr:uid="{C5AE71C9-0103-4A1E-9868-4467952626C3}"/>
+    <hyperlink ref="J403" r:id="rId250" xr:uid="{55C01FAB-BEB1-4BC3-91C3-F718732F7F9B}"/>
+    <hyperlink ref="J404" r:id="rId251" xr:uid="{74ADD8FD-DCCF-4B4D-8C3A-0A30BDDE41BE}"/>
+    <hyperlink ref="J405" r:id="rId252" xr:uid="{7C94A65D-2526-4670-A718-07DCB73FE9FE}"/>
+    <hyperlink ref="J406" r:id="rId253" xr:uid="{72E478EA-E21E-49E7-B7B3-2E92DC80F607}"/>
+    <hyperlink ref="J408" r:id="rId254" xr:uid="{16F24FFC-28B9-42E0-93D5-F3B969889846}"/>
+    <hyperlink ref="J409" r:id="rId255" xr:uid="{9C9F8B39-7FFE-475C-BCF9-8CA13B6567F9}"/>
+    <hyperlink ref="J411" r:id="rId256" xr:uid="{A3CF5159-C276-4BB4-9EB6-187A19B0B6DE}"/>
+    <hyperlink ref="J413" r:id="rId257" xr:uid="{221C1084-47BA-45B6-8EA4-ED41088810B7}"/>
+    <hyperlink ref="J415" r:id="rId258" xr:uid="{FE0EF6D3-3048-4554-B284-141FD0DE0EFF}"/>
+    <hyperlink ref="J416" r:id="rId259" xr:uid="{3753CF69-281F-45C2-BC63-61972CF912C2}"/>
+    <hyperlink ref="J418" r:id="rId260" xr:uid="{D785F79A-E85A-42AA-A584-4F2D3312FCE6}"/>
+    <hyperlink ref="J421" r:id="rId261" xr:uid="{E61FA0D3-A514-4103-88BA-13DAF4453199}"/>
+    <hyperlink ref="J422" r:id="rId262" xr:uid="{67297421-84C1-4E66-8742-CCBFF5A87B80}"/>
+    <hyperlink ref="J430" r:id="rId263" xr:uid="{ABE2D577-7347-4538-98E8-3D4F682274BC}"/>
+    <hyperlink ref="J431" r:id="rId264" xr:uid="{39996141-55C0-4ABB-93CE-4D2876458889}"/>
+    <hyperlink ref="J432" r:id="rId265" xr:uid="{5B21FD8C-4E42-4190-8418-49CE6FB15968}"/>
+    <hyperlink ref="J433" r:id="rId266" xr:uid="{AB5E9C72-2C1F-46EF-9FBC-754B1C9D0930}"/>
+    <hyperlink ref="J434" r:id="rId267" xr:uid="{EE9566B4-67D6-48F0-A7A9-8F258323ED07}"/>
+    <hyperlink ref="J435" r:id="rId268" xr:uid="{060FB273-5F2E-4F26-8155-C70EEA2985B8}"/>
+    <hyperlink ref="J436" r:id="rId269" xr:uid="{E4666100-B463-4063-8E8B-25B3A424390D}"/>
+    <hyperlink ref="J437" r:id="rId270" xr:uid="{CFD76F44-706E-49C9-AC87-5887B7F48C78}"/>
+    <hyperlink ref="J438" r:id="rId271" xr:uid="{F8EFC01F-4E09-4063-BBAC-B3EBDA000AEA}"/>
+    <hyperlink ref="J439" r:id="rId272" xr:uid="{87264F6D-5ABE-493A-84D2-A5856E6F7EBF}"/>
+    <hyperlink ref="J445" r:id="rId273" xr:uid="{69269300-FA02-495F-9F2A-CE088D2ABD17}"/>
+    <hyperlink ref="J447" r:id="rId274" xr:uid="{348F0C2D-1C10-4B68-889C-727BC0E14BF5}"/>
+    <hyperlink ref="J449" r:id="rId275" xr:uid="{2E0F75C7-101F-454D-90E5-C78F5ECFC6E5}"/>
+    <hyperlink ref="J450" r:id="rId276" xr:uid="{DBC2BDAB-3881-4393-865D-805CD11383BC}"/>
+    <hyperlink ref="J451" r:id="rId277" xr:uid="{8190EBCD-C526-41B5-8704-FAE0DBDC7169}"/>
+    <hyperlink ref="J452" r:id="rId278" xr:uid="{A3AEA2E4-A118-4544-9ED9-C4B067F06445}"/>
+    <hyperlink ref="J453" r:id="rId279" xr:uid="{5E64FE1A-BF72-4441-833D-3CCD8EED0C27}"/>
+    <hyperlink ref="J454" r:id="rId280" xr:uid="{D0ED3BB1-B17E-4F51-AB6B-579E38A6B761}"/>
+    <hyperlink ref="J455" r:id="rId281" xr:uid="{B64B739B-7C80-4544-8E0F-8A2A673B58DA}"/>
+    <hyperlink ref="J458" r:id="rId282" xr:uid="{B76C15F5-1DA8-40E3-A24D-DED181170BB5}"/>
+    <hyperlink ref="J460" r:id="rId283" xr:uid="{78521E02-8ACF-4394-8B5E-1BCC9491520F}"/>
+    <hyperlink ref="J461" r:id="rId284" xr:uid="{BDF27425-A735-4825-A93D-35A46878B9B8}"/>
+    <hyperlink ref="J462" r:id="rId285" xr:uid="{D968201B-51C1-4A8E-AB55-04071DA6E136}"/>
+    <hyperlink ref="J465" r:id="rId286" xr:uid="{67C950AC-2589-42B3-9FDF-05E748BC3A33}"/>
+    <hyperlink ref="J469" r:id="rId287" xr:uid="{11F393F7-F0FA-4EF2-89A1-F9F8B826E892}"/>
+    <hyperlink ref="J473" r:id="rId288" xr:uid="{C98DFC8F-7FE6-4522-855D-BC85E7347B78}"/>
+    <hyperlink ref="J476" r:id="rId289" xr:uid="{51E208FB-5E5B-4BCC-BD56-8A9470F750F1}"/>
+    <hyperlink ref="J478" r:id="rId290" xr:uid="{25C2424B-C4BB-4CBB-93A2-9232EBFBB82E}"/>
+    <hyperlink ref="J479" r:id="rId291" xr:uid="{B5712FBF-D038-409F-9FEF-5154B9A6F53B}"/>
+    <hyperlink ref="J480" r:id="rId292" xr:uid="{CF2E8F39-12E0-4108-883E-ABB4D25F0C7F}"/>
+    <hyperlink ref="J481" r:id="rId293" xr:uid="{7CADA484-531F-4BF4-AE57-D69F132CB5EC}"/>
+    <hyperlink ref="J482" r:id="rId294" xr:uid="{8C1DD05A-68D3-47D4-BA96-F1908517B1F6}"/>
+    <hyperlink ref="J484" r:id="rId295" xr:uid="{347B7B16-3EC2-445C-8325-EBBC066B9032}"/>
+    <hyperlink ref="J485" r:id="rId296" xr:uid="{6EE49938-830A-4CDD-85CA-5F4ACBD32CF6}"/>
+    <hyperlink ref="J488" r:id="rId297" xr:uid="{DA83B9C3-785D-4AC9-AF77-69587EBAC16F}"/>
+    <hyperlink ref="J489" r:id="rId298" xr:uid="{BA4D0330-BCBC-482B-8C4F-6C8BF4E75B55}"/>
+    <hyperlink ref="J490" r:id="rId299" xr:uid="{5E06AA10-395B-4109-8915-9AF35AC75ACA}"/>
+    <hyperlink ref="J491" r:id="rId300" xr:uid="{7F4D7174-8286-4F61-B345-745EF8736AE4}"/>
+    <hyperlink ref="J494" r:id="rId301" xr:uid="{E91D6DE4-9976-4684-9623-25D4CFEA2C84}"/>
+    <hyperlink ref="J496" r:id="rId302" xr:uid="{3C5F15D8-B3F2-4111-9D46-457244CC78C1}"/>
+    <hyperlink ref="J497" r:id="rId303" xr:uid="{5E340BF2-3433-489B-880C-8CB53D883214}"/>
+    <hyperlink ref="J498" r:id="rId304" xr:uid="{A31E441F-CE1B-4BD9-B373-9F8BAB22F4AB}"/>
+    <hyperlink ref="J499" r:id="rId305" xr:uid="{3CE17C78-5ADD-4C13-906F-AA3DA9007F75}"/>
+    <hyperlink ref="J500" r:id="rId306" xr:uid="{8DE0CE75-FC28-4200-B76C-83485A4EA16E}"/>
+    <hyperlink ref="J501" r:id="rId307" xr:uid="{7BE626B3-D34B-48D1-9C79-EDB6EDA2FCFF}"/>
+    <hyperlink ref="J503" r:id="rId308" xr:uid="{C7173589-EA41-4404-896B-D13A54F62B6E}"/>
+    <hyperlink ref="J504" r:id="rId309" xr:uid="{0DC651BD-7507-45F7-ABA8-97C600DDB4B8}"/>
+    <hyperlink ref="J508" r:id="rId310" xr:uid="{D813BF13-1D4F-40D9-A1B3-A23DD8119712}"/>
+    <hyperlink ref="J509" r:id="rId311" xr:uid="{8DD1B92E-9FE2-4D96-A3C1-071064F3BF6F}"/>
+    <hyperlink ref="J510" r:id="rId312" xr:uid="{A79B0B51-EF6B-460E-97CB-8CE705BB4F50}"/>
+    <hyperlink ref="J511" r:id="rId313" xr:uid="{7D42943F-7B82-40F6-B78D-5B19C6514551}"/>
+    <hyperlink ref="J513" r:id="rId314" xr:uid="{3FE61E86-F9D1-49D7-B887-A9584D67AC3E}"/>
+    <hyperlink ref="J515" r:id="rId315" xr:uid="{C9F2418E-6818-4A03-8307-17F8614602FC}"/>
+    <hyperlink ref="J516" r:id="rId316" xr:uid="{A1CCB637-AE82-4F54-B315-77633B02BE0C}"/>
+    <hyperlink ref="J519" r:id="rId317" xr:uid="{17A00A91-8FFA-4DAE-AC44-DE19DE07286E}"/>
+    <hyperlink ref="J523" r:id="rId318" xr:uid="{842E5C4F-E050-475B-93AA-A38694BB563C}"/>
+    <hyperlink ref="J524" r:id="rId319" xr:uid="{1B75A816-EA9D-4651-BC27-C3CDF2F31DD4}"/>
+    <hyperlink ref="J525" r:id="rId320" xr:uid="{726D973D-09E3-4F49-986F-36E752A9DA15}"/>
+    <hyperlink ref="J535" r:id="rId321" xr:uid="{6A10B80A-B464-4E3B-993E-966A07C507F1}"/>
+    <hyperlink ref="J536" r:id="rId322" xr:uid="{EAD75D2E-9F0C-47D1-B119-A3F71B497F93}"/>
+    <hyperlink ref="J537" r:id="rId323" xr:uid="{D4BC6D14-9CD4-40CD-AAC5-D6F73E04516F}"/>
+    <hyperlink ref="J538" r:id="rId324" xr:uid="{1EF1F014-B1D6-4CA4-B38C-027A50368E1C}"/>
+    <hyperlink ref="J539" r:id="rId325" xr:uid="{029C5D92-1010-43FD-B219-A5B08345B1DE}"/>
+    <hyperlink ref="J540" r:id="rId326" xr:uid="{7D9A9C8F-9488-4E89-992E-D269F505D080}"/>
+    <hyperlink ref="J541" r:id="rId327" xr:uid="{F38C2DFF-CFB4-478E-AC63-AB7BFCFA306C}"/>
+    <hyperlink ref="J543" r:id="rId328" xr:uid="{CB4B474B-4785-42B8-A737-F5DBF4895FA0}"/>
+    <hyperlink ref="J544" r:id="rId329" xr:uid="{7E99DFD6-9020-48AA-B4AA-1664C7003158}"/>
+    <hyperlink ref="J546" r:id="rId330" xr:uid="{7BE27276-4B96-47A5-8594-9F9E3786F12C}"/>
+    <hyperlink ref="J547" r:id="rId331" xr:uid="{257643CD-738E-4031-B940-E5B10181B568}"/>
+    <hyperlink ref="J548" r:id="rId332" xr:uid="{D1833AC2-3165-41E3-A4BF-75EE2EE47BEE}"/>
+    <hyperlink ref="J549" r:id="rId333" xr:uid="{368C8AFC-F90C-48DF-80A6-F17405F70EAE}"/>
+    <hyperlink ref="J550" r:id="rId334" xr:uid="{A3EA35D5-6046-46DA-9DC8-D372A82CCFA1}"/>
+    <hyperlink ref="J551" r:id="rId335" xr:uid="{176571D8-1DF7-4123-9810-39FD8C9A151D}"/>
+    <hyperlink ref="J552" r:id="rId336" xr:uid="{E926264E-F20D-487B-81F2-3E67A597DB47}"/>
+    <hyperlink ref="J555" r:id="rId337" xr:uid="{CA8EAE16-C616-4F60-B818-2099A07F1C18}"/>
+    <hyperlink ref="J556" r:id="rId338" xr:uid="{51378274-38DC-4E36-B0DE-DAE23496E707}"/>
+    <hyperlink ref="J558" r:id="rId339" xr:uid="{1083897C-F3CB-4D0E-8E3A-7C5E067B4A75}"/>
+    <hyperlink ref="J559" r:id="rId340" xr:uid="{EE44DDC3-61DF-4691-9A4C-0B22211E5306}"/>
+    <hyperlink ref="J560" r:id="rId341" xr:uid="{12DFF04E-1560-4420-BCC5-3D621288E02D}"/>
+    <hyperlink ref="J562" r:id="rId342" xr:uid="{744EC998-8435-4BEA-8E42-475A1C116454}"/>
+    <hyperlink ref="J569" r:id="rId343" xr:uid="{B07CE1B2-FBE2-4D75-809F-5DED20E1ECA9}"/>
+    <hyperlink ref="J570" r:id="rId344" xr:uid="{D1EA4A21-7A25-4D24-8232-FE7C6CA0F97A}"/>
+    <hyperlink ref="J571" r:id="rId345" xr:uid="{5B2CBEB4-4E1B-4FD7-8A17-A1DF7EB33D70}"/>
+    <hyperlink ref="J572" r:id="rId346" xr:uid="{4D1E280A-5E24-4BBF-87E6-F5C0EF4EED06}"/>
+    <hyperlink ref="J573" r:id="rId347" xr:uid="{F5670205-0BAB-469F-ABF1-DC081C693E18}"/>
+    <hyperlink ref="J574" r:id="rId348" xr:uid="{9594A829-D31F-4FBB-A3C6-9D6C2B4C62E8}"/>
+    <hyperlink ref="J575" r:id="rId349" xr:uid="{50ED46E3-0D3B-459D-A96D-077F45A9D1E3}"/>
+    <hyperlink ref="J576" r:id="rId350" xr:uid="{2960B9EA-C806-4E75-8324-3E0789066571}"/>
+    <hyperlink ref="J577" r:id="rId351" xr:uid="{CE127A12-4C07-4DB8-9AD4-665A74AB2FB5}"/>
+    <hyperlink ref="J578" r:id="rId352" xr:uid="{0F0DA096-6B71-4A5B-97DA-D0BC7A88CD88}"/>
+    <hyperlink ref="J579" r:id="rId353" xr:uid="{F160697F-0FB4-478C-99FB-62A2EFADCAD8}"/>
+    <hyperlink ref="J580" r:id="rId354" xr:uid="{62C8AAD3-B740-42C8-9832-7790F6AAE73B}"/>
+    <hyperlink ref="J581" r:id="rId355" xr:uid="{973B23DD-7EF9-495F-ABA9-03D980D25A86}"/>
+    <hyperlink ref="J582" r:id="rId356" xr:uid="{463C5476-4B3D-4D6A-BC59-1160F689F710}"/>
+    <hyperlink ref="J584" r:id="rId357" xr:uid="{D5B1635F-965C-4942-9DB8-F5160E413031}"/>
+    <hyperlink ref="J585" r:id="rId358" xr:uid="{5342C94F-C478-4C12-BCA5-AFC163291761}"/>
+    <hyperlink ref="J586" r:id="rId359" xr:uid="{511FA499-E1B8-4BB4-8DA8-4C5619E7AACA}"/>
+    <hyperlink ref="J587" r:id="rId360" xr:uid="{67CC7EE5-2764-40E7-A240-D4FA86485ED0}"/>
+    <hyperlink ref="J592" r:id="rId361" xr:uid="{34A01905-8F13-4154-94F8-12CE54BBBA0D}"/>
+    <hyperlink ref="J593" r:id="rId362" xr:uid="{C92B8CC2-8D07-451C-84B1-A5F14B75DE44}"/>
+    <hyperlink ref="J595" r:id="rId363" xr:uid="{6CDB1FFF-8E18-4784-828D-FBCD41F76D3D}"/>
+    <hyperlink ref="J596" r:id="rId364" xr:uid="{D55C9591-E0E1-4FA8-A21B-5BF22DC32C2A}"/>
+    <hyperlink ref="J598" r:id="rId365" xr:uid="{B91A60BE-9409-4947-81FA-CAB0DC1D6A25}"/>
+    <hyperlink ref="J599" r:id="rId366" xr:uid="{7B96E3AC-F3E5-4863-80D1-230102D779ED}"/>
+    <hyperlink ref="J602" r:id="rId367" xr:uid="{945D6136-7B57-4775-A46E-B08CF0D4650F}"/>
+    <hyperlink ref="J603" r:id="rId368" xr:uid="{283AF454-1DE5-4AAF-ACDB-1CDB999EA992}"/>
+    <hyperlink ref="J604" r:id="rId369" xr:uid="{2917B0F9-C541-4DE2-B281-003FF6DD5A05}"/>
+    <hyperlink ref="J605" r:id="rId370" xr:uid="{5A66925B-1DC1-44E0-987C-3FDCCF3BAFAC}"/>
+    <hyperlink ref="J606" r:id="rId371" xr:uid="{E53D81C2-E0D6-47D2-94D0-3BB94C7BD1DF}"/>
+    <hyperlink ref="J608" r:id="rId372" xr:uid="{6F645427-0056-4732-B8A0-F00529CA2DF6}"/>
+    <hyperlink ref="J609" r:id="rId373" xr:uid="{A31A53BF-ABB5-46E6-9E53-201F37F1E62C}"/>
+    <hyperlink ref="J611" r:id="rId374" xr:uid="{51CB001A-510B-4EA6-B70C-6E6899B78720}"/>
+    <hyperlink ref="J612" r:id="rId375" xr:uid="{3433D1A4-B387-4C26-A194-002D38980626}"/>
+    <hyperlink ref="J613" r:id="rId376" xr:uid="{B569DF3B-2FFD-4964-A359-1F0D509EED22}"/>
+    <hyperlink ref="J615" r:id="rId377" xr:uid="{0CC54770-2732-4B0A-8250-971D4701EE07}"/>
+    <hyperlink ref="J617" r:id="rId378" xr:uid="{02E6EFB2-3F85-42D4-A4C4-C4CE7301CA31}"/>
+    <hyperlink ref="J618" r:id="rId379" xr:uid="{C7879DB3-1024-4531-A0C7-C2EB593B1210}"/>
+    <hyperlink ref="J619" r:id="rId380" xr:uid="{59C6931B-DBD8-490A-B0C1-807FA4D813BB}"/>
+    <hyperlink ref="J622" r:id="rId381" xr:uid="{603232BC-50BF-4393-AD98-A185208F63EF}"/>
+    <hyperlink ref="J623" r:id="rId382" xr:uid="{A2B201C7-777E-466A-AAC4-E9A69E71A36E}"/>
+    <hyperlink ref="J624" r:id="rId383" xr:uid="{F47FEE3A-A9C4-4C8C-B4E2-B512C1D59B57}"/>
+    <hyperlink ref="J626" r:id="rId384" xr:uid="{DF7CFD9A-A331-43A6-B786-7F912D06A218}"/>
+    <hyperlink ref="J628" r:id="rId385" xr:uid="{0721CC77-B75D-4076-8337-9A196C6E7E41}"/>
+    <hyperlink ref="J629" r:id="rId386" xr:uid="{A3226F53-C51C-4FFF-A468-386510E3A7B7}"/>
+    <hyperlink ref="J631" r:id="rId387" xr:uid="{473496B0-6940-4FF4-B1B1-68E354C4846A}"/>
+    <hyperlink ref="J634" r:id="rId388" xr:uid="{3FC49A73-0D69-43FD-8858-3AF975CF1288}"/>
+    <hyperlink ref="J635" r:id="rId389" xr:uid="{6DBB7465-DC95-4FC5-8B8F-D189657E2F68}"/>
+    <hyperlink ref="J637" r:id="rId390" xr:uid="{9612A7A8-A684-4E5F-9B81-A1407D1F8F20}"/>
+    <hyperlink ref="J640" r:id="rId391" xr:uid="{5EA48750-5DD5-41A5-8F75-00F2F8764E28}"/>
+    <hyperlink ref="J641" r:id="rId392" xr:uid="{55EF801F-9DEF-45E3-9D24-F0F3A0E9832B}"/>
+    <hyperlink ref="J642" r:id="rId393" xr:uid="{983CD208-FC24-4955-B588-469AED6C905B}"/>
+    <hyperlink ref="J644" r:id="rId394" xr:uid="{ECD42BC7-41E7-40C0-9971-3953EB180FED}"/>
+    <hyperlink ref="J645" r:id="rId395" xr:uid="{6C4EBE40-F79C-4E6D-AA68-19B5A0B42AF5}"/>
+    <hyperlink ref="J648" r:id="rId396" xr:uid="{31E5C74C-2EDF-4E84-8CEF-FD3A363EB200}"/>
+    <hyperlink ref="J649" r:id="rId397" xr:uid="{379CC7E4-455F-4B6D-BAAC-7631374854F2}"/>
+    <hyperlink ref="J652" r:id="rId398" xr:uid="{F91F38A7-1755-4A7D-97C6-9A56C8C1619F}"/>
+    <hyperlink ref="J654" r:id="rId399" xr:uid="{702864B9-61BB-4638-A1A4-F9EC438924E5}"/>
+    <hyperlink ref="J656" r:id="rId400" xr:uid="{1DACF4FD-1351-45DA-A4F8-E803545D6F13}"/>
+    <hyperlink ref="J657" r:id="rId401" xr:uid="{208A5339-D1EA-4F37-9125-654728F47953}"/>
+    <hyperlink ref="J663" r:id="rId402" xr:uid="{36D95372-66D6-49EF-B5BA-3488D0E9B35F}"/>
+    <hyperlink ref="J664" r:id="rId403" xr:uid="{216BE0C3-1116-4024-80E8-6E6E72751DE9}"/>
+    <hyperlink ref="J665" r:id="rId404" xr:uid="{89766206-7D5E-4A89-800B-550317A9750F}"/>
+    <hyperlink ref="J666" r:id="rId405" xr:uid="{97D679F9-7BB9-46DB-AAB2-9F17138A4E1D}"/>
+    <hyperlink ref="J667" r:id="rId406" xr:uid="{E6488297-4C8E-47A9-95BF-B8710A68DC1A}"/>
+    <hyperlink ref="J668" r:id="rId407" xr:uid="{E65D469F-9C22-40B5-8288-71A632AAD78C}"/>
+    <hyperlink ref="J669" r:id="rId408" xr:uid="{0DF19C79-A305-4FFF-9D6C-A8A1C791DB22}"/>
+    <hyperlink ref="J670" r:id="rId409" xr:uid="{6232D801-3074-4FF0-B440-1F524855BE5C}"/>
+    <hyperlink ref="J671" r:id="rId410" xr:uid="{83F47890-DA33-43F3-A8C9-90CD69D94833}"/>
+    <hyperlink ref="J672" r:id="rId411" xr:uid="{358CD055-2A23-4D37-89EE-7DBE041F149E}"/>
+    <hyperlink ref="J673" r:id="rId412" xr:uid="{D6275C86-3B11-4D30-B3BC-2C3102533BFC}"/>
+    <hyperlink ref="J674" r:id="rId413" xr:uid="{2AB4C237-023C-45A3-97A1-3DA8B15270C3}"/>
+    <hyperlink ref="J675" r:id="rId414" xr:uid="{582E9A10-C27E-4340-9213-3EBB4CA8A592}"/>
+    <hyperlink ref="J676" r:id="rId415" xr:uid="{16CBDB42-59F1-4336-9EE9-58342D357B15}"/>
+    <hyperlink ref="J677" r:id="rId416" xr:uid="{D0F37D63-2BFF-40F9-8F36-C12D13D42913}"/>
+    <hyperlink ref="J679" r:id="rId417" xr:uid="{C7C5517E-E2DB-43F1-A48A-1CF0E03814B1}"/>
+    <hyperlink ref="J682" r:id="rId418" xr:uid="{F59F9513-556F-4C08-A2E6-EF06999F4A1E}"/>
+    <hyperlink ref="J683" r:id="rId419" xr:uid="{A7136557-F2A2-40E2-8454-929E4A646188}"/>
+    <hyperlink ref="J684" r:id="rId420" xr:uid="{8103C4CC-D703-409C-A325-881D9F0088F2}"/>
+    <hyperlink ref="J688" r:id="rId421" xr:uid="{006075CF-A25F-44EC-AE4E-BB3A3BB339A2}"/>
+    <hyperlink ref="J693" r:id="rId422" xr:uid="{4C7781CC-0060-480E-B9E2-539B6E8695D7}"/>
+    <hyperlink ref="J694" r:id="rId423" xr:uid="{92AEAA9E-B163-4FEF-8CF6-09E5CB5E7D8F}"/>
+    <hyperlink ref="J695" r:id="rId424" xr:uid="{442FE792-CB12-4DC0-BB35-1351245BD405}"/>
+    <hyperlink ref="J696" r:id="rId425" xr:uid="{5B58E406-1E5D-4FEA-A663-8AF8B3E28FAF}"/>
+    <hyperlink ref="J697" r:id="rId426" xr:uid="{F18C377B-C03A-4919-8EA5-9AD4204BC269}"/>
+    <hyperlink ref="J698" r:id="rId427" xr:uid="{43F6144F-BE57-4BEC-9F40-598FEE1F1C47}"/>
+    <hyperlink ref="J699" r:id="rId428" xr:uid="{6ABEE709-C724-4908-8E0F-1295E3A0404A}"/>
+    <hyperlink ref="J700" r:id="rId429" xr:uid="{1445410B-0B1B-433D-8B55-37EF04BD9F71}"/>
+    <hyperlink ref="J705" r:id="rId430" xr:uid="{B99669A4-B6EB-4B09-9AC3-CE7FBA14D6B6}"/>
+    <hyperlink ref="J708" r:id="rId431" xr:uid="{4C48C9AE-8DCB-429D-BD35-99B18DD3079A}"/>
+    <hyperlink ref="J712" r:id="rId432" xr:uid="{198578FE-DFC6-42A3-9CEF-FEE3E7599F31}"/>
+    <hyperlink ref="J713" r:id="rId433" xr:uid="{716A5E9E-0701-4B84-8760-9D02BD236ED0}"/>
+    <hyperlink ref="J714" r:id="rId434" xr:uid="{8CE8C2A7-AAD6-4902-8961-37842D43FD60}"/>
+    <hyperlink ref="J715" r:id="rId435" xr:uid="{0478DEE7-6239-44DD-A838-389A21BF1D96}"/>
+    <hyperlink ref="J718" r:id="rId436" xr:uid="{840084C8-6231-467E-830C-0313D7780106}"/>
+    <hyperlink ref="J720" r:id="rId437" xr:uid="{0DB67BB6-F8C7-4A4C-A47A-713EAEF90F2F}"/>
+    <hyperlink ref="J721" r:id="rId438" xr:uid="{D5C6705F-79B9-484F-B0C1-F9F947B7FF9D}"/>
+    <hyperlink ref="J722" r:id="rId439" xr:uid="{1DC1C238-5755-4EDF-9C0B-1EC7C098C991}"/>
+    <hyperlink ref="J725" r:id="rId440" xr:uid="{6265A1F9-7CB7-41DE-9B58-A87F7BC2ECD4}"/>
+    <hyperlink ref="J726" r:id="rId441" xr:uid="{9365325E-73DC-4FAC-B315-917C2FFBC483}"/>
+    <hyperlink ref="J728" r:id="rId442" xr:uid="{3894F854-4593-4C4B-9E18-3A2638E05F54}"/>
+    <hyperlink ref="J729" r:id="rId443" xr:uid="{08AC8FC5-E39D-4195-8BF0-9182D607E131}"/>
+    <hyperlink ref="J736" r:id="rId444" xr:uid="{F81E93DC-E3ED-4BA3-A3CD-BE6781457BAC}"/>
+    <hyperlink ref="J738" r:id="rId445" xr:uid="{545E7BC8-4E23-4677-AF7F-295E38A3C9F7}"/>
+    <hyperlink ref="J739" r:id="rId446" xr:uid="{3F8CAA90-CEC4-4F89-8808-D0976C65F057}"/>
+    <hyperlink ref="J740" r:id="rId447" xr:uid="{7F32212A-C656-42CF-A847-B11CF055951B}"/>
+    <hyperlink ref="J741" r:id="rId448" xr:uid="{12C4D08B-979B-4310-B331-CEA9188DD81B}"/>
+    <hyperlink ref="J742" r:id="rId449" xr:uid="{063D3F74-967E-4AC0-B298-88E53F960217}"/>
+    <hyperlink ref="J743" r:id="rId450" xr:uid="{29C1C865-BD9C-44C6-910E-6F9B417C8A67}"/>
+    <hyperlink ref="J744" r:id="rId451" xr:uid="{D7AAA251-623E-429F-BAFA-594E5AFBF4E8}"/>
+    <hyperlink ref="J747" r:id="rId452" xr:uid="{F9D4612C-D644-498E-86E4-D5B67DB791D9}"/>
+    <hyperlink ref="J748" r:id="rId453" xr:uid="{A075FDA3-74CF-4BE1-9CCD-1A118E9414DC}"/>
+    <hyperlink ref="J757" r:id="rId454" xr:uid="{CEA99DD8-79F3-45F7-B69C-62421611FA1B}"/>
+    <hyperlink ref="J758" r:id="rId455" xr:uid="{5E2FA710-4B7E-4B06-B40B-A3EFC6A91EA7}"/>
+    <hyperlink ref="J759" r:id="rId456" xr:uid="{50CE92DC-4AF2-49DC-87F4-7BF89AE0D3D5}"/>
+    <hyperlink ref="J760" r:id="rId457" xr:uid="{5D3106AC-92EA-414C-9024-B2E3744D2E75}"/>
+    <hyperlink ref="J761" r:id="rId458" xr:uid="{378DA3D9-5B19-4409-8178-D91082A7B3B8}"/>
+    <hyperlink ref="J762" r:id="rId459" xr:uid="{B411B6A5-74F8-40BE-B868-65D754111A6C}"/>
+    <hyperlink ref="J764" r:id="rId460" xr:uid="{E07F75E7-550E-4C21-824F-99C6B94E9FAA}"/>
+    <hyperlink ref="J765" r:id="rId461" xr:uid="{676DE678-2A21-4AF9-A6C6-48D43B72DD20}"/>
+    <hyperlink ref="J766" r:id="rId462" xr:uid="{A7F35031-216A-4D67-92E5-7733E849DE5F}"/>
+    <hyperlink ref="J767" r:id="rId463" xr:uid="{8319AC14-C34D-411B-BE1F-D635386864CF}"/>
+    <hyperlink ref="J769" r:id="rId464" xr:uid="{FD08CBD8-B81A-419F-BF1E-5D0C13667F01}"/>
+    <hyperlink ref="J770" r:id="rId465" xr:uid="{9B483576-4809-4E45-BD06-50AB4BED6A28}"/>
+    <hyperlink ref="J772" r:id="rId466" xr:uid="{E2C68385-D109-4457-A09D-763E7EFE3943}"/>
+    <hyperlink ref="J774" r:id="rId467" xr:uid="{337A80BC-4B76-4112-90C6-891C59A21F51}"/>
+    <hyperlink ref="J778" r:id="rId468" xr:uid="{43A122E8-081A-4DD1-9208-6D2488362D06}"/>
+    <hyperlink ref="J781" r:id="rId469" xr:uid="{40630495-08A4-486C-8EFF-5A51819DE830}"/>
+    <hyperlink ref="J783" r:id="rId470" xr:uid="{D3E59C74-5638-4C07-A981-30B4111DD06D}"/>
+    <hyperlink ref="J784" r:id="rId471" xr:uid="{E31076E5-AE71-4BD8-A9BC-F323651FA21E}"/>
+    <hyperlink ref="J785" r:id="rId472" xr:uid="{443CFED0-D40B-4A1E-B12F-D9FA2CDC2403}"/>
+    <hyperlink ref="J788" r:id="rId473" xr:uid="{616A1084-D49A-43BF-A41D-7C6289CD8295}"/>
+    <hyperlink ref="J789" r:id="rId474" xr:uid="{A6AD8239-B9F7-4CC6-A911-824BAD02688C}"/>
+    <hyperlink ref="J790" r:id="rId475" xr:uid="{EFAB30AD-0115-4C8D-977B-8B87D12D0FF0}"/>
+    <hyperlink ref="J794" r:id="rId476" xr:uid="{36997A90-6F50-40CD-965F-DDFDCC9EC94A}"/>
+    <hyperlink ref="J795" r:id="rId477" xr:uid="{E7D85512-4292-4F8E-ADD0-979B794C4C94}"/>
+    <hyperlink ref="J796" r:id="rId478" xr:uid="{A93D0531-4859-4EE7-8822-DF1B1E1541C5}"/>
+    <hyperlink ref="J797" r:id="rId479" xr:uid="{2CFB5803-D03D-44C7-AB3D-527C95B74FEB}"/>
+    <hyperlink ref="J799" r:id="rId480" xr:uid="{3B2D6249-5C3F-40C4-8894-2E9519A917BA}"/>
+    <hyperlink ref="J800" r:id="rId481" xr:uid="{EE12E9A8-7DFD-4331-A175-432ABA08CD8A}"/>
+    <hyperlink ref="J801" r:id="rId482" xr:uid="{9409A699-F238-4C93-A342-0F85D1995D9F}"/>
+    <hyperlink ref="J802" r:id="rId483" xr:uid="{40700BD1-6A30-4447-A7B8-A327A79660D6}"/>
+    <hyperlink ref="J803" r:id="rId484" xr:uid="{F8EBC4C0-75BA-4319-A8C8-EDA3054BC79F}"/>
+    <hyperlink ref="J804" r:id="rId485" xr:uid="{4B7D396E-7BB1-4DC2-BEE1-16571D913A6A}"/>
+    <hyperlink ref="J805" r:id="rId486" xr:uid="{3B922D1A-E102-4401-B048-D86EEF185746}"/>
+    <hyperlink ref="J806" r:id="rId487" xr:uid="{D0C95CFE-D432-41B1-A29B-FEEBBEACFFC9}"/>
+    <hyperlink ref="J808" r:id="rId488" xr:uid="{614ADFD7-F4A3-4A3E-9758-0A126A6058B9}"/>
+    <hyperlink ref="J810" r:id="rId489" xr:uid="{FD8739F0-964A-4B45-9168-4D30C5F0A553}"/>
+    <hyperlink ref="J811" r:id="rId490" xr:uid="{F5DF043D-980F-4EDB-8FDE-84B95870E21C}"/>
+    <hyperlink ref="J812" r:id="rId491" xr:uid="{9E505515-33C3-40C6-AEA4-17663E8C4C29}"/>
+    <hyperlink ref="J813" r:id="rId492" xr:uid="{804318CE-B81F-4B7E-8A2B-FDEBEC344C54}"/>
+    <hyperlink ref="J814" r:id="rId493" xr:uid="{5EC20BA9-307F-4F42-AC88-F49139953D77}"/>
+    <hyperlink ref="J815" r:id="rId494" xr:uid="{4F1FEF8B-0777-49EE-AF6C-8B042C66D64F}"/>
+    <hyperlink ref="J816" r:id="rId495" xr:uid="{80C04E72-0754-496B-B7E2-6FAE33F32203}"/>
+    <hyperlink ref="J817" r:id="rId496" xr:uid="{5B715961-FFFE-4E50-AC4E-B25F8A6587CA}"/>
+    <hyperlink ref="J818" r:id="rId497" xr:uid="{6CCF51BB-93AA-4B02-9629-DE3C4C13CA9C}"/>
+    <hyperlink ref="J819" r:id="rId498" xr:uid="{0F2EA6D3-8A41-4C55-88D2-E1AE44594342}"/>
+    <hyperlink ref="J820" r:id="rId499" xr:uid="{7293B270-6357-4CFD-9127-BA852E15B8B5}"/>
+    <hyperlink ref="J821" r:id="rId500" xr:uid="{F0AA3238-AE28-4BD7-9F03-9F99C2C24019}"/>
+    <hyperlink ref="J822" r:id="rId501" xr:uid="{B9736A8E-E513-4525-AD8B-2E48B025CD6A}"/>
+    <hyperlink ref="J825" r:id="rId502" xr:uid="{494E2C1D-F826-4CD4-8C33-87B449DB7862}"/>
+    <hyperlink ref="J826" r:id="rId503" xr:uid="{DB67B4AD-CB08-45F9-A971-FA68DFB6957E}"/>
+    <hyperlink ref="J827" r:id="rId504" xr:uid="{14335869-3568-4B9F-8172-4505B667FA92}"/>
+    <hyperlink ref="J828" r:id="rId505" xr:uid="{2A058F70-807C-4335-8B0E-B5328D80928D}"/>
+    <hyperlink ref="J831" r:id="rId506" xr:uid="{DDF3394F-1E45-4E5B-9E65-8E57264F46C6}"/>
+    <hyperlink ref="J832" r:id="rId507" xr:uid="{47AB11A1-0003-4560-9692-446D90A76CF8}"/>
+    <hyperlink ref="J833" r:id="rId508" xr:uid="{906B1208-BF0B-4B05-9084-C1CB4DD0E4CB}"/>
+    <hyperlink ref="J836" r:id="rId509" xr:uid="{F10386EA-9C83-42A9-AAD1-7EE1C01331B0}"/>
+    <hyperlink ref="J837" r:id="rId510" xr:uid="{4A9811E0-1051-40A6-9E1A-55F7C7ABEC84}"/>
+    <hyperlink ref="J838" r:id="rId511" xr:uid="{21BC5C4E-AE5D-4AA9-9DD5-6247C7497ECD}"/>
+    <hyperlink ref="J839" r:id="rId512" xr:uid="{70D58A9C-003A-4F3B-AD3D-FC696ED40D06}"/>
+    <hyperlink ref="J840" r:id="rId513" xr:uid="{A0DEA31B-4E44-4D32-8ECB-7D824E7C1F53}"/>
+    <hyperlink ref="J841" r:id="rId514" xr:uid="{A8C2E313-0C40-4AD4-BC39-E82066726ABC}"/>
+    <hyperlink ref="J842" r:id="rId515" xr:uid="{EB111470-B185-4BE8-A38C-033736E4164A}"/>
+    <hyperlink ref="J843" r:id="rId516" xr:uid="{830CAD64-6B37-4C80-BF02-C194A69136B6}"/>
+    <hyperlink ref="J844" r:id="rId517" xr:uid="{329D96B3-7FBA-4615-B395-3FEF0D4AB901}"/>
+    <hyperlink ref="J847" r:id="rId518" xr:uid="{CABD8417-BCBF-48FE-8093-ABDB3CA0564D}"/>
+    <hyperlink ref="J848" r:id="rId519" xr:uid="{5373766C-43AE-436F-8B95-072124791BD9}"/>
+    <hyperlink ref="J850" r:id="rId520" xr:uid="{0290B0C5-690B-4A67-BEA1-AF8F1783E5C2}"/>
+    <hyperlink ref="J852" r:id="rId521" xr:uid="{C3A5BF64-78E5-4763-9F44-08E30F67797E}"/>
+    <hyperlink ref="J853" r:id="rId522" xr:uid="{E3D89422-1F34-44BB-8241-71C7A649B4FE}"/>
+    <hyperlink ref="J856" r:id="rId523" xr:uid="{EBE1B290-E7B7-4487-8DFA-1E7D32B8614C}"/>
+    <hyperlink ref="J858" r:id="rId524" xr:uid="{B813935F-F9E0-4E23-B6F7-FBEC938E371D}"/>
+    <hyperlink ref="J861" r:id="rId525" xr:uid="{6D4116CF-7614-4AAB-8B3C-A4CE373DB76B}"/>
+    <hyperlink ref="J862" r:id="rId526" xr:uid="{2EF2C61E-A6AC-410F-BF11-C0F725740FB5}"/>
+    <hyperlink ref="J863" r:id="rId527" xr:uid="{CA0697BF-460F-4C94-9D37-5224B31E64F1}"/>
+    <hyperlink ref="J865" r:id="rId528" xr:uid="{9CC9F98D-AE31-4777-9625-26518D3BBC95}"/>
+    <hyperlink ref="J866" r:id="rId529" xr:uid="{BF011600-3879-4BB2-A866-3FDA3061492C}"/>
+    <hyperlink ref="J867" r:id="rId530" xr:uid="{398140AA-5AA9-4AAF-B9DD-3D902EAC7980}"/>
+    <hyperlink ref="J868" r:id="rId531" xr:uid="{A0472597-0114-42E6-BBAC-35F4AD37BFF3}"/>
+    <hyperlink ref="J870" r:id="rId532" xr:uid="{81CBC4AA-831C-4E38-A833-F58006FB646A}"/>
+    <hyperlink ref="J871" r:id="rId533" xr:uid="{E5A2317E-B8DF-4E2C-99D5-B3BF7206A650}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId512"/>
+  <pageSetup orientation="portrait" r:id="rId534"/>
   <tableParts count="1">
-    <tablePart r:id="rId513"/>
+    <tablePart r:id="rId535"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos junio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0D33F8-B649-4DCE-9AD2-7889BF6CD889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4407DC92-F329-47AC-B5C5-154283D2CFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Rechazos Calle" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$1080</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$1136</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9385" uniqueCount="2887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9863" uniqueCount="3029">
   <si>
     <t>Fecha</t>
   </si>
@@ -8726,6 +8726,433 @@
   <si>
     <t>El cliente va a recibir — seguí viaje — Es un cambio de dirección que fue informado.
 La dirección correcta es Esperanto 612</t>
+  </si>
+  <si>
+    <t>MQUXMF7NLAJA</t>
+  </si>
+  <si>
+    <t>MQUY1E0HXRXW</t>
+  </si>
+  <si>
+    <t>Faltó 6 Tostitos 10gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782479134/chbhud4o34hgkkfjj9nk.jpg</t>
+  </si>
+  <si>
+    <t>MQUYE39WLEQY</t>
+  </si>
+  <si>
+    <t>10:15 a. m.</t>
+  </si>
+  <si>
+    <t>Pepa comun</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Sin stock se descuenta la mercadería.</t>
+  </si>
+  <si>
+    <t>MQUYRDYMWWAS</t>
+  </si>
+  <si>
+    <t>Speedd</t>
+  </si>
+  <si>
+    <t>MQUYRXVCNBAZ</t>
+  </si>
+  <si>
+    <t>3 asado 77 des no pidio</t>
+  </si>
+  <si>
+    <t>MQUZ9G0F07Q0</t>
+  </si>
+  <si>
+    <t>Lays onda</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782481181/rw1sfinztqpzcgdaghnc.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Se descontó la mercadería. Mal armado</t>
+  </si>
+  <si>
+    <t>MQUZLD28DPNK</t>
+  </si>
+  <si>
+    <t>2 maniax jamon</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782481742/qpjvzb2pzx5rsf0kzmnq.jpg</t>
+  </si>
+  <si>
+    <t>MQUZQ0IQE4MW</t>
+  </si>
+  <si>
+    <t>10:53 a. m.</t>
+  </si>
+  <si>
+    <t>Roto spaghetti favorita</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782481966/uqcqlodxharaj1stikh8.jpg</t>
+  </si>
+  <si>
+    <t>MQV0DPXSR9VG</t>
+  </si>
+  <si>
+    <t>Falto un mani sal pelado 75 g</t>
+  </si>
+  <si>
+    <t>MQV0NE8EVXDN</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782483509/h2dewglu41rgwfkndg01.jpg</t>
+  </si>
+  <si>
+    <t>MQV0W1UGHFGK</t>
+  </si>
+  <si>
+    <t>5 maniax jamon</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782483912/p2xq1nqwioas5uis72wi.jpg</t>
+  </si>
+  <si>
+    <t>MQV19ZMHYIB9</t>
+  </si>
+  <si>
+    <t>MQV1LGBSLDWJ</t>
+  </si>
+  <si>
+    <t>MQV1LK83LB6B</t>
+  </si>
+  <si>
+    <t>Se descuenta pehuamar acanalada x 90 grs faltó</t>
+  </si>
+  <si>
+    <t>MQV2CMJ4F15N</t>
+  </si>
+  <si>
+    <t>MQV2FYQITIZQ</t>
+  </si>
+  <si>
+    <t>Alfajor mantecol</t>
+  </si>
+  <si>
+    <t>MQV2H8U4IMYY</t>
+  </si>
+  <si>
+    <t>MQV2LCSGWAGA</t>
+  </si>
+  <si>
+    <t>12:13 p. m.</t>
+  </si>
+  <si>
+    <t>No pidió galletas toddy</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782486776/nb2hks9ccvbatioqyerx.jpg</t>
+  </si>
+  <si>
+    <t>MQV2RS3N8L8E</t>
+  </si>
+  <si>
+    <t>Falta lays 85</t>
+  </si>
+  <si>
+    <t>MQV47SXVNLKA</t>
+  </si>
+  <si>
+    <t>Codito</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782489500/pl4s4vgxdojiprkmlbcc.jpg</t>
+  </si>
+  <si>
+    <t>MQV488OSN41P</t>
+  </si>
+  <si>
+    <t>MQV4NZB95X2P</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782490264/lm5kiyl84ovqplf9jiho.jpg</t>
+  </si>
+  <si>
+    <t>MQV50MNW93Q5</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782490855/gcjva9vjmwgpikffdwuj.jpg</t>
+  </si>
+  <si>
+    <t>MQV5JGZZMU7Z</t>
+  </si>
+  <si>
+    <t>Cargaron sal gruesa en vez de entrefina</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782491765/ohrexin4vjc7wrkn4lsb.jpg</t>
+  </si>
+  <si>
+    <t>MQV5LFCLK580</t>
+  </si>
+  <si>
+    <t>MQV5LLMPK2TG</t>
+  </si>
+  <si>
+    <t>01:37 p. m.</t>
+  </si>
+  <si>
+    <t>Rechaza esta boleta por falta de dinero</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782491826/fubpi3wma81edzbyqiih.jpg</t>
+  </si>
+  <si>
+    <t>MQV65PGT7VMC</t>
+  </si>
+  <si>
+    <t>01:52 p. m.</t>
+  </si>
+  <si>
+    <t>Mani con piel sin stock</t>
+  </si>
+  <si>
+    <t>MQV6QV6OW50F</t>
+  </si>
+  <si>
+    <t>MQV7HWPT1X34</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782495024/ldafzpylwhmwxz5r2aia.jpg</t>
+  </si>
+  <si>
+    <t>MQV7NVTYEPXF</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782495291/gftlitbeqfloulgrboco.jpg</t>
+  </si>
+  <si>
+    <t>MQV81SA4WDF1</t>
+  </si>
+  <si>
+    <t>Pidtacho</t>
+  </si>
+  <si>
+    <t>Dejá el pedido, lo resuelvo después — Hay 978 unidades en sistema</t>
+  </si>
+  <si>
+    <t>MQV87RPWO0IL</t>
+  </si>
+  <si>
+    <t>02:50 p. m.</t>
+  </si>
+  <si>
+    <t>Pepa ruedita rota 74</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Pep ruedita 74gr rota, se descuenta de la boleta.</t>
+  </si>
+  <si>
+    <t>MQV8CEQ822H3</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782496433/eo295lyv0xd2it5xjsxz.jpg</t>
+  </si>
+  <si>
+    <t>MQV8GF8TAXLL</t>
+  </si>
+  <si>
+    <t>Lo entregué ayer</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782496635/cw65st46lacvdxxux29z.jpg</t>
+  </si>
+  <si>
+    <t>MQV8S2ZW4LG2</t>
+  </si>
+  <si>
+    <t>Lo esperaban el martes</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782497178/ixrvkfunwiyas47nbiws.jpg</t>
+  </si>
+  <si>
+    <t>MQV8UL20Z905</t>
+  </si>
+  <si>
+    <t>Pescado raul</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782497285/csdzqnoi821dk4xlwbgu.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Se descuenta pescado Raúl sin stock</t>
+  </si>
+  <si>
+    <t>MQV91EMO8IJZ</t>
+  </si>
+  <si>
+    <t>ROMANO MARTIN</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782497599/f2vttvfw8oxjf5iahtya.jpg</t>
+  </si>
+  <si>
+    <t>MQV914PLQZW5</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782497595/l3543dvykgjvoyyj3v12.jpg</t>
+  </si>
+  <si>
+    <t>MQV9358AZND3</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782497685/aebep3u9o7vwpju2womi.jpg</t>
+  </si>
+  <si>
+    <t>MQV94J07JS1C</t>
+  </si>
+  <si>
+    <t>MQV9XSSR5Z0M</t>
+  </si>
+  <si>
+    <t>03:38 p. m.</t>
+  </si>
+  <si>
+    <t>Panceta</t>
+  </si>
+  <si>
+    <t>MQVA5KFFINFT</t>
+  </si>
+  <si>
+    <t>MQVAL0PQLNNX</t>
+  </si>
+  <si>
+    <t>03:56 p. m.</t>
+  </si>
+  <si>
+    <t>Falto un fantoche blanco</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Mercadería sin stock</t>
+  </si>
+  <si>
+    <t>MQVAQAIM0AUI</t>
+  </si>
+  <si>
+    <t>No quiso los biscochos</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782500441/xuy4eevdag38sy7tgwax.jpg</t>
+  </si>
+  <si>
+    <t>MQVAZMO9VCVP</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782500881/f5de4cbkrxgzm4vdrfbe.jpg</t>
+  </si>
+  <si>
+    <t>MQVB1ZK91BL0</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782501000/jnethkkh6hoqh6qszvmi.jpg</t>
+  </si>
+  <si>
+    <t>MQVD3A2NPVEE</t>
+  </si>
+  <si>
+    <t>05:07 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782504443/dbvsg7ekdcafaydugmkr.jpg</t>
+  </si>
+  <si>
+    <t>MQVD795GS6WI</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782504595/xomqurv3fuxmkqfclclb.jpg</t>
+  </si>
+  <si>
+    <t>MQVD8KD1TQMN</t>
+  </si>
+  <si>
+    <t>1 arroz gallo roto</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782504666/yke8banzd3jha5miyvjx.jpg</t>
+  </si>
+  <si>
+    <t>MQVD9WKYRL98</t>
+  </si>
+  <si>
+    <t>6 alf s stock</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782504748/j4lvmzte1khsd1kbiyel.jpg</t>
+  </si>
+  <si>
+    <t>MQVFKI7EET9V</t>
+  </si>
+  <si>
+    <t>06:16 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782508581/kb5miwfnnl0g2y2ymqmf.jpg</t>
+  </si>
+  <si>
+    <t>MQVFLE5C5LIQ</t>
+  </si>
+  <si>
+    <t>06:18 p. m.</t>
+  </si>
+  <si>
+    <t>3doritos de77 2 3d de 85 3 doritos 129 3 lays 1134</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782508615/kvaweern74z8bnn7y2vh.jpg</t>
+  </si>
+  <si>
+    <t>MQVFNUTSJDDL</t>
+  </si>
+  <si>
+    <t>Lo anterior q se envio esde la boleta 1206</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782508761/q7ra8xs4vrlpbspujtmz.jpg</t>
+  </si>
+  <si>
+    <t>MQVFR8F16Q3E</t>
+  </si>
+  <si>
+    <t>06:22 p. m.</t>
+  </si>
+  <si>
+    <t>3 doritos 129 
+3lays de 134</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782508887/bbfaltxrlh1tshzvjldc.jpg</t>
+  </si>
+  <si>
+    <t>MQVFTK5HIF80</t>
+  </si>
+  <si>
+    <t>06:23 p. m.</t>
+  </si>
+  <si>
+    <t>Menos 10 yerba playadito de 500g</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782508997/wbtabokwdmbp2c4ovmnz.jpg</t>
+  </si>
+  <si>
+    <t>MQVFV5LWFVA8</t>
+  </si>
+  <si>
+    <t>06:24 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782509074/smcwehd7fzmw3ouci2zb.jpg</t>
   </si>
 </sst>
 </file>
@@ -9116,8 +9543,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N1080">
-  <autoFilter ref="A1:N1080" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N1136">
+  <autoFilter ref="A1:N1136" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fecha"/>
@@ -9339,7 +9766,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N1080"/>
+  <dimension ref="A1:N1136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -53740,674 +54167,2992 @@
         <v>6</v>
       </c>
     </row>
+    <row r="1081" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1081" s="3" t="s">
+        <v>2887</v>
+      </c>
+      <c r="B1081" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1081" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1081" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1081" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1081" s="6">
+        <v>3203</v>
+      </c>
+      <c r="G1081" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1081" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1081" s="8"/>
+      <c r="J1081" s="8"/>
+      <c r="K1081" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1081" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1081" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1081" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1082" s="3" t="s">
+        <v>2888</v>
+      </c>
+      <c r="B1082" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1082" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1082" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1082" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1082" s="6">
+        <v>1838</v>
+      </c>
+      <c r="G1082" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1082" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1082" s="5" t="s">
+        <v>2889</v>
+      </c>
+      <c r="J1082" s="11" t="s">
+        <v>2890</v>
+      </c>
+      <c r="K1082" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1082" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1082" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1082" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1083" s="3" t="s">
+        <v>2891</v>
+      </c>
+      <c r="B1083" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1083" s="5" t="s">
+        <v>2892</v>
+      </c>
+      <c r="D1083" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1083" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1083" s="6">
+        <v>6105</v>
+      </c>
+      <c r="G1083" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1083" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1083" s="5" t="s">
+        <v>2893</v>
+      </c>
+      <c r="J1083" s="8"/>
+      <c r="K1083" s="5" t="s">
+        <v>2894</v>
+      </c>
+      <c r="L1083" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1083" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1083" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1084" s="3" t="s">
+        <v>2895</v>
+      </c>
+      <c r="B1084" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1084" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1084" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1084" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1084" s="6">
+        <v>4015</v>
+      </c>
+      <c r="G1084" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1084" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1084" s="5" t="s">
+        <v>2896</v>
+      </c>
+      <c r="J1084" s="8"/>
+      <c r="K1084" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1084" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1084" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1084" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1085" s="3" t="s">
+        <v>2897</v>
+      </c>
+      <c r="B1085" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1085" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="D1085" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1085" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1085" s="6">
+        <v>1404</v>
+      </c>
+      <c r="G1085" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1085" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1085" s="5" t="s">
+        <v>2898</v>
+      </c>
+      <c r="J1085" s="8"/>
+      <c r="K1085" s="8"/>
+      <c r="L1085" s="8"/>
+      <c r="M1085" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1085" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1086" s="3" t="s">
+        <v>2899</v>
+      </c>
+      <c r="B1086" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1086" s="5" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D1086" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1086" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1086" s="6">
+        <v>6403</v>
+      </c>
+      <c r="G1086" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1086" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1086" s="5" t="s">
+        <v>2900</v>
+      </c>
+      <c r="J1086" s="11" t="s">
+        <v>2901</v>
+      </c>
+      <c r="K1086" s="5" t="s">
+        <v>2902</v>
+      </c>
+      <c r="L1086" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1086" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1086" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1087" s="3" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B1087" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1087" s="5" t="s">
+        <v>2352</v>
+      </c>
+      <c r="D1087" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1087" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1087" s="6">
+        <v>2773</v>
+      </c>
+      <c r="G1087" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1087" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1087" s="5" t="s">
+        <v>2904</v>
+      </c>
+      <c r="J1087" s="11" t="s">
+        <v>2905</v>
+      </c>
+      <c r="K1087" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1087" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1087" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1087" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1088" s="3" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B1088" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1088" s="5" t="s">
+        <v>2907</v>
+      </c>
+      <c r="D1088" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1088" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1088" s="6">
+        <v>3121</v>
+      </c>
+      <c r="G1088" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1088" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1088" s="5" t="s">
+        <v>2908</v>
+      </c>
+      <c r="J1088" s="11" t="s">
+        <v>2909</v>
+      </c>
+      <c r="K1088" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1088" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1088" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1088" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1089" s="3" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B1089" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1089" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1089" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1089" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1089" s="6">
+        <v>3996</v>
+      </c>
+      <c r="G1089" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1089" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1089" s="5" t="s">
+        <v>2911</v>
+      </c>
+      <c r="J1089" s="8"/>
+      <c r="K1089" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1089" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1089" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1089" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1090" s="3" t="s">
+        <v>2912</v>
+      </c>
+      <c r="B1090" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1090" s="13">
+        <v>0.47083333333333333</v>
+      </c>
+      <c r="D1090" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1090" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1090" s="6">
+        <v>3723</v>
+      </c>
+      <c r="G1090" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1090" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1090" s="8"/>
+      <c r="J1090" s="11" t="s">
+        <v>2913</v>
+      </c>
+      <c r="K1090" s="8"/>
+      <c r="L1090" s="8"/>
+      <c r="M1090" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1090" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1091" s="3" t="s">
+        <v>2914</v>
+      </c>
+      <c r="B1091" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1091" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="D1091" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1091" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1091" s="6">
+        <v>1564</v>
+      </c>
+      <c r="G1091" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1091" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1091" s="5" t="s">
+        <v>2915</v>
+      </c>
+      <c r="J1091" s="11" t="s">
+        <v>2916</v>
+      </c>
+      <c r="K1091" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1091" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1091" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1091" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1092" s="3" t="s">
+        <v>2917</v>
+      </c>
+      <c r="B1092" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1092" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1092" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1092" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1092" s="6">
+        <v>11067</v>
+      </c>
+      <c r="G1092" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1092" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1092" s="8"/>
+      <c r="J1092" s="8"/>
+      <c r="K1092" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1092" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1092" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1092" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1093" s="3" t="s">
+        <v>2918</v>
+      </c>
+      <c r="B1093" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1093" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="D1093" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1093" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1093" s="6">
+        <v>11067</v>
+      </c>
+      <c r="G1093" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1093" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1093" s="8"/>
+      <c r="J1093" s="8"/>
+      <c r="K1093" s="8"/>
+      <c r="L1093" s="8"/>
+      <c r="M1093" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1093" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1094" s="3" t="s">
+        <v>2919</v>
+      </c>
+      <c r="B1094" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1094" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="D1094" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1094" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1094" s="6">
+        <v>5830</v>
+      </c>
+      <c r="G1094" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1094" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1094" s="5" t="s">
+        <v>2920</v>
+      </c>
+      <c r="J1094" s="8"/>
+      <c r="K1094" s="8"/>
+      <c r="L1094" s="8"/>
+      <c r="M1094" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1094" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1095" s="3" t="s">
+        <v>2921</v>
+      </c>
+      <c r="B1095" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1095" s="13">
+        <v>0.50416666666666665</v>
+      </c>
+      <c r="D1095" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1095" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1095" s="6">
+        <v>6207</v>
+      </c>
+      <c r="G1095" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1095" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1095" s="8"/>
+      <c r="J1095" s="8"/>
+      <c r="K1095" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1095" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1095" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1095" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1096" s="3" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B1096" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1096" s="13">
+        <v>0.50624999999999998</v>
+      </c>
+      <c r="D1096" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1096" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1096" s="6">
+        <v>4798</v>
+      </c>
+      <c r="G1096" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1096" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1096" s="5" t="s">
+        <v>2923</v>
+      </c>
+      <c r="J1096" s="8"/>
+      <c r="K1096" s="8"/>
+      <c r="L1096" s="8"/>
+      <c r="M1096" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1096" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1097" s="3" t="s">
+        <v>2924</v>
+      </c>
+      <c r="B1097" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1097" s="5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D1097" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1097" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1097" s="6">
+        <v>2856</v>
+      </c>
+      <c r="G1097" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1097" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1097" s="8"/>
+      <c r="J1097" s="8"/>
+      <c r="K1097" s="8"/>
+      <c r="L1097" s="8"/>
+      <c r="M1097" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1097" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1098" s="3" t="s">
+        <v>2925</v>
+      </c>
+      <c r="B1098" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1098" s="5" t="s">
+        <v>2926</v>
+      </c>
+      <c r="D1098" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1098" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1098" s="6">
+        <v>4902</v>
+      </c>
+      <c r="G1098" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1098" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1098" s="5" t="s">
+        <v>2927</v>
+      </c>
+      <c r="J1098" s="11" t="s">
+        <v>2928</v>
+      </c>
+      <c r="K1098" s="8"/>
+      <c r="L1098" s="8"/>
+      <c r="M1098" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1098" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1099" s="3" t="s">
+        <v>2929</v>
+      </c>
+      <c r="B1099" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1099" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D1099" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1099" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1099" s="6">
+        <v>7512</v>
+      </c>
+      <c r="G1099" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1099" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1099" s="5" t="s">
+        <v>2930</v>
+      </c>
+      <c r="J1099" s="8"/>
+      <c r="K1099" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1099" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1099" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1099" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1100" s="3" t="s">
+        <v>2931</v>
+      </c>
+      <c r="B1100" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1100" s="13">
+        <v>0.54027777777777775</v>
+      </c>
+      <c r="D1100" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1100" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1100" s="6">
+        <v>3179</v>
+      </c>
+      <c r="G1100" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1100" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1100" s="5" t="s">
+        <v>2932</v>
+      </c>
+      <c r="J1100" s="11" t="s">
+        <v>2933</v>
+      </c>
+      <c r="K1100" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1100" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1100" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1100" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1101" s="3" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B1101" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1101" s="13">
+        <v>0.54027777777777775</v>
+      </c>
+      <c r="D1101" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1101" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1101" s="6">
+        <v>3435</v>
+      </c>
+      <c r="G1101" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1101" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1101" s="8"/>
+      <c r="J1101" s="8"/>
+      <c r="K1101" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1101" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1101" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1101" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1102" s="3" t="s">
+        <v>2935</v>
+      </c>
+      <c r="B1102" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1102" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="D1102" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1102" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1102" s="6">
+        <v>4307</v>
+      </c>
+      <c r="G1102" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1102" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1102" s="8"/>
+      <c r="J1102" s="11" t="s">
+        <v>2936</v>
+      </c>
+      <c r="K1102" s="8"/>
+      <c r="L1102" s="8"/>
+      <c r="M1102" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1102" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1103" s="3" t="s">
+        <v>2937</v>
+      </c>
+      <c r="B1103" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1103" s="13">
+        <v>0.55625000000000002</v>
+      </c>
+      <c r="D1103" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1103" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1103" s="6">
+        <v>3179</v>
+      </c>
+      <c r="G1103" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1103" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1103" s="5" t="s">
+        <v>2092</v>
+      </c>
+      <c r="J1103" s="11" t="s">
+        <v>2938</v>
+      </c>
+      <c r="K1103" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1103" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1103" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1103" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1104" s="3" t="s">
+        <v>2939</v>
+      </c>
+      <c r="B1104" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1104" s="13">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="D1104" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1104" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1104" s="6">
+        <v>3705</v>
+      </c>
+      <c r="G1104" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1104" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1104" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="J1104" s="11" t="s">
+        <v>2941</v>
+      </c>
+      <c r="K1104" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1104" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1104" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1104" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1105" s="3" t="s">
+        <v>2942</v>
+      </c>
+      <c r="B1105" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1105" s="13">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="D1105" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1105" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1105" s="6">
+        <v>5517</v>
+      </c>
+      <c r="G1105" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1105" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1105" s="8"/>
+      <c r="J1105" s="8"/>
+      <c r="K1105" s="8"/>
+      <c r="L1105" s="8"/>
+      <c r="M1105" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1105" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1106" s="3" t="s">
+        <v>2943</v>
+      </c>
+      <c r="B1106" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1106" s="5" t="s">
+        <v>2944</v>
+      </c>
+      <c r="D1106" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1106" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1106" s="6">
+        <v>4900</v>
+      </c>
+      <c r="G1106" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1106" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1106" s="5" t="s">
+        <v>2945</v>
+      </c>
+      <c r="J1106" s="11" t="s">
+        <v>2946</v>
+      </c>
+      <c r="K1106" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1106" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1106" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1106" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1107" s="3" t="s">
+        <v>2947</v>
+      </c>
+      <c r="B1107" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1107" s="5" t="s">
+        <v>2948</v>
+      </c>
+      <c r="D1107" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1107" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1107" s="6">
+        <v>11000</v>
+      </c>
+      <c r="G1107" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1107" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1107" s="5" t="s">
+        <v>2949</v>
+      </c>
+      <c r="J1107" s="8"/>
+      <c r="K1107" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1107" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1107" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1107" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1108" s="3" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B1108" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1108" s="13">
+        <v>0.58958333333333335</v>
+      </c>
+      <c r="D1108" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1108" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1108" s="6">
+        <v>5189</v>
+      </c>
+      <c r="G1108" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1108" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1108" s="8"/>
+      <c r="J1108" s="8"/>
+      <c r="K1108" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1108" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1108" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1108" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1109" s="3" t="s">
+        <v>2951</v>
+      </c>
+      <c r="B1109" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1109" s="13">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="D1109" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1109" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1109" s="6">
+        <v>3117</v>
+      </c>
+      <c r="G1109" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1109" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1109" s="8"/>
+      <c r="J1109" s="11" t="s">
+        <v>2952</v>
+      </c>
+      <c r="K1109" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1109" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1109" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1109" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1110" s="3" t="s">
+        <v>2953</v>
+      </c>
+      <c r="B1110" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1110" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1110" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1110" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1110" s="6">
+        <v>4582</v>
+      </c>
+      <c r="G1110" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="H1110" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1110" s="8"/>
+      <c r="J1110" s="11" t="s">
+        <v>2954</v>
+      </c>
+      <c r="K1110" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1110" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1110" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1110" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1111" s="3" t="s">
+        <v>2955</v>
+      </c>
+      <c r="B1111" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1111" s="5" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D1111" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1111" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1111" s="6">
+        <v>6104</v>
+      </c>
+      <c r="G1111" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1111" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1111" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="J1111" s="8"/>
+      <c r="K1111" s="5" t="s">
+        <v>2957</v>
+      </c>
+      <c r="L1111" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1111" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1111" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1112" s="3" t="s">
+        <v>2958</v>
+      </c>
+      <c r="B1112" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1112" s="5" t="s">
+        <v>2959</v>
+      </c>
+      <c r="D1112" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1112" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1112" s="6">
+        <v>6104</v>
+      </c>
+      <c r="G1112" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1112" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1112" s="5" t="s">
+        <v>2960</v>
+      </c>
+      <c r="J1112" s="8"/>
+      <c r="K1112" s="5" t="s">
+        <v>2961</v>
+      </c>
+      <c r="L1112" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1112" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1112" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1113" s="3" t="s">
+        <v>2962</v>
+      </c>
+      <c r="B1113" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1113" s="5" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D1113" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1113" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1113" s="6">
+        <v>1569</v>
+      </c>
+      <c r="G1113" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1113" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1113" s="8"/>
+      <c r="J1113" s="11" t="s">
+        <v>2963</v>
+      </c>
+      <c r="K1113" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1113" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1113" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1113" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1114" s="3" t="s">
+        <v>2964</v>
+      </c>
+      <c r="B1114" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1114" s="13">
+        <v>0.62291666666666667</v>
+      </c>
+      <c r="D1114" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1114" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1114" s="6">
+        <v>4894</v>
+      </c>
+      <c r="G1114" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1114" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1114" s="5" t="s">
+        <v>2965</v>
+      </c>
+      <c r="J1114" s="11" t="s">
+        <v>2966</v>
+      </c>
+      <c r="K1114" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1114" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1114" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1114" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1115" s="3" t="s">
+        <v>2967</v>
+      </c>
+      <c r="B1115" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1115" s="5" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D1115" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1115" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1115" s="6">
+        <v>10941</v>
+      </c>
+      <c r="G1115" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1115" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1115" s="5" t="s">
+        <v>2968</v>
+      </c>
+      <c r="J1115" s="11" t="s">
+        <v>2969</v>
+      </c>
+      <c r="K1115" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1115" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1115" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1115" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1116" s="3" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1116" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1116" s="5" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D1116" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1116" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1116" s="6">
+        <v>5825</v>
+      </c>
+      <c r="G1116" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1116" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1116" s="5" t="s">
+        <v>2971</v>
+      </c>
+      <c r="J1116" s="11" t="s">
+        <v>2972</v>
+      </c>
+      <c r="K1116" s="5" t="s">
+        <v>2973</v>
+      </c>
+      <c r="L1116" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1116" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1116" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1117" s="3" t="s">
+        <v>2974</v>
+      </c>
+      <c r="B1117" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1117" s="13">
+        <v>0.63402777777777775</v>
+      </c>
+      <c r="D1117" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1117" s="5" t="s">
+        <v>2975</v>
+      </c>
+      <c r="F1117" s="6">
+        <v>67</v>
+      </c>
+      <c r="G1117" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1117" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1117" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J1117" s="11" t="s">
+        <v>2976</v>
+      </c>
+      <c r="K1117" s="8"/>
+      <c r="L1117" s="8"/>
+      <c r="M1117" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1117" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1118" s="3" t="s">
+        <v>2977</v>
+      </c>
+      <c r="B1118" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1118" s="5" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D1118" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1118" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1118" s="6">
+        <v>1575</v>
+      </c>
+      <c r="G1118" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1118" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1118" s="8"/>
+      <c r="J1118" s="11" t="s">
+        <v>2978</v>
+      </c>
+      <c r="K1118" s="8"/>
+      <c r="L1118" s="8"/>
+      <c r="M1118" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1118" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1119" s="3" t="s">
+        <v>2979</v>
+      </c>
+      <c r="B1119" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1119" s="5" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D1119" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1119" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1119" s="6">
+        <v>3351</v>
+      </c>
+      <c r="G1119" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1119" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1119" s="8"/>
+      <c r="J1119" s="11" t="s">
+        <v>2980</v>
+      </c>
+      <c r="K1119" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1119" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1119" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1119" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1120" s="3" t="s">
+        <v>2981</v>
+      </c>
+      <c r="B1120" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1120" s="5" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D1120" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1120" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1120" s="6">
+        <v>6962</v>
+      </c>
+      <c r="G1120" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1120" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="I1120" s="8"/>
+      <c r="J1120" s="8"/>
+      <c r="K1120" s="8"/>
+      <c r="L1120" s="8"/>
+      <c r="M1120" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1120" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1121" s="3" t="s">
+        <v>2982</v>
+      </c>
+      <c r="B1121" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1121" s="5" t="s">
+        <v>2983</v>
+      </c>
+      <c r="D1121" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1121" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1121" s="6">
+        <v>5802</v>
+      </c>
+      <c r="G1121" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1121" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1121" s="5" t="s">
+        <v>2984</v>
+      </c>
+      <c r="J1121" s="8"/>
+      <c r="K1121" s="8"/>
+      <c r="L1121" s="8"/>
+      <c r="M1121" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1121" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1122" s="3" t="s">
+        <v>2985</v>
+      </c>
+      <c r="B1122" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1122" s="13">
+        <v>0.65555555555555556</v>
+      </c>
+      <c r="D1122" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1122" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1122" s="6">
+        <v>5519</v>
+      </c>
+      <c r="G1122" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1122" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1122" s="8"/>
+      <c r="J1122" s="8"/>
+      <c r="K1122" s="8"/>
+      <c r="L1122" s="8"/>
+      <c r="M1122" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1122" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1123" s="3" t="s">
+        <v>2986</v>
+      </c>
+      <c r="B1123" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1123" s="5" t="s">
+        <v>2987</v>
+      </c>
+      <c r="D1123" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1123" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1123" s="6">
+        <v>5818</v>
+      </c>
+      <c r="G1123" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1123" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1123" s="5" t="s">
+        <v>2988</v>
+      </c>
+      <c r="J1123" s="8"/>
+      <c r="K1123" s="5" t="s">
+        <v>2989</v>
+      </c>
+      <c r="L1123" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1123" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1123" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1124" s="3" t="s">
+        <v>2990</v>
+      </c>
+      <c r="B1124" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1124" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="D1124" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1124" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1124" s="6">
+        <v>4902</v>
+      </c>
+      <c r="G1124" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1124" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1124" s="5" t="s">
+        <v>2991</v>
+      </c>
+      <c r="J1124" s="11" t="s">
+        <v>2992</v>
+      </c>
+      <c r="K1124" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1124" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1124" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1124" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1125" s="3" t="s">
+        <v>2993</v>
+      </c>
+      <c r="B1125" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1125" s="13">
+        <v>0.67222222222222228</v>
+      </c>
+      <c r="D1125" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1125" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1125" s="6">
+        <v>4774</v>
+      </c>
+      <c r="G1125" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1125" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1125" s="8"/>
+      <c r="J1125" s="11" t="s">
+        <v>2994</v>
+      </c>
+      <c r="K1125" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1125" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1125" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1125" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1126" s="3" t="s">
+        <v>2995</v>
+      </c>
+      <c r="B1126" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1126" s="13">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="D1126" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1126" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1126" s="6">
+        <v>5203</v>
+      </c>
+      <c r="G1126" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1126" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1126" s="8"/>
+      <c r="J1126" s="11" t="s">
+        <v>2996</v>
+      </c>
+      <c r="K1126" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1126" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1126" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1126" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1127" s="3" t="s">
+        <v>2997</v>
+      </c>
+      <c r="B1127" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1127" s="5" t="s">
+        <v>2998</v>
+      </c>
+      <c r="D1127" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1127" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1127" s="6">
+        <v>7234</v>
+      </c>
+      <c r="G1127" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1127" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1127" s="8"/>
+      <c r="J1127" s="11" t="s">
+        <v>2999</v>
+      </c>
+      <c r="K1127" s="8"/>
+      <c r="L1127" s="8"/>
+      <c r="M1127" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1127" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1128" s="3" t="s">
+        <v>3000</v>
+      </c>
+      <c r="B1128" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1128" s="5" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D1128" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1128" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1128" s="6">
+        <v>7234</v>
+      </c>
+      <c r="G1128" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1128" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1128" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1128" s="11" t="s">
+        <v>3001</v>
+      </c>
+      <c r="K1128" s="8"/>
+      <c r="L1128" s="8"/>
+      <c r="M1128" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1128" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1129" s="3" t="s">
+        <v>3002</v>
+      </c>
+      <c r="B1129" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1129" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D1129" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1129" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1129" s="6">
+        <v>7248</v>
+      </c>
+      <c r="G1129" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1129" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1129" s="5" t="s">
+        <v>3003</v>
+      </c>
+      <c r="J1129" s="11" t="s">
+        <v>3004</v>
+      </c>
+      <c r="K1129" s="8"/>
+      <c r="L1129" s="8"/>
+      <c r="M1129" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1129" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1130" s="3" t="s">
+        <v>3005</v>
+      </c>
+      <c r="B1130" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1130" s="5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D1130" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1130" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1130" s="6">
+        <v>6929</v>
+      </c>
+      <c r="G1130" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1130" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1130" s="5" t="s">
+        <v>3006</v>
+      </c>
+      <c r="J1130" s="11" t="s">
+        <v>3007</v>
+      </c>
+      <c r="K1130" s="8"/>
+      <c r="L1130" s="8"/>
+      <c r="M1130" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1130" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1131" s="3" t="s">
+        <v>3008</v>
+      </c>
+      <c r="B1131" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1131" s="5" t="s">
+        <v>3009</v>
+      </c>
+      <c r="D1131" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1131" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1131" s="6">
+        <v>2839</v>
+      </c>
+      <c r="G1131" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1131" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1131" s="8"/>
+      <c r="J1131" s="11" t="s">
+        <v>3010</v>
+      </c>
+      <c r="K1131" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1131" s="4">
+        <v>46199</v>
+      </c>
+      <c r="M1131" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1131" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1132" s="3" t="s">
+        <v>3011</v>
+      </c>
+      <c r="B1132" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1132" s="5" t="s">
+        <v>3012</v>
+      </c>
+      <c r="D1132" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1132" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F1132" s="6">
+        <v>1114</v>
+      </c>
+      <c r="G1132" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H1132" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1132" s="5" t="s">
+        <v>3013</v>
+      </c>
+      <c r="J1132" s="11" t="s">
+        <v>3014</v>
+      </c>
+      <c r="K1132" s="8"/>
+      <c r="L1132" s="8"/>
+      <c r="M1132" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1132" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1133" s="3" t="s">
+        <v>3015</v>
+      </c>
+      <c r="B1133" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1133" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="D1133" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1133" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F1133" s="6">
+        <v>1206</v>
+      </c>
+      <c r="G1133" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H1133" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1133" s="5" t="s">
+        <v>3016</v>
+      </c>
+      <c r="J1133" s="11" t="s">
+        <v>3017</v>
+      </c>
+      <c r="K1133" s="8"/>
+      <c r="L1133" s="8"/>
+      <c r="M1133" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1133" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1134" s="3" t="s">
+        <v>3018</v>
+      </c>
+      <c r="B1134" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1134" s="5" t="s">
+        <v>3019</v>
+      </c>
+      <c r="D1134" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1134" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F1134" s="6">
+        <v>1114</v>
+      </c>
+      <c r="G1134" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H1134" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1134" s="5" t="s">
+        <v>3020</v>
+      </c>
+      <c r="J1134" s="11" t="s">
+        <v>3021</v>
+      </c>
+      <c r="K1134" s="8"/>
+      <c r="L1134" s="8"/>
+      <c r="M1134" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1134" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1135" s="3" t="s">
+        <v>3022</v>
+      </c>
+      <c r="B1135" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1135" s="5" t="s">
+        <v>3023</v>
+      </c>
+      <c r="D1135" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1135" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F1135" s="6">
+        <v>1395</v>
+      </c>
+      <c r="G1135" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H1135" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1135" s="5" t="s">
+        <v>3024</v>
+      </c>
+      <c r="J1135" s="11" t="s">
+        <v>3025</v>
+      </c>
+      <c r="K1135" s="8"/>
+      <c r="L1135" s="8"/>
+      <c r="M1135" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1135" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1136" s="3" t="s">
+        <v>3026</v>
+      </c>
+      <c r="B1136" s="4">
+        <v>46199</v>
+      </c>
+      <c r="C1136" s="5" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1136" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1136" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F1136" s="6">
+        <v>904</v>
+      </c>
+      <c r="G1136" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H1136" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1136" s="8"/>
+      <c r="J1136" s="11" t="s">
+        <v>3028</v>
+      </c>
+      <c r="K1136" s="8"/>
+      <c r="L1136" s="8"/>
+      <c r="M1136" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1136" s="23">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J5" r:id="rId1" xr:uid="{32A924E4-4E90-47AF-9776-2B8602EFD807}"/>
-    <hyperlink ref="J7" r:id="rId2" xr:uid="{995B65D7-1ECB-4ED3-B789-A2FEE28C1E88}"/>
-    <hyperlink ref="J8" r:id="rId3" xr:uid="{5C635D17-93CC-4964-B63A-A4259DA117CF}"/>
-    <hyperlink ref="J10" r:id="rId4" xr:uid="{C6D77BDB-F45A-42D8-B2D4-EB4F0909A35E}"/>
-    <hyperlink ref="J13" r:id="rId5" xr:uid="{E7106D5E-0B78-4A74-805D-B2C62DCB6CCE}"/>
-    <hyperlink ref="J14" r:id="rId6" xr:uid="{5E58D9C4-1BD7-404B-9265-E8BCCFD381E9}"/>
-    <hyperlink ref="J17" r:id="rId7" xr:uid="{41C58F54-A4F9-4B62-A202-DCA53C31030B}"/>
-    <hyperlink ref="J19" r:id="rId8" xr:uid="{00FEA123-A263-4F82-821B-B51252AF1F8A}"/>
-    <hyperlink ref="J20" r:id="rId9" xr:uid="{492CB6E2-12FE-4428-868E-2821ED8BE992}"/>
-    <hyperlink ref="J21" r:id="rId10" xr:uid="{AE42E9D9-4D27-44D6-8702-388753FE3483}"/>
-    <hyperlink ref="J24" r:id="rId11" xr:uid="{3692A24E-EA7A-46BD-823E-A43C26BFD6B8}"/>
-    <hyperlink ref="J25" r:id="rId12" xr:uid="{8E3CA7B0-AEF8-4CFB-906B-FD551FDEF748}"/>
-    <hyperlink ref="J26" r:id="rId13" xr:uid="{5AEB08E2-0303-4EF3-A58D-E8CFF0ADA1B4}"/>
-    <hyperlink ref="J27" r:id="rId14" xr:uid="{C725F520-05C5-47D3-9C0F-0183FC86E68F}"/>
-    <hyperlink ref="J29" r:id="rId15" xr:uid="{25B96EDB-02E9-4679-BF2B-96E9DF4CA715}"/>
-    <hyperlink ref="J30" r:id="rId16" xr:uid="{85722860-8527-4666-B6B0-3D52A8F7A0F3}"/>
-    <hyperlink ref="J31" r:id="rId17" xr:uid="{9171355D-B3C4-4A4A-88CE-E581F158CBC3}"/>
-    <hyperlink ref="J34" r:id="rId18" xr:uid="{38FECEF6-3D7F-40CD-9323-4373A53DB235}"/>
-    <hyperlink ref="J35" r:id="rId19" xr:uid="{B49BA91B-4CC5-4033-B8BA-E0AF4E097471}"/>
-    <hyperlink ref="J36" r:id="rId20" xr:uid="{C4FD6806-F41D-47F5-94C4-C9D6534D61D5}"/>
-    <hyperlink ref="J37" r:id="rId21" xr:uid="{B7C35C80-EDBD-4687-B87B-240D19B21E18}"/>
-    <hyperlink ref="J38" r:id="rId22" xr:uid="{585A9484-B26B-4ACC-A775-16DBEBB808C0}"/>
-    <hyperlink ref="J46" r:id="rId23" xr:uid="{50AE12A1-1A8D-4EE1-90ED-85849C37A89F}"/>
-    <hyperlink ref="J47" r:id="rId24" xr:uid="{239D773D-26BD-4DF0-8A0E-1A4D740DC6E4}"/>
-    <hyperlink ref="J48" r:id="rId25" xr:uid="{51E5CFA2-D625-4ED6-89B7-C350A9443ACF}"/>
-    <hyperlink ref="J49" r:id="rId26" xr:uid="{36C66480-7860-49D6-8794-FFE1B89D2846}"/>
-    <hyperlink ref="J50" r:id="rId27" xr:uid="{FE0B6644-A447-4433-AC10-DDBA3BB44E20}"/>
-    <hyperlink ref="J52" r:id="rId28" xr:uid="{5E7C26C7-C87E-472D-B0FF-BDF4054A1A58}"/>
-    <hyperlink ref="J53" r:id="rId29" xr:uid="{499D1127-9EC1-4DE7-8136-6FF21291B24F}"/>
-    <hyperlink ref="J54" r:id="rId30" xr:uid="{18B1EFBC-07E7-4C81-9C14-E8205FE26BA3}"/>
-    <hyperlink ref="J56" r:id="rId31" xr:uid="{C543F0E8-D753-480A-B013-AA53C3C97B22}"/>
-    <hyperlink ref="J59" r:id="rId32" xr:uid="{C16B6485-978F-4F98-BB37-09A595B6C41A}"/>
-    <hyperlink ref="J61" r:id="rId33" xr:uid="{BE3835DB-4077-4966-BAA2-4FFE6FD48086}"/>
-    <hyperlink ref="J62" r:id="rId34" xr:uid="{43501BD8-7F40-4ACF-BCF6-B33EBBD63F69}"/>
-    <hyperlink ref="J63" r:id="rId35" xr:uid="{0CC86276-CDE0-4BCB-86BE-61599E8266F0}"/>
-    <hyperlink ref="J64" r:id="rId36" xr:uid="{CCAC92DB-CDB4-4281-B104-0815070FAEA0}"/>
-    <hyperlink ref="J69" r:id="rId37" xr:uid="{EBDDBE8D-17A5-4D2F-AC8B-0748A42B5543}"/>
-    <hyperlink ref="J71" r:id="rId38" xr:uid="{0E545CA9-7590-4673-9A14-10F3F42FDB4B}"/>
-    <hyperlink ref="J72" r:id="rId39" xr:uid="{ECF56C16-C4D2-4426-9FE2-82EE8C001A45}"/>
-    <hyperlink ref="J73" r:id="rId40" xr:uid="{E66FEBBB-A73C-479D-B8E0-5F4B5FAB3A50}"/>
-    <hyperlink ref="J74" r:id="rId41" xr:uid="{69A348F0-AF48-4EE9-9D4F-50EBA5E18DC8}"/>
-    <hyperlink ref="J75" r:id="rId42" xr:uid="{1A6CBDA9-D0AD-40EB-87C4-9DCF25BE3F76}"/>
-    <hyperlink ref="J76" r:id="rId43" xr:uid="{9C334AAE-68E8-4EEC-98E7-ABEB3261EDDA}"/>
-    <hyperlink ref="J78" r:id="rId44" xr:uid="{E2C828A6-5E32-475C-A637-DF8D0CD7F75F}"/>
-    <hyperlink ref="J80" r:id="rId45" xr:uid="{13FEC513-4403-4AFB-A65F-DEED9AB66CE9}"/>
-    <hyperlink ref="J86" r:id="rId46" xr:uid="{93A40753-010E-494D-A003-355C08C2FA97}"/>
-    <hyperlink ref="J88" r:id="rId47" xr:uid="{C03611F1-017E-4A2F-A703-2137012F9F8D}"/>
-    <hyperlink ref="J89" r:id="rId48" xr:uid="{366CBF9B-201E-40B9-8737-9665471086A0}"/>
-    <hyperlink ref="J90" r:id="rId49" xr:uid="{18950206-2558-485D-BBB9-9AA0638B5F2C}"/>
-    <hyperlink ref="J92" r:id="rId50" xr:uid="{BE96B8A7-D82C-4CC9-84C0-E6B41F3C6B9B}"/>
-    <hyperlink ref="J94" r:id="rId51" xr:uid="{440CF3C7-EBBC-444B-A3FE-B50D972954EF}"/>
-    <hyperlink ref="J95" r:id="rId52" xr:uid="{04DBE1F3-AF3E-4857-B823-A996B9D439C9}"/>
-    <hyperlink ref="J96" r:id="rId53" xr:uid="{31EFC16F-2DC7-440D-9856-DD3603FB6D97}"/>
-    <hyperlink ref="J101" r:id="rId54" xr:uid="{6962ED00-474A-4E0F-A63C-469B80CD5332}"/>
-    <hyperlink ref="J103" r:id="rId55" xr:uid="{1DF73DAC-0E4C-4379-B5FC-CDA380836245}"/>
-    <hyperlink ref="J104" r:id="rId56" xr:uid="{A295C1E3-1F59-4029-AF33-BE3806A4859B}"/>
-    <hyperlink ref="J105" r:id="rId57" xr:uid="{EC06412E-D28B-4745-8492-0C31F03DFD7B}"/>
-    <hyperlink ref="J106" r:id="rId58" xr:uid="{A3B35EC6-E03D-4CB1-B1D0-2AB4F1004B65}"/>
-    <hyperlink ref="J107" r:id="rId59" xr:uid="{66892C65-6CBB-4604-B8E0-57845407709E}"/>
-    <hyperlink ref="J109" r:id="rId60" xr:uid="{A1A8B81A-CB5C-4128-AAB9-BD7CDE19486F}"/>
-    <hyperlink ref="J110" r:id="rId61" xr:uid="{EBDC8B7D-2EBF-478E-A3BA-144D6C3E0305}"/>
-    <hyperlink ref="J111" r:id="rId62" xr:uid="{0B32A137-942B-4E2D-A1AE-0B994C4D0493}"/>
-    <hyperlink ref="J112" r:id="rId63" xr:uid="{A2565B9C-F0BA-407D-9AD5-1DC38D5194D3}"/>
-    <hyperlink ref="J113" r:id="rId64" xr:uid="{37AD72EA-F330-4677-ADCE-BD29DC2FA823}"/>
-    <hyperlink ref="J114" r:id="rId65" xr:uid="{FCB115C6-ED67-4282-87D3-739BB937B61D}"/>
-    <hyperlink ref="J116" r:id="rId66" xr:uid="{867D7E16-CE3B-4A57-8A57-B3ACE38B576F}"/>
-    <hyperlink ref="J117" r:id="rId67" xr:uid="{3B9B2F44-35DF-4D38-B0F5-863AA49619BE}"/>
-    <hyperlink ref="J118" r:id="rId68" xr:uid="{6C54B1ED-51EB-4079-AB39-5C7673011AB3}"/>
-    <hyperlink ref="J119" r:id="rId69" xr:uid="{42C3E9EB-CDEA-47B7-A136-8BBCEC45E341}"/>
-    <hyperlink ref="J120" r:id="rId70" xr:uid="{2D083A10-119A-4850-B348-D5EC4CE2FE0B}"/>
-    <hyperlink ref="J121" r:id="rId71" xr:uid="{9671905D-B370-45CC-B026-859628285E51}"/>
-    <hyperlink ref="J124" r:id="rId72" xr:uid="{F09712DC-7633-4FAF-BB56-7AB78C94B754}"/>
-    <hyperlink ref="J128" r:id="rId73" xr:uid="{75450E6B-CC93-4182-8AF3-4564963990FA}"/>
-    <hyperlink ref="J129" r:id="rId74" xr:uid="{B7520DE0-8616-4F77-903F-452C16909098}"/>
-    <hyperlink ref="J132" r:id="rId75" xr:uid="{14515023-477F-46C0-996E-DD917026AD08}"/>
-    <hyperlink ref="J134" r:id="rId76" xr:uid="{A21268DA-B563-4186-98CF-615D7D3510D5}"/>
-    <hyperlink ref="J135" r:id="rId77" xr:uid="{F55E693F-AD84-46F9-B2C7-ABC8AFA6D982}"/>
-    <hyperlink ref="J136" r:id="rId78" xr:uid="{EA686DF3-3309-4453-BB9C-D16C8B5A68EE}"/>
-    <hyperlink ref="J140" r:id="rId79" xr:uid="{A92EE539-130D-44F8-A5AA-DA9B1765C6B6}"/>
-    <hyperlink ref="J142" r:id="rId80" xr:uid="{8792BE6F-11AE-4F01-A4BD-420BA1FC5BAA}"/>
-    <hyperlink ref="J143" r:id="rId81" xr:uid="{71D0265C-6FE8-4C9E-B3AD-0AA783C30610}"/>
-    <hyperlink ref="J144" r:id="rId82" xr:uid="{3FE26AB8-AC55-4EE4-A515-776173842A4E}"/>
-    <hyperlink ref="J145" r:id="rId83" xr:uid="{CEEF4147-EE33-4950-87B9-B39030EEEA40}"/>
-    <hyperlink ref="J147" r:id="rId84" xr:uid="{04AB7B5B-463D-4AF2-86E6-9714ECD97EAF}"/>
-    <hyperlink ref="J149" r:id="rId85" xr:uid="{41524FAD-3EB4-474C-A701-2662EF353EF6}"/>
-    <hyperlink ref="J150" r:id="rId86" xr:uid="{2CFBA42B-C34C-4FB1-A6AF-176B31BCFE02}"/>
-    <hyperlink ref="J151" r:id="rId87" xr:uid="{71955CBA-A48A-47D1-B077-DCB73207DF94}"/>
-    <hyperlink ref="J152" r:id="rId88" xr:uid="{15D58C68-64C0-4118-BB90-D08B30229F8A}"/>
-    <hyperlink ref="J153" r:id="rId89" xr:uid="{04BA944C-418E-454F-BAA9-C3F182F50777}"/>
-    <hyperlink ref="J154" r:id="rId90" xr:uid="{64C52D91-5862-4C76-8CFB-36CEF93114D9}"/>
-    <hyperlink ref="J155" r:id="rId91" xr:uid="{B4358A6D-51C0-4313-9D2F-84F2D33DAD34}"/>
-    <hyperlink ref="J156" r:id="rId92" xr:uid="{8E9471A7-692B-4358-B3B4-269A54F65B81}"/>
-    <hyperlink ref="J159" r:id="rId93" xr:uid="{C74FD9C3-B615-47D5-BDED-3099D778F740}"/>
-    <hyperlink ref="J160" r:id="rId94" xr:uid="{963357F0-1732-42CC-8023-0E686BE3BA1D}"/>
-    <hyperlink ref="J161" r:id="rId95" xr:uid="{CAACF488-4408-4FB6-B263-D8B935397BF8}"/>
-    <hyperlink ref="J162" r:id="rId96" xr:uid="{C181A67F-141F-4D58-B297-D44BD6581ED3}"/>
-    <hyperlink ref="J164" r:id="rId97" xr:uid="{859A7B6E-4189-43E9-9685-5770ED183F62}"/>
-    <hyperlink ref="J165" r:id="rId98" xr:uid="{0B1D14E4-56BB-4996-9F22-BD84FF0E606E}"/>
-    <hyperlink ref="J167" r:id="rId99" xr:uid="{FE527744-16ED-4C80-942B-CBAFE843741E}"/>
-    <hyperlink ref="J168" r:id="rId100" xr:uid="{A7A3FDF6-FF7C-4576-91DD-7A0634C969A7}"/>
-    <hyperlink ref="J169" r:id="rId101" xr:uid="{0FDF4F1C-D07A-450E-B390-E1C3E747D5C2}"/>
-    <hyperlink ref="J171" r:id="rId102" xr:uid="{D3F909A3-1CEC-481B-B387-CD821421593E}"/>
-    <hyperlink ref="J172" r:id="rId103" xr:uid="{D15A3B3B-7C4E-47FE-835C-1C013AB6F7DB}"/>
-    <hyperlink ref="J173" r:id="rId104" xr:uid="{B04471FE-F805-4333-A413-6CFD68CB98D7}"/>
-    <hyperlink ref="J177" r:id="rId105" xr:uid="{B3C4BE8B-BAF3-4EBB-9D2A-C5DEFEFA71B1}"/>
-    <hyperlink ref="J178" r:id="rId106" xr:uid="{2FAA4143-DE5E-45B8-A9CF-209B21324B08}"/>
-    <hyperlink ref="J181" r:id="rId107" xr:uid="{329591F8-4316-429F-AA1A-A44226BE8928}"/>
-    <hyperlink ref="J182" r:id="rId108" xr:uid="{BADC8F64-C735-4EAF-B53F-CF65ABDE73E4}"/>
-    <hyperlink ref="J184" r:id="rId109" xr:uid="{2D0E8866-57F8-43D4-B0A1-EE932DB41EE3}"/>
-    <hyperlink ref="J186" r:id="rId110" xr:uid="{05C1E496-F03E-4B35-9CFF-689796DEB077}"/>
-    <hyperlink ref="J190" r:id="rId111" xr:uid="{355C6C83-1674-4B23-83B7-0D8B2E984A12}"/>
-    <hyperlink ref="J191" r:id="rId112" xr:uid="{D7A60E4E-A834-4621-9A30-695099E25582}"/>
-    <hyperlink ref="J192" r:id="rId113" xr:uid="{75857335-3F19-41BF-8C7B-7CA26AF7F8A9}"/>
-    <hyperlink ref="J193" r:id="rId114" xr:uid="{E9A2D19C-5FEA-4146-9CD5-D80A2CF2F78C}"/>
-    <hyperlink ref="J194" r:id="rId115" xr:uid="{5B602CAA-8ACE-4D4B-BA23-970D7A385944}"/>
-    <hyperlink ref="J195" r:id="rId116" xr:uid="{6F2C426F-53AA-48A7-9486-808E27512E8D}"/>
-    <hyperlink ref="J196" r:id="rId117" xr:uid="{88724AA3-CB95-4BEB-B014-B5B39B8CDEC1}"/>
-    <hyperlink ref="J199" r:id="rId118" xr:uid="{34D3CFCE-A28E-48D8-AB5B-539DBD85843E}"/>
-    <hyperlink ref="J201" r:id="rId119" xr:uid="{B19922BC-E7C0-44AB-9870-5739674B6EE7}"/>
-    <hyperlink ref="J202" r:id="rId120" xr:uid="{A5A9723D-943C-4109-B4F4-90BA779E55F6}"/>
-    <hyperlink ref="J203" r:id="rId121" xr:uid="{DC502B51-6131-4B52-949A-BABC9359DE2C}"/>
-    <hyperlink ref="J205" r:id="rId122" xr:uid="{FA1D274E-6E53-4B91-AFA3-426A405BF847}"/>
-    <hyperlink ref="J207" r:id="rId123" xr:uid="{256F55CF-5B22-42C9-934C-21D97BFAC247}"/>
-    <hyperlink ref="J209" r:id="rId124" xr:uid="{5598C36B-E8BA-4225-9BEF-CC9073B3C44C}"/>
-    <hyperlink ref="J210" r:id="rId125" xr:uid="{FC221FB1-06A6-486D-8DC4-A53952EDB6E4}"/>
-    <hyperlink ref="J211" r:id="rId126" xr:uid="{385F4097-B64A-429D-8B64-F325C9D37B71}"/>
-    <hyperlink ref="J212" r:id="rId127" xr:uid="{0581C41D-E9B0-4C9A-8C97-B83FA7185CCF}"/>
-    <hyperlink ref="J213" r:id="rId128" xr:uid="{26CBB23F-2775-466B-8E7F-9A33D6BCD650}"/>
-    <hyperlink ref="J214" r:id="rId129" xr:uid="{5467BAD1-6EFD-44CC-9E94-B2D2D8963D95}"/>
-    <hyperlink ref="J215" r:id="rId130" xr:uid="{03D56E90-002C-4A94-B298-C9E5624044E5}"/>
-    <hyperlink ref="J217" r:id="rId131" xr:uid="{3A5DF3F4-B443-4352-B928-11B9D743225A}"/>
-    <hyperlink ref="J219" r:id="rId132" xr:uid="{E10E39FE-AD2D-4B3E-B6AB-8A16D7C08A75}"/>
-    <hyperlink ref="J220" r:id="rId133" xr:uid="{12873E15-1E08-43BA-B0B8-8C10321FA005}"/>
-    <hyperlink ref="J221" r:id="rId134" xr:uid="{4AEEA60C-9906-4BC1-BFA2-ED35777474D2}"/>
-    <hyperlink ref="J222" r:id="rId135" xr:uid="{5BCDBC9B-C525-4FCC-AE78-CBC272ECB566}"/>
-    <hyperlink ref="J223" r:id="rId136" xr:uid="{54EB1A32-449A-49FC-BA67-BAE0A1250AC7}"/>
-    <hyperlink ref="J225" r:id="rId137" xr:uid="{465CEB64-1682-4051-8766-F8F9E0310125}"/>
-    <hyperlink ref="J228" r:id="rId138" xr:uid="{12E0CD73-4D5F-460E-9D8C-D083E1A4A678}"/>
-    <hyperlink ref="J230" r:id="rId139" xr:uid="{D393F800-CDEE-4E96-9540-3B3C3D37BCF6}"/>
-    <hyperlink ref="J234" r:id="rId140" xr:uid="{846433D5-721B-4AFA-A37B-E4D0146AA4C1}"/>
-    <hyperlink ref="J236" r:id="rId141" xr:uid="{2BFA713D-2B0F-41A3-8BB1-FAF8865B14E7}"/>
-    <hyperlink ref="J237" r:id="rId142" xr:uid="{32A96040-A585-4C17-B0F1-D5E6790E5DDC}"/>
-    <hyperlink ref="J238" r:id="rId143" xr:uid="{2717B00B-9340-4CC0-915F-DE26FA9D1A09}"/>
-    <hyperlink ref="J240" r:id="rId144" xr:uid="{A6E135DE-1CA5-4E5C-846D-E8E8E57E00E0}"/>
-    <hyperlink ref="J241" r:id="rId145" xr:uid="{A4A8036C-7AB9-4EB8-8779-6BFB6CB5AD20}"/>
-    <hyperlink ref="J242" r:id="rId146" xr:uid="{A90173E9-AE8E-45F4-BF73-BA3C5B77978B}"/>
-    <hyperlink ref="J243" r:id="rId147" xr:uid="{60278A6C-5A69-4BB4-96DC-6FF3E3A6BD35}"/>
-    <hyperlink ref="J246" r:id="rId148" xr:uid="{107F34C7-5CBF-49D8-B83D-C292243A081E}"/>
-    <hyperlink ref="J247" r:id="rId149" xr:uid="{730FEDE3-28EB-4FEC-BEA6-5473FC7C7DC5}"/>
-    <hyperlink ref="J250" r:id="rId150" xr:uid="{F6B04AFB-6EC4-46F3-ABE5-C41256F762F3}"/>
-    <hyperlink ref="J252" r:id="rId151" xr:uid="{51269946-FA70-4E5B-86DD-257A679F2385}"/>
-    <hyperlink ref="J254" r:id="rId152" xr:uid="{FCB484F7-CA45-43ED-A0FD-DFFF6DEF0923}"/>
-    <hyperlink ref="J255" r:id="rId153" xr:uid="{F4EB9647-2F1E-4E7B-91EB-248B13ECAAEA}"/>
-    <hyperlink ref="J256" r:id="rId154" xr:uid="{0F5D3735-AC76-4A8A-B357-32AEE387C431}"/>
-    <hyperlink ref="J258" r:id="rId155" xr:uid="{0DD28A21-D5DF-4D0B-AE8D-B17B1738E7F6}"/>
-    <hyperlink ref="J259" r:id="rId156" xr:uid="{44F32E82-FBC9-4D12-92E1-7D47685FE3C3}"/>
-    <hyperlink ref="J261" r:id="rId157" xr:uid="{0914038A-D777-40F2-A310-992CB1C74942}"/>
-    <hyperlink ref="J263" r:id="rId158" xr:uid="{E3F0B4DE-4AFD-470B-9A16-162DE7F756AF}"/>
-    <hyperlink ref="J265" r:id="rId159" xr:uid="{E6730428-EB3D-4DC0-8D80-580425B3B955}"/>
-    <hyperlink ref="J266" r:id="rId160" xr:uid="{076D555D-5DB9-4AD6-A734-DE4B1B813012}"/>
-    <hyperlink ref="J267" r:id="rId161" xr:uid="{7EB99867-05B3-4D7E-A08E-A4C768F70EF5}"/>
-    <hyperlink ref="J270" r:id="rId162" xr:uid="{92E18879-F69A-4E0E-93D8-307808F6A87D}"/>
-    <hyperlink ref="J271" r:id="rId163" xr:uid="{962CE41D-7706-4F4D-BC1D-E7E90A38EAE6}"/>
-    <hyperlink ref="J273" r:id="rId164" xr:uid="{31133AD2-C5B1-47F3-9794-BC7DFB3DD97C}"/>
-    <hyperlink ref="J274" r:id="rId165" xr:uid="{63C51F0C-3155-4A2C-9823-FF12FEE1F780}"/>
-    <hyperlink ref="J275" r:id="rId166" xr:uid="{453422EA-2659-4957-8CB4-E32487EC8EED}"/>
-    <hyperlink ref="J277" r:id="rId167" xr:uid="{E7CB317A-0D3E-4018-945F-28588818AB0D}"/>
-    <hyperlink ref="J278" r:id="rId168" xr:uid="{FEB314FA-4DA0-47AA-9DF2-F04E8FDD1469}"/>
-    <hyperlink ref="J279" r:id="rId169" xr:uid="{5E866AE6-87DD-4CFC-AAFD-0CD331849A63}"/>
-    <hyperlink ref="J280" r:id="rId170" xr:uid="{1E112EEF-E890-4C8C-A39B-C2C34D61E978}"/>
-    <hyperlink ref="J281" r:id="rId171" xr:uid="{BC996471-B1C0-450F-AE3B-C1D30CCB1E84}"/>
-    <hyperlink ref="J282" r:id="rId172" xr:uid="{C78A7D46-3B03-4F7C-AA52-40E3E4A438DF}"/>
-    <hyperlink ref="J283" r:id="rId173" xr:uid="{6862CB14-BE80-4EA2-B03D-2C6C720E58B3}"/>
-    <hyperlink ref="J286" r:id="rId174" xr:uid="{811BCE20-EC9F-4C88-855E-3DBA74DD5EEA}"/>
-    <hyperlink ref="J287" r:id="rId175" xr:uid="{9A24E05B-3664-4CAB-A753-C9C8667101D6}"/>
-    <hyperlink ref="J290" r:id="rId176" xr:uid="{F7FBF488-9129-40DB-AA17-311AADA5FE30}"/>
-    <hyperlink ref="J292" r:id="rId177" xr:uid="{F8EB98D5-A10F-469E-8920-615488C87E15}"/>
-    <hyperlink ref="J294" r:id="rId178" xr:uid="{027177F4-D779-439E-AA03-3FC986929506}"/>
-    <hyperlink ref="J296" r:id="rId179" xr:uid="{B3D51561-0693-4723-9709-EEDC5E7E7FDE}"/>
-    <hyperlink ref="J297" r:id="rId180" xr:uid="{3D39DD04-8E66-441A-8DA6-D2B778B39482}"/>
-    <hyperlink ref="J298" r:id="rId181" xr:uid="{979CB110-B7CF-418F-8C2C-2F93554316A8}"/>
-    <hyperlink ref="J299" r:id="rId182" xr:uid="{39217B2C-CC8E-45D7-9A17-E28BC49C7550}"/>
-    <hyperlink ref="J300" r:id="rId183" xr:uid="{1D855BED-4D87-4023-9C71-58E9BCDF991C}"/>
-    <hyperlink ref="J301" r:id="rId184" xr:uid="{43C9F155-7A43-4447-88B6-1119EABCBA86}"/>
-    <hyperlink ref="J303" r:id="rId185" xr:uid="{2931F21B-F021-47F7-BF6A-CB316558B11A}"/>
-    <hyperlink ref="J305" r:id="rId186" xr:uid="{5E04882D-0AAE-43EC-B9C4-57EC62B613A5}"/>
-    <hyperlink ref="J306" r:id="rId187" xr:uid="{6FB0B4F2-5F2A-4823-B15D-96A2148318AD}"/>
-    <hyperlink ref="J308" r:id="rId188" xr:uid="{65BF2B00-06F5-48A9-981A-E728BB12AAF2}"/>
-    <hyperlink ref="J309" r:id="rId189" xr:uid="{648787EE-1518-432D-9087-E3CDA8D00A5A}"/>
-    <hyperlink ref="J311" r:id="rId190" xr:uid="{2CED0312-3EC3-44D0-A2CE-2DF52C5B2BC4}"/>
-    <hyperlink ref="J312" r:id="rId191" xr:uid="{B8702F81-A8AC-4D2F-A8E1-7802E5CB17E6}"/>
-    <hyperlink ref="J314" r:id="rId192" xr:uid="{3EF4991F-E67D-4AB8-88D2-B457CBC77C4C}"/>
-    <hyperlink ref="J317" r:id="rId193" xr:uid="{2C722523-C2A0-4412-B9DA-A4D42F9D73E5}"/>
-    <hyperlink ref="J318" r:id="rId194" xr:uid="{B907E0A6-9F39-4867-A3F7-9A13063B3DEB}"/>
-    <hyperlink ref="J321" r:id="rId195" xr:uid="{0BBA91FC-8259-4D00-AECE-0D7D47F7E7E8}"/>
-    <hyperlink ref="J322" r:id="rId196" xr:uid="{1D9BF2EE-1407-4C84-A70A-86E45D0329DA}"/>
-    <hyperlink ref="J325" r:id="rId197" xr:uid="{65A69D08-3C17-4331-AC84-9385058C95C7}"/>
-    <hyperlink ref="J326" r:id="rId198" xr:uid="{745EE793-0623-403C-98DA-33CFE9B86FFE}"/>
-    <hyperlink ref="J329" r:id="rId199" xr:uid="{F459E661-6C48-4BC3-8BBB-B1C9E4C22069}"/>
-    <hyperlink ref="J330" r:id="rId200" xr:uid="{4E0ED9CB-BF52-46EE-8DA8-4B4AF15158BB}"/>
-    <hyperlink ref="J331" r:id="rId201" xr:uid="{D87C3F99-3141-4DCE-AFB4-7BDE5F5BC79B}"/>
-    <hyperlink ref="J333" r:id="rId202" xr:uid="{7C4E39F8-5E61-4C19-98A6-25BA00959E5C}"/>
-    <hyperlink ref="J334" r:id="rId203" xr:uid="{C0764C3C-2956-45E9-912F-948C0F2E0049}"/>
-    <hyperlink ref="J335" r:id="rId204" xr:uid="{184CB84F-B6DF-4C2D-A87D-D458E09E8AA5}"/>
-    <hyperlink ref="J336" r:id="rId205" xr:uid="{4A7122EF-FED2-4EC2-ACCB-6961F0AEC113}"/>
-    <hyperlink ref="J338" r:id="rId206" xr:uid="{B431E314-0907-4BCC-BE97-9456A5FC7FD2}"/>
-    <hyperlink ref="J340" r:id="rId207" xr:uid="{9634DA7B-18E4-460E-BE2D-32A9705B04F8}"/>
-    <hyperlink ref="J342" r:id="rId208" xr:uid="{9E0A3734-571F-4400-8123-9BC7AA07F70F}"/>
-    <hyperlink ref="J343" r:id="rId209" xr:uid="{22B22753-A72D-4E20-A9E9-00169A5256CE}"/>
-    <hyperlink ref="J344" r:id="rId210" xr:uid="{8FD27278-D9EF-482C-A897-920E66743200}"/>
-    <hyperlink ref="J346" r:id="rId211" xr:uid="{611C113D-68A9-4973-8777-407A8F489144}"/>
-    <hyperlink ref="J349" r:id="rId212" xr:uid="{F3026B37-08BD-47E6-952A-BCD60DFCA05F}"/>
-    <hyperlink ref="J350" r:id="rId213" xr:uid="{99A6D3C9-E902-4F6C-B9FD-04DEB0B9B638}"/>
-    <hyperlink ref="J352" r:id="rId214" xr:uid="{C1418C9D-729A-47B9-AF99-85A0A68BF82E}"/>
-    <hyperlink ref="J354" r:id="rId215" xr:uid="{0EA79A39-E723-4C66-B331-34607799A8A7}"/>
-    <hyperlink ref="J355" r:id="rId216" xr:uid="{6CF0C133-581F-4E6E-BAFB-9521D22EE912}"/>
-    <hyperlink ref="J356" r:id="rId217" xr:uid="{668CDD1C-B78D-4586-A205-D5482E4D44E2}"/>
-    <hyperlink ref="J357" r:id="rId218" xr:uid="{A926328C-CD0E-4010-85D8-C96E548846D1}"/>
-    <hyperlink ref="J358" r:id="rId219" xr:uid="{36E067A4-86EE-4258-8F2C-5510AA3D44F8}"/>
-    <hyperlink ref="J360" r:id="rId220" xr:uid="{BCF97176-49A1-4452-B0DA-B252F748216C}"/>
-    <hyperlink ref="J363" r:id="rId221" xr:uid="{7B277429-BB8A-4274-91C7-A7A5AE63F18C}"/>
-    <hyperlink ref="J364" r:id="rId222" xr:uid="{4BA40F84-3DD0-439E-9EE1-529A8CED544B}"/>
-    <hyperlink ref="J366" r:id="rId223" xr:uid="{99D4BD00-99E1-4CAC-A62E-D909AAC52BDF}"/>
-    <hyperlink ref="J368" r:id="rId224" xr:uid="{2AE201E3-748F-41A7-ADB9-4638F3FC1883}"/>
-    <hyperlink ref="J370" r:id="rId225" xr:uid="{EF6CFBF1-E9D3-4836-AA40-1A7DB6B41A28}"/>
-    <hyperlink ref="J371" r:id="rId226" xr:uid="{81540196-A2FB-4D0F-A7A9-11CBDF504958}"/>
-    <hyperlink ref="J372" r:id="rId227" xr:uid="{B59CDB09-ECEB-4E27-86F6-FB0FDD518D3F}"/>
-    <hyperlink ref="J373" r:id="rId228" xr:uid="{05A29968-5A95-4919-B88F-28DFC53F711E}"/>
-    <hyperlink ref="J374" r:id="rId229" xr:uid="{D3235884-CF22-4012-AF31-6C64C89762C7}"/>
-    <hyperlink ref="J375" r:id="rId230" xr:uid="{46252EC9-B25E-4FF5-957F-A1DF8DBAB1CA}"/>
-    <hyperlink ref="J376" r:id="rId231" xr:uid="{76CD5814-6BD5-4A23-B59B-D27E260A0E89}"/>
-    <hyperlink ref="J377" r:id="rId232" xr:uid="{E050A2CC-7942-4099-A656-C40F7D1A298D}"/>
-    <hyperlink ref="J378" r:id="rId233" xr:uid="{26D18CEA-CC25-472B-BFF1-16A50F8A64C1}"/>
-    <hyperlink ref="J379" r:id="rId234" xr:uid="{55864359-7728-4FCA-83E2-EEED6AD0548A}"/>
-    <hyperlink ref="J381" r:id="rId235" xr:uid="{BE6779F9-C9A6-4C39-A602-5FDE75079B00}"/>
-    <hyperlink ref="J383" r:id="rId236" xr:uid="{48CFA3CF-9001-4223-8BED-2DB431E4E225}"/>
-    <hyperlink ref="J384" r:id="rId237" xr:uid="{F4CCE2E9-B4B2-4EB8-93DC-4B682EFC2652}"/>
-    <hyperlink ref="J386" r:id="rId238" xr:uid="{D93DA8CB-4017-4A56-8858-D3CE8F5D3DC7}"/>
-    <hyperlink ref="J387" r:id="rId239" xr:uid="{57C3A44F-20A5-4E51-8953-C930F81F5575}"/>
-    <hyperlink ref="J388" r:id="rId240" xr:uid="{F7182023-A8DD-4F1F-9769-132EA2C3AC6E}"/>
-    <hyperlink ref="J390" r:id="rId241" xr:uid="{015F49FB-1489-4DBF-9DE1-05A9C2A377FE}"/>
-    <hyperlink ref="J391" r:id="rId242" xr:uid="{51689331-EC65-4B53-9AD9-C4AF361C5A23}"/>
-    <hyperlink ref="J394" r:id="rId243" xr:uid="{9C45A29B-1AC8-4B52-B7E5-102BCDA84324}"/>
-    <hyperlink ref="J395" r:id="rId244" xr:uid="{4803AFE0-0D6A-4216-AD13-439EC31877A5}"/>
-    <hyperlink ref="J396" r:id="rId245" xr:uid="{A9670DB4-CA7F-4503-BE5A-34065DD97429}"/>
-    <hyperlink ref="J397" r:id="rId246" xr:uid="{BA3E0652-9F03-4469-9C19-15DD69903D00}"/>
-    <hyperlink ref="J398" r:id="rId247" xr:uid="{E548B00E-47C1-4774-8D9F-D5D25E467E07}"/>
-    <hyperlink ref="J399" r:id="rId248" xr:uid="{75636C6F-78BB-42B2-977C-EA72796173E3}"/>
-    <hyperlink ref="J400" r:id="rId249" xr:uid="{CA87FAA1-0E09-4D3C-993E-7AD156219A7B}"/>
-    <hyperlink ref="J403" r:id="rId250" xr:uid="{1E74B860-4E19-41FB-B777-FFBDCB20A71D}"/>
-    <hyperlink ref="J404" r:id="rId251" xr:uid="{55327506-BFA5-4BD2-83B3-3885314B8A5B}"/>
-    <hyperlink ref="J405" r:id="rId252" xr:uid="{0129E742-0EE5-40E9-97D7-1DDF24BA7846}"/>
-    <hyperlink ref="J406" r:id="rId253" xr:uid="{B7CBA08E-D200-4DCD-A142-D95E1D39659D}"/>
-    <hyperlink ref="J408" r:id="rId254" xr:uid="{CC64506A-1AA3-4301-92D3-1CDAB68D9F5D}"/>
-    <hyperlink ref="J409" r:id="rId255" xr:uid="{D33ECFD8-B1BD-491B-A2DF-D462FABAC161}"/>
-    <hyperlink ref="J411" r:id="rId256" xr:uid="{57836487-FB92-4670-87E1-7F56EB0DA611}"/>
-    <hyperlink ref="J413" r:id="rId257" xr:uid="{4724CBD4-5DF3-4F83-98FD-40A042EDB522}"/>
-    <hyperlink ref="J415" r:id="rId258" xr:uid="{19E15558-E6BE-4782-8CBA-812589AAE925}"/>
-    <hyperlink ref="J416" r:id="rId259" xr:uid="{EA5177A5-49FF-45F2-9EB3-55F9ECF2BFCE}"/>
-    <hyperlink ref="J418" r:id="rId260" xr:uid="{46E828D8-37EE-4A2C-84BC-5D96BAFF77D6}"/>
-    <hyperlink ref="J421" r:id="rId261" xr:uid="{6596D015-1B8C-46F2-A0FD-7303389D4192}"/>
-    <hyperlink ref="J422" r:id="rId262" xr:uid="{AE5BF0AB-B5F2-4B53-BD81-ED02BB73D101}"/>
-    <hyperlink ref="J430" r:id="rId263" xr:uid="{F51FDB73-48FD-46D1-BE38-9FC5D876E750}"/>
-    <hyperlink ref="J431" r:id="rId264" xr:uid="{E4AFDA17-13F5-4CA9-941C-3B71E073E107}"/>
-    <hyperlink ref="J432" r:id="rId265" xr:uid="{05104686-3682-4243-BD79-5D8002314869}"/>
-    <hyperlink ref="J433" r:id="rId266" xr:uid="{F3E49677-3DA2-4D84-A11E-30A994785BD0}"/>
-    <hyperlink ref="J434" r:id="rId267" xr:uid="{77592EB7-3702-4FAC-B6A1-8B322ADBE8E6}"/>
-    <hyperlink ref="J435" r:id="rId268" xr:uid="{71511A0A-E0A3-458E-B509-8FE87F875E87}"/>
-    <hyperlink ref="J436" r:id="rId269" xr:uid="{C9CF313C-3610-4872-90DD-3CB6119747FD}"/>
-    <hyperlink ref="J437" r:id="rId270" xr:uid="{DD1128E8-EE29-4D65-9B3C-09F51084A755}"/>
-    <hyperlink ref="J438" r:id="rId271" xr:uid="{64567F06-746A-4886-99EF-CD129AD27BB6}"/>
-    <hyperlink ref="J439" r:id="rId272" xr:uid="{9E9520DF-C3D8-4D73-99D1-781CED8C54A8}"/>
-    <hyperlink ref="J445" r:id="rId273" xr:uid="{09A19C3A-A4C5-4DB9-9181-07308E47C58D}"/>
-    <hyperlink ref="J447" r:id="rId274" xr:uid="{21E073B7-A0E9-4887-A56A-1D8AB815BE6F}"/>
-    <hyperlink ref="J449" r:id="rId275" xr:uid="{82742D37-014F-4A3A-ABD9-73235F606DE1}"/>
-    <hyperlink ref="J450" r:id="rId276" xr:uid="{EA830EA4-C0A8-4139-BACF-104AB85DAFBF}"/>
-    <hyperlink ref="J451" r:id="rId277" xr:uid="{2948E026-A582-4DF6-96AF-CD058D62B21E}"/>
-    <hyperlink ref="J452" r:id="rId278" xr:uid="{38054356-C9B0-4E6B-8E28-12F8EB11B5D9}"/>
-    <hyperlink ref="J453" r:id="rId279" xr:uid="{4FA4EF28-FB61-4225-8655-7D6A4BC9D185}"/>
-    <hyperlink ref="J454" r:id="rId280" xr:uid="{D0696FF2-A6CE-4EB0-95B1-C1D482F7310D}"/>
-    <hyperlink ref="J455" r:id="rId281" xr:uid="{42A4CFAC-FC93-4FDA-917F-E244EC6DE789}"/>
-    <hyperlink ref="J458" r:id="rId282" xr:uid="{21107305-7296-4837-B92F-789F59F763A2}"/>
-    <hyperlink ref="J460" r:id="rId283" xr:uid="{D344DEAF-D4E8-413A-9AA0-2B43ECB4BF66}"/>
-    <hyperlink ref="J461" r:id="rId284" xr:uid="{A0759B56-6C8E-4815-9EAC-3C768EA913CA}"/>
-    <hyperlink ref="J462" r:id="rId285" xr:uid="{3063A5C1-429A-4A1E-A95C-8E7A59B335D7}"/>
-    <hyperlink ref="J465" r:id="rId286" xr:uid="{85DDD8EF-92A7-456C-9D92-7CB34FD4D38B}"/>
-    <hyperlink ref="J469" r:id="rId287" xr:uid="{2D783211-7070-4539-A99E-B0B7492C99AC}"/>
-    <hyperlink ref="J473" r:id="rId288" xr:uid="{2793B4FB-741D-4223-BCF5-2EB74901D739}"/>
-    <hyperlink ref="J476" r:id="rId289" xr:uid="{0598CC80-49BB-4E1F-A483-DD59B6182B1C}"/>
-    <hyperlink ref="J478" r:id="rId290" xr:uid="{A1066559-6926-4D9A-A323-2A22FA23BD38}"/>
-    <hyperlink ref="J479" r:id="rId291" xr:uid="{E99887EB-3C6B-4A49-832F-ED5CFFCAE6F1}"/>
-    <hyperlink ref="J480" r:id="rId292" xr:uid="{AEFB1C19-0F10-4B0B-9226-3C183F47615B}"/>
-    <hyperlink ref="J481" r:id="rId293" xr:uid="{8F48F736-7784-4523-9E4C-7B5D9B3D7965}"/>
-    <hyperlink ref="J482" r:id="rId294" xr:uid="{0D3D0632-82B3-4988-A8F5-EE8DF9275BEB}"/>
-    <hyperlink ref="J484" r:id="rId295" xr:uid="{3432DDF8-0DAC-4151-8448-72AA5B43E028}"/>
-    <hyperlink ref="J485" r:id="rId296" xr:uid="{8CB3A8E4-AC0A-4292-A47A-AC11E803AAF8}"/>
-    <hyperlink ref="J488" r:id="rId297" xr:uid="{22A42D26-024F-4056-938A-A7AEEA0722C0}"/>
-    <hyperlink ref="J489" r:id="rId298" xr:uid="{7BC97F4D-F500-48C7-BF0D-69C0D69C7EC8}"/>
-    <hyperlink ref="J490" r:id="rId299" xr:uid="{FB0F0EB0-231D-41BC-9700-BA04F04C88A5}"/>
-    <hyperlink ref="J491" r:id="rId300" xr:uid="{F5416967-FE80-4399-9CDE-096EECEB45A1}"/>
-    <hyperlink ref="J494" r:id="rId301" xr:uid="{384D949A-3247-4A0D-BF3C-345FFA6813B4}"/>
-    <hyperlink ref="J496" r:id="rId302" xr:uid="{05B32792-1D77-47B5-80E1-9DA19F5393EC}"/>
-    <hyperlink ref="J497" r:id="rId303" xr:uid="{186E0AB5-FC20-4317-BBB9-0973E3FA2D47}"/>
-    <hyperlink ref="J498" r:id="rId304" xr:uid="{FF6470BD-8D16-4CCB-9D71-4F2EC95186B2}"/>
-    <hyperlink ref="J499" r:id="rId305" xr:uid="{06216EEB-E813-490B-8BD0-7BA838308146}"/>
-    <hyperlink ref="J500" r:id="rId306" xr:uid="{1674DD2F-65FA-48FD-93B4-98F0F39E4ABC}"/>
-    <hyperlink ref="J501" r:id="rId307" xr:uid="{3517C316-7C6B-4F92-9C51-E2E47092DCAB}"/>
-    <hyperlink ref="J503" r:id="rId308" xr:uid="{3D891A29-1010-4C30-A9B9-E9589562F6F9}"/>
-    <hyperlink ref="J504" r:id="rId309" xr:uid="{317821F7-8304-4DF5-A5AB-8DF69CD9D704}"/>
-    <hyperlink ref="J508" r:id="rId310" xr:uid="{29A89C2B-2FDE-4764-8847-E69D62BF5E48}"/>
-    <hyperlink ref="J509" r:id="rId311" xr:uid="{DE8BEB5E-A190-4A8D-BFB9-5EF9C98150B5}"/>
-    <hyperlink ref="J510" r:id="rId312" xr:uid="{C0F6C9B8-C19F-482C-8E15-13ABE439A056}"/>
-    <hyperlink ref="J511" r:id="rId313" xr:uid="{E2C4F7F7-BD70-41E1-B7B9-0C06666FA963}"/>
-    <hyperlink ref="J513" r:id="rId314" xr:uid="{86FAB173-FCF8-47ED-8601-4B0F70A4E694}"/>
-    <hyperlink ref="J515" r:id="rId315" xr:uid="{95FE74DB-66EC-4118-83D1-B2CD7CFB8F08}"/>
-    <hyperlink ref="J516" r:id="rId316" xr:uid="{68428DAF-6D6D-4EA1-BEC8-4F2F6DC98576}"/>
-    <hyperlink ref="J519" r:id="rId317" xr:uid="{69777D45-2653-4A9C-9457-24D4C0154665}"/>
-    <hyperlink ref="J523" r:id="rId318" xr:uid="{07E4652F-E084-4BCA-8D23-B09704BDAD0F}"/>
-    <hyperlink ref="J524" r:id="rId319" xr:uid="{5AA13DFD-83D9-4544-B751-DA215F53CF02}"/>
-    <hyperlink ref="J525" r:id="rId320" xr:uid="{312ED658-6B53-4D74-AA80-D7370719B387}"/>
-    <hyperlink ref="J535" r:id="rId321" xr:uid="{50F6AA01-FCFE-49AF-A775-C549E0720EDB}"/>
-    <hyperlink ref="J536" r:id="rId322" xr:uid="{92C4995A-A192-46D6-9E16-4DEDAD6D87B6}"/>
-    <hyperlink ref="J537" r:id="rId323" xr:uid="{115F232B-7CE0-4542-AE38-E67596E56F04}"/>
-    <hyperlink ref="J538" r:id="rId324" xr:uid="{D145F7BF-0541-43CB-BD17-3F090ACB6A79}"/>
-    <hyperlink ref="J539" r:id="rId325" xr:uid="{8133612C-2012-4D3C-93E9-4693A6B65291}"/>
-    <hyperlink ref="J540" r:id="rId326" xr:uid="{906F06B9-A6CD-4C08-81F5-79BF87FF8BCA}"/>
-    <hyperlink ref="J541" r:id="rId327" xr:uid="{2AA59355-A694-4795-AD91-DA0FEECAF49D}"/>
-    <hyperlink ref="J543" r:id="rId328" xr:uid="{6200D3AD-FB8A-4C98-8833-AF14C1F067AB}"/>
-    <hyperlink ref="J544" r:id="rId329" xr:uid="{6B308498-8434-48AB-B012-4741BD8D0002}"/>
-    <hyperlink ref="J546" r:id="rId330" xr:uid="{4729221F-C289-456A-826C-1DD785A6B8CE}"/>
-    <hyperlink ref="J547" r:id="rId331" xr:uid="{6F72BA81-DDBF-4AC7-9503-A58BA9192132}"/>
-    <hyperlink ref="J548" r:id="rId332" xr:uid="{2F3CDF2F-D378-460C-865A-5B99787B9A34}"/>
-    <hyperlink ref="J549" r:id="rId333" xr:uid="{A462EF3D-715F-4D15-8EDA-37B714A22661}"/>
-    <hyperlink ref="J550" r:id="rId334" xr:uid="{731B8ACE-7F1A-497D-8ED8-22ECA7555055}"/>
-    <hyperlink ref="J551" r:id="rId335" xr:uid="{321A3F75-B49B-4E6F-815F-F1577288815D}"/>
-    <hyperlink ref="J552" r:id="rId336" xr:uid="{9788226A-50BF-4428-9FF4-7E830802136F}"/>
-    <hyperlink ref="J555" r:id="rId337" xr:uid="{8344891B-F4FB-4D0A-9FB5-FD796C14FCF8}"/>
-    <hyperlink ref="J556" r:id="rId338" xr:uid="{F3FA0074-7FB8-4D3A-9235-7CEC810E9CD9}"/>
-    <hyperlink ref="J558" r:id="rId339" xr:uid="{5FD9E3D1-F5E5-45E6-A8C1-7A2A7FFB3116}"/>
-    <hyperlink ref="J559" r:id="rId340" xr:uid="{C8F486C5-3B6F-4BEE-8473-8073742FE1B6}"/>
-    <hyperlink ref="J560" r:id="rId341" xr:uid="{8E1FA5D0-BB3A-465E-B0FC-49FE28546A5C}"/>
-    <hyperlink ref="J562" r:id="rId342" xr:uid="{A17D3DC8-81DA-420A-B374-3FCBB99E8C4A}"/>
-    <hyperlink ref="J569" r:id="rId343" xr:uid="{561886CB-CB97-4986-863C-0CBA8A352821}"/>
-    <hyperlink ref="J570" r:id="rId344" xr:uid="{C3CC1FF9-E36A-40E0-BA3C-DAC1861426BC}"/>
-    <hyperlink ref="J571" r:id="rId345" xr:uid="{23FD791C-A0A3-4B1E-8AEA-9C1A5076B162}"/>
-    <hyperlink ref="J572" r:id="rId346" xr:uid="{299B5EF6-64D6-4864-9D8B-DDCC363F4012}"/>
-    <hyperlink ref="J573" r:id="rId347" xr:uid="{A49393C5-99A0-4D99-A066-65E9E659D1A2}"/>
-    <hyperlink ref="J574" r:id="rId348" xr:uid="{1EE4C200-8266-494A-B317-82986F353F48}"/>
-    <hyperlink ref="J575" r:id="rId349" xr:uid="{D2A9FDA5-0677-4AC7-BDA4-DA69A52E490E}"/>
-    <hyperlink ref="J576" r:id="rId350" xr:uid="{6342CCDA-29B0-4FFD-9413-9B64D9265B6B}"/>
-    <hyperlink ref="J577" r:id="rId351" xr:uid="{12598853-4B7F-4B32-A401-DEBFB084E26D}"/>
-    <hyperlink ref="J578" r:id="rId352" xr:uid="{103BAFA4-6949-4C4D-83FA-E4FF4651CAE4}"/>
-    <hyperlink ref="J579" r:id="rId353" xr:uid="{D6B0AF20-9D02-42A8-B5F8-0B2991A7F985}"/>
-    <hyperlink ref="J580" r:id="rId354" xr:uid="{7B74B7F3-8573-4315-96E2-760D6F4EB176}"/>
-    <hyperlink ref="J581" r:id="rId355" xr:uid="{E74A6774-12D5-45FD-AABB-18482FBFB01B}"/>
-    <hyperlink ref="J582" r:id="rId356" xr:uid="{1F54E31C-17E9-4A7A-A441-54B598BEC14D}"/>
-    <hyperlink ref="J584" r:id="rId357" xr:uid="{1AB4F1FB-961C-4AF4-BF2D-FF8631A747B4}"/>
-    <hyperlink ref="J585" r:id="rId358" xr:uid="{9C6DB2BB-5574-4365-8A06-1FE42058E7FA}"/>
-    <hyperlink ref="J586" r:id="rId359" xr:uid="{610F1F7B-8CC4-4416-9552-008D50452816}"/>
-    <hyperlink ref="J587" r:id="rId360" xr:uid="{F0CA7DFA-E830-44CD-A181-4D2611EAE291}"/>
-    <hyperlink ref="J592" r:id="rId361" xr:uid="{612459CD-D3E0-493C-A46E-3C19C1509A92}"/>
-    <hyperlink ref="J593" r:id="rId362" xr:uid="{33A1B4B6-FB1A-4CEC-82FE-65423C912E50}"/>
-    <hyperlink ref="J595" r:id="rId363" xr:uid="{0A596A27-007E-407E-97DD-155F49F4C422}"/>
-    <hyperlink ref="J596" r:id="rId364" xr:uid="{1CF3F118-B8DE-4F40-ACAA-07936D063D0D}"/>
-    <hyperlink ref="J598" r:id="rId365" xr:uid="{A93A69FB-B337-4B15-9579-D0D552AD9067}"/>
-    <hyperlink ref="J599" r:id="rId366" xr:uid="{1EC44C1C-7DF5-4FA1-A55C-30D0350256F4}"/>
-    <hyperlink ref="J602" r:id="rId367" xr:uid="{DFE890CB-C8E5-4730-AB76-0D2F5E2EE601}"/>
-    <hyperlink ref="J603" r:id="rId368" xr:uid="{3DFD5017-9058-4837-B664-EA12DC042CB3}"/>
-    <hyperlink ref="J604" r:id="rId369" xr:uid="{B38ABEBB-4F0B-4592-8C9A-4CB780B45D61}"/>
-    <hyperlink ref="J605" r:id="rId370" xr:uid="{08DB3FD8-0EB1-4A04-A85D-D049949A41FE}"/>
-    <hyperlink ref="J606" r:id="rId371" xr:uid="{509702FE-8B78-4FB3-91D0-F2968972626C}"/>
-    <hyperlink ref="J608" r:id="rId372" xr:uid="{B525B178-0B22-4961-90B1-3A9BD760A0BD}"/>
-    <hyperlink ref="J609" r:id="rId373" xr:uid="{4CF0E18F-246B-4083-AB69-4B69B8B965B3}"/>
-    <hyperlink ref="J611" r:id="rId374" xr:uid="{053E8429-B5CF-486D-BB6E-6813AFBD7F85}"/>
-    <hyperlink ref="J612" r:id="rId375" xr:uid="{F9C81538-49DE-4B9C-9B20-5116B928092A}"/>
-    <hyperlink ref="J613" r:id="rId376" xr:uid="{80ED78F1-8079-4477-870C-1D091E5BE12F}"/>
-    <hyperlink ref="J615" r:id="rId377" xr:uid="{A8423458-8FC9-4CF2-AC0A-4C2FC739E3CF}"/>
-    <hyperlink ref="J617" r:id="rId378" xr:uid="{1CF6B184-98C3-4749-9BBC-C11D55CA4D0A}"/>
-    <hyperlink ref="J618" r:id="rId379" xr:uid="{45A9DC77-6F5B-4102-9675-87AAB0A7E8F1}"/>
-    <hyperlink ref="J619" r:id="rId380" xr:uid="{8AED1663-FD0F-44DA-AEA1-F9BEF6DCF60A}"/>
-    <hyperlink ref="J622" r:id="rId381" xr:uid="{F90A09D1-A897-4552-8D01-C4E1FC33D651}"/>
-    <hyperlink ref="J623" r:id="rId382" xr:uid="{9E5D10E2-E126-43BC-9B0D-076525EC42E2}"/>
-    <hyperlink ref="J624" r:id="rId383" xr:uid="{4EB00EAA-51BC-4DC5-96B7-61BC1725FD60}"/>
-    <hyperlink ref="J626" r:id="rId384" xr:uid="{98FDB0F5-66D4-4121-B17E-8351A91AD214}"/>
-    <hyperlink ref="J628" r:id="rId385" xr:uid="{80AA7CC7-6309-47DD-8892-0EB1B71EE03D}"/>
-    <hyperlink ref="J629" r:id="rId386" xr:uid="{E9D178AF-C6CD-428C-9B27-8B1CB1E44FE6}"/>
-    <hyperlink ref="J631" r:id="rId387" xr:uid="{ED11190D-D9CE-4974-81DF-168DEF85EFD5}"/>
-    <hyperlink ref="J634" r:id="rId388" xr:uid="{5CB3107B-0E8F-4938-BDB3-3021A609EA73}"/>
-    <hyperlink ref="J635" r:id="rId389" xr:uid="{3FC8C771-E486-4F12-A77F-D1CC90751D60}"/>
-    <hyperlink ref="J637" r:id="rId390" xr:uid="{6C6D4720-91B5-45A0-BDE9-9F834857F08E}"/>
-    <hyperlink ref="J640" r:id="rId391" xr:uid="{3DDF54F9-84E2-48A3-AD8C-E537A534ABBC}"/>
-    <hyperlink ref="J641" r:id="rId392" xr:uid="{660E4BED-EF94-4C4F-917A-027461167C0A}"/>
-    <hyperlink ref="J642" r:id="rId393" xr:uid="{B23FEF0D-DF20-4C3A-A295-525A824A6E46}"/>
-    <hyperlink ref="J644" r:id="rId394" xr:uid="{F5B975E2-9D5A-427C-8182-A8829CB805BA}"/>
-    <hyperlink ref="J645" r:id="rId395" xr:uid="{6B0C6DCB-E45F-4A29-9E73-4F1E04B9197F}"/>
-    <hyperlink ref="J648" r:id="rId396" xr:uid="{737C61D4-C687-4B27-AD41-0753B79BBE63}"/>
-    <hyperlink ref="J649" r:id="rId397" xr:uid="{08E6B199-14BD-4906-8C75-8F0D5D1CF8C1}"/>
-    <hyperlink ref="J652" r:id="rId398" xr:uid="{B4A030DF-0BC3-4D01-B4B6-16B0ACC64EC2}"/>
-    <hyperlink ref="J654" r:id="rId399" xr:uid="{684B3C08-14DA-4B04-8E4A-9B31E0412D1B}"/>
-    <hyperlink ref="J656" r:id="rId400" xr:uid="{EC24186B-4804-4C58-B12D-F28F2924EDA6}"/>
-    <hyperlink ref="J657" r:id="rId401" xr:uid="{8B64007E-A3F5-4EED-B7AF-24E43AA3099B}"/>
-    <hyperlink ref="J663" r:id="rId402" xr:uid="{73D3B250-1293-46F9-A98F-D5275DCCB677}"/>
-    <hyperlink ref="J664" r:id="rId403" xr:uid="{08025720-B248-4D9D-9867-11B00443903E}"/>
-    <hyperlink ref="J665" r:id="rId404" xr:uid="{4A3F0B9A-3B52-4EB1-BFE9-A2EE77AB6329}"/>
-    <hyperlink ref="J666" r:id="rId405" xr:uid="{2B44110D-8CF5-4196-A8F0-0F1B03B15293}"/>
-    <hyperlink ref="J667" r:id="rId406" xr:uid="{7D16965A-3CC8-42E9-87D6-1F426AEC17CD}"/>
-    <hyperlink ref="J668" r:id="rId407" xr:uid="{E809C561-9DC8-4AC6-8792-98B550BCF04D}"/>
-    <hyperlink ref="J669" r:id="rId408" xr:uid="{0E1C44F9-2D12-4D41-9A48-CEEEC303FAC3}"/>
-    <hyperlink ref="J670" r:id="rId409" xr:uid="{D588958A-FD1B-4BE6-B830-9DCD9956517E}"/>
-    <hyperlink ref="J671" r:id="rId410" xr:uid="{32D9B364-423F-4DDA-B473-72678FD637E8}"/>
-    <hyperlink ref="J672" r:id="rId411" xr:uid="{F22A08BA-64F2-4AF7-88D8-DEBA28383492}"/>
-    <hyperlink ref="J673" r:id="rId412" xr:uid="{A0381799-F00D-4419-BF87-690FA7606A13}"/>
-    <hyperlink ref="J674" r:id="rId413" xr:uid="{9640E72A-31FE-434C-B8B1-4B2E6641D3FC}"/>
-    <hyperlink ref="J675" r:id="rId414" xr:uid="{CEE54E1E-92AD-4117-A473-0A62DDA90BB9}"/>
-    <hyperlink ref="J676" r:id="rId415" xr:uid="{5C916FF6-651F-4DF4-A3CB-48405BBC8AE4}"/>
-    <hyperlink ref="J677" r:id="rId416" xr:uid="{5A69BF29-4D56-4C4B-BF95-A743B0D074E6}"/>
-    <hyperlink ref="J679" r:id="rId417" xr:uid="{3B2E2549-E297-4D3C-ADF1-4EF4C05EC156}"/>
-    <hyperlink ref="J682" r:id="rId418" xr:uid="{B7BBACED-A7F4-44B3-BF60-B4259ED7E295}"/>
-    <hyperlink ref="J683" r:id="rId419" xr:uid="{679293C2-D656-4F45-AE5C-ABC8B327FE95}"/>
-    <hyperlink ref="J684" r:id="rId420" xr:uid="{AC116A2F-BAB4-41BF-B821-F4C2FECD64AE}"/>
-    <hyperlink ref="J688" r:id="rId421" xr:uid="{58F01E98-66B9-4B5C-9DB5-F7D922056670}"/>
-    <hyperlink ref="J693" r:id="rId422" xr:uid="{EE95EAC8-1C89-4D8F-8FC2-CCE85619EE0D}"/>
-    <hyperlink ref="J694" r:id="rId423" xr:uid="{96F17937-EAB4-4324-B4D9-FDCE1F518939}"/>
-    <hyperlink ref="J695" r:id="rId424" xr:uid="{6BBAAD75-A08C-45C1-96E2-8F0D2F56B1D1}"/>
-    <hyperlink ref="J696" r:id="rId425" xr:uid="{8A7274E0-5187-4097-B17C-7FC735876E61}"/>
-    <hyperlink ref="J697" r:id="rId426" xr:uid="{3C026A8A-B8C2-4F41-A689-E8FC015D7A0B}"/>
-    <hyperlink ref="J698" r:id="rId427" xr:uid="{8C505027-EA3B-4B03-8CAE-5E34C2307663}"/>
-    <hyperlink ref="J699" r:id="rId428" xr:uid="{F731329C-47DB-479D-A13F-4B79984B7174}"/>
-    <hyperlink ref="J700" r:id="rId429" xr:uid="{E8F095C9-D568-4459-9508-98968312F6B0}"/>
-    <hyperlink ref="J705" r:id="rId430" xr:uid="{35B3288A-0293-47F1-9B3B-C1636F935A26}"/>
-    <hyperlink ref="J708" r:id="rId431" xr:uid="{8D097742-AEB7-4C23-95DB-B17DEA85EC9B}"/>
-    <hyperlink ref="J712" r:id="rId432" xr:uid="{254CA505-1855-4E3B-889E-F6EF5C2621FC}"/>
-    <hyperlink ref="J713" r:id="rId433" xr:uid="{91D7B60D-472E-4AC5-9906-8CCD4C755376}"/>
-    <hyperlink ref="J714" r:id="rId434" xr:uid="{31A65C41-64DA-4D71-89D1-B79CFEFFD4B3}"/>
-    <hyperlink ref="J715" r:id="rId435" xr:uid="{2CA4E74A-1DEA-4510-8037-EF039EDB5514}"/>
-    <hyperlink ref="J718" r:id="rId436" xr:uid="{97905C46-CD02-4956-8DC7-17225C507D47}"/>
-    <hyperlink ref="J720" r:id="rId437" xr:uid="{A67F4D6C-CF23-4783-BB62-662EADF23216}"/>
-    <hyperlink ref="J721" r:id="rId438" xr:uid="{F3CFAE7F-4E31-4AF3-825A-AFB98057E515}"/>
-    <hyperlink ref="J722" r:id="rId439" xr:uid="{813CEFB8-53E3-455F-B4EC-BB5E030C6229}"/>
-    <hyperlink ref="J725" r:id="rId440" xr:uid="{7BF1DA6C-09FA-4F80-9AF7-A0027EB533C2}"/>
-    <hyperlink ref="J726" r:id="rId441" xr:uid="{831AD1D5-735D-4B8F-89E8-212D3CBA1AC8}"/>
-    <hyperlink ref="J728" r:id="rId442" xr:uid="{1E4E580F-ED9B-47FF-BA61-D1C1A95B40D1}"/>
-    <hyperlink ref="J729" r:id="rId443" xr:uid="{28E7323E-8CDC-4CB4-A104-F37A5E469BA9}"/>
-    <hyperlink ref="J736" r:id="rId444" xr:uid="{427FE638-0490-46B1-B757-3D0D4589685E}"/>
-    <hyperlink ref="J738" r:id="rId445" xr:uid="{1A8C31B5-86D7-4075-97DC-599890B37AA8}"/>
-    <hyperlink ref="J739" r:id="rId446" xr:uid="{4706B9F7-337E-4A5A-B698-CD5B833F6597}"/>
-    <hyperlink ref="J740" r:id="rId447" xr:uid="{821A7DCC-9C01-478C-9202-4367F9D8F6B9}"/>
-    <hyperlink ref="J741" r:id="rId448" xr:uid="{CADA4C01-5C49-47D5-9E83-73349B6D1E9C}"/>
-    <hyperlink ref="J742" r:id="rId449" xr:uid="{002DBD8E-E256-4292-A23A-9D8931820D9B}"/>
-    <hyperlink ref="J743" r:id="rId450" xr:uid="{C644BE7C-36EB-424F-8300-EA456F451C3F}"/>
-    <hyperlink ref="J744" r:id="rId451" xr:uid="{06A29A00-FBBA-468F-B8FD-3922C3C2402D}"/>
-    <hyperlink ref="J747" r:id="rId452" xr:uid="{CDF5B424-9757-468C-AD76-9BD4316E3B2E}"/>
-    <hyperlink ref="J748" r:id="rId453" xr:uid="{7EC18904-E039-4590-B073-F2B9D13C1C3D}"/>
-    <hyperlink ref="J757" r:id="rId454" xr:uid="{402A6E31-C10F-4F6E-A06B-A5C8B531C1A1}"/>
-    <hyperlink ref="J758" r:id="rId455" xr:uid="{797B0EF4-4464-4D1D-BAF6-459F516CC684}"/>
-    <hyperlink ref="J759" r:id="rId456" xr:uid="{C33C05C5-C808-4207-9791-7941024B08AC}"/>
-    <hyperlink ref="J760" r:id="rId457" xr:uid="{4CCA4A99-61D4-4BCA-8786-B9AE3A89A685}"/>
-    <hyperlink ref="J761" r:id="rId458" xr:uid="{CF7F9855-292F-4314-AB42-EAB994589464}"/>
-    <hyperlink ref="J762" r:id="rId459" xr:uid="{E60BD6C1-85FB-41A4-B2F1-3E82D8A25A65}"/>
-    <hyperlink ref="J764" r:id="rId460" xr:uid="{8681E188-AC05-44C4-9D67-F2AF6F5F8C89}"/>
-    <hyperlink ref="J765" r:id="rId461" xr:uid="{D031DE21-6381-4BD9-83AF-3D40253BBA8E}"/>
-    <hyperlink ref="J766" r:id="rId462" xr:uid="{8C16F682-B7E6-4F78-BCE3-564C6424919D}"/>
-    <hyperlink ref="J767" r:id="rId463" xr:uid="{FCCF8D71-9A6F-417E-8FC8-86783F7E3F61}"/>
-    <hyperlink ref="J769" r:id="rId464" xr:uid="{61D97CF9-4951-48A3-A64B-082ED02E6087}"/>
-    <hyperlink ref="J770" r:id="rId465" xr:uid="{E8FDA524-DCE5-4FF5-9A0D-2E223C35D412}"/>
-    <hyperlink ref="J772" r:id="rId466" xr:uid="{C6F2F341-F506-4F76-B909-96D92F3E572A}"/>
-    <hyperlink ref="J774" r:id="rId467" xr:uid="{DE5EDAE9-AFB6-45D1-A8E5-1AD943F9F3D6}"/>
-    <hyperlink ref="J778" r:id="rId468" xr:uid="{E821772F-2451-430F-9632-EE3BBBA5E0AD}"/>
-    <hyperlink ref="J781" r:id="rId469" xr:uid="{812E82D2-59D4-45F4-8699-E6623865E45B}"/>
-    <hyperlink ref="J783" r:id="rId470" xr:uid="{E9159806-CF02-4B93-B834-5C92A3FEF201}"/>
-    <hyperlink ref="J784" r:id="rId471" xr:uid="{C1B4345C-0CA0-495E-AC95-DE89C44AB4A1}"/>
-    <hyperlink ref="J785" r:id="rId472" xr:uid="{48DBD3D0-3663-4108-8CE1-144966926348}"/>
-    <hyperlink ref="J788" r:id="rId473" xr:uid="{F67DD9CF-293B-4B70-9C61-C1FD82B14ACE}"/>
-    <hyperlink ref="J789" r:id="rId474" xr:uid="{6F4372F7-E60B-4ED6-BADD-EDB3E4E4DA72}"/>
-    <hyperlink ref="J790" r:id="rId475" xr:uid="{B548C074-B929-40C5-B3EA-C7568EEFB873}"/>
-    <hyperlink ref="J794" r:id="rId476" xr:uid="{B7D7BC20-D69B-4D65-B4B9-BCAF5D18CBA1}"/>
-    <hyperlink ref="J795" r:id="rId477" xr:uid="{FC8588C2-D91C-4E47-9BCD-C56D62D5EEED}"/>
-    <hyperlink ref="J796" r:id="rId478" xr:uid="{5458A8BB-4DE1-4948-99F1-92B4B16800F8}"/>
-    <hyperlink ref="J797" r:id="rId479" xr:uid="{8AFD7B68-A213-4930-B249-77F702EBB834}"/>
-    <hyperlink ref="J799" r:id="rId480" xr:uid="{D1055561-1665-4D99-977F-1AC5E6ADD198}"/>
-    <hyperlink ref="J800" r:id="rId481" xr:uid="{E8E830FE-B18B-4B3C-9641-7BC75E446224}"/>
-    <hyperlink ref="J801" r:id="rId482" xr:uid="{B25305A5-F10C-4892-82DC-B8B3E8634DE4}"/>
-    <hyperlink ref="J802" r:id="rId483" xr:uid="{112A6BD6-15BD-4327-BCCC-6734659D20C3}"/>
-    <hyperlink ref="J803" r:id="rId484" xr:uid="{9019BBC8-FBD8-4C8E-9B94-327D843CDAAB}"/>
-    <hyperlink ref="J804" r:id="rId485" xr:uid="{5EA1446E-3A1B-48AB-AC83-1C22DBC32BA1}"/>
-    <hyperlink ref="J805" r:id="rId486" xr:uid="{8AC0A4F0-5D58-4489-B3D4-7230C32AA7E3}"/>
-    <hyperlink ref="J806" r:id="rId487" xr:uid="{EEDE5897-CA91-4893-B96E-A10862D362E9}"/>
-    <hyperlink ref="J808" r:id="rId488" xr:uid="{DF597B6A-85DC-4E40-88FF-CF6638E17557}"/>
-    <hyperlink ref="J810" r:id="rId489" xr:uid="{1B8AFE25-888E-4E98-8D82-0A03F576F677}"/>
-    <hyperlink ref="J811" r:id="rId490" xr:uid="{3EAD005E-7DB0-4C1F-B869-4463816EC4EF}"/>
-    <hyperlink ref="J812" r:id="rId491" xr:uid="{FD67A3C4-D5D6-4882-8B3C-BED01EA16F65}"/>
-    <hyperlink ref="J813" r:id="rId492" xr:uid="{FA988798-19E7-4D3B-98B4-CC95C4FCF986}"/>
-    <hyperlink ref="J814" r:id="rId493" xr:uid="{80EB0931-E827-436A-847D-0E97709C8F5E}"/>
-    <hyperlink ref="J815" r:id="rId494" xr:uid="{72F92922-22EA-48E7-A354-9864F6CC171F}"/>
-    <hyperlink ref="J816" r:id="rId495" xr:uid="{F94E5BF2-A375-4442-8FB0-4E7B874905F5}"/>
-    <hyperlink ref="J817" r:id="rId496" xr:uid="{5ED591EE-35CD-42C7-BEA6-66CC572E5466}"/>
-    <hyperlink ref="J818" r:id="rId497" xr:uid="{87CFEF52-6570-4DB9-A632-D471E30D04B7}"/>
-    <hyperlink ref="J819" r:id="rId498" xr:uid="{9716C3CC-132E-43D5-A021-5344DE909AD3}"/>
-    <hyperlink ref="J820" r:id="rId499" xr:uid="{FCF51E0E-C89D-4037-A325-971862E65A3F}"/>
-    <hyperlink ref="J821" r:id="rId500" xr:uid="{15CD4932-6B42-422C-9267-52586EF19A00}"/>
-    <hyperlink ref="J822" r:id="rId501" xr:uid="{3F2BDFA9-2595-4F37-83DC-7737F7B61B5E}"/>
-    <hyperlink ref="J825" r:id="rId502" xr:uid="{155BA8F7-7A76-430A-A518-CEF8F919A63D}"/>
-    <hyperlink ref="J826" r:id="rId503" xr:uid="{6329DFBD-AD2E-42E1-A702-0EDD7E9D4D89}"/>
-    <hyperlink ref="J827" r:id="rId504" xr:uid="{849CB292-F846-495C-B312-C5D854918487}"/>
-    <hyperlink ref="J828" r:id="rId505" xr:uid="{38B89074-428B-462F-893A-5DC3023F8061}"/>
-    <hyperlink ref="J831" r:id="rId506" xr:uid="{D652B5FD-134B-43D3-899B-149E81346490}"/>
-    <hyperlink ref="J832" r:id="rId507" xr:uid="{C525FE36-2F88-4160-B02F-B7447D0821F4}"/>
-    <hyperlink ref="J833" r:id="rId508" xr:uid="{07B28EE3-8F75-459B-B102-96491C5B0D7C}"/>
-    <hyperlink ref="J836" r:id="rId509" xr:uid="{F6A53C2A-B682-4560-A696-174E9D98C47B}"/>
-    <hyperlink ref="J837" r:id="rId510" xr:uid="{A162EE8E-E284-4EE7-AABE-EFFF748F09F5}"/>
-    <hyperlink ref="J838" r:id="rId511" xr:uid="{94D8989D-18F8-44E4-8696-06232CBCC4D2}"/>
-    <hyperlink ref="J839" r:id="rId512" xr:uid="{5ABBBD89-0094-4B0F-8103-6F608C757EB9}"/>
-    <hyperlink ref="J840" r:id="rId513" xr:uid="{46096829-F57C-4155-95C7-47A434583617}"/>
-    <hyperlink ref="J841" r:id="rId514" xr:uid="{33AF1E85-1A20-4265-897C-34C6EE4E3094}"/>
-    <hyperlink ref="J842" r:id="rId515" xr:uid="{7CCB494C-C4A2-481B-8D60-AC55EEB0EE05}"/>
-    <hyperlink ref="J843" r:id="rId516" xr:uid="{172C76A9-FA92-44AE-8BD1-2566EFE2C3BC}"/>
-    <hyperlink ref="J844" r:id="rId517" xr:uid="{70971C91-63A5-452B-A767-44A549761681}"/>
-    <hyperlink ref="J847" r:id="rId518" xr:uid="{858C919C-E2A2-42E2-9EC4-B9A4551DE481}"/>
-    <hyperlink ref="J848" r:id="rId519" xr:uid="{E7EDC118-7CBB-4DCA-A64A-9968D7240A03}"/>
-    <hyperlink ref="J850" r:id="rId520" xr:uid="{3077F7AF-2F63-42B0-A6C9-1A186D6E0CEC}"/>
-    <hyperlink ref="J852" r:id="rId521" xr:uid="{45559466-C7A1-4DEA-B089-D09DAFC84158}"/>
-    <hyperlink ref="J853" r:id="rId522" xr:uid="{3F8D3BDD-0337-4333-978D-CA872947D934}"/>
-    <hyperlink ref="J856" r:id="rId523" xr:uid="{4D2C1894-3C98-47B9-A91E-0806C85CB876}"/>
-    <hyperlink ref="J858" r:id="rId524" xr:uid="{F405549B-420F-430A-9DD7-5A12202B1ED4}"/>
-    <hyperlink ref="J861" r:id="rId525" xr:uid="{A8A58825-AD6F-456E-A649-62FB425F5C0C}"/>
-    <hyperlink ref="J862" r:id="rId526" xr:uid="{DD1C9E9D-16B8-4BE5-8BA9-F67A0C16316D}"/>
-    <hyperlink ref="J863" r:id="rId527" xr:uid="{626F6273-126E-4018-9F6B-43D8138F8562}"/>
-    <hyperlink ref="J865" r:id="rId528" xr:uid="{3C71FA9B-29AA-4D79-8B97-9FC3B587D3C5}"/>
-    <hyperlink ref="J866" r:id="rId529" xr:uid="{0613F258-05FA-4761-80E7-466AE6CCBA43}"/>
-    <hyperlink ref="J867" r:id="rId530" xr:uid="{DB26C1E2-2251-4A79-A79E-9BC52E2E5A48}"/>
-    <hyperlink ref="J868" r:id="rId531" xr:uid="{D6A82AF6-47CA-4435-BAF5-D4CD9B68F2BF}"/>
-    <hyperlink ref="J870" r:id="rId532" xr:uid="{250688BB-BC57-4C3A-A679-3D99B5C5A14A}"/>
-    <hyperlink ref="J871" r:id="rId533" xr:uid="{1DC8109E-3C4F-4828-9871-6851FCD2D111}"/>
-    <hyperlink ref="J872" r:id="rId534" xr:uid="{F0D27D82-9E65-4178-B2AB-7A5DF4FFCC31}"/>
-    <hyperlink ref="J873" r:id="rId535" xr:uid="{8D7B8624-86DB-4358-B38D-843CFBEA8638}"/>
-    <hyperlink ref="J875" r:id="rId536" xr:uid="{6AE8089B-27F8-46F4-B968-FE77468FDEC5}"/>
-    <hyperlink ref="J877" r:id="rId537" xr:uid="{4D97D9D8-2A3E-4236-8361-1C18F045F886}"/>
-    <hyperlink ref="J878" r:id="rId538" xr:uid="{4FFB1820-7FA2-4263-B39A-DA6B95860349}"/>
-    <hyperlink ref="J880" r:id="rId539" xr:uid="{C9A28E94-BEF1-4BAE-B4E4-7B73E88EA585}"/>
-    <hyperlink ref="J882" r:id="rId540" xr:uid="{4A7D7E96-5B38-4203-AA28-8B610B440CF7}"/>
-    <hyperlink ref="J883" r:id="rId541" xr:uid="{130DD4F4-9B41-4BCF-9AF0-000056D2ECD8}"/>
-    <hyperlink ref="J884" r:id="rId542" xr:uid="{D4BF89EE-5539-48E6-8097-C0CC584E7B43}"/>
-    <hyperlink ref="J885" r:id="rId543" xr:uid="{9127F019-80F7-4022-80EE-691B9E08D62B}"/>
-    <hyperlink ref="J886" r:id="rId544" xr:uid="{CCFA0CFC-8ABA-4FAC-84A7-4C08444C22BF}"/>
-    <hyperlink ref="J888" r:id="rId545" xr:uid="{ACEC74C1-E58E-47ED-BAF4-CA4112D20CCD}"/>
-    <hyperlink ref="J889" r:id="rId546" xr:uid="{4353345C-FEEC-40A4-B308-AB30B93A5DA8}"/>
-    <hyperlink ref="J893" r:id="rId547" xr:uid="{80F97F30-029A-4A44-BC35-2BB5B8F10DE1}"/>
-    <hyperlink ref="J894" r:id="rId548" xr:uid="{161BCA5B-32C9-4538-AFD5-1499E7BEDC7B}"/>
-    <hyperlink ref="J895" r:id="rId549" xr:uid="{70048653-86E6-48C4-8F5C-5C6B1FF69C45}"/>
-    <hyperlink ref="J896" r:id="rId550" xr:uid="{C0411C9D-6B1B-423F-A6FB-4E82A0EE59BE}"/>
-    <hyperlink ref="J897" r:id="rId551" xr:uid="{4A117F9D-382A-46FB-81FA-BD127C359D69}"/>
-    <hyperlink ref="J899" r:id="rId552" xr:uid="{CEC56108-4368-4293-AE7B-4EB1EB27356E}"/>
-    <hyperlink ref="J900" r:id="rId553" xr:uid="{C389ADED-7E7B-427E-8592-529F29B2C829}"/>
-    <hyperlink ref="J905" r:id="rId554" xr:uid="{3655A4E5-EC87-4D77-9A6D-76424015BB83}"/>
-    <hyperlink ref="J906" r:id="rId555" xr:uid="{A560FE09-7A3B-4076-BCDD-97A161E1CC2A}"/>
-    <hyperlink ref="J907" r:id="rId556" xr:uid="{2980BDC5-81AA-4C7C-8C9D-C60BE98E3953}"/>
-    <hyperlink ref="J908" r:id="rId557" xr:uid="{F589D8C8-5865-444C-B7D9-658A62EB572B}"/>
-    <hyperlink ref="J909" r:id="rId558" xr:uid="{282FF2C7-2659-4585-BEF3-6D8F3C2BB069}"/>
-    <hyperlink ref="J910" r:id="rId559" xr:uid="{A06E3571-5A94-4F3F-9363-C74EDB576629}"/>
-    <hyperlink ref="J911" r:id="rId560" xr:uid="{EFB7CF6B-C8C0-4834-B8B8-B7283F360C6B}"/>
-    <hyperlink ref="J912" r:id="rId561" xr:uid="{4AB64ACD-44AF-4877-87B9-48580EBBCACA}"/>
-    <hyperlink ref="J913" r:id="rId562" xr:uid="{50494670-CB59-41F3-B4F0-0D5193461D4A}"/>
-    <hyperlink ref="J914" r:id="rId563" xr:uid="{83EE12FA-8435-46EA-9DF4-ACBE8DD124E6}"/>
-    <hyperlink ref="J915" r:id="rId564" xr:uid="{2675A071-3722-4BFD-99A1-BD9AA48BB1BD}"/>
-    <hyperlink ref="J916" r:id="rId565" xr:uid="{2484D753-5961-4447-99DA-349B1D5336DA}"/>
-    <hyperlink ref="J918" r:id="rId566" xr:uid="{425EAA8B-20A7-43CA-8312-21400A9E1940}"/>
-    <hyperlink ref="J919" r:id="rId567" xr:uid="{B910B821-3CDF-409C-B03F-EC6F0F31A8FA}"/>
-    <hyperlink ref="J922" r:id="rId568" xr:uid="{B22B4B78-3E3D-4B1F-AE0A-EDF00374778B}"/>
-    <hyperlink ref="J923" r:id="rId569" xr:uid="{C478C6A3-59B9-4501-8D8E-7AB2F6573094}"/>
-    <hyperlink ref="J925" r:id="rId570" xr:uid="{E13A8370-9FDE-4102-8E6B-B25A20201097}"/>
-    <hyperlink ref="J926" r:id="rId571" xr:uid="{254970DB-3A2C-4F14-B9D0-8C649B8ADA86}"/>
-    <hyperlink ref="J928" r:id="rId572" xr:uid="{147ED712-32D2-406F-B0EB-1CBCC92A7C6B}"/>
-    <hyperlink ref="J929" r:id="rId573" xr:uid="{D5328DFC-C18D-4FF6-B6F8-2AA9712F3897}"/>
-    <hyperlink ref="J930" r:id="rId574" xr:uid="{5F9BBDEF-CC54-4E8D-B260-A015AD0833CF}"/>
-    <hyperlink ref="J931" r:id="rId575" xr:uid="{D83CD9EA-DD6F-4481-A70F-FEAE83F496D9}"/>
-    <hyperlink ref="J932" r:id="rId576" xr:uid="{8688A1E6-3061-41A3-A24F-B1162F7BAAB7}"/>
-    <hyperlink ref="J933" r:id="rId577" xr:uid="{D7229E7C-4E4D-4CEA-98A7-A90B2E18B763}"/>
-    <hyperlink ref="J935" r:id="rId578" xr:uid="{0CBFE577-B157-46B1-84C0-BA89D58DC289}"/>
-    <hyperlink ref="J940" r:id="rId579" xr:uid="{D38AC36E-148A-4CF3-8747-FDC8BE73BAEF}"/>
-    <hyperlink ref="J941" r:id="rId580" xr:uid="{F2713C9B-3096-4DA4-A26F-3064BFF6DEF4}"/>
-    <hyperlink ref="J942" r:id="rId581" xr:uid="{FF53AB07-BBEE-4C0B-912A-235C86C1B10D}"/>
-    <hyperlink ref="J943" r:id="rId582" xr:uid="{D8A30DFF-0133-4A8B-8796-91AE3D08E8DE}"/>
-    <hyperlink ref="J944" r:id="rId583" xr:uid="{50CC9950-DF70-4ACA-957A-0072AD4C7466}"/>
-    <hyperlink ref="J946" r:id="rId584" xr:uid="{0BF73612-46B5-49BF-AAE0-02FF78F7E34D}"/>
-    <hyperlink ref="J947" r:id="rId585" xr:uid="{5FBDF20E-B6DC-4F62-9CE8-18191A23E233}"/>
-    <hyperlink ref="J948" r:id="rId586" xr:uid="{FEB53315-9297-4228-A236-20773C902696}"/>
-    <hyperlink ref="J949" r:id="rId587" xr:uid="{4AF94908-C50D-444D-9B71-6583754570C8}"/>
-    <hyperlink ref="J950" r:id="rId588" xr:uid="{0420756D-18EC-4D5F-AB11-C4F7C1618EFA}"/>
-    <hyperlink ref="J952" r:id="rId589" xr:uid="{0C8E7A7D-128D-486E-AA18-9D2C44060D78}"/>
-    <hyperlink ref="J953" r:id="rId590" xr:uid="{1E036446-38CE-4E82-B6AD-BC40C1E98481}"/>
-    <hyperlink ref="J954" r:id="rId591" xr:uid="{79C03424-F894-4D4C-818B-EB2366766457}"/>
-    <hyperlink ref="J955" r:id="rId592" xr:uid="{F9E1DBBF-BEFB-4C39-8029-D8C77978D43E}"/>
-    <hyperlink ref="J956" r:id="rId593" xr:uid="{E7F051F9-023D-4809-AE6F-E57A8CA65668}"/>
-    <hyperlink ref="J958" r:id="rId594" xr:uid="{008FBCF3-66AA-40A0-BD9B-1D2653D1400F}"/>
-    <hyperlink ref="J962" r:id="rId595" xr:uid="{13F8AA47-754B-4D83-8AFB-BF493ECCE6B7}"/>
-    <hyperlink ref="J963" r:id="rId596" xr:uid="{8636001F-62ED-4D6B-AA3A-C500D0663DC4}"/>
-    <hyperlink ref="J965" r:id="rId597" xr:uid="{19F0592F-070D-4DB4-B5D4-ACDF3174272F}"/>
-    <hyperlink ref="J968" r:id="rId598" xr:uid="{FDF34C7F-A83B-4153-A768-9DB41E214011}"/>
-    <hyperlink ref="J969" r:id="rId599" xr:uid="{12903847-0680-4D1F-8DDD-3409AC4EB9FD}"/>
-    <hyperlink ref="J971" r:id="rId600" xr:uid="{96F173C6-BF89-4B95-9223-25EED504BE4A}"/>
-    <hyperlink ref="J973" r:id="rId601" xr:uid="{D420230D-1A99-47B3-B0BB-C02FEFA6758B}"/>
-    <hyperlink ref="J974" r:id="rId602" xr:uid="{89FCE9E8-3038-43D7-B252-B7E3F3E3140C}"/>
-    <hyperlink ref="J975" r:id="rId603" xr:uid="{377CAF38-3CF1-453A-8D65-F7E1BB33DA3F}"/>
-    <hyperlink ref="J976" r:id="rId604" xr:uid="{EE8FBC19-F94C-44DD-954B-B78E9B0D7657}"/>
-    <hyperlink ref="J977" r:id="rId605" xr:uid="{83704EC0-BBFD-4CA6-B899-B3D9438EC073}"/>
-    <hyperlink ref="J981" r:id="rId606" xr:uid="{76BA06C1-AE61-4032-A454-089BB5C1890F}"/>
-    <hyperlink ref="J984" r:id="rId607" xr:uid="{88541482-4781-4E7D-957E-3F2F0A9DB0B4}"/>
-    <hyperlink ref="J986" r:id="rId608" xr:uid="{7B8F2528-EA25-4345-B2E7-35B969F40089}"/>
-    <hyperlink ref="J990" r:id="rId609" xr:uid="{821B2213-B249-47D6-B57C-1D483C68AECE}"/>
-    <hyperlink ref="J991" r:id="rId610" xr:uid="{6E1BCF06-3591-42AF-AADD-BCCB39D1DFC5}"/>
-    <hyperlink ref="J996" r:id="rId611" xr:uid="{FD8085CC-B219-42A7-933B-C2FE65F34EB2}"/>
-    <hyperlink ref="J997" r:id="rId612" xr:uid="{E4BED850-EAEA-4D60-B292-ADD214412205}"/>
-    <hyperlink ref="J999" r:id="rId613" xr:uid="{6BF52333-0D1D-428C-BEE3-0A456F0C97E2}"/>
-    <hyperlink ref="J1000" r:id="rId614" xr:uid="{30303EB1-8F17-4368-B241-90D09216816C}"/>
-    <hyperlink ref="J1003" r:id="rId615" xr:uid="{C00D3C92-EF2C-42A9-9CB8-787A23D76B91}"/>
-    <hyperlink ref="J1004" r:id="rId616" xr:uid="{B0B582E0-2A3B-4201-BF4B-7F95A1E9AFFD}"/>
-    <hyperlink ref="J1005" r:id="rId617" xr:uid="{8316377F-E62A-433D-A8F4-9DCB26FD7BF1}"/>
-    <hyperlink ref="J1006" r:id="rId618" xr:uid="{9323B583-0BD3-4A82-9CB1-8BFBB42BB903}"/>
-    <hyperlink ref="J1007" r:id="rId619" xr:uid="{3B8AB74C-2177-4B42-91CA-A357716E5A2B}"/>
-    <hyperlink ref="J1008" r:id="rId620" xr:uid="{137361EB-5E72-4759-8033-413CA567FDC1}"/>
-    <hyperlink ref="J1009" r:id="rId621" xr:uid="{FDBA1E05-F2D2-456E-AE00-F8BDA5F6AD8E}"/>
-    <hyperlink ref="J1011" r:id="rId622" xr:uid="{72785E54-E4AE-4C83-ACB7-E2E30F3F515C}"/>
-    <hyperlink ref="J1012" r:id="rId623" xr:uid="{2CB5E188-0621-42EB-A48C-2E315F7DF876}"/>
-    <hyperlink ref="J1016" r:id="rId624" xr:uid="{262F5A3A-3DD9-43EB-AF85-EB2F9B6313BE}"/>
-    <hyperlink ref="J1019" r:id="rId625" xr:uid="{50FB8081-BAFA-4B5F-8982-CDCBB589D80D}"/>
-    <hyperlink ref="J1020" r:id="rId626" xr:uid="{ACD1EEAB-4E44-4138-B1D2-21AACD19A1EC}"/>
-    <hyperlink ref="J1023" r:id="rId627" xr:uid="{EFDA9630-344B-481E-AC8B-3C79220A4402}"/>
-    <hyperlink ref="J1024" r:id="rId628" xr:uid="{4C0D9995-35A0-491A-9267-1CDDDF09EF44}"/>
-    <hyperlink ref="J1025" r:id="rId629" xr:uid="{B4934331-D9E4-4DDC-B314-E78C8E96BD6F}"/>
-    <hyperlink ref="J1026" r:id="rId630" xr:uid="{4501FB5C-CFF6-4AAC-B6DC-5A5C8B886C7E}"/>
-    <hyperlink ref="J1027" r:id="rId631" xr:uid="{213500AB-EEF5-492B-8BCC-4F047BDE49D1}"/>
-    <hyperlink ref="J1028" r:id="rId632" xr:uid="{EBDF4ECE-0B52-419A-A875-D7EFD4C6E865}"/>
-    <hyperlink ref="J1030" r:id="rId633" xr:uid="{091C6978-0F85-4733-892F-992F7248F035}"/>
-    <hyperlink ref="J1033" r:id="rId634" xr:uid="{E38660A4-5285-4EAE-838D-02EB2A703905}"/>
-    <hyperlink ref="J1034" r:id="rId635" xr:uid="{AB5052E9-876B-43A9-A095-7D63909A6B92}"/>
-    <hyperlink ref="J1036" r:id="rId636" xr:uid="{7BF66504-6FC6-4459-9C21-62AB52EA8B77}"/>
-    <hyperlink ref="J1037" r:id="rId637" xr:uid="{16C9D2D7-A25F-4395-AAE9-3DEB42B7C799}"/>
-    <hyperlink ref="J1041" r:id="rId638" xr:uid="{3D7590A7-EFEC-405F-9900-32B27C3ABE4B}"/>
-    <hyperlink ref="J1042" r:id="rId639" xr:uid="{24E0B837-B19B-4A8E-A3F2-440BE94722B8}"/>
-    <hyperlink ref="J1043" r:id="rId640" xr:uid="{D4D7C177-BC50-4AF9-B8BA-C12ABC4BBBFB}"/>
-    <hyperlink ref="J1044" r:id="rId641" xr:uid="{AD46BC56-73E4-4A6D-B5C0-AD5FEAA9CA0D}"/>
-    <hyperlink ref="J1046" r:id="rId642" xr:uid="{FC2D60AB-723C-40B1-B103-16AFF7D1B2F2}"/>
-    <hyperlink ref="J1047" r:id="rId643" xr:uid="{EDB9DDA4-45CE-4EDF-A924-55457A44CB36}"/>
-    <hyperlink ref="J1051" r:id="rId644" xr:uid="{DC8598D3-17AC-4B9D-BE95-BC6A20E53463}"/>
-    <hyperlink ref="J1052" r:id="rId645" xr:uid="{4CB3192F-BA4C-49EB-9B6F-7AF65DF75731}"/>
-    <hyperlink ref="J1054" r:id="rId646" xr:uid="{ACFDF7F1-5D3E-411C-A2CF-2436105632BD}"/>
-    <hyperlink ref="J1056" r:id="rId647" xr:uid="{37E56E31-6FAE-4A99-BC35-420BD468F296}"/>
-    <hyperlink ref="J1064" r:id="rId648" xr:uid="{26E51AB1-3D85-4003-AAF5-6DE4120FA9DD}"/>
-    <hyperlink ref="J1065" r:id="rId649" xr:uid="{53E0FE8D-21E6-4FED-98F9-61ACD5164706}"/>
-    <hyperlink ref="J1066" r:id="rId650" xr:uid="{89648FFF-A47B-4F0C-A828-1E4D5023FE26}"/>
-    <hyperlink ref="J1067" r:id="rId651" xr:uid="{AC978C55-654F-4FDC-8893-1CA7DEE8D5E9}"/>
-    <hyperlink ref="J1068" r:id="rId652" xr:uid="{5C508104-4327-470B-A324-383565E6746A}"/>
-    <hyperlink ref="J1069" r:id="rId653" xr:uid="{3F6B7438-4165-4FF4-B9C0-61B2AF750655}"/>
-    <hyperlink ref="J1070" r:id="rId654" xr:uid="{7A55F298-B639-4805-BB72-F22B0C4F0E5C}"/>
-    <hyperlink ref="J1071" r:id="rId655" xr:uid="{252B02A6-586B-4169-85FD-C2B1B2D03DC7}"/>
-    <hyperlink ref="J1072" r:id="rId656" xr:uid="{B26A08D6-0874-4412-BCF7-69665C2165CA}"/>
-    <hyperlink ref="J1073" r:id="rId657" xr:uid="{EEA8429A-BDA6-4654-8AAA-DD3E22E46EEF}"/>
-    <hyperlink ref="J1076" r:id="rId658" xr:uid="{0B78D5BB-5A32-4E03-BEDF-D4EE03E5141E}"/>
-    <hyperlink ref="J1077" r:id="rId659" xr:uid="{0C5093D4-C399-4EF2-A0B8-3F9D8B3810B1}"/>
-    <hyperlink ref="J1078" r:id="rId660" xr:uid="{27D98F89-77C2-407D-B850-E7700D16A094}"/>
-    <hyperlink ref="J1080" r:id="rId661" xr:uid="{4D629553-F767-41DE-976A-0A9FE89CE845}"/>
+    <hyperlink ref="J5" r:id="rId1" xr:uid="{92437417-C162-4407-B939-8502230DA785}"/>
+    <hyperlink ref="J7" r:id="rId2" xr:uid="{26AEEE2C-E5B6-42B5-90C1-04227B17D6AF}"/>
+    <hyperlink ref="J8" r:id="rId3" xr:uid="{D49D5EC8-795E-4046-B20E-9669D0A8181A}"/>
+    <hyperlink ref="J10" r:id="rId4" xr:uid="{83948578-227D-4D97-B99E-B77786EBA10F}"/>
+    <hyperlink ref="J13" r:id="rId5" xr:uid="{5DEFDF45-6659-42C9-94EF-F6BB1C55BD9C}"/>
+    <hyperlink ref="J14" r:id="rId6" xr:uid="{756591F7-E0F9-4FBF-BD65-F6D7B2F6E5F0}"/>
+    <hyperlink ref="J17" r:id="rId7" xr:uid="{A859291C-3010-4A97-A6FF-F979357B83AB}"/>
+    <hyperlink ref="J19" r:id="rId8" xr:uid="{9E78EEE4-9D53-4F7C-A2A6-4FF64D32EA0A}"/>
+    <hyperlink ref="J20" r:id="rId9" xr:uid="{20F49E54-974B-4220-ABDB-60377E4663FD}"/>
+    <hyperlink ref="J21" r:id="rId10" xr:uid="{CF9A1B77-60F1-4E50-A7FB-AF14BACAF1CD}"/>
+    <hyperlink ref="J24" r:id="rId11" xr:uid="{FC085762-1846-46D2-A95C-6C99F974F96B}"/>
+    <hyperlink ref="J25" r:id="rId12" xr:uid="{22C851C9-7C13-4FB6-B291-FC5D904ACD33}"/>
+    <hyperlink ref="J26" r:id="rId13" xr:uid="{F12BAA40-8111-461D-9D3F-16F4AD65F9F5}"/>
+    <hyperlink ref="J27" r:id="rId14" xr:uid="{2DD0DB41-8A2A-4DD1-95C3-A0852E1B8157}"/>
+    <hyperlink ref="J29" r:id="rId15" xr:uid="{FC6269E0-3064-4CEE-BDB9-68014BAA4C41}"/>
+    <hyperlink ref="J30" r:id="rId16" xr:uid="{629C2A47-25F3-4D93-952B-1DAB9C08EF54}"/>
+    <hyperlink ref="J31" r:id="rId17" xr:uid="{05B5CFBA-4D4F-45C3-85D6-E9ED81DA2C6B}"/>
+    <hyperlink ref="J34" r:id="rId18" xr:uid="{56D36681-F534-48F5-AC68-F01850D3FD84}"/>
+    <hyperlink ref="J35" r:id="rId19" xr:uid="{7F796C36-BA41-4EE5-B520-6B29D1E3311A}"/>
+    <hyperlink ref="J36" r:id="rId20" xr:uid="{9B3F581D-2B42-44E8-A484-D64A8F3116CC}"/>
+    <hyperlink ref="J37" r:id="rId21" xr:uid="{2543D87C-27CF-45C2-896C-191ABE8CED03}"/>
+    <hyperlink ref="J38" r:id="rId22" xr:uid="{5CDD5312-3E2E-433C-BD33-079142D95D75}"/>
+    <hyperlink ref="J46" r:id="rId23" xr:uid="{D91CA944-C73D-4C9C-9B50-8124FCF58052}"/>
+    <hyperlink ref="J47" r:id="rId24" xr:uid="{5860E774-3C03-4C96-BFC6-DD8AE826BCE1}"/>
+    <hyperlink ref="J48" r:id="rId25" xr:uid="{9A640ECD-4F99-4C47-948D-F0AA1CD2A267}"/>
+    <hyperlink ref="J49" r:id="rId26" xr:uid="{E129C2B1-E095-480A-A4E1-7C534C42A9CF}"/>
+    <hyperlink ref="J50" r:id="rId27" xr:uid="{E0F98824-C50E-414E-9C03-663AF059A888}"/>
+    <hyperlink ref="J52" r:id="rId28" xr:uid="{788740A4-2052-42FC-B0C5-A3B2DE60E936}"/>
+    <hyperlink ref="J53" r:id="rId29" xr:uid="{78455C3F-4C69-49A4-8546-7DEA58B8FFFB}"/>
+    <hyperlink ref="J54" r:id="rId30" xr:uid="{942AE54D-1800-4ADB-B9D4-BC76B0A1F274}"/>
+    <hyperlink ref="J56" r:id="rId31" xr:uid="{67D262B9-20F8-4F31-B3A0-FA9AC6B54119}"/>
+    <hyperlink ref="J59" r:id="rId32" xr:uid="{B41446DB-DF6F-4775-A1F3-217C6D17F8E8}"/>
+    <hyperlink ref="J61" r:id="rId33" xr:uid="{547C3393-E847-47B2-B2EB-048400DAB71F}"/>
+    <hyperlink ref="J62" r:id="rId34" xr:uid="{57A326C9-BD1E-40E6-9241-E75EFAB9178D}"/>
+    <hyperlink ref="J63" r:id="rId35" xr:uid="{D628055A-6A4B-41FD-9A45-40B54FAEE825}"/>
+    <hyperlink ref="J64" r:id="rId36" xr:uid="{35BE325D-9ABA-421C-A34E-511F116BE390}"/>
+    <hyperlink ref="J69" r:id="rId37" xr:uid="{EA711594-2C02-4B52-8737-AC838596E8FD}"/>
+    <hyperlink ref="J71" r:id="rId38" xr:uid="{69D991D3-C3CD-486E-A9A0-8B52C20BB29A}"/>
+    <hyperlink ref="J72" r:id="rId39" xr:uid="{678D66D4-4B5A-4D74-8E64-BEF075FC1AB2}"/>
+    <hyperlink ref="J73" r:id="rId40" xr:uid="{F9A1CB24-6779-438B-B87D-FC72482C657F}"/>
+    <hyperlink ref="J74" r:id="rId41" xr:uid="{F4BF7095-840E-4227-88FE-21B78E828F7C}"/>
+    <hyperlink ref="J75" r:id="rId42" xr:uid="{A0B92F19-97C2-4232-9038-BBCF5A551782}"/>
+    <hyperlink ref="J76" r:id="rId43" xr:uid="{203D9398-7300-4C80-B2F3-567884559611}"/>
+    <hyperlink ref="J78" r:id="rId44" xr:uid="{CB90CCAE-8AEF-4183-B005-551DFE6E6E50}"/>
+    <hyperlink ref="J80" r:id="rId45" xr:uid="{6B6582BC-9216-4C0B-8B47-689125A44AE4}"/>
+    <hyperlink ref="J86" r:id="rId46" xr:uid="{C5F4C605-E702-40E6-B5BE-C394EDE6CA7C}"/>
+    <hyperlink ref="J88" r:id="rId47" xr:uid="{A682507D-130E-4915-BDAC-A00C1B063264}"/>
+    <hyperlink ref="J89" r:id="rId48" xr:uid="{7684C8C7-7A10-4726-8ABB-E7E77FB6BDC7}"/>
+    <hyperlink ref="J90" r:id="rId49" xr:uid="{9C7AD19C-2163-4911-AB77-33D2D92CE4BA}"/>
+    <hyperlink ref="J92" r:id="rId50" xr:uid="{4C6574FA-88C6-48A0-86C0-6597EF90BAA7}"/>
+    <hyperlink ref="J94" r:id="rId51" xr:uid="{8CC0E2F8-152C-4F49-B0E5-7351AFE4B3C5}"/>
+    <hyperlink ref="J95" r:id="rId52" xr:uid="{6EFCED49-87B5-43F6-BF91-5972A3E15AF8}"/>
+    <hyperlink ref="J96" r:id="rId53" xr:uid="{2E82CEC2-A206-42FA-9191-A0E7E12D4B01}"/>
+    <hyperlink ref="J101" r:id="rId54" xr:uid="{34DAEA9D-744C-495E-9F94-CAF6592EB02E}"/>
+    <hyperlink ref="J103" r:id="rId55" xr:uid="{1E0F2CFB-6433-4704-B9FA-B5CEAD605FEE}"/>
+    <hyperlink ref="J104" r:id="rId56" xr:uid="{F93C7C5A-5654-402A-B443-0E98A28E0B41}"/>
+    <hyperlink ref="J105" r:id="rId57" xr:uid="{2B01E8A5-60CE-490E-A586-22BB51C418D3}"/>
+    <hyperlink ref="J106" r:id="rId58" xr:uid="{45A5EACE-D38D-43C1-AC42-91C517201269}"/>
+    <hyperlink ref="J107" r:id="rId59" xr:uid="{F39AB62B-AE19-405B-BA12-72D45CC0D677}"/>
+    <hyperlink ref="J109" r:id="rId60" xr:uid="{D6C2E4B0-2147-4B62-86D1-8E3D3AB3B912}"/>
+    <hyperlink ref="J110" r:id="rId61" xr:uid="{DA58BAB4-1632-442E-BC36-0D1D8559A32D}"/>
+    <hyperlink ref="J111" r:id="rId62" xr:uid="{4A9EF153-AA0B-463D-A76B-7D79097497E2}"/>
+    <hyperlink ref="J112" r:id="rId63" xr:uid="{59ED1730-7546-4FA6-89C8-C663C9D6A2A6}"/>
+    <hyperlink ref="J113" r:id="rId64" xr:uid="{4A0FA50F-B98C-4BC5-B8D3-DBA735EA4D1B}"/>
+    <hyperlink ref="J114" r:id="rId65" xr:uid="{F6B483B2-F07F-4DAF-8FBF-1810B5AEA7B9}"/>
+    <hyperlink ref="J116" r:id="rId66" xr:uid="{80434B5A-66F6-48AB-B5D5-4D9EB079E634}"/>
+    <hyperlink ref="J117" r:id="rId67" xr:uid="{94006EFE-F0CF-49CC-A818-8E6C9F6B3FAD}"/>
+    <hyperlink ref="J118" r:id="rId68" xr:uid="{49A98537-B042-46E3-ACC2-CAD6E2A5BC8B}"/>
+    <hyperlink ref="J119" r:id="rId69" xr:uid="{19CD9698-358A-4013-BC93-B8F5818390C9}"/>
+    <hyperlink ref="J120" r:id="rId70" xr:uid="{F28911F4-EAB1-41F8-95B9-CCDA3B353EC6}"/>
+    <hyperlink ref="J121" r:id="rId71" xr:uid="{728DF57D-FAEF-4D76-9556-CA8400757D93}"/>
+    <hyperlink ref="J124" r:id="rId72" xr:uid="{EE9322D3-0761-4F49-AC1A-D65352B5221C}"/>
+    <hyperlink ref="J128" r:id="rId73" xr:uid="{CCB131B6-9611-4CCC-9516-C80F8DFD71D5}"/>
+    <hyperlink ref="J129" r:id="rId74" xr:uid="{232A4D63-11BC-445D-A31A-E38D756BDA75}"/>
+    <hyperlink ref="J132" r:id="rId75" xr:uid="{063ABC51-16F5-48EF-9152-F045B3D7E384}"/>
+    <hyperlink ref="J134" r:id="rId76" xr:uid="{626B0E99-536B-48BA-BFF2-645E8211F6B7}"/>
+    <hyperlink ref="J135" r:id="rId77" xr:uid="{3CDA2746-F242-4C41-B536-1811C2FAD062}"/>
+    <hyperlink ref="J136" r:id="rId78" xr:uid="{46DE5865-C53F-43DC-B158-B3E7A2FB0AEF}"/>
+    <hyperlink ref="J140" r:id="rId79" xr:uid="{B23F7340-9AE1-41BC-8EA1-72AD0C52DE27}"/>
+    <hyperlink ref="J142" r:id="rId80" xr:uid="{EF3E3E3D-71AF-414B-B2DD-093EC3E01C3C}"/>
+    <hyperlink ref="J143" r:id="rId81" xr:uid="{F456F277-1F98-4DC2-9C0B-9BEAF2035FBA}"/>
+    <hyperlink ref="J144" r:id="rId82" xr:uid="{5387FF9D-EDA3-4EF6-A1A6-5594FA8284E9}"/>
+    <hyperlink ref="J145" r:id="rId83" xr:uid="{1E074B4A-2FC9-43FD-8FF1-0E4EC1A7A380}"/>
+    <hyperlink ref="J147" r:id="rId84" xr:uid="{8AC4F922-23CB-4B31-8E97-BA331F849B18}"/>
+    <hyperlink ref="J149" r:id="rId85" xr:uid="{3A387EE6-1F42-4188-B70F-9A7076F3066A}"/>
+    <hyperlink ref="J150" r:id="rId86" xr:uid="{13629192-90E7-4CD4-8A5C-92FF6A3D82F0}"/>
+    <hyperlink ref="J151" r:id="rId87" xr:uid="{A437D993-4FF7-402B-99FB-0CE13F319509}"/>
+    <hyperlink ref="J152" r:id="rId88" xr:uid="{EEAA4EFE-2A15-4BC7-B984-C8CACFC24CFE}"/>
+    <hyperlink ref="J153" r:id="rId89" xr:uid="{8263B751-BBEF-498B-8658-5562C15E00EC}"/>
+    <hyperlink ref="J154" r:id="rId90" xr:uid="{2418A966-119A-44EC-A67C-8C0C979EFDAE}"/>
+    <hyperlink ref="J155" r:id="rId91" xr:uid="{AD1F80F2-59F7-4C37-AB14-B57DC4BEE636}"/>
+    <hyperlink ref="J156" r:id="rId92" xr:uid="{E8DB16A1-DD02-45D5-8C43-5430F878F839}"/>
+    <hyperlink ref="J159" r:id="rId93" xr:uid="{7E83DA4E-5360-4DF9-B193-12AFCD68A822}"/>
+    <hyperlink ref="J160" r:id="rId94" xr:uid="{90A77ABE-0764-41D5-9096-ECD02B66BFDD}"/>
+    <hyperlink ref="J161" r:id="rId95" xr:uid="{3628E765-C9F4-4CF9-81DF-B36F23C64A2F}"/>
+    <hyperlink ref="J162" r:id="rId96" xr:uid="{8021F201-3309-46A4-B61E-FC73B1B23314}"/>
+    <hyperlink ref="J164" r:id="rId97" xr:uid="{219EABD8-6B28-4DB6-ABED-62160D524701}"/>
+    <hyperlink ref="J165" r:id="rId98" xr:uid="{689CD745-49A6-4A67-8FC0-A3395D8951EB}"/>
+    <hyperlink ref="J167" r:id="rId99" xr:uid="{8FD757B4-1060-483A-B692-BC43D4AFBF32}"/>
+    <hyperlink ref="J168" r:id="rId100" xr:uid="{92107096-0C85-44C9-B0DB-6730E14A7E4B}"/>
+    <hyperlink ref="J169" r:id="rId101" xr:uid="{F5330D28-8277-4460-9F0F-E14ACC31010F}"/>
+    <hyperlink ref="J171" r:id="rId102" xr:uid="{3692964F-CDD5-4020-81E8-9FBD13D051DF}"/>
+    <hyperlink ref="J172" r:id="rId103" xr:uid="{4D665B96-DAC8-4731-BA0B-2B2EE032F5F3}"/>
+    <hyperlink ref="J173" r:id="rId104" xr:uid="{4F7C6812-89F3-4084-9A8E-9378A663F480}"/>
+    <hyperlink ref="J177" r:id="rId105" xr:uid="{00BB1C50-072C-4551-A0ED-1248DD81FF93}"/>
+    <hyperlink ref="J178" r:id="rId106" xr:uid="{CAD8A98E-1D67-45A7-83CF-9EFA9BB36DA9}"/>
+    <hyperlink ref="J181" r:id="rId107" xr:uid="{B16749FE-A877-4D86-8BC8-82F27FF3DF81}"/>
+    <hyperlink ref="J182" r:id="rId108" xr:uid="{E147B0E3-4459-473A-9FFE-196D92DC0520}"/>
+    <hyperlink ref="J184" r:id="rId109" xr:uid="{CF90E2A6-CC91-4684-B446-6E87E242D852}"/>
+    <hyperlink ref="J186" r:id="rId110" xr:uid="{347E7462-F755-44AC-873F-A066C78D0AE6}"/>
+    <hyperlink ref="J190" r:id="rId111" xr:uid="{4756C2CD-0363-4665-9EF0-04D0E8206098}"/>
+    <hyperlink ref="J191" r:id="rId112" xr:uid="{AB53B976-AACF-4849-8C56-2D92C1484991}"/>
+    <hyperlink ref="J192" r:id="rId113" xr:uid="{706E118D-D89D-4EC2-A05A-FAEB8C9B2003}"/>
+    <hyperlink ref="J193" r:id="rId114" xr:uid="{C70EB0D1-8165-4E6A-A89A-5C3B1AB2F36D}"/>
+    <hyperlink ref="J194" r:id="rId115" xr:uid="{940EAE08-6E6A-4E23-A96A-BDF686B4AA80}"/>
+    <hyperlink ref="J195" r:id="rId116" xr:uid="{8D251F7C-A1D4-40B9-BC25-9D58A0F919E1}"/>
+    <hyperlink ref="J196" r:id="rId117" xr:uid="{AD441E91-E77C-49DA-AD9B-63DA079B89C3}"/>
+    <hyperlink ref="J199" r:id="rId118" xr:uid="{CDC31E6C-0FB9-4AF8-BFA3-66E91B9124BD}"/>
+    <hyperlink ref="J201" r:id="rId119" xr:uid="{58B1E876-A1E0-4398-B9A8-9CA983674447}"/>
+    <hyperlink ref="J202" r:id="rId120" xr:uid="{AC395B5D-43DC-414A-90F6-B8475080A4C3}"/>
+    <hyperlink ref="J203" r:id="rId121" xr:uid="{B549D20D-AFA3-49FF-B23E-5101F580C9DE}"/>
+    <hyperlink ref="J205" r:id="rId122" xr:uid="{098C2094-D096-4000-8986-EEE303B11208}"/>
+    <hyperlink ref="J207" r:id="rId123" xr:uid="{323A3207-C8DD-4ABF-8954-25EEF6266376}"/>
+    <hyperlink ref="J209" r:id="rId124" xr:uid="{3EBFEA5D-3D93-43AE-AFEB-DA4B6420D761}"/>
+    <hyperlink ref="J210" r:id="rId125" xr:uid="{64E806BB-B36F-45F0-895E-411DD35E6E3F}"/>
+    <hyperlink ref="J211" r:id="rId126" xr:uid="{D952BD5C-D867-48A7-9280-B87F904EBC94}"/>
+    <hyperlink ref="J212" r:id="rId127" xr:uid="{A72892C9-6693-4C6D-A6AD-83362E568761}"/>
+    <hyperlink ref="J213" r:id="rId128" xr:uid="{544A6C2E-87F2-4039-9711-90873A52D7F2}"/>
+    <hyperlink ref="J214" r:id="rId129" xr:uid="{0F794993-B1F8-490E-9AC0-B8434FB16200}"/>
+    <hyperlink ref="J215" r:id="rId130" xr:uid="{8C28FFEA-BF87-463C-A7BB-E03EF9737614}"/>
+    <hyperlink ref="J217" r:id="rId131" xr:uid="{8E26270D-534B-4781-B143-05F2C4711E7A}"/>
+    <hyperlink ref="J219" r:id="rId132" xr:uid="{9229E28F-9C5B-46D7-B20A-4E09CE3FB54C}"/>
+    <hyperlink ref="J220" r:id="rId133" xr:uid="{19D1906E-9A0E-497B-926B-1E9F5EE43256}"/>
+    <hyperlink ref="J221" r:id="rId134" xr:uid="{3725547C-FCCF-44E6-AB61-7527C52AE275}"/>
+    <hyperlink ref="J222" r:id="rId135" xr:uid="{FF0C33E1-5BFF-46FF-9C11-863D7A5DB15D}"/>
+    <hyperlink ref="J223" r:id="rId136" xr:uid="{E75A8C99-3D47-489F-B19D-1C1415FC2137}"/>
+    <hyperlink ref="J225" r:id="rId137" xr:uid="{37D411AB-6CFB-433E-B9DC-0F8496FE5D47}"/>
+    <hyperlink ref="J228" r:id="rId138" xr:uid="{333E969F-B010-43D7-9202-6A72021215A4}"/>
+    <hyperlink ref="J230" r:id="rId139" xr:uid="{D8DAE89D-0F78-47C6-8528-857BE55B8D3C}"/>
+    <hyperlink ref="J234" r:id="rId140" xr:uid="{578E3567-DC4B-480C-AD9F-9CDB37E946E4}"/>
+    <hyperlink ref="J236" r:id="rId141" xr:uid="{5B0863CE-EAE9-4560-B1FA-E3A994CD81CC}"/>
+    <hyperlink ref="J237" r:id="rId142" xr:uid="{61322D8D-8BAA-4A28-829C-EAD3FA4C70B7}"/>
+    <hyperlink ref="J238" r:id="rId143" xr:uid="{73B33770-17E5-47A9-9345-891C8B0305D3}"/>
+    <hyperlink ref="J240" r:id="rId144" xr:uid="{63B9DAEA-A9B5-41D5-AFE1-ABEBC3F45047}"/>
+    <hyperlink ref="J241" r:id="rId145" xr:uid="{D47AC031-3CC8-47E6-9F32-771FFD5656CA}"/>
+    <hyperlink ref="J242" r:id="rId146" xr:uid="{0760B2D0-1CCE-4B0C-8959-869971C8BF01}"/>
+    <hyperlink ref="J243" r:id="rId147" xr:uid="{8FF5035C-CF76-4EED-9BF7-7BCAC951C43E}"/>
+    <hyperlink ref="J246" r:id="rId148" xr:uid="{991B6543-45A5-4744-A0C9-50DC7F876635}"/>
+    <hyperlink ref="J247" r:id="rId149" xr:uid="{60964962-B16F-4750-B442-EB9A24F8532B}"/>
+    <hyperlink ref="J250" r:id="rId150" xr:uid="{8C60B55B-0F9A-409A-967C-F2CEC736F78B}"/>
+    <hyperlink ref="J252" r:id="rId151" xr:uid="{B4958E24-0CA1-4431-8D2D-D2BADA384DDC}"/>
+    <hyperlink ref="J254" r:id="rId152" xr:uid="{444E7ACB-01F9-494B-B5E4-6222CEFC506C}"/>
+    <hyperlink ref="J255" r:id="rId153" xr:uid="{3D95A3B1-2C17-4072-B4B8-5F6AAE19C373}"/>
+    <hyperlink ref="J256" r:id="rId154" xr:uid="{E6EEE847-9914-4335-9F69-3774FB4EE8A4}"/>
+    <hyperlink ref="J258" r:id="rId155" xr:uid="{D78F4674-2E8C-4544-983D-C7871BD52902}"/>
+    <hyperlink ref="J259" r:id="rId156" xr:uid="{BB1A41D9-C757-43A4-92C1-DA96B239A351}"/>
+    <hyperlink ref="J261" r:id="rId157" xr:uid="{11E11243-FF8B-4B5D-AC1F-F1D46EFE1AE2}"/>
+    <hyperlink ref="J263" r:id="rId158" xr:uid="{B5BE51CA-4689-4057-8350-A72840418BF9}"/>
+    <hyperlink ref="J265" r:id="rId159" xr:uid="{63A02F97-D84E-4A7D-9718-7577796B4CFF}"/>
+    <hyperlink ref="J266" r:id="rId160" xr:uid="{4517889F-9A7D-4787-88B7-DD063D441F64}"/>
+    <hyperlink ref="J267" r:id="rId161" xr:uid="{CE4FE0C3-59E0-4D5E-8811-62F9673B3C2A}"/>
+    <hyperlink ref="J270" r:id="rId162" xr:uid="{64507C62-7D61-4974-8E1E-594D5033E7B7}"/>
+    <hyperlink ref="J271" r:id="rId163" xr:uid="{C97C0B21-79FE-45E5-9CD3-4EA842ED8C00}"/>
+    <hyperlink ref="J273" r:id="rId164" xr:uid="{843AD0F7-06DC-4CE6-93E9-04F75507FDD8}"/>
+    <hyperlink ref="J274" r:id="rId165" xr:uid="{526816FA-352D-477A-807A-5A82FB3EF8D4}"/>
+    <hyperlink ref="J275" r:id="rId166" xr:uid="{CE7669E2-BA51-4148-90FC-9BD2B6E5E61E}"/>
+    <hyperlink ref="J277" r:id="rId167" xr:uid="{A133B113-4665-46FF-BBFC-07A72FDB8C8D}"/>
+    <hyperlink ref="J278" r:id="rId168" xr:uid="{81B59E7F-162A-4D4F-A53E-9EEC3501D6E9}"/>
+    <hyperlink ref="J279" r:id="rId169" xr:uid="{F296F9FB-99FC-4DF5-8324-293301FE610A}"/>
+    <hyperlink ref="J280" r:id="rId170" xr:uid="{3C31891E-0952-4CB0-A9FA-730AF40190BA}"/>
+    <hyperlink ref="J281" r:id="rId171" xr:uid="{CF7DFD96-0389-43AB-83CC-5F3791A12244}"/>
+    <hyperlink ref="J282" r:id="rId172" xr:uid="{7B46C4B4-B4C8-4AF3-B8E5-2107530655FD}"/>
+    <hyperlink ref="J283" r:id="rId173" xr:uid="{DBEEC3E2-936E-409D-AE52-CE744A91959B}"/>
+    <hyperlink ref="J286" r:id="rId174" xr:uid="{D21B91F9-C430-4059-AD9E-87ABFB8EC0D7}"/>
+    <hyperlink ref="J287" r:id="rId175" xr:uid="{9D8E324E-0155-4F93-BFA4-F43E15B36990}"/>
+    <hyperlink ref="J290" r:id="rId176" xr:uid="{F7CE39D7-34FB-406F-9E2F-6D19A938FDDD}"/>
+    <hyperlink ref="J292" r:id="rId177" xr:uid="{E327C42B-E5C7-48FC-A1DF-B7ADC8F800E3}"/>
+    <hyperlink ref="J294" r:id="rId178" xr:uid="{45CC213F-D608-4FA8-8303-534C431A384B}"/>
+    <hyperlink ref="J296" r:id="rId179" xr:uid="{B8A321D4-CD86-4160-9EBC-774D38251AF3}"/>
+    <hyperlink ref="J297" r:id="rId180" xr:uid="{CC30E8AE-5A39-42FC-868A-2A1EE65A8503}"/>
+    <hyperlink ref="J298" r:id="rId181" xr:uid="{158569BF-3C06-405A-9E3D-ABDC90B8BC2E}"/>
+    <hyperlink ref="J299" r:id="rId182" xr:uid="{AA032E40-EEA8-4AC4-AE80-F54FB3EA6D59}"/>
+    <hyperlink ref="J300" r:id="rId183" xr:uid="{A9C34FFF-CBEF-413F-A070-658C6D1C5DDA}"/>
+    <hyperlink ref="J301" r:id="rId184" xr:uid="{CCDFE489-C577-49DE-BAD8-7DA900DB051D}"/>
+    <hyperlink ref="J303" r:id="rId185" xr:uid="{C1A684E3-E506-43C3-8910-C047F929165A}"/>
+    <hyperlink ref="J305" r:id="rId186" xr:uid="{6F3E3EAF-0CC4-48D2-827F-94A5465C272C}"/>
+    <hyperlink ref="J306" r:id="rId187" xr:uid="{380D221E-A2F6-44AB-A54D-544240725F4F}"/>
+    <hyperlink ref="J308" r:id="rId188" xr:uid="{5AB9373F-8026-4EE6-A2D5-BCF011509464}"/>
+    <hyperlink ref="J309" r:id="rId189" xr:uid="{02FD18A1-DF85-4175-B33C-B5C4999E47E5}"/>
+    <hyperlink ref="J311" r:id="rId190" xr:uid="{D9F92F9A-7100-4F9E-8C3B-F27E4D951540}"/>
+    <hyperlink ref="J312" r:id="rId191" xr:uid="{64901999-944B-4396-A014-02D44B178E6E}"/>
+    <hyperlink ref="J314" r:id="rId192" xr:uid="{D368342B-A040-4F19-A156-263FF23DF295}"/>
+    <hyperlink ref="J317" r:id="rId193" xr:uid="{47643A94-5871-4A72-94BE-BC849BE83ED1}"/>
+    <hyperlink ref="J318" r:id="rId194" xr:uid="{0459A028-A529-4EF1-845C-CAA5E9D8DD38}"/>
+    <hyperlink ref="J321" r:id="rId195" xr:uid="{86EFD043-9C51-4729-820C-F2065883B1B1}"/>
+    <hyperlink ref="J322" r:id="rId196" xr:uid="{1B43B055-BF28-4A0E-A576-D9761379EF62}"/>
+    <hyperlink ref="J325" r:id="rId197" xr:uid="{DFE4152A-A1E2-4151-B5FB-85D089D815B3}"/>
+    <hyperlink ref="J326" r:id="rId198" xr:uid="{0A9CE250-CB5C-439D-8FD4-65BD4E18E69D}"/>
+    <hyperlink ref="J329" r:id="rId199" xr:uid="{B85C2190-4FB2-445D-B932-141AFE7259FB}"/>
+    <hyperlink ref="J330" r:id="rId200" xr:uid="{08838AFD-56DA-48B0-B140-BF9A21856251}"/>
+    <hyperlink ref="J331" r:id="rId201" xr:uid="{1BD53C0F-1C79-4F36-8ACB-6E4341D318CC}"/>
+    <hyperlink ref="J333" r:id="rId202" xr:uid="{B600680B-9195-459F-81ED-28E738EA9FA6}"/>
+    <hyperlink ref="J334" r:id="rId203" xr:uid="{D9ED18F5-DB46-4219-A936-E3C7D6BD9F0C}"/>
+    <hyperlink ref="J335" r:id="rId204" xr:uid="{181D1779-2C06-4852-876C-7A00DC4AFA76}"/>
+    <hyperlink ref="J336" r:id="rId205" xr:uid="{31CFD515-1034-437C-AB9F-2B4A7E8E0804}"/>
+    <hyperlink ref="J338" r:id="rId206" xr:uid="{FFAC084D-2307-43E8-8FAD-BE8EB8353B50}"/>
+    <hyperlink ref="J340" r:id="rId207" xr:uid="{E20F3B29-761B-4DB4-81FD-F416C3827A88}"/>
+    <hyperlink ref="J342" r:id="rId208" xr:uid="{33A80E00-6C25-4AEB-99D1-412696163C93}"/>
+    <hyperlink ref="J343" r:id="rId209" xr:uid="{BB535EEB-4CC8-48F7-AF56-3F37FF860F8C}"/>
+    <hyperlink ref="J344" r:id="rId210" xr:uid="{0562417B-AB14-41F7-868E-50FA9B42AA12}"/>
+    <hyperlink ref="J346" r:id="rId211" xr:uid="{BDDA9B0D-40A3-452C-BB51-DE95B71FA296}"/>
+    <hyperlink ref="J349" r:id="rId212" xr:uid="{85629D9A-6E09-4C87-ABF0-F49A31A850DD}"/>
+    <hyperlink ref="J350" r:id="rId213" xr:uid="{EC2B0FCA-8C25-4993-8B57-F066357CD0A9}"/>
+    <hyperlink ref="J352" r:id="rId214" xr:uid="{67399257-0C7F-4D1A-A7B7-778A1BE43449}"/>
+    <hyperlink ref="J354" r:id="rId215" xr:uid="{38133AED-83D7-4CC8-A211-5D34EA07AFB8}"/>
+    <hyperlink ref="J355" r:id="rId216" xr:uid="{8613D8F0-A768-4034-86C2-E173E236EDD6}"/>
+    <hyperlink ref="J356" r:id="rId217" xr:uid="{49ADDF88-8CE5-4E8E-9A55-9EE97B0A3E19}"/>
+    <hyperlink ref="J357" r:id="rId218" xr:uid="{D1E1A55A-59A2-4765-9004-903855E1F8EC}"/>
+    <hyperlink ref="J358" r:id="rId219" xr:uid="{714FE207-72FE-4DD6-81B7-96DF6A8E59EB}"/>
+    <hyperlink ref="J360" r:id="rId220" xr:uid="{3D8AE70C-23E1-4317-86C4-22A5F58F50F2}"/>
+    <hyperlink ref="J363" r:id="rId221" xr:uid="{68F929BD-5AFF-476D-90A8-6871A8E8ECBC}"/>
+    <hyperlink ref="J364" r:id="rId222" xr:uid="{67F49FAB-9A32-41E8-9EFA-DDA1E2A096E0}"/>
+    <hyperlink ref="J366" r:id="rId223" xr:uid="{57662126-BD9D-4CA1-BCA7-5B34BACF7FB5}"/>
+    <hyperlink ref="J368" r:id="rId224" xr:uid="{36047851-7709-4804-8594-B2AEFA6BF30A}"/>
+    <hyperlink ref="J370" r:id="rId225" xr:uid="{9D07BD76-AA07-4434-B202-7F005E6C845E}"/>
+    <hyperlink ref="J371" r:id="rId226" xr:uid="{952CD549-BD33-44D2-B0A5-4E51D76E22A9}"/>
+    <hyperlink ref="J372" r:id="rId227" xr:uid="{C126293C-5D34-4B39-B99D-BA99B8E77601}"/>
+    <hyperlink ref="J373" r:id="rId228" xr:uid="{7FC0B5B9-14DA-4090-BC40-424E0E762439}"/>
+    <hyperlink ref="J374" r:id="rId229" xr:uid="{BCBD7732-B1A9-4351-8869-912634AE41F0}"/>
+    <hyperlink ref="J375" r:id="rId230" xr:uid="{4722AF9D-DF27-49A5-B1C7-C2EA85D2B272}"/>
+    <hyperlink ref="J376" r:id="rId231" xr:uid="{CB4F0BD4-02B9-4B0D-9973-598E734C14C0}"/>
+    <hyperlink ref="J377" r:id="rId232" xr:uid="{50162AA6-4F4B-413F-9BD9-FFF22123EE35}"/>
+    <hyperlink ref="J378" r:id="rId233" xr:uid="{76FAD247-6595-46E2-9685-BE288C0A504D}"/>
+    <hyperlink ref="J379" r:id="rId234" xr:uid="{5B908820-60CD-4411-A177-D6495BB09460}"/>
+    <hyperlink ref="J381" r:id="rId235" xr:uid="{7D62BF9B-CE38-4F3F-8577-6047F54C37C8}"/>
+    <hyperlink ref="J383" r:id="rId236" xr:uid="{B5724BA3-61F7-49DB-AFD5-774C1783B122}"/>
+    <hyperlink ref="J384" r:id="rId237" xr:uid="{9C3DE604-6A60-4283-8FB1-8BD67A83C3FA}"/>
+    <hyperlink ref="J386" r:id="rId238" xr:uid="{D4D6AAC9-5BEB-4D52-B316-A69F0C27788C}"/>
+    <hyperlink ref="J387" r:id="rId239" xr:uid="{C2E2B96D-CB14-43EF-AB9C-26AB966CAA83}"/>
+    <hyperlink ref="J388" r:id="rId240" xr:uid="{247E0AFD-E01B-4943-9F75-4C589E79CD93}"/>
+    <hyperlink ref="J390" r:id="rId241" xr:uid="{85C11E66-03FE-4CB2-9D42-774BFDE58FB4}"/>
+    <hyperlink ref="J391" r:id="rId242" xr:uid="{54016571-E6CB-42A0-8E90-BA29D5C6B304}"/>
+    <hyperlink ref="J394" r:id="rId243" xr:uid="{794F6BD2-A09F-4E81-A7A2-CE2B9F8F1BAE}"/>
+    <hyperlink ref="J395" r:id="rId244" xr:uid="{CA099075-5CB0-4605-BB8B-11FFB9FA4E50}"/>
+    <hyperlink ref="J396" r:id="rId245" xr:uid="{71A3F5B3-6B32-47EC-9F59-94CF08762424}"/>
+    <hyperlink ref="J397" r:id="rId246" xr:uid="{A7E7C2BA-2944-48B7-9DFA-4C2A44E0BA80}"/>
+    <hyperlink ref="J398" r:id="rId247" xr:uid="{E3537969-D0CF-40D3-A4EA-5F57B6776EA4}"/>
+    <hyperlink ref="J399" r:id="rId248" xr:uid="{55C3DDB3-27D6-4DEE-959A-9D3EDEEDCE5D}"/>
+    <hyperlink ref="J400" r:id="rId249" xr:uid="{765814A1-78AC-4742-ABB4-F5D77C7E9135}"/>
+    <hyperlink ref="J403" r:id="rId250" xr:uid="{34CFD8BF-ACF4-4B7C-A8A1-C93ECC85768A}"/>
+    <hyperlink ref="J404" r:id="rId251" xr:uid="{C4574ECB-1DB1-44FE-A286-74D14A8BCB75}"/>
+    <hyperlink ref="J405" r:id="rId252" xr:uid="{0714233B-FBE3-442F-A57A-B6BB7E2E8DC0}"/>
+    <hyperlink ref="J406" r:id="rId253" xr:uid="{C91747D6-8569-4068-A182-52E5251A9A13}"/>
+    <hyperlink ref="J408" r:id="rId254" xr:uid="{D957FBFB-B3A1-49DA-86EC-7696B564A46F}"/>
+    <hyperlink ref="J409" r:id="rId255" xr:uid="{58042C80-6108-4150-9ABE-DF7DCC67148D}"/>
+    <hyperlink ref="J411" r:id="rId256" xr:uid="{96AC45F8-BD6D-42AC-A0CA-1A12ECC6B3E5}"/>
+    <hyperlink ref="J413" r:id="rId257" xr:uid="{A4AF4653-F0B7-4660-BE16-86B8DB4474B8}"/>
+    <hyperlink ref="J415" r:id="rId258" xr:uid="{58D6DB23-4409-457D-9638-FAD1A21E5133}"/>
+    <hyperlink ref="J416" r:id="rId259" xr:uid="{45219878-23FF-4178-915E-C5399E3EBB4B}"/>
+    <hyperlink ref="J418" r:id="rId260" xr:uid="{B84C8B0B-1894-48E8-AB6C-3B06A86CA6F2}"/>
+    <hyperlink ref="J421" r:id="rId261" xr:uid="{235ADF45-668C-4FC9-8E98-B5D1F1F116D2}"/>
+    <hyperlink ref="J422" r:id="rId262" xr:uid="{C8673AFC-0EFF-421D-BDB0-F5933631EDCC}"/>
+    <hyperlink ref="J430" r:id="rId263" xr:uid="{128AA4EF-CF31-4C66-94AB-85E8FC8B5BA0}"/>
+    <hyperlink ref="J431" r:id="rId264" xr:uid="{A56E0535-F065-4A95-9B9C-EBEA4FF3FEF6}"/>
+    <hyperlink ref="J432" r:id="rId265" xr:uid="{FA7199D6-BD89-423E-AE43-96F3E4FFC5A2}"/>
+    <hyperlink ref="J433" r:id="rId266" xr:uid="{C9FC7B61-AA9F-499F-8997-C01165925B8C}"/>
+    <hyperlink ref="J434" r:id="rId267" xr:uid="{EE3AE195-5094-448F-B21C-136CAFF80546}"/>
+    <hyperlink ref="J435" r:id="rId268" xr:uid="{D857D2A6-B897-4E2B-A44D-7869A01CE5D3}"/>
+    <hyperlink ref="J436" r:id="rId269" xr:uid="{653AA32A-6365-4A1F-80A8-51B23C654F6E}"/>
+    <hyperlink ref="J437" r:id="rId270" xr:uid="{2C199156-7045-4991-BAB7-E80ECACE00FC}"/>
+    <hyperlink ref="J438" r:id="rId271" xr:uid="{D50D14AE-9B5B-436F-AB7D-0918EFBF4BD9}"/>
+    <hyperlink ref="J439" r:id="rId272" xr:uid="{50651A2C-FB06-4897-9E4E-822BEFCBA9FE}"/>
+    <hyperlink ref="J445" r:id="rId273" xr:uid="{E0357B41-1AF0-4370-AACD-94D43172B4BE}"/>
+    <hyperlink ref="J447" r:id="rId274" xr:uid="{8B1ED451-BA42-478C-A920-FEF269460B4B}"/>
+    <hyperlink ref="J449" r:id="rId275" xr:uid="{2057F6D2-BC13-46A2-BCF1-87043BCC1012}"/>
+    <hyperlink ref="J450" r:id="rId276" xr:uid="{D2F965B6-AFD5-4239-A215-697EFD5F53E9}"/>
+    <hyperlink ref="J451" r:id="rId277" xr:uid="{ED9F2CA0-3448-42D8-85C6-F4A0EAD25695}"/>
+    <hyperlink ref="J452" r:id="rId278" xr:uid="{D044FB1B-4AC2-4DEF-8F0C-F023436112C4}"/>
+    <hyperlink ref="J453" r:id="rId279" xr:uid="{6A4013B9-A82F-40AE-9D9F-00C9DE63F431}"/>
+    <hyperlink ref="J454" r:id="rId280" xr:uid="{EAAF9454-C8C5-46B9-8234-D835C8ABF474}"/>
+    <hyperlink ref="J455" r:id="rId281" xr:uid="{B1F3616A-D77A-495D-B86E-F4CAF937C347}"/>
+    <hyperlink ref="J458" r:id="rId282" xr:uid="{D54C9401-6B92-48C0-AE6C-22A5BF2D473C}"/>
+    <hyperlink ref="J460" r:id="rId283" xr:uid="{20BA490D-BB6C-4A73-A834-24D3718CD9EA}"/>
+    <hyperlink ref="J461" r:id="rId284" xr:uid="{8CDF1494-48BD-47FE-8755-AD9A1AF54BF0}"/>
+    <hyperlink ref="J462" r:id="rId285" xr:uid="{50A82B8F-E98C-4898-9D4A-063CAF66AD0C}"/>
+    <hyperlink ref="J465" r:id="rId286" xr:uid="{CC69AA22-2E7C-4D6B-A556-E72526D29ADE}"/>
+    <hyperlink ref="J469" r:id="rId287" xr:uid="{85E49F64-4699-4F61-B47D-46AF537F3135}"/>
+    <hyperlink ref="J473" r:id="rId288" xr:uid="{672DF1B1-9D7A-4C3F-BCE2-D7C4DF5D2DD2}"/>
+    <hyperlink ref="J476" r:id="rId289" xr:uid="{4EA7D590-6439-4F3B-BB93-0B0EC04DEBD7}"/>
+    <hyperlink ref="J478" r:id="rId290" xr:uid="{97C8D5D3-DCEB-45EF-91C4-9E6D105957A2}"/>
+    <hyperlink ref="J479" r:id="rId291" xr:uid="{26B10118-173B-4FD8-812C-DE0EA8508642}"/>
+    <hyperlink ref="J480" r:id="rId292" xr:uid="{B6D69CD3-1C0B-4FD0-A43D-0FD29998AFD1}"/>
+    <hyperlink ref="J481" r:id="rId293" xr:uid="{DBFDC290-EB81-457A-82A7-219D3E9B267F}"/>
+    <hyperlink ref="J482" r:id="rId294" xr:uid="{1ED0910A-B11F-42CC-8F08-D0B1D274E193}"/>
+    <hyperlink ref="J484" r:id="rId295" xr:uid="{44F83480-683F-4073-80DD-9243E0AC9310}"/>
+    <hyperlink ref="J485" r:id="rId296" xr:uid="{B3C8B58F-83FF-4E3F-B3AA-5C2A2DBB449D}"/>
+    <hyperlink ref="J488" r:id="rId297" xr:uid="{63A0FD9F-1591-43D8-B14B-CA250B6A412F}"/>
+    <hyperlink ref="J489" r:id="rId298" xr:uid="{90B98E5F-D0DC-420D-BA9C-D9750A760507}"/>
+    <hyperlink ref="J490" r:id="rId299" xr:uid="{6A02C229-2814-430B-B754-B3404CB757CE}"/>
+    <hyperlink ref="J491" r:id="rId300" xr:uid="{E54DF1F6-DA2B-4762-93B3-63F549C4AC48}"/>
+    <hyperlink ref="J494" r:id="rId301" xr:uid="{E18AA0CD-2F24-4EF3-8ECF-3D3513BEC231}"/>
+    <hyperlink ref="J496" r:id="rId302" xr:uid="{E34659A2-090E-47E6-AE6D-BDCEA8A643F6}"/>
+    <hyperlink ref="J497" r:id="rId303" xr:uid="{1DD579FF-5B6D-4A50-BF04-30A7DE19ADB9}"/>
+    <hyperlink ref="J498" r:id="rId304" xr:uid="{624941DE-1026-4EE2-9361-F0CCA01FF97A}"/>
+    <hyperlink ref="J499" r:id="rId305" xr:uid="{8F45F44E-8E50-4A38-B0AB-104F8BB42F06}"/>
+    <hyperlink ref="J500" r:id="rId306" xr:uid="{CF6A4A2A-AEE4-4879-AB0C-CE242F9EE474}"/>
+    <hyperlink ref="J501" r:id="rId307" xr:uid="{0ED6C3D5-2779-4C40-B96C-6821C8F89E16}"/>
+    <hyperlink ref="J503" r:id="rId308" xr:uid="{E1340037-CC47-4592-99B2-7BC2A9203E43}"/>
+    <hyperlink ref="J504" r:id="rId309" xr:uid="{035E49D2-FA6C-4F2B-A356-C1CA824E663B}"/>
+    <hyperlink ref="J508" r:id="rId310" xr:uid="{A1D5F102-4035-4390-A4EA-A3FE2E403B48}"/>
+    <hyperlink ref="J509" r:id="rId311" xr:uid="{49B84140-3E1B-44DF-BCEB-577D5FA4B9F1}"/>
+    <hyperlink ref="J510" r:id="rId312" xr:uid="{21C7883E-2B2E-4F0D-A13F-F307B989E868}"/>
+    <hyperlink ref="J511" r:id="rId313" xr:uid="{0A98E39E-BF70-457F-BF44-A07C1EB8376D}"/>
+    <hyperlink ref="J513" r:id="rId314" xr:uid="{2162263D-1106-4F02-8168-451D751FB468}"/>
+    <hyperlink ref="J515" r:id="rId315" xr:uid="{0C8CD81B-F4EE-4F1D-A8AE-A19D6DBA8435}"/>
+    <hyperlink ref="J516" r:id="rId316" xr:uid="{393FC5EE-8932-40E9-9809-2A8CDB40E702}"/>
+    <hyperlink ref="J519" r:id="rId317" xr:uid="{01B048CD-6A96-4DBD-A465-D74C1BA801F7}"/>
+    <hyperlink ref="J523" r:id="rId318" xr:uid="{9C5A1513-01C6-4534-8298-942481956DC0}"/>
+    <hyperlink ref="J524" r:id="rId319" xr:uid="{DCD25738-8A59-457C-83E7-E54502AF8204}"/>
+    <hyperlink ref="J525" r:id="rId320" xr:uid="{A0DBE92D-7FB2-431E-8677-5B9B2BCC23BE}"/>
+    <hyperlink ref="J535" r:id="rId321" xr:uid="{858DDA6F-E4FE-4DC3-A1E3-B144A71B18A3}"/>
+    <hyperlink ref="J536" r:id="rId322" xr:uid="{0165C7C7-9AEF-42CA-A994-4BD01E9F91BE}"/>
+    <hyperlink ref="J537" r:id="rId323" xr:uid="{09D0816F-FCF8-4E41-95F4-3EE20F987B44}"/>
+    <hyperlink ref="J538" r:id="rId324" xr:uid="{B34470FF-DA2E-4308-B59D-5D56F15537A3}"/>
+    <hyperlink ref="J539" r:id="rId325" xr:uid="{35C3D916-3780-4998-8236-2559E9D4563A}"/>
+    <hyperlink ref="J540" r:id="rId326" xr:uid="{BB90AD54-8550-412F-B8C4-34461CDDBB56}"/>
+    <hyperlink ref="J541" r:id="rId327" xr:uid="{411C2AE8-2045-4080-99A8-9FB515BCD60C}"/>
+    <hyperlink ref="J543" r:id="rId328" xr:uid="{748F6176-1DB4-48E6-BA5A-83A29CBD48D9}"/>
+    <hyperlink ref="J544" r:id="rId329" xr:uid="{C0FDAE06-4CAE-499E-8148-102795A9C8D1}"/>
+    <hyperlink ref="J546" r:id="rId330" xr:uid="{1C64E955-7733-46BE-8AAE-5E4D68590495}"/>
+    <hyperlink ref="J547" r:id="rId331" xr:uid="{828F998E-5DF4-4716-A2D2-81A82C2B6CC8}"/>
+    <hyperlink ref="J548" r:id="rId332" xr:uid="{F0DAB9E9-5385-4744-AA3C-FC3B2E3ECA4B}"/>
+    <hyperlink ref="J549" r:id="rId333" xr:uid="{010E95BE-EC93-4FCA-B193-388217EF44FB}"/>
+    <hyperlink ref="J550" r:id="rId334" xr:uid="{DB387C60-1AC6-4678-A40C-D4CA627ACAAB}"/>
+    <hyperlink ref="J551" r:id="rId335" xr:uid="{292D0F31-D6AB-4F40-92CE-06A7A0F7F731}"/>
+    <hyperlink ref="J552" r:id="rId336" xr:uid="{A2CFE7D0-C308-4138-856C-1807BE5C85B8}"/>
+    <hyperlink ref="J555" r:id="rId337" xr:uid="{F9531B38-FDF5-4DEA-85A5-7AAFDD75BF7A}"/>
+    <hyperlink ref="J556" r:id="rId338" xr:uid="{086B8BD7-B3A0-4471-B1B8-45558403B1CA}"/>
+    <hyperlink ref="J558" r:id="rId339" xr:uid="{12889D05-7F33-4278-A103-570B2EF00153}"/>
+    <hyperlink ref="J559" r:id="rId340" xr:uid="{8D0BED8B-751D-4B6C-996D-431227BEC8C0}"/>
+    <hyperlink ref="J560" r:id="rId341" xr:uid="{949074CD-42AB-4FB2-B512-30FD96B0E9E8}"/>
+    <hyperlink ref="J562" r:id="rId342" xr:uid="{F5B74754-C88B-4935-8DAE-43797B6901E8}"/>
+    <hyperlink ref="J569" r:id="rId343" xr:uid="{B3A3E971-0289-4A9E-B5BC-328E3BF65D16}"/>
+    <hyperlink ref="J570" r:id="rId344" xr:uid="{B63EA640-85AE-492F-8CC9-D2E478269695}"/>
+    <hyperlink ref="J571" r:id="rId345" xr:uid="{FE467D69-8FE5-4C34-9374-691BC7A12007}"/>
+    <hyperlink ref="J572" r:id="rId346" xr:uid="{7D698BFA-7320-467B-A498-C66081E16796}"/>
+    <hyperlink ref="J573" r:id="rId347" xr:uid="{D6E37026-08EC-4D84-B62D-C2C563BD3BBA}"/>
+    <hyperlink ref="J574" r:id="rId348" xr:uid="{9A5D9932-3F32-4B4A-8E3C-E3664129E9F7}"/>
+    <hyperlink ref="J575" r:id="rId349" xr:uid="{E5DDBD18-1E07-461B-B085-BE7DE82E405B}"/>
+    <hyperlink ref="J576" r:id="rId350" xr:uid="{A53BCC1D-248D-49A1-9316-05218A87E456}"/>
+    <hyperlink ref="J577" r:id="rId351" xr:uid="{948CA08A-9D26-4365-ADD4-A8CD61DCBE4E}"/>
+    <hyperlink ref="J578" r:id="rId352" xr:uid="{41DAAD26-EFA7-4D13-9F22-A049FA4816A7}"/>
+    <hyperlink ref="J579" r:id="rId353" xr:uid="{0074F5A3-A722-4C29-9FAE-AF6C57475E44}"/>
+    <hyperlink ref="J580" r:id="rId354" xr:uid="{22F344FC-1C5D-49B5-9D19-8DA5BC91730D}"/>
+    <hyperlink ref="J581" r:id="rId355" xr:uid="{9D94C076-F406-4E8B-8EA8-1FAA56B424EC}"/>
+    <hyperlink ref="J582" r:id="rId356" xr:uid="{301D15F9-F4B6-47D0-9654-3231AFD4628A}"/>
+    <hyperlink ref="J584" r:id="rId357" xr:uid="{EE81E1A0-0FD1-4127-8E9A-F396FCB7D183}"/>
+    <hyperlink ref="J585" r:id="rId358" xr:uid="{80E3DC23-2E5E-46E0-B4D7-E1C84ED5F6B1}"/>
+    <hyperlink ref="J586" r:id="rId359" xr:uid="{ED5804DB-3238-4774-864B-099AF25DE241}"/>
+    <hyperlink ref="J587" r:id="rId360" xr:uid="{EE1AD39B-351A-4A8F-88E9-B70E0C01A13D}"/>
+    <hyperlink ref="J592" r:id="rId361" xr:uid="{1ED68771-BB48-4ABE-80C2-1F23D48A547F}"/>
+    <hyperlink ref="J593" r:id="rId362" xr:uid="{926D12AB-AB0D-4F6D-BB69-F3289C1DF6CB}"/>
+    <hyperlink ref="J595" r:id="rId363" xr:uid="{86793308-6DA5-449A-BF62-E2B7441A8A97}"/>
+    <hyperlink ref="J596" r:id="rId364" xr:uid="{8221E45B-24AB-4A54-9A4A-DE939308F8AD}"/>
+    <hyperlink ref="J598" r:id="rId365" xr:uid="{A2F0ECC2-5F43-4998-BEDE-716702A1901F}"/>
+    <hyperlink ref="J599" r:id="rId366" xr:uid="{C5989E04-5CD5-417F-8885-61FB77164543}"/>
+    <hyperlink ref="J602" r:id="rId367" xr:uid="{FC4FAAF9-D9EA-409E-82A6-B90170183C58}"/>
+    <hyperlink ref="J603" r:id="rId368" xr:uid="{49509BEC-410B-4E98-9B24-A2C728E0208F}"/>
+    <hyperlink ref="J604" r:id="rId369" xr:uid="{5BFDC61D-8E4C-4479-8F05-BE1BB87C7EAC}"/>
+    <hyperlink ref="J605" r:id="rId370" xr:uid="{C9F47D9E-E76E-4A45-994D-4B02CCC48457}"/>
+    <hyperlink ref="J606" r:id="rId371" xr:uid="{8DA53CD1-1110-4D84-8FAD-907D939D0541}"/>
+    <hyperlink ref="J608" r:id="rId372" xr:uid="{4F91CEB4-DE3D-46D7-9F4C-3F1D2A0EEED1}"/>
+    <hyperlink ref="J609" r:id="rId373" xr:uid="{5407D48E-D53F-4105-B132-4960C9792ACC}"/>
+    <hyperlink ref="J611" r:id="rId374" xr:uid="{C64F35B6-9176-4DA5-B145-A275D78A80F8}"/>
+    <hyperlink ref="J612" r:id="rId375" xr:uid="{B37FBF98-6E75-41CC-94D4-2B4A8B2D2035}"/>
+    <hyperlink ref="J613" r:id="rId376" xr:uid="{12854606-9A25-46B4-AC8E-22FB930A2A61}"/>
+    <hyperlink ref="J615" r:id="rId377" xr:uid="{EE15E61E-61CC-4DA6-9573-57DAE4B91894}"/>
+    <hyperlink ref="J617" r:id="rId378" xr:uid="{303CBA49-917D-412C-90CF-2E04CE115097}"/>
+    <hyperlink ref="J618" r:id="rId379" xr:uid="{1770CA8B-39D2-41AB-A4E3-16BC45321A36}"/>
+    <hyperlink ref="J619" r:id="rId380" xr:uid="{00851AFD-D16A-4B04-A95D-00385A035A06}"/>
+    <hyperlink ref="J622" r:id="rId381" xr:uid="{19913CEC-3AA6-44AB-98AD-B96DD0EB191D}"/>
+    <hyperlink ref="J623" r:id="rId382" xr:uid="{39D2FA89-38FB-4E4D-B41A-84ACE8D78DF0}"/>
+    <hyperlink ref="J624" r:id="rId383" xr:uid="{C28469D3-4119-4C01-8339-17917F13EFED}"/>
+    <hyperlink ref="J626" r:id="rId384" xr:uid="{B3FA1D4E-7AC1-4C69-B9A3-F6E4BB1A0688}"/>
+    <hyperlink ref="J628" r:id="rId385" xr:uid="{3C8C6861-4AED-4B5D-8359-F36A47AFF492}"/>
+    <hyperlink ref="J629" r:id="rId386" xr:uid="{E00BD8DF-EB2F-4631-831E-7429A218C8EC}"/>
+    <hyperlink ref="J631" r:id="rId387" xr:uid="{F3BB100D-574E-49F9-8DAF-4A80A375924A}"/>
+    <hyperlink ref="J634" r:id="rId388" xr:uid="{696B8607-4BAC-4F44-9A74-E5A423E991EC}"/>
+    <hyperlink ref="J635" r:id="rId389" xr:uid="{ADFAA3AF-C45B-49DD-8E3A-44C20A89FD65}"/>
+    <hyperlink ref="J637" r:id="rId390" xr:uid="{169E875B-D7BB-4F99-B944-00CDDC3FC975}"/>
+    <hyperlink ref="J640" r:id="rId391" xr:uid="{AA9C9A1B-3D11-4911-A6DE-60B96955A774}"/>
+    <hyperlink ref="J641" r:id="rId392" xr:uid="{9CC10317-9104-480B-9F13-885D1B9DB15E}"/>
+    <hyperlink ref="J642" r:id="rId393" xr:uid="{0190F85B-77A7-4C57-A8C2-DE7B3FC1E24F}"/>
+    <hyperlink ref="J644" r:id="rId394" xr:uid="{AB99F971-4541-4DDA-B9D8-138575C5254C}"/>
+    <hyperlink ref="J645" r:id="rId395" xr:uid="{44D9FEBA-DB23-4C40-94C4-7FC3FB724D83}"/>
+    <hyperlink ref="J648" r:id="rId396" xr:uid="{C051F1A4-6BE8-4A53-A74D-9196F20B3210}"/>
+    <hyperlink ref="J649" r:id="rId397" xr:uid="{AA3E0409-FBA3-4001-AE7D-1BE47FBDD751}"/>
+    <hyperlink ref="J652" r:id="rId398" xr:uid="{18B01CF0-77B6-4366-9F97-D21612EE6147}"/>
+    <hyperlink ref="J654" r:id="rId399" xr:uid="{DF655614-6388-421D-BB69-3D2D84C7A1BD}"/>
+    <hyperlink ref="J656" r:id="rId400" xr:uid="{5222BF02-E295-4B49-831E-25F9D7641540}"/>
+    <hyperlink ref="J657" r:id="rId401" xr:uid="{60E0A767-7D28-4D4D-A86A-2C268A560990}"/>
+    <hyperlink ref="J663" r:id="rId402" xr:uid="{0E09ADE4-4E9C-4AC9-9BBA-ECD07FCC643F}"/>
+    <hyperlink ref="J664" r:id="rId403" xr:uid="{ADB4A47D-41F1-4040-AA75-96606C1C00C2}"/>
+    <hyperlink ref="J665" r:id="rId404" xr:uid="{6C53C2D6-3AAF-46C7-800B-B3E446BD7358}"/>
+    <hyperlink ref="J666" r:id="rId405" xr:uid="{A473FA21-66E9-4AF7-AE33-FC55F814D4F7}"/>
+    <hyperlink ref="J667" r:id="rId406" xr:uid="{7FA853BC-9DAA-48F4-8434-C61189A163DD}"/>
+    <hyperlink ref="J668" r:id="rId407" xr:uid="{10AE8C77-AEA2-4DCF-9970-AB052D2ED148}"/>
+    <hyperlink ref="J669" r:id="rId408" xr:uid="{91CE5AC6-4944-4DC0-B21F-6C52030A6048}"/>
+    <hyperlink ref="J670" r:id="rId409" xr:uid="{0B414E31-B979-40E6-AAFC-CE83F94EA840}"/>
+    <hyperlink ref="J671" r:id="rId410" xr:uid="{D0D19974-CB7C-4ABD-94F0-5497C538D457}"/>
+    <hyperlink ref="J672" r:id="rId411" xr:uid="{16F3049D-9327-495F-8A20-1E7B3B637315}"/>
+    <hyperlink ref="J673" r:id="rId412" xr:uid="{6E2BCC77-8080-449D-91D1-BF613F3C5E9F}"/>
+    <hyperlink ref="J674" r:id="rId413" xr:uid="{3D9B35D9-E87E-4ADE-BFBC-AA2D3F3458BF}"/>
+    <hyperlink ref="J675" r:id="rId414" xr:uid="{965D793D-D157-43AF-95EE-4D16F3217E83}"/>
+    <hyperlink ref="J676" r:id="rId415" xr:uid="{97FCCD4A-1CAF-431D-82E1-1124DFB83A36}"/>
+    <hyperlink ref="J677" r:id="rId416" xr:uid="{A187D443-6516-475F-B345-6F418762F378}"/>
+    <hyperlink ref="J679" r:id="rId417" xr:uid="{CD7AF51E-AEEF-4E08-B09C-F953306D8E05}"/>
+    <hyperlink ref="J682" r:id="rId418" xr:uid="{0F8D5664-9B0D-49E6-BF70-2BADB7464A90}"/>
+    <hyperlink ref="J683" r:id="rId419" xr:uid="{ACB7FC4C-AC5C-492D-AB7C-4B09264FA2AD}"/>
+    <hyperlink ref="J684" r:id="rId420" xr:uid="{DD4E0E6D-6ABF-4DE6-BA59-8E92FCBFFD65}"/>
+    <hyperlink ref="J688" r:id="rId421" xr:uid="{A8CA0879-22C0-4A99-936F-A5EA9A4DC6D4}"/>
+    <hyperlink ref="J693" r:id="rId422" xr:uid="{E7033F5D-627A-49AA-AA63-DC71FB7B4A99}"/>
+    <hyperlink ref="J694" r:id="rId423" xr:uid="{E63FBE5B-7258-46F8-A434-8E25B78722C7}"/>
+    <hyperlink ref="J695" r:id="rId424" xr:uid="{8F4DB0C6-BA4B-4231-BFE6-6588EC5AAAC0}"/>
+    <hyperlink ref="J696" r:id="rId425" xr:uid="{C56DA798-A0C2-480F-9722-95F02D12DE97}"/>
+    <hyperlink ref="J697" r:id="rId426" xr:uid="{80D48220-0573-459B-8ED0-874EE1E52CA8}"/>
+    <hyperlink ref="J698" r:id="rId427" xr:uid="{C3DC3F30-0001-49EC-976B-30FC7063A592}"/>
+    <hyperlink ref="J699" r:id="rId428" xr:uid="{B8369234-E7C6-48AB-A4E6-1DD25B05CFB8}"/>
+    <hyperlink ref="J700" r:id="rId429" xr:uid="{DF5E9AEC-7B76-4893-BE9B-38DF397D9A24}"/>
+    <hyperlink ref="J705" r:id="rId430" xr:uid="{38884580-32A2-440F-B161-AC144DB53016}"/>
+    <hyperlink ref="J708" r:id="rId431" xr:uid="{15B3C8A3-351A-4703-A11A-5C316E5E2238}"/>
+    <hyperlink ref="J712" r:id="rId432" xr:uid="{A9C3DFBA-BCA9-44F4-8063-1DDA8F331C1B}"/>
+    <hyperlink ref="J713" r:id="rId433" xr:uid="{8E815F63-2E33-4727-9A58-DAAC049DB8C1}"/>
+    <hyperlink ref="J714" r:id="rId434" xr:uid="{CF067B6E-456F-44C5-B52B-377DB66B54F7}"/>
+    <hyperlink ref="J715" r:id="rId435" xr:uid="{177D40CA-35BE-4566-B491-732583BBBE7A}"/>
+    <hyperlink ref="J718" r:id="rId436" xr:uid="{89792798-975D-4BCC-9EED-B7AAB87E5A9F}"/>
+    <hyperlink ref="J720" r:id="rId437" xr:uid="{4A1495E7-B416-4836-9979-772462484B67}"/>
+    <hyperlink ref="J721" r:id="rId438" xr:uid="{3AB827D1-AED5-4BAF-869D-40F33CF573E8}"/>
+    <hyperlink ref="J722" r:id="rId439" xr:uid="{FDF4A4CB-1D7D-4541-99E9-78E1DCC7AD12}"/>
+    <hyperlink ref="J725" r:id="rId440" xr:uid="{7F96562D-60D6-46CA-A321-33A89E005447}"/>
+    <hyperlink ref="J726" r:id="rId441" xr:uid="{81DF3F28-888D-4C51-B489-03BA0C3F61B9}"/>
+    <hyperlink ref="J728" r:id="rId442" xr:uid="{255D0FAD-E3E9-4067-82EE-15BA4580046E}"/>
+    <hyperlink ref="J729" r:id="rId443" xr:uid="{FF114F67-7795-4D48-B8B1-9B2B2B813052}"/>
+    <hyperlink ref="J736" r:id="rId444" xr:uid="{788E8226-EC64-4AB4-A564-C2818E7A8692}"/>
+    <hyperlink ref="J738" r:id="rId445" xr:uid="{5E3399B1-2828-4506-90DD-45A014C8A18C}"/>
+    <hyperlink ref="J739" r:id="rId446" xr:uid="{CCC22DEC-3858-48AC-BC6C-7276E83A8F63}"/>
+    <hyperlink ref="J740" r:id="rId447" xr:uid="{0BE34E4C-E8D5-4B9D-8878-92DE447D9753}"/>
+    <hyperlink ref="J741" r:id="rId448" xr:uid="{AED20B76-FB58-463A-8A15-B1EC9B323601}"/>
+    <hyperlink ref="J742" r:id="rId449" xr:uid="{843B38FC-DA68-4ECD-A28C-2532591B4D27}"/>
+    <hyperlink ref="J743" r:id="rId450" xr:uid="{D49FBC3D-F246-4096-AB9D-FA1246A5A7EB}"/>
+    <hyperlink ref="J744" r:id="rId451" xr:uid="{A78F0163-2F03-4D7A-8772-83519003FD94}"/>
+    <hyperlink ref="J747" r:id="rId452" xr:uid="{A9CD81B7-2A9F-455C-B597-A0FAA584D3AE}"/>
+    <hyperlink ref="J748" r:id="rId453" xr:uid="{8880B9AB-CCF8-4C76-8D8E-5D0202AAAE8D}"/>
+    <hyperlink ref="J757" r:id="rId454" xr:uid="{98ACFD26-B498-428B-AFD2-46B9F11F0C87}"/>
+    <hyperlink ref="J758" r:id="rId455" xr:uid="{77E94A28-E1C5-41C3-8FAF-9852E1FD36B6}"/>
+    <hyperlink ref="J759" r:id="rId456" xr:uid="{5DAA0D02-ABC9-40B8-A26F-0B47A32D4A83}"/>
+    <hyperlink ref="J760" r:id="rId457" xr:uid="{750512F2-E8F8-45EF-8002-3D0D66B3B24F}"/>
+    <hyperlink ref="J761" r:id="rId458" xr:uid="{BF85A419-1282-4833-8D8C-A73E011DAE35}"/>
+    <hyperlink ref="J762" r:id="rId459" xr:uid="{5E89BCC1-2028-467B-9537-78E7450F8BD0}"/>
+    <hyperlink ref="J764" r:id="rId460" xr:uid="{9F492607-CC4C-4A30-B4E5-33CA14C7A6B9}"/>
+    <hyperlink ref="J765" r:id="rId461" xr:uid="{5B6B63CB-6926-460C-ACC1-1882EDA5BFC5}"/>
+    <hyperlink ref="J766" r:id="rId462" xr:uid="{137B13E4-CC7D-42AF-9C75-2828A61C5B14}"/>
+    <hyperlink ref="J767" r:id="rId463" xr:uid="{408D5749-3F43-45EE-B3DA-C45E54948CBB}"/>
+    <hyperlink ref="J769" r:id="rId464" xr:uid="{D3B15FC4-1778-41FF-8B79-9BB0787ADEC9}"/>
+    <hyperlink ref="J770" r:id="rId465" xr:uid="{3D504C95-A15B-4411-AABA-F017667BE88A}"/>
+    <hyperlink ref="J772" r:id="rId466" xr:uid="{EA77823B-4AB8-4A63-A147-9C095F3E4F53}"/>
+    <hyperlink ref="J774" r:id="rId467" xr:uid="{52116CEF-BD82-4E9E-8EB0-9E65B43D4282}"/>
+    <hyperlink ref="J778" r:id="rId468" xr:uid="{35505F82-CFC6-48F6-AF31-42030565027B}"/>
+    <hyperlink ref="J781" r:id="rId469" xr:uid="{9620F038-2CEB-45F8-B741-D6A1E85AF38B}"/>
+    <hyperlink ref="J783" r:id="rId470" xr:uid="{4B4DB440-459E-46A3-91C0-CC3E286A7D9D}"/>
+    <hyperlink ref="J784" r:id="rId471" xr:uid="{84ADE070-980A-49F1-B3EA-C3F97EEB1699}"/>
+    <hyperlink ref="J785" r:id="rId472" xr:uid="{676127B5-3AE6-450A-86F2-3893B5CB7E4E}"/>
+    <hyperlink ref="J788" r:id="rId473" xr:uid="{1BA851A6-CD4B-451C-B579-55B21E908530}"/>
+    <hyperlink ref="J789" r:id="rId474" xr:uid="{B76D1252-9099-4A6A-B375-DC2F240E082B}"/>
+    <hyperlink ref="J790" r:id="rId475" xr:uid="{EACF9D67-3322-420F-9F81-D23DFBFEA3C0}"/>
+    <hyperlink ref="J794" r:id="rId476" xr:uid="{705FD21F-2983-4DB6-93F5-86777975778A}"/>
+    <hyperlink ref="J795" r:id="rId477" xr:uid="{F3CE896A-E9A5-4527-899C-85AF26B0834F}"/>
+    <hyperlink ref="J796" r:id="rId478" xr:uid="{3BAC0AB3-B010-4BC2-A3F7-FD5E260125A7}"/>
+    <hyperlink ref="J797" r:id="rId479" xr:uid="{C42295A8-6603-4236-BC93-8AE36EC5B754}"/>
+    <hyperlink ref="J799" r:id="rId480" xr:uid="{26A317CE-7CA1-4EF5-A1C5-6B5484044B65}"/>
+    <hyperlink ref="J800" r:id="rId481" xr:uid="{AED07741-B55E-4D6C-BE34-5C0EDEB4EEB7}"/>
+    <hyperlink ref="J801" r:id="rId482" xr:uid="{722594B9-FFE2-47EE-BB08-EB443A079154}"/>
+    <hyperlink ref="J802" r:id="rId483" xr:uid="{6A20F88B-9695-4F93-8AC3-C2245CD7BFB4}"/>
+    <hyperlink ref="J803" r:id="rId484" xr:uid="{395545F9-1A7E-4592-BB42-0B7769A0D89D}"/>
+    <hyperlink ref="J804" r:id="rId485" xr:uid="{D3ACB6B6-464E-4C5B-BD3E-32CD8C7464A6}"/>
+    <hyperlink ref="J805" r:id="rId486" xr:uid="{36FBDA0C-4EC4-44CF-A787-1FE9FD2E0BCC}"/>
+    <hyperlink ref="J806" r:id="rId487" xr:uid="{6548A7D2-C797-41F1-A4B6-D5C73BBE8A51}"/>
+    <hyperlink ref="J808" r:id="rId488" xr:uid="{3F08D009-8AFE-4A31-A171-5BFF079A0931}"/>
+    <hyperlink ref="J810" r:id="rId489" xr:uid="{B04C71E7-3612-4EF7-AC04-5B80FBAF2227}"/>
+    <hyperlink ref="J811" r:id="rId490" xr:uid="{6A3950C5-3DF4-48BC-AF35-75CC0192254B}"/>
+    <hyperlink ref="J812" r:id="rId491" xr:uid="{F70CCC24-0B2A-4DCB-B688-59EC423FBBE7}"/>
+    <hyperlink ref="J813" r:id="rId492" xr:uid="{BEF9ADD6-58C5-4AD4-8FF9-4E409377B2D4}"/>
+    <hyperlink ref="J814" r:id="rId493" xr:uid="{F604D531-05A1-48AC-830E-E1275FADDDA0}"/>
+    <hyperlink ref="J815" r:id="rId494" xr:uid="{8F76AD90-D9B3-47B4-8111-E9FF7912E870}"/>
+    <hyperlink ref="J816" r:id="rId495" xr:uid="{C45180A3-164E-4CE8-9776-4CCFEB48AE03}"/>
+    <hyperlink ref="J817" r:id="rId496" xr:uid="{863E19FE-17AB-498C-AFCC-14817033208F}"/>
+    <hyperlink ref="J818" r:id="rId497" xr:uid="{54B369AC-B2AE-4270-B663-D4F191AF4DD1}"/>
+    <hyperlink ref="J819" r:id="rId498" xr:uid="{140EAD88-FCC3-4A0F-B902-0CB2A359F685}"/>
+    <hyperlink ref="J820" r:id="rId499" xr:uid="{0D1ED5A8-09DB-4780-9E0C-DFD7037DFD5E}"/>
+    <hyperlink ref="J821" r:id="rId500" xr:uid="{9C52BCBD-18B5-4A93-8863-0D7DF5A59D06}"/>
+    <hyperlink ref="J822" r:id="rId501" xr:uid="{A04400FB-214D-4AF6-87B2-6099419E5005}"/>
+    <hyperlink ref="J825" r:id="rId502" xr:uid="{13A934A9-671C-42E0-A985-3085B31A7E9B}"/>
+    <hyperlink ref="J826" r:id="rId503" xr:uid="{ED7D59B3-F42E-4A6B-9598-506A47FEF4A7}"/>
+    <hyperlink ref="J827" r:id="rId504" xr:uid="{EDDE9FDC-64C1-47D2-9E59-CA2762DAB713}"/>
+    <hyperlink ref="J828" r:id="rId505" xr:uid="{BF43BB96-CF31-4634-B514-DD78D3A0E172}"/>
+    <hyperlink ref="J831" r:id="rId506" xr:uid="{730A091A-8083-46C6-ACD6-AB8EBF017407}"/>
+    <hyperlink ref="J832" r:id="rId507" xr:uid="{DC2DEC17-EA1E-4CCE-BE59-93D672DA8BF7}"/>
+    <hyperlink ref="J833" r:id="rId508" xr:uid="{BB6922E0-8025-402E-A67A-7C914C33B9A8}"/>
+    <hyperlink ref="J836" r:id="rId509" xr:uid="{C0585FBC-8498-4CC0-9F15-1A00015052B6}"/>
+    <hyperlink ref="J837" r:id="rId510" xr:uid="{8570230C-389C-4038-ACA1-229BBC9BAD53}"/>
+    <hyperlink ref="J838" r:id="rId511" xr:uid="{F7B80C57-9F6A-4543-B074-2573ABCEC584}"/>
+    <hyperlink ref="J839" r:id="rId512" xr:uid="{8207215B-08D1-46AE-BBD3-1035E1D7048C}"/>
+    <hyperlink ref="J840" r:id="rId513" xr:uid="{FC7CB1A8-4FEA-4497-B5B4-A39BA3153D87}"/>
+    <hyperlink ref="J841" r:id="rId514" xr:uid="{CBF0402B-3635-4C92-B78F-A1BDE419A550}"/>
+    <hyperlink ref="J842" r:id="rId515" xr:uid="{AE62ACE8-8471-4955-A7D1-BDF633815463}"/>
+    <hyperlink ref="J843" r:id="rId516" xr:uid="{85D4B799-B164-42B0-BABB-072BA1A3D6BA}"/>
+    <hyperlink ref="J844" r:id="rId517" xr:uid="{65177B01-3558-4596-8F38-D43C764EB864}"/>
+    <hyperlink ref="J847" r:id="rId518" xr:uid="{0FF84ED9-8454-47FD-B316-4B9A70173E68}"/>
+    <hyperlink ref="J848" r:id="rId519" xr:uid="{1ED49319-0584-467E-9302-9D5E223B59F4}"/>
+    <hyperlink ref="J850" r:id="rId520" xr:uid="{B9094F1B-98AA-4DC2-80E9-622555E86D68}"/>
+    <hyperlink ref="J852" r:id="rId521" xr:uid="{A657C24A-0E78-45C8-9E71-B58739E36B77}"/>
+    <hyperlink ref="J853" r:id="rId522" xr:uid="{4077FB74-32B5-4DC9-B2C7-34C08988F32A}"/>
+    <hyperlink ref="J856" r:id="rId523" xr:uid="{B7706849-460D-4988-A49D-15D282DD2C47}"/>
+    <hyperlink ref="J858" r:id="rId524" xr:uid="{948FF48D-F86A-4C2F-B543-9AFA37ADCC86}"/>
+    <hyperlink ref="J861" r:id="rId525" xr:uid="{55A9A0AC-65E2-403D-A068-889473821D58}"/>
+    <hyperlink ref="J862" r:id="rId526" xr:uid="{376561C3-DF3F-4B73-BBC4-5696EF5ACA8A}"/>
+    <hyperlink ref="J863" r:id="rId527" xr:uid="{D775EBF5-6A9C-4732-A2CF-6F6B0671A9CA}"/>
+    <hyperlink ref="J865" r:id="rId528" xr:uid="{F88246EB-6242-40CF-A9BF-CAF00E99C001}"/>
+    <hyperlink ref="J866" r:id="rId529" xr:uid="{A76BD31B-BF78-4903-B62A-464E21A0BF39}"/>
+    <hyperlink ref="J867" r:id="rId530" xr:uid="{EF19E910-FE4C-4E86-AF47-473452FD6B31}"/>
+    <hyperlink ref="J868" r:id="rId531" xr:uid="{B8F082D0-98A4-4965-9DA0-116B90FA081A}"/>
+    <hyperlink ref="J870" r:id="rId532" xr:uid="{74EB3F50-1737-40E3-B27C-91F320896713}"/>
+    <hyperlink ref="J871" r:id="rId533" xr:uid="{60792E38-0B24-4502-9946-F378929375AB}"/>
+    <hyperlink ref="J872" r:id="rId534" xr:uid="{777E5F57-54B9-4C1F-A64C-E144981E6E84}"/>
+    <hyperlink ref="J873" r:id="rId535" xr:uid="{1BE7220F-0A84-476E-86D8-1F32FBFC3D68}"/>
+    <hyperlink ref="J875" r:id="rId536" xr:uid="{F9FD7240-522C-438E-BC75-53481A8DF253}"/>
+    <hyperlink ref="J877" r:id="rId537" xr:uid="{36386573-4622-4525-AC6A-86B73C188B8C}"/>
+    <hyperlink ref="J878" r:id="rId538" xr:uid="{81FC351E-5C86-4C7A-88F6-73D304AA8101}"/>
+    <hyperlink ref="J880" r:id="rId539" xr:uid="{9ADF0923-0EFE-426A-A357-CC02F903C89D}"/>
+    <hyperlink ref="J882" r:id="rId540" xr:uid="{D8CD8804-A082-4591-8289-EFB445395D7F}"/>
+    <hyperlink ref="J883" r:id="rId541" xr:uid="{9FBDF2E7-A465-407F-A945-50780DB5D6C1}"/>
+    <hyperlink ref="J884" r:id="rId542" xr:uid="{A1A34F15-1177-4AD3-BA63-3F3A1D8C779D}"/>
+    <hyperlink ref="J885" r:id="rId543" xr:uid="{E77CBEBC-E1E2-4C92-969F-6C0D430878BF}"/>
+    <hyperlink ref="J886" r:id="rId544" xr:uid="{C3C613E1-8694-4F33-A32A-BB05703A2550}"/>
+    <hyperlink ref="J888" r:id="rId545" xr:uid="{37BF0872-4A03-45C9-ABDA-8E67DAAE7BBD}"/>
+    <hyperlink ref="J889" r:id="rId546" xr:uid="{40285FC4-8E64-411E-9C7B-734503432D1A}"/>
+    <hyperlink ref="J893" r:id="rId547" xr:uid="{B5B50E5C-110C-4E9C-8E71-E3EC1F165931}"/>
+    <hyperlink ref="J894" r:id="rId548" xr:uid="{9360C61B-4D58-4D1A-ABFE-1FA25636ACBE}"/>
+    <hyperlink ref="J895" r:id="rId549" xr:uid="{051D7702-7702-41B9-8F47-5D87816D9A49}"/>
+    <hyperlink ref="J896" r:id="rId550" xr:uid="{A86373D8-3852-4526-841F-9C0A7C6E7259}"/>
+    <hyperlink ref="J897" r:id="rId551" xr:uid="{371882BA-31F5-4346-9451-9C401AC88ECF}"/>
+    <hyperlink ref="J899" r:id="rId552" xr:uid="{6A002F61-8AED-4E5B-BC83-55986146DC55}"/>
+    <hyperlink ref="J900" r:id="rId553" xr:uid="{47069B0A-BC67-4404-8939-A277B24B2B25}"/>
+    <hyperlink ref="J905" r:id="rId554" xr:uid="{1C988D06-9E69-465B-84DC-7727034BD76F}"/>
+    <hyperlink ref="J906" r:id="rId555" xr:uid="{CD4C0441-8DE1-4B1E-B687-556F2D3B0C7D}"/>
+    <hyperlink ref="J907" r:id="rId556" xr:uid="{7063487F-D4A9-4CE2-B8C3-82FFDA39E60A}"/>
+    <hyperlink ref="J908" r:id="rId557" xr:uid="{2C7B6297-B459-44F5-8884-0690A5A88C0C}"/>
+    <hyperlink ref="J909" r:id="rId558" xr:uid="{02A7F9A9-74CB-4C11-BF65-46553E5A25B0}"/>
+    <hyperlink ref="J910" r:id="rId559" xr:uid="{8E209C03-6B5F-4081-8EFA-5913FC77E401}"/>
+    <hyperlink ref="J911" r:id="rId560" xr:uid="{BE9D0DBC-FFF0-4C4E-8897-1FF0B2C9BC51}"/>
+    <hyperlink ref="J912" r:id="rId561" xr:uid="{04048352-097A-459A-B321-9E4C6CB12778}"/>
+    <hyperlink ref="J913" r:id="rId562" xr:uid="{348FDE81-EB64-4BCA-9572-5D31A105BD8C}"/>
+    <hyperlink ref="J914" r:id="rId563" xr:uid="{F9567989-DA91-4E6A-900F-52D8AED99C92}"/>
+    <hyperlink ref="J915" r:id="rId564" xr:uid="{E3AF29C2-DEF7-43DF-AD0D-2E3F414E35F2}"/>
+    <hyperlink ref="J916" r:id="rId565" xr:uid="{45584430-07D7-4058-B112-9EBCEA56A511}"/>
+    <hyperlink ref="J918" r:id="rId566" xr:uid="{47113754-6BDB-4F7C-B288-EF5CE0C0B9C9}"/>
+    <hyperlink ref="J919" r:id="rId567" xr:uid="{C205A6B2-4B44-40EA-B919-079299F0E045}"/>
+    <hyperlink ref="J922" r:id="rId568" xr:uid="{7C703D3C-F339-4BF7-92C1-C693D8ADA16D}"/>
+    <hyperlink ref="J923" r:id="rId569" xr:uid="{6C600C19-DF99-455A-A1D0-AA23759724BD}"/>
+    <hyperlink ref="J925" r:id="rId570" xr:uid="{FCAB65FC-07D1-422E-B2A7-3FB9EF0929CD}"/>
+    <hyperlink ref="J926" r:id="rId571" xr:uid="{01177C7E-3964-4DBC-973E-844E403671D4}"/>
+    <hyperlink ref="J928" r:id="rId572" xr:uid="{237F24EE-9F35-4123-A453-4CC6E8F7CE02}"/>
+    <hyperlink ref="J929" r:id="rId573" xr:uid="{1B91283F-81E7-4A23-927D-7772C4057B80}"/>
+    <hyperlink ref="J930" r:id="rId574" xr:uid="{170ACCD6-8091-4104-8FC4-DF3A156D6548}"/>
+    <hyperlink ref="J931" r:id="rId575" xr:uid="{F714436C-CED3-4826-9E46-3CCD2012B769}"/>
+    <hyperlink ref="J932" r:id="rId576" xr:uid="{35B94044-CB05-4614-8E25-6FC4B848D0AE}"/>
+    <hyperlink ref="J933" r:id="rId577" xr:uid="{431EFB2F-7ABE-4309-A314-E7354015E09D}"/>
+    <hyperlink ref="J935" r:id="rId578" xr:uid="{4AF7B7FD-3508-46D3-A7C0-8F46FD475A12}"/>
+    <hyperlink ref="J940" r:id="rId579" xr:uid="{7282146A-B40D-4A57-BE8F-1E0A69442B0B}"/>
+    <hyperlink ref="J941" r:id="rId580" xr:uid="{D157E729-9FE3-4DD4-A706-A810B2F73840}"/>
+    <hyperlink ref="J942" r:id="rId581" xr:uid="{5FDCBAC6-2E70-414D-AB02-7082E16F6D17}"/>
+    <hyperlink ref="J943" r:id="rId582" xr:uid="{9FD7437B-7E86-4A89-AE15-C177424CDBEC}"/>
+    <hyperlink ref="J944" r:id="rId583" xr:uid="{C9AE6DB2-0BD8-45A9-99D1-39D2FB817E08}"/>
+    <hyperlink ref="J946" r:id="rId584" xr:uid="{244C25D3-CE68-4215-9DE8-1327388D8840}"/>
+    <hyperlink ref="J947" r:id="rId585" xr:uid="{0C6185C0-7898-447C-A618-A7EC92BD1AF5}"/>
+    <hyperlink ref="J948" r:id="rId586" xr:uid="{F5843415-A37A-49F9-B33A-2FD19129950E}"/>
+    <hyperlink ref="J949" r:id="rId587" xr:uid="{DD1999B0-1BE4-4862-BD0D-E5A4185F7C00}"/>
+    <hyperlink ref="J950" r:id="rId588" xr:uid="{F5269955-67FC-4C87-B590-F98D2E46009B}"/>
+    <hyperlink ref="J952" r:id="rId589" xr:uid="{FA6B0C7E-EE90-4760-B0C4-71ABE3196562}"/>
+    <hyperlink ref="J953" r:id="rId590" xr:uid="{07965BC0-A473-461B-9CCC-F605A236B031}"/>
+    <hyperlink ref="J954" r:id="rId591" xr:uid="{3D6BCD16-C50A-414C-BBE2-1F0D15AF237B}"/>
+    <hyperlink ref="J955" r:id="rId592" xr:uid="{B1B455D0-3E9A-4503-9F5F-2CE50C159252}"/>
+    <hyperlink ref="J956" r:id="rId593" xr:uid="{8065BBAD-F7CB-41F3-8B3B-72C91FD3DFAB}"/>
+    <hyperlink ref="J958" r:id="rId594" xr:uid="{0B66D3D7-AEB9-4D00-947F-F90023FE28BB}"/>
+    <hyperlink ref="J962" r:id="rId595" xr:uid="{7A4861FD-5B27-4696-9830-4EF2F317FE50}"/>
+    <hyperlink ref="J963" r:id="rId596" xr:uid="{42BEE64B-AC84-44F2-946B-6EF43EE4883F}"/>
+    <hyperlink ref="J965" r:id="rId597" xr:uid="{75D0AB47-45D1-4388-84AC-443F9713E53A}"/>
+    <hyperlink ref="J968" r:id="rId598" xr:uid="{166A3FF2-A51B-44F8-87DD-9A1B2AB69668}"/>
+    <hyperlink ref="J969" r:id="rId599" xr:uid="{4F369509-65F1-4511-A833-1722E3BC30D8}"/>
+    <hyperlink ref="J971" r:id="rId600" xr:uid="{2F7704A9-736E-4CD0-AAE4-6FDDF9F27CE8}"/>
+    <hyperlink ref="J973" r:id="rId601" xr:uid="{7924AA75-9CD6-45D5-B99A-2A68DC17E93A}"/>
+    <hyperlink ref="J974" r:id="rId602" xr:uid="{232002F3-F384-4714-9E12-D328412CB92A}"/>
+    <hyperlink ref="J975" r:id="rId603" xr:uid="{EF1EABC6-BEA6-48B7-BA8B-C63FF1DC53D8}"/>
+    <hyperlink ref="J976" r:id="rId604" xr:uid="{CCDBB4E8-E35E-4A34-A1A4-A3E66D003683}"/>
+    <hyperlink ref="J977" r:id="rId605" xr:uid="{B7ECF985-0164-4412-8A8F-6DB340646900}"/>
+    <hyperlink ref="J981" r:id="rId606" xr:uid="{2AD769E5-68EE-4A86-A3DA-55CE7931747C}"/>
+    <hyperlink ref="J984" r:id="rId607" xr:uid="{20001AF8-EBED-417E-8A71-A8C2C3CF9874}"/>
+    <hyperlink ref="J986" r:id="rId608" xr:uid="{A12A61FA-1D1D-4062-93A7-DD4C41F026CC}"/>
+    <hyperlink ref="J990" r:id="rId609" xr:uid="{5C330F4C-256B-4430-8047-AE0FCD64AC6A}"/>
+    <hyperlink ref="J991" r:id="rId610" xr:uid="{57D4C0E5-B674-45BB-A817-9E4A1D43A48D}"/>
+    <hyperlink ref="J996" r:id="rId611" xr:uid="{9AA820E7-50B3-47E0-85B8-CF09FDEE9222}"/>
+    <hyperlink ref="J997" r:id="rId612" xr:uid="{23C38B8F-2461-4343-BB96-46CC829F2C62}"/>
+    <hyperlink ref="J999" r:id="rId613" xr:uid="{42017C05-DD15-4721-806F-2595428D5DBF}"/>
+    <hyperlink ref="J1000" r:id="rId614" xr:uid="{82184D32-3AFE-4661-A0DE-F7E0D0B95DA4}"/>
+    <hyperlink ref="J1003" r:id="rId615" xr:uid="{B91021A5-0205-44BD-A1F9-6F2E3BDC3AA4}"/>
+    <hyperlink ref="J1004" r:id="rId616" xr:uid="{74BA2B2E-1B37-47FE-BE74-65E0745F38EC}"/>
+    <hyperlink ref="J1005" r:id="rId617" xr:uid="{AEC0F090-186A-4865-9B35-C7A5669EF9FD}"/>
+    <hyperlink ref="J1006" r:id="rId618" xr:uid="{DB95782B-BC4D-429D-8BAE-235A22C172E0}"/>
+    <hyperlink ref="J1007" r:id="rId619" xr:uid="{2A289A2C-93D0-412D-B0FB-1DB7C9C94CDF}"/>
+    <hyperlink ref="J1008" r:id="rId620" xr:uid="{435D7543-E6B4-444A-8AA2-AB1F621C8612}"/>
+    <hyperlink ref="J1009" r:id="rId621" xr:uid="{1B4A792F-ACD7-43A7-932E-0CE988C58ED5}"/>
+    <hyperlink ref="J1011" r:id="rId622" xr:uid="{C12CC17B-6372-4992-BE09-15A3E48F04F8}"/>
+    <hyperlink ref="J1012" r:id="rId623" xr:uid="{3AC4F8E6-A5B9-43BC-8552-8D582A7A91D9}"/>
+    <hyperlink ref="J1016" r:id="rId624" xr:uid="{000BB294-3068-449F-908E-6B359582C9B0}"/>
+    <hyperlink ref="J1019" r:id="rId625" xr:uid="{8992C019-CB84-40C8-BA19-0F7AFE34D4FA}"/>
+    <hyperlink ref="J1020" r:id="rId626" xr:uid="{4AF07A09-EB41-4113-B83B-DFCA9B3EA915}"/>
+    <hyperlink ref="J1023" r:id="rId627" xr:uid="{0C715B7D-959D-4737-93D8-8E3384BB3BB2}"/>
+    <hyperlink ref="J1024" r:id="rId628" xr:uid="{FF9FE666-C866-483A-BA43-0BA26AC544AB}"/>
+    <hyperlink ref="J1025" r:id="rId629" xr:uid="{DDF76A14-8A6B-4585-BFBA-9F78BF514300}"/>
+    <hyperlink ref="J1026" r:id="rId630" xr:uid="{38A2C84C-FF2C-4BC3-90E5-1F9B074DA3EF}"/>
+    <hyperlink ref="J1027" r:id="rId631" xr:uid="{0591522E-35AE-43C5-BAF4-F420F1AF0D84}"/>
+    <hyperlink ref="J1028" r:id="rId632" xr:uid="{3430D2F7-664B-47CD-85AE-2B40119ED34B}"/>
+    <hyperlink ref="J1030" r:id="rId633" xr:uid="{3E243B30-7A97-4565-9A86-9C7A6373DA3C}"/>
+    <hyperlink ref="J1033" r:id="rId634" xr:uid="{4BE3D379-5FB8-4322-9669-A3FE9E12C71C}"/>
+    <hyperlink ref="J1034" r:id="rId635" xr:uid="{D95AA629-79C1-42F4-80F2-203D4E38CA92}"/>
+    <hyperlink ref="J1036" r:id="rId636" xr:uid="{69504F97-6DDC-4DCF-A5F0-245D587DD296}"/>
+    <hyperlink ref="J1037" r:id="rId637" xr:uid="{169C8212-0ED8-477D-9E5D-F3F37033AEA1}"/>
+    <hyperlink ref="J1041" r:id="rId638" xr:uid="{32C365DE-2ADF-4B76-BAED-8E7015ADC051}"/>
+    <hyperlink ref="J1042" r:id="rId639" xr:uid="{12C3A2A9-D763-4329-A81A-7947C84A1F36}"/>
+    <hyperlink ref="J1043" r:id="rId640" xr:uid="{345A7B5F-7A1A-4606-9C48-EBBB6206A6AC}"/>
+    <hyperlink ref="J1044" r:id="rId641" xr:uid="{FE2024CD-9B1A-4AB6-9EA1-BC66673BC2DE}"/>
+    <hyperlink ref="J1046" r:id="rId642" xr:uid="{18AB04A7-4CB6-4DCA-B227-5D58313D46A4}"/>
+    <hyperlink ref="J1047" r:id="rId643" xr:uid="{AA8B0722-11B6-4479-BA30-8896FE48A097}"/>
+    <hyperlink ref="J1051" r:id="rId644" xr:uid="{08850F3C-0036-4B8B-B897-3FA05E1DD828}"/>
+    <hyperlink ref="J1052" r:id="rId645" xr:uid="{74C903A4-681D-4499-99A9-129023538E8C}"/>
+    <hyperlink ref="J1054" r:id="rId646" xr:uid="{CD147121-1395-43F3-BFCF-9A3988DD8E8A}"/>
+    <hyperlink ref="J1056" r:id="rId647" xr:uid="{454A44C0-4B14-42D8-893A-CFAB4EAF849D}"/>
+    <hyperlink ref="J1064" r:id="rId648" xr:uid="{884294BE-427E-4975-99F7-3AFF5BCE1C3C}"/>
+    <hyperlink ref="J1065" r:id="rId649" xr:uid="{41D4A546-044E-4FD1-BF89-15D3D10B61FF}"/>
+    <hyperlink ref="J1066" r:id="rId650" xr:uid="{CA7A0D27-7A75-4E29-8D54-FB1D5B6E320C}"/>
+    <hyperlink ref="J1067" r:id="rId651" xr:uid="{DDA150BE-8ED8-4AE0-B5CC-BBC61BEFDA61}"/>
+    <hyperlink ref="J1068" r:id="rId652" xr:uid="{8DDCA776-E55A-491C-91B0-062CC4AC0EDF}"/>
+    <hyperlink ref="J1069" r:id="rId653" xr:uid="{B14F056E-2FB6-44E9-AC30-1E541788DB05}"/>
+    <hyperlink ref="J1070" r:id="rId654" xr:uid="{677153C8-0759-4902-BA7B-581987735EA6}"/>
+    <hyperlink ref="J1071" r:id="rId655" xr:uid="{288115C9-24CD-4B59-A386-280A9A071579}"/>
+    <hyperlink ref="J1072" r:id="rId656" xr:uid="{649B8EED-F58D-40C5-AE44-E7501839B175}"/>
+    <hyperlink ref="J1073" r:id="rId657" xr:uid="{432CA7A7-72E8-4045-B0B6-3DFB52AF631F}"/>
+    <hyperlink ref="J1076" r:id="rId658" xr:uid="{CC6A8575-6EEC-4F2C-A28B-0DAC6CA9D635}"/>
+    <hyperlink ref="J1077" r:id="rId659" xr:uid="{4D08E705-E8A0-440C-B81C-E6C1219BF030}"/>
+    <hyperlink ref="J1078" r:id="rId660" xr:uid="{8B244B83-F13A-4484-87C2-FC2DD8B237D6}"/>
+    <hyperlink ref="J1080" r:id="rId661" xr:uid="{D2A468E7-C797-4107-8A7F-15FA0B073781}"/>
+    <hyperlink ref="J1082" r:id="rId662" xr:uid="{4DA244F7-7E14-49F8-877B-294A0C8B3908}"/>
+    <hyperlink ref="J1086" r:id="rId663" xr:uid="{E8937F20-1C9D-478F-A095-49609DE5B09B}"/>
+    <hyperlink ref="J1087" r:id="rId664" xr:uid="{B36E2C8B-ED89-4DE1-806E-638B35A601A3}"/>
+    <hyperlink ref="J1088" r:id="rId665" xr:uid="{15785FEF-A412-48AD-9A83-2DE4D77D766A}"/>
+    <hyperlink ref="J1090" r:id="rId666" xr:uid="{10303626-2EE5-40C2-88BA-1D09F4535DC8}"/>
+    <hyperlink ref="J1091" r:id="rId667" xr:uid="{E0D05F3E-B118-429A-9848-CA2F9FEDC669}"/>
+    <hyperlink ref="J1098" r:id="rId668" xr:uid="{34786FF5-6020-4A34-975A-0504922508C0}"/>
+    <hyperlink ref="J1100" r:id="rId669" xr:uid="{6B875F50-EF34-4BBE-88F1-5D4BCF2E3164}"/>
+    <hyperlink ref="J1102" r:id="rId670" xr:uid="{A774B16C-B711-47EE-9721-D639FA7C491E}"/>
+    <hyperlink ref="J1103" r:id="rId671" xr:uid="{69583A86-3BD2-4F38-8E58-76CF577345B9}"/>
+    <hyperlink ref="J1104" r:id="rId672" xr:uid="{484668BC-9C9E-4E39-80EF-50525F37FA44}"/>
+    <hyperlink ref="J1106" r:id="rId673" xr:uid="{768D8655-98C0-4A1B-85A0-DD6980D7A19E}"/>
+    <hyperlink ref="J1109" r:id="rId674" xr:uid="{BD75613E-6A11-4F06-A8DD-7B499F8CB68F}"/>
+    <hyperlink ref="J1110" r:id="rId675" xr:uid="{5E4FAEC1-78B7-4610-B522-34690BB21C07}"/>
+    <hyperlink ref="J1113" r:id="rId676" xr:uid="{29F84B81-1324-415A-A7ED-73270EA94F66}"/>
+    <hyperlink ref="J1114" r:id="rId677" xr:uid="{59D543CA-0F5C-4FE4-A2E8-8A0F0474B18D}"/>
+    <hyperlink ref="J1115" r:id="rId678" xr:uid="{649ACE2B-139A-42C3-B6A8-5EDE1F609954}"/>
+    <hyperlink ref="J1116" r:id="rId679" xr:uid="{5131F61F-5CDA-46AB-A6D3-F29F7DD0B9A3}"/>
+    <hyperlink ref="J1117" r:id="rId680" xr:uid="{31437A31-B485-4FA3-A9F2-5D0A46A5A7D0}"/>
+    <hyperlink ref="J1118" r:id="rId681" xr:uid="{09F77F41-29FA-4AED-B040-140FE8B9CF8E}"/>
+    <hyperlink ref="J1119" r:id="rId682" xr:uid="{F881B1D2-5326-47AD-9C19-6CBC043067DC}"/>
+    <hyperlink ref="J1124" r:id="rId683" xr:uid="{535C8650-D9EA-429D-8B34-5B89230ACD8F}"/>
+    <hyperlink ref="J1125" r:id="rId684" xr:uid="{4D5B629A-0B0A-4FBC-B386-03B0F247F3B4}"/>
+    <hyperlink ref="J1126" r:id="rId685" xr:uid="{9EB718D0-4873-4E6F-B9C5-8CE0AE020F6D}"/>
+    <hyperlink ref="J1127" r:id="rId686" xr:uid="{F9ABF3D6-2E26-4259-BBA5-F1918A2625AD}"/>
+    <hyperlink ref="J1128" r:id="rId687" xr:uid="{C728419D-1D0F-4DE6-B4B8-3567739149CC}"/>
+    <hyperlink ref="J1129" r:id="rId688" xr:uid="{6AD56049-B8D9-4CF3-8E43-703BDC934266}"/>
+    <hyperlink ref="J1130" r:id="rId689" xr:uid="{725238DC-A483-4F60-849C-C033DAC32C98}"/>
+    <hyperlink ref="J1131" r:id="rId690" xr:uid="{B48B265D-72CB-4E13-99E0-48FD35990F98}"/>
+    <hyperlink ref="J1132" r:id="rId691" xr:uid="{078877EF-F092-4724-9598-CAD393F82EAA}"/>
+    <hyperlink ref="J1133" r:id="rId692" xr:uid="{693A1708-235D-4938-A162-206AC298B4E3}"/>
+    <hyperlink ref="J1134" r:id="rId693" xr:uid="{194DAD5C-9F51-49B6-B0A7-8288DFEEFD61}"/>
+    <hyperlink ref="J1135" r:id="rId694" xr:uid="{5D8ECEC4-A2CF-4A57-AD2E-59A40F5FED42}"/>
+    <hyperlink ref="J1136" r:id="rId695" xr:uid="{AB4B2CE1-FEB1-41CE-93D6-AA3D2E9FADD9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId662"/>
+  <pageSetup orientation="portrait" r:id="rId696"/>
   <tableParts count="1">
-    <tablePart r:id="rId663"/>
+    <tablePart r:id="rId697"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos junio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4407DC92-F329-47AC-B5C5-154283D2CFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F14C60-D12D-43E3-A47B-C92A63F79AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5115" yWindow="3015" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rechazos Calle" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$1136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rechazos Calle'!$A$1:$M$1192</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9863" uniqueCount="3029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10332" uniqueCount="3153">
   <si>
     <t>Fecha</t>
   </si>
@@ -9153,6 +9153,381 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782509074/smcwehd7fzmw3ouci2zb.jpg</t>
+  </si>
+  <si>
+    <t>MQWB9WEQUQMK</t>
+  </si>
+  <si>
+    <t>Pusieron 12 pehuamar matamoros en vez de lays asado
+1 maní sal y limón sin stock</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782561834/ay0lgwdmcyaa6sipddpj.jpg</t>
+  </si>
+  <si>
+    <t>MQWBT1PRSQPY</t>
+  </si>
+  <si>
+    <t>Rechazo 30 celusal entrefino</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — Mal facturado</t>
+  </si>
+  <si>
+    <t>MQWC12HDA6WK</t>
+  </si>
+  <si>
+    <t>Maniax sal y limón 4</t>
+  </si>
+  <si>
+    <t>MQWCIHIG012L</t>
+  </si>
+  <si>
+    <t>MQWCK37O7WGD</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782564039/odzwu6vyoaa4tkm17aoy.jpg</t>
+  </si>
+  <si>
+    <t>MQWCYJZ9C9X8</t>
+  </si>
+  <si>
+    <t>MQWDNZHBBCM2</t>
+  </si>
+  <si>
+    <t>Fue 1 Doritos queso 40gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782565844/brqlavzre4vcud5s6i49.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Mal Armado</t>
+  </si>
+  <si>
+    <t>MQWDZIOVT28M</t>
+  </si>
+  <si>
+    <t>Falta 1 Doritos x 40g 
+Desarmo otro cl</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782566385/xldytwxigonucxjartmh.jpg</t>
+  </si>
+  <si>
+    <t>MQWEH35OVWVC</t>
+  </si>
+  <si>
+    <t>MQWEMQFGNY1R</t>
+  </si>
+  <si>
+    <t>4 te de queso de 40</t>
+  </si>
+  <si>
+    <t>MQWEVXYRNHVP</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782567889/pkxvuz0alsjbexvaywop.jpg</t>
+  </si>
+  <si>
+    <t>MQWEY1G74LFD</t>
+  </si>
+  <si>
+    <t>MQWF5FPURKF1</t>
+  </si>
+  <si>
+    <t>Pepas frutos rojos sin stock</t>
+  </si>
+  <si>
+    <t>MQWG8QE1JLER</t>
+  </si>
+  <si>
+    <t>11:22 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782570166/s4sqb7m1smexwsj6uxxj.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Me confundí de clientes!! (Zona nueva)</t>
+  </si>
+  <si>
+    <t>MQWGB7NTYYL2</t>
+  </si>
+  <si>
+    <t>Falta un 3d de 43</t>
+  </si>
+  <si>
+    <t>MQWHSMU2LM87</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782572778/kbbeu3kdj39q7oytaezp.jpg</t>
+  </si>
+  <si>
+    <t>MQWHV3Z85R1R</t>
+  </si>
+  <si>
+    <t>MQWI4LQTKB4R</t>
+  </si>
+  <si>
+    <t>Faltó toddy cacao</t>
+  </si>
+  <si>
+    <t>MQWICGX56PIP</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782573701/ws5ahls4smtotxzpl6kq.jpg</t>
+  </si>
+  <si>
+    <t>Dejá el pedido, lo resuelvo después — Falta de mercaderia</t>
+  </si>
+  <si>
+    <t>MQWILPMVG270</t>
+  </si>
+  <si>
+    <t>Rechazo por el precio dice que te aviso</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782574135/itu6wgv04bcnpoyxj8v8.jpg</t>
+  </si>
+  <si>
+    <t>MQWO6FVNYYIC</t>
+  </si>
+  <si>
+    <t>03:05 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782583501/ezzcskoncetl6sv4wsaz.jpg</t>
+  </si>
+  <si>
+    <t>MQWO8KB9D6CC</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782583603/c3k4vyg6gndhx31uvnt4.jpg</t>
+  </si>
+  <si>
+    <t>MQWOKBPTTELR</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782584155/xkjuzo3mwhn1wnjr5gzj.jpg</t>
+  </si>
+  <si>
+    <t>MQZ0ZNEU6NSP</t>
+  </si>
+  <si>
+    <t>06:40 a. m.</t>
+  </si>
+  <si>
+    <t>Eran minifantoches negros</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782726004/a0l7gdrhbcoliengphgd.jpg</t>
+  </si>
+  <si>
+    <t>MQZ3VWM2CFAH</t>
+  </si>
+  <si>
+    <t>MQZ4NLSO8DTA</t>
+  </si>
+  <si>
+    <t>Pep común</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782732097/i5sdrecbswhqsywtolpw.jpg</t>
+  </si>
+  <si>
+    <t>MQZ5QRUT83QR</t>
+  </si>
+  <si>
+    <t>08:53 a. m.</t>
+  </si>
+  <si>
+    <t>Fue 1 unidad de lays 20gr y 1 de Doritos queso 20gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782733941/upvwjb4ejrzt37vfpeqa.jpg</t>
+  </si>
+  <si>
+    <t>MQZ5RTOWCNDW</t>
+  </si>
+  <si>
+    <t>Faltan 3 pep rueditas de 74 grs</t>
+  </si>
+  <si>
+    <t>MQZ5S0UC7CH3</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782733994/jvxh8yp5hcw7s4f2gfe2.jpg</t>
+  </si>
+  <si>
+    <t>MQZ6G6UMJSWJ</t>
+  </si>
+  <si>
+    <t>Hs ?</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782735117/tjxuk7fquw7r0grrrbim.jpg</t>
+  </si>
+  <si>
+    <t>MQZ7TD4C4RVE</t>
+  </si>
+  <si>
+    <t>No recibió las harinas</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782737411/edw4kfldrqdjf1hysmyq.jpg</t>
+  </si>
+  <si>
+    <t>MQZ7W8LQR2SX</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782737569/ya06bdyh1mzmz6l0vjj4.jpg</t>
+  </si>
+  <si>
+    <t>MQZ81W66DE5O</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782737813/nng8c9qtdvuqiqfbcoo6.jpg</t>
+  </si>
+  <si>
+    <t>MQZ898CFPL3L</t>
+  </si>
+  <si>
+    <t>MQZ8DMTD4HS5</t>
+  </si>
+  <si>
+    <t>MQZ8J3IOVK7D</t>
+  </si>
+  <si>
+    <t>5 dinamita 82 grs 5 dinamita 82 grs extra flaming</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Error de pedido de cliente por gramaje</t>
+  </si>
+  <si>
+    <t>MQZ8QM32CNUT</t>
+  </si>
+  <si>
+    <t>Rechaza esta boleta por el precio</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782738958/savvebtltvdbr3mwgrng.jpg</t>
+  </si>
+  <si>
+    <t>MQZ913WMWQ88</t>
+  </si>
+  <si>
+    <t>Pañalxx g x 50</t>
+  </si>
+  <si>
+    <t>MQZ9CY7PXLFV</t>
+  </si>
+  <si>
+    <t>12 speed</t>
+  </si>
+  <si>
+    <t>MQZ9PXI5P1LS</t>
+  </si>
+  <si>
+    <t>Rechaza alfajor blanco</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782740604/v5zrwywmorx1hczg4sz3.jpg</t>
+  </si>
+  <si>
+    <t>MQZ9RQ30H4K7</t>
+  </si>
+  <si>
+    <t>Pedido completo rechazado</t>
+  </si>
+  <si>
+    <t>MQZ9WDK4A764</t>
+  </si>
+  <si>
+    <t>MQZA3VNED05F</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782741269/vv3t8scsgsocjzwuv7tg.jpg</t>
+  </si>
+  <si>
+    <t>MQZA5T86AEMS</t>
+  </si>
+  <si>
+    <t>MQZALP89FD0Z</t>
+  </si>
+  <si>
+    <t>MQZANZO14AF5</t>
+  </si>
+  <si>
+    <t>MQZAOXHFWQI5</t>
+  </si>
+  <si>
+    <t>Pep comun 84g sin stock n</t>
+  </si>
+  <si>
+    <t>MQZB5VUYH102</t>
+  </si>
+  <si>
+    <t>2 twistos 40 grs faltaron</t>
+  </si>
+  <si>
+    <t>MQZBVXXAI1YI</t>
+  </si>
+  <si>
+    <t>Rechaza arroz luchetti</t>
+  </si>
+  <si>
+    <t>MQZC45B7Q56S</t>
+  </si>
+  <si>
+    <t>Faltaron 20 64054</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782744648/odqqh1codlc09i9ggqo1.jpg</t>
+  </si>
+  <si>
+    <t>El cliente va a recibir — seguí viaje — Falto 20 mani</t>
+  </si>
+  <si>
+    <t>MQZCC1M2S7Y9</t>
+  </si>
+  <si>
+    <t>Faltan 20 64055</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782745008/vibkbc3kkq2or3mqogbr.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El cliente va a recibir — seguí viaje — Falta de mercaderia 
+</t>
+  </si>
+  <si>
+    <t>MQZD3SLT3AUP</t>
+  </si>
+  <si>
+    <t>Un 3d de 23 g</t>
+  </si>
+  <si>
+    <t>MQZDJQXCYLG0</t>
+  </si>
+  <si>
+    <t>12:30 p. m.</t>
+  </si>
+  <si>
+    <t>Rechaza sal precio</t>
+  </si>
+  <si>
+    <t>MQZEGKHJKIVR</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782748565/dako4gumkphkq4xcefl0.jpg</t>
+  </si>
+  <si>
+    <t>MQZFI6WQE3BB</t>
+  </si>
+  <si>
+    <t>MQZG9Q0WJ68T</t>
+  </si>
+  <si>
+    <t>9761 faltan 3</t>
   </si>
 </sst>
 </file>
@@ -9543,8 +9918,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N1136">
-  <autoFilter ref="A1:N1136" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla_1" displayName="Tabla_1" ref="A1:N1192">
+  <autoFilter ref="A1:N1192" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fecha"/>
@@ -9766,7 +10141,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N1136"/>
+  <dimension ref="A1:N1192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -56451,708 +56826,3006 @@
         <v>6</v>
       </c>
     </row>
+    <row r="1137" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1137" s="3" t="s">
+        <v>3029</v>
+      </c>
+      <c r="B1137" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1137" s="13">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="D1137" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1137" s="5" t="s">
+        <v>2975</v>
+      </c>
+      <c r="F1137" s="6">
+        <v>2566</v>
+      </c>
+      <c r="G1137" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1137" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1137" s="5" t="s">
+        <v>3030</v>
+      </c>
+      <c r="J1137" s="11" t="s">
+        <v>3031</v>
+      </c>
+      <c r="K1137" s="8"/>
+      <c r="L1137" s="8"/>
+      <c r="M1137" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1137" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1138" s="3" t="s">
+        <v>3032</v>
+      </c>
+      <c r="B1138" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1138" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D1138" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1138" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1138" s="6">
+        <v>2556</v>
+      </c>
+      <c r="G1138" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1138" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1138" s="5" t="s">
+        <v>3033</v>
+      </c>
+      <c r="J1138" s="8"/>
+      <c r="K1138" s="5" t="s">
+        <v>3034</v>
+      </c>
+      <c r="L1138" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1138" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1138" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1139" s="3" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B1139" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1139" s="5" t="s">
+        <v>1245</v>
+      </c>
+      <c r="D1139" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1139" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1139" s="6">
+        <v>7125</v>
+      </c>
+      <c r="G1139" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1139" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1139" s="5" t="s">
+        <v>3036</v>
+      </c>
+      <c r="J1139" s="8"/>
+      <c r="K1139" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1139" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1139" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1139" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1140" s="3" t="s">
+        <v>3037</v>
+      </c>
+      <c r="B1140" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1140" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1140" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1140" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1140" s="6">
+        <v>7153</v>
+      </c>
+      <c r="G1140" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1140" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1140" s="8"/>
+      <c r="J1140" s="8"/>
+      <c r="K1140" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1140" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1140" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1140" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1141" s="3" t="s">
+        <v>3038</v>
+      </c>
+      <c r="B1141" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1141" s="13">
+        <v>0.40347222222222223</v>
+      </c>
+      <c r="D1141" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1141" s="5" t="s">
+        <v>2975</v>
+      </c>
+      <c r="F1141" s="6">
+        <v>4105</v>
+      </c>
+      <c r="G1141" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1141" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1141" s="8"/>
+      <c r="J1141" s="11" t="s">
+        <v>3039</v>
+      </c>
+      <c r="K1141" s="8"/>
+      <c r="L1141" s="8"/>
+      <c r="M1141" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1141" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1142" s="3" t="s">
+        <v>3040</v>
+      </c>
+      <c r="B1142" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1142" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D1142" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1142" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1142" s="6">
+        <v>7142</v>
+      </c>
+      <c r="G1142" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1142" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1142" s="8"/>
+      <c r="J1142" s="8"/>
+      <c r="K1142" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1142" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1142" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1142" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1143" s="3" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B1143" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1143" s="5" t="s">
+        <v>2333</v>
+      </c>
+      <c r="D1143" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1143" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1143" s="6">
+        <v>2206</v>
+      </c>
+      <c r="G1143" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1143" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1143" s="5" t="s">
+        <v>3042</v>
+      </c>
+      <c r="J1143" s="11" t="s">
+        <v>3043</v>
+      </c>
+      <c r="K1143" s="5" t="s">
+        <v>3044</v>
+      </c>
+      <c r="L1143" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1143" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1143" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1144" s="3" t="s">
+        <v>3045</v>
+      </c>
+      <c r="B1144" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1144" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1144" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1144" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1144" s="6">
+        <v>4363</v>
+      </c>
+      <c r="G1144" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1144" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1144" s="5" t="s">
+        <v>3046</v>
+      </c>
+      <c r="J1144" s="11" t="s">
+        <v>3047</v>
+      </c>
+      <c r="K1144" s="8"/>
+      <c r="L1144" s="8"/>
+      <c r="M1144" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1144" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1145" s="3" t="s">
+        <v>3048</v>
+      </c>
+      <c r="B1145" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1145" s="13">
+        <v>0.43958333333333333</v>
+      </c>
+      <c r="D1145" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1145" s="5" t="s">
+        <v>2975</v>
+      </c>
+      <c r="F1145" s="6">
+        <v>4345</v>
+      </c>
+      <c r="G1145" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1145" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1145" s="8"/>
+      <c r="J1145" s="8"/>
+      <c r="K1145" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1145" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1145" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1145" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1146" s="3" t="s">
+        <v>3049</v>
+      </c>
+      <c r="B1146" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1146" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D1146" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1146" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1146" s="6">
+        <v>7101</v>
+      </c>
+      <c r="G1146" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1146" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1146" s="5" t="s">
+        <v>3050</v>
+      </c>
+      <c r="J1146" s="8"/>
+      <c r="K1146" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1146" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1146" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1146" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1147" s="3" t="s">
+        <v>3051</v>
+      </c>
+      <c r="B1147" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1147" s="13">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D1147" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1147" s="5" t="s">
+        <v>2975</v>
+      </c>
+      <c r="F1147" s="6">
+        <v>4335</v>
+      </c>
+      <c r="G1147" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1147" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1147" s="8"/>
+      <c r="J1147" s="11" t="s">
+        <v>3052</v>
+      </c>
+      <c r="K1147" s="8"/>
+      <c r="L1147" s="8"/>
+      <c r="M1147" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1147" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1148" s="3" t="s">
+        <v>3053</v>
+      </c>
+      <c r="B1148" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1148" s="13">
+        <v>0.44861111111111113</v>
+      </c>
+      <c r="D1148" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1148" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1148" s="6">
+        <v>6566</v>
+      </c>
+      <c r="G1148" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1148" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1148" s="8"/>
+      <c r="J1148" s="8"/>
+      <c r="K1148" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1148" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1148" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1148" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1149" s="3" t="s">
+        <v>3054</v>
+      </c>
+      <c r="B1149" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1149" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="D1149" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1149" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1149" s="6">
+        <v>5261</v>
+      </c>
+      <c r="G1149" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1149" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1149" s="5" t="s">
+        <v>3055</v>
+      </c>
+      <c r="J1149" s="8"/>
+      <c r="K1149" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1149" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1149" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1149" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1150" s="3" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B1150" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1150" s="5" t="s">
+        <v>3057</v>
+      </c>
+      <c r="D1150" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1150" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1150" s="6">
+        <v>3505</v>
+      </c>
+      <c r="G1150" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1150" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1150" s="8"/>
+      <c r="J1150" s="11" t="s">
+        <v>3058</v>
+      </c>
+      <c r="K1150" s="5" t="s">
+        <v>3059</v>
+      </c>
+      <c r="L1150" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1150" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1150" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1151" s="3" t="s">
+        <v>3060</v>
+      </c>
+      <c r="B1151" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1151" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1151" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1151" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1151" s="6">
+        <v>4333</v>
+      </c>
+      <c r="G1151" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1151" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1151" s="5" t="s">
+        <v>3061</v>
+      </c>
+      <c r="J1151" s="8"/>
+      <c r="K1151" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1151" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1151" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1151" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1152" s="3" t="s">
+        <v>3062</v>
+      </c>
+      <c r="B1152" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1152" s="5" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D1152" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1152" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1152" s="6">
+        <v>4089</v>
+      </c>
+      <c r="G1152" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1152" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1152" s="8"/>
+      <c r="J1152" s="11" t="s">
+        <v>3063</v>
+      </c>
+      <c r="K1152" s="8"/>
+      <c r="L1152" s="8"/>
+      <c r="M1152" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1152" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1153" s="3" t="s">
+        <v>3064</v>
+      </c>
+      <c r="B1153" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1153" s="13">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="D1153" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1153" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1153" s="6">
+        <v>2649</v>
+      </c>
+      <c r="G1153" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1153" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1153" s="8"/>
+      <c r="J1153" s="8"/>
+      <c r="K1153" s="8"/>
+      <c r="L1153" s="8"/>
+      <c r="M1153" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1153" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1154" s="3" t="s">
+        <v>3065</v>
+      </c>
+      <c r="B1154" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1154" s="5" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D1154" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1154" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1154" s="6">
+        <v>3523</v>
+      </c>
+      <c r="G1154" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1154" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1154" s="5" t="s">
+        <v>3066</v>
+      </c>
+      <c r="J1154" s="8"/>
+      <c r="K1154" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1154" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1154" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1154" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1155" s="3" t="s">
+        <v>3067</v>
+      </c>
+      <c r="B1155" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1155" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1155" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1155" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1155" s="6">
+        <v>1499</v>
+      </c>
+      <c r="G1155" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1155" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1155" s="8"/>
+      <c r="J1155" s="11" t="s">
+        <v>3068</v>
+      </c>
+      <c r="K1155" s="5" t="s">
+        <v>3069</v>
+      </c>
+      <c r="L1155" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1155" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1155" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1156" s="3" t="s">
+        <v>3070</v>
+      </c>
+      <c r="B1156" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1156" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1156" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1156" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1156" s="6">
+        <v>3518</v>
+      </c>
+      <c r="G1156" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1156" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1156" s="5" t="s">
+        <v>3071</v>
+      </c>
+      <c r="J1156" s="11" t="s">
+        <v>3072</v>
+      </c>
+      <c r="K1156" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1156" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1156" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1156" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1157" s="3" t="s">
+        <v>3073</v>
+      </c>
+      <c r="B1157" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1157" s="5" t="s">
+        <v>3074</v>
+      </c>
+      <c r="D1157" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1157" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1157" s="6">
+        <v>5021</v>
+      </c>
+      <c r="G1157" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1157" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1157" s="8"/>
+      <c r="J1157" s="11" t="s">
+        <v>3075</v>
+      </c>
+      <c r="K1157" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1157" s="4">
+        <v>46201</v>
+      </c>
+      <c r="M1157" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1157" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1158" s="3" t="s">
+        <v>3076</v>
+      </c>
+      <c r="B1158" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1158" s="5" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D1158" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1158" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1158" s="6">
+        <v>4585</v>
+      </c>
+      <c r="G1158" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="H1158" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1158" s="8"/>
+      <c r="J1158" s="11" t="s">
+        <v>3077</v>
+      </c>
+      <c r="K1158" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1158" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1158" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1158" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1159" s="3" t="s">
+        <v>3078</v>
+      </c>
+      <c r="B1159" s="4">
+        <v>46200</v>
+      </c>
+      <c r="C1159" s="5" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D1159" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1159" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1159" s="6">
+        <v>3251</v>
+      </c>
+      <c r="G1159" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1159" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="I1159" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="J1159" s="11" t="s">
+        <v>3079</v>
+      </c>
+      <c r="K1159" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1159" s="4">
+        <v>46200</v>
+      </c>
+      <c r="M1159" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1159" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1160" s="3" t="s">
+        <v>3080</v>
+      </c>
+      <c r="B1160" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1160" s="5" t="s">
+        <v>3081</v>
+      </c>
+      <c r="D1160" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1160" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F1160" s="6">
+        <v>1162</v>
+      </c>
+      <c r="G1160" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H1160" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1160" s="5" t="s">
+        <v>3082</v>
+      </c>
+      <c r="J1160" s="11" t="s">
+        <v>3083</v>
+      </c>
+      <c r="K1160" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1160" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1160" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1160" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1161" s="3" t="s">
+        <v>3084</v>
+      </c>
+      <c r="B1161" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1161" s="13">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D1161" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1161" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1161" s="6">
+        <v>7317</v>
+      </c>
+      <c r="G1161" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1161" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1161" s="8"/>
+      <c r="J1161" s="8"/>
+      <c r="K1161" s="8"/>
+      <c r="L1161" s="8"/>
+      <c r="M1161" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1161" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1162" s="3" t="s">
+        <v>3085</v>
+      </c>
+      <c r="B1162" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1162" s="13">
+        <v>0.34861111111111109</v>
+      </c>
+      <c r="D1162" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1162" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1162" s="6">
+        <v>11010</v>
+      </c>
+      <c r="G1162" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1162" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1162" s="5" t="s">
+        <v>3086</v>
+      </c>
+      <c r="J1162" s="11" t="s">
+        <v>3087</v>
+      </c>
+      <c r="K1162" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1162" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1162" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1162" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1163" s="3" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B1163" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1163" s="5" t="s">
+        <v>3089</v>
+      </c>
+      <c r="D1163" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1163" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1163" s="6">
+        <v>1700</v>
+      </c>
+      <c r="G1163" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1163" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1163" s="5" t="s">
+        <v>3090</v>
+      </c>
+      <c r="J1163" s="11" t="s">
+        <v>3091</v>
+      </c>
+      <c r="K1163" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1163" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1163" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1163" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1164" s="3" t="s">
+        <v>3092</v>
+      </c>
+      <c r="B1164" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1164" s="5" t="s">
+        <v>3089</v>
+      </c>
+      <c r="D1164" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1164" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1164" s="6">
+        <v>2350</v>
+      </c>
+      <c r="G1164" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1164" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1164" s="5" t="s">
+        <v>3093</v>
+      </c>
+      <c r="J1164" s="8"/>
+      <c r="K1164" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1164" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1164" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1164" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1165" s="3" t="s">
+        <v>3094</v>
+      </c>
+      <c r="B1165" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1165" s="5" t="s">
+        <v>3089</v>
+      </c>
+      <c r="D1165" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1165" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1165" s="6">
+        <v>3675</v>
+      </c>
+      <c r="G1165" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1165" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1165" s="8"/>
+      <c r="J1165" s="11" t="s">
+        <v>3095</v>
+      </c>
+      <c r="K1165" s="8"/>
+      <c r="L1165" s="8"/>
+      <c r="M1165" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1165" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1166" s="3" t="s">
+        <v>3096</v>
+      </c>
+      <c r="B1166" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1166" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D1166" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1166" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1166" s="6">
+        <v>2417</v>
+      </c>
+      <c r="G1166" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1166" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1166" s="5" t="s">
+        <v>3097</v>
+      </c>
+      <c r="J1166" s="11" t="s">
+        <v>3098</v>
+      </c>
+      <c r="K1166" s="8"/>
+      <c r="L1166" s="8"/>
+      <c r="M1166" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1166" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1167" s="3" t="s">
+        <v>3099</v>
+      </c>
+      <c r="B1167" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1167" s="13">
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="D1167" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1167" s="5" t="s">
+        <v>2975</v>
+      </c>
+      <c r="F1167" s="6">
+        <v>3099</v>
+      </c>
+      <c r="G1167" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1167" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1167" s="5" t="s">
+        <v>3100</v>
+      </c>
+      <c r="J1167" s="11" t="s">
+        <v>3101</v>
+      </c>
+      <c r="K1167" s="8"/>
+      <c r="L1167" s="8"/>
+      <c r="M1167" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1167" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1168" s="3" t="s">
+        <v>3102</v>
+      </c>
+      <c r="B1168" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1168" s="5" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D1168" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1168" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1168" s="6">
+        <v>6438</v>
+      </c>
+      <c r="G1168" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1168" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1168" s="8"/>
+      <c r="J1168" s="11" t="s">
+        <v>3103</v>
+      </c>
+      <c r="K1168" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1168" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1168" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1168" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1169" s="3" t="s">
+        <v>3104</v>
+      </c>
+      <c r="B1169" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1169" s="5" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D1169" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1169" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1169" s="6">
+        <v>2772</v>
+      </c>
+      <c r="G1169" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1169" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1169" s="8"/>
+      <c r="J1169" s="11" t="s">
+        <v>3105</v>
+      </c>
+      <c r="K1169" s="8"/>
+      <c r="L1169" s="8"/>
+      <c r="M1169" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1169" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1170" s="3" t="s">
+        <v>3106</v>
+      </c>
+      <c r="B1170" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1170" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="D1170" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1170" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1170" s="6">
+        <v>7588</v>
+      </c>
+      <c r="G1170" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1170" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1170" s="8"/>
+      <c r="J1170" s="8"/>
+      <c r="K1170" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1170" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1170" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1170" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1171" s="3" t="s">
+        <v>3107</v>
+      </c>
+      <c r="B1171" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1171" s="13">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="D1171" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1171" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1171" s="6">
+        <v>7274</v>
+      </c>
+      <c r="G1171" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1171" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1171" s="8"/>
+      <c r="J1171" s="8"/>
+      <c r="K1171" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="L1171" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1171" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1171" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1172" s="3" t="s">
+        <v>3108</v>
+      </c>
+      <c r="B1172" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1172" s="5" t="s">
+        <v>2333</v>
+      </c>
+      <c r="D1172" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1172" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1172" s="6">
+        <v>2607</v>
+      </c>
+      <c r="G1172" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1172" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1172" s="5" t="s">
+        <v>3109</v>
+      </c>
+      <c r="J1172" s="8"/>
+      <c r="K1172" s="5" t="s">
+        <v>3110</v>
+      </c>
+      <c r="L1172" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1172" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1172" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1173" s="3" t="s">
+        <v>3111</v>
+      </c>
+      <c r="B1173" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1173" s="13">
+        <v>0.42777777777777776</v>
+      </c>
+      <c r="D1173" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1173" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1173" s="6">
+        <v>5303</v>
+      </c>
+      <c r="G1173" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1173" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1173" s="5" t="s">
+        <v>3112</v>
+      </c>
+      <c r="J1173" s="11" t="s">
+        <v>3113</v>
+      </c>
+      <c r="K1173" s="8"/>
+      <c r="L1173" s="8"/>
+      <c r="M1173" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1173" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1174" s="3" t="s">
+        <v>3114</v>
+      </c>
+      <c r="B1174" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1174" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="D1174" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1174" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1174" s="6">
+        <v>4830</v>
+      </c>
+      <c r="G1174" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1174" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1174" s="5" t="s">
+        <v>3115</v>
+      </c>
+      <c r="J1174" s="8"/>
+      <c r="K1174" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1174" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1174" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1174" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1175" s="3" t="s">
+        <v>3116</v>
+      </c>
+      <c r="B1175" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1175" s="5" t="s">
+        <v>2163</v>
+      </c>
+      <c r="D1175" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1175" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1175" s="6">
+        <v>1391</v>
+      </c>
+      <c r="G1175" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1175" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1175" s="5" t="s">
+        <v>3117</v>
+      </c>
+      <c r="J1175" s="8"/>
+      <c r="K1175" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1175" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1175" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1175" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1176" s="3" t="s">
+        <v>3118</v>
+      </c>
+      <c r="B1176" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1176" s="13">
+        <v>0.4465277777777778</v>
+      </c>
+      <c r="D1176" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1176" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1176" s="6">
+        <v>5536</v>
+      </c>
+      <c r="G1176" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1176" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1176" s="5" t="s">
+        <v>3119</v>
+      </c>
+      <c r="J1176" s="11" t="s">
+        <v>3120</v>
+      </c>
+      <c r="K1176" s="8"/>
+      <c r="L1176" s="8"/>
+      <c r="M1176" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1176" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1177" s="3" t="s">
+        <v>3121</v>
+      </c>
+      <c r="B1177" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1177" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1177" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1177" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1177" s="6">
+        <v>1693</v>
+      </c>
+      <c r="G1177" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1177" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1177" s="5" t="s">
+        <v>3122</v>
+      </c>
+      <c r="J1177" s="8"/>
+      <c r="K1177" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1177" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1177" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1177" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1178" s="3" t="s">
+        <v>3123</v>
+      </c>
+      <c r="B1178" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1178" s="5" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D1178" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1178" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1178" s="6">
+        <v>1863</v>
+      </c>
+      <c r="G1178" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1178" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1178" s="8"/>
+      <c r="J1178" s="8"/>
+      <c r="K1178" s="8"/>
+      <c r="L1178" s="8"/>
+      <c r="M1178" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1178" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1179" s="3" t="s">
+        <v>3124</v>
+      </c>
+      <c r="B1179" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1179" s="13">
+        <v>0.45416666666666666</v>
+      </c>
+      <c r="D1179" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1179" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1179" s="6">
+        <v>5560</v>
+      </c>
+      <c r="G1179" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1179" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1179" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="J1179" s="11" t="s">
+        <v>3125</v>
+      </c>
+      <c r="K1179" s="8"/>
+      <c r="L1179" s="8"/>
+      <c r="M1179" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1179" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1180" s="3" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B1180" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1180" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D1180" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1180" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1180" s="6">
+        <v>4040</v>
+      </c>
+      <c r="G1180" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1180" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1180" s="8"/>
+      <c r="J1180" s="8"/>
+      <c r="K1180" s="8"/>
+      <c r="L1180" s="8"/>
+      <c r="M1180" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1180" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1181" s="3" t="s">
+        <v>3127</v>
+      </c>
+      <c r="B1181" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1181" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1181" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1181" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1181" s="6">
+        <v>7569</v>
+      </c>
+      <c r="G1181" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1181" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1181" s="8"/>
+      <c r="J1181" s="8"/>
+      <c r="K1181" s="8"/>
+      <c r="L1181" s="8"/>
+      <c r="M1181" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1181" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1182" s="3" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B1182" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1182" s="13">
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="D1182" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1182" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1182" s="6">
+        <v>5530</v>
+      </c>
+      <c r="G1182" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1182" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1182" s="8"/>
+      <c r="J1182" s="8"/>
+      <c r="K1182" s="8"/>
+      <c r="L1182" s="8"/>
+      <c r="M1182" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1182" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1183" s="3" t="s">
+        <v>3129</v>
+      </c>
+      <c r="B1183" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1183" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1183" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1183" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1183" s="6">
+        <v>7569</v>
+      </c>
+      <c r="G1183" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1183" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1183" s="5" t="s">
+        <v>3130</v>
+      </c>
+      <c r="J1183" s="8"/>
+      <c r="K1183" s="8"/>
+      <c r="L1183" s="8"/>
+      <c r="M1183" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1183" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1184" s="3" t="s">
+        <v>3131</v>
+      </c>
+      <c r="B1184" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1184" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1184" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1184" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1184" s="6">
+        <v>1985</v>
+      </c>
+      <c r="G1184" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1184" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1184" s="5" t="s">
+        <v>3132</v>
+      </c>
+      <c r="J1184" s="8"/>
+      <c r="K1184" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1184" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1184" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1184" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1185" s="3" t="s">
+        <v>3133</v>
+      </c>
+      <c r="B1185" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1185" s="5" t="s">
+        <v>2186</v>
+      </c>
+      <c r="D1185" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1185" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1185" s="6">
+        <v>4748</v>
+      </c>
+      <c r="G1185" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1185" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1185" s="5" t="s">
+        <v>3134</v>
+      </c>
+      <c r="J1185" s="8"/>
+      <c r="K1185" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1185" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1185" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1185" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1186" s="3" t="s">
+        <v>3135</v>
+      </c>
+      <c r="B1186" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1186" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1186" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1186" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1186" s="6">
+        <v>1828</v>
+      </c>
+      <c r="G1186" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1186" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1186" s="5" t="s">
+        <v>3136</v>
+      </c>
+      <c r="J1186" s="11" t="s">
+        <v>3137</v>
+      </c>
+      <c r="K1186" s="5" t="s">
+        <v>3138</v>
+      </c>
+      <c r="L1186" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1186" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1186" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1187" s="3" t="s">
+        <v>3139</v>
+      </c>
+      <c r="B1187" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1187" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D1187" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1187" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1187" s="6">
+        <v>1928</v>
+      </c>
+      <c r="G1187" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1187" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1187" s="5" t="s">
+        <v>3140</v>
+      </c>
+      <c r="J1187" s="11" t="s">
+        <v>3141</v>
+      </c>
+      <c r="K1187" s="5" t="s">
+        <v>3142</v>
+      </c>
+      <c r="L1187" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1187" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1187" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1188" s="3" t="s">
+        <v>3143</v>
+      </c>
+      <c r="B1188" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1188" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D1188" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1188" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1188" s="6">
+        <v>6729</v>
+      </c>
+      <c r="G1188" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1188" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1188" s="5" t="s">
+        <v>3144</v>
+      </c>
+      <c r="J1188" s="8"/>
+      <c r="K1188" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1188" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1188" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1188" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1189" s="3" t="s">
+        <v>3145</v>
+      </c>
+      <c r="B1189" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1189" s="5" t="s">
+        <v>3146</v>
+      </c>
+      <c r="D1189" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1189" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1189" s="6">
+        <v>4772</v>
+      </c>
+      <c r="G1189" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1189" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1189" s="5" t="s">
+        <v>3147</v>
+      </c>
+      <c r="J1189" s="8"/>
+      <c r="K1189" s="8"/>
+      <c r="L1189" s="8"/>
+      <c r="M1189" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1189" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1190" s="3" t="s">
+        <v>3148</v>
+      </c>
+      <c r="B1190" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1190" s="13">
+        <v>0.53888888888888886</v>
+      </c>
+      <c r="D1190" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1190" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1190" s="6">
+        <v>4926</v>
+      </c>
+      <c r="G1190" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1190" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1190" s="8"/>
+      <c r="J1190" s="11" t="s">
+        <v>3149</v>
+      </c>
+      <c r="K1190" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1190" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1190" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1190" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1191" s="3" t="s">
+        <v>3150</v>
+      </c>
+      <c r="B1191" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1191" s="13">
+        <v>0.55902777777777779</v>
+      </c>
+      <c r="D1191" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1191" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1191" s="6">
+        <v>6699</v>
+      </c>
+      <c r="G1191" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1191" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1191" s="8"/>
+      <c r="J1191" s="8"/>
+      <c r="K1191" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1191" s="4">
+        <v>46202</v>
+      </c>
+      <c r="M1191" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1191" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1192" s="3" t="s">
+        <v>3151</v>
+      </c>
+      <c r="B1192" s="4">
+        <v>46202</v>
+      </c>
+      <c r="C1192" s="5" t="s">
+        <v>2475</v>
+      </c>
+      <c r="D1192" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1192" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1192" s="6">
+        <v>4766</v>
+      </c>
+      <c r="G1192" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1192" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1192" s="5" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J1192" s="8"/>
+      <c r="K1192" s="8"/>
+      <c r="L1192" s="8"/>
+      <c r="M1192" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N1192" s="23">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J5" r:id="rId1" xr:uid="{92437417-C162-4407-B939-8502230DA785}"/>
-    <hyperlink ref="J7" r:id="rId2" xr:uid="{26AEEE2C-E5B6-42B5-90C1-04227B17D6AF}"/>
-    <hyperlink ref="J8" r:id="rId3" xr:uid="{D49D5EC8-795E-4046-B20E-9669D0A8181A}"/>
-    <hyperlink ref="J10" r:id="rId4" xr:uid="{83948578-227D-4D97-B99E-B77786EBA10F}"/>
-    <hyperlink ref="J13" r:id="rId5" xr:uid="{5DEFDF45-6659-42C9-94EF-F6BB1C55BD9C}"/>
-    <hyperlink ref="J14" r:id="rId6" xr:uid="{756591F7-E0F9-4FBF-BD65-F6D7B2F6E5F0}"/>
-    <hyperlink ref="J17" r:id="rId7" xr:uid="{A859291C-3010-4A97-A6FF-F979357B83AB}"/>
-    <hyperlink ref="J19" r:id="rId8" xr:uid="{9E78EEE4-9D53-4F7C-A2A6-4FF64D32EA0A}"/>
-    <hyperlink ref="J20" r:id="rId9" xr:uid="{20F49E54-974B-4220-ABDB-60377E4663FD}"/>
-    <hyperlink ref="J21" r:id="rId10" xr:uid="{CF9A1B77-60F1-4E50-A7FB-AF14BACAF1CD}"/>
-    <hyperlink ref="J24" r:id="rId11" xr:uid="{FC085762-1846-46D2-A95C-6C99F974F96B}"/>
-    <hyperlink ref="J25" r:id="rId12" xr:uid="{22C851C9-7C13-4FB6-B291-FC5D904ACD33}"/>
-    <hyperlink ref="J26" r:id="rId13" xr:uid="{F12BAA40-8111-461D-9D3F-16F4AD65F9F5}"/>
-    <hyperlink ref="J27" r:id="rId14" xr:uid="{2DD0DB41-8A2A-4DD1-95C3-A0852E1B8157}"/>
-    <hyperlink ref="J29" r:id="rId15" xr:uid="{FC6269E0-3064-4CEE-BDB9-68014BAA4C41}"/>
-    <hyperlink ref="J30" r:id="rId16" xr:uid="{629C2A47-25F3-4D93-952B-1DAB9C08EF54}"/>
-    <hyperlink ref="J31" r:id="rId17" xr:uid="{05B5CFBA-4D4F-45C3-85D6-E9ED81DA2C6B}"/>
-    <hyperlink ref="J34" r:id="rId18" xr:uid="{56D36681-F534-48F5-AC68-F01850D3FD84}"/>
-    <hyperlink ref="J35" r:id="rId19" xr:uid="{7F796C36-BA41-4EE5-B520-6B29D1E3311A}"/>
-    <hyperlink ref="J36" r:id="rId20" xr:uid="{9B3F581D-2B42-44E8-A484-D64A8F3116CC}"/>
-    <hyperlink ref="J37" r:id="rId21" xr:uid="{2543D87C-27CF-45C2-896C-191ABE8CED03}"/>
-    <hyperlink ref="J38" r:id="rId22" xr:uid="{5CDD5312-3E2E-433C-BD33-079142D95D75}"/>
-    <hyperlink ref="J46" r:id="rId23" xr:uid="{D91CA944-C73D-4C9C-9B50-8124FCF58052}"/>
-    <hyperlink ref="J47" r:id="rId24" xr:uid="{5860E774-3C03-4C96-BFC6-DD8AE826BCE1}"/>
-    <hyperlink ref="J48" r:id="rId25" xr:uid="{9A640ECD-4F99-4C47-948D-F0AA1CD2A267}"/>
-    <hyperlink ref="J49" r:id="rId26" xr:uid="{E129C2B1-E095-480A-A4E1-7C534C42A9CF}"/>
-    <hyperlink ref="J50" r:id="rId27" xr:uid="{E0F98824-C50E-414E-9C03-663AF059A888}"/>
-    <hyperlink ref="J52" r:id="rId28" xr:uid="{788740A4-2052-42FC-B0C5-A3B2DE60E936}"/>
-    <hyperlink ref="J53" r:id="rId29" xr:uid="{78455C3F-4C69-49A4-8546-7DEA58B8FFFB}"/>
-    <hyperlink ref="J54" r:id="rId30" xr:uid="{942AE54D-1800-4ADB-B9D4-BC76B0A1F274}"/>
-    <hyperlink ref="J56" r:id="rId31" xr:uid="{67D262B9-20F8-4F31-B3A0-FA9AC6B54119}"/>
-    <hyperlink ref="J59" r:id="rId32" xr:uid="{B41446DB-DF6F-4775-A1F3-217C6D17F8E8}"/>
-    <hyperlink ref="J61" r:id="rId33" xr:uid="{547C3393-E847-47B2-B2EB-048400DAB71F}"/>
-    <hyperlink ref="J62" r:id="rId34" xr:uid="{57A326C9-BD1E-40E6-9241-E75EFAB9178D}"/>
-    <hyperlink ref="J63" r:id="rId35" xr:uid="{D628055A-6A4B-41FD-9A45-40B54FAEE825}"/>
-    <hyperlink ref="J64" r:id="rId36" xr:uid="{35BE325D-9ABA-421C-A34E-511F116BE390}"/>
-    <hyperlink ref="J69" r:id="rId37" xr:uid="{EA711594-2C02-4B52-8737-AC838596E8FD}"/>
-    <hyperlink ref="J71" r:id="rId38" xr:uid="{69D991D3-C3CD-486E-A9A0-8B52C20BB29A}"/>
-    <hyperlink ref="J72" r:id="rId39" xr:uid="{678D66D4-4B5A-4D74-8E64-BEF075FC1AB2}"/>
-    <hyperlink ref="J73" r:id="rId40" xr:uid="{F9A1CB24-6779-438B-B87D-FC72482C657F}"/>
-    <hyperlink ref="J74" r:id="rId41" xr:uid="{F4BF7095-840E-4227-88FE-21B78E828F7C}"/>
-    <hyperlink ref="J75" r:id="rId42" xr:uid="{A0B92F19-97C2-4232-9038-BBCF5A551782}"/>
-    <hyperlink ref="J76" r:id="rId43" xr:uid="{203D9398-7300-4C80-B2F3-567884559611}"/>
-    <hyperlink ref="J78" r:id="rId44" xr:uid="{CB90CCAE-8AEF-4183-B005-551DFE6E6E50}"/>
-    <hyperlink ref="J80" r:id="rId45" xr:uid="{6B6582BC-9216-4C0B-8B47-689125A44AE4}"/>
-    <hyperlink ref="J86" r:id="rId46" xr:uid="{C5F4C605-E702-40E6-B5BE-C394EDE6CA7C}"/>
-    <hyperlink ref="J88" r:id="rId47" xr:uid="{A682507D-130E-4915-BDAC-A00C1B063264}"/>
-    <hyperlink ref="J89" r:id="rId48" xr:uid="{7684C8C7-7A10-4726-8ABB-E7E77FB6BDC7}"/>
-    <hyperlink ref="J90" r:id="rId49" xr:uid="{9C7AD19C-2163-4911-AB77-33D2D92CE4BA}"/>
-    <hyperlink ref="J92" r:id="rId50" xr:uid="{4C6574FA-88C6-48A0-86C0-6597EF90BAA7}"/>
-    <hyperlink ref="J94" r:id="rId51" xr:uid="{8CC0E2F8-152C-4F49-B0E5-7351AFE4B3C5}"/>
-    <hyperlink ref="J95" r:id="rId52" xr:uid="{6EFCED49-87B5-43F6-BF91-5972A3E15AF8}"/>
-    <hyperlink ref="J96" r:id="rId53" xr:uid="{2E82CEC2-A206-42FA-9191-A0E7E12D4B01}"/>
-    <hyperlink ref="J101" r:id="rId54" xr:uid="{34DAEA9D-744C-495E-9F94-CAF6592EB02E}"/>
-    <hyperlink ref="J103" r:id="rId55" xr:uid="{1E0F2CFB-6433-4704-B9FA-B5CEAD605FEE}"/>
-    <hyperlink ref="J104" r:id="rId56" xr:uid="{F93C7C5A-5654-402A-B443-0E98A28E0B41}"/>
-    <hyperlink ref="J105" r:id="rId57" xr:uid="{2B01E8A5-60CE-490E-A586-22BB51C418D3}"/>
-    <hyperlink ref="J106" r:id="rId58" xr:uid="{45A5EACE-D38D-43C1-AC42-91C517201269}"/>
-    <hyperlink ref="J107" r:id="rId59" xr:uid="{F39AB62B-AE19-405B-BA12-72D45CC0D677}"/>
-    <hyperlink ref="J109" r:id="rId60" xr:uid="{D6C2E4B0-2147-4B62-86D1-8E3D3AB3B912}"/>
-    <hyperlink ref="J110" r:id="rId61" xr:uid="{DA58BAB4-1632-442E-BC36-0D1D8559A32D}"/>
-    <hyperlink ref="J111" r:id="rId62" xr:uid="{4A9EF153-AA0B-463D-A76B-7D79097497E2}"/>
-    <hyperlink ref="J112" r:id="rId63" xr:uid="{59ED1730-7546-4FA6-89C8-C663C9D6A2A6}"/>
-    <hyperlink ref="J113" r:id="rId64" xr:uid="{4A0FA50F-B98C-4BC5-B8D3-DBA735EA4D1B}"/>
-    <hyperlink ref="J114" r:id="rId65" xr:uid="{F6B483B2-F07F-4DAF-8FBF-1810B5AEA7B9}"/>
-    <hyperlink ref="J116" r:id="rId66" xr:uid="{80434B5A-66F6-48AB-B5D5-4D9EB079E634}"/>
-    <hyperlink ref="J117" r:id="rId67" xr:uid="{94006EFE-F0CF-49CC-A818-8E6C9F6B3FAD}"/>
-    <hyperlink ref="J118" r:id="rId68" xr:uid="{49A98537-B042-46E3-ACC2-CAD6E2A5BC8B}"/>
-    <hyperlink ref="J119" r:id="rId69" xr:uid="{19CD9698-358A-4013-BC93-B8F5818390C9}"/>
-    <hyperlink ref="J120" r:id="rId70" xr:uid="{F28911F4-EAB1-41F8-95B9-CCDA3B353EC6}"/>
-    <hyperlink ref="J121" r:id="rId71" xr:uid="{728DF57D-FAEF-4D76-9556-CA8400757D93}"/>
-    <hyperlink ref="J124" r:id="rId72" xr:uid="{EE9322D3-0761-4F49-AC1A-D65352B5221C}"/>
-    <hyperlink ref="J128" r:id="rId73" xr:uid="{CCB131B6-9611-4CCC-9516-C80F8DFD71D5}"/>
-    <hyperlink ref="J129" r:id="rId74" xr:uid="{232A4D63-11BC-445D-A31A-E38D756BDA75}"/>
-    <hyperlink ref="J132" r:id="rId75" xr:uid="{063ABC51-16F5-48EF-9152-F045B3D7E384}"/>
-    <hyperlink ref="J134" r:id="rId76" xr:uid="{626B0E99-536B-48BA-BFF2-645E8211F6B7}"/>
-    <hyperlink ref="J135" r:id="rId77" xr:uid="{3CDA2746-F242-4C41-B536-1811C2FAD062}"/>
-    <hyperlink ref="J136" r:id="rId78" xr:uid="{46DE5865-C53F-43DC-B158-B3E7A2FB0AEF}"/>
-    <hyperlink ref="J140" r:id="rId79" xr:uid="{B23F7340-9AE1-41BC-8EA1-72AD0C52DE27}"/>
-    <hyperlink ref="J142" r:id="rId80" xr:uid="{EF3E3E3D-71AF-414B-B2DD-093EC3E01C3C}"/>
-    <hyperlink ref="J143" r:id="rId81" xr:uid="{F456F277-1F98-4DC2-9C0B-9BEAF2035FBA}"/>
-    <hyperlink ref="J144" r:id="rId82" xr:uid="{5387FF9D-EDA3-4EF6-A1A6-5594FA8284E9}"/>
-    <hyperlink ref="J145" r:id="rId83" xr:uid="{1E074B4A-2FC9-43FD-8FF1-0E4EC1A7A380}"/>
-    <hyperlink ref="J147" r:id="rId84" xr:uid="{8AC4F922-23CB-4B31-8E97-BA331F849B18}"/>
-    <hyperlink ref="J149" r:id="rId85" xr:uid="{3A387EE6-1F42-4188-B70F-9A7076F3066A}"/>
-    <hyperlink ref="J150" r:id="rId86" xr:uid="{13629192-90E7-4CD4-8A5C-92FF6A3D82F0}"/>
-    <hyperlink ref="J151" r:id="rId87" xr:uid="{A437D993-4FF7-402B-99FB-0CE13F319509}"/>
-    <hyperlink ref="J152" r:id="rId88" xr:uid="{EEAA4EFE-2A15-4BC7-B984-C8CACFC24CFE}"/>
-    <hyperlink ref="J153" r:id="rId89" xr:uid="{8263B751-BBEF-498B-8658-5562C15E00EC}"/>
-    <hyperlink ref="J154" r:id="rId90" xr:uid="{2418A966-119A-44EC-A67C-8C0C979EFDAE}"/>
-    <hyperlink ref="J155" r:id="rId91" xr:uid="{AD1F80F2-59F7-4C37-AB14-B57DC4BEE636}"/>
-    <hyperlink ref="J156" r:id="rId92" xr:uid="{E8DB16A1-DD02-45D5-8C43-5430F878F839}"/>
-    <hyperlink ref="J159" r:id="rId93" xr:uid="{7E83DA4E-5360-4DF9-B193-12AFCD68A822}"/>
-    <hyperlink ref="J160" r:id="rId94" xr:uid="{90A77ABE-0764-41D5-9096-ECD02B66BFDD}"/>
-    <hyperlink ref="J161" r:id="rId95" xr:uid="{3628E765-C9F4-4CF9-81DF-B36F23C64A2F}"/>
-    <hyperlink ref="J162" r:id="rId96" xr:uid="{8021F201-3309-46A4-B61E-FC73B1B23314}"/>
-    <hyperlink ref="J164" r:id="rId97" xr:uid="{219EABD8-6B28-4DB6-ABED-62160D524701}"/>
-    <hyperlink ref="J165" r:id="rId98" xr:uid="{689CD745-49A6-4A67-8FC0-A3395D8951EB}"/>
-    <hyperlink ref="J167" r:id="rId99" xr:uid="{8FD757B4-1060-483A-B692-BC43D4AFBF32}"/>
-    <hyperlink ref="J168" r:id="rId100" xr:uid="{92107096-0C85-44C9-B0DB-6730E14A7E4B}"/>
-    <hyperlink ref="J169" r:id="rId101" xr:uid="{F5330D28-8277-4460-9F0F-E14ACC31010F}"/>
-    <hyperlink ref="J171" r:id="rId102" xr:uid="{3692964F-CDD5-4020-81E8-9FBD13D051DF}"/>
-    <hyperlink ref="J172" r:id="rId103" xr:uid="{4D665B96-DAC8-4731-BA0B-2B2EE032F5F3}"/>
-    <hyperlink ref="J173" r:id="rId104" xr:uid="{4F7C6812-89F3-4084-9A8E-9378A663F480}"/>
-    <hyperlink ref="J177" r:id="rId105" xr:uid="{00BB1C50-072C-4551-A0ED-1248DD81FF93}"/>
-    <hyperlink ref="J178" r:id="rId106" xr:uid="{CAD8A98E-1D67-45A7-83CF-9EFA9BB36DA9}"/>
-    <hyperlink ref="J181" r:id="rId107" xr:uid="{B16749FE-A877-4D86-8BC8-82F27FF3DF81}"/>
-    <hyperlink ref="J182" r:id="rId108" xr:uid="{E147B0E3-4459-473A-9FFE-196D92DC0520}"/>
-    <hyperlink ref="J184" r:id="rId109" xr:uid="{CF90E2A6-CC91-4684-B446-6E87E242D852}"/>
-    <hyperlink ref="J186" r:id="rId110" xr:uid="{347E7462-F755-44AC-873F-A066C78D0AE6}"/>
-    <hyperlink ref="J190" r:id="rId111" xr:uid="{4756C2CD-0363-4665-9EF0-04D0E8206098}"/>
-    <hyperlink ref="J191" r:id="rId112" xr:uid="{AB53B976-AACF-4849-8C56-2D92C1484991}"/>
-    <hyperlink ref="J192" r:id="rId113" xr:uid="{706E118D-D89D-4EC2-A05A-FAEB8C9B2003}"/>
-    <hyperlink ref="J193" r:id="rId114" xr:uid="{C70EB0D1-8165-4E6A-A89A-5C3B1AB2F36D}"/>
-    <hyperlink ref="J194" r:id="rId115" xr:uid="{940EAE08-6E6A-4E23-A96A-BDF686B4AA80}"/>
-    <hyperlink ref="J195" r:id="rId116" xr:uid="{8D251F7C-A1D4-40B9-BC25-9D58A0F919E1}"/>
-    <hyperlink ref="J196" r:id="rId117" xr:uid="{AD441E91-E77C-49DA-AD9B-63DA079B89C3}"/>
-    <hyperlink ref="J199" r:id="rId118" xr:uid="{CDC31E6C-0FB9-4AF8-BFA3-66E91B9124BD}"/>
-    <hyperlink ref="J201" r:id="rId119" xr:uid="{58B1E876-A1E0-4398-B9A8-9CA983674447}"/>
-    <hyperlink ref="J202" r:id="rId120" xr:uid="{AC395B5D-43DC-414A-90F6-B8475080A4C3}"/>
-    <hyperlink ref="J203" r:id="rId121" xr:uid="{B549D20D-AFA3-49FF-B23E-5101F580C9DE}"/>
-    <hyperlink ref="J205" r:id="rId122" xr:uid="{098C2094-D096-4000-8986-EEE303B11208}"/>
-    <hyperlink ref="J207" r:id="rId123" xr:uid="{323A3207-C8DD-4ABF-8954-25EEF6266376}"/>
-    <hyperlink ref="J209" r:id="rId124" xr:uid="{3EBFEA5D-3D93-43AE-AFEB-DA4B6420D761}"/>
-    <hyperlink ref="J210" r:id="rId125" xr:uid="{64E806BB-B36F-45F0-895E-411DD35E6E3F}"/>
-    <hyperlink ref="J211" r:id="rId126" xr:uid="{D952BD5C-D867-48A7-9280-B87F904EBC94}"/>
-    <hyperlink ref="J212" r:id="rId127" xr:uid="{A72892C9-6693-4C6D-A6AD-83362E568761}"/>
-    <hyperlink ref="J213" r:id="rId128" xr:uid="{544A6C2E-87F2-4039-9711-90873A52D7F2}"/>
-    <hyperlink ref="J214" r:id="rId129" xr:uid="{0F794993-B1F8-490E-9AC0-B8434FB16200}"/>
-    <hyperlink ref="J215" r:id="rId130" xr:uid="{8C28FFEA-BF87-463C-A7BB-E03EF9737614}"/>
-    <hyperlink ref="J217" r:id="rId131" xr:uid="{8E26270D-534B-4781-B143-05F2C4711E7A}"/>
-    <hyperlink ref="J219" r:id="rId132" xr:uid="{9229E28F-9C5B-46D7-B20A-4E09CE3FB54C}"/>
-    <hyperlink ref="J220" r:id="rId133" xr:uid="{19D1906E-9A0E-497B-926B-1E9F5EE43256}"/>
-    <hyperlink ref="J221" r:id="rId134" xr:uid="{3725547C-FCCF-44E6-AB61-7527C52AE275}"/>
-    <hyperlink ref="J222" r:id="rId135" xr:uid="{FF0C33E1-5BFF-46FF-9C11-863D7A5DB15D}"/>
-    <hyperlink ref="J223" r:id="rId136" xr:uid="{E75A8C99-3D47-489F-B19D-1C1415FC2137}"/>
-    <hyperlink ref="J225" r:id="rId137" xr:uid="{37D411AB-6CFB-433E-B9DC-0F8496FE5D47}"/>
-    <hyperlink ref="J228" r:id="rId138" xr:uid="{333E969F-B010-43D7-9202-6A72021215A4}"/>
-    <hyperlink ref="J230" r:id="rId139" xr:uid="{D8DAE89D-0F78-47C6-8528-857BE55B8D3C}"/>
-    <hyperlink ref="J234" r:id="rId140" xr:uid="{578E3567-DC4B-480C-AD9F-9CDB37E946E4}"/>
-    <hyperlink ref="J236" r:id="rId141" xr:uid="{5B0863CE-EAE9-4560-B1FA-E3A994CD81CC}"/>
-    <hyperlink ref="J237" r:id="rId142" xr:uid="{61322D8D-8BAA-4A28-829C-EAD3FA4C70B7}"/>
-    <hyperlink ref="J238" r:id="rId143" xr:uid="{73B33770-17E5-47A9-9345-891C8B0305D3}"/>
-    <hyperlink ref="J240" r:id="rId144" xr:uid="{63B9DAEA-A9B5-41D5-AFE1-ABEBC3F45047}"/>
-    <hyperlink ref="J241" r:id="rId145" xr:uid="{D47AC031-3CC8-47E6-9F32-771FFD5656CA}"/>
-    <hyperlink ref="J242" r:id="rId146" xr:uid="{0760B2D0-1CCE-4B0C-8959-869971C8BF01}"/>
-    <hyperlink ref="J243" r:id="rId147" xr:uid="{8FF5035C-CF76-4EED-9BF7-7BCAC951C43E}"/>
-    <hyperlink ref="J246" r:id="rId148" xr:uid="{991B6543-45A5-4744-A0C9-50DC7F876635}"/>
-    <hyperlink ref="J247" r:id="rId149" xr:uid="{60964962-B16F-4750-B442-EB9A24F8532B}"/>
-    <hyperlink ref="J250" r:id="rId150" xr:uid="{8C60B55B-0F9A-409A-967C-F2CEC736F78B}"/>
-    <hyperlink ref="J252" r:id="rId151" xr:uid="{B4958E24-0CA1-4431-8D2D-D2BADA384DDC}"/>
-    <hyperlink ref="J254" r:id="rId152" xr:uid="{444E7ACB-01F9-494B-B5E4-6222CEFC506C}"/>
-    <hyperlink ref="J255" r:id="rId153" xr:uid="{3D95A3B1-2C17-4072-B4B8-5F6AAE19C373}"/>
-    <hyperlink ref="J256" r:id="rId154" xr:uid="{E6EEE847-9914-4335-9F69-3774FB4EE8A4}"/>
-    <hyperlink ref="J258" r:id="rId155" xr:uid="{D78F4674-2E8C-4544-983D-C7871BD52902}"/>
-    <hyperlink ref="J259" r:id="rId156" xr:uid="{BB1A41D9-C757-43A4-92C1-DA96B239A351}"/>
-    <hyperlink ref="J261" r:id="rId157" xr:uid="{11E11243-FF8B-4B5D-AC1F-F1D46EFE1AE2}"/>
-    <hyperlink ref="J263" r:id="rId158" xr:uid="{B5BE51CA-4689-4057-8350-A72840418BF9}"/>
-    <hyperlink ref="J265" r:id="rId159" xr:uid="{63A02F97-D84E-4A7D-9718-7577796B4CFF}"/>
-    <hyperlink ref="J266" r:id="rId160" xr:uid="{4517889F-9A7D-4787-88B7-DD063D441F64}"/>
-    <hyperlink ref="J267" r:id="rId161" xr:uid="{CE4FE0C3-59E0-4D5E-8811-62F9673B3C2A}"/>
-    <hyperlink ref="J270" r:id="rId162" xr:uid="{64507C62-7D61-4974-8E1E-594D5033E7B7}"/>
-    <hyperlink ref="J271" r:id="rId163" xr:uid="{C97C0B21-79FE-45E5-9CD3-4EA842ED8C00}"/>
-    <hyperlink ref="J273" r:id="rId164" xr:uid="{843AD0F7-06DC-4CE6-93E9-04F75507FDD8}"/>
-    <hyperlink ref="J274" r:id="rId165" xr:uid="{526816FA-352D-477A-807A-5A82FB3EF8D4}"/>
-    <hyperlink ref="J275" r:id="rId166" xr:uid="{CE7669E2-BA51-4148-90FC-9BD2B6E5E61E}"/>
-    <hyperlink ref="J277" r:id="rId167" xr:uid="{A133B113-4665-46FF-BBFC-07A72FDB8C8D}"/>
-    <hyperlink ref="J278" r:id="rId168" xr:uid="{81B59E7F-162A-4D4F-A53E-9EEC3501D6E9}"/>
-    <hyperlink ref="J279" r:id="rId169" xr:uid="{F296F9FB-99FC-4DF5-8324-293301FE610A}"/>
-    <hyperlink ref="J280" r:id="rId170" xr:uid="{3C31891E-0952-4CB0-A9FA-730AF40190BA}"/>
-    <hyperlink ref="J281" r:id="rId171" xr:uid="{CF7DFD96-0389-43AB-83CC-5F3791A12244}"/>
-    <hyperlink ref="J282" r:id="rId172" xr:uid="{7B46C4B4-B4C8-4AF3-B8E5-2107530655FD}"/>
-    <hyperlink ref="J283" r:id="rId173" xr:uid="{DBEEC3E2-936E-409D-AE52-CE744A91959B}"/>
-    <hyperlink ref="J286" r:id="rId174" xr:uid="{D21B91F9-C430-4059-AD9E-87ABFB8EC0D7}"/>
-    <hyperlink ref="J287" r:id="rId175" xr:uid="{9D8E324E-0155-4F93-BFA4-F43E15B36990}"/>
-    <hyperlink ref="J290" r:id="rId176" xr:uid="{F7CE39D7-34FB-406F-9E2F-6D19A938FDDD}"/>
-    <hyperlink ref="J292" r:id="rId177" xr:uid="{E327C42B-E5C7-48FC-A1DF-B7ADC8F800E3}"/>
-    <hyperlink ref="J294" r:id="rId178" xr:uid="{45CC213F-D608-4FA8-8303-534C431A384B}"/>
-    <hyperlink ref="J296" r:id="rId179" xr:uid="{B8A321D4-CD86-4160-9EBC-774D38251AF3}"/>
-    <hyperlink ref="J297" r:id="rId180" xr:uid="{CC30E8AE-5A39-42FC-868A-2A1EE65A8503}"/>
-    <hyperlink ref="J298" r:id="rId181" xr:uid="{158569BF-3C06-405A-9E3D-ABDC90B8BC2E}"/>
-    <hyperlink ref="J299" r:id="rId182" xr:uid="{AA032E40-EEA8-4AC4-AE80-F54FB3EA6D59}"/>
-    <hyperlink ref="J300" r:id="rId183" xr:uid="{A9C34FFF-CBEF-413F-A070-658C6D1C5DDA}"/>
-    <hyperlink ref="J301" r:id="rId184" xr:uid="{CCDFE489-C577-49DE-BAD8-7DA900DB051D}"/>
-    <hyperlink ref="J303" r:id="rId185" xr:uid="{C1A684E3-E506-43C3-8910-C047F929165A}"/>
-    <hyperlink ref="J305" r:id="rId186" xr:uid="{6F3E3EAF-0CC4-48D2-827F-94A5465C272C}"/>
-    <hyperlink ref="J306" r:id="rId187" xr:uid="{380D221E-A2F6-44AB-A54D-544240725F4F}"/>
-    <hyperlink ref="J308" r:id="rId188" xr:uid="{5AB9373F-8026-4EE6-A2D5-BCF011509464}"/>
-    <hyperlink ref="J309" r:id="rId189" xr:uid="{02FD18A1-DF85-4175-B33C-B5C4999E47E5}"/>
-    <hyperlink ref="J311" r:id="rId190" xr:uid="{D9F92F9A-7100-4F9E-8C3B-F27E4D951540}"/>
-    <hyperlink ref="J312" r:id="rId191" xr:uid="{64901999-944B-4396-A014-02D44B178E6E}"/>
-    <hyperlink ref="J314" r:id="rId192" xr:uid="{D368342B-A040-4F19-A156-263FF23DF295}"/>
-    <hyperlink ref="J317" r:id="rId193" xr:uid="{47643A94-5871-4A72-94BE-BC849BE83ED1}"/>
-    <hyperlink ref="J318" r:id="rId194" xr:uid="{0459A028-A529-4EF1-845C-CAA5E9D8DD38}"/>
-    <hyperlink ref="J321" r:id="rId195" xr:uid="{86EFD043-9C51-4729-820C-F2065883B1B1}"/>
-    <hyperlink ref="J322" r:id="rId196" xr:uid="{1B43B055-BF28-4A0E-A576-D9761379EF62}"/>
-    <hyperlink ref="J325" r:id="rId197" xr:uid="{DFE4152A-A1E2-4151-B5FB-85D089D815B3}"/>
-    <hyperlink ref="J326" r:id="rId198" xr:uid="{0A9CE250-CB5C-439D-8FD4-65BD4E18E69D}"/>
-    <hyperlink ref="J329" r:id="rId199" xr:uid="{B85C2190-4FB2-445D-B932-141AFE7259FB}"/>
-    <hyperlink ref="J330" r:id="rId200" xr:uid="{08838AFD-56DA-48B0-B140-BF9A21856251}"/>
-    <hyperlink ref="J331" r:id="rId201" xr:uid="{1BD53C0F-1C79-4F36-8ACB-6E4341D318CC}"/>
-    <hyperlink ref="J333" r:id="rId202" xr:uid="{B600680B-9195-459F-81ED-28E738EA9FA6}"/>
-    <hyperlink ref="J334" r:id="rId203" xr:uid="{D9ED18F5-DB46-4219-A936-E3C7D6BD9F0C}"/>
-    <hyperlink ref="J335" r:id="rId204" xr:uid="{181D1779-2C06-4852-876C-7A00DC4AFA76}"/>
-    <hyperlink ref="J336" r:id="rId205" xr:uid="{31CFD515-1034-437C-AB9F-2B4A7E8E0804}"/>
-    <hyperlink ref="J338" r:id="rId206" xr:uid="{FFAC084D-2307-43E8-8FAD-BE8EB8353B50}"/>
-    <hyperlink ref="J340" r:id="rId207" xr:uid="{E20F3B29-761B-4DB4-81FD-F416C3827A88}"/>
-    <hyperlink ref="J342" r:id="rId208" xr:uid="{33A80E00-6C25-4AEB-99D1-412696163C93}"/>
-    <hyperlink ref="J343" r:id="rId209" xr:uid="{BB535EEB-4CC8-48F7-AF56-3F37FF860F8C}"/>
-    <hyperlink ref="J344" r:id="rId210" xr:uid="{0562417B-AB14-41F7-868E-50FA9B42AA12}"/>
-    <hyperlink ref="J346" r:id="rId211" xr:uid="{BDDA9B0D-40A3-452C-BB51-DE95B71FA296}"/>
-    <hyperlink ref="J349" r:id="rId212" xr:uid="{85629D9A-6E09-4C87-ABF0-F49A31A850DD}"/>
-    <hyperlink ref="J350" r:id="rId213" xr:uid="{EC2B0FCA-8C25-4993-8B57-F066357CD0A9}"/>
-    <hyperlink ref="J352" r:id="rId214" xr:uid="{67399257-0C7F-4D1A-A7B7-778A1BE43449}"/>
-    <hyperlink ref="J354" r:id="rId215" xr:uid="{38133AED-83D7-4CC8-A211-5D34EA07AFB8}"/>
-    <hyperlink ref="J355" r:id="rId216" xr:uid="{8613D8F0-A768-4034-86C2-E173E236EDD6}"/>
-    <hyperlink ref="J356" r:id="rId217" xr:uid="{49ADDF88-8CE5-4E8E-9A55-9EE97B0A3E19}"/>
-    <hyperlink ref="J357" r:id="rId218" xr:uid="{D1E1A55A-59A2-4765-9004-903855E1F8EC}"/>
-    <hyperlink ref="J358" r:id="rId219" xr:uid="{714FE207-72FE-4DD6-81B7-96DF6A8E59EB}"/>
-    <hyperlink ref="J360" r:id="rId220" xr:uid="{3D8AE70C-23E1-4317-86C4-22A5F58F50F2}"/>
-    <hyperlink ref="J363" r:id="rId221" xr:uid="{68F929BD-5AFF-476D-90A8-6871A8E8ECBC}"/>
-    <hyperlink ref="J364" r:id="rId222" xr:uid="{67F49FAB-9A32-41E8-9EFA-DDA1E2A096E0}"/>
-    <hyperlink ref="J366" r:id="rId223" xr:uid="{57662126-BD9D-4CA1-BCA7-5B34BACF7FB5}"/>
-    <hyperlink ref="J368" r:id="rId224" xr:uid="{36047851-7709-4804-8594-B2AEFA6BF30A}"/>
-    <hyperlink ref="J370" r:id="rId225" xr:uid="{9D07BD76-AA07-4434-B202-7F005E6C845E}"/>
-    <hyperlink ref="J371" r:id="rId226" xr:uid="{952CD549-BD33-44D2-B0A5-4E51D76E22A9}"/>
-    <hyperlink ref="J372" r:id="rId227" xr:uid="{C126293C-5D34-4B39-B99D-BA99B8E77601}"/>
-    <hyperlink ref="J373" r:id="rId228" xr:uid="{7FC0B5B9-14DA-4090-BC40-424E0E762439}"/>
-    <hyperlink ref="J374" r:id="rId229" xr:uid="{BCBD7732-B1A9-4351-8869-912634AE41F0}"/>
-    <hyperlink ref="J375" r:id="rId230" xr:uid="{4722AF9D-DF27-49A5-B1C7-C2EA85D2B272}"/>
-    <hyperlink ref="J376" r:id="rId231" xr:uid="{CB4F0BD4-02B9-4B0D-9973-598E734C14C0}"/>
-    <hyperlink ref="J377" r:id="rId232" xr:uid="{50162AA6-4F4B-413F-9BD9-FFF22123EE35}"/>
-    <hyperlink ref="J378" r:id="rId233" xr:uid="{76FAD247-6595-46E2-9685-BE288C0A504D}"/>
-    <hyperlink ref="J379" r:id="rId234" xr:uid="{5B908820-60CD-4411-A177-D6495BB09460}"/>
-    <hyperlink ref="J381" r:id="rId235" xr:uid="{7D62BF9B-CE38-4F3F-8577-6047F54C37C8}"/>
-    <hyperlink ref="J383" r:id="rId236" xr:uid="{B5724BA3-61F7-49DB-AFD5-774C1783B122}"/>
-    <hyperlink ref="J384" r:id="rId237" xr:uid="{9C3DE604-6A60-4283-8FB1-8BD67A83C3FA}"/>
-    <hyperlink ref="J386" r:id="rId238" xr:uid="{D4D6AAC9-5BEB-4D52-B316-A69F0C27788C}"/>
-    <hyperlink ref="J387" r:id="rId239" xr:uid="{C2E2B96D-CB14-43EF-AB9C-26AB966CAA83}"/>
-    <hyperlink ref="J388" r:id="rId240" xr:uid="{247E0AFD-E01B-4943-9F75-4C589E79CD93}"/>
-    <hyperlink ref="J390" r:id="rId241" xr:uid="{85C11E66-03FE-4CB2-9D42-774BFDE58FB4}"/>
-    <hyperlink ref="J391" r:id="rId242" xr:uid="{54016571-E6CB-42A0-8E90-BA29D5C6B304}"/>
-    <hyperlink ref="J394" r:id="rId243" xr:uid="{794F6BD2-A09F-4E81-A7A2-CE2B9F8F1BAE}"/>
-    <hyperlink ref="J395" r:id="rId244" xr:uid="{CA099075-5CB0-4605-BB8B-11FFB9FA4E50}"/>
-    <hyperlink ref="J396" r:id="rId245" xr:uid="{71A3F5B3-6B32-47EC-9F59-94CF08762424}"/>
-    <hyperlink ref="J397" r:id="rId246" xr:uid="{A7E7C2BA-2944-48B7-9DFA-4C2A44E0BA80}"/>
-    <hyperlink ref="J398" r:id="rId247" xr:uid="{E3537969-D0CF-40D3-A4EA-5F57B6776EA4}"/>
-    <hyperlink ref="J399" r:id="rId248" xr:uid="{55C3DDB3-27D6-4DEE-959A-9D3EDEEDCE5D}"/>
-    <hyperlink ref="J400" r:id="rId249" xr:uid="{765814A1-78AC-4742-ABB4-F5D77C7E9135}"/>
-    <hyperlink ref="J403" r:id="rId250" xr:uid="{34CFD8BF-ACF4-4B7C-A8A1-C93ECC85768A}"/>
-    <hyperlink ref="J404" r:id="rId251" xr:uid="{C4574ECB-1DB1-44FE-A286-74D14A8BCB75}"/>
-    <hyperlink ref="J405" r:id="rId252" xr:uid="{0714233B-FBE3-442F-A57A-B6BB7E2E8DC0}"/>
-    <hyperlink ref="J406" r:id="rId253" xr:uid="{C91747D6-8569-4068-A182-52E5251A9A13}"/>
-    <hyperlink ref="J408" r:id="rId254" xr:uid="{D957FBFB-B3A1-49DA-86EC-7696B564A46F}"/>
-    <hyperlink ref="J409" r:id="rId255" xr:uid="{58042C80-6108-4150-9ABE-DF7DCC67148D}"/>
-    <hyperlink ref="J411" r:id="rId256" xr:uid="{96AC45F8-BD6D-42AC-A0CA-1A12ECC6B3E5}"/>
-    <hyperlink ref="J413" r:id="rId257" xr:uid="{A4AF4653-F0B7-4660-BE16-86B8DB4474B8}"/>
-    <hyperlink ref="J415" r:id="rId258" xr:uid="{58D6DB23-4409-457D-9638-FAD1A21E5133}"/>
-    <hyperlink ref="J416" r:id="rId259" xr:uid="{45219878-23FF-4178-915E-C5399E3EBB4B}"/>
-    <hyperlink ref="J418" r:id="rId260" xr:uid="{B84C8B0B-1894-48E8-AB6C-3B06A86CA6F2}"/>
-    <hyperlink ref="J421" r:id="rId261" xr:uid="{235ADF45-668C-4FC9-8E98-B5D1F1F116D2}"/>
-    <hyperlink ref="J422" r:id="rId262" xr:uid="{C8673AFC-0EFF-421D-BDB0-F5933631EDCC}"/>
-    <hyperlink ref="J430" r:id="rId263" xr:uid="{128AA4EF-CF31-4C66-94AB-85E8FC8B5BA0}"/>
-    <hyperlink ref="J431" r:id="rId264" xr:uid="{A56E0535-F065-4A95-9B9C-EBEA4FF3FEF6}"/>
-    <hyperlink ref="J432" r:id="rId265" xr:uid="{FA7199D6-BD89-423E-AE43-96F3E4FFC5A2}"/>
-    <hyperlink ref="J433" r:id="rId266" xr:uid="{C9FC7B61-AA9F-499F-8997-C01165925B8C}"/>
-    <hyperlink ref="J434" r:id="rId267" xr:uid="{EE3AE195-5094-448F-B21C-136CAFF80546}"/>
-    <hyperlink ref="J435" r:id="rId268" xr:uid="{D857D2A6-B897-4E2B-A44D-7869A01CE5D3}"/>
-    <hyperlink ref="J436" r:id="rId269" xr:uid="{653AA32A-6365-4A1F-80A8-51B23C654F6E}"/>
-    <hyperlink ref="J437" r:id="rId270" xr:uid="{2C199156-7045-4991-BAB7-E80ECACE00FC}"/>
-    <hyperlink ref="J438" r:id="rId271" xr:uid="{D50D14AE-9B5B-436F-AB7D-0918EFBF4BD9}"/>
-    <hyperlink ref="J439" r:id="rId272" xr:uid="{50651A2C-FB06-4897-9E4E-822BEFCBA9FE}"/>
-    <hyperlink ref="J445" r:id="rId273" xr:uid="{E0357B41-1AF0-4370-AACD-94D43172B4BE}"/>
-    <hyperlink ref="J447" r:id="rId274" xr:uid="{8B1ED451-BA42-478C-A920-FEF269460B4B}"/>
-    <hyperlink ref="J449" r:id="rId275" xr:uid="{2057F6D2-BC13-46A2-BCF1-87043BCC1012}"/>
-    <hyperlink ref="J450" r:id="rId276" xr:uid="{D2F965B6-AFD5-4239-A215-697EFD5F53E9}"/>
-    <hyperlink ref="J451" r:id="rId277" xr:uid="{ED9F2CA0-3448-42D8-85C6-F4A0EAD25695}"/>
-    <hyperlink ref="J452" r:id="rId278" xr:uid="{D044FB1B-4AC2-4DEF-8F0C-F023436112C4}"/>
-    <hyperlink ref="J453" r:id="rId279" xr:uid="{6A4013B9-A82F-40AE-9D9F-00C9DE63F431}"/>
-    <hyperlink ref="J454" r:id="rId280" xr:uid="{EAAF9454-C8C5-46B9-8234-D835C8ABF474}"/>
-    <hyperlink ref="J455" r:id="rId281" xr:uid="{B1F3616A-D77A-495D-B86E-F4CAF937C347}"/>
-    <hyperlink ref="J458" r:id="rId282" xr:uid="{D54C9401-6B92-48C0-AE6C-22A5BF2D473C}"/>
-    <hyperlink ref="J460" r:id="rId283" xr:uid="{20BA490D-BB6C-4A73-A834-24D3718CD9EA}"/>
-    <hyperlink ref="J461" r:id="rId284" xr:uid="{8CDF1494-48BD-47FE-8755-AD9A1AF54BF0}"/>
-    <hyperlink ref="J462" r:id="rId285" xr:uid="{50A82B8F-E98C-4898-9D4A-063CAF66AD0C}"/>
-    <hyperlink ref="J465" r:id="rId286" xr:uid="{CC69AA22-2E7C-4D6B-A556-E72526D29ADE}"/>
-    <hyperlink ref="J469" r:id="rId287" xr:uid="{85E49F64-4699-4F61-B47D-46AF537F3135}"/>
-    <hyperlink ref="J473" r:id="rId288" xr:uid="{672DF1B1-9D7A-4C3F-BCE2-D7C4DF5D2DD2}"/>
-    <hyperlink ref="J476" r:id="rId289" xr:uid="{4EA7D590-6439-4F3B-BB93-0B0EC04DEBD7}"/>
-    <hyperlink ref="J478" r:id="rId290" xr:uid="{97C8D5D3-DCEB-45EF-91C4-9E6D105957A2}"/>
-    <hyperlink ref="J479" r:id="rId291" xr:uid="{26B10118-173B-4FD8-812C-DE0EA8508642}"/>
-    <hyperlink ref="J480" r:id="rId292" xr:uid="{B6D69CD3-1C0B-4FD0-A43D-0FD29998AFD1}"/>
-    <hyperlink ref="J481" r:id="rId293" xr:uid="{DBFDC290-EB81-457A-82A7-219D3E9B267F}"/>
-    <hyperlink ref="J482" r:id="rId294" xr:uid="{1ED0910A-B11F-42CC-8F08-D0B1D274E193}"/>
-    <hyperlink ref="J484" r:id="rId295" xr:uid="{44F83480-683F-4073-80DD-9243E0AC9310}"/>
-    <hyperlink ref="J485" r:id="rId296" xr:uid="{B3C8B58F-83FF-4E3F-B3AA-5C2A2DBB449D}"/>
-    <hyperlink ref="J488" r:id="rId297" xr:uid="{63A0FD9F-1591-43D8-B14B-CA250B6A412F}"/>
-    <hyperlink ref="J489" r:id="rId298" xr:uid="{90B98E5F-D0DC-420D-BA9C-D9750A760507}"/>
-    <hyperlink ref="J490" r:id="rId299" xr:uid="{6A02C229-2814-430B-B754-B3404CB757CE}"/>
-    <hyperlink ref="J491" r:id="rId300" xr:uid="{E54DF1F6-DA2B-4762-93B3-63F549C4AC48}"/>
-    <hyperlink ref="J494" r:id="rId301" xr:uid="{E18AA0CD-2F24-4EF3-8ECF-3D3513BEC231}"/>
-    <hyperlink ref="J496" r:id="rId302" xr:uid="{E34659A2-090E-47E6-AE6D-BDCEA8A643F6}"/>
-    <hyperlink ref="J497" r:id="rId303" xr:uid="{1DD579FF-5B6D-4A50-BF04-30A7DE19ADB9}"/>
-    <hyperlink ref="J498" r:id="rId304" xr:uid="{624941DE-1026-4EE2-9361-F0CCA01FF97A}"/>
-    <hyperlink ref="J499" r:id="rId305" xr:uid="{8F45F44E-8E50-4A38-B0AB-104F8BB42F06}"/>
-    <hyperlink ref="J500" r:id="rId306" xr:uid="{CF6A4A2A-AEE4-4879-AB0C-CE242F9EE474}"/>
-    <hyperlink ref="J501" r:id="rId307" xr:uid="{0ED6C3D5-2779-4C40-B96C-6821C8F89E16}"/>
-    <hyperlink ref="J503" r:id="rId308" xr:uid="{E1340037-CC47-4592-99B2-7BC2A9203E43}"/>
-    <hyperlink ref="J504" r:id="rId309" xr:uid="{035E49D2-FA6C-4F2B-A356-C1CA824E663B}"/>
-    <hyperlink ref="J508" r:id="rId310" xr:uid="{A1D5F102-4035-4390-A4EA-A3FE2E403B48}"/>
-    <hyperlink ref="J509" r:id="rId311" xr:uid="{49B84140-3E1B-44DF-BCEB-577D5FA4B9F1}"/>
-    <hyperlink ref="J510" r:id="rId312" xr:uid="{21C7883E-2B2E-4F0D-A13F-F307B989E868}"/>
-    <hyperlink ref="J511" r:id="rId313" xr:uid="{0A98E39E-BF70-457F-BF44-A07C1EB8376D}"/>
-    <hyperlink ref="J513" r:id="rId314" xr:uid="{2162263D-1106-4F02-8168-451D751FB468}"/>
-    <hyperlink ref="J515" r:id="rId315" xr:uid="{0C8CD81B-F4EE-4F1D-A8AE-A19D6DBA8435}"/>
-    <hyperlink ref="J516" r:id="rId316" xr:uid="{393FC5EE-8932-40E9-9809-2A8CDB40E702}"/>
-    <hyperlink ref="J519" r:id="rId317" xr:uid="{01B048CD-6A96-4DBD-A465-D74C1BA801F7}"/>
-    <hyperlink ref="J523" r:id="rId318" xr:uid="{9C5A1513-01C6-4534-8298-942481956DC0}"/>
-    <hyperlink ref="J524" r:id="rId319" xr:uid="{DCD25738-8A59-457C-83E7-E54502AF8204}"/>
-    <hyperlink ref="J525" r:id="rId320" xr:uid="{A0DBE92D-7FB2-431E-8677-5B9B2BCC23BE}"/>
-    <hyperlink ref="J535" r:id="rId321" xr:uid="{858DDA6F-E4FE-4DC3-A1E3-B144A71B18A3}"/>
-    <hyperlink ref="J536" r:id="rId322" xr:uid="{0165C7C7-9AEF-42CA-A994-4BD01E9F91BE}"/>
-    <hyperlink ref="J537" r:id="rId323" xr:uid="{09D0816F-FCF8-4E41-95F4-3EE20F987B44}"/>
-    <hyperlink ref="J538" r:id="rId324" xr:uid="{B34470FF-DA2E-4308-B59D-5D56F15537A3}"/>
-    <hyperlink ref="J539" r:id="rId325" xr:uid="{35C3D916-3780-4998-8236-2559E9D4563A}"/>
-    <hyperlink ref="J540" r:id="rId326" xr:uid="{BB90AD54-8550-412F-B8C4-34461CDDBB56}"/>
-    <hyperlink ref="J541" r:id="rId327" xr:uid="{411C2AE8-2045-4080-99A8-9FB515BCD60C}"/>
-    <hyperlink ref="J543" r:id="rId328" xr:uid="{748F6176-1DB4-48E6-BA5A-83A29CBD48D9}"/>
-    <hyperlink ref="J544" r:id="rId329" xr:uid="{C0FDAE06-4CAE-499E-8148-102795A9C8D1}"/>
-    <hyperlink ref="J546" r:id="rId330" xr:uid="{1C64E955-7733-46BE-8AAE-5E4D68590495}"/>
-    <hyperlink ref="J547" r:id="rId331" xr:uid="{828F998E-5DF4-4716-A2D2-81A82C2B6CC8}"/>
-    <hyperlink ref="J548" r:id="rId332" xr:uid="{F0DAB9E9-5385-4744-AA3C-FC3B2E3ECA4B}"/>
-    <hyperlink ref="J549" r:id="rId333" xr:uid="{010E95BE-EC93-4FCA-B193-388217EF44FB}"/>
-    <hyperlink ref="J550" r:id="rId334" xr:uid="{DB387C60-1AC6-4678-A40C-D4CA627ACAAB}"/>
-    <hyperlink ref="J551" r:id="rId335" xr:uid="{292D0F31-D6AB-4F40-92CE-06A7A0F7F731}"/>
-    <hyperlink ref="J552" r:id="rId336" xr:uid="{A2CFE7D0-C308-4138-856C-1807BE5C85B8}"/>
-    <hyperlink ref="J555" r:id="rId337" xr:uid="{F9531B38-FDF5-4DEA-85A5-7AAFDD75BF7A}"/>
-    <hyperlink ref="J556" r:id="rId338" xr:uid="{086B8BD7-B3A0-4471-B1B8-45558403B1CA}"/>
-    <hyperlink ref="J558" r:id="rId339" xr:uid="{12889D05-7F33-4278-A103-570B2EF00153}"/>
-    <hyperlink ref="J559" r:id="rId340" xr:uid="{8D0BED8B-751D-4B6C-996D-431227BEC8C0}"/>
-    <hyperlink ref="J560" r:id="rId341" xr:uid="{949074CD-42AB-4FB2-B512-30FD96B0E9E8}"/>
-    <hyperlink ref="J562" r:id="rId342" xr:uid="{F5B74754-C88B-4935-8DAE-43797B6901E8}"/>
-    <hyperlink ref="J569" r:id="rId343" xr:uid="{B3A3E971-0289-4A9E-B5BC-328E3BF65D16}"/>
-    <hyperlink ref="J570" r:id="rId344" xr:uid="{B63EA640-85AE-492F-8CC9-D2E478269695}"/>
-    <hyperlink ref="J571" r:id="rId345" xr:uid="{FE467D69-8FE5-4C34-9374-691BC7A12007}"/>
-    <hyperlink ref="J572" r:id="rId346" xr:uid="{7D698BFA-7320-467B-A498-C66081E16796}"/>
-    <hyperlink ref="J573" r:id="rId347" xr:uid="{D6E37026-08EC-4D84-B62D-C2C563BD3BBA}"/>
-    <hyperlink ref="J574" r:id="rId348" xr:uid="{9A5D9932-3F32-4B4A-8E3C-E3664129E9F7}"/>
-    <hyperlink ref="J575" r:id="rId349" xr:uid="{E5DDBD18-1E07-461B-B085-BE7DE82E405B}"/>
-    <hyperlink ref="J576" r:id="rId350" xr:uid="{A53BCC1D-248D-49A1-9316-05218A87E456}"/>
-    <hyperlink ref="J577" r:id="rId351" xr:uid="{948CA08A-9D26-4365-ADD4-A8CD61DCBE4E}"/>
-    <hyperlink ref="J578" r:id="rId352" xr:uid="{41DAAD26-EFA7-4D13-9F22-A049FA4816A7}"/>
-    <hyperlink ref="J579" r:id="rId353" xr:uid="{0074F5A3-A722-4C29-9FAE-AF6C57475E44}"/>
-    <hyperlink ref="J580" r:id="rId354" xr:uid="{22F344FC-1C5D-49B5-9D19-8DA5BC91730D}"/>
-    <hyperlink ref="J581" r:id="rId355" xr:uid="{9D94C076-F406-4E8B-8EA8-1FAA56B424EC}"/>
-    <hyperlink ref="J582" r:id="rId356" xr:uid="{301D15F9-F4B6-47D0-9654-3231AFD4628A}"/>
-    <hyperlink ref="J584" r:id="rId357" xr:uid="{EE81E1A0-0FD1-4127-8E9A-F396FCB7D183}"/>
-    <hyperlink ref="J585" r:id="rId358" xr:uid="{80E3DC23-2E5E-46E0-B4D7-E1C84ED5F6B1}"/>
-    <hyperlink ref="J586" r:id="rId359" xr:uid="{ED5804DB-3238-4774-864B-099AF25DE241}"/>
-    <hyperlink ref="J587" r:id="rId360" xr:uid="{EE1AD39B-351A-4A8F-88E9-B70E0C01A13D}"/>
-    <hyperlink ref="J592" r:id="rId361" xr:uid="{1ED68771-BB48-4ABE-80C2-1F23D48A547F}"/>
-    <hyperlink ref="J593" r:id="rId362" xr:uid="{926D12AB-AB0D-4F6D-BB69-F3289C1DF6CB}"/>
-    <hyperlink ref="J595" r:id="rId363" xr:uid="{86793308-6DA5-449A-BF62-E2B7441A8A97}"/>
-    <hyperlink ref="J596" r:id="rId364" xr:uid="{8221E45B-24AB-4A54-9A4A-DE939308F8AD}"/>
-    <hyperlink ref="J598" r:id="rId365" xr:uid="{A2F0ECC2-5F43-4998-BEDE-716702A1901F}"/>
-    <hyperlink ref="J599" r:id="rId366" xr:uid="{C5989E04-5CD5-417F-8885-61FB77164543}"/>
-    <hyperlink ref="J602" r:id="rId367" xr:uid="{FC4FAAF9-D9EA-409E-82A6-B90170183C58}"/>
-    <hyperlink ref="J603" r:id="rId368" xr:uid="{49509BEC-410B-4E98-9B24-A2C728E0208F}"/>
-    <hyperlink ref="J604" r:id="rId369" xr:uid="{5BFDC61D-8E4C-4479-8F05-BE1BB87C7EAC}"/>
-    <hyperlink ref="J605" r:id="rId370" xr:uid="{C9F47D9E-E76E-4A45-994D-4B02CCC48457}"/>
-    <hyperlink ref="J606" r:id="rId371" xr:uid="{8DA53CD1-1110-4D84-8FAD-907D939D0541}"/>
-    <hyperlink ref="J608" r:id="rId372" xr:uid="{4F91CEB4-DE3D-46D7-9F4C-3F1D2A0EEED1}"/>
-    <hyperlink ref="J609" r:id="rId373" xr:uid="{5407D48E-D53F-4105-B132-4960C9792ACC}"/>
-    <hyperlink ref="J611" r:id="rId374" xr:uid="{C64F35B6-9176-4DA5-B145-A275D78A80F8}"/>
-    <hyperlink ref="J612" r:id="rId375" xr:uid="{B37FBF98-6E75-41CC-94D4-2B4A8B2D2035}"/>
-    <hyperlink ref="J613" r:id="rId376" xr:uid="{12854606-9A25-46B4-AC8E-22FB930A2A61}"/>
-    <hyperlink ref="J615" r:id="rId377" xr:uid="{EE15E61E-61CC-4DA6-9573-57DAE4B91894}"/>
-    <hyperlink ref="J617" r:id="rId378" xr:uid="{303CBA49-917D-412C-90CF-2E04CE115097}"/>
-    <hyperlink ref="J618" r:id="rId379" xr:uid="{1770CA8B-39D2-41AB-A4E3-16BC45321A36}"/>
-    <hyperlink ref="J619" r:id="rId380" xr:uid="{00851AFD-D16A-4B04-A95D-00385A035A06}"/>
-    <hyperlink ref="J622" r:id="rId381" xr:uid="{19913CEC-3AA6-44AB-98AD-B96DD0EB191D}"/>
-    <hyperlink ref="J623" r:id="rId382" xr:uid="{39D2FA89-38FB-4E4D-B41A-84ACE8D78DF0}"/>
-    <hyperlink ref="J624" r:id="rId383" xr:uid="{C28469D3-4119-4C01-8339-17917F13EFED}"/>
-    <hyperlink ref="J626" r:id="rId384" xr:uid="{B3FA1D4E-7AC1-4C69-B9A3-F6E4BB1A0688}"/>
-    <hyperlink ref="J628" r:id="rId385" xr:uid="{3C8C6861-4AED-4B5D-8359-F36A47AFF492}"/>
-    <hyperlink ref="J629" r:id="rId386" xr:uid="{E00BD8DF-EB2F-4631-831E-7429A218C8EC}"/>
-    <hyperlink ref="J631" r:id="rId387" xr:uid="{F3BB100D-574E-49F9-8DAF-4A80A375924A}"/>
-    <hyperlink ref="J634" r:id="rId388" xr:uid="{696B8607-4BAC-4F44-9A74-E5A423E991EC}"/>
-    <hyperlink ref="J635" r:id="rId389" xr:uid="{ADFAA3AF-C45B-49DD-8E3A-44C20A89FD65}"/>
-    <hyperlink ref="J637" r:id="rId390" xr:uid="{169E875B-D7BB-4F99-B944-00CDDC3FC975}"/>
-    <hyperlink ref="J640" r:id="rId391" xr:uid="{AA9C9A1B-3D11-4911-A6DE-60B96955A774}"/>
-    <hyperlink ref="J641" r:id="rId392" xr:uid="{9CC10317-9104-480B-9F13-885D1B9DB15E}"/>
-    <hyperlink ref="J642" r:id="rId393" xr:uid="{0190F85B-77A7-4C57-A8C2-DE7B3FC1E24F}"/>
-    <hyperlink ref="J644" r:id="rId394" xr:uid="{AB99F971-4541-4DDA-B9D8-138575C5254C}"/>
-    <hyperlink ref="J645" r:id="rId395" xr:uid="{44D9FEBA-DB23-4C40-94C4-7FC3FB724D83}"/>
-    <hyperlink ref="J648" r:id="rId396" xr:uid="{C051F1A4-6BE8-4A53-A74D-9196F20B3210}"/>
-    <hyperlink ref="J649" r:id="rId397" xr:uid="{AA3E0409-FBA3-4001-AE7D-1BE47FBDD751}"/>
-    <hyperlink ref="J652" r:id="rId398" xr:uid="{18B01CF0-77B6-4366-9F97-D21612EE6147}"/>
-    <hyperlink ref="J654" r:id="rId399" xr:uid="{DF655614-6388-421D-BB69-3D2D84C7A1BD}"/>
-    <hyperlink ref="J656" r:id="rId400" xr:uid="{5222BF02-E295-4B49-831E-25F9D7641540}"/>
-    <hyperlink ref="J657" r:id="rId401" xr:uid="{60E0A767-7D28-4D4D-A86A-2C268A560990}"/>
-    <hyperlink ref="J663" r:id="rId402" xr:uid="{0E09ADE4-4E9C-4AC9-9BBA-ECD07FCC643F}"/>
-    <hyperlink ref="J664" r:id="rId403" xr:uid="{ADB4A47D-41F1-4040-AA75-96606C1C00C2}"/>
-    <hyperlink ref="J665" r:id="rId404" xr:uid="{6C53C2D6-3AAF-46C7-800B-B3E446BD7358}"/>
-    <hyperlink ref="J666" r:id="rId405" xr:uid="{A473FA21-66E9-4AF7-AE33-FC55F814D4F7}"/>
-    <hyperlink ref="J667" r:id="rId406" xr:uid="{7FA853BC-9DAA-48F4-8434-C61189A163DD}"/>
-    <hyperlink ref="J668" r:id="rId407" xr:uid="{10AE8C77-AEA2-4DCF-9970-AB052D2ED148}"/>
-    <hyperlink ref="J669" r:id="rId408" xr:uid="{91CE5AC6-4944-4DC0-B21F-6C52030A6048}"/>
-    <hyperlink ref="J670" r:id="rId409" xr:uid="{0B414E31-B979-40E6-AAFC-CE83F94EA840}"/>
-    <hyperlink ref="J671" r:id="rId410" xr:uid="{D0D19974-CB7C-4ABD-94F0-5497C538D457}"/>
-    <hyperlink ref="J672" r:id="rId411" xr:uid="{16F3049D-9327-495F-8A20-1E7B3B637315}"/>
-    <hyperlink ref="J673" r:id="rId412" xr:uid="{6E2BCC77-8080-449D-91D1-BF613F3C5E9F}"/>
-    <hyperlink ref="J674" r:id="rId413" xr:uid="{3D9B35D9-E87E-4ADE-BFBC-AA2D3F3458BF}"/>
-    <hyperlink ref="J675" r:id="rId414" xr:uid="{965D793D-D157-43AF-95EE-4D16F3217E83}"/>
-    <hyperlink ref="J676" r:id="rId415" xr:uid="{97FCCD4A-1CAF-431D-82E1-1124DFB83A36}"/>
-    <hyperlink ref="J677" r:id="rId416" xr:uid="{A187D443-6516-475F-B345-6F418762F378}"/>
-    <hyperlink ref="J679" r:id="rId417" xr:uid="{CD7AF51E-AEEF-4E08-B09C-F953306D8E05}"/>
-    <hyperlink ref="J682" r:id="rId418" xr:uid="{0F8D5664-9B0D-49E6-BF70-2BADB7464A90}"/>
-    <hyperlink ref="J683" r:id="rId419" xr:uid="{ACB7FC4C-AC5C-492D-AB7C-4B09264FA2AD}"/>
-    <hyperlink ref="J684" r:id="rId420" xr:uid="{DD4E0E6D-6ABF-4DE6-BA59-8E92FCBFFD65}"/>
-    <hyperlink ref="J688" r:id="rId421" xr:uid="{A8CA0879-22C0-4A99-936F-A5EA9A4DC6D4}"/>
-    <hyperlink ref="J693" r:id="rId422" xr:uid="{E7033F5D-627A-49AA-AA63-DC71FB7B4A99}"/>
-    <hyperlink ref="J694" r:id="rId423" xr:uid="{E63FBE5B-7258-46F8-A434-8E25B78722C7}"/>
-    <hyperlink ref="J695" r:id="rId424" xr:uid="{8F4DB0C6-BA4B-4231-BFE6-6588EC5AAAC0}"/>
-    <hyperlink ref="J696" r:id="rId425" xr:uid="{C56DA798-A0C2-480F-9722-95F02D12DE97}"/>
-    <hyperlink ref="J697" r:id="rId426" xr:uid="{80D48220-0573-459B-8ED0-874EE1E52CA8}"/>
-    <hyperlink ref="J698" r:id="rId427" xr:uid="{C3DC3F30-0001-49EC-976B-30FC7063A592}"/>
-    <hyperlink ref="J699" r:id="rId428" xr:uid="{B8369234-E7C6-48AB-A4E6-1DD25B05CFB8}"/>
-    <hyperlink ref="J700" r:id="rId429" xr:uid="{DF5E9AEC-7B76-4893-BE9B-38DF397D9A24}"/>
-    <hyperlink ref="J705" r:id="rId430" xr:uid="{38884580-32A2-440F-B161-AC144DB53016}"/>
-    <hyperlink ref="J708" r:id="rId431" xr:uid="{15B3C8A3-351A-4703-A11A-5C316E5E2238}"/>
-    <hyperlink ref="J712" r:id="rId432" xr:uid="{A9C3DFBA-BCA9-44F4-8063-1DDA8F331C1B}"/>
-    <hyperlink ref="J713" r:id="rId433" xr:uid="{8E815F63-2E33-4727-9A58-DAAC049DB8C1}"/>
-    <hyperlink ref="J714" r:id="rId434" xr:uid="{CF067B6E-456F-44C5-B52B-377DB66B54F7}"/>
-    <hyperlink ref="J715" r:id="rId435" xr:uid="{177D40CA-35BE-4566-B491-732583BBBE7A}"/>
-    <hyperlink ref="J718" r:id="rId436" xr:uid="{89792798-975D-4BCC-9EED-B7AAB87E5A9F}"/>
-    <hyperlink ref="J720" r:id="rId437" xr:uid="{4A1495E7-B416-4836-9979-772462484B67}"/>
-    <hyperlink ref="J721" r:id="rId438" xr:uid="{3AB827D1-AED5-4BAF-869D-40F33CF573E8}"/>
-    <hyperlink ref="J722" r:id="rId439" xr:uid="{FDF4A4CB-1D7D-4541-99E9-78E1DCC7AD12}"/>
-    <hyperlink ref="J725" r:id="rId440" xr:uid="{7F96562D-60D6-46CA-A321-33A89E005447}"/>
-    <hyperlink ref="J726" r:id="rId441" xr:uid="{81DF3F28-888D-4C51-B489-03BA0C3F61B9}"/>
-    <hyperlink ref="J728" r:id="rId442" xr:uid="{255D0FAD-E3E9-4067-82EE-15BA4580046E}"/>
-    <hyperlink ref="J729" r:id="rId443" xr:uid="{FF114F67-7795-4D48-B8B1-9B2B2B813052}"/>
-    <hyperlink ref="J736" r:id="rId444" xr:uid="{788E8226-EC64-4AB4-A564-C2818E7A8692}"/>
-    <hyperlink ref="J738" r:id="rId445" xr:uid="{5E3399B1-2828-4506-90DD-45A014C8A18C}"/>
-    <hyperlink ref="J739" r:id="rId446" xr:uid="{CCC22DEC-3858-48AC-BC6C-7276E83A8F63}"/>
-    <hyperlink ref="J740" r:id="rId447" xr:uid="{0BE34E4C-E8D5-4B9D-8878-92DE447D9753}"/>
-    <hyperlink ref="J741" r:id="rId448" xr:uid="{AED20B76-FB58-463A-8A15-B1EC9B323601}"/>
-    <hyperlink ref="J742" r:id="rId449" xr:uid="{843B38FC-DA68-4ECD-A28C-2532591B4D27}"/>
-    <hyperlink ref="J743" r:id="rId450" xr:uid="{D49FBC3D-F246-4096-AB9D-FA1246A5A7EB}"/>
-    <hyperlink ref="J744" r:id="rId451" xr:uid="{A78F0163-2F03-4D7A-8772-83519003FD94}"/>
-    <hyperlink ref="J747" r:id="rId452" xr:uid="{A9CD81B7-2A9F-455C-B597-A0FAA584D3AE}"/>
-    <hyperlink ref="J748" r:id="rId453" xr:uid="{8880B9AB-CCF8-4C76-8D8E-5D0202AAAE8D}"/>
-    <hyperlink ref="J757" r:id="rId454" xr:uid="{98ACFD26-B498-428B-AFD2-46B9F11F0C87}"/>
-    <hyperlink ref="J758" r:id="rId455" xr:uid="{77E94A28-E1C5-41C3-8FAF-9852E1FD36B6}"/>
-    <hyperlink ref="J759" r:id="rId456" xr:uid="{5DAA0D02-ABC9-40B8-A26F-0B47A32D4A83}"/>
-    <hyperlink ref="J760" r:id="rId457" xr:uid="{750512F2-E8F8-45EF-8002-3D0D66B3B24F}"/>
-    <hyperlink ref="J761" r:id="rId458" xr:uid="{BF85A419-1282-4833-8D8C-A73E011DAE35}"/>
-    <hyperlink ref="J762" r:id="rId459" xr:uid="{5E89BCC1-2028-467B-9537-78E7450F8BD0}"/>
-    <hyperlink ref="J764" r:id="rId460" xr:uid="{9F492607-CC4C-4A30-B4E5-33CA14C7A6B9}"/>
-    <hyperlink ref="J765" r:id="rId461" xr:uid="{5B6B63CB-6926-460C-ACC1-1882EDA5BFC5}"/>
-    <hyperlink ref="J766" r:id="rId462" xr:uid="{137B13E4-CC7D-42AF-9C75-2828A61C5B14}"/>
-    <hyperlink ref="J767" r:id="rId463" xr:uid="{408D5749-3F43-45EE-B3DA-C45E54948CBB}"/>
-    <hyperlink ref="J769" r:id="rId464" xr:uid="{D3B15FC4-1778-41FF-8B79-9BB0787ADEC9}"/>
-    <hyperlink ref="J770" r:id="rId465" xr:uid="{3D504C95-A15B-4411-AABA-F017667BE88A}"/>
-    <hyperlink ref="J772" r:id="rId466" xr:uid="{EA77823B-4AB8-4A63-A147-9C095F3E4F53}"/>
-    <hyperlink ref="J774" r:id="rId467" xr:uid="{52116CEF-BD82-4E9E-8EB0-9E65B43D4282}"/>
-    <hyperlink ref="J778" r:id="rId468" xr:uid="{35505F82-CFC6-48F6-AF31-42030565027B}"/>
-    <hyperlink ref="J781" r:id="rId469" xr:uid="{9620F038-2CEB-45F8-B741-D6A1E85AF38B}"/>
-    <hyperlink ref="J783" r:id="rId470" xr:uid="{4B4DB440-459E-46A3-91C0-CC3E286A7D9D}"/>
-    <hyperlink ref="J784" r:id="rId471" xr:uid="{84ADE070-980A-49F1-B3EA-C3F97EEB1699}"/>
-    <hyperlink ref="J785" r:id="rId472" xr:uid="{676127B5-3AE6-450A-86F2-3893B5CB7E4E}"/>
-    <hyperlink ref="J788" r:id="rId473" xr:uid="{1BA851A6-CD4B-451C-B579-55B21E908530}"/>
-    <hyperlink ref="J789" r:id="rId474" xr:uid="{B76D1252-9099-4A6A-B375-DC2F240E082B}"/>
-    <hyperlink ref="J790" r:id="rId475" xr:uid="{EACF9D67-3322-420F-9F81-D23DFBFEA3C0}"/>
-    <hyperlink ref="J794" r:id="rId476" xr:uid="{705FD21F-2983-4DB6-93F5-86777975778A}"/>
-    <hyperlink ref="J795" r:id="rId477" xr:uid="{F3CE896A-E9A5-4527-899C-85AF26B0834F}"/>
-    <hyperlink ref="J796" r:id="rId478" xr:uid="{3BAC0AB3-B010-4BC2-A3F7-FD5E260125A7}"/>
-    <hyperlink ref="J797" r:id="rId479" xr:uid="{C42295A8-6603-4236-BC93-8AE36EC5B754}"/>
-    <hyperlink ref="J799" r:id="rId480" xr:uid="{26A317CE-7CA1-4EF5-A1C5-6B5484044B65}"/>
-    <hyperlink ref="J800" r:id="rId481" xr:uid="{AED07741-B55E-4D6C-BE34-5C0EDEB4EEB7}"/>
-    <hyperlink ref="J801" r:id="rId482" xr:uid="{722594B9-FFE2-47EE-BB08-EB443A079154}"/>
-    <hyperlink ref="J802" r:id="rId483" xr:uid="{6A20F88B-9695-4F93-8AC3-C2245CD7BFB4}"/>
-    <hyperlink ref="J803" r:id="rId484" xr:uid="{395545F9-1A7E-4592-BB42-0B7769A0D89D}"/>
-    <hyperlink ref="J804" r:id="rId485" xr:uid="{D3ACB6B6-464E-4C5B-BD3E-32CD8C7464A6}"/>
-    <hyperlink ref="J805" r:id="rId486" xr:uid="{36FBDA0C-4EC4-44CF-A787-1FE9FD2E0BCC}"/>
-    <hyperlink ref="J806" r:id="rId487" xr:uid="{6548A7D2-C797-41F1-A4B6-D5C73BBE8A51}"/>
-    <hyperlink ref="J808" r:id="rId488" xr:uid="{3F08D009-8AFE-4A31-A171-5BFF079A0931}"/>
-    <hyperlink ref="J810" r:id="rId489" xr:uid="{B04C71E7-3612-4EF7-AC04-5B80FBAF2227}"/>
-    <hyperlink ref="J811" r:id="rId490" xr:uid="{6A3950C5-3DF4-48BC-AF35-75CC0192254B}"/>
-    <hyperlink ref="J812" r:id="rId491" xr:uid="{F70CCC24-0B2A-4DCB-B688-59EC423FBBE7}"/>
-    <hyperlink ref="J813" r:id="rId492" xr:uid="{BEF9ADD6-58C5-4AD4-8FF9-4E409377B2D4}"/>
-    <hyperlink ref="J814" r:id="rId493" xr:uid="{F604D531-05A1-48AC-830E-E1275FADDDA0}"/>
-    <hyperlink ref="J815" r:id="rId494" xr:uid="{8F76AD90-D9B3-47B4-8111-E9FF7912E870}"/>
-    <hyperlink ref="J816" r:id="rId495" xr:uid="{C45180A3-164E-4CE8-9776-4CCFEB48AE03}"/>
-    <hyperlink ref="J817" r:id="rId496" xr:uid="{863E19FE-17AB-498C-AFCC-14817033208F}"/>
-    <hyperlink ref="J818" r:id="rId497" xr:uid="{54B369AC-B2AE-4270-B663-D4F191AF4DD1}"/>
-    <hyperlink ref="J819" r:id="rId498" xr:uid="{140EAD88-FCC3-4A0F-B902-0CB2A359F685}"/>
-    <hyperlink ref="J820" r:id="rId499" xr:uid="{0D1ED5A8-09DB-4780-9E0C-DFD7037DFD5E}"/>
-    <hyperlink ref="J821" r:id="rId500" xr:uid="{9C52BCBD-18B5-4A93-8863-0D7DF5A59D06}"/>
-    <hyperlink ref="J822" r:id="rId501" xr:uid="{A04400FB-214D-4AF6-87B2-6099419E5005}"/>
-    <hyperlink ref="J825" r:id="rId502" xr:uid="{13A934A9-671C-42E0-A985-3085B31A7E9B}"/>
-    <hyperlink ref="J826" r:id="rId503" xr:uid="{ED7D59B3-F42E-4A6B-9598-506A47FEF4A7}"/>
-    <hyperlink ref="J827" r:id="rId504" xr:uid="{EDDE9FDC-64C1-47D2-9E59-CA2762DAB713}"/>
-    <hyperlink ref="J828" r:id="rId505" xr:uid="{BF43BB96-CF31-4634-B514-DD78D3A0E172}"/>
-    <hyperlink ref="J831" r:id="rId506" xr:uid="{730A091A-8083-46C6-ACD6-AB8EBF017407}"/>
-    <hyperlink ref="J832" r:id="rId507" xr:uid="{DC2DEC17-EA1E-4CCE-BE59-93D672DA8BF7}"/>
-    <hyperlink ref="J833" r:id="rId508" xr:uid="{BB6922E0-8025-402E-A67A-7C914C33B9A8}"/>
-    <hyperlink ref="J836" r:id="rId509" xr:uid="{C0585FBC-8498-4CC0-9F15-1A00015052B6}"/>
-    <hyperlink ref="J837" r:id="rId510" xr:uid="{8570230C-389C-4038-ACA1-229BBC9BAD53}"/>
-    <hyperlink ref="J838" r:id="rId511" xr:uid="{F7B80C57-9F6A-4543-B074-2573ABCEC584}"/>
-    <hyperlink ref="J839" r:id="rId512" xr:uid="{8207215B-08D1-46AE-BBD3-1035E1D7048C}"/>
-    <hyperlink ref="J840" r:id="rId513" xr:uid="{FC7CB1A8-4FEA-4497-B5B4-A39BA3153D87}"/>
-    <hyperlink ref="J841" r:id="rId514" xr:uid="{CBF0402B-3635-4C92-B78F-A1BDE419A550}"/>
-    <hyperlink ref="J842" r:id="rId515" xr:uid="{AE62ACE8-8471-4955-A7D1-BDF633815463}"/>
-    <hyperlink ref="J843" r:id="rId516" xr:uid="{85D4B799-B164-42B0-BABB-072BA1A3D6BA}"/>
-    <hyperlink ref="J844" r:id="rId517" xr:uid="{65177B01-3558-4596-8F38-D43C764EB864}"/>
-    <hyperlink ref="J847" r:id="rId518" xr:uid="{0FF84ED9-8454-47FD-B316-4B9A70173E68}"/>
-    <hyperlink ref="J848" r:id="rId519" xr:uid="{1ED49319-0584-467E-9302-9D5E223B59F4}"/>
-    <hyperlink ref="J850" r:id="rId520" xr:uid="{B9094F1B-98AA-4DC2-80E9-622555E86D68}"/>
-    <hyperlink ref="J852" r:id="rId521" xr:uid="{A657C24A-0E78-45C8-9E71-B58739E36B77}"/>
-    <hyperlink ref="J853" r:id="rId522" xr:uid="{4077FB74-32B5-4DC9-B2C7-34C08988F32A}"/>
-    <hyperlink ref="J856" r:id="rId523" xr:uid="{B7706849-460D-4988-A49D-15D282DD2C47}"/>
-    <hyperlink ref="J858" r:id="rId524" xr:uid="{948FF48D-F86A-4C2F-B543-9AFA37ADCC86}"/>
-    <hyperlink ref="J861" r:id="rId525" xr:uid="{55A9A0AC-65E2-403D-A068-889473821D58}"/>
-    <hyperlink ref="J862" r:id="rId526" xr:uid="{376561C3-DF3F-4B73-BBC4-5696EF5ACA8A}"/>
-    <hyperlink ref="J863" r:id="rId527" xr:uid="{D775EBF5-6A9C-4732-A2CF-6F6B0671A9CA}"/>
-    <hyperlink ref="J865" r:id="rId528" xr:uid="{F88246EB-6242-40CF-A9BF-CAF00E99C001}"/>
-    <hyperlink ref="J866" r:id="rId529" xr:uid="{A76BD31B-BF78-4903-B62A-464E21A0BF39}"/>
-    <hyperlink ref="J867" r:id="rId530" xr:uid="{EF19E910-FE4C-4E86-AF47-473452FD6B31}"/>
-    <hyperlink ref="J868" r:id="rId531" xr:uid="{B8F082D0-98A4-4965-9DA0-116B90FA081A}"/>
-    <hyperlink ref="J870" r:id="rId532" xr:uid="{74EB3F50-1737-40E3-B27C-91F320896713}"/>
-    <hyperlink ref="J871" r:id="rId533" xr:uid="{60792E38-0B24-4502-9946-F378929375AB}"/>
-    <hyperlink ref="J872" r:id="rId534" xr:uid="{777E5F57-54B9-4C1F-A64C-E144981E6E84}"/>
-    <hyperlink ref="J873" r:id="rId535" xr:uid="{1BE7220F-0A84-476E-86D8-1F32FBFC3D68}"/>
-    <hyperlink ref="J875" r:id="rId536" xr:uid="{F9FD7240-522C-438E-BC75-53481A8DF253}"/>
-    <hyperlink ref="J877" r:id="rId537" xr:uid="{36386573-4622-4525-AC6A-86B73C188B8C}"/>
-    <hyperlink ref="J878" r:id="rId538" xr:uid="{81FC351E-5C86-4C7A-88F6-73D304AA8101}"/>
-    <hyperlink ref="J880" r:id="rId539" xr:uid="{9ADF0923-0EFE-426A-A357-CC02F903C89D}"/>
-    <hyperlink ref="J882" r:id="rId540" xr:uid="{D8CD8804-A082-4591-8289-EFB445395D7F}"/>
-    <hyperlink ref="J883" r:id="rId541" xr:uid="{9FBDF2E7-A465-407F-A945-50780DB5D6C1}"/>
-    <hyperlink ref="J884" r:id="rId542" xr:uid="{A1A34F15-1177-4AD3-BA63-3F3A1D8C779D}"/>
-    <hyperlink ref="J885" r:id="rId543" xr:uid="{E77CBEBC-E1E2-4C92-969F-6C0D430878BF}"/>
-    <hyperlink ref="J886" r:id="rId544" xr:uid="{C3C613E1-8694-4F33-A32A-BB05703A2550}"/>
-    <hyperlink ref="J888" r:id="rId545" xr:uid="{37BF0872-4A03-45C9-ABDA-8E67DAAE7BBD}"/>
-    <hyperlink ref="J889" r:id="rId546" xr:uid="{40285FC4-8E64-411E-9C7B-734503432D1A}"/>
-    <hyperlink ref="J893" r:id="rId547" xr:uid="{B5B50E5C-110C-4E9C-8E71-E3EC1F165931}"/>
-    <hyperlink ref="J894" r:id="rId548" xr:uid="{9360C61B-4D58-4D1A-ABFE-1FA25636ACBE}"/>
-    <hyperlink ref="J895" r:id="rId549" xr:uid="{051D7702-7702-41B9-8F47-5D87816D9A49}"/>
-    <hyperlink ref="J896" r:id="rId550" xr:uid="{A86373D8-3852-4526-841F-9C0A7C6E7259}"/>
-    <hyperlink ref="J897" r:id="rId551" xr:uid="{371882BA-31F5-4346-9451-9C401AC88ECF}"/>
-    <hyperlink ref="J899" r:id="rId552" xr:uid="{6A002F61-8AED-4E5B-BC83-55986146DC55}"/>
-    <hyperlink ref="J900" r:id="rId553" xr:uid="{47069B0A-BC67-4404-8939-A277B24B2B25}"/>
-    <hyperlink ref="J905" r:id="rId554" xr:uid="{1C988D06-9E69-465B-84DC-7727034BD76F}"/>
-    <hyperlink ref="J906" r:id="rId555" xr:uid="{CD4C0441-8DE1-4B1E-B687-556F2D3B0C7D}"/>
-    <hyperlink ref="J907" r:id="rId556" xr:uid="{7063487F-D4A9-4CE2-B8C3-82FFDA39E60A}"/>
-    <hyperlink ref="J908" r:id="rId557" xr:uid="{2C7B6297-B459-44F5-8884-0690A5A88C0C}"/>
-    <hyperlink ref="J909" r:id="rId558" xr:uid="{02A7F9A9-74CB-4C11-BF65-46553E5A25B0}"/>
-    <hyperlink ref="J910" r:id="rId559" xr:uid="{8E209C03-6B5F-4081-8EFA-5913FC77E401}"/>
-    <hyperlink ref="J911" r:id="rId560" xr:uid="{BE9D0DBC-FFF0-4C4E-8897-1FF0B2C9BC51}"/>
-    <hyperlink ref="J912" r:id="rId561" xr:uid="{04048352-097A-459A-B321-9E4C6CB12778}"/>
-    <hyperlink ref="J913" r:id="rId562" xr:uid="{348FDE81-EB64-4BCA-9572-5D31A105BD8C}"/>
-    <hyperlink ref="J914" r:id="rId563" xr:uid="{F9567989-DA91-4E6A-900F-52D8AED99C92}"/>
-    <hyperlink ref="J915" r:id="rId564" xr:uid="{E3AF29C2-DEF7-43DF-AD0D-2E3F414E35F2}"/>
-    <hyperlink ref="J916" r:id="rId565" xr:uid="{45584430-07D7-4058-B112-9EBCEA56A511}"/>
-    <hyperlink ref="J918" r:id="rId566" xr:uid="{47113754-6BDB-4F7C-B288-EF5CE0C0B9C9}"/>
-    <hyperlink ref="J919" r:id="rId567" xr:uid="{C205A6B2-4B44-40EA-B919-079299F0E045}"/>
-    <hyperlink ref="J922" r:id="rId568" xr:uid="{7C703D3C-F339-4BF7-92C1-C693D8ADA16D}"/>
-    <hyperlink ref="J923" r:id="rId569" xr:uid="{6C600C19-DF99-455A-A1D0-AA23759724BD}"/>
-    <hyperlink ref="J925" r:id="rId570" xr:uid="{FCAB65FC-07D1-422E-B2A7-3FB9EF0929CD}"/>
-    <hyperlink ref="J926" r:id="rId571" xr:uid="{01177C7E-3964-4DBC-973E-844E403671D4}"/>
-    <hyperlink ref="J928" r:id="rId572" xr:uid="{237F24EE-9F35-4123-A453-4CC6E8F7CE02}"/>
-    <hyperlink ref="J929" r:id="rId573" xr:uid="{1B91283F-81E7-4A23-927D-7772C4057B80}"/>
-    <hyperlink ref="J930" r:id="rId574" xr:uid="{170ACCD6-8091-4104-8FC4-DF3A156D6548}"/>
-    <hyperlink ref="J931" r:id="rId575" xr:uid="{F714436C-CED3-4826-9E46-3CCD2012B769}"/>
-    <hyperlink ref="J932" r:id="rId576" xr:uid="{35B94044-CB05-4614-8E25-6FC4B848D0AE}"/>
-    <hyperlink ref="J933" r:id="rId577" xr:uid="{431EFB2F-7ABE-4309-A314-E7354015E09D}"/>
-    <hyperlink ref="J935" r:id="rId578" xr:uid="{4AF7B7FD-3508-46D3-A7C0-8F46FD475A12}"/>
-    <hyperlink ref="J940" r:id="rId579" xr:uid="{7282146A-B40D-4A57-BE8F-1E0A69442B0B}"/>
-    <hyperlink ref="J941" r:id="rId580" xr:uid="{D157E729-9FE3-4DD4-A706-A810B2F73840}"/>
-    <hyperlink ref="J942" r:id="rId581" xr:uid="{5FDCBAC6-2E70-414D-AB02-7082E16F6D17}"/>
-    <hyperlink ref="J943" r:id="rId582" xr:uid="{9FD7437B-7E86-4A89-AE15-C177424CDBEC}"/>
-    <hyperlink ref="J944" r:id="rId583" xr:uid="{C9AE6DB2-0BD8-45A9-99D1-39D2FB817E08}"/>
-    <hyperlink ref="J946" r:id="rId584" xr:uid="{244C25D3-CE68-4215-9DE8-1327388D8840}"/>
-    <hyperlink ref="J947" r:id="rId585" xr:uid="{0C6185C0-7898-447C-A618-A7EC92BD1AF5}"/>
-    <hyperlink ref="J948" r:id="rId586" xr:uid="{F5843415-A37A-49F9-B33A-2FD19129950E}"/>
-    <hyperlink ref="J949" r:id="rId587" xr:uid="{DD1999B0-1BE4-4862-BD0D-E5A4185F7C00}"/>
-    <hyperlink ref="J950" r:id="rId588" xr:uid="{F5269955-67FC-4C87-B590-F98D2E46009B}"/>
-    <hyperlink ref="J952" r:id="rId589" xr:uid="{FA6B0C7E-EE90-4760-B0C4-71ABE3196562}"/>
-    <hyperlink ref="J953" r:id="rId590" xr:uid="{07965BC0-A473-461B-9CCC-F605A236B031}"/>
-    <hyperlink ref="J954" r:id="rId591" xr:uid="{3D6BCD16-C50A-414C-BBE2-1F0D15AF237B}"/>
-    <hyperlink ref="J955" r:id="rId592" xr:uid="{B1B455D0-3E9A-4503-9F5F-2CE50C159252}"/>
-    <hyperlink ref="J956" r:id="rId593" xr:uid="{8065BBAD-F7CB-41F3-8B3B-72C91FD3DFAB}"/>
-    <hyperlink ref="J958" r:id="rId594" xr:uid="{0B66D3D7-AEB9-4D00-947F-F90023FE28BB}"/>
-    <hyperlink ref="J962" r:id="rId595" xr:uid="{7A4861FD-5B27-4696-9830-4EF2F317FE50}"/>
-    <hyperlink ref="J963" r:id="rId596" xr:uid="{42BEE64B-AC84-44F2-946B-6EF43EE4883F}"/>
-    <hyperlink ref="J965" r:id="rId597" xr:uid="{75D0AB47-45D1-4388-84AC-443F9713E53A}"/>
-    <hyperlink ref="J968" r:id="rId598" xr:uid="{166A3FF2-A51B-44F8-87DD-9A1B2AB69668}"/>
-    <hyperlink ref="J969" r:id="rId599" xr:uid="{4F369509-65F1-4511-A833-1722E3BC30D8}"/>
-    <hyperlink ref="J971" r:id="rId600" xr:uid="{2F7704A9-736E-4CD0-AAE4-6FDDF9F27CE8}"/>
-    <hyperlink ref="J973" r:id="rId601" xr:uid="{7924AA75-9CD6-45D5-B99A-2A68DC17E93A}"/>
-    <hyperlink ref="J974" r:id="rId602" xr:uid="{232002F3-F384-4714-9E12-D328412CB92A}"/>
-    <hyperlink ref="J975" r:id="rId603" xr:uid="{EF1EABC6-BEA6-48B7-BA8B-C63FF1DC53D8}"/>
-    <hyperlink ref="J976" r:id="rId604" xr:uid="{CCDBB4E8-E35E-4A34-A1A4-A3E66D003683}"/>
-    <hyperlink ref="J977" r:id="rId605" xr:uid="{B7ECF985-0164-4412-8A8F-6DB340646900}"/>
-    <hyperlink ref="J981" r:id="rId606" xr:uid="{2AD769E5-68EE-4A86-A3DA-55CE7931747C}"/>
-    <hyperlink ref="J984" r:id="rId607" xr:uid="{20001AF8-EBED-417E-8A71-A8C2C3CF9874}"/>
-    <hyperlink ref="J986" r:id="rId608" xr:uid="{A12A61FA-1D1D-4062-93A7-DD4C41F026CC}"/>
-    <hyperlink ref="J990" r:id="rId609" xr:uid="{5C330F4C-256B-4430-8047-AE0FCD64AC6A}"/>
-    <hyperlink ref="J991" r:id="rId610" xr:uid="{57D4C0E5-B674-45BB-A817-9E4A1D43A48D}"/>
-    <hyperlink ref="J996" r:id="rId611" xr:uid="{9AA820E7-50B3-47E0-85B8-CF09FDEE9222}"/>
-    <hyperlink ref="J997" r:id="rId612" xr:uid="{23C38B8F-2461-4343-BB96-46CC829F2C62}"/>
-    <hyperlink ref="J999" r:id="rId613" xr:uid="{42017C05-DD15-4721-806F-2595428D5DBF}"/>
-    <hyperlink ref="J1000" r:id="rId614" xr:uid="{82184D32-3AFE-4661-A0DE-F7E0D0B95DA4}"/>
-    <hyperlink ref="J1003" r:id="rId615" xr:uid="{B91021A5-0205-44BD-A1F9-6F2E3BDC3AA4}"/>
-    <hyperlink ref="J1004" r:id="rId616" xr:uid="{74BA2B2E-1B37-47FE-BE74-65E0745F38EC}"/>
-    <hyperlink ref="J1005" r:id="rId617" xr:uid="{AEC0F090-186A-4865-9B35-C7A5669EF9FD}"/>
-    <hyperlink ref="J1006" r:id="rId618" xr:uid="{DB95782B-BC4D-429D-8BAE-235A22C172E0}"/>
-    <hyperlink ref="J1007" r:id="rId619" xr:uid="{2A289A2C-93D0-412D-B0FB-1DB7C9C94CDF}"/>
-    <hyperlink ref="J1008" r:id="rId620" xr:uid="{435D7543-E6B4-444A-8AA2-AB1F621C8612}"/>
-    <hyperlink ref="J1009" r:id="rId621" xr:uid="{1B4A792F-ACD7-43A7-932E-0CE988C58ED5}"/>
-    <hyperlink ref="J1011" r:id="rId622" xr:uid="{C12CC17B-6372-4992-BE09-15A3E48F04F8}"/>
-    <hyperlink ref="J1012" r:id="rId623" xr:uid="{3AC4F8E6-A5B9-43BC-8552-8D582A7A91D9}"/>
-    <hyperlink ref="J1016" r:id="rId624" xr:uid="{000BB294-3068-449F-908E-6B359582C9B0}"/>
-    <hyperlink ref="J1019" r:id="rId625" xr:uid="{8992C019-CB84-40C8-BA19-0F7AFE34D4FA}"/>
-    <hyperlink ref="J1020" r:id="rId626" xr:uid="{4AF07A09-EB41-4113-B83B-DFCA9B3EA915}"/>
-    <hyperlink ref="J1023" r:id="rId627" xr:uid="{0C715B7D-959D-4737-93D8-8E3384BB3BB2}"/>
-    <hyperlink ref="J1024" r:id="rId628" xr:uid="{FF9FE666-C866-483A-BA43-0BA26AC544AB}"/>
-    <hyperlink ref="J1025" r:id="rId629" xr:uid="{DDF76A14-8A6B-4585-BFBA-9F78BF514300}"/>
-    <hyperlink ref="J1026" r:id="rId630" xr:uid="{38A2C84C-FF2C-4BC3-90E5-1F9B074DA3EF}"/>
-    <hyperlink ref="J1027" r:id="rId631" xr:uid="{0591522E-35AE-43C5-BAF4-F420F1AF0D84}"/>
-    <hyperlink ref="J1028" r:id="rId632" xr:uid="{3430D2F7-664B-47CD-85AE-2B40119ED34B}"/>
-    <hyperlink ref="J1030" r:id="rId633" xr:uid="{3E243B30-7A97-4565-9A86-9C7A6373DA3C}"/>
-    <hyperlink ref="J1033" r:id="rId634" xr:uid="{4BE3D379-5FB8-4322-9669-A3FE9E12C71C}"/>
-    <hyperlink ref="J1034" r:id="rId635" xr:uid="{D95AA629-79C1-42F4-80F2-203D4E38CA92}"/>
-    <hyperlink ref="J1036" r:id="rId636" xr:uid="{69504F97-6DDC-4DCF-A5F0-245D587DD296}"/>
-    <hyperlink ref="J1037" r:id="rId637" xr:uid="{169C8212-0ED8-477D-9E5D-F3F37033AEA1}"/>
-    <hyperlink ref="J1041" r:id="rId638" xr:uid="{32C365DE-2ADF-4B76-BAED-8E7015ADC051}"/>
-    <hyperlink ref="J1042" r:id="rId639" xr:uid="{12C3A2A9-D763-4329-A81A-7947C84A1F36}"/>
-    <hyperlink ref="J1043" r:id="rId640" xr:uid="{345A7B5F-7A1A-4606-9C48-EBBB6206A6AC}"/>
-    <hyperlink ref="J1044" r:id="rId641" xr:uid="{FE2024CD-9B1A-4AB6-9EA1-BC66673BC2DE}"/>
-    <hyperlink ref="J1046" r:id="rId642" xr:uid="{18AB04A7-4CB6-4DCA-B227-5D58313D46A4}"/>
-    <hyperlink ref="J1047" r:id="rId643" xr:uid="{AA8B0722-11B6-4479-BA30-8896FE48A097}"/>
-    <hyperlink ref="J1051" r:id="rId644" xr:uid="{08850F3C-0036-4B8B-B897-3FA05E1DD828}"/>
-    <hyperlink ref="J1052" r:id="rId645" xr:uid="{74C903A4-681D-4499-99A9-129023538E8C}"/>
-    <hyperlink ref="J1054" r:id="rId646" xr:uid="{CD147121-1395-43F3-BFCF-9A3988DD8E8A}"/>
-    <hyperlink ref="J1056" r:id="rId647" xr:uid="{454A44C0-4B14-42D8-893A-CFAB4EAF849D}"/>
-    <hyperlink ref="J1064" r:id="rId648" xr:uid="{884294BE-427E-4975-99F7-3AFF5BCE1C3C}"/>
-    <hyperlink ref="J1065" r:id="rId649" xr:uid="{41D4A546-044E-4FD1-BF89-15D3D10B61FF}"/>
-    <hyperlink ref="J1066" r:id="rId650" xr:uid="{CA7A0D27-7A75-4E29-8D54-FB1D5B6E320C}"/>
-    <hyperlink ref="J1067" r:id="rId651" xr:uid="{DDA150BE-8ED8-4AE0-B5CC-BBC61BEFDA61}"/>
-    <hyperlink ref="J1068" r:id="rId652" xr:uid="{8DDCA776-E55A-491C-91B0-062CC4AC0EDF}"/>
-    <hyperlink ref="J1069" r:id="rId653" xr:uid="{B14F056E-2FB6-44E9-AC30-1E541788DB05}"/>
-    <hyperlink ref="J1070" r:id="rId654" xr:uid="{677153C8-0759-4902-BA7B-581987735EA6}"/>
-    <hyperlink ref="J1071" r:id="rId655" xr:uid="{288115C9-24CD-4B59-A386-280A9A071579}"/>
-    <hyperlink ref="J1072" r:id="rId656" xr:uid="{649B8EED-F58D-40C5-AE44-E7501839B175}"/>
-    <hyperlink ref="J1073" r:id="rId657" xr:uid="{432CA7A7-72E8-4045-B0B6-3DFB52AF631F}"/>
-    <hyperlink ref="J1076" r:id="rId658" xr:uid="{CC6A8575-6EEC-4F2C-A28B-0DAC6CA9D635}"/>
-    <hyperlink ref="J1077" r:id="rId659" xr:uid="{4D08E705-E8A0-440C-B81C-E6C1219BF030}"/>
-    <hyperlink ref="J1078" r:id="rId660" xr:uid="{8B244B83-F13A-4484-87C2-FC2DD8B237D6}"/>
-    <hyperlink ref="J1080" r:id="rId661" xr:uid="{D2A468E7-C797-4107-8A7F-15FA0B073781}"/>
-    <hyperlink ref="J1082" r:id="rId662" xr:uid="{4DA244F7-7E14-49F8-877B-294A0C8B3908}"/>
-    <hyperlink ref="J1086" r:id="rId663" xr:uid="{E8937F20-1C9D-478F-A095-49609DE5B09B}"/>
-    <hyperlink ref="J1087" r:id="rId664" xr:uid="{B36E2C8B-ED89-4DE1-806E-638B35A601A3}"/>
-    <hyperlink ref="J1088" r:id="rId665" xr:uid="{15785FEF-A412-48AD-9A83-2DE4D77D766A}"/>
-    <hyperlink ref="J1090" r:id="rId666" xr:uid="{10303626-2EE5-40C2-88BA-1D09F4535DC8}"/>
-    <hyperlink ref="J1091" r:id="rId667" xr:uid="{E0D05F3E-B118-429A-9848-CA2F9FEDC669}"/>
-    <hyperlink ref="J1098" r:id="rId668" xr:uid="{34786FF5-6020-4A34-975A-0504922508C0}"/>
-    <hyperlink ref="J1100" r:id="rId669" xr:uid="{6B875F50-EF34-4BBE-88F1-5D4BCF2E3164}"/>
-    <hyperlink ref="J1102" r:id="rId670" xr:uid="{A774B16C-B711-47EE-9721-D639FA7C491E}"/>
-    <hyperlink ref="J1103" r:id="rId671" xr:uid="{69583A86-3BD2-4F38-8E58-76CF577345B9}"/>
-    <hyperlink ref="J1104" r:id="rId672" xr:uid="{484668BC-9C9E-4E39-80EF-50525F37FA44}"/>
-    <hyperlink ref="J1106" r:id="rId673" xr:uid="{768D8655-98C0-4A1B-85A0-DD6980D7A19E}"/>
-    <hyperlink ref="J1109" r:id="rId674" xr:uid="{BD75613E-6A11-4F06-A8DD-7B499F8CB68F}"/>
-    <hyperlink ref="J1110" r:id="rId675" xr:uid="{5E4FAEC1-78B7-4610-B522-34690BB21C07}"/>
-    <hyperlink ref="J1113" r:id="rId676" xr:uid="{29F84B81-1324-415A-A7ED-73270EA94F66}"/>
-    <hyperlink ref="J1114" r:id="rId677" xr:uid="{59D543CA-0F5C-4FE4-A2E8-8A0F0474B18D}"/>
-    <hyperlink ref="J1115" r:id="rId678" xr:uid="{649ACE2B-139A-42C3-B6A8-5EDE1F609954}"/>
-    <hyperlink ref="J1116" r:id="rId679" xr:uid="{5131F61F-5CDA-46AB-A6D3-F29F7DD0B9A3}"/>
-    <hyperlink ref="J1117" r:id="rId680" xr:uid="{31437A31-B485-4FA3-A9F2-5D0A46A5A7D0}"/>
-    <hyperlink ref="J1118" r:id="rId681" xr:uid="{09F77F41-29FA-4AED-B040-140FE8B9CF8E}"/>
-    <hyperlink ref="J1119" r:id="rId682" xr:uid="{F881B1D2-5326-47AD-9C19-6CBC043067DC}"/>
-    <hyperlink ref="J1124" r:id="rId683" xr:uid="{535C8650-D9EA-429D-8B34-5B89230ACD8F}"/>
-    <hyperlink ref="J1125" r:id="rId684" xr:uid="{4D5B629A-0B0A-4FBC-B386-03B0F247F3B4}"/>
-    <hyperlink ref="J1126" r:id="rId685" xr:uid="{9EB718D0-4873-4E6F-B9C5-8CE0AE020F6D}"/>
-    <hyperlink ref="J1127" r:id="rId686" xr:uid="{F9ABF3D6-2E26-4259-BBA5-F1918A2625AD}"/>
-    <hyperlink ref="J1128" r:id="rId687" xr:uid="{C728419D-1D0F-4DE6-B4B8-3567739149CC}"/>
-    <hyperlink ref="J1129" r:id="rId688" xr:uid="{6AD56049-B8D9-4CF3-8E43-703BDC934266}"/>
-    <hyperlink ref="J1130" r:id="rId689" xr:uid="{725238DC-A483-4F60-849C-C033DAC32C98}"/>
-    <hyperlink ref="J1131" r:id="rId690" xr:uid="{B48B265D-72CB-4E13-99E0-48FD35990F98}"/>
-    <hyperlink ref="J1132" r:id="rId691" xr:uid="{078877EF-F092-4724-9598-CAD393F82EAA}"/>
-    <hyperlink ref="J1133" r:id="rId692" xr:uid="{693A1708-235D-4938-A162-206AC298B4E3}"/>
-    <hyperlink ref="J1134" r:id="rId693" xr:uid="{194DAD5C-9F51-49B6-B0A7-8288DFEEFD61}"/>
-    <hyperlink ref="J1135" r:id="rId694" xr:uid="{5D8ECEC4-A2CF-4A57-AD2E-59A40F5FED42}"/>
-    <hyperlink ref="J1136" r:id="rId695" xr:uid="{AB4B2CE1-FEB1-41CE-93D6-AA3D2E9FADD9}"/>
+    <hyperlink ref="J5" r:id="rId1" xr:uid="{2792E19E-4D64-443D-B606-ED8B2FE7B089}"/>
+    <hyperlink ref="J7" r:id="rId2" xr:uid="{B8E461C6-FF77-4C45-BA4A-EC683C4341F8}"/>
+    <hyperlink ref="J8" r:id="rId3" xr:uid="{4B94D61B-D561-418F-8BC0-C38BD680C584}"/>
+    <hyperlink ref="J10" r:id="rId4" xr:uid="{A00652FA-58D3-476F-AC84-1103A8ADC08B}"/>
+    <hyperlink ref="J13" r:id="rId5" xr:uid="{7B4CB757-5546-4642-9305-D7616C9F0D45}"/>
+    <hyperlink ref="J14" r:id="rId6" xr:uid="{D8C042FE-B18B-4429-AC75-460275E82147}"/>
+    <hyperlink ref="J17" r:id="rId7" xr:uid="{A2519C0F-1BBA-487F-8E96-3C915B9B8D15}"/>
+    <hyperlink ref="J19" r:id="rId8" xr:uid="{46BEEA34-FE65-4037-8024-F42900EF1F4A}"/>
+    <hyperlink ref="J20" r:id="rId9" xr:uid="{93BA4F21-7263-4897-B4FC-105B385D8BA5}"/>
+    <hyperlink ref="J21" r:id="rId10" xr:uid="{F9765BB0-2161-439E-8154-FC75AD26D934}"/>
+    <hyperlink ref="J24" r:id="rId11" xr:uid="{2349760B-C92A-40A2-9EA0-A60204667459}"/>
+    <hyperlink ref="J25" r:id="rId12" xr:uid="{65C1C92A-C63F-44FC-AE8B-C62BAC7D960B}"/>
+    <hyperlink ref="J26" r:id="rId13" xr:uid="{C61B6D7A-AEB8-4517-A09A-657901E2D0BC}"/>
+    <hyperlink ref="J27" r:id="rId14" xr:uid="{994FA3EE-2527-455D-8193-DE8D05D16AA4}"/>
+    <hyperlink ref="J29" r:id="rId15" xr:uid="{C050271D-FDB3-4524-98B7-6CEDB92A2D2A}"/>
+    <hyperlink ref="J30" r:id="rId16" xr:uid="{09A0089F-5AC6-44DD-8C8C-84EBF7C89938}"/>
+    <hyperlink ref="J31" r:id="rId17" xr:uid="{C96FDE64-CA0E-4CA1-91BA-DC70CD7F0076}"/>
+    <hyperlink ref="J34" r:id="rId18" xr:uid="{4CEC010F-CA15-48A0-AE09-01A3433F6861}"/>
+    <hyperlink ref="J35" r:id="rId19" xr:uid="{3DBB6E91-4E0A-41D4-ACAB-0BFC8507E019}"/>
+    <hyperlink ref="J36" r:id="rId20" xr:uid="{F72CBF62-3DED-4287-A649-25C0AAF98BD2}"/>
+    <hyperlink ref="J37" r:id="rId21" xr:uid="{33C39F19-A2E6-4020-814E-5B6D67D44E3E}"/>
+    <hyperlink ref="J38" r:id="rId22" xr:uid="{6031840D-F40C-4DC5-8FF5-78AD33465BB2}"/>
+    <hyperlink ref="J46" r:id="rId23" xr:uid="{55148062-F788-4937-9C8A-8B5EA9EF1C47}"/>
+    <hyperlink ref="J47" r:id="rId24" xr:uid="{F4A6E7F9-00EC-450B-9531-6F5BAED0A70D}"/>
+    <hyperlink ref="J48" r:id="rId25" xr:uid="{3C421176-D77E-4078-97C9-26FF1BE7A3A4}"/>
+    <hyperlink ref="J49" r:id="rId26" xr:uid="{0CE3F5F9-E4C7-46BC-8894-36B1B6562C4F}"/>
+    <hyperlink ref="J50" r:id="rId27" xr:uid="{33327639-F499-4420-B9AD-83535511282F}"/>
+    <hyperlink ref="J52" r:id="rId28" xr:uid="{706E10AD-C593-4E31-8E6F-413C8DACC684}"/>
+    <hyperlink ref="J53" r:id="rId29" xr:uid="{EF5B9E42-AAE8-43B0-A750-ABEC98680A06}"/>
+    <hyperlink ref="J54" r:id="rId30" xr:uid="{421B1052-5660-46E9-AB81-0609D8043A2C}"/>
+    <hyperlink ref="J56" r:id="rId31" xr:uid="{FF9AFFE9-51E2-4BA8-B895-30D989848D18}"/>
+    <hyperlink ref="J59" r:id="rId32" xr:uid="{C635AB18-147C-4EF0-94EA-7A42794CBC38}"/>
+    <hyperlink ref="J61" r:id="rId33" xr:uid="{8B4EACCA-F296-41B8-83C4-8B82EDD1337B}"/>
+    <hyperlink ref="J62" r:id="rId34" xr:uid="{51662213-55FA-4459-A5F6-813B2694A438}"/>
+    <hyperlink ref="J63" r:id="rId35" xr:uid="{AF0D714A-D142-48F7-8ECB-D336AECA89E1}"/>
+    <hyperlink ref="J64" r:id="rId36" xr:uid="{813E2D3D-E944-4974-9E44-987ECBAD5A88}"/>
+    <hyperlink ref="J69" r:id="rId37" xr:uid="{5B5F4616-775E-4570-BE05-C75C71D783E9}"/>
+    <hyperlink ref="J71" r:id="rId38" xr:uid="{CD8636AC-C1D5-4800-B636-BC3812ACC240}"/>
+    <hyperlink ref="J72" r:id="rId39" xr:uid="{C2DF0FD7-96AE-4950-AF2B-0499A439BE9F}"/>
+    <hyperlink ref="J73" r:id="rId40" xr:uid="{DA0CDF86-ED1D-48C5-B6C0-C3B9DC8519E6}"/>
+    <hyperlink ref="J74" r:id="rId41" xr:uid="{396F4AAA-BE52-449D-BFF2-786577D1DDFE}"/>
+    <hyperlink ref="J75" r:id="rId42" xr:uid="{06DA3A12-825F-4305-B753-3E78B553F3F1}"/>
+    <hyperlink ref="J76" r:id="rId43" xr:uid="{40065C83-9AB1-44CE-B639-39C4604D5FAA}"/>
+    <hyperlink ref="J78" r:id="rId44" xr:uid="{29045A81-9017-4199-9A85-3CF08B899232}"/>
+    <hyperlink ref="J80" r:id="rId45" xr:uid="{56D5218B-36D6-4C3C-AFBA-C332824B46B6}"/>
+    <hyperlink ref="J86" r:id="rId46" xr:uid="{3C9A0223-CD1B-4EEC-BB40-35A679462132}"/>
+    <hyperlink ref="J88" r:id="rId47" xr:uid="{0F9A7F2C-874D-4374-883D-AED7F097CB6B}"/>
+    <hyperlink ref="J89" r:id="rId48" xr:uid="{409A07E9-A5D4-4718-B1F7-40C9E2769ADD}"/>
+    <hyperlink ref="J90" r:id="rId49" xr:uid="{6D7CB21F-0A79-4004-B8A5-C61C3A1CEAAA}"/>
+    <hyperlink ref="J92" r:id="rId50" xr:uid="{7AB566E6-544E-411B-908A-C13E774C0CD5}"/>
+    <hyperlink ref="J94" r:id="rId51" xr:uid="{C1E50AA7-A91E-475F-BC42-38731337C46F}"/>
+    <hyperlink ref="J95" r:id="rId52" xr:uid="{E5C763DD-F2E8-4C22-9EE3-D67428AD8FF7}"/>
+    <hyperlink ref="J96" r:id="rId53" xr:uid="{CC15FF67-19C3-431F-A4F7-677E37D8ECAC}"/>
+    <hyperlink ref="J101" r:id="rId54" xr:uid="{704E5B98-D0A6-4700-B9B8-25E9E411C19B}"/>
+    <hyperlink ref="J103" r:id="rId55" xr:uid="{E5890099-3BF4-4E7C-9238-19A43F9C49CA}"/>
+    <hyperlink ref="J104" r:id="rId56" xr:uid="{0919C872-E784-43E9-848A-CD9E8F850372}"/>
+    <hyperlink ref="J105" r:id="rId57" xr:uid="{95469EEF-1AB3-492A-B100-B3AADCF794B8}"/>
+    <hyperlink ref="J106" r:id="rId58" xr:uid="{3BC1C25D-B19B-4856-A015-19AB6C87E533}"/>
+    <hyperlink ref="J107" r:id="rId59" xr:uid="{B0E4FBA2-8635-4F3E-9620-0C59DE06B6E3}"/>
+    <hyperlink ref="J109" r:id="rId60" xr:uid="{A48C8236-B330-408C-B16B-B00651BA1335}"/>
+    <hyperlink ref="J110" r:id="rId61" xr:uid="{3A442435-8B15-4F8F-BC26-8AC758C00087}"/>
+    <hyperlink ref="J111" r:id="rId62" xr:uid="{C43FE886-751B-42AC-9206-75370B70790C}"/>
+    <hyperlink ref="J112" r:id="rId63" xr:uid="{70696DFF-9980-4CF8-BA59-8600BF5C64F7}"/>
+    <hyperlink ref="J113" r:id="rId64" xr:uid="{4E04EFDB-4A0F-4693-9A0B-1E0E64E816D2}"/>
+    <hyperlink ref="J114" r:id="rId65" xr:uid="{BF5A57D7-DFCC-42F0-8E1B-E7C52BB886FD}"/>
+    <hyperlink ref="J116" r:id="rId66" xr:uid="{FC75B432-7100-4996-B28A-5751C027CDA3}"/>
+    <hyperlink ref="J117" r:id="rId67" xr:uid="{9623E471-9A3E-44C5-BDE0-850375B6868C}"/>
+    <hyperlink ref="J118" r:id="rId68" xr:uid="{A1CE0879-E546-4425-86FD-7E6AE55795C6}"/>
+    <hyperlink ref="J119" r:id="rId69" xr:uid="{0513ACAB-862B-4004-88D5-5BA9E2A87BF6}"/>
+    <hyperlink ref="J120" r:id="rId70" xr:uid="{D12C1CAF-5F58-41B8-BDC4-3BDBBCD2AC8F}"/>
+    <hyperlink ref="J121" r:id="rId71" xr:uid="{374A81C1-06B6-4036-92D2-6748A7CEE1F1}"/>
+    <hyperlink ref="J124" r:id="rId72" xr:uid="{84DE143E-F124-4BD9-9A61-DFA99BE8ED0F}"/>
+    <hyperlink ref="J128" r:id="rId73" xr:uid="{6F0290EC-C6FA-4A81-ACB9-FD98E3D77DF7}"/>
+    <hyperlink ref="J129" r:id="rId74" xr:uid="{FE1CEC87-F6F0-4526-8C6A-6DF5E8F1DC98}"/>
+    <hyperlink ref="J132" r:id="rId75" xr:uid="{9CA06DF6-0CFD-4227-9D28-9C85207A3129}"/>
+    <hyperlink ref="J134" r:id="rId76" xr:uid="{D887642B-31AA-4D80-ACBC-247B6B894606}"/>
+    <hyperlink ref="J135" r:id="rId77" xr:uid="{9FD4204C-6F33-4EC8-820D-328B362D27DC}"/>
+    <hyperlink ref="J136" r:id="rId78" xr:uid="{F9B5D47C-E5C5-47C7-9A4C-FB5E1B321E76}"/>
+    <hyperlink ref="J140" r:id="rId79" xr:uid="{8D1E9762-FAC2-4D1E-A465-22ADFE95538F}"/>
+    <hyperlink ref="J142" r:id="rId80" xr:uid="{35E2512E-C97C-4D27-95E9-AE1D4A33111E}"/>
+    <hyperlink ref="J143" r:id="rId81" xr:uid="{ED979049-9F38-4A5C-B526-B2846BDE9049}"/>
+    <hyperlink ref="J144" r:id="rId82" xr:uid="{C4D360DB-4D0D-4D8B-8F37-4C3DC5BFD844}"/>
+    <hyperlink ref="J145" r:id="rId83" xr:uid="{944C9711-5008-491A-B555-9682CE4B29EF}"/>
+    <hyperlink ref="J147" r:id="rId84" xr:uid="{3E0FB90A-4134-467E-BDF2-4400E3A2D695}"/>
+    <hyperlink ref="J149" r:id="rId85" xr:uid="{CAB85DD7-151A-4E5E-AF49-FB19001F736B}"/>
+    <hyperlink ref="J150" r:id="rId86" xr:uid="{1C671DAA-44EE-4166-AF2F-55A1E5E298E1}"/>
+    <hyperlink ref="J151" r:id="rId87" xr:uid="{AFDE5692-8049-47A1-978D-28AF545F64FE}"/>
+    <hyperlink ref="J152" r:id="rId88" xr:uid="{89C45A8F-60DF-4557-BEC8-EF1FBE5283BB}"/>
+    <hyperlink ref="J153" r:id="rId89" xr:uid="{331E975B-14B5-4ABE-8ADF-DADC40508AE5}"/>
+    <hyperlink ref="J154" r:id="rId90" xr:uid="{64552B30-6DA2-409F-A530-B9D0B5A31EDA}"/>
+    <hyperlink ref="J155" r:id="rId91" xr:uid="{2B213786-74B1-4394-9D7D-3CFCAD9148EF}"/>
+    <hyperlink ref="J156" r:id="rId92" xr:uid="{A6D6BA9F-3571-4F57-BCE0-6F35D33488DC}"/>
+    <hyperlink ref="J159" r:id="rId93" xr:uid="{AB0D5307-95A4-456B-91DA-70002181DA3C}"/>
+    <hyperlink ref="J160" r:id="rId94" xr:uid="{B2112142-404B-4B38-879E-B301D4BB99EF}"/>
+    <hyperlink ref="J161" r:id="rId95" xr:uid="{D7208082-852C-4E53-81E0-FAE694556818}"/>
+    <hyperlink ref="J162" r:id="rId96" xr:uid="{E57D6392-8B4B-4F68-B20B-A802F435E6CE}"/>
+    <hyperlink ref="J164" r:id="rId97" xr:uid="{36A13C46-51D5-4009-A527-221C568FCAB5}"/>
+    <hyperlink ref="J165" r:id="rId98" xr:uid="{228BD2D0-4BA6-4D2D-8C20-4BB395148822}"/>
+    <hyperlink ref="J167" r:id="rId99" xr:uid="{32AEB8D2-4A09-41A8-9532-AB54F63DC793}"/>
+    <hyperlink ref="J168" r:id="rId100" xr:uid="{581A10C0-5ABE-4729-969C-F1FDEC222C04}"/>
+    <hyperlink ref="J169" r:id="rId101" xr:uid="{AC14907C-5F47-4682-A3CF-85C32FD50EAD}"/>
+    <hyperlink ref="J171" r:id="rId102" xr:uid="{43ACC3C5-AF97-4C55-8081-01519F5302B3}"/>
+    <hyperlink ref="J172" r:id="rId103" xr:uid="{4F012F66-D37B-434C-84B6-0CF3AC53E5F1}"/>
+    <hyperlink ref="J173" r:id="rId104" xr:uid="{81E63C35-645E-4777-9229-9F89623CBA07}"/>
+    <hyperlink ref="J177" r:id="rId105" xr:uid="{368CA51A-9244-4123-AE3C-4A2E0D4E7595}"/>
+    <hyperlink ref="J178" r:id="rId106" xr:uid="{34BEAFE1-84CA-40DC-8F72-36DA5C33AF8A}"/>
+    <hyperlink ref="J181" r:id="rId107" xr:uid="{385BB478-427C-4431-BD09-2B360B4FDB10}"/>
+    <hyperlink ref="J182" r:id="rId108" xr:uid="{140F9368-FB48-413B-ADF2-AB6B9967D771}"/>
+    <hyperlink ref="J184" r:id="rId109" xr:uid="{099A8A1E-563E-4DB5-BA11-AB701FD7903C}"/>
+    <hyperlink ref="J186" r:id="rId110" xr:uid="{28221375-DD99-4875-807E-67DDD5E78121}"/>
+    <hyperlink ref="J190" r:id="rId111" xr:uid="{01578EC1-6883-4389-A059-ACBFDEDC0E08}"/>
+    <hyperlink ref="J191" r:id="rId112" xr:uid="{6D0FD022-BFBF-4C16-969A-69BE49FD1B22}"/>
+    <hyperlink ref="J192" r:id="rId113" xr:uid="{D6631740-7DBC-4FDD-9BBB-14F5EF708640}"/>
+    <hyperlink ref="J193" r:id="rId114" xr:uid="{44F3B738-6A28-4CC8-9DA5-EDEF542DCA46}"/>
+    <hyperlink ref="J194" r:id="rId115" xr:uid="{A3F2E6AD-6B53-49F9-8570-B8C87FAD1D29}"/>
+    <hyperlink ref="J195" r:id="rId116" xr:uid="{F954FFF2-101D-4C3F-B6ED-9F0E43814A6C}"/>
+    <hyperlink ref="J196" r:id="rId117" xr:uid="{124E6F41-C92B-4BFF-A45E-2456CB7371A2}"/>
+    <hyperlink ref="J199" r:id="rId118" xr:uid="{1335CF50-121A-4858-A470-3F137125AFEF}"/>
+    <hyperlink ref="J201" r:id="rId119" xr:uid="{F66FCFE8-6D35-48F9-A8B1-4E5CE5391DA5}"/>
+    <hyperlink ref="J202" r:id="rId120" xr:uid="{5EE8A67E-3C22-468D-809D-3FFC1686C7C5}"/>
+    <hyperlink ref="J203" r:id="rId121" xr:uid="{B848BCB3-E549-47DA-ABBF-1CEBB6804CD1}"/>
+    <hyperlink ref="J205" r:id="rId122" xr:uid="{FA15ADBF-E7B8-446F-9822-DBC4482F4970}"/>
+    <hyperlink ref="J207" r:id="rId123" xr:uid="{79AD0A7C-5500-4774-8A78-39EE43561FC0}"/>
+    <hyperlink ref="J209" r:id="rId124" xr:uid="{EAC08C3C-F4E8-4FB1-B640-0BAC60C36775}"/>
+    <hyperlink ref="J210" r:id="rId125" xr:uid="{9272C580-743A-49F9-AF8B-AAD53D84CB0D}"/>
+    <hyperlink ref="J211" r:id="rId126" xr:uid="{ABA78A1D-326F-4285-97EB-D11EB35F8B58}"/>
+    <hyperlink ref="J212" r:id="rId127" xr:uid="{316B4E69-E893-4C84-901B-44CFE64D4C5C}"/>
+    <hyperlink ref="J213" r:id="rId128" xr:uid="{2AEF9373-BF63-47BC-82CD-5EF921FBE51C}"/>
+    <hyperlink ref="J214" r:id="rId129" xr:uid="{2C264E77-514B-4FA2-9D4A-762AB8B9A7AE}"/>
+    <hyperlink ref="J215" r:id="rId130" xr:uid="{A892216E-7FFC-49BA-8C63-9A4C93C330D2}"/>
+    <hyperlink ref="J217" r:id="rId131" xr:uid="{90EC40E5-A175-4FED-84E4-9C1A431F9611}"/>
+    <hyperlink ref="J219" r:id="rId132" xr:uid="{AA26422E-8B29-4E7C-AD5A-B104166F099F}"/>
+    <hyperlink ref="J220" r:id="rId133" xr:uid="{E4F9623A-2D60-45DF-98E3-9494608CA1DC}"/>
+    <hyperlink ref="J221" r:id="rId134" xr:uid="{A174621B-28C4-47B0-9A2A-60FEC2420BFE}"/>
+    <hyperlink ref="J222" r:id="rId135" xr:uid="{DCAB3D9A-1935-49E1-95C2-A918762417A5}"/>
+    <hyperlink ref="J223" r:id="rId136" xr:uid="{1DEC7B95-4025-4B42-A906-167029260BD0}"/>
+    <hyperlink ref="J225" r:id="rId137" xr:uid="{816BD3AE-4B13-4923-9F1D-0EA69090DD3E}"/>
+    <hyperlink ref="J228" r:id="rId138" xr:uid="{E056696D-04B2-4217-9252-0FDC18181D13}"/>
+    <hyperlink ref="J230" r:id="rId139" xr:uid="{86504072-5AD7-4087-A47A-C26178B3767B}"/>
+    <hyperlink ref="J234" r:id="rId140" xr:uid="{7F022F96-CBBE-4A07-9842-53C3D938B7C7}"/>
+    <hyperlink ref="J236" r:id="rId141" xr:uid="{80FEA3FB-313E-4C03-AD71-FF7D95A54218}"/>
+    <hyperlink ref="J237" r:id="rId142" xr:uid="{36AA3705-9A10-4F85-B103-61AD9AB4EA44}"/>
+    <hyperlink ref="J238" r:id="rId143" xr:uid="{DA814CC5-0E3C-41AA-80F1-E86C0EF7F63D}"/>
+    <hyperlink ref="J240" r:id="rId144" xr:uid="{8D51E90E-478C-4319-8655-C08B5AF9BC6D}"/>
+    <hyperlink ref="J241" r:id="rId145" xr:uid="{20F06C66-5B0B-4A28-8E15-8C4FB4A6DFC9}"/>
+    <hyperlink ref="J242" r:id="rId146" xr:uid="{9316BC14-0019-4CDD-8FAD-8565C0957CC2}"/>
+    <hyperlink ref="J243" r:id="rId147" xr:uid="{B7685F60-29EC-49B5-986D-F7CF86EB6698}"/>
+    <hyperlink ref="J246" r:id="rId148" xr:uid="{71D53843-62F9-4329-B2FD-80300E5C63CD}"/>
+    <hyperlink ref="J247" r:id="rId149" xr:uid="{7915E27F-7E60-4366-A213-D3C572A7081D}"/>
+    <hyperlink ref="J250" r:id="rId150" xr:uid="{B61C883B-CA32-4ABC-9E60-41CE9D94E9EA}"/>
+    <hyperlink ref="J252" r:id="rId151" xr:uid="{E19A5E9D-BA4E-443C-8315-25F25634E698}"/>
+    <hyperlink ref="J254" r:id="rId152" xr:uid="{87204161-E987-486A-9DE7-D0DFC3D93A53}"/>
+    <hyperlink ref="J255" r:id="rId153" xr:uid="{FD2DA467-4855-4212-BA1A-E7BB2B12FD68}"/>
+    <hyperlink ref="J256" r:id="rId154" xr:uid="{CEA4B2C9-B34C-4FEB-B701-FE9C7365917B}"/>
+    <hyperlink ref="J258" r:id="rId155" xr:uid="{F5147F9C-FC59-44D8-8494-2470BF6ED574}"/>
+    <hyperlink ref="J259" r:id="rId156" xr:uid="{9C84C4A6-CFB6-4538-AE62-BD3CB75573D8}"/>
+    <hyperlink ref="J261" r:id="rId157" xr:uid="{082E11EF-0B3B-492E-8EAB-112A2863132D}"/>
+    <hyperlink ref="J263" r:id="rId158" xr:uid="{FC5DC844-0353-4581-B373-C012A88D0D3D}"/>
+    <hyperlink ref="J265" r:id="rId159" xr:uid="{AE5C53CD-69AB-4F87-827A-1EB92B2E50B0}"/>
+    <hyperlink ref="J266" r:id="rId160" xr:uid="{3C4BD2E4-84BD-4529-87AD-A8F86722107E}"/>
+    <hyperlink ref="J267" r:id="rId161" xr:uid="{5263C906-987F-436C-BDFB-7B92A10E989B}"/>
+    <hyperlink ref="J270" r:id="rId162" xr:uid="{7260D772-CC40-40F0-B122-1E06E20D9D97}"/>
+    <hyperlink ref="J271" r:id="rId163" xr:uid="{B3092D1F-8A63-4E40-A2AC-464F5CC0B273}"/>
+    <hyperlink ref="J273" r:id="rId164" xr:uid="{48D7B717-9975-4893-A51C-62F8C2BD1293}"/>
+    <hyperlink ref="J274" r:id="rId165" xr:uid="{0D49D29A-C2F4-40DD-9821-E6F0A97CD045}"/>
+    <hyperlink ref="J275" r:id="rId166" xr:uid="{7EC9E489-30CD-4CA0-8BBD-E21CE42109A3}"/>
+    <hyperlink ref="J277" r:id="rId167" xr:uid="{5C18E539-F2C9-409F-9AC3-56FF7F65B83B}"/>
+    <hyperlink ref="J278" r:id="rId168" xr:uid="{B8577FEB-F0AA-4A7C-A1AF-81050964B983}"/>
+    <hyperlink ref="J279" r:id="rId169" xr:uid="{530B103A-BD71-4764-8958-1499132ED0ED}"/>
+    <hyperlink ref="J280" r:id="rId170" xr:uid="{F7D7F375-12B6-4802-9F33-B83290928212}"/>
+    <hyperlink ref="J281" r:id="rId171" xr:uid="{F784AAF1-89F4-496C-B508-1A52E0BFD793}"/>
+    <hyperlink ref="J282" r:id="rId172" xr:uid="{1CEB7EFD-4153-4A81-90D5-5C8A454EFC69}"/>
+    <hyperlink ref="J283" r:id="rId173" xr:uid="{C0272EFE-829F-427E-BFA9-E2D0E5DC61FA}"/>
+    <hyperlink ref="J286" r:id="rId174" xr:uid="{A67254E3-C1DB-4FBD-A51D-50DA708E2BDB}"/>
+    <hyperlink ref="J287" r:id="rId175" xr:uid="{30214C28-BB24-4943-8D21-4411753A8D2C}"/>
+    <hyperlink ref="J290" r:id="rId176" xr:uid="{94A210AC-9A85-423C-90B6-51C50D1552EE}"/>
+    <hyperlink ref="J292" r:id="rId177" xr:uid="{6A573769-48DD-40A0-8BA3-854E7681AEDC}"/>
+    <hyperlink ref="J294" r:id="rId178" xr:uid="{79C9CF5B-30E9-4367-8400-433C9725DF64}"/>
+    <hyperlink ref="J296" r:id="rId179" xr:uid="{EEE2F8FD-678F-420E-BF97-5B8E92CE50F0}"/>
+    <hyperlink ref="J297" r:id="rId180" xr:uid="{234C1250-A194-41EE-BC4A-D75D40319DD4}"/>
+    <hyperlink ref="J298" r:id="rId181" xr:uid="{1551C214-F8AF-46B7-AF3A-92DCE051E20E}"/>
+    <hyperlink ref="J299" r:id="rId182" xr:uid="{7E375803-048B-4748-A54F-FEE4A516D3A6}"/>
+    <hyperlink ref="J300" r:id="rId183" xr:uid="{302CE030-BF80-4EB4-9E40-81D3088EBB9B}"/>
+    <hyperlink ref="J301" r:id="rId184" xr:uid="{1358906E-52B5-4000-9041-20505EE4564E}"/>
+    <hyperlink ref="J303" r:id="rId185" xr:uid="{FC998DB0-EAF6-4B3D-B3BA-457BC1E372BD}"/>
+    <hyperlink ref="J305" r:id="rId186" xr:uid="{2F6AF5AD-40F8-4871-9F71-76BB4F9917DC}"/>
+    <hyperlink ref="J306" r:id="rId187" xr:uid="{18C643B3-3343-430F-B574-739596C0E219}"/>
+    <hyperlink ref="J308" r:id="rId188" xr:uid="{C8418A3A-DD8F-4C1C-8535-73C082D180C4}"/>
+    <hyperlink ref="J309" r:id="rId189" xr:uid="{B9B41940-946C-4DA5-88F6-C17CE87B8677}"/>
+    <hyperlink ref="J311" r:id="rId190" xr:uid="{6B791876-BC9D-4754-997C-49DD51F23FB7}"/>
+    <hyperlink ref="J312" r:id="rId191" xr:uid="{1407B4CA-1F6C-41D7-9FE6-FBAA6506F56A}"/>
+    <hyperlink ref="J314" r:id="rId192" xr:uid="{01C9216A-66BD-440F-82F4-E9DE63C4FD46}"/>
+    <hyperlink ref="J317" r:id="rId193" xr:uid="{EC14D0B1-8B71-40BA-B287-E5F7DB4B314C}"/>
+    <hyperlink ref="J318" r:id="rId194" xr:uid="{3CC7E703-5AD3-47FF-8CD1-DB8DD9155C4B}"/>
+    <hyperlink ref="J321" r:id="rId195" xr:uid="{951F2EC7-BC6C-42EA-B22A-29E23328926D}"/>
+    <hyperlink ref="J322" r:id="rId196" xr:uid="{B83DDAAA-1A4A-4979-87D2-8EB6B155F72F}"/>
+    <hyperlink ref="J325" r:id="rId197" xr:uid="{000B5323-CE55-4332-AEE8-B841092CA7C1}"/>
+    <hyperlink ref="J326" r:id="rId198" xr:uid="{A02D9943-B826-4B85-9FBB-B05246A8FF31}"/>
+    <hyperlink ref="J329" r:id="rId199" xr:uid="{C89F1598-5F61-4A74-BAE8-F26E745DB448}"/>
+    <hyperlink ref="J330" r:id="rId200" xr:uid="{8807EC8B-95AF-443C-8464-9DE68660B391}"/>
+    <hyperlink ref="J331" r:id="rId201" xr:uid="{5A41CB88-59B3-42B9-A9BF-493EE5BA6296}"/>
+    <hyperlink ref="J333" r:id="rId202" xr:uid="{81262684-0736-49D2-8C3A-F59F48CC488E}"/>
+    <hyperlink ref="J334" r:id="rId203" xr:uid="{1E19E608-43D1-4A29-8AAC-2A7BD7E4DE82}"/>
+    <hyperlink ref="J335" r:id="rId204" xr:uid="{6AD4A4D0-F6D3-4703-AB73-ECB752997119}"/>
+    <hyperlink ref="J336" r:id="rId205" xr:uid="{5A0F8032-F554-4686-860D-AF9E640B6681}"/>
+    <hyperlink ref="J338" r:id="rId206" xr:uid="{00B258C1-A0C9-43A0-A368-D9A8651B8141}"/>
+    <hyperlink ref="J340" r:id="rId207" xr:uid="{E0B8FA3F-98FC-417F-9531-02FBB8981961}"/>
+    <hyperlink ref="J342" r:id="rId208" xr:uid="{5CC92266-1C90-44F6-B799-6571D5F9A591}"/>
+    <hyperlink ref="J343" r:id="rId209" xr:uid="{15CE61FF-14D8-4E90-8A30-0C7C85A6E823}"/>
+    <hyperlink ref="J344" r:id="rId210" xr:uid="{EEE65FC3-D95B-4169-B33F-6F7F954BD5DE}"/>
+    <hyperlink ref="J346" r:id="rId211" xr:uid="{C383415E-1B92-47FF-B8CE-E9CC9A7411A1}"/>
+    <hyperlink ref="J349" r:id="rId212" xr:uid="{CA7C0473-79E6-4959-A069-AC1BB8657BFF}"/>
+    <hyperlink ref="J350" r:id="rId213" xr:uid="{EB2A7CFB-42D4-452A-9115-88223EEB164A}"/>
+    <hyperlink ref="J352" r:id="rId214" xr:uid="{1297BE59-82E2-4301-BC5C-EB01A84B5791}"/>
+    <hyperlink ref="J354" r:id="rId215" xr:uid="{ED22DD9E-45B9-4565-8E18-17B09145F91A}"/>
+    <hyperlink ref="J355" r:id="rId216" xr:uid="{4B159317-0094-4441-9A40-A19F15DD294F}"/>
+    <hyperlink ref="J356" r:id="rId217" xr:uid="{EB94FCEA-1638-445D-A095-676256AA905F}"/>
+    <hyperlink ref="J357" r:id="rId218" xr:uid="{F1EF7DC0-4250-41D7-8DF8-6D0B5F6D7C42}"/>
+    <hyperlink ref="J358" r:id="rId219" xr:uid="{7622FBA0-9AD7-45E0-BC17-2BF043AE9300}"/>
+    <hyperlink ref="J360" r:id="rId220" xr:uid="{518BBC8E-1EE0-435D-A20C-CB02E204515A}"/>
+    <hyperlink ref="J363" r:id="rId221" xr:uid="{BFD9730A-54C2-45F9-9A20-8DDE760775DB}"/>
+    <hyperlink ref="J364" r:id="rId222" xr:uid="{0C88A383-5C2B-41CA-9B56-A5F0D2020AE9}"/>
+    <hyperlink ref="J366" r:id="rId223" xr:uid="{13CAFEA4-3597-4674-84C4-2893D7CD3225}"/>
+    <hyperlink ref="J368" r:id="rId224" xr:uid="{6F2ADB7B-50FA-40B9-8E6F-DF50BCA389B9}"/>
+    <hyperlink ref="J370" r:id="rId225" xr:uid="{6AD87E53-EBAB-4AA5-8FA0-5C030614DFEF}"/>
+    <hyperlink ref="J371" r:id="rId226" xr:uid="{1AC3AAB2-3915-4394-AE36-56BA181CC1D1}"/>
+    <hyperlink ref="J372" r:id="rId227" xr:uid="{C6C957FC-639D-42EC-9062-6AAF76DCB720}"/>
+    <hyperlink ref="J373" r:id="rId228" xr:uid="{60B914B5-ED96-41D0-8466-0911666F5BF4}"/>
+    <hyperlink ref="J374" r:id="rId229" xr:uid="{5E375412-E511-49A3-BFAA-D37E267BC2F1}"/>
+    <hyperlink ref="J375" r:id="rId230" xr:uid="{F0454566-B9CF-4F99-B03F-A04D0F60F33A}"/>
+    <hyperlink ref="J376" r:id="rId231" xr:uid="{25BFE809-CAD8-44D6-8441-C77BABEA90F0}"/>
+    <hyperlink ref="J377" r:id="rId232" xr:uid="{17F70B48-54D1-4437-9D27-0E2D103BE1A3}"/>
+    <hyperlink ref="J378" r:id="rId233" xr:uid="{B1274EBA-8DD4-41D2-AB6C-5F475CC49030}"/>
+    <hyperlink ref="J379" r:id="rId234" xr:uid="{261F35BE-D318-4F56-8398-6EEA02CD0F66}"/>
+    <hyperlink ref="J381" r:id="rId235" xr:uid="{7B1FA688-2327-42E6-BB70-1B8371FE14A1}"/>
+    <hyperlink ref="J383" r:id="rId236" xr:uid="{056C10FF-BF9F-4ED9-A0F0-55A4350C0393}"/>
+    <hyperlink ref="J384" r:id="rId237" xr:uid="{CCD5BB44-7A7E-4E34-8F46-1945541E5357}"/>
+    <hyperlink ref="J386" r:id="rId238" xr:uid="{648A013C-08CA-4125-B62A-0CAB2CC0AEAE}"/>
+    <hyperlink ref="J387" r:id="rId239" xr:uid="{A2B95A30-434F-4804-B5D6-2F7AFED9B36B}"/>
+    <hyperlink ref="J388" r:id="rId240" xr:uid="{8ED62BA3-FC3C-46F6-BBED-6F832FF049BD}"/>
+    <hyperlink ref="J390" r:id="rId241" xr:uid="{7708C2B3-4C42-4766-A87F-45C11443E2A0}"/>
+    <hyperlink ref="J391" r:id="rId242" xr:uid="{45D09BCC-A57B-4829-B5CD-C61C93F17989}"/>
+    <hyperlink ref="J394" r:id="rId243" xr:uid="{F7623BB7-49E4-489B-9E3F-D0C3B62DEEF4}"/>
+    <hyperlink ref="J395" r:id="rId244" xr:uid="{83C948C5-0D23-4866-902A-D227ED0E3E05}"/>
+    <hyperlink ref="J396" r:id="rId245" xr:uid="{C1D6B658-EB9B-491B-BC53-2DE20369CE7A}"/>
+    <hyperlink ref="J397" r:id="rId246" xr:uid="{5920549A-4BD3-4B8B-A3C3-C7B2119F3C77}"/>
+    <hyperlink ref="J398" r:id="rId247" xr:uid="{76E0F729-4E7F-4CEA-9C65-3A86CA444257}"/>
+    <hyperlink ref="J399" r:id="rId248" xr:uid="{45E35B8B-B8EA-434E-B6B8-DC14153168A2}"/>
+    <hyperlink ref="J400" r:id="rId249" xr:uid="{C508AD18-2F64-4930-AA29-C8A812D40CB4}"/>
+    <hyperlink ref="J403" r:id="rId250" xr:uid="{1C21B093-93AF-4A22-80BB-C4242596776C}"/>
+    <hyperlink ref="J404" r:id="rId251" xr:uid="{42F5B1D3-24BE-4404-8E6A-87D15EC29C5A}"/>
+    <hyperlink ref="J405" r:id="rId252" xr:uid="{53F34CD1-9570-486C-99D7-78453C6A9819}"/>
+    <hyperlink ref="J406" r:id="rId253" xr:uid="{2C012E94-5414-4A7E-A7AB-CF7A1FC72B93}"/>
+    <hyperlink ref="J408" r:id="rId254" xr:uid="{483C577F-C6BC-415E-ADCE-F0B2B27C3464}"/>
+    <hyperlink ref="J409" r:id="rId255" xr:uid="{5F4FD2AF-2CBB-4857-B6B0-EFF04FC42E4F}"/>
+    <hyperlink ref="J411" r:id="rId256" xr:uid="{00CD48F4-E862-493F-8ED8-E57701896D72}"/>
+    <hyperlink ref="J413" r:id="rId257" xr:uid="{7C0B55F3-9019-4908-924D-BB18633C45E7}"/>
+    <hyperlink ref="J415" r:id="rId258" xr:uid="{9CD168F3-8DEE-4630-AC15-AC9E45D088C2}"/>
+    <hyperlink ref="J416" r:id="rId259" xr:uid="{821DEC4F-7581-4C63-9E6A-A49C6E4327DA}"/>
+    <hyperlink ref="J418" r:id="rId260" xr:uid="{DB9D73A5-716A-4F92-8D92-B754363E73F0}"/>
+    <hyperlink ref="J421" r:id="rId261" xr:uid="{98B3A997-A2E9-4AC2-9A46-4796F5FFA178}"/>
+    <hyperlink ref="J422" r:id="rId262" xr:uid="{70C092EF-B41B-4986-8F0E-6D2ADEC64116}"/>
+    <hyperlink ref="J430" r:id="rId263" xr:uid="{090ED92E-2835-4BEA-A1B3-48125773EB03}"/>
+    <hyperlink ref="J431" r:id="rId264" xr:uid="{E8FD57E4-914B-4314-9450-BDC327459908}"/>
+    <hyperlink ref="J432" r:id="rId265" xr:uid="{F6C03C87-95AC-4463-BACB-EDDCF59FD48E}"/>
+    <hyperlink ref="J433" r:id="rId266" xr:uid="{A0F83C69-6768-46BC-BB2B-F2772B621029}"/>
+    <hyperlink ref="J434" r:id="rId267" xr:uid="{C443897B-1D94-40F4-8DED-351575D45761}"/>
+    <hyperlink ref="J435" r:id="rId268" xr:uid="{5278EF76-DA4C-40DF-A945-99AEE7411599}"/>
+    <hyperlink ref="J436" r:id="rId269" xr:uid="{70DBB4AC-5D3A-4327-9206-BC1D7C89A6A8}"/>
+    <hyperlink ref="J437" r:id="rId270" xr:uid="{1C04AFEE-D46A-42DA-8A5A-021821947159}"/>
+    <hyperlink ref="J438" r:id="rId271" xr:uid="{3356A64F-3C51-4AAC-9868-AE56740D312C}"/>
+    <hyperlink ref="J439" r:id="rId272" xr:uid="{5227CDA5-BFD1-48F0-AC4A-17C6BE4E5E1F}"/>
+    <hyperlink ref="J445" r:id="rId273" xr:uid="{BD9430E7-F713-4B13-815E-CD30BA64CB53}"/>
+    <hyperlink ref="J447" r:id="rId274" xr:uid="{76CFBB07-64A2-461A-BF72-92316F1E5327}"/>
+    <hyperlink ref="J449" r:id="rId275" xr:uid="{727C4B42-3270-43A9-85BB-7BD28CC4C99F}"/>
+    <hyperlink ref="J450" r:id="rId276" xr:uid="{3B7CACB7-5A4F-4225-8E84-8FA3BF50F377}"/>
+    <hyperlink ref="J451" r:id="rId277" xr:uid="{2A6CCA10-62B1-4AB7-B46C-E020F27D4D98}"/>
+    <hyperlink ref="J452" r:id="rId278" xr:uid="{0243F074-B6E4-4DF3-A133-40F584A2187E}"/>
+    <hyperlink ref="J453" r:id="rId279" xr:uid="{49423B1E-F37C-427E-AA51-99B8A18A5D1C}"/>
+    <hyperlink ref="J454" r:id="rId280" xr:uid="{3CBE627C-1002-48A1-B0A1-E77BD637D5EE}"/>
+    <hyperlink ref="J455" r:id="rId281" xr:uid="{2789932B-8117-4411-B92E-4091EF7948C2}"/>
+    <hyperlink ref="J458" r:id="rId282" xr:uid="{269EDF68-C187-431B-A238-079AD2E813CB}"/>
+    <hyperlink ref="J460" r:id="rId283" xr:uid="{CB3AE283-190E-49B4-B9DB-C114996533C4}"/>
+    <hyperlink ref="J461" r:id="rId284" xr:uid="{C76B3727-4FE8-4554-B2DA-0609AE79267C}"/>
+    <hyperlink ref="J462" r:id="rId285" xr:uid="{3D17055D-B088-45D4-B43E-A5B9DB8288E8}"/>
+    <hyperlink ref="J465" r:id="rId286" xr:uid="{8AB93B36-0151-4560-9B19-02A7252E0BE5}"/>
+    <hyperlink ref="J469" r:id="rId287" xr:uid="{237BBD22-E1CE-4F6D-A189-DE8371B8F053}"/>
+    <hyperlink ref="J473" r:id="rId288" xr:uid="{DDAA3B38-408D-4EDA-9D9C-B912EF70B064}"/>
+    <hyperlink ref="J476" r:id="rId289" xr:uid="{77DD0003-FF94-494B-9567-796D6CFDCE0D}"/>
+    <hyperlink ref="J478" r:id="rId290" xr:uid="{23CAC974-8D43-415F-97D1-6165CC3BD29B}"/>
+    <hyperlink ref="J479" r:id="rId291" xr:uid="{7570C959-E123-43EC-BC61-575D3BF3A244}"/>
+    <hyperlink ref="J480" r:id="rId292" xr:uid="{17035B9D-3FBE-4DA0-9E95-D1EF5B3F31B0}"/>
+    <hyperlink ref="J481" r:id="rId293" xr:uid="{70270191-D02F-40FB-A231-D5DB2212DC45}"/>
+    <hyperlink ref="J482" r:id="rId294" xr:uid="{A7F734E2-2A41-4BAD-BE13-66E752AD518F}"/>
+    <hyperlink ref="J484" r:id="rId295" xr:uid="{1B22DF2D-7A20-4716-924A-4C1D98DD31DC}"/>
+    <hyperlink ref="J485" r:id="rId296" xr:uid="{F21B51B6-B6D0-49E3-8B42-D87C766FDED3}"/>
+    <hyperlink ref="J488" r:id="rId297" xr:uid="{98F9624A-DF55-4935-9165-EEE0F3EBBCBA}"/>
+    <hyperlink ref="J489" r:id="rId298" xr:uid="{EA18D81E-B4CF-4A54-8C67-9089F0CAC0D1}"/>
+    <hyperlink ref="J490" r:id="rId299" xr:uid="{D461B437-A18A-4DAD-9551-74C8773918DB}"/>
+    <hyperlink ref="J491" r:id="rId300" xr:uid="{15C63B62-9022-4332-8245-D359D2D40550}"/>
+    <hyperlink ref="J494" r:id="rId301" xr:uid="{61CAD911-9B43-468E-9925-6AA920C32F62}"/>
+    <hyperlink ref="J496" r:id="rId302" xr:uid="{33476F99-D402-4104-AB81-27295C423A1F}"/>
+    <hyperlink ref="J497" r:id="rId303" xr:uid="{932D1CDE-84E0-4A26-8F2F-0E91F63CA73E}"/>
+    <hyperlink ref="J498" r:id="rId304" xr:uid="{2AFBC1FE-501F-46FA-A0AA-C20A3260AD07}"/>
+    <hyperlink ref="J499" r:id="rId305" xr:uid="{B41E4493-71A2-483F-86DB-569134E68040}"/>
+    <hyperlink ref="J500" r:id="rId306" xr:uid="{EAB7B4D9-0788-4729-813E-570B49557BED}"/>
+    <hyperlink ref="J501" r:id="rId307" xr:uid="{74088C24-A1F3-43A1-8DA4-0E25C8A41288}"/>
+    <hyperlink ref="J503" r:id="rId308" xr:uid="{34D6DD01-99EB-4ED3-9C15-C4BDAC4B4825}"/>
+    <hyperlink ref="J504" r:id="rId309" xr:uid="{B52803B5-A117-4138-B84C-C1C58B263A57}"/>
+    <hyperlink ref="J508" r:id="rId310" xr:uid="{58533B5C-EA3B-4134-9866-21F274305C31}"/>
+    <hyperlink ref="J509" r:id="rId311" xr:uid="{C4576BD7-4F29-4FBF-89A6-D011EC58C4E1}"/>
+    <hyperlink ref="J510" r:id="rId312" xr:uid="{DDAE2724-AA7C-4375-A01D-12773E8436DF}"/>
+    <hyperlink ref="J511" r:id="rId313" xr:uid="{E3BE3F53-B40E-4556-BE94-53E6969524DE}"/>
+    <hyperlink ref="J513" r:id="rId314" xr:uid="{43BF54F8-CB26-42E7-ABC7-4F53A4B59410}"/>
+    <hyperlink ref="J515" r:id="rId315" xr:uid="{E5234EA3-EC79-4B70-AF3B-D61A3C61412D}"/>
+    <hyperlink ref="J516" r:id="rId316" xr:uid="{684E7898-5590-4B44-85D7-4F287A4CC772}"/>
+    <hyperlink ref="J519" r:id="rId317" xr:uid="{0580AB05-DB8F-495B-AC24-B63B29E26482}"/>
+    <hyperlink ref="J523" r:id="rId318" xr:uid="{A42E85B1-AFF8-4712-931F-B0D072BA9DB2}"/>
+    <hyperlink ref="J524" r:id="rId319" xr:uid="{1CD64D89-DCAF-4069-B385-0D344338CAB5}"/>
+    <hyperlink ref="J525" r:id="rId320" xr:uid="{F71E6053-C0EF-4A1A-9FC6-7238B0CFE769}"/>
+    <hyperlink ref="J535" r:id="rId321" xr:uid="{91F7EE41-263B-475E-BC16-F8A896250C49}"/>
+    <hyperlink ref="J536" r:id="rId322" xr:uid="{0C844E14-77A3-4C29-BDD4-FDED1F1BACE4}"/>
+    <hyperlink ref="J537" r:id="rId323" xr:uid="{D147FD03-0467-48EC-B9A5-BFC420B43E1A}"/>
+    <hyperlink ref="J538" r:id="rId324" xr:uid="{4B009AE1-5E8B-4A42-A47F-8CD4621769CB}"/>
+    <hyperlink ref="J539" r:id="rId325" xr:uid="{9776F0B2-F422-49F2-AAC5-22FAAB8AF01E}"/>
+    <hyperlink ref="J540" r:id="rId326" xr:uid="{D55EBB9E-DD1E-4FCC-B495-F1817590C42D}"/>
+    <hyperlink ref="J541" r:id="rId327" xr:uid="{2C3F9FFF-D7BD-49FF-BEBD-8145E6F097D7}"/>
+    <hyperlink ref="J543" r:id="rId328" xr:uid="{934E0D73-E949-4FE9-9698-10A6C859C155}"/>
+    <hyperlink ref="J544" r:id="rId329" xr:uid="{577CF2CD-4102-4EE8-A055-04703F5CC595}"/>
+    <hyperlink ref="J546" r:id="rId330" xr:uid="{B9C7A5D5-1DE6-4916-B5EC-CF2A9AFA65E9}"/>
+    <hyperlink ref="J547" r:id="rId331" xr:uid="{DF32DFDB-EF54-4B63-BDB4-B6AE007EE8A4}"/>
+    <hyperlink ref="J548" r:id="rId332" xr:uid="{5758D91F-09AA-42D3-B9B2-C8862989B3CE}"/>
+    <hyperlink ref="J549" r:id="rId333" xr:uid="{EABC8887-661B-44F8-B67E-6F23ECA40102}"/>
+    <hyperlink ref="J550" r:id="rId334" xr:uid="{C921BFA1-501F-4ADF-A26F-64C462D3EF9D}"/>
+    <hyperlink ref="J551" r:id="rId335" xr:uid="{CEC411E7-6DA0-4848-B31A-A6D2FB92FBDB}"/>
+    <hyperlink ref="J552" r:id="rId336" xr:uid="{2F8B9797-B71E-43B2-99B7-92A0D8F7E568}"/>
+    <hyperlink ref="J555" r:id="rId337" xr:uid="{FE5165B4-82AC-4BA3-95CC-F1FD50CE6A34}"/>
+    <hyperlink ref="J556" r:id="rId338" xr:uid="{B6F754A1-3287-4D3F-8BEB-1BF393759413}"/>
+    <hyperlink ref="J558" r:id="rId339" xr:uid="{A6B16A80-516A-415E-8BB7-EE19E0A94580}"/>
+    <hyperlink ref="J559" r:id="rId340" xr:uid="{5B82BE94-05C7-474E-A118-FAEDE3440999}"/>
+    <hyperlink ref="J560" r:id="rId341" xr:uid="{85E693C5-44DE-4A24-AC0E-B6DF37A581A2}"/>
+    <hyperlink ref="J562" r:id="rId342" xr:uid="{E72E61AE-AB39-4015-9297-73A82FE71554}"/>
+    <hyperlink ref="J569" r:id="rId343" xr:uid="{9EC598F9-04D9-485C-8BAC-C6EE4466A1B2}"/>
+    <hyperlink ref="J570" r:id="rId344" xr:uid="{44904DD9-2E12-425B-8F52-1EABDDB69D1F}"/>
+    <hyperlink ref="J571" r:id="rId345" xr:uid="{CC69C16A-B305-439F-8271-E89CAE523202}"/>
+    <hyperlink ref="J572" r:id="rId346" xr:uid="{BBBBFCCD-7C19-4E08-BC92-65E12FF48D44}"/>
+    <hyperlink ref="J573" r:id="rId347" xr:uid="{14EA7333-8848-4408-81FF-48587DD50501}"/>
+    <hyperlink ref="J574" r:id="rId348" xr:uid="{564A314F-2C61-40E6-8B24-D3F66A463333}"/>
+    <hyperlink ref="J575" r:id="rId349" xr:uid="{38E30552-1F17-422D-9258-CAC12D4D9F9E}"/>
+    <hyperlink ref="J576" r:id="rId350" xr:uid="{95EB69B1-E97E-4759-B058-4425684272BB}"/>
+    <hyperlink ref="J577" r:id="rId351" xr:uid="{AFCCF780-CCBB-4269-B1C0-74BB88383C2E}"/>
+    <hyperlink ref="J578" r:id="rId352" xr:uid="{BD525F32-3047-496F-94CD-722663BA92BC}"/>
+    <hyperlink ref="J579" r:id="rId353" xr:uid="{65845721-BF4F-4599-8E1A-B5B6E1EDD016}"/>
+    <hyperlink ref="J580" r:id="rId354" xr:uid="{6C00ADF2-F7C4-4AFF-9419-2668035AAF9C}"/>
+    <hyperlink ref="J581" r:id="rId355" xr:uid="{76B52258-FE91-495D-995B-A4DD1D67055F}"/>
+    <hyperlink ref="J582" r:id="rId356" xr:uid="{34370859-3DD5-4822-8FB1-A5A181B68DC7}"/>
+    <hyperlink ref="J584" r:id="rId357" xr:uid="{0C63ED35-78DF-4B19-A5A9-CCE81B513D49}"/>
+    <hyperlink ref="J585" r:id="rId358" xr:uid="{FF8829E8-22A0-400A-BD0F-D16C897BFA79}"/>
+    <hyperlink ref="J586" r:id="rId359" xr:uid="{448051EC-48D2-489E-8849-D33F96B82099}"/>
+    <hyperlink ref="J587" r:id="rId360" xr:uid="{0B99188E-127D-43C5-A790-00B9DD02D08F}"/>
+    <hyperlink ref="J592" r:id="rId361" xr:uid="{AF960DAE-5245-495C-A6B9-A0A3CCC835FE}"/>
+    <hyperlink ref="J593" r:id="rId362" xr:uid="{22633C03-73E0-4227-9804-F50FDB3E0A65}"/>
+    <hyperlink ref="J595" r:id="rId363" xr:uid="{1E50EE9D-8B44-4DB8-97AF-0CAD12C61347}"/>
+    <hyperlink ref="J596" r:id="rId364" xr:uid="{14CBC8C7-EB75-4D74-B484-19F6291351B9}"/>
+    <hyperlink ref="J598" r:id="rId365" xr:uid="{6C9FE14F-E140-4B0A-87F6-F899A534759E}"/>
+    <hyperlink ref="J599" r:id="rId366" xr:uid="{6E121DE7-7D60-4DD9-852D-E31BE5ED9D13}"/>
+    <hyperlink ref="J602" r:id="rId367" xr:uid="{A7960B06-026F-4336-802B-05A0004F292E}"/>
+    <hyperlink ref="J603" r:id="rId368" xr:uid="{80353E95-2604-4A90-BC4A-D5684E206402}"/>
+    <hyperlink ref="J604" r:id="rId369" xr:uid="{DD0A6304-F04F-4E9C-B26E-A451EA68A992}"/>
+    <hyperlink ref="J605" r:id="rId370" xr:uid="{00A35B81-624B-4660-A524-F377897B1625}"/>
+    <hyperlink ref="J606" r:id="rId371" xr:uid="{1B9FE899-7F2C-4662-8870-7B798B9DE13F}"/>
+    <hyperlink ref="J608" r:id="rId372" xr:uid="{4A90D73E-7155-4717-864E-9DE8D7CAD972}"/>
+    <hyperlink ref="J609" r:id="rId373" xr:uid="{E6EED710-552C-4EB9-9AEE-FB254985C68F}"/>
+    <hyperlink ref="J611" r:id="rId374" xr:uid="{D7A9F7C7-1330-47E4-9ACE-C59F45292837}"/>
+    <hyperlink ref="J612" r:id="rId375" xr:uid="{937EB21A-65B4-4A24-ACCC-48CDE81FCF4B}"/>
+    <hyperlink ref="J613" r:id="rId376" xr:uid="{AA84E7F4-0F7D-4D8D-9D49-CFA20F975EC9}"/>
+    <hyperlink ref="J615" r:id="rId377" xr:uid="{24C7D167-4DFA-48AA-82DB-4050906C99FA}"/>
+    <hyperlink ref="J617" r:id="rId378" xr:uid="{AE80EF9F-3726-4D29-BA88-01811CF84FE2}"/>
+    <hyperlink ref="J618" r:id="rId379" xr:uid="{4580E0A3-ED62-431B-9754-849F64174760}"/>
+    <hyperlink ref="J619" r:id="rId380" xr:uid="{3A0A27E4-432A-4589-9246-940FE21BF15E}"/>
+    <hyperlink ref="J622" r:id="rId381" xr:uid="{E3057289-FFE9-40E2-A450-DB643CF27B06}"/>
+    <hyperlink ref="J623" r:id="rId382" xr:uid="{D89B6172-2469-437A-A0BF-4FE475D4F775}"/>
+    <hyperlink ref="J624" r:id="rId383" xr:uid="{EF684974-8820-452A-9ADD-C561EC8FACA5}"/>
+    <hyperlink ref="J626" r:id="rId384" xr:uid="{8C273DFE-5DD0-4AD5-9F82-1CA9251611D3}"/>
+    <hyperlink ref="J628" r:id="rId385" xr:uid="{8A7A9432-7FB0-40EC-AEF4-05DDAD1C5735}"/>
+    <hyperlink ref="J629" r:id="rId386" xr:uid="{F9C9038D-66A2-46A9-9757-DD2C42C93B10}"/>
+    <hyperlink ref="J631" r:id="rId387" xr:uid="{8E9EB641-88AF-487B-9D7F-E954BBD24857}"/>
+    <hyperlink ref="J634" r:id="rId388" xr:uid="{C774A5D2-0CE0-4F93-A12A-BD3D53DAD45B}"/>
+    <hyperlink ref="J635" r:id="rId389" xr:uid="{83A87E34-A6B7-4330-9370-A94E59A1E2DA}"/>
+    <hyperlink ref="J637" r:id="rId390" xr:uid="{BBEF2F46-7D28-417F-919C-88130B67F361}"/>
+    <hyperlink ref="J640" r:id="rId391" xr:uid="{82C517BC-43E8-41EB-830F-704CC7EDE3AC}"/>
+    <hyperlink ref="J641" r:id="rId392" xr:uid="{6F6817EE-230B-444B-9FAC-F4013C3AFD19}"/>
+    <hyperlink ref="J642" r:id="rId393" xr:uid="{8983D546-2FA3-48C1-B37A-932A8842EAEC}"/>
+    <hyperlink ref="J644" r:id="rId394" xr:uid="{9D82F970-5D5E-43F8-A462-611FE7B44486}"/>
+    <hyperlink ref="J645" r:id="rId395" xr:uid="{4AADF96F-F03E-429C-8389-FE847DE9650D}"/>
+    <hyperlink ref="J648" r:id="rId396" xr:uid="{160377C2-7B9F-4DE6-8120-B80DF2483847}"/>
+    <hyperlink ref="J649" r:id="rId397" xr:uid="{F0FAB323-56A5-4B38-91D1-7DA7EE7F303D}"/>
+    <hyperlink ref="J652" r:id="rId398" xr:uid="{1073EBAF-D985-4798-B34F-B7A7DDFAE9EE}"/>
+    <hyperlink ref="J654" r:id="rId399" xr:uid="{F2B8558F-8C8F-459D-A2A2-6B4CB5DF9007}"/>
+    <hyperlink ref="J656" r:id="rId400" xr:uid="{577AF9D4-663E-424A-9DAA-B8D7C34823D5}"/>
+    <hyperlink ref="J657" r:id="rId401" xr:uid="{04370E96-ABCE-4B3F-8E45-B363A21253DF}"/>
+    <hyperlink ref="J663" r:id="rId402" xr:uid="{DDFDB22E-6383-4120-9128-EAA3CFB899BF}"/>
+    <hyperlink ref="J664" r:id="rId403" xr:uid="{1164C78A-EDD5-4747-86E3-F21891094424}"/>
+    <hyperlink ref="J665" r:id="rId404" xr:uid="{B2738F7F-1699-40B8-A1BA-C8127EBF425D}"/>
+    <hyperlink ref="J666" r:id="rId405" xr:uid="{B638A2D7-A24B-49EC-89E6-885A53963240}"/>
+    <hyperlink ref="J667" r:id="rId406" xr:uid="{4C90CD4B-0B87-41BC-AC5A-53D2C62840B6}"/>
+    <hyperlink ref="J668" r:id="rId407" xr:uid="{3309C9CF-55BD-4B24-8457-46A7F318457D}"/>
+    <hyperlink ref="J669" r:id="rId408" xr:uid="{DBD977FB-BD26-412E-89AE-6F8C94DE0120}"/>
+    <hyperlink ref="J670" r:id="rId409" xr:uid="{D3309D12-6F35-4913-904B-6325DCEF4BF7}"/>
+    <hyperlink ref="J671" r:id="rId410" xr:uid="{FDA20B92-4C15-4265-884D-D320E4FE7EFA}"/>
+    <hyperlink ref="J672" r:id="rId411" xr:uid="{2354632C-50B1-4AEF-8481-AB31CE6795A0}"/>
+    <hyperlink ref="J673" r:id="rId412" xr:uid="{724CC223-4589-421C-A418-1DB9908F01A1}"/>
+    <hyperlink ref="J674" r:id="rId413" xr:uid="{EE51F179-14C5-43DA-B458-5077383FB983}"/>
+    <hyperlink ref="J675" r:id="rId414" xr:uid="{76D6BA1F-9CE3-4A56-B369-4E9AF060B627}"/>
+    <hyperlink ref="J676" r:id="rId415" xr:uid="{3E959E5B-676F-4E42-97ED-778598903C05}"/>
+    <hyperlink ref="J677" r:id="rId416" xr:uid="{020DF6D9-878A-4CEB-BD59-23D5B3446A59}"/>
+    <hyperlink ref="J679" r:id="rId417" xr:uid="{8F24A5E9-EB58-4E5B-BECF-331E1DC8C783}"/>
+    <hyperlink ref="J682" r:id="rId418" xr:uid="{8F75485C-9C25-4DE7-AC0E-EFBAAFC86A90}"/>
+    <hyperlink ref="J683" r:id="rId419" xr:uid="{B3220F30-58C0-4D66-BCE7-C6520F96A267}"/>
+    <hyperlink ref="J684" r:id="rId420" xr:uid="{F87A2D75-99D1-40F3-83B4-D40BDD0D584D}"/>
+    <hyperlink ref="J688" r:id="rId421" xr:uid="{C36776FB-5AB5-49FB-922C-21C29CD26747}"/>
+    <hyperlink ref="J693" r:id="rId422" xr:uid="{CFA01E7F-825A-47EA-BEC5-A15A3BECFCD9}"/>
+    <hyperlink ref="J694" r:id="rId423" xr:uid="{3B647615-65DC-491F-9336-0EFFBAE5DA16}"/>
+    <hyperlink ref="J695" r:id="rId424" xr:uid="{580A8F12-6B98-41B5-BF59-16C0B1E3562F}"/>
+    <hyperlink ref="J696" r:id="rId425" xr:uid="{D9CF6BC7-0626-4CEC-841B-6B2D67F12E4F}"/>
+    <hyperlink ref="J697" r:id="rId426" xr:uid="{6D63DB5B-6200-4E23-9624-71BE7BC55946}"/>
+    <hyperlink ref="J698" r:id="rId427" xr:uid="{10BA0AE5-2070-4639-9F02-78D52ED03680}"/>
+    <hyperlink ref="J699" r:id="rId428" xr:uid="{5B24830C-4BFD-4F02-9016-93F17E66081F}"/>
+    <hyperlink ref="J700" r:id="rId429" xr:uid="{8D2B3125-00A0-433B-9EDD-DFC9ED7DD901}"/>
+    <hyperlink ref="J705" r:id="rId430" xr:uid="{94854633-D892-4EAC-9D18-B2F08D56F141}"/>
+    <hyperlink ref="J708" r:id="rId431" xr:uid="{0C534EF5-BB7C-47D1-918B-9E707F7DBE72}"/>
+    <hyperlink ref="J712" r:id="rId432" xr:uid="{FFF7B803-A10D-4079-81A2-D2D285FD95A9}"/>
+    <hyperlink ref="J713" r:id="rId433" xr:uid="{691C0CD7-50FF-47B1-BCE0-FF676CE34466}"/>
+    <hyperlink ref="J714" r:id="rId434" xr:uid="{3821DB93-1CCF-4EF2-A0A1-2A9BA634A797}"/>
+    <hyperlink ref="J715" r:id="rId435" xr:uid="{653D10A8-A7CB-438F-93AC-C6D88EA9B7A2}"/>
+    <hyperlink ref="J718" r:id="rId436" xr:uid="{32C588E5-9F2B-4C77-8A50-73C4AA2A8A06}"/>
+    <hyperlink ref="J720" r:id="rId437" xr:uid="{9B11E065-0108-4F53-8852-D89168753619}"/>
+    <hyperlink ref="J721" r:id="rId438" xr:uid="{690DC372-7358-4689-8831-F97ABCB5E1DF}"/>
+    <hyperlink ref="J722" r:id="rId439" xr:uid="{306136B9-F423-4230-A2C9-5182F0631429}"/>
+    <hyperlink ref="J725" r:id="rId440" xr:uid="{1BA04FD9-7D99-4FB0-BEB5-D5E31016FD3A}"/>
+    <hyperlink ref="J726" r:id="rId441" xr:uid="{3DA6CCBA-CDCF-43AC-9ACF-C31FD0750F7C}"/>
+    <hyperlink ref="J728" r:id="rId442" xr:uid="{ACDEE710-6261-4EEE-A534-AC257BF96D5B}"/>
+    <hyperlink ref="J729" r:id="rId443" xr:uid="{BB7636C6-6C52-477B-A502-0FD5EEE74945}"/>
+    <hyperlink ref="J736" r:id="rId444" xr:uid="{B862FB8A-C300-411E-9325-564EF62865BA}"/>
+    <hyperlink ref="J738" r:id="rId445" xr:uid="{3CA027C7-3E20-455B-ACC0-0CDCCE17E36B}"/>
+    <hyperlink ref="J739" r:id="rId446" xr:uid="{18506F19-9999-47DE-B824-4B886E18CAAE}"/>
+    <hyperlink ref="J740" r:id="rId447" xr:uid="{E8B35219-92C5-44F8-AC19-556CED065F09}"/>
+    <hyperlink ref="J741" r:id="rId448" xr:uid="{B5E6DBA2-ABBB-47E7-99B6-6978AF9DFF1A}"/>
+    <hyperlink ref="J742" r:id="rId449" xr:uid="{4B6B5886-93E7-4C92-BA00-3E7B988BC320}"/>
+    <hyperlink ref="J743" r:id="rId450" xr:uid="{DBC4EE59-E2DF-4F35-947F-E36F36186A37}"/>
+    <hyperlink ref="J744" r:id="rId451" xr:uid="{38E3EB4E-0B92-4FAB-835E-DA9636B9523B}"/>
+    <hyperlink ref="J747" r:id="rId452" xr:uid="{FFBCB215-E88C-4BBE-B1DD-0A35E0A663DD}"/>
+    <hyperlink ref="J748" r:id="rId453" xr:uid="{2AF7219F-A28B-436D-B146-A1C4C76D6CDD}"/>
+    <hyperlink ref="J757" r:id="rId454" xr:uid="{A08B0A89-B18C-437F-9925-AA90E9C67FC7}"/>
+    <hyperlink ref="J758" r:id="rId455" xr:uid="{BBAAF20E-6C99-4F67-87D2-F69F493F03BB}"/>
+    <hyperlink ref="J759" r:id="rId456" xr:uid="{4AD3A728-DB3E-4E02-AAFF-E99901D18570}"/>
+    <hyperlink ref="J760" r:id="rId457" xr:uid="{530C903E-1137-46C6-B1FA-9BB88B9FE029}"/>
+    <hyperlink ref="J761" r:id="rId458" xr:uid="{1E1FF8E9-889D-4C19-8EF8-1C9A26745DCC}"/>
+    <hyperlink ref="J762" r:id="rId459" xr:uid="{3BC1400A-222B-4FF9-9DD8-7724D2F34C9C}"/>
+    <hyperlink ref="J764" r:id="rId460" xr:uid="{ED89C3BB-BDC1-412C-BFE2-B1E3A2E0A2D1}"/>
+    <hyperlink ref="J765" r:id="rId461" xr:uid="{4C47FA46-17AC-478F-98AD-95E744A6D49E}"/>
+    <hyperlink ref="J766" r:id="rId462" xr:uid="{AC6AE6C9-4DD5-44D2-89C6-DCBF1424153F}"/>
+    <hyperlink ref="J767" r:id="rId463" xr:uid="{838EC70D-7426-46D6-8DE6-30A9D9D75C69}"/>
+    <hyperlink ref="J769" r:id="rId464" xr:uid="{8B604096-0750-4E04-9631-88155400E2C4}"/>
+    <hyperlink ref="J770" r:id="rId465" xr:uid="{B35C37E9-908B-419D-8949-59521BC53C97}"/>
+    <hyperlink ref="J772" r:id="rId466" xr:uid="{D341003A-953E-4E98-A047-DC386FE2BAE4}"/>
+    <hyperlink ref="J774" r:id="rId467" xr:uid="{FB2D432E-C58B-4136-BCBC-3A6EA3865817}"/>
+    <hyperlink ref="J778" r:id="rId468" xr:uid="{B6DBBFD3-4E74-404A-BB28-A52F711F0098}"/>
+    <hyperlink ref="J781" r:id="rId469" xr:uid="{943FF318-35D2-4A5C-9B50-8EECE94FA9C6}"/>
+    <hyperlink ref="J783" r:id="rId470" xr:uid="{800F6900-51D1-451C-8D6F-7C4CA65BF8E5}"/>
+    <hyperlink ref="J784" r:id="rId471" xr:uid="{10C38ED6-D596-430D-B213-C74072D2DCDF}"/>
+    <hyperlink ref="J785" r:id="rId472" xr:uid="{22E0213B-0B94-4C91-81AB-A4E6F16FEA20}"/>
+    <hyperlink ref="J788" r:id="rId473" xr:uid="{CEC99D9A-89B7-44C4-B918-A29DC2C604F4}"/>
+    <hyperlink ref="J789" r:id="rId474" xr:uid="{ABC3D3DB-5EAA-469D-A52A-F58181485025}"/>
+    <hyperlink ref="J790" r:id="rId475" xr:uid="{3EAF19BA-3A8B-408D-AF48-4E3EFA56CD68}"/>
+    <hyperlink ref="J794" r:id="rId476" xr:uid="{60BEE96B-004C-4834-BE2A-D80E475E57B6}"/>
+    <hyperlink ref="J795" r:id="rId477" xr:uid="{FAEDAD82-601B-481C-83E5-E9FF7AD2F99D}"/>
+    <hyperlink ref="J796" r:id="rId478" xr:uid="{47A77608-9787-48BF-A291-DB2D5A8B5CE3}"/>
+    <hyperlink ref="J797" r:id="rId479" xr:uid="{0F63412F-DB6D-42F7-9B80-BAA39B00E717}"/>
+    <hyperlink ref="J799" r:id="rId480" xr:uid="{123CD25F-4844-499B-82B6-2CF4DE03C68A}"/>
+    <hyperlink ref="J800" r:id="rId481" xr:uid="{BA55C4F9-E658-47B5-827D-66365B6916DC}"/>
+    <hyperlink ref="J801" r:id="rId482" xr:uid="{A3980522-7DC5-4159-A97D-119BFA522A7C}"/>
+    <hyperlink ref="J802" r:id="rId483" xr:uid="{BD124F46-9BB6-44C4-B4E7-82B271A1A511}"/>
+    <hyperlink ref="J803" r:id="rId484" xr:uid="{587E2E9F-FCF4-4981-BB0A-CC97B5A32869}"/>
+    <hyperlink ref="J804" r:id="rId485" xr:uid="{F656DD0A-54EB-4DE1-BF46-5766C336A57E}"/>
+    <hyperlink ref="J805" r:id="rId486" xr:uid="{E99E08CA-F6EE-4B22-9E5E-1B3507F54CDD}"/>
+    <hyperlink ref="J806" r:id="rId487" xr:uid="{33958338-2250-4202-9A4B-839C87DA8563}"/>
+    <hyperlink ref="J808" r:id="rId488" xr:uid="{63111949-E8E3-4732-AEC8-8E7ED4C042CF}"/>
+    <hyperlink ref="J810" r:id="rId489" xr:uid="{EFB7CEA7-A702-460B-B982-F744DB6F0C06}"/>
+    <hyperlink ref="J811" r:id="rId490" xr:uid="{18CAC9CA-ED21-44E0-902C-3DDC49AEFF63}"/>
+    <hyperlink ref="J812" r:id="rId491" xr:uid="{369AB8A3-A037-4B81-A80F-ABD8A799429D}"/>
+    <hyperlink ref="J813" r:id="rId492" xr:uid="{A643C6AF-8E80-4863-BF4B-85FF85EE96B4}"/>
+    <hyperlink ref="J814" r:id="rId493" xr:uid="{7881BB1A-BA99-4174-B0AA-46E84D9F33CB}"/>
+    <hyperlink ref="J815" r:id="rId494" xr:uid="{276179E0-1448-451D-97E5-A86F7F6DB59D}"/>
+    <hyperlink ref="J816" r:id="rId495" xr:uid="{68D21B76-0118-486C-B216-28E41F8DABB7}"/>
+    <hyperlink ref="J817" r:id="rId496" xr:uid="{7029ADF2-6074-4DF2-A045-7F6EFB64AFAF}"/>
+    <hyperlink ref="J818" r:id="rId497" xr:uid="{E789BCE1-94B1-4A3D-94C2-88B28DD8334B}"/>
+    <hyperlink ref="J819" r:id="rId498" xr:uid="{D04846B3-A03D-49DC-840D-79732E829F64}"/>
+    <hyperlink ref="J820" r:id="rId499" xr:uid="{1E145ABB-A17B-4022-9A79-85EC59AEF431}"/>
+    <hyperlink ref="J821" r:id="rId500" xr:uid="{2B3979ED-7454-4466-8890-AD2B492598E2}"/>
+    <hyperlink ref="J822" r:id="rId501" xr:uid="{B6B28130-24BA-4C2C-A4A9-E1A03C7851F0}"/>
+    <hyperlink ref="J825" r:id="rId502" xr:uid="{7294F4FC-3EA5-4D35-BCAF-8E1BA9526D19}"/>
+    <hyperlink ref="J826" r:id="rId503" xr:uid="{D21D6EA6-5FDD-43FC-98F8-CB53F0895FC3}"/>
+    <hyperlink ref="J827" r:id="rId504" xr:uid="{F1B5FD3C-56F1-4009-8BC2-84914D8319FD}"/>
+    <hyperlink ref="J828" r:id="rId505" xr:uid="{E860A6A9-F07A-4784-9618-4A69260DB3E3}"/>
+    <hyperlink ref="J831" r:id="rId506" xr:uid="{8129FE7C-D72B-4001-A250-C9CAF3562CFF}"/>
+    <hyperlink ref="J832" r:id="rId507" xr:uid="{3C704653-1479-49D6-A52A-E6AE562FB58C}"/>
+    <hyperlink ref="J833" r:id="rId508" xr:uid="{E3CB6CAD-B813-47CD-B3C7-55F552893591}"/>
+    <hyperlink ref="J836" r:id="rId509" xr:uid="{F63705AA-1A24-432A-A7E4-E22295124DAB}"/>
+    <hyperlink ref="J837" r:id="rId510" xr:uid="{036DAF3E-56E4-4B13-820A-36DA9C66F128}"/>
+    <hyperlink ref="J838" r:id="rId511" xr:uid="{CBFD50C4-34A8-4D4B-A958-4D53777F5BFA}"/>
+    <hyperlink ref="J839" r:id="rId512" xr:uid="{8844D382-C0A3-48A1-A9EC-B2109EECA41F}"/>
+    <hyperlink ref="J840" r:id="rId513" xr:uid="{0781AD2A-1E1B-4296-B2AD-6A3C8A9CEBA2}"/>
+    <hyperlink ref="J841" r:id="rId514" xr:uid="{FE89C12A-5624-4EDF-80F1-922F61B6DF75}"/>
+    <hyperlink ref="J842" r:id="rId515" xr:uid="{7E7B5BEB-C118-4732-8C6F-644A06E6246E}"/>
+    <hyperlink ref="J843" r:id="rId516" xr:uid="{1A3D7D12-0966-4EC5-B204-2A48D5FD3743}"/>
+    <hyperlink ref="J844" r:id="rId517" xr:uid="{B3736B3B-9346-40C9-9290-4A9EE41684C0}"/>
+    <hyperlink ref="J847" r:id="rId518" xr:uid="{E7620B1A-3CF4-4F98-BFBA-6E037AA90E28}"/>
+    <hyperlink ref="J848" r:id="rId519" xr:uid="{CF263B78-6172-46A4-BED2-05A988CAEB4F}"/>
+    <hyperlink ref="J850" r:id="rId520" xr:uid="{31816EF6-8B8B-4928-9A25-16C148BE956F}"/>
+    <hyperlink ref="J852" r:id="rId521" xr:uid="{3A655771-DF82-496B-9BAA-E0709294BF89}"/>
+    <hyperlink ref="J853" r:id="rId522" xr:uid="{B55820B3-BB60-4928-91D7-8C914E69EBB5}"/>
+    <hyperlink ref="J856" r:id="rId523" xr:uid="{938F4BE0-EC1A-4D27-8DBA-BC4BFFA8B20F}"/>
+    <hyperlink ref="J858" r:id="rId524" xr:uid="{5BCCAA14-5699-4684-AD5B-44D6C69792D3}"/>
+    <hyperlink ref="J861" r:id="rId525" xr:uid="{0912E182-C221-4C54-9F2C-3024A7CEFB83}"/>
+    <hyperlink ref="J862" r:id="rId526" xr:uid="{BD72D19E-DC41-4D90-B521-586BC1C91778}"/>
+    <hyperlink ref="J863" r:id="rId527" xr:uid="{953D56E4-A1CE-4991-9769-1CCBCF50FA01}"/>
+    <hyperlink ref="J865" r:id="rId528" xr:uid="{61C23E94-7EE8-48EE-A210-9DE649567237}"/>
+    <hyperlink ref="J866" r:id="rId529" xr:uid="{C895C670-B62D-4C68-94E2-DAA0436BFCD2}"/>
+    <hyperlink ref="J867" r:id="rId530" xr:uid="{4CBBC671-DCAD-4EEB-AB15-EEB5F651A25B}"/>
+    <hyperlink ref="J868" r:id="rId531" xr:uid="{E2295496-ED85-4B01-812A-5D9AAD0FB82B}"/>
+    <hyperlink ref="J870" r:id="rId532" xr:uid="{53804D45-64E2-4EE6-BF7B-7CEF522F9762}"/>
+    <hyperlink ref="J871" r:id="rId533" xr:uid="{8AD07AC3-33D8-4976-A893-30ADAA48C084}"/>
+    <hyperlink ref="J872" r:id="rId534" xr:uid="{14949C01-6F63-4892-9100-17FA46DE9B87}"/>
+    <hyperlink ref="J873" r:id="rId535" xr:uid="{D76DFA99-CE23-4A8A-B01A-A12CB19FA87B}"/>
+    <hyperlink ref="J875" r:id="rId536" xr:uid="{86404E3C-7FA9-4F99-9B81-D62447A0CFAF}"/>
+    <hyperlink ref="J877" r:id="rId537" xr:uid="{6BD7E980-E40C-4248-BF67-DF514E7CD5E7}"/>
+    <hyperlink ref="J878" r:id="rId538" xr:uid="{583EDCF5-C561-443B-804A-A95BE72F9BA9}"/>
+    <hyperlink ref="J880" r:id="rId539" xr:uid="{17E412F6-6AB0-43C9-BEBB-EE3F36B1E3D1}"/>
+    <hyperlink ref="J882" r:id="rId540" xr:uid="{219775B8-D820-4ADC-BDB1-8445D63EB1BC}"/>
+    <hyperlink ref="J883" r:id="rId541" xr:uid="{203E8A0B-88DD-4405-BB4B-1B1DC520FA35}"/>
+    <hyperlink ref="J884" r:id="rId542" xr:uid="{7A8F1A85-A41D-47E9-8DB7-B372E28001CE}"/>
+    <hyperlink ref="J885" r:id="rId543" xr:uid="{93696F7F-18F4-49BE-9EB2-ED03FF9F5A6B}"/>
+    <hyperlink ref="J886" r:id="rId544" xr:uid="{658F0806-7D82-43CC-BD06-0ECC85D082EB}"/>
+    <hyperlink ref="J888" r:id="rId545" xr:uid="{66123690-1018-440E-97DB-BC1416D21E9A}"/>
+    <hyperlink ref="J889" r:id="rId546" xr:uid="{DFD608A0-324D-489A-AAEA-B8ED51401D58}"/>
+    <hyperlink ref="J893" r:id="rId547" xr:uid="{3ED64635-D787-400F-B140-344CF6AFF99B}"/>
+    <hyperlink ref="J894" r:id="rId548" xr:uid="{6BA457C6-F17A-4225-965E-E9D1275A3AC1}"/>
+    <hyperlink ref="J895" r:id="rId549" xr:uid="{3B17E5B2-EFF8-4CD5-A8C8-7642AB3D3F8F}"/>
+    <hyperlink ref="J896" r:id="rId550" xr:uid="{94654B25-8B0A-40B1-B148-E12EDC41F027}"/>
+    <hyperlink ref="J897" r:id="rId551" xr:uid="{89067AEC-3BE4-4A94-B800-391902C45757}"/>
+    <hyperlink ref="J899" r:id="rId552" xr:uid="{2BC00944-3B56-4D1D-8DE8-17FF1D3581E8}"/>
+    <hyperlink ref="J900" r:id="rId553" xr:uid="{58773BE8-A7D9-4F11-8CE5-4506EC540264}"/>
+    <hyperlink ref="J905" r:id="rId554" xr:uid="{11CA87DB-E02F-4148-8238-013EE6A6EDED}"/>
+    <hyperlink ref="J906" r:id="rId555" xr:uid="{4B5B4424-BD15-4337-88D9-1E50E6A2B7FD}"/>
+    <hyperlink ref="J907" r:id="rId556" xr:uid="{76218C6B-E406-4557-9E7E-16EDE34CC947}"/>
+    <hyperlink ref="J908" r:id="rId557" xr:uid="{1B7ACCCB-800C-4958-8CCB-93A6BBE040A7}"/>
+    <hyperlink ref="J909" r:id="rId558" xr:uid="{E2EE749C-A138-49B1-B4B6-865412081721}"/>
+    <hyperlink ref="J910" r:id="rId559" xr:uid="{B0168651-8983-4DFF-A409-F6C8EDE79380}"/>
+    <hyperlink ref="J911" r:id="rId560" xr:uid="{56C6AF32-DD4B-421A-A04E-C98AB5917167}"/>
+    <hyperlink ref="J912" r:id="rId561" xr:uid="{AFB304BB-2625-4E19-AB98-7E9B0A151A17}"/>
+    <hyperlink ref="J913" r:id="rId562" xr:uid="{1C544C32-7072-46E9-88DD-AE18FE020C36}"/>
+    <hyperlink ref="J914" r:id="rId563" xr:uid="{EB533965-57EB-4B34-A982-68AC8512C21D}"/>
+    <hyperlink ref="J915" r:id="rId564" xr:uid="{C62F82DF-7BB3-4EB8-BECA-D8B2D48C71B1}"/>
+    <hyperlink ref="J916" r:id="rId565" xr:uid="{4D5CFB46-EE16-455C-A4F6-DDBF89C11E78}"/>
+    <hyperlink ref="J918" r:id="rId566" xr:uid="{43CBC125-05EB-4998-B270-23B9A864FF9C}"/>
+    <hyperlink ref="J919" r:id="rId567" xr:uid="{493F53DC-6DFB-4338-84AD-276652472457}"/>
+    <hyperlink ref="J922" r:id="rId568" xr:uid="{534AE20E-0855-4374-ACE5-54CB863870D6}"/>
+    <hyperlink ref="J923" r:id="rId569" xr:uid="{A31AFA9F-7325-4365-8335-FCD4571F2D2F}"/>
+    <hyperlink ref="J925" r:id="rId570" xr:uid="{D2AFA102-BC18-4487-BB9E-A606B4058B33}"/>
+    <hyperlink ref="J926" r:id="rId571" xr:uid="{A4261F37-C532-4335-86AE-D89D06D5A322}"/>
+    <hyperlink ref="J928" r:id="rId572" xr:uid="{4342D9B6-6103-41E2-8ECB-586986DAC60F}"/>
+    <hyperlink ref="J929" r:id="rId573" xr:uid="{C25FCF53-6D03-4272-A1BE-67DFBA360613}"/>
+    <hyperlink ref="J930" r:id="rId574" xr:uid="{7E30AEC8-B53B-40CC-8B98-F67E43ADEE8B}"/>
+    <hyperlink ref="J931" r:id="rId575" xr:uid="{6DC764B7-9EED-40BD-8B5F-BFB946BD571F}"/>
+    <hyperlink ref="J932" r:id="rId576" xr:uid="{51AE6EDC-D8CB-43E4-9E1F-59FEE7CBA170}"/>
+    <hyperlink ref="J933" r:id="rId577" xr:uid="{6B1B1EDB-3896-4B7F-8374-72901ECCB2A4}"/>
+    <hyperlink ref="J935" r:id="rId578" xr:uid="{6E29495D-2E52-4D2B-8398-B0424F6AD0E1}"/>
+    <hyperlink ref="J940" r:id="rId579" xr:uid="{40DF0529-0F36-4F08-B7BD-78228AE77600}"/>
+    <hyperlink ref="J941" r:id="rId580" xr:uid="{EFE6BBD7-B2AD-448E-80A9-8712F3D1F481}"/>
+    <hyperlink ref="J942" r:id="rId581" xr:uid="{827309A8-096B-47C0-AAA6-C1DA676E421A}"/>
+    <hyperlink ref="J943" r:id="rId582" xr:uid="{2448ABAF-6160-4449-8739-B73354A3ECED}"/>
+    <hyperlink ref="J944" r:id="rId583" xr:uid="{392A19D2-AF49-4C01-B722-590AD511E0BE}"/>
+    <hyperlink ref="J946" r:id="rId584" xr:uid="{19BA6AC7-5974-4811-B4C5-A43C7D301F7A}"/>
+    <hyperlink ref="J947" r:id="rId585" xr:uid="{DEC89270-A84C-4F04-8510-74D6840993CA}"/>
+    <hyperlink ref="J948" r:id="rId586" xr:uid="{224BA808-2875-496D-99DE-5B5E7450D23F}"/>
+    <hyperlink ref="J949" r:id="rId587" xr:uid="{F56AB277-CC68-41FB-A024-BE6ED88E8600}"/>
+    <hyperlink ref="J950" r:id="rId588" xr:uid="{38CDDD2C-810C-4C69-9AA9-3CFCF53FC8F8}"/>
+    <hyperlink ref="J952" r:id="rId589" xr:uid="{A78344E9-1E6C-4FE7-9E19-A8247A706149}"/>
+    <hyperlink ref="J953" r:id="rId590" xr:uid="{E509723E-2503-4B03-8F61-DA83BCC8AF12}"/>
+    <hyperlink ref="J954" r:id="rId591" xr:uid="{F27ABD4D-931C-4467-A93D-667FD04A1E46}"/>
+    <hyperlink ref="J955" r:id="rId592" xr:uid="{83EE4756-C369-41D5-BF54-5F811AEDC4D5}"/>
+    <hyperlink ref="J956" r:id="rId593" xr:uid="{88774468-7235-4B58-A879-1B968BAEAADF}"/>
+    <hyperlink ref="J958" r:id="rId594" xr:uid="{9E7BD913-14EF-4D10-A487-59E2C723A2D4}"/>
+    <hyperlink ref="J962" r:id="rId595" xr:uid="{7943D32C-90DE-4EB4-B562-259123F3A89F}"/>
+    <hyperlink ref="J963" r:id="rId596" xr:uid="{70DBE881-5077-441C-9B50-B034447295A2}"/>
+    <hyperlink ref="J965" r:id="rId597" xr:uid="{9EA14C8B-3C93-418C-8A8B-F24C266F478C}"/>
+    <hyperlink ref="J968" r:id="rId598" xr:uid="{8617EFF8-DF63-433D-A25F-CC4696075031}"/>
+    <hyperlink ref="J969" r:id="rId599" xr:uid="{7D105549-EFA3-4553-9A2C-BD3969B930EF}"/>
+    <hyperlink ref="J971" r:id="rId600" xr:uid="{A3BABCEB-74BF-432D-95A2-41C25D4670F1}"/>
+    <hyperlink ref="J973" r:id="rId601" xr:uid="{260F2CAB-986D-4F41-8759-97B227DE4CA6}"/>
+    <hyperlink ref="J974" r:id="rId602" xr:uid="{3BF977A2-DB40-4ACE-9AF9-601461676F1C}"/>
+    <hyperlink ref="J975" r:id="rId603" xr:uid="{203DCCCE-5549-427B-8365-AAD43805246C}"/>
+    <hyperlink ref="J976" r:id="rId604" xr:uid="{74F71C10-793E-40A6-B8AE-1EE1B73A5CC8}"/>
+    <hyperlink ref="J977" r:id="rId605" xr:uid="{ADD0F581-E1C0-4083-AAC9-62412A50FBB8}"/>
+    <hyperlink ref="J981" r:id="rId606" xr:uid="{C6022E15-8657-441A-8962-7BFC6BA499E4}"/>
+    <hyperlink ref="J984" r:id="rId607" xr:uid="{3C76A9EC-4B4B-4A22-8715-D4B0CF7F5E05}"/>
+    <hyperlink ref="J986" r:id="rId608" xr:uid="{54F96821-C248-4E70-A6A5-4D1B99D288E3}"/>
+    <hyperlink ref="J990" r:id="rId609" xr:uid="{6B7BFBA7-C038-499C-A5B1-6C13AE7B66F5}"/>
+    <hyperlink ref="J991" r:id="rId610" xr:uid="{7E7041C2-B23A-4A11-B997-8A06B07B97B5}"/>
+    <hyperlink ref="J996" r:id="rId611" xr:uid="{2DBBE10F-8822-46D9-AA56-F06123A46B7D}"/>
+    <hyperlink ref="J997" r:id="rId612" xr:uid="{96D3B5F4-32CA-4218-B474-74E6A4427D94}"/>
+    <hyperlink ref="J999" r:id="rId613" xr:uid="{FF6081E4-DD1B-4BB3-B6A8-7883FFCABEB3}"/>
+    <hyperlink ref="J1000" r:id="rId614" xr:uid="{C3657196-898D-466B-A8FC-A8C75EC2E432}"/>
+    <hyperlink ref="J1003" r:id="rId615" xr:uid="{A1647F4D-F289-4F51-B6BB-0708EAA62C7A}"/>
+    <hyperlink ref="J1004" r:id="rId616" xr:uid="{0E556C35-D521-4066-B6A1-5FB53C70671A}"/>
+    <hyperlink ref="J1005" r:id="rId617" xr:uid="{C86AD829-2A23-4E46-8C08-FF48C37D7422}"/>
+    <hyperlink ref="J1006" r:id="rId618" xr:uid="{AA8365DA-78EF-4D6E-A984-A02370F7553E}"/>
+    <hyperlink ref="J1007" r:id="rId619" xr:uid="{C54180C0-2E4F-4B6D-939D-F0D8144F9B5B}"/>
+    <hyperlink ref="J1008" r:id="rId620" xr:uid="{0CE73332-C24A-4962-89B7-63970812E654}"/>
+    <hyperlink ref="J1009" r:id="rId621" xr:uid="{5B4ABA1D-3C6F-4855-9644-DCF039408002}"/>
+    <hyperlink ref="J1011" r:id="rId622" xr:uid="{B46ADF9A-2117-4B8C-9656-BF4D16DA1CF0}"/>
+    <hyperlink ref="J1012" r:id="rId623" xr:uid="{63063672-6C54-4117-B855-C0CE4EADB663}"/>
+    <hyperlink ref="J1016" r:id="rId624" xr:uid="{FCE13C1B-048E-43EE-A010-E680241CA357}"/>
+    <hyperlink ref="J1019" r:id="rId625" xr:uid="{B3B3F2C7-E345-4A59-9946-4E8BD9DA6D59}"/>
+    <hyperlink ref="J1020" r:id="rId626" xr:uid="{259F1E9F-3114-480A-A087-4CD39A5A6D0C}"/>
+    <hyperlink ref="J1023" r:id="rId627" xr:uid="{4B69103B-1C3A-4DAA-A21F-78433E35C2D5}"/>
+    <hyperlink ref="J1024" r:id="rId628" xr:uid="{D48394F4-F163-4860-99F1-AFA16F1CF278}"/>
+    <hyperlink ref="J1025" r:id="rId629" xr:uid="{9EF14159-F893-4B10-B5D6-87B28BAF5F1D}"/>
+    <hyperlink ref="J1026" r:id="rId630" xr:uid="{9CB597C4-ACEE-42E1-B48F-CE56ED0E5C2B}"/>
+    <hyperlink ref="J1027" r:id="rId631" xr:uid="{4597C0C6-C40F-424D-AD9A-491B243635EF}"/>
+    <hyperlink ref="J1028" r:id="rId632" xr:uid="{EC62B0CD-1575-484A-8E6B-69080B4DB049}"/>
+    <hyperlink ref="J1030" r:id="rId633" xr:uid="{A468CF9D-9C09-4F75-9C16-9D5A6E2C246C}"/>
+    <hyperlink ref="J1033" r:id="rId634" xr:uid="{83A3F491-ADFB-4D4A-B763-36ABB1AE5B1C}"/>
+    <hyperlink ref="J1034" r:id="rId635" xr:uid="{6DD1609B-917A-40C3-A92B-4AC77569D337}"/>
+    <hyperlink ref="J1036" r:id="rId636" xr:uid="{834D9792-FA78-4E9B-B4ED-E3E9551315BD}"/>
+    <hyperlink ref="J1037" r:id="rId637" xr:uid="{A078794D-2B15-4DA1-9775-214F36EC3744}"/>
+    <hyperlink ref="J1041" r:id="rId638" xr:uid="{556ADD80-6E48-4C44-BD97-0843B517EB85}"/>
+    <hyperlink ref="J1042" r:id="rId639" xr:uid="{2DF3D7C0-CCDF-4353-A893-1BF35882FF1F}"/>
+    <hyperlink ref="J1043" r:id="rId640" xr:uid="{5428A1E4-F6B4-41CB-A31C-198E7E2201BE}"/>
+    <hyperlink ref="J1044" r:id="rId641" xr:uid="{B5860222-230E-46B6-8EA2-BEC139C598A4}"/>
+    <hyperlink ref="J1046" r:id="rId642" xr:uid="{89B2E2DA-8308-42DE-AD92-7A499F2D7110}"/>
+    <hyperlink ref="J1047" r:id="rId643" xr:uid="{0CDE6E63-1ABC-4AFD-9DA7-9BA1D7EC0BC0}"/>
+    <hyperlink ref="J1051" r:id="rId644" xr:uid="{98888F6F-7AC6-4F89-B1D5-0D28A5B8DF4C}"/>
+    <hyperlink ref="J1052" r:id="rId645" xr:uid="{3063467F-0717-40D2-8098-751814195BC1}"/>
+    <hyperlink ref="J1054" r:id="rId646" xr:uid="{1D7902EE-920D-4921-99A8-8CFEAB26A8A6}"/>
+    <hyperlink ref="J1056" r:id="rId647" xr:uid="{507D1327-1B62-498D-800F-86CEADCACB50}"/>
+    <hyperlink ref="J1064" r:id="rId648" xr:uid="{C8D98EF4-E7B9-46BC-8D04-00932D11F4EF}"/>
+    <hyperlink ref="J1065" r:id="rId649" xr:uid="{A4D92131-6428-468F-BDDE-F25CD72428A3}"/>
+    <hyperlink ref="J1066" r:id="rId650" xr:uid="{66C5777A-53EA-4B79-9355-BEB858C77495}"/>
+    <hyperlink ref="J1067" r:id="rId651" xr:uid="{50172FF0-F0EB-46FB-9827-115C03AF4723}"/>
+    <hyperlink ref="J1068" r:id="rId652" xr:uid="{ECCC4B96-26C9-4B8D-B705-60AFDFA10798}"/>
+    <hyperlink ref="J1069" r:id="rId653" xr:uid="{C96833D4-6403-4701-AAE2-12F21662EA80}"/>
+    <hyperlink ref="J1070" r:id="rId654" xr:uid="{6B555173-F35D-4B91-B197-4739ECD59A5A}"/>
+    <hyperlink ref="J1071" r:id="rId655" xr:uid="{8137B651-9F72-44E4-AD19-42D128709F96}"/>
+    <hyperlink ref="J1072" r:id="rId656" xr:uid="{AD2D9517-AE4D-4D4C-B4EB-667DCBB7AA05}"/>
+    <hyperlink ref="J1073" r:id="rId657" xr:uid="{28EA2485-AC78-4F7F-91A2-A28F68A0709B}"/>
+    <hyperlink ref="J1076" r:id="rId658" xr:uid="{A2A11EDD-2D84-4201-BF84-776AFBBEBB82}"/>
+    <hyperlink ref="J1077" r:id="rId659" xr:uid="{8D9CE343-8AED-44E1-809B-84265F52D156}"/>
+    <hyperlink ref="J1078" r:id="rId660" xr:uid="{FEB5CC0C-B4C1-42AF-A125-12B7CEB9827A}"/>
+    <hyperlink ref="J1080" r:id="rId661" xr:uid="{64B46AAB-F151-436F-9B7D-E1C9DAD77893}"/>
+    <hyperlink ref="J1082" r:id="rId662" xr:uid="{BC6614FD-EF1E-4750-A9C8-0D59B1D43C84}"/>
+    <hyperlink ref="J1086" r:id="rId663" xr:uid="{95E243A5-632F-4D46-A263-00B34D8C3118}"/>
+    <hyperlink ref="J1087" r:id="rId664" xr:uid="{28970629-6758-4BDC-B4BD-DA989E91A87F}"/>
+    <hyperlink ref="J1088" r:id="rId665" xr:uid="{FB17AEB7-E12B-425C-A7E9-B9793AD986D6}"/>
+    <hyperlink ref="J1090" r:id="rId666" xr:uid="{04955FFE-D7AE-44B2-B76E-E6BB9C403F5A}"/>
+    <hyperlink ref="J1091" r:id="rId667" xr:uid="{EE2F9FA3-4996-4613-AFB9-275F63C07251}"/>
+    <hyperlink ref="J1098" r:id="rId668" xr:uid="{C4D81C48-CF98-4709-BA4B-2BC7F8A0C3C9}"/>
+    <hyperlink ref="J1100" r:id="rId669" xr:uid="{80F6E6CC-98EC-4680-AC26-BCD18B449851}"/>
+    <hyperlink ref="J1102" r:id="rId670" xr:uid="{ACB141BB-83B6-4C6B-B8F0-2891EF6D32EB}"/>
+    <hyperlink ref="J1103" r:id="rId671" xr:uid="{FF830601-F61A-49A3-884A-C6569D199621}"/>
+    <hyperlink ref="J1104" r:id="rId672" xr:uid="{32C4F334-CD8C-428D-934C-A75D400EAE27}"/>
+    <hyperlink ref="J1106" r:id="rId673" xr:uid="{7A74257D-D3E2-4C89-BAE9-727624C15A80}"/>
+    <hyperlink ref="J1109" r:id="rId674" xr:uid="{DB447AC2-97EE-46E5-B94E-A5D5D339A6A1}"/>
+    <hyperlink ref="J1110" r:id="rId675" xr:uid="{5455D9C3-B229-4D40-9DD6-B90827DF0259}"/>
+    <hyperlink ref="J1113" r:id="rId676" xr:uid="{305FC8FD-A97B-4A9D-9F58-518375AB2EB0}"/>
+    <hyperlink ref="J1114" r:id="rId677" xr:uid="{2484D319-EAF2-4580-A605-25FA98307782}"/>
+    <hyperlink ref="J1115" r:id="rId678" xr:uid="{2250C000-3531-4FF4-8CFC-C4A373BC8108}"/>
+    <hyperlink ref="J1116" r:id="rId679" xr:uid="{223CCC87-7383-47B9-9E5C-80C4E72F6D36}"/>
+    <hyperlink ref="J1117" r:id="rId680" xr:uid="{FEBC8D25-D60C-4D3D-B2D0-B23DA5A55747}"/>
+    <hyperlink ref="J1118" r:id="rId681" xr:uid="{C2746052-CB8F-41D9-B037-D2291841B5F2}"/>
+    <hyperlink ref="J1119" r:id="rId682" xr:uid="{7517035D-2796-40E2-BDB6-01B2949361CF}"/>
+    <hyperlink ref="J1124" r:id="rId683" xr:uid="{3597E40A-A31E-4848-8C00-69087D446569}"/>
+    <hyperlink ref="J1125" r:id="rId684" xr:uid="{7DC5C954-1363-41D3-A68F-EC307CF33BE2}"/>
+    <hyperlink ref="J1126" r:id="rId685" xr:uid="{6AC96F8E-090A-4EFA-BF23-2D8A9F56FC43}"/>
+    <hyperlink ref="J1127" r:id="rId686" xr:uid="{DD03EA53-2998-4F53-A81B-93D751E26FE1}"/>
+    <hyperlink ref="J1128" r:id="rId687" xr:uid="{3FB5D4E5-C3DB-4742-9F49-EDD18644C23B}"/>
+    <hyperlink ref="J1129" r:id="rId688" xr:uid="{CB8C159C-E52F-4D68-993E-14C19499106B}"/>
+    <hyperlink ref="J1130" r:id="rId689" xr:uid="{192D764A-3A6D-4828-AB5A-98A94908094A}"/>
+    <hyperlink ref="J1131" r:id="rId690" xr:uid="{5474606A-FA9A-4604-A3AA-5A53454DCF8E}"/>
+    <hyperlink ref="J1132" r:id="rId691" xr:uid="{362CB9AA-691B-45F9-94FA-1FB151246684}"/>
+    <hyperlink ref="J1133" r:id="rId692" xr:uid="{0E1BF81D-F240-403D-8A82-9DA891D8B4DD}"/>
+    <hyperlink ref="J1134" r:id="rId693" xr:uid="{8EB6FCA8-F7C8-4ED5-882E-FAFCC1DFD1AE}"/>
+    <hyperlink ref="J1135" r:id="rId694" xr:uid="{125CD212-BAE3-4D79-A396-30201F86C669}"/>
+    <hyperlink ref="J1136" r:id="rId695" xr:uid="{86AC1E00-052B-4CD2-B78C-DB0B77D67C09}"/>
+    <hyperlink ref="J1137" r:id="rId696" xr:uid="{A1F1791C-DB8D-450B-9309-3B314CB734DD}"/>
+    <hyperlink ref="J1141" r:id="rId697" xr:uid="{1D130E5E-67C7-4F61-8371-36FEDC542997}"/>
+    <hyperlink ref="J1143" r:id="rId698" xr:uid="{A1514D98-144F-42E6-8BC1-8CD290592CC4}"/>
+    <hyperlink ref="J1144" r:id="rId699" xr:uid="{0C7589AC-D37B-4848-9225-AC80D07ADBF8}"/>
+    <hyperlink ref="J1147" r:id="rId700" xr:uid="{F64979C7-CF30-49EE-855A-762202E915B7}"/>
+    <hyperlink ref="J1150" r:id="rId701" xr:uid="{F21BA8C0-430B-49E9-8750-BFBE727CAF94}"/>
+    <hyperlink ref="J1152" r:id="rId702" xr:uid="{0A095912-71E2-4CA5-8A65-7ABB66823D3C}"/>
+    <hyperlink ref="J1155" r:id="rId703" xr:uid="{2825C89C-99D3-4FF1-BCA5-178AC5479658}"/>
+    <hyperlink ref="J1156" r:id="rId704" xr:uid="{6C57F0A0-0CF7-4089-A40D-B3132B3B47EA}"/>
+    <hyperlink ref="J1157" r:id="rId705" xr:uid="{BDAF42A7-74D7-4D4C-B5FA-6BFE89BDB04F}"/>
+    <hyperlink ref="J1158" r:id="rId706" xr:uid="{9521DD7F-55DC-4A14-AE2B-992F14FA80B0}"/>
+    <hyperlink ref="J1159" r:id="rId707" xr:uid="{BF0A4073-F7D3-4C35-88FA-93E7C8A6599E}"/>
+    <hyperlink ref="J1160" r:id="rId708" xr:uid="{6FD7ED5A-3FA5-44B9-96E0-132459933C48}"/>
+    <hyperlink ref="J1162" r:id="rId709" xr:uid="{3D110EAF-3566-42F8-9453-8A3BECBA10CE}"/>
+    <hyperlink ref="J1163" r:id="rId710" xr:uid="{8AE75AB1-BDD5-45F3-94F1-9E6309EFF6C9}"/>
+    <hyperlink ref="J1165" r:id="rId711" xr:uid="{9E5F1C9D-7BA9-4380-8544-2D71DD74EAB2}"/>
+    <hyperlink ref="J1166" r:id="rId712" xr:uid="{A35B2F2A-6423-4EB0-B19A-8A5689422289}"/>
+    <hyperlink ref="J1167" r:id="rId713" xr:uid="{1B6A0E94-ACC4-4553-8E55-E98EC83B6CB7}"/>
+    <hyperlink ref="J1168" r:id="rId714" xr:uid="{8D8D6913-606B-4AF6-85FA-49A1793B2FE6}"/>
+    <hyperlink ref="J1169" r:id="rId715" xr:uid="{0B3CD165-BE3E-4743-A0C4-7091F4927BEF}"/>
+    <hyperlink ref="J1173" r:id="rId716" xr:uid="{08D696F6-730D-4143-BB97-34EA8CB657F4}"/>
+    <hyperlink ref="J1176" r:id="rId717" xr:uid="{36876ACC-6D09-4645-A773-6C22834B5501}"/>
+    <hyperlink ref="J1179" r:id="rId718" xr:uid="{51119CE9-620A-4493-8C86-107B0D9191A5}"/>
+    <hyperlink ref="J1186" r:id="rId719" xr:uid="{25EABCB1-68ED-4FD1-9C6D-AA7213C25EDB}"/>
+    <hyperlink ref="J1187" r:id="rId720" xr:uid="{D0F725E1-BF69-4F14-9746-8C13B393CEE7}"/>
+    <hyperlink ref="J1190" r:id="rId721" xr:uid="{423B6F41-2E6D-43F3-AD06-D9B75D853638}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId696"/>
+  <pageSetup orientation="portrait" r:id="rId722"/>
   <tableParts count="1">
-    <tablePart r:id="rId697"/>
+    <tablePart r:id="rId723"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEE0809-6098-4E10-8BAE-38C9994887CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD9A0DE-D56B-41B8-A4CC-DD216A2FB2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="501">
   <si>
     <t>Fecha</t>
   </si>
@@ -782,6 +782,764 @@
   </si>
   <si>
     <t>Falto 1 cheto crema 85 grs</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — Llamé al cliente pero no contesta. Vuelvo a llamar en un rato.</t>
+  </si>
+  <si>
+    <t>MR3NJJDWUWF4</t>
+  </si>
+  <si>
+    <t>12:22 p. m.</t>
+  </si>
+  <si>
+    <t>Faltaron 6 Doritos 40 grs</t>
+  </si>
+  <si>
+    <t>MR3NJH2VTGFC</t>
+  </si>
+  <si>
+    <t>12:21 p. m.</t>
+  </si>
+  <si>
+    <t>MR3NLAT53H7S</t>
+  </si>
+  <si>
+    <t>12:23 p. m.</t>
+  </si>
+  <si>
+    <t>Pedido repatido</t>
+  </si>
+  <si>
+    <t>MR3ODZDXQ4WL</t>
+  </si>
+  <si>
+    <t>12:45 p. m.</t>
+  </si>
+  <si>
+    <t>Faltó 8 chetos x 43</t>
+  </si>
+  <si>
+    <t>MR3OPIDMD96B</t>
+  </si>
+  <si>
+    <t>12:54 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783007654/owwtzhmfamgpjkgu1arc.jpg</t>
+  </si>
+  <si>
+    <t>MR3P3JM7EAOA</t>
+  </si>
+  <si>
+    <t>MR3PG6IMAVR8</t>
+  </si>
+  <si>
+    <t>01:15 p. m.</t>
+  </si>
+  <si>
+    <t>MOLINA JORGE GABRIEL</t>
+  </si>
+  <si>
+    <t>No quiso el pedido</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783008899/rhnzk5jdqulz2rxvilym.jpg</t>
+  </si>
+  <si>
+    <t>MR3PY8X17JA3</t>
+  </si>
+  <si>
+    <t>MR3Q66N766Z8</t>
+  </si>
+  <si>
+    <t>01:35 p. m.</t>
+  </si>
+  <si>
+    <t>Rechaza pepsico 
+Higienol max</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783010114/do52fcrlgmwmu2g5j0hg.jpg</t>
+  </si>
+  <si>
+    <t>MR3Q96VHFU6Y</t>
+  </si>
+  <si>
+    <t>MR3QEUGCYQA3</t>
+  </si>
+  <si>
+    <t>01:42 p. m.</t>
+  </si>
+  <si>
+    <t>MR3QITX00IAD</t>
+  </si>
+  <si>
+    <t>01:45 p. m.</t>
+  </si>
+  <si>
+    <t>Le falta 1 Doritos ala tira
+Desarmo otro cl</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783010703/zfy2gpqjea5jvdwwvwu5.jpg</t>
+  </si>
+  <si>
+    <t>MR3QV8RB4202</t>
+  </si>
+  <si>
+    <t>01:55 p. m.</t>
+  </si>
+  <si>
+    <t>Le falta una máquina ala tira</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783011282/jlkexb6inkruimkajlk3.jpg</t>
+  </si>
+  <si>
+    <t>MR3QX9GZNCM3</t>
+  </si>
+  <si>
+    <t>Segunda ves que paso</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783011379/z6yadgzmisefvn6hjc5q.jpg</t>
+  </si>
+  <si>
+    <t>MR3RA4Q9519W</t>
+  </si>
+  <si>
+    <t>MR3RXV7QZDDI</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783013077/eqc3qz0dp7uihok7bog9.jpg</t>
+  </si>
+  <si>
+    <t>MR3SM3PZ5N1I</t>
+  </si>
+  <si>
+    <t>MR3SRMZEWG9E</t>
+  </si>
+  <si>
+    <t>MR3T0JIO1H9A</t>
+  </si>
+  <si>
+    <t>02:54 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783014881/mwqlhfxk00gxn04go57d.jpg</t>
+  </si>
+  <si>
+    <t>MR3TXLF5XJQ4</t>
+  </si>
+  <si>
+    <t>03:21 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783016463/nssjfywktk1s9sjp82nb.jpg</t>
+  </si>
+  <si>
+    <t>MR3TZBKTUWP9</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783016505/oc0vmsfbimbsbncpcauy.jpg</t>
+  </si>
+  <si>
+    <t>MR3TYYIOPINS</t>
+  </si>
+  <si>
+    <t>RUEDA CUJAR ALEXANDER GREGOREVICHS</t>
+  </si>
+  <si>
+    <t>Rechaza esta boleta repetida</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783016518/mzjh72i8twpzuel4nid5.jpg</t>
+  </si>
+  <si>
+    <t>MR3U08UADLQV</t>
+  </si>
+  <si>
+    <t>03:23 p. m.</t>
+  </si>
+  <si>
+    <t>Preferido rebozador era 20 unid no 1, y sin stock 6 preferido pan rallado</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783016548/kcg7jlrr408zzmxiugmq.jpg</t>
+  </si>
+  <si>
+    <t>MR3U284M4A7D</t>
+  </si>
+  <si>
+    <t>1 s stock pañuelo elite</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783016684/rr4tktwt4hztnofv0rcq.jpg</t>
+  </si>
+  <si>
+    <t>MR3U41D5C0W8</t>
+  </si>
+  <si>
+    <t>MR3U55AEOHNV</t>
+  </si>
+  <si>
+    <t>03:26 p. m.</t>
+  </si>
+  <si>
+    <t>Dice que pidió fantoche night , no day</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783016776/ld3zhxxdwd5zhhulvw02.jpg</t>
+  </si>
+  <si>
+    <t>MR3VLA0HQVVN</t>
+  </si>
+  <si>
+    <t>MR3W2F3ZGU5A</t>
+  </si>
+  <si>
+    <t>MR3W6D8AV4II</t>
+  </si>
+  <si>
+    <t>04:23 p. m.</t>
+  </si>
+  <si>
+    <t>GUIRAO LUIS ANTONIO</t>
+  </si>
+  <si>
+    <t>ORDOÑEZ RODRIGUEZ ISMAEL MARTIN</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783020197/snhasmfgsxlnnzsp65cn.jpg</t>
+  </si>
+  <si>
+    <t>MR3XE6ZVEN5O</t>
+  </si>
+  <si>
+    <t>04:57 p. m.</t>
+  </si>
+  <si>
+    <t>4 lays de 40 faltaron</t>
+  </si>
+  <si>
+    <t>MR3XFYRVJ0G9</t>
+  </si>
+  <si>
+    <t>04:58 p. m.</t>
+  </si>
+  <si>
+    <t>CISTERNA DIEGO SEBASTIAN</t>
+  </si>
+  <si>
+    <t>Doritos de 77 falra</t>
+  </si>
+  <si>
+    <t>MR3ZK4N36EPN</t>
+  </si>
+  <si>
+    <t>05:58 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783025898/ejlfj5jnsalk7brd1chh.jpg</t>
+  </si>
+  <si>
+    <t>El cliente va a recibir — seguí viaje</t>
+  </si>
+  <si>
+    <t>MR4W70XULMQF</t>
+  </si>
+  <si>
+    <t>MR4WCRC5PXH5</t>
+  </si>
+  <si>
+    <t>09:16 a. m.</t>
+  </si>
+  <si>
+    <t>Pep rueditas de 120 faltaron 25 und</t>
+  </si>
+  <si>
+    <t>MR4X74Z0ZVOT</t>
+  </si>
+  <si>
+    <t>No quiere está boleta por qué no tiene descuento</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783082374/qvrv8dnoepg7kzxnrb9v.jpg</t>
+  </si>
+  <si>
+    <t>MR4XB3QXH7XK</t>
+  </si>
+  <si>
+    <t>09:42 a. m.</t>
+  </si>
+  <si>
+    <t>El cliente lo espera el día lunes al pedido</t>
+  </si>
+  <si>
+    <t>MR4XD5FRU1MR</t>
+  </si>
+  <si>
+    <t>09:44 a. m.</t>
+  </si>
+  <si>
+    <t>2 fantoche origen</t>
+  </si>
+  <si>
+    <t>MR4XGX4ZE1KU</t>
+  </si>
+  <si>
+    <t>09:47 a. m.</t>
+  </si>
+  <si>
+    <t>Pañuelitos elite</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783082835/x6ohmtlyozslrihk7dee.jpg</t>
+  </si>
+  <si>
+    <t>MR4XJ5BWIKIS</t>
+  </si>
+  <si>
+    <t>09:48 a. m.</t>
+  </si>
+  <si>
+    <t>MR4XPJJM5GWN</t>
+  </si>
+  <si>
+    <t>09:54 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783083241/hzoicsob276baqkgpplx.jpg</t>
+  </si>
+  <si>
+    <t>MR4XVKDJSXUN</t>
+  </si>
+  <si>
+    <t>MR4YLRJJ9352</t>
+  </si>
+  <si>
+    <t>Rechaza twistos</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783084748/xidajtl1qxn0srocxh8y.jpg</t>
+  </si>
+  <si>
+    <t>MR4YOY7GN2O9</t>
+  </si>
+  <si>
+    <t>10:21 a. m.</t>
+  </si>
+  <si>
+    <t>Pidió individuales</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783084883/n2fxfegtpj3ru2cbdwnp.jpg</t>
+  </si>
+  <si>
+    <t>MR4YSF5WYKWS</t>
+  </si>
+  <si>
+    <t>10:24 a. m.</t>
+  </si>
+  <si>
+    <t>Falto 2 chetos 85grs</t>
+  </si>
+  <si>
+    <t>MR4YVZ1TGF9M</t>
+  </si>
+  <si>
+    <t>10:27 a. m.</t>
+  </si>
+  <si>
+    <t>Pidió solo dos twuistos de jamón y dos de queso , rechaza lo otro</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783085218/jjpzfnrt7xyduy9pncuq.jpg</t>
+  </si>
+  <si>
+    <t>MR4YY0U7XD7D</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783085319/bcdvpuecwfgeiojlc55h.jpg</t>
+  </si>
+  <si>
+    <t>MR4Z72NHY32C</t>
+  </si>
+  <si>
+    <t>10:35 a. m.</t>
+  </si>
+  <si>
+    <t>Faltó 2 Cheetos crema 85gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783085735/wlssprnn5ssmfljgkhnu.jpg</t>
+  </si>
+  <si>
+    <t>MR4ZI7EQW4QB</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783086257/g61hnc3pifjlfilaiuug.jpg</t>
+  </si>
+  <si>
+    <t>MR4ZLCK03USL</t>
+  </si>
+  <si>
+    <t>10:46 a. m.</t>
+  </si>
+  <si>
+    <t>Cocinero aceto balsámico di moderna</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783086395/i9afzxndxj9grvskyi2u.jpg</t>
+  </si>
+  <si>
+    <t>MR4ZPM86MD7Q</t>
+  </si>
+  <si>
+    <t>Falta queso y cebolla</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783086598/e9261hq8cjlwnbwp2mgq.jpg</t>
+  </si>
+  <si>
+    <t>MR50HCN0OPAG</t>
+  </si>
+  <si>
+    <t>11:11 a. m.</t>
+  </si>
+  <si>
+    <t>No pidió las de aroz</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783087891/x9b6lfti5um0txisycqn.jpg</t>
+  </si>
+  <si>
+    <t>MR50RKIQGSNC</t>
+  </si>
+  <si>
+    <t>11:19 a. m.</t>
+  </si>
+  <si>
+    <t>Don satur rota se descuenta una sola unidad</t>
+  </si>
+  <si>
+    <t>MR514AJMWT8H</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783088969/ls0ji5reey7fwls4yeql.jpg</t>
+  </si>
+  <si>
+    <t>MR51BD7TNTSS</t>
+  </si>
+  <si>
+    <t>11:35 a. m.</t>
+  </si>
+  <si>
+    <t>Gallo de medio roto no se entrega</t>
+  </si>
+  <si>
+    <t>MR52BNIMKQQ6</t>
+  </si>
+  <si>
+    <t>12:03 p. m.</t>
+  </si>
+  <si>
+    <t>Pañuelo</t>
+  </si>
+  <si>
+    <t>MR52GADET0WD</t>
+  </si>
+  <si>
+    <t>12:07 p. m.</t>
+  </si>
+  <si>
+    <t>Fecha corta</t>
+  </si>
+  <si>
+    <t>MR52WS6RRDMM</t>
+  </si>
+  <si>
+    <t>MR538JLXCREW</t>
+  </si>
+  <si>
+    <t>12:28 p. m.</t>
+  </si>
+  <si>
+    <t>MR539TBALWVU</t>
+  </si>
+  <si>
+    <t>MR53MAEQEC0Z</t>
+  </si>
+  <si>
+    <t>12:39 p. m.</t>
+  </si>
+  <si>
+    <t>Full mani alfajores</t>
+  </si>
+  <si>
+    <t>MR54694R5MSL</t>
+  </si>
+  <si>
+    <t>MR552U3V6VOX</t>
+  </si>
+  <si>
+    <t>01:20 p. m.</t>
+  </si>
+  <si>
+    <t>Caballo de angel</t>
+  </si>
+  <si>
+    <t>MR555OQU9HK1</t>
+  </si>
+  <si>
+    <t>El cliente va a recibir — seguí viaje — Descontar lo que no va. Gracias</t>
+  </si>
+  <si>
+    <t>MR55EE9VXU1U</t>
+  </si>
+  <si>
+    <t>01:29 p. m.</t>
+  </si>
+  <si>
+    <t>Falto 1 serrano 77grs</t>
+  </si>
+  <si>
+    <t>MR565V9U4X50</t>
+  </si>
+  <si>
+    <t>El cliente va a recibir — seguí viaje — Descontar lo que no tiene stock</t>
+  </si>
+  <si>
+    <t>MR56ZK99FUMS</t>
+  </si>
+  <si>
+    <t>Rechaza estas 2 boletas</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783098811/p7svneukppo9gnnnqwhh.jpg</t>
+  </si>
+  <si>
+    <t>MR57QUIQMKNZ</t>
+  </si>
+  <si>
+    <t>MR58256KVYGS</t>
+  </si>
+  <si>
+    <t>MR581WYJOV0Z</t>
+  </si>
+  <si>
+    <t>02:43 p. m.</t>
+  </si>
+  <si>
+    <t>MR58OEDX714Z</t>
+  </si>
+  <si>
+    <t>03:01 p. m.</t>
+  </si>
+  <si>
+    <t>Cerrado por duelo</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783101661/dtedysyrrghw2fmst2ga.jpg</t>
+  </si>
+  <si>
+    <t>MR592KXAR73M</t>
+  </si>
+  <si>
+    <t>MR5A84MCI4HS</t>
+  </si>
+  <si>
+    <t>03:44 p. m.</t>
+  </si>
+  <si>
+    <t>Prueba</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Abre a las 18hs, esperalo 😝</t>
+  </si>
+  <si>
+    <t>MR5A9MJ1S10Q</t>
+  </si>
+  <si>
+    <t>03:45 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783104336/cdgsr9boobhwe3xwgyyd.jpg</t>
+  </si>
+  <si>
+    <t>MR5EUJRKGX5A</t>
+  </si>
+  <si>
+    <t>05:54 p. m.</t>
+  </si>
+  <si>
+    <t>Pidió clásico</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783112030/rollhdnxu0yhhphqboig.jpg</t>
+  </si>
+  <si>
+    <t>MR6B41RHVIAD</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783166216/d1r3dywjxwqwzeqbtwat.jpg</t>
+  </si>
+  <si>
+    <t>MR6B9ELEAL7R</t>
+  </si>
+  <si>
+    <t>09:01 a. m.</t>
+  </si>
+  <si>
+    <t>7 pepas terapin frutos rojos</t>
+  </si>
+  <si>
+    <t>MR6CO0U37QWD</t>
+  </si>
+  <si>
+    <t>Full nani choco 19 und</t>
+  </si>
+  <si>
+    <t>MR6DG8N8T5NS</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783170141/gm8c4dv9xjwojlwobyda.jpg</t>
+  </si>
+  <si>
+    <t>MR6DFMD557AP</t>
+  </si>
+  <si>
+    <t>10:01 a. m.</t>
+  </si>
+  <si>
+    <t>MR6E0I1RU9ZO</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783171083/hquw60j4fsgeztyum4z1.jpg</t>
+  </si>
+  <si>
+    <t>MR6E21UN3RWM</t>
+  </si>
+  <si>
+    <t>MR6E2HT2GVKJ</t>
+  </si>
+  <si>
+    <t>10:19 a. m.</t>
+  </si>
+  <si>
+    <t>MR6EGV8ZJ5AG</t>
+  </si>
+  <si>
+    <t>MR6EIFPT7YXZ</t>
+  </si>
+  <si>
+    <t>10:32 a. m.</t>
+  </si>
+  <si>
+    <t>MR6EMAVR9LGJ</t>
+  </si>
+  <si>
+    <t>Pepas de frutos rojos</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783172111/ch1mg4ftqrbj2tkq3dis.jpg</t>
+  </si>
+  <si>
+    <t>MR6ESY3RVLIB</t>
+  </si>
+  <si>
+    <t>MR6F97WGMBET</t>
+  </si>
+  <si>
+    <t>10:53 a. m.</t>
+  </si>
+  <si>
+    <t>Rechazo Doritos de 40 grs estaban cambiados</t>
+  </si>
+  <si>
+    <t>MR6F9V527U8M</t>
+  </si>
+  <si>
+    <t>10:54 a. m.</t>
+  </si>
+  <si>
+    <t>Fueron 5 Doritos dinamita 45gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783173222/gen7efvocstwxp4ss9xn.jpg</t>
+  </si>
+  <si>
+    <t>Dejá el pedido, lo resuelvo después — Eran dinamita 82g</t>
+  </si>
+  <si>
+    <t>MR6FV7SPQ8ET</t>
+  </si>
+  <si>
+    <t>11:10 a. m.</t>
+  </si>
+  <si>
+    <t>Doritos devuelve no era lo que pidio gramaje</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783174215/zlxhnw6nqgjzodassjzc.jpg</t>
+  </si>
+  <si>
+    <t>MR6GK5QTMLEG</t>
+  </si>
+  <si>
+    <t>MR6GO19M3DKU</t>
+  </si>
+  <si>
+    <t>11:32 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783175542/lftjqnyvc5dm1nxouknc.jpg</t>
+  </si>
+  <si>
+    <t>MR6H2V6V1JKM</t>
+  </si>
+  <si>
+    <t>11:44 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783176235/qrtqq5ribuqnef6jhewm.jpg</t>
+  </si>
+  <si>
+    <t>MR6HYHHYHKAM</t>
+  </si>
+  <si>
+    <t>12:08 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783177711/sk7a8yj6hm2ohhwitvij.jpg</t>
+  </si>
+  <si>
+    <t>MR6JR4DGOOLJ</t>
+  </si>
+  <si>
+    <t>12:59 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783180731/jt2gwe1fhewpixhqqtge.jpg</t>
+  </si>
+  <si>
+    <t>MR6Y1DFG15XK</t>
+  </si>
+  <si>
+    <t>07:39 p. m.</t>
+  </si>
+  <si>
+    <t>Vino tinto sin stock 3 unidades</t>
+  </si>
+  <si>
+    <t>MR7192P77P70</t>
+  </si>
+  <si>
+    <t>09:08 p. m.</t>
+  </si>
+  <si>
+    <t>Falto cheto queso cr</t>
   </si>
 </sst>
 </file>
@@ -1021,8 +1779,8 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1572,10 +2330,10 @@
         <v>37</v>
       </c>
       <c r="J5" s="6"/>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="2">
         <v>46204</v>
       </c>
       <c r="M5" s="3" t="s">
@@ -1803,19 +2561,21 @@
       <c r="G11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="8" t="s">
         <v>42</v>
       </c>
       <c r="I11" s="6"/>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K11" s="3"/>
-      <c r="L11" s="2"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
       <c r="M11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="15"/>
+      <c r="N11" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="12" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -1842,10 +2602,10 @@
       <c r="H12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="9" t="s">
         <v>69</v>
       </c>
       <c r="K12" s="3" t="s">
@@ -1857,7 +2617,9 @@
       <c r="M12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N12" s="15"/>
+      <c r="N12" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="13" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1881,19 +2643,21 @@
       <c r="G13" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="5" t="s">
         <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="2"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
       <c r="M13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="15"/>
+      <c r="N13" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1917,10 +2681,10 @@
       <c r="G14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="3"/>
+      <c r="I14" s="6"/>
       <c r="J14" s="9" t="s">
         <v>76</v>
       </c>
@@ -1933,7 +2697,9 @@
       <c r="M14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N14" s="15"/>
+      <c r="N14" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="15" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1942,7 +2708,7 @@
       <c r="B15" s="2">
         <v>46204</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -1957,10 +2723,10 @@
       <c r="G15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J15" s="6"/>
@@ -1973,7 +2739,9 @@
       <c r="M15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N15" s="15"/>
+      <c r="N15" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="16" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -2000,10 +2768,10 @@
       <c r="H16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="9" t="s">
         <v>84</v>
       </c>
       <c r="K16" s="3" t="s">
@@ -2015,7 +2783,9 @@
       <c r="M16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N16" s="15"/>
+      <c r="N16" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="17" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -2039,7 +2809,7 @@
       <c r="G17" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I17" s="3" t="s">
@@ -2048,16 +2818,18 @@
       <c r="J17" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="2">
         <v>46204</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N17" s="15"/>
+      <c r="N17" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="18" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -2081,10 +2853,10 @@
       <c r="G18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="3" t="s">
         <v>93</v>
       </c>
       <c r="J18" s="6"/>
@@ -2097,7 +2869,9 @@
       <c r="M18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N18" s="15"/>
+      <c r="N18" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="19" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -2121,13 +2895,13 @@
       <c r="G19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="J19" s="9"/>
+      <c r="J19" s="6"/>
       <c r="K19" s="3" t="s">
         <v>26</v>
       </c>
@@ -2137,7 +2911,9 @@
       <c r="M19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N19" s="15"/>
+      <c r="N19" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="20" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -2161,7 +2937,7 @@
       <c r="G20" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="5" t="s">
         <v>24</v>
       </c>
       <c r="I20" s="3" t="s">
@@ -2170,16 +2946,18 @@
       <c r="J20" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="2">
         <v>46204</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N20" s="15"/>
+      <c r="N20" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="21" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -2203,7 +2981,7 @@
       <c r="G21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I21" s="3" t="s">
@@ -2221,7 +2999,9 @@
       <c r="M21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N21" s="15"/>
+      <c r="N21" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="22" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -2245,11 +3025,11 @@
       <c r="G22" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="3"/>
-      <c r="J22" s="6" t="s">
+      <c r="I22" s="6"/>
+      <c r="J22" s="9" t="s">
         <v>106</v>
       </c>
       <c r="K22" s="3" t="s">
@@ -2261,7 +3041,9 @@
       <c r="M22" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N22" s="15"/>
+      <c r="N22" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="23" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -2285,10 +3067,10 @@
       <c r="G23" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="3" t="s">
         <v>111</v>
       </c>
       <c r="J23" s="6"/>
@@ -2301,7 +3083,9 @@
       <c r="M23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N23" s="15"/>
+      <c r="N23" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="24" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -2328,7 +3112,7 @@
       <c r="H24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="3"/>
+      <c r="I24" s="6"/>
       <c r="J24" s="9" t="s">
         <v>113</v>
       </c>
@@ -2341,7 +3125,9 @@
       <c r="M24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N24" s="15"/>
+      <c r="N24" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="25" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -2365,7 +3151,7 @@
       <c r="G25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="3" t="s">
         <v>117</v>
       </c>
       <c r="I25" s="6"/>
@@ -2377,7 +3163,9 @@
       <c r="M25" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N25" s="15"/>
+      <c r="N25" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="26" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -2405,17 +3193,19 @@
         <v>122</v>
       </c>
       <c r="I26" s="6"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="6" t="s">
+      <c r="J26" s="6"/>
+      <c r="K26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L26" s="19">
+      <c r="L26" s="2">
         <v>46204</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N26" s="15"/>
+      <c r="N26" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="27" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -2439,19 +3229,21 @@
       <c r="G27" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="3"/>
+      <c r="I27" s="6"/>
       <c r="J27" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="2"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
       <c r="M27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N27" s="15"/>
+      <c r="N27" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="28" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -2475,21 +3267,23 @@
       <c r="G28" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="10" t="s">
         <v>19</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="J28" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="2"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
       <c r="M28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="15"/>
+      <c r="N28" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="29" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -2513,21 +3307,23 @@
       <c r="G29" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="H29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="3" t="s">
         <v>133</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="K29" s="3"/>
-      <c r="L29" s="2"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
       <c r="M29" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N29" s="15"/>
+      <c r="N29" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="30" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -2551,10 +3347,10 @@
       <c r="G30" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="3" t="s">
         <v>137</v>
       </c>
       <c r="J30" s="9" t="s">
@@ -2569,7 +3365,9 @@
       <c r="M30" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N30" s="15"/>
+      <c r="N30" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="31" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -2593,10 +3391,10 @@
       <c r="G31" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="3"/>
+      <c r="I31" s="6"/>
       <c r="J31" s="9" t="s">
         <v>141</v>
       </c>
@@ -2605,7 +3403,9 @@
       <c r="M31" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N31" s="15"/>
+      <c r="N31" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="32" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -2645,7 +3445,9 @@
       <c r="M32" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N32" s="15"/>
+      <c r="N32" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="33" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -2669,13 +3471,13 @@
       <c r="G33" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="5" t="s">
         <v>24</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J33" s="6" t="s">
+      <c r="J33" s="9" t="s">
         <v>146</v>
       </c>
       <c r="K33" s="3" t="s">
@@ -2687,7 +3489,9 @@
       <c r="M33" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N33" s="15"/>
+      <c r="N33" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="34" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -2717,13 +3521,15 @@
       <c r="I34" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="J34" s="9"/>
+      <c r="J34" s="6"/>
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
       <c r="M34" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N34" s="15"/>
+      <c r="N34" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="35" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -2747,7 +3553,7 @@
       <c r="G35" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I35" s="6"/>
@@ -2763,7 +3569,9 @@
       <c r="M35" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N35" s="15"/>
+      <c r="N35" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="36" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
@@ -2787,23 +3595,25 @@
       <c r="G36" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="8" t="s">
         <v>42</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J36" s="9"/>
-      <c r="K36" s="6" t="s">
+      <c r="J36" s="6"/>
+      <c r="K36" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="L36" s="19">
+      <c r="L36" s="2">
         <v>46204</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N36" s="15"/>
+      <c r="N36" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="37" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
@@ -2827,7 +3637,7 @@
       <c r="G37" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H37" s="5" t="s">
         <v>24</v>
       </c>
       <c r="I37" s="6"/>
@@ -2843,7 +3653,9 @@
       <c r="M37" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N37" s="15"/>
+      <c r="N37" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="38" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -2852,7 +3664,7 @@
       <c r="B38" s="2">
         <v>46204</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -2867,7 +3679,7 @@
       <c r="G38" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H38" s="12" t="s">
+      <c r="H38" s="8" t="s">
         <v>42</v>
       </c>
       <c r="I38" s="3" t="s">
@@ -2881,7 +3693,9 @@
       <c r="M38" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N38" s="15"/>
+      <c r="N38" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="39" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
@@ -2905,10 +3719,10 @@
       <c r="G39" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="H39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="I39" s="3" t="s">
         <v>165</v>
       </c>
       <c r="J39" s="6"/>
@@ -2921,7 +3735,9 @@
       <c r="M39" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N39" s="15"/>
+      <c r="N39" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="40" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -2945,10 +3761,10 @@
       <c r="G40" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H40" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I40" s="3" t="s">
         <v>168</v>
       </c>
       <c r="J40" s="6"/>
@@ -2961,7 +3777,9 @@
       <c r="M40" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N40" s="15"/>
+      <c r="N40" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="41" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -2985,10 +3803,10 @@
       <c r="G41" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H41" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="I41" s="3" t="s">
         <v>171</v>
       </c>
       <c r="J41" s="6"/>
@@ -3001,7 +3819,9 @@
       <c r="M41" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N41" s="15"/>
+      <c r="N41" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="42" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
@@ -3025,21 +3845,23 @@
       <c r="G42" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H42" s="13" t="s">
+      <c r="H42" s="5" t="s">
         <v>24</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="J42" s="6" t="s">
+      <c r="J42" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="K42" s="3"/>
-      <c r="L42" s="2"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
       <c r="M42" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N42" s="15"/>
+      <c r="N42" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="43" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
@@ -3048,7 +3870,7 @@
       <c r="B43" s="2">
         <v>46204</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="3" t="s">
         <v>178</v>
       </c>
       <c r="D43" s="3" t="s">
@@ -3070,12 +3892,14 @@
         <v>179</v>
       </c>
       <c r="J43" s="6"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="2"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
       <c r="M43" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N43" s="15"/>
+      <c r="N43" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="44" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
@@ -3084,7 +3908,7 @@
       <c r="B44" s="2">
         <v>46204</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="3" t="s">
         <v>181</v>
       </c>
       <c r="D44" s="3" t="s">
@@ -3105,7 +3929,7 @@
       <c r="I44" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="J44" s="6" t="s">
+      <c r="J44" s="9" t="s">
         <v>184</v>
       </c>
       <c r="K44" s="3" t="s">
@@ -3117,7 +3941,9 @@
       <c r="M44" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N44" s="15"/>
+      <c r="N44" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="45" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
@@ -3126,7 +3952,7 @@
       <c r="B45" s="2">
         <v>46204</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="3" t="s">
         <v>186</v>
       </c>
       <c r="D45" s="3" t="s">
@@ -3141,21 +3967,23 @@
       <c r="G45" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H45" s="12" t="s">
         <v>110</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J45" s="6" t="s">
+      <c r="J45" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="K45" s="3"/>
-      <c r="L45" s="2"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
       <c r="M45" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N45" s="15"/>
+      <c r="N45" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="46" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
@@ -3179,7 +4007,7 @@
       <c r="G46" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H46" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I46" s="3" t="s">
@@ -3197,7 +4025,9 @@
       <c r="M46" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N46" s="15"/>
+      <c r="N46" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="47" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
@@ -3221,25 +4051,27 @@
       <c r="G47" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="H47" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I47" s="6" t="s">
+      <c r="I47" s="3" t="s">
         <v>197</v>
       </c>
       <c r="J47" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="K47" s="6" t="s">
+      <c r="K47" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L47" s="19">
+      <c r="L47" s="2">
         <v>46205</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N47" s="15"/>
+      <c r="N47" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="48" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
@@ -3263,19 +4095,21 @@
       <c r="G48" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H48" s="5" t="s">
         <v>24</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="J48" s="9"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="2"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
       <c r="M48" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N48" s="15"/>
+      <c r="N48" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="49" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
@@ -3299,10 +4133,10 @@
       <c r="G49" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H49" s="7" t="s">
+      <c r="H49" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I49" s="6" t="s">
+      <c r="I49" s="3" t="s">
         <v>205</v>
       </c>
       <c r="J49" s="9" t="s">
@@ -3317,7 +4151,9 @@
       <c r="M49" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N49" s="15"/>
+      <c r="N49" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="50" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
@@ -3341,11 +4177,11 @@
       <c r="G50" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H50" s="7" t="s">
+      <c r="H50" s="5" t="s">
         <v>24</v>
       </c>
       <c r="I50" s="6"/>
-      <c r="J50" s="9"/>
+      <c r="J50" s="6"/>
       <c r="K50" s="3" t="s">
         <v>32</v>
       </c>
@@ -3355,7 +4191,9 @@
       <c r="M50" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N50" s="15"/>
+      <c r="N50" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="51" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
@@ -3379,21 +4217,23 @@
       <c r="G51" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H51" s="5" t="s">
+      <c r="H51" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I51" s="6" t="s">
+      <c r="I51" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J51" s="6" t="s">
+      <c r="J51" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="K51" s="3"/>
-      <c r="L51" s="2"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
       <c r="M51" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N51" s="15"/>
+      <c r="N51" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="52" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
@@ -3420,16 +4260,18 @@
       <c r="H52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I52" s="6" t="s">
+      <c r="I52" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="J52" s="9"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="2"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
       <c r="M52" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N52" s="15"/>
+      <c r="N52" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="53" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
@@ -3438,7 +4280,7 @@
       <c r="B53" s="2">
         <v>46205</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="3" t="s">
         <v>218</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -3453,13 +4295,13 @@
       <c r="G53" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H53" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I53" s="6" t="s">
+      <c r="I53" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="J53" s="9"/>
+      <c r="J53" s="6"/>
       <c r="K53" s="3" t="s">
         <v>44</v>
       </c>
@@ -3469,7 +4311,9 @@
       <c r="M53" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N53" s="15"/>
+      <c r="N53" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="54" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
@@ -3493,13 +4337,13 @@
       <c r="G54" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H54" s="5" t="s">
+      <c r="H54" s="8" t="s">
         <v>42</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="J54" s="9"/>
+      <c r="J54" s="6"/>
       <c r="K54" s="3" t="s">
         <v>32</v>
       </c>
@@ -3509,7 +4353,9 @@
       <c r="M54" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N54" s="15"/>
+      <c r="N54" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="55" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
@@ -3536,10 +4382,10 @@
       <c r="H55" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I55" s="6" t="s">
+      <c r="I55" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="J55" s="6" t="s">
+      <c r="J55" s="9" t="s">
         <v>225</v>
       </c>
       <c r="K55" s="6"/>
@@ -3547,7 +4393,9 @@
       <c r="M55" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N55" s="15"/>
+      <c r="N55" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="56" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
@@ -3575,13 +4423,15 @@
         <v>110</v>
       </c>
       <c r="I56" s="6"/>
-      <c r="J56" s="9"/>
+      <c r="J56" s="6"/>
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
       <c r="M56" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N56" s="15"/>
+      <c r="N56" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="57" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
@@ -3605,13 +4455,13 @@
       <c r="G57" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="J57" s="6" t="s">
+      <c r="J57" s="9" t="s">
         <v>231</v>
       </c>
       <c r="K57" s="3" t="s">
@@ -3623,7 +4473,9 @@
       <c r="M57" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N57" s="15"/>
+      <c r="N57" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="58" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
@@ -3632,7 +4484,7 @@
       <c r="B58" s="2">
         <v>46205</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="3" t="s">
         <v>234</v>
       </c>
       <c r="D58" s="3" t="s">
@@ -3647,23 +4499,25 @@
       <c r="G58" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="H58" s="5" t="s">
+      <c r="H58" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I58" s="6" t="s">
+      <c r="I58" s="3" t="s">
         <v>236</v>
       </c>
       <c r="J58" s="6"/>
-      <c r="K58" s="6" t="s">
+      <c r="K58" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L58" s="19">
+      <c r="L58" s="2">
         <v>46205</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N58" s="15"/>
+      <c r="N58" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="59" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
@@ -3690,14 +4544,16 @@
       <c r="H59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I59" s="3"/>
-      <c r="J59" s="9"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="2"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
       <c r="M59" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N59" s="15"/>
+      <c r="N59" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="60" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
@@ -3706,7 +4562,7 @@
       <c r="B60" s="2">
         <v>46205</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="3" t="s">
         <v>240</v>
       </c>
       <c r="D60" s="3" t="s">
@@ -3724,16 +4580,18 @@
       <c r="H60" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I60" s="6" t="s">
+      <c r="I60" s="3" t="s">
         <v>241</v>
       </c>
       <c r="J60" s="6"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="2"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
       <c r="M60" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N60" s="15"/>
+      <c r="N60" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="61" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
@@ -3757,19 +4615,21 @@
       <c r="G61" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H61" s="12" t="s">
+      <c r="H61" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I61" s="6" t="s">
+      <c r="I61" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="J61" s="9"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="2"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
       <c r="M61" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N61" s="15"/>
+      <c r="N61" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="62" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
@@ -3793,17 +4653,19 @@
       <c r="G62" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="H62" s="8" t="s">
         <v>42</v>
       </c>
       <c r="I62" s="6"/>
-      <c r="J62" s="9"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="2"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
       <c r="M62" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N62" s="15"/>
+      <c r="N62" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="63" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
@@ -3827,17 +4689,23 @@
       <c r="G63" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H63" s="8" t="s">
+      <c r="H63" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="I63" s="3"/>
-      <c r="J63" s="9"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="2"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="L63" s="2">
+        <v>46205</v>
+      </c>
       <c r="M63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N63" s="15"/>
+        <v>27</v>
+      </c>
+      <c r="N63" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="64" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
@@ -3861,1667 +4729,4159 @@
       <c r="G64" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="H64" s="12" t="s">
+      <c r="H64" s="8" t="s">
         <v>42</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="J64" s="9"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="2"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L64" s="2">
+        <v>46205</v>
+      </c>
       <c r="M64" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N64" s="15"/>
+        <v>27</v>
+      </c>
+      <c r="N64" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="65" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="3"/>
+      <c r="A65" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F65" s="4">
+        <v>1988</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="J65" s="6"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="2"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="15"/>
+      <c r="K65" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L65" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N65" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="66" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="5"/>
+      <c r="A66" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B66" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="4">
+        <v>6642</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="2"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="15"/>
+      <c r="K66" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L66" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N66" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="67" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="1"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="3"/>
+      <c r="A67" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B67" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F67" s="4">
+        <v>4853</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H67" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>257</v>
+      </c>
       <c r="J67" s="6"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="2"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="15"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N67" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="68" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="11"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="6"/>
+      <c r="A68" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="4">
+        <v>6589</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="J68" s="6"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="15"/>
+      <c r="K68" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L68" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N68" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="69" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="8"/>
+      <c r="A69" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B69" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F69" s="4">
+        <v>7438</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="I69" s="6"/>
-      <c r="J69" s="9"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="2"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="15"/>
+      <c r="J69" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N69" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="70" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="1"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="5"/>
+      <c r="A70" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B70" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C70" s="11">
+        <v>0.54513888888888884</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F70" s="4">
+        <v>5453</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="2"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="15"/>
+      <c r="K70" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L70" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N70" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="71" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="1"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="9"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="15"/>
+      <c r="A71" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B71" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F71" s="4">
+        <v>3674</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L71" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N71" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="72" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="1"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="9"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="15"/>
+      <c r="A72" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C72" s="11">
+        <v>0.56111111111111112</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F72" s="4">
+        <v>5424</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N72" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="73" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="1"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="9"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="15"/>
+      <c r="A73" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B73" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F73" s="4">
+        <v>6855</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="J73" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N73" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="74" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="1"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="9"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="15"/>
+      <c r="A74" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B74" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C74" s="11">
+        <v>0.56736111111111109</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F74" s="4">
+        <v>5425</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N74" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="75" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="1"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="10"/>
-      <c r="I75" s="3"/>
-      <c r="J75" s="9"/>
+      <c r="A75" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B75" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F75" s="4">
+        <v>6887</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="15"/>
+      <c r="M75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N75" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="76" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="9"/>
+      <c r="A76" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B76" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F76" s="4">
+        <v>6867</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="J76" s="9" t="s">
+        <v>281</v>
+      </c>
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="15"/>
+      <c r="M76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N76" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="77" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="3"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="2"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="15"/>
+      <c r="A77" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B77" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F77" s="4">
+        <v>6869</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="J77" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+      <c r="M77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N77" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="78" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="3"/>
-      <c r="J78" s="9"/>
-      <c r="K78" s="3"/>
-      <c r="L78" s="2"/>
-      <c r="M78" s="3"/>
-      <c r="N78" s="15"/>
+      <c r="A78" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B78" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C78" s="11">
+        <v>0.5805555555555556</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F78" s="4">
+        <v>7481</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H78" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N78" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="79" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="3"/>
+      <c r="A79" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B79" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C79" s="11">
+        <v>0.58750000000000002</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F79" s="4">
+        <v>5445</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I79" s="6"/>
       <c r="J79" s="6"/>
-      <c r="K79" s="3"/>
-      <c r="L79" s="2"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="15"/>
+      <c r="K79" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L79" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N79" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="80" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="3"/>
-      <c r="H80" s="12"/>
-      <c r="I80" s="3"/>
-      <c r="J80" s="9"/>
-      <c r="K80" s="3"/>
-      <c r="L80" s="2"/>
-      <c r="M80" s="3"/>
-      <c r="N80" s="15"/>
+      <c r="A80" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B80" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C80" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F80" s="4">
+        <v>5151</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I80" s="6"/>
+      <c r="J80" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L80" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N80" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="81" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="1"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="13"/>
+      <c r="A81" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B81" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C81" s="11">
+        <v>0.61319444444444449</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F81" s="4">
+        <v>5471</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I81" s="6"/>
       <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
-      <c r="M81" s="3"/>
-      <c r="N81" s="15"/>
+      <c r="K81" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L81" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N81" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="82" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="1"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="5"/>
-      <c r="I82" s="3"/>
+      <c r="A82" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B82" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C82" s="11">
+        <v>0.61597222222222225</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F82" s="4">
+        <v>5454</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H82" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I82" s="6"/>
       <c r="J82" s="6"/>
-      <c r="K82" s="3"/>
-      <c r="L82" s="2"/>
-      <c r="M82" s="3"/>
-      <c r="N82" s="15"/>
+      <c r="K82" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L82" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N82" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="83" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="1"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="7"/>
+      <c r="A83" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B83" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F83" s="4">
+        <v>4236</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I83" s="6"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="3"/>
-      <c r="L83" s="2"/>
-      <c r="M83" s="3"/>
-      <c r="N83" s="15"/>
+      <c r="J83" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L83" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N83" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="84" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="1"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="11"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="7"/>
+      <c r="A84" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B84" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F84" s="4">
+        <v>6874</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H84" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="3"/>
-      <c r="L84" s="2"/>
-      <c r="M84" s="3"/>
-      <c r="N84" s="15"/>
+      <c r="J84" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
+      <c r="M84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N84" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="85" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="1"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="7"/>
+      <c r="A85" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B85" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F85" s="4">
+        <v>6874</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I85" s="6"/>
-      <c r="J85" s="6"/>
+      <c r="J85" s="9" t="s">
+        <v>301</v>
+      </c>
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
-      <c r="M85" s="3"/>
-      <c r="N85" s="15"/>
+      <c r="M85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N85" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="86" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="1"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="6"/>
-      <c r="J86" s="9"/>
+      <c r="A86" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B86" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C86" s="11">
+        <v>0.64027777777777772</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F86" s="4">
+        <v>5122</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H86" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>305</v>
+      </c>
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
-      <c r="M86" s="3"/>
-      <c r="N86" s="15"/>
+      <c r="M86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N86" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="87" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="1"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="11"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="6"/>
+      <c r="A87" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B87" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F87" s="4">
+        <v>6350</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>309</v>
+      </c>
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
-      <c r="M87" s="3"/>
-      <c r="N87" s="15"/>
+      <c r="M87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N87" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="88" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="1"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="3"/>
-      <c r="J88" s="9"/>
-      <c r="K88" s="3"/>
-      <c r="L88" s="2"/>
-      <c r="M88" s="3"/>
-      <c r="N88" s="15"/>
+      <c r="A88" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B88" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F88" s="4">
+        <v>6350</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
+      <c r="M88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N88" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="89" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="1"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="11"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="5"/>
-      <c r="I89" s="3"/>
-      <c r="J89" s="9"/>
-      <c r="K89" s="3"/>
-      <c r="L89" s="2"/>
-      <c r="M89" s="3"/>
-      <c r="N89" s="15"/>
+      <c r="A89" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B89" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F89" s="4">
+        <v>6334</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
+      <c r="M89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N89" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="90" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="1"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="11"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="5"/>
-      <c r="I90" s="3"/>
-      <c r="J90" s="9"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="2"/>
-      <c r="M90" s="3"/>
-      <c r="N90" s="15"/>
+      <c r="A90" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B90" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C90" s="11">
+        <v>0.64236111111111116</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F90" s="4">
+        <v>4526</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L90" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N90" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="91" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="1"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="6"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="2"/>
-      <c r="M91" s="3"/>
-      <c r="N91" s="15"/>
+      <c r="A91" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B91" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F91" s="4">
+        <v>6884</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N91" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="92" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="1"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="5"/>
+      <c r="A92" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B92" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C92" s="11">
+        <v>0.67152777777777772</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F92" s="4">
+        <v>4558</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="I92" s="6"/>
-      <c r="J92" s="9"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="2"/>
-      <c r="M92" s="3"/>
-      <c r="N92" s="15"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="6"/>
+      <c r="M92" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N92" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="93" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="11"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="8"/>
+      <c r="A93" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B93" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C93" s="11">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F93" s="4">
+        <v>4539</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="I93" s="6"/>
       <c r="J93" s="6"/>
-      <c r="K93" s="3"/>
-      <c r="L93" s="2"/>
-      <c r="M93" s="3"/>
-      <c r="N93" s="15"/>
+      <c r="K93" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L93" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M93" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N93" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="94" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="3"/>
-      <c r="H94" s="7"/>
+      <c r="A94" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B94" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C94" s="11">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F94" s="4">
+        <v>4539</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="I94" s="6"/>
-      <c r="J94" s="9"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
-      <c r="M94" s="3"/>
-      <c r="N94" s="15"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L94" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N94" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="95" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="1"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="8"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="9"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="2"/>
-      <c r="M95" s="3"/>
-      <c r="N95" s="15"/>
+      <c r="A95" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B95" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F95" s="4">
+        <v>10886</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I95" s="6"/>
+      <c r="J95" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="K95" s="6"/>
+      <c r="L95" s="6"/>
+      <c r="M95" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N95" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="96" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="1"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="12"/>
+      <c r="A96" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B96" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F96" s="4">
+        <v>10886</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="I96" s="6"/>
-      <c r="J96" s="9"/>
+      <c r="J96" s="9" t="s">
+        <v>324</v>
+      </c>
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
-      <c r="M96" s="3"/>
-      <c r="N96" s="15"/>
+      <c r="M96" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N96" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="97" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="1"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="8"/>
-      <c r="I97" s="3"/>
+      <c r="A97" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B97" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F97" s="4">
+        <v>4807</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>327</v>
+      </c>
       <c r="J97" s="6"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="2"/>
-      <c r="M97" s="3"/>
-      <c r="N97" s="15"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N97" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="98" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="1"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="3"/>
-      <c r="H98" s="8"/>
-      <c r="I98" s="3"/>
+      <c r="A98" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B98" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F98" s="4">
+        <v>5102</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>331</v>
+      </c>
       <c r="J98" s="6"/>
-      <c r="K98" s="6"/>
-      <c r="L98" s="6"/>
-      <c r="M98" s="3"/>
-      <c r="N98" s="15"/>
+      <c r="K98" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L98" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N98" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="99" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="1"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="3"/>
-      <c r="H99" s="13"/>
-      <c r="I99" s="3"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="3"/>
-      <c r="L99" s="2"/>
-      <c r="M99" s="3"/>
-      <c r="N99" s="15"/>
+      <c r="A99" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B99" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F99" s="4">
+        <v>1319</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H99" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I99" s="6"/>
+      <c r="J99" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="L99" s="2">
+        <v>46205</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N99" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="100" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="1"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="3"/>
-      <c r="H100" s="13"/>
-      <c r="I100" s="3"/>
+      <c r="A100" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B100" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C100" s="11">
+        <v>0.38263888888888886</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F100" s="4">
+        <v>4032</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I100" s="6"/>
       <c r="J100" s="6"/>
-      <c r="K100" s="3"/>
-      <c r="L100" s="2"/>
-      <c r="M100" s="3"/>
-      <c r="N100" s="15"/>
+      <c r="K100" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L100" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N100" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="101" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="1"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="11"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="3"/>
-      <c r="H101" s="5"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="9"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="2"/>
-      <c r="M101" s="3"/>
-      <c r="N101" s="15"/>
+      <c r="A101" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B101" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F101" s="4">
+        <v>6526</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H101" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J101" s="6"/>
+      <c r="K101" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L101" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N101" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="102" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="1"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="11"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="3"/>
-      <c r="H102" s="7"/>
-      <c r="I102" s="3"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="6"/>
-      <c r="M102" s="3"/>
-      <c r="N102" s="15"/>
+      <c r="A102" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B102" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F102" s="4">
+        <v>3455</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H102" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J102" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L102" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N102" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="103" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="1"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="5"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="9"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="2"/>
-      <c r="M103" s="3"/>
-      <c r="N103" s="15"/>
+      <c r="A103" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B103" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F103" s="4">
+        <v>3455</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H103" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J103" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="K103" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L103" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M103" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N103" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="104" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="1"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="3"/>
-      <c r="H104" s="8"/>
-      <c r="I104" s="3"/>
-      <c r="J104" s="9"/>
-      <c r="K104" s="3"/>
-      <c r="L104" s="2"/>
-      <c r="M104" s="3"/>
-      <c r="N104" s="15"/>
+      <c r="A104" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B104" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F104" s="4">
+        <v>3802</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H104" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
+      <c r="M104" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N104" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="105" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="1"/>
-      <c r="B105" s="2"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-      <c r="F105" s="4"/>
-      <c r="G105" s="3"/>
-      <c r="H105" s="8"/>
-      <c r="I105" s="3"/>
-      <c r="J105" s="9"/>
-      <c r="K105" s="6"/>
-      <c r="L105" s="6"/>
-      <c r="M105" s="3"/>
-      <c r="N105" s="15"/>
+      <c r="A105" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B105" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F105" s="4">
+        <v>1599</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="J105" s="6"/>
+      <c r="K105" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L105" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M105" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N105" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="106" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="1"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="3"/>
-      <c r="H106" s="10"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="9"/>
-      <c r="K106" s="3"/>
-      <c r="L106" s="2"/>
-      <c r="M106" s="3"/>
-      <c r="N106" s="15"/>
+      <c r="A106" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B106" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F106" s="4">
+        <v>11243</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="J106" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L106" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M106" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N106" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="107" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="1"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="3"/>
-      <c r="H107" s="12"/>
+      <c r="A107" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B107" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F107" s="4">
+        <v>3825</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H107" s="13" t="s">
+        <v>122</v>
+      </c>
       <c r="I107" s="6"/>
-      <c r="J107" s="9"/>
+      <c r="J107" s="6"/>
       <c r="K107" s="6"/>
       <c r="L107" s="6"/>
-      <c r="M107" s="3"/>
-      <c r="N107" s="15"/>
+      <c r="M107" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N107" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="108" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="1"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="3"/>
-      <c r="H108" s="10"/>
-      <c r="I108" s="3"/>
-      <c r="J108" s="6"/>
-      <c r="K108" s="3"/>
-      <c r="L108" s="2"/>
-      <c r="M108" s="3"/>
-      <c r="N108" s="15"/>
+      <c r="A108" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B108" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F108" s="4">
+        <v>1852</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I108" s="6"/>
+      <c r="J108" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
+      <c r="M108" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N108" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="109" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="1"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="4"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="10"/>
-      <c r="I109" s="3"/>
-      <c r="J109" s="9"/>
-      <c r="K109" s="3"/>
-      <c r="L109" s="2"/>
-      <c r="M109" s="3"/>
-      <c r="N109" s="15"/>
+      <c r="A109" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B109" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C109" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F109" s="4">
+        <v>4318</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H109" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I109" s="6"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L109" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M109" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N109" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="110" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="1"/>
-      <c r="B110" s="2"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="4"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="7"/>
+      <c r="A110" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B110" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C110" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F110" s="4">
+        <v>4318</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H110" s="12" t="s">
+        <v>110</v>
+      </c>
       <c r="I110" s="6"/>
-      <c r="J110" s="9"/>
-      <c r="K110" s="3"/>
-      <c r="L110" s="2"/>
-      <c r="M110" s="3"/>
-      <c r="N110" s="15"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L110" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M110" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N110" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="111" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="1"/>
-      <c r="B111" s="2"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="4"/>
-      <c r="G111" s="3"/>
-      <c r="H111" s="5"/>
-      <c r="I111" s="6"/>
-      <c r="J111" s="9"/>
-      <c r="K111" s="3"/>
-      <c r="L111" s="2"/>
-      <c r="M111" s="3"/>
-      <c r="N111" s="15"/>
+      <c r="A111" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B111" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C111" s="11">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F111" s="4">
+        <v>4772</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H111" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J111" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="K111" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="L111" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M111" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N111" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="112" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="1"/>
-      <c r="B112" s="2"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
-      <c r="F112" s="4"/>
-      <c r="G112" s="3"/>
-      <c r="H112" s="10"/>
-      <c r="I112" s="3"/>
-      <c r="J112" s="9"/>
-      <c r="K112" s="3"/>
-      <c r="L112" s="2"/>
-      <c r="M112" s="3"/>
-      <c r="N112" s="15"/>
+      <c r="A112" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B112" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F112" s="4">
+        <v>4885</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H112" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="J112" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="K112" s="6"/>
+      <c r="L112" s="6"/>
+      <c r="M112" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N112" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="113" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="1"/>
-      <c r="B113" s="2"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-      <c r="F113" s="4"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="5"/>
-      <c r="I113" s="6"/>
-      <c r="J113" s="9"/>
-      <c r="K113" s="3"/>
-      <c r="L113" s="2"/>
-      <c r="M113" s="3"/>
-      <c r="N113" s="15"/>
+      <c r="A113" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B113" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F113" s="4">
+        <v>1404</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H113" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J113" s="6"/>
+      <c r="K113" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L113" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M113" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N113" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="114" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="1"/>
-      <c r="B114" s="2"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="4"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="12"/>
-      <c r="I114" s="3"/>
-      <c r="J114" s="9"/>
-      <c r="K114" s="3"/>
-      <c r="L114" s="2"/>
-      <c r="M114" s="3"/>
-      <c r="N114" s="15"/>
+      <c r="A114" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B114" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F114" s="4">
+        <v>4301</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H114" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="J114" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="K114" s="6"/>
+      <c r="L114" s="6"/>
+      <c r="M114" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N114" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="115" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="1"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-      <c r="F115" s="4"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="8"/>
-      <c r="I115" s="3"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="3"/>
-      <c r="L115" s="2"/>
-      <c r="M115" s="3"/>
-      <c r="N115" s="15"/>
+      <c r="A115" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B115" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C115" s="11">
+        <v>0.43611111111111112</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F115" s="4">
+        <v>3733</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I115" s="6"/>
+      <c r="J115" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="K115" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L115" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M115" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N115" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="116" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="1"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="4"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="12"/>
-      <c r="I116" s="3"/>
-      <c r="J116" s="9"/>
-      <c r="K116" s="3"/>
-      <c r="L116" s="2"/>
-      <c r="M116" s="3"/>
-      <c r="N116" s="15"/>
+      <c r="A116" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B116" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F116" s="4">
+        <v>10741</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="J116" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="K116" s="6"/>
+      <c r="L116" s="6"/>
+      <c r="M116" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N116" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="117" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="1"/>
-      <c r="B117" s="2"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="F117" s="4"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="5"/>
+      <c r="A117" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B117" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C117" s="11">
+        <v>0.44722222222222224</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F117" s="4">
+        <v>3718</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I117" s="6"/>
-      <c r="J117" s="9"/>
-      <c r="K117" s="3"/>
-      <c r="L117" s="2"/>
-      <c r="M117" s="3"/>
-      <c r="N117" s="15"/>
+      <c r="J117" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="K117" s="6"/>
+      <c r="L117" s="6"/>
+      <c r="M117" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N117" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="118" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="1"/>
-      <c r="B118" s="2"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="4"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="8"/>
-      <c r="I118" s="3"/>
-      <c r="J118" s="9"/>
-      <c r="K118" s="3"/>
-      <c r="L118" s="2"/>
-      <c r="M118" s="3"/>
-      <c r="N118" s="15"/>
+      <c r="A118" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B118" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F118" s="4">
+        <v>7248</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H118" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="J118" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="K118" s="6"/>
+      <c r="L118" s="6"/>
+      <c r="M118" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N118" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="119" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="1"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-      <c r="F119" s="4"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="8"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="9"/>
-      <c r="K119" s="3"/>
-      <c r="L119" s="2"/>
-      <c r="M119" s="3"/>
-      <c r="N119" s="15"/>
+      <c r="A119" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B119" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C119" s="11">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F119" s="4">
+        <v>3738</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H119" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J119" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="K119" s="6"/>
+      <c r="L119" s="6"/>
+      <c r="M119" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N119" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="120" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="1"/>
-      <c r="B120" s="2"/>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
-      <c r="F120" s="4"/>
-      <c r="G120" s="3"/>
-      <c r="H120" s="10"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="9"/>
-      <c r="K120" s="3"/>
-      <c r="L120" s="2"/>
-      <c r="M120" s="3"/>
-      <c r="N120" s="15"/>
+      <c r="A120" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B120" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F120" s="4">
+        <v>4902</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H120" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="J120" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="K120" s="6"/>
+      <c r="L120" s="6"/>
+      <c r="M120" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N120" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="121" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="1"/>
-      <c r="B121" s="2"/>
-      <c r="C121" s="11"/>
-      <c r="D121" s="3"/>
-      <c r="E121" s="3"/>
-      <c r="F121" s="4"/>
-      <c r="G121" s="3"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="6"/>
-      <c r="J121" s="9"/>
-      <c r="K121" s="6"/>
-      <c r="L121" s="6"/>
-      <c r="M121" s="3"/>
-      <c r="N121" s="15"/>
+      <c r="A121" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B121" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F121" s="4">
+        <v>5825</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H121" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="J121" s="6"/>
+      <c r="K121" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L121" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M121" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N121" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="122" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="1"/>
-      <c r="B122" s="2"/>
-      <c r="C122" s="11"/>
-      <c r="D122" s="3"/>
-      <c r="E122" s="3"/>
-      <c r="F122" s="4"/>
-      <c r="G122" s="3"/>
-      <c r="H122" s="8"/>
-      <c r="I122" s="3"/>
-      <c r="J122" s="6"/>
-      <c r="K122" s="6"/>
-      <c r="L122" s="6"/>
-      <c r="M122" s="3"/>
-      <c r="N122" s="15"/>
+      <c r="A122" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B122" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F122" s="4">
+        <v>2842</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I122" s="6"/>
+      <c r="J122" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="K122" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L122" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M122" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N122" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="123" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="1"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="3"/>
-      <c r="D123" s="3"/>
-      <c r="E123" s="3"/>
-      <c r="F123" s="4"/>
-      <c r="G123" s="3"/>
-      <c r="H123" s="8"/>
-      <c r="I123" s="3"/>
+      <c r="A123" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B123" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F123" s="4">
+        <v>6417</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H123" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>399</v>
+      </c>
       <c r="J123" s="6"/>
-      <c r="K123" s="3"/>
-      <c r="L123" s="2"/>
-      <c r="M123" s="3"/>
-      <c r="N123" s="15"/>
+      <c r="K123" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L123" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M123" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N123" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="124" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="1"/>
-      <c r="B124" s="2"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="3"/>
-      <c r="E124" s="3"/>
-      <c r="F124" s="4"/>
-      <c r="G124" s="3"/>
-      <c r="H124" s="13"/>
-      <c r="I124" s="6"/>
-      <c r="J124" s="9"/>
-      <c r="K124" s="3"/>
-      <c r="L124" s="2"/>
-      <c r="M124" s="3"/>
-      <c r="N124" s="15"/>
+      <c r="A124" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B124" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F124" s="4">
+        <v>6417</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H124" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="J124" s="6"/>
+      <c r="K124" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L124" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M124" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N124" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="125" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="1"/>
-      <c r="B125" s="2"/>
-      <c r="C125" s="3"/>
-      <c r="D125" s="3"/>
-      <c r="E125" s="3"/>
-      <c r="F125" s="4"/>
-      <c r="G125" s="3"/>
-      <c r="H125" s="5"/>
-      <c r="I125" s="6"/>
+      <c r="A125" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B125" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F125" s="4">
+        <v>4591</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H125" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>402</v>
+      </c>
       <c r="J125" s="6"/>
-      <c r="K125" s="3"/>
-      <c r="L125" s="2"/>
-      <c r="M125" s="3"/>
-      <c r="N125" s="15"/>
+      <c r="K125" s="6"/>
+      <c r="L125" s="6"/>
+      <c r="M125" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N125" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="126" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="1"/>
-      <c r="B126" s="2"/>
-      <c r="C126" s="11"/>
-      <c r="D126" s="3"/>
-      <c r="E126" s="3"/>
-      <c r="F126" s="4"/>
-      <c r="G126" s="3"/>
-      <c r="H126" s="5"/>
-      <c r="I126" s="3"/>
+      <c r="A126" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B126" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F126" s="4">
+        <v>2086</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H126" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>405</v>
+      </c>
       <c r="J126" s="6"/>
-      <c r="K126" s="3"/>
-      <c r="L126" s="2"/>
-      <c r="M126" s="3"/>
-      <c r="N126" s="15"/>
+      <c r="K126" s="6"/>
+      <c r="L126" s="6"/>
+      <c r="M126" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N126" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="127" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="1"/>
-      <c r="B127" s="2"/>
-      <c r="C127" s="3"/>
-      <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
-      <c r="F127" s="4"/>
-      <c r="G127" s="3"/>
-      <c r="H127" s="5"/>
-      <c r="I127" s="3"/>
+      <c r="A127" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B127" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C127" s="11">
+        <v>0.5131944444444444</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F127" s="4">
+        <v>4015</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H127" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I127" s="6"/>
       <c r="J127" s="6"/>
-      <c r="K127" s="6"/>
-      <c r="L127" s="6"/>
-      <c r="M127" s="3"/>
-      <c r="N127" s="15"/>
+      <c r="K127" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L127" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M127" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N127" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="128" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="1"/>
-      <c r="B128" s="2"/>
-      <c r="C128" s="3"/>
-      <c r="D128" s="3"/>
-      <c r="E128" s="3"/>
-      <c r="F128" s="4"/>
-      <c r="G128" s="3"/>
-      <c r="H128" s="8"/>
+      <c r="A128" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B128" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F128" s="4">
+        <v>5213</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H128" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I128" s="6"/>
-      <c r="J128" s="9"/>
-      <c r="K128" s="3"/>
-      <c r="L128" s="2"/>
-      <c r="M128" s="3"/>
-      <c r="N128" s="15"/>
+      <c r="J128" s="6"/>
+      <c r="K128" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L128" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M128" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N128" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="129" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="1"/>
-      <c r="B129" s="2"/>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
-      <c r="F129" s="4"/>
-      <c r="G129" s="3"/>
-      <c r="H129" s="5"/>
+      <c r="A129" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B129" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C129" s="11">
+        <v>0.52013888888888893</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F129" s="4">
+        <v>3435</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H129" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="I129" s="6"/>
-      <c r="J129" s="9"/>
+      <c r="J129" s="6"/>
       <c r="K129" s="6"/>
       <c r="L129" s="6"/>
-      <c r="M129" s="3"/>
-      <c r="N129" s="15"/>
+      <c r="M129" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N129" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="130" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="1"/>
-      <c r="B130" s="2"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="3"/>
-      <c r="E130" s="3"/>
-      <c r="F130" s="4"/>
-      <c r="G130" s="3"/>
-      <c r="H130" s="10"/>
-      <c r="I130" s="3"/>
+      <c r="A130" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B130" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F130" s="19">
+        <v>11335</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H130" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>412</v>
+      </c>
       <c r="J130" s="6"/>
-      <c r="K130" s="3"/>
-      <c r="L130" s="2"/>
-      <c r="M130" s="3"/>
-      <c r="N130" s="15"/>
+      <c r="K130" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L130" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M130" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N130" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="131" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="1"/>
-      <c r="B131" s="2"/>
-      <c r="C131" s="3"/>
-      <c r="D131" s="3"/>
-      <c r="E131" s="3"/>
-      <c r="F131" s="4"/>
-      <c r="G131" s="3"/>
-      <c r="H131" s="10"/>
-      <c r="I131" s="3"/>
+      <c r="A131" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B131" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F131" s="4">
+        <v>11245</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H131" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I131" s="6"/>
       <c r="J131" s="6"/>
-      <c r="K131" s="3"/>
-      <c r="L131" s="2"/>
-      <c r="M131" s="3"/>
-      <c r="N131" s="15"/>
+      <c r="K131" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L131" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M131" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N131" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="132" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="1"/>
-      <c r="B132" s="2"/>
-      <c r="C132" s="3"/>
-      <c r="D132" s="3"/>
-      <c r="E132" s="3"/>
-      <c r="F132" s="4"/>
-      <c r="G132" s="3"/>
-      <c r="H132" s="8"/>
-      <c r="I132" s="3"/>
-      <c r="J132" s="9"/>
+      <c r="A132" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B132" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F132" s="4">
+        <v>4583</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H132" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="J132" s="6"/>
       <c r="K132" s="6"/>
       <c r="L132" s="6"/>
-      <c r="M132" s="3"/>
-      <c r="N132" s="15"/>
+      <c r="M132" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N132" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="133" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="1"/>
-      <c r="B133" s="2"/>
-      <c r="C133" s="3"/>
-      <c r="D133" s="3"/>
-      <c r="E133" s="3"/>
-      <c r="F133" s="4"/>
-      <c r="G133" s="3"/>
-      <c r="H133" s="10"/>
-      <c r="I133" s="3"/>
+      <c r="A133" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B133" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C133" s="11">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F133" s="4">
+        <v>7236</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H133" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I133" s="6"/>
       <c r="J133" s="6"/>
-      <c r="K133" s="3"/>
-      <c r="L133" s="2"/>
-      <c r="M133" s="3"/>
-      <c r="N133" s="15"/>
+      <c r="K133" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="L133" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M133" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N133" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="134" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="1"/>
-      <c r="B134" s="2"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="3"/>
-      <c r="E134" s="3"/>
-      <c r="F134" s="4"/>
-      <c r="G134" s="3"/>
-      <c r="H134" s="7"/>
-      <c r="I134" s="3"/>
-      <c r="J134" s="9"/>
-      <c r="K134" s="3"/>
-      <c r="L134" s="2"/>
-      <c r="M134" s="3"/>
-      <c r="N134" s="15"/>
+      <c r="A134" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B134" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F134" s="4">
+        <v>1735</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H134" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="J134" s="6"/>
+      <c r="K134" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L134" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M134" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N134" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="135" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="1"/>
-      <c r="B135" s="2"/>
-      <c r="C135" s="3"/>
-      <c r="D135" s="3"/>
-      <c r="E135" s="3"/>
-      <c r="F135" s="4"/>
-      <c r="G135" s="3"/>
-      <c r="H135" s="10"/>
-      <c r="I135" s="3"/>
-      <c r="J135" s="9"/>
-      <c r="K135" s="6"/>
-      <c r="L135" s="6"/>
-      <c r="M135" s="3"/>
-      <c r="N135" s="15"/>
+      <c r="A135" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B135" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C135" s="11">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F135" s="4">
+        <v>7227</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H135" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I135" s="6"/>
+      <c r="J135" s="6"/>
+      <c r="K135" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="L135" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M135" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N135" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="136" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="1"/>
-      <c r="B136" s="2"/>
-      <c r="C136" s="3"/>
-      <c r="D136" s="3"/>
-      <c r="E136" s="3"/>
-      <c r="F136" s="4"/>
-      <c r="G136" s="3"/>
-      <c r="H136" s="5"/>
-      <c r="I136" s="3"/>
-      <c r="J136" s="9"/>
-      <c r="K136" s="3"/>
-      <c r="L136" s="2"/>
-      <c r="M136" s="3"/>
-      <c r="N136" s="15"/>
+      <c r="A136" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B136" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C136" s="11">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F136" s="4">
+        <v>3718</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="J136" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="K136" s="6"/>
+      <c r="L136" s="6"/>
+      <c r="M136" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N136" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="137" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="1"/>
-      <c r="B137" s="2"/>
-      <c r="C137" s="3"/>
-      <c r="D137" s="3"/>
-      <c r="E137" s="3"/>
-      <c r="F137" s="4"/>
-      <c r="G137" s="3"/>
-      <c r="H137" s="5"/>
-      <c r="I137" s="3"/>
+      <c r="A137" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B137" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C137" s="11">
+        <v>0.6069444444444444</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F137" s="4">
+        <v>6673</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I137" s="6"/>
       <c r="J137" s="6"/>
-      <c r="K137" s="3"/>
-      <c r="L137" s="2"/>
-      <c r="M137" s="3"/>
-      <c r="N137" s="15"/>
+      <c r="K137" s="6"/>
+      <c r="L137" s="6"/>
+      <c r="M137" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N137" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="138" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="1"/>
-      <c r="B138" s="2"/>
-      <c r="C138" s="3"/>
-      <c r="D138" s="3"/>
-      <c r="E138" s="3"/>
-      <c r="F138" s="4"/>
-      <c r="G138" s="3"/>
-      <c r="H138" s="5"/>
+      <c r="A138" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B138" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C138" s="11">
+        <v>0.61319444444444449</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F138" s="4">
+        <v>4017</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I138" s="6"/>
       <c r="J138" s="6"/>
-      <c r="K138" s="6"/>
-      <c r="L138" s="6"/>
-      <c r="M138" s="3"/>
-      <c r="N138" s="15"/>
+      <c r="K138" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L138" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M138" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N138" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="139" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="1"/>
-      <c r="B139" s="2"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="3"/>
-      <c r="E139" s="3"/>
-      <c r="F139" s="4"/>
-      <c r="G139" s="3"/>
-      <c r="H139" s="5"/>
-      <c r="I139" s="3"/>
+      <c r="A139" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B139" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F139" s="4">
+        <v>6380</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H139" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I139" s="6"/>
       <c r="J139" s="6"/>
-      <c r="K139" s="3"/>
-      <c r="L139" s="2"/>
-      <c r="M139" s="3"/>
-      <c r="N139" s="15"/>
+      <c r="K139" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L139" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M139" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N139" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="140" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="1"/>
-      <c r="B140" s="2"/>
-      <c r="C140" s="3"/>
-      <c r="D140" s="3"/>
-      <c r="E140" s="3"/>
-      <c r="F140" s="4"/>
-      <c r="G140" s="3"/>
-      <c r="H140" s="5"/>
-      <c r="I140" s="6"/>
-      <c r="J140" s="9"/>
-      <c r="K140" s="3"/>
-      <c r="L140" s="2"/>
-      <c r="M140" s="3"/>
-      <c r="N140" s="15"/>
+      <c r="A140" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B140" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F140" s="4">
+        <v>6666</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H140" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="J140" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="K140" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L140" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M140" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N140" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="141" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="1"/>
-      <c r="B141" s="2"/>
-      <c r="C141" s="3"/>
-      <c r="D141" s="3"/>
-      <c r="E141" s="3"/>
-      <c r="F141" s="4"/>
-      <c r="G141" s="3"/>
-      <c r="H141" s="5"/>
-      <c r="I141" s="3"/>
+      <c r="A141" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B141" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C141" s="11">
+        <v>0.63402777777777775</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F141" s="4">
+        <v>4296</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H141" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I141" s="6"/>
       <c r="J141" s="6"/>
-      <c r="K141" s="6"/>
-      <c r="L141" s="6"/>
-      <c r="M141" s="3"/>
-      <c r="N141" s="15"/>
+      <c r="K141" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L141" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M141" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N141" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="142" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="1"/>
-      <c r="B142" s="2"/>
-      <c r="C142" s="3"/>
-      <c r="D142" s="3"/>
-      <c r="E142" s="3"/>
-      <c r="F142" s="4"/>
-      <c r="G142" s="3"/>
-      <c r="H142" s="10"/>
-      <c r="I142" s="3"/>
-      <c r="J142" s="9"/>
-      <c r="K142" s="3"/>
-      <c r="L142" s="2"/>
-      <c r="M142" s="3"/>
-      <c r="N142" s="15"/>
+      <c r="A142" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B142" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F142" s="4">
+        <v>33333</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H142" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="J142" s="6"/>
+      <c r="K142" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="L142" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M142" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N142" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="143" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="1"/>
-      <c r="B143" s="2"/>
-      <c r="C143" s="3"/>
-      <c r="D143" s="3"/>
-      <c r="E143" s="3"/>
-      <c r="F143" s="4"/>
-      <c r="G143" s="3"/>
-      <c r="H143" s="7"/>
+      <c r="A143" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B143" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F143" s="4">
+        <v>7519</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I143" s="6"/>
-      <c r="J143" s="9"/>
-      <c r="K143" s="6"/>
-      <c r="L143" s="6"/>
-      <c r="M143" s="3"/>
-      <c r="N143" s="15"/>
+      <c r="J143" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="K143" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L143" s="2">
+        <v>46206</v>
+      </c>
+      <c r="M143" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N143" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="144" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="1"/>
-      <c r="B144" s="2"/>
-      <c r="C144" s="3"/>
-      <c r="D144" s="3"/>
-      <c r="E144" s="3"/>
-      <c r="F144" s="4"/>
-      <c r="G144" s="3"/>
-      <c r="H144" s="5"/>
-      <c r="I144" s="3"/>
-      <c r="J144" s="9"/>
+      <c r="A144" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B144" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F144" s="4">
+        <v>1881</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H144" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="J144" s="9" t="s">
+        <v>446</v>
+      </c>
       <c r="K144" s="6"/>
       <c r="L144" s="6"/>
-      <c r="M144" s="3"/>
-      <c r="N144" s="15"/>
+      <c r="M144" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N144" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="145" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="1"/>
-      <c r="B145" s="2"/>
-      <c r="C145" s="3"/>
-      <c r="D145" s="3"/>
-      <c r="E145" s="3"/>
-      <c r="F145" s="4"/>
-      <c r="G145" s="3"/>
-      <c r="H145" s="13"/>
-      <c r="I145" s="3"/>
-      <c r="J145" s="9"/>
-      <c r="K145" s="3"/>
-      <c r="L145" s="2"/>
-      <c r="M145" s="3"/>
-      <c r="N145" s="15"/>
+      <c r="A145" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B145" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C145" s="11">
+        <v>0.37291666666666667</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F145" s="4">
+        <v>4054</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H145" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I145" s="6"/>
+      <c r="J145" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="K145" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L145" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M145" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N145" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="146" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="1"/>
-      <c r="B146" s="2"/>
-      <c r="C146" s="3"/>
-      <c r="D146" s="3"/>
-      <c r="E146" s="3"/>
-      <c r="F146" s="4"/>
-      <c r="G146" s="3"/>
-      <c r="H146" s="7"/>
-      <c r="I146" s="3"/>
+      <c r="A146" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B146" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F146" s="4">
+        <v>4398</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H146" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>451</v>
+      </c>
       <c r="J146" s="6"/>
-      <c r="K146" s="3"/>
-      <c r="L146" s="2"/>
-      <c r="M146" s="3"/>
-      <c r="N146" s="15"/>
+      <c r="K146" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L146" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M146" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N146" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="147" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="1"/>
-      <c r="B147" s="2"/>
-      <c r="C147" s="3"/>
-      <c r="D147" s="3"/>
-      <c r="E147" s="3"/>
-      <c r="F147" s="4"/>
-      <c r="G147" s="3"/>
-      <c r="H147" s="8"/>
-      <c r="I147" s="3"/>
-      <c r="J147" s="9"/>
-      <c r="K147" s="3"/>
-      <c r="L147" s="2"/>
-      <c r="M147" s="3"/>
-      <c r="N147" s="15"/>
+      <c r="A147" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B147" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F147" s="4">
+        <v>4663</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H147" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="J147" s="6"/>
+      <c r="K147" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L147" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M147" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N147" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="148" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="1"/>
-      <c r="B148" s="2"/>
-      <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
-      <c r="E148" s="3"/>
-      <c r="F148" s="4"/>
-      <c r="G148" s="3"/>
-      <c r="H148" s="5"/>
-      <c r="I148" s="3"/>
-      <c r="J148" s="6"/>
-      <c r="K148" s="3"/>
-      <c r="L148" s="2"/>
-      <c r="M148" s="3"/>
-      <c r="N148" s="15"/>
+      <c r="A148" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B148" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F148" s="4">
+        <v>3215</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H148" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I148" s="6"/>
+      <c r="J148" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="K148" s="6"/>
+      <c r="L148" s="6"/>
+      <c r="M148" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N148" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="149" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="1"/>
-      <c r="B149" s="2"/>
-      <c r="C149" s="3"/>
-      <c r="D149" s="3"/>
-      <c r="E149" s="3"/>
-      <c r="F149" s="4"/>
-      <c r="G149" s="3"/>
-      <c r="H149" s="5"/>
+      <c r="A149" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B149" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F149" s="4">
+        <v>4057</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>19</v>
+      </c>
       <c r="I149" s="6"/>
-      <c r="J149" s="9"/>
-      <c r="K149" s="3"/>
-      <c r="L149" s="2"/>
-      <c r="M149" s="3"/>
-      <c r="N149" s="15"/>
+      <c r="J149" s="6"/>
+      <c r="K149" s="6"/>
+      <c r="L149" s="6"/>
+      <c r="M149" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N149" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="150" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="1"/>
-      <c r="B150" s="2"/>
-      <c r="C150" s="3"/>
-      <c r="D150" s="3"/>
-      <c r="E150" s="3"/>
-      <c r="F150" s="4"/>
-      <c r="G150" s="3"/>
-      <c r="H150" s="5"/>
+      <c r="A150" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B150" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C150" s="11">
+        <v>0.42916666666666664</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F150" s="4">
+        <v>4061</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I150" s="6"/>
-      <c r="J150" s="9"/>
-      <c r="K150" s="3"/>
-      <c r="L150" s="2"/>
-      <c r="M150" s="3"/>
-      <c r="N150" s="15"/>
+      <c r="J150" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="K150" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L150" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M150" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N150" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="151" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="1"/>
-      <c r="B151" s="2"/>
-      <c r="C151" s="3"/>
-      <c r="D151" s="3"/>
-      <c r="E151" s="3"/>
-      <c r="F151" s="4"/>
-      <c r="G151" s="3"/>
-      <c r="H151" s="3"/>
-      <c r="I151" s="3"/>
-      <c r="J151" s="9"/>
-      <c r="K151" s="3"/>
-      <c r="L151" s="2"/>
-      <c r="M151" s="3"/>
-      <c r="N151" s="15"/>
+      <c r="A151" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B151" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C151" s="11">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F151" s="4">
+        <v>4404</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H151" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I151" s="6"/>
+      <c r="J151" s="6"/>
+      <c r="K151" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L151" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M151" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N151" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="152" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="1"/>
-      <c r="B152" s="2"/>
-      <c r="C152" s="3"/>
-      <c r="D152" s="3"/>
-      <c r="E152" s="3"/>
-      <c r="F152" s="4"/>
-      <c r="G152" s="3"/>
-      <c r="H152" s="8"/>
-      <c r="I152" s="3"/>
-      <c r="J152" s="9"/>
-      <c r="K152" s="3"/>
-      <c r="L152" s="2"/>
-      <c r="M152" s="3"/>
-      <c r="N152" s="15"/>
+      <c r="A152" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B152" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F152" s="4">
+        <v>4049</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I152" s="6"/>
+      <c r="J152" s="6"/>
+      <c r="K152" s="6"/>
+      <c r="L152" s="6"/>
+      <c r="M152" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N152" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="153" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="1"/>
-      <c r="B153" s="2"/>
-      <c r="C153" s="3"/>
-      <c r="D153" s="3"/>
-      <c r="E153" s="3"/>
-      <c r="F153" s="4"/>
-      <c r="G153" s="3"/>
-      <c r="H153" s="8"/>
-      <c r="I153" s="3"/>
-      <c r="J153" s="9"/>
-      <c r="K153" s="3"/>
-      <c r="L153" s="2"/>
-      <c r="M153" s="3"/>
-      <c r="N153" s="15"/>
+      <c r="A153" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B153" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C153" s="11">
+        <v>0.43819444444444444</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F153" s="4">
+        <v>3532</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="H153" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I153" s="6"/>
+      <c r="J153" s="6"/>
+      <c r="K153" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L153" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M153" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N153" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="154" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="1"/>
-      <c r="B154" s="2"/>
-      <c r="C154" s="3"/>
-      <c r="D154" s="3"/>
-      <c r="E154" s="3"/>
-      <c r="F154" s="4"/>
-      <c r="G154" s="3"/>
-      <c r="H154" s="8"/>
+      <c r="A154" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B154" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F154" s="4">
+        <v>4680</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H154" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I154" s="6"/>
-      <c r="J154" s="9"/>
-      <c r="K154" s="3"/>
-      <c r="L154" s="2"/>
-      <c r="M154" s="3"/>
-      <c r="N154" s="15"/>
+      <c r="J154" s="6"/>
+      <c r="K154" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L154" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M154" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N154" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="155" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="1"/>
-      <c r="B155" s="2"/>
-      <c r="C155" s="3"/>
-      <c r="D155" s="3"/>
-      <c r="E155" s="3"/>
-      <c r="F155" s="4"/>
-      <c r="G155" s="3"/>
-      <c r="H155" s="5"/>
-      <c r="I155" s="6"/>
-      <c r="J155" s="9"/>
-      <c r="K155" s="3"/>
-      <c r="L155" s="2"/>
-      <c r="M155" s="3"/>
-      <c r="N155" s="15"/>
+      <c r="A155" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B155" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F155" s="4">
+        <v>7100</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H155" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="J155" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="K155" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L155" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M155" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N155" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="156" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="1"/>
-      <c r="B156" s="2"/>
-      <c r="C156" s="3"/>
-      <c r="D156" s="3"/>
-      <c r="E156" s="3"/>
-      <c r="F156" s="4"/>
-      <c r="G156" s="3"/>
-      <c r="H156" s="12"/>
-      <c r="I156" s="3"/>
-      <c r="J156" s="9"/>
-      <c r="K156" s="3"/>
-      <c r="L156" s="2"/>
-      <c r="M156" s="3"/>
-      <c r="N156" s="15"/>
+      <c r="A156" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B156" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C156" s="11">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F156" s="4">
+        <v>4419</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H156" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I156" s="6"/>
+      <c r="J156" s="6"/>
+      <c r="K156" s="6"/>
+      <c r="L156" s="6"/>
+      <c r="M156" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N156" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="157" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="1"/>
-      <c r="B157" s="2"/>
-      <c r="C157" s="3"/>
-      <c r="D157" s="3"/>
-      <c r="E157" s="3"/>
-      <c r="F157" s="4"/>
-      <c r="G157" s="3"/>
-      <c r="H157" s="5"/>
-      <c r="I157" s="3"/>
+      <c r="A157" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B157" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F157" s="4">
+        <v>11106</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H157" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>472</v>
+      </c>
       <c r="J157" s="6"/>
-      <c r="K157" s="3"/>
-      <c r="L157" s="2"/>
-      <c r="M157" s="3"/>
-      <c r="N157" s="15"/>
+      <c r="K157" s="6"/>
+      <c r="L157" s="6"/>
+      <c r="M157" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N157" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="158" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="1"/>
-      <c r="B158" s="2"/>
-      <c r="C158" s="11"/>
-      <c r="D158" s="3"/>
-      <c r="E158" s="3"/>
-      <c r="F158" s="4"/>
-      <c r="G158" s="3"/>
-      <c r="H158" s="5"/>
-      <c r="I158" s="3"/>
-      <c r="J158" s="6"/>
-      <c r="K158" s="3"/>
-      <c r="L158" s="2"/>
-      <c r="M158" s="3"/>
-      <c r="N158" s="15"/>
+      <c r="A158" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B158" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F158" s="4">
+        <v>2466</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H158" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="J158" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="K158" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="L158" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M158" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N158" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="159" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="1"/>
-      <c r="B159" s="2"/>
-      <c r="C159" s="11"/>
-      <c r="D159" s="3"/>
-      <c r="E159" s="3"/>
-      <c r="F159" s="4"/>
-      <c r="G159" s="3"/>
-      <c r="H159" s="5"/>
-      <c r="I159" s="6"/>
-      <c r="J159" s="9"/>
-      <c r="K159" s="3"/>
-      <c r="L159" s="2"/>
-      <c r="M159" s="3"/>
-      <c r="N159" s="15"/>
+      <c r="A159" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B159" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F159" s="4">
+        <v>2466</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H159" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="J159" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="K159" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="L159" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M159" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N159" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="160" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="1"/>
-      <c r="B160" s="2"/>
-      <c r="C160" s="3"/>
-      <c r="D160" s="3"/>
-      <c r="E160" s="3"/>
-      <c r="F160" s="4"/>
-      <c r="G160" s="3"/>
-      <c r="H160" s="7"/>
-      <c r="I160" s="3"/>
-      <c r="J160" s="9"/>
-      <c r="K160" s="3"/>
-      <c r="L160" s="2"/>
-      <c r="M160" s="3"/>
-      <c r="N160" s="15"/>
+      <c r="A160" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B160" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F160" s="4">
+        <v>7434</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H160" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="J160" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="K160" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L160" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M160" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N160" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="161" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="1"/>
-      <c r="B161" s="2"/>
-      <c r="C161" s="3"/>
-      <c r="D161" s="3"/>
-      <c r="E161" s="3"/>
-      <c r="F161" s="4"/>
-      <c r="G161" s="3"/>
-      <c r="H161" s="8"/>
-      <c r="I161" s="3"/>
-      <c r="J161" s="9"/>
-      <c r="K161" s="3"/>
-      <c r="L161" s="2"/>
-      <c r="M161" s="3"/>
-      <c r="N161" s="15"/>
+      <c r="A161" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B161" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C161" s="11">
+        <v>0.47847222222222224</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F161" s="4">
+        <v>5296</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H161" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I161" s="6"/>
+      <c r="J161" s="6"/>
+      <c r="K161" s="6"/>
+      <c r="L161" s="6"/>
+      <c r="M161" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N161" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="162" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="1"/>
-      <c r="B162" s="2"/>
-      <c r="C162" s="3"/>
-      <c r="D162" s="3"/>
-      <c r="E162" s="3"/>
-      <c r="F162" s="4"/>
-      <c r="G162" s="3"/>
-      <c r="H162" s="5"/>
+      <c r="A162" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B162" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F162" s="4">
+        <v>4804</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H162" s="13" t="s">
+        <v>122</v>
+      </c>
       <c r="I162" s="6"/>
-      <c r="J162" s="9"/>
+      <c r="J162" s="9" t="s">
+        <v>485</v>
+      </c>
       <c r="K162" s="6"/>
       <c r="L162" s="6"/>
-      <c r="M162" s="3"/>
-      <c r="N162" s="15"/>
+      <c r="M162" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N162" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="163" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="1"/>
-      <c r="B163" s="2"/>
-      <c r="C163" s="3"/>
-      <c r="D163" s="3"/>
-      <c r="E163" s="3"/>
-      <c r="F163" s="4"/>
-      <c r="G163" s="3"/>
-      <c r="H163" s="8"/>
-      <c r="I163" s="3"/>
-      <c r="J163" s="6"/>
-      <c r="K163" s="3"/>
-      <c r="L163" s="2"/>
-      <c r="M163" s="3"/>
-      <c r="N163" s="15"/>
+      <c r="A163" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B163" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F163" s="4">
+        <v>11296</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H163" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I163" s="6"/>
+      <c r="J163" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="K163" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L163" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M163" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N163" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="164" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="1"/>
-      <c r="B164" s="2"/>
-      <c r="C164" s="3"/>
-      <c r="D164" s="3"/>
-      <c r="E164" s="3"/>
-      <c r="F164" s="4"/>
-      <c r="G164" s="3"/>
-      <c r="H164" s="5"/>
-      <c r="I164" s="3"/>
-      <c r="J164" s="9"/>
-      <c r="K164" s="3"/>
-      <c r="L164" s="2"/>
-      <c r="M164" s="3"/>
-      <c r="N164" s="15"/>
+      <c r="A164" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B164" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F164" s="4">
+        <v>4358</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H164" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I164" s="6"/>
+      <c r="J164" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="K164" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L164" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M164" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N164" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="165" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="1"/>
-      <c r="B165" s="2"/>
-      <c r="C165" s="3"/>
-      <c r="D165" s="3"/>
-      <c r="E165" s="3"/>
-      <c r="F165" s="4"/>
-      <c r="G165" s="3"/>
-      <c r="H165" s="12"/>
-      <c r="I165" s="3"/>
-      <c r="J165" s="9"/>
-      <c r="K165" s="3"/>
-      <c r="L165" s="2"/>
-      <c r="M165" s="3"/>
-      <c r="N165" s="15"/>
+      <c r="A165" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B165" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F165" s="4">
+        <v>7042</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H165" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I165" s="6"/>
+      <c r="J165" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="K165" s="6"/>
+      <c r="L165" s="6"/>
+      <c r="M165" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N165" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="166" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="1"/>
-      <c r="B166" s="2"/>
-      <c r="C166" s="11"/>
-      <c r="D166" s="3"/>
-      <c r="E166" s="3"/>
-      <c r="F166" s="4"/>
-      <c r="G166" s="3"/>
-      <c r="H166" s="8"/>
-      <c r="I166" s="3"/>
+      <c r="A166" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B166" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F166" s="4">
+        <v>5238</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H166" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>497</v>
+      </c>
       <c r="J166" s="6"/>
-      <c r="K166" s="6"/>
-      <c r="L166" s="6"/>
-      <c r="M166" s="3"/>
-      <c r="N166" s="15"/>
+      <c r="K166" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L166" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M166" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N166" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="167" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="1"/>
-      <c r="B167" s="2"/>
-      <c r="C167" s="3"/>
-      <c r="D167" s="3"/>
-      <c r="E167" s="3"/>
-      <c r="F167" s="4"/>
-      <c r="G167" s="3"/>
-      <c r="H167" s="7"/>
-      <c r="I167" s="6"/>
-      <c r="J167" s="9"/>
-      <c r="K167" s="3"/>
-      <c r="L167" s="2"/>
-      <c r="M167" s="3"/>
-      <c r="N167" s="15"/>
+      <c r="A167" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B167" s="2">
+        <v>46207</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F167" s="4">
+        <v>4051</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="H167" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="J167" s="6"/>
+      <c r="K167" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L167" s="2">
+        <v>46207</v>
+      </c>
+      <c r="M167" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N167" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="168" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
@@ -22180,10 +25540,89 @@
       <c r="N1208" s="15"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J8" r:id="rId1" xr:uid="{07918FA9-C77F-4A0C-A261-32EA059DA0D6}"/>
+    <hyperlink ref="J10" r:id="rId2" xr:uid="{35079F5D-7D33-44B3-94FE-4188725A197D}"/>
+    <hyperlink ref="J11" r:id="rId3" xr:uid="{DA6C8A57-8132-4DE2-B2A9-7176EDB1F816}"/>
+    <hyperlink ref="J12" r:id="rId4" xr:uid="{3EDE3F6A-6B4D-4235-8A35-DBEDB74A5918}"/>
+    <hyperlink ref="J14" r:id="rId5" xr:uid="{29D3EE15-31AC-4155-ABAB-EB406BD6BD8A}"/>
+    <hyperlink ref="J16" r:id="rId6" xr:uid="{BD6CACFF-3D91-434A-99A8-163D74D57DBE}"/>
+    <hyperlink ref="J17" r:id="rId7" xr:uid="{EE85335E-6866-4D4E-830E-9D27AFA9010C}"/>
+    <hyperlink ref="J20" r:id="rId8" xr:uid="{FB423B8C-E97E-46AD-ACBE-42B2504A28F7}"/>
+    <hyperlink ref="J21" r:id="rId9" xr:uid="{66DD1FFC-C94E-4236-A940-B6F31430B612}"/>
+    <hyperlink ref="J22" r:id="rId10" xr:uid="{1E613827-4FCC-4341-96EB-5D75AAA8D325}"/>
+    <hyperlink ref="J24" r:id="rId11" xr:uid="{859ECDA1-F495-4C68-890B-82EECD178CFC}"/>
+    <hyperlink ref="J25" r:id="rId12" xr:uid="{A43EAACF-743A-4206-BE2A-98AD0FD19FDD}"/>
+    <hyperlink ref="J27" r:id="rId13" xr:uid="{8BF84E77-A726-43FE-8021-2FB32D28CDDD}"/>
+    <hyperlink ref="J28" r:id="rId14" xr:uid="{5A39B5F3-9142-465C-889E-4A1778D6F8C4}"/>
+    <hyperlink ref="J29" r:id="rId15" xr:uid="{B619E563-2B5D-4FC5-AC01-F7C7CD180168}"/>
+    <hyperlink ref="J30" r:id="rId16" xr:uid="{FF4B135C-1C7A-44B5-980D-7FE349CEA3A5}"/>
+    <hyperlink ref="J31" r:id="rId17" xr:uid="{332DDA28-6D46-4758-89B5-A4F7EFA2F21C}"/>
+    <hyperlink ref="J33" r:id="rId18" xr:uid="{6B47C7E7-F6DE-40A2-953A-5D3A250BCAC4}"/>
+    <hyperlink ref="J35" r:id="rId19" xr:uid="{736679CF-9406-4348-9191-CF491DA34D5A}"/>
+    <hyperlink ref="J37" r:id="rId20" xr:uid="{F3C3279E-F984-4128-9B04-1E0CA2E1A16B}"/>
+    <hyperlink ref="J38" r:id="rId21" xr:uid="{4E52841B-1C43-4BFA-889F-41A6EAD2CED7}"/>
+    <hyperlink ref="J42" r:id="rId22" xr:uid="{306ACF3D-EF52-46EC-8395-6B713C9EBDD0}"/>
+    <hyperlink ref="J44" r:id="rId23" xr:uid="{A43C8C69-4B58-4963-965D-E1DA4725AA64}"/>
+    <hyperlink ref="J45" r:id="rId24" xr:uid="{B0DF4654-38F7-4DE6-92C1-6625E3E261E4}"/>
+    <hyperlink ref="J46" r:id="rId25" xr:uid="{AF776FAE-83F4-4AA6-B7C8-DB625CD9D8CE}"/>
+    <hyperlink ref="J47" r:id="rId26" xr:uid="{93ECE2C3-D4DB-4093-8283-0851C6BCB32D}"/>
+    <hyperlink ref="J49" r:id="rId27" xr:uid="{6F980D43-01A8-43EC-88A7-361DACC9F3E8}"/>
+    <hyperlink ref="J51" r:id="rId28" xr:uid="{69775998-231B-49CD-AC85-C92F5E54BD69}"/>
+    <hyperlink ref="J55" r:id="rId29" xr:uid="{8F1C941E-EC0A-4464-8BBB-A7AE5069B4C2}"/>
+    <hyperlink ref="J57" r:id="rId30" xr:uid="{E1C79454-F315-4ADA-9471-658319D1F847}"/>
+    <hyperlink ref="J69" r:id="rId31" xr:uid="{6AC0113D-4799-4C79-B05B-04F1751CC8AF}"/>
+    <hyperlink ref="J71" r:id="rId32" xr:uid="{B29B16B9-4CD2-4A8C-974A-B4E6189353F2}"/>
+    <hyperlink ref="J73" r:id="rId33" xr:uid="{4E68FAF7-A264-4BF6-988D-C6C7F0D2EF91}"/>
+    <hyperlink ref="J76" r:id="rId34" xr:uid="{022A00ED-75F3-4919-9964-877CFF9723D4}"/>
+    <hyperlink ref="J77" r:id="rId35" xr:uid="{D1607EC8-A6E9-4AE4-B69D-77BEC8D1E34D}"/>
+    <hyperlink ref="J78" r:id="rId36" xr:uid="{23982911-83FD-4E42-B8D5-1E68E24F643D}"/>
+    <hyperlink ref="J80" r:id="rId37" xr:uid="{84CDF53D-142E-4AD3-ACCA-885D455FBF98}"/>
+    <hyperlink ref="J83" r:id="rId38" xr:uid="{9E641901-6AE0-4D2F-A23A-098F89E0E198}"/>
+    <hyperlink ref="J84" r:id="rId39" xr:uid="{EC6218D3-4042-4770-BC03-3F1A48A2C0CA}"/>
+    <hyperlink ref="J85" r:id="rId40" xr:uid="{3D5EDB0E-253F-4B75-B39F-B06DCB4FF516}"/>
+    <hyperlink ref="J86" r:id="rId41" xr:uid="{312E8B1F-F690-4680-8E94-2A90AC6F4A86}"/>
+    <hyperlink ref="J87" r:id="rId42" xr:uid="{C271801F-D585-4682-9878-A49CCD99634A}"/>
+    <hyperlink ref="J88" r:id="rId43" xr:uid="{8E8B84E2-5707-49CC-9597-7C03E5EDF7A2}"/>
+    <hyperlink ref="J89" r:id="rId44" xr:uid="{4F727DAA-9547-43F8-87EB-E3D9636526CB}"/>
+    <hyperlink ref="J91" r:id="rId45" xr:uid="{9A999195-6202-4A84-908C-8D187D906BAF}"/>
+    <hyperlink ref="J95" r:id="rId46" xr:uid="{ED642DC3-8708-40BB-BB17-1BC4563347C7}"/>
+    <hyperlink ref="J96" r:id="rId47" xr:uid="{17B1B02F-4AEA-4542-8A55-758BFD09DFC7}"/>
+    <hyperlink ref="J99" r:id="rId48" xr:uid="{3C8A43BA-80BE-4357-8994-50EBC52C6D0E}"/>
+    <hyperlink ref="J102" r:id="rId49" xr:uid="{83D31369-D31D-4A0D-85FC-646E48816E2D}"/>
+    <hyperlink ref="J103" r:id="rId50" xr:uid="{827B1BBC-D430-4EE3-B331-8059CB346965}"/>
+    <hyperlink ref="J106" r:id="rId51" xr:uid="{1B677242-6767-45BE-9801-039A287F14F9}"/>
+    <hyperlink ref="J108" r:id="rId52" xr:uid="{B79DC16D-5AA9-409E-9D16-775E0EC47C99}"/>
+    <hyperlink ref="J111" r:id="rId53" xr:uid="{354A16A1-10B6-41F9-B45A-C247ABD06B93}"/>
+    <hyperlink ref="J112" r:id="rId54" xr:uid="{C4DD775A-FBF3-4F67-8C80-4E4F1B4B5CBF}"/>
+    <hyperlink ref="J114" r:id="rId55" xr:uid="{F90B5C1D-EE1C-4F96-92DB-032930E14517}"/>
+    <hyperlink ref="J115" r:id="rId56" xr:uid="{2F894019-E3D0-4C96-8180-080D16B3957A}"/>
+    <hyperlink ref="J116" r:id="rId57" xr:uid="{B8CF4B31-9B2F-4213-891A-5EF55269F741}"/>
+    <hyperlink ref="J117" r:id="rId58" xr:uid="{C5679E06-BF8C-4975-96E3-9F055537C930}"/>
+    <hyperlink ref="J118" r:id="rId59" xr:uid="{0766EB21-1494-41F0-A8CA-4FB217AFA34B}"/>
+    <hyperlink ref="J119" r:id="rId60" xr:uid="{D696E27C-C4DC-448D-8DE3-E8C5EB803565}"/>
+    <hyperlink ref="J120" r:id="rId61" xr:uid="{38E78744-A3A5-4751-9182-6DDF28DB972D}"/>
+    <hyperlink ref="J122" r:id="rId62" xr:uid="{52F886BD-C7CF-4FBC-A5BB-37DD85082F46}"/>
+    <hyperlink ref="J136" r:id="rId63" xr:uid="{3B6893DC-0BB5-4F2B-B048-2EED1B0E0D23}"/>
+    <hyperlink ref="J140" r:id="rId64" xr:uid="{005A0CE1-1B05-477C-83BF-5383FC5F1620}"/>
+    <hyperlink ref="J143" r:id="rId65" xr:uid="{72625D25-94F0-4B93-AD04-F89DF769E82B}"/>
+    <hyperlink ref="J144" r:id="rId66" xr:uid="{F7EF2183-3458-4B88-AFE2-32C1054C6352}"/>
+    <hyperlink ref="J145" r:id="rId67" xr:uid="{9E9BACB0-0146-4162-813F-1D26D3D5B352}"/>
+    <hyperlink ref="J148" r:id="rId68" xr:uid="{16B31D15-A07C-4F6C-A6F8-AF1C4F867071}"/>
+    <hyperlink ref="J150" r:id="rId69" xr:uid="{D073D596-F32E-4F7E-9F41-F77CFED1F249}"/>
+    <hyperlink ref="J155" r:id="rId70" xr:uid="{AF7CA951-9505-4089-866B-3F1DA08F1C7B}"/>
+    <hyperlink ref="J158" r:id="rId71" xr:uid="{436A729E-76E4-4751-B4B3-927F8254455C}"/>
+    <hyperlink ref="J159" r:id="rId72" xr:uid="{E0786708-2D29-4B31-968B-D431BD74F2E2}"/>
+    <hyperlink ref="J160" r:id="rId73" xr:uid="{73F7FB3F-1222-4BF4-B3CA-32FEC1279432}"/>
+    <hyperlink ref="J162" r:id="rId74" xr:uid="{2E719EAE-32B3-43B3-95EB-23F49789DA1A}"/>
+    <hyperlink ref="J163" r:id="rId75" xr:uid="{02A10C12-0B29-44AF-832C-6FDE9806B4D2}"/>
+    <hyperlink ref="J164" r:id="rId76" xr:uid="{36B335E9-A9EA-4CFE-B505-D6FAF13F8D3B}"/>
+    <hyperlink ref="J165" r:id="rId77" xr:uid="{B84175AE-4A85-4206-A17F-6434C9525B30}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId78"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId79"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD9A0DE-D56B-41B8-A4CC-DD216A2FB2CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2E0954-2355-4B5B-9F9E-D0A81CD0258F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1732" uniqueCount="607">
   <si>
     <t>Fecha</t>
   </si>
@@ -1540,6 +1540,325 @@
   </si>
   <si>
     <t>Falto cheto queso cr</t>
+  </si>
+  <si>
+    <t>MR9529SN8AOD</t>
+  </si>
+  <si>
+    <t>Falto pep ramita</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783337452/gicuytyogbwdqb6heo8i.jpg</t>
+  </si>
+  <si>
+    <t>MR95IUWE2KT5</t>
+  </si>
+  <si>
+    <t>Super ddl</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783338222/mtagmpxk4tq7uaatentq.jpg</t>
+  </si>
+  <si>
+    <t>MR96EH5W2ELT</t>
+  </si>
+  <si>
+    <t>09:08 a. m.</t>
+  </si>
+  <si>
+    <t>Rechaza papel</t>
+  </si>
+  <si>
+    <t>MR96H1OC2VX3</t>
+  </si>
+  <si>
+    <t>09:10 a. m.</t>
+  </si>
+  <si>
+    <t>Rechaza oeguamar de 450 porque están sin aire las bolsas</t>
+  </si>
+  <si>
+    <t>MR97LSNKW7WS</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783341720/p5tglad1kp227uyyzufv.jpg</t>
+  </si>
+  <si>
+    <t>MR97M29HJD63</t>
+  </si>
+  <si>
+    <t>Codito</t>
+  </si>
+  <si>
+    <t>MR989NCD5JRE</t>
+  </si>
+  <si>
+    <t>10:00 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783342838/e3vool4umk6gkmkpbptu.jpg</t>
+  </si>
+  <si>
+    <t>MR98FJCGEL4G</t>
+  </si>
+  <si>
+    <t>10:05 a. m.</t>
+  </si>
+  <si>
+    <t>Pepas terapin</t>
+  </si>
+  <si>
+    <t>MR98GXBC8O12</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783343171/jmzflecr0xq34qk0iwrt.jpg</t>
+  </si>
+  <si>
+    <t>MR98K9WLFFYS</t>
+  </si>
+  <si>
+    <t>MR98OOZTFO4U</t>
+  </si>
+  <si>
+    <t>10:12 a. m.</t>
+  </si>
+  <si>
+    <t>Rechaza moños y tirabuzón</t>
+  </si>
+  <si>
+    <t>MR98VI0129MG</t>
+  </si>
+  <si>
+    <t>MR991BINIU12</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783344119/kclu64loge3c0gmzhnvg.jpg</t>
+  </si>
+  <si>
+    <t>MR99CVS9OVSJ</t>
+  </si>
+  <si>
+    <t>10:31 a. m.</t>
+  </si>
+  <si>
+    <t>Gelatina</t>
+  </si>
+  <si>
+    <t>MR9A23GTG0SD</t>
+  </si>
+  <si>
+    <t>10:50 a. m.</t>
+  </si>
+  <si>
+    <t>MR9A5V5A78WT</t>
+  </si>
+  <si>
+    <t>MR9AILCL6TPY</t>
+  </si>
+  <si>
+    <t>11:03 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783346610/v7mcytvagswmktxtxhiu.jpg</t>
+  </si>
+  <si>
+    <t>MR9AIU0EHSUG</t>
+  </si>
+  <si>
+    <t>Dirección incorrecta o insuficiente</t>
+  </si>
+  <si>
+    <t>MR9B9W2T6Q95</t>
+  </si>
+  <si>
+    <t>MR9BJ812YXGR</t>
+  </si>
+  <si>
+    <t>MR9BQ98GJ3CV</t>
+  </si>
+  <si>
+    <t>11:37 a. m.</t>
+  </si>
+  <si>
+    <t>Bizcocheulo de los Mon roto devuelve una sola unidad</t>
+  </si>
+  <si>
+    <t>MR9BW9FEQ4YF</t>
+  </si>
+  <si>
+    <t>Favorita bisc</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783348966/sa1utzuycbfx1ijnjj9l.jpg</t>
+  </si>
+  <si>
+    <t>MR9C9GQ3GLKK</t>
+  </si>
+  <si>
+    <t>11:52 a. m.</t>
+  </si>
+  <si>
+    <t>Faltaron 5 Doritos de 40 grs</t>
+  </si>
+  <si>
+    <t>MR9E2VX5ZT8B</t>
+  </si>
+  <si>
+    <t>MR9E3EE4R1BE</t>
+  </si>
+  <si>
+    <t>Full mani</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783352618/ktzoz5bzzjn9uhhfn3kc.jpg</t>
+  </si>
+  <si>
+    <t>MR9EY7IJA1R4</t>
+  </si>
+  <si>
+    <t>01:08 p. m.</t>
+  </si>
+  <si>
+    <t>No pidió pilas</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783354057/tfcfrcq3mvbwnnmnr873.jpg</t>
+  </si>
+  <si>
+    <t>MR9FBRR83KRG</t>
+  </si>
+  <si>
+    <t>01:18 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783354694/rmnf4eir0yq6lvcdjzrd.jpg</t>
+  </si>
+  <si>
+    <t>MR9FCYTEEKHO</t>
+  </si>
+  <si>
+    <t>01:19 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783354748/vartlaldxr8rfa723xe4.jpg</t>
+  </si>
+  <si>
+    <t>MR9FN0FKQH5B</t>
+  </si>
+  <si>
+    <t>Falta lays 330</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783355218/ammaptocgcfbmhbqaylg.jpg</t>
+  </si>
+  <si>
+    <t>MR9G3MRWT85R</t>
+  </si>
+  <si>
+    <t>Cerrado por vacaciones</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783356006/uoksih1rlpbzknsu4qtr.jpg</t>
+  </si>
+  <si>
+    <t>MR9GB8EJ61RE</t>
+  </si>
+  <si>
+    <t>No abre los lunes</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783356343/zwjzbhg818xdajur4mou.jpg</t>
+  </si>
+  <si>
+    <t>MR9GTVON9GA4</t>
+  </si>
+  <si>
+    <t>02:00 p. m.</t>
+  </si>
+  <si>
+    <t>MR9GUVYGZ4OG</t>
+  </si>
+  <si>
+    <t>MR9GUGUOLDE7</t>
+  </si>
+  <si>
+    <t>02:01 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783357250/eegqegex7pycxgrs8zaf.jpg</t>
+  </si>
+  <si>
+    <t>MR9GVNTDD3VV</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783357305/d6m1093bvdfpvbossoql.jpg</t>
+  </si>
+  <si>
+    <t>MR9GVXAHY9WD</t>
+  </si>
+  <si>
+    <t>02:02 p. m.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yerba se confundió de sabor
+</t>
+  </si>
+  <si>
+    <t>MR9KICE9S6KI</t>
+  </si>
+  <si>
+    <t>Faltó 1 acanalada 420g.s</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783363477/ypk3qyad5ns4jjasaeds.jpg</t>
+  </si>
+  <si>
+    <t>MR9OR8D6FY2M</t>
+  </si>
+  <si>
+    <t>05:43 p. m.</t>
+  </si>
+  <si>
+    <t>Tenia no las quizo</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783370549/cbc9i7syhpvjwjjrty98.jpg</t>
+  </si>
+  <si>
+    <t>MRAJLMJTSQQX</t>
+  </si>
+  <si>
+    <t>08:05 a. m.</t>
+  </si>
+  <si>
+    <t>Alfajores</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783422332/g6zeeqdpwft1e0dfusna.jpg</t>
+  </si>
+  <si>
+    <t>MRAKTJKLJDHJ</t>
+  </si>
+  <si>
+    <t>08:40 a. m.</t>
+  </si>
+  <si>
+    <t>Faltó 5 3d 143gr, 1 Doritos queso 129gr y 1 200gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783424384/trh5msypajqpl8hbrqds.jpg</t>
+  </si>
+  <si>
+    <t>MRAL33T1U12R</t>
+  </si>
+  <si>
+    <t>08:47 a. m.</t>
+  </si>
+  <si>
+    <t>Esto no lo pidió dice el cliente</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783424831/iehx4affbpzt1x41atao.jpg</t>
   </si>
 </sst>
 </file>
@@ -1635,7 +1954,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1718,12 +2037,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF284E3F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF284E3F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF284E3F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1780,6 +2144,27 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2182,38 +2567,38 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="21">
         <v>46204</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="23">
         <v>4228</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="3" t="s">
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="15">
+      <c r="N2" s="26">
         <v>7</v>
       </c>
     </row>
@@ -8884,660 +9269,1638 @@
       </c>
     </row>
     <row r="168" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="1"/>
-      <c r="B168" s="2"/>
-      <c r="C168" s="3"/>
-      <c r="D168" s="3"/>
-      <c r="E168" s="3"/>
-      <c r="F168" s="4"/>
-      <c r="G168" s="3"/>
-      <c r="H168" s="13"/>
-      <c r="I168" s="6"/>
-      <c r="J168" s="9"/>
+      <c r="A168" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B168" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C168" s="11">
+        <v>0.35486111111111113</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F168" s="4">
+        <v>11010</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H168" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I168" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="J168" s="9" t="s">
+        <v>503</v>
+      </c>
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
-      <c r="M168" s="3"/>
-      <c r="N168" s="15"/>
+      <c r="M168" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N168" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="169" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="1"/>
-      <c r="B169" s="2"/>
-      <c r="C169" s="3"/>
-      <c r="D169" s="3"/>
-      <c r="E169" s="3"/>
-      <c r="F169" s="4"/>
-      <c r="G169" s="3"/>
-      <c r="H169" s="13"/>
-      <c r="I169" s="6"/>
-      <c r="J169" s="9"/>
+      <c r="A169" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B169" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C169" s="11">
+        <v>0.36388888888888887</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F169" s="4">
+        <v>5595</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I169" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="J169" s="9" t="s">
+        <v>506</v>
+      </c>
       <c r="K169" s="6"/>
       <c r="L169" s="6"/>
-      <c r="M169" s="3"/>
-      <c r="N169" s="15"/>
+      <c r="M169" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N169" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="170" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="1"/>
-      <c r="B170" s="2"/>
-      <c r="C170" s="11"/>
-      <c r="D170" s="3"/>
-      <c r="E170" s="3"/>
-      <c r="F170" s="4"/>
-      <c r="G170" s="3"/>
-      <c r="H170" s="5"/>
-      <c r="I170" s="3"/>
+      <c r="A170" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B170" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F170" s="4">
+        <v>6597</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H170" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I170" s="3" t="s">
+        <v>509</v>
+      </c>
       <c r="J170" s="6"/>
-      <c r="K170" s="3"/>
-      <c r="L170" s="2"/>
-      <c r="M170" s="3"/>
-      <c r="N170" s="15"/>
+      <c r="K170" s="6"/>
+      <c r="L170" s="6"/>
+      <c r="M170" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N170" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="171" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="1"/>
-      <c r="B171" s="2"/>
-      <c r="C171" s="3"/>
-      <c r="D171" s="3"/>
-      <c r="E171" s="3"/>
-      <c r="F171" s="4"/>
-      <c r="G171" s="3"/>
-      <c r="H171" s="5"/>
-      <c r="I171" s="6"/>
-      <c r="J171" s="9"/>
-      <c r="K171" s="6"/>
-      <c r="L171" s="6"/>
-      <c r="M171" s="3"/>
-      <c r="N171" s="15"/>
+      <c r="A171" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B171" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F171" s="4">
+        <v>7560</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H171" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="J171" s="6"/>
+      <c r="K171" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L171" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M171" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N171" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="172" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="1"/>
-      <c r="B172" s="2"/>
-      <c r="C172" s="3"/>
-      <c r="D172" s="3"/>
-      <c r="E172" s="3"/>
-      <c r="F172" s="4"/>
-      <c r="G172" s="3"/>
-      <c r="H172" s="8"/>
-      <c r="I172" s="3"/>
-      <c r="J172" s="9"/>
-      <c r="K172" s="3"/>
-      <c r="L172" s="2"/>
-      <c r="M172" s="3"/>
-      <c r="N172" s="15"/>
+      <c r="A172" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B172" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F172" s="4">
+        <v>2462</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H172" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I172" s="6"/>
+      <c r="J172" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="K172" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L172" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M172" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N172" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="173" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="1"/>
-      <c r="B173" s="2"/>
-      <c r="C173" s="3"/>
-      <c r="D173" s="3"/>
-      <c r="E173" s="3"/>
-      <c r="F173" s="4"/>
-      <c r="G173" s="3"/>
-      <c r="H173" s="8"/>
-      <c r="I173" s="3"/>
-      <c r="J173" s="9"/>
-      <c r="K173" s="3"/>
-      <c r="L173" s="2"/>
-      <c r="M173" s="3"/>
-      <c r="N173" s="15"/>
+      <c r="A173" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B173" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F173" s="4">
+        <v>3660</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H173" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I173" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="J173" s="6"/>
+      <c r="K173" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L173" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M173" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N173" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="174" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="1"/>
-      <c r="B174" s="2"/>
-      <c r="C174" s="11"/>
-      <c r="D174" s="3"/>
-      <c r="E174" s="3"/>
-      <c r="F174" s="4"/>
-      <c r="G174" s="3"/>
-      <c r="H174" s="5"/>
+      <c r="A174" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B174" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F174" s="4">
+        <v>6984</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H174" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="I174" s="6"/>
-      <c r="J174" s="6"/>
-      <c r="K174" s="3"/>
-      <c r="L174" s="2"/>
-      <c r="M174" s="3"/>
-      <c r="N174" s="15"/>
+      <c r="J174" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="K174" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="L174" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M174" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N174" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="175" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="1"/>
-      <c r="B175" s="2"/>
-      <c r="C175" s="11"/>
-      <c r="D175" s="3"/>
-      <c r="E175" s="3"/>
-      <c r="F175" s="4"/>
-      <c r="G175" s="3"/>
-      <c r="H175" s="5"/>
-      <c r="I175" s="3"/>
+      <c r="A175" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B175" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F175" s="4">
+        <v>3787</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H175" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I175" s="3" t="s">
+        <v>522</v>
+      </c>
       <c r="J175" s="6"/>
-      <c r="K175" s="3"/>
-      <c r="L175" s="2"/>
-      <c r="M175" s="3"/>
-      <c r="N175" s="15"/>
+      <c r="K175" s="6"/>
+      <c r="L175" s="6"/>
+      <c r="M175" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N175" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="176" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="1"/>
-      <c r="B176" s="2"/>
-      <c r="C176" s="3"/>
-      <c r="D176" s="3"/>
-      <c r="E176" s="3"/>
-      <c r="F176" s="4"/>
-      <c r="G176" s="3"/>
-      <c r="H176" s="8"/>
-      <c r="I176" s="3"/>
-      <c r="J176" s="6"/>
-      <c r="K176" s="6"/>
-      <c r="L176" s="6"/>
-      <c r="M176" s="3"/>
-      <c r="N176" s="15"/>
+      <c r="A176" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B176" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F176" s="4">
+        <v>2797</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H176" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I176" s="6"/>
+      <c r="J176" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="K176" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="L176" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M176" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N176" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="177" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="1"/>
-      <c r="B177" s="2"/>
-      <c r="C177" s="3"/>
-      <c r="D177" s="3"/>
-      <c r="E177" s="3"/>
-      <c r="F177" s="4"/>
-      <c r="G177" s="3"/>
-      <c r="H177" s="5"/>
+      <c r="A177" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B177" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C177" s="11">
+        <v>0.42222222222222222</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F177" s="4">
+        <v>7283</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H177" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="I177" s="6"/>
-      <c r="J177" s="9"/>
-      <c r="K177" s="3"/>
-      <c r="L177" s="2"/>
-      <c r="M177" s="3"/>
-      <c r="N177" s="15"/>
+      <c r="J177" s="6"/>
+      <c r="K177" s="6"/>
+      <c r="L177" s="6"/>
+      <c r="M177" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N177" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="178" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="1"/>
-      <c r="B178" s="2"/>
-      <c r="C178" s="3"/>
-      <c r="D178" s="3"/>
-      <c r="E178" s="3"/>
-      <c r="F178" s="4"/>
-      <c r="G178" s="3"/>
-      <c r="H178" s="5"/>
-      <c r="I178" s="6"/>
-      <c r="J178" s="9"/>
-      <c r="K178" s="6"/>
-      <c r="L178" s="6"/>
-      <c r="M178" s="3"/>
-      <c r="N178" s="15"/>
+      <c r="A178" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B178" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F178" s="4">
+        <v>10948</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H178" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I178" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="J178" s="6"/>
+      <c r="K178" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L178" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M178" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N178" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="179" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="1"/>
-      <c r="B179" s="2"/>
-      <c r="C179" s="3"/>
-      <c r="D179" s="3"/>
-      <c r="E179" s="3"/>
-      <c r="F179" s="4"/>
-      <c r="G179" s="3"/>
-      <c r="H179" s="5"/>
-      <c r="I179" s="3"/>
+      <c r="A179" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B179" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C179" s="11">
+        <v>0.4284722222222222</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F179" s="4">
+        <v>6709</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H179" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I179" s="6"/>
       <c r="J179" s="6"/>
-      <c r="K179" s="3"/>
-      <c r="L179" s="2"/>
-      <c r="M179" s="3"/>
-      <c r="N179" s="15"/>
+      <c r="K179" s="6"/>
+      <c r="L179" s="6"/>
+      <c r="M179" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N179" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="180" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="1"/>
-      <c r="B180" s="2"/>
-      <c r="C180" s="3"/>
-      <c r="D180" s="3"/>
-      <c r="E180" s="3"/>
-      <c r="F180" s="4"/>
-      <c r="G180" s="3"/>
-      <c r="H180" s="8"/>
-      <c r="I180" s="3"/>
-      <c r="J180" s="6"/>
-      <c r="K180" s="3"/>
-      <c r="L180" s="2"/>
-      <c r="M180" s="3"/>
-      <c r="N180" s="15"/>
+      <c r="A180" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B180" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C180" s="11">
+        <v>0.43194444444444446</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F180" s="4">
+        <v>11174</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H180" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I180" s="6"/>
+      <c r="J180" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="K180" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L180" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M180" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N180" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="181" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="1"/>
-      <c r="B181" s="2"/>
-      <c r="C181" s="3"/>
-      <c r="D181" s="3"/>
-      <c r="E181" s="3"/>
-      <c r="F181" s="4"/>
-      <c r="G181" s="3"/>
-      <c r="H181" s="5"/>
-      <c r="I181" s="3"/>
-      <c r="J181" s="9"/>
-      <c r="K181" s="3"/>
-      <c r="L181" s="2"/>
-      <c r="M181" s="3"/>
-      <c r="N181" s="15"/>
+      <c r="A181" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B181" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F181" s="4">
+        <v>3682</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H181" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="J181" s="6"/>
+      <c r="K181" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L181" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M181" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N181" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="182" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="1"/>
-      <c r="B182" s="2"/>
-      <c r="C182" s="3"/>
-      <c r="D182" s="3"/>
-      <c r="E182" s="3"/>
-      <c r="F182" s="4"/>
-      <c r="G182" s="3"/>
-      <c r="H182" s="8"/>
-      <c r="I182" s="3"/>
-      <c r="J182" s="9"/>
-      <c r="K182" s="3"/>
-      <c r="L182" s="2"/>
-      <c r="M182" s="3"/>
-      <c r="N182" s="15"/>
+      <c r="A182" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B182" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F182" s="4">
+        <v>2519</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H182" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I182" s="6"/>
+      <c r="J182" s="6"/>
+      <c r="K182" s="6"/>
+      <c r="L182" s="6"/>
+      <c r="M182" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N182" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="183" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="1"/>
-      <c r="B183" s="2"/>
-      <c r="C183" s="11"/>
-      <c r="D183" s="3"/>
-      <c r="E183" s="3"/>
-      <c r="F183" s="4"/>
-      <c r="G183" s="3"/>
-      <c r="H183" s="7"/>
-      <c r="I183" s="3"/>
+      <c r="A183" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B183" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F183" s="4">
+        <v>3824</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H183" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I183" s="6"/>
       <c r="J183" s="6"/>
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
-      <c r="M183" s="3"/>
-      <c r="N183" s="15"/>
+      <c r="M183" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N183" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="184" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="1"/>
-      <c r="B184" s="2"/>
-      <c r="C184" s="3"/>
-      <c r="D184" s="3"/>
-      <c r="E184" s="3"/>
-      <c r="F184" s="4"/>
-      <c r="G184" s="3"/>
-      <c r="H184" s="8"/>
-      <c r="I184" s="3"/>
-      <c r="J184" s="9"/>
-      <c r="K184" s="3"/>
-      <c r="L184" s="2"/>
-      <c r="M184" s="3"/>
-      <c r="N184" s="15"/>
+      <c r="A184" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B184" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F184" s="4">
+        <v>3189</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H184" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I184" s="6"/>
+      <c r="J184" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="K184" s="6"/>
+      <c r="L184" s="6"/>
+      <c r="M184" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N184" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="185" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="1"/>
-      <c r="B185" s="2"/>
-      <c r="C185" s="11"/>
-      <c r="D185" s="3"/>
-      <c r="E185" s="3"/>
-      <c r="F185" s="4"/>
-      <c r="G185" s="3"/>
-      <c r="H185" s="5"/>
-      <c r="I185" s="3"/>
+      <c r="A185" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B185" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C185" s="11">
+        <v>0.46111111111111114</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F185" s="4">
+        <v>6706</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H185" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="I185" s="6"/>
       <c r="J185" s="6"/>
-      <c r="K185" s="3"/>
-      <c r="L185" s="2"/>
-      <c r="M185" s="3"/>
-      <c r="N185" s="15"/>
+      <c r="K185" s="6"/>
+      <c r="L185" s="6"/>
+      <c r="M185" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N185" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="186" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="1"/>
-      <c r="B186" s="2"/>
-      <c r="C186" s="3"/>
-      <c r="D186" s="3"/>
-      <c r="E186" s="3"/>
-      <c r="F186" s="4"/>
-      <c r="G186" s="3"/>
-      <c r="H186" s="5"/>
-      <c r="I186" s="3"/>
-      <c r="J186" s="9"/>
-      <c r="K186" s="3"/>
-      <c r="L186" s="2"/>
-      <c r="M186" s="3"/>
-      <c r="N186" s="15"/>
+      <c r="A186" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B186" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C186" s="11">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F186" s="4">
+        <v>6742</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H186" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I186" s="6"/>
+      <c r="J186" s="6"/>
+      <c r="K186" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L186" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M186" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N186" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="187" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="1"/>
-      <c r="B187" s="2"/>
-      <c r="C187" s="11"/>
-      <c r="D187" s="3"/>
-      <c r="E187" s="3"/>
-      <c r="F187" s="4"/>
-      <c r="G187" s="3"/>
-      <c r="H187" s="8"/>
+      <c r="A187" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B187" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C187" s="11">
+        <v>0.48055555555555557</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F187" s="4">
+        <v>6742</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H187" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="I187" s="6"/>
       <c r="J187" s="6"/>
-      <c r="K187" s="3"/>
-      <c r="L187" s="2"/>
-      <c r="M187" s="3"/>
-      <c r="N187" s="15"/>
+      <c r="K187" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L187" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M187" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N187" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="188" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="1"/>
-      <c r="B188" s="2"/>
-      <c r="C188" s="3"/>
-      <c r="D188" s="3"/>
-      <c r="E188" s="3"/>
-      <c r="F188" s="4"/>
-      <c r="G188" s="3"/>
-      <c r="H188" s="14"/>
-      <c r="I188" s="3"/>
+      <c r="A188" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B188" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F188" s="4">
+        <v>4805</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H188" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I188" s="3" t="s">
+        <v>547</v>
+      </c>
       <c r="J188" s="6"/>
-      <c r="K188" s="3"/>
-      <c r="L188" s="2"/>
-      <c r="M188" s="3"/>
-      <c r="N188" s="15"/>
+      <c r="K188" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L188" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M188" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N188" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="189" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="1"/>
-      <c r="B189" s="2"/>
-      <c r="C189" s="3"/>
-      <c r="D189" s="3"/>
-      <c r="E189" s="3"/>
-      <c r="F189" s="4"/>
-      <c r="G189" s="3"/>
-      <c r="H189" s="7"/>
-      <c r="I189" s="6"/>
-      <c r="J189" s="6"/>
-      <c r="K189" s="3"/>
-      <c r="L189" s="2"/>
-      <c r="M189" s="3"/>
-      <c r="N189" s="15"/>
+      <c r="A189" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B189" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C189" s="11">
+        <v>0.48819444444444443</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F189" s="4">
+        <v>11174</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H189" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I189" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="J189" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="K189" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L189" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M189" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N189" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="190" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="1"/>
-      <c r="B190" s="2"/>
-      <c r="C190" s="3"/>
-      <c r="D190" s="3"/>
-      <c r="E190" s="3"/>
-      <c r="F190" s="4"/>
-      <c r="G190" s="3"/>
-      <c r="H190" s="7"/>
-      <c r="I190" s="3"/>
-      <c r="J190" s="9"/>
-      <c r="K190" s="3"/>
-      <c r="L190" s="2"/>
-      <c r="M190" s="3"/>
-      <c r="N190" s="15"/>
+      <c r="A190" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B190" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F190" s="4">
+        <v>2581</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H190" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="J190" s="6"/>
+      <c r="K190" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L190" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M190" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N190" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="191" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="1"/>
-      <c r="B191" s="2"/>
-      <c r="C191" s="3"/>
-      <c r="D191" s="3"/>
-      <c r="E191" s="3"/>
-      <c r="F191" s="4"/>
-      <c r="G191" s="3"/>
-      <c r="H191" s="5"/>
+      <c r="A191" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B191" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C191" s="11">
+        <v>0.52986111111111112</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F191" s="4">
+        <v>6709</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H191" s="13" t="s">
+        <v>122</v>
+      </c>
       <c r="I191" s="6"/>
-      <c r="J191" s="9"/>
-      <c r="K191" s="3"/>
-      <c r="L191" s="2"/>
-      <c r="M191" s="3"/>
-      <c r="N191" s="15"/>
+      <c r="J191" s="6"/>
+      <c r="K191" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L191" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M191" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N191" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="192" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="1"/>
-      <c r="B192" s="2"/>
-      <c r="C192" s="3"/>
-      <c r="D192" s="3"/>
-      <c r="E192" s="3"/>
-      <c r="F192" s="4"/>
-      <c r="G192" s="3"/>
-      <c r="H192" s="5"/>
-      <c r="I192" s="6"/>
-      <c r="J192" s="9"/>
-      <c r="K192" s="3"/>
-      <c r="L192" s="2"/>
-      <c r="M192" s="3"/>
-      <c r="N192" s="15"/>
+      <c r="A192" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B192" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C192" s="11">
+        <v>0.52986111111111112</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F192" s="4">
+        <v>5568</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H192" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="J192" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="K192" s="6"/>
+      <c r="L192" s="6"/>
+      <c r="M192" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N192" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="193" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="1"/>
-      <c r="B193" s="2"/>
-      <c r="C193" s="3"/>
-      <c r="D193" s="3"/>
-      <c r="E193" s="3"/>
-      <c r="F193" s="4"/>
-      <c r="G193" s="3"/>
-      <c r="H193" s="5"/>
-      <c r="I193" s="3"/>
-      <c r="J193" s="9"/>
+      <c r="A193" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B193" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F193" s="4">
+        <v>7009</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H193" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="J193" s="9" t="s">
+        <v>561</v>
+      </c>
       <c r="K193" s="6"/>
       <c r="L193" s="6"/>
-      <c r="M193" s="3"/>
-      <c r="N193" s="15"/>
+      <c r="M193" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N193" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="194" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="1"/>
-      <c r="B194" s="2"/>
-      <c r="C194" s="3"/>
-      <c r="D194" s="3"/>
-      <c r="E194" s="3"/>
-      <c r="F194" s="4"/>
-      <c r="G194" s="3"/>
-      <c r="H194" s="7"/>
+      <c r="A194" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B194" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F194" s="4">
+        <v>6991</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H194" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I194" s="6"/>
-      <c r="J194" s="9"/>
+      <c r="J194" s="9" t="s">
+        <v>564</v>
+      </c>
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
-      <c r="M194" s="3"/>
-      <c r="N194" s="15"/>
+      <c r="M194" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N194" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="195" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="1"/>
-      <c r="B195" s="2"/>
-      <c r="C195" s="3"/>
-      <c r="D195" s="3"/>
-      <c r="E195" s="3"/>
-      <c r="F195" s="4"/>
-      <c r="G195" s="3"/>
-      <c r="H195" s="5"/>
+      <c r="A195" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B195" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F195" s="4">
+        <v>6977</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H195" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I195" s="6"/>
-      <c r="J195" s="9"/>
-      <c r="K195" s="6"/>
-      <c r="L195" s="6"/>
-      <c r="M195" s="3"/>
-      <c r="N195" s="15"/>
+      <c r="J195" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="K195" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L195" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M195" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N195" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="196" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="1"/>
-      <c r="B196" s="2"/>
-      <c r="C196" s="3"/>
-      <c r="D196" s="3"/>
-      <c r="E196" s="3"/>
-      <c r="F196" s="4"/>
-      <c r="G196" s="3"/>
-      <c r="H196" s="13"/>
-      <c r="I196" s="6"/>
-      <c r="J196" s="9"/>
-      <c r="K196" s="3"/>
-      <c r="L196" s="2"/>
-      <c r="M196" s="3"/>
-      <c r="N196" s="15"/>
+      <c r="A196" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B196" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C196" s="11">
+        <v>0.56041666666666667</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F196" s="4">
+        <v>5599</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H196" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="J196" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="K196" s="6"/>
+      <c r="L196" s="6"/>
+      <c r="M196" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N196" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="197" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="1"/>
-      <c r="B197" s="2"/>
-      <c r="C197" s="11"/>
-      <c r="D197" s="3"/>
-      <c r="E197" s="3"/>
-      <c r="F197" s="4"/>
-      <c r="G197" s="3"/>
-      <c r="H197" s="8"/>
-      <c r="I197" s="6"/>
-      <c r="J197" s="6"/>
+      <c r="A197" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B197" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F197" s="4">
+        <v>6429</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H197" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="J197" s="9" t="s">
+        <v>573</v>
+      </c>
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
-      <c r="M197" s="3"/>
-      <c r="N197" s="15"/>
+      <c r="M197" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N197" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="198" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="1"/>
-      <c r="B198" s="2"/>
-      <c r="C198" s="11"/>
-      <c r="D198" s="3"/>
-      <c r="E198" s="3"/>
-      <c r="F198" s="4"/>
-      <c r="G198" s="3"/>
-      <c r="H198" s="5"/>
-      <c r="I198" s="6"/>
-      <c r="J198" s="6"/>
+      <c r="A198" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B198" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C198" s="11">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F198" s="4">
+        <v>5583</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H198" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="J198" s="9" t="s">
+        <v>576</v>
+      </c>
       <c r="K198" s="6"/>
       <c r="L198" s="6"/>
-      <c r="M198" s="3"/>
-      <c r="N198" s="15"/>
+      <c r="M198" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N198" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="199" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="1"/>
-      <c r="B199" s="2"/>
-      <c r="C199" s="3"/>
-      <c r="D199" s="3"/>
-      <c r="E199" s="3"/>
-      <c r="F199" s="4"/>
-      <c r="G199" s="3"/>
-      <c r="H199" s="5"/>
-      <c r="I199" s="3"/>
-      <c r="J199" s="9"/>
-      <c r="K199" s="3"/>
-      <c r="L199" s="2"/>
-      <c r="M199" s="3"/>
-      <c r="N199" s="15"/>
+      <c r="A199" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B199" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F199" s="4">
+        <v>3870</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H199" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I199" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="J199" s="6"/>
+      <c r="K199" s="6"/>
+      <c r="L199" s="6"/>
+      <c r="M199" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N199" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="200" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="1"/>
-      <c r="B200" s="2"/>
-      <c r="C200" s="3"/>
-      <c r="D200" s="3"/>
-      <c r="E200" s="3"/>
-      <c r="F200" s="4"/>
-      <c r="G200" s="3"/>
-      <c r="H200" s="10"/>
-      <c r="I200" s="3"/>
+      <c r="A200" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B200" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F200" s="4">
+        <v>4818</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H200" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I200" s="6"/>
       <c r="J200" s="6"/>
-      <c r="K200" s="3"/>
-      <c r="L200" s="2"/>
-      <c r="M200" s="3"/>
-      <c r="N200" s="15"/>
+      <c r="K200" s="6"/>
+      <c r="L200" s="6"/>
+      <c r="M200" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N200" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="201" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="1"/>
-      <c r="B201" s="2"/>
-      <c r="C201" s="3"/>
-      <c r="D201" s="3"/>
-      <c r="E201" s="3"/>
-      <c r="F201" s="4"/>
-      <c r="G201" s="3"/>
-      <c r="H201" s="8"/>
+      <c r="A201" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B201" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F201" s="4">
+        <v>10938</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H201" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I201" s="6"/>
-      <c r="J201" s="9"/>
-      <c r="K201" s="3"/>
-      <c r="L201" s="2"/>
-      <c r="M201" s="3"/>
-      <c r="N201" s="15"/>
+      <c r="J201" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="K201" s="6"/>
+      <c r="L201" s="6"/>
+      <c r="M201" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N201" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="202" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="1"/>
-      <c r="B202" s="2"/>
-      <c r="C202" s="3"/>
-      <c r="D202" s="3"/>
-      <c r="E202" s="3"/>
-      <c r="F202" s="4"/>
-      <c r="G202" s="3"/>
-      <c r="H202" s="12"/>
+      <c r="A202" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="B202" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F202" s="4">
+        <v>7011</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H202" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="I202" s="6"/>
-      <c r="J202" s="9"/>
-      <c r="K202" s="3"/>
-      <c r="L202" s="2"/>
-      <c r="M202" s="3"/>
-      <c r="N202" s="15"/>
+      <c r="J202" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="K202" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L202" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M202" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N202" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="203" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="1"/>
-      <c r="B203" s="2"/>
-      <c r="C203" s="3"/>
-      <c r="D203" s="3"/>
-      <c r="E203" s="3"/>
-      <c r="F203" s="4"/>
-      <c r="G203" s="3"/>
-      <c r="H203" s="5"/>
-      <c r="I203" s="6"/>
-      <c r="J203" s="9"/>
-      <c r="K203" s="3"/>
-      <c r="L203" s="2"/>
-      <c r="M203" s="3"/>
-      <c r="N203" s="15"/>
+      <c r="A203" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B203" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F203" s="4">
+        <v>5137</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H203" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="I203" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="J203" s="6"/>
+      <c r="K203" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L203" s="2">
+        <v>46209</v>
+      </c>
+      <c r="M203" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N203" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="204" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="1"/>
-      <c r="B204" s="2"/>
-      <c r="C204" s="3"/>
-      <c r="D204" s="3"/>
-      <c r="E204" s="3"/>
-      <c r="F204" s="4"/>
-      <c r="G204" s="3"/>
-      <c r="H204" s="8"/>
-      <c r="I204" s="3"/>
-      <c r="J204" s="6"/>
-      <c r="K204" s="3"/>
-      <c r="L204" s="2"/>
-      <c r="M204" s="3"/>
-      <c r="N204" s="15"/>
+      <c r="A204" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B204" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F204" s="4">
+        <v>1335</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H204" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I204" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="J204" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="K204" s="6"/>
+      <c r="L204" s="6"/>
+      <c r="M204" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N204" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="205" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="1"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="3"/>
-      <c r="D205" s="3"/>
-      <c r="E205" s="3"/>
-      <c r="F205" s="4"/>
-      <c r="G205" s="3"/>
-      <c r="H205" s="5"/>
-      <c r="I205" s="6"/>
-      <c r="J205" s="9"/>
-      <c r="K205" s="3"/>
-      <c r="L205" s="2"/>
-      <c r="M205" s="3"/>
-      <c r="N205" s="15"/>
+      <c r="A205" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="B205" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F205" s="4">
+        <v>275</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="H205" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I205" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="J205" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="K205" s="6"/>
+      <c r="L205" s="6"/>
+      <c r="M205" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N205" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="206" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="1"/>
-      <c r="B206" s="2"/>
-      <c r="C206" s="11"/>
-      <c r="D206" s="3"/>
-      <c r="E206" s="3"/>
-      <c r="F206" s="4"/>
-      <c r="G206" s="3"/>
-      <c r="H206" s="5"/>
-      <c r="I206" s="6"/>
-      <c r="J206" s="6"/>
-      <c r="K206" s="3"/>
-      <c r="L206" s="2"/>
-      <c r="M206" s="3"/>
-      <c r="N206" s="15"/>
+      <c r="A206" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="B206" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F206" s="4">
+        <v>3841</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H206" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I206" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="J206" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="K206" s="6"/>
+      <c r="L206" s="6"/>
+      <c r="M206" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N206" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="207" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="1"/>
-      <c r="B207" s="2"/>
-      <c r="C207" s="3"/>
-      <c r="D207" s="3"/>
-      <c r="E207" s="3"/>
-      <c r="F207" s="4"/>
-      <c r="G207" s="3"/>
-      <c r="H207" s="5"/>
-      <c r="I207" s="6"/>
-      <c r="J207" s="9"/>
-      <c r="K207" s="3"/>
-      <c r="L207" s="2"/>
-      <c r="M207" s="3"/>
-      <c r="N207" s="15"/>
+      <c r="A207" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B207" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F207" s="4">
+        <v>2069</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H207" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I207" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="J207" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="K207" s="6"/>
+      <c r="L207" s="6"/>
+      <c r="M207" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N207" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="208" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="1"/>
-      <c r="B208" s="2"/>
-      <c r="C208" s="3"/>
-      <c r="D208" s="3"/>
-      <c r="E208" s="3"/>
-      <c r="F208" s="4"/>
-      <c r="G208" s="3"/>
-      <c r="H208" s="5"/>
-      <c r="I208" s="6"/>
-      <c r="J208" s="6"/>
-      <c r="K208" s="3"/>
-      <c r="L208" s="2"/>
-      <c r="M208" s="3"/>
-      <c r="N208" s="15"/>
+      <c r="A208" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B208" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F208" s="4">
+        <v>4121</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H208" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I208" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="J208" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="K208" s="6"/>
+      <c r="L208" s="6"/>
+      <c r="M208" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N208" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="209" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
@@ -25541,88 +26904,110 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J8" r:id="rId1" xr:uid="{07918FA9-C77F-4A0C-A261-32EA059DA0D6}"/>
-    <hyperlink ref="J10" r:id="rId2" xr:uid="{35079F5D-7D33-44B3-94FE-4188725A197D}"/>
-    <hyperlink ref="J11" r:id="rId3" xr:uid="{DA6C8A57-8132-4DE2-B2A9-7176EDB1F816}"/>
-    <hyperlink ref="J12" r:id="rId4" xr:uid="{3EDE3F6A-6B4D-4235-8A35-DBEDB74A5918}"/>
-    <hyperlink ref="J14" r:id="rId5" xr:uid="{29D3EE15-31AC-4155-ABAB-EB406BD6BD8A}"/>
-    <hyperlink ref="J16" r:id="rId6" xr:uid="{BD6CACFF-3D91-434A-99A8-163D74D57DBE}"/>
-    <hyperlink ref="J17" r:id="rId7" xr:uid="{EE85335E-6866-4D4E-830E-9D27AFA9010C}"/>
-    <hyperlink ref="J20" r:id="rId8" xr:uid="{FB423B8C-E97E-46AD-ACBE-42B2504A28F7}"/>
-    <hyperlink ref="J21" r:id="rId9" xr:uid="{66DD1FFC-C94E-4236-A940-B6F31430B612}"/>
-    <hyperlink ref="J22" r:id="rId10" xr:uid="{1E613827-4FCC-4341-96EB-5D75AAA8D325}"/>
-    <hyperlink ref="J24" r:id="rId11" xr:uid="{859ECDA1-F495-4C68-890B-82EECD178CFC}"/>
-    <hyperlink ref="J25" r:id="rId12" xr:uid="{A43EAACF-743A-4206-BE2A-98AD0FD19FDD}"/>
-    <hyperlink ref="J27" r:id="rId13" xr:uid="{8BF84E77-A726-43FE-8021-2FB32D28CDDD}"/>
-    <hyperlink ref="J28" r:id="rId14" xr:uid="{5A39B5F3-9142-465C-889E-4A1778D6F8C4}"/>
-    <hyperlink ref="J29" r:id="rId15" xr:uid="{B619E563-2B5D-4FC5-AC01-F7C7CD180168}"/>
-    <hyperlink ref="J30" r:id="rId16" xr:uid="{FF4B135C-1C7A-44B5-980D-7FE349CEA3A5}"/>
-    <hyperlink ref="J31" r:id="rId17" xr:uid="{332DDA28-6D46-4758-89B5-A4F7EFA2F21C}"/>
-    <hyperlink ref="J33" r:id="rId18" xr:uid="{6B47C7E7-F6DE-40A2-953A-5D3A250BCAC4}"/>
-    <hyperlink ref="J35" r:id="rId19" xr:uid="{736679CF-9406-4348-9191-CF491DA34D5A}"/>
-    <hyperlink ref="J37" r:id="rId20" xr:uid="{F3C3279E-F984-4128-9B04-1E0CA2E1A16B}"/>
-    <hyperlink ref="J38" r:id="rId21" xr:uid="{4E52841B-1C43-4BFA-889F-41A6EAD2CED7}"/>
-    <hyperlink ref="J42" r:id="rId22" xr:uid="{306ACF3D-EF52-46EC-8395-6B713C9EBDD0}"/>
-    <hyperlink ref="J44" r:id="rId23" xr:uid="{A43C8C69-4B58-4963-965D-E1DA4725AA64}"/>
-    <hyperlink ref="J45" r:id="rId24" xr:uid="{B0DF4654-38F7-4DE6-92C1-6625E3E261E4}"/>
-    <hyperlink ref="J46" r:id="rId25" xr:uid="{AF776FAE-83F4-4AA6-B7C8-DB625CD9D8CE}"/>
-    <hyperlink ref="J47" r:id="rId26" xr:uid="{93ECE2C3-D4DB-4093-8283-0851C6BCB32D}"/>
-    <hyperlink ref="J49" r:id="rId27" xr:uid="{6F980D43-01A8-43EC-88A7-361DACC9F3E8}"/>
-    <hyperlink ref="J51" r:id="rId28" xr:uid="{69775998-231B-49CD-AC85-C92F5E54BD69}"/>
-    <hyperlink ref="J55" r:id="rId29" xr:uid="{8F1C941E-EC0A-4464-8BBB-A7AE5069B4C2}"/>
-    <hyperlink ref="J57" r:id="rId30" xr:uid="{E1C79454-F315-4ADA-9471-658319D1F847}"/>
-    <hyperlink ref="J69" r:id="rId31" xr:uid="{6AC0113D-4799-4C79-B05B-04F1751CC8AF}"/>
-    <hyperlink ref="J71" r:id="rId32" xr:uid="{B29B16B9-4CD2-4A8C-974A-B4E6189353F2}"/>
-    <hyperlink ref="J73" r:id="rId33" xr:uid="{4E68FAF7-A264-4BF6-988D-C6C7F0D2EF91}"/>
-    <hyperlink ref="J76" r:id="rId34" xr:uid="{022A00ED-75F3-4919-9964-877CFF9723D4}"/>
-    <hyperlink ref="J77" r:id="rId35" xr:uid="{D1607EC8-A6E9-4AE4-B69D-77BEC8D1E34D}"/>
-    <hyperlink ref="J78" r:id="rId36" xr:uid="{23982911-83FD-4E42-B8D5-1E68E24F643D}"/>
-    <hyperlink ref="J80" r:id="rId37" xr:uid="{84CDF53D-142E-4AD3-ACCA-885D455FBF98}"/>
-    <hyperlink ref="J83" r:id="rId38" xr:uid="{9E641901-6AE0-4D2F-A23A-098F89E0E198}"/>
-    <hyperlink ref="J84" r:id="rId39" xr:uid="{EC6218D3-4042-4770-BC03-3F1A48A2C0CA}"/>
-    <hyperlink ref="J85" r:id="rId40" xr:uid="{3D5EDB0E-253F-4B75-B39F-B06DCB4FF516}"/>
-    <hyperlink ref="J86" r:id="rId41" xr:uid="{312E8B1F-F690-4680-8E94-2A90AC6F4A86}"/>
-    <hyperlink ref="J87" r:id="rId42" xr:uid="{C271801F-D585-4682-9878-A49CCD99634A}"/>
-    <hyperlink ref="J88" r:id="rId43" xr:uid="{8E8B84E2-5707-49CC-9597-7C03E5EDF7A2}"/>
-    <hyperlink ref="J89" r:id="rId44" xr:uid="{4F727DAA-9547-43F8-87EB-E3D9636526CB}"/>
-    <hyperlink ref="J91" r:id="rId45" xr:uid="{9A999195-6202-4A84-908C-8D187D906BAF}"/>
-    <hyperlink ref="J95" r:id="rId46" xr:uid="{ED642DC3-8708-40BB-BB17-1BC4563347C7}"/>
-    <hyperlink ref="J96" r:id="rId47" xr:uid="{17B1B02F-4AEA-4542-8A55-758BFD09DFC7}"/>
-    <hyperlink ref="J99" r:id="rId48" xr:uid="{3C8A43BA-80BE-4357-8994-50EBC52C6D0E}"/>
-    <hyperlink ref="J102" r:id="rId49" xr:uid="{83D31369-D31D-4A0D-85FC-646E48816E2D}"/>
-    <hyperlink ref="J103" r:id="rId50" xr:uid="{827B1BBC-D430-4EE3-B331-8059CB346965}"/>
-    <hyperlink ref="J106" r:id="rId51" xr:uid="{1B677242-6767-45BE-9801-039A287F14F9}"/>
-    <hyperlink ref="J108" r:id="rId52" xr:uid="{B79DC16D-5AA9-409E-9D16-775E0EC47C99}"/>
-    <hyperlink ref="J111" r:id="rId53" xr:uid="{354A16A1-10B6-41F9-B45A-C247ABD06B93}"/>
-    <hyperlink ref="J112" r:id="rId54" xr:uid="{C4DD775A-FBF3-4F67-8C80-4E4F1B4B5CBF}"/>
-    <hyperlink ref="J114" r:id="rId55" xr:uid="{F90B5C1D-EE1C-4F96-92DB-032930E14517}"/>
-    <hyperlink ref="J115" r:id="rId56" xr:uid="{2F894019-E3D0-4C96-8180-080D16B3957A}"/>
-    <hyperlink ref="J116" r:id="rId57" xr:uid="{B8CF4B31-9B2F-4213-891A-5EF55269F741}"/>
-    <hyperlink ref="J117" r:id="rId58" xr:uid="{C5679E06-BF8C-4975-96E3-9F055537C930}"/>
-    <hyperlink ref="J118" r:id="rId59" xr:uid="{0766EB21-1494-41F0-A8CA-4FB217AFA34B}"/>
-    <hyperlink ref="J119" r:id="rId60" xr:uid="{D696E27C-C4DC-448D-8DE3-E8C5EB803565}"/>
-    <hyperlink ref="J120" r:id="rId61" xr:uid="{38E78744-A3A5-4751-9182-6DDF28DB972D}"/>
-    <hyperlink ref="J122" r:id="rId62" xr:uid="{52F886BD-C7CF-4FBC-A5BB-37DD85082F46}"/>
-    <hyperlink ref="J136" r:id="rId63" xr:uid="{3B6893DC-0BB5-4F2B-B048-2EED1B0E0D23}"/>
-    <hyperlink ref="J140" r:id="rId64" xr:uid="{005A0CE1-1B05-477C-83BF-5383FC5F1620}"/>
-    <hyperlink ref="J143" r:id="rId65" xr:uid="{72625D25-94F0-4B93-AD04-F89DF769E82B}"/>
-    <hyperlink ref="J144" r:id="rId66" xr:uid="{F7EF2183-3458-4B88-AFE2-32C1054C6352}"/>
-    <hyperlink ref="J145" r:id="rId67" xr:uid="{9E9BACB0-0146-4162-813F-1D26D3D5B352}"/>
-    <hyperlink ref="J148" r:id="rId68" xr:uid="{16B31D15-A07C-4F6C-A6F8-AF1C4F867071}"/>
-    <hyperlink ref="J150" r:id="rId69" xr:uid="{D073D596-F32E-4F7E-9F41-F77CFED1F249}"/>
-    <hyperlink ref="J155" r:id="rId70" xr:uid="{AF7CA951-9505-4089-866B-3F1DA08F1C7B}"/>
-    <hyperlink ref="J158" r:id="rId71" xr:uid="{436A729E-76E4-4751-B4B3-927F8254455C}"/>
-    <hyperlink ref="J159" r:id="rId72" xr:uid="{E0786708-2D29-4B31-968B-D431BD74F2E2}"/>
-    <hyperlink ref="J160" r:id="rId73" xr:uid="{73F7FB3F-1222-4BF4-B3CA-32FEC1279432}"/>
-    <hyperlink ref="J162" r:id="rId74" xr:uid="{2E719EAE-32B3-43B3-95EB-23F49789DA1A}"/>
-    <hyperlink ref="J163" r:id="rId75" xr:uid="{02A10C12-0B29-44AF-832C-6FDE9806B4D2}"/>
-    <hyperlink ref="J164" r:id="rId76" xr:uid="{36B335E9-A9EA-4CFE-B505-D6FAF13F8D3B}"/>
-    <hyperlink ref="J165" r:id="rId77" xr:uid="{B84175AE-4A85-4206-A17F-6434C9525B30}"/>
+    <hyperlink ref="J8" r:id="rId1" xr:uid="{AAFA035B-D7C2-4D88-8CFB-C024E6710195}"/>
+    <hyperlink ref="J10" r:id="rId2" xr:uid="{3A1D1167-2920-4E6B-96C5-8EEB8E99F3E9}"/>
+    <hyperlink ref="J11" r:id="rId3" xr:uid="{A3A4EE5D-E371-4B4E-8D95-1F7F8E39B422}"/>
+    <hyperlink ref="J12" r:id="rId4" xr:uid="{D5249930-1853-4DB6-BE6C-0682D3914D24}"/>
+    <hyperlink ref="J14" r:id="rId5" xr:uid="{7E622E4D-E41B-483C-AFF3-B8ECF10548E5}"/>
+    <hyperlink ref="J16" r:id="rId6" xr:uid="{57F751B0-1AA8-45CB-9BE8-4EE9C0E4D406}"/>
+    <hyperlink ref="J17" r:id="rId7" xr:uid="{5DD65956-CA33-42B5-B37C-EE1CA3E26059}"/>
+    <hyperlink ref="J20" r:id="rId8" xr:uid="{491CAB95-CB62-4C62-8ECC-A3A096E4E203}"/>
+    <hyperlink ref="J21" r:id="rId9" xr:uid="{7B56DB73-A403-4E39-BB67-3A89D1DB9698}"/>
+    <hyperlink ref="J22" r:id="rId10" xr:uid="{E91B7980-AF9F-4ECC-9129-03D6B512102B}"/>
+    <hyperlink ref="J24" r:id="rId11" xr:uid="{6D830266-50E8-4E78-A7A5-843719BD9725}"/>
+    <hyperlink ref="J25" r:id="rId12" xr:uid="{724326D5-D3D2-4A37-919C-DEA0DD1E1E7B}"/>
+    <hyperlink ref="J27" r:id="rId13" xr:uid="{BB484F34-809F-4FA8-927B-72FB7191AC20}"/>
+    <hyperlink ref="J28" r:id="rId14" xr:uid="{20A9CD27-2312-4616-8D3D-EBEDDE258DF3}"/>
+    <hyperlink ref="J29" r:id="rId15" xr:uid="{9FD7ABCC-7F05-4974-B85D-9DA9974DB48D}"/>
+    <hyperlink ref="J30" r:id="rId16" xr:uid="{5789D184-C426-48A5-A2A8-4803CFB8BE35}"/>
+    <hyperlink ref="J31" r:id="rId17" xr:uid="{636D6CDE-0FE9-4319-ADC2-E98BD821A5C4}"/>
+    <hyperlink ref="J33" r:id="rId18" xr:uid="{D6B90C77-F9D0-4176-8476-3A8D91420822}"/>
+    <hyperlink ref="J35" r:id="rId19" xr:uid="{816899C2-B834-48C8-A2A0-C75E80E122F7}"/>
+    <hyperlink ref="J37" r:id="rId20" xr:uid="{D752027B-C80B-4750-96D5-69F34D50849E}"/>
+    <hyperlink ref="J38" r:id="rId21" xr:uid="{358FD447-F001-4542-8241-BDFF57D7B07B}"/>
+    <hyperlink ref="J42" r:id="rId22" xr:uid="{1ED5C51D-5B86-4158-899A-91CF0E8D8383}"/>
+    <hyperlink ref="J44" r:id="rId23" xr:uid="{73065470-AC3E-474F-8314-200EB91CEBDA}"/>
+    <hyperlink ref="J45" r:id="rId24" xr:uid="{05D8262E-3AC4-400E-BA68-F87D0EDBAC00}"/>
+    <hyperlink ref="J46" r:id="rId25" xr:uid="{C640ED26-FA31-4F92-BBAD-6689D85DE5D5}"/>
+    <hyperlink ref="J47" r:id="rId26" xr:uid="{32AC0497-F751-4EF8-B827-32DDC79A7B31}"/>
+    <hyperlink ref="J49" r:id="rId27" xr:uid="{F980732B-8020-4598-88A2-738F244D16F1}"/>
+    <hyperlink ref="J51" r:id="rId28" xr:uid="{6FD4EF62-00D3-4D53-B29C-404A3B6A1C31}"/>
+    <hyperlink ref="J55" r:id="rId29" xr:uid="{11A7EFD0-C3B2-45B0-A39C-9DD4689951CA}"/>
+    <hyperlink ref="J57" r:id="rId30" xr:uid="{0C852B78-EB2B-4DEF-BD58-B49B9A942A2B}"/>
+    <hyperlink ref="J69" r:id="rId31" xr:uid="{848059F8-EC57-4D72-ACEF-664F8245C011}"/>
+    <hyperlink ref="J71" r:id="rId32" xr:uid="{B21DE554-CFE0-4E7C-9C87-5E17D6613793}"/>
+    <hyperlink ref="J73" r:id="rId33" xr:uid="{A7C7383A-3770-48C7-8A3B-A4D18C3E6630}"/>
+    <hyperlink ref="J76" r:id="rId34" xr:uid="{2AA2CF6B-7D55-49FE-A05E-4A694ABF8191}"/>
+    <hyperlink ref="J77" r:id="rId35" xr:uid="{D5D7C6A8-F4DF-4241-A058-90732C6CEBB4}"/>
+    <hyperlink ref="J78" r:id="rId36" xr:uid="{E57156FF-C895-4591-90A4-E8722429F5D8}"/>
+    <hyperlink ref="J80" r:id="rId37" xr:uid="{0405EBA7-7802-4487-8D6C-2CEAEFB5682B}"/>
+    <hyperlink ref="J83" r:id="rId38" xr:uid="{619C0695-8990-4C67-9B48-897A4C5F8056}"/>
+    <hyperlink ref="J84" r:id="rId39" xr:uid="{26DBC0F5-795F-4028-A6E8-FC093588340F}"/>
+    <hyperlink ref="J85" r:id="rId40" xr:uid="{7798A97F-7A4D-45CA-B593-13BF9D5C8A82}"/>
+    <hyperlink ref="J86" r:id="rId41" xr:uid="{12F7B17C-6010-4178-AD78-BAE31F66FEEC}"/>
+    <hyperlink ref="J87" r:id="rId42" xr:uid="{79AD77BD-F98A-4C63-9AC6-245E8264AE45}"/>
+    <hyperlink ref="J88" r:id="rId43" xr:uid="{AF72A5E5-553B-4C08-A368-81AC58877DAA}"/>
+    <hyperlink ref="J89" r:id="rId44" xr:uid="{E384FA46-1267-4D38-B292-D36B72E58A7C}"/>
+    <hyperlink ref="J91" r:id="rId45" xr:uid="{17802515-5786-40F2-A245-F9ECD92FC517}"/>
+    <hyperlink ref="J95" r:id="rId46" xr:uid="{102A5220-793E-4E96-A310-8F5DF99CEE7C}"/>
+    <hyperlink ref="J96" r:id="rId47" xr:uid="{97BD398B-B85B-463F-948B-5005DD5227C3}"/>
+    <hyperlink ref="J99" r:id="rId48" xr:uid="{54EDED40-DA79-444E-8CC9-B5AA9AB6E2B3}"/>
+    <hyperlink ref="J102" r:id="rId49" xr:uid="{B336CCF5-1E96-4853-A2BD-3D4860C2F288}"/>
+    <hyperlink ref="J103" r:id="rId50" xr:uid="{87EF8BA9-12E6-460A-8AC5-DCD2E253A2F2}"/>
+    <hyperlink ref="J106" r:id="rId51" xr:uid="{9105FDC7-F081-4D54-AF66-238A4910FC43}"/>
+    <hyperlink ref="J108" r:id="rId52" xr:uid="{3B8963F7-A259-4DD1-A7D6-5A17A3CBA6E6}"/>
+    <hyperlink ref="J111" r:id="rId53" xr:uid="{FF1C7C37-A2F3-4379-802E-92F8AA22261D}"/>
+    <hyperlink ref="J112" r:id="rId54" xr:uid="{FDD84049-4454-4D79-BE07-85727643A32F}"/>
+    <hyperlink ref="J114" r:id="rId55" xr:uid="{26C98585-4452-46CA-AF7E-51CCD33EB059}"/>
+    <hyperlink ref="J115" r:id="rId56" xr:uid="{0B267DFF-CF12-4FD6-9643-1AFB08B8413D}"/>
+    <hyperlink ref="J116" r:id="rId57" xr:uid="{03971458-09E8-4251-8CFF-A3F57AD7D908}"/>
+    <hyperlink ref="J117" r:id="rId58" xr:uid="{F414BCA8-23D7-45FD-A358-222E43B0535F}"/>
+    <hyperlink ref="J118" r:id="rId59" xr:uid="{E6677820-87AF-4836-ACEB-67B145E7A26F}"/>
+    <hyperlink ref="J119" r:id="rId60" xr:uid="{3758B9DA-5C7D-4936-94C9-7E4F18125A5F}"/>
+    <hyperlink ref="J120" r:id="rId61" xr:uid="{A0D819A3-B6AF-48C2-9954-EBE5D2A9C5E8}"/>
+    <hyperlink ref="J122" r:id="rId62" xr:uid="{C2559072-9FC9-4D47-9340-B64A48831C01}"/>
+    <hyperlink ref="J136" r:id="rId63" xr:uid="{BB10ACCD-7223-490D-ABCC-F8149AB09292}"/>
+    <hyperlink ref="J140" r:id="rId64" xr:uid="{7DC551A2-1589-4878-938F-D5DFB1932E98}"/>
+    <hyperlink ref="J143" r:id="rId65" xr:uid="{E76B1A58-43AE-48BE-87F6-A48DA22AB625}"/>
+    <hyperlink ref="J144" r:id="rId66" xr:uid="{08641C2D-0D3D-4C97-B42A-A58153DCCBFC}"/>
+    <hyperlink ref="J145" r:id="rId67" xr:uid="{26EFB9D4-F931-45E3-B7B1-7B3A6782088D}"/>
+    <hyperlink ref="J148" r:id="rId68" xr:uid="{9F1A70B7-EB31-4C7D-A4ED-4769C2AF4D7D}"/>
+    <hyperlink ref="J150" r:id="rId69" xr:uid="{8D4018E8-5819-4188-B521-B655C0F96485}"/>
+    <hyperlink ref="J155" r:id="rId70" xr:uid="{8DAC85C3-BA1C-4F04-BC56-23E0AED3E9A4}"/>
+    <hyperlink ref="J158" r:id="rId71" xr:uid="{16DEA54F-7213-481A-8B9F-E569000F6F2C}"/>
+    <hyperlink ref="J159" r:id="rId72" xr:uid="{56BD6924-8802-4222-BD05-AE1902F61469}"/>
+    <hyperlink ref="J160" r:id="rId73" xr:uid="{CF609295-917E-4DEF-B6EF-82E85F64B69A}"/>
+    <hyperlink ref="J162" r:id="rId74" xr:uid="{D651A4EA-538E-4076-BDD9-542D4C47845C}"/>
+    <hyperlink ref="J163" r:id="rId75" xr:uid="{8464A5C1-5C7D-4AC3-A778-D2B3786AF55F}"/>
+    <hyperlink ref="J164" r:id="rId76" xr:uid="{388B322E-FDC2-4A9C-A808-D9A0F164DFD7}"/>
+    <hyperlink ref="J165" r:id="rId77" xr:uid="{38CECFEC-6870-48EA-82CE-DBDD0D1784FE}"/>
+    <hyperlink ref="J168" r:id="rId78" xr:uid="{AB3EEDD9-18DC-4921-A186-43481FFE5465}"/>
+    <hyperlink ref="J169" r:id="rId79" xr:uid="{B1A34AD1-B984-4CE8-84E9-B2BE4126DC47}"/>
+    <hyperlink ref="J172" r:id="rId80" xr:uid="{982541D5-184F-4D09-9A15-52CF391B7B27}"/>
+    <hyperlink ref="J174" r:id="rId81" xr:uid="{88E47D8C-C152-4284-BC71-5AFBB3120AED}"/>
+    <hyperlink ref="J176" r:id="rId82" xr:uid="{ED3B88E8-55AC-45CA-8FF1-9309E45A0BE8}"/>
+    <hyperlink ref="J180" r:id="rId83" xr:uid="{E9B0F3DE-4337-404E-A3ED-BADFEEE6E681}"/>
+    <hyperlink ref="J184" r:id="rId84" xr:uid="{B4A5D6E0-85E2-47A4-B2DA-4D33C44A616B}"/>
+    <hyperlink ref="J189" r:id="rId85" xr:uid="{54816F3A-21FB-4B57-B692-A4D3AF5A4C03}"/>
+    <hyperlink ref="J192" r:id="rId86" xr:uid="{2AA4F8C4-9140-4410-BD37-2796594237EF}"/>
+    <hyperlink ref="J193" r:id="rId87" xr:uid="{3973CB73-A1A8-4836-9002-7D800E77C13C}"/>
+    <hyperlink ref="J194" r:id="rId88" xr:uid="{345AE80E-DB2D-41A4-9B4A-DE2F5E47D95E}"/>
+    <hyperlink ref="J195" r:id="rId89" xr:uid="{C4CBA5A5-96D8-4451-B86F-F30945D741C4}"/>
+    <hyperlink ref="J196" r:id="rId90" xr:uid="{72E6B6A0-7DC1-417A-AA86-97BFB5CFEC6A}"/>
+    <hyperlink ref="J197" r:id="rId91" xr:uid="{6B6E24BE-B045-45FF-8EAB-7A608C7CE96E}"/>
+    <hyperlink ref="J198" r:id="rId92" xr:uid="{178EA191-192E-43FF-9F40-A9E7831A3D81}"/>
+    <hyperlink ref="J201" r:id="rId93" xr:uid="{9EFE9EFE-5389-4837-A970-B9078DE63BE2}"/>
+    <hyperlink ref="J202" r:id="rId94" xr:uid="{D043B9CE-4534-416E-87E0-0F3A655CD8CC}"/>
+    <hyperlink ref="J204" r:id="rId95" xr:uid="{F4507B65-720A-43FD-8AA0-FA70AE6B98EB}"/>
+    <hyperlink ref="J205" r:id="rId96" xr:uid="{5667A71D-36BC-4749-838B-DBB2578F6549}"/>
+    <hyperlink ref="J206" r:id="rId97" xr:uid="{495B8238-CB12-4565-9BA3-0EDB84AE3467}"/>
+    <hyperlink ref="J207" r:id="rId98" xr:uid="{FFB4A62B-EB35-4B34-BE7C-B3A96EB398B8}"/>
+    <hyperlink ref="J208" r:id="rId99" xr:uid="{31D4442A-CBEC-4A7A-82D2-B90DDF1CE649}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId78"/>
+  <pageSetup orientation="portrait" r:id="rId100"/>
   <tableParts count="1">
-    <tablePart r:id="rId79"/>
+    <tablePart r:id="rId101"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2808F767-264D-4A85-8954-20197F0AEAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF509C6-6DAA-4C81-A9BA-EB02EDACA255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="610">
   <si>
     <t>Fecha</t>
   </si>
@@ -201,418 +201,64 @@
     <t>DIAZ OMAR EDUARDO</t>
   </si>
   <si>
-    <t>MR29KMM873EO</t>
-  </si>
-  <si>
-    <t>01:03 p. m.</t>
-  </si>
-  <si>
     <t>ROMERO PARAVICINI DIANA DE JESUS</t>
   </si>
   <si>
-    <t>Faltan 3d 43 en combo se retira la boleta</t>
-  </si>
-  <si>
-    <t>Retirá la mercadería — no se puede entregar — Mal armado</t>
-  </si>
-  <si>
-    <t>MR2A2I7BWPG0</t>
-  </si>
-  <si>
-    <t>01:16 p. m.</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782922593/zws7uuuwhjv5mjfiarum.jpg</t>
-  </si>
-  <si>
-    <t>MR2AWLEPTW6Q</t>
-  </si>
-  <si>
     <t>01:40 p. m.</t>
   </si>
   <si>
-    <t>Enviaron 2 acanalas x 450 en lugar del Doritos pizza</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782924002/kxjsxegebewybohisemv.jpg</t>
-  </si>
-  <si>
-    <t>MR2B4LSK2Z57</t>
-  </si>
-  <si>
-    <t>Rechaza suerox frutilla vto corto</t>
-  </si>
-  <si>
-    <t>MR2CNDZNDMWQ</t>
-  </si>
-  <si>
-    <t>02:29 p. m.</t>
-  </si>
-  <si>
-    <t>Faltaron 4 quaker inst 280</t>
-  </si>
-  <si>
-    <t>MR2COOL0UDO1</t>
-  </si>
-  <si>
-    <t>02:30 p. m.</t>
-  </si>
-  <si>
-    <t>5 Satur negros no pidio</t>
-  </si>
-  <si>
-    <t>MR2EJIAJD26M</t>
-  </si>
-  <si>
-    <t>03:22 p. m.</t>
-  </si>
-  <si>
     <t>OYOLA GASTON AGUSTIN</t>
   </si>
   <si>
-    <t>Gelatina cereza</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782930131/o5sdmkst14mtppnqoqow.jpg</t>
-  </si>
-  <si>
-    <t>MR2EN6E5CF7S</t>
-  </si>
-  <si>
     <t>03:25 p. m.</t>
   </si>
   <si>
-    <t>Falto 3 ketchup 77 grs</t>
-  </si>
-  <si>
-    <t>MR2J5T1FNEAZ</t>
-  </si>
-  <si>
-    <t>05:32 p. m.</t>
-  </si>
-  <si>
     <t>BERNAHOLA JORGE AGUSTIN</t>
   </si>
   <si>
-    <t>Alfajores fantoche origen</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782937879/aneezbmhrsnc2ic1x8t8.jpg</t>
-  </si>
-  <si>
-    <t>MR2J8QF9QLX8</t>
-  </si>
-  <si>
-    <t>05:34 p. m.</t>
-  </si>
-  <si>
-    <t>No pidió tostadas sin sal</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782938001/i1gucphkh8hxf6otefnt.jpg</t>
-  </si>
-  <si>
-    <t>MR2MSPQNRHS3</t>
-  </si>
-  <si>
-    <t>07:13 p. m.</t>
-  </si>
-  <si>
     <t>ROMANO RODRIGO ERNESTO</t>
   </si>
   <si>
     <t>BAZAN LUCIANO MANUEL</t>
   </si>
   <si>
-    <t>Cronico</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782943976/rtgn8sqtjartamvukfzb.jpg</t>
-  </si>
-  <si>
-    <t>MR2MTZ2PGFO8</t>
-  </si>
-  <si>
-    <t>07:14 p. m.</t>
-  </si>
-  <si>
-    <t>Pedido anulado</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782944039/wsomtyuvgo47oknnqgcv.jpg</t>
-  </si>
-  <si>
-    <t>MR3EMHTM4JAS</t>
-  </si>
-  <si>
-    <t>08:12 a. m.</t>
-  </si>
-  <si>
     <t>MOREIRA AIRALDI TOBIAS URIEL</t>
   </si>
   <si>
-    <t>Pepa frutos ro</t>
-  </si>
-  <si>
-    <t>MR3F0GJ1MLBG</t>
-  </si>
-  <si>
-    <t>08:23 a. m.</t>
-  </si>
-  <si>
-    <t>Dice que pidió Cheetos de ketchup y desc lays de queso y cebolla también</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782991394/yfpvrup2oq1ax6e3wlr9.jpg</t>
-  </si>
-  <si>
-    <t>MR3GRXN4GGOZ</t>
-  </si>
-  <si>
     <t>MARTINEZ PEREZ JORGE LEANDRO</t>
   </si>
   <si>
-    <t>MR3HT7S57CL6</t>
-  </si>
-  <si>
-    <t>09:41 a. m.</t>
-  </si>
-  <si>
     <t>GONZALEZ CECILIA GUADALUPE</t>
   </si>
   <si>
-    <t>Fue 5 Doritos queso 20gr</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1782996069/uky5bx6q33af7tidwjpf.jpg</t>
-  </si>
-  <si>
-    <t>MR3IGPISJY3J</t>
-  </si>
-  <si>
-    <t>09:59 a. m.</t>
-  </si>
-  <si>
-    <t>Spped 12u</t>
-  </si>
-  <si>
-    <t>MR3IPWHY01TI</t>
-  </si>
-  <si>
     <t>10:06 a. m.</t>
   </si>
   <si>
-    <t>Faltó 4</t>
-  </si>
-  <si>
-    <t>MR3JKLP69F1C</t>
-  </si>
-  <si>
-    <t>Falto Luchetti tirabuzón al huevo 4 und
-Y favorita biz de chocolate sin stock</t>
-  </si>
-  <si>
-    <t>MR3KXOTYG0DG</t>
-  </si>
-  <si>
     <t>11:08 a. m.</t>
   </si>
   <si>
-    <t>Falta pep comun</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783001315/bjg3jdqkhdmicebyci3e.jpg</t>
-  </si>
-  <si>
-    <t>MR3L7CE5O3ZJ</t>
-  </si>
-  <si>
-    <t>11:16 a. m.</t>
-  </si>
-  <si>
     <t>PULIDO LARA EFRAIM JOSE</t>
   </si>
   <si>
-    <t>MR3L6745RAUN</t>
-  </si>
-  <si>
-    <t>Pep comun sin stock y arroz gallo 1 roto</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783001750/qol7e6heqxn9jybkuvix.jpg</t>
-  </si>
-  <si>
-    <t>Retirá la mercadería — no se puede entregar — El arroz es de mi compañera de Molinos, Mariana</t>
-  </si>
-  <si>
-    <t>MR3LL1LNQHS0</t>
-  </si>
-  <si>
     <t>11:27 a. m.</t>
   </si>
   <si>
     <t>GONZALEZ MARIA CANDELARIA</t>
   </si>
   <si>
-    <t>Rechazo 18 suerox</t>
-  </si>
-  <si>
-    <t>MR3LO7T96SNU</t>
-  </si>
-  <si>
     <t>11:29 a. m.</t>
   </si>
   <si>
-    <t>MR3MH631X5CD</t>
-  </si>
-  <si>
-    <t>11:51 a. m.</t>
-  </si>
-  <si>
-    <t>Una sal entrefina de kilo rota</t>
-  </si>
-  <si>
-    <t>MR3MJDT2R9BV</t>
-  </si>
-  <si>
     <t>MORENO LOBO JOHAN JAVIER</t>
   </si>
   <si>
-    <t>MR3MJSKO7G08</t>
-  </si>
-  <si>
-    <t>11:53 a. m.</t>
-  </si>
-  <si>
-    <t>MR3N71UBV02V</t>
-  </si>
-  <si>
-    <t>12:12 p. m.</t>
-  </si>
-  <si>
-    <t>Falto 1 cheto crema 85 grs</t>
-  </si>
-  <si>
-    <t>Retirá la mercadería — no se puede entregar — Llamé al cliente pero no contesta. Vuelvo a llamar en un rato.</t>
-  </si>
-  <si>
-    <t>MR3NJJDWUWF4</t>
-  </si>
-  <si>
-    <t>12:22 p. m.</t>
-  </si>
-  <si>
-    <t>Faltaron 6 Doritos 40 grs</t>
-  </si>
-  <si>
-    <t>MR3NJH2VTGFC</t>
-  </si>
-  <si>
-    <t>12:21 p. m.</t>
-  </si>
-  <si>
-    <t>MR3NLAT53H7S</t>
-  </si>
-  <si>
-    <t>12:23 p. m.</t>
-  </si>
-  <si>
-    <t>Pedido repatido</t>
-  </si>
-  <si>
-    <t>MR3ODZDXQ4WL</t>
-  </si>
-  <si>
-    <t>12:45 p. m.</t>
-  </si>
-  <si>
-    <t>Faltó 8 chetos x 43</t>
-  </si>
-  <si>
-    <t>MR3OPIDMD96B</t>
-  </si>
-  <si>
     <t>12:54 p. m.</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783007654/owwtzhmfamgpjkgu1arc.jpg</t>
-  </si>
-  <si>
-    <t>MR3P3JM7EAOA</t>
-  </si>
-  <si>
-    <t>MR3PG6IMAVR8</t>
-  </si>
-  <si>
-    <t>01:15 p. m.</t>
-  </si>
-  <si>
     <t>MOLINA JORGE GABRIEL</t>
   </si>
   <si>
-    <t>No quiso el pedido</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783008899/rhnzk5jdqulz2rxvilym.jpg</t>
-  </si>
-  <si>
-    <t>MR3PY8X17JA3</t>
-  </si>
-  <si>
-    <t>MR3Q66N766Z8</t>
-  </si>
-  <si>
-    <t>01:35 p. m.</t>
-  </si>
-  <si>
-    <t>Rechaza pepsico 
-Higienol max</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783010114/do52fcrlgmwmu2g5j0hg.jpg</t>
-  </si>
-  <si>
-    <t>MR3Q96VHFU6Y</t>
-  </si>
-  <si>
-    <t>MR3QEUGCYQA3</t>
-  </si>
-  <si>
     <t>01:42 p. m.</t>
-  </si>
-  <si>
-    <t>MR3QITX00IAD</t>
-  </si>
-  <si>
-    <t>01:45 p. m.</t>
-  </si>
-  <si>
-    <t>Le falta 1 Doritos ala tira
-Desarmo otro cl</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783010703/zfy2gpqjea5jvdwwvwu5.jpg</t>
-  </si>
-  <si>
-    <t>MR3QV8RB4202</t>
-  </si>
-  <si>
-    <t>01:55 p. m.</t>
-  </si>
-  <si>
-    <t>Le falta una máquina ala tira</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783011282/jlkexb6inkruimkajlk3.jpg</t>
-  </si>
-  <si>
-    <t>MR3QX9GZNCM3</t>
-  </si>
-  <si>
-    <t>Segunda ves que paso</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783011379/z6yadgzmisefvn6hjc5q.jpg</t>
   </si>
   <si>
     <t>MR3RA4Q9519W</t>
@@ -1829,6 +1475,396 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783512093/vgszaq71ibfmk9abzt4i.jpg</t>
+  </si>
+  <si>
+    <t>MRC1PYRG3R9J</t>
+  </si>
+  <si>
+    <t>09:24 a. m.</t>
+  </si>
+  <si>
+    <t>Dinamita x 45 no venden</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783513415/vvlthfbsk1uacuiq0nmr.jpg</t>
+  </si>
+  <si>
+    <t>MRC2BHM645MX</t>
+  </si>
+  <si>
+    <t>09:37 a. m.</t>
+  </si>
+  <si>
+    <t>Falto 1 paq</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783514238/cymcchumnc6kmkln5qdz.jpg</t>
+  </si>
+  <si>
+    <t>MRC2OMM7ZC2B</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783514852/lteuge41jndsscmua42q.jpg</t>
+  </si>
+  <si>
+    <t>MRC2O9UH6DF0</t>
+  </si>
+  <si>
+    <t>6 sexy fish</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783514845/x0ipk12emigzpx2vddgd.jpg</t>
+  </si>
+  <si>
+    <t>MRC2U8S97RE7</t>
+  </si>
+  <si>
+    <t>09:52 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783515111/hbzfaq2trji3t7s5py1w.jpg</t>
+  </si>
+  <si>
+    <t>MRC3FPGWF63N</t>
+  </si>
+  <si>
+    <t>10:08 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783516115/qshugmysuyboqruwbcim.jpg</t>
+  </si>
+  <si>
+    <t>MRC3GMAZFL5G</t>
+  </si>
+  <si>
+    <t>10:09 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783516155/wivsvsxpu1ij22v9mv8q.jpg</t>
+  </si>
+  <si>
+    <t>MRC3KLTZ77I9</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783516344/v5ryabsb6hzhgpxv2zan.jpg</t>
+  </si>
+  <si>
+    <t>MRC3QIF6FV3Z</t>
+  </si>
+  <si>
+    <t>10:17 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783516627/iyxbr0is07hrsjaht28s.jpg</t>
+  </si>
+  <si>
+    <t>MRC3W0RT27B3</t>
+  </si>
+  <si>
+    <t>Alfajores tody 20 unidades</t>
+  </si>
+  <si>
+    <t>MRC447364WA1</t>
+  </si>
+  <si>
+    <t>10:28 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783517258/rp4fqk3sxqxaykp0wxjf.jpg</t>
+  </si>
+  <si>
+    <t>MRC47534P132</t>
+  </si>
+  <si>
+    <t>Faltó 5 Doritos pizza 35gr</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783517422/dalkbhkwztmqjjjtar77.jpg</t>
+  </si>
+  <si>
+    <t>MRC4KYGY57H4</t>
+  </si>
+  <si>
+    <t>10:40 a. m.</t>
+  </si>
+  <si>
+    <t>6 doritos 40</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783518037/hha8kgshuu8rvx09jqj1.jpg</t>
+  </si>
+  <si>
+    <t>MRC4PAYUNI4L</t>
+  </si>
+  <si>
+    <t>10:44 a. m.</t>
+  </si>
+  <si>
+    <t>MRC4X6Q9IBB9</t>
+  </si>
+  <si>
+    <t>Falto 3 d 143g</t>
+  </si>
+  <si>
+    <t>MRC5KRBJLH8F</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783519717/enjbo3aqrjtpuxbod6jx.jpg</t>
+  </si>
+  <si>
+    <t>MRC5PPPVCRAM</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783519947/wwv0ihwfkbiie1ukuaa9.jpg</t>
+  </si>
+  <si>
+    <t>MRC5RRKHKLTO</t>
+  </si>
+  <si>
+    <t>11:14 a. m.</t>
+  </si>
+  <si>
+    <t>1 paq roto</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783520038/bxewymepuzbc76p0i4pm.jpg</t>
+  </si>
+  <si>
+    <t>MRC5SWCBDWI5</t>
+  </si>
+  <si>
+    <t>Rechaza sal rotas</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783520095/uf0cygxgzryetwzx3cpo.jpg</t>
+  </si>
+  <si>
+    <t>MRC5X61K4QJ4</t>
+  </si>
+  <si>
+    <t>11:18 a. m.</t>
+  </si>
+  <si>
+    <t>Cerrado 11:18 hrs</t>
+  </si>
+  <si>
+    <t>MRC685R8ZM2X</t>
+  </si>
+  <si>
+    <t>S fecha de vencimiento</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783520815/djwptlj4idau2zhphz73.jpg</t>
+  </si>
+  <si>
+    <t>MRC6SD6NX1AU</t>
+  </si>
+  <si>
+    <t>20 toddy alfajores</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783521746/foppzjwiheyhv3uxaig9.jpg</t>
+  </si>
+  <si>
+    <t>MRC7J8QESRGO</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783522992/gkrp5rbie0hdqlylxefy.jpg</t>
+  </si>
+  <si>
+    <t>MRC7QHNIO6AY</t>
+  </si>
+  <si>
+    <t>12:09 p. m.</t>
+  </si>
+  <si>
+    <t>Sin stock alfajores toddy</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Sin stock, se descuenta la mercadería</t>
+  </si>
+  <si>
+    <t>MRC7X5U1RWNF</t>
+  </si>
+  <si>
+    <t>12:14 p. m.</t>
+  </si>
+  <si>
+    <t>Mandaron doritos</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783523659/kgl5xrhqyheooqxf8sql.jpg</t>
+  </si>
+  <si>
+    <t>MRC8F496HAAT</t>
+  </si>
+  <si>
+    <t>10 Alf Marley blanco</t>
+  </si>
+  <si>
+    <t>MRC8I3AP40R2</t>
+  </si>
+  <si>
+    <t>12:31 p. m.</t>
+  </si>
+  <si>
+    <t>Faltan los alfajores full maní x 12 y los chocolates full maní</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783524642/aczdzqdxra7ctne9lfpo.jpg</t>
+  </si>
+  <si>
+    <t>MRC8WXM91OSF</t>
+  </si>
+  <si>
+    <t>12:42 p. m.</t>
+  </si>
+  <si>
+    <t>Faltaron</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783525334/baqrteeh6czhoapuxu1r.jpg</t>
+  </si>
+  <si>
+    <t>MRC9EKLRIZD7</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783526140/lfxhuua8ila0dtljvpyo.jpg</t>
+  </si>
+  <si>
+    <t>MRC9KC6Y5QSG</t>
+  </si>
+  <si>
+    <t>01:00 p. m.</t>
+  </si>
+  <si>
+    <t>Dice que si no es cuenta corriente no paga</t>
+  </si>
+  <si>
+    <t>Dejá el pedido, lo resuelvo después — Estoy hablando con Naty para que se lo puedan dejar</t>
+  </si>
+  <si>
+    <t>MRC9Z501TYC6</t>
+  </si>
+  <si>
+    <t>01:12 p. m.</t>
+  </si>
+  <si>
+    <t>Pasé 3 veces nunca abrió la cl</t>
+  </si>
+  <si>
+    <t>MRCA2F6M40BB</t>
+  </si>
+  <si>
+    <t>01:14 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783527259/helthfdtswfk7f7y3jsw.jpg</t>
+  </si>
+  <si>
+    <t>MRCB1NSZSDF3</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783528896/xun2rp6bqrrzusfgwfud.jpg</t>
+  </si>
+  <si>
+    <t>MRCBNG6VSF83</t>
+  </si>
+  <si>
+    <t>01:59 p. m.</t>
+  </si>
+  <si>
+    <t>Mandaron 6 Doritos de 129 gts y estaba facturado chettos de 140 grs</t>
+  </si>
+  <si>
+    <t>MRCCO035VU68</t>
+  </si>
+  <si>
+    <t>02:27 p. m.</t>
+  </si>
+  <si>
+    <t>6 galletas de salvado ind x 110gr</t>
+  </si>
+  <si>
+    <t>MRCDAL0XPZXB</t>
+  </si>
+  <si>
+    <t>02:45 p. m.</t>
+  </si>
+  <si>
+    <t>12 elixir cacao 5 twistos queso 155grs</t>
+  </si>
+  <si>
+    <t>MRCDCQ9BBM16</t>
+  </si>
+  <si>
+    <t>02:46 p. m.</t>
+  </si>
+  <si>
+    <t>Falto 1 pehuamar acan 90grs</t>
+  </si>
+  <si>
+    <t>MRCDE8ZS17SB</t>
+  </si>
+  <si>
+    <t>02:48 p. m.</t>
+  </si>
+  <si>
+    <t>5 3d 85 grs por fecha corta no recibe</t>
+  </si>
+  <si>
+    <t>MRCDPKD5BF1N</t>
+  </si>
+  <si>
+    <t>Faltan 2 doritos 129g</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783533392/f2kydm7mhwxwiwtt9jjy.jpg</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Se descuentan 2 Doritos que faltaron</t>
+  </si>
+  <si>
+    <t>MRCDXX23I5TR</t>
+  </si>
+  <si>
+    <t>03:03 p. m.</t>
+  </si>
+  <si>
+    <t>Zona peligrosa o camino malo</t>
+  </si>
+  <si>
+    <t>Mal geolocalizado. Zona roja</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783533768/q2kuik1yh9gemlwlidzp.jpg</t>
+  </si>
+  <si>
+    <t>MRCF47OORP43</t>
+  </si>
+  <si>
+    <t>03:35 p. m.</t>
+  </si>
+  <si>
+    <t>Faltaron 4 twistos 95 jamon</t>
+  </si>
+  <si>
+    <t>MRDK5GEXFZFS</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783604664/fui3urmibnlkydgontou.jpg</t>
+  </si>
+  <si>
+    <t>MREUKCYLQMTW</t>
+  </si>
+  <si>
+    <t>08:24 a. m.</t>
+  </si>
+  <si>
+    <t>Roto</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1783682621/tpgota6bxp18r71tl775.jpg</t>
   </si>
 </sst>
 </file>
@@ -1924,7 +1960,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -2007,57 +2043,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF284E3F"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF284E3F"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF284E3F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2115,36 +2106,6 @@
     </xf>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2546,77 +2507,77 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
-        <v>426</v>
-      </c>
-      <c r="B2" s="21">
+      <c r="A2" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" s="2">
         <v>46209</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="4">
+        <v>2797</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D2" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="23">
-        <v>2797</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25" t="s">
-        <v>427</v>
-      </c>
-      <c r="K2" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="L2" s="27">
+      <c r="L2" s="2">
         <v>46209</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="M2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="26">
+      <c r="N2" s="15">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>510</v>
+        <v>393</v>
       </c>
       <c r="B3" s="2">
         <v>46210</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>224</v>
+        <v>107</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F3" s="4">
         <v>4622</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="10" t="s">
         <v>17</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>512</v>
+        <v>394</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>395</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>21</v>
@@ -2633,19 +2594,19 @@
     </row>
     <row r="4" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>513</v>
+        <v>396</v>
       </c>
       <c r="B4" s="2">
         <v>46210</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>514</v>
+        <v>397</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F4" s="4">
         <v>4913</v>
@@ -2653,14 +2614,14 @@
       <c r="G4" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>516</v>
+        <v>398</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>399</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>21</v>
@@ -2677,19 +2638,19 @@
     </row>
     <row r="5" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>517</v>
+        <v>400</v>
       </c>
       <c r="B5" s="2">
         <v>46210</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>518</v>
+        <v>401</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F5" s="4">
         <v>4885</v>
@@ -2697,17 +2658,17 @@
       <c r="G5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>520</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
       <c r="M5" s="3" t="s">
         <v>18</v>
       </c>
@@ -2717,19 +2678,19 @@
     </row>
     <row r="6" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>521</v>
+        <v>404</v>
       </c>
       <c r="B6" s="2">
         <v>46210</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>518</v>
+        <v>401</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F6" s="4">
         <v>4892</v>
@@ -2737,17 +2698,17 @@
       <c r="G6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
       <c r="M6" s="3" t="s">
         <v>18</v>
       </c>
@@ -2757,13 +2718,13 @@
     </row>
     <row r="7" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>524</v>
+        <v>407</v>
       </c>
       <c r="B7" s="2">
         <v>46210</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>525</v>
+        <v>408</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>14</v>
@@ -2777,17 +2738,17 @@
       <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="6" t="s">
-        <v>526</v>
-      </c>
-      <c r="K7" s="6" t="s">
+      <c r="I7" s="6"/>
+      <c r="J7" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="2">
         <v>46210</v>
       </c>
       <c r="M7" s="3" t="s">
@@ -2799,13 +2760,13 @@
     </row>
     <row r="8" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>527</v>
+        <v>410</v>
       </c>
       <c r="B8" s="2">
         <v>46210</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>528</v>
+      <c r="C8" s="3" t="s">
+        <v>411</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>14</v>
@@ -2819,14 +2780,14 @@
       <c r="G8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>529</v>
+      <c r="I8" s="3" t="s">
+        <v>412</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>530</v>
+        <v>413</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
@@ -2839,13 +2800,13 @@
     </row>
     <row r="9" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>531</v>
+        <v>414</v>
       </c>
       <c r="B9" s="2">
         <v>46210</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>532</v>
+        <v>415</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>14</v>
@@ -2859,10 +2820,10 @@
       <c r="G9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="3"/>
+      <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
@@ -2875,13 +2836,13 @@
     </row>
     <row r="10" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>533</v>
+        <v>416</v>
       </c>
       <c r="B10" s="2">
         <v>46210</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>532</v>
+        <v>415</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>14</v>
@@ -2895,11 +2856,11 @@
       <c r="G10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I10" s="6"/>
-      <c r="J10" s="9"/>
+      <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="3" t="s">
@@ -2911,13 +2872,13 @@
     </row>
     <row r="11" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>534</v>
+        <v>417</v>
       </c>
       <c r="B11" s="2">
         <v>46210</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>532</v>
+        <v>415</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>14</v>
@@ -2931,17 +2892,17 @@
       <c r="G11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="J11" s="9"/>
-      <c r="K11" s="6" t="s">
+      <c r="I11" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="2">
         <v>46210</v>
       </c>
       <c r="M11" s="3" t="s">
@@ -2953,13 +2914,13 @@
     </row>
     <row r="12" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>536</v>
+        <v>419</v>
       </c>
       <c r="B12" s="2">
         <v>46210</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>537</v>
+      <c r="C12" s="3" t="s">
+        <v>420</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>14</v>
@@ -2971,15 +2932,15 @@
         <v>1389</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="J12" s="9"/>
+        <v>421</v>
+      </c>
+      <c r="J12" s="6"/>
       <c r="K12" s="3" t="s">
         <v>25</v>
       </c>
@@ -2995,13 +2956,13 @@
     </row>
     <row r="13" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>539</v>
+        <v>422</v>
       </c>
       <c r="B13" s="2">
         <v>46210</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>540</v>
+        <v>423</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>14</v>
@@ -3019,13 +2980,13 @@
         <v>20</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>535</v>
+        <v>418</v>
       </c>
       <c r="J13" s="6"/>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="2">
         <v>46210</v>
       </c>
       <c r="M13" s="3" t="s">
@@ -3037,13 +2998,13 @@
     </row>
     <row r="14" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>541</v>
+        <v>424</v>
       </c>
       <c r="B14" s="2">
         <v>46210</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>542</v>
+        <v>425</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>14</v>
@@ -3057,13 +3018,13 @@
       <c r="G14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="J14" s="9"/>
+      <c r="I14" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="J14" s="6"/>
       <c r="K14" s="3" t="s">
         <v>31</v>
       </c>
@@ -3079,13 +3040,13 @@
     </row>
     <row r="15" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>544</v>
+        <v>427</v>
       </c>
       <c r="B15" s="2">
         <v>46210</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>545</v>
+        <v>428</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>14</v>
@@ -3103,11 +3064,11 @@
         <v>30</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>546</v>
+        <v>429</v>
       </c>
       <c r="J15" s="6"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="2"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
       <c r="M15" s="3" t="s">
         <v>18</v>
       </c>
@@ -3117,13 +3078,13 @@
     </row>
     <row r="16" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>547</v>
+        <v>430</v>
       </c>
       <c r="B16" s="2">
         <v>46210</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>548</v>
+      <c r="C16" s="3" t="s">
+        <v>431</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>14</v>
@@ -3137,15 +3098,15 @@
       <c r="G16" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="J16" s="9"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
       <c r="M16" s="3" t="s">
         <v>18</v>
       </c>
@@ -3155,13 +3116,13 @@
     </row>
     <row r="17" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>550</v>
+        <v>433</v>
       </c>
       <c r="B17" s="2">
         <v>46210</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>551</v>
+        <v>434</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>14</v>
@@ -3175,13 +3136,13 @@
       <c r="G17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="J17" s="9"/>
+        <v>435</v>
+      </c>
+      <c r="J17" s="6"/>
       <c r="K17" s="3" t="s">
         <v>21</v>
       </c>
@@ -3197,13 +3158,13 @@
     </row>
     <row r="18" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>553</v>
+        <v>436</v>
       </c>
       <c r="B18" s="2">
         <v>46210</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>554</v>
+        <v>437</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>14</v>
@@ -3217,13 +3178,13 @@
       <c r="G18" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="3"/>
+      <c r="I18" s="6"/>
       <c r="J18" s="6"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="2"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
       <c r="M18" s="3" t="s">
         <v>18</v>
       </c>
@@ -3233,13 +3194,13 @@
     </row>
     <row r="19" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>555</v>
+        <v>438</v>
       </c>
       <c r="B19" s="2">
         <v>46210</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>554</v>
+        <v>437</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>14</v>
@@ -3253,13 +3214,13 @@
       <c r="G19" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I19" s="3"/>
+      <c r="I19" s="6"/>
       <c r="J19" s="6"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="2"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
       <c r="M19" s="3" t="s">
         <v>18</v>
       </c>
@@ -3269,13 +3230,13 @@
     </row>
     <row r="20" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>556</v>
+        <v>439</v>
       </c>
       <c r="B20" s="2">
         <v>46210</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>557</v>
+      <c r="C20" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>14</v>
@@ -3289,13 +3250,13 @@
       <c r="G20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="J20" s="9"/>
+        <v>441</v>
+      </c>
+      <c r="J20" s="6"/>
       <c r="K20" s="3" t="s">
         <v>25</v>
       </c>
@@ -3311,13 +3272,13 @@
     </row>
     <row r="21" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>559</v>
+        <v>442</v>
       </c>
       <c r="B21" s="2">
         <v>46210</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>232</v>
+        <v>115</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>14</v>
@@ -3329,15 +3290,15 @@
         <v>1917</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="J21" s="9"/>
+        <v>443</v>
+      </c>
+      <c r="J21" s="6"/>
       <c r="K21" s="3" t="s">
         <v>25</v>
       </c>
@@ -3353,33 +3314,33 @@
     </row>
     <row r="22" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>561</v>
+        <v>444</v>
       </c>
       <c r="B22" s="2">
         <v>46210</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>562</v>
+      <c r="C22" s="3" t="s">
+        <v>445</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>563</v>
+        <v>446</v>
       </c>
       <c r="F22" s="4">
         <v>774</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="H22" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="H22" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>565</v>
-      </c>
-      <c r="J22" s="9"/>
+      <c r="I22" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="J22" s="6"/>
       <c r="K22" s="3" t="s">
         <v>25</v>
       </c>
@@ -3395,13 +3356,13 @@
     </row>
     <row r="23" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>566</v>
+        <v>449</v>
       </c>
       <c r="B23" s="2">
         <v>46210</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>567</v>
+        <v>450</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>14</v>
@@ -3413,13 +3374,13 @@
         <v>1834</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H23" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H23" s="13" t="s">
         <v>52</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>568</v>
+        <v>451</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="3" t="s">
@@ -3437,33 +3398,33 @@
     </row>
     <row r="24" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>569</v>
+        <v>452</v>
       </c>
       <c r="B24" s="2">
         <v>46210</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>570</v>
+      <c r="C24" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>571</v>
+        <v>454</v>
       </c>
       <c r="F24" s="4">
         <v>660</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="H24" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="H24" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I24" s="6"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="2"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
       <c r="M24" s="3" t="s">
         <v>18</v>
       </c>
@@ -3473,33 +3434,33 @@
     </row>
     <row r="25" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>573</v>
+        <v>456</v>
       </c>
       <c r="B25" s="2">
         <v>46210</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>574</v>
+        <v>457</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>571</v>
+        <v>454</v>
       </c>
       <c r="F25" s="4">
         <v>11251</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="H25" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="H25" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="J25" s="9"/>
+      <c r="I25" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="J25" s="6"/>
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
       <c r="M25" s="3" t="s">
@@ -3511,35 +3472,35 @@
     </row>
     <row r="26" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>576</v>
+        <v>459</v>
       </c>
       <c r="B26" s="2">
         <v>46210</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="16">
         <v>0.99861111111111112</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>577</v>
+        <v>460</v>
       </c>
       <c r="F26" s="4">
         <v>2105</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="H26" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="H26" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I26" s="6" t="s">
-        <v>579</v>
+      <c r="I26" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="J26" s="6"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="2"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
       <c r="M26" s="3" t="s">
         <v>18</v>
       </c>
@@ -3549,33 +3510,33 @@
     </row>
     <row r="27" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>580</v>
+        <v>463</v>
       </c>
       <c r="B27" s="2">
         <v>46210</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="16">
         <v>0.99930555555555556</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>577</v>
+        <v>460</v>
       </c>
       <c r="F27" s="4">
         <v>1857</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="H27" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="H27" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="6" t="s">
-        <v>581</v>
-      </c>
-      <c r="J27" s="9"/>
+      <c r="I27" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="J27" s="6"/>
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
       <c r="M27" s="3" t="s">
@@ -3587,33 +3548,33 @@
     </row>
     <row r="28" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>582</v>
+        <v>465</v>
       </c>
       <c r="B28" s="2">
         <v>46211</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="16">
         <v>0</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>577</v>
+        <v>460</v>
       </c>
       <c r="F28" s="4">
         <v>2183</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="H28" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="J28" s="9"/>
+        <v>466</v>
+      </c>
+      <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
       <c r="M28" s="3" t="s">
@@ -3625,39 +3586,39 @@
     </row>
     <row r="29" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>584</v>
+        <v>467</v>
       </c>
       <c r="B29" s="2">
         <v>46211</v>
       </c>
-      <c r="C29" s="11" t="s">
-        <v>585</v>
+      <c r="C29" s="3" t="s">
+        <v>468</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F29" s="4">
         <v>4178</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>586</v>
+        <v>469</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="K29" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="2">
         <v>46211</v>
       </c>
       <c r="M29" s="3" t="s">
@@ -3669,19 +3630,19 @@
     </row>
     <row r="30" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>588</v>
+        <v>471</v>
       </c>
       <c r="B30" s="2">
         <v>46211</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>589</v>
+        <v>472</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="F30" s="4">
         <v>5085</v>
@@ -3692,9 +3653,9 @@
       <c r="H30" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I30" s="3"/>
+      <c r="I30" s="6"/>
       <c r="J30" s="9" t="s">
-        <v>590</v>
+        <v>473</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>21</v>
@@ -3711,19 +3672,19 @@
     </row>
     <row r="31" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>588</v>
+        <v>471</v>
       </c>
       <c r="B31" s="2">
         <v>46211</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>589</v>
+        <v>472</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="F31" s="4">
         <v>5085</v>
@@ -3731,17 +3692,17 @@
       <c r="G31" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="10" t="s">
         <v>17</v>
       </c>
       <c r="I31" s="6"/>
       <c r="J31" s="9" t="s">
-        <v>590</v>
-      </c>
-      <c r="K31" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="2">
         <v>46211</v>
       </c>
       <c r="M31" s="3" t="s">
@@ -3753,13 +3714,13 @@
     </row>
     <row r="32" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>591</v>
+        <v>474</v>
       </c>
       <c r="B32" s="2">
         <v>46211</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>592</v>
+        <v>475</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>14</v>
@@ -3773,15 +3734,15 @@
       <c r="G32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>593</v>
+        <v>476</v>
       </c>
       <c r="J32" s="6"/>
       <c r="K32" s="3" t="s">
-        <v>594</v>
+        <v>477</v>
       </c>
       <c r="L32" s="2">
         <v>46211</v>
@@ -3795,19 +3756,19 @@
     </row>
     <row r="33" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>595</v>
+        <v>478</v>
       </c>
       <c r="B33" s="2">
         <v>46211</v>
       </c>
-      <c r="C33" s="11" t="s">
-        <v>353</v>
+      <c r="C33" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F33" s="4">
         <v>4477</v>
@@ -3815,15 +3776,15 @@
       <c r="G33" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I33" s="3"/>
+      <c r="I33" s="6"/>
       <c r="J33" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
       <c r="M33" s="3" t="s">
         <v>18</v>
       </c>
@@ -3833,19 +3794,19 @@
     </row>
     <row r="34" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>595</v>
+        <v>478</v>
       </c>
       <c r="B34" s="2">
         <v>46211</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>353</v>
+        <v>236</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F34" s="4">
         <v>4477</v>
@@ -3853,12 +3814,12 @@
       <c r="G34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I34" s="3"/>
-      <c r="J34" s="6" t="s">
-        <v>596</v>
+      <c r="I34" s="6"/>
+      <c r="J34" s="9" t="s">
+        <v>479</v>
       </c>
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
@@ -3871,19 +3832,19 @@
     </row>
     <row r="35" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>595</v>
+        <v>478</v>
       </c>
       <c r="B35" s="2">
         <v>46211</v>
       </c>
-      <c r="C35" s="11" t="s">
-        <v>353</v>
+      <c r="C35" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F35" s="4">
         <v>4477</v>
@@ -3891,15 +3852,15 @@
       <c r="G35" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H35" s="13" t="s">
         <v>52</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="K35" s="3"/>
-      <c r="L35" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
       <c r="M35" s="3" t="s">
         <v>18</v>
       </c>
@@ -3909,41 +3870,39 @@
     </row>
     <row r="36" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>55</v>
+        <v>480</v>
       </c>
       <c r="B36" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>56</v>
+        <v>481</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F36" s="4">
-        <v>4499</v>
+        <v>6298</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>30</v>
+        <v>39</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J36" s="6"/>
-      <c r="K36" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L36" s="2">
-        <v>46204</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
       <c r="M36" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N36" s="15">
         <v>7</v>
@@ -3951,13 +3910,13 @@
     </row>
     <row r="37" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>60</v>
+        <v>484</v>
       </c>
       <c r="B37" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>61</v>
+        <v>485</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>14</v>
@@ -3966,26 +3925,24 @@
         <v>38</v>
       </c>
       <c r="F37" s="4">
-        <v>6827</v>
+        <v>6312</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" s="6"/>
+        <v>39</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>486</v>
+      </c>
       <c r="J37" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L37" s="2">
-        <v>46204</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
       <c r="M37" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N37" s="15">
         <v>7</v>
@@ -3993,39 +3950,41 @@
     </row>
     <row r="38" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>63</v>
+        <v>488</v>
       </c>
       <c r="B38" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>64</v>
+        <v>136</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F38" s="4">
-        <v>6822</v>
+        <v>5040</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>65</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I38" s="6"/>
       <c r="J38" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
+        <v>489</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L38" s="2">
+        <v>46211</v>
+      </c>
       <c r="M38" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N38" s="15">
         <v>7</v>
@@ -4033,38 +3992,40 @@
     </row>
     <row r="39" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>67</v>
+        <v>490</v>
       </c>
       <c r="B39" s="2">
-        <v>46204</v>
-      </c>
-      <c r="C39" s="11">
-        <v>0.57430555555555551</v>
+        <v>46211</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>136</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F39" s="4">
-        <v>5710</v>
+        <v>2521</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="J39" s="6"/>
+        <v>491</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>492</v>
+      </c>
       <c r="K39" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L39" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>22</v>
@@ -4075,41 +4036,39 @@
     </row>
     <row r="40" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>69</v>
+        <v>493</v>
       </c>
       <c r="B40" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>70</v>
+        <v>494</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F40" s="4">
-        <v>1957</v>
+        <v>6310</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J40" s="6"/>
-      <c r="K40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L40" s="2">
-        <v>46204</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
       <c r="M40" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N40" s="15">
         <v>7</v>
@@ -4117,38 +4076,38 @@
     </row>
     <row r="41" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>496</v>
       </c>
       <c r="B41" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>73</v>
+        <v>497</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F41" s="4">
-        <v>1957</v>
+        <v>4511</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J41" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I41" s="6"/>
+      <c r="J41" s="9" t="s">
+        <v>498</v>
+      </c>
       <c r="K41" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L41" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>22</v>
@@ -4159,39 +4118,41 @@
     </row>
     <row r="42" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>75</v>
+        <v>499</v>
       </c>
       <c r="B42" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>76</v>
+        <v>500</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F42" s="4">
-        <v>4466</v>
+        <v>4511</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>78</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I42" s="6"/>
       <c r="J42" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6"/>
+        <v>501</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="2">
+        <v>46211</v>
+      </c>
       <c r="M42" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N42" s="15">
         <v>7</v>
@@ -4199,37 +4160,41 @@
     </row>
     <row r="43" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>80</v>
+        <v>502</v>
       </c>
       <c r="B43" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F43" s="4">
-        <v>1992</v>
+        <v>10925</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
+        <v>27</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="6"/>
+      <c r="J43" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L43" s="2">
+        <v>46211</v>
+      </c>
       <c r="M43" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N43" s="15">
         <v>7</v>
@@ -4237,40 +4202,38 @@
     </row>
     <row r="44" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>83</v>
+        <v>504</v>
       </c>
       <c r="B44" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>84</v>
+        <v>505</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="F44" s="4">
-        <v>4159</v>
+        <v>5071</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>86</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="6"/>
       <c r="J44" s="9" t="s">
-        <v>87</v>
+        <v>506</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="L44" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>22</v>
@@ -4281,39 +4244,41 @@
     </row>
     <row r="45" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>88</v>
+        <v>507</v>
       </c>
       <c r="B45" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F45" s="4">
-        <v>5379</v>
+        <v>11096</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H45" s="12" t="s">
-        <v>49</v>
+        <v>116</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
+        <v>508</v>
+      </c>
+      <c r="J45" s="6"/>
+      <c r="K45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L45" s="2">
+        <v>46211</v>
+      </c>
       <c r="M45" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N45" s="15">
         <v>7</v>
@@ -4321,40 +4286,38 @@
     </row>
     <row r="46" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>92</v>
+        <v>509</v>
       </c>
       <c r="B46" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>93</v>
+        <v>510</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="F46" s="4">
-        <v>208</v>
+        <v>5076</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>96</v>
-      </c>
+      <c r="I46" s="6"/>
       <c r="J46" s="9" t="s">
-        <v>97</v>
+        <v>511</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>21</v>
       </c>
       <c r="L46" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>22</v>
@@ -4365,40 +4328,40 @@
     </row>
     <row r="47" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>98</v>
+        <v>512</v>
       </c>
       <c r="B47" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="F47" s="4">
-        <v>63</v>
+        <v>1289</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H47" s="12" t="s">
-        <v>49</v>
+        <v>69</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>100</v>
+        <v>513</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>101</v>
+        <v>514</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L47" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>22</v>
@@ -4409,33 +4372,35 @@
     </row>
     <row r="48" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>102</v>
+        <v>515</v>
       </c>
       <c r="B48" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>103</v>
+        <v>516</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F48" s="4">
-        <v>4868</v>
+        <v>4747</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>20</v>
+        <v>62</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J48" s="6"/>
+        <v>517</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>518</v>
+      </c>
       <c r="K48" s="6"/>
       <c r="L48" s="6"/>
       <c r="M48" s="3" t="s">
@@ -4447,43 +4412,35 @@
     </row>
     <row r="49" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>106</v>
+        <v>519</v>
       </c>
       <c r="B49" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>107</v>
+        <v>520</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="F49" s="4">
-        <v>6338</v>
+        <v>3615</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L49" s="2">
-        <v>46205</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
       <c r="M49" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N49" s="15">
         <v>7</v>
@@ -4491,36 +4448,38 @@
     </row>
     <row r="50" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>110</v>
+        <v>521</v>
       </c>
       <c r="B50" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C50" s="11">
-        <v>0.38333333333333336</v>
+        <v>0.45208333333333334</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="F50" s="4">
-        <v>4531</v>
+        <v>5694</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I50" s="6"/>
+      <c r="I50" s="3" t="s">
+        <v>522</v>
+      </c>
       <c r="J50" s="6"/>
       <c r="K50" s="3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L50" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>22</v>
@@ -4531,39 +4490,41 @@
     </row>
     <row r="51" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>112</v>
+        <v>523</v>
       </c>
       <c r="B51" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="F51" s="4">
-        <v>2122</v>
+        <v>6793</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H51" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>115</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="6"/>
       <c r="J51" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
+        <v>524</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L51" s="2">
+        <v>46211</v>
+      </c>
       <c r="M51" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N51" s="15">
         <v>7</v>
@@ -4571,37 +4532,41 @@
     </row>
     <row r="52" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>117</v>
+        <v>525</v>
       </c>
       <c r="B52" s="2">
-        <v>46205</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>118</v>
+        <v>46211</v>
+      </c>
+      <c r="C52" s="11">
+        <v>0.46666666666666667</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F52" s="4">
-        <v>3957</v>
+        <v>6800</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L52" s="2">
+        <v>46211</v>
+      </c>
       <c r="M52" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N52" s="15">
         <v>7</v>
@@ -4609,38 +4574,40 @@
     </row>
     <row r="53" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>120</v>
+        <v>527</v>
       </c>
       <c r="B53" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>121</v>
+        <v>528</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F53" s="4">
-        <v>6650</v>
+        <v>2685</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H53" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J53" s="6"/>
+        <v>529</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>530</v>
+      </c>
       <c r="K53" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L53" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="M53" s="3" t="s">
         <v>22</v>
@@ -4651,41 +4618,39 @@
     </row>
     <row r="54" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>123</v>
+        <v>531</v>
       </c>
       <c r="B54" s="2">
-        <v>46205</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>42</v>
+        <v>46211</v>
+      </c>
+      <c r="C54" s="11">
+        <v>0.46875</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F54" s="4">
-        <v>3950</v>
+        <v>5714</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H54" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J54" s="6"/>
-      <c r="K54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L54" s="2">
-        <v>46205</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="J54" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
       <c r="M54" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N54" s="15">
         <v>7</v>
@@ -4693,35 +4658,33 @@
     </row>
     <row r="55" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>125</v>
+        <v>534</v>
       </c>
       <c r="B55" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>126</v>
+        <v>535</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F55" s="4">
-        <v>7201</v>
+        <v>3022</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H55" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J55" s="9" t="s">
-        <v>128</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="J55" s="6"/>
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
       <c r="M55" s="3" t="s">
@@ -4733,31 +4696,35 @@
     </row>
     <row r="56" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>129</v>
+        <v>537</v>
       </c>
       <c r="B56" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F56" s="4">
-        <v>6049</v>
+        <v>2684</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H56" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
+        <v>27</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="J56" s="9" t="s">
+        <v>539</v>
+      </c>
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
       <c r="M56" s="3" t="s">
@@ -4769,40 +4736,40 @@
     </row>
     <row r="57" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>540</v>
       </c>
       <c r="B57" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C57" s="11">
-        <v>0.46944444444444444</v>
+        <v>0.48819444444444443</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F57" s="4">
-        <v>4563</v>
+        <v>2725</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>133</v>
+        <v>541</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>134</v>
+        <v>542</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="L57" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>22</v>
@@ -4813,38 +4780,38 @@
     </row>
     <row r="58" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>136</v>
+        <v>543</v>
       </c>
       <c r="B58" s="2">
-        <v>46205</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>137</v>
+        <v>46211</v>
+      </c>
+      <c r="C58" s="11">
+        <v>0.50208333333333333</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F58" s="4">
-        <v>1291</v>
+        <v>2697</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H58" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J58" s="6"/>
+        <v>47</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I58" s="6"/>
+      <c r="J58" s="9" t="s">
+        <v>544</v>
+      </c>
       <c r="K58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="L58" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>22</v>
@@ -4855,35 +4822,41 @@
     </row>
     <row r="59" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>140</v>
+        <v>545</v>
       </c>
       <c r="B59" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>141</v>
+        <v>546</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F59" s="4">
-        <v>6055</v>
+        <v>5995</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I59" s="6"/>
+      <c r="I59" s="3" t="s">
+        <v>547</v>
+      </c>
       <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
+      <c r="K59" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="L59" s="2">
+        <v>46211</v>
+      </c>
       <c r="M59" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N59" s="15">
         <v>7</v>
@@ -4891,33 +4864,35 @@
     </row>
     <row r="60" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>142</v>
+        <v>549</v>
       </c>
       <c r="B60" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>143</v>
+        <v>550</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F60" s="4">
-        <v>3969</v>
+        <v>4795</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="H60" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J60" s="6"/>
+        <v>551</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>552</v>
+      </c>
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
       <c r="M60" s="3" t="s">
@@ -4929,31 +4904,31 @@
     </row>
     <row r="61" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>142</v>
+        <v>553</v>
       </c>
       <c r="B61" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F61" s="4">
-        <v>3969</v>
+        <v>1963</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H61" s="8" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>144</v>
+        <v>554</v>
       </c>
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
@@ -4967,31 +4942,35 @@
     </row>
     <row r="62" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>145</v>
+        <v>555</v>
       </c>
       <c r="B62" s="2">
-        <v>46205</v>
-      </c>
-      <c r="C62" s="11">
-        <v>0.49513888888888891</v>
+        <v>46211</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>556</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="F62" s="4">
-        <v>5451</v>
+        <v>6794</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H62" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>558</v>
+      </c>
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
       <c r="M62" s="3" t="s">
@@ -5003,39 +4982,39 @@
     </row>
     <row r="63" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>147</v>
+        <v>559</v>
       </c>
       <c r="B63" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>148</v>
+        <v>560</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="F63" s="4">
-        <v>7185</v>
+        <v>2335</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H63" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="L63" s="2">
-        <v>46205</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
       <c r="M63" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N63" s="15">
         <v>7</v>
@@ -5043,41 +5022,37 @@
     </row>
     <row r="64" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>149</v>
+        <v>563</v>
       </c>
       <c r="B64" s="2">
-        <v>46205</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>150</v>
+        <v>46211</v>
+      </c>
+      <c r="C64" s="11">
+        <v>0.53819444444444442</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F64" s="4">
-        <v>1774</v>
+        <v>6001</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J64" s="6"/>
-      <c r="K64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L64" s="2">
-        <v>46205</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I64" s="6"/>
+      <c r="J64" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
       <c r="M64" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N64" s="15">
         <v>7</v>
@@ -5085,38 +5060,38 @@
     </row>
     <row r="65" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>153</v>
+        <v>565</v>
       </c>
       <c r="B65" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>154</v>
+        <v>566</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F65" s="4">
-        <v>1988</v>
+        <v>7413</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H65" s="8" t="s">
-        <v>30</v>
+        <v>53</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>155</v>
+        <v>567</v>
       </c>
       <c r="J65" s="6"/>
       <c r="K65" s="3" t="s">
-        <v>31</v>
+        <v>568</v>
       </c>
       <c r="L65" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="M65" s="3" t="s">
         <v>22</v>
@@ -5127,36 +5102,38 @@
     </row>
     <row r="66" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>156</v>
+        <v>569</v>
       </c>
       <c r="B66" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>157</v>
+        <v>570</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="F66" s="4">
-        <v>6642</v>
+        <v>4496</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I66" s="6"/>
+        <v>55</v>
+      </c>
+      <c r="H66" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>571</v>
+      </c>
       <c r="J66" s="6"/>
       <c r="K66" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L66" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>22</v>
@@ -5167,33 +5144,33 @@
     </row>
     <row r="67" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>158</v>
+        <v>572</v>
       </c>
       <c r="B67" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>159</v>
+        <v>573</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="F67" s="4">
-        <v>4853</v>
+        <v>4814</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H67" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="J67" s="6"/>
+      <c r="H67" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I67" s="6"/>
+      <c r="J67" s="9" t="s">
+        <v>574</v>
+      </c>
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
       <c r="M67" s="3" t="s">
@@ -5205,41 +5182,37 @@
     </row>
     <row r="68" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>161</v>
+        <v>575</v>
       </c>
       <c r="B68" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="F68" s="4">
-        <v>6589</v>
+        <v>1958</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J68" s="6"/>
-      <c r="K68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L68" s="2">
-        <v>46205</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="H68" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I68" s="6"/>
+      <c r="J68" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
       <c r="M68" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N68" s="15">
         <v>7</v>
@@ -5247,33 +5220,33 @@
     </row>
     <row r="69" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>164</v>
+        <v>577</v>
       </c>
       <c r="B69" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>165</v>
+        <v>578</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>50</v>
+        <v>454</v>
       </c>
       <c r="F69" s="4">
-        <v>7438</v>
+        <v>98</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I69" s="6"/>
-      <c r="J69" s="9" t="s">
-        <v>166</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="J69" s="6"/>
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
       <c r="M69" s="3" t="s">
@@ -5285,36 +5258,38 @@
     </row>
     <row r="70" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>167</v>
+        <v>580</v>
       </c>
       <c r="B70" s="2">
-        <v>46205</v>
-      </c>
-      <c r="C70" s="11">
-        <v>0.54513888888888884</v>
+        <v>46211</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>581</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>111</v>
+        <v>446</v>
       </c>
       <c r="F70" s="4">
-        <v>5453</v>
+        <v>2608</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>36</v>
+        <v>447</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I70" s="6"/>
+      <c r="I70" s="3" t="s">
+        <v>582</v>
+      </c>
       <c r="J70" s="6"/>
       <c r="K70" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L70" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="M70" s="3" t="s">
         <v>22</v>
@@ -5325,43 +5300,37 @@
     </row>
     <row r="71" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>168</v>
+        <v>583</v>
       </c>
       <c r="B71" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>169</v>
+        <v>584</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>170</v>
+        <v>43</v>
       </c>
       <c r="F71" s="4">
-        <v>3674</v>
+        <v>1957</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>37</v>
+        <v>44</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J71" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L71" s="2">
-        <v>46205</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
       <c r="M71" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N71" s="15">
         <v>7</v>
@@ -5369,30 +5338,32 @@
     </row>
     <row r="72" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>173</v>
+        <v>586</v>
       </c>
       <c r="B72" s="2">
-        <v>46205</v>
-      </c>
-      <c r="C72" s="11">
-        <v>0.56111111111111112</v>
+        <v>46211</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>587</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="F72" s="4">
-        <v>5424</v>
+        <v>1957</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H72" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I72" s="6"/>
+      <c r="I72" s="3" t="s">
+        <v>588</v>
+      </c>
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
@@ -5405,35 +5376,33 @@
     </row>
     <row r="73" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>174</v>
+        <v>589</v>
       </c>
       <c r="B73" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>175</v>
+        <v>590</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F73" s="4">
-        <v>6855</v>
+        <v>1957</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>20</v>
+        <v>44</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="J73" s="9" t="s">
-        <v>177</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="J73" s="6"/>
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
       <c r="M73" s="3" t="s">
@@ -5445,35 +5414,43 @@
     </row>
     <row r="74" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>178</v>
+        <v>592</v>
       </c>
       <c r="B74" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C74" s="11">
-        <v>0.56736111111111109</v>
+        <v>0.62291666666666667</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="F74" s="4">
-        <v>5425</v>
+        <v>6007</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H74" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
+      <c r="I74" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="L74" s="2">
+        <v>46211</v>
+      </c>
       <c r="M74" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N74" s="15">
         <v>7</v>
@@ -5481,31 +5458,35 @@
     </row>
     <row r="75" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>179</v>
+        <v>596</v>
       </c>
       <c r="B75" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>180</v>
+        <v>597</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F75" s="4">
-        <v>6887</v>
+        <v>4794</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I75" s="6"/>
-      <c r="J75" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="J75" s="9" t="s">
+        <v>600</v>
+      </c>
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
       <c r="M75" s="3" t="s">
@@ -5517,35 +5498,33 @@
     </row>
     <row r="76" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>181</v>
+        <v>601</v>
       </c>
       <c r="B76" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>182</v>
+        <v>602</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F76" s="4">
-        <v>6867</v>
+        <v>1992</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H76" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="J76" s="9" t="s">
-        <v>184</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="J76" s="6"/>
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
       <c r="M76" s="3" t="s">
@@ -5557,34 +5536,32 @@
     </row>
     <row r="77" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>185</v>
+        <v>604</v>
       </c>
       <c r="B77" s="2">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>186</v>
+        <v>520</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F77" s="4">
-        <v>6869</v>
+        <v>1326</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H77" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>187</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I77" s="6"/>
       <c r="J77" s="9" t="s">
-        <v>188</v>
+        <v>605</v>
       </c>
       <c r="K77" s="6"/>
       <c r="L77" s="6"/>
@@ -5597,34 +5574,34 @@
     </row>
     <row r="78" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>189</v>
+        <v>606</v>
       </c>
       <c r="B78" s="2">
-        <v>46205</v>
-      </c>
-      <c r="C78" s="11">
-        <v>0.5805555555555556</v>
+        <v>46213</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>607</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="F78" s="4">
-        <v>7481</v>
+        <v>2195</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H78" s="13" t="s">
-        <v>52</v>
+        <v>44</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>190</v>
+        <v>608</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>191</v>
+        <v>609</v>
       </c>
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
@@ -5637,7 +5614,7 @@
     </row>
     <row r="79" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>192</v>
+        <v>75</v>
       </c>
       <c r="B79" s="2">
         <v>46205</v>
@@ -5649,7 +5626,7 @@
         <v>14</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F79" s="4">
         <v>5445</v>
@@ -5677,7 +5654,7 @@
     </row>
     <row r="80" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="B80" s="2">
         <v>46205</v>
@@ -5702,7 +5679,7 @@
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="9" t="s">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="K80" s="3" t="s">
         <v>21</v>
@@ -5719,7 +5696,7 @@
     </row>
     <row r="81" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="B81" s="2">
         <v>46205</v>
@@ -5731,7 +5708,7 @@
         <v>14</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F81" s="4">
         <v>5471</v>
@@ -5759,7 +5736,7 @@
     </row>
     <row r="82" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>196</v>
+        <v>79</v>
       </c>
       <c r="B82" s="2">
         <v>46205</v>
@@ -5771,7 +5748,7 @@
         <v>14</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F82" s="4">
         <v>5454</v>
@@ -5799,13 +5776,13 @@
     </row>
     <row r="83" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="B83" s="2">
         <v>46205</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>198</v>
+        <v>81</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>14</v>
@@ -5824,7 +5801,7 @@
       </c>
       <c r="I83" s="6"/>
       <c r="J83" s="9" t="s">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>21</v>
@@ -5841,19 +5818,19 @@
     </row>
     <row r="84" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>200</v>
+        <v>83</v>
       </c>
       <c r="B84" s="2">
         <v>46205</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F84" s="4">
         <v>6874</v>
@@ -5866,7 +5843,7 @@
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="9" t="s">
-        <v>202</v>
+        <v>85</v>
       </c>
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
@@ -5879,19 +5856,19 @@
     </row>
     <row r="85" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>203</v>
+        <v>86</v>
       </c>
       <c r="B85" s="2">
         <v>46205</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F85" s="4">
         <v>6874</v>
@@ -5904,7 +5881,7 @@
       </c>
       <c r="I85" s="6"/>
       <c r="J85" s="9" t="s">
-        <v>204</v>
+        <v>87</v>
       </c>
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
@@ -5917,7 +5894,7 @@
     </row>
     <row r="86" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>205</v>
+        <v>88</v>
       </c>
       <c r="B86" s="2">
         <v>46205</v>
@@ -5935,16 +5912,16 @@
         <v>5122</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="H86" s="12" t="s">
         <v>49</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>207</v>
+        <v>90</v>
       </c>
       <c r="J86" s="9" t="s">
-        <v>208</v>
+        <v>91</v>
       </c>
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
@@ -5957,19 +5934,19 @@
     </row>
     <row r="87" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>209</v>
+        <v>92</v>
       </c>
       <c r="B87" s="2">
         <v>46205</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F87" s="4">
         <v>6350</v>
@@ -5981,10 +5958,10 @@
         <v>20</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>212</v>
+        <v>95</v>
       </c>
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
@@ -5997,19 +5974,19 @@
     </row>
     <row r="88" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>209</v>
+        <v>92</v>
       </c>
       <c r="B88" s="2">
         <v>46205</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>210</v>
+        <v>93</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F88" s="4">
         <v>6350</v>
@@ -6021,10 +5998,10 @@
         <v>20</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="J88" s="9" t="s">
-        <v>212</v>
+        <v>95</v>
       </c>
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
@@ -6037,19 +6014,19 @@
     </row>
     <row r="89" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="B89" s="2">
         <v>46205</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F89" s="4">
         <v>6334</v>
@@ -6061,10 +6038,10 @@
         <v>20</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>214</v>
+        <v>97</v>
       </c>
       <c r="J89" s="9" t="s">
-        <v>215</v>
+        <v>98</v>
       </c>
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
@@ -6077,7 +6054,7 @@
     </row>
     <row r="90" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>216</v>
+        <v>99</v>
       </c>
       <c r="B90" s="2">
         <v>46205</v>
@@ -6089,7 +6066,7 @@
         <v>14</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F90" s="4">
         <v>4526</v>
@@ -6117,19 +6094,19 @@
     </row>
     <row r="91" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>217</v>
+        <v>100</v>
       </c>
       <c r="B91" s="2">
         <v>46205</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>218</v>
+        <v>101</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F91" s="4">
         <v>6884</v>
@@ -6141,10 +6118,10 @@
         <v>17</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>219</v>
+        <v>102</v>
       </c>
       <c r="J91" s="9" t="s">
-        <v>220</v>
+        <v>103</v>
       </c>
       <c r="K91" s="6"/>
       <c r="L91" s="6"/>
@@ -6157,7 +6134,7 @@
     </row>
     <row r="92" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="B92" s="2">
         <v>46205</v>
@@ -6169,7 +6146,7 @@
         <v>14</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F92" s="4">
         <v>4558</v>
@@ -6193,7 +6170,7 @@
     </row>
     <row r="93" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>222</v>
+        <v>105</v>
       </c>
       <c r="B93" s="2">
         <v>46205</v>
@@ -6205,7 +6182,7 @@
         <v>14</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F93" s="4">
         <v>4539</v>
@@ -6233,7 +6210,7 @@
     </row>
     <row r="94" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>222</v>
+        <v>105</v>
       </c>
       <c r="B94" s="2">
         <v>46205</v>
@@ -6245,7 +6222,7 @@
         <v>14</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F94" s="4">
         <v>4539</v>
@@ -6273,32 +6250,32 @@
     </row>
     <row r="95" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>223</v>
+        <v>106</v>
       </c>
       <c r="B95" s="2">
         <v>46205</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>224</v>
+        <v>107</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="F95" s="4">
         <v>10886</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>226</v>
+        <v>109</v>
       </c>
       <c r="H95" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I95" s="6"/>
       <c r="J95" s="9" t="s">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
@@ -6311,32 +6288,32 @@
     </row>
     <row r="96" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>223</v>
+        <v>106</v>
       </c>
       <c r="B96" s="2">
         <v>46205</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>224</v>
+        <v>107</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="F96" s="4">
         <v>10886</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>226</v>
+        <v>109</v>
       </c>
       <c r="H96" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="9" t="s">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
@@ -6349,13 +6326,13 @@
     </row>
     <row r="97" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="B97" s="2">
         <v>46205</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>14</v>
@@ -6367,13 +6344,13 @@
         <v>4807</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="H97" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="J97" s="6"/>
       <c r="K97" s="6"/>
@@ -6387,13 +6364,13 @@
     </row>
     <row r="98" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>231</v>
+        <v>114</v>
       </c>
       <c r="B98" s="2">
         <v>46205</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>232</v>
+        <v>115</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>14</v>
@@ -6405,13 +6382,13 @@
         <v>5102</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
       <c r="H98" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>234</v>
+        <v>117</v>
       </c>
       <c r="J98" s="6"/>
       <c r="K98" s="3" t="s">
@@ -6429,35 +6406,35 @@
     </row>
     <row r="99" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>235</v>
+        <v>118</v>
       </c>
       <c r="B99" s="2">
         <v>46205</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>236</v>
+        <v>119</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="F99" s="4">
         <v>1319</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>226</v>
+        <v>109</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I99" s="6"/>
       <c r="J99" s="9" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>238</v>
+        <v>121</v>
       </c>
       <c r="L99" s="2">
         <v>46205</v>
@@ -6471,7 +6448,7 @@
     </row>
     <row r="100" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>239</v>
+        <v>122</v>
       </c>
       <c r="B100" s="2">
         <v>46206</v>
@@ -6483,7 +6460,7 @@
         <v>14</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F100" s="4">
         <v>4032</v>
@@ -6511,13 +6488,13 @@
     </row>
     <row r="101" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>240</v>
+        <v>123</v>
       </c>
       <c r="B101" s="2">
         <v>46206</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>241</v>
+        <v>124</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>14</v>
@@ -6535,7 +6512,7 @@
         <v>30</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>242</v>
+        <v>125</v>
       </c>
       <c r="J101" s="6"/>
       <c r="K101" s="3" t="s">
@@ -6553,7 +6530,7 @@
     </row>
     <row r="102" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>243</v>
+        <v>126</v>
       </c>
       <c r="B102" s="2">
         <v>46206</v>
@@ -6571,16 +6548,16 @@
         <v>3455</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
       <c r="H102" s="12" t="s">
         <v>49</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>244</v>
+        <v>127</v>
       </c>
       <c r="J102" s="9" t="s">
-        <v>245</v>
+        <v>128</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>31</v>
@@ -6597,7 +6574,7 @@
     </row>
     <row r="103" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>243</v>
+        <v>126</v>
       </c>
       <c r="B103" s="2">
         <v>46206</v>
@@ -6615,16 +6592,16 @@
         <v>3455</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
       <c r="H103" s="12" t="s">
         <v>49</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>244</v>
+        <v>127</v>
       </c>
       <c r="J103" s="9" t="s">
-        <v>245</v>
+        <v>128</v>
       </c>
       <c r="K103" s="3" t="s">
         <v>31</v>
@@ -6641,13 +6618,13 @@
     </row>
     <row r="104" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>246</v>
+        <v>129</v>
       </c>
       <c r="B104" s="2">
         <v>46206</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>247</v>
+        <v>130</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>14</v>
@@ -6665,7 +6642,7 @@
         <v>37</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>248</v>
+        <v>131</v>
       </c>
       <c r="J104" s="6"/>
       <c r="K104" s="6"/>
@@ -6679,13 +6656,13 @@
     </row>
     <row r="105" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>249</v>
+        <v>132</v>
       </c>
       <c r="B105" s="2">
         <v>46206</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>250</v>
+        <v>133</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>14</v>
@@ -6697,13 +6674,13 @@
         <v>1599</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="H105" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>251</v>
+        <v>134</v>
       </c>
       <c r="J105" s="6"/>
       <c r="K105" s="3" t="s">
@@ -6721,19 +6698,19 @@
     </row>
     <row r="106" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>252</v>
+        <v>135</v>
       </c>
       <c r="B106" s="2">
         <v>46206</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>253</v>
+        <v>136</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F106" s="4">
         <v>11243</v>
@@ -6745,10 +6722,10 @@
         <v>20</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>254</v>
+        <v>137</v>
       </c>
       <c r="J106" s="9" t="s">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="K106" s="3" t="s">
         <v>31</v>
@@ -6765,13 +6742,13 @@
     </row>
     <row r="107" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>256</v>
+        <v>139</v>
       </c>
       <c r="B107" s="2">
         <v>46206</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>257</v>
+        <v>140</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>14</v>
@@ -6783,7 +6760,7 @@
         <v>3825</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="H107" s="13" t="s">
         <v>52</v>
@@ -6801,19 +6778,19 @@
     </row>
     <row r="108" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>258</v>
+        <v>141</v>
       </c>
       <c r="B108" s="2">
         <v>46206</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>259</v>
+        <v>142</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="F108" s="4">
         <v>1852</v>
@@ -6826,7 +6803,7 @@
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="9" t="s">
-        <v>260</v>
+        <v>143</v>
       </c>
       <c r="K108" s="6"/>
       <c r="L108" s="6"/>
@@ -6839,7 +6816,7 @@
     </row>
     <row r="109" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>261</v>
+        <v>144</v>
       </c>
       <c r="B109" s="2">
         <v>46206</v>
@@ -6851,13 +6828,13 @@
         <v>14</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F109" s="4">
         <v>4318</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
       <c r="H109" s="12" t="s">
         <v>49</v>
@@ -6879,7 +6856,7 @@
     </row>
     <row r="110" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>261</v>
+        <v>144</v>
       </c>
       <c r="B110" s="2">
         <v>46206</v>
@@ -6891,13 +6868,13 @@
         <v>14</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F110" s="4">
         <v>4318</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
       <c r="H110" s="12" t="s">
         <v>49</v>
@@ -6919,7 +6896,7 @@
     </row>
     <row r="111" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>262</v>
+        <v>145</v>
       </c>
       <c r="B111" s="2">
         <v>46206</v>
@@ -6943,13 +6920,13 @@
         <v>49</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>263</v>
+        <v>146</v>
       </c>
       <c r="J111" s="9" t="s">
-        <v>264</v>
+        <v>147</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>238</v>
+        <v>121</v>
       </c>
       <c r="L111" s="2">
         <v>46206</v>
@@ -6963,13 +6940,13 @@
     </row>
     <row r="112" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>265</v>
+        <v>148</v>
       </c>
       <c r="B112" s="2">
         <v>46206</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>266</v>
+        <v>149</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>14</v>
@@ -6981,16 +6958,16 @@
         <v>4885</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="H112" s="12" t="s">
         <v>49</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>267</v>
+        <v>150</v>
       </c>
       <c r="J112" s="9" t="s">
-        <v>268</v>
+        <v>151</v>
       </c>
       <c r="K112" s="6"/>
       <c r="L112" s="6"/>
@@ -7003,13 +6980,13 @@
     </row>
     <row r="113" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>269</v>
+        <v>152</v>
       </c>
       <c r="B113" s="2">
         <v>46206</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>270</v>
+        <v>153</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>14</v>
@@ -7021,13 +6998,13 @@
         <v>1404</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="H113" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>271</v>
+        <v>154</v>
       </c>
       <c r="J113" s="6"/>
       <c r="K113" s="3" t="s">
@@ -7045,13 +7022,13 @@
     </row>
     <row r="114" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>272</v>
+        <v>155</v>
       </c>
       <c r="B114" s="2">
         <v>46206</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>273</v>
+        <v>156</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>14</v>
@@ -7063,16 +7040,16 @@
         <v>4301</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="H114" s="10" t="s">
         <v>17</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>274</v>
+        <v>157</v>
       </c>
       <c r="J114" s="9" t="s">
-        <v>275</v>
+        <v>158</v>
       </c>
       <c r="K114" s="6"/>
       <c r="L114" s="6"/>
@@ -7085,7 +7062,7 @@
     </row>
     <row r="115" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>276</v>
+        <v>159</v>
       </c>
       <c r="B115" s="2">
         <v>46206</v>
@@ -7110,7 +7087,7 @@
       </c>
       <c r="I115" s="6"/>
       <c r="J115" s="9" t="s">
-        <v>277</v>
+        <v>160</v>
       </c>
       <c r="K115" s="3" t="s">
         <v>21</v>
@@ -7127,19 +7104,19 @@
     </row>
     <row r="116" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>278</v>
+        <v>161</v>
       </c>
       <c r="B116" s="2">
         <v>46206</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>279</v>
+        <v>162</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="F116" s="4">
         <v>10741</v>
@@ -7151,10 +7128,10 @@
         <v>30</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>280</v>
+        <v>163</v>
       </c>
       <c r="J116" s="9" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="K116" s="6"/>
       <c r="L116" s="6"/>
@@ -7167,7 +7144,7 @@
     </row>
     <row r="117" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>282</v>
+        <v>165</v>
       </c>
       <c r="B117" s="2">
         <v>46206</v>
@@ -7192,7 +7169,7 @@
       </c>
       <c r="I117" s="6"/>
       <c r="J117" s="9" t="s">
-        <v>283</v>
+        <v>166</v>
       </c>
       <c r="K117" s="6"/>
       <c r="L117" s="6"/>
@@ -7205,19 +7182,19 @@
     </row>
     <row r="118" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>284</v>
+        <v>167</v>
       </c>
       <c r="B118" s="2">
         <v>46206</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>285</v>
+        <v>168</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F118" s="4">
         <v>7248</v>
@@ -7229,10 +7206,10 @@
         <v>20</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>286</v>
+        <v>169</v>
       </c>
       <c r="J118" s="9" t="s">
-        <v>287</v>
+        <v>170</v>
       </c>
       <c r="K118" s="6"/>
       <c r="L118" s="6"/>
@@ -7245,7 +7222,7 @@
     </row>
     <row r="119" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>288</v>
+        <v>171</v>
       </c>
       <c r="B119" s="2">
         <v>46206</v>
@@ -7269,10 +7246,10 @@
         <v>30</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>289</v>
+        <v>172</v>
       </c>
       <c r="J119" s="9" t="s">
-        <v>290</v>
+        <v>173</v>
       </c>
       <c r="K119" s="6"/>
       <c r="L119" s="6"/>
@@ -7285,13 +7262,13 @@
     </row>
     <row r="120" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>291</v>
+        <v>174</v>
       </c>
       <c r="B120" s="2">
         <v>46206</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>292</v>
+        <v>175</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>14</v>
@@ -7303,16 +7280,16 @@
         <v>4902</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="H120" s="12" t="s">
         <v>49</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>293</v>
+        <v>176</v>
       </c>
       <c r="J120" s="9" t="s">
-        <v>294</v>
+        <v>177</v>
       </c>
       <c r="K120" s="6"/>
       <c r="L120" s="6"/>
@@ -7325,13 +7302,13 @@
     </row>
     <row r="121" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>295</v>
+        <v>178</v>
       </c>
       <c r="B121" s="2">
         <v>46206</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>296</v>
+        <v>179</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>14</v>
@@ -7349,7 +7326,7 @@
         <v>20</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
       <c r="J121" s="6"/>
       <c r="K121" s="3" t="s">
@@ -7367,13 +7344,13 @@
     </row>
     <row r="122" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>298</v>
+        <v>181</v>
       </c>
       <c r="B122" s="2">
         <v>46206</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>14</v>
@@ -7385,14 +7362,14 @@
         <v>2842</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="H122" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I122" s="6"/>
       <c r="J122" s="9" t="s">
-        <v>299</v>
+        <v>182</v>
       </c>
       <c r="K122" s="3" t="s">
         <v>31</v>
@@ -7409,13 +7386,13 @@
     </row>
     <row r="123" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="B123" s="2">
         <v>46206</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>301</v>
+        <v>184</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>14</v>
@@ -7433,7 +7410,7 @@
         <v>20</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>302</v>
+        <v>185</v>
       </c>
       <c r="J123" s="6"/>
       <c r="K123" s="3" t="s">
@@ -7451,13 +7428,13 @@
     </row>
     <row r="124" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="B124" s="2">
         <v>46206</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>301</v>
+        <v>184</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>14</v>
@@ -7475,7 +7452,7 @@
         <v>20</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>302</v>
+        <v>185</v>
       </c>
       <c r="J124" s="6"/>
       <c r="K124" s="3" t="s">
@@ -7493,13 +7470,13 @@
     </row>
     <row r="125" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>303</v>
+        <v>186</v>
       </c>
       <c r="B125" s="2">
         <v>46206</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>304</v>
+        <v>187</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>14</v>
@@ -7517,7 +7494,7 @@
         <v>20</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>305</v>
+        <v>188</v>
       </c>
       <c r="J125" s="6"/>
       <c r="K125" s="6"/>
@@ -7531,31 +7508,31 @@
     </row>
     <row r="126" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>306</v>
+        <v>189</v>
       </c>
       <c r="B126" s="2">
         <v>46206</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>307</v>
+        <v>190</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="F126" s="4">
         <v>2086</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>226</v>
+        <v>109</v>
       </c>
       <c r="H126" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>308</v>
+        <v>191</v>
       </c>
       <c r="J126" s="6"/>
       <c r="K126" s="6"/>
@@ -7569,7 +7546,7 @@
     </row>
     <row r="127" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>309</v>
+        <v>192</v>
       </c>
       <c r="B127" s="2">
         <v>46206</v>
@@ -7581,13 +7558,13 @@
         <v>14</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F127" s="4">
         <v>4015</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
       <c r="H127" s="12" t="s">
         <v>49</v>
@@ -7609,13 +7586,13 @@
     </row>
     <row r="128" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>310</v>
+        <v>193</v>
       </c>
       <c r="B128" s="2">
         <v>46206</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>311</v>
+        <v>194</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>14</v>
@@ -7649,7 +7626,7 @@
     </row>
     <row r="129" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>312</v>
+        <v>195</v>
       </c>
       <c r="B129" s="2">
         <v>46206</v>
@@ -7661,7 +7638,7 @@
         <v>14</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F129" s="4">
         <v>3435</v>
@@ -7685,13 +7662,13 @@
     </row>
     <row r="130" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>313</v>
+        <v>196</v>
       </c>
       <c r="B130" s="2">
         <v>46206</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>314</v>
+        <v>197</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>14</v>
@@ -7703,13 +7680,13 @@
         <v>11335</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H130" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>315</v>
+        <v>198</v>
       </c>
       <c r="J130" s="6"/>
       <c r="K130" s="3" t="s">
@@ -7727,13 +7704,13 @@
     </row>
     <row r="131" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>316</v>
+        <v>199</v>
       </c>
       <c r="B131" s="2">
         <v>46206</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>14</v>
@@ -7745,7 +7722,7 @@
         <v>11245</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H131" s="7" t="s">
         <v>37</v>
@@ -7767,13 +7744,13 @@
     </row>
     <row r="132" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>317</v>
+        <v>200</v>
       </c>
       <c r="B132" s="2">
         <v>46206</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>318</v>
+        <v>201</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>14</v>
@@ -7791,7 +7768,7 @@
         <v>20</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>319</v>
+        <v>202</v>
       </c>
       <c r="J132" s="6"/>
       <c r="K132" s="6"/>
@@ -7805,7 +7782,7 @@
     </row>
     <row r="133" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>320</v>
+        <v>203</v>
       </c>
       <c r="B133" s="2">
         <v>46206</v>
@@ -7817,7 +7794,7 @@
         <v>14</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F133" s="4">
         <v>7236</v>
@@ -7831,7 +7808,7 @@
       <c r="I133" s="6"/>
       <c r="J133" s="6"/>
       <c r="K133" s="3" t="s">
-        <v>321</v>
+        <v>204</v>
       </c>
       <c r="L133" s="2">
         <v>46206</v>
@@ -7845,13 +7822,13 @@
     </row>
     <row r="134" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>322</v>
+        <v>205</v>
       </c>
       <c r="B134" s="2">
         <v>46206</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>323</v>
+        <v>206</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>14</v>
@@ -7863,13 +7840,13 @@
         <v>1735</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="H134" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>324</v>
+        <v>207</v>
       </c>
       <c r="J134" s="6"/>
       <c r="K134" s="3" t="s">
@@ -7887,7 +7864,7 @@
     </row>
     <row r="135" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>325</v>
+        <v>208</v>
       </c>
       <c r="B135" s="2">
         <v>46206</v>
@@ -7899,7 +7876,7 @@
         <v>14</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F135" s="4">
         <v>7227</v>
@@ -7913,7 +7890,7 @@
       <c r="I135" s="6"/>
       <c r="J135" s="6"/>
       <c r="K135" s="3" t="s">
-        <v>326</v>
+        <v>209</v>
       </c>
       <c r="L135" s="2">
         <v>46206</v>
@@ -7927,7 +7904,7 @@
     </row>
     <row r="136" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>327</v>
+        <v>210</v>
       </c>
       <c r="B136" s="2">
         <v>46206</v>
@@ -7951,10 +7928,10 @@
         <v>37</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>328</v>
+        <v>211</v>
       </c>
       <c r="J136" s="9" t="s">
-        <v>329</v>
+        <v>212</v>
       </c>
       <c r="K136" s="6"/>
       <c r="L136" s="6"/>
@@ -7967,7 +7944,7 @@
     </row>
     <row r="137" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>330</v>
+        <v>213</v>
       </c>
       <c r="B137" s="2">
         <v>46206</v>
@@ -7979,13 +7956,13 @@
         <v>14</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F137" s="4">
         <v>6673</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="H137" s="7" t="s">
         <v>37</v>
@@ -8003,7 +7980,7 @@
     </row>
     <row r="138" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>331</v>
+        <v>214</v>
       </c>
       <c r="B138" s="2">
         <v>46206</v>
@@ -8015,13 +7992,13 @@
         <v>14</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F138" s="4">
         <v>4017</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
       <c r="H138" s="7" t="s">
         <v>37</v>
@@ -8043,13 +8020,13 @@
     </row>
     <row r="139" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>332</v>
+        <v>215</v>
       </c>
       <c r="B139" s="2">
         <v>46206</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>333</v>
+        <v>216</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>14</v>
@@ -8061,7 +8038,7 @@
         <v>6380</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="H139" s="7" t="s">
         <v>37</v>
@@ -8083,19 +8060,19 @@
     </row>
     <row r="140" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>334</v>
+        <v>217</v>
       </c>
       <c r="B140" s="2">
         <v>46206</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>335</v>
+        <v>218</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="F140" s="4">
         <v>6666</v>
@@ -8107,10 +8084,10 @@
         <v>52</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>336</v>
+        <v>219</v>
       </c>
       <c r="J140" s="9" t="s">
-        <v>337</v>
+        <v>220</v>
       </c>
       <c r="K140" s="3" t="s">
         <v>31</v>
@@ -8127,7 +8104,7 @@
     </row>
     <row r="141" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>338</v>
+        <v>221</v>
       </c>
       <c r="B141" s="2">
         <v>46206</v>
@@ -8139,13 +8116,13 @@
         <v>14</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F141" s="4">
         <v>4296</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
       <c r="H141" s="7" t="s">
         <v>37</v>
@@ -8167,19 +8144,19 @@
     </row>
     <row r="142" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>339</v>
+        <v>222</v>
       </c>
       <c r="B142" s="2">
         <v>46206</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>340</v>
+        <v>223</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F142" s="4">
         <v>33333</v>
@@ -8191,11 +8168,11 @@
         <v>52</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>341</v>
+        <v>224</v>
       </c>
       <c r="J142" s="6"/>
       <c r="K142" s="3" t="s">
-        <v>342</v>
+        <v>225</v>
       </c>
       <c r="L142" s="2">
         <v>46206</v>
@@ -8209,19 +8186,19 @@
     </row>
     <row r="143" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>343</v>
+        <v>226</v>
       </c>
       <c r="B143" s="2">
         <v>46206</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>344</v>
+        <v>227</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="F143" s="4">
         <v>7519</v>
@@ -8234,7 +8211,7 @@
       </c>
       <c r="I143" s="6"/>
       <c r="J143" s="9" t="s">
-        <v>345</v>
+        <v>228</v>
       </c>
       <c r="K143" s="3" t="s">
         <v>21</v>
@@ -8251,34 +8228,34 @@
     </row>
     <row r="144" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>346</v>
+        <v>229</v>
       </c>
       <c r="B144" s="2">
         <v>46206</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>347</v>
+        <v>230</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="F144" s="4">
         <v>1881</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>226</v>
+        <v>109</v>
       </c>
       <c r="H144" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>348</v>
+        <v>231</v>
       </c>
       <c r="J144" s="9" t="s">
-        <v>349</v>
+        <v>232</v>
       </c>
       <c r="K144" s="6"/>
       <c r="L144" s="6"/>
@@ -8291,7 +8268,7 @@
     </row>
     <row r="145" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>350</v>
+        <v>233</v>
       </c>
       <c r="B145" s="2">
         <v>46207</v>
@@ -8316,7 +8293,7 @@
       </c>
       <c r="I145" s="6"/>
       <c r="J145" s="9" t="s">
-        <v>351</v>
+        <v>234</v>
       </c>
       <c r="K145" s="3" t="s">
         <v>21</v>
@@ -8333,13 +8310,13 @@
     </row>
     <row r="146" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>352</v>
+        <v>235</v>
       </c>
       <c r="B146" s="2">
         <v>46207</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>353</v>
+        <v>236</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>14</v>
@@ -8351,13 +8328,13 @@
         <v>4398</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="H146" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>354</v>
+        <v>237</v>
       </c>
       <c r="J146" s="6"/>
       <c r="K146" s="3" t="s">
@@ -8375,7 +8352,7 @@
     </row>
     <row r="147" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>355</v>
+        <v>238</v>
       </c>
       <c r="B147" s="2">
         <v>46207</v>
@@ -8393,13 +8370,13 @@
         <v>4663</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="H147" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>356</v>
+        <v>239</v>
       </c>
       <c r="J147" s="6"/>
       <c r="K147" s="3" t="s">
@@ -8417,7 +8394,7 @@
     </row>
     <row r="148" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>357</v>
+        <v>240</v>
       </c>
       <c r="B148" s="2">
         <v>46207</v>
@@ -8442,7 +8419,7 @@
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="9" t="s">
-        <v>358</v>
+        <v>241</v>
       </c>
       <c r="K148" s="6"/>
       <c r="L148" s="6"/>
@@ -8455,13 +8432,13 @@
     </row>
     <row r="149" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>359</v>
+        <v>242</v>
       </c>
       <c r="B149" s="2">
         <v>46207</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>360</v>
+        <v>243</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>14</v>
@@ -8473,7 +8450,7 @@
         <v>4057</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>17</v>
@@ -8491,7 +8468,7 @@
     </row>
     <row r="150" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>361</v>
+        <v>244</v>
       </c>
       <c r="B150" s="2">
         <v>46207</v>
@@ -8516,7 +8493,7 @@
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="9" t="s">
-        <v>362</v>
+        <v>245</v>
       </c>
       <c r="K150" s="3" t="s">
         <v>21</v>
@@ -8533,7 +8510,7 @@
     </row>
     <row r="151" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>363</v>
+        <v>246</v>
       </c>
       <c r="B151" s="2">
         <v>46207</v>
@@ -8545,13 +8522,13 @@
         <v>14</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F151" s="4">
         <v>4404</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H151" s="12" t="s">
         <v>49</v>
@@ -8573,13 +8550,13 @@
     </row>
     <row r="152" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>364</v>
+        <v>247</v>
       </c>
       <c r="B152" s="2">
         <v>46207</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>14</v>
@@ -8591,7 +8568,7 @@
         <v>4049</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="H152" s="7" t="s">
         <v>37</v>
@@ -8609,7 +8586,7 @@
     </row>
     <row r="153" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>366</v>
+        <v>249</v>
       </c>
       <c r="B153" s="2">
         <v>46207</v>
@@ -8627,7 +8604,7 @@
         <v>3532</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>233</v>
+        <v>116</v>
       </c>
       <c r="H153" s="13" t="s">
         <v>52</v>
@@ -8649,13 +8626,13 @@
     </row>
     <row r="154" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>367</v>
+        <v>250</v>
       </c>
       <c r="B154" s="2">
         <v>46207</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>368</v>
+        <v>251</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>14</v>
@@ -8667,7 +8644,7 @@
         <v>4680</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="H154" s="7" t="s">
         <v>37</v>
@@ -8689,13 +8666,13 @@
     </row>
     <row r="155" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>369</v>
+        <v>252</v>
       </c>
       <c r="B155" s="2">
         <v>46207</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>279</v>
+        <v>162</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>14</v>
@@ -8713,10 +8690,10 @@
         <v>20</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>370</v>
+        <v>253</v>
       </c>
       <c r="J155" s="9" t="s">
-        <v>371</v>
+        <v>254</v>
       </c>
       <c r="K155" s="3" t="s">
         <v>31</v>
@@ -8733,7 +8710,7 @@
     </row>
     <row r="156" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>372</v>
+        <v>255</v>
       </c>
       <c r="B156" s="2">
         <v>46207</v>
@@ -8745,13 +8722,13 @@
         <v>14</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F156" s="4">
         <v>4419</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H156" s="13" t="s">
         <v>52</v>
@@ -8769,13 +8746,13 @@
     </row>
     <row r="157" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>373</v>
+        <v>256</v>
       </c>
       <c r="B157" s="2">
         <v>46207</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>374</v>
+        <v>257</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>14</v>
@@ -8787,13 +8764,13 @@
         <v>11106</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="H157" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I157" s="3" t="s">
-        <v>375</v>
+        <v>258</v>
       </c>
       <c r="J157" s="6"/>
       <c r="K157" s="6"/>
@@ -8807,37 +8784,37 @@
     </row>
     <row r="158" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>376</v>
+        <v>259</v>
       </c>
       <c r="B158" s="2">
         <v>46207</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>377</v>
+        <v>260</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="F158" s="4">
         <v>2466</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="H158" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I158" s="3" t="s">
-        <v>378</v>
+        <v>261</v>
       </c>
       <c r="J158" s="9" t="s">
-        <v>379</v>
+        <v>262</v>
       </c>
       <c r="K158" s="3" t="s">
-        <v>380</v>
+        <v>263</v>
       </c>
       <c r="L158" s="2">
         <v>46207</v>
@@ -8851,37 +8828,37 @@
     </row>
     <row r="159" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>376</v>
+        <v>259</v>
       </c>
       <c r="B159" s="2">
         <v>46207</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>377</v>
+        <v>260</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="F159" s="4">
         <v>2466</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="H159" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>378</v>
+        <v>261</v>
       </c>
       <c r="J159" s="9" t="s">
-        <v>379</v>
+        <v>262</v>
       </c>
       <c r="K159" s="3" t="s">
-        <v>380</v>
+        <v>263</v>
       </c>
       <c r="L159" s="2">
         <v>46207</v>
@@ -8895,13 +8872,13 @@
     </row>
     <row r="160" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>381</v>
+        <v>264</v>
       </c>
       <c r="B160" s="2">
         <v>46207</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>382</v>
+        <v>265</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>14</v>
@@ -8919,10 +8896,10 @@
         <v>30</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>383</v>
+        <v>266</v>
       </c>
       <c r="J160" s="9" t="s">
-        <v>384</v>
+        <v>267</v>
       </c>
       <c r="K160" s="3" t="s">
         <v>21</v>
@@ -8939,7 +8916,7 @@
     </row>
     <row r="161" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>385</v>
+        <v>268</v>
       </c>
       <c r="B161" s="2">
         <v>46207</v>
@@ -8951,13 +8928,13 @@
         <v>14</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F161" s="4">
         <v>5296</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="H161" s="13" t="s">
         <v>52</v>
@@ -8975,13 +8952,13 @@
     </row>
     <row r="162" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>386</v>
+        <v>269</v>
       </c>
       <c r="B162" s="2">
         <v>46207</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>387</v>
+        <v>270</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>14</v>
@@ -8993,14 +8970,14 @@
         <v>4804</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="H162" s="13" t="s">
         <v>52</v>
       </c>
       <c r="I162" s="6"/>
       <c r="J162" s="9" t="s">
-        <v>388</v>
+        <v>271</v>
       </c>
       <c r="K162" s="6"/>
       <c r="L162" s="6"/>
@@ -9013,32 +8990,32 @@
     </row>
     <row r="163" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>389</v>
+        <v>272</v>
       </c>
       <c r="B163" s="2">
         <v>46207</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>390</v>
+        <v>273</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="F163" s="4">
         <v>11296</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H163" s="7" t="s">
         <v>37</v>
       </c>
       <c r="I163" s="6"/>
       <c r="J163" s="9" t="s">
-        <v>391</v>
+        <v>274</v>
       </c>
       <c r="K163" s="3" t="s">
         <v>21</v>
@@ -9055,13 +9032,13 @@
     </row>
     <row r="164" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>392</v>
+        <v>275</v>
       </c>
       <c r="B164" s="2">
         <v>46207</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>393</v>
+        <v>276</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>14</v>
@@ -9073,14 +9050,14 @@
         <v>4358</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="H164" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I164" s="6"/>
       <c r="J164" s="9" t="s">
-        <v>394</v>
+        <v>277</v>
       </c>
       <c r="K164" s="3" t="s">
         <v>31</v>
@@ -9097,13 +9074,13 @@
     </row>
     <row r="165" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>395</v>
+        <v>278</v>
       </c>
       <c r="B165" s="2">
         <v>46207</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>396</v>
+        <v>279</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>14</v>
@@ -9122,7 +9099,7 @@
       </c>
       <c r="I165" s="6"/>
       <c r="J165" s="9" t="s">
-        <v>397</v>
+        <v>280</v>
       </c>
       <c r="K165" s="6"/>
       <c r="L165" s="6"/>
@@ -9135,13 +9112,13 @@
     </row>
     <row r="166" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>398</v>
+        <v>281</v>
       </c>
       <c r="B166" s="2">
         <v>46207</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>399</v>
+        <v>282</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>14</v>
@@ -9159,7 +9136,7 @@
         <v>20</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>400</v>
+        <v>283</v>
       </c>
       <c r="J166" s="6"/>
       <c r="K166" s="3" t="s">
@@ -9177,13 +9154,13 @@
     </row>
     <row r="167" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>401</v>
+        <v>284</v>
       </c>
       <c r="B167" s="2">
         <v>46207</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>402</v>
+        <v>285</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>14</v>
@@ -9201,7 +9178,7 @@
         <v>30</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>403</v>
+        <v>286</v>
       </c>
       <c r="J167" s="6"/>
       <c r="K167" s="3" t="s">
@@ -9219,7 +9196,7 @@
     </row>
     <row r="168" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>404</v>
+        <v>287</v>
       </c>
       <c r="B168" s="2">
         <v>46209</v>
@@ -9243,10 +9220,10 @@
         <v>30</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>405</v>
+        <v>288</v>
       </c>
       <c r="J168" s="9" t="s">
-        <v>406</v>
+        <v>289</v>
       </c>
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
@@ -9259,7 +9236,7 @@
     </row>
     <row r="169" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>407</v>
+        <v>290</v>
       </c>
       <c r="B169" s="2">
         <v>46209</v>
@@ -9277,16 +9254,16 @@
         <v>5595</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="H169" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I169" s="3" t="s">
-        <v>408</v>
+        <v>291</v>
       </c>
       <c r="J169" s="9" t="s">
-        <v>409</v>
+        <v>292</v>
       </c>
       <c r="K169" s="6"/>
       <c r="L169" s="6"/>
@@ -9299,13 +9276,13 @@
     </row>
     <row r="170" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>410</v>
+        <v>293</v>
       </c>
       <c r="B170" s="2">
         <v>46209</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>411</v>
+        <v>294</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>14</v>
@@ -9323,7 +9300,7 @@
         <v>17</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>412</v>
+        <v>295</v>
       </c>
       <c r="J170" s="6"/>
       <c r="K170" s="6"/>
@@ -9337,13 +9314,13 @@
     </row>
     <row r="171" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>413</v>
+        <v>296</v>
       </c>
       <c r="B171" s="2">
         <v>46209</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>414</v>
+        <v>297</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>14</v>
@@ -9361,7 +9338,7 @@
         <v>30</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>415</v>
+        <v>298</v>
       </c>
       <c r="J171" s="6"/>
       <c r="K171" s="3" t="s">
@@ -9379,13 +9356,13 @@
     </row>
     <row r="172" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>416</v>
+        <v>299</v>
       </c>
       <c r="B172" s="2">
         <v>46209</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>247</v>
+        <v>130</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>14</v>
@@ -9404,7 +9381,7 @@
       </c>
       <c r="I172" s="6"/>
       <c r="J172" s="9" t="s">
-        <v>417</v>
+        <v>300</v>
       </c>
       <c r="K172" s="3" t="s">
         <v>21</v>
@@ -9421,13 +9398,13 @@
     </row>
     <row r="173" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>418</v>
+        <v>301</v>
       </c>
       <c r="B173" s="2">
         <v>46209</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>247</v>
+        <v>130</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>14</v>
@@ -9445,7 +9422,7 @@
         <v>20</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>419</v>
+        <v>302</v>
       </c>
       <c r="J173" s="6"/>
       <c r="K173" s="3" t="s">
@@ -9463,13 +9440,13 @@
     </row>
     <row r="174" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>420</v>
+        <v>303</v>
       </c>
       <c r="B174" s="2">
         <v>46209</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>421</v>
+        <v>304</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>14</v>
@@ -9488,10 +9465,10 @@
       </c>
       <c r="I174" s="6"/>
       <c r="J174" s="9" t="s">
-        <v>422</v>
+        <v>305</v>
       </c>
       <c r="K174" s="3" t="s">
-        <v>238</v>
+        <v>121</v>
       </c>
       <c r="L174" s="2">
         <v>46209</v>
@@ -9505,13 +9482,13 @@
     </row>
     <row r="175" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>423</v>
+        <v>306</v>
       </c>
       <c r="B175" s="2">
         <v>46209</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>424</v>
+        <v>307</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>14</v>
@@ -9529,7 +9506,7 @@
         <v>20</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>425</v>
+        <v>308</v>
       </c>
       <c r="J175" s="6"/>
       <c r="K175" s="6"/>
@@ -9543,13 +9520,13 @@
     </row>
     <row r="176" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>426</v>
+        <v>309</v>
       </c>
       <c r="B176" s="2">
         <v>46209</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>14</v>
@@ -9568,10 +9545,10 @@
       </c>
       <c r="I176" s="6"/>
       <c r="J176" s="9" t="s">
-        <v>427</v>
+        <v>310</v>
       </c>
       <c r="K176" s="3" t="s">
-        <v>238</v>
+        <v>121</v>
       </c>
       <c r="L176" s="2">
         <v>46209</v>
@@ -9585,7 +9562,7 @@
     </row>
     <row r="177" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>428</v>
+        <v>311</v>
       </c>
       <c r="B177" s="2">
         <v>46209</v>
@@ -9597,7 +9574,7 @@
         <v>14</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F177" s="4">
         <v>7283</v>
@@ -9621,13 +9598,13 @@
     </row>
     <row r="178" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>429</v>
+        <v>312</v>
       </c>
       <c r="B178" s="2">
         <v>46209</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>430</v>
+        <v>313</v>
       </c>
       <c r="D178" s="3" t="s">
         <v>14</v>
@@ -9645,7 +9622,7 @@
         <v>37</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>431</v>
+        <v>314</v>
       </c>
       <c r="J178" s="6"/>
       <c r="K178" s="3" t="s">
@@ -9663,7 +9640,7 @@
     </row>
     <row r="179" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>432</v>
+        <v>315</v>
       </c>
       <c r="B179" s="2">
         <v>46209</v>
@@ -9675,7 +9652,7 @@
         <v>14</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F179" s="4">
         <v>6709</v>
@@ -9699,7 +9676,7 @@
     </row>
     <row r="180" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>433</v>
+        <v>316</v>
       </c>
       <c r="B180" s="2">
         <v>46209</v>
@@ -9724,7 +9701,7 @@
       </c>
       <c r="I180" s="6"/>
       <c r="J180" s="9" t="s">
-        <v>434</v>
+        <v>317</v>
       </c>
       <c r="K180" s="3" t="s">
         <v>31</v>
@@ -9741,13 +9718,13 @@
     </row>
     <row r="181" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>435</v>
+        <v>318</v>
       </c>
       <c r="B181" s="2">
         <v>46209</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>436</v>
+        <v>319</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>14</v>
@@ -9765,7 +9742,7 @@
         <v>20</v>
       </c>
       <c r="I181" s="3" t="s">
-        <v>437</v>
+        <v>320</v>
       </c>
       <c r="J181" s="6"/>
       <c r="K181" s="3" t="s">
@@ -9783,13 +9760,13 @@
     </row>
     <row r="182" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>438</v>
+        <v>321</v>
       </c>
       <c r="B182" s="2">
         <v>46209</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>439</v>
+        <v>322</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>14</v>
@@ -9819,13 +9796,13 @@
     </row>
     <row r="183" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>440</v>
+        <v>323</v>
       </c>
       <c r="B183" s="2">
         <v>46209</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>374</v>
+        <v>257</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>14</v>
@@ -9855,32 +9832,32 @@
     </row>
     <row r="184" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>441</v>
+        <v>324</v>
       </c>
       <c r="B184" s="2">
         <v>46209</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>442</v>
+        <v>325</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="F184" s="4">
         <v>3189</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="H184" s="13" t="s">
         <v>52</v>
       </c>
       <c r="I184" s="6"/>
       <c r="J184" s="9" t="s">
-        <v>443</v>
+        <v>326</v>
       </c>
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
@@ -9893,7 +9870,7 @@
     </row>
     <row r="185" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>444</v>
+        <v>327</v>
       </c>
       <c r="B185" s="2">
         <v>46209</v>
@@ -9905,7 +9882,7 @@
         <v>14</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F185" s="4">
         <v>6706</v>
@@ -9914,7 +9891,7 @@
         <v>47</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>445</v>
+        <v>328</v>
       </c>
       <c r="I185" s="6"/>
       <c r="J185" s="6"/>
@@ -9929,7 +9906,7 @@
     </row>
     <row r="186" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>446</v>
+        <v>329</v>
       </c>
       <c r="B186" s="2">
         <v>46209</v>
@@ -9941,7 +9918,7 @@
         <v>14</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F186" s="4">
         <v>6742</v>
@@ -9969,7 +9946,7 @@
     </row>
     <row r="187" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>447</v>
+        <v>330</v>
       </c>
       <c r="B187" s="2">
         <v>46209</v>
@@ -9981,7 +9958,7 @@
         <v>14</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F187" s="4">
         <v>6742</v>
@@ -10009,13 +9986,13 @@
     </row>
     <row r="188" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>448</v>
+        <v>331</v>
       </c>
       <c r="B188" s="2">
         <v>46209</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>449</v>
+        <v>332</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>14</v>
@@ -10033,7 +10010,7 @@
         <v>20</v>
       </c>
       <c r="I188" s="3" t="s">
-        <v>450</v>
+        <v>333</v>
       </c>
       <c r="J188" s="6"/>
       <c r="K188" s="3" t="s">
@@ -10051,7 +10028,7 @@
     </row>
     <row r="189" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>451</v>
+        <v>334</v>
       </c>
       <c r="B189" s="2">
         <v>46209</v>
@@ -10075,10 +10052,10 @@
         <v>20</v>
       </c>
       <c r="I189" s="3" t="s">
-        <v>452</v>
+        <v>335</v>
       </c>
       <c r="J189" s="9" t="s">
-        <v>453</v>
+        <v>336</v>
       </c>
       <c r="K189" s="3" t="s">
         <v>25</v>
@@ -10095,13 +10072,13 @@
     </row>
     <row r="190" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>454</v>
+        <v>337</v>
       </c>
       <c r="B190" s="2">
         <v>46209</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>455</v>
+        <v>338</v>
       </c>
       <c r="D190" s="3" t="s">
         <v>14</v>
@@ -10113,13 +10090,13 @@
         <v>2581</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="H190" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I190" s="3" t="s">
-        <v>456</v>
+        <v>339</v>
       </c>
       <c r="J190" s="6"/>
       <c r="K190" s="3" t="s">
@@ -10137,7 +10114,7 @@
     </row>
     <row r="191" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>457</v>
+        <v>340</v>
       </c>
       <c r="B191" s="2">
         <v>46209</v>
@@ -10149,7 +10126,7 @@
         <v>14</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="F191" s="4">
         <v>6709</v>
@@ -10177,7 +10154,7 @@
     </row>
     <row r="192" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>458</v>
+        <v>341</v>
       </c>
       <c r="B192" s="2">
         <v>46209</v>
@@ -10195,16 +10172,16 @@
         <v>5568</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="H192" s="5" t="s">
         <v>20</v>
       </c>
       <c r="I192" s="3" t="s">
-        <v>459</v>
+        <v>342</v>
       </c>
       <c r="J192" s="9" t="s">
-        <v>460</v>
+        <v>343</v>
       </c>
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
@@ -10217,13 +10194,13 @@
     </row>
     <row r="193" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>461</v>
+        <v>344</v>
       </c>
       <c r="B193" s="2">
         <v>46209</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>462</v>
+        <v>345</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>14</v>
@@ -10241,10 +10218,10 @@
         <v>17</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>463</v>
+        <v>346</v>
       </c>
       <c r="J193" s="9" t="s">
-        <v>464</v>
+        <v>347</v>
       </c>
       <c r="K193" s="6"/>
       <c r="L193" s="6"/>
@@ -10257,13 +10234,13 @@
     </row>
     <row r="194" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>465</v>
+        <v>348</v>
       </c>
       <c r="B194" s="2">
         <v>46209</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>466</v>
+        <v>349</v>
       </c>
       <c r="D194" s="3" t="s">
         <v>14</v>
@@ -10282,7 +10259,7 @@
       </c>
       <c r="I194" s="6"/>
       <c r="J194" s="9" t="s">
-        <v>467</v>
+        <v>350</v>
       </c>
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
@@ -10295,13 +10272,13 @@
     </row>
     <row r="195" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>468</v>
+        <v>351</v>
       </c>
       <c r="B195" s="2">
         <v>46209</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>469</v>
+        <v>352</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>14</v>
@@ -10320,7 +10297,7 @@
       </c>
       <c r="I195" s="6"/>
       <c r="J195" s="9" t="s">
-        <v>470</v>
+        <v>353</v>
       </c>
       <c r="K195" s="3" t="s">
         <v>21</v>
@@ -10337,7 +10314,7 @@
     </row>
     <row r="196" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>471</v>
+        <v>354</v>
       </c>
       <c r="B196" s="2">
         <v>46209</v>
@@ -10355,16 +10332,16 @@
         <v>5599</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="H196" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I196" s="3" t="s">
-        <v>472</v>
+        <v>355</v>
       </c>
       <c r="J196" s="9" t="s">
-        <v>473</v>
+        <v>356</v>
       </c>
       <c r="K196" s="6"/>
       <c r="L196" s="6"/>
@@ -10377,13 +10354,13 @@
     </row>
     <row r="197" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>474</v>
+        <v>357</v>
       </c>
       <c r="B197" s="2">
         <v>46209</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>14</v>
@@ -10401,10 +10378,10 @@
         <v>52</v>
       </c>
       <c r="I197" s="3" t="s">
-        <v>475</v>
+        <v>358</v>
       </c>
       <c r="J197" s="9" t="s">
-        <v>476</v>
+        <v>359</v>
       </c>
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
@@ -10417,7 +10394,7 @@
     </row>
     <row r="198" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>477</v>
+        <v>360</v>
       </c>
       <c r="B198" s="2">
         <v>46209</v>
@@ -10441,10 +10418,10 @@
         <v>52</v>
       </c>
       <c r="I198" s="3" t="s">
-        <v>478</v>
+        <v>361</v>
       </c>
       <c r="J198" s="9" t="s">
-        <v>479</v>
+        <v>362</v>
       </c>
       <c r="K198" s="6"/>
       <c r="L198" s="6"/>
@@ -10457,13 +10434,13 @@
     </row>
     <row r="199" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>480</v>
+        <v>363</v>
       </c>
       <c r="B199" s="2">
         <v>46209</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>481</v>
+        <v>364</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>14</v>
@@ -10481,7 +10458,7 @@
         <v>20</v>
       </c>
       <c r="I199" s="3" t="s">
-        <v>425</v>
+        <v>308</v>
       </c>
       <c r="J199" s="6"/>
       <c r="K199" s="6"/>
@@ -10495,13 +10472,13 @@
     </row>
     <row r="200" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>482</v>
+        <v>365</v>
       </c>
       <c r="B200" s="2">
         <v>46209</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>481</v>
+        <v>364</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>14</v>
@@ -10531,19 +10508,19 @@
     </row>
     <row r="201" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>483</v>
+        <v>366</v>
       </c>
       <c r="B201" s="2">
         <v>46209</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>484</v>
+        <v>367</v>
       </c>
       <c r="D201" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="F201" s="4">
         <v>10938</v>
@@ -10556,7 +10533,7 @@
       </c>
       <c r="I201" s="6"/>
       <c r="J201" s="9" t="s">
-        <v>485</v>
+        <v>368</v>
       </c>
       <c r="K201" s="6"/>
       <c r="L201" s="6"/>
@@ -10569,19 +10546,19 @@
     </row>
     <row r="202" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>486</v>
+        <v>369</v>
       </c>
       <c r="B202" s="2">
         <v>46209</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>484</v>
+        <v>367</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="F202" s="4">
         <v>7011</v>
@@ -10594,7 +10571,7 @@
       </c>
       <c r="I202" s="6"/>
       <c r="J202" s="9" t="s">
-        <v>487</v>
+        <v>370</v>
       </c>
       <c r="K202" s="3" t="s">
         <v>21</v>
@@ -10611,13 +10588,13 @@
     </row>
     <row r="203" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>488</v>
+        <v>371</v>
       </c>
       <c r="B203" s="2">
         <v>46209</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>489</v>
+        <v>372</v>
       </c>
       <c r="D203" s="3" t="s">
         <v>14</v>
@@ -10635,7 +10612,7 @@
         <v>49</v>
       </c>
       <c r="I203" s="3" t="s">
-        <v>490</v>
+        <v>373</v>
       </c>
       <c r="J203" s="6"/>
       <c r="K203" s="3" t="s">
@@ -10653,34 +10630,34 @@
     </row>
     <row r="204" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>491</v>
+        <v>374</v>
       </c>
       <c r="B204" s="2">
         <v>46209</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>344</v>
+        <v>227</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="F204" s="4">
         <v>1335</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>226</v>
+        <v>109</v>
       </c>
       <c r="H204" s="8" t="s">
         <v>30</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>492</v>
+        <v>375</v>
       </c>
       <c r="J204" s="9" t="s">
-        <v>493</v>
+        <v>376</v>
       </c>
       <c r="K204" s="6"/>
       <c r="L204" s="6"/>
@@ -10693,34 +10670,34 @@
     </row>
     <row r="205" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>494</v>
+        <v>377</v>
       </c>
       <c r="B205" s="2">
         <v>46209</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>495</v>
+        <v>378</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="F205" s="4">
         <v>275</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="H205" s="10" t="s">
         <v>17</v>
       </c>
       <c r="I205" s="3" t="s">
-        <v>496</v>
+        <v>379</v>
       </c>
       <c r="J205" s="9" t="s">
-        <v>497</v>
+        <v>380</v>
       </c>
       <c r="K205" s="6"/>
       <c r="L205" s="6"/>
@@ -10733,13 +10710,13 @@
     </row>
     <row r="206" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>498</v>
+        <v>381</v>
       </c>
       <c r="B206" s="2">
         <v>46210</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>499</v>
+        <v>382</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>14</v>
@@ -10757,10 +10734,10 @@
         <v>20</v>
       </c>
       <c r="I206" s="3" t="s">
-        <v>500</v>
+        <v>383</v>
       </c>
       <c r="J206" s="9" t="s">
-        <v>501</v>
+        <v>384</v>
       </c>
       <c r="K206" s="6"/>
       <c r="L206" s="6"/>
@@ -10773,19 +10750,19 @@
     </row>
     <row r="207" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>502</v>
+        <v>385</v>
       </c>
       <c r="B207" s="2">
         <v>46210</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>503</v>
+        <v>386</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="F207" s="4">
         <v>2069</v>
@@ -10797,10 +10774,10 @@
         <v>30</v>
       </c>
       <c r="I207" s="3" t="s">
-        <v>504</v>
+        <v>387</v>
       </c>
       <c r="J207" s="9" t="s">
-        <v>505</v>
+        <v>388</v>
       </c>
       <c r="K207" s="6"/>
       <c r="L207" s="6"/>
@@ -10813,13 +10790,13 @@
     </row>
     <row r="208" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>506</v>
+        <v>389</v>
       </c>
       <c r="B208" s="2">
         <v>46210</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>507</v>
+        <v>390</v>
       </c>
       <c r="D208" s="3" t="s">
         <v>14</v>
@@ -10831,16 +10808,16 @@
         <v>4121</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="H208" s="10" t="s">
         <v>17</v>
       </c>
       <c r="I208" s="3" t="s">
-        <v>508</v>
+        <v>391</v>
       </c>
       <c r="J208" s="9" t="s">
-        <v>509</v>
+        <v>392</v>
       </c>
       <c r="K208" s="6"/>
       <c r="L208" s="6"/>
@@ -26853,91 +26830,116 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J37" r:id="rId1" xr:uid="{D752027B-C80B-4750-96D5-69F34D50849E}"/>
-    <hyperlink ref="J38" r:id="rId2" xr:uid="{358FD447-F001-4542-8241-BDFF57D7B07B}"/>
-    <hyperlink ref="J42" r:id="rId3" xr:uid="{1ED5C51D-5B86-4158-899A-91CF0E8D8383}"/>
-    <hyperlink ref="J44" r:id="rId4" xr:uid="{73065470-AC3E-474F-8314-200EB91CEBDA}"/>
-    <hyperlink ref="J45" r:id="rId5" xr:uid="{05D8262E-3AC4-400E-BA68-F87D0EDBAC00}"/>
-    <hyperlink ref="J46" r:id="rId6" xr:uid="{C640ED26-FA31-4F92-BBAD-6689D85DE5D5}"/>
-    <hyperlink ref="J47" r:id="rId7" xr:uid="{32AC0497-F751-4EF8-B827-32DDC79A7B31}"/>
-    <hyperlink ref="J49" r:id="rId8" xr:uid="{F980732B-8020-4598-88A2-738F244D16F1}"/>
-    <hyperlink ref="J51" r:id="rId9" xr:uid="{6FD4EF62-00D3-4D53-B29C-404A3B6A1C31}"/>
-    <hyperlink ref="J55" r:id="rId10" xr:uid="{11A7EFD0-C3B2-45B0-A39C-9DD4689951CA}"/>
-    <hyperlink ref="J57" r:id="rId11" xr:uid="{0C852B78-EB2B-4DEF-BD58-B49B9A942A2B}"/>
-    <hyperlink ref="J69" r:id="rId12" xr:uid="{848059F8-EC57-4D72-ACEF-664F8245C011}"/>
-    <hyperlink ref="J71" r:id="rId13" xr:uid="{B21DE554-CFE0-4E7C-9C87-5E17D6613793}"/>
-    <hyperlink ref="J73" r:id="rId14" xr:uid="{A7C7383A-3770-48C7-8A3B-A4D18C3E6630}"/>
-    <hyperlink ref="J76" r:id="rId15" xr:uid="{2AA2CF6B-7D55-49FE-A05E-4A694ABF8191}"/>
-    <hyperlink ref="J77" r:id="rId16" xr:uid="{D5D7C6A8-F4DF-4241-A058-90732C6CEBB4}"/>
-    <hyperlink ref="J78" r:id="rId17" xr:uid="{E57156FF-C895-4591-90A4-E8722429F5D8}"/>
-    <hyperlink ref="J80" r:id="rId18" xr:uid="{0405EBA7-7802-4487-8D6C-2CEAEFB5682B}"/>
-    <hyperlink ref="J83" r:id="rId19" xr:uid="{619C0695-8990-4C67-9B48-897A4C5F8056}"/>
-    <hyperlink ref="J84" r:id="rId20" xr:uid="{26DBC0F5-795F-4028-A6E8-FC093588340F}"/>
-    <hyperlink ref="J85" r:id="rId21" xr:uid="{7798A97F-7A4D-45CA-B593-13BF9D5C8A82}"/>
-    <hyperlink ref="J86" r:id="rId22" xr:uid="{12F7B17C-6010-4178-AD78-BAE31F66FEEC}"/>
-    <hyperlink ref="J87" r:id="rId23" xr:uid="{79AD77BD-F98A-4C63-9AC6-245E8264AE45}"/>
-    <hyperlink ref="J88" r:id="rId24" xr:uid="{AF72A5E5-553B-4C08-A368-81AC58877DAA}"/>
-    <hyperlink ref="J89" r:id="rId25" xr:uid="{E384FA46-1267-4D38-B292-D36B72E58A7C}"/>
-    <hyperlink ref="J91" r:id="rId26" xr:uid="{17802515-5786-40F2-A245-F9ECD92FC517}"/>
-    <hyperlink ref="J95" r:id="rId27" xr:uid="{102A5220-793E-4E96-A310-8F5DF99CEE7C}"/>
-    <hyperlink ref="J96" r:id="rId28" xr:uid="{97BD398B-B85B-463F-948B-5005DD5227C3}"/>
-    <hyperlink ref="J99" r:id="rId29" xr:uid="{54EDED40-DA79-444E-8CC9-B5AA9AB6E2B3}"/>
-    <hyperlink ref="J102" r:id="rId30" xr:uid="{B336CCF5-1E96-4853-A2BD-3D4860C2F288}"/>
-    <hyperlink ref="J103" r:id="rId31" xr:uid="{87EF8BA9-12E6-460A-8AC5-DCD2E253A2F2}"/>
-    <hyperlink ref="J106" r:id="rId32" xr:uid="{9105FDC7-F081-4D54-AF66-238A4910FC43}"/>
-    <hyperlink ref="J108" r:id="rId33" xr:uid="{3B8963F7-A259-4DD1-A7D6-5A17A3CBA6E6}"/>
-    <hyperlink ref="J111" r:id="rId34" xr:uid="{FF1C7C37-A2F3-4379-802E-92F8AA22261D}"/>
-    <hyperlink ref="J112" r:id="rId35" xr:uid="{FDD84049-4454-4D79-BE07-85727643A32F}"/>
-    <hyperlink ref="J114" r:id="rId36" xr:uid="{26C98585-4452-46CA-AF7E-51CCD33EB059}"/>
-    <hyperlink ref="J115" r:id="rId37" xr:uid="{0B267DFF-CF12-4FD6-9643-1AFB08B8413D}"/>
-    <hyperlink ref="J116" r:id="rId38" xr:uid="{03971458-09E8-4251-8CFF-A3F57AD7D908}"/>
-    <hyperlink ref="J117" r:id="rId39" xr:uid="{F414BCA8-23D7-45FD-A358-222E43B0535F}"/>
-    <hyperlink ref="J118" r:id="rId40" xr:uid="{E6677820-87AF-4836-ACEB-67B145E7A26F}"/>
-    <hyperlink ref="J119" r:id="rId41" xr:uid="{3758B9DA-5C7D-4936-94C9-7E4F18125A5F}"/>
-    <hyperlink ref="J120" r:id="rId42" xr:uid="{A0D819A3-B6AF-48C2-9954-EBE5D2A9C5E8}"/>
-    <hyperlink ref="J122" r:id="rId43" xr:uid="{C2559072-9FC9-4D47-9340-B64A48831C01}"/>
-    <hyperlink ref="J136" r:id="rId44" xr:uid="{BB10ACCD-7223-490D-ABCC-F8149AB09292}"/>
-    <hyperlink ref="J140" r:id="rId45" xr:uid="{7DC551A2-1589-4878-938F-D5DFB1932E98}"/>
-    <hyperlink ref="J143" r:id="rId46" xr:uid="{E76B1A58-43AE-48BE-87F6-A48DA22AB625}"/>
-    <hyperlink ref="J144" r:id="rId47" xr:uid="{08641C2D-0D3D-4C97-B42A-A58153DCCBFC}"/>
-    <hyperlink ref="J145" r:id="rId48" xr:uid="{26EFB9D4-F931-45E3-B7B1-7B3A6782088D}"/>
-    <hyperlink ref="J148" r:id="rId49" xr:uid="{9F1A70B7-EB31-4C7D-A4ED-4769C2AF4D7D}"/>
-    <hyperlink ref="J150" r:id="rId50" xr:uid="{8D4018E8-5819-4188-B521-B655C0F96485}"/>
-    <hyperlink ref="J155" r:id="rId51" xr:uid="{8DAC85C3-BA1C-4F04-BC56-23E0AED3E9A4}"/>
-    <hyperlink ref="J158" r:id="rId52" xr:uid="{16DEA54F-7213-481A-8B9F-E569000F6F2C}"/>
-    <hyperlink ref="J159" r:id="rId53" xr:uid="{56BD6924-8802-4222-BD05-AE1902F61469}"/>
-    <hyperlink ref="J160" r:id="rId54" xr:uid="{CF609295-917E-4DEF-B6EF-82E85F64B69A}"/>
-    <hyperlink ref="J162" r:id="rId55" xr:uid="{D651A4EA-538E-4076-BDD9-542D4C47845C}"/>
-    <hyperlink ref="J163" r:id="rId56" xr:uid="{8464A5C1-5C7D-4AC3-A778-D2B3786AF55F}"/>
-    <hyperlink ref="J164" r:id="rId57" xr:uid="{388B322E-FDC2-4A9C-A808-D9A0F164DFD7}"/>
-    <hyperlink ref="J165" r:id="rId58" xr:uid="{38CECFEC-6870-48EA-82CE-DBDD0D1784FE}"/>
-    <hyperlink ref="J168" r:id="rId59" xr:uid="{AB3EEDD9-18DC-4921-A186-43481FFE5465}"/>
-    <hyperlink ref="J169" r:id="rId60" xr:uid="{B1A34AD1-B984-4CE8-84E9-B2BE4126DC47}"/>
-    <hyperlink ref="J172" r:id="rId61" xr:uid="{982541D5-184F-4D09-9A15-52CF391B7B27}"/>
-    <hyperlink ref="J174" r:id="rId62" xr:uid="{88E47D8C-C152-4284-BC71-5AFBB3120AED}"/>
-    <hyperlink ref="J176" r:id="rId63" xr:uid="{ED3B88E8-55AC-45CA-8FF1-9309E45A0BE8}"/>
-    <hyperlink ref="J180" r:id="rId64" xr:uid="{E9B0F3DE-4337-404E-A3ED-BADFEEE6E681}"/>
-    <hyperlink ref="J184" r:id="rId65" xr:uid="{B4A5D6E0-85E2-47A4-B2DA-4D33C44A616B}"/>
-    <hyperlink ref="J189" r:id="rId66" xr:uid="{54816F3A-21FB-4B57-B692-A4D3AF5A4C03}"/>
-    <hyperlink ref="J192" r:id="rId67" xr:uid="{2AA4F8C4-9140-4410-BD37-2796594237EF}"/>
-    <hyperlink ref="J193" r:id="rId68" xr:uid="{3973CB73-A1A8-4836-9002-7D800E77C13C}"/>
-    <hyperlink ref="J194" r:id="rId69" xr:uid="{345AE80E-DB2D-41A4-9B4A-DE2F5E47D95E}"/>
-    <hyperlink ref="J195" r:id="rId70" xr:uid="{C4CBA5A5-96D8-4451-B86F-F30945D741C4}"/>
-    <hyperlink ref="J196" r:id="rId71" xr:uid="{72E6B6A0-7DC1-417A-AA86-97BFB5CFEC6A}"/>
-    <hyperlink ref="J197" r:id="rId72" xr:uid="{6B6E24BE-B045-45FF-8EAB-7A608C7CE96E}"/>
-    <hyperlink ref="J198" r:id="rId73" xr:uid="{178EA191-192E-43FF-9F40-A9E7831A3D81}"/>
-    <hyperlink ref="J201" r:id="rId74" xr:uid="{9EFE9EFE-5389-4837-A970-B9078DE63BE2}"/>
-    <hyperlink ref="J202" r:id="rId75" xr:uid="{D043B9CE-4534-416E-87E0-0F3A655CD8CC}"/>
-    <hyperlink ref="J204" r:id="rId76" xr:uid="{F4507B65-720A-43FD-8AA0-FA70AE6B98EB}"/>
-    <hyperlink ref="J205" r:id="rId77" xr:uid="{5667A71D-36BC-4749-838B-DBB2578F6549}"/>
-    <hyperlink ref="J206" r:id="rId78" xr:uid="{495B8238-CB12-4565-9BA3-0EDB84AE3467}"/>
-    <hyperlink ref="J207" r:id="rId79" xr:uid="{FFB4A62B-EB35-4B34-BE7C-B3A96EB398B8}"/>
-    <hyperlink ref="J208" r:id="rId80" xr:uid="{31D4442A-CBEC-4A7A-82D2-B90DDF1CE649}"/>
+    <hyperlink ref="J80" r:id="rId1" xr:uid="{0405EBA7-7802-4487-8D6C-2CEAEFB5682B}"/>
+    <hyperlink ref="J83" r:id="rId2" xr:uid="{619C0695-8990-4C67-9B48-897A4C5F8056}"/>
+    <hyperlink ref="J84" r:id="rId3" xr:uid="{26DBC0F5-795F-4028-A6E8-FC093588340F}"/>
+    <hyperlink ref="J85" r:id="rId4" xr:uid="{7798A97F-7A4D-45CA-B593-13BF9D5C8A82}"/>
+    <hyperlink ref="J86" r:id="rId5" xr:uid="{12F7B17C-6010-4178-AD78-BAE31F66FEEC}"/>
+    <hyperlink ref="J87" r:id="rId6" xr:uid="{79AD77BD-F98A-4C63-9AC6-245E8264AE45}"/>
+    <hyperlink ref="J88" r:id="rId7" xr:uid="{AF72A5E5-553B-4C08-A368-81AC58877DAA}"/>
+    <hyperlink ref="J89" r:id="rId8" xr:uid="{E384FA46-1267-4D38-B292-D36B72E58A7C}"/>
+    <hyperlink ref="J91" r:id="rId9" xr:uid="{17802515-5786-40F2-A245-F9ECD92FC517}"/>
+    <hyperlink ref="J95" r:id="rId10" xr:uid="{102A5220-793E-4E96-A310-8F5DF99CEE7C}"/>
+    <hyperlink ref="J96" r:id="rId11" xr:uid="{97BD398B-B85B-463F-948B-5005DD5227C3}"/>
+    <hyperlink ref="J99" r:id="rId12" xr:uid="{54EDED40-DA79-444E-8CC9-B5AA9AB6E2B3}"/>
+    <hyperlink ref="J102" r:id="rId13" xr:uid="{B336CCF5-1E96-4853-A2BD-3D4860C2F288}"/>
+    <hyperlink ref="J103" r:id="rId14" xr:uid="{87EF8BA9-12E6-460A-8AC5-DCD2E253A2F2}"/>
+    <hyperlink ref="J106" r:id="rId15" xr:uid="{9105FDC7-F081-4D54-AF66-238A4910FC43}"/>
+    <hyperlink ref="J108" r:id="rId16" xr:uid="{3B8963F7-A259-4DD1-A7D6-5A17A3CBA6E6}"/>
+    <hyperlink ref="J111" r:id="rId17" xr:uid="{FF1C7C37-A2F3-4379-802E-92F8AA22261D}"/>
+    <hyperlink ref="J112" r:id="rId18" xr:uid="{FDD84049-4454-4D79-BE07-85727643A32F}"/>
+    <hyperlink ref="J114" r:id="rId19" xr:uid="{26C98585-4452-46CA-AF7E-51CCD33EB059}"/>
+    <hyperlink ref="J115" r:id="rId20" xr:uid="{0B267DFF-CF12-4FD6-9643-1AFB08B8413D}"/>
+    <hyperlink ref="J116" r:id="rId21" xr:uid="{03971458-09E8-4251-8CFF-A3F57AD7D908}"/>
+    <hyperlink ref="J117" r:id="rId22" xr:uid="{F414BCA8-23D7-45FD-A358-222E43B0535F}"/>
+    <hyperlink ref="J118" r:id="rId23" xr:uid="{E6677820-87AF-4836-ACEB-67B145E7A26F}"/>
+    <hyperlink ref="J119" r:id="rId24" xr:uid="{3758B9DA-5C7D-4936-94C9-7E4F18125A5F}"/>
+    <hyperlink ref="J120" r:id="rId25" xr:uid="{A0D819A3-B6AF-48C2-9954-EBE5D2A9C5E8}"/>
+    <hyperlink ref="J122" r:id="rId26" xr:uid="{C2559072-9FC9-4D47-9340-B64A48831C01}"/>
+    <hyperlink ref="J136" r:id="rId27" xr:uid="{BB10ACCD-7223-490D-ABCC-F8149AB09292}"/>
+    <hyperlink ref="J140" r:id="rId28" xr:uid="{7DC551A2-1589-4878-938F-D5DFB1932E98}"/>
+    <hyperlink ref="J143" r:id="rId29" xr:uid="{E76B1A58-43AE-48BE-87F6-A48DA22AB625}"/>
+    <hyperlink ref="J144" r:id="rId30" xr:uid="{08641C2D-0D3D-4C97-B42A-A58153DCCBFC}"/>
+    <hyperlink ref="J145" r:id="rId31" xr:uid="{26EFB9D4-F931-45E3-B7B1-7B3A6782088D}"/>
+    <hyperlink ref="J148" r:id="rId32" xr:uid="{9F1A70B7-EB31-4C7D-A4ED-4769C2AF4D7D}"/>
+    <hyperlink ref="J150" r:id="rId33" xr:uid="{8D4018E8-5819-4188-B521-B655C0F96485}"/>
+    <hyperlink ref="J155" r:id="rId34" xr:uid="{8DAC85C3-BA1C-4F04-BC56-23E0AED3E9A4}"/>
+    <hyperlink ref="J158" r:id="rId35" xr:uid="{16DEA54F-7213-481A-8B9F-E569000F6F2C}"/>
+    <hyperlink ref="J159" r:id="rId36" xr:uid="{56BD6924-8802-4222-BD05-AE1902F61469}"/>
+    <hyperlink ref="J160" r:id="rId37" xr:uid="{CF609295-917E-4DEF-B6EF-82E85F64B69A}"/>
+    <hyperlink ref="J162" r:id="rId38" xr:uid="{D651A4EA-538E-4076-BDD9-542D4C47845C}"/>
+    <hyperlink ref="J163" r:id="rId39" xr:uid="{8464A5C1-5C7D-4AC3-A778-D2B3786AF55F}"/>
+    <hyperlink ref="J164" r:id="rId40" xr:uid="{388B322E-FDC2-4A9C-A808-D9A0F164DFD7}"/>
+    <hyperlink ref="J165" r:id="rId41" xr:uid="{38CECFEC-6870-48EA-82CE-DBDD0D1784FE}"/>
+    <hyperlink ref="J168" r:id="rId42" xr:uid="{AB3EEDD9-18DC-4921-A186-43481FFE5465}"/>
+    <hyperlink ref="J169" r:id="rId43" xr:uid="{B1A34AD1-B984-4CE8-84E9-B2BE4126DC47}"/>
+    <hyperlink ref="J172" r:id="rId44" xr:uid="{982541D5-184F-4D09-9A15-52CF391B7B27}"/>
+    <hyperlink ref="J174" r:id="rId45" xr:uid="{88E47D8C-C152-4284-BC71-5AFBB3120AED}"/>
+    <hyperlink ref="J176" r:id="rId46" xr:uid="{ED3B88E8-55AC-45CA-8FF1-9309E45A0BE8}"/>
+    <hyperlink ref="J180" r:id="rId47" xr:uid="{E9B0F3DE-4337-404E-A3ED-BADFEEE6E681}"/>
+    <hyperlink ref="J184" r:id="rId48" xr:uid="{B4A5D6E0-85E2-47A4-B2DA-4D33C44A616B}"/>
+    <hyperlink ref="J189" r:id="rId49" xr:uid="{54816F3A-21FB-4B57-B692-A4D3AF5A4C03}"/>
+    <hyperlink ref="J192" r:id="rId50" xr:uid="{2AA4F8C4-9140-4410-BD37-2796594237EF}"/>
+    <hyperlink ref="J193" r:id="rId51" xr:uid="{3973CB73-A1A8-4836-9002-7D800E77C13C}"/>
+    <hyperlink ref="J194" r:id="rId52" xr:uid="{345AE80E-DB2D-41A4-9B4A-DE2F5E47D95E}"/>
+    <hyperlink ref="J195" r:id="rId53" xr:uid="{C4CBA5A5-96D8-4451-B86F-F30945D741C4}"/>
+    <hyperlink ref="J196" r:id="rId54" xr:uid="{72E6B6A0-7DC1-417A-AA86-97BFB5CFEC6A}"/>
+    <hyperlink ref="J197" r:id="rId55" xr:uid="{6B6E24BE-B045-45FF-8EAB-7A608C7CE96E}"/>
+    <hyperlink ref="J198" r:id="rId56" xr:uid="{178EA191-192E-43FF-9F40-A9E7831A3D81}"/>
+    <hyperlink ref="J201" r:id="rId57" xr:uid="{9EFE9EFE-5389-4837-A970-B9078DE63BE2}"/>
+    <hyperlink ref="J202" r:id="rId58" xr:uid="{D043B9CE-4534-416E-87E0-0F3A655CD8CC}"/>
+    <hyperlink ref="J204" r:id="rId59" xr:uid="{F4507B65-720A-43FD-8AA0-FA70AE6B98EB}"/>
+    <hyperlink ref="J205" r:id="rId60" xr:uid="{5667A71D-36BC-4749-838B-DBB2578F6549}"/>
+    <hyperlink ref="J206" r:id="rId61" xr:uid="{495B8238-CB12-4565-9BA3-0EDB84AE3467}"/>
+    <hyperlink ref="J207" r:id="rId62" xr:uid="{FFB4A62B-EB35-4B34-BE7C-B3A96EB398B8}"/>
+    <hyperlink ref="J208" r:id="rId63" xr:uid="{31D4442A-CBEC-4A7A-82D2-B90DDF1CE649}"/>
+    <hyperlink ref="J2" r:id="rId64" xr:uid="{EEDF6F50-87A6-45E0-ACF5-D67B1BD4F3B6}"/>
+    <hyperlink ref="J3" r:id="rId65" xr:uid="{A5BC66FF-AAE5-47D5-B5E9-3CFB42DA7AFF}"/>
+    <hyperlink ref="J4" r:id="rId66" xr:uid="{3F417B4C-90DF-458E-A441-83D020DC2ED8}"/>
+    <hyperlink ref="J5" r:id="rId67" xr:uid="{0AB199D9-19AD-4CA5-89B7-E7E562A33CE2}"/>
+    <hyperlink ref="J6" r:id="rId68" xr:uid="{A3D6D2D7-8128-472B-8073-7A2B26EB5045}"/>
+    <hyperlink ref="J7" r:id="rId69" xr:uid="{0B1F70CB-A2AE-4290-ADBD-74C6ADF34343}"/>
+    <hyperlink ref="J8" r:id="rId70" xr:uid="{AE824144-1154-481E-9B88-7FA17C44DB54}"/>
+    <hyperlink ref="J29" r:id="rId71" xr:uid="{E910EC45-51E0-4C35-AE5E-8BE69345848D}"/>
+    <hyperlink ref="J30" r:id="rId72" xr:uid="{A48609FE-6C32-4F05-B1F2-11E2B19B004D}"/>
+    <hyperlink ref="J31" r:id="rId73" xr:uid="{E761D8C0-8E22-4C44-B3D6-4D3B19C1577D}"/>
+    <hyperlink ref="J33" r:id="rId74" xr:uid="{DA3CE9B0-528C-4E5F-9FE9-EC2E3391EACD}"/>
+    <hyperlink ref="J34" r:id="rId75" xr:uid="{B94CA2F7-5B57-49E2-AA15-E589F6776B06}"/>
+    <hyperlink ref="J35" r:id="rId76" xr:uid="{2CC782CB-FC09-44C4-8622-5262CD9F7334}"/>
+    <hyperlink ref="J36" r:id="rId77" xr:uid="{E2F056E3-805B-4F25-90D1-5BAA532A083B}"/>
+    <hyperlink ref="J37" r:id="rId78" xr:uid="{2BD90393-53AF-4F55-917A-A5B80E9AB52D}"/>
+    <hyperlink ref="J38" r:id="rId79" xr:uid="{A0A54D0D-365B-4917-BABC-7B43930BB08C}"/>
+    <hyperlink ref="J39" r:id="rId80" xr:uid="{9029938E-A50F-41AE-AC58-8D933BAA1913}"/>
+    <hyperlink ref="J40" r:id="rId81" xr:uid="{D59625AF-B17C-4F7D-8ACD-E177A0CCACB0}"/>
+    <hyperlink ref="J41" r:id="rId82" xr:uid="{D6327052-33BD-4E31-8C06-2A4E8C1711D4}"/>
+    <hyperlink ref="J42" r:id="rId83" xr:uid="{12A81F9F-C781-4FC6-AEBF-4E095E2683C3}"/>
+    <hyperlink ref="J43" r:id="rId84" xr:uid="{ED43B25F-044B-4D90-A85B-44D2C7FD7521}"/>
+    <hyperlink ref="J44" r:id="rId85" xr:uid="{091DE4B5-14C4-4E2A-AFCB-C248DB9D5EC3}"/>
+    <hyperlink ref="J46" r:id="rId86" xr:uid="{C329BF8B-1F71-4FEF-AA37-59A4D7D2F738}"/>
+    <hyperlink ref="J47" r:id="rId87" xr:uid="{B8C47210-2EA4-450A-8008-CDFB0FD0287A}"/>
+    <hyperlink ref="J48" r:id="rId88" xr:uid="{572203B4-F636-4DCE-B884-139A588B2E5A}"/>
+    <hyperlink ref="J51" r:id="rId89" xr:uid="{9212BB47-E23E-4710-B6D9-D3CA9BC4C4F3}"/>
+    <hyperlink ref="J52" r:id="rId90" xr:uid="{8689F5B2-4242-4C28-BE3F-C633784BAD84}"/>
+    <hyperlink ref="J53" r:id="rId91" xr:uid="{BCBADA5D-CABB-4B77-AB37-7F0EA7E818D8}"/>
+    <hyperlink ref="J54" r:id="rId92" xr:uid="{5719D695-0334-41D0-9553-8816B8BE68F3}"/>
+    <hyperlink ref="J56" r:id="rId93" xr:uid="{94F2567D-706B-483D-8F47-5B9E5A69CE21}"/>
+    <hyperlink ref="J57" r:id="rId94" xr:uid="{F52D6092-899A-467C-AA20-2DD526F8235F}"/>
+    <hyperlink ref="J58" r:id="rId95" xr:uid="{F44013DB-1F97-4B1D-8E59-681BC6FA1412}"/>
+    <hyperlink ref="J60" r:id="rId96" xr:uid="{EADA2D5D-C508-468C-88D4-4C7EA01F67BB}"/>
+    <hyperlink ref="J62" r:id="rId97" xr:uid="{D21543DB-1DC5-4566-BC56-785F46071AF6}"/>
+    <hyperlink ref="J63" r:id="rId98" xr:uid="{234D0888-D7AE-44BE-8598-CA3D3A0095E5}"/>
+    <hyperlink ref="J64" r:id="rId99" xr:uid="{47FAE7F7-DF9D-457E-B83C-5D17D09F571B}"/>
+    <hyperlink ref="J67" r:id="rId100" xr:uid="{081EBF3D-1E2D-4127-9F50-351012CED323}"/>
+    <hyperlink ref="J68" r:id="rId101" xr:uid="{4699D05A-636B-45FA-A350-36BFDAD22163}"/>
+    <hyperlink ref="J74" r:id="rId102" xr:uid="{C80937C6-28D3-4DFA-ABBE-D6438B4B2BF1}"/>
+    <hyperlink ref="J75" r:id="rId103" xr:uid="{5CE51594-75DF-4993-9621-A99BFF54D979}"/>
+    <hyperlink ref="J77" r:id="rId104" xr:uid="{5C0325EA-CF36-42F2-A790-8927AD7603E1}"/>
+    <hyperlink ref="J78" r:id="rId105" xr:uid="{BD874182-B46A-4145-B153-9CE2B828097C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId81"/>
+  <pageSetup orientation="portrait" r:id="rId106"/>
   <tableParts count="1">
-    <tablePart r:id="rId82"/>
+    <tablePart r:id="rId107"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Registro_de_Rechazos.xlsx
+++ b/data/Registro_de_Rechazos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5352DD11-568D-40D7-B377-39EAC6203BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79721E38-0718-4B4E-9C73-D12FE8E31ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5440" uniqueCount="1697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6285" uniqueCount="1936">
   <si>
     <t>Fecha</t>
   </si>
@@ -5139,6 +5139,726 @@
   </si>
   <si>
     <t>Tres sal estuches rotas</t>
+  </si>
+  <si>
+    <t>MRNRB3MSABHE</t>
+  </si>
+  <si>
+    <t>MRNRCKPZ8X9U</t>
+  </si>
+  <si>
+    <t>02:03 p. m.</t>
+  </si>
+  <si>
+    <t>MRNRH7M7MQFE</t>
+  </si>
+  <si>
+    <t>02:07 p. m.</t>
+  </si>
+  <si>
+    <t>MRNRQBC0J4X9</t>
+  </si>
+  <si>
+    <t>02:14 p. m.</t>
+  </si>
+  <si>
+    <t>Rechaza yerba</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784222053/to5vrvwg4gmlvfawhiqw.jpg</t>
+  </si>
+  <si>
+    <t>MRNRSZPNXW62</t>
+  </si>
+  <si>
+    <t>MRNSBCRERGI0</t>
+  </si>
+  <si>
+    <t>Rechaza alfajores</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784223039/rddfh3lkknsalthqeqf8.jpg</t>
+  </si>
+  <si>
+    <t>MRNSD2IEQHVD</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Si hizo pedido José estás ahí ?</t>
+  </si>
+  <si>
+    <t>MRNSSYGH24OK</t>
+  </si>
+  <si>
+    <t>02:44 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784223857/uskpezy6cdooo576yty8.jpg</t>
+  </si>
+  <si>
+    <t>MRNT3BICY4BX</t>
+  </si>
+  <si>
+    <t>02:52 p. m.</t>
+  </si>
+  <si>
+    <t>Faltaron los twistos de 95 grs</t>
+  </si>
+  <si>
+    <t>MRNT4RWX8WH1</t>
+  </si>
+  <si>
+    <t>02:53 p. m.</t>
+  </si>
+  <si>
+    <t>Faltaron los pep ramitas x 120 grs</t>
+  </si>
+  <si>
+    <t>MRNTFR4HVV7N</t>
+  </si>
+  <si>
+    <t>03:02 p. m.</t>
+  </si>
+  <si>
+    <t>Alf toddy mousse</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784224927/ysrhltga7d4nkwoclkdy.jpg</t>
+  </si>
+  <si>
+    <t>MRNTH3SJ58HL</t>
+  </si>
+  <si>
+    <t>Se desc 7 unid de megarrollo</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784224991/u39zzhywtsrnfggkem0x.jpg</t>
+  </si>
+  <si>
+    <t>MRNTILHJ9JC4</t>
+  </si>
+  <si>
+    <t>03:04 p. m.</t>
+  </si>
+  <si>
+    <t>1 nobleza rota</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784225054/kiievmck3tk6vd7waeb8.jpg</t>
+  </si>
+  <si>
+    <t>MRNU777G7Q81</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784226198/hvswozezgdiylhz8nuec.jpg</t>
+  </si>
+  <si>
+    <t>MRNUYKXLECUP</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784227475/ukip2zo2ubvsnjsgjijo.jpg</t>
+  </si>
+  <si>
+    <t>MRNVFWDLEJ4H</t>
+  </si>
+  <si>
+    <t>03:58 p. m.</t>
+  </si>
+  <si>
+    <t>MRNW0B90TQ11</t>
+  </si>
+  <si>
+    <t>04:14 p. m.</t>
+  </si>
+  <si>
+    <t>1 sal gruesa rota</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784229238/xjgi3ntv02qahydlg5mv.jpg</t>
+  </si>
+  <si>
+    <t>MRNW7ZBVZLEV</t>
+  </si>
+  <si>
+    <t>04:19 p. m.</t>
+  </si>
+  <si>
+    <t>MRNWLEAA1USM</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784230239/xptc379kcsadj96usgfe.jpg</t>
+  </si>
+  <si>
+    <t>MRNWMKHISDG0</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784230277/kbsbhfauj8kvifuiv3sg.jpg</t>
+  </si>
+  <si>
+    <t>MRNWO6D48C2Z</t>
+  </si>
+  <si>
+    <t>04:32 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784230354/mnzide478pnpqi2o6x88.jpg</t>
+  </si>
+  <si>
+    <t>MRNYWESSX171</t>
+  </si>
+  <si>
+    <t>Falto 1 caja de doritos de 77g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dejá el pedido, lo resuelvo después — Para la gente del deposito que ARME BIEN LOS PEDIDOS 
+</t>
+  </si>
+  <si>
+    <t>MRNYYUW2HSXD</t>
+  </si>
+  <si>
+    <t>Gallo arroz verdeo</t>
+  </si>
+  <si>
+    <t>MRNZ076YEL5D</t>
+  </si>
+  <si>
+    <t>Avena Quaker 4 unidades</t>
+  </si>
+  <si>
+    <t>MRNZ2175DUF4</t>
+  </si>
+  <si>
+    <t>Avena Quaker 5 unidades</t>
+  </si>
+  <si>
+    <t>MRO02VQD1PPA</t>
+  </si>
+  <si>
+    <t>06:08 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784236090/saw7hrirrsqj70tp8fpv.jpg</t>
+  </si>
+  <si>
+    <t>MROSWBWXEVYO</t>
+  </si>
+  <si>
+    <t>MROUEQZ2XRUQ</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784287019/sshbi9xljuupca13p3lh.jpg</t>
+  </si>
+  <si>
+    <t>MROUS8HVFCXW</t>
+  </si>
+  <si>
+    <t>08:27 a. m.</t>
+  </si>
+  <si>
+    <t>Faltó 4 Twistos x95 jamón</t>
+  </si>
+  <si>
+    <t>MROV8HO11YRI</t>
+  </si>
+  <si>
+    <t>No recibe porque hace meses que pide que le hagan boletas con los cambios</t>
+  </si>
+  <si>
+    <t>MROVQFNP620K</t>
+  </si>
+  <si>
+    <t>Don satur agridulce rotas dos unidades</t>
+  </si>
+  <si>
+    <t>MROVTUB5ZA16</t>
+  </si>
+  <si>
+    <t>08:57 a. m.</t>
+  </si>
+  <si>
+    <t>Rechaza pehuamar x 230 15 unidades</t>
+  </si>
+  <si>
+    <t>Retirá la mercadería — no se puede entregar — El pedido lo hicieron ellos por la app.</t>
+  </si>
+  <si>
+    <t>MROX0AQPF6WE</t>
+  </si>
+  <si>
+    <t>09:30 a. m.</t>
+  </si>
+  <si>
+    <t>Rechaza esta boleta</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784291379/btxgvlocbvama8reqozc.jpg</t>
+  </si>
+  <si>
+    <t>MROXD1BAXRTA</t>
+  </si>
+  <si>
+    <t>09:39 a. m.</t>
+  </si>
+  <si>
+    <t>Falta lays de 85 una unidad</t>
+  </si>
+  <si>
+    <t>Me comunico con el cliente ahora — Mal armado, se descuenta la Lays faltante</t>
+  </si>
+  <si>
+    <t>MROXVYZ851AV</t>
+  </si>
+  <si>
+    <t>Pedía tw de queso y vinieron de jamon</t>
+  </si>
+  <si>
+    <t>MROY7CZ3DQN7</t>
+  </si>
+  <si>
+    <t>10:03 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784293393/zxgzpvf1zbadxobcd4vd.jpg</t>
+  </si>
+  <si>
+    <t>MROYCB07QZFO</t>
+  </si>
+  <si>
+    <t>10:07 a. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784293625/ec8m15qyphtrufhlgp61.jpg</t>
+  </si>
+  <si>
+    <t>MROYPCYN8LWC</t>
+  </si>
+  <si>
+    <t>20 Twistos x 155 sin stock</t>
+  </si>
+  <si>
+    <t>MROYUGC62O99</t>
+  </si>
+  <si>
+    <t>MROZ0FPVREJR</t>
+  </si>
+  <si>
+    <t>10:26 a. m.</t>
+  </si>
+  <si>
+    <t>No pidio celusal</t>
+  </si>
+  <si>
+    <t>MROZ0T98920G</t>
+  </si>
+  <si>
+    <t>MROZL9ZGLF8R</t>
+  </si>
+  <si>
+    <t>10:43 a. m.</t>
+  </si>
+  <si>
+    <t>Pedía tostadas clásicas riera y facturaron leiva</t>
+  </si>
+  <si>
+    <t>MROZSOCOLZ3E</t>
+  </si>
+  <si>
+    <t>MRP0E9X63M7I</t>
+  </si>
+  <si>
+    <t>MRP0T3M4H97J</t>
+  </si>
+  <si>
+    <t>MRP1J2XEAKGB</t>
+  </si>
+  <si>
+    <t>11:36 a. m.</t>
+  </si>
+  <si>
+    <t>Clásica de 20 , tuistos de 40 ,jamón serrano</t>
+  </si>
+  <si>
+    <t>MRP2J9HNDZYD</t>
+  </si>
+  <si>
+    <t>MRP2LNROKCA2</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784300777/o4rxcuqpbamurjumpy2m.jpg</t>
+  </si>
+  <si>
+    <t>MRP2VCHMXAMV</t>
+  </si>
+  <si>
+    <t>12:15 p. m.</t>
+  </si>
+  <si>
+    <t>Tokke choco relleno</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784301234/wbspf1fhnzb55vp2uwjm.jpg</t>
+  </si>
+  <si>
+    <t>MRP2YLT3196Z</t>
+  </si>
+  <si>
+    <t>MRP3IFOLV48Y</t>
+  </si>
+  <si>
+    <t>MRP3PTVFZ3MU</t>
+  </si>
+  <si>
+    <t>12:37 p. m.</t>
+  </si>
+  <si>
+    <t>MRP461PBTFXJ</t>
+  </si>
+  <si>
+    <t>Rechaza 6 serena nobleza</t>
+  </si>
+  <si>
+    <t>MRP4BV1G8ZQV</t>
+  </si>
+  <si>
+    <t>Falta pep ramita y ruedita</t>
+  </si>
+  <si>
+    <t>MRP4FREVDG11</t>
+  </si>
+  <si>
+    <t>12:58 p. m.</t>
+  </si>
+  <si>
+    <t>No se deja pedido por ser como y estar mal armado faltan los 3d de 85</t>
+  </si>
+  <si>
+    <t>MRP59LJ3D8MH</t>
+  </si>
+  <si>
+    <t>No pidio</t>
+  </si>
+  <si>
+    <t>MRP5A1XO7UPT</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784305270/dtu9ubd9l4zve8mmhkxn.jpg</t>
+  </si>
+  <si>
+    <t>MRP5GD9I3FBU</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784305668/asy3izkjnpu2nks40kvs.jpg</t>
+  </si>
+  <si>
+    <t>MRP5K1EQDP2M</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784305749/sundmmo7qicslhzct37g.jpg</t>
+  </si>
+  <si>
+    <t>MRP5X23PJ6AJ</t>
+  </si>
+  <si>
+    <t>MRP689VCL9UR</t>
+  </si>
+  <si>
+    <t>01:48 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784306868/cnxdhry4zgepsm3tmgbc.jpg</t>
+  </si>
+  <si>
+    <t>MRP69HT034DF</t>
+  </si>
+  <si>
+    <t>MRP6A46J3JN0</t>
+  </si>
+  <si>
+    <t>01:49 p. m.</t>
+  </si>
+  <si>
+    <t>MRP6BDK2RSD2</t>
+  </si>
+  <si>
+    <t>01:50 p. m.</t>
+  </si>
+  <si>
+    <t>MRP6LCM4UAL1</t>
+  </si>
+  <si>
+    <t>01:58 p. m.</t>
+  </si>
+  <si>
+    <t>Rechaza clasicas</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784307486/l78pkeatigtd5de3laao.jpg</t>
+  </si>
+  <si>
+    <t>MRP6QWL6B4QW</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784307743/sgf2hvuputdvrr12lgbj.jpg</t>
+  </si>
+  <si>
+    <t>MRP6RCBP6GO7</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784307757/xnwuoo3onyxxqqdxphp6.jpg</t>
+  </si>
+  <si>
+    <t>MRP7M6ELLA1E</t>
+  </si>
+  <si>
+    <t>Rechaza</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784309199/saccoo2o4nzhltrusnij.jpg</t>
+  </si>
+  <si>
+    <t>MRP7NN91KZLO</t>
+  </si>
+  <si>
+    <t>02:28 p. m.</t>
+  </si>
+  <si>
+    <t>No le mandaron los cambios</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784309277/fayzyjxtqasi0bi9jb07.jpg</t>
+  </si>
+  <si>
+    <t>MRP7WA0JOBQE</t>
+  </si>
+  <si>
+    <t>02:34 p. m.</t>
+  </si>
+  <si>
+    <t>Pep común 3</t>
+  </si>
+  <si>
+    <t>MRP7YS9A39F3</t>
+  </si>
+  <si>
+    <t>Acanalada de 135 faltan</t>
+  </si>
+  <si>
+    <t>MRP82EFOS05J</t>
+  </si>
+  <si>
+    <t>02:39 p. m.</t>
+  </si>
+  <si>
+    <t>Mandaron lays en vez de Cheetos crema</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784309955/vhhs4oipatqfvsbhxxk5.jpg</t>
+  </si>
+  <si>
+    <t>MRP8APZIFL8D</t>
+  </si>
+  <si>
+    <t>MRP8K3COSV8M</t>
+  </si>
+  <si>
+    <t>MRP8SMF92S62</t>
+  </si>
+  <si>
+    <t>Faltan tostitos</t>
+  </si>
+  <si>
+    <t>MRPA4WYCXZA9</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784313481/wo6mkerc6kxjaogs8hr5.jpg</t>
+  </si>
+  <si>
+    <t>MRPCJLSTUNBX</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784317480/uerd07ffklttynb35hnn.jpg</t>
+  </si>
+  <si>
+    <t>MRPFAS36AYIH</t>
+  </si>
+  <si>
+    <t>06:01 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784322100/zjbh1drrzjj7x7ciumyb.jpg</t>
+  </si>
+  <si>
+    <t>MRPFAX27EQ09</t>
+  </si>
+  <si>
+    <t>06:02 p. m.</t>
+  </si>
+  <si>
+    <t>Lo marcado sin stock</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784322118/rreect6ruxvvqsf6ws62.jpg</t>
+  </si>
+  <si>
+    <t>MRPFBUUNSRF1</t>
+  </si>
+  <si>
+    <t>06:04 p. m.</t>
+  </si>
+  <si>
+    <t>3 sweet chill 74
+3 chetos ondulados de 80
+3 dinamita 45</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784322191/wtylx5xqyvg8q883eykq.jpg</t>
+  </si>
+  <si>
+    <t>MRPFF4K00E9Q</t>
+  </si>
+  <si>
+    <t>06:05 p. m.</t>
+  </si>
+  <si>
+    <t>2 ondas de 70</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784322318/ijeiicarej87sms5g9q8.jpg</t>
+  </si>
+  <si>
+    <t>MRPK6WOLYTRG</t>
+  </si>
+  <si>
+    <t>Smirnof red berrior 48 unidades</t>
+  </si>
+  <si>
+    <t>MRQBO0Q7OHD2</t>
+  </si>
+  <si>
+    <t>09:07 a. m.</t>
+  </si>
+  <si>
+    <t>6 toddy triple alf</t>
+  </si>
+  <si>
+    <t>MRQC0WFQ0XKD</t>
+  </si>
+  <si>
+    <t>Dinamita de 82</t>
+  </si>
+  <si>
+    <t>MRQCQ739UC0J</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784378255/a32aoy4wq7vgz66p5kzq.jpg</t>
+  </si>
+  <si>
+    <t>MRQCUZPEL20J</t>
+  </si>
+  <si>
+    <t>Faltó twistos x 95 grs</t>
+  </si>
+  <si>
+    <t>MRQCVOH18DGZ</t>
+  </si>
+  <si>
+    <t>MRQD5YH1LVX0</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784379016/fvv635hqnud7yedjlosm.jpg</t>
+  </si>
+  <si>
+    <t>MRQDGOHFKYXQ</t>
+  </si>
+  <si>
+    <t>MRQDWYMYMK6K</t>
+  </si>
+  <si>
+    <t>10:10 a. m.</t>
+  </si>
+  <si>
+    <t>Oeguamar de chimi falto dos</t>
+  </si>
+  <si>
+    <t>MRQDYYP3RJ39</t>
+  </si>
+  <si>
+    <t>MRQDZYIC7CJI</t>
+  </si>
+  <si>
+    <t>10:13 a. m.</t>
+  </si>
+  <si>
+    <t>MRQED6JFS6OG</t>
+  </si>
+  <si>
+    <t>MRQERI1G3063</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784381684/sazhrw4pprzl2zjxhazl.jpg</t>
+  </si>
+  <si>
+    <t>MRQFEMIPVXIK</t>
+  </si>
+  <si>
+    <t>No quiso una Duracell aa</t>
+  </si>
+  <si>
+    <t>MRQFIRUCPDZP</t>
+  </si>
+  <si>
+    <t>10:55 a. m.</t>
+  </si>
+  <si>
+    <t>Rechazo las pilas</t>
+  </si>
+  <si>
+    <t>MRQMY15IV4Y9</t>
+  </si>
+  <si>
+    <t>02:23 p. m.</t>
+  </si>
+  <si>
+    <t>MRQN03M9GKCS</t>
+  </si>
+  <si>
+    <t>02:25 p. m.</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784395527/bwhteredubeiwa2yleue.jpg</t>
+  </si>
+  <si>
+    <t>MRQN24HZBVN4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784395642/npp7groehxosfv9ajqpi.jpg</t>
+  </si>
+  <si>
+    <t>MRQN4PJSEQAL</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784395731/ix2fbuekidhttpfeprog.jpg</t>
+  </si>
+  <si>
+    <t>MRQN5Z8MMJKL</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784395784/hzawm3hsehds20c7zvf6.jpg</t>
+  </si>
+  <si>
+    <t>MRQN6Z7FTO4V</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dahri8jfr/image/upload/v1784395830/o7kzod9mba7twto1iz7v.jpg</t>
+  </si>
+  <si>
+    <t>MRQNUHGH5CYQ</t>
+  </si>
+  <si>
+    <t>02:49 p. m.</t>
+  </si>
+  <si>
+    <t>Falto 3 3d 43 grs</t>
   </si>
 </sst>
 </file>
@@ -31969,1668 +32689,4114 @@
       </c>
     </row>
     <row r="652" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A652" s="1"/>
-      <c r="B652" s="2"/>
-      <c r="C652" s="3"/>
-      <c r="D652" s="3"/>
-      <c r="E652" s="3"/>
-      <c r="F652" s="4"/>
-      <c r="G652" s="3"/>
-      <c r="H652" s="13"/>
+      <c r="A652" s="1" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B652" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C652" s="11">
+        <v>0.58472222222222225</v>
+      </c>
+      <c r="D652" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E652" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F652" s="4">
+        <v>5411</v>
+      </c>
+      <c r="G652" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H652" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="I652" s="6"/>
-      <c r="J652" s="9"/>
-      <c r="K652" s="3"/>
-      <c r="L652" s="2"/>
-      <c r="M652" s="3"/>
-      <c r="N652" s="15"/>
+      <c r="J652" s="6"/>
+      <c r="K652" s="6"/>
+      <c r="L652" s="6"/>
+      <c r="M652" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N652" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="653" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A653" s="1"/>
-      <c r="B653" s="2"/>
-      <c r="C653" s="11"/>
-      <c r="D653" s="3"/>
-      <c r="E653" s="3"/>
-      <c r="F653" s="4"/>
-      <c r="G653" s="3"/>
-      <c r="H653" s="12"/>
+      <c r="A653" s="1" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B653" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C653" s="3" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D653" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E653" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F653" s="4">
+        <v>3958</v>
+      </c>
+      <c r="G653" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H653" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="I653" s="6"/>
       <c r="J653" s="6"/>
-      <c r="K653" s="3"/>
-      <c r="L653" s="2"/>
-      <c r="M653" s="3"/>
-      <c r="N653" s="15"/>
+      <c r="K653" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L653" s="2">
+        <v>46219</v>
+      </c>
+      <c r="M653" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N653" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="654" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A654" s="1"/>
-      <c r="B654" s="2"/>
-      <c r="C654" s="3"/>
-      <c r="D654" s="3"/>
-      <c r="E654" s="3"/>
-      <c r="F654" s="4"/>
-      <c r="G654" s="3"/>
-      <c r="H654" s="5"/>
-      <c r="I654" s="3"/>
-      <c r="J654" s="9"/>
-      <c r="K654" s="6"/>
-      <c r="L654" s="6"/>
-      <c r="M654" s="3"/>
-      <c r="N654" s="15"/>
+      <c r="A654" s="1" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B654" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D654" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E654" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F654" s="4">
+        <v>6608</v>
+      </c>
+      <c r="G654" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H654" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I654" s="6"/>
+      <c r="J654" s="6"/>
+      <c r="K654" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L654" s="2">
+        <v>46219</v>
+      </c>
+      <c r="M654" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N654" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="655" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A655" s="1"/>
-      <c r="B655" s="2"/>
-      <c r="C655" s="3"/>
-      <c r="D655" s="3"/>
-      <c r="E655" s="3"/>
-      <c r="F655" s="4"/>
-      <c r="G655" s="3"/>
-      <c r="H655" s="8"/>
-      <c r="I655" s="3"/>
-      <c r="J655" s="6"/>
-      <c r="K655" s="3"/>
-      <c r="L655" s="2"/>
-      <c r="M655" s="3"/>
-      <c r="N655" s="15"/>
+      <c r="A655" s="1" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B655" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C655" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D655" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E655" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F655" s="4">
+        <v>7198</v>
+      </c>
+      <c r="G655" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H655" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I655" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="J655" s="9" t="s">
+        <v>1705</v>
+      </c>
+      <c r="K655" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L655" s="2">
+        <v>46219</v>
+      </c>
+      <c r="M655" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N655" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="656" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A656" s="1"/>
-      <c r="B656" s="2"/>
-      <c r="C656" s="3"/>
-      <c r="D656" s="3"/>
-      <c r="E656" s="3"/>
-      <c r="F656" s="4"/>
-      <c r="G656" s="3"/>
-      <c r="H656" s="5"/>
+      <c r="A656" s="1" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B656" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D656" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E656" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F656" s="4">
+        <v>11081</v>
+      </c>
+      <c r="G656" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H656" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="I656" s="6"/>
-      <c r="J656" s="9"/>
-      <c r="K656" s="6"/>
-      <c r="L656" s="6"/>
-      <c r="M656" s="3"/>
-      <c r="N656" s="15"/>
+      <c r="J656" s="6"/>
+      <c r="K656" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L656" s="2">
+        <v>46219</v>
+      </c>
+      <c r="M656" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N656" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="657" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A657" s="1"/>
-      <c r="B657" s="2"/>
-      <c r="C657" s="3"/>
-      <c r="D657" s="3"/>
-      <c r="E657" s="3"/>
-      <c r="F657" s="4"/>
-      <c r="G657" s="3"/>
-      <c r="H657" s="12"/>
-      <c r="I657" s="6"/>
-      <c r="J657" s="9"/>
-      <c r="K657" s="3"/>
-      <c r="L657" s="2"/>
-      <c r="M657" s="3"/>
-      <c r="N657" s="15"/>
+      <c r="A657" s="1" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B657" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C657" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="D657" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E657" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F657" s="4">
+        <v>6906</v>
+      </c>
+      <c r="G657" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H657" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I657" s="3" t="s">
+        <v>1708</v>
+      </c>
+      <c r="J657" s="9" t="s">
+        <v>1709</v>
+      </c>
+      <c r="K657" s="6"/>
+      <c r="L657" s="6"/>
+      <c r="M657" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N657" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="658" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A658" s="1"/>
-      <c r="B658" s="2"/>
-      <c r="C658" s="3"/>
-      <c r="D658" s="3"/>
-      <c r="E658" s="3"/>
-      <c r="F658" s="4"/>
-      <c r="G658" s="3"/>
-      <c r="H658" s="8"/>
-      <c r="I658" s="3"/>
+      <c r="A658" s="1" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B658" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="D658" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E658" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F658" s="4">
+        <v>6171</v>
+      </c>
+      <c r="G658" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H658" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I658" s="6"/>
       <c r="J658" s="6"/>
-      <c r="K658" s="3"/>
-      <c r="L658" s="2"/>
-      <c r="M658" s="3"/>
-      <c r="N658" s="15"/>
+      <c r="K658" s="3" t="s">
+        <v>1711</v>
+      </c>
+      <c r="L658" s="2">
+        <v>46219</v>
+      </c>
+      <c r="M658" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N658" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="659" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A659" s="1"/>
-      <c r="B659" s="2"/>
-      <c r="C659" s="11"/>
-      <c r="D659" s="3"/>
-      <c r="E659" s="3"/>
-      <c r="F659" s="4"/>
-      <c r="G659" s="3"/>
-      <c r="H659" s="3"/>
+      <c r="A659" s="1" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B659" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C659" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="D659" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E659" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F659" s="4">
+        <v>6166</v>
+      </c>
+      <c r="G659" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H659" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="I659" s="6"/>
-      <c r="J659" s="6"/>
-      <c r="K659" s="6"/>
-      <c r="L659" s="6"/>
-      <c r="M659" s="3"/>
-      <c r="N659" s="15"/>
+      <c r="J659" s="9" t="s">
+        <v>1714</v>
+      </c>
+      <c r="K659" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L659" s="2">
+        <v>46219</v>
+      </c>
+      <c r="M659" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N659" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="660" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A660" s="1"/>
-      <c r="B660" s="2"/>
-      <c r="C660" s="3"/>
-      <c r="D660" s="3"/>
-      <c r="E660" s="3"/>
-      <c r="F660" s="4"/>
-      <c r="G660" s="3"/>
-      <c r="H660" s="8"/>
-      <c r="I660" s="3"/>
+      <c r="A660" s="1" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B660" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="D660" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E660" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F660" s="4">
+        <v>10718</v>
+      </c>
+      <c r="G660" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H660" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I660" s="3" t="s">
+        <v>1717</v>
+      </c>
       <c r="J660" s="6"/>
       <c r="K660" s="6"/>
       <c r="L660" s="6"/>
-      <c r="M660" s="3"/>
-      <c r="N660" s="15"/>
+      <c r="M660" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N660" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="661" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A661" s="1"/>
-      <c r="B661" s="2"/>
-      <c r="C661" s="3"/>
-      <c r="D661" s="3"/>
-      <c r="E661" s="3"/>
-      <c r="F661" s="4"/>
-      <c r="G661" s="3"/>
-      <c r="H661" s="10"/>
-      <c r="I661" s="6"/>
+      <c r="A661" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B661" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C661" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D661" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E661" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F661" s="4">
+        <v>7453</v>
+      </c>
+      <c r="G661" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H661" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I661" s="3" t="s">
+        <v>1720</v>
+      </c>
       <c r="J661" s="6"/>
-      <c r="K661" s="3"/>
-      <c r="L661" s="2"/>
-      <c r="M661" s="3"/>
-      <c r="N661" s="15"/>
+      <c r="K661" s="6"/>
+      <c r="L661" s="6"/>
+      <c r="M661" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N661" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="662" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A662" s="1"/>
-      <c r="B662" s="2"/>
-      <c r="C662" s="3"/>
-      <c r="D662" s="3"/>
-      <c r="E662" s="3"/>
-      <c r="F662" s="4"/>
-      <c r="G662" s="3"/>
-      <c r="H662" s="7"/>
-      <c r="I662" s="6"/>
-      <c r="J662" s="6"/>
-      <c r="K662" s="3"/>
-      <c r="L662" s="2"/>
-      <c r="M662" s="3"/>
-      <c r="N662" s="15"/>
+      <c r="A662" s="1" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B662" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C662" s="3" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D662" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E662" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F662" s="4">
+        <v>6337</v>
+      </c>
+      <c r="G662" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H662" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I662" s="3" t="s">
+        <v>1723</v>
+      </c>
+      <c r="J662" s="9" t="s">
+        <v>1724</v>
+      </c>
+      <c r="K662" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L662" s="2">
+        <v>46219</v>
+      </c>
+      <c r="M662" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N662" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="663" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A663" s="1"/>
-      <c r="B663" s="2"/>
-      <c r="C663" s="3"/>
-      <c r="D663" s="3"/>
-      <c r="E663" s="3"/>
-      <c r="F663" s="4"/>
-      <c r="G663" s="3"/>
-      <c r="H663" s="8"/>
-      <c r="I663" s="3"/>
-      <c r="J663" s="9"/>
+      <c r="A663" s="1" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B663" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C663" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D663" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E663" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F663" s="4">
+        <v>6350</v>
+      </c>
+      <c r="G663" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H663" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I663" s="3" t="s">
+        <v>1726</v>
+      </c>
+      <c r="J663" s="9" t="s">
+        <v>1727</v>
+      </c>
       <c r="K663" s="6"/>
       <c r="L663" s="6"/>
-      <c r="M663" s="3"/>
-      <c r="N663" s="15"/>
+      <c r="M663" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N663" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="664" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A664" s="1"/>
-      <c r="B664" s="2"/>
-      <c r="C664" s="3"/>
-      <c r="D664" s="3"/>
-      <c r="E664" s="3"/>
-      <c r="F664" s="4"/>
-      <c r="G664" s="3"/>
-      <c r="H664" s="5"/>
-      <c r="I664" s="6"/>
-      <c r="J664" s="9"/>
-      <c r="K664" s="6"/>
-      <c r="L664" s="6"/>
-      <c r="M664" s="3"/>
-      <c r="N664" s="15"/>
+      <c r="A664" s="1" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B664" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>1729</v>
+      </c>
+      <c r="D664" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E664" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F664" s="4">
+        <v>6364</v>
+      </c>
+      <c r="G664" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H664" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I664" s="3" t="s">
+        <v>1730</v>
+      </c>
+      <c r="J664" s="9" t="s">
+        <v>1731</v>
+      </c>
+      <c r="K664" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L664" s="2">
+        <v>46219</v>
+      </c>
+      <c r="M664" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N664" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="665" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A665" s="1"/>
-      <c r="B665" s="2"/>
-      <c r="C665" s="3"/>
-      <c r="D665" s="3"/>
-      <c r="E665" s="3"/>
-      <c r="F665" s="4"/>
-      <c r="G665" s="3"/>
-      <c r="H665" s="8"/>
-      <c r="I665" s="3"/>
-      <c r="J665" s="9"/>
-      <c r="K665" s="3"/>
-      <c r="L665" s="2"/>
-      <c r="M665" s="3"/>
-      <c r="N665" s="15"/>
+      <c r="A665" s="1" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B665" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C665" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="D665" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E665" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F665" s="4">
+        <v>6891</v>
+      </c>
+      <c r="G665" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H665" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I665" s="6"/>
+      <c r="J665" s="9" t="s">
+        <v>1733</v>
+      </c>
+      <c r="K665" s="6"/>
+      <c r="L665" s="6"/>
+      <c r="M665" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N665" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="666" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A666" s="1"/>
-      <c r="B666" s="2"/>
-      <c r="C666" s="3"/>
-      <c r="D666" s="3"/>
-      <c r="E666" s="3"/>
-      <c r="F666" s="4"/>
-      <c r="G666" s="3"/>
-      <c r="H666" s="5"/>
+      <c r="A666" s="1" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B666" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="D666" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E666" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F666" s="4">
+        <v>9791</v>
+      </c>
+      <c r="G666" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H666" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="I666" s="6"/>
-      <c r="J666" s="9"/>
-      <c r="K666" s="3"/>
-      <c r="L666" s="2"/>
-      <c r="M666" s="3"/>
-      <c r="N666" s="15"/>
+      <c r="J666" s="9" t="s">
+        <v>1735</v>
+      </c>
+      <c r="K666" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L666" s="2">
+        <v>46219</v>
+      </c>
+      <c r="M666" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N666" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="667" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A667" s="1"/>
-      <c r="B667" s="2"/>
-      <c r="C667" s="3"/>
-      <c r="D667" s="3"/>
-      <c r="E667" s="3"/>
-      <c r="F667" s="4"/>
-      <c r="G667" s="3"/>
-      <c r="H667" s="5"/>
-      <c r="I667" s="3"/>
-      <c r="J667" s="9"/>
+      <c r="A667" s="1" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B667" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C667" s="3" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D667" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E667" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F667" s="4">
+        <v>7169</v>
+      </c>
+      <c r="G667" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H667" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="I667" s="6"/>
+      <c r="J667" s="6"/>
       <c r="K667" s="6"/>
       <c r="L667" s="6"/>
-      <c r="M667" s="3"/>
-      <c r="N667" s="15"/>
+      <c r="M667" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N667" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="668" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A668" s="1"/>
-      <c r="B668" s="2"/>
-      <c r="C668" s="3"/>
-      <c r="D668" s="3"/>
-      <c r="E668" s="3"/>
-      <c r="F668" s="4"/>
-      <c r="G668" s="3"/>
-      <c r="H668" s="5"/>
-      <c r="I668" s="3"/>
-      <c r="J668" s="9"/>
-      <c r="K668" s="3"/>
-      <c r="L668" s="2"/>
-      <c r="M668" s="3"/>
-      <c r="N668" s="15"/>
+      <c r="A668" s="1" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B668" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D668" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E668" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F668" s="4">
+        <v>6338</v>
+      </c>
+      <c r="G668" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H668" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I668" s="3" t="s">
+        <v>1740</v>
+      </c>
+      <c r="J668" s="9" t="s">
+        <v>1741</v>
+      </c>
+      <c r="K668" s="6"/>
+      <c r="L668" s="6"/>
+      <c r="M668" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N668" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="669" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A669" s="1"/>
-      <c r="B669" s="2"/>
-      <c r="C669" s="3"/>
-      <c r="D669" s="3"/>
-      <c r="E669" s="3"/>
-      <c r="F669" s="4"/>
-      <c r="G669" s="3"/>
-      <c r="H669" s="8"/>
-      <c r="I669" s="3"/>
-      <c r="J669" s="9"/>
-      <c r="K669" s="3"/>
-      <c r="L669" s="2"/>
-      <c r="M669" s="3"/>
-      <c r="N669" s="15"/>
+      <c r="A669" s="1" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B669" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D669" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E669" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F669" s="4">
+        <v>4752</v>
+      </c>
+      <c r="G669" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H669" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I669" s="6"/>
+      <c r="J669" s="6"/>
+      <c r="K669" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L669" s="2">
+        <v>46219</v>
+      </c>
+      <c r="M669" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N669" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="670" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A670" s="1"/>
-      <c r="B670" s="2"/>
-      <c r="C670" s="3"/>
-      <c r="D670" s="3"/>
-      <c r="E670" s="3"/>
-      <c r="F670" s="4"/>
-      <c r="G670" s="3"/>
-      <c r="H670" s="8"/>
-      <c r="I670" s="3"/>
-      <c r="J670" s="9"/>
+      <c r="A670" s="1" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B670" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D670" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E670" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F670" s="4">
+        <v>334</v>
+      </c>
+      <c r="G670" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H670" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I670" s="6"/>
+      <c r="J670" s="9" t="s">
+        <v>1745</v>
+      </c>
       <c r="K670" s="6"/>
       <c r="L670" s="6"/>
-      <c r="M670" s="3"/>
-      <c r="N670" s="15"/>
+      <c r="M670" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N670" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="671" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A671" s="1"/>
-      <c r="B671" s="2"/>
-      <c r="C671" s="3"/>
-      <c r="D671" s="3"/>
-      <c r="E671" s="3"/>
-      <c r="F671" s="4"/>
-      <c r="G671" s="3"/>
-      <c r="H671" s="7"/>
-      <c r="I671" s="3"/>
-      <c r="J671" s="9"/>
-      <c r="K671" s="3"/>
-      <c r="L671" s="2"/>
-      <c r="M671" s="3"/>
-      <c r="N671" s="15"/>
+      <c r="A671" s="1" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B671" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D671" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E671" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F671" s="4">
+        <v>319</v>
+      </c>
+      <c r="G671" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H671" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I671" s="6"/>
+      <c r="J671" s="9" t="s">
+        <v>1747</v>
+      </c>
+      <c r="K671" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L671" s="2">
+        <v>46219</v>
+      </c>
+      <c r="M671" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N671" s="15">
+        <v>7</v>
+      </c>
     </row>
     <row r="672" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A672" s="1"/>
-      <c r="B672" s="2"/>
-      <c r="C672" s="3"/>
-      <c r="D672" s="3"/>
-      <c r="E672" s="3"/>
-      <c r="F672" s="4"/>
-      <c r="G672" s="3"/>
-      <c r="H672" s="12"/>
+      <c r="A672" s="1" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B672" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D672" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E672" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F672" s="4">
+        <v>319</v>
+      </c>
+      <c r="G672" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H672" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="I672" s="6"/>
-      <c r="J672" s="9"/>
-      <c r="K672" s="6"/>
-      <c r="L672" s="6"/>
-      <c r="M672" s="3"/>
-      <c r="N672" s="15"/>
+      <c r="J672" s="9" t="s">
+        <v>1750</v>
+      </c>
+      <c r="K672" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L672" s="2">
+        <v>46219</v>
+      </c>
+      <c r="M672" s="3" t="s">
+        <v>22</v>
+      </c>
+      